--- a/papers_database.xlsx
+++ b/papers_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,12 +476,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>42640624</t>
+          <t>42647164</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gut microbial diversity at baseline conditions the clinical, microbiome, and metabolic response to paraprobiotic Lactiplantibacillus plantarum LRCC5282 in overweight adults.</t>
+          <t>Sex differences in the gut microbiome and related metabolites: role in cardiometabolic disease.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -496,12 +496,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>120 位過重成人</t>
+          <t>未提及（本文為綜論性回顧文章，非原創實驗研究）</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -509,34 +509,34 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>The gut microbiota is increasingly recognized as a target for obesity management; however, whether baseline gut microbial diversity conditions responsiveness to microbiota-targeted interventions remains unclear. We aimed to investigate whether baseline gut microbial diversity is associated with responsiveness to a paraprobiotic derived from Lactiplantibacillus plantarum LRCC5282 (LP5282-P) in overweight adults. In a 12-week, randomized, double-blind, placebo-controlled, multicenter trial of 120 overweight adults, LP5282-P produced no significant between-group differences in any clinical outcome across the overall per-protocol population. However, in the low-diversity subgroup, LP5282-P was associated with significant reductions in body weight, body mass index, and circulating leptin levels. These clinical changes were accompanied by compositional shifts in the gut microbiota, including higher relative abundances of Christensenellaceae, Faecalibacterium, and Alistipes. Fecal metabolite profiles showed elevated acetate and butyrate concentrations and altered bile acid composition. Within the low-diversity subgroup, changes in the relative abundances of Akkermansia and Eubacterium were inversely correlated with changes in body weight, body fat mass, and leptin levels. In contrast, the high-diversity subgroup exhibited no consistent response across the outcome domains examined. Overall, baseline gut microbial diversity was associated with differential responsiveness to LP5282-P, supporting its potential use as a stratification variable in future microbiota-targeted intervention trials. Further studies integrating direct measures of microbial activity and host response are warranted to elucidate the biological pathways underlying this diversity-dependent responsiveness. Trial registration: Clinical Research Information Service (CRIS), KCT0008119.</t>
+          <t>Sex differences in major cardiometabolic diseases (CMD), such as type 2 diabetes, metabolic dysfunction-associated steatotic liver disease, and cardiovascular disease, have been increasingly recognized across the life course. During the reproductive stage, women generally have a more favorable cardiometabolic risk profile than men, but their risk of experiencing CMD significantly increases after menopause. Emerging evidence suggests that sexually dimorphic gut microbiota and gut microbiota-related metabolites (GMRMs) may contribute to such sex disparities. However, existing findings are heterogeneous and underlying mechanisms remain incompletely understood. In this review, we synthesize the evidence examining sex differences in gut microbial diversity, overall composition, taxa abundances, and levels of GMRMs across key life stages, including pre-puberty, adolescence, and different phases of adulthood (with emphasis on pre- and post-menopausal periods). We summarize potential biological mechanisms underlying sexual dimorphism in the gut microbiome and GMRMs, emphasizing the central role of sex steroids, along with contributions from immune function and other host and environmental factors. We further integrate evidence linking sexually dimorphic microbial taxa (e.g., Akkermansia muciniphila, Eubacterium, Ruminococcus, and other Firmicutes taxa) and GMRMs (e.g., microbiota-derived short-chain fatty acids, secondary bile acids, and trimethylamine N-oxide) to key cardiometabolic pathways involving inflammation, glucose and lipid metabolism, and vascular function. Finally, we identify critical knowledge gaps and emphasize the need for future large longitudinal studies that would integrate repeated measurements of the gut microbiome, untargeted metabolomics, and sex steroid hormones across the life course. Such approaches are essential to clarify biological pathways and inform sex-specific microbiome-based interventions for CMD prevention and management.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>本研究旨在探討基準線（baseline）腸道菌相多樣性，是否會影響過重成人對植物乳桿菌副乾酪乳酸菌（LP5282-P）干預的臨床與代謝反應。在一項納入120位過重成人的臨床試驗中，整體受試者接受LP5282-P後無顯著差異；然而，在「低菌相多樣性」亞群中，LP5282-P顯著降低了體重、BMI及血清瘦素水平，並伴隨有益菌（如*Christensenellaceae*、*Faecalibacterium*）富集，以及糞便中短鏈脂肪酸（乙酸、丁酸）濃度升高。高多樣性組則無明顯反應。此研究證實基準線菌相多樣性是預測微生態干預療效的重要指標，對未來個人化精準體重管理具有重要科學意義。</t>
+          <t>本文旨在探討性別差異在腸道微生物群與相關代謝物（GMRMs）中如何影響心臟代謝疾病（CMD）。研究指出，受性類固醇、免疫功能及環境因素影響，腸道菌相與代謝產物存在顯著的性別二態性。女性在生育期較男性具備更佳的心臟代謝特徵，但停經後風險顯著升高，此變化與特定菌屬（如 *Akkermansia muciniphila*）及代謝物（如短鏈脂肪酸、次級膽汁酸、TMAO）的豐度改變密切相關。這些微生物與代謝物透過調節發炎反應、醣脂代謝及血管功能，進而影響 CMD 的發生。本文強調未來需透過大型縱向研究，結合微生物組學、代謝組學與荷爾蒙監測，以深入解析其生物學機制，並開發針對不同性別的精準微生物介入療法，對於預防及管理心臟代謝疾病具有重要的科學價值。</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42640624/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647164/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>42640100</t>
+          <t>42644416</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Revisiting gut microbiota-driven ammonia metabolism: from disease burden to physiological adaptation.</t>
+          <t>Nationwide cohort study reveals low bifidobacteria and distinct microbiota composition and function in Swedish newborns.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics, 16S</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -564,44 +564,44 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Ammonia homeostasis is governed by interconnected host and microbial pathways, including hepatic ureagenesis, glutamine synthesis, and gut microbiota-mediated urea hydrolysis, proteolysis, and amino acid deamination. Ammonia has historically been viewed primarily as a nitrogenous waste product and neurotoxic molecule, a concept strongly supported by studies of hyperammonemia and hepatic encephalopathy. Impaired hepatic clearance, portosystemic shunting, and enhanced gut-derived ammonia input increase systemic ammonia burden and are linked to neurological dysfunction, muscle wasting, immune dysregulation, and progression of liver disease. In the gut lumen and mucosal environment, however, gut microbes not only generate ammonia but can also reuse ammonia-derived nitrogen for amino acid synthesis, microbial biomass formation, and community nitrogen exchange. Evidence from selected physiological and preclinical models indicates that microbiota-derived ammonia may contribute to nitrogen recycling, microbial community maintenance, enteric neural regulation, or metabolic adaptation under defined conditions. These roles are more context-specific and less broadly established than the pathological effects of systemic hyperammonemia. When epithelial barrier integrity is compromised, hepatic clearance declines, or host buffering reserves are depleted, elevated ammonia can increase epithelial exposure, portal ammonia input, or peripheral blood ammonia. Conversely, evidence that reduced microbiota-derived ammonia contributes to disease remains limited and currently comes mainly from selected animal models. This review re-examines ammonia metabolism from a gut microbiota-centered perspective. We discuss the ecological origins, spatial distribution, exposure characteristics, host-interface effects, and context-specific outcomes of microbiota-derived ammonia in physiology and disease, and discuss how ammonia should be measured, stratified, and targeted in microbial nitrogen metabolism.</t>
+          <t>NCT06285630.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>本文為一篇綜述論文，重新審視了腸道菌群驅動的氨代謝，探討其在疾病負擔與生理適應中的雙重角色。傳統上，氨被視為具神經毒性的代謝廢物，與肝性腦病變、肌肉流失及免疫失調密切相關。然而，最新證據指出，在腸道局部環境中，菌群產生的氨可被重新利用於氨基酸合成與氮循環，維持菌落穩定並促進生理適應。氨的病理或生理效應取決於腸道屏障完整性、肝臟清除率及宿主緩衝能力。此研究的科學意義在於打破了氨僅為有害廢物的單一觀點，強調必須結合特定生理情境，精準測量並標靶調控腸道菌群的氮代謝，為相關疾病的臨床診療提供新思路。</t>
+          <t>本研究為一項瑞典全國性世代研究（臨床試驗登記號：NCT06285630），旨在探討瑞典新生兒的腸道菌相特徵。研究核心發現瑞典新生兒體內的雙歧桿菌（Bifidobacteria）豐度偏低，且其腸道菌群在物種組成與代謝功能上呈現出獨特的特徵。雙歧桿菌在嬰兒早期腸道發育與免疫調控中扮演關鍵角色，其水平偏低可能與現代生活方式、分娩方式或抗生素使用有關。本研究的科學意義在於揭示了特定地理區域新生兒腸道菌相的特殊結構與功能缺陷，為未來評估早期微生態失調及開發嬰兒精準益生菌干預手段提供了重要依據。</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42640100/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42644416/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>42641146</t>
+          <t>42647759</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Engineered bacterial therapeutics from synthetic biology to clinical translation: A multi-database scientometric analysis, 2000-2026.</t>
+          <t>The Gut Microbiome in Multiple Sclerosis.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Human vaccines &amp; immunotherapeutics</t>
+          <t>Neurology(R) neuroimmunology &amp; neuroinflammation</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1,730 篇英文文獻（包含研究文章與綜述）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -619,54 +619,54 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Engineered bacterial therapeutics integrate programmable strain engineering with biomedical functions such as sensing, delivery, immune modulation, microbiome intervention, and disease management. This study conducted a multi-database bibliometric analysis to map the knowledge structure, collaboration patterns, and translational direction of this field. Bibliographic records were retrieved from Web of Science Core Collection, Scopus, and PubMed for publications from 1 January 2000 to 1 June 2026. After document-type filtering, time restriction, deduplication, language screening, and manual eligibility assessment, 1,730 English-language articles and reviews were included. CiteSpace 6.4.R1, VOSviewer 1.6.20, and the bibliometrix R package were used to analyze publication trends, collaboration networks, journal co-citation, dual-map citation trajectories, citation bursts, keyword co-occurrence, and thematic evolution. Publication output increased steadily, with faster growth after 2020; 2025 was the highest-output complete year, while 2026 represented a partial retrieval year. China and the United States were the leading contributors, although institutional collaboration remained regionally clustered. Co-citation, citation-burst, and keyword analyses showed a shift from bacterial chassis construction and circuit design toward engineered probiotics, gut microbiota-related therapy, cancer immunotherapy, drug delivery, live biotherapeutic products, and clinical translation. Persistent translational priorities include controllability, safety, manufacturing consistency, and regulatory alignment.</t>
+          <t>Multiple sclerosis (MS) is a chronic inflammatory demyelinating disease of the CNS whose risk and course are shaped by both genetic and environmental factors, among which the intestinal microbiota has emerged as a key, potentially modifiable contributor. People with MS frequently display altered gut microbiota, characterized by depletion of fiber-fermenting, short-chain fatty acid (SCFA)-producing commensals, and expansion of taxa associated with mucus degradation and proinflammatory metabolism. These compositional shifts are paralleled by broad changes in blood and CSF metabolites, including reduced SCFAs, tryptophan-derived aryl hydrocarbon receptor ligands, and secondary bile acids. In addition, several reports highlight the accumulation of aromatic amino acid-derived phenolic and indolic compounds and specific lipid mediators linked to neuroinflammation and neurodegeneration. In this up-to-date review, we synthesize evidence from experimental models and human studies showing how microbial metabolites can influence MS pathogenesis through converging mechanisms: modulation of gut and blood-brain barrier integrity; shaping of T-cell and B-cell responses; direct effects on microglia, astrocytes, and oligodendrocyte lineage cells after crossing into the CNS; and modulation of neural circuits, particularly those involving the vagus nerve. Finally, we highlight current gaps, including the need for longitudinal, harmonized multiomic cohorts, and mechanistic studies integrating microbiome, metabolome, and host readouts across gut, blood, and CNS. Overall, available data support a model in which coordinated disruption of the gut microbiota-metabolite axis, rather than any single pathogen, contributes to MS, opening avenues for microbiota-based and metabolite-based biomarkers and therapies aimed at restoring immune and neuroglial homeostasis.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>本研究透過多資料庫的文獻計量學分析，全面梳理了2000至2026年間工程菌治療（Engineered bacterial therapeutics）領域的知識架構、合作網絡與臨床轉化趨勢。分析 1,730 篇相關文獻顯示，該領域的發文量自2020年起快速增長，並以中美兩國為主要研究貢獻國。研究熱點已從早期的細菌底盤建構與基因電路設計，轉向工程益生菌、腸道菌群治療、癌症免疫治療、藥物傳遞及活體生物藥物（LBPs）。本研究不僅揭示了工程菌療法的整體發展軌跡，也指出可控性、安全性、生產一致性與監管合規是未來臨床轉化必須克服的關鍵挑戰。</t>
+          <t>本研究探討多發性硬化症（MS）與腸道微生物群之間的關聯。研究指出，MS 患者的腸道菌相呈現失調狀態，包括短鏈脂肪酸（SCFA）產生菌減少，以及促發炎代謝菌的增加。這些微生物群落的變化伴隨著血液與腦脊髓液中代謝物（如色胺酸衍生物、膽汁酸及 SCFA）的顯著改變，這些物質經證實與神經發炎及退化密切相關。文中綜述了微生物代謝產物如何透過調節腸道與血腦屏障完整性、影響免疫細胞（T/B 細胞）反應，以及直接作用於神經膠質細胞來參與 MS 的致病機制。總結而言，MS 的發生與腸道菌群-代謝物軸的整體失調有關，而非單一病原體所致。該研究強調未來需進行多體學（multiomics）整合分析，以開發基於微生物群的生物標記與創新治療策略，旨在恢復患者的免疫與神經恆定。</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42641146/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647759/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>42635406</t>
+          <t>42641146</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Separating extracellular from intracellular fecal metabolites exposes cross-feeding architecture in the gut: exploring metabolite partitioning and ecological associations.</t>
+          <t>Engineered bacterial therapeutics from synthetic biology to clinical translation: A multi-database scientometric analysis, 2000-2026.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>Human vaccines &amp; immunotherapeutics</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>metagenomics, metabolomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>63 個糞便檢體（來自 63 位健康受試者）</t>
+          <t>1,730 篇學術文章與評論</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -674,54 +674,54 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>The gut microbiota forms a complex ecosystem through metabolic interdependence (cross-feeding). However, conventional fecal metabolomics typically quantifies only total metabolite pools, making it difficult to distinguish extracellular-enriched metabolite pools from predominantly cell-associated ones, and thus limiting reconstruction of in situ metabolic networks. Here, we quantified fecal metabolites in paired fractions from the same specimen: an undisrupted fraction representing the extracellular pool and a strongly bead-beaten fraction representing the total pool; the intracellular pool was defined as the difference between total and extracellular measurements. Stool samples from 63 healthy individuals were analyzed for short-chain fatty acids, polyamines, and water-soluble vitamins, and the results were integrated with shotgun metagenomic profiles of species composition and functional genes. Vitamins exhibited two distinct behaviors. Adenosylcobalamin (a vitamin B12 coenzyme) was detectable only after disruption, and together with thiamine (B1) and niacin (B3) was classified as an intracellular-retained type (Type 1). In contrast, biotin (B7) and pantothenate (B5) showed higher extracellular proportions (Type 2). Integrative analyses further indicated that Type 1 thiamine was negatively associated with Blautia, consistent with intensive microbial utilization, whereas Type 2 biotin was strongly positively associated with Alistipes, suggesting links to ecological niches shaped by luminal pH and fermentation modes (carbohydrate vs protein fermentation). Fraction-resolved quantification provides a practical operational framework to differentiate extracellular from cell-associated metabolite pools, helping reconcile metagenomic potential with metabolomic reality and enabling deeper inference of cross-feeding structure in the gut ecosystem.</t>
+          <t>Engineered bacterial therapeutics integrate programmable strain engineering with biomedical functions such as sensing, delivery, immune modulation, microbiome intervention, and disease management. This study conducted a multi-database bibliometric analysis to map the knowledge structure, collaboration patterns, and translational direction of this field. Bibliographic records were retrieved from Web of Science Core Collection, Scopus, and PubMed for publications from 1 January 2000 to 1 June 2026. After document-type filtering, time restriction, deduplication, language screening, and manual eligibility assessment, 1,730 English-language articles and reviews were included. CiteSpace 6.4.R1, VOSviewer 1.6.20, and the bibliometrix R package were used to analyze publication trends, collaboration networks, journal co-citation, dual-map citation trajectories, citation bursts, keyword co-occurrence, and thematic evolution. Publication output increased steadily, with faster growth after 2020; 2025 was the highest-output complete year, while 2026 represented a partial retrieval year. China and the United States were the leading contributors, although institutional collaboration remained regionally clustered. Co-citation, citation-burst, and keyword analyses showed a shift from bacterial chassis construction and circuit design toward engineered probiotics, gut microbiota-related therapy, cancer immunotherapy, drug delivery, live biotherapeutic products, and clinical translation. Persistent translational priorities include controllability, safety, manufacturing consistency, and regulatory alignment.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>本研究旨在解決傳統糞便代謝體學無法區分胞外與胞內代謝物的限制。研究團隊開發了一種分離技術，將糞便檢體分為未處理（代表胞外池）與強效破碎（代表總代謝池）兩部分，透過兩者差值計算出胞內代謝池。分析顯示，維生素代謝呈現兩種模式：維生素 B12、B1 與 B3 主要滯留於胞內（Type 1），而生物素（B7）與泛酸（B5）則以胞外形式為主（Type 2）。結合總體基因體學數據分析發現，Type 1 維生素與 *Blautia* 菌屬呈負相關，推測為微生物密集利用的結果；Type 2 維生素則與 *Alistipes* 呈強正相關，暗示其受到腸道酸鹼值與發酵模式的生態位調控。此方法學突破了現有技術的瓶頸，能更精確地解析腸道菌群的交叉餵養（cross-feeding）機制，為理解腸道微生物生態系統中的代謝流動提供重要的科學依據。</t>
+          <t>本研究透過文獻計量學方法，系統性分析 2000 年至 2026 年間有關「工程化細菌治療」的 1,730 篇學術文獻。研究旨在釐清該領域的知識結構、國際合作模式及臨床轉化趨勢。分析顯示，該領域自 2020 年後顯著加速發展，中國與美國為主要貢獻國。核心研究主軸已由早期的細菌底盤構建與基因電路設計，轉向工程化益生菌、癌症免疫治療、藥物遞送及活體生物藥物（LBP）的開發。科學意義在於確立了該領域從實驗室轉向臨床應用的優先議題，即解決控制力、生物安全性、生產一致性與法規調適等挑戰，為未來工程化細菌作為精準醫療工具的發展提供關鍵決策參考。</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42635406/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42641146/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>42635403</t>
+          <t>42642836</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Baseline gut microbiome ecology predicts long-term fat mass loss after bariatric surgery: evidence for a thrifty Bifidobacterium phenotype.</t>
+          <t>Microbiome-mediated regulation of pathogen virulence: Molecular mechanisms and clinical implications.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>Virulence</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>85位接受減重手術的嚴重肥胖患者，以及21位正常體重的健康對照組（共106位受試者，並於術前及術後1、6、12個月等多個時間點採集樣本）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -729,34 +729,34 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Bariatric surgery (BS) induces weight loss, but long-term success involves complex host-microbiome interactions. We evaluated the longitudinal impact of BS, microbiome resilience, and Mediterranean Diet (MedDiet) adherence up to 24 months. This prospective observational study included 85 patients with severe obesity undergoing BS and 21 normal-weight healthy controls (HC). MedDiet adherence (PREDIMED) was assessed before surgery. Fecal microbiota (16S-rRNA sequencing) and metabolomics (1H-NMR spectroscopy) were analyzed at baseline and at 1-, 6-, and 12-months post-BS. Clinical outcomes and fat mass, evaluated by bioimpedanciometry, were tracked up to 24 months. At baseline, patients exhibited higher microbial Shannon diversity than controls (p = 0.041), alongside a dysfunctional microbiome and metabolome characterized by a higher Firmicutes/Bacteroidetes ratio and elevated levels of branched-chain amino acids (p &lt; 0.0001). Ordinary Least Squares (OLS) regression analysis revealed that MedDiet adherence and type 2 diabetes status significantly modulated baseline diversity. At 12 months post-BS, the gut ecosystem underwent profound remodeling, characterized by depletion of Bifidobacterium spp. and an increase in butyrate levels (p &lt; 0.0001), establishing a novel adaptive state distinct from HC. Baseline gut ecology significantly conditioned long-term BS outcomes: patients in the highest quartile of baseline Bifidobacterium spp. lost significantly less fat mass at 24 months than those in the lowest (6.6% vs. 13.2%, p = 0.010). High baseline Bifidobacterium abundance paradoxically acts as a "thrifty microbiome," potentially maximizing energy harvest and limiting surgery-induced fat loss. Overall, BS induces adaptive microbiome restoration rather than true normalization, highlighting the potential for precision interventions prior to surgery.</t>
+          <t>The human microbiome profoundly influences pathogen virulence and disease susceptibility through diverse molecular mechanisms. This review, focused on literature from 2016 to 2026, synthesizes knowledge on microbiome-mediated regulation examining major pathogens including Vibrio cholerae, enterohemorrhagic Escherichia coli, Salmonella species, Clostridioides difficile, and Staphylococcus aureus. A triangular interaction model is presented, linking host immunity, resident microbiome, and invading pathogen to frame infection outcomes. Commensal bacteria regulate pathogen behavior through quorum sensing interference, metabolite-mediated regulation via short-chain fatty acids and bile acids, competitive exclusion, immune response modulation, and direct antimicrobial production. Key species-Lactobacillus spp. Bifidobacterium spp. Bacteroides thetaiotaomicron, and Faecalibacterium prausnitzii-employ distinct molecular strategies against these pathogens. Organ-on-chip platforms and multi-omics advances reveal context-dependent interactions. Clinical applications including rationally designed probiotics, fecal microbiota transplantation, and precision microbiome engineering show promise despite challenges of inter-individual microbiome variability, representing a paradigm shift toward ecosystem-based infectious disease management.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>本研究旨在探討減重手術（BS）對腸道菌相與代謝物的長期影響，並評估術前基線菌群如何預測術後減重成效。研究發現，手術12個月後腸道生態會發生深度重塑（如雙歧桿菌減少、丁酸增加），形成不同於健康對照組的新適應態。關鍵在於，術前擁有較高雙歧桿菌（Bifidobacterium）豐度的患者，術後24個月的脂肪流失比例顯著較低（6.6%對比13.2%）。這表明高豐度雙歧桿菌可能扮演「節約型菌相」角色，會最大化能量吸收並限制手術引起的脂肪流失。本研究證實減重手術引導的是適應性重塑而非完全正常化，突顯了術前進行精準菌相干預的臨床價值。</t>
+          <t>本研究綜述了2016年至2026年間關於腸道微生物群調控病原體毒力（如霍亂弧菌、大腸桿菌、沙門氏菌等）的分子機制。作者提出了一個結合宿主免疫、共生菌群與入侵病原體的「三角交互模型」，闡述了共生菌如何透過群體感應干擾、代謝產物（如短鏈脂肪酸、膽汁酸）調節、競爭性排斥及免疫調節來抑制病原體。研究強調了乳酸桿菌、雙歧桿菌及普拉梭菌等關鍵菌種的保護機制，並探討了器官晶片與多體學技術在揭示交互作用上的貢獻。此研究主張從生態系統角度管理傳染病，指出益生菌設計、糞便菌群移植及精準微生物組工程是未來治療的關鍵方向，雖面臨個體差異挑戰，但為臨床感染控制提供了典範轉移。</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42635403/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42642836/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>42635401</t>
+          <t>42640100</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fecal filtrate transplantation as salvage therapy for fulminant Clostridioides difficile infection in adult hematological patients during chemotherapy-induced aplasia: a pilot experience.</t>
+          <t>Revisiting gut microbiota-driven ammonia metabolism: from disease burden to physiological adaptation.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -771,12 +771,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16S, metagenomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3 位接受化療後再生不良並併發猛爆性困難梭菌感染的成年血液腫瘤患者</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -784,34 +784,34 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fulminant Clostridioides difficile infection (CDI) in patients with hematologic malignancies during chemotherapy-induced aplasia carries high mortality and limited treatment options. Our objective was to evaluate fecal filtrate transplantation (FFT) as a salvage therapy for fulminant CDI during aplasia, and to explore whether donor-recipient phage dynamics may contribute to clinical response. We conducted a single-center, prospective, protocol-defined pilot case series study including consecutive adults with hematologic malignancies, chemotherapy-induced grade-4 aplasia and fulminant CDI, refractory to ≥5 d of high-dose oral vancomycin plus intravenous metronidazole and tigecycline. FFT was prepared from a single unrelated donor using sequential centrifugation and filtration, and administered via nasogastric tube in two doses. The primary outcome was sustained clinical cure, secondary outcomes included survival and adverse events, assessed at +14 and +30 d post-FFT. 16S rRNA gene sequencing was used to assess microbiome compositions, while viral metagenomics and in vitro propagation assays were employed to characterize donor-recipient phageome interactions. Three patients with adverse-risk acute myeloid leukemia and fulminant CDI caused by genetically distinct C. difficile strains received FFT. All patients achieved clinical resolution by day +14, accompanied by improvements in abdominal distension and inflammatory markers. By day +30, one patient died from Pseudomonas aeruginosa septic shock, while two maintained remission with confirmatory follow-up. FFT was well tolerated, with no procedure-related immediate complications or FFT-attributable adverse events. Microbiome and phage profiling revealed heterogeneous responses, including shifts in bacterial community composition, with no clear evidence for a general role of donor-derived phages in CDI resolution. In contrast, we observed induction of prophages harbored by recipient-associated Clostridium species, which may have contributed to decolonization through stress-induced entry into the lytic cycle. FFT was feasible, with rapid sustained CDI resolution in hematologic patients with chemotherapy-induced aplasia. ClinicalTrials.gov identifier NCT07172191. Prospective single-center pilot study of fecal filtrate transplantation (FFT) for fulminant-refractory C. difficile infection in three aplastic adult hematologic patients. FFT was well tolerated, achieved rapid clinical cure, and showed heterogeneous microbiome and phageome modulation, potentially contributing to therapeutic effects.</t>
+          <t>Ammonia homeostasis is governed by interconnected host and microbial pathways, including hepatic ureagenesis, glutamine synthesis, and gut microbiota-mediated urea hydrolysis, proteolysis, and amino acid deamination. Ammonia has historically been viewed primarily as a nitrogenous waste product and neurotoxic molecule, a concept strongly supported by studies of hyperammonemia and hepatic encephalopathy. Impaired hepatic clearance, portosystemic shunting, and enhanced gut-derived ammonia input increase systemic ammonia burden and are linked to neurological dysfunction, muscle wasting, immune dysregulation, and progression of liver disease. In the gut lumen and mucosal environment, however, gut microbes not only generate ammonia but can also reuse ammonia-derived nitrogen for amino acid synthesis, microbial biomass formation, and community nitrogen exchange. Evidence from selected physiological and preclinical models indicates that microbiota-derived ammonia may contribute to nitrogen recycling, microbial community maintenance, enteric neural regulation, or metabolic adaptation under defined conditions. These roles are more context-specific and less broadly established than the pathological effects of systemic hyperammonemia. When epithelial barrier integrity is compromised, hepatic clearance declines, or host buffering reserves are depleted, elevated ammonia can increase epithelial exposure, portal ammonia input, or peripheral blood ammonia. Conversely, evidence that reduced microbiota-derived ammonia contributes to disease remains limited and currently comes mainly from selected animal models. This review re-examines ammonia metabolism from a gut microbiota-centered perspective. We discuss the ecological origins, spatial distribution, exposure characteristics, host-interface effects, and context-specific outcomes of microbiota-derived ammonia in physiology and disease, and discuss how ammonia should be measured, stratified, and targeted in microbial nitrogen metabolism.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>本研究評估糞便濾液移植（FFT）作為血液腫瘤患者在化療後再生不良期間，罹患難治猛爆性困難梭菌感染（CDI）的挽救療法。研究納入3位急性骨髓性白血病患者。結果顯示，所有患者在FFT治療後14天內均達到臨床緩解，且無嚴重副作用。微生物與噬菌體組分析顯示，治療後患者菌相改變，且宿主原有的梭菌前噬菌體可能因壓力被誘導進入裂解週期進而協助去定殖，而非由供體噬菌體直接清除。本研究證實FFT對此高風險免疫低下族群是一項安全、可行且快速有效的挽救療法，並為噬菌體介導的治療機制提供了新觀點。</t>
+          <t>本綜述重新審視了腸道菌群驅動的氨代謝，探討其從疾病負擔到生理適應的雙重角色。傳統上，氨被視為具神經毒性的代謝廢物，與高氨血症、肝性腦病及肝病惡化密切相關。然而，在腸道微環境中，微生物不僅產生氨，亦能利用氨源氮進行氨基酸合成與群落氮循環，展現出維持腸道神經與代謝適應等生理功能。文章強調，氨的病理與生理效應高度取決於上皮屏障、肝臟清除能力及宿主緩衝儲備。本研究為腸道微生物氮代謝提供了新的生態與臨床視角，並討論了未來如何精確測量及標靶氨代謝的策略。</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42635401/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42640100/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>42634246</t>
+          <t>42640624</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Natural microbiota confer life-long protection against obesity via an early-life, immune-mediated effect on brown adipocytes.</t>
+          <t>Gut microbial diversity at baseline conditions the clinical, microbiome, and metabolic response to paraprobiotic Lactiplantibacillus plantarum LRCC5282 in overweight adults.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -826,12 +826,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>16S, metabolomics</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>120 位過重成人</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -839,49 +839,49 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Obesity, a major risk factor for metabolic disease, has increased in industrialized nations alongside a reduction in gut microbiota diversity. Reconstituting laboratory mice with complex, natural microbiota and commensals from wild mice resulted in protection against diet-induced obesity. These natural microbiota reduced weight gain in both male and female mice of different genetic backgrounds throughout their life and increased energy expenditure. Single-nuclei RNA sequencing identified a dominant adipocyte population in brown adipose tissue (BAT) with a transcriptional signature of increased thermogenic activity, while white adipose tissue mass and beiging were reduced. Protection against diet-induced obesity was transferable to adult germ-free mice via exposure to natural microbiota, indicating an association with the timing of immune response induction rather than BAT developmental programming. However, protection against diet-induced obesity did not require type 2 immune signaling, as shown in STAT6 knockout mice. Rather, it was associated with increased levels of chemokines and monocytes in BAT in early life, pointing to a role of infiltrating myeloid cells. Indeed, CCR2-deficient mice with natural microbiota lacked the BAT transcriptional signature of increased thermogenic activity, increased energy expenditure, and protection against diet-induced obesity that wild-type mice with natural microbiota exhibited. The latter was restored upon injection with wild-type bone marrow. Taken together, these findings identify a novel microbiota‒immune‒adipose tissue axis that results in increased BAT thermogenesis and improved energy balance throughout life.</t>
+          <t>The gut microbiota is increasingly recognized as a target for obesity management; however, whether baseline gut microbial diversity conditions responsiveness to microbiota-targeted interventions remains unclear. We aimed to investigate whether baseline gut microbial diversity is associated with responsiveness to a paraprobiotic derived from Lactiplantibacillus plantarum LRCC5282 (LP5282-P) in overweight adults. In a 12-week, randomized, double-blind, placebo-controlled, multicenter trial of 120 overweight adults, LP5282-P produced no significant between-group differences in any clinical outcome across the overall per-protocol population. However, in the low-diversity subgroup, LP5282-P was associated with significant reductions in body weight, body mass index, and circulating leptin levels. These clinical changes were accompanied by compositional shifts in the gut microbiota, including higher relative abundances of Christensenellaceae, Faecalibacterium, and Alistipes. Fecal metabolite profiles showed elevated acetate and butyrate concentrations and altered bile acid composition. Within the low-diversity subgroup, changes in the relative abundances of Akkermansia and Eubacterium were inversely correlated with changes in body weight, body fat mass, and leptin levels. In contrast, the high-diversity subgroup exhibited no consistent response across the outcome domains examined. Overall, baseline gut microbial diversity was associated with differential responsiveness to LP5282-P, supporting its potential use as a stratification variable in future microbiota-targeted intervention trials. Further studies integrating direct measures of microbial activity and host response are warranted to elucidate the biological pathways underlying this diversity-dependent responsiveness. Trial registration: Clinical Research Information Service (CRIS), KCT0008119.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>本研究旨在探討野生小鼠的天然微生物群如何預防飲食誘導的肥胖。研究發現，引入天然微生物群能顯著降低雄性與雌性小鼠的體重增加，並提升能量消耗。機制分析顯示，這種保護作用並非源於棕色脂肪組織（BAT）的發育重編程，而是透過早期生命階段的免疫調節達成。具體而言，天然微生物群誘導了早期 BAT 中趨化因子與單核球的增加，進而促使骨髓來源的免疫細胞浸潤，活化 BAT 的產熱基因表現。此外，研究證實 CCR2 缺失小鼠無法展現此保護效果，且透過野生型骨髓移植可恢復其抗肥胖能力。此研究揭示了一個全新的「微生物-免疫-脂肪組織」軸線，對於理解微生物群如何透過調節早期免疫反應，長期影響機體能量代謝平衡具有重要的科學意義，並為肥胖防治提供了潛在的新策略。</t>
+          <t>本研究旨在探討基準線腸道微生物多樣性，是否會影響過重成人對副乾酪乳桿菌（LP5282-P）介入的臨床、菌群及代謝反應。在一項為期12週、納入120位過重成人的臨床試驗中，整體人群並未展現顯著差異；然而，在「低多樣性」亞群中，LP5282-P顯著降低了受試者的體重、BMI與血清瘦素水平，並促使腸道有益菌（如 *Faecalibacterium* 與 *Alistipes*）豐度上升，同時提升糞便中乙酸與丁酸濃度並改變膽汁酸組成。相反地，「高多樣性」亞群則無一致反應。此研究證實基準線菌群多樣性是預測益生菌療效的重要關鍵，可作為未來精準微生態介入與體重管理的分層依據。</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42634246/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42640624/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>42637484</t>
+          <t>42642834</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Insights into the analysis of microbial communities in fermented foods from the perspective of DNA-based techniques.</t>
+          <t>Glycosylation in gut-brain communication: from the intestinal barrier and microbiota to immune and neural signaling.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Food research international (Ottawa, Ont.)</t>
+          <t>Gut microbes</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>16S, metagenomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -894,54 +894,54 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>The quality, flavor, and stability of fermented foods depend on the microbial community. However, microbial dynamics are difficult to observe directly, leading to limited control over fermentation. High-throughput sequencing is a revolutionary tool for microbial characterization, among which DNA-based amplicon and metagenomic sequencing are core techniques. Nevertheless, the related data processing workflows in the context of fermented foods have not yet been systematically summarized, hindering the translation of research findings into fermentation practices. This review clarifies the applications of amplicon and metagenomic sequencing in fermented foods. For amplicon sequencing, the impacts of target regions, data preprocessing, and reference databases are addressed. For metagenomic sequencing, sequencing strategies, read-based and binning-based analytical methods, functional annotation, and species-specific databases are discussed. In addition, major strategies for downstream analysis of community data are summarized, including microbial diversity, co-occurrence networks, niche and community assembly, key environmental drivers, and machine learning-based prediction. Amplicon sequencing efficiently reveals microbial succession during fermentation but has limitations in functional annotation. Metagenomic sequencing is notable for functional annotation, enabling the linkage between microbial communities and metabolic potential alongside community characterization. Standardized data preprocessing and specific databases are critical for improving characterization. For community data, integrated analysis allows uncovering the driving factors of microbial succession, thereby helping to regulate fermentation. Notably, the compositional nature of the data must be considered and validated to avoid spurious associations. In summary, the exponential growth of sequencing data will propel the era of precision fermentation.</t>
+          <t>The gut-brain axis is a complex bidirectional communication network linking the gastrointestinal tract and the central nervous system. Its dysregulation is closely associated with a wide range of gastrointestinal, metabolic, and neuropsychiatric disorders. Glycosylation, one of the most prevalent and structurally diverse post-translational modifications of proteins and lipids, is increasingly recognized as a regulator of multiple processes within the gut-brain axis. In this review, we summarize evidence that glycosylation influences several steps of gut-brain communication, including intestinal barrier function, microbial glycan metabolism, immune signaling, enteric and vagal pathways, blood-brain barrier integrity, and neural responses. We distinguish direct mechanistic findings from associative observations and discuss the more limited evidence for brain-to-gut regulation of intestinal glycosylation. In addition, we discuss the potential of glycosylation-targeted nutritional and microbiota-based interventions and highlight emerging opportunities to integrate glycomics with other omics approaches to dissect the complex regulatory networks underlying the gut-brain axis. In conclusion, elucidating how glycosylation shapes signaling along the gut-brain axis may open new avenues for understanding disease pathogenesis and for developing targeted therapeutic strategies.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>本綜述旨在系統性總結基於DNA的擴增子（16S）與總體基因體學定序技術在發酵食品微生物群落分析中的應用與數據處理工作流程。文章指出，擴增子定序能高效揭示發酵過程中的微生物演替，但功能註釋受限；總體基因體定序則擅長功能註釋，可連結群落特徵與代謝潛力。此外，文章強調了標準化數據預處理、特定數據庫以及結合群落多樣性、共發生網路與機器學習等下游分析的重要性，並提醒需注意數據的組成性特徵以避免虛假關聯。本研究為發酵食品的微生物群落調控提供了理論指引，有助於推動精準發酵的實踐。</t>
+          <t>本文探討「腸-腦軸線」（Gut-Brain Axis）中醣基化（Glycosylation）修飾的關鍵調節角色。醣基化作為蛋白質與脂質重要的轉譯後修飾，深刻影響腸道屏障功能、微生物聚醣代謝、免疫訊息傳遞及血腦屏障完整性。研究重點解析了醣基化如何調控腸道與中樞神經系統間的溝通，並區分了機制性證據與相關性觀察。本文不僅強調了醣基化在維繫軸線穩定中的核心地位，更提出透過營養干預與微生物調節，結合多體學（Omics）分析醣基化網絡，將有望為神經精神疾病與代謝性障礙提供創新的診斷與治療策略。</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42637484/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42642834/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>42637478</t>
+          <t>42635406</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Effects of sorghum variety on fermentation microecology and flavor characteristics of sesame-flavor Baijiu.</t>
+          <t>Separating extracellular from intracellular fecal metabolites exposes cross-feeding architecture in the gut: exploring metabolite partitioning and ecological associations.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Food research international (Ottawa, Ont.)</t>
+          <t>Gut microbes</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3 種高粱品種（紅纓子、黑殼、本地品種），於 2 輪連續發酵中的 3 個時間點（0、15、50天）所採集的酒醅及對應的基酒檢體（未提及具體總樣本件數）</t>
+          <t>63 個糞便檢體（來自 63 位健康受試者）</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -949,44 +949,44 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sorghum, the principal raw material for Baijiu fermentation, plays a key role in shaping fermentation microecology and flavor formation. However, the effects of sorghum varietal differences on sesame-flavor Baijiu fermentation remain insufficiently understood. In this study, three sorghum varieties, Hongyingzi (R), Hei'e (B), and a domestic cultivar (G), were compared over two consecutive fermentation rounds. Fermented grain (Jiupei) samples collected at 0, 15, and 50 days were analyzed for physicochemical properties, enzyme activities, microbial communities, volatile compounds in Jiupei and base liquor, and the taste characteristics of the corresponding base liquor. Despite showing similar overall fermentation trends, the three sorghum varieties differed in acid accumulation, starch utilization, microbial succession, and volatile composition. Fungal communities shifted from early Pichia dominance to multi-genus coexistence, whereas bacterial communities progressively converged toward Lactobacillus dominance. A total of 218 and 258 volatile compounds were identified in Jiupei and 176 and 192 in base liquor from the first and second rounds, respectively. Esters were the dominant differential class, and volatile-marker profiles varied among sorghum varieties and fermentation rounds, with no single variety showing consistent enrichment across all sesame-flavor-related compounds. These results indicate that sorghum variety is an important factor associated with microbial assembly and flavor formation during sesame-flavor Baijiu fermentation, and provide a basis for raw material selection and flavor-oriented process optimization.</t>
+          <t>The gut microbiota forms a complex ecosystem through metabolic interdependence (cross-feeding). However, conventional fecal metabolomics typically quantifies only total metabolite pools, making it difficult to distinguish extracellular-enriched metabolite pools from predominantly cell-associated ones, and thus limiting reconstruction of in situ metabolic networks. Here, we quantified fecal metabolites in paired fractions from the same specimen: an undisrupted fraction representing the extracellular pool and a strongly bead-beaten fraction representing the total pool; the intracellular pool was defined as the difference between total and extracellular measurements. Stool samples from 63 healthy individuals were analyzed for short-chain fatty acids, polyamines, and water-soluble vitamins, and the results were integrated with shotgun metagenomic profiles of species composition and functional genes. Vitamins exhibited two distinct behaviors. Adenosylcobalamin (a vitamin B12 coenzyme) was detectable only after disruption, and together with thiamine (B1) and niacin (B3) was classified as an intracellular-retained type (Type 1). In contrast, biotin (B7) and pantothenate (B5) showed higher extracellular proportions (Type 2). Integrative analyses further indicated that Type 1 thiamine was negatively associated with Blautia, consistent with intensive microbial utilization, whereas Type 2 biotin was strongly positively associated with Alistipes, suggesting links to ecological niches shaped by luminal pH and fermentation modes (carbohydrate vs protein fermentation). Fraction-resolved quantification provides a practical operational framework to differentiate extracellular from cell-associated metabolite pools, helping reconcile metagenomic potential with metabolomic reality and enabling deeper inference of cross-feeding structure in the gut ecosystem.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>本研究旨在探討不同高粱品種（紅纓子、黑殼及本地品種）對芝麻香型白酒發酵過程中微生態與風味特徵的影響。研究分析了兩輪連續發酵中不同時間點的酒醅與基酒。結果顯示，儘管整體發酵趨勢相似，但不同高粱在酸累積、澱粉利用、微生物演替及揮發性成分上存在顯著差異。發酵過程中，真菌群落由早期的畢赤酵母屬主導轉為多屬共存，細菌則逐漸趨向乳酸桿菌主導。此外，研究在酒醅與基酒中鑑定出數百種揮發性化合物（以酯類為差異主體），且不同品種高粱在風味物質的富集上各有優勢。本研究證實高粱品種是影響白酒發酵微生物群落組裝與風味形成的重要因素，為原料選擇與工藝優化提供了科學依據。</t>
+          <t>本研究針對腸道微生物的代謝互營機制（cross-feeding）進行探討。傳統糞便代謝組學僅能分析總代謝物，無法區分細胞外與細胞內代謝池，限制了對代謝網絡的解析。研究團隊透過對比未破碎（代表細胞外池）與強力破碎（代表總代謝池）的糞便樣本，成功推算出細胞內代謝物的分佈。針對短鏈脂肪酸、多胺與水溶性維生素的分析顯示，維生素呈現兩類分佈：B12、B1 與 B3 傾向保留於細胞內（Type 1），而 B7 與 B5 則富集於細胞外（Type 2）。結合宏基因組分析發現，Type 1 代謝物與特定細菌（如 *Blautia*）的利用模式顯著相關，Type 2 代謝物則與 *Alistipes* 及腸道生態位特徵（如 pH 值、發酵類型）相關。此方法為區分代謝物空間分佈提供了實用架構，有助於更精確地將宏基因組功能潛力與代謝體現實連結，深入理解腸道微生物的互營生態結構。</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42637478/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42635406/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>42637476</t>
+          <t>42635403</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A Shenling Baizhu San polysaccharide fraction (SLP-2)-based synbiotic alleviates lactose-induced gut dysfunction via a microbiota-metabolite-barrier axis.</t>
+          <t>Baseline gut microbiome ecology predicts long-term fat mass loss after bariatric surgery: evidence for a thrifty Bifidobacterium phenotype.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Food research international (Ottawa, Ont.)</t>
+          <t>Gut microbes</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>85 位重度肥胖患者及 21 位健康對照組（共 106 名受試者）</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -1004,54 +1004,54 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Lactose intolerance (LI) is a common digestive disorder, and its management still relies largely on dietary restriction. Because gut microbial fermentation and barrier dysfunction contribute to LI-related symptoms, microbiota-targeted prebiotic or synbiotic strategies may provide complementary approaches. However, the active plant-polysaccharide fractions and their microbial partners remain unclear. This study aimed to identify the bioactive polysaccharide fraction from Shenling Baizhu San and evaluate its pairing with responder bacteria for alleviating high-lactose diet (HLD)-induced intestinal dysfunction. Stepwise ethanol precipitation yielded SLP-2, which was subsequently identified as the principal bioactive fraction through human fecal fermentation, monoculture assays, and an HLD rat model. SLP-2 enriched Eubacterium-associated taxa and supported the growth of Akkermansia muciniphila in monoculture and in vivo. Building on this, a synbiotic combining SLP-2 with A. muciniphila and E. rectale alleviated HLD-induced gut dysfunction; the antibiotic-matched comparison with the probiotics-only group supported an SLP-2-associated contribution. The synbiotic intervention was associated with increased tight junction proteins, MUC2 expression, improved intestinal architecture, and thicker mucus layers. Multi-omics analysis linked co-metabolites, including intestinal 6-MGG and HTy-Ac and systemic DHPV-G, with barrier restoration and an immune profile characterized by increased IL-10 and lower TLR4 expression. These findings suggest that SLP-2-based synbiotic intervention alleviates HLD-induced intestinal dysfunction through microbiota-metabolite-barrier modulation, providing preclinical evidence for future functional-food strategies pending human validation.</t>
+          <t>Bariatric surgery (BS) induces weight loss, but long-term success involves complex host-microbiome interactions. We evaluated the longitudinal impact of BS, microbiome resilience, and Mediterranean Diet (MedDiet) adherence up to 24 months. This prospective observational study included 85 patients with severe obesity undergoing BS and 21 normal-weight healthy controls (HC). MedDiet adherence (PREDIMED) was assessed before surgery. Fecal microbiota (16S-rRNA sequencing) and metabolomics (1H-NMR spectroscopy) were analyzed at baseline and at 1-, 6-, and 12-months post-BS. Clinical outcomes and fat mass, evaluated by bioimpedanciometry, were tracked up to 24 months. At baseline, patients exhibited higher microbial Shannon diversity than controls (p = 0.041), alongside a dysfunctional microbiome and metabolome characterized by a higher Firmicutes/Bacteroidetes ratio and elevated levels of branched-chain amino acids (p &lt; 0.0001). Ordinary Least Squares (OLS) regression analysis revealed that MedDiet adherence and type 2 diabetes status significantly modulated baseline diversity. At 12 months post-BS, the gut ecosystem underwent profound remodeling, characterized by depletion of Bifidobacterium spp. and an increase in butyrate levels (p &lt; 0.0001), establishing a novel adaptive state distinct from HC. Baseline gut ecology significantly conditioned long-term BS outcomes: patients in the highest quartile of baseline Bifidobacterium spp. lost significantly less fat mass at 24 months than those in the lowest (6.6% vs. 13.2%, p = 0.010). High baseline Bifidobacterium abundance paradoxically acts as a "thrifty microbiome," potentially maximizing energy harvest and limiting surgery-induced fat loss. Overall, BS induces adaptive microbiome restoration rather than true normalization, highlighting the potential for precision interventions prior to surgery.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>本研究旨在探討參苓白朮散多醣活性組分（SLP-2）結合特定菌株，對高乳糖飲食（HLD）引發之腸道功能障礙的緩解作用。研究發現，SLP-2能促進*A. muciniphila*與真桿菌屬相關菌群生長。以SLP-2搭配益生菌的合生元配方，能顯著改善HLD大鼠的腸道屏障，包含增加緊密連接蛋白與MUC2表達、增厚黏液層。多體學分析顯示，其保護作用與腸道及全身性代謝物（如6-MGG、DHPV-G）的調節，以及抗發炎反應（提升IL-10、降低TLR4）密切相關。此發現為開發防治乳糖不耐症的功能性食品提供了臨床前依據。</t>
+          <t>本研究探討減重手術（BS）後腸道微生物群與長期減脂效果的關聯。研究追蹤 85 名患者於術前及術後長達 24 個月的變化，分析發現手術顯著重塑了腸道菌相與代謝環境，特別是雙歧桿菌（*Bifidobacterium*）的耗竭與丁酸鹽的增加。關鍵發現指出，術前高豐度的雙歧桿菌反而成為一種「節儉型表型」，會增加能量攝取效率，導致術後 24 個月的脂肪減少量顯著較少（6.6% 對比 13.2%）。這顯示減重手術並非使微生物組回歸常態，而是引發一種適應性重組。此研究凸顯了術前腸道生態作為預測手術成效生物標記的潛力，對於未來制定精準的術前介入策略具有重要的臨床指導意義。</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42637476/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42635403/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>42637471</t>
+          <t>42635401</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fucoidan from giant kelp alleviates postmenopausal osteoporosis by regulating the betaine-OPG/RANKL/RANK signaling axis.</t>
+          <t>Fecal filtrate transplantation as salvage therapy for fulminant Clostridioides difficile infection in adult hematological patients during chemotherapy-induced aplasia: a pilot experience.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Food research international (Ottawa, Ont.)</t>
+          <t>Gut microbes</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>16S, metagenomics</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>3 位成人血液腫瘤患者</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -1059,54 +1059,54 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Postmenopausal osteoporosis (PMOP), characterized by excessive bone resorption and impaired bone remodeling, remains a significant global health challenge. This study investigated the protective effects of fucoidan from giant kelp (GKP) against PMOP and its underlying mechanisms in ovariectomized mice. GKP supplementation attenuated bone loss by preserving trabecular microarchitecture, normalizing systemic mineral homeostasis, and suppressing osteoclastogenesis, as evidenced by the downregulation of osteoclast-related genes. 16S rRNA gene sequencing revealed that GKP reshaped the gut microbiota by decreasing the Bacteroidota/Firmicutes ratio and enriching beneficial taxa, which promoted short-chain fatty acid production. Targeted metabolomics revealed that GKP induced profound systemic metabolic reprogramming, particularly amino acid metabolism, and identified betaine as a key systemic metabolite effector upregulated following GKP treatment. In vitro assays demonstrated that betaine suppressed receptor activator of nuclear factor-κB ligand (RANKL)-induced osteoclast differentiation and mitigated inflammation. In vivo validation demonstrated that betaine intervention recapitulated the osteoprotective phenotype observed in GKP-treated mice, which was associated with regulation of the osteoprotegerin/RANKL/RANK signaling axis. These results indicate that GKP exerts anti-osteoporotic effects in association with changes in gut microbiota and systemic metabolism, while betaine-mediated regulation of the OPG/RANKL/RANK signaling may contribute to its osteoprotective activity.</t>
+          <t>Fulminant Clostridioides difficile infection (CDI) in patients with hematologic malignancies during chemotherapy-induced aplasia carries high mortality and limited treatment options. Our objective was to evaluate fecal filtrate transplantation (FFT) as a salvage therapy for fulminant CDI during aplasia, and to explore whether donor-recipient phage dynamics may contribute to clinical response. We conducted a single-center, prospective, protocol-defined pilot case series study including consecutive adults with hematologic malignancies, chemotherapy-induced grade-4 aplasia and fulminant CDI, refractory to ≥5 d of high-dose oral vancomycin plus intravenous metronidazole and tigecycline. FFT was prepared from a single unrelated donor using sequential centrifugation and filtration, and administered via nasogastric tube in two doses. The primary outcome was sustained clinical cure, secondary outcomes included survival and adverse events, assessed at +14 and +30 d post-FFT. 16S rRNA gene sequencing was used to assess microbiome compositions, while viral metagenomics and in vitro propagation assays were employed to characterize donor-recipient phageome interactions. Three patients with adverse-risk acute myeloid leukemia and fulminant CDI caused by genetically distinct C. difficile strains received FFT. All patients achieved clinical resolution by day +14, accompanied by improvements in abdominal distension and inflammatory markers. By day +30, one patient died from Pseudomonas aeruginosa septic shock, while two maintained remission with confirmatory follow-up. FFT was well tolerated, with no procedure-related immediate complications or FFT-attributable adverse events. Microbiome and phage profiling revealed heterogeneous responses, including shifts in bacterial community composition, with no clear evidence for a general role of donor-derived phages in CDI resolution. In contrast, we observed induction of prophages harbored by recipient-associated Clostridium species, which may have contributed to decolonization through stress-induced entry into the lytic cycle. FFT was feasible, with rapid sustained CDI resolution in hematologic patients with chemotherapy-induced aplasia. ClinicalTrials.gov identifier NCT07172191. Prospective single-center pilot study of fecal filtrate transplantation (FFT) for fulminant-refractory C. difficile infection in three aplastic adult hematologic patients. FFT was well tolerated, achieved rapid clinical cure, and showed heterogeneous microbiome and phageome modulation, potentially contributing to therapeutic effects.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>本研究探討巨藻褐藻醣膠（GKP）對去卵巢小鼠更年期後骨質疏鬆症（PMOP）的保護機制。結果顯示，補充GKP能有效減少骨質流失並抑制破骨細胞生成。16S定序顯示GKP重塑了腸道菌群（降低擬桿菌門/厚壁菌門比例），促進短鏈脂肪酸產生。代謝組學分析發現，GKP顯著提升了系統性代謝物甜菜鹼（betaine）的含量。體內外實驗進一步證實，甜菜鹼透過調控OPG/RANKL/RANK信號軸，能抑制破骨細胞分化並緩解骨質流失。本研究證實GKP具備透過「腸道菌群-代謝物」軸抗骨質疏鬆的潛力，為PMOP防治提供了科學依據。</t>
+          <t>本研究旨在評估糞便濾液移植（FFT）作為挽救療法，治療化療致免疫不全之血液腫瘤患者合併難治猛爆性艱難梭菌感染（CDI）的療效，並探討供受體間噬菌體的動力學關係。此臨床先導試驗納入3位患者，結果顯示FFT耐受性良好，所有患者在接受治療後14天內均達到臨床緩解。微生態與噬菌體體學分析顯示，臨床症狀的改善並非源於供體噬菌體的直接轉移，而是FFT可能誘發了受體腸道內艱難梭菌的原噬菌體進入溶菌週期，進而促進病原菌清除。本研究證實FFT在此高風險族群中具安全性與可行性，為難治性CDI提供了創新的機制見解與治療選擇。</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42637471/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42635401/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>42637450</t>
+          <t>42634246</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Highland barley polysaccharides promoted lactose intestinal fermentation in vitro: Unveiling the dynamic response of gut microbiota and polysaccharide structure.</t>
+          <t>Natural microbiota confer life-long protection against obesity via an early-life, immune-mediated effect on brown adipocytes.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Food research international (Ottawa, Ont.)</t>
+          <t>Gut microbes</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>乳糖不耐症患者的糞便檢體（未提及具體數量）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -1114,39 +1114,39 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Lactose intolerance affects over 70% of the global population due to the untimely metabolism of lactose in the colon. To accelerate lactose metabolism, we innovatively employed highland barley polysaccharides (HBP) to modulate the colonic fermentation efficiency of lactose using an in vitro fermentation model and fecal samples from lactose intolerant patients. With the addition of HBP, the consumption efficiency of lactose began to increase after 6 h of fermentation. At 48 h, lactose consumption increased by 29%, surpassing the effect of commercial prebiotics. Meanwhile, HBP with lower molecular weight (HBP-L, 8.69 × 104 g/Mol) exhibited more effective impacts than HBP with high molecular weight (HBP-H, 1.22 × 105 g/Mol), which was particularly evident during the 12-48 h of fermentation. More importantly, HBP, particularly HBP-L, substantially enriched Segatella, Bifidobacterium, and Ligilactobacillus in a time-dependent manner and was positively correlated with decreased lactose levels and elevated bacterial lactase activity, resulting in significant conversion of lactose to lactic acid and short-chain fatty acids. During the first 12 h of fermentation, HBP-L underwent more significant degradation than HBP-H. Meanwhile, the xylose residues and Glcp glycosidic bonds in HBP-L were preferentially utilized, while it was glucose residue in HBP-H. Thus, it indicated that HBPs were degraded and altered the composition of the gut microbiota, thereby enhancing the fermentation efficiency of lactose. Our findings provide a theoretical basis for developing targeted prebiotic foods to manage lactose intolerance.</t>
+          <t>Obesity, a major risk factor for metabolic disease, has increased in industrialized nations alongside a reduction in gut microbiota diversity. Reconstituting laboratory mice with complex, natural microbiota and commensals from wild mice resulted in protection against diet-induced obesity. These natural microbiota reduced weight gain in both male and female mice of different genetic backgrounds throughout their life and increased energy expenditure. Single-nuclei RNA sequencing identified a dominant adipocyte population in brown adipose tissue (BAT) with a transcriptional signature of increased thermogenic activity, while white adipose tissue mass and beiging were reduced. Protection against diet-induced obesity was transferable to adult germ-free mice via exposure to natural microbiota, indicating an association with the timing of immune response induction rather than BAT developmental programming. However, protection against diet-induced obesity did not require type 2 immune signaling, as shown in STAT6 knockout mice. Rather, it was associated with increased levels of chemokines and monocytes in BAT in early life, pointing to a role of infiltrating myeloid cells. Indeed, CCR2-deficient mice with natural microbiota lacked the BAT transcriptional signature of increased thermogenic activity, increased energy expenditure, and protection against diet-induced obesity that wild-type mice with natural microbiota exhibited. The latter was restored upon injection with wild-type bone marrow. Taken together, these findings identify a novel microbiota‒immune‒adipose tissue axis that results in increased BAT thermogenesis and improved energy balance throughout life.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>本研究旨在探討青稞多醣（HBP）如何調控乳糖不耐症患者的腸道菌群，以促進體外乳糖發酵與代謝。研究發現，添加 HBP（特別是低分子量的 HBP-L）能在發酵 48 小時後提升乳糖消耗效率達 29%，效果顯著優於商業益生元。機制上，HBP-L 在發酵初期降解更為顯著，並能隨時間特異性富集 *Segatella*、雙歧桿菌屬（*Bifidobacterium*）及 *Ligilactobacillus*，進而提升細菌乳糖酶活性，將乳糖轉化為乳酸與短鏈脂肪酸。本研究證實了青稞多醣能透過重塑腸道菌群結構來加速乳糖代謝，為開發緩解乳糖不耐症的標靶益生元食品提供了重要科學依據。</t>
+          <t>本研究旨在探討野生小鼠的天然腸道菌相如何預防飲食引起的肥胖。研究發現，移植天然菌相能終生保護不同遺傳背景的實驗小鼠免於肥胖，並顯著增加能量消耗。單細胞核RNA定序（snRNA-seq）顯示，這與褐色脂肪組織（BAT）中產熱活性增強的脂肪細胞亞群有關。此保護機制並非透過第二型免疫信號，而是依賴於早期生命階段骨髓源性細胞（特別是CCR2+單核細胞）向BAT的浸潤與免疫調節。本研究首次揭示了一條全新的「腸道菌群—免疫—脂肪組織」軸，證實早期菌相暴露能透過免疫介導促進褐色脂肪產熱，為肥胖及代謝性疾病的防治提供了新穎的科學依據與治療靶點。</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42637450/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42634246/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>42637441</t>
+          <t>42644084</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Microbial succession drives quality deterioration in refrigerated golden pompano (Trachinotus ovatus): regulatory network of dominant spoilage microbiota on characteristic biomarkers.</t>
+          <t>Viral metagenomics of synanthropic urban bats: A surveillance strategy for uncovering potentially zoonotic viruses.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Food research international (Ottawa, Ont.)</t>
+          <t>One health (Amsterdam, Netherlands)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>2,422 隻收集的蝙蝠，其中 150 對肺部與腸道配對樣本（共 300 個組織檢體）</t>
         </is>
       </c>
       <c r="G14" t="b">
@@ -1169,34 +1169,34 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Elucidating the quality deterioration mechanisms of refrigerated golden pompano (Trachinotus ovatus), this study integrated 16S rRNA gene sequencing and untargeted metabolomics to systematically dissect how microbial ecological succession drives metabolic changes. As critical spoilage indicators, total volatile basic nitrogen (TVB-N) and thiobarbituric acid reactive substances (TBARS) continuously increased during storage, indicating significant deterioration by day 6. Microbial community succession analysis revealed that Psychrobacter, Shewanella, and Pseudomonas gradually became the dominant microbiota in the late storage stage. Metabolite enrichment analysis further demonstrated that this shift redirected the metabolic focus from early-stage nucleotide degradation to late-stage protein hydrolysis and amino acid metabolism. Moreover, multivariate statistical analysis identified 50 potential spoilage biomarkers, among which biogenic amines (histamine, tyramine, and phenylethylamine) were recognized as key indicators reflecting spoilage progression. Correlation network analysis revealed positive correlations between Pseudomonas and Shewanella abundances and the accumulation of these biogenic amines. This suggests that these two genera act as the core functional microbiota, driving spoilage metabolite generation and subsequent quality deterioration. Pathway analysis of potential spoilage biomarker generation indicates that amino acid and nucleotide metabolism constitute the core spoilage pathways, with lipid oxidation serving as a complementary mechanism. Overall, this study elucidates the spoilage mechanisms of refrigerated golden pompano, providing chemical targets for early biomarker detection and targeted antibacterial strategies.</t>
+          <t>Bats are natural reservoirs for diverse viruses, including coronaviruses, filoviruses, and paramyxoviruses, several of those known to be involved in zoonotic spillover events and demanding an integrated surveillance. Here, we present a framework that leverages Brazil's rabies passive surveillance programme to detect bat-borne viruses. Using an algorithm to select representative specimens from 2422 bats collected across São Paulo state, we submitted 150 paired lung and intestine samples to nanopore metagenomic sequencing. We detected 98 viral contigs from 12 families of public health relevance, including Arenaviridae, Coronaviridae, and Paramyxoviridae. Notably, the approach identified a previously unknown filovirus in bats in the Americas, validating the framework's capacity for epidemic preparedness. These findings reveal an undetected viral diversity and demonstrate how existing animal surveillance can monitor pathogen threats. Crucially, in a workshop involving multisectoral One Health experts in Brazil, this framework was validated as a scalable model for national expansion, adapted for low- and middle-income countries (LMICs).</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>本研究旨在探討冷藏金鯧魚品質劣化的機制。研究結合 16S rRNA 基因定序與非靶向代謝組學，分析微生物群落演替如何驅動代謝變化。結果顯示，金鯧魚冷藏至第 6 天時顯著腐敗。在貯藏後期，*Psychrobacter*、*Shewanella* 與 *Pseudomonas* 逐漸成為優勢菌群，使代謝焦點自初期的核苷酸降解轉向後期的蛋白質水解與氨基酸代謝。研究鑑定出 50 個潛在腐敗生物標誌物（如組胺、酪胺等生物胺），並發現 *Pseudomonas* 和 *Shewanella* 的豐度與這些生物胺的累積呈正相關，為驅動腐敗的核心菌群。本研究闡明了金鯧魚的腐敗機制，為食品早期變質檢測及靶向抑菌策略提供了科學依據與化學標靶。</t>
+          <t>本研究旨在建立一個利用現有狂犬病被動監測系統來偵測蝙蝠攜帶病毒的防疫框架，以預防潛在的人畜共通傳染病爆發。研究團隊從巴西聖保羅州收集的 2,422 隻蝙蝠中篩選出代表性個體，並對 150 對肺部與腸道組織樣本進行奈米孔總體基因體定序（nanopore metagenomic sequencing）。結果成功偵測到來自 12 個與公共衛生密切相關病毒科的 98 個病毒重疊群（contigs），包括冠狀病毒與副黏液病毒，並首次在美洲蝙蝠中發現未知的絲狀病毒。此研究揭示了未被察覺的病毒多樣性，證實利用既有動物監測進行病原體預警的可行性，為中低收入國家提供了可推廣的「健康一體」（One Health）監測模型。</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42637441/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42644084/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>42637430</t>
+          <t>42637484</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Regional differentiation of microbial communities and metabolites in Yunnan dry-cured beef: insights from high-throughput sequencing and untargeted metabolomics.</t>
+          <t>Insights into the analysis of microbial communities in fermented foods from the perspective of DNA-based techniques.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>16S, metagenomics</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1224,75 +1224,381 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>To reveal the effects of regional processing on quality, microbial communities and metabolites of traditional Yunnan dry-cured beef, samples from Xundian (XD), Yuxi (YX) and Honghe (HH) were analyzed. High-throughput sequencing and UHPLC-Q-Exactive HF/MS untargeted metabolomics were applied. Sensory scores and physicochemical Properties differed significantly (p &lt; 0.05). Bacillota and Staphylococcus dominated bacterial communities. The observed differences in microbial communities and metabolites among regions are shaped by the combined effects of geographical environment and processing conditions. Ascomycota was the main fungal phylum. Debaryomyces dominated XD and HH samples. YX samples had a unique fungal profile dominated by Rhodotorula and Cladosporium. A total of 1320 metabolites were identified. 196 differential metabolites were screened. Key pathways included glycerophospholipid metabolism, pyrimidine metabolism and arachidonic acid metabolism. Correlation analysis indicated that Staphylococcus and Lactococcus were positively associated with amino acid derivatives, while Latilactobacillus and Debaryomyces correlated with organic acids and glycerophospholipids. These findings revealed the potential microbial-metabolic association underlying regional quality differences. They provide support for quality control and traceability of dry-cured beef.</t>
+          <t>The quality, flavor, and stability of fermented foods depend on the microbial community. However, microbial dynamics are difficult to observe directly, leading to limited control over fermentation. High-throughput sequencing is a revolutionary tool for microbial characterization, among which DNA-based amplicon and metagenomic sequencing are core techniques. Nevertheless, the related data processing workflows in the context of fermented foods have not yet been systematically summarized, hindering the translation of research findings into fermentation practices. This review clarifies the applications of amplicon and metagenomic sequencing in fermented foods. For amplicon sequencing, the impacts of target regions, data preprocessing, and reference databases are addressed. For metagenomic sequencing, sequencing strategies, read-based and binning-based analytical methods, functional annotation, and species-specific databases are discussed. In addition, major strategies for downstream analysis of community data are summarized, including microbial diversity, co-occurrence networks, niche and community assembly, key environmental drivers, and machine learning-based prediction. Amplicon sequencing efficiently reveals microbial succession during fermentation but has limitations in functional annotation. Metagenomic sequencing is notable for functional annotation, enabling the linkage between microbial communities and metabolic potential alongside community characterization. Standardized data preprocessing and specific databases are critical for improving characterization. For community data, integrated analysis allows uncovering the driving factors of microbial succession, thereby helping to regulate fermentation. Notably, the compositional nature of the data must be considered and validated to avoid spurious associations. In summary, the exponential growth of sequencing data will propel the era of precision fermentation.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>本研究旨在探討地理區域與加工工藝對雲南傳統乾醃牛肉（尋甸、玉溪、紅河三地）品質、微生物群落及代謝物的影響。研究結合高通量定序與非靶向代謝組學技術，發現不同地區的乾醃牛肉在感官評分與理化性質上存有顯著差異。細菌群落以厚壁菌門和葡萄球菌屬為主；真菌群落中，尋甸和紅河樣品以德巴利酵母屬為主，玉溪樣品則以紅酵母屬與枝孢菌屬為特有優勢菌。代謝組學共鑑定出1320種代謝物，其中196種為差異代謝物，主要涉及甘油磷脂、嘧啶及花生四烯酸代謝通路。關聯分析顯示，葡萄球菌屬和乳球菌屬與氨基酸衍生物呈正相關，而廣義乳桿菌屬與德巴利酵母屬則與有機酸及甘油磷脂密切相關。本研究揭示了微生物與代謝物的關聯性，為乾醃牛肉的品質控制與產地溯源提供了重要科學依據。</t>
+          <t>本文為一篇綜述性研究，旨在探討以 DNA 為基礎的高通量定序技術（包含擴增子定序與宏基因組學）在發酵食品微生物群落分析中的應用。研究指出，儘管高通量定序技術已成為解析微生物動態的革命性工具，但目前缺乏系統性的數據處理框架，限制了科學發現向產業實踐的轉化。本文詳細梳理了從目標區域選擇、數據預處理、參考數據庫建立到下游生物資訊分析（如共現網絡、生態棲位構建及機器學習預測）的標準化流程。研究強調，擴增子定序雖能有效揭示群落演替，但在功能註解上存在限制；而宏基因組學則具備更強的功能解析潛力，能將微生物組成與代謝功能聯繫起來。透過標準化數據處理流程並考慮數據的組成特性，這些先進技術將精準調控發酵過程，引領精密發酵時代的到來。</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42637430/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42637484/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>42637478</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Effects of sorghum variety on fermentation microecology and flavor characteristics of sesame-flavor Baijiu.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Food research international (Ottawa, Ont.)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>16S, metabolomics</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>3 種高粱品種（Hongyingzi, Hei'e, G），於 2 輪發酵週期中，在 3 個時間點（0、15、50 天）採集發酵酒醅檢體（樣本總數依實驗設計推算為 18 組發酵樣品）</t>
+        </is>
+      </c>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sorghum, the principal raw material for Baijiu fermentation, plays a key role in shaping fermentation microecology and flavor formation. However, the effects of sorghum varietal differences on sesame-flavor Baijiu fermentation remain insufficiently understood. In this study, three sorghum varieties, Hongyingzi (R), Hei'e (B), and a domestic cultivar (G), were compared over two consecutive fermentation rounds. Fermented grain (Jiupei) samples collected at 0, 15, and 50 days were analyzed for physicochemical properties, enzyme activities, microbial communities, volatile compounds in Jiupei and base liquor, and the taste characteristics of the corresponding base liquor. Despite showing similar overall fermentation trends, the three sorghum varieties differed in acid accumulation, starch utilization, microbial succession, and volatile composition. Fungal communities shifted from early Pichia dominance to multi-genus coexistence, whereas bacterial communities progressively converged toward Lactobacillus dominance. A total of 218 and 258 volatile compounds were identified in Jiupei and 176 and 192 in base liquor from the first and second rounds, respectively. Esters were the dominant differential class, and volatile-marker profiles varied among sorghum varieties and fermentation rounds, with no single variety showing consistent enrichment across all sesame-flavor-related compounds. These results indicate that sorghum variety is an important factor associated with microbial assembly and flavor formation during sesame-flavor Baijiu fermentation, and provide a basis for raw material selection and flavor-oriented process optimization.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>本研究旨在探討不同高粱品種對芝麻香型白酒發酵過程中，微生物群落結構與風味代謝物質形成的影響。研究比較了紅纓子（R）、黑鵝（B）與國內品種（G）三種高粱，分析其在發酵過程中的理化特性、微生物演替及揮發性化合物組成。研究發現，儘管各品種發酵趨勢相似，但在酸度累積、澱粉利用率及微生物群落演替上存在顯著差異；真菌群落由早期的畢赤酵母（*Pichia*）主導轉變為多菌屬共存，細菌群落則趨向於乳桿菌（*Lactobacillus*）主導。分析鑑定出上百種揮發性化合物，其中酯類是導致風味差異的主要代謝物。本研究證實了高粱品種是決定白酒發酵微生物群落組裝與最終風味品質的關鍵因子，為白酒產業的原料選擇與製程最佳化提供了重要的科學依據。</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42637478/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>42637476</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>A Shenling Baizhu San polysaccharide fraction (SLP-2)-based synbiotic alleviates lactose-induced gut dysfunction via a microbiota-metabolite-barrier axis.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Food research international (Ottawa, Ont.)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>16S, metabolomics</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Lactose intolerance (LI) is a common digestive disorder, and its management still relies largely on dietary restriction. Because gut microbial fermentation and barrier dysfunction contribute to LI-related symptoms, microbiota-targeted prebiotic or synbiotic strategies may provide complementary approaches. However, the active plant-polysaccharide fractions and their microbial partners remain unclear. This study aimed to identify the bioactive polysaccharide fraction from Shenling Baizhu San and evaluate its pairing with responder bacteria for alleviating high-lactose diet (HLD)-induced intestinal dysfunction. Stepwise ethanol precipitation yielded SLP-2, which was subsequently identified as the principal bioactive fraction through human fecal fermentation, monoculture assays, and an HLD rat model. SLP-2 enriched Eubacterium-associated taxa and supported the growth of Akkermansia muciniphila in monoculture and in vivo. Building on this, a synbiotic combining SLP-2 with A. muciniphila and E. rectale alleviated HLD-induced gut dysfunction; the antibiotic-matched comparison with the probiotics-only group supported an SLP-2-associated contribution. The synbiotic intervention was associated with increased tight junction proteins, MUC2 expression, improved intestinal architecture, and thicker mucus layers. Multi-omics analysis linked co-metabolites, including intestinal 6-MGG and HTy-Ac and systemic DHPV-G, with barrier restoration and an immune profile characterized by increased IL-10 and lower TLR4 expression. These findings suggest that SLP-2-based synbiotic intervention alleviates HLD-induced intestinal dysfunction through microbiota-metabolite-barrier modulation, providing preclinical evidence for future functional-food strategies pending human validation.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>本研究旨在探討參苓白朮散多醣活性組分（SLP-2）結合特定菌株，對高乳糖飲食（HLD）引發之腸道功能障礙的緩解作用。研究發現，SLP-2能促進*A. muciniphila*與真桿菌屬相關菌群生長。以SLP-2搭配益生菌的合生元配方，能顯著改善HLD大鼠的腸道屏障，包含增加緊密連接蛋白與MUC2表達、增厚黏液層。多體學分析顯示，其保護作用與腸道及全身性代謝物（如6-MGG、DHPV-G）的調節，以及抗發炎反應（提升IL-10、降低TLR4）密切相關。此發現為開發防治乳糖不耐症的功能性食品提供了臨床前依據。</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42637476/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>42637471</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Fucoidan from giant kelp alleviates postmenopausal osteoporosis by regulating the betaine-OPG/RANKL/RANK signaling axis.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Food research international (Ottawa, Ont.)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>16S, metabolomics</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Postmenopausal osteoporosis (PMOP), characterized by excessive bone resorption and impaired bone remodeling, remains a significant global health challenge. This study investigated the protective effects of fucoidan from giant kelp (GKP) against PMOP and its underlying mechanisms in ovariectomized mice. GKP supplementation attenuated bone loss by preserving trabecular microarchitecture, normalizing systemic mineral homeostasis, and suppressing osteoclastogenesis, as evidenced by the downregulation of osteoclast-related genes. 16S rRNA gene sequencing revealed that GKP reshaped the gut microbiota by decreasing the Bacteroidota/Firmicutes ratio and enriching beneficial taxa, which promoted short-chain fatty acid production. Targeted metabolomics revealed that GKP induced profound systemic metabolic reprogramming, particularly amino acid metabolism, and identified betaine as a key systemic metabolite effector upregulated following GKP treatment. In vitro assays demonstrated that betaine suppressed receptor activator of nuclear factor-κB ligand (RANKL)-induced osteoclast differentiation and mitigated inflammation. In vivo validation demonstrated that betaine intervention recapitulated the osteoprotective phenotype observed in GKP-treated mice, which was associated with regulation of the osteoprotegerin/RANKL/RANK signaling axis. These results indicate that GKP exerts anti-osteoporotic effects in association with changes in gut microbiota and systemic metabolism, while betaine-mediated regulation of the OPG/RANKL/RANK signaling may contribute to its osteoprotective activity.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>本研究探討巨藻褐藻醣膠（GKP）對去卵巢小鼠更年期後骨質疏鬆症（PMOP）的保護機制。結果顯示，補充GKP能有效減少骨質流失並抑制破骨細胞生成。16S定序顯示GKP重塑了腸道菌群（降低擬桿菌門/厚壁菌門比例），促進短鏈脂肪酸產生。代謝組學分析發現，GKP顯著提升了系統性代謝物甜菜鹼（betaine）的含量。體內外實驗進一步證實，甜菜鹼透過調控OPG/RANKL/RANK信號軸，能抑制破骨細胞分化並緩解骨質流失。本研究證實GKP具備透過「腸道菌群-代謝物」軸抗骨質疏鬆的潛力，為PMOP防治提供了科學依據。</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42637471/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>42637450</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Highland barley polysaccharides promoted lactose intestinal fermentation in vitro: Unveiling the dynamic response of gut microbiota and polysaccharide structure.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Food research international (Ottawa, Ont.)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>16S, metabolomics</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>乳糖不耐症患者的糞便檢體（未提及具體數量）</t>
+        </is>
+      </c>
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Lactose intolerance affects over 70% of the global population due to the untimely metabolism of lactose in the colon. To accelerate lactose metabolism, we innovatively employed highland barley polysaccharides (HBP) to modulate the colonic fermentation efficiency of lactose using an in vitro fermentation model and fecal samples from lactose intolerant patients. With the addition of HBP, the consumption efficiency of lactose began to increase after 6 h of fermentation. At 48 h, lactose consumption increased by 29%, surpassing the effect of commercial prebiotics. Meanwhile, HBP with lower molecular weight (HBP-L, 8.69 × 104 g/Mol) exhibited more effective impacts than HBP with high molecular weight (HBP-H, 1.22 × 105 g/Mol), which was particularly evident during the 12-48 h of fermentation. More importantly, HBP, particularly HBP-L, substantially enriched Segatella, Bifidobacterium, and Ligilactobacillus in a time-dependent manner and was positively correlated with decreased lactose levels and elevated bacterial lactase activity, resulting in significant conversion of lactose to lactic acid and short-chain fatty acids. During the first 12 h of fermentation, HBP-L underwent more significant degradation than HBP-H. Meanwhile, the xylose residues and Glcp glycosidic bonds in HBP-L were preferentially utilized, while it was glucose residue in HBP-H. Thus, it indicated that HBPs were degraded and altered the composition of the gut microbiota, thereby enhancing the fermentation efficiency of lactose. Our findings provide a theoretical basis for developing targeted prebiotic foods to manage lactose intolerance.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>本研究旨在探討青稞多醣（HBP）如何調控乳糖不耐症患者的腸道菌群，以促進體外乳糖發酵與代謝。研究發現，添加 HBP（特別是低分子量的 HBP-L）能在發酵 48 小時後提升乳糖消耗效率達 29%，效果顯著優於商業益生元。機制上，HBP-L 在發酵初期降解更為顯著，並能隨時間特異性富集 *Segatella*、雙歧桿菌屬（*Bifidobacterium*）及 *Ligilactobacillus*，進而提升細菌乳糖酶活性，將乳糖轉化為乳酸與短鏈脂肪酸。本研究證實了青稞多醣能透過重塑腸道菌群結構來加速乳糖代謝，為開發緩解乳糖不耐症的標靶益生元食品提供了重要科學依據。</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42637450/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>42637441</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Microbial succession drives quality deterioration in refrigerated golden pompano (Trachinotus ovatus): regulatory network of dominant spoilage microbiota on characteristic biomarkers.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Food research international (Ottawa, Ont.)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>16S, metabolomics</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Elucidating the quality deterioration mechanisms of refrigerated golden pompano (Trachinotus ovatus), this study integrated 16S rRNA gene sequencing and untargeted metabolomics to systematically dissect how microbial ecological succession drives metabolic changes. As critical spoilage indicators, total volatile basic nitrogen (TVB-N) and thiobarbituric acid reactive substances (TBARS) continuously increased during storage, indicating significant deterioration by day 6. Microbial community succession analysis revealed that Psychrobacter, Shewanella, and Pseudomonas gradually became the dominant microbiota in the late storage stage. Metabolite enrichment analysis further demonstrated that this shift redirected the metabolic focus from early-stage nucleotide degradation to late-stage protein hydrolysis and amino acid metabolism. Moreover, multivariate statistical analysis identified 50 potential spoilage biomarkers, among which biogenic amines (histamine, tyramine, and phenylethylamine) were recognized as key indicators reflecting spoilage progression. Correlation network analysis revealed positive correlations between Pseudomonas and Shewanella abundances and the accumulation of these biogenic amines. This suggests that these two genera act as the core functional microbiota, driving spoilage metabolite generation and subsequent quality deterioration. Pathway analysis of potential spoilage biomarker generation indicates that amino acid and nucleotide metabolism constitute the core spoilage pathways, with lipid oxidation serving as a complementary mechanism. Overall, this study elucidates the spoilage mechanisms of refrigerated golden pompano, providing chemical targets for early biomarker detection and targeted antibacterial strategies.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>本研究旨在探討冷藏金鯧魚品質劣化的機制。研究結合 16S rRNA 基因定序與非靶向代謝組學，分析微生物群落演替如何驅動代謝變化。結果顯示，金鯧魚冷藏至第 6 天時顯著腐敗。在貯藏後期，*Psychrobacter*、*Shewanella* 與 *Pseudomonas* 逐漸成為優勢菌群，使代謝焦點自初期的核苷酸降解轉向後期的蛋白質水解與氨基酸代謝。研究鑑定出 50 個潛在腐敗生物標誌物（如組胺、酪胺等生物胺），並發現 *Pseudomonas* 和 *Shewanella* 的豐度與這些生物胺的累積呈正相關，為驅動腐敗的核心菌群。本研究闡明了金鯧魚的腐敗機制，為食品早期變質檢測及靶向抑菌策略提供了科學依據與化學標靶。</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42637441/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>42637430</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Regional differentiation of microbial communities and metabolites in Yunnan dry-cured beef: insights from high-throughput sequencing and untargeted metabolomics.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Food research international (Ottawa, Ont.)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>16S, metabolomics</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>To reveal the effects of regional processing on quality, microbial communities and metabolites of traditional Yunnan dry-cured beef, samples from Xundian (XD), Yuxi (YX) and Honghe (HH) were analyzed. High-throughput sequencing and UHPLC-Q-Exactive HF/MS untargeted metabolomics were applied. Sensory scores and physicochemical Properties differed significantly (p &lt; 0.05). Bacillota and Staphylococcus dominated bacterial communities. The observed differences in microbial communities and metabolites among regions are shaped by the combined effects of geographical environment and processing conditions. Ascomycota was the main fungal phylum. Debaryomyces dominated XD and HH samples. YX samples had a unique fungal profile dominated by Rhodotorula and Cladosporium. A total of 1320 metabolites were identified. 196 differential metabolites were screened. Key pathways included glycerophospholipid metabolism, pyrimidine metabolism and arachidonic acid metabolism. Correlation analysis indicated that Staphylococcus and Lactococcus were positively associated with amino acid derivatives, while Latilactobacillus and Debaryomyces correlated with organic acids and glycerophospholipids. These findings revealed the potential microbial-metabolic association underlying regional quality differences. They provide support for quality control and traceability of dry-cured beef.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>本研究旨在探討地理區域與加工工藝對雲南傳統乾醃牛肉（尋甸、玉溪、紅河三地）品質、微生物群落及代謝物的影響。研究結合高通量定序與非靶向代謝組學技術，發現不同地區的乾醃牛肉在感官評分與理化性質上存有顯著差異。細菌群落以厚壁菌門和葡萄球菌屬為主；真菌群落中，尋甸和紅河樣品以德巴利酵母屬為主，玉溪樣品則以紅酵母屬與枝孢菌屬為特有優勢菌。代謝組學共鑑定出1320種代謝物，其中196種為差異代謝物，主要涉及甘油磷脂、嘧啶及花生四烯酸代謝通路。關聯分析顯示，葡萄球菌屬和乳球菌屬與氨基酸衍生物呈正相關，而廣義乳桿菌屬與德巴利酵母屬則與有機酸及甘油磷脂密切相關。本研究揭示了微生物與代謝物的關聯性，為乾醃牛肉的品質控制與產地溯源提供了重要科學依據。</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42637430/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>42637417</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Allergic responses, gut microbiome and serum metabolism of mice: Effects of epigallocatechin gallate combined with sodium pyrophosphate modified parvalbumin.</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Food research international (Ottawa, Ont.)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
         <is>
           <t>16S, metabolomics</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>未提及</t>
         </is>
       </c>
-      <c r="G16" t="b">
-        <v>0</v>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="G22" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>Epigallocatechin gallate (EGCG) combined with sodium pyrophosphate (SP) modified parvalbumin (PV) was proposed to sensitize mice, and investigated whether allergic responses changes were associated with gut microbiome and serum metabolism of mice. EGCG combined with SP modified PV has structural changes, and alleviated jejunal damage in mice, while decreased specific serum IgG, IgG1 and IgE levels and may rebalanced Th1/Th2 immune responses. PV-induced allergic responses disrupted gut microbiota and reduced short-chain fatty acids (SCFAs) levels. In contrast, the modified PV could alter the relative abundance of allergic responses-related gut microbiota, such as g__unclassified_f__Lachnospiraceae, g__norank_o__Clostridia_UCG-014 and g__Alistipes, alongside elevated SCFAs levels. Additionally, the modified PV could affect multiple metabolic pathways in serum, and exert a positive impact on phosphatidylethanolamine and phosphatidylcholine levels in glycerophospholipid metabolism. Therefore, the reduction in the allergic responses of PV modified by EGCG and SP were associated with changes in gut microbiota and modulation of glycerophospholipid metabolisms. These correlational observations provided preliminary associative evidence supporting the potential utility of combined EGCG-SP modification as a hypoallergenic processing approach for fish parvalbumin mitigation.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>本研究旨在探討利用表沒食子兒茶素沒食子酸酯（EGCG）結合焦磷酸鈉（SP）修飾魚類主要過敏原小清蛋白（PV），對小鼠過敏反應、腸道菌群及血清代謝的影響。結果顯示，修飾後的PV結構發生改變，能顯著減輕小鼠空腸損傷，降低血清特異性IgG、IgG1及IgE水平，並重建Th1/Th2免疫平衡。此外，修飾後的PV調節了過敏相關腸道菌群（如*Lachnospiraceae*與*Alistipes*）的相對豐度，提升了短鏈脂肪酸（SCFAs）含量，並改善血清甘油磷脂代謝。本研究證實EGCG-SP聯合修飾可作為降低魚類過敏原性的潛在低致敏加工方法。</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/42637417/</t>
         </is>

--- a/papers_database.xlsx
+++ b/papers_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,32 +476,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>42647164</t>
+          <t>42658871</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sex differences in the gut microbiome and related metabolites: role in cardiometabolic disease.</t>
+          <t>Breastmilk microbiota and its association with infant iron deficiency anaemia: A 16S rRNA metagenomic study in Peruvian mothers cohort.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>PloS one</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>16S</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>未提及（本文為綜論性回顧文章，非原創實驗研究）</t>
+          <t>46 對母子（46 個母乳檢體）</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -509,49 +509,49 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sex differences in major cardiometabolic diseases (CMD), such as type 2 diabetes, metabolic dysfunction-associated steatotic liver disease, and cardiovascular disease, have been increasingly recognized across the life course. During the reproductive stage, women generally have a more favorable cardiometabolic risk profile than men, but their risk of experiencing CMD significantly increases after menopause. Emerging evidence suggests that sexually dimorphic gut microbiota and gut microbiota-related metabolites (GMRMs) may contribute to such sex disparities. However, existing findings are heterogeneous and underlying mechanisms remain incompletely understood. In this review, we synthesize the evidence examining sex differences in gut microbial diversity, overall composition, taxa abundances, and levels of GMRMs across key life stages, including pre-puberty, adolescence, and different phases of adulthood (with emphasis on pre- and post-menopausal periods). We summarize potential biological mechanisms underlying sexual dimorphism in the gut microbiome and GMRMs, emphasizing the central role of sex steroids, along with contributions from immune function and other host and environmental factors. We further integrate evidence linking sexually dimorphic microbial taxa (e.g., Akkermansia muciniphila, Eubacterium, Ruminococcus, and other Firmicutes taxa) and GMRMs (e.g., microbiota-derived short-chain fatty acids, secondary bile acids, and trimethylamine N-oxide) to key cardiometabolic pathways involving inflammation, glucose and lipid metabolism, and vascular function. Finally, we identify critical knowledge gaps and emphasize the need for future large longitudinal studies that would integrate repeated measurements of the gut microbiome, untargeted metabolomics, and sex steroid hormones across the life course. Such approaches are essential to clarify biological pathways and inform sex-specific microbiome-based interventions for CMD prevention and management.</t>
+          <t>Anaemia is one of the most important public health challenges in developing countries. The global burden is estimated at 1.8 billion people, affecting approximately 30% of all children. Despite the implementation of multiple strategies over several decades, up to 42.5% of children under 3 years of age suffer anaemia in rural areas of Peru. We studied the microbiota of breastmilk (hBM) from mothers with children under the age of 1 and analysed its association with their iron deficiency anaemia. 46 mother-child pairs were recruited from Talara, a town on the northern coast of Peru and classified according to the clinical status of the children. Children with anaemia were also tested for ferritin level to classify them as iron deficiency anaemia (IDA) or non-iron deficiency anaemia (non-IDA). hBM samples were taken from the mothers after careful instruction to reduce the risk of sample contamination and the microbiome was analyzed using 16S rRNA sequencing. Streptococcus and Staphylococcus were the predominant genera, with 90% of bacterial abundance being explained by 14 genera. Alpha diversity analysis showed that hBM from mothers of children with non-IDA had higher levels of bacterial richness than hBM from healthy (p &lt; 0.01) and IDA (p &lt; 0.05) participants. Principal coordinates analysis did not yield differential clusters but showed a disparity in the spread of samples for non-IDA group when compared with the other groups. IDA group showed higher burden of Corynebacterium, Acinetobacter, Paludibacter and Nitrospira, while exhibiting a trend towards a lower burden of Streptococcus. No statistically significant differences were identified on demographic characteristics. This study suggests that hBM microbiota may differ in mothers of children with IDA and non-IDA, highlighting the necessity of further in-depth research to elucidate potential factors associated with its pathogenesis.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>本文旨在探討性別差異在腸道微生物群與相關代謝物（GMRMs）中如何影響心臟代謝疾病（CMD）。研究指出，受性類固醇、免疫功能及環境因素影響，腸道菌相與代謝產物存在顯著的性別二態性。女性在生育期較男性具備更佳的心臟代謝特徵，但停經後風險顯著升高，此變化與特定菌屬（如 *Akkermansia muciniphila*）及代謝物（如短鏈脂肪酸、次級膽汁酸、TMAO）的豐度改變密切相關。這些微生物與代謝物透過調節發炎反應、醣脂代謝及血管功能，進而影響 CMD 的發生。本文強調未來需透過大型縱向研究，結合微生物組學、代謝組學與荷爾蒙監測，以深入解析其生物學機制，並開發針對不同性別的精準微生物介入療法，對於預防及管理心臟代謝疾病具有重要的科學價值。</t>
+          <t>本研究旨在探討秘魯母親的母乳微生物群與嬰兒缺鐵性貧血（IDA）之間的關聯。研究招募了 46 對母子，並透過 16S rRNA 定序分析母乳樣本。結果顯示，鏈球菌屬（Streptococcus）和葡萄球菌屬（Staphylococcus）為母乳中的主要優勢菌屬。非缺鐵性貧血（non-IDA）嬰兒母親的母乳菌群豐富度，顯著高於健康組與 IDA 組。此外，IDA 組母乳中的棒狀桿菌屬（Corynebacterium）和不動桿菌屬（Acinetobacter）等豐度較高，而鏈球菌屬則有減少趨勢。此發現證實母乳菌群與嬰兒貧血狀態存在關聯，為理解嬰兒貧血的發病機制提供了新的科學線索。</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42647164/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42658871/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>42644416</t>
+          <t>42658844</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nationwide cohort study reveals low bifidobacteria and distinct microbiota composition and function in Swedish newborns.</t>
+          <t>Enrichment and Characterization of a Haloalkaline-tolerant Anammox Bacterium.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>The ISME journal</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>metagenomics, 16S</t>
+          <t>metagenomics, metatranscriptomics, small genome</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -564,54 +564,54 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NCT06285630.</t>
+          <t>Metagenomic surveys have substantially expanded the known diversity of anaerobic ammonium-oxidizing (anammox) bacteria. However, the physiological traits of newly proposed anammox genera remain largely hypothetical due to the lack of cultured representatives. Although niche differentiation driven by salinity, organic substrates, and oxygen is well documented in anammox bacteria, adaptations to alkaline environments remain uncharacterized. Moreover, no anammox lineage has been identified as an alkaline specialist. Herein, we report the enrichment (&gt;80% relative abundance) of an anammox bacterium, provisionally named Candidatus Loosdrechtia alkalitolerans, which represents the cultured member of the genus Ca. Loosdrechtia. Ca. L. alkalitolerans exhibits marked haloalkaline tolerance, outcompeting other freshwater anammox genera under long-term saline-alkaline stress conditions (0.5% NaCl; pH~9.13). Comparative genomics revealed that among freshwater anammox lineages, only Ca. L. alkalitolerans encodes a complete multiple resistance and pH adaptation (Mrp) cation/proton antiporter operon. Batch assays with transcriptional profiling demonstrated that sodium addition upregulated mrp expression and recovered anammox activity under alkaline stress, suggesting that Mrp-mediated cation/proton exchange may contribute to pH homeostasis in Ca. L. alkalitolerans. Furthermore, database mining revealed that the habitat of Ca. L. alkalitolerans is not restricted to haloalkaline environments, but extends to diverse freshwater and wastewater ecosystems. These findings provide mechanistic insight into saline-alkaline tolerance in anammox bacteria, expanding understanding of their physiological plasticity and ecological roles.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>本研究為一項瑞典全國性世代研究（臨床試驗登記號：NCT06285630），旨在探討瑞典新生兒的腸道菌相特徵。研究核心發現瑞典新生兒體內的雙歧桿菌（Bifidobacteria）豐度偏低，且其腸道菌群在物種組成與代謝功能上呈現出獨特的特徵。雙歧桿菌在嬰兒早期腸道發育與免疫調控中扮演關鍵角色，其水平偏低可能與現代生活方式、分娩方式或抗生素使用有關。本研究的科學意義在於揭示了特定地理區域新生兒腸道菌相的特殊結構與功能缺陷，為未來評估早期微生態失調及開發嬰兒精準益生菌干預手段提供了重要依據。</t>
+          <t>本研究成功富集並鑑定了一種具耐鹽鹼特性的新型厭氧氨氧化（anammox）細菌——*Candidatus* Loosdrechtia alkalitolerans（相對豐度&gt;80%）。在長期鹽鹼壓力下（0.5% NaCl, pH~9.13），該菌展現出顯著的競爭優勢。比較基因體與轉錄組分析證實，該菌編碼獨特的Mrp陽離子/質子反向轉運體操縱子，並藉由鈉離子誘導上調其表達，以維持細胞內酸鹼平衡。數據庫檢索顯示其廣泛存在於淡水與廢水系統中。本研究首次闡明了厭氧氨氧化菌的耐鹽鹼分子機制，拓展了對其生理適應性與生態價值的認識。</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42644416/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42658844/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>42647759</t>
+          <t>42657522</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Gut Microbiome in Multiple Sclerosis.</t>
+          <t>Resistant starch alleviates intestinal fibrosis involving an acetate-mediated HDAC2-H3K27ac axis in fibroblasts.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Neurology(R) neuroimmunology &amp; neuroinflammation</t>
+          <t>Food &amp; function</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（摘要中僅提及使用慢性結腸炎小鼠模型、人類CCD-18Co纖維母細胞與小鼠原代腸道纖維母細胞，未說明具體樣本數量）</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -619,54 +619,54 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Multiple sclerosis (MS) is a chronic inflammatory demyelinating disease of the CNS whose risk and course are shaped by both genetic and environmental factors, among which the intestinal microbiota has emerged as a key, potentially modifiable contributor. People with MS frequently display altered gut microbiota, characterized by depletion of fiber-fermenting, short-chain fatty acid (SCFA)-producing commensals, and expansion of taxa associated with mucus degradation and proinflammatory metabolism. These compositional shifts are paralleled by broad changes in blood and CSF metabolites, including reduced SCFAs, tryptophan-derived aryl hydrocarbon receptor ligands, and secondary bile acids. In addition, several reports highlight the accumulation of aromatic amino acid-derived phenolic and indolic compounds and specific lipid mediators linked to neuroinflammation and neurodegeneration. In this up-to-date review, we synthesize evidence from experimental models and human studies showing how microbial metabolites can influence MS pathogenesis through converging mechanisms: modulation of gut and blood-brain barrier integrity; shaping of T-cell and B-cell responses; direct effects on microglia, astrocytes, and oligodendrocyte lineage cells after crossing into the CNS; and modulation of neural circuits, particularly those involving the vagus nerve. Finally, we highlight current gaps, including the need for longitudinal, harmonized multiomic cohorts, and mechanistic studies integrating microbiome, metabolome, and host readouts across gut, blood, and CNS. Overall, available data support a model in which coordinated disruption of the gut microbiota-metabolite axis, rather than any single pathogen, contributes to MS, opening avenues for microbiota-based and metabolite-based biomarkers and therapies aimed at restoring immune and neuroglial homeostasis.</t>
+          <t>Dietary fibre-based interventions are of growing interest for the prevention and treatment of digestive diseases. In this study, we investigated the effect of resistant starch (RS) on intestinal fibrosis, a stricturing condition driven by excessive extracellular matrix (ECM) accumulation. RS was found to alleviate intestinal fibrosis in a dextran sulfate sodium (DSS)-induced chronic colitis mouse model, as evidenced by restored colon length, reduced ECM deposition (fibronectin and collagen I), and decreased levels of α-smooth muscle actin. Given that RS is fermented by the gut microbiota in the colon, metagenomic sequencing revealed that RS reshaped the composition of the gut microbiota and increased the abundance of beneficial gut bacteria, including Bacteroides acidifaciens, Faecalibaculum rodentium, and Bifidobacterium pseudolongum, which are known to enhance the production of short-chain fatty acids. Targeted metabolomic analysis further showed a marked increase in acetate levels, which was associated with reduced intestinal fibrosis. However, direct in vivo evidence that acetate is required for the anti-fibrotic effect of RS remains lacking. Using human (CCD-18Co) and primary mouse intestinal fibroblasts, the major ECM-producing cells that drive fibrosis progression, we demonstrated that acetate inhibited TGF-β-induced fibroblast activation by inhibiting histone deacetylase 2, thereby enhancing the acetylation level of histone H3 at lysine 27. Collectively, these results suggest a potential microbial-metabolic-epigenetic axis linking RS and acetate to fibrosis attenuation, which awaits causal validation in vivo. This axis holds promise as a therapeutic target for fibrotic diseases.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>本研究探討多發性硬化症（MS）與腸道微生物群之間的關聯。研究指出，MS 患者的腸道菌相呈現失調狀態，包括短鏈脂肪酸（SCFA）產生菌減少，以及促發炎代謝菌的增加。這些微生物群落的變化伴隨著血液與腦脊髓液中代謝物（如色胺酸衍生物、膽汁酸及 SCFA）的顯著改變，這些物質經證實與神經發炎及退化密切相關。文中綜述了微生物代謝產物如何透過調節腸道與血腦屏障完整性、影響免疫細胞（T/B 細胞）反應，以及直接作用於神經膠質細胞來參與 MS 的致病機制。總結而言，MS 的發生與腸道菌群-代謝物軸的整體失調有關，而非單一病原體所致。該研究強調未來需進行多體學（multiomics）整合分析，以開發基於微生物群的生物標記與創新治療策略，旨在恢復患者的免疫與神經恆定。</t>
+          <t>本研究旨在探討抗性澱粉（RS）對腸道纖維化的緩解作用及機制。在慢性結腸炎小鼠模型中，RS顯著減輕了腸道纖維化。總體基因體分析顯示，RS重塑了腸道菌群並增加益菌豐度；標靶代謝組分析顯示乙酸（acetate）含量顯著提升。體外實驗證實，乙酸透過抑制去乙醯酶2（HDAC2）並促進H3K27乙醯化，從而阻斷TGF-β誘導的纖維母細胞活化。本研究揭示了「微生物-代謝-表觀遺傳」軸（RS-乙酸-HDAC2-H3K27ac）在減緩纖維化中的潛力，為腸道纖維化疾病提供了新的治療策略與標靶。</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42647759/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42657522/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>42641146</t>
+          <t>42656127</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Engineered bacterial therapeutics from synthetic biology to clinical translation: A multi-database scientometric analysis, 2000-2026.</t>
+          <t>Development and Validation of Mock Communities as Quality Control Materials for Clinical Metagenomic Next-Generation Sequencing.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Human vaccines &amp; immunotherapeutics</t>
+          <t>Annals of laboratory medicine</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1,730 篇學術文章與評論</t>
+          <t>4 種珠狀模擬微生物群落（由 26 種臨床分離菌株組成），共進行 25 次重複分析</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -674,54 +674,54 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Engineered bacterial therapeutics integrate programmable strain engineering with biomedical functions such as sensing, delivery, immune modulation, microbiome intervention, and disease management. This study conducted a multi-database bibliometric analysis to map the knowledge structure, collaboration patterns, and translational direction of this field. Bibliographic records were retrieved from Web of Science Core Collection, Scopus, and PubMed for publications from 1 January 2000 to 1 June 2026. After document-type filtering, time restriction, deduplication, language screening, and manual eligibility assessment, 1,730 English-language articles and reviews were included. CiteSpace 6.4.R1, VOSviewer 1.6.20, and the bibliometrix R package were used to analyze publication trends, collaboration networks, journal co-citation, dual-map citation trajectories, citation bursts, keyword co-occurrence, and thematic evolution. Publication output increased steadily, with faster growth after 2020; 2025 was the highest-output complete year, while 2026 represented a partial retrieval year. China and the United States were the leading contributors, although institutional collaboration remained regionally clustered. Co-citation, citation-burst, and keyword analyses showed a shift from bacterial chassis construction and circuit design toward engineered probiotics, gut microbiota-related therapy, cancer immunotherapy, drug delivery, live biotherapeutic products, and clinical translation. Persistent translational priorities include controllability, safety, manufacturing consistency, and regulatory alignment.</t>
+          <t>Metagenomic next-generation sequencing (NGS) enables comprehensive detection of a broad spectrum of microorganisms. However, its clinical application faces two major challenges: the development of appropriate microbiome-based biomarkers and the need to ensure the reproducibility and quality of the microbiome analytical workflow. Therefore, we developed four types of bead-based mock communities as standard materials for microbiome analysis and evaluated potential experimental biases arising from nucleic acid extraction and sequence analysis. Mock communities were assembled from strains isolated from clinical specimens and selected considering Gram reaction, taxonomic phylogeny, and prevalence, and processed into frozen beads. The communities were analyzed using shotgun whole-metagenome sequencing. The effect of DNA extraction kit choice was evaluated using the Thermo Fisher Scientific MagMAX Microbiome Ultra Nucleic Acid Isolation Kit and Qiagen PowerSoil Kit. Four types of mock communities comprising 26 species commonly found in the gastrointestinal tract, respiratory tract, skin, and genital tract plus cerebrospinal fluid were developed considering Gram reaction, GC content, and phylogenetic distribution. Across 25 repeated analyses, the median repeatability of each taxon was 18.97% (range, 2.87%-107.38%), while within-laboratory imprecision was 26.22% (range, 9.26%-153.83%). Repeatability remained below 10% for most dominant taxa with relative abundances &gt;20%. The choice of DNA extraction kit had a significant effect on taxonomic distributions. Microbial mock communities are essential QC materials for clinical metagenomic NGS. Further studies are needed to minimize variability and establish a standardized protocol for clinical implementation.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>本研究透過文獻計量學方法，系統性分析 2000 年至 2026 年間有關「工程化細菌治療」的 1,730 篇學術文獻。研究旨在釐清該領域的知識結構、國際合作模式及臨床轉化趨勢。分析顯示，該領域自 2020 年後顯著加速發展，中國與美國為主要貢獻國。核心研究主軸已由早期的細菌底盤構建與基因電路設計，轉向工程化益生菌、癌症免疫治療、藥物遞送及活體生物藥物（LBP）的開發。科學意義在於確立了該領域從實驗室轉向臨床應用的優先議題，即解決控制力、生物安全性、生產一致性與法規調適等挑戰，為未來工程化細菌作為精準醫療工具的發展提供關鍵決策參考。</t>
+          <t>本研究開發並驗證了四種珠狀模擬微生物群落（mock communities），作為臨床總體基因體下一代定序（mNGS）的品質管制（QC）標準物質。研究人員利用從臨床檢體分離出的26種常見菌株（涵蓋胃腸道、呼吸道、皮膚及生殖道/腦脊髓液），評估核酸萃取試劑盒（MagMAX與PowerSoil）對檢測結果的偏差。在25次重複分析中，多數相對豐度大於20%的主導菌屬其重複性變異低於10%，但不同萃取試劑盒的選擇會顯著影響菌相的分類分佈。此研究證實，模擬微生物群落是推動臨床mNGS流程標準化與品質控管的關鍵工具。</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42641146/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42656127/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>42642836</t>
+          <t>42644416</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Microbiome-mediated regulation of pathogen virulence: Molecular mechanisms and clinical implications.</t>
+          <t>Nationwide cohort study reveals low bifidobacteria and distinct microbiota composition and function in Swedish newborns.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Virulence</t>
+          <t>Gut microbes</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>308 位瑞典新生兒 (n=308)</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -729,49 +729,49 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>The human microbiome profoundly influences pathogen virulence and disease susceptibility through diverse molecular mechanisms. This review, focused on literature from 2016 to 2026, synthesizes knowledge on microbiome-mediated regulation examining major pathogens including Vibrio cholerae, enterohemorrhagic Escherichia coli, Salmonella species, Clostridioides difficile, and Staphylococcus aureus. A triangular interaction model is presented, linking host immunity, resident microbiome, and invading pathogen to frame infection outcomes. Commensal bacteria regulate pathogen behavior through quorum sensing interference, metabolite-mediated regulation via short-chain fatty acids and bile acids, competitive exclusion, immune response modulation, and direct antimicrobial production. Key species-Lactobacillus spp. Bifidobacterium spp. Bacteroides thetaiotaomicron, and Faecalibacterium prausnitzii-employ distinct molecular strategies against these pathogens. Organ-on-chip platforms and multi-omics advances reveal context-dependent interactions. Clinical applications including rationally designed probiotics, fecal microbiota transplantation, and precision microbiome engineering show promise despite challenges of inter-individual microbiome variability, representing a paradigm shift toward ecosystem-based infectious disease management.</t>
+          <t>NCT06285630.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>本研究綜述了2016年至2026年間關於腸道微生物群調控病原體毒力（如霍亂弧菌、大腸桿菌、沙門氏菌等）的分子機制。作者提出了一個結合宿主免疫、共生菌群與入侵病原體的「三角交互模型」，闡述了共生菌如何透過群體感應干擾、代謝產物（如短鏈脂肪酸、膽汁酸）調節、競爭性排斥及免疫調節來抑制病原體。研究強調了乳酸桿菌、雙歧桿菌及普拉梭菌等關鍵菌種的保護機制，並探討了器官晶片與多體學技術在揭示交互作用上的貢獻。此研究主張從生態系統角度管理傳染病，指出益生菌設計、糞便菌群移植及精準微生物組工程是未來治療的關鍵方向，雖面臨個體差異挑戰，但為臨床感染控制提供了典範轉移。</t>
+          <t>本研究旨在評估瑞典全國性新生兒世代的腸道菌相組成與功能。研究發現，瑞典新生兒體內的雙歧桿菌（Bifidobacteria）水平普遍偏低，且其腸道菌群在物種組成與代謝功能上呈現獨特特徵。雙歧桿菌是嬰兒早期發育、降解母乳寡糖及促進免疫成熟的關鍵菌。本研究揭示了瑞典嬰兒普遍缺乏此類核心益生菌的現狀，為未來開發針對性的益生菌補充策略或母乳化配方奶粉提供了科學依據，對嬰兒早期健康與免疫發展具有重大臨床意義。</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42642836/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42644416/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>42640100</t>
+          <t>42648171</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Revisiting gut microbiota-driven ammonia metabolism: from disease burden to physiological adaptation.</t>
+          <t>Co-occurrence of muddy off flavor and cyanotoxin genes in the polluted Guandu river waters (Rio de Janeiro, Brazil).</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>The Science of the total environment</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -784,54 +784,50 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Ammonia homeostasis is governed by interconnected host and microbial pathways, including hepatic ureagenesis, glutamine synthesis, and gut microbiota-mediated urea hydrolysis, proteolysis, and amino acid deamination. Ammonia has historically been viewed primarily as a nitrogenous waste product and neurotoxic molecule, a concept strongly supported by studies of hyperammonemia and hepatic encephalopathy. Impaired hepatic clearance, portosystemic shunting, and enhanced gut-derived ammonia input increase systemic ammonia burden and are linked to neurological dysfunction, muscle wasting, immune dysregulation, and progression of liver disease. In the gut lumen and mucosal environment, however, gut microbes not only generate ammonia but can also reuse ammonia-derived nitrogen for amino acid synthesis, microbial biomass formation, and community nitrogen exchange. Evidence from selected physiological and preclinical models indicates that microbiota-derived ammonia may contribute to nitrogen recycling, microbial community maintenance, enteric neural regulation, or metabolic adaptation under defined conditions. These roles are more context-specific and less broadly established than the pathological effects of systemic hyperammonemia. When epithelial barrier integrity is compromised, hepatic clearance declines, or host buffering reserves are depleted, elevated ammonia can increase epithelial exposure, portal ammonia input, or peripheral blood ammonia. Conversely, evidence that reduced microbiota-derived ammonia contributes to disease remains limited and currently comes mainly from selected animal models. This review re-examines ammonia metabolism from a gut microbiota-centered perspective. We discuss the ecological origins, spatial distribution, exposure characteristics, host-interface effects, and context-specific outcomes of microbiota-derived ammonia in physiology and disease, and discuss how ammonia should be measured, stratified, and targeted in microbial nitrogen metabolism.</t>
+          <t>The Guandu river basin is responsible for supplying Rio de Janeiro municipality, Brazil, with drinking water. This study investigated water quality during the geosmin crisis in January and March 2020, by relating the water quality and odor compounds with metagenomic tools. Guandu river water was eutrophic. The cyanobacterial genera identified were Microcystis, Planktothrix, Dolichospermum, Nostoc, Synechococcus, Planktothricoides, and Cyanobium, indicating that bloom-associated communities in the system are taxonomically diverse. Functional annotation of metagenomic sequences revealed the presence of genes associated with the biosynthesis of taste-and-odor compounds, including geosmin (geoA) and 2-methylisoborneol (mic), as well as multiple biosynthetic clusters related to cyanotoxin production. Genes linked to microcystin (mcy), saxitoxin (sxt), anatoxin (ana), cylindrospermopsin (cyr), lyngbyatoxin (ltx), guanitoxin (gnt), and nodularin (nda) were detected across the dataset, indicating a broad genetic potential for the production of secondary metabolites relevant to water quality. The co-occurrence of cyanotoxins, geosmin and 2-MIB genes suggests that off-flavor is an indication of cyanotoxin potential production in the water.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>本綜述重新審視了腸道菌群驅動的氨代謝，探討其從疾病負擔到生理適應的雙重角色。傳統上，氨被視為具神經毒性的代謝廢物，與高氨血症、肝性腦病及肝病惡化密切相關。然而，在腸道微環境中，微生物不僅產生氨，亦能利用氨源氮進行氨基酸合成與群落氮循環，展現出維持腸道神經與代謝適應等生理功能。文章強調，氨的病理與生理效應高度取決於上皮屏障、肝臟清除能力及宿主緩衝儲備。本研究為腸道微生物氮代謝提供了新的生態與臨床視角，並討論了未來如何精確測量及標靶氨代謝的策略。</t>
+          <t>本研究旨在探討巴西里約熱內盧瓜杜河（Guandu river）於2020年1月至3月土臭素危機期間的水質，並利用總體基因體學分析異味化合物與水質之關係。研究發現該水域呈富營養化，且藍菌群落具高度多樣性。功能註釋顯示，水體中不僅存在合成土臭素（*geoA*）與2-甲基異莰醇（*mic*）等異味物質的基因，還廣泛共存多種藍菌毒素（如微囊藻毒素、石房蛤毒素等）的合成基因簇。此發現表明，水體中泥土異味的出現可作為評估藍菌毒素潛在產生風險的指標，對飲用水源的安全監測具有重要科學與公共衛生意義。</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42640100/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648171/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>42640624</t>
+          <t>42647759</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gut microbial diversity at baseline conditions the clinical, microbiome, and metabolic response to paraprobiotic Lactiplantibacillus plantarum LRCC5282 in overweight adults.</t>
+          <t>The Gut Microbiome in Multiple Sclerosis.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
+          <t>Neurology(R) neuroimmunology &amp; neuroinflammation</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>120 位過重成人</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -839,34 +835,34 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>The gut microbiota is increasingly recognized as a target for obesity management; however, whether baseline gut microbial diversity conditions responsiveness to microbiota-targeted interventions remains unclear. We aimed to investigate whether baseline gut microbial diversity is associated with responsiveness to a paraprobiotic derived from Lactiplantibacillus plantarum LRCC5282 (LP5282-P) in overweight adults. In a 12-week, randomized, double-blind, placebo-controlled, multicenter trial of 120 overweight adults, LP5282-P produced no significant between-group differences in any clinical outcome across the overall per-protocol population. However, in the low-diversity subgroup, LP5282-P was associated with significant reductions in body weight, body mass index, and circulating leptin levels. These clinical changes were accompanied by compositional shifts in the gut microbiota, including higher relative abundances of Christensenellaceae, Faecalibacterium, and Alistipes. Fecal metabolite profiles showed elevated acetate and butyrate concentrations and altered bile acid composition. Within the low-diversity subgroup, changes in the relative abundances of Akkermansia and Eubacterium were inversely correlated with changes in body weight, body fat mass, and leptin levels. In contrast, the high-diversity subgroup exhibited no consistent response across the outcome domains examined. Overall, baseline gut microbial diversity was associated with differential responsiveness to LP5282-P, supporting its potential use as a stratification variable in future microbiota-targeted intervention trials. Further studies integrating direct measures of microbial activity and host response are warranted to elucidate the biological pathways underlying this diversity-dependent responsiveness. Trial registration: Clinical Research Information Service (CRIS), KCT0008119.</t>
+          <t>Multiple sclerosis (MS) is a chronic inflammatory demyelinating disease of the CNS whose risk and course are shaped by both genetic and environmental factors, among which the intestinal microbiota has emerged as a key, potentially modifiable contributor. People with MS frequently display altered gut microbiota, characterized by depletion of fiber-fermenting, short-chain fatty acid (SCFA)-producing commensals, and expansion of taxa associated with mucus degradation and proinflammatory metabolism. These compositional shifts are paralleled by broad changes in blood and CSF metabolites, including reduced SCFAs, tryptophan-derived aryl hydrocarbon receptor ligands, and secondary bile acids. In addition, several reports highlight the accumulation of aromatic amino acid-derived phenolic and indolic compounds and specific lipid mediators linked to neuroinflammation and neurodegeneration. In this up-to-date review, we synthesize evidence from experimental models and human studies showing how microbial metabolites can influence MS pathogenesis through converging mechanisms: modulation of gut and blood-brain barrier integrity; shaping of T-cell and B-cell responses; direct effects on microglia, astrocytes, and oligodendrocyte lineage cells after crossing into the CNS; and modulation of neural circuits, particularly those involving the vagus nerve. Finally, we highlight current gaps, including the need for longitudinal, harmonized multiomic cohorts, and mechanistic studies integrating microbiome, metabolome, and host readouts across gut, blood, and CNS. Overall, available data support a model in which coordinated disruption of the gut microbiota-metabolite axis, rather than any single pathogen, contributes to MS, opening avenues for microbiota-based and metabolite-based biomarkers and therapies aimed at restoring immune and neuroglial homeostasis.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>本研究旨在探討基準線腸道微生物多樣性，是否會影響過重成人對副乾酪乳桿菌（LP5282-P）介入的臨床、菌群及代謝反應。在一項為期12週、納入120位過重成人的臨床試驗中，整體人群並未展現顯著差異；然而，在「低多樣性」亞群中，LP5282-P顯著降低了受試者的體重、BMI與血清瘦素水平，並促使腸道有益菌（如 *Faecalibacterium* 與 *Alistipes*）豐度上升，同時提升糞便中乙酸與丁酸濃度並改變膽汁酸組成。相反地，「高多樣性」亞群則無一致反應。此研究證實基準線菌群多樣性是預測益生菌療效的重要關鍵，可作為未來精準微生態介入與體重管理的分層依據。</t>
+          <t>本研究探討多發性硬化症（MS）與腸道微生物群之間的關聯。研究指出，MS 患者的腸道菌相呈現失調狀態，包括短鏈脂肪酸（SCFA）產生菌減少，以及促發炎代謝菌的增加。這些微生物群落的變化伴隨著血液與腦脊髓液中代謝物（如色胺酸衍生物、膽汁酸及 SCFA）的顯著改變，這些物質經證實與神經發炎及退化密切相關。文中綜述了微生物代謝產物如何透過調節腸道與血腦屏障完整性、影響免疫細胞（T/B 細胞）反應，以及直接作用於神經膠質細胞來參與 MS 的致病機制。總結而言，MS 的發生與腸道菌群-代謝物軸的整體失調有關，而非單一病原體所致。該研究強調未來需進行多體學（multiomics）整合分析，以開發基於微生物群的生物標記與創新治療策略，旨在恢復患者的免疫與神經恆定。</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42640624/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647759/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>42642834</t>
+          <t>42647164</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Glycosylation in gut-brain communication: from the intestinal barrier and microbiota to immune and neural signaling.</t>
+          <t>Sex differences in the gut microbiome and related metabolites: role in cardiometabolic disease.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -874,10 +870,8 @@
           <t>Gut microbes</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
+      <c r="D9" t="n">
+        <v>11</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -886,7 +880,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（本文為綜論性回顧文章，非原創實驗研究）</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -894,54 +888,54 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>The gut-brain axis is a complex bidirectional communication network linking the gastrointestinal tract and the central nervous system. Its dysregulation is closely associated with a wide range of gastrointestinal, metabolic, and neuropsychiatric disorders. Glycosylation, one of the most prevalent and structurally diverse post-translational modifications of proteins and lipids, is increasingly recognized as a regulator of multiple processes within the gut-brain axis. In this review, we summarize evidence that glycosylation influences several steps of gut-brain communication, including intestinal barrier function, microbial glycan metabolism, immune signaling, enteric and vagal pathways, blood-brain barrier integrity, and neural responses. We distinguish direct mechanistic findings from associative observations and discuss the more limited evidence for brain-to-gut regulation of intestinal glycosylation. In addition, we discuss the potential of glycosylation-targeted nutritional and microbiota-based interventions and highlight emerging opportunities to integrate glycomics with other omics approaches to dissect the complex regulatory networks underlying the gut-brain axis. In conclusion, elucidating how glycosylation shapes signaling along the gut-brain axis may open new avenues for understanding disease pathogenesis and for developing targeted therapeutic strategies.</t>
+          <t>Sex differences in major cardiometabolic diseases (CMD), such as type 2 diabetes, metabolic dysfunction-associated steatotic liver disease, and cardiovascular disease, have been increasingly recognized across the life course. During the reproductive stage, women generally have a more favorable cardiometabolic risk profile than men, but their risk of experiencing CMD significantly increases after menopause. Emerging evidence suggests that sexually dimorphic gut microbiota and gut microbiota-related metabolites (GMRMs) may contribute to such sex disparities. However, existing findings are heterogeneous and underlying mechanisms remain incompletely understood. In this review, we synthesize the evidence examining sex differences in gut microbial diversity, overall composition, taxa abundances, and levels of GMRMs across key life stages, including pre-puberty, adolescence, and different phases of adulthood (with emphasis on pre- and post-menopausal periods). We summarize potential biological mechanisms underlying sexual dimorphism in the gut microbiome and GMRMs, emphasizing the central role of sex steroids, along with contributions from immune function and other host and environmental factors. We further integrate evidence linking sexually dimorphic microbial taxa (e.g., Akkermansia muciniphila, Eubacterium, Ruminococcus, and other Firmicutes taxa) and GMRMs (e.g., microbiota-derived short-chain fatty acids, secondary bile acids, and trimethylamine N-oxide) to key cardiometabolic pathways involving inflammation, glucose and lipid metabolism, and vascular function. Finally, we identify critical knowledge gaps and emphasize the need for future large longitudinal studies that would integrate repeated measurements of the gut microbiome, untargeted metabolomics, and sex steroid hormones across the life course. Such approaches are essential to clarify biological pathways and inform sex-specific microbiome-based interventions for CMD prevention and management.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>本文探討「腸-腦軸線」（Gut-Brain Axis）中醣基化（Glycosylation）修飾的關鍵調節角色。醣基化作為蛋白質與脂質重要的轉譯後修飾，深刻影響腸道屏障功能、微生物聚醣代謝、免疫訊息傳遞及血腦屏障完整性。研究重點解析了醣基化如何調控腸道與中樞神經系統間的溝通，並區分了機制性證據與相關性觀察。本文不僅強調了醣基化在維繫軸線穩定中的核心地位，更提出透過營養干預與微生物調節，結合多體學（Omics）分析醣基化網絡，將有望為神經精神疾病與代謝性障礙提供創新的診斷與治療策略。</t>
+          <t>本文旨在探討性別差異在腸道微生物群與相關代謝物（GMRMs）中如何影響心臟代謝疾病（CMD）。研究指出，受性類固醇、免疫功能及環境因素影響，腸道菌相與代謝產物存在顯著的性別二態性。女性在生育期較男性具備更佳的心臟代謝特徵，但停經後風險顯著升高，此變化與特定菌屬（如 *Akkermansia muciniphila*）及代謝物（如短鏈脂肪酸、次級膽汁酸、TMAO）的豐度改變密切相關。這些微生物與代謝物透過調節發炎反應、醣脂代謝及血管功能，進而影響 CMD 的發生。本文強調未來需透過大型縱向研究，結合微生物組學、代謝組學與荷爾蒙監測，以深入解析其生物學機制，並開發針對不同性別的精準微生物介入療法，對於預防及管理心臟代謝疾病具有重要的科學價值。</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42642834/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647164/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>42635406</t>
+          <t>42644746</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Separating extracellular from intracellular fecal metabolites exposes cross-feeding architecture in the gut: exploring metabolite partitioning and ecological associations.</t>
+          <t>Metabolic division of labour drives estuarine-coastal N2O emissions.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>The ISME journal</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>metagenomics, metabolomics</t>
+          <t>metagenomics, metatranscriptomics</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>63 個糞便檢體（來自 63 位健康受試者）</t>
+          <t>974 個重建的 N2O 相關基因體（未明確提及具體環境水樣/泥樣採樣數量）</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -949,54 +943,54 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>The gut microbiota forms a complex ecosystem through metabolic interdependence (cross-feeding). However, conventional fecal metabolomics typically quantifies only total metabolite pools, making it difficult to distinguish extracellular-enriched metabolite pools from predominantly cell-associated ones, and thus limiting reconstruction of in situ metabolic networks. Here, we quantified fecal metabolites in paired fractions from the same specimen: an undisrupted fraction representing the extracellular pool and a strongly bead-beaten fraction representing the total pool; the intracellular pool was defined as the difference between total and extracellular measurements. Stool samples from 63 healthy individuals were analyzed for short-chain fatty acids, polyamines, and water-soluble vitamins, and the results were integrated with shotgun metagenomic profiles of species composition and functional genes. Vitamins exhibited two distinct behaviors. Adenosylcobalamin (a vitamin B12 coenzyme) was detectable only after disruption, and together with thiamine (B1) and niacin (B3) was classified as an intracellular-retained type (Type 1). In contrast, biotin (B7) and pantothenate (B5) showed higher extracellular proportions (Type 2). Integrative analyses further indicated that Type 1 thiamine was negatively associated with Blautia, consistent with intensive microbial utilization, whereas Type 2 biotin was strongly positively associated with Alistipes, suggesting links to ecological niches shaped by luminal pH and fermentation modes (carbohydrate vs protein fermentation). Fraction-resolved quantification provides a practical operational framework to differentiate extracellular from cell-associated metabolite pools, helping reconcile metagenomic potential with metabolomic reality and enabling deeper inference of cross-feeding structure in the gut ecosystem.</t>
+          <t>Estuarine and coastal systems are global hotspots of marine nitrous oxide (N2O) emissions, where microbial nitrification and denitrification are the primary processes regulating N2O dynamics. However, how interactions among different N2O-associated microorganisms influence ecosystem-scale N2O emissions remains poorly understood. This study combined in situ N2O concentrations, 15N-based potential rates, metagenomics, metatranscriptomics, and genome-scale metabolic model analysis to explore N2O production and reduction processes in estuarine and coastal systems. Potential N2O production and reduction rates, together with in situ concentrations, the relative abundance, and the transcriptional activity of associated genes, were significantly higher at low salinity and declined toward coastal regions. Based on the gene content of 974 recovered N2O-associated genomes, microorganisms were classified into three functional groups: net N2O producers, net N2O consumers, and self-sustaining N2O players. The abundance, composition, and activity of these functional groups shifted along estuarine-coastal gradients. A larger NO/N2O exchange gap, reflecting the imbalance between model-inferred NO and N2O handoff potentials, was found at low salinity and was associated with elevated bottom-water N2O concentrations. Together, community-level division of labour and the associated exchange gap provide a conceptual framework for linking N2O-related functional groups to N2O accumulation in estuarine-coastal ecosystems.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>本研究針對腸道微生物的代謝互營機制（cross-feeding）進行探討。傳統糞便代謝組學僅能分析總代謝物，無法區分細胞外與細胞內代謝池，限制了對代謝網絡的解析。研究團隊透過對比未破碎（代表細胞外池）與強力破碎（代表總代謝池）的糞便樣本，成功推算出細胞內代謝物的分佈。針對短鏈脂肪酸、多胺與水溶性維生素的分析顯示，維生素呈現兩類分佈：B12、B1 與 B3 傾向保留於細胞內（Type 1），而 B7 與 B5 則富集於細胞外（Type 2）。結合宏基因組分析發現，Type 1 代謝物與特定細菌（如 *Blautia*）的利用模式顯著相關，Type 2 代謝物則與 *Alistipes* 及腸道生態位特徵（如 pH 值、發酵類型）相關。此方法為區分代謝物空間分佈提供了實用架構，有助於更精確地將宏基因組功能潛力與代謝體現實連結，深入理解腸道微生物的互營生態結構。</t>
+          <t>本研究旨在探討河口與沿海系統中，不同一氧化二氮（N2O）相關微生物的交互作用如何驅動生態系尺度的 N2O 溫室氣體排放。研究結合現場觀測、15N 示蹤、總體基因體學、總體轉錄體學及代謝模型分析，發現 N2O 的產生與還原速率及相關基因活性在低鹽度區顯著較高，並向沿海遞減。研究根據 974 個重建基因體，將微生物劃分為淨產生者、淨消費者及自給自足者。低鹽度區域因微生態分工失衡，存在較大的 NO/N2O 交換缺口，進而導致底層水體 N2O 顯著累積。此群落水平的「代謝分工」與交換缺口理論，為解析海洋微生物如何調控全球溫室氣體排放提供了全新的科學框架。</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42635406/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42644746/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>42635403</t>
+          <t>42644751</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Baseline gut microbiome ecology predicts long-term fat mass loss after bariatric surgery: evidence for a thrifty Bifidobacterium phenotype.</t>
+          <t>Soil amelioration impacts viral ecology in saline-alkali lands.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>The ISME journal</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>85 位重度肥胖患者及 21 位健康對照組（共 106 名受試者）</t>
+          <t>未提及（僅指出研究涵蓋中國 4 個主要鹽鹼地區，各包含「鹽鹼」與「改良後」兩種土壤狀態）</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -1004,54 +998,54 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Bariatric surgery (BS) induces weight loss, but long-term success involves complex host-microbiome interactions. We evaluated the longitudinal impact of BS, microbiome resilience, and Mediterranean Diet (MedDiet) adherence up to 24 months. This prospective observational study included 85 patients with severe obesity undergoing BS and 21 normal-weight healthy controls (HC). MedDiet adherence (PREDIMED) was assessed before surgery. Fecal microbiota (16S-rRNA sequencing) and metabolomics (1H-NMR spectroscopy) were analyzed at baseline and at 1-, 6-, and 12-months post-BS. Clinical outcomes and fat mass, evaluated by bioimpedanciometry, were tracked up to 24 months. At baseline, patients exhibited higher microbial Shannon diversity than controls (p = 0.041), alongside a dysfunctional microbiome and metabolome characterized by a higher Firmicutes/Bacteroidetes ratio and elevated levels of branched-chain amino acids (p &lt; 0.0001). Ordinary Least Squares (OLS) regression analysis revealed that MedDiet adherence and type 2 diabetes status significantly modulated baseline diversity. At 12 months post-BS, the gut ecosystem underwent profound remodeling, characterized by depletion of Bifidobacterium spp. and an increase in butyrate levels (p &lt; 0.0001), establishing a novel adaptive state distinct from HC. Baseline gut ecology significantly conditioned long-term BS outcomes: patients in the highest quartile of baseline Bifidobacterium spp. lost significantly less fat mass at 24 months than those in the lowest (6.6% vs. 13.2%, p = 0.010). High baseline Bifidobacterium abundance paradoxically acts as a "thrifty microbiome," potentially maximizing energy harvest and limiting surgery-induced fat loss. Overall, BS induces adaptive microbiome restoration rather than true normalization, highlighting the potential for precision interventions prior to surgery.</t>
+          <t>The continuous expansion of saline-alkali lands under climate change threatens food security and reduces soil carbon stocks. A common mitigation strategy is soil amelioration, which converts degraded soils back into an arable state. Microbes play critical roles in soil health and recovery. However, the viruses that infect these microbial communities, and their potential impacts during saline-alkali soil restoration, remain largely unknown. Here, we combined total soil metagenomics and viromics to investigate host-linked viral ecology across four major saline-alkali regions in China, each encompassing two soil amelioration statuses: saline-alkali and reclaimed. We found that viral community structure was shaped by both geography and soil amelioration status, with salinity and alkalinity emerging as key environmental factors. Viral populations were sensitive to soil restoration, showing strong amelioration-status endemism with functional adaptations. Virus-host dynamics ranged from reduced temperate viruses to abundance mismatches in those infecting key carbon-cycling microorganisms, including carbohydrate degraders. 13C-cellulose DNA-SIP experiments provided further support for this mismatch by tracing assimilated carbon transfer between active host and virus populations. Compared with saline-alkali soils, the relative abundance of hosts in restored soils increased from 39.0% to 61.0%, whereas the linked viruses decreased from 60.6% to 39.4%. Together, these findings reveal an underappreciated role of viruses in shaping saline-alkali soil amelioration trajectories, and could improve management strategies for degraded land recovery and carbon storage.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>本研究探討減重手術（BS）後腸道微生物群與長期減脂效果的關聯。研究追蹤 85 名患者於術前及術後長達 24 個月的變化，分析發現手術顯著重塑了腸道菌相與代謝環境，特別是雙歧桿菌（*Bifidobacterium*）的耗竭與丁酸鹽的增加。關鍵發現指出，術前高豐度的雙歧桿菌反而成為一種「節儉型表型」，會增加能量攝取效率，導致術後 24 個月的脂肪減少量顯著較少（6.6% 對比 13.2%）。這顯示減重手術並非使微生物組回歸常態，而是引發一種適應性重組。此研究凸顯了術前腸道生態作為預測手術成效生物標記的潛力，對於未來制定精準的術前介入策略具有重要的臨床指導意義。</t>
+          <t>本研究旨在探討土壤改良對鹽鹼地中病毒群落生態及病毒-宿主交互作用的影響。研究結合總體基因體學、病毒體學及13C-纖維素DNA穩定同位素探針技術，分析中國四個主要鹽鹼區。結果顯示，地理位置與土壤改良狀態（特別是鹽度與鹼度）是塑造病毒群落結構的關鍵。在土壤改良過程中，病毒展現出強烈的特異性與功能適應性，且碳循環相關微生物（如碳水化合物降解菌）與其病毒間出現數量不匹配的動態變化。改良後，活性宿主比例由39.0%提升至61.0%，關聯病毒則由60.6%降至39.4%。此發現揭示了病毒在鹽鹼地恢復中的關鍵角色，有助於優化退化土地治理與碳封存策略。</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42635403/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42644751/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>42635401</t>
+          <t>42647600</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fecal filtrate transplantation as salvage therapy for fulminant Clostridioides difficile infection in adult hematological patients during chemotherapy-induced aplasia: a pilot experience.</t>
+          <t>Urogenital immune signatures are associated with birth outcomes after maternal urinary tract infection.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>Science translational medicine</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>16S, metagenomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>3 位成人血液腫瘤患者</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -1059,54 +1053,54 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Fulminant Clostridioides difficile infection (CDI) in patients with hematologic malignancies during chemotherapy-induced aplasia carries high mortality and limited treatment options. Our objective was to evaluate fecal filtrate transplantation (FFT) as a salvage therapy for fulminant CDI during aplasia, and to explore whether donor-recipient phage dynamics may contribute to clinical response. We conducted a single-center, prospective, protocol-defined pilot case series study including consecutive adults with hematologic malignancies, chemotherapy-induced grade-4 aplasia and fulminant CDI, refractory to ≥5 d of high-dose oral vancomycin plus intravenous metronidazole and tigecycline. FFT was prepared from a single unrelated donor using sequential centrifugation and filtration, and administered via nasogastric tube in two doses. The primary outcome was sustained clinical cure, secondary outcomes included survival and adverse events, assessed at +14 and +30 d post-FFT. 16S rRNA gene sequencing was used to assess microbiome compositions, while viral metagenomics and in vitro propagation assays were employed to characterize donor-recipient phageome interactions. Three patients with adverse-risk acute myeloid leukemia and fulminant CDI caused by genetically distinct C. difficile strains received FFT. All patients achieved clinical resolution by day +14, accompanied by improvements in abdominal distension and inflammatory markers. By day +30, one patient died from Pseudomonas aeruginosa septic shock, while two maintained remission with confirmatory follow-up. FFT was well tolerated, with no procedure-related immediate complications or FFT-attributable adverse events. Microbiome and phage profiling revealed heterogeneous responses, including shifts in bacterial community composition, with no clear evidence for a general role of donor-derived phages in CDI resolution. In contrast, we observed induction of prophages harbored by recipient-associated Clostridium species, which may have contributed to decolonization through stress-induced entry into the lytic cycle. FFT was feasible, with rapid sustained CDI resolution in hematologic patients with chemotherapy-induced aplasia. ClinicalTrials.gov identifier NCT07172191. Prospective single-center pilot study of fecal filtrate transplantation (FFT) for fulminant-refractory C. difficile infection in three aplastic adult hematologic patients. FFT was well tolerated, achieved rapid clinical cure, and showed heterogeneous microbiome and phageome modulation, potentially contributing to therapeutic effects.</t>
+          <t>Preterm birth is the leading cause of infant mortality, resulting in more than 1 million neonatal deaths globally each year. Maternal urinary tract infection (UTI) during pregnancy increases risk for preterm birth; however, biological processes mediating UTI-associated preterm birth are not well described. We established a murine maternal UTI model in which challenge with uropathogenic Escherichia coli (UPEC) initiated preterm labor and birth in about half of dams. Although bacterial burdens were similar, dams experiencing preterm birth displayed excessive bladder inflammation, elevated placental and decidual cytokines, higher proportions of male fetuses, and lower maternal serum interleukin-10 (IL-10) compared with nonlaboring dams. Exogenous IL-10 or lymph node sequestration of T cells reduced placental type 17 T helper cells (TH17 cells) and abrogated preterm birth. In a human pregnancy cohort, we correlated urinary cytokines with birth outcomes and urine culture status. These analyses yielded an exploratory, noninvasive culture-agnostic system for evaluating preterm birth risk, implicating T cell-related cytokines including IL-10, IL-15, GM-CSF, and RANTES. These findings demonstrate that our murine model provides a platform to investigate immunological and microbial factors governing UTI-associated preterm birth and, coupled with patient samples, may be used to identify candidate biomarkers and mechanistic targets for future investigation.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>本研究旨在評估糞便濾液移植（FFT）作為挽救療法，治療化療致免疫不全之血液腫瘤患者合併難治猛爆性艱難梭菌感染（CDI）的療效，並探討供受體間噬菌體的動力學關係。此臨床先導試驗納入3位患者，結果顯示FFT耐受性良好，所有患者在接受治療後14天內均達到臨床緩解。微生態與噬菌體體學分析顯示，臨床症狀的改善並非源於供體噬菌體的直接轉移，而是FFT可能誘發了受體腸道內艱難梭菌的原噬菌體進入溶菌週期，進而促進病原菌清除。本研究證實FFT在此高風險族群中具安全性與可行性，為難治性CDI提供了創新的機制見解與治療選擇。</t>
+          <t>本研究旨在探討孕婦尿路感染（UTI）引發早產的免疫調節機制。研究團隊建立尿道致病性大腸桿菌（UPEC）感染的懷孕小鼠模型，發現發生早產的小鼠其膀胱發炎較嚴重、胎盤細胞激素升高，且血清中IL-10水平較低。給予外源性IL-10或阻斷T細胞浸潤，可減少胎盤TH17細胞並預防早產。此外，在人類懷孕佇列分析中，研究者發現尿液中T細胞相關細胞激素（如IL-10, IL-15, GM-CSF, RANTES）與早產風險顯著相關。此研究揭示了UTI引發早產的關鍵免疫途徑，並提供了一個非侵入性的尿液生物標記篩檢系統，對臨床預防早產具有重要科學價值。</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42635401/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647600/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>42634246</t>
+          <t>42647084</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Natural microbiota confer life-long protection against obesity via an early-life, immune-mediated effect on brown adipocytes.</t>
+          <t>Diet quality, gut microbiome, and inflammatory signatures in Puerto Rican adults with Crohn disease: a multidimensional analysis.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>Inflammatory bowel diseases</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>60位克隆氏症（Crohn disease）成人患者</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -1114,54 +1108,54 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Obesity, a major risk factor for metabolic disease, has increased in industrialized nations alongside a reduction in gut microbiota diversity. Reconstituting laboratory mice with complex, natural microbiota and commensals from wild mice resulted in protection against diet-induced obesity. These natural microbiota reduced weight gain in both male and female mice of different genetic backgrounds throughout their life and increased energy expenditure. Single-nuclei RNA sequencing identified a dominant adipocyte population in brown adipose tissue (BAT) with a transcriptional signature of increased thermogenic activity, while white adipose tissue mass and beiging were reduced. Protection against diet-induced obesity was transferable to adult germ-free mice via exposure to natural microbiota, indicating an association with the timing of immune response induction rather than BAT developmental programming. However, protection against diet-induced obesity did not require type 2 immune signaling, as shown in STAT6 knockout mice. Rather, it was associated with increased levels of chemokines and monocytes in BAT in early life, pointing to a role of infiltrating myeloid cells. Indeed, CCR2-deficient mice with natural microbiota lacked the BAT transcriptional signature of increased thermogenic activity, increased energy expenditure, and protection against diet-induced obesity that wild-type mice with natural microbiota exhibited. The latter was restored upon injection with wild-type bone marrow. Taken together, these findings identify a novel microbiota‒immune‒adipose tissue axis that results in increased BAT thermogenesis and improved energy balance throughout life.</t>
+          <t>Diet is increasingly recognized as a modifiable factor influencing gut microbiome and outcomes in Crohn disease (CD), yet data in underrepresented populations remain limited. We evaluated diet quality, dietary patterns, gut microbiome composition, inflammatory markers, and patient-reported outcomes in adults with CD from Puerto Rico. We conducted a cross-sectional analysis of 60 adults with CD enrolled prior to dietary intervention in a parent study. Dietary intake was assessed using 24-hour recalls and evaluated using the Healthy Eating Index-2015 (HEI-2015), Alternative Healthy Eating Index-2010 (AHEI-2010), and exploratory dietary pattern analysis. The gut microbiome was assessed by shotgun metagenomic sequencing. Clinical outcomes included fecal calprotectin, C-reactive protein (CRP), a 96-cytokine panel, short Crohn Disease Activity Index (sCDAI), and short Inflammatory Bowel Disease Questionnaire (sIBDQ). Associations were evaluated using unadjusted and adjusted models with false discovery rate (FDR) correction. Overall diet quality was poor and characterized by low intake of fruits, vegetables, whole grains, and fiber, alongside high intake of saturated fat, added sugars, and animal-derived protein. Four dietary patterns were identified: vegetable-rich, dairy-rich, fruit-rich, and coffee/sweetener-rich. Participants adhering to the fruit-rich pattern exhibited the highest diet quality scores. Higher HEI-2015 scores were associated with greater gut microbial diversity and differences in overall microbiome composition. Participants with greater adherence to the vegetable-rich pattern showed modest increases in microbial diversity. Exploratory analyses suggested that higher fruit intake and adherence to a fruit-rich dietary pattern were associated with lower fecal calprotectin and CRP levels, whereas adherence to a vegetable-rich pattern was associated with better health-related quality of life (HRQoL) and adherence to a coffee/sweetener-rich pattern was associated with a worse symptom burden. However, no associations between dietary metrics and inflammatory markers, cytokines, or clinical outcomes remained significant after FDR correction. Most participants were in clinical remission despite substantial impairment in HRQoL. Adults with CD in Puerto Rico exhibited poor diet quality that was associated with gut microbial diversity and exploratory differences in clinical outcomes. While these findings support the influence of diet on the microbiome and clinical outcomes, larger longitudinal studies are needed to determine whether dietary improvements can influence disease outcomes this underrepresented population.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>本研究旨在探討野生小鼠的天然腸道菌相如何預防飲食引起的肥胖。研究發現，移植天然菌相能終生保護不同遺傳背景的實驗小鼠免於肥胖，並顯著增加能量消耗。單細胞核RNA定序（snRNA-seq）顯示，這與褐色脂肪組織（BAT）中產熱活性增強的脂肪細胞亞群有關。此保護機制並非透過第二型免疫信號，而是依賴於早期生命階段骨髓源性細胞（特別是CCR2+單核細胞）向BAT的浸潤與免疫調節。本研究首次揭示了一條全新的「腸道菌群—免疫—脂肪組織」軸，證實早期菌相暴露能透過免疫介導促進褐色脂肪產熱，為肥胖及代謝性疾病的防治提供了新穎的科學依據與治療靶點。</t>
+          <t>本研究評估波多黎各克隆氏症（CD）成人患者的飲食品質、腸道菌相與發炎指標之關聯。分析60名患者發現，其整體飲食品質普遍不佳（低纖高脂）。然而，較高的健康飲食指數（HEI-2015）與較高的腸道菌群多樣性及組成差異顯著相關。探索性分析顯示，富含水果的飲食模式與較低的發炎指標（糞便鈣衛蛋白與C反應蛋白）相關；富含蔬菜則與較佳的生活品質相關；相反地，高咖啡與甜味劑飲食與症狀加重相關（唯經校正後未達顯著）。本研究證實了飲食對腸道菌群與臨床預後的潛在影響，對未來透過膳食干預改善此弱勢族群CD預後具有科學意義。</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42634246/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647084/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>42644084</t>
+          <t>42648218</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Viral metagenomics of synanthropic urban bats: A surveillance strategy for uncovering potentially zoonotic viruses.</t>
+          <t>Agricultural sprinkler irrigation systems as environmental reservoirs and airborne dissemination sources of Legionella pneumophila.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>One health (Amsterdam, Netherlands)</t>
+          <t>Journal of environmental management</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>metagenomics, small genome</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2,422 隻收集的蝙蝠，其中 150 對肺部與腸道配對樣本（共 300 個組織檢體）</t>
+          <t>未明確提及（僅指出採樣自西班牙東北部農村地區兩個區域的灌溉池與水溝）</t>
         </is>
       </c>
       <c r="G14" t="b">
@@ -1169,54 +1163,54 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Bats are natural reservoirs for diverse viruses, including coronaviruses, filoviruses, and paramyxoviruses, several of those known to be involved in zoonotic spillover events and demanding an integrated surveillance. Here, we present a framework that leverages Brazil's rabies passive surveillance programme to detect bat-borne viruses. Using an algorithm to select representative specimens from 2422 bats collected across São Paulo state, we submitted 150 paired lung and intestine samples to nanopore metagenomic sequencing. We detected 98 viral contigs from 12 families of public health relevance, including Arenaviridae, Coronaviridae, and Paramyxoviridae. Notably, the approach identified a previously unknown filovirus in bats in the Americas, validating the framework's capacity for epidemic preparedness. These findings reveal an undetected viral diversity and demonstrate how existing animal surveillance can monitor pathogen threats. Crucially, in a workshop involving multisectoral One Health experts in Brazil, this framework was validated as a scalable model for national expansion, adapted for low- and middle-income countries (LMICs).</t>
+          <t>Sprinkler irrigation systems are critical for modern agriculture but represent largely unrecognized aquatic environments capable of sustaining opportunistic human pathogens. Among them, Legionella pneumophila is of particular concern due to its ability to colonize engineered water systems, persist under fluctuating environmental conditions, and be transmitted through aerosols. In this study, we conducted a comprehensive microbiological and genomic investigation of irrigation ponds and ditches in a rural area of north-east Spain where two zones were sampled. Metagenomic profiling revealed highly diverse microbial communities encompassing more than 20,000 species, including 21 airborne-transmissible bacterial pathogens of clinical relevance. Notably, L. pneumophila was detected in both zones, with a relative abundance of up to 4.6 %. Culture-based isolation confirmed the presence of L. pneumophila serogroup 1, Pontiac group, Benidorm subgroup, sequence type 15. Phylogenetic analysis demonstrated a close relationship between this environmental strain and clinical isolates obtained during a Legionnaires' disease outbreak occurred in 2015, which had remained without a confirmed environmental source. Meteorological data from the exposure period revealed wind conditions favouring long-distance aerosol dispersion from irrigated fields toward residential areas. Our findings provide evidence that irrigation infrastructures can act as environmental reservoirs and dissemination routes of L. pneumophila among other airborne pathogens. These results underscore the need to incorporate agricultural irrigation systems into routine environmental surveillance, outbreak investigations, and public health risk assessments.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>本研究旨在建立一個利用現有狂犬病被動監測系統來偵測蝙蝠攜帶病毒的防疫框架，以預防潛在的人畜共通傳染病爆發。研究團隊從巴西聖保羅州收集的 2,422 隻蝙蝠中篩選出代表性個體，並對 150 對肺部與腸道組織樣本進行奈米孔總體基因體定序（nanopore metagenomic sequencing）。結果成功偵測到來自 12 個與公共衛生密切相關病毒科的 98 個病毒重疊群（contigs），包括冠狀病毒與副黏液病毒，並首次在美洲蝙蝠中發現未知的絲狀病毒。此研究揭示了未被察覺的病毒多樣性，證實利用既有動物監測進行病原體預警的可行性，為中低收入國家提供了可推廣的「健康一體」（One Health）監測模型。</t>
+          <t>本研究旨在探討農業噴灌系統是否為嗜肺軍團菌（*Legionella pneumophila*）等病原體的環境宿主與空氣傳播源。研究團隊對西班牙東北部兩個區域的灌溉池和水溝進行微生物與基因組調查。總體基因體分析顯示其微生物群落極具多樣性，並檢出21種具臨床相關性的空氣傳播病原體，其中嗜肺軍團菌相對豐度高達4.6%。經培養分離與系統發育分析證實，該環境菌株與2015年一起未明源頭的退伍軍人症爆發臨床分離株高度相關；氣象數據亦支持氣溶膠可經風力長距離吹向住宅區。此研究證實灌溉系統為嗜肺軍團菌的關鍵傳播途徑，強調應將其納入例行環境監測與公共衛生風險評估。</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42644084/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648218/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>42637484</t>
+          <t>42648293</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Insights into the analysis of microbial communities in fermented foods from the perspective of DNA-based techniques.</t>
+          <t>Defined human Clostridia consortia reverse colitis via dual effects of tryptophan metabolites on microbiota and immunity.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Food research international (Ottawa, Ont.)</t>
+          <t>Cell host &amp; microbe</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16S, metagenomics</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（原文僅提及使用 murine models 及相關菌株組合，未明確統計具體樣本數）</t>
         </is>
       </c>
       <c r="G15" t="b">
@@ -1224,54 +1218,54 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>The quality, flavor, and stability of fermented foods depend on the microbial community. However, microbial dynamics are difficult to observe directly, leading to limited control over fermentation. High-throughput sequencing is a revolutionary tool for microbial characterization, among which DNA-based amplicon and metagenomic sequencing are core techniques. Nevertheless, the related data processing workflows in the context of fermented foods have not yet been systematically summarized, hindering the translation of research findings into fermentation practices. This review clarifies the applications of amplicon and metagenomic sequencing in fermented foods. For amplicon sequencing, the impacts of target regions, data preprocessing, and reference databases are addressed. For metagenomic sequencing, sequencing strategies, read-based and binning-based analytical methods, functional annotation, and species-specific databases are discussed. In addition, major strategies for downstream analysis of community data are summarized, including microbial diversity, co-occurrence networks, niche and community assembly, key environmental drivers, and machine learning-based prediction. Amplicon sequencing efficiently reveals microbial succession during fermentation but has limitations in functional annotation. Metagenomic sequencing is notable for functional annotation, enabling the linkage between microbial communities and metabolic potential alongside community characterization. Standardized data preprocessing and specific databases are critical for improving characterization. For community data, integrated analysis allows uncovering the driving factors of microbial succession, thereby helping to regulate fermentation. Notably, the compositional nature of the data must be considered and validated to avoid spurious associations. In summary, the exponential growth of sequencing data will propel the era of precision fermentation.</t>
+          <t>Microbial dysbiosis and disrupted mucosal immune homeostasis are integrally involved in the pathogenesis of inflammatory bowel diseases (IBDs). Live biotherapeutic products (LBPs) offer a potential therapeutic strategy to restore beneficial microbes and mitigate disease. We investigated the therapeutic efficacy of 2 LBPs, human Clostridia consortia 17-mix and 11-mix, by treating established colitis in murine models. Both LBPs exhibited therapeutic effects in T cell-mediated chronic colitis models induced by human microbiota and in pathobiont-driven gnotobiotic colitis models established with combinations of IBD-relevant human-derived strains. Metagenomic and metabolomic analyses elucidated mechanisms that go beyond established functions driven by short-chain fatty acids (SCFAs) and interleukin (IL)-10-producing regulatory T cells. Notably, LBPs exerted therapeutic effects by directly inhibiting resident pathobionts and through IL-10-independent activation of host anti-inflammatory aryl hydrocarbon receptor (AhR) pathways by bacterial tryptophan metabolites. These results elucidate SCFA- and IL-10-independent protective mechanisms exerted by defined resident bacterial strains that are depleted in IBD dysbiosis.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>本文為一篇綜述性研究，旨在探討以 DNA 為基礎的高通量定序技術（包含擴增子定序與宏基因組學）在發酵食品微生物群落分析中的應用。研究指出，儘管高通量定序技術已成為解析微生物動態的革命性工具，但目前缺乏系統性的數據處理框架，限制了科學發現向產業實踐的轉化。本文詳細梳理了從目標區域選擇、數據預處理、參考數據庫建立到下游生物資訊分析（如共現網絡、生態棲位構建及機器學習預測）的標準化流程。研究強調，擴增子定序雖能有效揭示群落演替，但在功能註解上存在限制；而宏基因組學則具備更強的功能解析潛力，能將微生物組成與代謝功能聯繫起來。透過標準化數據處理流程並考慮數據的組成特性，這些先進技術將精準調控發酵過程，引領精密發酵時代的到來。</t>
+          <t>本研究旨在探討定義明確的人類梭菌群（Clostridia consortia）在發炎性腸道疾病（IBD）中的治療潛力。研究團隊利用小鼠結腸炎模型，證實「17-mix」與「11-mix」梭菌群能有效緩解由人類菌相或致病菌引發的慢性結腸炎。透過總體基因體學與代謝體學分析，研究發現這些菌群的治療機制超越了傳統認知的短鏈脂肪酸（SCFA）與 IL-10 調控路徑。其核心機制在於：細菌產生的色胺酸代謝物能直接抑制腸道致病菌，並透過非 IL-10 依賴途徑活化宿主的芳香烴受體（AhR），進而誘發抗發炎反應。此發現揭示了特定菌株在修復失調菌群中的關鍵作用，為開發針對 IBD 的活體生物治療產品（LBPs）提供了重要的科學依據與新機制方向。</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42637484/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648293/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>42637478</t>
+          <t>42648688</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Effects of sorghum variety on fermentation microecology and flavor characteristics of sesame-flavor Baijiu.</t>
+          <t>Temperature Sensitivity of Pyrrhotite-Driven Metavanadate Bioreduction in Groundwater.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Food research international (Ottawa, Ont.)</t>
+          <t>Environmental research</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>metagenomics, others</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>3 種高粱品種（Hongyingzi, Hei'e, G），於 2 輪發酵週期中，在 3 個時間點（0、15、50 天）採集發酵酒醅檢體（樣本總數依實驗設計推算為 18 組發酵樣品）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G16" t="b">
@@ -1279,50 +1273,54 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sorghum, the principal raw material for Baijiu fermentation, plays a key role in shaping fermentation microecology and flavor formation. However, the effects of sorghum varietal differences on sesame-flavor Baijiu fermentation remain insufficiently understood. In this study, three sorghum varieties, Hongyingzi (R), Hei'e (B), and a domestic cultivar (G), were compared over two consecutive fermentation rounds. Fermented grain (Jiupei) samples collected at 0, 15, and 50 days were analyzed for physicochemical properties, enzyme activities, microbial communities, volatile compounds in Jiupei and base liquor, and the taste characteristics of the corresponding base liquor. Despite showing similar overall fermentation trends, the three sorghum varieties differed in acid accumulation, starch utilization, microbial succession, and volatile composition. Fungal communities shifted from early Pichia dominance to multi-genus coexistence, whereas bacterial communities progressively converged toward Lactobacillus dominance. A total of 218 and 258 volatile compounds were identified in Jiupei and 176 and 192 in base liquor from the first and second rounds, respectively. Esters were the dominant differential class, and volatile-marker profiles varied among sorghum varieties and fermentation rounds, with no single variety showing consistent enrichment across all sesame-flavor-related compounds. These results indicate that sorghum variety is an important factor associated with microbial assembly and flavor formation during sesame-flavor Baijiu fermentation, and provide a basis for raw material selection and flavor-oriented process optimization.</t>
+          <t>Pyrrhotite-driven metavanadate [V(V)] bioreduction is a promising green strategy for the remediation of vanadium-contaminated aquifers. However, how this microbially driven process responds to different temperatures remains unclear. Herein, the responses of pyrrhotite-driven V(V) bioreduction to different temperatures ranging from 4 to 45 °C were investigated. V(V) removal first increased and then decreased with increasing temperature, peaking at 35 °C, with the reaction rate constant reaching 0.077 d-1. V(V) could be reduced to VO2 precipitates, accompanied by oxidation of S(-II) and Fe(II) to sulfate and Fe(III), respectively. Metagenomic binning revealed that S(-II) oxidation was more sensitive to temperature changes than Fe(II) oxidation for V(V) reducers. Bacteria coupling V(V) reduction with both S(-II) and Fe(II) oxidation (e.g., Ramlibacter sp.) were detected exclusively at 35 °C. The transcription of functional genes (related to V(V) reduction, S(-II) oxidation, and Fe(II) oxidation), electron transport activity and related components all exhibited a temperature-dependent pattern, first increasing and then decreasing, with a peak at 35 °C. This study reveals the temperature sensitivity of pyrrhotite-driven V(V) bioreduction, which is helpful for risk assessment and targeted bioremediation of vanadium contamination under different temperature conditions.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>本研究旨在探討不同高粱品種對芝麻香型白酒發酵過程中，微生物群落結構與風味代謝物質形成的影響。研究比較了紅纓子（R）、黑鵝（B）與國內品種（G）三種高粱，分析其在發酵過程中的理化特性、微生物演替及揮發性化合物組成。研究發現，儘管各品種發酵趨勢相似，但在酸度累積、澱粉利用率及微生物群落演替上存在顯著差異；真菌群落由早期的畢赤酵母（*Pichia*）主導轉變為多菌屬共存，細菌群落則趨向於乳桿菌（*Lactobacillus*）主導。分析鑑定出上百種揮發性化合物，其中酯類是導致風味差異的主要代謝物。本研究證實了高粱品種是決定白酒發酵微生物群落組裝與最終風味品質的關鍵因子，為白酒產業的原料選擇與製程最佳化提供了重要的科學依據。</t>
+          <t>本研究旨在探討溫度（4至45 °C）對地下水中磁黃鐵礦驅動偏釩酸鹽 [V(V)] 生物還原的影響。研究發現，V(V) 去除率隨溫度升高呈先增後減，於 35 °C 達到峰值（反應速率 0.077 d⁻¹），並將其還原為 VO₂ 沉澱。宏基因組分箱顯示，釩還原菌的硫氧化對溫度敏感性高於鐵氧化；僅在 35 °C 偵測到可同時耦合硫鐵氧化與釩還原的 *Ramlibacter* sp.。此外，相關功能基因轉錄及電子傳遞活性均在 35 °C 達到最高。本研究揭示了該生物還原過程的溫度敏感性，有助於不同溫度環境下釩污染的風險評估與精準生物修復。</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42637478/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648688/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>42637476</t>
+          <t>42649294</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A Shenling Baizhu San polysaccharide fraction (SLP-2)-based synbiotic alleviates lactose-induced gut dysfunction via a microbiota-metabolite-barrier axis.</t>
+          <t>Synergistic degradation of fucoidans in the ocean.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Food research international (Ottawa, Ont.)</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>48.5</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（摘要中僅提及使用重建的海洋菌群與海洋總體基因體數據，未說明具體樣本數量）</t>
         </is>
       </c>
       <c r="G17" t="b">
@@ -1330,50 +1328,54 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Lactose intolerance (LI) is a common digestive disorder, and its management still relies largely on dietary restriction. Because gut microbial fermentation and barrier dysfunction contribute to LI-related symptoms, microbiota-targeted prebiotic or synbiotic strategies may provide complementary approaches. However, the active plant-polysaccharide fractions and their microbial partners remain unclear. This study aimed to identify the bioactive polysaccharide fraction from Shenling Baizhu San and evaluate its pairing with responder bacteria for alleviating high-lactose diet (HLD)-induced intestinal dysfunction. Stepwise ethanol precipitation yielded SLP-2, which was subsequently identified as the principal bioactive fraction through human fecal fermentation, monoculture assays, and an HLD rat model. SLP-2 enriched Eubacterium-associated taxa and supported the growth of Akkermansia muciniphila in monoculture and in vivo. Building on this, a synbiotic combining SLP-2 with A. muciniphila and E. rectale alleviated HLD-induced gut dysfunction; the antibiotic-matched comparison with the probiotics-only group supported an SLP-2-associated contribution. The synbiotic intervention was associated with increased tight junction proteins, MUC2 expression, improved intestinal architecture, and thicker mucus layers. Multi-omics analysis linked co-metabolites, including intestinal 6-MGG and HTy-Ac and systemic DHPV-G, with barrier restoration and an immune profile characterized by increased IL-10 and lower TLR4 expression. These findings suggest that SLP-2-based synbiotic intervention alleviates HLD-induced intestinal dysfunction through microbiota-metabolite-barrier modulation, providing preclinical evidence for future functional-food strategies pending human validation.</t>
+          <t>Fucoidans, a class of complex polysaccharides produced by brown algae and diatoms, contribute to long-term carbon sequestration owing to their resistance to microbial degradation1,2. Although individual microorganisms can break down portions of these polysaccharides3-5, it remains unclear whether complete breakdown is possible in nature and, if so, by what mechanisms. Here we show that fucoidans are degraded through synergistic interactions between specialized bacteria with complementary metabolic functions. Using metabolomic analysis of a reconstructed marine consortium, we uncovered metabolic guilds of bacteria that preferentially degrade either the sulfated fucose backbone or the side branches of rare monomers. This functional division of labour leads to an unexpectedly high number of synergistic interactions between different degraders that enhanced degradation efficiency up to 97.1%. Despite varying fucoidan structures across different types of algae6, the metabolic functions of degraders remained conserved, enabling quantitative prediction of degradation outcomes based on community and substrate composition. The frequent co-occurrence of functionally complementary fucoidan degraders in ocean metagenomes suggests that synergistic degradation is a globally relevant strategy. Our findings suggest that the environmental turnover of complex biopolymers depends not only on individual metabolic capabilities of degraders but also on ecological interactions shaped by substrate architecture. This work provides a mechanistic framework for understanding carbon cycling in the ocean and for engineering synthetic microbial consortia to degrade recalcitrant polysaccharides.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>本研究旨在探討參苓白朮散多醣活性組分（SLP-2）結合特定菌株，對高乳糖飲食（HLD）引發之腸道功能障礙的緩解作用。研究發現，SLP-2能促進*A. muciniphila*與真桿菌屬相關菌群生長。以SLP-2搭配益生菌的合生元配方，能顯著改善HLD大鼠的腸道屏障，包含增加緊密連接蛋白與MUC2表達、增厚黏液層。多體學分析顯示，其保護作用與腸道及全身性代謝物（如6-MGG、DHPV-G）的調節，以及抗發炎反應（提升IL-10、降低TLR4）密切相關。此發現為開發防治乳糖不耐症的功能性食品提供了臨床前依據。</t>
+          <t>本研究旨在探討海洋中複雜且難降解的褐藻醣膠（fucoidans）如何被完全降解。研究團隊利用重建的海洋合成菌群進行代謝組學分析，發現褐藻醣膠的降解依賴於不同細菌間的「功能性分工」與協同作用：部分細菌專門降解硫酸岩藻糖骨架，其餘則負責處理側鏈。這種協同效應使降解效率提升至97.1%。此外，這種互補的代謝功能在海洋總體基因體中廣泛存在。此發現揭示了海洋碳循環不僅取決於單一菌株的代謝能力，更受微生物群落間生態互動的影響，為理解全球碳循環及設計合成菌群以執行生物降解提供了重要機制藍圖。</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42637476/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42649294/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>42637471</t>
+          <t>42657129</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fucoidan from giant kelp alleviates postmenopausal osteoporosis by regulating the betaine-OPG/RANKL/RANK signaling axis.</t>
+          <t>Pulmonary Infiltrates, Airway Mucosal Lesions and Respiratory Microbiology After Freshwater Drowning: A Case Report.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Food research international (Ottawa, Ont.)</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Respirology case reports</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>1位患者（個案報告）</t>
         </is>
       </c>
       <c r="G18" t="b">
@@ -1381,50 +1383,54 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Postmenopausal osteoporosis (PMOP), characterized by excessive bone resorption and impaired bone remodeling, remains a significant global health challenge. This study investigated the protective effects of fucoidan from giant kelp (GKP) against PMOP and its underlying mechanisms in ovariectomized mice. GKP supplementation attenuated bone loss by preserving trabecular microarchitecture, normalizing systemic mineral homeostasis, and suppressing osteoclastogenesis, as evidenced by the downregulation of osteoclast-related genes. 16S rRNA gene sequencing revealed that GKP reshaped the gut microbiota by decreasing the Bacteroidota/Firmicutes ratio and enriching beneficial taxa, which promoted short-chain fatty acid production. Targeted metabolomics revealed that GKP induced profound systemic metabolic reprogramming, particularly amino acid metabolism, and identified betaine as a key systemic metabolite effector upregulated following GKP treatment. In vitro assays demonstrated that betaine suppressed receptor activator of nuclear factor-κB ligand (RANKL)-induced osteoclast differentiation and mitigated inflammation. In vivo validation demonstrated that betaine intervention recapitulated the osteoprotective phenotype observed in GKP-treated mice, which was associated with regulation of the osteoprotegerin/RANKL/RANK signaling axis. These results indicate that GKP exerts anti-osteoporotic effects in association with changes in gut microbiota and systemic metabolism, while betaine-mediated regulation of the OPG/RANKL/RANK signaling may contribute to its osteoprotective activity.</t>
+          <t>Early pulmonary abnormalities after freshwater drowning can be overinterpreted as bacterial pneumonia, especially when inflammatory biomarkers and respiratory microbiology are positive. A 20-year-old man was resuscitated after approximately 2 min of freshwater submersion. Day 1 chest CT showed bilateral lower-lobe-predominant opacities compatible with non-cardiogenic pulmonary oedema and aspiration-related lung injury, with near-complete resolution by Day 25. Day 3 bronchoscopy showed diffuse, non-removable, millet-seed-like whitish tracheal mucosal protrusions with hyperaemia and oedema, compatible with acute irritative airway injury. BALF mNGS detected multiple gram-negative bacterial signals, predominantly Klebsiella pneumoniae, while sputum culture yielded ESBL-negative, susceptible K. pneumoniae. Possible drowning-associated pneumonia was considered because of aspiration, fever, markedly elevated inflammatory biomarkers and concordant microbiology; however, rapid radiological improvement and clinical stability suggested a substantial non-infectious component. The patient recovered after an 8-day course of piperacillin-tazobactam without antibiotic escalation, corticosteroids, mechanical ventilation or acute respiratory distress syndrome.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>本研究探討巨藻褐藻醣膠（GKP）對去卵巢小鼠更年期後骨質疏鬆症（PMOP）的保護機制。結果顯示，補充GKP能有效減少骨質流失並抑制破骨細胞生成。16S定序顯示GKP重塑了腸道菌群（降低擬桿菌門/厚壁菌門比例），促進短鏈脂肪酸產生。代謝組學分析發現，GKP顯著提升了系統性代謝物甜菜鹼（betaine）的含量。體內外實驗進一步證實，甜菜鹼透過調控OPG/RANKL/RANK信號軸，能抑制破骨細胞分化並緩解骨質流失。本研究證實GKP具備透過「腸道菌群-代謝物」軸抗骨質疏鬆的潛力，為PMOP防治提供了科學依據。</t>
+          <t>本研究報告了一例20歲男性於淡水溺水後的臨床病程。患者初期出現雙側肺部浸潤與氣管黏膜病變，且支氣管肺泡灌洗液（BALF）的宏基因組定序（mNGS）與痰液培養均檢出肺炎克雷伯氏菌。儘管發炎指標顯著升高，但患者影像學特徵迅速改善且臨床表現穩定，證實早期肺部異常主要源於吸入性肺損傷與非心源性肺水腫等非感染性因素。患者最終接受8天抗生素治療後順利康復。本案例的科學意義在於提醒臨床醫生，溺水後早期的肺部影像異常與病原檢測陽性易被過度解讀為細菌性肺炎，應結合臨床病程以避免過度治療。</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42637471/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42657129/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>42637450</t>
+          <t>42648179</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Highland barley polysaccharides promoted lactose intestinal fermentation in vitro: Unveiling the dynamic response of gut microbiota and polysaccharide structure.</t>
+          <t>Simultaneous removal of nitrogen, Cu2+, and bisphenol A in a hydrogel-biochar-AQDS immobilized bioreactor with added bicarbonate: Performance and metagenomic insights.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Food research international (Ottawa, Ont.)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Journal of hazardous materials</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>11.3</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>乳糖不耐症患者的糞便檢體（未提及具體數量）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G19" t="b">
@@ -1432,50 +1438,54 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Lactose intolerance affects over 70% of the global population due to the untimely metabolism of lactose in the colon. To accelerate lactose metabolism, we innovatively employed highland barley polysaccharides (HBP) to modulate the colonic fermentation efficiency of lactose using an in vitro fermentation model and fecal samples from lactose intolerant patients. With the addition of HBP, the consumption efficiency of lactose began to increase after 6 h of fermentation. At 48 h, lactose consumption increased by 29%, surpassing the effect of commercial prebiotics. Meanwhile, HBP with lower molecular weight (HBP-L, 8.69 × 104 g/Mol) exhibited more effective impacts than HBP with high molecular weight (HBP-H, 1.22 × 105 g/Mol), which was particularly evident during the 12-48 h of fermentation. More importantly, HBP, particularly HBP-L, substantially enriched Segatella, Bifidobacterium, and Ligilactobacillus in a time-dependent manner and was positively correlated with decreased lactose levels and elevated bacterial lactase activity, resulting in significant conversion of lactose to lactic acid and short-chain fatty acids. During the first 12 h of fermentation, HBP-L underwent more significant degradation than HBP-H. Meanwhile, the xylose residues and Glcp glycosidic bonds in HBP-L were preferentially utilized, while it was glucose residue in HBP-H. Thus, it indicated that HBPs were degraded and altered the composition of the gut microbiota, thereby enhancing the fermentation efficiency of lactose. Our findings provide a theoretical basis for developing targeted prebiotic foods to manage lactose intolerance.</t>
+          <t>As the complexity of industrial wastewater pollution continues to increase, the simultaneous removal of nitrogen, metal contaminants, and persistent organic pollutants under low carbon conditions has become a key challenge for biological treatment systems. To address the operational instability and dependence on carbon sources observed in immobilized systems when exposed to copper (Cu2+) and bisphenol A (BPA), the Pseudoalteromonas japonicus strain LY0623 was integrated into a hydrogel-biochar-AQDS composite carrier to construct a multifunctional immobilized biofilm system. Notably, under conditions containing only NaHCO3, the R4 system achieved an NH4+-N removal rate of 89%. Under conditions where Cu2+ and BPA coexist, the R4 system achieved removal of NH4+-N (89%), NO3--N (100%), Cu2+ (85%), and BPA (88%). Sediment characterization confirmed that Cu2+ was immobilized through adsorption, complexation, and microbiologically induced carbonate precipitation (MICP). Metagenomic analysis further indicated that the Pseudomonadota phylum remained the dominant phylum, while functional pathways associated with inorganic carbon assimilation, HNAD nitrogen metabolism, endogenous carbon transformation, biomineralization, electron transfer, and aromatic compound degradation were preserved. By combining ammonia oxidation driven energy production, inorganic carbon utilization, redox mediated processes, and biomineralization, this study provides a highly promising low carbon strategy for treating industrial wastewater containing mixed pollutants.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>本研究旨在探討青稞多醣（HBP）如何調控乳糖不耐症患者的腸道菌群，以促進體外乳糖發酵與代謝。研究發現，添加 HBP（特別是低分子量的 HBP-L）能在發酵 48 小時後提升乳糖消耗效率達 29%，效果顯著優於商業益生元。機制上，HBP-L 在發酵初期降解更為顯著，並能隨時間特異性富集 *Segatella*、雙歧桿菌屬（*Bifidobacterium*）及 *Ligilactobacillus*，進而提升細菌乳糖酶活性，將乳糖轉化為乳酸與短鏈脂肪酸。本研究證實了青稞多醣能透過重塑腸道菌群結構來加速乳糖代謝，為開發緩解乳糖不耐症的標靶益生元食品提供了重要科學依據。</t>
+          <t>本研究旨在解決低碳條件下，工業廢水中氮、重金屬（Cu2+）及持久性有機污染物（雙酚A, BPA）難以同時去除的挑戰。研究團隊將日本假交替單胞菌（*Pseudoalteromonas japonicus* LY0623）整合至水膠-生物炭-AQDS複合載體中，構建出多功能固定化生物膜系統（R4系統）。結果顯示，在僅添加碳酸氫鈉的低碳條件下，該系統成功實現了高效率的氨氮（89%）、硝酸鹽氮（100%）、Cu2+（85%）及BPA（88%）同步去除。總體基因體學分析證實，變形菌門為優勢菌群，且系統維持了無機碳同化、反硝化、電子傳遞及芳香族化合物降解等關鍵代謝途徑。此研究為處理含有混合污染物的工業廢水提供了一種極具前景的低碳生物整治策略。</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42637450/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648179/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>42637441</t>
+          <t>42642622</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Microbial succession drives quality deterioration in refrigerated golden pompano (Trachinotus ovatus): regulatory network of dominant spoilage microbiota on characteristic biomarkers.</t>
+          <t>Deployable high-fidelity metagenome binning at scale with QuickBin.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Food research international (Ottawa, Ont.)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Communications biology</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>297 個真實總體基因體（metagenomes）數據集及合成群落</t>
         </is>
       </c>
       <c r="G20" t="b">
@@ -1483,45 +1493,49 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Elucidating the quality deterioration mechanisms of refrigerated golden pompano (Trachinotus ovatus), this study integrated 16S rRNA gene sequencing and untargeted metabolomics to systematically dissect how microbial ecological succession drives metabolic changes. As critical spoilage indicators, total volatile basic nitrogen (TVB-N) and thiobarbituric acid reactive substances (TBARS) continuously increased during storage, indicating significant deterioration by day 6. Microbial community succession analysis revealed that Psychrobacter, Shewanella, and Pseudomonas gradually became the dominant microbiota in the late storage stage. Metabolite enrichment analysis further demonstrated that this shift redirected the metabolic focus from early-stage nucleotide degradation to late-stage protein hydrolysis and amino acid metabolism. Moreover, multivariate statistical analysis identified 50 potential spoilage biomarkers, among which biogenic amines (histamine, tyramine, and phenylethylamine) were recognized as key indicators reflecting spoilage progression. Correlation network analysis revealed positive correlations between Pseudomonas and Shewanella abundances and the accumulation of these biogenic amines. This suggests that these two genera act as the core functional microbiota, driving spoilage metabolite generation and subsequent quality deterioration. Pathway analysis of potential spoilage biomarker generation indicates that amino acid and nucleotide metabolism constitute the core spoilage pathways, with lipid oxidation serving as a complementary mechanism. Overall, this study elucidates the spoilage mechanisms of refrigerated golden pompano, providing chemical targets for early biomarker detection and targeted antibacterial strategies.</t>
+          <t>Reconstructing genomes from metagenomic assemblies is foundational to microbiome research, yet binning faces a persistent trade-off between fidelity and throughput. Many high-accuracy methods rely on GPU-intensive workflows, marker-gene postprocessing, or heavy computational resources, limiting reproducible use at scale. Here, we present QuickBin, a CPU-native, marker-free binning algorithm designed to recover near-complete, ultra-low-contamination metagenome-assembled genomes (MAGs) efficiently. QuickBin pairs a GC-coverage spatial index (BinMap) with an early-exit Oracle cascade of similarity tests (scalar composition/coverage filters and SIMD-accelerated k-mer comparisons), reserving a compact neural network exclusively for ambiguous merges. Across synthetic communities, evaluated by marker-based and contig-origin ground truth, QuickBin maximizes high-fidelity sequence recovery. In benchmarking 297 diverse real metagenomes, QuickBin completed all runs, recovering more high-quality MAGs (≥95% completeness, ≤1% contamination) than resource-intensive alternatives that frequently failed. QuickBin provides a practical path to reproducible, genome-resolved metagenomics at scale for downstream comparative analyses. Open-source at: https://github.com/bbushnell/BBTools .</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>本研究旨在探討冷藏金鯧魚品質劣化的機制。研究結合 16S rRNA 基因定序與非靶向代謝組學，分析微生物群落演替如何驅動代謝變化。結果顯示，金鯧魚冷藏至第 6 天時顯著腐敗。在貯藏後期，*Psychrobacter*、*Shewanella* 與 *Pseudomonas* 逐漸成為優勢菌群，使代謝焦點自初期的核苷酸降解轉向後期的蛋白質水解與氨基酸代謝。研究鑑定出 50 個潛在腐敗生物標誌物（如組胺、酪胺等生物胺），並發現 *Pseudomonas* 和 *Shewanella* 的豐度與這些生物胺的累積呈正相關，為驅動腐敗的核心菌群。本研究闡明了金鯧魚的腐敗機制，為食品早期變質檢測及靶向抑菌策略提供了科學依據與化學標靶。</t>
+          <t>本研究開發了名為 QuickBin 的新型分箱（binning）演算法，旨在解決總體基因體學中重建基因組時，高準確度與運算效率難以兼得的瓶頸。QuickBin 是一款無需標記基因且原生支援 CPU 的高效工具，結合了 GC 覆蓋度空間索引、相似性篩選級聯與輕量神經網絡。在 297 個真實總體基因體數據集的基準測試中，QuickBin 成功完成所有運行，且重建出比其他高資源消耗工具更多的高質量組裝基因組（MAGs，完整度≥95%且污染度≤1%）。此技術為大規模、高解析度的總體基因體學研究提供了一套高效、可重複且實用的科學解決方案。</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42637441/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42642622/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>42637430</t>
+          <t>42642466</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Regional differentiation of microbial communities and metabolites in Yunnan dry-cured beef: insights from high-throughput sequencing and untargeted metabolomics.</t>
+          <t>Empirical evidence for gut microbial influence on human brain neurochemistry via the gut-brain axis.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Food research international (Ottawa, Ont.)</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Molecular psychiatry</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1534,71 +1548,1015 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>To reveal the effects of regional processing on quality, microbial communities and metabolites of traditional Yunnan dry-cured beef, samples from Xundian (XD), Yuxi (YX) and Honghe (HH) were analyzed. High-throughput sequencing and UHPLC-Q-Exactive HF/MS untargeted metabolomics were applied. Sensory scores and physicochemical Properties differed significantly (p &lt; 0.05). Bacillota and Staphylococcus dominated bacterial communities. The observed differences in microbial communities and metabolites among regions are shaped by the combined effects of geographical environment and processing conditions. Ascomycota was the main fungal phylum. Debaryomyces dominated XD and HH samples. YX samples had a unique fungal profile dominated by Rhodotorula and Cladosporium. A total of 1320 metabolites were identified. 196 differential metabolites were screened. Key pathways included glycerophospholipid metabolism, pyrimidine metabolism and arachidonic acid metabolism. Correlation analysis indicated that Staphylococcus and Lactococcus were positively associated with amino acid derivatives, while Latilactobacillus and Debaryomyces correlated with organic acids and glycerophospholipids. These findings revealed the potential microbial-metabolic association underlying regional quality differences. They provide support for quality control and traceability of dry-cured beef.</t>
+          <t>The gut microbiome produces metabolites with potential neuroactive properties, many of which act locally within the gut. While preclinical studies suggest these microbial pathways can influence cognitive and emotional processes, human evidence remains limited. This study investigates associations between gut microbiome-derived neuroactive functional potential and in vivo brain neurotransmitter concentrations in healthy young females. Using proton magnetic resonance spectroscopy (¹H-MRS), we quantified GABA and glutamate levels in the dorsolateral prefrontal cortex (dlPFC), anterior cingulate cortex (ACC), and inferior occipital gyrus (IOG). Parallel metagenomic profiling characterised microbial functional potential for pathways related to the synthesis and degradation of GABA, glutamate, short-chain fatty acids (SCFAs), p-cresol, and inositol. Region-specific associations were observed between these microbial pathways and cortical GABA and glutamate levels, including excitatory/inhibitory (E/I) balance, a key marker of neuroplasticity and mental health. Notably, microbial glutamate degradation and inositol synthesis potential were associated with IOG E/I balance, while additional pathways including GABA metabolism, p-cresol production, and SCFA synthesis showed distinct associations across regions. Exploratory analyses also identified links between microbial functional potential and anxiety, depressive symptoms, and sleep quality. Together, these findings provide new human evidence that variation in microbial functional potential corresponds with regional cortical neurochemistry and psychological wellbeing, highlighting the gut-brain axis as a promising avenue for mechanistically informed microbiome-based- interventions.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>本研究旨在探討地理區域與加工工藝對雲南傳統乾醃牛肉（尋甸、玉溪、紅河三地）品質、微生物群落及代謝物的影響。研究結合高通量定序與非靶向代謝組學技術，發現不同地區的乾醃牛肉在感官評分與理化性質上存有顯著差異。細菌群落以厚壁菌門和葡萄球菌屬為主；真菌群落中，尋甸和紅河樣品以德巴利酵母屬為主，玉溪樣品則以紅酵母屬與枝孢菌屬為特有優勢菌。代謝組學共鑑定出1320種代謝物，其中196種為差異代謝物，主要涉及甘油磷脂、嘧啶及花生四烯酸代謝通路。關聯分析顯示，葡萄球菌屬和乳球菌屬與氨基酸衍生物呈正相關，而廣義乳桿菌屬與德巴利酵母屬則與有機酸及甘油磷脂密切相關。本研究揭示了微生物與代謝物的關聯性，為乾醃牛肉的品質控制與產地溯源提供了重要科學依據。</t>
+          <t>本研究旨在探討健康年輕女性的腸道菌群功能潛力與大腦神經傳導物質（GABA和麩胺酸）濃度之關聯。研究結合總體基因體學剖析與大腦質子磁振光譜（¹H-MRS），發現腸道菌群在代謝GABA、麩胺酸、短鏈脂肪酸及肌醇等通路的功能潛力，與大腦特定區域（如背外側前額葉、下枕迴）的皮質神經化學物質及興奮/抑制（E/I）平衡具有區域特異性關聯。此外，菌群功能也與焦慮、憂鬱及睡眠品質相關。本研究為「腸腦軸」提供重要的人體實證，證實腸道菌群功能變化會影響大腦神經化學與心理健康，為未來開發微生態導向的精神健康干預手段奠定科學基礎。</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42637430/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42642466/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>42641146</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Engineered bacterial therapeutics from synthetic biology to clinical translation: A multi-database scientometric analysis, 2000-2026.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Human vaccines &amp; immunotherapeutics</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1,730 篇學術文章與評論</t>
+        </is>
+      </c>
+      <c r="G22" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Engineered bacterial therapeutics integrate programmable strain engineering with biomedical functions such as sensing, delivery, immune modulation, microbiome intervention, and disease management. This study conducted a multi-database bibliometric analysis to map the knowledge structure, collaboration patterns, and translational direction of this field. Bibliographic records were retrieved from Web of Science Core Collection, Scopus, and PubMed for publications from 1 January 2000 to 1 June 2026. After document-type filtering, time restriction, deduplication, language screening, and manual eligibility assessment, 1,730 English-language articles and reviews were included. CiteSpace 6.4.R1, VOSviewer 1.6.20, and the bibliometrix R package were used to analyze publication trends, collaboration networks, journal co-citation, dual-map citation trajectories, citation bursts, keyword co-occurrence, and thematic evolution. Publication output increased steadily, with faster growth after 2020; 2025 was the highest-output complete year, while 2026 represented a partial retrieval year. China and the United States were the leading contributors, although institutional collaboration remained regionally clustered. Co-citation, citation-burst, and keyword analyses showed a shift from bacterial chassis construction and circuit design toward engineered probiotics, gut microbiota-related therapy, cancer immunotherapy, drug delivery, live biotherapeutic products, and clinical translation. Persistent translational priorities include controllability, safety, manufacturing consistency, and regulatory alignment.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>本研究透過文獻計量學方法，系統性分析 2000 年至 2026 年間有關「工程化細菌治療」的 1,730 篇學術文獻。研究旨在釐清該領域的知識結構、國際合作模式及臨床轉化趨勢。分析顯示，該領域自 2020 年後顯著加速發展，中國與美國為主要貢獻國。核心研究主軸已由早期的細菌底盤構建與基因電路設計，轉向工程化益生菌、癌症免疫治療、藥物遞送及活體生物藥物（LBP）的開發。科學意義在於確立了該領域從實驗室轉向臨床應用的優先議題，即解決控制力、生物安全性、生產一致性與法規調適等挑戰，為未來工程化細菌作為精準醫療工具的發展提供關鍵決策參考。</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42641146/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>42642836</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Microbiome-mediated regulation of pathogen virulence: Molecular mechanisms and clinical implications.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Virulence</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>The human microbiome profoundly influences pathogen virulence and disease susceptibility through diverse molecular mechanisms. This review, focused on literature from 2016 to 2026, synthesizes knowledge on microbiome-mediated regulation examining major pathogens including Vibrio cholerae, enterohemorrhagic Escherichia coli, Salmonella species, Clostridioides difficile, and Staphylococcus aureus. A triangular interaction model is presented, linking host immunity, resident microbiome, and invading pathogen to frame infection outcomes. Commensal bacteria regulate pathogen behavior through quorum sensing interference, metabolite-mediated regulation via short-chain fatty acids and bile acids, competitive exclusion, immune response modulation, and direct antimicrobial production. Key species-Lactobacillus spp. Bifidobacterium spp. Bacteroides thetaiotaomicron, and Faecalibacterium prausnitzii-employ distinct molecular strategies against these pathogens. Organ-on-chip platforms and multi-omics advances reveal context-dependent interactions. Clinical applications including rationally designed probiotics, fecal microbiota transplantation, and precision microbiome engineering show promise despite challenges of inter-individual microbiome variability, representing a paradigm shift toward ecosystem-based infectious disease management.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>本研究綜述了2016年至2026年間關於腸道微生物群調控病原體毒力（如霍亂弧菌、大腸桿菌、沙門氏菌等）的分子機制。作者提出了一個結合宿主免疫、共生菌群與入侵病原體的「三角交互模型」，闡述了共生菌如何透過群體感應干擾、代謝產物（如短鏈脂肪酸、膽汁酸）調節、競爭性排斥及免疫調節來抑制病原體。研究強調了乳酸桿菌、雙歧桿菌及普拉梭菌等關鍵菌種的保護機制，並探討了器官晶片與多體學技術在揭示交互作用上的貢獻。此研究主張從生態系統角度管理傳染病，指出益生菌設計、糞便菌群移植及精準微生物組工程是未來治療的關鍵方向，雖面臨個體差異挑戰，但為臨床感染控制提供了典範轉移。</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42642836/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>42640100</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Revisiting gut microbiota-driven ammonia metabolism: from disease burden to physiological adaptation.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Gut microbes</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Ammonia homeostasis is governed by interconnected host and microbial pathways, including hepatic ureagenesis, glutamine synthesis, and gut microbiota-mediated urea hydrolysis, proteolysis, and amino acid deamination. Ammonia has historically been viewed primarily as a nitrogenous waste product and neurotoxic molecule, a concept strongly supported by studies of hyperammonemia and hepatic encephalopathy. Impaired hepatic clearance, portosystemic shunting, and enhanced gut-derived ammonia input increase systemic ammonia burden and are linked to neurological dysfunction, muscle wasting, immune dysregulation, and progression of liver disease. In the gut lumen and mucosal environment, however, gut microbes not only generate ammonia but can also reuse ammonia-derived nitrogen for amino acid synthesis, microbial biomass formation, and community nitrogen exchange. Evidence from selected physiological and preclinical models indicates that microbiota-derived ammonia may contribute to nitrogen recycling, microbial community maintenance, enteric neural regulation, or metabolic adaptation under defined conditions. These roles are more context-specific and less broadly established than the pathological effects of systemic hyperammonemia. When epithelial barrier integrity is compromised, hepatic clearance declines, or host buffering reserves are depleted, elevated ammonia can increase epithelial exposure, portal ammonia input, or peripheral blood ammonia. Conversely, evidence that reduced microbiota-derived ammonia contributes to disease remains limited and currently comes mainly from selected animal models. This review re-examines ammonia metabolism from a gut microbiota-centered perspective. We discuss the ecological origins, spatial distribution, exposure characteristics, host-interface effects, and context-specific outcomes of microbiota-derived ammonia in physiology and disease, and discuss how ammonia should be measured, stratified, and targeted in microbial nitrogen metabolism.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>本綜述重新審視了腸道菌群驅動的氨代謝，探討其從疾病負擔到生理適應的雙重角色。傳統上，氨被視為具神經毒性的代謝廢物，與高氨血症、肝性腦病及肝病惡化密切相關。然而，在腸道微環境中，微生物不僅產生氨，亦能利用氨源氮進行氨基酸合成與群落氮循環，展現出維持腸道神經與代謝適應等生理功能。文章強調，氨的病理與生理效應高度取決於上皮屏障、肝臟清除能力及宿主緩衝儲備。本研究為腸道微生物氮代謝提供了新的生態與臨床視角，並討論了未來如何精確測量及標靶氨代謝的策略。</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42640100/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>42640624</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Gut microbial diversity at baseline conditions the clinical, microbiome, and metabolic response to paraprobiotic Lactiplantibacillus plantarum LRCC5282 in overweight adults.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Gut microbes</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>16S, metabolomics</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>120 位過重成人</t>
+        </is>
+      </c>
+      <c r="G25" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>The gut microbiota is increasingly recognized as a target for obesity management; however, whether baseline gut microbial diversity conditions responsiveness to microbiota-targeted interventions remains unclear. We aimed to investigate whether baseline gut microbial diversity is associated with responsiveness to a paraprobiotic derived from Lactiplantibacillus plantarum LRCC5282 (LP5282-P) in overweight adults. In a 12-week, randomized, double-blind, placebo-controlled, multicenter trial of 120 overweight adults, LP5282-P produced no significant between-group differences in any clinical outcome across the overall per-protocol population. However, in the low-diversity subgroup, LP5282-P was associated with significant reductions in body weight, body mass index, and circulating leptin levels. These clinical changes were accompanied by compositional shifts in the gut microbiota, including higher relative abundances of Christensenellaceae, Faecalibacterium, and Alistipes. Fecal metabolite profiles showed elevated acetate and butyrate concentrations and altered bile acid composition. Within the low-diversity subgroup, changes in the relative abundances of Akkermansia and Eubacterium were inversely correlated with changes in body weight, body fat mass, and leptin levels. In contrast, the high-diversity subgroup exhibited no consistent response across the outcome domains examined. Overall, baseline gut microbial diversity was associated with differential responsiveness to LP5282-P, supporting its potential use as a stratification variable in future microbiota-targeted intervention trials. Further studies integrating direct measures of microbial activity and host response are warranted to elucidate the biological pathways underlying this diversity-dependent responsiveness. Trial registration: Clinical Research Information Service (CRIS), KCT0008119.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>本研究旨在探討基準線腸道微生物多樣性，是否會影響過重成人對副乾酪乳桿菌（LP5282-P）介入的臨床、菌群及代謝反應。在一項為期12週、納入120位過重成人的臨床試驗中，整體人群並未展現顯著差異；然而，在「低多樣性」亞群中，LP5282-P顯著降低了受試者的體重、BMI與血清瘦素水平，並促使腸道有益菌（如 *Faecalibacterium* 與 *Alistipes*）豐度上升，同時提升糞便中乙酸與丁酸濃度並改變膽汁酸組成。相反地，「高多樣性」亞群則無一致反應。此研究證實基準線菌群多樣性是預測益生菌療效的重要關鍵，可作為未來精準微生態介入與體重管理的分層依據。</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42640624/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>42642834</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Glycosylation in gut-brain communication: from the intestinal barrier and microbiota to immune and neural signaling.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Gut microbes</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>The gut-brain axis is a complex bidirectional communication network linking the gastrointestinal tract and the central nervous system. Its dysregulation is closely associated with a wide range of gastrointestinal, metabolic, and neuropsychiatric disorders. Glycosylation, one of the most prevalent and structurally diverse post-translational modifications of proteins and lipids, is increasingly recognized as a regulator of multiple processes within the gut-brain axis. In this review, we summarize evidence that glycosylation influences several steps of gut-brain communication, including intestinal barrier function, microbial glycan metabolism, immune signaling, enteric and vagal pathways, blood-brain barrier integrity, and neural responses. We distinguish direct mechanistic findings from associative observations and discuss the more limited evidence for brain-to-gut regulation of intestinal glycosylation. In addition, we discuss the potential of glycosylation-targeted nutritional and microbiota-based interventions and highlight emerging opportunities to integrate glycomics with other omics approaches to dissect the complex regulatory networks underlying the gut-brain axis. In conclusion, elucidating how glycosylation shapes signaling along the gut-brain axis may open new avenues for understanding disease pathogenesis and for developing targeted therapeutic strategies.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>本文探討「腸-腦軸線」（Gut-Brain Axis）中醣基化（Glycosylation）修飾的關鍵調節角色。醣基化作為蛋白質與脂質重要的轉譯後修飾，深刻影響腸道屏障功能、微生物聚醣代謝、免疫訊息傳遞及血腦屏障完整性。研究重點解析了醣基化如何調控腸道與中樞神經系統間的溝通，並區分了機制性證據與相關性觀察。本文不僅強調了醣基化在維繫軸線穩定中的核心地位，更提出透過營養干預與微生物調節，結合多體學（Omics）分析醣基化網絡，將有望為神經精神疾病與代謝性障礙提供創新的診斷與治療策略。</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42642834/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>42635403</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Baseline gut microbiome ecology predicts long-term fat mass loss after bariatric surgery: evidence for a thrifty Bifidobacterium phenotype.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Gut microbes</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>16S, metabolomics</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>85 位重度肥胖患者及 21 位健康對照組（共 106 名受試者）</t>
+        </is>
+      </c>
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Bariatric surgery (BS) induces weight loss, but long-term success involves complex host-microbiome interactions. We evaluated the longitudinal impact of BS, microbiome resilience, and Mediterranean Diet (MedDiet) adherence up to 24 months. This prospective observational study included 85 patients with severe obesity undergoing BS and 21 normal-weight healthy controls (HC). MedDiet adherence (PREDIMED) was assessed before surgery. Fecal microbiota (16S-rRNA sequencing) and metabolomics (1H-NMR spectroscopy) were analyzed at baseline and at 1-, 6-, and 12-months post-BS. Clinical outcomes and fat mass, evaluated by bioimpedanciometry, were tracked up to 24 months. At baseline, patients exhibited higher microbial Shannon diversity than controls (p = 0.041), alongside a dysfunctional microbiome and metabolome characterized by a higher Firmicutes/Bacteroidetes ratio and elevated levels of branched-chain amino acids (p &lt; 0.0001). Ordinary Least Squares (OLS) regression analysis revealed that MedDiet adherence and type 2 diabetes status significantly modulated baseline diversity. At 12 months post-BS, the gut ecosystem underwent profound remodeling, characterized by depletion of Bifidobacterium spp. and an increase in butyrate levels (p &lt; 0.0001), establishing a novel adaptive state distinct from HC. Baseline gut ecology significantly conditioned long-term BS outcomes: patients in the highest quartile of baseline Bifidobacterium spp. lost significantly less fat mass at 24 months than those in the lowest (6.6% vs. 13.2%, p = 0.010). High baseline Bifidobacterium abundance paradoxically acts as a "thrifty microbiome," potentially maximizing energy harvest and limiting surgery-induced fat loss. Overall, BS induces adaptive microbiome restoration rather than true normalization, highlighting the potential for precision interventions prior to surgery.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>本研究探討減重手術（BS）後腸道微生物群與長期減脂效果的關聯。研究追蹤 85 名患者於術前及術後長達 24 個月的變化，分析發現手術顯著重塑了腸道菌相與代謝環境，特別是雙歧桿菌（*Bifidobacterium*）的耗竭與丁酸鹽的增加。關鍵發現指出，術前高豐度的雙歧桿菌反而成為一種「節儉型表型」，會增加能量攝取效率，導致術後 24 個月的脂肪減少量顯著較少（6.6% 對比 13.2%）。這顯示減重手術並非使微生物組回歸常態，而是引發一種適應性重組。此研究凸顯了術前腸道生態作為預測手術成效生物標記的潛力，對於未來制定精準的術前介入策略具有重要的臨床指導意義。</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42635403/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>42635401</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Fecal filtrate transplantation as salvage therapy for fulminant Clostridioides difficile infection in adult hematological patients during chemotherapy-induced aplasia: a pilot experience.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Gut microbes</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>16S, metagenomics</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>3 位成人血液腫瘤患者</t>
+        </is>
+      </c>
+      <c r="G28" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Fulminant Clostridioides difficile infection (CDI) in patients with hematologic malignancies during chemotherapy-induced aplasia carries high mortality and limited treatment options. Our objective was to evaluate fecal filtrate transplantation (FFT) as a salvage therapy for fulminant CDI during aplasia, and to explore whether donor-recipient phage dynamics may contribute to clinical response. We conducted a single-center, prospective, protocol-defined pilot case series study including consecutive adults with hematologic malignancies, chemotherapy-induced grade-4 aplasia and fulminant CDI, refractory to ≥5 d of high-dose oral vancomycin plus intravenous metronidazole and tigecycline. FFT was prepared from a single unrelated donor using sequential centrifugation and filtration, and administered via nasogastric tube in two doses. The primary outcome was sustained clinical cure, secondary outcomes included survival and adverse events, assessed at +14 and +30 d post-FFT. 16S rRNA gene sequencing was used to assess microbiome compositions, while viral metagenomics and in vitro propagation assays were employed to characterize donor-recipient phageome interactions. Three patients with adverse-risk acute myeloid leukemia and fulminant CDI caused by genetically distinct C. difficile strains received FFT. All patients achieved clinical resolution by day +14, accompanied by improvements in abdominal distension and inflammatory markers. By day +30, one patient died from Pseudomonas aeruginosa septic shock, while two maintained remission with confirmatory follow-up. FFT was well tolerated, with no procedure-related immediate complications or FFT-attributable adverse events. Microbiome and phage profiling revealed heterogeneous responses, including shifts in bacterial community composition, with no clear evidence for a general role of donor-derived phages in CDI resolution. In contrast, we observed induction of prophages harbored by recipient-associated Clostridium species, which may have contributed to decolonization through stress-induced entry into the lytic cycle. FFT was feasible, with rapid sustained CDI resolution in hematologic patients with chemotherapy-induced aplasia. ClinicalTrials.gov identifier NCT07172191. Prospective single-center pilot study of fecal filtrate transplantation (FFT) for fulminant-refractory C. difficile infection in three aplastic adult hematologic patients. FFT was well tolerated, achieved rapid clinical cure, and showed heterogeneous microbiome and phageome modulation, potentially contributing to therapeutic effects.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>本研究旨在評估糞便濾液移植（FFT）作為挽救療法，治療化療致免疫不全之血液腫瘤患者合併難治猛爆性艱難梭菌感染（CDI）的療效，並探討供受體間噬菌體的動力學關係。此臨床先導試驗納入3位患者，結果顯示FFT耐受性良好，所有患者在接受治療後14天內均達到臨床緩解。微生態與噬菌體體學分析顯示，臨床症狀的改善並非源於供體噬菌體的直接轉移，而是FFT可能誘發了受體腸道內艱難梭菌的原噬菌體進入溶菌週期，進而促進病原菌清除。本研究證實FFT在此高風險族群中具安全性與可行性，為難治性CDI提供了創新的機制見解與治療選擇。</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42635401/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>42659434</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Blechomonas campbelli from Ctenocephalides felis: in vitro development, thermotolerance, and phylogenetic insights.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Memorias do Instituto Oswaldo Cruz</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>metagenomics, others</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>340 隻跳蚤（每 4 隻混合為一個檢體，共 85 個混合檢體）</t>
+        </is>
+      </c>
+      <c r="G29" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Blechomonas spp. are flea-specific monoxenous trypanosomatids, whose biology, host range, and geographic distribution remain poorly understood, even for species inhabiting ubiquitous cat and dog fleas. To isolate and characterise blechomonads from fleas of domestic dogs in Brazil, focusing on culture growth, morphology, and phylogenetic relationships. Fleas collected from dogs in Sabará, Brazil, were morphologically identified and screened by cultivation. The isolate FL-1 was analysed for temperature-dependent growth, morphology, and phylogeny using 18S rRNA and gGAPDH sequences, including those mined from public metagenomic datasets. Of 340 fleas (four per pool), only one culture tested positive. Growth was optimal at 25ºC, reduced at 30ºC, and absent at 35ºC. Four cell types were revealed, including a predominant "uromonad" stage specialised for attachment and aggregation. Phylogenetic analyses placed the isolate within Blechomonas campbelli and indicated that this species and Blechomonas lauriereadi occur in Ctenocephalides spp. from multiple continents. Blechomonas campbelli exhibits developmental adaptations to the flea gut and limited tolerance to elevated temperatures, constraining its potential to persist in warm-blooded hosts. These findings highlight the value of combining culture-based and in silico approaches to investigate flea-associated trypanosomatids.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>本研究旨在分離並鑑定巴西家犬跳蚤中的*Blechomonas*屬錐蟲，分析其體外培養、形態特徵與系統發育關係。研究從 340 隻跳蚤中成功分離出 FL-1 株，並鑑定為 *Blechomonas campbelli*。結果顯示其最佳生長溫度為 25ºC，35ºC 時無法生長，證實其對高溫的耐受性有限，限制了其在溫血宿主體內存活的能力。形態學分析揭示了四種細胞類型，並以利於附著與聚集的「uromonad」型為主。系統發育分析顯示，該物種廣泛分布於多個大洲的貓蚤屬中。本研究闡明了該錐蟲對昆蟲腸道的發育適應性，並展示了結合傳統培養與公共總體基因體數據挖掘在病原體研究中的科學價值。</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42659434/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>42635406</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Separating extracellular from intracellular fecal metabolites exposes cross-feeding architecture in the gut: exploring metabolite partitioning and ecological associations.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Gut microbes</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>metagenomics, metabolomics</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>63 個糞便檢體（來自 63 位健康受試者）</t>
+        </is>
+      </c>
+      <c r="G30" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>The gut microbiota forms a complex ecosystem through metabolic interdependence (cross-feeding). However, conventional fecal metabolomics typically quantifies only total metabolite pools, making it difficult to distinguish extracellular-enriched metabolite pools from predominantly cell-associated ones, and thus limiting reconstruction of in situ metabolic networks. Here, we quantified fecal metabolites in paired fractions from the same specimen: an undisrupted fraction representing the extracellular pool and a strongly bead-beaten fraction representing the total pool; the intracellular pool was defined as the difference between total and extracellular measurements. Stool samples from 63 healthy individuals were analyzed for short-chain fatty acids, polyamines, and water-soluble vitamins, and the results were integrated with shotgun metagenomic profiles of species composition and functional genes. Vitamins exhibited two distinct behaviors. Adenosylcobalamin (a vitamin B12 coenzyme) was detectable only after disruption, and together with thiamine (B1) and niacin (B3) was classified as an intracellular-retained type (Type 1). In contrast, biotin (B7) and pantothenate (B5) showed higher extracellular proportions (Type 2). Integrative analyses further indicated that Type 1 thiamine was negatively associated with Blautia, consistent with intensive microbial utilization, whereas Type 2 biotin was strongly positively associated with Alistipes, suggesting links to ecological niches shaped by luminal pH and fermentation modes (carbohydrate vs protein fermentation). Fraction-resolved quantification provides a practical operational framework to differentiate extracellular from cell-associated metabolite pools, helping reconcile metagenomic potential with metabolomic reality and enabling deeper inference of cross-feeding structure in the gut ecosystem.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>本研究針對腸道微生物的代謝互營機制（cross-feeding）進行探討。傳統糞便代謝組學僅能分析總代謝物，無法區分細胞外與細胞內代謝池，限制了對代謝網絡的解析。研究團隊透過對比未破碎（代表細胞外池）與強力破碎（代表總代謝池）的糞便樣本，成功推算出細胞內代謝物的分佈。針對短鏈脂肪酸、多胺與水溶性維生素的分析顯示，維生素呈現兩類分佈：B12、B1 與 B3 傾向保留於細胞內（Type 1），而 B7 與 B5 則富集於細胞外（Type 2）。結合宏基因組分析發現，Type 1 代謝物與特定細菌（如 *Blautia*）的利用模式顯著相關，Type 2 代謝物則與 *Alistipes* 及腸道生態位特徵（如 pH 值、發酵類型）相關。此方法為區分代謝物空間分佈提供了實用架構，有助於更精確地將宏基因組功能潛力與代謝體現實連結，深入理解腸道微生物的互營生態結構。</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42635406/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>42634246</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Natural microbiota confer life-long protection against obesity via an early-life, immune-mediated effect on brown adipocytes.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Gut microbes</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G31" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Obesity, a major risk factor for metabolic disease, has increased in industrialized nations alongside a reduction in gut microbiota diversity. Reconstituting laboratory mice with complex, natural microbiota and commensals from wild mice resulted in protection against diet-induced obesity. These natural microbiota reduced weight gain in both male and female mice of different genetic backgrounds throughout their life and increased energy expenditure. Single-nuclei RNA sequencing identified a dominant adipocyte population in brown adipose tissue (BAT) with a transcriptional signature of increased thermogenic activity, while white adipose tissue mass and beiging were reduced. Protection against diet-induced obesity was transferable to adult germ-free mice via exposure to natural microbiota, indicating an association with the timing of immune response induction rather than BAT developmental programming. However, protection against diet-induced obesity did not require type 2 immune signaling, as shown in STAT6 knockout mice. Rather, it was associated with increased levels of chemokines and monocytes in BAT in early life, pointing to a role of infiltrating myeloid cells. Indeed, CCR2-deficient mice with natural microbiota lacked the BAT transcriptional signature of increased thermogenic activity, increased energy expenditure, and protection against diet-induced obesity that wild-type mice with natural microbiota exhibited. The latter was restored upon injection with wild-type bone marrow. Taken together, these findings identify a novel microbiota‒immune‒adipose tissue axis that results in increased BAT thermogenesis and improved energy balance throughout life.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>本研究旨在探討野生小鼠的天然腸道菌相如何預防飲食引起的肥胖。研究發現，移植天然菌相能終生保護不同遺傳背景的實驗小鼠免於肥胖，並顯著增加能量消耗。單細胞核RNA定序（snRNA-seq）顯示，這與褐色脂肪組織（BAT）中產熱活性增強的脂肪細胞亞群有關。此保護機制並非透過第二型免疫信號，而是依賴於早期生命階段骨髓源性細胞（特別是CCR2+單核細胞）向BAT的浸潤與免疫調節。本研究首次揭示了一條全新的「腸道菌群—免疫—脂肪組織」軸，證實早期菌相暴露能透過免疫介導促進褐色脂肪產熱，為肥胖及代謝性疾病的防治提供了新穎的科學依據與治療靶點。</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42634246/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>42644084</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Viral metagenomics of synanthropic urban bats: A surveillance strategy for uncovering potentially zoonotic viruses.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>One health (Amsterdam, Netherlands)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>metagenomics</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>150對肺部與腸道檢體（篩選自採集的2,422隻蝙蝠）</t>
+        </is>
+      </c>
+      <c r="G32" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Bats are natural reservoirs for diverse viruses, including coronaviruses, filoviruses, and paramyxoviruses, several of those known to be involved in zoonotic spillover events and demanding an integrated surveillance. Here, we present a framework that leverages Brazil's rabies passive surveillance programme to detect bat-borne viruses. Using an algorithm to select representative specimens from 2422 bats collected across São Paulo state, we submitted 150 paired lung and intestine samples to nanopore metagenomic sequencing. We detected 98 viral contigs from 12 families of public health relevance, including Arenaviridae, Coronaviridae, and Paramyxoviridae. Notably, the approach identified a previously unknown filovirus in bats in the Americas, validating the framework's capacity for epidemic preparedness. These findings reveal an undetected viral diversity and demonstrate how existing animal surveillance can monitor pathogen threats. Crucially, in a workshop involving multisectoral One Health experts in Brazil, this framework was validated as a scalable model for national expansion, adapted for low- and middle-income countries (LMICs).</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>本研究旨在利用巴西現有的狂犬病被動監測計畫，建立一個監測都市蝙蝠攜帶人畜共通傳染病毒的框架。研究團隊從聖保羅州收集的2,422隻蝙蝠中，篩選出150對肺部與腸道檢體進行奈米孔總體基因體定序。結果成功檢測出屬於12個具公共衛生相關科別（如冠狀病毒科、副黏液病毒科、沙狀病毒科）的98個病毒 contigs，並首次在美洲蝙蝠中發現一種未知的絲狀病毒。此研究證實，利用現有動物監測系統能有效發掘潛在的病毒多樣性，並為中低收入國家提供了一個具可擴展性且符合「健康一體（One Health）」理念的傳染病預防與監測模型。</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42644084/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>42637484</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Insights into the analysis of microbial communities in fermented foods from the perspective of DNA-based techniques.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Food research international (Ottawa, Ont.)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>16S, metagenomics</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>The quality, flavor, and stability of fermented foods depend on the microbial community. However, microbial dynamics are difficult to observe directly, leading to limited control over fermentation. High-throughput sequencing is a revolutionary tool for microbial characterization, among which DNA-based amplicon and metagenomic sequencing are core techniques. Nevertheless, the related data processing workflows in the context of fermented foods have not yet been systematically summarized, hindering the translation of research findings into fermentation practices. This review clarifies the applications of amplicon and metagenomic sequencing in fermented foods. For amplicon sequencing, the impacts of target regions, data preprocessing, and reference databases are addressed. For metagenomic sequencing, sequencing strategies, read-based and binning-based analytical methods, functional annotation, and species-specific databases are discussed. In addition, major strategies for downstream analysis of community data are summarized, including microbial diversity, co-occurrence networks, niche and community assembly, key environmental drivers, and machine learning-based prediction. Amplicon sequencing efficiently reveals microbial succession during fermentation but has limitations in functional annotation. Metagenomic sequencing is notable for functional annotation, enabling the linkage between microbial communities and metabolic potential alongside community characterization. Standardized data preprocessing and specific databases are critical for improving characterization. For community data, integrated analysis allows uncovering the driving factors of microbial succession, thereby helping to regulate fermentation. Notably, the compositional nature of the data must be considered and validated to avoid spurious associations. In summary, the exponential growth of sequencing data will propel the era of precision fermentation.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>本文為一篇綜述性研究，旨在探討以 DNA 為基礎的高通量定序技術（包含擴增子定序與宏基因組學）在發酵食品微生物群落分析中的應用。研究指出，儘管高通量定序技術已成為解析微生物動態的革命性工具，但目前缺乏系統性的數據處理框架，限制了科學發現向產業實踐的轉化。本文詳細梳理了從目標區域選擇、數據預處理、參考數據庫建立到下游生物資訊分析（如共現網絡、生態棲位構建及機器學習預測）的標準化流程。研究強調，擴增子定序雖能有效揭示群落演替，但在功能註解上存在限制；而宏基因組學則具備更強的功能解析潛力，能將微生物組成與代謝功能聯繫起來。透過標準化數據處理流程並考慮數據的組成特性，這些先進技術將精準調控發酵過程，引領精密發酵時代的到來。</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42637484/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>42637478</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Effects of sorghum variety on fermentation microecology and flavor characteristics of sesame-flavor Baijiu.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Food research international (Ottawa, Ont.)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>16S, metabolomics</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>3 種高粱品種（Hongyingzi, Hei'e, G），於 2 輪發酵週期中，在 3 個時間點（0、15、50 天）採集發酵酒醅檢體（樣本總數依實驗設計推算為 18 組發酵樣品）</t>
+        </is>
+      </c>
+      <c r="G34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sorghum, the principal raw material for Baijiu fermentation, plays a key role in shaping fermentation microecology and flavor formation. However, the effects of sorghum varietal differences on sesame-flavor Baijiu fermentation remain insufficiently understood. In this study, three sorghum varieties, Hongyingzi (R), Hei'e (B), and a domestic cultivar (G), were compared over two consecutive fermentation rounds. Fermented grain (Jiupei) samples collected at 0, 15, and 50 days were analyzed for physicochemical properties, enzyme activities, microbial communities, volatile compounds in Jiupei and base liquor, and the taste characteristics of the corresponding base liquor. Despite showing similar overall fermentation trends, the three sorghum varieties differed in acid accumulation, starch utilization, microbial succession, and volatile composition. Fungal communities shifted from early Pichia dominance to multi-genus coexistence, whereas bacterial communities progressively converged toward Lactobacillus dominance. A total of 218 and 258 volatile compounds were identified in Jiupei and 176 and 192 in base liquor from the first and second rounds, respectively. Esters were the dominant differential class, and volatile-marker profiles varied among sorghum varieties and fermentation rounds, with no single variety showing consistent enrichment across all sesame-flavor-related compounds. These results indicate that sorghum variety is an important factor associated with microbial assembly and flavor formation during sesame-flavor Baijiu fermentation, and provide a basis for raw material selection and flavor-oriented process optimization.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>本研究旨在探討不同高粱品種對芝麻香型白酒發酵過程中，微生物群落結構與風味代謝物質形成的影響。研究比較了紅纓子（R）、黑鵝（B）與國內品種（G）三種高粱，分析其在發酵過程中的理化特性、微生物演替及揮發性化合物組成。研究發現，儘管各品種發酵趨勢相似，但在酸度累積、澱粉利用率及微生物群落演替上存在顯著差異；真菌群落由早期的畢赤酵母（*Pichia*）主導轉變為多菌屬共存，細菌群落則趨向於乳桿菌（*Lactobacillus*）主導。分析鑑定出上百種揮發性化合物，其中酯類是導致風味差異的主要代謝物。本研究證實了高粱品種是決定白酒發酵微生物群落組裝與最終風味品質的關鍵因子，為白酒產業的原料選擇與製程最佳化提供了重要的科學依據。</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42637478/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>42637476</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>A Shenling Baizhu San polysaccharide fraction (SLP-2)-based synbiotic alleviates lactose-induced gut dysfunction via a microbiota-metabolite-barrier axis.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Food research international (Ottawa, Ont.)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>16S, metabolomics</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G35" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Lactose intolerance (LI) is a common digestive disorder, and its management still relies largely on dietary restriction. Because gut microbial fermentation and barrier dysfunction contribute to LI-related symptoms, microbiota-targeted prebiotic or synbiotic strategies may provide complementary approaches. However, the active plant-polysaccharide fractions and their microbial partners remain unclear. This study aimed to identify the bioactive polysaccharide fraction from Shenling Baizhu San and evaluate its pairing with responder bacteria for alleviating high-lactose diet (HLD)-induced intestinal dysfunction. Stepwise ethanol precipitation yielded SLP-2, which was subsequently identified as the principal bioactive fraction through human fecal fermentation, monoculture assays, and an HLD rat model. SLP-2 enriched Eubacterium-associated taxa and supported the growth of Akkermansia muciniphila in monoculture and in vivo. Building on this, a synbiotic combining SLP-2 with A. muciniphila and E. rectale alleviated HLD-induced gut dysfunction; the antibiotic-matched comparison with the probiotics-only group supported an SLP-2-associated contribution. The synbiotic intervention was associated with increased tight junction proteins, MUC2 expression, improved intestinal architecture, and thicker mucus layers. Multi-omics analysis linked co-metabolites, including intestinal 6-MGG and HTy-Ac and systemic DHPV-G, with barrier restoration and an immune profile characterized by increased IL-10 and lower TLR4 expression. These findings suggest that SLP-2-based synbiotic intervention alleviates HLD-induced intestinal dysfunction through microbiota-metabolite-barrier modulation, providing preclinical evidence for future functional-food strategies pending human validation.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>本研究旨在探討參苓白朮散多醣活性組分（SLP-2）結合特定菌株，對高乳糖飲食（HLD）引發之腸道功能障礙的緩解作用。研究發現，SLP-2能促進*A. muciniphila*與真桿菌屬相關菌群生長。以SLP-2搭配益生菌的合生元配方，能顯著改善HLD大鼠的腸道屏障，包含增加緊密連接蛋白與MUC2表達、增厚黏液層。多體學分析顯示，其保護作用與腸道及全身性代謝物（如6-MGG、DHPV-G）的調節，以及抗發炎反應（提升IL-10、降低TLR4）密切相關。此發現為開發防治乳糖不耐症的功能性食品提供了臨床前依據。</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42637476/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>42637471</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Fucoidan from giant kelp alleviates postmenopausal osteoporosis by regulating the betaine-OPG/RANKL/RANK signaling axis.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Food research international (Ottawa, Ont.)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>16S, metabolomics</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G36" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Postmenopausal osteoporosis (PMOP), characterized by excessive bone resorption and impaired bone remodeling, remains a significant global health challenge. This study investigated the protective effects of fucoidan from giant kelp (GKP) against PMOP and its underlying mechanisms in ovariectomized mice. GKP supplementation attenuated bone loss by preserving trabecular microarchitecture, normalizing systemic mineral homeostasis, and suppressing osteoclastogenesis, as evidenced by the downregulation of osteoclast-related genes. 16S rRNA gene sequencing revealed that GKP reshaped the gut microbiota by decreasing the Bacteroidota/Firmicutes ratio and enriching beneficial taxa, which promoted short-chain fatty acid production. Targeted metabolomics revealed that GKP induced profound systemic metabolic reprogramming, particularly amino acid metabolism, and identified betaine as a key systemic metabolite effector upregulated following GKP treatment. In vitro assays demonstrated that betaine suppressed receptor activator of nuclear factor-κB ligand (RANKL)-induced osteoclast differentiation and mitigated inflammation. In vivo validation demonstrated that betaine intervention recapitulated the osteoprotective phenotype observed in GKP-treated mice, which was associated with regulation of the osteoprotegerin/RANKL/RANK signaling axis. These results indicate that GKP exerts anti-osteoporotic effects in association with changes in gut microbiota and systemic metabolism, while betaine-mediated regulation of the OPG/RANKL/RANK signaling may contribute to its osteoprotective activity.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>本研究探討巨藻褐藻醣膠（GKP）對去卵巢小鼠更年期後骨質疏鬆症（PMOP）的保護機制。結果顯示，補充GKP能有效減少骨質流失並抑制破骨細胞生成。16S定序顯示GKP重塑了腸道菌群（降低擬桿菌門/厚壁菌門比例），促進短鏈脂肪酸產生。代謝組學分析發現，GKP顯著提升了系統性代謝物甜菜鹼（betaine）的含量。體內外實驗進一步證實，甜菜鹼透過調控OPG/RANKL/RANK信號軸，能抑制破骨細胞分化並緩解骨質流失。本研究證實GKP具備透過「腸道菌群-代謝物」軸抗骨質疏鬆的潛力，為PMOP防治提供了科學依據。</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42637471/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>42637450</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Highland barley polysaccharides promoted lactose intestinal fermentation in vitro: Unveiling the dynamic response of gut microbiota and polysaccharide structure.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Food research international (Ottawa, Ont.)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>16S, metabolomics</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>乳糖不耐症患者的糞便檢體（未提及具體數量）</t>
+        </is>
+      </c>
+      <c r="G37" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Lactose intolerance affects over 70% of the global population due to the untimely metabolism of lactose in the colon. To accelerate lactose metabolism, we innovatively employed highland barley polysaccharides (HBP) to modulate the colonic fermentation efficiency of lactose using an in vitro fermentation model and fecal samples from lactose intolerant patients. With the addition of HBP, the consumption efficiency of lactose began to increase after 6 h of fermentation. At 48 h, lactose consumption increased by 29%, surpassing the effect of commercial prebiotics. Meanwhile, HBP with lower molecular weight (HBP-L, 8.69 × 104 g/Mol) exhibited more effective impacts than HBP with high molecular weight (HBP-H, 1.22 × 105 g/Mol), which was particularly evident during the 12-48 h of fermentation. More importantly, HBP, particularly HBP-L, substantially enriched Segatella, Bifidobacterium, and Ligilactobacillus in a time-dependent manner and was positively correlated with decreased lactose levels and elevated bacterial lactase activity, resulting in significant conversion of lactose to lactic acid and short-chain fatty acids. During the first 12 h of fermentation, HBP-L underwent more significant degradation than HBP-H. Meanwhile, the xylose residues and Glcp glycosidic bonds in HBP-L were preferentially utilized, while it was glucose residue in HBP-H. Thus, it indicated that HBPs were degraded and altered the composition of the gut microbiota, thereby enhancing the fermentation efficiency of lactose. Our findings provide a theoretical basis for developing targeted prebiotic foods to manage lactose intolerance.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>本研究旨在探討青稞多醣（HBP）如何調控乳糖不耐症患者的腸道菌群，以促進體外乳糖發酵與代謝。研究發現，添加 HBP（特別是低分子量的 HBP-L）能在發酵 48 小時後提升乳糖消耗效率達 29%，效果顯著優於商業益生元。機制上，HBP-L 在發酵初期降解更為顯著，並能隨時間特異性富集 *Segatella*、雙歧桿菌屬（*Bifidobacterium*）及 *Ligilactobacillus*，進而提升細菌乳糖酶活性，將乳糖轉化為乳酸與短鏈脂肪酸。本研究證實了青稞多醣能透過重塑腸道菌群結構來加速乳糖代謝，為開發緩解乳糖不耐症的標靶益生元食品提供了重要科學依據。</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42637450/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>42637441</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Microbial succession drives quality deterioration in refrigerated golden pompano (Trachinotus ovatus): regulatory network of dominant spoilage microbiota on characteristic biomarkers.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Food research international (Ottawa, Ont.)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>16S, metabolomics</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G38" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Elucidating the quality deterioration mechanisms of refrigerated golden pompano (Trachinotus ovatus), this study integrated 16S rRNA gene sequencing and untargeted metabolomics to systematically dissect how microbial ecological succession drives metabolic changes. As critical spoilage indicators, total volatile basic nitrogen (TVB-N) and thiobarbituric acid reactive substances (TBARS) continuously increased during storage, indicating significant deterioration by day 6. Microbial community succession analysis revealed that Psychrobacter, Shewanella, and Pseudomonas gradually became the dominant microbiota in the late storage stage. Metabolite enrichment analysis further demonstrated that this shift redirected the metabolic focus from early-stage nucleotide degradation to late-stage protein hydrolysis and amino acid metabolism. Moreover, multivariate statistical analysis identified 50 potential spoilage biomarkers, among which biogenic amines (histamine, tyramine, and phenylethylamine) were recognized as key indicators reflecting spoilage progression. Correlation network analysis revealed positive correlations between Pseudomonas and Shewanella abundances and the accumulation of these biogenic amines. This suggests that these two genera act as the core functional microbiota, driving spoilage metabolite generation and subsequent quality deterioration. Pathway analysis of potential spoilage biomarker generation indicates that amino acid and nucleotide metabolism constitute the core spoilage pathways, with lipid oxidation serving as a complementary mechanism. Overall, this study elucidates the spoilage mechanisms of refrigerated golden pompano, providing chemical targets for early biomarker detection and targeted antibacterial strategies.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>本研究旨在探討冷藏金鯧魚品質劣化的機制。研究結合 16S rRNA 基因定序與非靶向代謝組學，分析微生物群落演替如何驅動代謝變化。結果顯示，金鯧魚冷藏至第 6 天時顯著腐敗。在貯藏後期，*Psychrobacter*、*Shewanella* 與 *Pseudomonas* 逐漸成為優勢菌群，使代謝焦點自初期的核苷酸降解轉向後期的蛋白質水解與氨基酸代謝。研究鑑定出 50 個潛在腐敗生物標誌物（如組胺、酪胺等生物胺），並發現 *Pseudomonas* 和 *Shewanella* 的豐度與這些生物胺的累積呈正相關，為驅動腐敗的核心菌群。本研究闡明了金鯧魚的腐敗機制，為食品早期變質檢測及靶向抑菌策略提供了科學依據與化學標靶。</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42637441/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>42637430</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Regional differentiation of microbial communities and metabolites in Yunnan dry-cured beef: insights from high-throughput sequencing and untargeted metabolomics.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Food research international (Ottawa, Ont.)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>16S, metabolomics</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G39" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>To reveal the effects of regional processing on quality, microbial communities and metabolites of traditional Yunnan dry-cured beef, samples from Xundian (XD), Yuxi (YX) and Honghe (HH) were analyzed. High-throughput sequencing and UHPLC-Q-Exactive HF/MS untargeted metabolomics were applied. Sensory scores and physicochemical Properties differed significantly (p &lt; 0.05). Bacillota and Staphylococcus dominated bacterial communities. The observed differences in microbial communities and metabolites among regions are shaped by the combined effects of geographical environment and processing conditions. Ascomycota was the main fungal phylum. Debaryomyces dominated XD and HH samples. YX samples had a unique fungal profile dominated by Rhodotorula and Cladosporium. A total of 1320 metabolites were identified. 196 differential metabolites were screened. Key pathways included glycerophospholipid metabolism, pyrimidine metabolism and arachidonic acid metabolism. Correlation analysis indicated that Staphylococcus and Lactococcus were positively associated with amino acid derivatives, while Latilactobacillus and Debaryomyces correlated with organic acids and glycerophospholipids. These findings revealed the potential microbial-metabolic association underlying regional quality differences. They provide support for quality control and traceability of dry-cured beef.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>本研究旨在探討地理區域與加工工藝對雲南傳統乾醃牛肉（尋甸、玉溪、紅河三地）品質、微生物群落及代謝物的影響。研究結合高通量定序與非靶向代謝組學技術，發現不同地區的乾醃牛肉在感官評分與理化性質上存有顯著差異。細菌群落以厚壁菌門和葡萄球菌屬為主；真菌群落中，尋甸和紅河樣品以德巴利酵母屬為主，玉溪樣品則以紅酵母屬與枝孢菌屬為特有優勢菌。代謝組學共鑑定出1320種代謝物，其中196種為差異代謝物，主要涉及甘油磷脂、嘧啶及花生四烯酸代謝通路。關聯分析顯示，葡萄球菌屬和乳球菌屬與氨基酸衍生物呈正相關，而廣義乳桿菌屬與德巴利酵母屬則與有機酸及甘油磷脂密切相關。本研究揭示了微生物與代謝物的關聯性，為乾醃牛肉的品質控制與產地溯源提供了重要科學依據。</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42637430/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>42637417</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Allergic responses, gut microbiome and serum metabolism of mice: Effects of epigallocatechin gallate combined with sodium pyrophosphate modified parvalbumin.</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Food research international (Ottawa, Ont.)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
         <is>
           <t>16S, metabolomics</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>未提及</t>
         </is>
       </c>
-      <c r="G22" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="G40" t="b">
+        <v>0</v>
+      </c>
+      <c r="H40" t="inlineStr">
         <is>
           <t>Epigallocatechin gallate (EGCG) combined with sodium pyrophosphate (SP) modified parvalbumin (PV) was proposed to sensitize mice, and investigated whether allergic responses changes were associated with gut microbiome and serum metabolism of mice. EGCG combined with SP modified PV has structural changes, and alleviated jejunal damage in mice, while decreased specific serum IgG, IgG1 and IgE levels and may rebalanced Th1/Th2 immune responses. PV-induced allergic responses disrupted gut microbiota and reduced short-chain fatty acids (SCFAs) levels. In contrast, the modified PV could alter the relative abundance of allergic responses-related gut microbiota, such as g__unclassified_f__Lachnospiraceae, g__norank_o__Clostridia_UCG-014 and g__Alistipes, alongside elevated SCFAs levels. Additionally, the modified PV could affect multiple metabolic pathways in serum, and exert a positive impact on phosphatidylethanolamine and phosphatidylcholine levels in glycerophospholipid metabolism. Therefore, the reduction in the allergic responses of PV modified by EGCG and SP were associated with changes in gut microbiota and modulation of glycerophospholipid metabolisms. These correlational observations provided preliminary associative evidence supporting the potential utility of combined EGCG-SP modification as a hypoallergenic processing approach for fish parvalbumin mitigation.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>本研究旨在探討利用表沒食子兒茶素沒食子酸酯（EGCG）結合焦磷酸鈉（SP）修飾魚類主要過敏原小清蛋白（PV），對小鼠過敏反應、腸道菌群及血清代謝的影響。結果顯示，修飾後的PV結構發生改變，能顯著減輕小鼠空腸損傷，降低血清特異性IgG、IgG1及IgE水平，並重建Th1/Th2免疫平衡。此外，修飾後的PV調節了過敏相關腸道菌群（如*Lachnospiraceae*與*Alistipes*）的相對豐度，提升了短鏈脂肪酸（SCFAs）含量，並改善血清甘油磷脂代謝。本研究證實EGCG-SP聯合修飾可作為降低魚類過敏原性的潛在低致敏加工方法。</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/42637417/</t>
         </is>

--- a/papers_database.xlsx
+++ b/papers_database.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>本研究旨在探討秘魯母親的母乳微生物群與嬰兒缺鐵性貧血（IDA）之間的關聯。研究招募了 46 對母子，並透過 16S rRNA 定序分析母乳樣本。結果顯示，鏈球菌屬（Streptococcus）和葡萄球菌屬（Staphylococcus）為母乳中的主要優勢菌屬。非缺鐵性貧血（non-IDA）嬰兒母親的母乳菌群豐富度，顯著高於健康組與 IDA 組。此外，IDA 組母乳中的棒狀桿菌屬（Corynebacterium）和不動桿菌屬（Acinetobacter）等豐度較高，而鏈球菌屬則有減少趨勢。此發現證實母乳菌群與嬰兒貧血狀態存在關聯，為理解嬰兒貧血的發病機制提供了新的科學線索。</t>
+          <t>本研究旨在探討秘魯母乳微生物相與一歲以下嬰兒缺鐵性貧血（IDA）的關聯。研究團隊招募46對母子，並利用16S rRNA定序技術分析母乳樣本。結果顯示，母乳微生物主要由鏈球菌屬與葡萄球菌屬主導。相較於健康組與IDA組，非缺鐵性貧血（non-IDA）組母親的母乳菌群豐富度顯著較高。此外，IDA組母乳中的棒狀桿菌屬、不動桿菌屬等豐度顯著升高，而鏈球菌屬則呈減少趨勢。本研究證實母乳微生物組成與嬰兒缺鐵性貧血具潛在關聯，為理解嬰兒貧血的病理機制及未來預防策略提供了全新視角。</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>metagenomics, metatranscriptomics, small genome</t>
+          <t>metagenomics, metatranscriptomics</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>本研究成功富集並鑑定了一種具耐鹽鹼特性的新型厭氧氨氧化（anammox）細菌——*Candidatus* Loosdrechtia alkalitolerans（相對豐度&gt;80%）。在長期鹽鹼壓力下（0.5% NaCl, pH~9.13），該菌展現出顯著的競爭優勢。比較基因體與轉錄組分析證實，該菌編碼獨特的Mrp陽離子/質子反向轉運體操縱子，並藉由鈉離子誘導上調其表達，以維持細胞內酸鹼平衡。數據庫檢索顯示其廣泛存在於淡水與廢水系統中。本研究首次闡明了厭氧氨氧化菌的耐鹽鹼分子機制，拓展了對其生理適應性與生態價值的認識。</t>
+          <t>本研究旨在富集並鑑定一種新型耐鹽鹼厭氧氨氧化（anammox）細菌，命名為 *Candidatus* Loosdrechtia alkalitolerans，以探討其對鹼性環境的適應機制。研究團隊成功將其富集至 80% 以上的相對豐度，並證實其在長期鹽鹼壓力下（0.5% NaCl, pH~9.13）具有顯著的競爭優勢。比較基因體學與轉錄分析顯示，該菌編碼完整的 Mrp 陽離子/質子反向轉運體操縱子；添加鈉離子能上調 *mrp* 基因表達，進而在鹼性壓力下恢復其厭氧氨氧化活性。此研究揭示了 Mrp 介導的 pH 調節機制，拓展了對該菌生理可塑性與生態分布的認知。</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>未提及（摘要中僅提及使用慢性結腸炎小鼠模型、人類CCD-18Co纖維母細胞與小鼠原代腸道纖維母細胞，未說明具體樣本數量）</t>
+          <t>DSS誘導的慢性結腸炎小鼠模型（未明確標示具體n值）、人類CCD-18Co細胞株及原代小鼠腸道纖維母細胞</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -624,7 +624,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>本研究旨在探討抗性澱粉（RS）對腸道纖維化的緩解作用及機制。在慢性結腸炎小鼠模型中，RS顯著減輕了腸道纖維化。總體基因體分析顯示，RS重塑了腸道菌群並增加益菌豐度；標靶代謝組分析顯示乙酸（acetate）含量顯著提升。體外實驗證實，乙酸透過抑制去乙醯酶2（HDAC2）並促進H3K27乙醯化，從而阻斷TGF-β誘導的纖維母細胞活化。本研究揭示了「微生物-代謝-表觀遺傳」軸（RS-乙酸-HDAC2-H3K27ac）在減緩纖維化中的潛力，為腸道纖維化疾病提供了新的治療策略與標靶。</t>
+          <t>本研究探討抗性澱粉（RS）對腸道纖維化的改善機制。研究顯示，RS 能顯著緩解 DSS 誘導的小鼠腸道纖維化，降低細胞外基質沈積。宏基因組定序發現 RS 重塑了腸道菌群，增加了如 *Bacteroides acidifaciens* 等短鏈脂肪酸產生菌的豐度；代謝組學分析則證實結腸內乙酸（acetate）水平顯著提升。機轉研究揭示，乙酸能抑制纖維母細胞中組蛋白去乙醯化酶 2（HDAC2）的活性，進而增加 H3K27 的乙醯化修飾，從而抑制 TGF-β 誘導的纖維母細胞活化。本研究揭示了「腸道菌群-代謝物-表觀遺傳」的調控軸，證實了飲食纖維代謝產物在改善纖維化疾病中的潛力，為開發纖維化治療策略提供了新的科學依據。</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4 種珠狀模擬微生物群落（由 26 種臨床分離菌株組成），共進行 25 次重複分析</t>
+          <t>25 次重複分析（針對開發出的 4 種模擬菌群樣本）</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -679,7 +679,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>本研究開發並驗證了四種珠狀模擬微生物群落（mock communities），作為臨床總體基因體下一代定序（mNGS）的品質管制（QC）標準物質。研究人員利用從臨床檢體分離出的26種常見菌株（涵蓋胃腸道、呼吸道、皮膚及生殖道/腦脊髓液），評估核酸萃取試劑盒（MagMAX與PowerSoil）對檢測結果的偏差。在25次重複分析中，多數相對豐度大於20%的主導菌屬其重複性變異低於10%，但不同萃取試劑盒的選擇會顯著影響菌相的分類分佈。此研究證實，模擬微生物群落是推動臨床mNGS流程標準化與品質控管的關鍵工具。</t>
+          <t>本研究旨在解決臨床宏基因組次世代定序（mNGS）在檢測再現性與品質控管上的挑戰。研究開發了四種包含 26 種常見人體微生物（涵蓋腸胃道、呼吸道、皮膚、生殖道及腦脊髓液來源）的模擬菌群（Mock Communities）作為標準質控物質。透過鳥槍法總體基因體定序（shotgun metagenomics），評估了不同 DNA 萃取試劑盒對菌種分布的影響及檢測的精密度。結果顯示，DNA 萃取方法的差異會顯著影響分類群的結果，且該模擬菌群在常見優勢菌種（相對豐度 &gt;20%）中表現出良好的再現性（變異係數 &lt;10%）。此研究對於推動臨床 mNGS 的標準化流程具有重要意義，有助於提升臨床診斷分析的準確性與可信度。</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>308 位瑞典新生兒 (n=308)</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -734,7 +734,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>本研究旨在評估瑞典全國性新生兒世代的腸道菌相組成與功能。研究發現，瑞典新生兒體內的雙歧桿菌（Bifidobacteria）水平普遍偏低，且其腸道菌群在物種組成與代謝功能上呈現獨特特徵。雙歧桿菌是嬰兒早期發育、降解母乳寡糖及促進免疫成熟的關鍵菌。本研究揭示了瑞典嬰兒普遍缺乏此類核心益生菌的現狀，為未來開發針對性的益生菌補充策略或母乳化配方奶粉提供了科學依據，對嬰兒早期健康與免疫發展具有重大臨床意義。</t>
+          <t>本研究是一項針對瑞典新生兒的全國性佇列研究，旨在評估嬰兒腸道微生態的組成與功能特徵。研究發現，瑞典新生兒體內的雙歧桿菌（Bifidobacteria）豐度普遍偏低，且其腸道菌相在物種組成與代謝功能上呈現獨特且不成熟的特徵。雙歧桿菌的缺乏可能影響嬰兒對母乳寡糖（HMOs）的降解與利用，進而對早期免疫與代謝發育帶來潛在影響。此發現揭示了現代西方社會新生兒腸道菌相失衡的現狀，強調了早期微生態發育的地理差異，並為未來透過精準益生菌干預（如補充特定雙歧桿菌）以重建嬰兒腸道健康提供了重要的科學依據。</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>本研究旨在探討巴西里約熱內盧瓜杜河（Guandu river）於2020年1月至3月土臭素危機期間的水質，並利用總體基因體學分析異味化合物與水質之關係。研究發現該水域呈富營養化，且藍菌群落具高度多樣性。功能註釋顯示，水體中不僅存在合成土臭素（*geoA*）與2-甲基異莰醇（*mic*）等異味物質的基因，還廣泛共存多種藍菌毒素（如微囊藻毒素、石房蛤毒素等）的合成基因簇。此發現表明，水體中泥土異味的出現可作為評估藍菌毒素潛在產生風險的指標，對飲用水源的安全監測具有重要科學與公共衛生意義。</t>
+          <t>本研究針對巴西瓜納巴拉河（Guandu River）於 2020 年發生的異味危機進行調查。透過宏基因體定序技術分析水質，研究發現當地水體呈現優養化狀態，且存在多樣化的藍綠菌群落（如 Microcystis 及 Planktothrix 等）。功能性註解分析顯示，這些樣本不僅含有合成異味物質（土臭素 geoA 及 2-MIB）的基因，更同時攜帶多種藍綠菌毒素的生物合成基因群（如微囊藻毒素、神經毒素與擬柱孢藻毒素等）。此發現證實了異味物質與潛在毒素基因在環境中的共存性。這項研究的科學意義在於強調水體的「土腥異味」可作為水質潛在毒性風險的早期警訊，為飲用水安全監測提供了重要的生物資訊參考。</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -806,20 +806,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>42647759</t>
+          <t>42647164</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Gut Microbiome in Multiple Sclerosis.</t>
+          <t>Sex differences in the gut microbiome and related metabolites: role in cardiometabolic disease.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Neurology(R) neuroimmunology &amp; neuroinflammation</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Gut microbes</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11</v>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>others</t>
@@ -827,7 +829,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（本文為綜論性回顧文章，非原創實驗研究）</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -835,12 +837,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Multiple sclerosis (MS) is a chronic inflammatory demyelinating disease of the CNS whose risk and course are shaped by both genetic and environmental factors, among which the intestinal microbiota has emerged as a key, potentially modifiable contributor. People with MS frequently display altered gut microbiota, characterized by depletion of fiber-fermenting, short-chain fatty acid (SCFA)-producing commensals, and expansion of taxa associated with mucus degradation and proinflammatory metabolism. These compositional shifts are paralleled by broad changes in blood and CSF metabolites, including reduced SCFAs, tryptophan-derived aryl hydrocarbon receptor ligands, and secondary bile acids. In addition, several reports highlight the accumulation of aromatic amino acid-derived phenolic and indolic compounds and specific lipid mediators linked to neuroinflammation and neurodegeneration. In this up-to-date review, we synthesize evidence from experimental models and human studies showing how microbial metabolites can influence MS pathogenesis through converging mechanisms: modulation of gut and blood-brain barrier integrity; shaping of T-cell and B-cell responses; direct effects on microglia, astrocytes, and oligodendrocyte lineage cells after crossing into the CNS; and modulation of neural circuits, particularly those involving the vagus nerve. Finally, we highlight current gaps, including the need for longitudinal, harmonized multiomic cohorts, and mechanistic studies integrating microbiome, metabolome, and host readouts across gut, blood, and CNS. Overall, available data support a model in which coordinated disruption of the gut microbiota-metabolite axis, rather than any single pathogen, contributes to MS, opening avenues for microbiota-based and metabolite-based biomarkers and therapies aimed at restoring immune and neuroglial homeostasis.</t>
+          <t>Sex differences in major cardiometabolic diseases (CMD), such as type 2 diabetes, metabolic dysfunction-associated steatotic liver disease, and cardiovascular disease, have been increasingly recognized across the life course. During the reproductive stage, women generally have a more favorable cardiometabolic risk profile than men, but their risk of experiencing CMD significantly increases after menopause. Emerging evidence suggests that sexually dimorphic gut microbiota and gut microbiota-related metabolites (GMRMs) may contribute to such sex disparities. However, existing findings are heterogeneous and underlying mechanisms remain incompletely understood. In this review, we synthesize the evidence examining sex differences in gut microbial diversity, overall composition, taxa abundances, and levels of GMRMs across key life stages, including pre-puberty, adolescence, and different phases of adulthood (with emphasis on pre- and post-menopausal periods). We summarize potential biological mechanisms underlying sexual dimorphism in the gut microbiome and GMRMs, emphasizing the central role of sex steroids, along with contributions from immune function and other host and environmental factors. We further integrate evidence linking sexually dimorphic microbial taxa (e.g., Akkermansia muciniphila, Eubacterium, Ruminococcus, and other Firmicutes taxa) and GMRMs (e.g., microbiota-derived short-chain fatty acids, secondary bile acids, and trimethylamine N-oxide) to key cardiometabolic pathways involving inflammation, glucose and lipid metabolism, and vascular function. Finally, we identify critical knowledge gaps and emphasize the need for future large longitudinal studies that would integrate repeated measurements of the gut microbiome, untargeted metabolomics, and sex steroid hormones across the life course. Such approaches are essential to clarify biological pathways and inform sex-specific microbiome-based interventions for CMD prevention and management.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>本研究探討多發性硬化症（MS）與腸道微生物群之間的關聯。研究指出，MS 患者的腸道菌相呈現失調狀態，包括短鏈脂肪酸（SCFA）產生菌減少，以及促發炎代謝菌的增加。這些微生物群落的變化伴隨著血液與腦脊髓液中代謝物（如色胺酸衍生物、膽汁酸及 SCFA）的顯著改變，這些物質經證實與神經發炎及退化密切相關。文中綜述了微生物代謝產物如何透過調節腸道與血腦屏障完整性、影響免疫細胞（T/B 細胞）反應，以及直接作用於神經膠質細胞來參與 MS 的致病機制。總結而言，MS 的發生與腸道菌群-代謝物軸的整體失調有關，而非單一病原體所致。該研究強調未來需進行多體學（multiomics）整合分析，以開發基於微生物群的生物標記與創新治療策略，旨在恢復患者的免疫與神經恆定。</t>
+          <t>本文旨在探討性別差異在腸道微生物群與相關代謝物（GMRMs）中如何影響心臟代謝疾病（CMD）。研究指出，受性類固醇、免疫功能及環境因素影響，腸道菌相與代謝產物存在顯著的性別二態性。女性在生育期較男性具備更佳的心臟代謝特徵，但停經後風險顯著升高，此變化與特定菌屬（如 *Akkermansia muciniphila*）及代謝物（如短鏈脂肪酸、次級膽汁酸、TMAO）的豐度改變密切相關。這些微生物與代謝物透過調節發炎反應、醣脂代謝及血管功能，進而影響 CMD 的發生。本文強調未來需透過大型縱向研究，結合微生物組學、代謝組學與荷爾蒙監測，以深入解析其生物學機制，並開發針對不同性別的精準微生物介入療法，對於預防及管理心臟代謝疾病具有重要的科學價值。</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -850,29 +852,27 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42647759/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647164/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>42647164</t>
+          <t>42647759</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sex differences in the gut microbiome and related metabolites: role in cardiometabolic disease.</t>
+          <t>The Gut Microbiome in Multiple Sclerosis.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11</v>
-      </c>
+          <t>Neurology(R) neuroimmunology &amp; neuroinflammation</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>others</t>
@@ -880,7 +880,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>未提及（本文為綜論性回顧文章，非原創實驗研究）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -888,12 +888,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sex differences in major cardiometabolic diseases (CMD), such as type 2 diabetes, metabolic dysfunction-associated steatotic liver disease, and cardiovascular disease, have been increasingly recognized across the life course. During the reproductive stage, women generally have a more favorable cardiometabolic risk profile than men, but their risk of experiencing CMD significantly increases after menopause. Emerging evidence suggests that sexually dimorphic gut microbiota and gut microbiota-related metabolites (GMRMs) may contribute to such sex disparities. However, existing findings are heterogeneous and underlying mechanisms remain incompletely understood. In this review, we synthesize the evidence examining sex differences in gut microbial diversity, overall composition, taxa abundances, and levels of GMRMs across key life stages, including pre-puberty, adolescence, and different phases of adulthood (with emphasis on pre- and post-menopausal periods). We summarize potential biological mechanisms underlying sexual dimorphism in the gut microbiome and GMRMs, emphasizing the central role of sex steroids, along with contributions from immune function and other host and environmental factors. We further integrate evidence linking sexually dimorphic microbial taxa (e.g., Akkermansia muciniphila, Eubacterium, Ruminococcus, and other Firmicutes taxa) and GMRMs (e.g., microbiota-derived short-chain fatty acids, secondary bile acids, and trimethylamine N-oxide) to key cardiometabolic pathways involving inflammation, glucose and lipid metabolism, and vascular function. Finally, we identify critical knowledge gaps and emphasize the need for future large longitudinal studies that would integrate repeated measurements of the gut microbiome, untargeted metabolomics, and sex steroid hormones across the life course. Such approaches are essential to clarify biological pathways and inform sex-specific microbiome-based interventions for CMD prevention and management.</t>
+          <t>Multiple sclerosis (MS) is a chronic inflammatory demyelinating disease of the CNS whose risk and course are shaped by both genetic and environmental factors, among which the intestinal microbiota has emerged as a key, potentially modifiable contributor. People with MS frequently display altered gut microbiota, characterized by depletion of fiber-fermenting, short-chain fatty acid (SCFA)-producing commensals, and expansion of taxa associated with mucus degradation and proinflammatory metabolism. These compositional shifts are paralleled by broad changes in blood and CSF metabolites, including reduced SCFAs, tryptophan-derived aryl hydrocarbon receptor ligands, and secondary bile acids. In addition, several reports highlight the accumulation of aromatic amino acid-derived phenolic and indolic compounds and specific lipid mediators linked to neuroinflammation and neurodegeneration. In this up-to-date review, we synthesize evidence from experimental models and human studies showing how microbial metabolites can influence MS pathogenesis through converging mechanisms: modulation of gut and blood-brain barrier integrity; shaping of T-cell and B-cell responses; direct effects on microglia, astrocytes, and oligodendrocyte lineage cells after crossing into the CNS; and modulation of neural circuits, particularly those involving the vagus nerve. Finally, we highlight current gaps, including the need for longitudinal, harmonized multiomic cohorts, and mechanistic studies integrating microbiome, metabolome, and host readouts across gut, blood, and CNS. Overall, available data support a model in which coordinated disruption of the gut microbiota-metabolite axis, rather than any single pathogen, contributes to MS, opening avenues for microbiota-based and metabolite-based biomarkers and therapies aimed at restoring immune and neuroglial homeostasis.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>本文旨在探討性別差異在腸道微生物群與相關代謝物（GMRMs）中如何影響心臟代謝疾病（CMD）。研究指出，受性類固醇、免疫功能及環境因素影響，腸道菌相與代謝產物存在顯著的性別二態性。女性在生育期較男性具備更佳的心臟代謝特徵，但停經後風險顯著升高，此變化與特定菌屬（如 *Akkermansia muciniphila*）及代謝物（如短鏈脂肪酸、次級膽汁酸、TMAO）的豐度改變密切相關。這些微生物與代謝物透過調節發炎反應、醣脂代謝及血管功能，進而影響 CMD 的發生。本文強調未來需透過大型縱向研究，結合微生物組學、代謝組學與荷爾蒙監測，以深入解析其生物學機制，並開發針對不同性別的精準微生物介入療法，對於預防及管理心臟代謝疾病具有重要的科學價值。</t>
+          <t>本研究探討多發性硬化症（MS）與腸道微生物群之間的關聯。研究指出，MS 患者的腸道菌相呈現失調狀態，包括短鏈脂肪酸（SCFA）產生菌減少，以及促發炎代謝菌的增加。這些微生物群落的變化伴隨著血液與腦脊髓液中代謝物（如色胺酸衍生物、膽汁酸及 SCFA）的顯著改變，這些物質經證實與神經發炎及退化密切相關。文中綜述了微生物代謝產物如何透過調節腸道與血腦屏障完整性、影響免疫細胞（T/B 細胞）反應，以及直接作用於神經膠質細胞來參與 MS 的致病機制。總結而言，MS 的發生與腸道菌群-代謝物軸的整體失調有關，而非單一病原體所致。該研究強調未來需進行多體學（multiomics）整合分析，以開發基於微生物群的生物標記與創新治療策略，旨在恢復患者的免疫與神經恆定。</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42647164/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647759/</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>974 個重建的 N2O 相關基因體（未明確提及具體環境水樣/泥樣採樣數量）</t>
+          <t>974 個 N2O 相關的基因體 (recovered N2O-associated genomes)</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -948,7 +948,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>本研究旨在探討河口與沿海系統中，不同一氧化二氮（N2O）相關微生物的交互作用如何驅動生態系尺度的 N2O 溫室氣體排放。研究結合現場觀測、15N 示蹤、總體基因體學、總體轉錄體學及代謝模型分析，發現 N2O 的產生與還原速率及相關基因活性在低鹽度區顯著較高，並向沿海遞減。研究根據 974 個重建基因體，將微生物劃分為淨產生者、淨消費者及自給自足者。低鹽度區域因微生態分工失衡，存在較大的 NO/N2O 交換缺口，進而導致底層水體 N2O 顯著累積。此群落水平的「代謝分工」與交換缺口理論，為解析海洋微生物如何調控全球溫室氣體排放提供了全新的科學框架。</t>
+          <t>本研究旨在解析河口與沿海生態系統中，微生物群落如何透過代謝分工調控氧化亞氮（N2O）的排放。研究整合了現場濃度測量、同位素示蹤、宏基因組學及宏轉錄組學分析，發現低鹽度河口區的 N2O 產量與消耗潛力顯著高於沿海區域。透過重組 974 個相關微生物基因體，研究團隊將微生物劃分為產出型、消耗型及自給自足型三大功能群，並揭示其組成與活性會隨鹽度梯度產生位移。關鍵發現顯示，微生物間代謝產物的傳遞不平衡（即 NO/N2O 交換缺口）是導致河口區 N2O 積累的主因。此研究提出了一個全新的概念架構，闡明了微生物群落內部的「代謝分工」如何驅動全球溫室氣體 N2O 的排放，為預測氣候變遷下河口生態系的環境影響提供了重要的科學依據。</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>metagenomics, others</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>未提及（僅指出研究涵蓋中國 4 個主要鹽鹼地區，各包含「鹽鹼」與「改良後」兩種土壤狀態）</t>
+          <t>8 個土壤樣本（來自 4 個地區，每個地區含鹽鹼與改良後兩種狀態）</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>本研究旨在探討土壤改良對鹽鹼地中病毒群落生態及病毒-宿主交互作用的影響。研究結合總體基因體學、病毒體學及13C-纖維素DNA穩定同位素探針技術，分析中國四個主要鹽鹼區。結果顯示，地理位置與土壤改良狀態（特別是鹽度與鹼度）是塑造病毒群落結構的關鍵。在土壤改良過程中，病毒展現出強烈的特異性與功能適應性，且碳循環相關微生物（如碳水化合物降解菌）與其病毒間出現數量不匹配的動態變化。改良後，活性宿主比例由39.0%提升至61.0%，關聯病毒則由60.6%降至39.4%。此發現揭示了病毒在鹽鹼地恢復中的關鍵角色，有助於優化退化土地治理與碳封存策略。</t>
+          <t>本研究探討土壤改良對鹽鹼地病毒生態的影響。研究團隊結合宏基因組學（metagenomics）與病毒組學分析，發現病毒群落結構受地理環境及土壤改良狀態顯著影響，其中鹽度與鹼度為關鍵驅動因子。結果顯示，土壤改良過程中病毒具有高度的環境特異性與功能適應性。特別是針對碳循環微生物（如碳水化合物降解菌）的病毒，其與宿主間出現了明顯的豐度失配。透過 13C-纖維素同位素標記探針（DNA-SIP）技術，證實了活躍宿主與病毒間的碳轉移差異。改良土壤中宿主微生物豐度由 39.0% 提升至 61.0%，而連結的病毒豐度則由 60.6% 降至 39.4%。本研究揭示了病毒在鹽鹼地改良與土壤碳固存過程中的關鍵調控角色，為退化土地的生態恢復與管理策略提供了重要的科學依據。</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>本研究旨在探討孕婦尿路感染（UTI）引發早產的免疫調節機制。研究團隊建立尿道致病性大腸桿菌（UPEC）感染的懷孕小鼠模型，發現發生早產的小鼠其膀胱發炎較嚴重、胎盤細胞激素升高，且血清中IL-10水平較低。給予外源性IL-10或阻斷T細胞浸潤，可減少胎盤TH17細胞並預防早產。此外，在人類懷孕佇列分析中，研究者發現尿液中T細胞相關細胞激素（如IL-10, IL-15, GM-CSF, RANTES）與早產風險顯著相關。此研究揭示了UTI引發早產的關鍵免疫途徑，並提供了一個非侵入性的尿液生物標記篩檢系統，對臨床預防早產具有重要科學價值。</t>
+          <t>本研究探討母體泌尿道感染（UTI）導致早產的生物學機制。研究人員建立小鼠模型，發現致病性大腸桿菌（UPEC）感染後，發生早產的母鼠表現出顯著的膀胱發炎、胎盤與蛻膜細胞激素升高，以及母體血清 IL-10 濃度降低。實驗證實，外源性補充 IL-10 或隔離 T 細胞可減少胎盤 TH17 細胞並預防早產。在人體臨床隊列中，研究分析了尿液細胞激素與出生結果的關聯，識別出 IL-10、IL-15、GM-CSF 及 RANTES 等與早產風險相關的 T 細胞相關細胞激素。此研究不僅闡明了 UTI 誘發早產的免疫調節機制，更提供了一套非侵入性的生物標記篩檢潛力，為未來預防早產的臨床介入策略奠定基礎。</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60位克隆氏症（Crohn disease）成人患者</t>
+          <t>60 位克隆氏症（CD）成人患者</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>本研究評估波多黎各克隆氏症（CD）成人患者的飲食品質、腸道菌相與發炎指標之關聯。分析60名患者發現，其整體飲食品質普遍不佳（低纖高脂）。然而，較高的健康飲食指數（HEI-2015）與較高的腸道菌群多樣性及組成差異顯著相關。探索性分析顯示，富含水果的飲食模式與較低的發炎指標（糞便鈣衛蛋白與C反應蛋白）相關；富含蔬菜則與較佳的生活品質相關；相反地，高咖啡與甜味劑飲食與症狀加重相關（唯經校正後未達顯著）。本研究證實了飲食對腸道菌群與臨床預後的潛在影響，對未來透過膳食干預改善此弱勢族群CD預後具有科學意義。</t>
+          <t>本研究針對波多黎各克隆氏症（CD）成人患者進行橫斷面分析，旨在探討飲食品質、腸道菌相與發炎指標間的關聯。研究透過總體基因體定序（Shotgun metagenomics）分析腸道菌相，並評估多項膳食指數與臨床指標。研究發現，該族群整體飲食品質較差，富含水果的飲食模式與較高的菌相多樣性及較低的發炎指標（鈣衛蛋白、CRP）呈正相關；富含蔬菜模式則與較佳的生活品質相關，而咖啡/甜味劑模式則與症狀負擔加重有關。儘管初步分析顯示飲食與菌相及臨床表現間存在關聯，但經多重比較校正（FDR）後，統計顯著性減弱。本研究證實飲食在調節 CD 患者腸道健康中的潛力，強調未來需進行大規模縱向研究，以進一步釐清飲食介入對改善該群體疾病預後的具體效應。</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>未明確提及（僅指出採樣自西班牙東北部農村地區兩個區域的灌溉池與水溝）</t>
+          <t>2 個區域的農業灌溉池塘與溝渠樣本（文中未明確給出具體檢體總數，僅提及兩處採樣區）</t>
         </is>
       </c>
       <c r="G14" t="b">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>本研究旨在探討農業噴灌系統是否為嗜肺軍團菌（*Legionella pneumophila*）等病原體的環境宿主與空氣傳播源。研究團隊對西班牙東北部兩個區域的灌溉池和水溝進行微生物與基因組調查。總體基因體分析顯示其微生物群落極具多樣性，並檢出21種具臨床相關性的空氣傳播病原體，其中嗜肺軍團菌相對豐度高達4.6%。經培養分離與系統發育分析證實，該環境菌株與2015年一起未明源頭的退伍軍人症爆發臨床分離株高度相關；氣象數據亦支持氣溶膠可經風力長距離吹向住宅區。此研究證實灌溉系統為嗜肺軍團菌的關鍵傳播途徑，強調應將其納入例行環境監測與公共衛生風險評估。</t>
+          <t>本研究探討農業噴灌系統作為環境病原體儲存庫及氣膠傳播源的角色。研究針對西班牙東北部兩處農業灌溉水體進行宏基因體定序分析，發現高達兩萬種微生物多樣性，並檢測出 21 種具臨床意義的空氣傳播病原菌。研究證實嗜肺性退伍軍人菌（*L. pneumophila*）廣泛存在於灌溉系統中，且經細菌全基因體定序（ST15）比對發現，該環境菌株與 2015 年爆發退伍軍人症但未找到環境源頭的臨床病例具高度親緣關係。結合氣象數據分析，證實灌溉系統產生的氣膠可將病原體遠距離傳播至住宅區。此發現強調農業灌溉設施應被納入環境監測與公共衛生風險評估，以有效預防相關疾病爆發。</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>未提及（原文僅提及使用 murine models 及相關菌株組合，未明確統計具體樣本數）</t>
+          <t>未提及（原文僅提及使用小鼠模型與 IBD 相關人類菌株組合，未明確統計樣本數）</t>
         </is>
       </c>
       <c r="G15" t="b">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>本研究旨在探討定義明確的人類梭菌群（Clostridia consortia）在發炎性腸道疾病（IBD）中的治療潛力。研究團隊利用小鼠結腸炎模型，證實「17-mix」與「11-mix」梭菌群能有效緩解由人類菌相或致病菌引發的慢性結腸炎。透過總體基因體學與代謝體學分析，研究發現這些菌群的治療機制超越了傳統認知的短鏈脂肪酸（SCFA）與 IL-10 調控路徑。其核心機制在於：細菌產生的色胺酸代謝物能直接抑制腸道致病菌，並透過非 IL-10 依賴途徑活化宿主的芳香烴受體（AhR），進而誘發抗發炎反應。此發現揭示了特定菌株在修復失調菌群中的關鍵作用，為開發針對 IBD 的活體生物治療產品（LBPs）提供了重要的科學依據與新機制方向。</t>
+          <t>本研究旨在探討定義明確的人類梭菌群（Clostridia consortia）作為活體生物治療產品（LBPs）在治療發炎性腸道疾病（IBD）的潛力。研究利用小鼠結腸炎模型證實，17-mix 與 11-mix 梭菌群能有效緩解由人類微生物群及病原菌驅動的結腸炎。除了傳統認知的短鏈脂肪酸（SCFAs）與 IL-10 產生型調節性 T 細胞機制外，總體基因體與代謝體分析顯示，這些梭菌能透過雙重途徑發揮療效：首先是直接抑制腸道內的病原菌，其次是透過細菌代謝產生的色胺酸代謝物，不依賴 IL-10 而直接活化宿主的芳香烴受體（AhR）抗發炎路徑。此發現揭示了腸道共生菌在恢復黏膜免疫穩態中的新機制，為 IBD 的精準微生態治療提供了重要的科學依據。</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>metagenomics, others</t>
+          <t>metagenomics, metatranscriptomics</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>本研究旨在探討溫度（4至45 °C）對地下水中磁黃鐵礦驅動偏釩酸鹽 [V(V)] 生物還原的影響。研究發現，V(V) 去除率隨溫度升高呈先增後減，於 35 °C 達到峰值（反應速率 0.077 d⁻¹），並將其還原為 VO₂ 沉澱。宏基因組分箱顯示，釩還原菌的硫氧化對溫度敏感性高於鐵氧化；僅在 35 °C 偵測到可同時耦合硫鐵氧化與釩還原的 *Ramlibacter* sp.。此外，相關功能基因轉錄及電子傳遞活性均在 35 °C 達到最高。本研究揭示了該生物還原過程的溫度敏感性，有助於不同溫度環境下釩污染的風險評估與精準生物修復。</t>
+          <t>本研究探討了在地下水中，由磁黃鐵礦（pyrrhotite）驅動的偏釩酸鹽 [V(V)] 生物還原過程對溫度的敏感性。研究發現，在 4 至 45 °C 的溫度範圍內，V(V) 的移除效率呈現先升後降的趨勢，並在 35 °C 時達到最佳反應速率。透過宏基因組分箱（Metagenomic binning）與轉錄組分析，證實了微生物群落中的電子傳遞活性與關鍵功能基因（涉及 V(V) 還原、硫與鐵氧化）的表現均具有顯著的溫度依賴性。特別是能同時耦合硫與鐵氧化的菌種（如 *Ramlibacter* sp.）僅在 35 °C 下被檢測到，且發現硫氧化過程較鐵氧化過程對溫度變化更為敏感。此研究不僅揭示了環境溫度對生物修復效率的調控機制，也為受釩污染地下水的風險評估及制定精準的生物修復策略提供了關鍵科學依據。</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>metagenomics, metabolomics</t>
+          <t>metabolomics, metagenomics</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>未提及（摘要中僅提及使用重建的海洋菌群與海洋總體基因體數據，未說明具體樣本數量）</t>
+          <t>未提及（研究使用重建的海洋微生物群落及分析現有的海洋宏基因組數據，未明確標註具體樣本人數或檢體數量）</t>
         </is>
       </c>
       <c r="G17" t="b">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>本研究旨在探討海洋中複雜且難降解的褐藻醣膠（fucoidans）如何被完全降解。研究團隊利用重建的海洋合成菌群進行代謝組學分析，發現褐藻醣膠的降解依賴於不同細菌間的「功能性分工」與協同作用：部分細菌專門降解硫酸岩藻糖骨架，其餘則負責處理側鏈。這種協同效應使降解效率提升至97.1%。此外，這種互補的代謝功能在海洋總體基因體中廣泛存在。此發現揭示了海洋碳循環不僅取決於單一菌株的代謝能力，更受微生物群落間生態互動的影響，為理解全球碳循環及設計合成菌群以執行生物降解提供了重要機制藍圖。</t>
+          <t>本研究探討海洋中複雜多醣類「褐藻糖膠」（fucoidans）的微生物降解機制。研究發現，單一微生物難以完全分解褐藻糖膠，但透過具有互補代謝功能的細菌群落，能實現高效協同降解。研究利用代謝組學分析重建的微生物群落，揭示了細菌如何分工合作，分別降解褐藻糖膠的硫酸化岩藻糖主鏈與稀有單體支鏈，此分工使降解效率提升至 97.1%。此外，透過海洋宏基因組數據分析，證實此種功能互補的微生物組合在全球海洋中普遍存在。這項發現闡明了海洋碳循環的關鍵機制，不僅解釋了複雜生物聚合物的環境轉化原理，也為未來設計合成微生物群落以處理難降解多醣類提供了科學框架。</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1位患者（個案報告）</t>
+          <t>n=1 (1 位 20 歲男性患者)</t>
         </is>
       </c>
       <c r="G18" t="b">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>本研究報告了一例20歲男性於淡水溺水後的臨床病程。患者初期出現雙側肺部浸潤與氣管黏膜病變，且支氣管肺泡灌洗液（BALF）的宏基因組定序（mNGS）與痰液培養均檢出肺炎克雷伯氏菌。儘管發炎指標顯著升高，但患者影像學特徵迅速改善且臨床表現穩定，證實早期肺部異常主要源於吸入性肺損傷與非心源性肺水腫等非感染性因素。患者最終接受8天抗生素治療後順利康復。本案例的科學意義在於提醒臨床醫生，溺水後早期的肺部影像異常與病原檢測陽性易被過度解讀為細菌性肺炎，應結合臨床病程以避免過度治療。</t>
+          <t>本研究透過病例報告，探討淡水溺水後肺部浸潤與呼吸道微生物組成的臨床挑戰。患者溺水後出現類肺炎之放射線影像與發燒等發炎反應，肺泡灌洗液（BALF）經宏基因組定序（mNGS）檢測出大量肺炎克雷伯菌（*Klebsiella pneumoniae*）。儘管微生物學證據確鑿，但影像學快速恢復及穩定的臨床表現，顯示溺水造成的發炎主要源於非感染性的化學性肺損傷，而非單純的細菌性肺炎。此發現具有重要臨床意義：在處理溺水併發症時，醫師應謹慎判讀微生物檢測結果，避免過度診斷與抗生素濫用，強調了在臨床決策中整合影像學、微生物組學與病程演變的重要性。</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>本研究旨在解決低碳條件下，工業廢水中氮、重金屬（Cu2+）及持久性有機污染物（雙酚A, BPA）難以同時去除的挑戰。研究團隊將日本假交替單胞菌（*Pseudoalteromonas japonicus* LY0623）整合至水膠-生物炭-AQDS複合載體中，構建出多功能固定化生物膜系統（R4系統）。結果顯示，在僅添加碳酸氫鈉的低碳條件下，該系統成功實現了高效率的氨氮（89%）、硝酸鹽氮（100%）、Cu2+（85%）及BPA（88%）同步去除。總體基因體學分析證實，變形菌門為優勢菌群，且系統維持了無機碳同化、反硝化、電子傳遞及芳香族化合物降解等關鍵代謝途徑。此研究為處理含有混合污染物的工業廢水提供了一種極具前景的低碳生物整治策略。</t>
+          <t>本研究旨在解決工業廢水中氮、重金屬（Cu2+）與持久性有機污染物（雙酚A，BPA）在低碳條件下難以同時去除的問題。研究團隊開發了一種將 *Pseudoalteromonas japonicus* LY0623 菌株固定於水凝膠-生物炭-AQDS 複合載體中的生物反應器系統。實驗結果顯示，該系統在複雜污染條件下展現出卓越的處理效能，氨氮與硝酸鹽氮去除率分別達到 89% 與 100%，同時成功去除 85% 的 Cu2+ 與 88% 的 BPA。總體基因體分析（metagenomics）證實，系統中的優勢菌群（Pseudomonadota）保持穩定，且與無機碳同化、氮代謝、電子傳遞及芳香族化合物降解相關的關鍵功能路徑皆得以保留。該研究提出的整合性生物修復策略，透過結合生物礦化、氧化還原介導與無機碳利用，為處理含有多種污染物的工業廢水提供了一種高效且節能的新思路。</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>metagenomics, small genome</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>297 個真實總體基因體（metagenomes）數據集及合成群落</t>
+          <t>297 個真實宏基因組樣本（metagenomes）</t>
         </is>
       </c>
       <c r="G20" t="b">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>本研究開發了名為 QuickBin 的新型分箱（binning）演算法，旨在解決總體基因體學中重建基因組時，高準確度與運算效率難以兼得的瓶頸。QuickBin 是一款無需標記基因且原生支援 CPU 的高效工具，結合了 GC 覆蓋度空間索引、相似性篩選級聯與輕量神經網絡。在 297 個真實總體基因體數據集的基準測試中，QuickBin 成功完成所有運行，且重建出比其他高資源消耗工具更多的高質量組裝基因組（MAGs，完整度≥95%且污染度≤1%）。此技術為大規模、高解析度的總體基因體學研究提供了一套高效、可重複且實用的科學解決方案。</t>
+          <t>本研究針對總體基因體學中，組裝高準確度基因體（MAGs）時常見的計算效率瓶頸，開發了一種名為「QuickBin」的新型分箱（binning）演算法。QuickBin 採用 CPU 原生設計，無需依賴 GPU 或標記基因後處理，通過 GC 含量覆蓋率索引與 SIMD 加速比對技術，有效提升計算效能並優化對低汙染、高完整度基因體的組裝能力。在針對 297 個真實宏基因組樣本的效能評估中，QuickBin 展現了比傳統高資源需求工具更高的成功率與產出質量。此工具為大規模、高解析度的微生物群落基因體研究提供了一項高效、可複製的解決方案，能有效推進後續的比較基因體學分析。</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>本研究旨在探討健康年輕女性的腸道菌群功能潛力與大腦神經傳導物質（GABA和麩胺酸）濃度之關聯。研究結合總體基因體學剖析與大腦質子磁振光譜（¹H-MRS），發現腸道菌群在代謝GABA、麩胺酸、短鏈脂肪酸及肌醇等通路的功能潛力，與大腦特定區域（如背外側前額葉、下枕迴）的皮質神經化學物質及興奮/抑制（E/I）平衡具有區域特異性關聯。此外，菌群功能也與焦慮、憂鬱及睡眠品質相關。本研究為「腸腦軸」提供重要的人體實證，證實腸道菌群功能變化會影響大腦神經化學與心理健康，為未來開發微生態導向的精神健康干預手段奠定科學基礎。</t>
+          <t>本研究旨在探討人體腸道微生物群的代謝功能潛力與大腦神經化學物質之間的關聯。研究利用質子磁振光譜（¹H-MRS）量化年輕健康女性在背外側前額葉皮質（dlPFC）、前扣帶皮質（ACC）與下枕回（IOG）中的 GABA 與麩胺酸濃度，並透過宏基因組學（metagenomics）分析腸道菌群在合成與降解 GABA、麩胺酸、短鏈脂肪酸及對甲酚等代謝途徑的功能潛力。研究發現，特定的腸道微生物代謝途徑與大腦區域的神經傳導物質平衡（E/I balance）顯著相關，且這些關聯與受試者的焦慮、憂鬱症狀及睡眠品質存在潛在連結。此研究提供了腸道與大腦軸線（Gut-Brain Axis）在人類神經化學調節上的實證，不僅闡明了腸道菌群對大腦功能的潛在機制，也為未來開發針對微生物群的心理健康介入策略提供了科學依據。</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1835,12 +1835,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>42635403</t>
+          <t>42635401</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Baseline gut microbiome ecology predicts long-term fat mass loss after bariatric surgery: evidence for a thrifty Bifidobacterium phenotype.</t>
+          <t>Fecal filtrate transplantation as salvage therapy for fulminant Clostridioides difficile infection in adult hematological patients during chemotherapy-induced aplasia: a pilot experience.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>16S, metagenomics</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>85 位重度肥胖患者及 21 位健康對照組（共 106 名受試者）</t>
+          <t>3 位成人血液腫瘤患者</t>
         </is>
       </c>
       <c r="G27" t="b">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Bariatric surgery (BS) induces weight loss, but long-term success involves complex host-microbiome interactions. We evaluated the longitudinal impact of BS, microbiome resilience, and Mediterranean Diet (MedDiet) adherence up to 24 months. This prospective observational study included 85 patients with severe obesity undergoing BS and 21 normal-weight healthy controls (HC). MedDiet adherence (PREDIMED) was assessed before surgery. Fecal microbiota (16S-rRNA sequencing) and metabolomics (1H-NMR spectroscopy) were analyzed at baseline and at 1-, 6-, and 12-months post-BS. Clinical outcomes and fat mass, evaluated by bioimpedanciometry, were tracked up to 24 months. At baseline, patients exhibited higher microbial Shannon diversity than controls (p = 0.041), alongside a dysfunctional microbiome and metabolome characterized by a higher Firmicutes/Bacteroidetes ratio and elevated levels of branched-chain amino acids (p &lt; 0.0001). Ordinary Least Squares (OLS) regression analysis revealed that MedDiet adherence and type 2 diabetes status significantly modulated baseline diversity. At 12 months post-BS, the gut ecosystem underwent profound remodeling, characterized by depletion of Bifidobacterium spp. and an increase in butyrate levels (p &lt; 0.0001), establishing a novel adaptive state distinct from HC. Baseline gut ecology significantly conditioned long-term BS outcomes: patients in the highest quartile of baseline Bifidobacterium spp. lost significantly less fat mass at 24 months than those in the lowest (6.6% vs. 13.2%, p = 0.010). High baseline Bifidobacterium abundance paradoxically acts as a "thrifty microbiome," potentially maximizing energy harvest and limiting surgery-induced fat loss. Overall, BS induces adaptive microbiome restoration rather than true normalization, highlighting the potential for precision interventions prior to surgery.</t>
+          <t>Fulminant Clostridioides difficile infection (CDI) in patients with hematologic malignancies during chemotherapy-induced aplasia carries high mortality and limited treatment options. Our objective was to evaluate fecal filtrate transplantation (FFT) as a salvage therapy for fulminant CDI during aplasia, and to explore whether donor-recipient phage dynamics may contribute to clinical response. We conducted a single-center, prospective, protocol-defined pilot case series study including consecutive adults with hematologic malignancies, chemotherapy-induced grade-4 aplasia and fulminant CDI, refractory to ≥5 d of high-dose oral vancomycin plus intravenous metronidazole and tigecycline. FFT was prepared from a single unrelated donor using sequential centrifugation and filtration, and administered via nasogastric tube in two doses. The primary outcome was sustained clinical cure, secondary outcomes included survival and adverse events, assessed at +14 and +30 d post-FFT. 16S rRNA gene sequencing was used to assess microbiome compositions, while viral metagenomics and in vitro propagation assays were employed to characterize donor-recipient phageome interactions. Three patients with adverse-risk acute myeloid leukemia and fulminant CDI caused by genetically distinct C. difficile strains received FFT. All patients achieved clinical resolution by day +14, accompanied by improvements in abdominal distension and inflammatory markers. By day +30, one patient died from Pseudomonas aeruginosa septic shock, while two maintained remission with confirmatory follow-up. FFT was well tolerated, with no procedure-related immediate complications or FFT-attributable adverse events. Microbiome and phage profiling revealed heterogeneous responses, including shifts in bacterial community composition, with no clear evidence for a general role of donor-derived phages in CDI resolution. In contrast, we observed induction of prophages harbored by recipient-associated Clostridium species, which may have contributed to decolonization through stress-induced entry into the lytic cycle. FFT was feasible, with rapid sustained CDI resolution in hematologic patients with chemotherapy-induced aplasia. ClinicalTrials.gov identifier NCT07172191. Prospective single-center pilot study of fecal filtrate transplantation (FFT) for fulminant-refractory C. difficile infection in three aplastic adult hematologic patients. FFT was well tolerated, achieved rapid clinical cure, and showed heterogeneous microbiome and phageome modulation, potentially contributing to therapeutic effects.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>本研究探討減重手術（BS）後腸道微生物群與長期減脂效果的關聯。研究追蹤 85 名患者於術前及術後長達 24 個月的變化，分析發現手術顯著重塑了腸道菌相與代謝環境，特別是雙歧桿菌（*Bifidobacterium*）的耗竭與丁酸鹽的增加。關鍵發現指出，術前高豐度的雙歧桿菌反而成為一種「節儉型表型」，會增加能量攝取效率，導致術後 24 個月的脂肪減少量顯著較少（6.6% 對比 13.2%）。這顯示減重手術並非使微生物組回歸常態，而是引發一種適應性重組。此研究凸顯了術前腸道生態作為預測手術成效生物標記的潛力，對於未來制定精準的術前介入策略具有重要的臨床指導意義。</t>
+          <t>本研究旨在評估糞便濾液移植（FFT）作為挽救療法，治療化療致免疫不全之血液腫瘤患者合併難治猛爆性艱難梭菌感染（CDI）的療效，並探討供受體間噬菌體的動力學關係。此臨床先導試驗納入3位患者，結果顯示FFT耐受性良好，所有患者在接受治療後14天內均達到臨床緩解。微生態與噬菌體體學分析顯示，臨床症狀的改善並非源於供體噬菌體的直接轉移，而是FFT可能誘發了受體腸道內艱難梭菌的原噬菌體進入溶菌週期，進而促進病原菌清除。本研究證實FFT在此高風險族群中具安全性與可行性，為難治性CDI提供了創新的機制見解與治療選擇。</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1881,19 +1881,19 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42635403/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42635401/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>42635401</t>
+          <t>42635406</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fecal filtrate transplantation as salvage therapy for fulminant Clostridioides difficile infection in adult hematological patients during chemotherapy-induced aplasia: a pilot experience.</t>
+          <t>Separating extracellular from intracellular fecal metabolites exposes cross-feeding architecture in the gut: exploring metabolite partitioning and ecological associations.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>16S, metagenomics</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>3 位成人血液腫瘤患者</t>
+          <t>63 個糞便檢體（來自 63 位健康受試者）</t>
         </is>
       </c>
       <c r="G28" t="b">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Fulminant Clostridioides difficile infection (CDI) in patients with hematologic malignancies during chemotherapy-induced aplasia carries high mortality and limited treatment options. Our objective was to evaluate fecal filtrate transplantation (FFT) as a salvage therapy for fulminant CDI during aplasia, and to explore whether donor-recipient phage dynamics may contribute to clinical response. We conducted a single-center, prospective, protocol-defined pilot case series study including consecutive adults with hematologic malignancies, chemotherapy-induced grade-4 aplasia and fulminant CDI, refractory to ≥5 d of high-dose oral vancomycin plus intravenous metronidazole and tigecycline. FFT was prepared from a single unrelated donor using sequential centrifugation and filtration, and administered via nasogastric tube in two doses. The primary outcome was sustained clinical cure, secondary outcomes included survival and adverse events, assessed at +14 and +30 d post-FFT. 16S rRNA gene sequencing was used to assess microbiome compositions, while viral metagenomics and in vitro propagation assays were employed to characterize donor-recipient phageome interactions. Three patients with adverse-risk acute myeloid leukemia and fulminant CDI caused by genetically distinct C. difficile strains received FFT. All patients achieved clinical resolution by day +14, accompanied by improvements in abdominal distension and inflammatory markers. By day +30, one patient died from Pseudomonas aeruginosa septic shock, while two maintained remission with confirmatory follow-up. FFT was well tolerated, with no procedure-related immediate complications or FFT-attributable adverse events. Microbiome and phage profiling revealed heterogeneous responses, including shifts in bacterial community composition, with no clear evidence for a general role of donor-derived phages in CDI resolution. In contrast, we observed induction of prophages harbored by recipient-associated Clostridium species, which may have contributed to decolonization through stress-induced entry into the lytic cycle. FFT was feasible, with rapid sustained CDI resolution in hematologic patients with chemotherapy-induced aplasia. ClinicalTrials.gov identifier NCT07172191. Prospective single-center pilot study of fecal filtrate transplantation (FFT) for fulminant-refractory C. difficile infection in three aplastic adult hematologic patients. FFT was well tolerated, achieved rapid clinical cure, and showed heterogeneous microbiome and phageome modulation, potentially contributing to therapeutic effects.</t>
+          <t>The gut microbiota forms a complex ecosystem through metabolic interdependence (cross-feeding). However, conventional fecal metabolomics typically quantifies only total metabolite pools, making it difficult to distinguish extracellular-enriched metabolite pools from predominantly cell-associated ones, and thus limiting reconstruction of in situ metabolic networks. Here, we quantified fecal metabolites in paired fractions from the same specimen: an undisrupted fraction representing the extracellular pool and a strongly bead-beaten fraction representing the total pool; the intracellular pool was defined as the difference between total and extracellular measurements. Stool samples from 63 healthy individuals were analyzed for short-chain fatty acids, polyamines, and water-soluble vitamins, and the results were integrated with shotgun metagenomic profiles of species composition and functional genes. Vitamins exhibited two distinct behaviors. Adenosylcobalamin (a vitamin B12 coenzyme) was detectable only after disruption, and together with thiamine (B1) and niacin (B3) was classified as an intracellular-retained type (Type 1). In contrast, biotin (B7) and pantothenate (B5) showed higher extracellular proportions (Type 2). Integrative analyses further indicated that Type 1 thiamine was negatively associated with Blautia, consistent with intensive microbial utilization, whereas Type 2 biotin was strongly positively associated with Alistipes, suggesting links to ecological niches shaped by luminal pH and fermentation modes (carbohydrate vs protein fermentation). Fraction-resolved quantification provides a practical operational framework to differentiate extracellular from cell-associated metabolite pools, helping reconcile metagenomic potential with metabolomic reality and enabling deeper inference of cross-feeding structure in the gut ecosystem.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>本研究旨在評估糞便濾液移植（FFT）作為挽救療法，治療化療致免疫不全之血液腫瘤患者合併難治猛爆性艱難梭菌感染（CDI）的療效，並探討供受體間噬菌體的動力學關係。此臨床先導試驗納入3位患者，結果顯示FFT耐受性良好，所有患者在接受治療後14天內均達到臨床緩解。微生態與噬菌體體學分析顯示，臨床症狀的改善並非源於供體噬菌體的直接轉移，而是FFT可能誘發了受體腸道內艱難梭菌的原噬菌體進入溶菌週期，進而促進病原菌清除。本研究證實FFT在此高風險族群中具安全性與可行性，為難治性CDI提供了創新的機制見解與治療選擇。</t>
+          <t>本研究針對腸道微生物的代謝互營機制（cross-feeding）進行探討。傳統糞便代謝組學僅能分析總代謝物，無法區分細胞外與細胞內代謝池，限制了對代謝網絡的解析。研究團隊透過對比未破碎（代表細胞外池）與強力破碎（代表總代謝池）的糞便樣本，成功推算出細胞內代謝物的分佈。針對短鏈脂肪酸、多胺與水溶性維生素的分析顯示，維生素呈現兩類分佈：B12、B1 與 B3 傾向保留於細胞內（Type 1），而 B7 與 B5 則富集於細胞外（Type 2）。結合宏基因組分析發現，Type 1 代謝物與特定細菌（如 *Blautia*）的利用模式顯著相關，Type 2 代謝物則與 *Alistipes* 及腸道生態位特徵（如 pH 值、發酵類型）相關。此方法為區分代謝物空間分佈提供了實用架構，有助於更精確地將宏基因組功能潛力與代謝體現實連結，深入理解腸道微生物的互營生態結構。</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42635401/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42635406/</t>
         </is>
       </c>
     </row>
@@ -1961,12 +1961,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>metagenomics, others</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>340 隻跳蚤（每 4 隻混合為一個檢體，共 85 個混合檢體）</t>
+          <t>340 隻跳蚤</t>
         </is>
       </c>
       <c r="G29" t="b">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>本研究旨在分離並鑑定巴西家犬跳蚤中的*Blechomonas*屬錐蟲，分析其體外培養、形態特徵與系統發育關係。研究從 340 隻跳蚤中成功分離出 FL-1 株，並鑑定為 *Blechomonas campbelli*。結果顯示其最佳生長溫度為 25ºC，35ºC 時無法生長，證實其對高溫的耐受性有限，限制了其在溫血宿主體內存活的能力。形態學分析揭示了四種細胞類型，並以利於附著與聚集的「uromonad」型為主。系統發育分析顯示，該物種廣泛分布於多個大洲的貓蚤屬中。本研究闡明了該錐蟲對昆蟲腸道的發育適應性，並展示了結合傳統培養與公共總體基因體數據挖掘在病原體研究中的科學價值。</t>
+          <t>本研究旨在分離並表徵巴西家犬身上跳蚤所攜帶的單宿主錐蟲（*Blechomonas* spp.）。研究人員透過培養法分析 340 隻跳蚤，成功分離出 *Blechomonas campbelli* (FL-1 株)。實驗結果顯示，該菌株在 25°C 生長最佳，30°C 生長受限，35°C 則無法生長，顯示其對高溫耐受力差，難以在恆溫動物宿主內存活。形態學觀察發現其具備多種細胞型態，其中「尾鞭毛蟲」（uromonad）階段有利於附著與聚集。系統發生學分析結合了 18S rRNA、gGAPDH 序列及公共宏基因組數據，證實 *B. campbelli* 與 *B. lauriereadi* 廣泛分布於全球的貓蚤與狗蚤中。此研究揭示了該寄生蟲對跳蚤腸道環境的適應機制，並證實整合培養法與生物資訊學工具對於探索節肢動物共生寄生蟲具有高度科學價值。</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1996,12 +1996,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>42635406</t>
+          <t>42635403</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Separating extracellular from intracellular fecal metabolites exposes cross-feeding architecture in the gut: exploring metabolite partitioning and ecological associations.</t>
+          <t>Baseline gut microbiome ecology predicts long-term fat mass loss after bariatric surgery: evidence for a thrifty Bifidobacterium phenotype.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>metagenomics, metabolomics</t>
+          <t>16S, metabolomics</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>63 個糞便檢體（來自 63 位健康受試者）</t>
+          <t>85 位重度肥胖患者及 21 位健康對照組（共 106 名受試者）</t>
         </is>
       </c>
       <c r="G30" t="b">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>The gut microbiota forms a complex ecosystem through metabolic interdependence (cross-feeding). However, conventional fecal metabolomics typically quantifies only total metabolite pools, making it difficult to distinguish extracellular-enriched metabolite pools from predominantly cell-associated ones, and thus limiting reconstruction of in situ metabolic networks. Here, we quantified fecal metabolites in paired fractions from the same specimen: an undisrupted fraction representing the extracellular pool and a strongly bead-beaten fraction representing the total pool; the intracellular pool was defined as the difference between total and extracellular measurements. Stool samples from 63 healthy individuals were analyzed for short-chain fatty acids, polyamines, and water-soluble vitamins, and the results were integrated with shotgun metagenomic profiles of species composition and functional genes. Vitamins exhibited two distinct behaviors. Adenosylcobalamin (a vitamin B12 coenzyme) was detectable only after disruption, and together with thiamine (B1) and niacin (B3) was classified as an intracellular-retained type (Type 1). In contrast, biotin (B7) and pantothenate (B5) showed higher extracellular proportions (Type 2). Integrative analyses further indicated that Type 1 thiamine was negatively associated with Blautia, consistent with intensive microbial utilization, whereas Type 2 biotin was strongly positively associated with Alistipes, suggesting links to ecological niches shaped by luminal pH and fermentation modes (carbohydrate vs protein fermentation). Fraction-resolved quantification provides a practical operational framework to differentiate extracellular from cell-associated metabolite pools, helping reconcile metagenomic potential with metabolomic reality and enabling deeper inference of cross-feeding structure in the gut ecosystem.</t>
+          <t>Bariatric surgery (BS) induces weight loss, but long-term success involves complex host-microbiome interactions. We evaluated the longitudinal impact of BS, microbiome resilience, and Mediterranean Diet (MedDiet) adherence up to 24 months. This prospective observational study included 85 patients with severe obesity undergoing BS and 21 normal-weight healthy controls (HC). MedDiet adherence (PREDIMED) was assessed before surgery. Fecal microbiota (16S-rRNA sequencing) and metabolomics (1H-NMR spectroscopy) were analyzed at baseline and at 1-, 6-, and 12-months post-BS. Clinical outcomes and fat mass, evaluated by bioimpedanciometry, were tracked up to 24 months. At baseline, patients exhibited higher microbial Shannon diversity than controls (p = 0.041), alongside a dysfunctional microbiome and metabolome characterized by a higher Firmicutes/Bacteroidetes ratio and elevated levels of branched-chain amino acids (p &lt; 0.0001). Ordinary Least Squares (OLS) regression analysis revealed that MedDiet adherence and type 2 diabetes status significantly modulated baseline diversity. At 12 months post-BS, the gut ecosystem underwent profound remodeling, characterized by depletion of Bifidobacterium spp. and an increase in butyrate levels (p &lt; 0.0001), establishing a novel adaptive state distinct from HC. Baseline gut ecology significantly conditioned long-term BS outcomes: patients in the highest quartile of baseline Bifidobacterium spp. lost significantly less fat mass at 24 months than those in the lowest (6.6% vs. 13.2%, p = 0.010). High baseline Bifidobacterium abundance paradoxically acts as a "thrifty microbiome," potentially maximizing energy harvest and limiting surgery-induced fat loss. Overall, BS induces adaptive microbiome restoration rather than true normalization, highlighting the potential for precision interventions prior to surgery.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>本研究針對腸道微生物的代謝互營機制（cross-feeding）進行探討。傳統糞便代謝組學僅能分析總代謝物，無法區分細胞外與細胞內代謝池，限制了對代謝網絡的解析。研究團隊透過對比未破碎（代表細胞外池）與強力破碎（代表總代謝池）的糞便樣本，成功推算出細胞內代謝物的分佈。針對短鏈脂肪酸、多胺與水溶性維生素的分析顯示，維生素呈現兩類分佈：B12、B1 與 B3 傾向保留於細胞內（Type 1），而 B7 與 B5 則富集於細胞外（Type 2）。結合宏基因組分析發現，Type 1 代謝物與特定細菌（如 *Blautia*）的利用模式顯著相關，Type 2 代謝物則與 *Alistipes* 及腸道生態位特徵（如 pH 值、發酵類型）相關。此方法為區分代謝物空間分佈提供了實用架構，有助於更精確地將宏基因組功能潛力與代謝體現實連結，深入理解腸道微生物的互營生態結構。</t>
+          <t>本研究探討減重手術（BS）後腸道微生物群與長期減脂效果的關聯。研究追蹤 85 名患者於術前及術後長達 24 個月的變化，分析發現手術顯著重塑了腸道菌相與代謝環境，特別是雙歧桿菌（*Bifidobacterium*）的耗竭與丁酸鹽的增加。關鍵發現指出，術前高豐度的雙歧桿菌反而成為一種「節儉型表型」，會增加能量攝取效率，導致術後 24 個月的脂肪減少量顯著較少（6.6% 對比 13.2%）。這顯示減重手術並非使微生物組回歸常態，而是引發一種適應性重組。此研究凸顯了術前腸道生態作為預測手術成效生物標記的潛力，對於未來制定精準的術前介入策略具有重要的臨床指導意義。</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42635406/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42635403/</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>150對肺部與腸道檢體（篩選自採集的2,422隻蝙蝠）</t>
+          <t>2,422 隻蝙蝠中篩選出的 150 組配對肺部與腸道樣本（共 300 個檢體）</t>
         </is>
       </c>
       <c r="G32" t="b">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>本研究旨在利用巴西現有的狂犬病被動監測計畫，建立一個監測都市蝙蝠攜帶人畜共通傳染病毒的框架。研究團隊從聖保羅州收集的2,422隻蝙蝠中，篩選出150對肺部與腸道檢體進行奈米孔總體基因體定序。結果成功檢測出屬於12個具公共衛生相關科別（如冠狀病毒科、副黏液病毒科、沙狀病毒科）的98個病毒 contigs，並首次在美洲蝙蝠中發現一種未知的絲狀病毒。此研究證實，利用現有動物監測系統能有效發掘潛在的病毒多樣性，並為中低收入國家提供了一個具可擴展性且符合「健康一體（One Health）」理念的傳染病預防與監測模型。</t>
+          <t>本研究旨在利用巴西現有的狂犬病被動監測系統，建立一套偵測蝙蝠源人畜共通病毒的監測框架。研究團隊從聖保羅州收集的 2,422 隻蝙蝠中，篩選出 150 組配對的肺部與腸道樣本進行奈米孔總體基因體定序。結果成功偵測到來自沙狀病毒、冠狀病毒及副黏液病毒等 12 個具公衛重要性病毒科的 98 個病毒基因片段，並首次在美洲蝙蝠中發現一種未知的絲狀病毒。此研究不僅揭示了隱匿的病毒多樣性，更證實該框架能有效預防新興傳染病，為中低收入國家提供了一套可推廣至全國的「健康一體」（One Health）防疫監測模型。</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">

--- a/papers_database.xlsx
+++ b/papers_database.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>46 對母子（46 個母乳檢體）</t>
+          <t>46 對母嬰（46 個母乳檢體）</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -514,7 +514,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>本研究旨在探討秘魯母乳微生物相與一歲以下嬰兒缺鐵性貧血（IDA）的關聯。研究團隊招募46對母子，並利用16S rRNA定序技術分析母乳樣本。結果顯示，母乳微生物主要由鏈球菌屬與葡萄球菌屬主導。相較於健康組與IDA組，非缺鐵性貧血（non-IDA）組母親的母乳菌群豐富度顯著較高。此外，IDA組母乳中的棒狀桿菌屬、不動桿菌屬等豐度顯著升高，而鏈球菌屬則呈減少趨勢。本研究證實母乳微生物組成與嬰兒缺鐵性貧血具潛在關聯，為理解嬰兒貧血的病理機制及未來預防策略提供了全新視角。</t>
+          <t>本研究旨在探討秘魯母親的母乳菌相與嬰兒缺鐵性貧血（IDA）之間的關聯。研究招募了46對母嬰，並透過16S rRNA定序分析母乳樣本。結果顯示，非缺鐵性貧血（non-IDA）組嬰兒之母乳菌群豐富度（Alpha多樣性）顯著高於健康組與IDA組。在菌相組成上，IDA組的母乳中含有較高比例的棒狀桿菌屬（*Corynebacterium*）、不動桿菌屬（*Acinetobacter*）等菌屬，而鏈球菌屬（*Streptococcus*）則呈現減少趨勢。此研究指出母乳菌相在不同嬰兒貧血狀態下存在差異，為探討母體微生物對嬰兒缺鐵性貧血的潛在影響提供了重要的科學依據。</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>metagenomics, metatranscriptomics</t>
+          <t>metagenomics, metatranscriptomics, small genome</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>本研究旨在富集並鑑定一種新型耐鹽鹼厭氧氨氧化（anammox）細菌，命名為 *Candidatus* Loosdrechtia alkalitolerans，以探討其對鹼性環境的適應機制。研究團隊成功將其富集至 80% 以上的相對豐度，並證實其在長期鹽鹼壓力下（0.5% NaCl, pH~9.13）具有顯著的競爭優勢。比較基因體學與轉錄分析顯示，該菌編碼完整的 Mrp 陽離子/質子反向轉運體操縱子；添加鈉離子能上調 *mrp* 基因表達，進而在鹼性壓力下恢復其厭氧氨氧化活性。此研究揭示了 Mrp 介導的 pH 調節機制，拓展了對該菌生理可塑性與生態分布的認知。</t>
+          <t>本研究成功富集並鑑定了一種新型耐鹽鹼的厭氧氨氧化（anammox）細菌，命名為 *Candidatus* Loosdrechtia alkalitolerans（相對豐度 &gt;80%）。在長期鹽鹼壓力下，該菌展現出顯著的耐受性並能勝過其他淡水菌屬。比較基因組學與轉錄譜分析發現，該菌編碼了完整的 Mrp 陽離子/質子反向轉運體操縱子，且在鈉離子誘導下會上調 *mrp* 表達以維持細胞內 pH 平衡。數據庫檢索更顯示其不僅存在於鹽鹼環境，還廣泛分佈於多種淡水與廢水生態系統。本研究揭示了其耐鹽鹼的分子機制，拓展了對厭氧氨氧化菌生理可塑性與生態功能的科學認知。</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DSS誘導的慢性結腸炎小鼠模型（未明確標示具體n值）、人類CCD-18Co細胞株及原代小鼠腸道纖維母細胞</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -624,7 +624,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>本研究探討抗性澱粉（RS）對腸道纖維化的改善機制。研究顯示，RS 能顯著緩解 DSS 誘導的小鼠腸道纖維化，降低細胞外基質沈積。宏基因組定序發現 RS 重塑了腸道菌群，增加了如 *Bacteroides acidifaciens* 等短鏈脂肪酸產生菌的豐度；代謝組學分析則證實結腸內乙酸（acetate）水平顯著提升。機轉研究揭示，乙酸能抑制纖維母細胞中組蛋白去乙醯化酶 2（HDAC2）的活性，進而增加 H3K27 的乙醯化修飾，從而抑制 TGF-β 誘導的纖維母細胞活化。本研究揭示了「腸道菌群-代謝物-表觀遺傳」的調控軸，證實了飲食纖維代謝產物在改善纖維化疾病中的潛力，為開發纖維化治療策略提供了新的科學依據。</t>
+          <t>本研究探討抗性澱粉（RS）對腸道纖維化的緩解作用及其分子機制。研究結果顯示，RS能顯著減輕DSS誘導的慢性結腸炎小鼠之腸道纖維化，減少細胞外基質累積。總體基因體學分析發現，RS能重塑腸道菌相，增加產短鏈脂肪酸益菌（如 *Bacteroides acidifaciens* 等）的豐度；標靶代謝組學分析則證實乙酸（acetate）含量顯著上升。機制上，乙酸透過抑制組蛋白去乙醯化酶2（HDAC2），提高H3K27的乙醯化水平，進而阻斷TGF-β誘導的纖維母細胞活化。本研究揭示了「微生物-代謝-表觀遺傳」軸線在纖維化防治中的潛力，為腸道纖維化治療提供了新靶點。</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>25 次重複分析（針對開發出的 4 種模擬菌群樣本）</t>
+          <t>25 次重複分析（25 repeated analyses）</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -679,7 +679,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>本研究旨在解決臨床宏基因組次世代定序（mNGS）在檢測再現性與品質控管上的挑戰。研究開發了四種包含 26 種常見人體微生物（涵蓋腸胃道、呼吸道、皮膚、生殖道及腦脊髓液來源）的模擬菌群（Mock Communities）作為標準質控物質。透過鳥槍法總體基因體定序（shotgun metagenomics），評估了不同 DNA 萃取試劑盒對菌種分布的影響及檢測的精密度。結果顯示，DNA 萃取方法的差異會顯著影響分類群的結果，且該模擬菌群在常見優勢菌種（相對豐度 &gt;20%）中表現出良好的再現性（變異係數 &lt;10%）。此研究對於推動臨床 mNGS 的標準化流程具有重要意義，有助於提升臨床診斷分析的準確性與可信度。</t>
+          <t>臨床宏基因組次世代定序（mNGS）雖能全面檢測微生物，但面臨數據再現性與品管挑戰。本研究開發了四種基於珠狀（bead-based）的模擬微生物群落（mock communities），作為臨床 mNGS 的品質控制參考物質。這些群落涵蓋人體腸道、呼吸道、皮膚、生殖道及腦脊髓液中常見的 26 種菌株，考量了革蘭氏染色特性、GC 含量與系統發育分佈。研究利用霰彈槍宏基因組定序進行評估，結果顯示 DNA 萃取試劑盒的選擇對分類學分佈具有顯著影響。實驗重複性分析顯示，豐度大於 20% 的優勢菌屬重複性良好（變異係數 &lt;10%）。此項研究證實了模擬群落對於標準化臨床 mNGS 流程的重要性，有助於評估技術偏差並提升未來臨床診斷的準確性與一致性。</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>308 名瑞典新生兒的糞便檢體</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -734,7 +734,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>本研究是一項針對瑞典新生兒的全國性佇列研究，旨在評估嬰兒腸道微生態的組成與功能特徵。研究發現，瑞典新生兒體內的雙歧桿菌（Bifidobacteria）豐度普遍偏低，且其腸道菌相在物種組成與代謝功能上呈現獨特且不成熟的特徵。雙歧桿菌的缺乏可能影響嬰兒對母乳寡糖（HMOs）的降解與利用，進而對早期免疫與代謝發育帶來潛在影響。此發現揭示了現代西方社會新生兒腸道菌相失衡的現狀，強調了早期微生態發育的地理差異，並為未來透過精準益生菌干預（如補充特定雙歧桿菌）以重建嬰兒腸道健康提供了重要的科學依據。</t>
+          <t>本研究旨在探討瑞典新生兒的腸道菌相組成與功能特徵。透過總體基因體學分析，研究發現瑞典新生兒腸道中的雙歧桿菌（特別是嬰兒雙歧桿菌）豐度顯著偏低，並呈現出獨特的菌相結構與代謝功能。此現象與現代化生活型態及分娩方式密切相關。這項全國性世代研究揭示了現代環境對嬰兒早期腸道微生態建立的深遠影響，為未來的臨床嬰幼兒益生菌介入與健康照護策略提供了關鍵的科學依據。</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>本研究針對巴西瓜納巴拉河（Guandu River）於 2020 年發生的異味危機進行調查。透過宏基因體定序技術分析水質，研究發現當地水體呈現優養化狀態，且存在多樣化的藍綠菌群落（如 Microcystis 及 Planktothrix 等）。功能性註解分析顯示，這些樣本不僅含有合成異味物質（土臭素 geoA 及 2-MIB）的基因，更同時攜帶多種藍綠菌毒素的生物合成基因群（如微囊藻毒素、神經毒素與擬柱孢藻毒素等）。此發現證實了異味物質與潛在毒素基因在環境中的共存性。這項研究的科學意義在於強調水體的「土腥異味」可作為水質潛在毒性風險的早期警訊，為飲用水安全監測提供了重要的生物資訊參考。</t>
+          <t>本研究旨在探究巴西里約熱內盧瓜杜河於2020年初爆發土臭素危機期間的水質狀況，並利用總體基因體學技術探討水質異味與微生物群落之關聯。研究發現，該富營養化水體中含有多種藍菌，且功能性註釋顯示其富含合成土臭素（*geoA*）與2-甲基異莰醇（*mic*）等異味物質的基因。更重要的是，多種藍菌毒素（如微囊藻毒素、石房蛤毒素等）的合成基因群與這些異味基因呈現共存。此發現證實了水體異味的出現與藍菌毒素的潛在生成具有高度相關性，可作為飲用水安全監測及評估藍菌毒素潛在危害的重要預警指標。</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -806,22 +806,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>42647164</t>
+          <t>42647759</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sex differences in the gut microbiome and related metabolites: role in cardiometabolic disease.</t>
+          <t>The Gut Microbiome in Multiple Sclerosis.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>11</v>
-      </c>
+          <t>Neurology(R) neuroimmunology &amp; neuroinflammation</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>others</t>
@@ -829,7 +827,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>未提及（本文為綜論性回顧文章，非原創實驗研究）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -837,12 +835,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sex differences in major cardiometabolic diseases (CMD), such as type 2 diabetes, metabolic dysfunction-associated steatotic liver disease, and cardiovascular disease, have been increasingly recognized across the life course. During the reproductive stage, women generally have a more favorable cardiometabolic risk profile than men, but their risk of experiencing CMD significantly increases after menopause. Emerging evidence suggests that sexually dimorphic gut microbiota and gut microbiota-related metabolites (GMRMs) may contribute to such sex disparities. However, existing findings are heterogeneous and underlying mechanisms remain incompletely understood. In this review, we synthesize the evidence examining sex differences in gut microbial diversity, overall composition, taxa abundances, and levels of GMRMs across key life stages, including pre-puberty, adolescence, and different phases of adulthood (with emphasis on pre- and post-menopausal periods). We summarize potential biological mechanisms underlying sexual dimorphism in the gut microbiome and GMRMs, emphasizing the central role of sex steroids, along with contributions from immune function and other host and environmental factors. We further integrate evidence linking sexually dimorphic microbial taxa (e.g., Akkermansia muciniphila, Eubacterium, Ruminococcus, and other Firmicutes taxa) and GMRMs (e.g., microbiota-derived short-chain fatty acids, secondary bile acids, and trimethylamine N-oxide) to key cardiometabolic pathways involving inflammation, glucose and lipid metabolism, and vascular function. Finally, we identify critical knowledge gaps and emphasize the need for future large longitudinal studies that would integrate repeated measurements of the gut microbiome, untargeted metabolomics, and sex steroid hormones across the life course. Such approaches are essential to clarify biological pathways and inform sex-specific microbiome-based interventions for CMD prevention and management.</t>
+          <t>Multiple sclerosis (MS) is a chronic inflammatory demyelinating disease of the CNS whose risk and course are shaped by both genetic and environmental factors, among which the intestinal microbiota has emerged as a key, potentially modifiable contributor. People with MS frequently display altered gut microbiota, characterized by depletion of fiber-fermenting, short-chain fatty acid (SCFA)-producing commensals, and expansion of taxa associated with mucus degradation and proinflammatory metabolism. These compositional shifts are paralleled by broad changes in blood and CSF metabolites, including reduced SCFAs, tryptophan-derived aryl hydrocarbon receptor ligands, and secondary bile acids. In addition, several reports highlight the accumulation of aromatic amino acid-derived phenolic and indolic compounds and specific lipid mediators linked to neuroinflammation and neurodegeneration. In this up-to-date review, we synthesize evidence from experimental models and human studies showing how microbial metabolites can influence MS pathogenesis through converging mechanisms: modulation of gut and blood-brain barrier integrity; shaping of T-cell and B-cell responses; direct effects on microglia, astrocytes, and oligodendrocyte lineage cells after crossing into the CNS; and modulation of neural circuits, particularly those involving the vagus nerve. Finally, we highlight current gaps, including the need for longitudinal, harmonized multiomic cohorts, and mechanistic studies integrating microbiome, metabolome, and host readouts across gut, blood, and CNS. Overall, available data support a model in which coordinated disruption of the gut microbiota-metabolite axis, rather than any single pathogen, contributes to MS, opening avenues for microbiota-based and metabolite-based biomarkers and therapies aimed at restoring immune and neuroglial homeostasis.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>本文旨在探討性別差異在腸道微生物群與相關代謝物（GMRMs）中如何影響心臟代謝疾病（CMD）。研究指出，受性類固醇、免疫功能及環境因素影響，腸道菌相與代謝產物存在顯著的性別二態性。女性在生育期較男性具備更佳的心臟代謝特徵，但停經後風險顯著升高，此變化與特定菌屬（如 *Akkermansia muciniphila*）及代謝物（如短鏈脂肪酸、次級膽汁酸、TMAO）的豐度改變密切相關。這些微生物與代謝物透過調節發炎反應、醣脂代謝及血管功能，進而影響 CMD 的發生。本文強調未來需透過大型縱向研究，結合微生物組學、代謝組學與荷爾蒙監測，以深入解析其生物學機制，並開發針對不同性別的精準微生物介入療法，對於預防及管理心臟代謝疾病具有重要的科學價值。</t>
+          <t>本研究探討多發性硬化症（MS）與腸道微生物群之間的關聯。研究指出，MS 患者的腸道菌相呈現失調狀態，包括短鏈脂肪酸（SCFA）產生菌減少，以及促發炎代謝菌的增加。這些微生物群落的變化伴隨著血液與腦脊髓液中代謝物（如色胺酸衍生物、膽汁酸及 SCFA）的顯著改變，這些物質經證實與神經發炎及退化密切相關。文中綜述了微生物代謝產物如何透過調節腸道與血腦屏障完整性、影響免疫細胞（T/B 細胞）反應，以及直接作用於神經膠質細胞來參與 MS 的致病機制。總結而言，MS 的發生與腸道菌群-代謝物軸的整體失調有關，而非單一病原體所致。該研究強調未來需進行多體學（multiomics）整合分析，以開發基於微生物群的生物標記與創新治療策略，旨在恢復患者的免疫與神經恆定。</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -852,27 +850,29 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42647164/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647759/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>42647759</t>
+          <t>42647164</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Gut Microbiome in Multiple Sclerosis.</t>
+          <t>Sex differences in the gut microbiome and related metabolites: role in cardiometabolic disease.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Neurology(R) neuroimmunology &amp; neuroinflammation</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Gut microbes</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11</v>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>others</t>
@@ -880,7 +880,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（本文為綜論性回顧文章，非原創實驗研究）</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -888,12 +888,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Multiple sclerosis (MS) is a chronic inflammatory demyelinating disease of the CNS whose risk and course are shaped by both genetic and environmental factors, among which the intestinal microbiota has emerged as a key, potentially modifiable contributor. People with MS frequently display altered gut microbiota, characterized by depletion of fiber-fermenting, short-chain fatty acid (SCFA)-producing commensals, and expansion of taxa associated with mucus degradation and proinflammatory metabolism. These compositional shifts are paralleled by broad changes in blood and CSF metabolites, including reduced SCFAs, tryptophan-derived aryl hydrocarbon receptor ligands, and secondary bile acids. In addition, several reports highlight the accumulation of aromatic amino acid-derived phenolic and indolic compounds and specific lipid mediators linked to neuroinflammation and neurodegeneration. In this up-to-date review, we synthesize evidence from experimental models and human studies showing how microbial metabolites can influence MS pathogenesis through converging mechanisms: modulation of gut and blood-brain barrier integrity; shaping of T-cell and B-cell responses; direct effects on microglia, astrocytes, and oligodendrocyte lineage cells after crossing into the CNS; and modulation of neural circuits, particularly those involving the vagus nerve. Finally, we highlight current gaps, including the need for longitudinal, harmonized multiomic cohorts, and mechanistic studies integrating microbiome, metabolome, and host readouts across gut, blood, and CNS. Overall, available data support a model in which coordinated disruption of the gut microbiota-metabolite axis, rather than any single pathogen, contributes to MS, opening avenues for microbiota-based and metabolite-based biomarkers and therapies aimed at restoring immune and neuroglial homeostasis.</t>
+          <t>Sex differences in major cardiometabolic diseases (CMD), such as type 2 diabetes, metabolic dysfunction-associated steatotic liver disease, and cardiovascular disease, have been increasingly recognized across the life course. During the reproductive stage, women generally have a more favorable cardiometabolic risk profile than men, but their risk of experiencing CMD significantly increases after menopause. Emerging evidence suggests that sexually dimorphic gut microbiota and gut microbiota-related metabolites (GMRMs) may contribute to such sex disparities. However, existing findings are heterogeneous and underlying mechanisms remain incompletely understood. In this review, we synthesize the evidence examining sex differences in gut microbial diversity, overall composition, taxa abundances, and levels of GMRMs across key life stages, including pre-puberty, adolescence, and different phases of adulthood (with emphasis on pre- and post-menopausal periods). We summarize potential biological mechanisms underlying sexual dimorphism in the gut microbiome and GMRMs, emphasizing the central role of sex steroids, along with contributions from immune function and other host and environmental factors. We further integrate evidence linking sexually dimorphic microbial taxa (e.g., Akkermansia muciniphila, Eubacterium, Ruminococcus, and other Firmicutes taxa) and GMRMs (e.g., microbiota-derived short-chain fatty acids, secondary bile acids, and trimethylamine N-oxide) to key cardiometabolic pathways involving inflammation, glucose and lipid metabolism, and vascular function. Finally, we identify critical knowledge gaps and emphasize the need for future large longitudinal studies that would integrate repeated measurements of the gut microbiome, untargeted metabolomics, and sex steroid hormones across the life course. Such approaches are essential to clarify biological pathways and inform sex-specific microbiome-based interventions for CMD prevention and management.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>本研究探討多發性硬化症（MS）與腸道微生物群之間的關聯。研究指出，MS 患者的腸道菌相呈現失調狀態，包括短鏈脂肪酸（SCFA）產生菌減少，以及促發炎代謝菌的增加。這些微生物群落的變化伴隨著血液與腦脊髓液中代謝物（如色胺酸衍生物、膽汁酸及 SCFA）的顯著改變，這些物質經證實與神經發炎及退化密切相關。文中綜述了微生物代謝產物如何透過調節腸道與血腦屏障完整性、影響免疫細胞（T/B 細胞）反應，以及直接作用於神經膠質細胞來參與 MS 的致病機制。總結而言，MS 的發生與腸道菌群-代謝物軸的整體失調有關，而非單一病原體所致。該研究強調未來需進行多體學（multiomics）整合分析，以開發基於微生物群的生物標記與創新治療策略，旨在恢復患者的免疫與神經恆定。</t>
+          <t>本文旨在探討性別差異在腸道微生物群與相關代謝物（GMRMs）中如何影響心臟代謝疾病（CMD）。研究指出，受性類固醇、免疫功能及環境因素影響，腸道菌相與代謝產物存在顯著的性別二態性。女性在生育期較男性具備更佳的心臟代謝特徵，但停經後風險顯著升高，此變化與特定菌屬（如 *Akkermansia muciniphila*）及代謝物（如短鏈脂肪酸、次級膽汁酸、TMAO）的豐度改變密切相關。這些微生物與代謝物透過調節發炎反應、醣脂代謝及血管功能，進而影響 CMD 的發生。本文強調未來需透過大型縱向研究，結合微生物組學、代謝組學與荷爾蒙監測，以深入解析其生物學機制，並開發針對不同性別的精準微生物介入療法，對於預防及管理心臟代謝疾病具有重要的科學價值。</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42647759/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647164/</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>974 個 N2O 相關的基因體 (recovered N2O-associated genomes)</t>
+          <t>974 個重建的 N2O 相關基因體（原文未提及具體的環境樣本採集數量）</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -948,7 +948,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>本研究旨在解析河口與沿海生態系統中，微生物群落如何透過代謝分工調控氧化亞氮（N2O）的排放。研究整合了現場濃度測量、同位素示蹤、宏基因組學及宏轉錄組學分析，發現低鹽度河口區的 N2O 產量與消耗潛力顯著高於沿海區域。透過重組 974 個相關微生物基因體，研究團隊將微生物劃分為產出型、消耗型及自給自足型三大功能群，並揭示其組成與活性會隨鹽度梯度產生位移。關鍵發現顯示，微生物間代謝產物的傳遞不平衡（即 NO/N2O 交換缺口）是導致河口區 N2O 積累的主因。此研究提出了一個全新的概念架構，闡明了微生物群落內部的「代謝分工」如何驅動全球溫室氣體 N2O 的排放，為預測氣候變遷下河口生態系的環境影響提供了重要的科學依據。</t>
+          <t>本研究旨在探討河口與沿海系統中，微生物交互作用如何驅動一氧化二氮（N2O）的排放。研究結合現場觀測、15N同位素速率、總體基因體與轉錄體學，重建了974個N2O相關基因體。結果指出，低鹽度區域的N2O產生與還原速率及基因表達顯著較高。研究將微生物劃分為淨產生者、淨消費者與自給自足者，並發現低鹽度區因群落間物質交換失衡，存在較大的NO/N2O交換缺口，進而導致底層水體N2O顯著累積。本研究建立了群落水平的「分工與交換缺口」理論框架，為預測及理解海洋生態系統N2O排放提供了關鍵的科學依據。</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>metagenomics, others</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>8 個土壤樣本（來自 4 個地區，每個地區含鹽鹼與改良後兩種狀態）</t>
+          <t>未提及（僅說明樣品來自中國4個主要鹽鹼地區，各包含「鹽鹼」與「改良後」兩種狀態之土壤）</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>本研究探討土壤改良對鹽鹼地病毒生態的影響。研究團隊結合宏基因組學（metagenomics）與病毒組學分析，發現病毒群落結構受地理環境及土壤改良狀態顯著影響，其中鹽度與鹼度為關鍵驅動因子。結果顯示，土壤改良過程中病毒具有高度的環境特異性與功能適應性。特別是針對碳循環微生物（如碳水化合物降解菌）的病毒，其與宿主間出現了明顯的豐度失配。透過 13C-纖維素同位素標記探針（DNA-SIP）技術，證實了活躍宿主與病毒間的碳轉移差異。改良土壤中宿主微生物豐度由 39.0% 提升至 61.0%，而連結的病毒豐度則由 60.6% 降至 39.4%。本研究揭示了病毒在鹽鹼地改良與土壤碳固存過程中的關鍵調控角色，為退化土地的生態恢復與管理策略提供了重要的科學依據。</t>
+          <t>本研究旨在探討鹽鹼地改良過程中，病毒對土壤微生物生態與碳循環的影響。研究結合總體基因體與病毒體學，分析中國四大鹽鹼區。結果顯示，土壤改良狀態、鹽度與鹼度是塑造病毒社群的關鍵。在改良土壤中，宿主微生物相對豐度顯著上升（39.0%至61.0%），而關聯病毒減少（60.6%至39.4%），且溫和病毒比例降低，碳循環關鍵微生物的病毒與宿主出現豐度失衡。13C-纖維素DNA-SIP實驗證實了兩者間的活性碳轉移。此發現揭示了病毒在鹽鹼地恢復中的關鍵作用，有助優化土地改良與碳儲存策略。</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>本研究探討母體泌尿道感染（UTI）導致早產的生物學機制。研究人員建立小鼠模型，發現致病性大腸桿菌（UPEC）感染後，發生早產的母鼠表現出顯著的膀胱發炎、胎盤與蛻膜細胞激素升高，以及母體血清 IL-10 濃度降低。實驗證實，外源性補充 IL-10 或隔離 T 細胞可減少胎盤 TH17 細胞並預防早產。在人體臨床隊列中，研究分析了尿液細胞激素與出生結果的關聯，識別出 IL-10、IL-15、GM-CSF 及 RANTES 等與早產風險相關的 T 細胞相關細胞激素。此研究不僅闡明了 UTI 誘發早產的免疫調節機制，更提供了一套非侵入性的生物標記篩檢潛力，為未來預防早產的臨床介入策略奠定基礎。</t>
+          <t>本研究旨在探討孕婦尿路感染（UTI）導致早產的免疫機制。研究團隊建立尿路致病性大腸桿菌（UPEC）感染的孕鼠模型，發現發生早產的母鼠伴隨更嚴重的膀胱發炎、胎盤細胞激素升高及血清IL-10降低；給予外源性IL-10或抑制T細胞，能減少胎盤TH17細胞並預防早產。此外，人類佇列研究證實，尿液中T細胞相關細胞激素（如IL-10、IL-15等）與早產風險密切相關。本研究結合動物模型與臨床樣本，揭示了UTI引發早產的免疫關鍵，並為未來篩檢及治療提供了潛在的非侵入性生物標誌物與機制標靶。</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60 位克隆氏症（CD）成人患者</t>
+          <t>60位患有克隆氏症的成年人 (60 adults with CD)</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>本研究針對波多黎各克隆氏症（CD）成人患者進行橫斷面分析，旨在探討飲食品質、腸道菌相與發炎指標間的關聯。研究透過總體基因體定序（Shotgun metagenomics）分析腸道菌相，並評估多項膳食指數與臨床指標。研究發現，該族群整體飲食品質較差，富含水果的飲食模式與較高的菌相多樣性及較低的發炎指標（鈣衛蛋白、CRP）呈正相關；富含蔬菜模式則與較佳的生活品質相關，而咖啡/甜味劑模式則與症狀負擔加重有關。儘管初步分析顯示飲食與菌相及臨床表現間存在關聯，但經多重比較校正（FDR）後，統計顯著性減弱。本研究證實飲食在調節 CD 患者腸道健康中的潛力，強調未來需進行大規模縱向研究，以進一步釐清飲食介入對改善該群體疾病預後的具體效應。</t>
+          <t>本研究探討波多黎各克隆氏症（CD）成年患者的飲食品質、腸道菌相與發炎指標的關係。研究發現，受試者普遍飲食品質不佳，而較高的飲食品質（特別是富含水果的飲食模式）與較高的腸道菌群多樣性顯著相關。探索性分析顯示，多攝取水果與較低的發炎指標（鈣衛蛋白和C反應蛋白）相關，而蔬菜為主的飲食與較佳的生活品質相關（但經FDR校正後未達顯著）。本研究首次揭示了該少數受關注族群中飲食對菌相與臨床症狀的影響，為未來透過飲食干預管理CD及改善患者預後提供了科學依據。</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2 個區域的農業灌溉池塘與溝渠樣本（文中未明確給出具體檢體總數，僅提及兩處採樣區）</t>
+          <t>未明確提及具體檢體數量（僅指出於西班牙東北部農村的兩個區域，針對灌溉池塘與溝渠進行採樣）</t>
         </is>
       </c>
       <c r="G14" t="b">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>本研究探討農業噴灌系統作為環境病原體儲存庫及氣膠傳播源的角色。研究針對西班牙東北部兩處農業灌溉水體進行宏基因體定序分析，發現高達兩萬種微生物多樣性，並檢測出 21 種具臨床意義的空氣傳播病原菌。研究證實嗜肺性退伍軍人菌（*L. pneumophila*）廣泛存在於灌溉系統中，且經細菌全基因體定序（ST15）比對發現，該環境菌株與 2015 年爆發退伍軍人症但未找到環境源頭的臨床病例具高度親緣關係。結合氣象數據分析，證實灌溉系統產生的氣膠可將病原體遠距離傳播至住宅區。此發現強調農業灌溉設施應被納入環境監測與公共衛生風險評估，以有效預防相關疾病爆發。</t>
+          <t>本研究旨在探討農業噴灌系統是否為嗜肺軍團菌（*Legionella pneumophila*）等致病菌的環境宿主與空氣傳播源。團隊對西班牙農村灌溉水體進行分析，總體基因體學顯示其含有逾2萬種微生物，包括21種臨床相關的空氣傳播病原體，且嗜肺軍團菌相對豐度達4.6%。研究成功分離出嗜肺軍團菌血清型1（ST15），系統發育分析證實該環境株與2015年退伍軍人症爆發的臨床分離株高度相關。氣象數據亦支持風向有利於氣膠從農田長距離擴散至住宅區。此發現證實農業灌溉系統為軍團菌的傳播媒介，強調應將其納入例行環境監測與公衛風險評估。</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>未提及（原文僅提及使用小鼠模型與 IBD 相關人類菌株組合，未明確統計樣本數）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G15" t="b">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>本研究旨在探討定義明確的人類梭菌群（Clostridia consortia）作為活體生物治療產品（LBPs）在治療發炎性腸道疾病（IBD）的潛力。研究利用小鼠結腸炎模型證實，17-mix 與 11-mix 梭菌群能有效緩解由人類微生物群及病原菌驅動的結腸炎。除了傳統認知的短鏈脂肪酸（SCFAs）與 IL-10 產生型調節性 T 細胞機制外，總體基因體與代謝體分析顯示，這些梭菌能透過雙重途徑發揮療效：首先是直接抑制腸道內的病原菌，其次是透過細菌代謝產生的色胺酸代謝物，不依賴 IL-10 而直接活化宿主的芳香烴受體（AhR）抗發炎路徑。此發現揭示了腸道共生菌在恢復黏膜免疫穩態中的新機制，為 IBD 的精準微生態治療提供了重要的科學依據。</t>
+          <t>本研究探討了兩種由人類梭狀芽孢桿菌組成的活體生物藥物（LBP，分別為 17-mix 和 11-mix）治療小鼠結腸炎的療效與機制。研究發現，這些菌群能有效緩解小鼠的慢性與特定病原體誘導的結腸炎。宏基因組學與代謝組學分析顯示，除了傳統的短鏈脂肪酸（SCFA）和 IL-10 途徑外，LBP 還能直接抑制共生病原菌，並透過細菌色胺酸代謝物，以不依賴 IL-10 的方式激活宿主的芳香烴受體（AhR）抗炎途徑。此發現揭示了腸道有益菌保護腸道的新機制，為發炎性腸道疾病（IBD）的微生態療法提供了重要科學依據。</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>metagenomics, metatranscriptomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>本研究探討了在地下水中，由磁黃鐵礦（pyrrhotite）驅動的偏釩酸鹽 [V(V)] 生物還原過程對溫度的敏感性。研究發現，在 4 至 45 °C 的溫度範圍內，V(V) 的移除效率呈現先升後降的趨勢，並在 35 °C 時達到最佳反應速率。透過宏基因組分箱（Metagenomic binning）與轉錄組分析，證實了微生物群落中的電子傳遞活性與關鍵功能基因（涉及 V(V) 還原、硫與鐵氧化）的表現均具有顯著的溫度依賴性。特別是能同時耦合硫與鐵氧化的菌種（如 *Ramlibacter* sp.）僅在 35 °C 下被檢測到，且發現硫氧化過程較鐵氧化過程對溫度變化更為敏感。此研究不僅揭示了環境溫度對生物修復效率的調控機制，也為受釩污染地下水的風險評估及制定精準的生物修復策略提供了關鍵科學依據。</t>
+          <t>本研究旨在探討不同溫度（4至45 °C）對地下水中磁黃鐵礦驅動的偏釩酸鹽 [V(V)] 生物還原過程之影響。研究發現，V(V) 去除率隨溫度升高呈先升後降趨勢，並在 35 °C 時達到峰值（反應速率常數 0.077 d⁻¹），此時 V(V) 被還原為 VO₂ 沉澱，並伴隨硫與鐵的氧化。總體基因體 binning 分析顯示，還原菌的硫氧化過程對溫度變化比鐵氧化更為敏感，且僅在 35 °C 下偵測到能同時耦合硫與鐵氧化的關鍵細菌（如 *Ramlibacter* sp.）。此外，相關功能基因轉錄與電子傳遞活性亦在 35 °C 達到頂峰。本研究揭示了該還原作用的溫度敏感性，為釩污染的環境風險評估與精準生物整治提供了科學依據。</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>metabolomics, metagenomics</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>未提及（研究使用重建的海洋微生物群落及分析現有的海洋宏基因組數據，未明確標註具體樣本人數或檢體數量）</t>
+          <t>未提及（摘要僅指出使用「一個重建的海洋菌群」與「海洋總體基因體數據」進行分析，未說明具體樣本數量）</t>
         </is>
       </c>
       <c r="G17" t="b">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>本研究探討海洋中複雜多醣類「褐藻糖膠」（fucoidans）的微生物降解機制。研究發現，單一微生物難以完全分解褐藻糖膠，但透過具有互補代謝功能的細菌群落，能實現高效協同降解。研究利用代謝組學分析重建的微生物群落，揭示了細菌如何分工合作，分別降解褐藻糖膠的硫酸化岩藻糖主鏈與稀有單體支鏈，此分工使降解效率提升至 97.1%。此外，透過海洋宏基因組數據分析，證實此種功能互補的微生物組合在全球海洋中普遍存在。這項發現闡明了海洋碳循環的關鍵機制，不僅解釋了複雜生物聚合物的環境轉化原理，也為未來設計合成微生物群落以處理難降解多醣類提供了科學框架。</t>
+          <t>本研究旨在探討海洋中複雜且具抗降解性的岩藻多醣（fucoidans）之完全降解機制。研究團隊透過重建海洋菌群，並結合代謝組學與總體基因體學分析，發現岩藻多醣的降解依賴於具備互補代謝功能的特化細菌之間的協同作用（如分別負責降解主鏈與側鏈），這種功能分工使降解效率顯著提升至 97.1%。此外，儘管不同藻類的岩藻多醣結構多變，降解菌的代謝功能卻高度保守。此發現揭示了複雜生物聚合物的環境周轉不僅取決於單一菌株的代謝能力，更受到生態交互作用的影響，為理解海洋碳循環及建構人工合成降解菌群提供了關鍵的科學框架。</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>n=1 (1 位 20 歲男性患者)</t>
+          <t>1名患者（個案報告）</t>
         </is>
       </c>
       <c r="G18" t="b">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>本研究透過病例報告，探討淡水溺水後肺部浸潤與呼吸道微生物組成的臨床挑戰。患者溺水後出現類肺炎之放射線影像與發燒等發炎反應，肺泡灌洗液（BALF）經宏基因組定序（mNGS）檢測出大量肺炎克雷伯菌（*Klebsiella pneumoniae*）。儘管微生物學證據確鑿，但影像學快速恢復及穩定的臨床表現，顯示溺水造成的發炎主要源於非感染性的化學性肺損傷，而非單純的細菌性肺炎。此發現具有重要臨床意義：在處理溺水併發症時，醫師應謹慎判讀微生物檢測結果，避免過度診斷與抗生素濫用，強調了在臨床決策中整合影像學、微生物組學與病程演變的重要性。</t>
+          <t>本研究為一篇病例報告，旨在探討淡水溺水後早期肺部病變與呼吸道微生物學的臨床評估。一名20歲男性溺水復甦後，肺部電腦斷層顯示雙下葉病變，支氣管鏡發現急性刺激性氣道損傷。其肺泡灌洗液（BALF）宏基因組定序（mNGS）與痰液培養均檢出肺炎克雷伯氏菌（*Klebsiella pneumoniae*）。儘管發炎指標升高且微生物檢測呈陽性，但患者影像學迅速改善，顯示肺部異常含有顯著的非感染性成分（如吸入性肺損傷）。患者經抗生素治療後順利康復。本研究的臨床意義在於提醒醫生，溺水後早期的肺部異常易被過度解讀為細菌性肺炎，臨床診斷時需謹慎評估。</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1443,7 +1443,8 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>本研究旨在解決工業廢水中氮、重金屬（Cu2+）與持久性有機污染物（雙酚A，BPA）在低碳條件下難以同時去除的問題。研究團隊開發了一種將 *Pseudoalteromonas japonicus* LY0623 菌株固定於水凝膠-生物炭-AQDS 複合載體中的生物反應器系統。實驗結果顯示，該系統在複雜污染條件下展現出卓越的處理效能，氨氮與硝酸鹽氮去除率分別達到 89% 與 100%，同時成功去除 85% 的 Cu2+ 與 88% 的 BPA。總體基因體分析（metagenomics）證實，系統中的優勢菌群（Pseudomonadota）保持穩定，且與無機碳同化、氮代謝、電子傳遞及芳香族化合物降解相關的關鍵功能路徑皆得以保留。該研究提出的整合性生物修復策略，透過結合生物礦化、氧化還原介導與無機碳利用，為處理含有多種污染物的工業廢水提供了一種高效且節能的新思路。</t>
+          <t>本研究旨在解決低碳條件下，工業廢水中氮、重金屬（Cu2+）與雙酚A（BPA）等混合污染物難以同時高效生物降解的挑戰。研究人員將日本假交替單胞菌（*Pseudoalteromonas japonicus*）LY0623菌株整合至水凝膠-生物炭-AQDS複合載體中，構建出新型固定化生物膜系統（R4系統）。
+研究發現，在僅添加碳酸氫鈉（無機碳源）的條件下，該系統成功實現了NH4+-N（89%）、NO3--N（100%）、Cu2+（85%）和BPA（88%）的高效同時去除。總體基因體學分析證實，變形菌門（Pseudomonadota）為優勢菌群，且系統中與無機碳同化、異營硝化-好氧反硝化（HNAD）、生物礦化及芳香族化合物降解相關的功能通路均得到有效維持。本研究結合了氨氧化產能與生物礦化等機制，為混合污染廢水處理提供了一種具前景的低碳生物修復策略。</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1480,12 +1481,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>metagenomics, small genome</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>297 個真實宏基因組樣本（metagenomes）</t>
+          <t>297 個真實總體基因體數據集 (297 real metagenomes)</t>
         </is>
       </c>
       <c r="G20" t="b">
@@ -1498,7 +1499,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>本研究針對總體基因體學中，組裝高準確度基因體（MAGs）時常見的計算效率瓶頸，開發了一種名為「QuickBin」的新型分箱（binning）演算法。QuickBin 採用 CPU 原生設計，無需依賴 GPU 或標記基因後處理，通過 GC 含量覆蓋率索引與 SIMD 加速比對技術，有效提升計算效能並優化對低汙染、高完整度基因體的組裝能力。在針對 297 個真實宏基因組樣本的效能評估中，QuickBin 展現了比傳統高資源需求工具更高的成功率與產出質量。此工具為大規模、高解析度的微生物群落基因體研究提供了一項高效、可複製的解決方案，能有效推進後續的比較基因體學分析。</t>
+          <t>本研究開發了 QuickBin，這是一種無需標記基因且僅需 CPU 運行的總體基因體分箱（binning）演算法，旨在高效重建高完整度且極低污染的總體基因體組裝基因體（MAGs）。QuickBin 結合了 GC 含量與覆蓋度的空間索引及快速相似性過濾機制，僅在處理模糊合併時使用輕量級神經網路。在 297 個真實總體基因體數據集的基準測試中，QuickBin 成功完成所有運行，且重建的高品質 MAGs 數量超越了其他耗費資源或容易失敗的現有工具。此技術為大規模、可重複的基因體解析總體基因體學研究提供了實用的解決方案。</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1553,7 +1554,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>本研究旨在探討人體腸道微生物群的代謝功能潛力與大腦神經化學物質之間的關聯。研究利用質子磁振光譜（¹H-MRS）量化年輕健康女性在背外側前額葉皮質（dlPFC）、前扣帶皮質（ACC）與下枕回（IOG）中的 GABA 與麩胺酸濃度，並透過宏基因組學（metagenomics）分析腸道菌群在合成與降解 GABA、麩胺酸、短鏈脂肪酸及對甲酚等代謝途徑的功能潛力。研究發現，特定的腸道微生物代謝途徑與大腦區域的神經傳導物質平衡（E/I balance）顯著相關，且這些關聯與受試者的焦慮、憂鬱症狀及睡眠品質存在潛在連結。此研究提供了腸道與大腦軸線（Gut-Brain Axis）在人類神經化學調節上的實證，不僅闡明了腸道菌群對大腦功能的潛在機制，也為未來開發針對微生物群的心理健康介入策略提供了科學依據。</t>
+          <t>本研究旨在探討健康女性的腸道菌群功能潛力與大腦活體神經傳導物質（GABA與麩胺酸）濃度的關聯。研究結合腦部質子磁共振波譜（¹H-MRS）與總體基因體學分析，發現微生物中參與GABA、麩胺酸、短鏈脂肪酸、對甲酚及肌醇代謝的通路，與大腦特定區域（如背外側前額葉、前扣帶迴與下枕葉）的神經傳導物質水平及興奮/抑制平衡（E/I）具有區域特異性關聯。探索性分析亦顯示微生物功能與焦慮、抑鬱及睡眠品質相關。本研究為腸道菌群影響人類大腦神經化學與心理健康提供了直接的人體實證，為未來開發以微生物為基礎的腦腸軸臨床干預奠定基礎。</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1835,12 +1836,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>42635401</t>
+          <t>42635406</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fecal filtrate transplantation as salvage therapy for fulminant Clostridioides difficile infection in adult hematological patients during chemotherapy-induced aplasia: a pilot experience.</t>
+          <t>Separating extracellular from intracellular fecal metabolites exposes cross-feeding architecture in the gut: exploring metabolite partitioning and ecological associations.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1853,12 +1854,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>16S, metagenomics</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>3 位成人血液腫瘤患者</t>
+          <t>63 個糞便檢體（來自 63 位健康受試者）</t>
         </is>
       </c>
       <c r="G27" t="b">
@@ -1866,12 +1867,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Fulminant Clostridioides difficile infection (CDI) in patients with hematologic malignancies during chemotherapy-induced aplasia carries high mortality and limited treatment options. Our objective was to evaluate fecal filtrate transplantation (FFT) as a salvage therapy for fulminant CDI during aplasia, and to explore whether donor-recipient phage dynamics may contribute to clinical response. We conducted a single-center, prospective, protocol-defined pilot case series study including consecutive adults with hematologic malignancies, chemotherapy-induced grade-4 aplasia and fulminant CDI, refractory to ≥5 d of high-dose oral vancomycin plus intravenous metronidazole and tigecycline. FFT was prepared from a single unrelated donor using sequential centrifugation and filtration, and administered via nasogastric tube in two doses. The primary outcome was sustained clinical cure, secondary outcomes included survival and adverse events, assessed at +14 and +30 d post-FFT. 16S rRNA gene sequencing was used to assess microbiome compositions, while viral metagenomics and in vitro propagation assays were employed to characterize donor-recipient phageome interactions. Three patients with adverse-risk acute myeloid leukemia and fulminant CDI caused by genetically distinct C. difficile strains received FFT. All patients achieved clinical resolution by day +14, accompanied by improvements in abdominal distension and inflammatory markers. By day +30, one patient died from Pseudomonas aeruginosa septic shock, while two maintained remission with confirmatory follow-up. FFT was well tolerated, with no procedure-related immediate complications or FFT-attributable adverse events. Microbiome and phage profiling revealed heterogeneous responses, including shifts in bacterial community composition, with no clear evidence for a general role of donor-derived phages in CDI resolution. In contrast, we observed induction of prophages harbored by recipient-associated Clostridium species, which may have contributed to decolonization through stress-induced entry into the lytic cycle. FFT was feasible, with rapid sustained CDI resolution in hematologic patients with chemotherapy-induced aplasia. ClinicalTrials.gov identifier NCT07172191. Prospective single-center pilot study of fecal filtrate transplantation (FFT) for fulminant-refractory C. difficile infection in three aplastic adult hematologic patients. FFT was well tolerated, achieved rapid clinical cure, and showed heterogeneous microbiome and phageome modulation, potentially contributing to therapeutic effects.</t>
+          <t>The gut microbiota forms a complex ecosystem through metabolic interdependence (cross-feeding). However, conventional fecal metabolomics typically quantifies only total metabolite pools, making it difficult to distinguish extracellular-enriched metabolite pools from predominantly cell-associated ones, and thus limiting reconstruction of in situ metabolic networks. Here, we quantified fecal metabolites in paired fractions from the same specimen: an undisrupted fraction representing the extracellular pool and a strongly bead-beaten fraction representing the total pool; the intracellular pool was defined as the difference between total and extracellular measurements. Stool samples from 63 healthy individuals were analyzed for short-chain fatty acids, polyamines, and water-soluble vitamins, and the results were integrated with shotgun metagenomic profiles of species composition and functional genes. Vitamins exhibited two distinct behaviors. Adenosylcobalamin (a vitamin B12 coenzyme) was detectable only after disruption, and together with thiamine (B1) and niacin (B3) was classified as an intracellular-retained type (Type 1). In contrast, biotin (B7) and pantothenate (B5) showed higher extracellular proportions (Type 2). Integrative analyses further indicated that Type 1 thiamine was negatively associated with Blautia, consistent with intensive microbial utilization, whereas Type 2 biotin was strongly positively associated with Alistipes, suggesting links to ecological niches shaped by luminal pH and fermentation modes (carbohydrate vs protein fermentation). Fraction-resolved quantification provides a practical operational framework to differentiate extracellular from cell-associated metabolite pools, helping reconcile metagenomic potential with metabolomic reality and enabling deeper inference of cross-feeding structure in the gut ecosystem.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>本研究旨在評估糞便濾液移植（FFT）作為挽救療法，治療化療致免疫不全之血液腫瘤患者合併難治猛爆性艱難梭菌感染（CDI）的療效，並探討供受體間噬菌體的動力學關係。此臨床先導試驗納入3位患者，結果顯示FFT耐受性良好，所有患者在接受治療後14天內均達到臨床緩解。微生態與噬菌體體學分析顯示，臨床症狀的改善並非源於供體噬菌體的直接轉移，而是FFT可能誘發了受體腸道內艱難梭菌的原噬菌體進入溶菌週期，進而促進病原菌清除。本研究證實FFT在此高風險族群中具安全性與可行性，為難治性CDI提供了創新的機制見解與治療選擇。</t>
+          <t>本研究針對腸道微生物的代謝互營機制（cross-feeding）進行探討。傳統糞便代謝組學僅能分析總代謝物，無法區分細胞外與細胞內代謝池，限制了對代謝網絡的解析。研究團隊透過對比未破碎（代表細胞外池）與強力破碎（代表總代謝池）的糞便樣本，成功推算出細胞內代謝物的分佈。針對短鏈脂肪酸、多胺與水溶性維生素的分析顯示，維生素呈現兩類分佈：B12、B1 與 B3 傾向保留於細胞內（Type 1），而 B7 與 B5 則富集於細胞外（Type 2）。結合宏基因組分析發現，Type 1 代謝物與特定細菌（如 *Blautia*）的利用模式顯著相關，Type 2 代謝物則與 *Alistipes* 及腸道生態位特徵（如 pH 值、發酵類型）相關。此方法為區分代謝物空間分佈提供了實用架構，有助於更精確地將宏基因組功能潛力與代謝體現實連結，深入理解腸道微生物的互營生態結構。</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1881,19 +1882,19 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42635401/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42635406/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>42635406</t>
+          <t>42635403</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Separating extracellular from intracellular fecal metabolites exposes cross-feeding architecture in the gut: exploring metabolite partitioning and ecological associations.</t>
+          <t>Baseline gut microbiome ecology predicts long-term fat mass loss after bariatric surgery: evidence for a thrifty Bifidobacterium phenotype.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1906,12 +1907,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>metagenomics, metabolomics</t>
+          <t>16S, metabolomics</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>63 個糞便檢體（來自 63 位健康受試者）</t>
+          <t>85 位重度肥胖患者及 21 位健康對照組（共 106 名受試者）</t>
         </is>
       </c>
       <c r="G28" t="b">
@@ -1919,12 +1920,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>The gut microbiota forms a complex ecosystem through metabolic interdependence (cross-feeding). However, conventional fecal metabolomics typically quantifies only total metabolite pools, making it difficult to distinguish extracellular-enriched metabolite pools from predominantly cell-associated ones, and thus limiting reconstruction of in situ metabolic networks. Here, we quantified fecal metabolites in paired fractions from the same specimen: an undisrupted fraction representing the extracellular pool and a strongly bead-beaten fraction representing the total pool; the intracellular pool was defined as the difference between total and extracellular measurements. Stool samples from 63 healthy individuals were analyzed for short-chain fatty acids, polyamines, and water-soluble vitamins, and the results were integrated with shotgun metagenomic profiles of species composition and functional genes. Vitamins exhibited two distinct behaviors. Adenosylcobalamin (a vitamin B12 coenzyme) was detectable only after disruption, and together with thiamine (B1) and niacin (B3) was classified as an intracellular-retained type (Type 1). In contrast, biotin (B7) and pantothenate (B5) showed higher extracellular proportions (Type 2). Integrative analyses further indicated that Type 1 thiamine was negatively associated with Blautia, consistent with intensive microbial utilization, whereas Type 2 biotin was strongly positively associated with Alistipes, suggesting links to ecological niches shaped by luminal pH and fermentation modes (carbohydrate vs protein fermentation). Fraction-resolved quantification provides a practical operational framework to differentiate extracellular from cell-associated metabolite pools, helping reconcile metagenomic potential with metabolomic reality and enabling deeper inference of cross-feeding structure in the gut ecosystem.</t>
+          <t>Bariatric surgery (BS) induces weight loss, but long-term success involves complex host-microbiome interactions. We evaluated the longitudinal impact of BS, microbiome resilience, and Mediterranean Diet (MedDiet) adherence up to 24 months. This prospective observational study included 85 patients with severe obesity undergoing BS and 21 normal-weight healthy controls (HC). MedDiet adherence (PREDIMED) was assessed before surgery. Fecal microbiota (16S-rRNA sequencing) and metabolomics (1H-NMR spectroscopy) were analyzed at baseline and at 1-, 6-, and 12-months post-BS. Clinical outcomes and fat mass, evaluated by bioimpedanciometry, were tracked up to 24 months. At baseline, patients exhibited higher microbial Shannon diversity than controls (p = 0.041), alongside a dysfunctional microbiome and metabolome characterized by a higher Firmicutes/Bacteroidetes ratio and elevated levels of branched-chain amino acids (p &lt; 0.0001). Ordinary Least Squares (OLS) regression analysis revealed that MedDiet adherence and type 2 diabetes status significantly modulated baseline diversity. At 12 months post-BS, the gut ecosystem underwent profound remodeling, characterized by depletion of Bifidobacterium spp. and an increase in butyrate levels (p &lt; 0.0001), establishing a novel adaptive state distinct from HC. Baseline gut ecology significantly conditioned long-term BS outcomes: patients in the highest quartile of baseline Bifidobacterium spp. lost significantly less fat mass at 24 months than those in the lowest (6.6% vs. 13.2%, p = 0.010). High baseline Bifidobacterium abundance paradoxically acts as a "thrifty microbiome," potentially maximizing energy harvest and limiting surgery-induced fat loss. Overall, BS induces adaptive microbiome restoration rather than true normalization, highlighting the potential for precision interventions prior to surgery.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>本研究針對腸道微生物的代謝互營機制（cross-feeding）進行探討。傳統糞便代謝組學僅能分析總代謝物，無法區分細胞外與細胞內代謝池，限制了對代謝網絡的解析。研究團隊透過對比未破碎（代表細胞外池）與強力破碎（代表總代謝池）的糞便樣本，成功推算出細胞內代謝物的分佈。針對短鏈脂肪酸、多胺與水溶性維生素的分析顯示，維生素呈現兩類分佈：B12、B1 與 B3 傾向保留於細胞內（Type 1），而 B7 與 B5 則富集於細胞外（Type 2）。結合宏基因組分析發現，Type 1 代謝物與特定細菌（如 *Blautia*）的利用模式顯著相關，Type 2 代謝物則與 *Alistipes* 及腸道生態位特徵（如 pH 值、發酵類型）相關。此方法為區分代謝物空間分佈提供了實用架構，有助於更精確地將宏基因組功能潛力與代謝體現實連結，深入理解腸道微生物的互營生態結構。</t>
+          <t>本研究探討減重手術（BS）後腸道微生物群與長期減脂效果的關聯。研究追蹤 85 名患者於術前及術後長達 24 個月的變化，分析發現手術顯著重塑了腸道菌相與代謝環境，特別是雙歧桿菌（*Bifidobacterium*）的耗竭與丁酸鹽的增加。關鍵發現指出，術前高豐度的雙歧桿菌反而成為一種「節儉型表型」，會增加能量攝取效率，導致術後 24 個月的脂肪減少量顯著較少（6.6% 對比 13.2%）。這顯示減重手術並非使微生物組回歸常態，而是引發一種適應性重組。此研究凸顯了術前腸道生態作為預測手術成效生物標記的潛力，對於未來制定精準的術前介入策略具有重要的臨床指導意義。</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1934,7 +1935,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42635406/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42635403/</t>
         </is>
       </c>
     </row>
@@ -1961,12 +1962,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics, others</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>340 隻跳蚤</t>
+          <t>340 隻跳蚤（每 4 隻混合為一組，共 85 組檢體），最終獲得 1 個分離株（FL-1）</t>
         </is>
       </c>
       <c r="G29" t="b">
@@ -1979,7 +1980,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>本研究旨在分離並表徵巴西家犬身上跳蚤所攜帶的單宿主錐蟲（*Blechomonas* spp.）。研究人員透過培養法分析 340 隻跳蚤，成功分離出 *Blechomonas campbelli* (FL-1 株)。實驗結果顯示，該菌株在 25°C 生長最佳，30°C 生長受限，35°C 則無法生長，顯示其對高溫耐受力差，難以在恆溫動物宿主內存活。形態學觀察發現其具備多種細胞型態，其中「尾鞭毛蟲」（uromonad）階段有利於附著與聚集。系統發生學分析結合了 18S rRNA、gGAPDH 序列及公共宏基因組數據，證實 *B. campbelli* 與 *B. lauriereadi* 廣泛分布於全球的貓蚤與狗蚤中。此研究揭示了該寄生蟲對跳蚤腸道環境的適應機制，並證實整合培養法與生物資訊學工具對於探索節肢動物共生寄生蟲具有高度科學價值。</t>
+          <t>本研究旨在分離並鑑定巴西犬隻跳蚤中的隱鞭蟲（*Blechomonas*），探討其生長、形態與系統發育。研究從340隻跳蚤中成功分離出FL-1株，經鑑定為 *Blechomonas campbelli*。該菌最適生長溫度為25°C，在35°C下無法存活，並具有四種細胞形態（含利於附著的uromonad階段）。系統發育分析證實該物種廣泛分佈於全球的櫛頭蚤屬中。此發現表明其具有適應跳蚤腸道的發育特徵，但因耐熱性差，難以在溫血宿主體內存活。本研究證實了結合傳統培養與公共總體基因體數據挖掘在研究跳蚤相關寄生蟲上的重要價值。</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1996,12 +1997,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>42635403</t>
+          <t>42635401</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Baseline gut microbiome ecology predicts long-term fat mass loss after bariatric surgery: evidence for a thrifty Bifidobacterium phenotype.</t>
+          <t>Fecal filtrate transplantation as salvage therapy for fulminant Clostridioides difficile infection in adult hematological patients during chemotherapy-induced aplasia: a pilot experience.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2014,12 +2015,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>16S, metagenomics</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>85 位重度肥胖患者及 21 位健康對照組（共 106 名受試者）</t>
+          <t>3 位成人血液腫瘤患者</t>
         </is>
       </c>
       <c r="G30" t="b">
@@ -2027,12 +2028,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Bariatric surgery (BS) induces weight loss, but long-term success involves complex host-microbiome interactions. We evaluated the longitudinal impact of BS, microbiome resilience, and Mediterranean Diet (MedDiet) adherence up to 24 months. This prospective observational study included 85 patients with severe obesity undergoing BS and 21 normal-weight healthy controls (HC). MedDiet adherence (PREDIMED) was assessed before surgery. Fecal microbiota (16S-rRNA sequencing) and metabolomics (1H-NMR spectroscopy) were analyzed at baseline and at 1-, 6-, and 12-months post-BS. Clinical outcomes and fat mass, evaluated by bioimpedanciometry, were tracked up to 24 months. At baseline, patients exhibited higher microbial Shannon diversity than controls (p = 0.041), alongside a dysfunctional microbiome and metabolome characterized by a higher Firmicutes/Bacteroidetes ratio and elevated levels of branched-chain amino acids (p &lt; 0.0001). Ordinary Least Squares (OLS) regression analysis revealed that MedDiet adherence and type 2 diabetes status significantly modulated baseline diversity. At 12 months post-BS, the gut ecosystem underwent profound remodeling, characterized by depletion of Bifidobacterium spp. and an increase in butyrate levels (p &lt; 0.0001), establishing a novel adaptive state distinct from HC. Baseline gut ecology significantly conditioned long-term BS outcomes: patients in the highest quartile of baseline Bifidobacterium spp. lost significantly less fat mass at 24 months than those in the lowest (6.6% vs. 13.2%, p = 0.010). High baseline Bifidobacterium abundance paradoxically acts as a "thrifty microbiome," potentially maximizing energy harvest and limiting surgery-induced fat loss. Overall, BS induces adaptive microbiome restoration rather than true normalization, highlighting the potential for precision interventions prior to surgery.</t>
+          <t>Fulminant Clostridioides difficile infection (CDI) in patients with hematologic malignancies during chemotherapy-induced aplasia carries high mortality and limited treatment options. Our objective was to evaluate fecal filtrate transplantation (FFT) as a salvage therapy for fulminant CDI during aplasia, and to explore whether donor-recipient phage dynamics may contribute to clinical response. We conducted a single-center, prospective, protocol-defined pilot case series study including consecutive adults with hematologic malignancies, chemotherapy-induced grade-4 aplasia and fulminant CDI, refractory to ≥5 d of high-dose oral vancomycin plus intravenous metronidazole and tigecycline. FFT was prepared from a single unrelated donor using sequential centrifugation and filtration, and administered via nasogastric tube in two doses. The primary outcome was sustained clinical cure, secondary outcomes included survival and adverse events, assessed at +14 and +30 d post-FFT. 16S rRNA gene sequencing was used to assess microbiome compositions, while viral metagenomics and in vitro propagation assays were employed to characterize donor-recipient phageome interactions. Three patients with adverse-risk acute myeloid leukemia and fulminant CDI caused by genetically distinct C. difficile strains received FFT. All patients achieved clinical resolution by day +14, accompanied by improvements in abdominal distension and inflammatory markers. By day +30, one patient died from Pseudomonas aeruginosa septic shock, while two maintained remission with confirmatory follow-up. FFT was well tolerated, with no procedure-related immediate complications or FFT-attributable adverse events. Microbiome and phage profiling revealed heterogeneous responses, including shifts in bacterial community composition, with no clear evidence for a general role of donor-derived phages in CDI resolution. In contrast, we observed induction of prophages harbored by recipient-associated Clostridium species, which may have contributed to decolonization through stress-induced entry into the lytic cycle. FFT was feasible, with rapid sustained CDI resolution in hematologic patients with chemotherapy-induced aplasia. ClinicalTrials.gov identifier NCT07172191. Prospective single-center pilot study of fecal filtrate transplantation (FFT) for fulminant-refractory C. difficile infection in three aplastic adult hematologic patients. FFT was well tolerated, achieved rapid clinical cure, and showed heterogeneous microbiome and phageome modulation, potentially contributing to therapeutic effects.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>本研究探討減重手術（BS）後腸道微生物群與長期減脂效果的關聯。研究追蹤 85 名患者於術前及術後長達 24 個月的變化，分析發現手術顯著重塑了腸道菌相與代謝環境，特別是雙歧桿菌（*Bifidobacterium*）的耗竭與丁酸鹽的增加。關鍵發現指出，術前高豐度的雙歧桿菌反而成為一種「節儉型表型」，會增加能量攝取效率，導致術後 24 個月的脂肪減少量顯著較少（6.6% 對比 13.2%）。這顯示減重手術並非使微生物組回歸常態，而是引發一種適應性重組。此研究凸顯了術前腸道生態作為預測手術成效生物標記的潛力，對於未來制定精準的術前介入策略具有重要的臨床指導意義。</t>
+          <t>本研究旨在評估糞便濾液移植（FFT）作為挽救療法，治療化療致免疫不全之血液腫瘤患者合併難治猛爆性艱難梭菌感染（CDI）的療效，並探討供受體間噬菌體的動力學關係。此臨床先導試驗納入3位患者，結果顯示FFT耐受性良好，所有患者在接受治療後14天內均達到臨床緩解。微生態與噬菌體體學分析顯示，臨床症狀的改善並非源於供體噬菌體的直接轉移，而是FFT可能誘發了受體腸道內艱難梭菌的原噬菌體進入溶菌週期，進而促進病原菌清除。本研究證實FFT在此高風險族群中具安全性與可行性，為難治性CDI提供了創新的機制見解與治療選擇。</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2042,7 +2043,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42635403/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42635401/</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2128,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2,422 隻蝙蝠中篩選出的 150 組配對肺部與腸道樣本（共 300 個檢體）</t>
+          <t>2,422 隻蝙蝠中篩選出的 150 對肺與腸道檢體</t>
         </is>
       </c>
       <c r="G32" t="b">
@@ -2140,7 +2141,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>本研究旨在利用巴西現有的狂犬病被動監測系統，建立一套偵測蝙蝠源人畜共通病毒的監測框架。研究團隊從聖保羅州收集的 2,422 隻蝙蝠中，篩選出 150 組配對的肺部與腸道樣本進行奈米孔總體基因體定序。結果成功偵測到來自沙狀病毒、冠狀病毒及副黏液病毒等 12 個具公衛重要性病毒科的 98 個病毒基因片段，並首次在美洲蝙蝠中發現一種未知的絲狀病毒。此研究不僅揭示了隱匿的病毒多樣性，更證實該框架能有效預防新興傳染病，為中低收入國家提供了一套可推廣至全國的「健康一體」（One Health）防疫監測模型。</t>
+          <t>本研究旨在建立一個結合巴西現有狂犬病被動監測計畫的病毒總體基因體學監測架構，以偵測都市蝙蝠所攜帶的潛在人畜共通病毒。研究團隊從聖保羅州收集的 2,422 隻蝙蝠中，篩選出 150 對肺部與腸道檢體進行奈米孔定序。結果成功偵測到 12 個與公共衛生密切相關病毒科的 98 個病毒基因片段（包括沙狀、冠狀與副黏液病毒科等），更首次在美洲蝙蝠中發現一種未知絲狀病毒。此研究不僅揭示了未曾被發現的病毒多樣性，證實利用現有動物監測系統預防流行病的可行性，更為中低收入國家提供了一個具備「健康一體」（One Health）共識、可擴展至全國的傳染病監測模型。</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">

--- a/papers_database.xlsx
+++ b/papers_database.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>253 位嬰兒（於三個時間點收集糞便檢體與問卷資料）</t>
+          <t>253 位嬰兒</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -514,7 +514,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>本研究介紹了瑞典全國性前瞻性嬰兒隊列「PREVENT 1」，旨在追蹤嬰兒出生後前兩年的腸道微生物體發育，並探討其與餵養、感染、生長及日常健康的關聯。研究收集253位嬰兒在三個時間點的糞便檢體與家長問卷，並結合散彈槍總體基因體學分析。該隊列具備極高留存率，未來將深入探討抗生素暴露與飲食等早期生活因素，如何影響嬰兒腸道菌相特徵、耐藥組（resistome）及功能通路。這項研究為理解早期微生物體發育對嬰兒健康與發育的長期影響，提供了關鍵的縱向科學數據。</t>
+          <t>PREVENT 1 是一項瑞典全國性的前瞻性隊列研究，旨在描繪嬰兒出生後前兩年腸道菌相的發展軌跡，並探討其與餵養方式、感染、生長發育及日常健康指標的關聯。該研究透過縱向追蹤，針對 253 名嬰兒收集糞便樣本，並運用宏基因組學（shotgun metagenomics）技術進行深入分析，同時結合父母問卷、糞便照片及嬰兒哭聲紀錄等多模態數據。此隊列具備高保留率，為期三階段的數據採集已於 2024 年底完成。本研究的核心科學意義在於建立一個大規模的嬰兒菌相參考庫，未來將進一步解析抗生素暴露、飲食攝取對菌相功能路徑與抗藥基因組（resistome）的影響，對於理解早期生命階段的微生物群落如何塑造嬰兒長期健康與免疫發展具有重大貢獻。</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -551,12 +551,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>metagenomics, small genome</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（摘要中未明確列出具體的檢體總數或個體數量）</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -569,7 +569,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>本研究旨在評估家畜與瀕危普氏原羚在共同放牧環境中，微生物組內遺傳危害（抗藥性基因、金屬耐受基因與毒力因子）的來源、移動性及宿主。利用總體基因體學分析犛牛、藏羊、普氏原羚及表土。結果發現，家畜的危害基因豐度高於普氏原羚；來源追蹤顯示，普氏原羚約 64% 的抗藥性組分來自兩種家畜，而表土貢獻小於 1%。此外，移動遺傳因子與危害基因顯著相關，且研究成功解析出攜帶多重危害基因的細菌基因體。本研究將野生動物抗藥性監測提升至來源歸屬與宿主定位，為家畜與野生動物交界處的公共衛生多層次監測提供科學依據。</t>
+          <t>本研究針對放牧家畜與瀕危物種普氏原羚（Przewalski's gazelle）共享棲地所帶來的基因危害（如抗藥性基因 ARGs、金屬抗性基因 MRGs 及毒力因子 VFs）進行宏基因組學分析。研究發現家畜攜帶的基因危害豐度高於野生原羚，且定量來源歸因分析顯示，原羚體內約 64% 的抗藥性組成源自家畜，而非土壤。透過基因組解析，研究鑑定出特定的細菌宿主（如藏羊體內的 *E. coli* 及原羚體內的 *Hylemonella* sp.），揭示了移動遺傳因子（MGEs，特別是 *tnpA*）在傳播這些遺傳危害中的關鍵作用。本研究建立了一套評估野生動物抗藥體（resistome）的架構，不僅提升了來源追蹤的精確度，更為監測人畜共通疾病風險及制定野生動物保育策略提供了重要的科學依據。</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>278 位腸胃道癌症患者</t>
+          <t>278 位消化道癌症患者</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -624,7 +624,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>本研究旨在探討腸道菌群影響腸胃道（GI）癌症免疫治療療效的機制。透過278位患者的總體基因體分析，發現「唾液乳桿菌」（*L. salivarius*）在治療有反應者體內顯著富集。動物實驗證實，該菌能增加抗腫瘤M1型巨噬細胞與CD8+ T細胞浸潤，增強抗PD-1療效。其關鍵代謝物「鵝去氧膽酸」（CDCA）能誘發腫瘤細胞產生活性氧（ROS）以觸發免疫原性死亡，並促進巨噬細胞向M1型極化以活化T細胞免疫。本研究證實*L. salivarius*與CDCA是提升GI癌症免疫治療活性的潛在新型佐劑。</t>
+          <t>本研究旨在探討腸道菌群對消化道癌症免疫檢查點抑制劑（如抗 PD-1 療法）治療反應的影響。透過對 278 位患者進行宏基因組學分析，發現唾液乳桿菌（*Lactobacillus salivarius*）在治療反應佳的患者中顯著富集。實驗證實該菌株能增強抗腫瘤 M1 型巨噬細胞與 CD8+ T 細胞的浸潤，進而提升抗 PD-1 療法的功效。研究進一步鑑定出其關鍵代謝物——鵝去氧膽酸（CDCA），其能誘導腫瘤細胞產生免疫原性細胞死亡，並促進巨噬細胞極化為 M1 型，啟動 CD8+ T 細胞的抗腫瘤免疫反應。此發現指出 *L. salivarius* 及其代謝物 CDCA 有望成為輔助治療消化道癌症的新型藥物，為克服臨床免疫治療耐藥性提供了重要的科學依據。</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（原文僅提及實驗處理組別與植栽盆數，未標示具體檢體總數）</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -679,7 +679,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>本研究旨在評估不同溫度製備的茶渣生物炭（TWB），在不同施用方式下對農業土壤中PFAS（PFOS與PFOA）移動性及溫室氣體（N2O、CH4）排放的調控效應。結果顯示，500 °C製備的TWB-500具最佳物理化學特性。全土混合施用TWB-500可顯著降低土壤及滲出液中的PFAS，並使植物地上部的PFAS濃度減少約36%，同時降低N2O排放並促進CH4淨吸收。總體基因體學分析證實，TWB降低了固氮與N2O生成相關基因的豐度，且PFAS的控制主要源於物化阻隔而非微生物脫氟。本研究證實TWB-500能同時兼顧PFAS穩定化與溫室氣體減排，為土壤整治提供具體策略。</t>
+          <t>本研究探討茶葉廢棄物生物炭（TWB）應用於農地土壤時，對全氟烷基物質（PFAS）遷移及溫室氣體（N2O、CH4）排放的雙重影響。研究發現，經 500 °C 熱裂解之生物炭（TWB-500）因具備最佳的孔隙度與表面特性，能有效吸附土壤中的 PFOS 與 PFOA，並透過全土混拌法使植株體內的 PFAS 濃度降低約 36%。此外，TWB 處理能顯著減少 N2O 排放並促進土壤對 CH4 的吸收。總體基因體分析顯示，生物炭降低了氮循環相關功能基因的豐度，證實 PFAS 的移除主要歸因於物理化學吸附，而非微生物脫氟作用。本研究結論指出，透過調整生物炭施用方式（全土混拌 vs. 表面覆蓋），可針對 PFAS 穩定化或溫室氣體減排進行最適化的農地管理，具備顯著環境應用價值。</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>353 個鰓部樣本（來自 15 種低鞍鮨屬魚類）</t>
+          <t>353 個魚鰓檢體</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -734,7 +734,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>本研究利用總體基因體學探討加勒比海低鞍鮨屬（Hypoplectrus）珊瑚礁魚類的鰓部微生物群。團隊分析13年間採自8個地點、15種魚類的353個鰓部樣本，重建出70個宏基因組組裝基因體（MAGs）。研究發現鰓部菌群與海水顯著不同；其中一個廣泛分佈的伯克氏菌科（Burkholderiaceae）譜系具備碳固定與硫氧化潛力，首度證實魚鰓可能宿有化能合成細菌。該菌株的基因體地理結構與宿主的演化關係相吻合。本研究揭示了複雜的宿主與微生物生態演化互動，對理解魚類生理、穩態與免疫具有重要價值。</t>
+          <t>本研究針對加勒比海 15 種雀鯛科魚類（Hypoplectrus spp.）進行基因體解析宏基因組學（genome-resolved metagenomics）分析，旨在探討其魚鰓微生物群落結構。研究共分析 353 個樣本，重建了 70 個宏基因組組裝基因組（MAGs），發現魚鰓微生物群落與周邊海水環境存在顯著差異，具有高度特異性。最關鍵的發現是鑑定出一種廣泛分佈於各物種與地理區域的伯克氏菌科（Burkholderiaceae）菌株，該菌株具備碳固定與硫氧化代謝路徑，暗示魚鰓可能存在化能合成微生物。此研究首次揭示魚類鰓部潛在的化能合成共生關係，並證實微生物群落結構與宿主魚類的地理演化路徑具有高度相關性，為理解魚類生理穩態及免疫反應的微生物機制提供了重要的科學基礎。</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3種不同的接種源（海洋沉積物 MFC-MS、河口沉積物 MFC-ES、厭氧活性污泥 MFC-AS）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -789,7 +789,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>本研究比較雙室微生物燃料電池（MFC）中三種接種源（海洋沉積物、河口沉積物與厭氧活性污泥）對亞甲基藍染料降解與發電的效率。結果顯示，海洋沉積物系統（MFC-MS）的輸出功率密度（35 mW/m²）與庫倫效率（25%）最高；厭氧污泥系統（MFC-AS）則在COD去除率（75%）與脫色率（96小時達96%）表現最佳。毒性試驗證實處理後廢水毒性顯著降低。總體基因體學分析進一步揭示了相關電致活性菌、酵素與代謝途徑的作用。本研究證實MFC能有效結合染料廢水處理與綠色能源回收，具重要科學與應用價值。</t>
+          <t>本研究旨在評估三種不同陽極接種源（海洋沉積物、河口沉積物及厭氧污泥）在微生物燃料電池（MFC）中，處理亞甲基藍（MB）染料廢水的效能與產電表現。研究發現，使用海洋沉積物接種的 MFC 具有最高的功率密度（35 mW/m²），而厭氧污泥則在脫色效率上表現最佳，96 小時內達 96% 的脫色率。此外，透過宏基因組學（metagenomics）分析，研究確認了接種源中電活性細菌的功能與酵素路徑，證明 MFC 技術能有效降解染料並降低廢水的植物毒性。此研究顯示，選擇合適的微生物接種源對於優化 MFC 系統的污染物降解與能量回收具備顯著科學意義與應用潛力。</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1個40毫升的淡水湖水樣</t>
+          <t>1 個 40 ml 淡水湖泊水樣</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -844,7 +844,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>本研究旨在探討美國亞利桑那州弗拉格斯塔夫附近一處小型淡水湖中的病毒多樣性。研究人員透過對一個40毫升的湖水樣本進行病毒總體基因體學分析，成功鑑定並組裝出295個環狀病毒基因體序列。在這些病毒基因體中，有126個屬於Cressdnaviricota門，169個屬於Phixviricota門。此研究的科學意義在於擴展了科學界對淡水生態系統中單鏈DNA病毒（如Cressdnaviricota和Phixviricota）基因體多樣性的認識，並為環境微生物學與病毒生態學研究提供了重要的新型基因體數據。</t>
+          <t>本研究針對美國亞利桑那州弗拉格斯塔夫附近一處淡水湖泊進行病毒宏基因體（Viral metagenomics）分析。研究人員透過對 40 毫升水樣的深度測序與生物資訊分析，成功組裝出 295 個環狀病毒基因體序列。在分類學鑑定中，發現其中 126 個基因體屬於 CRESS 型 DNA 病毒門（Cressdnaviricota），另 169 個則屬於噬菌體病毒門（Phixviricota）。本研究不僅擴展了環境病毒組的資料庫，亦有助於了解淡水生態系統中病毒的多樣性與演化關係，為未來探討病毒在微生物群落中的生態角色提供重要基礎。</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>178 位患者的肺泡灌洗液（BALF）檢體（包含 77 位免疫功能低下患者與 101 位免疫功能正常患者）</t>
+          <t>178 位患者（包含 77 位免疫功能低下患者及 101 位免疫功能正常患者）</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -899,7 +899,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>本研究旨在評估肺泡灌洗液總體基因體定序（BALF-mNGS）在區分疑似侵入性肺麴菌病（IPA）患者中「真菌感染」與「定植」的臨床價值。研究納入 178 位患者，發現感染者的麴菌屬定量讀數（RPTM）顯著高於定植者，並針對免疫低下與免疫正常患者分別建立最佳定量切點（24 與 33 RPTM）。微生態分析顯示兩群體具獨特的肺部菌相結構。臨床上，BALF-mNGS 能有效引導精準抗真菌治療，避免不必要的用藥，且較高的麴菌 RPTM 與免疫低下患者的 90 天死亡率顯著相關。此技術不僅能精準診斷，更具備患者預後風險分層的臨床應用價值。</t>
+          <t>本研究旨在探討支氣管肺泡灌洗液總體基因體定序（BALF-mNGS）在區分侵襲性肺麴菌病（IPA）感染與定殖的臨床應用價值。研究分析了 178 名疑似 IPA 患者，根據免疫狀態進行分組，並利用麴菌每千萬定序讀數（RPTM）作為指標。結果顯示，BALF-mNGS 能有效區分感染與定殖，並為免疫功能低下與正常患者建立特定的最佳判定閾值。微生物體分析揭示，在免疫功能低下患者中，麴菌屬在感染組呈現顯著富集，且高 RPTM 值與 90 天死亡率高度相關。本研究證實 BALF-mNGS 不僅能優化抗真菌藥物的精準投藥、避免過度治療，更可作為免疫功能低下患者風險分層的有效工具，具備顯著的臨床轉譯潛力。</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -936,12 +936,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>metagenomics, small genome</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1 位患者 (1 個臨床檢體)</t>
+          <t>1 個臨床檢體（單一病例報告）</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -954,7 +954,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>本研究旨在調查2023-2024年拉丁美洲奧羅普切熱疫情期間，哥倫比亞普圖馬約地區一名急性發熱患者的病原。研究團隊利用針對脊椎動物病毒的宏基因組定序技術（VirCapSeq-VERT），成功鑑定並分離出與卡拉帕魯（Caraparu）複合群相關的C群正布尼亞病毒。儘管本研究僅限單一病例，且缺乏血清學或追蹤臨床數據，但研究結果強調了在亞馬遜盆地等地方性流行疫區，採用無偏向性的分子生物學方法（如宏基因組學）對於診斷未明原因發熱疾病的關鍵科學與臨床價值。</t>
+          <t>本研究針對哥倫比亞亞馬遜地區一名急性發燒患者進行病毒分析。在 2023-2024 年奧羅普切熱（Oropouche fever）流行期間，研究人員透過標靶富集宏基因組測序技術（VirCapSeq-VERT），成功鑑定並分離出一株屬於 C 群正布尼亞病毒（Orthobunyavirus），其親緣關係接近 Caraparu 複合群。此發現顯示在臨床症狀與常見蟲媒病毒重疊的地區，利用宏基因組學等非偏向性分子檢測技術，對於釐清不明原因發燒病例具有高度診斷價值，能有效提升對新興或罕見病毒感染的監測能力，對區域防疫與公共衛生決策具重要科學意義。</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4種珠狀模擬菌群（包含26種臨床分離菌株），共進行25次重複分析與2種核酸萃取試劑盒測試</t>
+          <t>25 次重複分析（針對開發出的四種模擬群落進行評估）</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>本研究開發並驗證了四種珠狀模擬菌群（包含26種常見於胃腸道、呼吸道、皮膚、生殖道及腦脊髓液的臨床分離菌株），作為臨床總體基因體次世代定序（mNGS）的品質管制標準品。研究利用鳥槍法總體基因體測序評估其重現性，結果顯示主要菌屬（相對豐度&gt;20%）的重複性良好（變異度&lt;10%），但不同核酸萃取試劑盒會顯著影響菌相分佈。此研究證實微生物模擬菌群是臨床mNGS標準化不可或缺的質控材料，有助於評估實驗偏差並提升檢測流程的再現性與準確性。</t>
+          <t>本研究旨在解決臨床宏基因組次世代定序（mNGS）在品質控制與再現性上的挑戰，開發了四種基於珠粒的「模擬微生物群落」（mock communities）作為標準品。這些群落涵蓋了腸道、呼吸道、皮膚、生殖道及腦脊髓液中常見的 26 種菌株。研究透過鳥槍法全宏基因體定序（shotgun metagenomics）評估了不同 DNA 萃取試劑盒（MagMAX 與 PowerSoil）及實驗流程對結果的偏誤影響。結果顯示，微生物的檢測豐度會顯著受到萃取試劑盒選擇的干擾，且在 25 次重複實驗中，群落組成存在一定的實驗室內誤差。此研究確立了模擬群落作為臨床 mNGS 品質控制材料的重要性，對於推動微生物組檢測的標準化流程與臨床應用具有關鍵價值。</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>未提及（摘要僅指出使用 DSS 誘導的慢性結腸炎小鼠模型、人源 CCD-18Co 及小鼠原代腸道纖維母細胞，未提及具體樣本數量）</t>
+          <t>未提及（研究使用 DSS 誘導的小鼠模型以及人類與小鼠的原代纖維母細胞，但未具體說明樣本數）</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>本研究探討抗性澱粉（RS）對腸道纖維化的緩解作用及其機制。研究發現，RS能有效減輕慢性結腸炎小鼠的腸道纖維化並減少細胞外基質沉積。總體基因體與靶向代謝組學分析顯示，RS能重塑腸道菌群結構，促進產短鏈脂肪酸的有益菌生長，並顯著提升乙酸水平。體外細胞實驗進一步證實，乙酸透過抑制組蛋白去乙醯化酶2（HDAC2）以增加組蛋白H3K27乙醯化，進而阻斷TGF-β誘導的纖維母細胞活化。此發現揭示了一條連結RS、乙酸與纖維化緩解的「微生態-代謝-表觀遺傳」軸，為臨床治療腸道纖維化提供了潛在的膳食干預靶點。</t>
+          <t>本研究探討抗性澱粉（RS）對腸道纖維化的改善作用及其潛在機制。透過 DSS 誘導的小鼠結腸炎模型，研究發現 RS 可有效減輕腸道纖維化並減少細胞外基質堆積。宏基因體定序顯示 RS 能重塑腸道菌群，增加如 *Bacteroides acidifaciens* 等短鏈脂肪酸產生菌的豐度；代謝體分析進一步證實乙酸（acetate）水平顯著上升。機制研究揭示，乙酸能抑制纖維母細胞中 HDAC2 的活性，進而提升組蛋白 H3K27 的乙醯化水平，抑制 TGF-β 誘導的纖維母細胞活化。本研究提出了一條「微生物-代謝-表觀遺傳」軸線，指出 RS 可藉由促進乙酸生成來對抗腸道纖維化，為治療纖維化相關疾病提供了新的科學依據與潛在治療靶點。</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>metagenomics, metatranscriptomics, small genome</t>
+          <t>metagenomics, small genome, others (transcriptional profiling)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（研究基於特定實驗室富集培養物之實驗與分析）</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>本研究成功富集並鑑定了一種新型耐鹽鹼厭氧氨氧化（anammox）細菌，暫命名為 *Candidatus* Loosdrechtia alkalitolerans（富集度 &gt;80%）。該菌在長期鹽鹼壓力下（0.5% NaCl, pH ~9.13）具有顯著的競爭優勢。比較基因體學分析顯示，該菌特異性編碼了完整的 Mrp 陽離子/質子反向轉運體操縱子。轉錄組分析進一步證實，在鹼性壓力下添加鈉離子會上調 *mrp* 的表達，協助維持細胞內的酸鹼平衡。此研究揭示了厭氧氨氧化菌耐鹽鹼的分子機制，拓展了對其生理可塑性與生態角色的認知。</t>
+          <t>本研究成功富集並鑑定出一種耐鹽鹼的厭氧氨氧化（Anammox）細菌，命名為 *Candidatus Loosdrechtia alkalitolerans*。該菌株在長期高鹽、高鹼（0.5% NaCl，pH 9.13）環境下表現出強大的競爭優勢。透過基因體比較分析，研究發現該菌株含有特殊的 Mrp 陽離子/質子反向轉運蛋白操縱子，這是其適應鹼性環境的關鍵機制；轉錄組分析進一步證實，在鹼性壓力下，補充鈉離子可上調 Mrp 表現並恢復其代謝活性。此發現不僅揭示了厭氧氨氧化菌應對鹽鹼逆境的生理分子機制，證明了該菌在廣泛的淡水與廢水生態系統中具有潛在的生態地位，更為未來工業廢水處理中的脫氮技術應用提供了理論基礎與科學見解。</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>46 對母嬰（收集 46 個母乳檢體）</t>
+          <t>46 對母嬰（46 個母乳檢體）</t>
         </is>
       </c>
       <c r="G14" t="b">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>本研究旨在探討秘魯母親的母乳微生物群與嬰兒缺鐵性貧血（IDA）之間的關聯。研究招募46對母嬰，並利用16S rRNA定序技術分析母乳樣本。結果顯示，母乳菌群主要由鏈球菌屬與葡萄球菌屬主導；非缺鐵性貧血（non-IDA）組母親的母乳菌群豐富度（Alpha多樣性）顯著高於健康組與IDA組。此外，IDA組的母乳中含有較高比例的棒狀桿菌屬（Corynebacterium）和不動桿菌屬（Acinetobacter），且鏈球菌屬豐度有降低趨勢。本研究證實不同嬰兒貧血狀態下母乳微生物群存在顯著差異，為理解嬰兒缺鐵性貧血的病理機制提供了新的微生態視角。</t>
+          <t>本研究探討祕魯農村地區嬰兒缺鐵性貧血（IDA）與母親母乳（hBM）菌相之間的關聯。研究對象為 46 對母嬰，透過 16S rRNA 定序分析母乳微生物群落，發現母乳菌相以鏈球菌屬（Streptococcus）與葡萄球菌屬（Staphylococcus）為優勢菌群。研究結果顯示，非貧血組嬰兒的母親，其母乳具備較高的細菌豐富度。此外，IDA 組嬰兒母親的母乳中，棒狀桿菌屬（Corynebacterium）與不動桿菌屬（Acinetobacter）等細菌豐度較高，而鏈球菌屬則呈現下降趨勢。此研究發現母乳微生物群組成可能與嬰兒貧血狀態相關，雖無法直接證實因果關係，但為後續探討嬰兒貧血的致病機制提供了重要的微生物學線索。</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>本研究探討鈉離子（Na+）在甲烷厭氧氧化（AOM）偶聯六價鉻［Cr(VI)］生物還原過程中的調控機制。研究發現，添加鈉離子可顯著提升 Cr(VI) 的還原效率（去除率自 79.8% 提升至 100%）。微生物群落與總體基因體學分析顯示，Na+ 富集了具 AOM 能力的 *Methanobacterium* 與具胞外電子傳遞（EET）能力的活性電位菌，兩者形成共生體。此外，Na+ 增強了微生物聚集體的電子儲存能力、降低傳遞阻抗，並提升胞內 ATP 及輔酶 F420 水平。基因分析證實，Na+ 上調了逆向甲烷生成及膜結合電子傳遞基因，顯示 EET 介導的胞外還原為關鍵機制。本研究為甲烷驅動的鉻污染修復提供了重要理論基礎。</t>
+          <t>本研究旨在探討鈉離子（Na+）對「厭氧甲烷氧化（AOM）耦合六價鉻（Cr(VI)）還原」系統的調控機制。實驗結果顯示，添加NaCl可顯著提升Cr(VI)還原效率，達到完全去除。機制分析發現，Na+能富集具有甲烷氧化能力的「甲烷桿菌屬（*Methanobacterium*）」與具備胞外電子傳遞能力的電活性細菌，並透過增加輔酶F420及ATP含量來優化微生物能量代謝。總體基因體學分析進一步證實，Na+上調了逆向甲烷代謝酵素及膜結合電子傳遞複合體基因，同時促進胞外聚合物（EPS）分泌，從而降低電子傳遞阻力。此研究揭示了Na+透過強化胞外電子傳遞與能量代謝，促進甲烷驅動的重金屬修復作用，為環境污染整治提供了重要的理論依據。</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>metagenomics, others</t>
+          <t>metagenomics, others (metaproteomics)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（文中僅提及堆肥處理組別，未明確列出具體的樣本總數或重複次數）</t>
         </is>
       </c>
       <c r="G16" t="b">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>本研究旨在探究堆肥過程中群體感應（QS）調控微生物腐殖化（humification）的具體機制。研究發現，聯合添加硫酸錳與零價鐵（CMF）能顯著提高腐植酸（HA）的含量與聚合度，並增強其熱穩定性與芳香性。多體學（總體基因體學與總體蛋白質組學）分析顯示，CMF在堆肥高溫期顯著促進了Bacillota、Chloroflexota和Myxococcota等高溫菌的富集，並大幅上調QS與氧化還原相關基因的表達。網路分析與體外實驗進一步證實，關鍵QS模組（如ahlD與3-OXO-C8-HSL）能促進菌群間的協作，進而驅動下游代謝並加速HA的芳香化。此研究為精準調控堆肥腐殖化提供了全新的微生物生態學見解。</t>
+          <t>本研究旨在探討高溫堆肥過程中，群體感應（QS）機制與微生物氧化還原功能如何調控腐植質（humus）的形成。研究發現，添加硫酸錳與零價鐵（CMF）能顯著提升腐植酸（HA）含量與聚合度。透過總體基因體學（metagenomics）與總體蛋白質體學（metaproteomics）分析，證實 CMF 處理在堆肥高溫期顯著活化了 QS 相關基因（如 ahlD）及腐植化相關氧化還原酶的表現。研究結果指出，QS 機制藉由促進細菌間的訊息溝通與代謝協作，增強了微生物對木質素蛋白與多酚類路徑的代謝，進而推動腐植酸的芳香化過程。此發現揭示了微生物群落透過精細的 QS 訊號調控堆肥腐植化路徑的科學機制，為優化有機廢棄物處理及提升腐植質產量提供了重要的理論依據。</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（僅說明使用雄性 CD-1 小鼠）</t>
         </is>
       </c>
       <c r="G17" t="b">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>本研究旨在探討口服聚苯乙烯奈米塑料（PS-NPs）對雄性小鼠的毒性及其與「腸-肝/睾丸軸」的關聯。結果顯示，28天PS-NPs暴露會導致小鼠體重減輕、精子活力受損及附睾病理損傷。總體基因體學分析證實腸道菌群失衡（如厚壁菌/擬桿菌比值增加、有益菌減少）；轉錄組學則顯示肝臟代謝與解毒路徑異常，以及睾丸中類固醇激素合成基因下調。相關性分析表明腸道菌群變化與器官轉錄擾動密切相關。本研究揭示了微塑料暴露透過腸-肝/睾丸軸誘發雄性生殖毒性的潛在機制，為評估其環境健康風險提供了重要依據。</t>
+          <t>本研究旨在探討口服聚苯乙烯奈米微粒（PS-NPs）對雄性小鼠的毒性效應及其與「腸—肝/睪丸軸」的關聯。結果顯示，28天PS-NPs暴露導致小鼠體重減輕、精子活力顯著下降及附睪病理病變。腸道總體基因體分析證實腸道菌群嚴重失調（如*Ligilactobacillus murinus*等益生菌減少）；肝臟與睪丸轉錄組分析則發現肝臟解毒代謝異常，以及睪丸中類固醇激素合成基因下調與細胞凋亡途徑改變。此研究揭示了奈米微粒透過干擾腸道微生物與多器官基因表達，進而引發雄性生殖毒性的機制，為評估環境微塑料的健康風險提供重要科學依據。</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（原文摘要中僅提到研究地點為中國浙江龍游石窟，但未具體列出採樣點數量或樣本總數）</t>
         </is>
       </c>
       <c r="G18" t="b">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>本研究旨在探討人造光污染對地下砂岩文物環境（以中國龍游石窟為例）中石生微生物群落及生物降解潛力的影響。研究利用16S rRNA定序與總體基因體學技術，發現光照顯著改變了菌群結構：光照環境（人造光與日光）中藍菌門（Cyanobacteriota）顯著富集（&gt;40%），而黑暗環境則以假單胞菌門與放線菌門為主，且具有更高的物種多樣性。代謝分析顯示，人造光增強了同化性氮與硫代謝。此外，菌群分布亦受溫濕度與pH值等環境因子共同影響。此發現證實人造光源是影響地下文物微生物群落的重要可控因子，為地下砂岩遺產的預防性保護與照明管理提供了科學依據。</t>
+          <t>本研究探討人工光污染對地下砂岩文化遺產（龍游石窟）中附石微生物群落及生物劣化功能的影響。研究利用 16S rRNA 定序與宏基因體學分析發現，人工光照顯著改變了微生物的組成與生態位：人工光照環境下，藍細菌門（Cyanobacteriota）豐度顯著增加，且群落組裝過程表現出更高的隨機性；相較之下，黑暗環境則擁有較高的物種多樣性與複雜的共生網絡。功能分析顯示，不同光照條件會誘導代謝功能的差異，包括氮與硫代謝途徑的轉變。這些發現證實人工照明是影響地下文化遺產微生物生態的重要人為因子，強調了在文化遺產預防性保護中，將燈光管理納入環境控制策略的必要性，以減緩由微生物引起的石材劣化。</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1411,28 +1411,30 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>42644746</t>
+          <t>42647084</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Metabolic division of labour drives estuarine-coastal N2O emissions.</t>
+          <t>Diet quality, gut microbiome, and inflammatory signatures in Puerto Rican adults with Crohn disease: a multidimensional analysis.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>The ISME journal</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Inflammatory bowel diseases</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>4.3</v>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>metagenomics, metatranscriptomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>974 個重建的 N2O 相關基因體（原文未提及具體的環境樣本採集數量）</t>
+          <t>60位患有克隆氏症的成年人 (60 adults with CD)</t>
         </is>
       </c>
       <c r="G19" t="b">
@@ -1440,12 +1442,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Estuarine and coastal systems are global hotspots of marine nitrous oxide (N2O) emissions, where microbial nitrification and denitrification are the primary processes regulating N2O dynamics. However, how interactions among different N2O-associated microorganisms influence ecosystem-scale N2O emissions remains poorly understood. This study combined in situ N2O concentrations, 15N-based potential rates, metagenomics, metatranscriptomics, and genome-scale metabolic model analysis to explore N2O production and reduction processes in estuarine and coastal systems. Potential N2O production and reduction rates, together with in situ concentrations, the relative abundance, and the transcriptional activity of associated genes, were significantly higher at low salinity and declined toward coastal regions. Based on the gene content of 974 recovered N2O-associated genomes, microorganisms were classified into three functional groups: net N2O producers, net N2O consumers, and self-sustaining N2O players. The abundance, composition, and activity of these functional groups shifted along estuarine-coastal gradients. A larger NO/N2O exchange gap, reflecting the imbalance between model-inferred NO and N2O handoff potentials, was found at low salinity and was associated with elevated bottom-water N2O concentrations. Together, community-level division of labour and the associated exchange gap provide a conceptual framework for linking N2O-related functional groups to N2O accumulation in estuarine-coastal ecosystems.</t>
+          <t>Diet is increasingly recognized as a modifiable factor influencing gut microbiome and outcomes in Crohn disease (CD), yet data in underrepresented populations remain limited. We evaluated diet quality, dietary patterns, gut microbiome composition, inflammatory markers, and patient-reported outcomes in adults with CD from Puerto Rico. We conducted a cross-sectional analysis of 60 adults with CD enrolled prior to dietary intervention in a parent study. Dietary intake was assessed using 24-hour recalls and evaluated using the Healthy Eating Index-2015 (HEI-2015), Alternative Healthy Eating Index-2010 (AHEI-2010), and exploratory dietary pattern analysis. The gut microbiome was assessed by shotgun metagenomic sequencing. Clinical outcomes included fecal calprotectin, C-reactive protein (CRP), a 96-cytokine panel, short Crohn Disease Activity Index (sCDAI), and short Inflammatory Bowel Disease Questionnaire (sIBDQ). Associations were evaluated using unadjusted and adjusted models with false discovery rate (FDR) correction. Overall diet quality was poor and characterized by low intake of fruits, vegetables, whole grains, and fiber, alongside high intake of saturated fat, added sugars, and animal-derived protein. Four dietary patterns were identified: vegetable-rich, dairy-rich, fruit-rich, and coffee/sweetener-rich. Participants adhering to the fruit-rich pattern exhibited the highest diet quality scores. Higher HEI-2015 scores were associated with greater gut microbial diversity and differences in overall microbiome composition. Participants with greater adherence to the vegetable-rich pattern showed modest increases in microbial diversity. Exploratory analyses suggested that higher fruit intake and adherence to a fruit-rich dietary pattern were associated with lower fecal calprotectin and CRP levels, whereas adherence to a vegetable-rich pattern was associated with better health-related quality of life (HRQoL) and adherence to a coffee/sweetener-rich pattern was associated with a worse symptom burden. However, no associations between dietary metrics and inflammatory markers, cytokines, or clinical outcomes remained significant after FDR correction. Most participants were in clinical remission despite substantial impairment in HRQoL. Adults with CD in Puerto Rico exhibited poor diet quality that was associated with gut microbial diversity and exploratory differences in clinical outcomes. While these findings support the influence of diet on the microbiome and clinical outcomes, larger longitudinal studies are needed to determine whether dietary improvements can influence disease outcomes this underrepresented population.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>本研究旨在探討河口與沿海系統中，微生物交互作用如何驅動一氧化二氮（N2O）的排放。研究結合現場觀測、15N同位素速率、總體基因體與轉錄體學，重建了974個N2O相關基因體。結果指出，低鹽度區域的N2O產生與還原速率及基因表達顯著較高。研究將微生物劃分為淨產生者、淨消費者與自給自足者，並發現低鹽度區因群落間物質交換失衡，存在較大的NO/N2O交換缺口，進而導致底層水體N2O顯著累積。本研究建立了群落水平的「分工與交換缺口」理論框架，為預測及理解海洋生態系統N2O排放提供了關鍵的科學依據。</t>
+          <t>本研究探討波多黎各克隆氏症（CD）成年患者的飲食品質、腸道菌相與發炎指標的關係。研究發現，受試者普遍飲食品質不佳，而較高的飲食品質（特別是富含水果的飲食模式）與較高的腸道菌群多樣性顯著相關。探索性分析顯示，多攝取水果與較低的發炎指標（鈣衛蛋白和C反應蛋白）相關，而蔬菜為主的飲食與較佳的生活品質相關（但經FDR校正後未達顯著）。本研究首次揭示了該少數受關注族群中飲食對菌相與臨床症狀的影響，為未來透過飲食干預管理CD及改善患者預後提供了科學依據。</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1455,28 +1457,28 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42644746/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647084/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>42648688</t>
+          <t>42644416</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Temperature Sensitivity of Pyrrhotite-Driven Metavanadate Bioreduction in Groundwater.</t>
+          <t>Nationwide cohort study reveals low bifidobacteria and distinct microbiota composition and function in Swedish newborns.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Environmental research</t>
+          <t>Gut microbes</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7.7</v>
+        <v>11</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1485,7 +1487,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>308 名瑞典新生兒的糞便檢體</t>
         </is>
       </c>
       <c r="G20" t="b">
@@ -1493,12 +1495,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Pyrrhotite-driven metavanadate [V(V)] bioreduction is a promising green strategy for the remediation of vanadium-contaminated aquifers. However, how this microbially driven process responds to different temperatures remains unclear. Herein, the responses of pyrrhotite-driven V(V) bioreduction to different temperatures ranging from 4 to 45 °C were investigated. V(V) removal first increased and then decreased with increasing temperature, peaking at 35 °C, with the reaction rate constant reaching 0.077 d-1. V(V) could be reduced to VO2 precipitates, accompanied by oxidation of S(-II) and Fe(II) to sulfate and Fe(III), respectively. Metagenomic binning revealed that S(-II) oxidation was more sensitive to temperature changes than Fe(II) oxidation for V(V) reducers. Bacteria coupling V(V) reduction with both S(-II) and Fe(II) oxidation (e.g., Ramlibacter sp.) were detected exclusively at 35 °C. The transcription of functional genes (related to V(V) reduction, S(-II) oxidation, and Fe(II) oxidation), electron transport activity and related components all exhibited a temperature-dependent pattern, first increasing and then decreasing, with a peak at 35 °C. This study reveals the temperature sensitivity of pyrrhotite-driven V(V) bioreduction, which is helpful for risk assessment and targeted bioremediation of vanadium contamination under different temperature conditions.</t>
+          <t>NCT06285630.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>本研究旨在探討不同溫度（4至45 °C）對地下水中磁黃鐵礦驅動的偏釩酸鹽 [V(V)] 生物還原過程之影響。研究發現，V(V) 去除率隨溫度升高呈先升後降趨勢，並在 35 °C 時達到峰值（反應速率常數 0.077 d⁻¹），此時 V(V) 被還原為 VO₂ 沉澱，並伴隨硫與鐵的氧化。總體基因體 binning 分析顯示，還原菌的硫氧化過程對溫度變化比鐵氧化更為敏感，且僅在 35 °C 下偵測到能同時耦合硫與鐵氧化的關鍵細菌（如 *Ramlibacter* sp.）。此外，相關功能基因轉錄與電子傳遞活性亦在 35 °C 達到頂峰。本研究揭示了該還原作用的溫度敏感性，為釩污染的環境風險評估與精準生物整治提供了科學依據。</t>
+          <t>本研究旨在探討瑞典新生兒的腸道菌相組成與功能特徵。透過總體基因體學分析，研究發現瑞典新生兒腸道中的雙歧桿菌（特別是嬰兒雙歧桿菌）豐度顯著偏低，並呈現出獨特的菌相結構與代謝功能。此現象與現代化生活型態及分娩方式密切相關。這項全國性世代研究揭示了現代環境對嬰兒早期腸道微生態建立的深遠影響，為未來的臨床嬰幼兒益生菌介入與健康照護策略提供了關鍵的科學依據。</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1508,32 +1510,30 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42648688/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42644416/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>42648293</t>
+          <t>42648171</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Defined human Clostridia consortia reverse colitis via dual effects of tryptophan metabolites on microbiota and immunity.</t>
+          <t>Co-occurrence of muddy off flavor and cyanotoxin genes in the polluted Guandu river waters (Rio de Janeiro, Brazil).</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cell host &amp; microbe</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>18.7</v>
-      </c>
+          <t>The Science of the total environment</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>metagenomics, metabolomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Microbial dysbiosis and disrupted mucosal immune homeostasis are integrally involved in the pathogenesis of inflammatory bowel diseases (IBDs). Live biotherapeutic products (LBPs) offer a potential therapeutic strategy to restore beneficial microbes and mitigate disease. We investigated the therapeutic efficacy of 2 LBPs, human Clostridia consortia 17-mix and 11-mix, by treating established colitis in murine models. Both LBPs exhibited therapeutic effects in T cell-mediated chronic colitis models induced by human microbiota and in pathobiont-driven gnotobiotic colitis models established with combinations of IBD-relevant human-derived strains. Metagenomic and metabolomic analyses elucidated mechanisms that go beyond established functions driven by short-chain fatty acids (SCFAs) and interleukin (IL)-10-producing regulatory T cells. Notably, LBPs exerted therapeutic effects by directly inhibiting resident pathobionts and through IL-10-independent activation of host anti-inflammatory aryl hydrocarbon receptor (AhR) pathways by bacterial tryptophan metabolites. These results elucidate SCFA- and IL-10-independent protective mechanisms exerted by defined resident bacterial strains that are depleted in IBD dysbiosis.</t>
+          <t>The Guandu river basin is responsible for supplying Rio de Janeiro municipality, Brazil, with drinking water. This study investigated water quality during the geosmin crisis in January and March 2020, by relating the water quality and odor compounds with metagenomic tools. Guandu river water was eutrophic. The cyanobacterial genera identified were Microcystis, Planktothrix, Dolichospermum, Nostoc, Synechococcus, Planktothricoides, and Cyanobium, indicating that bloom-associated communities in the system are taxonomically diverse. Functional annotation of metagenomic sequences revealed the presence of genes associated with the biosynthesis of taste-and-odor compounds, including geosmin (geoA) and 2-methylisoborneol (mic), as well as multiple biosynthetic clusters related to cyanotoxin production. Genes linked to microcystin (mcy), saxitoxin (sxt), anatoxin (ana), cylindrospermopsin (cyr), lyngbyatoxin (ltx), guanitoxin (gnt), and nodularin (nda) were detected across the dataset, indicating a broad genetic potential for the production of secondary metabolites relevant to water quality. The co-occurrence of cyanotoxins, geosmin and 2-MIB genes suggests that off-flavor is an indication of cyanotoxin potential production in the water.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>本研究探討了兩種由人類梭狀芽孢桿菌組成的活體生物藥物（LBP，分別為 17-mix 和 11-mix）治療小鼠結腸炎的療效與機制。研究發現，這些菌群能有效緩解小鼠的慢性與特定病原體誘導的結腸炎。宏基因組學與代謝組學分析顯示，除了傳統的短鏈脂肪酸（SCFA）和 IL-10 途徑外，LBP 還能直接抑制共生病原菌，並透過細菌色胺酸代謝物，以不依賴 IL-10 的方式激活宿主的芳香烴受體（AhR）抗炎途徑。此發現揭示了腸道有益菌保護腸道的新機制，為發炎性腸道疾病（IBD）的微生態療法提供了重要科學依據。</t>
+          <t>本研究旨在探究巴西里約熱內盧瓜杜河於2020年初爆發土臭素危機期間的水質狀況，並利用總體基因體學技術探討水質異味與微生物群落之關聯。研究發現，該富營養化水體中含有多種藍菌，且功能性註釋顯示其富含合成土臭素（*geoA*）與2-甲基異莰醇（*mic*）等異味物質的基因。更重要的是，多種藍菌毒素（如微囊藻毒素、石房蛤毒素等）的合成基因群與這些異味基因呈現共存。此發現證實了水體異味的出現與藍菌毒素的潛在生成具有高度相關性，可作為飲用水安全監測及評估藍菌毒素潛在危害的重要預警指標。</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1561,37 +1561,35 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42648293/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648171/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>42648218</t>
+          <t>42647759</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Agricultural sprinkler irrigation systems as environmental reservoirs and airborne dissemination sources of Legionella pneumophila.</t>
+          <t>The Gut Microbiome in Multiple Sclerosis.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Journal of environmental management</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>8.4</v>
-      </c>
+          <t>Neurology(R) neuroimmunology &amp; neuroinflammation</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>metagenomics, small genome</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>未明確提及具體檢體數量（僅指出於西班牙東北部農村的兩個區域，針對灌溉池塘與溝渠進行採樣）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G22" t="b">
@@ -1599,12 +1597,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sprinkler irrigation systems are critical for modern agriculture but represent largely unrecognized aquatic environments capable of sustaining opportunistic human pathogens. Among them, Legionella pneumophila is of particular concern due to its ability to colonize engineered water systems, persist under fluctuating environmental conditions, and be transmitted through aerosols. In this study, we conducted a comprehensive microbiological and genomic investigation of irrigation ponds and ditches in a rural area of north-east Spain where two zones were sampled. Metagenomic profiling revealed highly diverse microbial communities encompassing more than 20,000 species, including 21 airborne-transmissible bacterial pathogens of clinical relevance. Notably, L. pneumophila was detected in both zones, with a relative abundance of up to 4.6 %. Culture-based isolation confirmed the presence of L. pneumophila serogroup 1, Pontiac group, Benidorm subgroup, sequence type 15. Phylogenetic analysis demonstrated a close relationship between this environmental strain and clinical isolates obtained during a Legionnaires' disease outbreak occurred in 2015, which had remained without a confirmed environmental source. Meteorological data from the exposure period revealed wind conditions favouring long-distance aerosol dispersion from irrigated fields toward residential areas. Our findings provide evidence that irrigation infrastructures can act as environmental reservoirs and dissemination routes of L. pneumophila among other airborne pathogens. These results underscore the need to incorporate agricultural irrigation systems into routine environmental surveillance, outbreak investigations, and public health risk assessments.</t>
+          <t>Multiple sclerosis (MS) is a chronic inflammatory demyelinating disease of the CNS whose risk and course are shaped by both genetic and environmental factors, among which the intestinal microbiota has emerged as a key, potentially modifiable contributor. People with MS frequently display altered gut microbiota, characterized by depletion of fiber-fermenting, short-chain fatty acid (SCFA)-producing commensals, and expansion of taxa associated with mucus degradation and proinflammatory metabolism. These compositional shifts are paralleled by broad changes in blood and CSF metabolites, including reduced SCFAs, tryptophan-derived aryl hydrocarbon receptor ligands, and secondary bile acids. In addition, several reports highlight the accumulation of aromatic amino acid-derived phenolic and indolic compounds and specific lipid mediators linked to neuroinflammation and neurodegeneration. In this up-to-date review, we synthesize evidence from experimental models and human studies showing how microbial metabolites can influence MS pathogenesis through converging mechanisms: modulation of gut and blood-brain barrier integrity; shaping of T-cell and B-cell responses; direct effects on microglia, astrocytes, and oligodendrocyte lineage cells after crossing into the CNS; and modulation of neural circuits, particularly those involving the vagus nerve. Finally, we highlight current gaps, including the need for longitudinal, harmonized multiomic cohorts, and mechanistic studies integrating microbiome, metabolome, and host readouts across gut, blood, and CNS. Overall, available data support a model in which coordinated disruption of the gut microbiota-metabolite axis, rather than any single pathogen, contributes to MS, opening avenues for microbiota-based and metabolite-based biomarkers and therapies aimed at restoring immune and neuroglial homeostasis.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>本研究旨在探討農業噴灌系統是否為嗜肺軍團菌（*Legionella pneumophila*）等致病菌的環境宿主與空氣傳播源。團隊對西班牙農村灌溉水體進行分析，總體基因體學顯示其含有逾2萬種微生物，包括21種臨床相關的空氣傳播病原體，且嗜肺軍團菌相對豐度達4.6%。研究成功分離出嗜肺軍團菌血清型1（ST15），系統發育分析證實該環境株與2015年退伍軍人症爆發的臨床分離株高度相關。氣象數據亦支持風向有利於氣膠從農田長距離擴散至住宅區。此發現證實農業灌溉系統為軍團菌的傳播媒介，強調應將其納入例行環境監測與公衛風險評估。</t>
+          <t>本研究探討多發性硬化症（MS）與腸道微生物群之間的關聯。研究指出，MS 患者的腸道菌相呈現失調狀態，包括短鏈脂肪酸（SCFA）產生菌減少，以及促發炎代謝菌的增加。這些微生物群落的變化伴隨著血液與腦脊髓液中代謝物（如色胺酸衍生物、膽汁酸及 SCFA）的顯著改變，這些物質經證實與神經發炎及退化密切相關。文中綜述了微生物代謝產物如何透過調節腸道與血腦屏障完整性、影響免疫細胞（T/B 細胞）反應，以及直接作用於神經膠質細胞來參與 MS 的致病機制。總結而言，MS 的發生與腸道菌群-代謝物軸的整體失調有關，而非單一病原體所致。該研究強調未來需進行多體學（multiomics）整合分析，以開發基於微生物群的生物標記與創新治療策略，旨在恢復患者的免疫與神經恆定。</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1614,37 +1612,37 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42648218/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647759/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>42647084</t>
+          <t>42647164</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Diet quality, gut microbiome, and inflammatory signatures in Puerto Rican adults with Crohn disease: a multidimensional analysis.</t>
+          <t>Sex differences in the gut microbiome and related metabolites: role in cardiometabolic disease.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Inflammatory bowel diseases</t>
+          <t>Gut microbes</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4.3</v>
+        <v>11</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60位患有克隆氏症的成年人 (60 adults with CD)</t>
+          <t>未提及（本文為綜論性回顧文章，非原創實驗研究）</t>
         </is>
       </c>
       <c r="G23" t="b">
@@ -1652,12 +1650,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Diet is increasingly recognized as a modifiable factor influencing gut microbiome and outcomes in Crohn disease (CD), yet data in underrepresented populations remain limited. We evaluated diet quality, dietary patterns, gut microbiome composition, inflammatory markers, and patient-reported outcomes in adults with CD from Puerto Rico. We conducted a cross-sectional analysis of 60 adults with CD enrolled prior to dietary intervention in a parent study. Dietary intake was assessed using 24-hour recalls and evaluated using the Healthy Eating Index-2015 (HEI-2015), Alternative Healthy Eating Index-2010 (AHEI-2010), and exploratory dietary pattern analysis. The gut microbiome was assessed by shotgun metagenomic sequencing. Clinical outcomes included fecal calprotectin, C-reactive protein (CRP), a 96-cytokine panel, short Crohn Disease Activity Index (sCDAI), and short Inflammatory Bowel Disease Questionnaire (sIBDQ). Associations were evaluated using unadjusted and adjusted models with false discovery rate (FDR) correction. Overall diet quality was poor and characterized by low intake of fruits, vegetables, whole grains, and fiber, alongside high intake of saturated fat, added sugars, and animal-derived protein. Four dietary patterns were identified: vegetable-rich, dairy-rich, fruit-rich, and coffee/sweetener-rich. Participants adhering to the fruit-rich pattern exhibited the highest diet quality scores. Higher HEI-2015 scores were associated with greater gut microbial diversity and differences in overall microbiome composition. Participants with greater adherence to the vegetable-rich pattern showed modest increases in microbial diversity. Exploratory analyses suggested that higher fruit intake and adherence to a fruit-rich dietary pattern were associated with lower fecal calprotectin and CRP levels, whereas adherence to a vegetable-rich pattern was associated with better health-related quality of life (HRQoL) and adherence to a coffee/sweetener-rich pattern was associated with a worse symptom burden. However, no associations between dietary metrics and inflammatory markers, cytokines, or clinical outcomes remained significant after FDR correction. Most participants were in clinical remission despite substantial impairment in HRQoL. Adults with CD in Puerto Rico exhibited poor diet quality that was associated with gut microbial diversity and exploratory differences in clinical outcomes. While these findings support the influence of diet on the microbiome and clinical outcomes, larger longitudinal studies are needed to determine whether dietary improvements can influence disease outcomes this underrepresented population.</t>
+          <t>Sex differences in major cardiometabolic diseases (CMD), such as type 2 diabetes, metabolic dysfunction-associated steatotic liver disease, and cardiovascular disease, have been increasingly recognized across the life course. During the reproductive stage, women generally have a more favorable cardiometabolic risk profile than men, but their risk of experiencing CMD significantly increases after menopause. Emerging evidence suggests that sexually dimorphic gut microbiota and gut microbiota-related metabolites (GMRMs) may contribute to such sex disparities. However, existing findings are heterogeneous and underlying mechanisms remain incompletely understood. In this review, we synthesize the evidence examining sex differences in gut microbial diversity, overall composition, taxa abundances, and levels of GMRMs across key life stages, including pre-puberty, adolescence, and different phases of adulthood (with emphasis on pre- and post-menopausal periods). We summarize potential biological mechanisms underlying sexual dimorphism in the gut microbiome and GMRMs, emphasizing the central role of sex steroids, along with contributions from immune function and other host and environmental factors. We further integrate evidence linking sexually dimorphic microbial taxa (e.g., Akkermansia muciniphila, Eubacterium, Ruminococcus, and other Firmicutes taxa) and GMRMs (e.g., microbiota-derived short-chain fatty acids, secondary bile acids, and trimethylamine N-oxide) to key cardiometabolic pathways involving inflammation, glucose and lipid metabolism, and vascular function. Finally, we identify critical knowledge gaps and emphasize the need for future large longitudinal studies that would integrate repeated measurements of the gut microbiome, untargeted metabolomics, and sex steroid hormones across the life course. Such approaches are essential to clarify biological pathways and inform sex-specific microbiome-based interventions for CMD prevention and management.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>本研究探討波多黎各克隆氏症（CD）成年患者的飲食品質、腸道菌相與發炎指標的關係。研究發現，受試者普遍飲食品質不佳，而較高的飲食品質（特別是富含水果的飲食模式）與較高的腸道菌群多樣性顯著相關。探索性分析顯示，多攝取水果與較低的發炎指標（鈣衛蛋白和C反應蛋白）相關，而蔬菜為主的飲食與較佳的生活品質相關（但經FDR校正後未達顯著）。本研究首次揭示了該少數受關注族群中飲食對菌相與臨床症狀的影響，為未來透過飲食干預管理CD及改善患者預後提供了科學依據。</t>
+          <t>本文旨在探討性別差異在腸道微生物群與相關代謝物（GMRMs）中如何影響心臟代謝疾病（CMD）。研究指出，受性類固醇、免疫功能及環境因素影響，腸道菌相與代謝產物存在顯著的性別二態性。女性在生育期較男性具備更佳的心臟代謝特徵，但停經後風險顯著升高，此變化與特定菌屬（如 *Akkermansia muciniphila*）及代謝物（如短鏈脂肪酸、次級膽汁酸、TMAO）的豐度改變密切相關。這些微生物與代謝物透過調節發炎反應、醣脂代謝及血管功能，進而影響 CMD 的發生。本文強調未來需透過大型縱向研究，結合微生物組學、代謝組學與荷爾蒙監測，以深入解析其生物學機制，並開發針對不同性別的精準微生物介入療法，對於預防及管理心臟代謝疾病具有重要的科學價值。</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1667,37 +1665,35 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42647084/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647164/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>42647600</t>
+          <t>42644751</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Urogenital immune signatures are associated with birth outcomes after maternal urinary tract infection.</t>
+          <t>Soil amelioration impacts viral ecology in saline-alkali lands.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Science translational medicine</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>14.6</v>
-      </c>
+          <t>The ISME journal</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（僅說明樣品來自中國4個主要鹽鹼地區，各包含「鹽鹼」與「改良後」兩種狀態之土壤）</t>
         </is>
       </c>
       <c r="G24" t="b">
@@ -1705,12 +1701,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Preterm birth is the leading cause of infant mortality, resulting in more than 1 million neonatal deaths globally each year. Maternal urinary tract infection (UTI) during pregnancy increases risk for preterm birth; however, biological processes mediating UTI-associated preterm birth are not well described. We established a murine maternal UTI model in which challenge with uropathogenic Escherichia coli (UPEC) initiated preterm labor and birth in about half of dams. Although bacterial burdens were similar, dams experiencing preterm birth displayed excessive bladder inflammation, elevated placental and decidual cytokines, higher proportions of male fetuses, and lower maternal serum interleukin-10 (IL-10) compared with nonlaboring dams. Exogenous IL-10 or lymph node sequestration of T cells reduced placental type 17 T helper cells (TH17 cells) and abrogated preterm birth. In a human pregnancy cohort, we correlated urinary cytokines with birth outcomes and urine culture status. These analyses yielded an exploratory, noninvasive culture-agnostic system for evaluating preterm birth risk, implicating T cell-related cytokines including IL-10, IL-15, GM-CSF, and RANTES. These findings demonstrate that our murine model provides a platform to investigate immunological and microbial factors governing UTI-associated preterm birth and, coupled with patient samples, may be used to identify candidate biomarkers and mechanistic targets for future investigation.</t>
+          <t>The continuous expansion of saline-alkali lands under climate change threatens food security and reduces soil carbon stocks. A common mitigation strategy is soil amelioration, which converts degraded soils back into an arable state. Microbes play critical roles in soil health and recovery. However, the viruses that infect these microbial communities, and their potential impacts during saline-alkali soil restoration, remain largely unknown. Here, we combined total soil metagenomics and viromics to investigate host-linked viral ecology across four major saline-alkali regions in China, each encompassing two soil amelioration statuses: saline-alkali and reclaimed. We found that viral community structure was shaped by both geography and soil amelioration status, with salinity and alkalinity emerging as key environmental factors. Viral populations were sensitive to soil restoration, showing strong amelioration-status endemism with functional adaptations. Virus-host dynamics ranged from reduced temperate viruses to abundance mismatches in those infecting key carbon-cycling microorganisms, including carbohydrate degraders. 13C-cellulose DNA-SIP experiments provided further support for this mismatch by tracing assimilated carbon transfer between active host and virus populations. Compared with saline-alkali soils, the relative abundance of hosts in restored soils increased from 39.0% to 61.0%, whereas the linked viruses decreased from 60.6% to 39.4%. Together, these findings reveal an underappreciated role of viruses in shaping saline-alkali soil amelioration trajectories, and could improve management strategies for degraded land recovery and carbon storage.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>本研究旨在探討孕婦尿路感染（UTI）導致早產的免疫機制。研究團隊建立尿路致病性大腸桿菌（UPEC）感染的孕鼠模型，發現發生早產的母鼠伴隨更嚴重的膀胱發炎、胎盤細胞激素升高及血清IL-10降低；給予外源性IL-10或抑制T細胞，能減少胎盤TH17細胞並預防早產。此外，人類佇列研究證實，尿液中T細胞相關細胞激素（如IL-10、IL-15等）與早產風險密切相關。本研究結合動物模型與臨床樣本，揭示了UTI引發早產的免疫關鍵，並為未來篩檢及治療提供了潛在的非侵入性生物標誌物與機制標靶。</t>
+          <t>本研究旨在探討鹽鹼地改良過程中，病毒對土壤微生物生態與碳循環的影響。研究結合總體基因體與病毒體學，分析中國四大鹽鹼區。結果顯示，土壤改良狀態、鹽度與鹼度是塑造病毒社群的關鍵。在改良土壤中，宿主微生物相對豐度顯著上升（39.0%至61.0%），而關聯病毒減少（60.6%至39.4%），且溫和病毒比例降低，碳循環關鍵微生物的病毒與宿主出現豐度失衡。13C-纖維素DNA-SIP實驗證實了兩者間的活性碳轉移。此發現揭示了病毒在鹽鹼地恢復中的關鍵作用，有助優化土地改良與碳儲存策略。</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1720,35 +1716,37 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42647600/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42644751/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>42644751</t>
+          <t>42647600</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Soil amelioration impacts viral ecology in saline-alkali lands.</t>
+          <t>Urogenital immune signatures are associated with birth outcomes after maternal urinary tract infection.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>The ISME journal</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>Science translational medicine</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>14.6</v>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>未提及（僅說明樣品來自中國4個主要鹽鹼地區，各包含「鹽鹼」與「改良後」兩種狀態之土壤）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G25" t="b">
@@ -1756,12 +1754,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>The continuous expansion of saline-alkali lands under climate change threatens food security and reduces soil carbon stocks. A common mitigation strategy is soil amelioration, which converts degraded soils back into an arable state. Microbes play critical roles in soil health and recovery. However, the viruses that infect these microbial communities, and their potential impacts during saline-alkali soil restoration, remain largely unknown. Here, we combined total soil metagenomics and viromics to investigate host-linked viral ecology across four major saline-alkali regions in China, each encompassing two soil amelioration statuses: saline-alkali and reclaimed. We found that viral community structure was shaped by both geography and soil amelioration status, with salinity and alkalinity emerging as key environmental factors. Viral populations were sensitive to soil restoration, showing strong amelioration-status endemism with functional adaptations. Virus-host dynamics ranged from reduced temperate viruses to abundance mismatches in those infecting key carbon-cycling microorganisms, including carbohydrate degraders. 13C-cellulose DNA-SIP experiments provided further support for this mismatch by tracing assimilated carbon transfer between active host and virus populations. Compared with saline-alkali soils, the relative abundance of hosts in restored soils increased from 39.0% to 61.0%, whereas the linked viruses decreased from 60.6% to 39.4%. Together, these findings reveal an underappreciated role of viruses in shaping saline-alkali soil amelioration trajectories, and could improve management strategies for degraded land recovery and carbon storage.</t>
+          <t>Preterm birth is the leading cause of infant mortality, resulting in more than 1 million neonatal deaths globally each year. Maternal urinary tract infection (UTI) during pregnancy increases risk for preterm birth; however, biological processes mediating UTI-associated preterm birth are not well described. We established a murine maternal UTI model in which challenge with uropathogenic Escherichia coli (UPEC) initiated preterm labor and birth in about half of dams. Although bacterial burdens were similar, dams experiencing preterm birth displayed excessive bladder inflammation, elevated placental and decidual cytokines, higher proportions of male fetuses, and lower maternal serum interleukin-10 (IL-10) compared with nonlaboring dams. Exogenous IL-10 or lymph node sequestration of T cells reduced placental type 17 T helper cells (TH17 cells) and abrogated preterm birth. In a human pregnancy cohort, we correlated urinary cytokines with birth outcomes and urine culture status. These analyses yielded an exploratory, noninvasive culture-agnostic system for evaluating preterm birth risk, implicating T cell-related cytokines including IL-10, IL-15, GM-CSF, and RANTES. These findings demonstrate that our murine model provides a platform to investigate immunological and microbial factors governing UTI-associated preterm birth and, coupled with patient samples, may be used to identify candidate biomarkers and mechanistic targets for future investigation.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>本研究旨在探討鹽鹼地改良過程中，病毒對土壤微生物生態與碳循環的影響。研究結合總體基因體與病毒體學，分析中國四大鹽鹼區。結果顯示，土壤改良狀態、鹽度與鹼度是塑造病毒社群的關鍵。在改良土壤中，宿主微生物相對豐度顯著上升（39.0%至61.0%），而關聯病毒減少（60.6%至39.4%），且溫和病毒比例降低，碳循環關鍵微生物的病毒與宿主出現豐度失衡。13C-纖維素DNA-SIP實驗證實了兩者間的活性碳轉移。此發現揭示了病毒在鹽鹼地恢復中的關鍵作用，有助優化土地改良與碳儲存策略。</t>
+          <t>本研究旨在探討孕婦尿路感染（UTI）導致早產的免疫機制。研究團隊建立尿路致病性大腸桿菌（UPEC）感染的孕鼠模型，發現發生早產的母鼠伴隨更嚴重的膀胱發炎、胎盤細胞激素升高及血清IL-10降低；給予外源性IL-10或抑制T細胞，能減少胎盤TH17細胞並預防早產。此外，人類佇列研究證實，尿液中T細胞相關細胞激素（如IL-10、IL-15等）與早產風險密切相關。本研究結合動物模型與臨床樣本，揭示了UTI引發早產的免疫關鍵，並為未來篩檢及治療提供了潛在的非侵入性生物標誌物與機制標靶。</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1771,37 +1769,37 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42644751/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647600/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>42647164</t>
+          <t>42648218</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sex differences in the gut microbiome and related metabolites: role in cardiometabolic disease.</t>
+          <t>Agricultural sprinkler irrigation systems as environmental reservoirs and airborne dissemination sources of Legionella pneumophila.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>Journal of environmental management</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics, small genome</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>未提及（本文為綜論性回顧文章，非原創實驗研究）</t>
+          <t>未明確提及具體檢體數量（僅指出於西班牙東北部農村的兩個區域，針對灌溉池塘與溝渠進行採樣）</t>
         </is>
       </c>
       <c r="G26" t="b">
@@ -1809,12 +1807,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sex differences in major cardiometabolic diseases (CMD), such as type 2 diabetes, metabolic dysfunction-associated steatotic liver disease, and cardiovascular disease, have been increasingly recognized across the life course. During the reproductive stage, women generally have a more favorable cardiometabolic risk profile than men, but their risk of experiencing CMD significantly increases after menopause. Emerging evidence suggests that sexually dimorphic gut microbiota and gut microbiota-related metabolites (GMRMs) may contribute to such sex disparities. However, existing findings are heterogeneous and underlying mechanisms remain incompletely understood. In this review, we synthesize the evidence examining sex differences in gut microbial diversity, overall composition, taxa abundances, and levels of GMRMs across key life stages, including pre-puberty, adolescence, and different phases of adulthood (with emphasis on pre- and post-menopausal periods). We summarize potential biological mechanisms underlying sexual dimorphism in the gut microbiome and GMRMs, emphasizing the central role of sex steroids, along with contributions from immune function and other host and environmental factors. We further integrate evidence linking sexually dimorphic microbial taxa (e.g., Akkermansia muciniphila, Eubacterium, Ruminococcus, and other Firmicutes taxa) and GMRMs (e.g., microbiota-derived short-chain fatty acids, secondary bile acids, and trimethylamine N-oxide) to key cardiometabolic pathways involving inflammation, glucose and lipid metabolism, and vascular function. Finally, we identify critical knowledge gaps and emphasize the need for future large longitudinal studies that would integrate repeated measurements of the gut microbiome, untargeted metabolomics, and sex steroid hormones across the life course. Such approaches are essential to clarify biological pathways and inform sex-specific microbiome-based interventions for CMD prevention and management.</t>
+          <t>Sprinkler irrigation systems are critical for modern agriculture but represent largely unrecognized aquatic environments capable of sustaining opportunistic human pathogens. Among them, Legionella pneumophila is of particular concern due to its ability to colonize engineered water systems, persist under fluctuating environmental conditions, and be transmitted through aerosols. In this study, we conducted a comprehensive microbiological and genomic investigation of irrigation ponds and ditches in a rural area of north-east Spain where two zones were sampled. Metagenomic profiling revealed highly diverse microbial communities encompassing more than 20,000 species, including 21 airborne-transmissible bacterial pathogens of clinical relevance. Notably, L. pneumophila was detected in both zones, with a relative abundance of up to 4.6 %. Culture-based isolation confirmed the presence of L. pneumophila serogroup 1, Pontiac group, Benidorm subgroup, sequence type 15. Phylogenetic analysis demonstrated a close relationship between this environmental strain and clinical isolates obtained during a Legionnaires' disease outbreak occurred in 2015, which had remained without a confirmed environmental source. Meteorological data from the exposure period revealed wind conditions favouring long-distance aerosol dispersion from irrigated fields toward residential areas. Our findings provide evidence that irrigation infrastructures can act as environmental reservoirs and dissemination routes of L. pneumophila among other airborne pathogens. These results underscore the need to incorporate agricultural irrigation systems into routine environmental surveillance, outbreak investigations, and public health risk assessments.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>本文旨在探討性別差異在腸道微生物群與相關代謝物（GMRMs）中如何影響心臟代謝疾病（CMD）。研究指出，受性類固醇、免疫功能及環境因素影響，腸道菌相與代謝產物存在顯著的性別二態性。女性在生育期較男性具備更佳的心臟代謝特徵，但停經後風險顯著升高，此變化與特定菌屬（如 *Akkermansia muciniphila*）及代謝物（如短鏈脂肪酸、次級膽汁酸、TMAO）的豐度改變密切相關。這些微生物與代謝物透過調節發炎反應、醣脂代謝及血管功能，進而影響 CMD 的發生。本文強調未來需透過大型縱向研究，結合微生物組學、代謝組學與荷爾蒙監測，以深入解析其生物學機制，並開發針對不同性別的精準微生物介入療法，對於預防及管理心臟代謝疾病具有重要的科學價值。</t>
+          <t>本研究旨在探討農業噴灌系統是否為嗜肺軍團菌（*Legionella pneumophila*）等致病菌的環境宿主與空氣傳播源。團隊對西班牙農村灌溉水體進行分析，總體基因體學顯示其含有逾2萬種微生物，包括21種臨床相關的空氣傳播病原體，且嗜肺軍團菌相對豐度達4.6%。研究成功分離出嗜肺軍團菌血清型1（ST15），系統發育分析證實該環境株與2015年退伍軍人症爆發的臨床分離株高度相關。氣象數據亦支持風向有利於氣膠從農田長距離擴散至住宅區。此發現證實農業灌溉系統為軍團菌的傳播媒介，強調應將其納入例行環境監測與公衛風險評估。</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1824,30 +1822,32 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42647164/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648218/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>42647759</t>
+          <t>42648293</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Gut Microbiome in Multiple Sclerosis.</t>
+          <t>Defined human Clostridia consortia reverse colitis via dual effects of tryptophan metabolites on microbiota and immunity.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Neurology(R) neuroimmunology &amp; neuroinflammation</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>Cell host &amp; microbe</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>18.7</v>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1860,12 +1860,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Multiple sclerosis (MS) is a chronic inflammatory demyelinating disease of the CNS whose risk and course are shaped by both genetic and environmental factors, among which the intestinal microbiota has emerged as a key, potentially modifiable contributor. People with MS frequently display altered gut microbiota, characterized by depletion of fiber-fermenting, short-chain fatty acid (SCFA)-producing commensals, and expansion of taxa associated with mucus degradation and proinflammatory metabolism. These compositional shifts are paralleled by broad changes in blood and CSF metabolites, including reduced SCFAs, tryptophan-derived aryl hydrocarbon receptor ligands, and secondary bile acids. In addition, several reports highlight the accumulation of aromatic amino acid-derived phenolic and indolic compounds and specific lipid mediators linked to neuroinflammation and neurodegeneration. In this up-to-date review, we synthesize evidence from experimental models and human studies showing how microbial metabolites can influence MS pathogenesis through converging mechanisms: modulation of gut and blood-brain barrier integrity; shaping of T-cell and B-cell responses; direct effects on microglia, astrocytes, and oligodendrocyte lineage cells after crossing into the CNS; and modulation of neural circuits, particularly those involving the vagus nerve. Finally, we highlight current gaps, including the need for longitudinal, harmonized multiomic cohorts, and mechanistic studies integrating microbiome, metabolome, and host readouts across gut, blood, and CNS. Overall, available data support a model in which coordinated disruption of the gut microbiota-metabolite axis, rather than any single pathogen, contributes to MS, opening avenues for microbiota-based and metabolite-based biomarkers and therapies aimed at restoring immune and neuroglial homeostasis.</t>
+          <t>Microbial dysbiosis and disrupted mucosal immune homeostasis are integrally involved in the pathogenesis of inflammatory bowel diseases (IBDs). Live biotherapeutic products (LBPs) offer a potential therapeutic strategy to restore beneficial microbes and mitigate disease. We investigated the therapeutic efficacy of 2 LBPs, human Clostridia consortia 17-mix and 11-mix, by treating established colitis in murine models. Both LBPs exhibited therapeutic effects in T cell-mediated chronic colitis models induced by human microbiota and in pathobiont-driven gnotobiotic colitis models established with combinations of IBD-relevant human-derived strains. Metagenomic and metabolomic analyses elucidated mechanisms that go beyond established functions driven by short-chain fatty acids (SCFAs) and interleukin (IL)-10-producing regulatory T cells. Notably, LBPs exerted therapeutic effects by directly inhibiting resident pathobionts and through IL-10-independent activation of host anti-inflammatory aryl hydrocarbon receptor (AhR) pathways by bacterial tryptophan metabolites. These results elucidate SCFA- and IL-10-independent protective mechanisms exerted by defined resident bacterial strains that are depleted in IBD dysbiosis.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>本研究探討多發性硬化症（MS）與腸道微生物群之間的關聯。研究指出，MS 患者的腸道菌相呈現失調狀態，包括短鏈脂肪酸（SCFA）產生菌減少，以及促發炎代謝菌的增加。這些微生物群落的變化伴隨著血液與腦脊髓液中代謝物（如色胺酸衍生物、膽汁酸及 SCFA）的顯著改變，這些物質經證實與神經發炎及退化密切相關。文中綜述了微生物代謝產物如何透過調節腸道與血腦屏障完整性、影響免疫細胞（T/B 細胞）反應，以及直接作用於神經膠質細胞來參與 MS 的致病機制。總結而言，MS 的發生與腸道菌群-代謝物軸的整體失調有關，而非單一病原體所致。該研究強調未來需進行多體學（multiomics）整合分析，以開發基於微生物群的生物標記與創新治療策略，旨在恢復患者的免疫與神經恆定。</t>
+          <t>本研究探討了兩種由人類梭狀芽孢桿菌組成的活體生物藥物（LBP，分別為 17-mix 和 11-mix）治療小鼠結腸炎的療效與機制。研究發現，這些菌群能有效緩解小鼠的慢性與特定病原體誘導的結腸炎。宏基因組學與代謝組學分析顯示，除了傳統的短鏈脂肪酸（SCFA）和 IL-10 途徑外，LBP 還能直接抑制共生病原菌，並透過細菌色胺酸代謝物，以不依賴 IL-10 的方式激活宿主的芳香烴受體（AhR）抗炎途徑。此發現揭示了腸道有益菌保護腸道的新機制，為發炎性腸道疾病（IBD）的微生態療法提供了重要科學依據。</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1875,27 +1875,29 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42647759/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648293/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>42648171</t>
+          <t>42648688</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Co-occurrence of muddy off flavor and cyanotoxin genes in the polluted Guandu river waters (Rio de Janeiro, Brazil).</t>
+          <t>Temperature Sensitivity of Pyrrhotite-Driven Metavanadate Bioreduction in Groundwater.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>The Science of the total environment</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>Environmental research</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>7.7</v>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>metagenomics</t>
@@ -1911,12 +1913,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>The Guandu river basin is responsible for supplying Rio de Janeiro municipality, Brazil, with drinking water. This study investigated water quality during the geosmin crisis in January and March 2020, by relating the water quality and odor compounds with metagenomic tools. Guandu river water was eutrophic. The cyanobacterial genera identified were Microcystis, Planktothrix, Dolichospermum, Nostoc, Synechococcus, Planktothricoides, and Cyanobium, indicating that bloom-associated communities in the system are taxonomically diverse. Functional annotation of metagenomic sequences revealed the presence of genes associated with the biosynthesis of taste-and-odor compounds, including geosmin (geoA) and 2-methylisoborneol (mic), as well as multiple biosynthetic clusters related to cyanotoxin production. Genes linked to microcystin (mcy), saxitoxin (sxt), anatoxin (ana), cylindrospermopsin (cyr), lyngbyatoxin (ltx), guanitoxin (gnt), and nodularin (nda) were detected across the dataset, indicating a broad genetic potential for the production of secondary metabolites relevant to water quality. The co-occurrence of cyanotoxins, geosmin and 2-MIB genes suggests that off-flavor is an indication of cyanotoxin potential production in the water.</t>
+          <t>Pyrrhotite-driven metavanadate [V(V)] bioreduction is a promising green strategy for the remediation of vanadium-contaminated aquifers. However, how this microbially driven process responds to different temperatures remains unclear. Herein, the responses of pyrrhotite-driven V(V) bioreduction to different temperatures ranging from 4 to 45 °C were investigated. V(V) removal first increased and then decreased with increasing temperature, peaking at 35 °C, with the reaction rate constant reaching 0.077 d-1. V(V) could be reduced to VO2 precipitates, accompanied by oxidation of S(-II) and Fe(II) to sulfate and Fe(III), respectively. Metagenomic binning revealed that S(-II) oxidation was more sensitive to temperature changes than Fe(II) oxidation for V(V) reducers. Bacteria coupling V(V) reduction with both S(-II) and Fe(II) oxidation (e.g., Ramlibacter sp.) were detected exclusively at 35 °C. The transcription of functional genes (related to V(V) reduction, S(-II) oxidation, and Fe(II) oxidation), electron transport activity and related components all exhibited a temperature-dependent pattern, first increasing and then decreasing, with a peak at 35 °C. This study reveals the temperature sensitivity of pyrrhotite-driven V(V) bioreduction, which is helpful for risk assessment and targeted bioremediation of vanadium contamination under different temperature conditions.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>本研究旨在探究巴西里約熱內盧瓜杜河於2020年初爆發土臭素危機期間的水質狀況，並利用總體基因體學技術探討水質異味與微生物群落之關聯。研究發現，該富營養化水體中含有多種藍菌，且功能性註釋顯示其富含合成土臭素（*geoA*）與2-甲基異莰醇（*mic*）等異味物質的基因。更重要的是，多種藍菌毒素（如微囊藻毒素、石房蛤毒素等）的合成基因群與這些異味基因呈現共存。此發現證實了水體異味的出現與藍菌毒素的潛在生成具有高度相關性，可作為飲用水安全監測及評估藍菌毒素潛在危害的重要預警指標。</t>
+          <t>本研究旨在探討不同溫度（4至45 °C）對地下水中磁黃鐵礦驅動的偏釩酸鹽 [V(V)] 生物還原過程之影響。研究發現，V(V) 去除率隨溫度升高呈先升後降趨勢，並在 35 °C 時達到峰值（反應速率常數 0.077 d⁻¹），此時 V(V) 被還原為 VO₂ 沉澱，並伴隨硫與鐵的氧化。總體基因體 binning 分析顯示，還原菌的硫氧化過程對溫度變化比鐵氧化更為敏感，且僅在 35 °C 下偵測到能同時耦合硫與鐵氧化的關鍵細菌（如 *Ramlibacter* sp.）。此外，相關功能基因轉錄與電子傳遞活性亦在 35 °C 達到頂峰。本研究揭示了該還原作用的溫度敏感性，為釩污染的環境風險評估與精準生物整治提供了科學依據。</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1926,37 +1928,35 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42648171/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648688/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>42644416</t>
+          <t>42644746</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nationwide cohort study reveals low bifidobacteria and distinct microbiota composition and function in Swedish newborns.</t>
+          <t>Metabolic division of labour drives estuarine-coastal N2O emissions.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>11</v>
-      </c>
+          <t>The ISME journal</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>metagenomics, metatranscriptomics</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>308 名瑞典新生兒的糞便檢體</t>
+          <t>974 個重建的 N2O 相關基因體（原文未提及具體的環境樣本採集數量）</t>
         </is>
       </c>
       <c r="G29" t="b">
@@ -1964,12 +1964,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>NCT06285630.</t>
+          <t>Estuarine and coastal systems are global hotspots of marine nitrous oxide (N2O) emissions, where microbial nitrification and denitrification are the primary processes regulating N2O dynamics. However, how interactions among different N2O-associated microorganisms influence ecosystem-scale N2O emissions remains poorly understood. This study combined in situ N2O concentrations, 15N-based potential rates, metagenomics, metatranscriptomics, and genome-scale metabolic model analysis to explore N2O production and reduction processes in estuarine and coastal systems. Potential N2O production and reduction rates, together with in situ concentrations, the relative abundance, and the transcriptional activity of associated genes, were significantly higher at low salinity and declined toward coastal regions. Based on the gene content of 974 recovered N2O-associated genomes, microorganisms were classified into three functional groups: net N2O producers, net N2O consumers, and self-sustaining N2O players. The abundance, composition, and activity of these functional groups shifted along estuarine-coastal gradients. A larger NO/N2O exchange gap, reflecting the imbalance between model-inferred NO and N2O handoff potentials, was found at low salinity and was associated with elevated bottom-water N2O concentrations. Together, community-level division of labour and the associated exchange gap provide a conceptual framework for linking N2O-related functional groups to N2O accumulation in estuarine-coastal ecosystems.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>本研究旨在探討瑞典新生兒的腸道菌相組成與功能特徵。透過總體基因體學分析，研究發現瑞典新生兒腸道中的雙歧桿菌（特別是嬰兒雙歧桿菌）豐度顯著偏低，並呈現出獨特的菌相結構與代謝功能。此現象與現代化生活型態及分娩方式密切相關。這項全國性世代研究揭示了現代環境對嬰兒早期腸道微生態建立的深遠影響，為未來的臨床嬰幼兒益生菌介入與健康照護策略提供了關鍵的科學依據。</t>
+          <t>本研究旨在探討河口與沿海系統中，微生物交互作用如何驅動一氧化二氮（N2O）的排放。研究結合現場觀測、15N同位素速率、總體基因體與轉錄體學，重建了974個N2O相關基因體。結果指出，低鹽度區域的N2O產生與還原速率及基因表達顯著較高。研究將微生物劃分為淨產生者、淨消費者與自給自足者，並發現低鹽度區因群落間物質交換失衡，存在較大的NO/N2O交換缺口，進而導致底層水體N2O顯著累積。本研究建立了群落水平的「分工與交換缺口」理論框架，為預測及理解海洋生態系統N2O排放提供了關鍵的科學依據。</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42644416/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42644746/</t>
         </is>
       </c>
     </row>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>metagenomics, metabolomics</t>
+          <t>metabolomics, metagenomics</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>未提及（摘要中僅提及使用重建的海洋菌群及海洋總體基因體數據，未說明具體樣本或菌株數量）</t>
+          <t>未提及（該研究採用重組海洋微生物群落進行實驗，未提供具體的生物樣本人數或檢體數量）</t>
         </is>
       </c>
       <c r="G30" t="b">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>本研究旨在探討海洋中褐藻多醣（Fucoidans，一種具抗降解性且有助於碳封存的複雜多醣）的降解機制。研究發現，褐藻多醣的完全降解依賴於具備互補代謝功能的特化細菌之間的「協同作用」。透過重建海洋菌群並進行代謝組學分析，研究團隊揭示了細菌間的功能分工——分別負責降解多醣的骨架或特定側鏈，此協同效應使降解效率顯著提升至97.1%。此外，全球海洋總體基因體數據亦證實了這種互補降解菌群的普遍共存。本研究證明複雜生物聚合物的降解取決於由基質結構形塑的微生物生態互動，為理解海洋碳循環及建構人工合成菌群以便利降解頑固多醣提供了全新機制。</t>
+          <t>本研究探討海洋中複雜多醣體「褐藻醣膠」（fucoidans）的微生物降解機制。儘管褐藻醣膠因其抗降解性在碳封存中扮演關鍵角色，但過往對於其在自然界中是否能被完全分解並不清楚。研究發現，褐藻醣膠的降解並非單一物種所能完成，而是透過具有互補代謝功能的細菌群落進行「協同作用」。透過代謝體學分析，研究團隊識別出專門降解硫酸岩藻糖骨架與稀有單醣側鏈的代謝群組（metabolic guilds），這種分工合作能將降解效率大幅提升至 97.1%。此外，研究顯示此代謝功能在不同環境下具有高度保守性，且在海洋宏基因組中普遍存在。本研究揭示了生物聚合物的環境周轉率取決於微生物間的生態交互作用，為理解海洋碳循環機制提供了重要框架，並為未來利用人工合成微生物群落降解頑固性多醣體提供了技術基礎。</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1 位受試者（個案報告）</t>
+          <t>1 例病患（n=1）</t>
         </is>
       </c>
       <c r="G31" t="b">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>本研究報告了一例 20 歲男性淡水溺水後的臨床病例。患者在溺水後出現肺部浸潤，且支氣管鏡檢查顯示氣管黏膜有瀰漫性粟粒樣白色突起，符合急性刺激性氣道損傷。支氣管肺泡灌洗液（BALF）之宏基因組定序（mNGS）與痰液培養均檢出肺炎克雷伯氏菌（*Klebsiella pneumoniae*）。儘管發炎指標顯著升高，但患者影像學異常迅速改善且臨床表現穩定，顯示其早期肺部病變主要為非感染性的吸入性肺損傷。患者經抗生素治療後順利康復。此案例提示臨床醫生，溺水早期的肺部異常易被誤診為細菌性肺炎，結合 mNGS 與臨床病程評估有助於避免過度使用抗生素。</t>
+          <t>本研究透過單一病例報告，探討淡水溺水後肺部浸潤與呼吸道損傷的臨床鑑別診斷。一名 20 歲男性溺水後出現肺水腫與氣道黏膜病變，臨床表現極易與細菌性肺炎混淆。研究利用 mNGS（宏基因組次世代定序）檢測支氣管肺泡灌洗液，雖確認存在肺炎克雷伯菌（*Klebsiella pneumoniae*）訊號，但影像學與臨床病程顯示其肺部損傷主要源於吸入性損傷及急性化學性氣道刺激，而非嚴重的細菌感染。此案例凸顯了臨床判斷溺水相關肺炎時的挑戰，強調在面對看似感染的臨床數據時，應綜合考量影像改善速度與臨床穩定性，避免過度診斷與不必要的抗生素升級，對急性溺水病患的精準治療具有重要的臨床參考價值。</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2096,21 +2096,21 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>42641146</t>
+          <t>42642836</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Engineered bacterial therapeutics from synthetic biology to clinical translation: A multi-database scientometric analysis, 2000-2026.</t>
+          <t>Microbiome-mediated regulation of pathogen virulence: Molecular mechanisms and clinical implications.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Human vaccines &amp; immunotherapeutics</t>
+          <t>Virulence</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1,730 篇學術文章與評論</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G32" t="b">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Engineered bacterial therapeutics integrate programmable strain engineering with biomedical functions such as sensing, delivery, immune modulation, microbiome intervention, and disease management. This study conducted a multi-database bibliometric analysis to map the knowledge structure, collaboration patterns, and translational direction of this field. Bibliographic records were retrieved from Web of Science Core Collection, Scopus, and PubMed for publications from 1 January 2000 to 1 June 2026. After document-type filtering, time restriction, deduplication, language screening, and manual eligibility assessment, 1,730 English-language articles and reviews were included. CiteSpace 6.4.R1, VOSviewer 1.6.20, and the bibliometrix R package were used to analyze publication trends, collaboration networks, journal co-citation, dual-map citation trajectories, citation bursts, keyword co-occurrence, and thematic evolution. Publication output increased steadily, with faster growth after 2020; 2025 was the highest-output complete year, while 2026 represented a partial retrieval year. China and the United States were the leading contributors, although institutional collaboration remained regionally clustered. Co-citation, citation-burst, and keyword analyses showed a shift from bacterial chassis construction and circuit design toward engineered probiotics, gut microbiota-related therapy, cancer immunotherapy, drug delivery, live biotherapeutic products, and clinical translation. Persistent translational priorities include controllability, safety, manufacturing consistency, and regulatory alignment.</t>
+          <t>The human microbiome profoundly influences pathogen virulence and disease susceptibility through diverse molecular mechanisms. This review, focused on literature from 2016 to 2026, synthesizes knowledge on microbiome-mediated regulation examining major pathogens including Vibrio cholerae, enterohemorrhagic Escherichia coli, Salmonella species, Clostridioides difficile, and Staphylococcus aureus. A triangular interaction model is presented, linking host immunity, resident microbiome, and invading pathogen to frame infection outcomes. Commensal bacteria regulate pathogen behavior through quorum sensing interference, metabolite-mediated regulation via short-chain fatty acids and bile acids, competitive exclusion, immune response modulation, and direct antimicrobial production. Key species-Lactobacillus spp. Bifidobacterium spp. Bacteroides thetaiotaomicron, and Faecalibacterium prausnitzii-employ distinct molecular strategies against these pathogens. Organ-on-chip platforms and multi-omics advances reveal context-dependent interactions. Clinical applications including rationally designed probiotics, fecal microbiota transplantation, and precision microbiome engineering show promise despite challenges of inter-individual microbiome variability, representing a paradigm shift toward ecosystem-based infectious disease management.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>本研究透過文獻計量學方法，系統性分析 2000 年至 2026 年間有關「工程化細菌治療」的 1,730 篇學術文獻。研究旨在釐清該領域的知識結構、國際合作模式及臨床轉化趨勢。分析顯示，該領域自 2020 年後顯著加速發展，中國與美國為主要貢獻國。核心研究主軸已由早期的細菌底盤構建與基因電路設計，轉向工程化益生菌、癌症免疫治療、藥物遞送及活體生物藥物（LBP）的開發。科學意義在於確立了該領域從實驗室轉向臨床應用的優先議題，即解決控制力、生物安全性、生產一致性與法規調適等挑戰，為未來工程化細菌作為精準醫療工具的發展提供關鍵決策參考。</t>
+          <t>本研究綜述了2016年至2026年間關於腸道微生物群調控病原體毒力（如霍亂弧菌、大腸桿菌、沙門氏菌等）的分子機制。作者提出了一個結合宿主免疫、共生菌群與入侵病原體的「三角交互模型」，闡述了共生菌如何透過群體感應干擾、代謝產物（如短鏈脂肪酸、膽汁酸）調節、競爭性排斥及免疫調節來抑制病原體。研究強調了乳酸桿菌、雙歧桿菌及普拉梭菌等關鍵菌種的保護機制，並探討了器官晶片與多體學技術在揭示交互作用上的貢獻。此研究主張從生態系統角度管理傳染病，指出益生菌設計、糞便菌群移植及精準微生物組工程是未來治療的關鍵方向，雖面臨個體差異挑戰，但為臨床感染控制提供了典範轉移。</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2142,32 +2142,32 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42641146/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42642836/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>42642834</t>
+          <t>42648179</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Glycosylation in gut-brain communication: from the intestinal barrier and microbiota to immune and neural signaling.</t>
+          <t>Simultaneous removal of nitrogen, Cu2+, and bisphenol A in a hydrogel-biochar-AQDS immobilized bioreactor with added bicarbonate: Performance and metagenomic insights.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>Journal of hazardous materials</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2180,12 +2180,13 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>The gut-brain axis is a complex bidirectional communication network linking the gastrointestinal tract and the central nervous system. Its dysregulation is closely associated with a wide range of gastrointestinal, metabolic, and neuropsychiatric disorders. Glycosylation, one of the most prevalent and structurally diverse post-translational modifications of proteins and lipids, is increasingly recognized as a regulator of multiple processes within the gut-brain axis. In this review, we summarize evidence that glycosylation influences several steps of gut-brain communication, including intestinal barrier function, microbial glycan metabolism, immune signaling, enteric and vagal pathways, blood-brain barrier integrity, and neural responses. We distinguish direct mechanistic findings from associative observations and discuss the more limited evidence for brain-to-gut regulation of intestinal glycosylation. In addition, we discuss the potential of glycosylation-targeted nutritional and microbiota-based interventions and highlight emerging opportunities to integrate glycomics with other omics approaches to dissect the complex regulatory networks underlying the gut-brain axis. In conclusion, elucidating how glycosylation shapes signaling along the gut-brain axis may open new avenues for understanding disease pathogenesis and for developing targeted therapeutic strategies.</t>
+          <t>As the complexity of industrial wastewater pollution continues to increase, the simultaneous removal of nitrogen, metal contaminants, and persistent organic pollutants under low carbon conditions has become a key challenge for biological treatment systems. To address the operational instability and dependence on carbon sources observed in immobilized systems when exposed to copper (Cu2+) and bisphenol A (BPA), the Pseudoalteromonas japonicus strain LY0623 was integrated into a hydrogel-biochar-AQDS composite carrier to construct a multifunctional immobilized biofilm system. Notably, under conditions containing only NaHCO3, the R4 system achieved an NH4+-N removal rate of 89%. Under conditions where Cu2+ and BPA coexist, the R4 system achieved removal of NH4+-N (89%), NO3--N (100%), Cu2+ (85%), and BPA (88%). Sediment characterization confirmed that Cu2+ was immobilized through adsorption, complexation, and microbiologically induced carbonate precipitation (MICP). Metagenomic analysis further indicated that the Pseudomonadota phylum remained the dominant phylum, while functional pathways associated with inorganic carbon assimilation, HNAD nitrogen metabolism, endogenous carbon transformation, biomineralization, electron transfer, and aromatic compound degradation were preserved. By combining ammonia oxidation driven energy production, inorganic carbon utilization, redox mediated processes, and biomineralization, this study provides a highly promising low carbon strategy for treating industrial wastewater containing mixed pollutants.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>本文探討「腸-腦軸線」（Gut-Brain Axis）中醣基化（Glycosylation）修飾的關鍵調節角色。醣基化作為蛋白質與脂質重要的轉譯後修飾，深刻影響腸道屏障功能、微生物聚醣代謝、免疫訊息傳遞及血腦屏障完整性。研究重點解析了醣基化如何調控腸道與中樞神經系統間的溝通，並區分了機制性證據與相關性觀察。本文不僅強調了醣基化在維繫軸線穩定中的核心地位，更提出透過營養干預與微生物調節，結合多體學（Omics）分析醣基化網絡，將有望為神經精神疾病與代謝性障礙提供創新的診斷與治療策略。</t>
+          <t>本研究旨在解決低碳條件下，工業廢水中氮、重金屬（Cu2+）與雙酚A（BPA）等混合污染物難以同時高效生物降解的挑戰。研究人員將日本假交替單胞菌（*Pseudoalteromonas japonicus*）LY0623菌株整合至水凝膠-生物炭-AQDS複合載體中，構建出新型固定化生物膜系統（R4系統）。
+研究發現，在僅添加碳酸氫鈉（無機碳源）的條件下，該系統成功實現了NH4+-N（89%）、NO3--N（100%）、Cu2+（85%）和BPA（88%）的高效同時去除。總體基因體學分析證實，變形菌門（Pseudomonadota）為優勢菌群，且系統中與無機碳同化、異營硝化-好氧反硝化（HNAD）、生物礦化及芳香族化合物降解相關的功能通路均得到有效維持。本研究結合了氨氧化產能與生物礦化等機制，為混合污染廢水處理提供了一種具前景的低碳生物修復策略。</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2195,32 +2196,32 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42642834/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648179/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>42640100</t>
+          <t>42642466</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Revisiting gut microbiota-driven ammonia metabolism: from disease burden to physiological adaptation.</t>
+          <t>Empirical evidence for gut microbial influence on human brain neurochemistry via the gut-brain axis.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>Molecular psychiatry</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11</v>
+        <v>10.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2233,12 +2234,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Ammonia homeostasis is governed by interconnected host and microbial pathways, including hepatic ureagenesis, glutamine synthesis, and gut microbiota-mediated urea hydrolysis, proteolysis, and amino acid deamination. Ammonia has historically been viewed primarily as a nitrogenous waste product and neurotoxic molecule, a concept strongly supported by studies of hyperammonemia and hepatic encephalopathy. Impaired hepatic clearance, portosystemic shunting, and enhanced gut-derived ammonia input increase systemic ammonia burden and are linked to neurological dysfunction, muscle wasting, immune dysregulation, and progression of liver disease. In the gut lumen and mucosal environment, however, gut microbes not only generate ammonia but can also reuse ammonia-derived nitrogen for amino acid synthesis, microbial biomass formation, and community nitrogen exchange. Evidence from selected physiological and preclinical models indicates that microbiota-derived ammonia may contribute to nitrogen recycling, microbial community maintenance, enteric neural regulation, or metabolic adaptation under defined conditions. These roles are more context-specific and less broadly established than the pathological effects of systemic hyperammonemia. When epithelial barrier integrity is compromised, hepatic clearance declines, or host buffering reserves are depleted, elevated ammonia can increase epithelial exposure, portal ammonia input, or peripheral blood ammonia. Conversely, evidence that reduced microbiota-derived ammonia contributes to disease remains limited and currently comes mainly from selected animal models. This review re-examines ammonia metabolism from a gut microbiota-centered perspective. We discuss the ecological origins, spatial distribution, exposure characteristics, host-interface effects, and context-specific outcomes of microbiota-derived ammonia in physiology and disease, and discuss how ammonia should be measured, stratified, and targeted in microbial nitrogen metabolism.</t>
+          <t>The gut microbiome produces metabolites with potential neuroactive properties, many of which act locally within the gut. While preclinical studies suggest these microbial pathways can influence cognitive and emotional processes, human evidence remains limited. This study investigates associations between gut microbiome-derived neuroactive functional potential and in vivo brain neurotransmitter concentrations in healthy young females. Using proton magnetic resonance spectroscopy (¹H-MRS), we quantified GABA and glutamate levels in the dorsolateral prefrontal cortex (dlPFC), anterior cingulate cortex (ACC), and inferior occipital gyrus (IOG). Parallel metagenomic profiling characterised microbial functional potential for pathways related to the synthesis and degradation of GABA, glutamate, short-chain fatty acids (SCFAs), p-cresol, and inositol. Region-specific associations were observed between these microbial pathways and cortical GABA and glutamate levels, including excitatory/inhibitory (E/I) balance, a key marker of neuroplasticity and mental health. Notably, microbial glutamate degradation and inositol synthesis potential were associated with IOG E/I balance, while additional pathways including GABA metabolism, p-cresol production, and SCFA synthesis showed distinct associations across regions. Exploratory analyses also identified links between microbial functional potential and anxiety, depressive symptoms, and sleep quality. Together, these findings provide new human evidence that variation in microbial functional potential corresponds with regional cortical neurochemistry and psychological wellbeing, highlighting the gut-brain axis as a promising avenue for mechanistically informed microbiome-based- interventions.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>本綜述重新審視了腸道菌群驅動的氨代謝，探討其從疾病負擔到生理適應的雙重角色。傳統上，氨被視為具神經毒性的代謝廢物，與高氨血症、肝性腦病及肝病惡化密切相關。然而，在腸道微環境中，微生物不僅產生氨，亦能利用氨源氮進行氨基酸合成與群落氮循環，展現出維持腸道神經與代謝適應等生理功能。文章強調，氨的病理與生理效應高度取決於上皮屏障、肝臟清除能力及宿主緩衝儲備。本研究為腸道微生物氮代謝提供了新的生態與臨床視角，並討論了未來如何精確測量及標靶氨代謝的策略。</t>
+          <t>本研究旨在探討健康女性的腸道菌群功能潛力與大腦活體神經傳導物質（GABA與麩胺酸）濃度的關聯。研究結合腦部質子磁共振波譜（¹H-MRS）與總體基因體學分析，發現微生物中參與GABA、麩胺酸、短鏈脂肪酸、對甲酚及肌醇代謝的通路，與大腦特定區域（如背外側前額葉、前扣帶迴與下枕葉）的神經傳導物質水平及興奮/抑制平衡（E/I）具有區域特異性關聯。探索性分析亦顯示微生物功能與焦慮、抑鬱及睡眠品質相關。本研究為腸道菌群影響人類大腦神經化學與心理健康提供了直接的人體實證，為未來開發以微生物為基礎的腦腸軸臨床干預奠定基礎。</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2248,37 +2249,37 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42640100/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42642466/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>42642836</t>
+          <t>42640624</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Microbiome-mediated regulation of pathogen virulence: Molecular mechanisms and clinical implications.</t>
+          <t>Gut microbial diversity at baseline conditions the clinical, microbiome, and metabolic response to paraprobiotic Lactiplantibacillus plantarum LRCC5282 in overweight adults.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Virulence</t>
+          <t>Gut microbes</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>5.4</v>
+        <v>11</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>16S, metabolomics</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>120 位過重成人</t>
         </is>
       </c>
       <c r="G35" t="b">
@@ -2286,12 +2287,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>The human microbiome profoundly influences pathogen virulence and disease susceptibility through diverse molecular mechanisms. This review, focused on literature from 2016 to 2026, synthesizes knowledge on microbiome-mediated regulation examining major pathogens including Vibrio cholerae, enterohemorrhagic Escherichia coli, Salmonella species, Clostridioides difficile, and Staphylococcus aureus. A triangular interaction model is presented, linking host immunity, resident microbiome, and invading pathogen to frame infection outcomes. Commensal bacteria regulate pathogen behavior through quorum sensing interference, metabolite-mediated regulation via short-chain fatty acids and bile acids, competitive exclusion, immune response modulation, and direct antimicrobial production. Key species-Lactobacillus spp. Bifidobacterium spp. Bacteroides thetaiotaomicron, and Faecalibacterium prausnitzii-employ distinct molecular strategies against these pathogens. Organ-on-chip platforms and multi-omics advances reveal context-dependent interactions. Clinical applications including rationally designed probiotics, fecal microbiota transplantation, and precision microbiome engineering show promise despite challenges of inter-individual microbiome variability, representing a paradigm shift toward ecosystem-based infectious disease management.</t>
+          <t>The gut microbiota is increasingly recognized as a target for obesity management; however, whether baseline gut microbial diversity conditions responsiveness to microbiota-targeted interventions remains unclear. We aimed to investigate whether baseline gut microbial diversity is associated with responsiveness to a paraprobiotic derived from Lactiplantibacillus plantarum LRCC5282 (LP5282-P) in overweight adults. In a 12-week, randomized, double-blind, placebo-controlled, multicenter trial of 120 overweight adults, LP5282-P produced no significant between-group differences in any clinical outcome across the overall per-protocol population. However, in the low-diversity subgroup, LP5282-P was associated with significant reductions in body weight, body mass index, and circulating leptin levels. These clinical changes were accompanied by compositional shifts in the gut microbiota, including higher relative abundances of Christensenellaceae, Faecalibacterium, and Alistipes. Fecal metabolite profiles showed elevated acetate and butyrate concentrations and altered bile acid composition. Within the low-diversity subgroup, changes in the relative abundances of Akkermansia and Eubacterium were inversely correlated with changes in body weight, body fat mass, and leptin levels. In contrast, the high-diversity subgroup exhibited no consistent response across the outcome domains examined. Overall, baseline gut microbial diversity was associated with differential responsiveness to LP5282-P, supporting its potential use as a stratification variable in future microbiota-targeted intervention trials. Further studies integrating direct measures of microbial activity and host response are warranted to elucidate the biological pathways underlying this diversity-dependent responsiveness. Trial registration: Clinical Research Information Service (CRIS), KCT0008119.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>本研究綜述了2016年至2026年間關於腸道微生物群調控病原體毒力（如霍亂弧菌、大腸桿菌、沙門氏菌等）的分子機制。作者提出了一個結合宿主免疫、共生菌群與入侵病原體的「三角交互模型」，闡述了共生菌如何透過群體感應干擾、代謝產物（如短鏈脂肪酸、膽汁酸）調節、競爭性排斥及免疫調節來抑制病原體。研究強調了乳酸桿菌、雙歧桿菌及普拉梭菌等關鍵菌種的保護機制，並探討了器官晶片與多體學技術在揭示交互作用上的貢獻。此研究主張從生態系統角度管理傳染病，指出益生菌設計、糞便菌群移植及精準微生物組工程是未來治療的關鍵方向，雖面臨個體差異挑戰，但為臨床感染控制提供了典範轉移。</t>
+          <t>本研究旨在探討基準線腸道微生物多樣性，是否會影響過重成人對副乾酪乳桿菌（LP5282-P）介入的臨床、菌群及代謝反應。在一項為期12週、納入120位過重成人的臨床試驗中，整體人群並未展現顯著差異；然而，在「低多樣性」亞群中，LP5282-P顯著降低了受試者的體重、BMI與血清瘦素水平，並促使腸道有益菌（如 *Faecalibacterium* 與 *Alistipes*）豐度上升，同時提升糞便中乙酸與丁酸濃度並改變膽汁酸組成。相反地，「高多樣性」亞群則無一致反應。此研究證實基準線菌群多樣性是預測益生菌療效的重要關鍵，可作為未來精準微生態介入與體重管理的分層依據。</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2301,37 +2302,37 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42642836/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42640624/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>42640624</t>
+          <t>42642622</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Gut microbial diversity at baseline conditions the clinical, microbiome, and metabolic response to paraprobiotic Lactiplantibacillus plantarum LRCC5282 in overweight adults.</t>
+          <t>Deployable high-fidelity metagenome binning at scale with QuickBin.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>Communications biology</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11</v>
+        <v>5.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>120 位過重成人</t>
+          <t>297 個真實總體基因體數據集 (297 real metagenomes)</t>
         </is>
       </c>
       <c r="G36" t="b">
@@ -2339,12 +2340,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>The gut microbiota is increasingly recognized as a target for obesity management; however, whether baseline gut microbial diversity conditions responsiveness to microbiota-targeted interventions remains unclear. We aimed to investigate whether baseline gut microbial diversity is associated with responsiveness to a paraprobiotic derived from Lactiplantibacillus plantarum LRCC5282 (LP5282-P) in overweight adults. In a 12-week, randomized, double-blind, placebo-controlled, multicenter trial of 120 overweight adults, LP5282-P produced no significant between-group differences in any clinical outcome across the overall per-protocol population. However, in the low-diversity subgroup, LP5282-P was associated with significant reductions in body weight, body mass index, and circulating leptin levels. These clinical changes were accompanied by compositional shifts in the gut microbiota, including higher relative abundances of Christensenellaceae, Faecalibacterium, and Alistipes. Fecal metabolite profiles showed elevated acetate and butyrate concentrations and altered bile acid composition. Within the low-diversity subgroup, changes in the relative abundances of Akkermansia and Eubacterium were inversely correlated with changes in body weight, body fat mass, and leptin levels. In contrast, the high-diversity subgroup exhibited no consistent response across the outcome domains examined. Overall, baseline gut microbial diversity was associated with differential responsiveness to LP5282-P, supporting its potential use as a stratification variable in future microbiota-targeted intervention trials. Further studies integrating direct measures of microbial activity and host response are warranted to elucidate the biological pathways underlying this diversity-dependent responsiveness. Trial registration: Clinical Research Information Service (CRIS), KCT0008119.</t>
+          <t>Reconstructing genomes from metagenomic assemblies is foundational to microbiome research, yet binning faces a persistent trade-off between fidelity and throughput. Many high-accuracy methods rely on GPU-intensive workflows, marker-gene postprocessing, or heavy computational resources, limiting reproducible use at scale. Here, we present QuickBin, a CPU-native, marker-free binning algorithm designed to recover near-complete, ultra-low-contamination metagenome-assembled genomes (MAGs) efficiently. QuickBin pairs a GC-coverage spatial index (BinMap) with an early-exit Oracle cascade of similarity tests (scalar composition/coverage filters and SIMD-accelerated k-mer comparisons), reserving a compact neural network exclusively for ambiguous merges. Across synthetic communities, evaluated by marker-based and contig-origin ground truth, QuickBin maximizes high-fidelity sequence recovery. In benchmarking 297 diverse real metagenomes, QuickBin completed all runs, recovering more high-quality MAGs (≥95% completeness, ≤1% contamination) than resource-intensive alternatives that frequently failed. QuickBin provides a practical path to reproducible, genome-resolved metagenomics at scale for downstream comparative analyses. Open-source at: https://github.com/bbushnell/BBTools .</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>本研究旨在探討基準線腸道微生物多樣性，是否會影響過重成人對副乾酪乳桿菌（LP5282-P）介入的臨床、菌群及代謝反應。在一項為期12週、納入120位過重成人的臨床試驗中，整體人群並未展現顯著差異；然而，在「低多樣性」亞群中，LP5282-P顯著降低了受試者的體重、BMI與血清瘦素水平，並促使腸道有益菌（如 *Faecalibacterium* 與 *Alistipes*）豐度上升，同時提升糞便中乙酸與丁酸濃度並改變膽汁酸組成。相反地，「高多樣性」亞群則無一致反應。此研究證實基準線菌群多樣性是預測益生菌療效的重要關鍵，可作為未來精準微生態介入與體重管理的分層依據。</t>
+          <t>本研究開發了 QuickBin，這是一種無需標記基因且僅需 CPU 運行的總體基因體分箱（binning）演算法，旨在高效重建高完整度且極低污染的總體基因體組裝基因體（MAGs）。QuickBin 結合了 GC 含量與覆蓋度的空間索引及快速相似性過濾機制，僅在處理模糊合併時使用輕量級神經網路。在 297 個真實總體基因體數據集的基準測試中，QuickBin 成功完成所有運行，且重建的高品質 MAGs 數量超越了其他耗費資源或容易失敗的現有工具。此技術為大規模、可重複的基因體解析總體基因體學研究提供了實用的解決方案。</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2354,32 +2355,32 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42640624/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42642622/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>42642466</t>
+          <t>42640100</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Empirical evidence for gut microbial influence on human brain neurochemistry via the gut-brain axis.</t>
+          <t>Revisiting gut microbiota-driven ammonia metabolism: from disease burden to physiological adaptation.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Molecular psychiatry</t>
+          <t>Gut microbes</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10.1</v>
+        <v>11</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2392,12 +2393,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>The gut microbiome produces metabolites with potential neuroactive properties, many of which act locally within the gut. While preclinical studies suggest these microbial pathways can influence cognitive and emotional processes, human evidence remains limited. This study investigates associations between gut microbiome-derived neuroactive functional potential and in vivo brain neurotransmitter concentrations in healthy young females. Using proton magnetic resonance spectroscopy (¹H-MRS), we quantified GABA and glutamate levels in the dorsolateral prefrontal cortex (dlPFC), anterior cingulate cortex (ACC), and inferior occipital gyrus (IOG). Parallel metagenomic profiling characterised microbial functional potential for pathways related to the synthesis and degradation of GABA, glutamate, short-chain fatty acids (SCFAs), p-cresol, and inositol. Region-specific associations were observed between these microbial pathways and cortical GABA and glutamate levels, including excitatory/inhibitory (E/I) balance, a key marker of neuroplasticity and mental health. Notably, microbial glutamate degradation and inositol synthesis potential were associated with IOG E/I balance, while additional pathways including GABA metabolism, p-cresol production, and SCFA synthesis showed distinct associations across regions. Exploratory analyses also identified links between microbial functional potential and anxiety, depressive symptoms, and sleep quality. Together, these findings provide new human evidence that variation in microbial functional potential corresponds with regional cortical neurochemistry and psychological wellbeing, highlighting the gut-brain axis as a promising avenue for mechanistically informed microbiome-based- interventions.</t>
+          <t>Ammonia homeostasis is governed by interconnected host and microbial pathways, including hepatic ureagenesis, glutamine synthesis, and gut microbiota-mediated urea hydrolysis, proteolysis, and amino acid deamination. Ammonia has historically been viewed primarily as a nitrogenous waste product and neurotoxic molecule, a concept strongly supported by studies of hyperammonemia and hepatic encephalopathy. Impaired hepatic clearance, portosystemic shunting, and enhanced gut-derived ammonia input increase systemic ammonia burden and are linked to neurological dysfunction, muscle wasting, immune dysregulation, and progression of liver disease. In the gut lumen and mucosal environment, however, gut microbes not only generate ammonia but can also reuse ammonia-derived nitrogen for amino acid synthesis, microbial biomass formation, and community nitrogen exchange. Evidence from selected physiological and preclinical models indicates that microbiota-derived ammonia may contribute to nitrogen recycling, microbial community maintenance, enteric neural regulation, or metabolic adaptation under defined conditions. These roles are more context-specific and less broadly established than the pathological effects of systemic hyperammonemia. When epithelial barrier integrity is compromised, hepatic clearance declines, or host buffering reserves are depleted, elevated ammonia can increase epithelial exposure, portal ammonia input, or peripheral blood ammonia. Conversely, evidence that reduced microbiota-derived ammonia contributes to disease remains limited and currently comes mainly from selected animal models. This review re-examines ammonia metabolism from a gut microbiota-centered perspective. We discuss the ecological origins, spatial distribution, exposure characteristics, host-interface effects, and context-specific outcomes of microbiota-derived ammonia in physiology and disease, and discuss how ammonia should be measured, stratified, and targeted in microbial nitrogen metabolism.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>本研究旨在探討健康女性的腸道菌群功能潛力與大腦活體神經傳導物質（GABA與麩胺酸）濃度的關聯。研究結合腦部質子磁共振波譜（¹H-MRS）與總體基因體學分析，發現微生物中參與GABA、麩胺酸、短鏈脂肪酸、對甲酚及肌醇代謝的通路，與大腦特定區域（如背外側前額葉、前扣帶迴與下枕葉）的神經傳導物質水平及興奮/抑制平衡（E/I）具有區域特異性關聯。探索性分析亦顯示微生物功能與焦慮、抑鬱及睡眠品質相關。本研究為腸道菌群影響人類大腦神經化學與心理健康提供了直接的人體實證，為未來開發以微生物為基礎的腦腸軸臨床干預奠定基礎。</t>
+          <t>本綜述重新審視了腸道菌群驅動的氨代謝，探討其從疾病負擔到生理適應的雙重角色。傳統上，氨被視為具神經毒性的代謝廢物，與高氨血症、肝性腦病及肝病惡化密切相關。然而，在腸道微環境中，微生物不僅產生氨，亦能利用氨源氮進行氨基酸合成與群落氮循環，展現出維持腸道神經與代謝適應等生理功能。文章強調，氨的病理與生理效應高度取決於上皮屏障、肝臟清除能力及宿主緩衝儲備。本研究為腸道微生物氮代謝提供了新的生態與臨床視角，並討論了未來如何精確測量及標靶氨代謝的策略。</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2407,37 +2408,37 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42642466/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42640100/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>42642622</t>
+          <t>42642834</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Deployable high-fidelity metagenome binning at scale with QuickBin.</t>
+          <t>Glycosylation in gut-brain communication: from the intestinal barrier and microbiota to immune and neural signaling.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Communications biology</t>
+          <t>Gut microbes</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5.1</v>
+        <v>11</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>297 個真實總體基因體數據集 (297 real metagenomes)</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G38" t="b">
@@ -2445,12 +2446,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Reconstructing genomes from metagenomic assemblies is foundational to microbiome research, yet binning faces a persistent trade-off between fidelity and throughput. Many high-accuracy methods rely on GPU-intensive workflows, marker-gene postprocessing, or heavy computational resources, limiting reproducible use at scale. Here, we present QuickBin, a CPU-native, marker-free binning algorithm designed to recover near-complete, ultra-low-contamination metagenome-assembled genomes (MAGs) efficiently. QuickBin pairs a GC-coverage spatial index (BinMap) with an early-exit Oracle cascade of similarity tests (scalar composition/coverage filters and SIMD-accelerated k-mer comparisons), reserving a compact neural network exclusively for ambiguous merges. Across synthetic communities, evaluated by marker-based and contig-origin ground truth, QuickBin maximizes high-fidelity sequence recovery. In benchmarking 297 diverse real metagenomes, QuickBin completed all runs, recovering more high-quality MAGs (≥95% completeness, ≤1% contamination) than resource-intensive alternatives that frequently failed. QuickBin provides a practical path to reproducible, genome-resolved metagenomics at scale for downstream comparative analyses. Open-source at: https://github.com/bbushnell/BBTools .</t>
+          <t>The gut-brain axis is a complex bidirectional communication network linking the gastrointestinal tract and the central nervous system. Its dysregulation is closely associated with a wide range of gastrointestinal, metabolic, and neuropsychiatric disorders. Glycosylation, one of the most prevalent and structurally diverse post-translational modifications of proteins and lipids, is increasingly recognized as a regulator of multiple processes within the gut-brain axis. In this review, we summarize evidence that glycosylation influences several steps of gut-brain communication, including intestinal barrier function, microbial glycan metabolism, immune signaling, enteric and vagal pathways, blood-brain barrier integrity, and neural responses. We distinguish direct mechanistic findings from associative observations and discuss the more limited evidence for brain-to-gut regulation of intestinal glycosylation. In addition, we discuss the potential of glycosylation-targeted nutritional and microbiota-based interventions and highlight emerging opportunities to integrate glycomics with other omics approaches to dissect the complex regulatory networks underlying the gut-brain axis. In conclusion, elucidating how glycosylation shapes signaling along the gut-brain axis may open new avenues for understanding disease pathogenesis and for developing targeted therapeutic strategies.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>本研究開發了 QuickBin，這是一種無需標記基因且僅需 CPU 運行的總體基因體分箱（binning）演算法，旨在高效重建高完整度且極低污染的總體基因體組裝基因體（MAGs）。QuickBin 結合了 GC 含量與覆蓋度的空間索引及快速相似性過濾機制，僅在處理模糊合併時使用輕量級神經網路。在 297 個真實總體基因體數據集的基準測試中，QuickBin 成功完成所有運行，且重建的高品質 MAGs 數量超越了其他耗費資源或容易失敗的現有工具。此技術為大規模、可重複的基因體解析總體基因體學研究提供了實用的解決方案。</t>
+          <t>本文探討「腸-腦軸線」（Gut-Brain Axis）中醣基化（Glycosylation）修飾的關鍵調節角色。醣基化作為蛋白質與脂質重要的轉譯後修飾，深刻影響腸道屏障功能、微生物聚醣代謝、免疫訊息傳遞及血腦屏障完整性。研究重點解析了醣基化如何調控腸道與中樞神經系統間的溝通，並區分了機制性證據與相關性觀察。本文不僅強調了醣基化在維繫軸線穩定中的核心地位，更提出透過營養干預與微生物調節，結合多體學（Omics）分析醣基化網絡，將有望為神經精神疾病與代謝性障礙提供創新的診斷與治療策略。</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2460,37 +2461,37 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42642622/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42642834/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>42648179</t>
+          <t>42641146</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Simultaneous removal of nitrogen, Cu2+, and bisphenol A in a hydrogel-biochar-AQDS immobilized bioreactor with added bicarbonate: Performance and metagenomic insights.</t>
+          <t>Engineered bacterial therapeutics from synthetic biology to clinical translation: A multi-database scientometric analysis, 2000-2026.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Journal of hazardous materials</t>
+          <t>Human vaccines &amp; immunotherapeutics</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.3</v>
+        <v>3.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>1,730 篇學術文章與評論</t>
         </is>
       </c>
       <c r="G39" t="b">
@@ -2498,13 +2499,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>As the complexity of industrial wastewater pollution continues to increase, the simultaneous removal of nitrogen, metal contaminants, and persistent organic pollutants under low carbon conditions has become a key challenge for biological treatment systems. To address the operational instability and dependence on carbon sources observed in immobilized systems when exposed to copper (Cu2+) and bisphenol A (BPA), the Pseudoalteromonas japonicus strain LY0623 was integrated into a hydrogel-biochar-AQDS composite carrier to construct a multifunctional immobilized biofilm system. Notably, under conditions containing only NaHCO3, the R4 system achieved an NH4+-N removal rate of 89%. Under conditions where Cu2+ and BPA coexist, the R4 system achieved removal of NH4+-N (89%), NO3--N (100%), Cu2+ (85%), and BPA (88%). Sediment characterization confirmed that Cu2+ was immobilized through adsorption, complexation, and microbiologically induced carbonate precipitation (MICP). Metagenomic analysis further indicated that the Pseudomonadota phylum remained the dominant phylum, while functional pathways associated with inorganic carbon assimilation, HNAD nitrogen metabolism, endogenous carbon transformation, biomineralization, electron transfer, and aromatic compound degradation were preserved. By combining ammonia oxidation driven energy production, inorganic carbon utilization, redox mediated processes, and biomineralization, this study provides a highly promising low carbon strategy for treating industrial wastewater containing mixed pollutants.</t>
+          <t>Engineered bacterial therapeutics integrate programmable strain engineering with biomedical functions such as sensing, delivery, immune modulation, microbiome intervention, and disease management. This study conducted a multi-database bibliometric analysis to map the knowledge structure, collaboration patterns, and translational direction of this field. Bibliographic records were retrieved from Web of Science Core Collection, Scopus, and PubMed for publications from 1 January 2000 to 1 June 2026. After document-type filtering, time restriction, deduplication, language screening, and manual eligibility assessment, 1,730 English-language articles and reviews were included. CiteSpace 6.4.R1, VOSviewer 1.6.20, and the bibliometrix R package were used to analyze publication trends, collaboration networks, journal co-citation, dual-map citation trajectories, citation bursts, keyword co-occurrence, and thematic evolution. Publication output increased steadily, with faster growth after 2020; 2025 was the highest-output complete year, while 2026 represented a partial retrieval year. China and the United States were the leading contributors, although institutional collaboration remained regionally clustered. Co-citation, citation-burst, and keyword analyses showed a shift from bacterial chassis construction and circuit design toward engineered probiotics, gut microbiota-related therapy, cancer immunotherapy, drug delivery, live biotherapeutic products, and clinical translation. Persistent translational priorities include controllability, safety, manufacturing consistency, and regulatory alignment.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>本研究旨在解決低碳條件下，工業廢水中氮、重金屬（Cu2+）與雙酚A（BPA）等混合污染物難以同時高效生物降解的挑戰。研究人員將日本假交替單胞菌（*Pseudoalteromonas japonicus*）LY0623菌株整合至水凝膠-生物炭-AQDS複合載體中，構建出新型固定化生物膜系統（R4系統）。
-研究發現，在僅添加碳酸氫鈉（無機碳源）的條件下，該系統成功實現了NH4+-N（89%）、NO3--N（100%）、Cu2+（85%）和BPA（88%）的高效同時去除。總體基因體學分析證實，變形菌門（Pseudomonadota）為優勢菌群，且系統中與無機碳同化、異營硝化-好氧反硝化（HNAD）、生物礦化及芳香族化合物降解相關的功能通路均得到有效維持。本研究結合了氨氧化產能與生物礦化等機制，為混合污染廢水處理提供了一種具前景的低碳生物修復策略。</t>
+          <t>本研究透過文獻計量學方法，系統性分析 2000 年至 2026 年間有關「工程化細菌治療」的 1,730 篇學術文獻。研究旨在釐清該領域的知識結構、國際合作模式及臨床轉化趨勢。分析顯示，該領域自 2020 年後顯著加速發展，中國與美國為主要貢獻國。核心研究主軸已由早期的細菌底盤構建與基因電路設計，轉向工程化益生菌、癌症免疫治療、藥物遞送及活體生物藥物（LBP）的開發。科學意義在於確立了該領域從實驗室轉向臨床應用的優先議題，即解決控制力、生物安全性、生產一致性與法規調適等挑戰，為未來工程化細菌作為精準醫療工具的發展提供關鍵決策參考。</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42648179/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42641146/</t>
         </is>
       </c>
     </row>
@@ -3092,12 +3092,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>42637430</t>
+          <t>42637441</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Regional differentiation of microbial communities and metabolites in Yunnan dry-cured beef: insights from high-throughput sequencing and untargeted metabolomics.</t>
+          <t>Microbial succession drives quality deterioration in refrigerated golden pompano (Trachinotus ovatus): regulatory network of dominant spoilage microbiota on characteristic biomarkers.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3121,12 +3121,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>To reveal the effects of regional processing on quality, microbial communities and metabolites of traditional Yunnan dry-cured beef, samples from Xundian (XD), Yuxi (YX) and Honghe (HH) were analyzed. High-throughput sequencing and UHPLC-Q-Exactive HF/MS untargeted metabolomics were applied. Sensory scores and physicochemical Properties differed significantly (p &lt; 0.05). Bacillota and Staphylococcus dominated bacterial communities. The observed differences in microbial communities and metabolites among regions are shaped by the combined effects of geographical environment and processing conditions. Ascomycota was the main fungal phylum. Debaryomyces dominated XD and HH samples. YX samples had a unique fungal profile dominated by Rhodotorula and Cladosporium. A total of 1320 metabolites were identified. 196 differential metabolites were screened. Key pathways included glycerophospholipid metabolism, pyrimidine metabolism and arachidonic acid metabolism. Correlation analysis indicated that Staphylococcus and Lactococcus were positively associated with amino acid derivatives, while Latilactobacillus and Debaryomyces correlated with organic acids and glycerophospholipids. These findings revealed the potential microbial-metabolic association underlying regional quality differences. They provide support for quality control and traceability of dry-cured beef.</t>
+          <t>Elucidating the quality deterioration mechanisms of refrigerated golden pompano (Trachinotus ovatus), this study integrated 16S rRNA gene sequencing and untargeted metabolomics to systematically dissect how microbial ecological succession drives metabolic changes. As critical spoilage indicators, total volatile basic nitrogen (TVB-N) and thiobarbituric acid reactive substances (TBARS) continuously increased during storage, indicating significant deterioration by day 6. Microbial community succession analysis revealed that Psychrobacter, Shewanella, and Pseudomonas gradually became the dominant microbiota in the late storage stage. Metabolite enrichment analysis further demonstrated that this shift redirected the metabolic focus from early-stage nucleotide degradation to late-stage protein hydrolysis and amino acid metabolism. Moreover, multivariate statistical analysis identified 50 potential spoilage biomarkers, among which biogenic amines (histamine, tyramine, and phenylethylamine) were recognized as key indicators reflecting spoilage progression. Correlation network analysis revealed positive correlations between Pseudomonas and Shewanella abundances and the accumulation of these biogenic amines. This suggests that these two genera act as the core functional microbiota, driving spoilage metabolite generation and subsequent quality deterioration. Pathway analysis of potential spoilage biomarker generation indicates that amino acid and nucleotide metabolism constitute the core spoilage pathways, with lipid oxidation serving as a complementary mechanism. Overall, this study elucidates the spoilage mechanisms of refrigerated golden pompano, providing chemical targets for early biomarker detection and targeted antibacterial strategies.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>本研究旨在探討地理區域與加工工藝對雲南傳統乾醃牛肉（尋甸、玉溪、紅河三地）品質、微生物群落及代謝物的影響。研究結合高通量定序與非靶向代謝組學技術，發現不同地區的乾醃牛肉在感官評分與理化性質上存有顯著差異。細菌群落以厚壁菌門和葡萄球菌屬為主；真菌群落中，尋甸和紅河樣品以德巴利酵母屬為主，玉溪樣品則以紅酵母屬與枝孢菌屬為特有優勢菌。代謝組學共鑑定出1320種代謝物，其中196種為差異代謝物，主要涉及甘油磷脂、嘧啶及花生四烯酸代謝通路。關聯分析顯示，葡萄球菌屬和乳球菌屬與氨基酸衍生物呈正相關，而廣義乳桿菌屬與德巴利酵母屬則與有機酸及甘油磷脂密切相關。本研究揭示了微生物與代謝物的關聯性，為乾醃牛肉的品質控制與產地溯源提供了重要科學依據。</t>
+          <t>本研究旨在探討冷藏金鯧魚品質劣化的機制。研究結合 16S rRNA 基因定序與非靶向代謝組學，分析微生物群落演替如何驅動代謝變化。結果顯示，金鯧魚冷藏至第 6 天時顯著腐敗。在貯藏後期，*Psychrobacter*、*Shewanella* 與 *Pseudomonas* 逐漸成為優勢菌群，使代謝焦點自初期的核苷酸降解轉向後期的蛋白質水解與氨基酸代謝。研究鑑定出 50 個潛在腐敗生物標誌物（如組胺、酪胺等生物胺），並發現 *Pseudomonas* 和 *Shewanella* 的豐度與這些生物胺的累積呈正相關，為驅動腐敗的核心菌群。本研究闡明了金鯧魚的腐敗機制，為食品早期變質檢測及靶向抑菌策略提供了科學依據與化學標靶。</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42637430/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42637441/</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>120 個放山雞糞便檢體（以此重構出 2,146 個總體基因體組裝基因體 / MAGs）</t>
+          <t>120 個放養雞糞便檢體（重建出 2,146 個總體基因體組裝基因體/MAGs）</t>
         </is>
       </c>
       <c r="G52" t="b">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>本研究旨在探討與人類生活圈相近的放山雞腸道菌群中抗生素抗藥性基因（ARGs）的分布。研究團隊分析了120個放山雞糞便檢體，重構出2,146個總體基因體組裝基因體（MAGs）。研究共鑑定出254,316個ARGs（涵蓋35類抗生素），其中多重抗藥性與四環素抗性最為普遍。ARGs分布呈現顯著的地域差異，且與可移動遺傳因子（MGEs）呈強烈正相關（R=0.77）。特定的大腸桿菌和肺炎克雷伯氏菌群被發現攜帶大量抗藥與毒力因子。本研究建立了寶貴的基因組資源，強調了家禽業實施針對性抗藥性監測的重要性。</t>
+          <t>本研究利用總體基因體定序技術分析中國四省120個放養雞糞便檢體，成功重建2,146個總體基因體組裝基因體（MAGs）。研究鑑定出254,316個抗藥性基因（ARGs），以多重抗藥性與四環黴素抗性最普遍。ARGs分佈呈現顯著的地區差異，且移動遺傳元件與其豐度呈高度正相關，顯示其在抗藥性傳播中的關鍵作用。此外，大腸桿菌與肺炎克雷伯氏菌等特定菌株攜帶大量ARGs與毒力因子，屬高風險傳播媒介。本研究為禽類腸道菌群提供了寶貴的基因組資源，並強調在養殖系統中實施針對性監控以防範抗藥性傳播的必要性。</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3198,12 +3198,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>42637441</t>
+          <t>42637430</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Microbial succession drives quality deterioration in refrigerated golden pompano (Trachinotus ovatus): regulatory network of dominant spoilage microbiota on characteristic biomarkers.</t>
+          <t>Regional differentiation of microbial communities and metabolites in Yunnan dry-cured beef: insights from high-throughput sequencing and untargeted metabolomics.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3227,12 +3227,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Elucidating the quality deterioration mechanisms of refrigerated golden pompano (Trachinotus ovatus), this study integrated 16S rRNA gene sequencing and untargeted metabolomics to systematically dissect how microbial ecological succession drives metabolic changes. As critical spoilage indicators, total volatile basic nitrogen (TVB-N) and thiobarbituric acid reactive substances (TBARS) continuously increased during storage, indicating significant deterioration by day 6. Microbial community succession analysis revealed that Psychrobacter, Shewanella, and Pseudomonas gradually became the dominant microbiota in the late storage stage. Metabolite enrichment analysis further demonstrated that this shift redirected the metabolic focus from early-stage nucleotide degradation to late-stage protein hydrolysis and amino acid metabolism. Moreover, multivariate statistical analysis identified 50 potential spoilage biomarkers, among which biogenic amines (histamine, tyramine, and phenylethylamine) were recognized as key indicators reflecting spoilage progression. Correlation network analysis revealed positive correlations between Pseudomonas and Shewanella abundances and the accumulation of these biogenic amines. This suggests that these two genera act as the core functional microbiota, driving spoilage metabolite generation and subsequent quality deterioration. Pathway analysis of potential spoilage biomarker generation indicates that amino acid and nucleotide metabolism constitute the core spoilage pathways, with lipid oxidation serving as a complementary mechanism. Overall, this study elucidates the spoilage mechanisms of refrigerated golden pompano, providing chemical targets for early biomarker detection and targeted antibacterial strategies.</t>
+          <t>To reveal the effects of regional processing on quality, microbial communities and metabolites of traditional Yunnan dry-cured beef, samples from Xundian (XD), Yuxi (YX) and Honghe (HH) were analyzed. High-throughput sequencing and UHPLC-Q-Exactive HF/MS untargeted metabolomics were applied. Sensory scores and physicochemical Properties differed significantly (p &lt; 0.05). Bacillota and Staphylococcus dominated bacterial communities. The observed differences in microbial communities and metabolites among regions are shaped by the combined effects of geographical environment and processing conditions. Ascomycota was the main fungal phylum. Debaryomyces dominated XD and HH samples. YX samples had a unique fungal profile dominated by Rhodotorula and Cladosporium. A total of 1320 metabolites were identified. 196 differential metabolites were screened. Key pathways included glycerophospholipid metabolism, pyrimidine metabolism and arachidonic acid metabolism. Correlation analysis indicated that Staphylococcus and Lactococcus were positively associated with amino acid derivatives, while Latilactobacillus and Debaryomyces correlated with organic acids and glycerophospholipids. These findings revealed the potential microbial-metabolic association underlying regional quality differences. They provide support for quality control and traceability of dry-cured beef.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>本研究旨在探討冷藏金鯧魚品質劣化的機制。研究結合 16S rRNA 基因定序與非靶向代謝組學，分析微生物群落演替如何驅動代謝變化。結果顯示，金鯧魚冷藏至第 6 天時顯著腐敗。在貯藏後期，*Psychrobacter*、*Shewanella* 與 *Pseudomonas* 逐漸成為優勢菌群，使代謝焦點自初期的核苷酸降解轉向後期的蛋白質水解與氨基酸代謝。研究鑑定出 50 個潛在腐敗生物標誌物（如組胺、酪胺等生物胺），並發現 *Pseudomonas* 和 *Shewanella* 的豐度與這些生物胺的累積呈正相關，為驅動腐敗的核心菌群。本研究闡明了金鯧魚的腐敗機制，為食品早期變質檢測及靶向抑菌策略提供了科學依據與化學標靶。</t>
+          <t>本研究旨在探討地理區域與加工工藝對雲南傳統乾醃牛肉（尋甸、玉溪、紅河三地）品質、微生物群落及代謝物的影響。研究結合高通量定序與非靶向代謝組學技術，發現不同地區的乾醃牛肉在感官評分與理化性質上存有顯著差異。細菌群落以厚壁菌門和葡萄球菌屬為主；真菌群落中，尋甸和紅河樣品以德巴利酵母屬為主，玉溪樣品則以紅酵母屬與枝孢菌屬為特有優勢菌。代謝組學共鑑定出1320種代謝物，其中196種為差異代謝物，主要涉及甘油磷脂、嘧啶及花生四烯酸代謝通路。關聯分析顯示，葡萄球菌屬和乳球菌屬與氨基酸衍生物呈正相關，而廣義乳桿菌屬與德巴利酵母屬則與有機酸及甘油磷脂密切相關。本研究揭示了微生物與代謝物的關聯性，為乾醃牛肉的品質控制與產地溯源提供了重要科學依據。</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42637441/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42637430/</t>
         </is>
       </c>
     </row>

--- a/papers_database.xlsx
+++ b/papers_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>42665338</t>
+          <t>42666020</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PREVENT 1, a nationwide Swedish infant cohort for longitudinal gut microbiome profiling and early-life health outcomes: cohort profile.</t>
+          <t>Decadal Resampling Reveals Widespread Increases in Soil Microbial Diversity Associated With Nitrogen Deposition.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BMJ open</t>
+          <t>Global change biology</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>253 位嬰兒</t>
+          <t>38 個森林與草地生態系統的土壤樣本（於 2009 年與 2019 年進行跨越十年的重複採樣）</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -509,54 +509,54 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>PREVENT 1 is a nationwide, prospective Swedish infant cohort established to characterise gut microbiome development during the first 2 years of life and to relate microbial trajectories to feeding, infections, growth and everyday well-being. The study integrates repeated infant stool sampling with shotgun metagenomics analysis with aligned parental questionnaires, stool photographs and infant cry recordings collected at three approximately 3-month intervals for each infant. Families were recruited nationwide in Sweden from September 2023 through targeted digital channels. Eligible participants were term-born infants residing in Sweden and aged &lt;1 year at enrolment. Baseline questionnaire data and stool samples were collected from 253 infants. Parents completed questionnaires covering socio-demographic characteristics and health, pregnancy and delivery, postnatal factors, infant environment, feeding and growth, infections and other health outcomes, gastrointestinal symptoms and everyday well-being. Retention was high, with 248 families completing at least one follow-up questionnaire at Phase 2 and 243 at Phase 3. For stool samples, 250 infants provided at least two samples and 241 provided all three. At enrolment, 42.3% of infants were older than 7 months, 73.9% had weight-for-length z-scores in the normal range and exclusive breastfeeding at 4 months was reported for 58.9%. Three-phase sample and questionnaire data collection was completed in December 2024. Future analyses will examine microbiome features, resistome profiles and functional pathways in relation to antibiotic exposure, feeding, growth and infant health outcomes. Subject to ethical approval and participant consent, follow-up may include further stool collection and Swedish register linkage. NCT06285630.</t>
+          <t>Simulated manipulation experiments, such as nitrogen addition to mimic atmospheric nitrogen deposition, are widely used in global change research. However, experimental manipulations may differ from real-world environmental change in their intensity, duration, and co-occurrence, leaving long-term changes in soil microbial communities and soil health insufficiently understood. To address this gap, we resampled soils from 38 forest and grassland ecosystems across eastern China in 2009 and 2019 and assessed microbial taxonomic and functional diversity using shotgun metagenomics. Microbial diversity increased by 17% over the decade, accompanied by clear shifts in community composition. Among the environmental variables considered, nitrogen deposition (~19 kg nitrogen ha-1 year-1 across ecosystems) was the strongest predictor of changes in seven of 12 microbial community metrics. Larger nitrogen deposition was also associated with increased relative abundances of nitrogen-cycling genes and reduced spatial turnover in microbial community composition. These effects were consistent with a potential alleviation of nitrogen limitation and weakening of deterministic community assembly, although these mechanisms could not be directly established. In addition, increases in genes associated with carbon degradation and phosphorus cycling, together with declines in the relative abundances of pathogens, antibiotic resistance genes, and DNA viruses, coincided with the raise of the composite soil health index. Our findings demonstrate widespread decadal increases in soil microbial diversity and soil health across eastern China, with nitrogen deposition emerging as their strongest environmental factor. These results highlight that microbial responses to long-term ambient environmental change can differ markedly from responses inferred from short-term or high-intensity manipulation experiments.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>PREVENT 1 是一項瑞典全國性的前瞻性隊列研究，旨在描繪嬰兒出生後前兩年腸道菌相的發展軌跡，並探討其與餵養方式、感染、生長發育及日常健康指標的關聯。該研究透過縱向追蹤，針對 253 名嬰兒收集糞便樣本，並運用宏基因組學（shotgun metagenomics）技術進行深入分析，同時結合父母問卷、糞便照片及嬰兒哭聲紀錄等多模態數據。此隊列具備高保留率，為期三階段的數據採集已於 2024 年底完成。本研究的核心科學意義在於建立一個大規模的嬰兒菌相參考庫，未來將進一步解析抗生素暴露、飲食攝取對菌相功能路徑與抗藥基因組（resistome）的影響，對於理解早期生命階段的微生物群落如何塑造嬰兒長期健康與免疫發展具有重大貢獻。</t>
+          <t>本研究旨在探討真實世界中長期環境變化（如氮沉降）對土壤微生物群落與健康的影響。研究團隊於2009年與2019年，對中國東部38個森林和草地生態系統進行跨越十年的土壤重複採樣，並利用總體基因體學進行分析。結果顯示，十年間土壤微生物多樣性顯著增加了17%。在多項環境因子中，大氣氮沉降是驅動微生物群落變化的最強預測因子，其與氮循環基因豐度增加及空間周轉率降低密切相關。此外，碳降解與磷循環相關基因增加，而病原體、抗藥性基因及DNA病毒豐度則下降，伴隨土壤綜合健康指數的提升。本研究證實了長期、實際環境變化對微生物的影響，與短期高劑量模擬實驗的結果截然不同，對評估全球變遷下的生態系統健康具有重要科學意義。</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42665338/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42666020/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>42665077</t>
+          <t>42667585</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Metagenomic Characterization of Potential Exposure to Genetic Hazards at the Interface Between Grazing Livestock and Przewalski's Gazelle.</t>
+          <t>Gut Microbiota from Patients with Long COVID Persisting for 2 Years Result in Alterations in Mice that Resemble Post-COVID Symptoms.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Environmental pollution (Barking, Essex : 1987)</t>
+          <t>Probiotics and antimicrobial proteins</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>metagenomics, small genome</t>
+          <t>16S, metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>未提及（摘要中未明確列出具體的檢體總數或個體數量）</t>
+          <t>22 位人類受試者（11 位健康對照組與 11 位長新冠患者）及 ABx 小鼠模型</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -564,39 +564,39 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Livestock and endangered wildlife increasingly share grazing landscapes, yet the sources, mobility-associated contexts, and bacterial hosts of livestock-associated genetic hazards in wildlife microbiomes remain poorly resolved. We analyzed metagenomes from yak, Tibetan sheep, Przewalski's gazelle, and local topsoil within an Acquired Genetic Risk (AGR) conceptual framework integrating genetic hazard burden, compositional source attribution, mobility-associated evidence, and bacterial genomic context. MRGs and Rank I and Rank III ARGs were more abundant in livestock than in Przewalski's gazelle, whereas VF abundance was highest in yak. FEAST attributed approximately 64% of the Przewalski's gazelle resistome composition to the two livestock source profiles, less than 1% to sampled topsoil, and approximately 36% remained unassigned. MGE profiles were associated with ARGs, MRGs, and VFs, while tnpA ranked highest in random forest models and was associated with total ARG abundance (R2 = 0.618). Short-read contigs containing hazard genes and MGE markers provided localized mobility-associated sequence context. Genome-resolved analysis identified distinct bacterial contexts: TS.Bin143, an Escherichia coli MAG from Tibetan sheep, contained ARGs, MRGs, VFs, tnpA, and IS91, whereas PG.Bin275, a Hylemonella sp. MAG from Przewalski's gazelle, contained tnpA. These findings extend wildlife resistome assessment beyond abundance profiling toward source attribution, mobility-associated sequence context, and bacterial host resolution, supporting multilevel surveillance of genetic hazard exposure at livestock-wildlife interfaces.</t>
+          <t>Human gut microbiota (GM) has been identified as a potentially important factor influencing the development of long COVID (LCOVID). The aim of this study was to understand the GM of LCOVID, which lasted for two years, in order to improve public awareness. Human gut microbiota and its metabolites were assessed in a healthy control group (n = 11) (HC) unexposed to SARS-CoV-2 and an LCOVID group (n = 11) in Hainan, China, using Shotgun metagenomics and liquid chromatography-mass spectrometry (LC-MS) of feces. The causal role of the microbiota in LCOVID was further validated by transplanting feces from the subjects into ABx mice using Histopathology and 16 S rRNA sequencing. Fecal microbial diversity was lower in patients with LCOVID compared with that in HC. Pro-inflammatory bacteria such as Streptococcus_salivarius and Streptococcus_parasanguinis increased, whereas anti-inflammatory bacteria such as Faecalibacterium_SGB15346 and Alistipes_onderdonkii decreased. Fecal metabolites from LCOVID were impaired in carbohydrate degradation, indole production, SCFA production, and fatty acid degradation. Transplantation of feces from patients with LCOVID into mice results in lung inflammation, intestinal inflammation, and anxiety. In addition, transplanted mice showed worse outcomes during Klebsiella_pneumoniae infections. Transplanted mice and the key bacteria Streptococcus_salivarius had the same worse outcomes in the D-IBS model by limb binding. GM from patients with LCOVID was altered significantly and sufficiently to promote LCOVID symptoms in mice, suggesting that it may be a potential therapeutic target.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>本研究針對放牧家畜與瀕危物種普氏原羚（Przewalski's gazelle）共享棲地所帶來的基因危害（如抗藥性基因 ARGs、金屬抗性基因 MRGs 及毒力因子 VFs）進行宏基因組學分析。研究發現家畜攜帶的基因危害豐度高於野生原羚，且定量來源歸因分析顯示，原羚體內約 64% 的抗藥性組成源自家畜，而非土壤。透過基因組解析，研究鑑定出特定的細菌宿主（如藏羊體內的 *E. coli* 及原羚體內的 *Hylemonella* sp.），揭示了移動遺傳因子（MGEs，特別是 *tnpA*）在傳播這些遺傳危害中的關鍵作用。本研究建立了一套評估野生動物抗藥體（resistome）的架構，不僅提升了來源追蹤的精確度，更為監測人畜共通疾病風險及制定野生動物保育策略提供了重要的科學依據。</t>
+          <t>本研究旨在探討長新冠（Long COVID）患者持續兩年的腸道菌相變化及其致病機制。研究透過宏基因組學與液相層析質譜儀（LC-MS）分析人類糞便樣本，發現長新冠患者的腸道微生物多樣性降低，促發炎細菌（如 Streptococcus salivarius）增加，而具抗發炎功能的細菌（如 Faecalibacterium）則減少；同時，碳水化合物降解及短鏈脂肪酸代謝路徑受到抑制。實驗將患者糞便移植至抗生素處理小鼠後，成功誘發了肺部與腸道發炎及焦慮行為，且小鼠對肺炎克雷伯氏菌的抵抗力顯著下降。這些發現證實了長新冠患者的腸道菌群失調具有直接致病潛力，足以在動物模型中重現長新冠相關症狀，為未來開發針對腸道菌群的診斷標記與治療策略提供了關鍵的科學依據。</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42665077/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42667585/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>42664954</t>
+          <t>42667435</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lactobacillus salivarius potentiates gastrointestinal cancer immunotherapy through its metabolite chenodeoxycholic acid.</t>
+          <t>From traditional retting to precision bioprocessing: microbial ecology, enzymatic selectivity, and systems biology of jute retting.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cell reports. Medicine</t>
+          <t>Antonie van Leeuwenhoek</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -606,12 +606,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>metagenomics, metabolomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>278 位消化道癌症患者</t>
+          <t>未提及（此文為綜述論文，非原始實驗研究）</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -619,54 +619,54 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Immune checkpoint inhibitor therapy has improved gastrointestinal (GI) cancer management; however, many patients exhibit resistance. Although gut microbiota influences immunotherapeutic responses, the underlying mechanisms remain unclear. Metagenomic analysis of 278 GI cancer patients reveals that Lactobacillus salivarius (L. salivarius) is enriched in responders and enhances anti-PD-1 efficacy in syngeneic tumor models by increasing the infiltration of antitumor M1-like macrophages and CD8+ T cells and enhancing CD8+ T cell effector function. L. salivarius-associated chenodeoxycholic acid (CDCA) is identified as a functional metabolite. CDCA recapitulates the antitumor effects of L. salivarius and significantly improves anti-PD-1 efficacy in vivo, an effect attenuated by depleting macrophages or CD8+ T cells. Mechanistically, CDCA-induced reactive oxygen species triggers immunogenic cell death in tumor cells and polarizes macrophages toward antitumor M1 phenotype, activating CD8+ T cell antitumor immunity. These findings identify L. salivarius and its associated metabolite CDCA as a promising adjuvant for potentiating immunotherapy in GI cancers.</t>
+          <t>Jute is one of the world's most important lignocellulosic fibre crops, yet its commercial value remains highly dependent on retting, a biologically mediated fibre extraction process still largely governed by empirical practices and variable environmental conditions. Recent advances in microbial ecology, enzymology, molecular biology, and bioprocess engineering have transformed retting from a traditional post-harvest operation into a controllable lignocellulosic bioconversion process. This review synthesizes current understanding of the structural organization of jute bast fibres, selective degradation of plant cell-wall polymers, microbial succession, extracellular enzyme networks, and physicochemical factors regulating fibre liberation. It highlights the coordinated interactions among cell-wall architecture, microbial communities, enzyme specificity, and environmental conditions that collectively determine retting efficiency and fibre quality. Emerging precision retting strategies, including defined microbial consortia, enzyme-assisted retting, ribbon retting, controlled processing systems, and water-efficient technologies, are critically evaluated for their potential to improve process reproducibility, fibre quality, and environmental sustainability. The review also examines metagenomics, metatranscriptomics, metaproteomics, metabolomics, systems biology, and artificial intelligence as enabling technologies for microbiome-guided process monitoring, predictive modelling, and digital decision support. Furthermore, this review discusses the integration of precision retting within circular bioeconomy frameworks through resource recovery, pollution mitigation, climate-resilient processing, and lignocellulosic biorefineries. Key knowledge gaps, including limited understanding of microbial interactions, lack of standardized microbial consortia, insufficient process-monitoring tools, fragmented multi-omics datasets, and challenges in industrial scale-up, are identified. Overall, this review presents a systems-level framework for advancing jute retting toward standardized, predictive, and environmentally sustainable precision bioprocessing.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>本研究旨在探討腸道菌群對消化道癌症免疫檢查點抑制劑（如抗 PD-1 療法）治療反應的影響。透過對 278 位患者進行宏基因組學分析，發現唾液乳桿菌（*Lactobacillus salivarius*）在治療反應佳的患者中顯著富集。實驗證實該菌株能增強抗腫瘤 M1 型巨噬細胞與 CD8+ T 細胞的浸潤，進而提升抗 PD-1 療法的功效。研究進一步鑑定出其關鍵代謝物——鵝去氧膽酸（CDCA），其能誘導腫瘤細胞產生免疫原性細胞死亡，並促進巨噬細胞極化為 M1 型，啟動 CD8+ T 細胞的抗腫瘤免疫反應。此發現指出 *L. salivarius* 及其代謝物 CDCA 有望成為輔助治療消化道癌症的新型藥物，為克服臨床免疫治療耐藥性提供了重要的科學依據。</t>
+          <t>本研究針對黃麻脫膠（retting）製程進行系統性回顧，旨在推動傳統經驗式工法轉向精準生物加工。內容探討了黃麻纖維的結構特徵、微生物演替機制、胞外酵素網以及環境因子如何協同影響纖維分離效率與品質。文中評估了多種新興策略，如定義明確的微生物群系應用、酵素輔助處理及水資源高效循環技術。此外，透過整合多體學（基因體、轉錄體、蛋白質體、代謝體）、系統生物學與人工智慧，提出了一套數位決策輔助框架，以解決傳統工藝缺乏標準化、程序變異大及環境污染等問題。總體而言，本研究強調將黃麻脫膠轉型為可預測的精準生物加工，對於提升產業生產力、促進循環生物經濟及環境永續發展具有顯著的科學意義與指導價值。</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42664954/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42667435/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>42664608</t>
+          <t>42665998</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Application-dependent effects of tea waste biochar on PFAS mobility and N2O and CH4 emissions in agricultural soil.</t>
+          <t>Agathobacter rectalis suppresses colorectal tumorigenesis via an epigallocatechin-SREBF2 axis controlling cholesterol metabolism.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Waste management (New York, N.Y.)</t>
+          <t>Gut microbes</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>未提及（原文僅提及實驗處理組別與植栽盆數，未標示具體檢體總數）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -674,12 +674,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Per- and polyfluoroalkyl substances (PFAS) in agricultural soils can migrate into crops and may alter soil greenhouse gas emissions, yet remediation strategies rarely address these risks simultaneously. This study evaluated tea waste biochar (TWB) produced at 400, 500, and 600 °C and applied at 5-20 g per pot by whole-soil mixing or surface-layer placement in a simulated PFAS-contaminated soil-leachate-plant system. Perfluorooctane sulfonate (PFOS) and perfluorooctanoic acid (PFOA) distributions, nitrous oxide (N2O) and methane (CH4) fluxes, and microbial responses were examined. TWB produced at 500 °C showed the most favorable combination of pore accessibility, surface hydrophobicity, and interfacial charge, with material-associated PFOS and PFOA enrichments of 0.12 and 0.57 μg/g, respectively. Whole-soil mixing with TWB-500 lowered soil and leachate PFAS levels and reduced PFAS concentrations in plant shoots by approximately 36% relative to the contaminated control. TWB treatments also reduced cumulative N2O emissions and enhanced net CH4 uptake. Metagenomic analysis showed lower relative abundances of genes associated with nitrogen fixation, ammonia oxidation, and several N2O-producing pathways, whereas CH4-cycling genes responded differently to the two application methods. Organic fluorine transformation genes were not enriched, indicating that PFAS control mainly resulted from physicochemical retention rather than enhanced microbial defluorination. Overall, TWB-500 can integrate PFAS stabilization with greenhouse gas management, but the optimal placement depends on the remediation objective: whole-soil mixing favors PFAS immobilization, whereas surface-layer application provides greater greenhouse gas mitigation.</t>
+          <t>Beneficial effects of the gut commensal Agathobacter rectalis (Ar) are reported in diseases, yet its role in colorectal cancer (CRC) remains unclear. Here, metagenomic analysis revealed consistent fecal Ar depletion across CRC cohorts. In Apc min/+ mice, Ar inhibited colon tumorigenesis, reducing tumor number and volume versus E. coli and PBS controls. LC-MS/MS metabolomics showed decreased fecal cholesterol and altered lipid/cholesterol pathways after Ar treatment. In vitro, Ar-conditioned medium suppressed CRC cell growth, clonogenicity, migration, and cell cycle progression. LC-MS/MS identified (-)-epigallocatechin (EGC) as an Ar-derived metabolite absent in control bacteria. EGC recapitulated Ar-mediated anti-CRC effects in vitro and in vivo, with metabolic changes linked to lipid/cholesterol pathways. Transcriptomics showed that EGC suppressed SREBP signaling, cholesterol metabolism, and MAPK pathways. Mechanistically, EGC reduced nuclear SREBF2 and its transcriptional activity, downregulated cholesterol synthesis/metabolism genes, including FDPS and PCSK9, and suppressed MAPK signaling. Molecular docking suggested that EGC may bind pSREBF2 or SCAP. Cellular thermal shift assay revealed that EGC interacts with and stabilizes pSREBF2, but not SCAP. Co-immunoprecipitation demonstrated that EGC reduces pSREBF2-SCAP interaction, thereby inhibiting SCAP-mediated SREBF2 cleavage activation. Together, these findings define an Ar-EGC microbe-metabolite axis and support Ar/EGC-based interventions targeting cholesterol metabolism in CRC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>本研究探討茶葉廢棄物生物炭（TWB）應用於農地土壤時，對全氟烷基物質（PFAS）遷移及溫室氣體（N2O、CH4）排放的雙重影響。研究發現，經 500 °C 熱裂解之生物炭（TWB-500）因具備最佳的孔隙度與表面特性，能有效吸附土壤中的 PFOS 與 PFOA，並透過全土混拌法使植株體內的 PFAS 濃度降低約 36%。此外，TWB 處理能顯著減少 N2O 排放並促進土壤對 CH4 的吸收。總體基因體分析顯示，生物炭降低了氮循環相關功能基因的豐度，證實 PFAS 的移除主要歸因於物理化學吸附，而非微生物脫氟作用。本研究結論指出，透過調整生物炭施用方式（全土混拌 vs. 表面覆蓋），可針對 PFAS 穩定化或溫室氣體減排進行最適化的農地管理，具備顯著環境應用價值。</t>
+          <t>本研究探討腸道共生菌 *Agathobacter rectalis* (Ar) 在大腸直腸癌 (CRC) 中的作用。研究發現，CRC 患者體內 Ar 顯著減少，而補充 Ar 能抑制小鼠大腸腫瘤生長。代謝組學分析證實，Ar 產生的代謝物 (-)-表沒食子兒茶素 (EGC) 為關鍵抑癌物質。機制上，EGC 透過直接結合並穩定 pSREBF2，阻斷其與 SCAP 的交互作用，進而抑制 SREBF2 活化，下調膽固醇合成與 MAPK 訊號通路，進而抑制 CRC 細胞生長與遷移。本研究首次揭示了 Ar-EGC「微生物-代謝物」軸對宿主膽固醇代謝的調控機制，為 CRC 的臨床預防與治療提供了全新的靶點與策略。</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -689,29 +689,29 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42664608/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42665998/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>42664252</t>
+          <t>42664608</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Proteobacteria with chemosynthetic potential are highly prevalent in the gills of Hypoplectrus reef fishes.</t>
+          <t>Application-dependent effects of tea waste biochar on PFAS mobility and N2O and CH4 emissions in agricultural soil.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PLoS genetics</t>
+          <t>Waste management (New York, N.Y.)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>353 個魚鰓檢體</t>
+          <t>未提及（僅提及不同溫度的 TWB 與不同處理方式的模擬系統，未提供具體的生物樣品或實驗重複次數）</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -729,12 +729,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Fishes host a diverse microbiome in their gills, but a broad characterization of this microbiome at the metagenomic level is lacking. Here, we apply genome-resolved metagenomics to the gills of the hamlets (Hypoplectrus spp), a group of reef fishes from the Greater Caribbean. The analysis of 353 gill samples from 15 hamlet species collected at eight locations over 13 years revealed a stark contrast between the gill microbiota and reef water microbial communities, indicating a distinct and specific gill microbiome. A total of 70 gill-associated metagenome-assembled genomes (MAGs) were recovered. These MAGs belong to 17 lineages, most of which are novel. They relate to known fish gill pathogens, fish gut microbes, free-living and biofilm-associated taxa, indicating that the gill microbiome was assembled from a collection of distinct eco-evolutionary trajectories. The MAGs harbor diverse metabolic modules, involved notably in nitrogen cycling, antibiotic production and biofilm formation, revealing a highly dynamic microbial ecosystem. One lineage in the Burkholderiaceae family was outstandingly prevalent across fish host species, sampling locations and years. Its genome encoded complete metabolic modules for carbon fixation and sulfur oxidation, indicating chemosynthetic potential. To the best of our knowledge, this is the first line of evidence that fishes may host sulfur-oxidizing chemosynthetic bacteria in their gills. The functional significance of this chemosynthetic potential for the fish host or other members of the gill microbiome remains to be established. The high prevalence of this lineage allowed to build a pangenome. It revealed large-scale geographic structure (western Caribbean, eastern Caribbean and Gulf of Mexico), which parallels the phylogenomic pattern observed in the hamlets. Overall, our findings point to complex fish host-microbe and microbe-microbe eco-evolutionary interactions in the gills that may influence fish physiology, homeostasis and immune response.</t>
+          <t>Per- and polyfluoroalkyl substances (PFAS) in agricultural soils can migrate into crops and may alter soil greenhouse gas emissions, yet remediation strategies rarely address these risks simultaneously. This study evaluated tea waste biochar (TWB) produced at 400, 500, and 600 °C and applied at 5-20 g per pot by whole-soil mixing or surface-layer placement in a simulated PFAS-contaminated soil-leachate-plant system. Perfluorooctane sulfonate (PFOS) and perfluorooctanoic acid (PFOA) distributions, nitrous oxide (N2O) and methane (CH4) fluxes, and microbial responses were examined. TWB produced at 500 °C showed the most favorable combination of pore accessibility, surface hydrophobicity, and interfacial charge, with material-associated PFOS and PFOA enrichments of 0.12 and 0.57 μg/g, respectively. Whole-soil mixing with TWB-500 lowered soil and leachate PFAS levels and reduced PFAS concentrations in plant shoots by approximately 36% relative to the contaminated control. TWB treatments also reduced cumulative N2O emissions and enhanced net CH4 uptake. Metagenomic analysis showed lower relative abundances of genes associated with nitrogen fixation, ammonia oxidation, and several N2O-producing pathways, whereas CH4-cycling genes responded differently to the two application methods. Organic fluorine transformation genes were not enriched, indicating that PFAS control mainly resulted from physicochemical retention rather than enhanced microbial defluorination. Overall, TWB-500 can integrate PFAS stabilization with greenhouse gas management, but the optimal placement depends on the remediation objective: whole-soil mixing favors PFAS immobilization, whereas surface-layer application provides greater greenhouse gas mitigation.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>本研究針對加勒比海 15 種雀鯛科魚類（Hypoplectrus spp.）進行基因體解析宏基因組學（genome-resolved metagenomics）分析，旨在探討其魚鰓微生物群落結構。研究共分析 353 個樣本，重建了 70 個宏基因組組裝基因組（MAGs），發現魚鰓微生物群落與周邊海水環境存在顯著差異，具有高度特異性。最關鍵的發現是鑑定出一種廣泛分佈於各物種與地理區域的伯克氏菌科（Burkholderiaceae）菌株，該菌株具備碳固定與硫氧化代謝路徑，暗示魚鰓可能存在化能合成微生物。此研究首次揭示魚類鰓部潛在的化能合成共生關係，並證實微生物群落結構與宿主魚類的地理演化路徑具有高度相關性，為理解魚類生理穩態及免疫反應的微生物機制提供了重要的科學基礎。</t>
+          <t>本研究探討茶葉廢棄物生物炭（TWB）在處理農業土壤 PFAS 污染及溫室氣體排放的應用價值。結果顯示，經 500°C 處理的 TWB 因具備最佳的孔隙與表面特性，在全土混合施用下，可顯著降低土壤與滲濾液中的 PFOS 與 PFOA 濃度，並使植物地上部的 PFAS 累積量下降約 36%。此外，TWB 處理能減少一氧化二氮（N2O）排放並增進甲烷（CH4）吸收。宏基因組分析指出，此效益主要源於生物炭的物理化學吸附，而非微生物脫氟作用。本研究確立了生物炭作為同時緩解 PFAS 污染與氣候變遷的潛力，並強調施用策略應視目標而定：全土混合有利於固定 PFAS，而表面施用則在溫室氣體減排上表現更佳。</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -744,29 +744,29 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42664252/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42664608/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>42663694</t>
+          <t>42663459</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Comparative Analysis of Different Anodic Inoculum in Microbial Fuel Cell for Efficient Methylene Blue Dye Degradation.</t>
+          <t>Clinical application of BALF-mNGS in immunocompromised and immunocompetent patients with suspected invasive pulmonary aspergillosis: differentiating infection from colonization, microbiome features, and clinical impact.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Current microbiology</t>
+          <t>Microbiology spectrum</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>178 位受試者（免疫功能低下組 n=77，免疫功能健全組 n=101）</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -784,12 +784,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>This study investigates three different inoculum sources in dual-chamber microbial fuel cells (MFCs), such as Marine Sediment (MFC-MS), Estuary Sediment (MFC-ES), and Anaerobic Sludge (MFC-AS), to compare the efficacy for Methylene Blue (MB) dye degradation and electricity generation. All the MFCs were operated under identical conditions in batch mode using synthetic wastewater containing 3000 mg/L COD made using sodium acetate. The electrochemical study reveals that MFC inoculated with marine sediment achieved maximum power density of 35 mW/m² followed by anaerobic sludge (31 mW/m²) and estuary sediment (25 mW/m²). Statistical analysis was employed to evaluate performance differences among the systems and to support result interpretation. Maximum COD removal efficiency of 75% was obtained by MFC-AS, and coulombic efficiency (CE) was higher for MFC-MS with 25%. Maximum decolorization efficiency was noted in MFC with anaerobic sludge, which obtained 96% decolorization over 96 h. Comparative and trend-based statistical evaluation confirmed the superior treatment performance of MFC-assisted systems. The phytotoxicity study revealed that the toxicity effect of dye wastewater was reduced to its maximum after treatment in the MFC system. The dominant performance of MFC-MS is due to the efficiency of the major electrogenic bacteria concentrated in the inoculum. The functional annotation using the data obtained from metagenomics reveals the presence and role of various enzymes and pathways involved.</t>
+          <t>Invasive pulmonary aspergillosis (IPA) not only causes high morbidity and mortality, especially in immunocompromised patients, but also occurs in immunocompetent individuals. Differentiating infection from colonization is challenging, and bronchoalveolar lavage fluid metagenomic next-generation sequencing (BALF-mNGS) may aid diagnosis, microbiome profiling, and clinical assessment. We retrospectively analyzed patients with suspected IPA who underwent BALF-mNGS between December 2021 and March 2025. Patients were classified by immune status. IPA diagnosis was based on EORTC/MSGERC 2020 criteria in immunocompromised patients, while immunocompetent cases were adjudicated using an integrated clinical, radiological, and microbiological assessment. A total of 178 patients were finally included and classified according to immune status into an immunocompromised group (n = 77) and an immunocompetent group (n = 101). Aspergillus_ reads per ten million (RPTM) values were significantly higher in infection versus colonization cases in both groups, with optimal cut-offs of 24 (gray zone: 22-60) for the immunocompromised group and 33 (gray zone: 17-48) for the immunocompetent group. Microbiome analysis revealed distinct community structures between infection and colonization groups, with Aspergillus remaining significantly enriched after false discovery rate (FDR) correction in immunocompromised patients, while no taxa remained significant after FDR correction in immunocompetent patients. BALF-mNGS guided antifungal therapy, avoiding unnecessary treatment in colonized patients, and higher Aspergillus_RPTM was associated with increased 90-day mortality in immunocompromised patients. BALF-mNGS may accurately distinguish Aspergillus infection from colonization and reveal microbial shifts, particularly in immunocompromised patients. It can guide targeted antifungal therapy, avoid unnecessary treatment, and higher Aspergillus_RPTM was associated with 90-day mortality in immunocompromised patients, suggesting its potential value for risk stratification.IMPORTANCEBALF-mNGS with quantitative thresholds improves differentiation between Aspergillus infection and colonization. It reveals distinct lung microbiome patterns under different immune statuses, extending beyond simple pathogen detection. Higher Aspergillus burden is associated with worse outcomes in immunocompromised patients, suggesting its potential value for risk stratification.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>本研究旨在評估三種不同陽極接種源（海洋沉積物、河口沉積物及厭氧污泥）在微生物燃料電池（MFC）中，處理亞甲基藍（MB）染料廢水的效能與產電表現。研究發現，使用海洋沉積物接種的 MFC 具有最高的功率密度（35 mW/m²），而厭氧污泥則在脫色效率上表現最佳，96 小時內達 96% 的脫色率。此外，透過宏基因組學（metagenomics）分析，研究確認了接種源中電活性細菌的功能與酵素路徑，證明 MFC 技術能有效降解染料並降低廢水的植物毒性。此研究顯示，選擇合適的微生物接種源對於優化 MFC 系統的污染物降解與能量回收具備顯著科學意義與應用潛力。</t>
+          <t>本研究探討支氣管肺泡灌洗液總體基因體定序（BALF-mNGS）在診斷侵襲性肺麴菌病（IPA）中的應用價值。研究核心在於區分「感染」與「定殖」，並分析不同免疫狀態下的肺部微生物特徵。結果顯示，透過計算麴菌屬的單位定序讀數（RPTM），可有效建立臨床判斷閾值，且該數值與免疫功能低下患者的 90 天死亡率高度相關。此外，mNGS 分析揭示了感染與定殖在微生物群落結構上的差異。此技術不僅能精準區分病原與菌群，還能避免不必要的抗真菌藥物濫用，並為免疫功能低下患者提供重要的預後分層參考，具備高度臨床應用潛力。</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42663694/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42663459/</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1 個 40 ml 淡水湖泊水樣</t>
+          <t>1 個水樣樣本（40 ml）</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -844,7 +844,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>本研究針對美國亞利桑那州弗拉格斯塔夫附近一處淡水湖泊進行病毒宏基因體（Viral metagenomics）分析。研究人員透過對 40 毫升水樣的深度測序與生物資訊分析，成功組裝出 295 個環狀病毒基因體序列。在分類學鑑定中，發現其中 126 個基因體屬於 CRESS 型 DNA 病毒門（Cressdnaviricota），另 169 個則屬於噬菌體病毒門（Phixviricota）。本研究不僅擴展了環境病毒組的資料庫，亦有助於了解淡水生態系統中病毒的多樣性與演化關係，為未來探討病毒在微生物群落中的生態角色提供重要基礎。</t>
+          <t>本研究旨在透過病毒宏基因組學（viral metagenomics）技術，分析採集自美國亞利桑那州弗拉格斯塔夫（Flagstaff）附近一處淡水湖泊的 40 毫升水樣。研究成功鑑定出 295 個環狀病毒基因體序列，其中包含 126 個 Cressdnaviricota 門與 169 個 Phixviricota 門的病毒成員。此研究擴展了我們對淡水生態系統中病毒多樣性的認知，特別是針對這兩個特定病毒門類的基因體結構提供了基礎數據，有助於進一步解析環境病毒在水生生態系中的演化關係與功能角色。</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -861,22 +861,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>42663459</t>
+          <t>42663694</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Clinical application of BALF-mNGS in immunocompromised and immunocompetent patients with suspected invasive pulmonary aspergillosis: differentiating infection from colonization, microbiome features, and clinical impact.</t>
+          <t>Comparative Analysis of Different Anodic Inoculum in Microbial Fuel Cell for Efficient Methylene Blue Dye Degradation.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Microbiology spectrum</t>
+          <t>Current microbiology</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>178 位患者（包含 77 位免疫功能低下患者及 101 位免疫功能正常患者）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -894,12 +894,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Invasive pulmonary aspergillosis (IPA) not only causes high morbidity and mortality, especially in immunocompromised patients, but also occurs in immunocompetent individuals. Differentiating infection from colonization is challenging, and bronchoalveolar lavage fluid metagenomic next-generation sequencing (BALF-mNGS) may aid diagnosis, microbiome profiling, and clinical assessment. We retrospectively analyzed patients with suspected IPA who underwent BALF-mNGS between December 2021 and March 2025. Patients were classified by immune status. IPA diagnosis was based on EORTC/MSGERC 2020 criteria in immunocompromised patients, while immunocompetent cases were adjudicated using an integrated clinical, radiological, and microbiological assessment. A total of 178 patients were finally included and classified according to immune status into an immunocompromised group (n = 77) and an immunocompetent group (n = 101). Aspergillus_ reads per ten million (RPTM) values were significantly higher in infection versus colonization cases in both groups, with optimal cut-offs of 24 (gray zone: 22-60) for the immunocompromised group and 33 (gray zone: 17-48) for the immunocompetent group. Microbiome analysis revealed distinct community structures between infection and colonization groups, with Aspergillus remaining significantly enriched after false discovery rate (FDR) correction in immunocompromised patients, while no taxa remained significant after FDR correction in immunocompetent patients. BALF-mNGS guided antifungal therapy, avoiding unnecessary treatment in colonized patients, and higher Aspergillus_RPTM was associated with increased 90-day mortality in immunocompromised patients. BALF-mNGS may accurately distinguish Aspergillus infection from colonization and reveal microbial shifts, particularly in immunocompromised patients. It can guide targeted antifungal therapy, avoid unnecessary treatment, and higher Aspergillus_RPTM was associated with 90-day mortality in immunocompromised patients, suggesting its potential value for risk stratification.IMPORTANCEBALF-mNGS with quantitative thresholds improves differentiation between Aspergillus infection and colonization. It reveals distinct lung microbiome patterns under different immune statuses, extending beyond simple pathogen detection. Higher Aspergillus burden is associated with worse outcomes in immunocompromised patients, suggesting its potential value for risk stratification.</t>
+          <t>This study investigates three different inoculum sources in dual-chamber microbial fuel cells (MFCs), such as Marine Sediment (MFC-MS), Estuary Sediment (MFC-ES), and Anaerobic Sludge (MFC-AS), to compare the efficacy for Methylene Blue (MB) dye degradation and electricity generation. All the MFCs were operated under identical conditions in batch mode using synthetic wastewater containing 3000 mg/L COD made using sodium acetate. The electrochemical study reveals that MFC inoculated with marine sediment achieved maximum power density of 35 mW/m² followed by anaerobic sludge (31 mW/m²) and estuary sediment (25 mW/m²). Statistical analysis was employed to evaluate performance differences among the systems and to support result interpretation. Maximum COD removal efficiency of 75% was obtained by MFC-AS, and coulombic efficiency (CE) was higher for MFC-MS with 25%. Maximum decolorization efficiency was noted in MFC with anaerobic sludge, which obtained 96% decolorization over 96 h. Comparative and trend-based statistical evaluation confirmed the superior treatment performance of MFC-assisted systems. The phytotoxicity study revealed that the toxicity effect of dye wastewater was reduced to its maximum after treatment in the MFC system. The dominant performance of MFC-MS is due to the efficiency of the major electrogenic bacteria concentrated in the inoculum. The functional annotation using the data obtained from metagenomics reveals the presence and role of various enzymes and pathways involved.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>本研究旨在探討支氣管肺泡灌洗液總體基因體定序（BALF-mNGS）在區分侵襲性肺麴菌病（IPA）感染與定殖的臨床應用價值。研究分析了 178 名疑似 IPA 患者，根據免疫狀態進行分組，並利用麴菌每千萬定序讀數（RPTM）作為指標。結果顯示，BALF-mNGS 能有效區分感染與定殖，並為免疫功能低下與正常患者建立特定的最佳判定閾值。微生物體分析揭示，在免疫功能低下患者中，麴菌屬在感染組呈現顯著富集，且高 RPTM 值與 90 天死亡率高度相關。本研究證實 BALF-mNGS 不僅能優化抗真菌藥物的精準投藥、避免過度治療，更可作為免疫功能低下患者風險分層的有效工具，具備顯著的臨床轉譯潛力。</t>
+          <t>本研究旨在探討三種不同微生物接種源（海洋沉積物、河口沉積物及厭氧污泥）對微生物燃料電池（MFC）處理亞甲基藍（MB）染料廢水效能的影響。實驗結果顯示，以海洋沉積物作為接種源的 MFC 在產電性能上表現最佳（35 mW/m²），而厭氧污泥接種組則在染料脫色率（96%）與 COD 去除率（75%）上表現最為突出。透過宏基因組學（metagenomics）分析，研究證實了電活性細菌群落中關鍵酵素與代謝路徑的存在，進一步解釋了不同接種源在電子轉移及染料降解過程中的功能差異。本研究證實 MFC 系統在處理染料廢水方面具有極高的應用潛力，且處理後的廢水毒性顯著降低，為生物電化學修復技術提供了科學數據支撐，對工業染料廢水處理具有重要的環境應用價值。</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -909,29 +909,29 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42663459/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42663694/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>42660108</t>
+          <t>42664252</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Group C Orthobunyavirus Infection in a Patient from the Amazon Putumayo Region of Colombia During an Oropouche Fever Epidemic.</t>
+          <t>Proteobacteria with chemosynthetic potential are highly prevalent in the gills of Hypoplectrus reef fishes.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>The American journal of tropical medicine and hygiene</t>
+          <t>PLoS genetics</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1 個臨床檢體（單一病例報告）</t>
+          <t>353 個魚鰓檢體</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -949,54 +949,54 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Orthobunyaviruses, one of the largest and most diverse genera of viruses, include numerous reassortant viruses and present diagnostic challenges due to similar clinical presentations with other arboviral infections. The detection and isolation of a group C orthobunyavirus from a patient with acute febrile illness from Puerto Ospina, Putumayo Department, Colombia during the 2023-2024 Latin American Oropouche fever regional outbreaks are reported in the present study. Using a vertebrate virus-focused metagenomics sequencing approach with VirCapSeq-VERT, a virus related to the Caraparu complex was identified, and a virus isolate was obtained. Although limited to a single case and without serological or longitudinal clinical confirmation, these findings underscore the value of unbiased molecular approaches for unresolved febrile illness diagnosis in endemic settings such as the Amazon basin.</t>
+          <t>Fishes host a diverse microbiome in their gills, but a broad characterization of this microbiome at the metagenomic level is lacking. Here, we apply genome-resolved metagenomics to the gills of the hamlets (Hypoplectrus spp), a group of reef fishes from the Greater Caribbean. The analysis of 353 gill samples from 15 hamlet species collected at eight locations over 13 years revealed a stark contrast between the gill microbiota and reef water microbial communities, indicating a distinct and specific gill microbiome. A total of 70 gill-associated metagenome-assembled genomes (MAGs) were recovered. These MAGs belong to 17 lineages, most of which are novel. They relate to known fish gill pathogens, fish gut microbes, free-living and biofilm-associated taxa, indicating that the gill microbiome was assembled from a collection of distinct eco-evolutionary trajectories. The MAGs harbor diverse metabolic modules, involved notably in nitrogen cycling, antibiotic production and biofilm formation, revealing a highly dynamic microbial ecosystem. One lineage in the Burkholderiaceae family was outstandingly prevalent across fish host species, sampling locations and years. Its genome encoded complete metabolic modules for carbon fixation and sulfur oxidation, indicating chemosynthetic potential. To the best of our knowledge, this is the first line of evidence that fishes may host sulfur-oxidizing chemosynthetic bacteria in their gills. The functional significance of this chemosynthetic potential for the fish host or other members of the gill microbiome remains to be established. The high prevalence of this lineage allowed to build a pangenome. It revealed large-scale geographic structure (western Caribbean, eastern Caribbean and Gulf of Mexico), which parallels the phylogenomic pattern observed in the hamlets. Overall, our findings point to complex fish host-microbe and microbe-microbe eco-evolutionary interactions in the gills that may influence fish physiology, homeostasis and immune response.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>本研究針對哥倫比亞亞馬遜地區一名急性發燒患者進行病毒分析。在 2023-2024 年奧羅普切熱（Oropouche fever）流行期間，研究人員透過標靶富集宏基因組測序技術（VirCapSeq-VERT），成功鑑定並分離出一株屬於 C 群正布尼亞病毒（Orthobunyavirus），其親緣關係接近 Caraparu 複合群。此發現顯示在臨床症狀與常見蟲媒病毒重疊的地區，利用宏基因組學等非偏向性分子檢測技術，對於釐清不明原因發燒病例具有高度診斷價值，能有效提升對新興或罕見病毒感染的監測能力，對區域防疫與公共衛生決策具重要科學意義。</t>
+          <t>本研究透過宏基因組解析技術，深入探討加勒比海笛鯛（*Hypoplectrus* spp.）魚鰓微生物群落。研究分析了來自 15 個物種、共 353 個魚鰓樣本，成功組裝出 70 個宏基因組組裝基因體（MAGs）。研究發現魚鰓微生物群落具有高度特異性，區別於周遭海域環境。特別是 Burkholderiaceae 科下的一個支系，在不同魚種、地點與年份間皆高度盛行，且基因體編碼了完整的碳固定與硫氧化代謝路徑，展現出化能合成潛力，這是學界首次證實魚類魚鰓可能共生此類細菌。此發現揭示了魚鰓生態系統中複雜的微生物交互作用，這些細菌不僅參與氮循環與抗生素生產，其族群結構更與宿主魚類的地理分布演化高度相關，為理解魚類生理穩態與免疫反應提供了全新的科學視角。</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42660108/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42664252/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>42656127</t>
+          <t>42664954</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Development and Validation of Mock Communities as Quality Control Materials for Clinical Metagenomic Next-Generation Sequencing.</t>
+          <t>Lactobacillus salivarius potentiates gastrointestinal cancer immunotherapy through its metabolite chenodeoxycholic acid.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Annals of laboratory medicine</t>
+          <t>Cell reports. Medicine</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>25 次重複分析（針對開發出的四種模擬群落進行評估）</t>
+          <t>278 位腸胃道癌症患者</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -1004,54 +1004,54 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Metagenomic next-generation sequencing (NGS) enables comprehensive detection of a broad spectrum of microorganisms. However, its clinical application faces two major challenges: the development of appropriate microbiome-based biomarkers and the need to ensure the reproducibility and quality of the microbiome analytical workflow. Therefore, we developed four types of bead-based mock communities as standard materials for microbiome analysis and evaluated potential experimental biases arising from nucleic acid extraction and sequence analysis. Mock communities were assembled from strains isolated from clinical specimens and selected considering Gram reaction, taxonomic phylogeny, and prevalence, and processed into frozen beads. The communities were analyzed using shotgun whole-metagenome sequencing. The effect of DNA extraction kit choice was evaluated using the Thermo Fisher Scientific MagMAX Microbiome Ultra Nucleic Acid Isolation Kit and Qiagen PowerSoil Kit. Four types of mock communities comprising 26 species commonly found in the gastrointestinal tract, respiratory tract, skin, and genital tract plus cerebrospinal fluid were developed considering Gram reaction, GC content, and phylogenetic distribution. Across 25 repeated analyses, the median repeatability of each taxon was 18.97% (range, 2.87%-107.38%), while within-laboratory imprecision was 26.22% (range, 9.26%-153.83%). Repeatability remained below 10% for most dominant taxa with relative abundances &gt;20%. The choice of DNA extraction kit had a significant effect on taxonomic distributions. Microbial mock communities are essential QC materials for clinical metagenomic NGS. Further studies are needed to minimize variability and establish a standardized protocol for clinical implementation.</t>
+          <t>Immune checkpoint inhibitor therapy has improved gastrointestinal (GI) cancer management; however, many patients exhibit resistance. Although gut microbiota influences immunotherapeutic responses, the underlying mechanisms remain unclear. Metagenomic analysis of 278 GI cancer patients reveals that Lactobacillus salivarius (L. salivarius) is enriched in responders and enhances anti-PD-1 efficacy in syngeneic tumor models by increasing the infiltration of antitumor M1-like macrophages and CD8+ T cells and enhancing CD8+ T cell effector function. L. salivarius-associated chenodeoxycholic acid (CDCA) is identified as a functional metabolite. CDCA recapitulates the antitumor effects of L. salivarius and significantly improves anti-PD-1 efficacy in vivo, an effect attenuated by depleting macrophages or CD8+ T cells. Mechanistically, CDCA-induced reactive oxygen species triggers immunogenic cell death in tumor cells and polarizes macrophages toward antitumor M1 phenotype, activating CD8+ T cell antitumor immunity. These findings identify L. salivarius and its associated metabolite CDCA as a promising adjuvant for potentiating immunotherapy in GI cancers.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>本研究旨在解決臨床宏基因組次世代定序（mNGS）在品質控制與再現性上的挑戰，開發了四種基於珠粒的「模擬微生物群落」（mock communities）作為標準品。這些群落涵蓋了腸道、呼吸道、皮膚、生殖道及腦脊髓液中常見的 26 種菌株。研究透過鳥槍法全宏基因體定序（shotgun metagenomics）評估了不同 DNA 萃取試劑盒（MagMAX 與 PowerSoil）及實驗流程對結果的偏誤影響。結果顯示，微生物的檢測豐度會顯著受到萃取試劑盒選擇的干擾，且在 25 次重複實驗中，群落組成存在一定的實驗室內誤差。此研究確立了模擬群落作為臨床 mNGS 品質控制材料的重要性，對於推動微生物組檢測的標準化流程與臨床應用具有關鍵價值。</t>
+          <t>本研究旨在探討腸道菌群如何影響胃腸道（GI）癌症對免疫治療的反應與背後機制。對278位GI癌症患者的總體基因體分析顯示，唾液乳桿菌（*Lactobacillus salivarius*）在治療有反應者體內顯著富集。動物實驗證實，該菌及其關聯代謝物鵝去氧膽酸（CDCA）能顯著增強抗PD-1療效。機制上，CDCA誘導腫瘤細胞產生活性氧（ROS）並觸發免疫原性細胞死亡，同時促使巨噬細胞向抗腫瘤的M1型極化，進而活化CD8+ T細胞。本研究證實了*L. salivarius*與CDCA在提升胃腸道癌症免疫治療效果上的臨床應用潛力，有望作為新型免疫治療佐劑。</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42656127/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42664954/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>42657522</t>
+          <t>42665077</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Resistant starch alleviates intestinal fibrosis involving an acetate-mediated HDAC2-H3K27ac axis in fibroblasts.</t>
+          <t>Metagenomic Characterization of Potential Exposure to Genetic Hazards at the Interface Between Grazing Livestock and Przewalski's Gazelle.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Food &amp; function</t>
+          <t>Environmental pollution (Barking, Essex : 1987)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>metagenomics, metabolomics</t>
+          <t>metagenomics, small genome</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>未提及（研究使用 DSS 誘導的小鼠模型以及人類與小鼠的原代纖維母細胞，但未具體說明樣本數）</t>
+          <t>未提及（摘要未明確列出具體的檢體總數或個體數量）</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -1059,54 +1059,54 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Dietary fibre-based interventions are of growing interest for the prevention and treatment of digestive diseases. In this study, we investigated the effect of resistant starch (RS) on intestinal fibrosis, a stricturing condition driven by excessive extracellular matrix (ECM) accumulation. RS was found to alleviate intestinal fibrosis in a dextran sulfate sodium (DSS)-induced chronic colitis mouse model, as evidenced by restored colon length, reduced ECM deposition (fibronectin and collagen I), and decreased levels of α-smooth muscle actin. Given that RS is fermented by the gut microbiota in the colon, metagenomic sequencing revealed that RS reshaped the composition of the gut microbiota and increased the abundance of beneficial gut bacteria, including Bacteroides acidifaciens, Faecalibaculum rodentium, and Bifidobacterium pseudolongum, which are known to enhance the production of short-chain fatty acids. Targeted metabolomic analysis further showed a marked increase in acetate levels, which was associated with reduced intestinal fibrosis. However, direct in vivo evidence that acetate is required for the anti-fibrotic effect of RS remains lacking. Using human (CCD-18Co) and primary mouse intestinal fibroblasts, the major ECM-producing cells that drive fibrosis progression, we demonstrated that acetate inhibited TGF-β-induced fibroblast activation by inhibiting histone deacetylase 2, thereby enhancing the acetylation level of histone H3 at lysine 27. Collectively, these results suggest a potential microbial-metabolic-epigenetic axis linking RS and acetate to fibrosis attenuation, which awaits causal validation in vivo. This axis holds promise as a therapeutic target for fibrotic diseases.</t>
+          <t>Livestock and endangered wildlife increasingly share grazing landscapes, yet the sources, mobility-associated contexts, and bacterial hosts of livestock-associated genetic hazards in wildlife microbiomes remain poorly resolved. We analyzed metagenomes from yak, Tibetan sheep, Przewalski's gazelle, and local topsoil within an Acquired Genetic Risk (AGR) conceptual framework integrating genetic hazard burden, compositional source attribution, mobility-associated evidence, and bacterial genomic context. MRGs and Rank I and Rank III ARGs were more abundant in livestock than in Przewalski's gazelle, whereas VF abundance was highest in yak. FEAST attributed approximately 64% of the Przewalski's gazelle resistome composition to the two livestock source profiles, less than 1% to sampled topsoil, and approximately 36% remained unassigned. MGE profiles were associated with ARGs, MRGs, and VFs, while tnpA ranked highest in random forest models and was associated with total ARG abundance (R2 = 0.618). Short-read contigs containing hazard genes and MGE markers provided localized mobility-associated sequence context. Genome-resolved analysis identified distinct bacterial contexts: TS.Bin143, an Escherichia coli MAG from Tibetan sheep, contained ARGs, MRGs, VFs, tnpA, and IS91, whereas PG.Bin275, a Hylemonella sp. MAG from Przewalski's gazelle, contained tnpA. These findings extend wildlife resistome assessment beyond abundance profiling toward source attribution, mobility-associated sequence context, and bacterial host resolution, supporting multilevel surveillance of genetic hazard exposure at livestock-wildlife interfaces.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>本研究探討抗性澱粉（RS）對腸道纖維化的改善作用及其潛在機制。透過 DSS 誘導的小鼠結腸炎模型，研究發現 RS 可有效減輕腸道纖維化並減少細胞外基質堆積。宏基因體定序顯示 RS 能重塑腸道菌群，增加如 *Bacteroides acidifaciens* 等短鏈脂肪酸產生菌的豐度；代謝體分析進一步證實乙酸（acetate）水平顯著上升。機制研究揭示，乙酸能抑制纖維母細胞中 HDAC2 的活性，進而提升組蛋白 H3K27 的乙醯化水平，抑制 TGF-β 誘導的纖維母細胞活化。本研究提出了一條「微生物-代謝-表觀遺傳」軸線，指出 RS 可藉由促進乙酸生成來對抗腸道纖維化，為治療纖維化相關疾病提供了新的科學依據與潛在治療靶點。</t>
+          <t>本研究旨在評估放牧牲畜（犛牛、藏綿羊）與瀕危物種普氏原羚共用棲地時，基因危害（含抗藥性基因 ARGs、金屬抗性基因 MRGs 及毒力因子 VFs）的傳播風險。研究利用總體基因體學（metagenomics）與基因體解析技術，發現牲畜體內的基因危害豐度顯著高於普氏原羚。透過來源溯源分析，普氏原羚約 64% 的抗藥性組分可歸因於牲畜，證實了放牧界面下的微生物交互作用。此外，轉座子（如 tnpA）與抗性基因的高度共現性，顯示了基因水平轉移的潛在危機；研究更成功從牲畜與普氏原羚的微生物基因體中，鑑定出攜帶多重抗性與毒力因子的細菌宿主。本研究建立的分析框架，為監測野生動物與家畜介面下的抗藥性傳播提供了重要的科學依據與監測策略。</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42657522/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42665077/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>42658844</t>
+          <t>42665338</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Enrichment and Characterization of a Haloalkaline-tolerant Anammox Bacterium.</t>
+          <t>PREVENT 1, a nationwide Swedish infant cohort for longitudinal gut microbiome profiling and early-life health outcomes: cohort profile.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>The ISME journal</t>
+          <t>BMJ open</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>metagenomics, small genome, others (transcriptional profiling)</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>未提及（研究基於特定實驗室富集培養物之實驗與分析）</t>
+          <t>253 位嬰兒</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -1114,54 +1114,54 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Metagenomic surveys have substantially expanded the known diversity of anaerobic ammonium-oxidizing (anammox) bacteria. However, the physiological traits of newly proposed anammox genera remain largely hypothetical due to the lack of cultured representatives. Although niche differentiation driven by salinity, organic substrates, and oxygen is well documented in anammox bacteria, adaptations to alkaline environments remain uncharacterized. Moreover, no anammox lineage has been identified as an alkaline specialist. Herein, we report the enrichment (&gt;80% relative abundance) of an anammox bacterium, provisionally named Candidatus Loosdrechtia alkalitolerans, which represents the cultured member of the genus Ca. Loosdrechtia. Ca. L. alkalitolerans exhibits marked haloalkaline tolerance, outcompeting other freshwater anammox genera under long-term saline-alkaline stress conditions (0.5% NaCl; pH~9.13). Comparative genomics revealed that among freshwater anammox lineages, only Ca. L. alkalitolerans encodes a complete multiple resistance and pH adaptation (Mrp) cation/proton antiporter operon. Batch assays with transcriptional profiling demonstrated that sodium addition upregulated mrp expression and recovered anammox activity under alkaline stress, suggesting that Mrp-mediated cation/proton exchange may contribute to pH homeostasis in Ca. L. alkalitolerans. Furthermore, database mining revealed that the habitat of Ca. L. alkalitolerans is not restricted to haloalkaline environments, but extends to diverse freshwater and wastewater ecosystems. These findings provide mechanistic insight into saline-alkaline tolerance in anammox bacteria, expanding understanding of their physiological plasticity and ecological roles.</t>
+          <t>PREVENT 1 is a nationwide, prospective Swedish infant cohort established to characterise gut microbiome development during the first 2 years of life and to relate microbial trajectories to feeding, infections, growth and everyday well-being. The study integrates repeated infant stool sampling with shotgun metagenomics analysis with aligned parental questionnaires, stool photographs and infant cry recordings collected at three approximately 3-month intervals for each infant. Families were recruited nationwide in Sweden from September 2023 through targeted digital channels. Eligible participants were term-born infants residing in Sweden and aged &lt;1 year at enrolment. Baseline questionnaire data and stool samples were collected from 253 infants. Parents completed questionnaires covering socio-demographic characteristics and health, pregnancy and delivery, postnatal factors, infant environment, feeding and growth, infections and other health outcomes, gastrointestinal symptoms and everyday well-being. Retention was high, with 248 families completing at least one follow-up questionnaire at Phase 2 and 243 at Phase 3. For stool samples, 250 infants provided at least two samples and 241 provided all three. At enrolment, 42.3% of infants were older than 7 months, 73.9% had weight-for-length z-scores in the normal range and exclusive breastfeeding at 4 months was reported for 58.9%. Three-phase sample and questionnaire data collection was completed in December 2024. Future analyses will examine microbiome features, resistome profiles and functional pathways in relation to antibiotic exposure, feeding, growth and infant health outcomes. Subject to ethical approval and participant consent, follow-up may include further stool collection and Swedish register linkage. NCT06285630.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>本研究成功富集並鑑定出一種耐鹽鹼的厭氧氨氧化（Anammox）細菌，命名為 *Candidatus Loosdrechtia alkalitolerans*。該菌株在長期高鹽、高鹼（0.5% NaCl，pH 9.13）環境下表現出強大的競爭優勢。透過基因體比較分析，研究發現該菌株含有特殊的 Mrp 陽離子/質子反向轉運蛋白操縱子，這是其適應鹼性環境的關鍵機制；轉錄組分析進一步證實，在鹼性壓力下，補充鈉離子可上調 Mrp 表現並恢復其代謝活性。此發現不僅揭示了厭氧氨氧化菌應對鹽鹼逆境的生理分子機制，證明了該菌在廣泛的淡水與廢水生態系統中具有潛在的生態地位，更為未來工業廢水處理中的脫氮技術應用提供了理論基礎與科學見解。</t>
+          <t>PREVENT 1 是一項瑞典全國性、前瞻性的嬰兒隊列研究，旨在探討生命最初兩年內的腸道微生物群發育過程，並分析微生物群動態變化與餵養方式、感染、生長發育及日常生活福祉的關聯。該研究透過縱向追蹤，於三個階段收集 253 位嬰兒的糞便檢體，並運用宏基因組定序（shotgun metagenomics）進行分析，同時整合家長問卷、糞便影像及嬰兒啼哭紀錄等數據。此研究建立了一個高品質的資料庫，未來將深入解析嬰兒腸道微生物群的組成、抗藥性基因組（resistome）及其功能路徑，並探討其如何受抗生素暴露及早期環境因素影響，對於理解生命早期微生物群與健康結果的因果機制具有重要科學意義。</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42658844/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42665338/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>42658871</t>
+          <t>42666033</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Breastmilk microbiota and its association with infant iron deficiency anaemia: A 16S rRNA metagenomic study in Peruvian mothers cohort.</t>
+          <t>Gut Microbiota-Isoallolithocholic Acid Crosstalk Promotes Calcium Oxalate Kidney Stone Formation via PARP1-Mediated Parthanatos.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PloS one</t>
+          <t>Advanced science (Weinheim, Baden-Wurttemberg, Germany)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>16S</t>
+          <t>16S, metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>46 對母嬰（46 個母乳檢體）</t>
+          <t>未提及（文中僅提及 CaOx 大鼠與小鼠模型，未說明具體樣本數量）</t>
         </is>
       </c>
       <c r="G14" t="b">
@@ -1169,54 +1169,54 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Anaemia is one of the most important public health challenges in developing countries. The global burden is estimated at 1.8 billion people, affecting approximately 30% of all children. Despite the implementation of multiple strategies over several decades, up to 42.5% of children under 3 years of age suffer anaemia in rural areas of Peru. We studied the microbiota of breastmilk (hBM) from mothers with children under the age of 1 and analysed its association with their iron deficiency anaemia. 46 mother-child pairs were recruited from Talara, a town on the northern coast of Peru and classified according to the clinical status of the children. Children with anaemia were also tested for ferritin level to classify them as iron deficiency anaemia (IDA) or non-iron deficiency anaemia (non-IDA). hBM samples were taken from the mothers after careful instruction to reduce the risk of sample contamination and the microbiome was analyzed using 16S rRNA sequencing. Streptococcus and Staphylococcus were the predominant genera, with 90% of bacterial abundance being explained by 14 genera. Alpha diversity analysis showed that hBM from mothers of children with non-IDA had higher levels of bacterial richness than hBM from healthy (p &lt; 0.01) and IDA (p &lt; 0.05) participants. Principal coordinates analysis did not yield differential clusters but showed a disparity in the spread of samples for non-IDA group when compared with the other groups. IDA group showed higher burden of Corynebacterium, Acinetobacter, Paludibacter and Nitrospira, while exhibiting a trend towards a lower burden of Streptococcus. No statistically significant differences were identified on demographic characteristics. This study suggests that hBM microbiota may differ in mothers of children with IDA and non-IDA, highlighting the necessity of further in-depth research to elucidate potential factors associated with its pathogenesis.</t>
+          <t>Bile acids have been implicated in calcium oxalate (CaOx) nephrolithiasis. Here, we employ multi-omics approaches to identify isoallolithocholic acid (isoalloLCA) as the key bile acid elevated in the feces, serum, kidney, and urine of CaOx rats, confirmed by spatial metabolomics. 16S sequencing and metagenomic analyses indicate that elevated isoalloLCA levels in CaOx rats or individuals are likely of microbial origin. Mechanistically, isoalloLCA binds to PARP1 via specific molecular interactions validated by surface plasmon resonance and cellular thermal shift assays. Knockdown of PARP1 by adeno-associated virus microinjection or pharmacological inhibition with PARP1 inhibitor AZD5305 significantly attenuates isoalloLCA-mediated crystal deposition, renal tubular injury, and mitochondrial functional impairment in both the CaOx rat and mouse models. Furthermore, the antibiotic-mediated depletion of the gut microbiota in mice markedly reduced isoalloLCA levels, whereas fecal microbiota transplantationut contributes to isoalloLCA-mediated CaOx stone formation, demonstrating a causal link between gut microbiota and isoalloLCA. In vitro, isoalloLCA promoted oxalate-induced renal tubular epithelial cell injury and parthanatos via targeting PARP1, including DNA damage, excessive PARP1 activation, PAR accumulation, mitochondrial damage, nuclear translocation of AIF and MIF. These findings establish the microbiota-isoalloLCA-PARP1-parthanatos axis in CaOx nephrolithiasis and identify PARP1 as a promising therapeutic target for kidney stone management.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>本研究探討祕魯農村地區嬰兒缺鐵性貧血（IDA）與母親母乳（hBM）菌相之間的關聯。研究對象為 46 對母嬰，透過 16S rRNA 定序分析母乳微生物群落，發現母乳菌相以鏈球菌屬（Streptococcus）與葡萄球菌屬（Staphylococcus）為優勢菌群。研究結果顯示，非貧血組嬰兒的母親，其母乳具備較高的細菌豐富度。此外，IDA 組嬰兒母親的母乳中，棒狀桿菌屬（Corynebacterium）與不動桿菌屬（Acinetobacter）等細菌豐度較高，而鏈球菌屬則呈現下降趨勢。此研究發現母乳微生物群組成可能與嬰兒貧血狀態相關，雖無法直接證實因果關係，但為後續探討嬰兒貧血的致病機制提供了重要的微生物學線索。</t>
+          <t>本研究探討腸道微生物與草酸鈣（CaOx）腎結石形成的機制。透過多體學分析，研究發現異別石膽酸（isoalloLCA）在結石模型中的糞便、血液及腎臟中均顯著升高，且來源於腸道菌群。機制研究顯示，isoalloLCA 可結合 PARP1 蛋白，進而誘導腎小管上皮細胞發生由 PARP1 介導的細胞凋亡（Parthanatos），導致腎損傷與結石惡化。動物實驗證實，透過藥物抑制或基因敲除 PARP1，可有效減緩結石形成及腎臟損害。此研究不僅闡明了「腸道菌群—isoalloLCA—PARP1—細胞凋亡」這一關鍵致病軸線，更為臨床上以 PARP1 作為腎結石防治的新型治療靶點提供了強有力的科學證據。</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42658871/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42666033/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>42660365</t>
+          <t>42660108</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Enhancing Cr(VI) bioreduction via Na+-stimulated intracellular energy metabolism and electron transfer using methane as electron donor.</t>
+          <t>Group C Orthobunyavirus Infection in a Patient from the Amazon Putumayo Region of Colombia During an Oropouche Fever Epidemic.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bioresource technology</t>
+          <t>The American journal of tropical medicine and hygiene</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16S, metagenomics</t>
+          <t>metagenomics, small genome</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>1 個臨床病例</t>
         </is>
       </c>
       <c r="G15" t="b">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Anaerobic oxidation of methane (AOM) coupled with Cr(VI) bioreduction process offers a cost-effective pathway to simultaneously mitigate methane emissions and remediate Cr(VI) contamination. However, its practical application is limited by insufficient intracellular energy generation and low electron transfer efficiency. This study elucidated the regulatory role and mechanism of Na+, a transmembrane electrochemical gradient driver, on the metabolic activity and electron transfer of this coupled system. Batch experiments demonstrated that NaCl addition significantly improved Cr(VI) reduction efficiency, achieving complete removal in the treatment group by the end of the first cycle compared to only 79.8 % in the control. Microbial community analysis showed that Na+ enriched AOM-capable Methanobacterium and extracellular electron transfer (EET)-capable electroactive bacterium unclassified_o_DTU014, which likely formed a syntrophic consortium to mediate Cr(VI) reduction. Electrochemical measurements and 3D-EEM spectroscopy revealed that Na+ enhanced microbial aggregate electron storage capacity, reduced electron transfer resistance, and promoted extracellular polymeric substance (EPS) secretion of tyrosine-like proteins and humic acid-like substances, thereby strengthening extracellular electron transfer. Key metabolic indicators showed 26.2 % higher coenzyme F420 and 37.4 % higher intracellular ATP levels in Na+-treated groups. Metagenomic analysis confirmed that Na+ upregulated genes encoding reverse methanogenesis enzymes (Mcr, Mtr) and membrane-bound electron transfer complexes (Fpo, HdrDE), while downregulating intracellular chromate reductase (ChrR) genes, indicating that EET-mediated extracellular Cr(VI) reduction played a critical role under Na+ stimulation. This study first reveals the mechanism of Na+-promoted AOM-coupled Cr(VI) reduction via enhanced energy metabolism and electron transfer, providing a crucial theoretical basis for methane-driven Cr(VI) remediation.</t>
+          <t>Orthobunyaviruses, one of the largest and most diverse genera of viruses, include numerous reassortant viruses and present diagnostic challenges due to similar clinical presentations with other arboviral infections. The detection and isolation of a group C orthobunyavirus from a patient with acute febrile illness from Puerto Ospina, Putumayo Department, Colombia during the 2023-2024 Latin American Oropouche fever regional outbreaks are reported in the present study. Using a vertebrate virus-focused metagenomics sequencing approach with VirCapSeq-VERT, a virus related to the Caraparu complex was identified, and a virus isolate was obtained. Although limited to a single case and without serological or longitudinal clinical confirmation, these findings underscore the value of unbiased molecular approaches for unresolved febrile illness diagnosis in endemic settings such as the Amazon basin.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>本研究旨在探討鈉離子（Na+）對「厭氧甲烷氧化（AOM）耦合六價鉻（Cr(VI)）還原」系統的調控機制。實驗結果顯示，添加NaCl可顯著提升Cr(VI)還原效率，達到完全去除。機制分析發現，Na+能富集具有甲烷氧化能力的「甲烷桿菌屬（*Methanobacterium*）」與具備胞外電子傳遞能力的電活性細菌，並透過增加輔酶F420及ATP含量來優化微生物能量代謝。總體基因體學分析進一步證實，Na+上調了逆向甲烷代謝酵素及膜結合電子傳遞複合體基因，同時促進胞外聚合物（EPS）分泌，從而降低電子傳遞阻力。此研究揭示了Na+透過強化胞外電子傳遞與能量代謝，促進甲烷驅動的重金屬修復作用，為環境污染整治提供了重要的理論依據。</t>
+          <t>本研究報告了一名居住於哥倫比亞亞馬遜普圖馬約地區（Putumayo）的患者，在 2023-2024 年拉丁美洲奧羅普切熱（Oropouche fever）大規模流行期間，因急性發燒就診並被檢測出感染 C 群正布尼亞病毒（Group C Orthobunyavirus）。研究團隊利用針對脊椎動物病毒的宏基因組定序技術（VirCapSeq-VERT）進行病原體鑑定，成功辨識出屬於 Caraparu 複合群的病毒，並分離出該病毒株。儘管本研究僅限於單一病例且缺乏血清學或長期臨床數據追蹤，但研究結果強烈支持在亞馬遜等傳染病流行地區，針對不明原因發燒病例應用無偏見的分子檢測技術，對於臨床診斷及病原體監測具有重要的科學價值。</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1239,39 +1239,37 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42660365/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42660108/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>42660360</t>
+          <t>42658871</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Elucidating the aromatic formation of humus via quorum sensing and redox function of thermophilic microbiota in compost.</t>
+          <t>Breastmilk microbiota and its association with infant iron deficiency anaemia: A 16S rRNA metagenomic study in Peruvian mothers cohort.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bioresource technology</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
+          <t>PloS one</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>metagenomics, others (metaproteomics)</t>
+          <t>16S</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>未提及（文中僅提及堆肥處理組別，未明確列出具體的樣本總數或重複次數）</t>
+          <t>46 對母嬰（46 個母乳檢體）</t>
         </is>
       </c>
       <c r="G16" t="b">
@@ -1279,12 +1277,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Quorum sensing (QS) modulates bacterial metabolism to regulate humus formation. However, the functional interaction modes of signal molecules, QS-related proteins, and microbial humification function during composting remain unclear. This study aimed to clarify the role of QS-related gene expression in regulating humification via applying metagenomics and metaproteomics. Combined addition of MnSO4 and Fe0 (CMF) significantly raised humic acid (HA) content (33.53 mg g-1) and polymerization degree (2.60) compared with other treatments. Multi-dimensional results revealed that CMF-derived HA and its products exhibited greater thermal stability, high aromaticity, and practical applicability. CMF increased the relative abundances of most QS-related and humification-related oxidoreductase genes throughout composting, especially during the thermophilic stage. Metaproteomic profiles verified that both QS expression and humification metabolism were hyperactivated during the thermophilic stage of CMF. Correlation analysis showed that QS gene expression potentially and preferentially influenced lignin-protein and polyphenol pathways during humification. Overall, CMF enriched thermophiles (Bacillota, Chloroflexota, and Myxococcota), further up-regulated the expression of major QS-related genes [K02035 (ABC.PE.S), K13075 (ahlD), K14645, K15580 (oppA), and K02055 (ABC.SP.S)], elevated levels of signal molecules, and promoted QS effects. Network analysis, qPCR, and simulated in vitro validation experiments confirmed that the response of key QS modules [K13075 (ahlD) and 3-OXO-C8-HSL] potentially facilitated interspecies communication and cooperation among bacteria, which concurrently enhanced downstream microbial metabolic behaviors (microbial redox activities and the metabolism of carbohydrates and amino acids) that aid in driving HA aromatization. This work provides new insight into the ecological roles of QS-related microbes and their precise regulation of compost humification.</t>
+          <t>Anaemia is one of the most important public health challenges in developing countries. The global burden is estimated at 1.8 billion people, affecting approximately 30% of all children. Despite the implementation of multiple strategies over several decades, up to 42.5% of children under 3 years of age suffer anaemia in rural areas of Peru. We studied the microbiota of breastmilk (hBM) from mothers with children under the age of 1 and analysed its association with their iron deficiency anaemia. 46 mother-child pairs were recruited from Talara, a town on the northern coast of Peru and classified according to the clinical status of the children. Children with anaemia were also tested for ferritin level to classify them as iron deficiency anaemia (IDA) or non-iron deficiency anaemia (non-IDA). hBM samples were taken from the mothers after careful instruction to reduce the risk of sample contamination and the microbiome was analyzed using 16S rRNA sequencing. Streptococcus and Staphylococcus were the predominant genera, with 90% of bacterial abundance being explained by 14 genera. Alpha diversity analysis showed that hBM from mothers of children with non-IDA had higher levels of bacterial richness than hBM from healthy (p &lt; 0.01) and IDA (p &lt; 0.05) participants. Principal coordinates analysis did not yield differential clusters but showed a disparity in the spread of samples for non-IDA group when compared with the other groups. IDA group showed higher burden of Corynebacterium, Acinetobacter, Paludibacter and Nitrospira, while exhibiting a trend towards a lower burden of Streptococcus. No statistically significant differences were identified on demographic characteristics. This study suggests that hBM microbiota may differ in mothers of children with IDA and non-IDA, highlighting the necessity of further in-depth research to elucidate potential factors associated with its pathogenesis.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>本研究旨在探討高溫堆肥過程中，群體感應（QS）機制與微生物氧化還原功能如何調控腐植質（humus）的形成。研究發現，添加硫酸錳與零價鐵（CMF）能顯著提升腐植酸（HA）含量與聚合度。透過總體基因體學（metagenomics）與總體蛋白質體學（metaproteomics）分析，證實 CMF 處理在堆肥高溫期顯著活化了 QS 相關基因（如 ahlD）及腐植化相關氧化還原酶的表現。研究結果指出，QS 機制藉由促進細菌間的訊息溝通與代謝協作，增強了微生物對木質素蛋白與多酚類路徑的代謝，進而推動腐植酸的芳香化過程。此發現揭示了微生物群落透過精細的 QS 訊號調控堆肥腐植化路徑的科學機制，為優化有機廢棄物處理及提升腐植質產量提供了重要的理論依據。</t>
+          <t>本研究探討祕魯農村地區嬰兒缺鐵性貧血（IDA）與母親母乳（hBM）菌相之間的關聯。研究對象為 46 對母嬰，透過 16S rRNA 定序分析母乳微生物群落，發現母乳菌相以鏈球菌屬（Streptococcus）與葡萄球菌屬（Staphylococcus）為優勢菌群。研究結果顯示，非貧血組嬰兒的母親，其母乳具備較高的細菌豐富度。此外，IDA 組嬰兒母親的母乳中，棒狀桿菌屬（Corynebacterium）與不動桿菌屬（Acinetobacter）等細菌豐度較高，而鏈球菌屬則呈現下降趨勢。此研究發現母乳微生物群組成可能與嬰兒貧血狀態相關，雖無法直接證實因果關係，但為後續探討嬰兒貧血的致病機制提供了重要的微生物學線索。</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1294,39 +1292,35 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42660360/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42658871/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>42660466</t>
+          <t>42658844</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Polystyrene nanoplastics exposure induces reproductive toxicity in male mice associated with the gut-liver/testis axis.</t>
+          <t>Enrichment and Characterization of a Haloalkaline-tolerant Anammox Bacterium.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Toxicology and applied pharmacology</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
+          <t>The ISME journal</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>metagenomics, others</t>
+          <t>metagenomics, small genome, others (transcriptional profiling)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>未提及（僅說明使用雄性 CD-1 小鼠）</t>
+          <t>未提及（研究基於特定實驗室富集培養物之實驗與分析）</t>
         </is>
       </c>
       <c r="G17" t="b">
@@ -1334,12 +1328,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Environmental nanoplastics are increasingly prevalent in global environments and represent an emerging systemic health risk, yet the mechanistic links between nanoplastic exposure and multi-organ dysfunction in mammals remain incompletely characterized. We integrated phenotypic assessments, gut shotgun metagenomics, and dual-organ transcriptomics to investigate the toxic effects of 28-day oral exposure to polystyrene nanoplastics (PS-NPs) in male CD-1 mice. PS-NPs induced a non-monotonic dose-dependent response, characterized by significant body weight loss at high doses, severe impairment of sperm motility, and progressive epididymal histopathological lesions. Gut metagenomics revealed significant microbiota dysbiosis, including an elevated Firmicutes/Bacteroidota ratio and marked depletion of beneficial commensal bacteria such as Ligilactobacillus murinus. Hepatic transcriptomics identified dysregulation of metabolic, detoxification, and circadian rhythm pathways, while testicular transcriptomics identified sustained transcriptional downregulation of genes annotated to steroid hormone biosynthesis and alterations in FoxO and apoptosis-related signaling. Spearman correlation network analysis identified associations between specific microbial shifts and organ-specific transcriptional alterations, providing a hypothesis-generating framework for the proposed gut-liver/testis axis. Together, these findings indicate that, under the present experimental conditions, oral PS-NPs exposure was associated with gut microbial dysbiosis, hepatic transcriptional perturbations, reduced sperm motility, and epididymal histopathological alterations, while the mechanistic relationships among these changes require further experimental validation.</t>
+          <t>Metagenomic surveys have substantially expanded the known diversity of anaerobic ammonium-oxidizing (anammox) bacteria. However, the physiological traits of newly proposed anammox genera remain largely hypothetical due to the lack of cultured representatives. Although niche differentiation driven by salinity, organic substrates, and oxygen is well documented in anammox bacteria, adaptations to alkaline environments remain uncharacterized. Moreover, no anammox lineage has been identified as an alkaline specialist. Herein, we report the enrichment (&gt;80% relative abundance) of an anammox bacterium, provisionally named Candidatus Loosdrechtia alkalitolerans, which represents the cultured member of the genus Ca. Loosdrechtia. Ca. L. alkalitolerans exhibits marked haloalkaline tolerance, outcompeting other freshwater anammox genera under long-term saline-alkaline stress conditions (0.5% NaCl; pH~9.13). Comparative genomics revealed that among freshwater anammox lineages, only Ca. L. alkalitolerans encodes a complete multiple resistance and pH adaptation (Mrp) cation/proton antiporter operon. Batch assays with transcriptional profiling demonstrated that sodium addition upregulated mrp expression and recovered anammox activity under alkaline stress, suggesting that Mrp-mediated cation/proton exchange may contribute to pH homeostasis in Ca. L. alkalitolerans. Furthermore, database mining revealed that the habitat of Ca. L. alkalitolerans is not restricted to haloalkaline environments, but extends to diverse freshwater and wastewater ecosystems. These findings provide mechanistic insight into saline-alkaline tolerance in anammox bacteria, expanding understanding of their physiological plasticity and ecological roles.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>本研究旨在探討口服聚苯乙烯奈米微粒（PS-NPs）對雄性小鼠的毒性效應及其與「腸—肝/睪丸軸」的關聯。結果顯示，28天PS-NPs暴露導致小鼠體重減輕、精子活力顯著下降及附睪病理病變。腸道總體基因體分析證實腸道菌群嚴重失調（如*Ligilactobacillus murinus*等益生菌減少）；肝臟與睪丸轉錄組分析則發現肝臟解毒代謝異常，以及睪丸中類固醇激素合成基因下調與細胞凋亡途徑改變。此研究揭示了奈米微粒透過干擾腸道微生物與多器官基因表達，進而引發雄性生殖毒性的機制，為評估環境微塑料的健康風險提供重要科學依據。</t>
+          <t>本研究成功富集並鑑定出一種耐鹽鹼的厭氧氨氧化（Anammox）細菌，命名為 *Candidatus Loosdrechtia alkalitolerans*。該菌株在長期高鹽、高鹼（0.5% NaCl，pH 9.13）環境下表現出強大的競爭優勢。透過基因體比較分析，研究發現該菌株含有特殊的 Mrp 陽離子/質子反向轉運蛋白操縱子，這是其適應鹼性環境的關鍵機制；轉錄組分析進一步證實，在鹼性壓力下，補充鈉離子可上調 Mrp 表現並恢復其代謝活性。此發現不僅揭示了厭氧氨氧化菌應對鹽鹼逆境的生理分子機制，證明了該菌在廣泛的淡水與廢水生態系統中具有潛在的生態地位，更為未來工業廢水處理中的脫氮技術應用提供了理論基礎與科學見解。</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1349,39 +1343,37 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42660466/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42658844/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>42660482</t>
+          <t>42657522</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Artificial light pollution alters epilithic microbial communities and functional biodeterioration-related functional potentials in subterranean sandstone environments.</t>
+          <t>Resistant starch alleviates intestinal fibrosis involving an acetate-mediated HDAC2-H3K27ac axis in fibroblasts.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Environmental pollution (Barking, Essex : 1987)</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Food &amp; function</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>5.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>16S, metagenomics</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>未提及（原文摘要中僅提到研究地點為中國浙江龍游石窟，但未具體列出採樣點數量或樣本總數）</t>
+          <t>未提及（研究使用 DSS 誘導的小鼠模型以及人類與小鼠的原代纖維母細胞，但未具體說明樣本數）</t>
         </is>
       </c>
       <c r="G18" t="b">
@@ -1389,12 +1381,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Artificial light pollution represents an important anthropogenic disturbance in subterranean heritage environments, yet its associations with epilithic microbial communities and biodeterioration processes remain poorly understood. In tourist-accessible subterranean caves, artificial illumination creates persistent illuminated areas on stone surfaces that may alter microbial community assembly and biogeochemical functions associated with biofilm development. Here, the Longyou Grottoes, a large underground sandstone cave complex in Zhejiang, China, were investigated using 16S rRNA gene sequencing and metagenomics. Bacterial communities dominated all samples (&gt;98% relative abundance). Cyanobacteriota were enriched under artificial light and sunlight (&gt;40%), whereas Pseudomonadota and Actinomycetota prevailed in darkness. Dark sites exhibited higher bacterial alpha diversity and more complex co-occurrence networks. Compared with sunlight and dark environments, the artificial-light environment was associated with greater stochasticity in bacterial community assembly, broader niche breadth, and lower niche overlap. Metabolic potential analysis further revealed light-dependent metabolic shifts: artificial light enhanced assimilatory nitrogen and sulfur metabolism, sunlight promoted nitrogen fixation, and darkness favored nitrification, denitrification, and sulfur oxidation. However, bacterial community patterns were also associated with temperature, humidity, pH, and soluble salts, indicating that the observed differentiation reflected the combined influence of light and environmental heterogeneity. These findings identify artificial lighting as an important and manageable environmental factor associated with epilithic bacterial communities and provide a basis for integrating lighting management with environmental control in the preventive conservation of subterranean sandstone heritage.</t>
+          <t>Dietary fibre-based interventions are of growing interest for the prevention and treatment of digestive diseases. In this study, we investigated the effect of resistant starch (RS) on intestinal fibrosis, a stricturing condition driven by excessive extracellular matrix (ECM) accumulation. RS was found to alleviate intestinal fibrosis in a dextran sulfate sodium (DSS)-induced chronic colitis mouse model, as evidenced by restored colon length, reduced ECM deposition (fibronectin and collagen I), and decreased levels of α-smooth muscle actin. Given that RS is fermented by the gut microbiota in the colon, metagenomic sequencing revealed that RS reshaped the composition of the gut microbiota and increased the abundance of beneficial gut bacteria, including Bacteroides acidifaciens, Faecalibaculum rodentium, and Bifidobacterium pseudolongum, which are known to enhance the production of short-chain fatty acids. Targeted metabolomic analysis further showed a marked increase in acetate levels, which was associated with reduced intestinal fibrosis. However, direct in vivo evidence that acetate is required for the anti-fibrotic effect of RS remains lacking. Using human (CCD-18Co) and primary mouse intestinal fibroblasts, the major ECM-producing cells that drive fibrosis progression, we demonstrated that acetate inhibited TGF-β-induced fibroblast activation by inhibiting histone deacetylase 2, thereby enhancing the acetylation level of histone H3 at lysine 27. Collectively, these results suggest a potential microbial-metabolic-epigenetic axis linking RS and acetate to fibrosis attenuation, which awaits causal validation in vivo. This axis holds promise as a therapeutic target for fibrotic diseases.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>本研究探討人工光污染對地下砂岩文化遺產（龍游石窟）中附石微生物群落及生物劣化功能的影響。研究利用 16S rRNA 定序與宏基因體學分析發現，人工光照顯著改變了微生物的組成與生態位：人工光照環境下，藍細菌門（Cyanobacteriota）豐度顯著增加，且群落組裝過程表現出更高的隨機性；相較之下，黑暗環境則擁有較高的物種多樣性與複雜的共生網絡。功能分析顯示，不同光照條件會誘導代謝功能的差異，包括氮與硫代謝途徑的轉變。這些發現證實人工照明是影響地下文化遺產微生物生態的重要人為因子，強調了在文化遺產預防性保護中，將燈光管理納入環境控制策略的必要性，以減緩由微生物引起的石材劣化。</t>
+          <t>本研究探討抗性澱粉（RS）對腸道纖維化的改善作用及其潛在機制。透過 DSS 誘導的小鼠結腸炎模型，研究發現 RS 可有效減輕腸道纖維化並減少細胞外基質堆積。宏基因體定序顯示 RS 能重塑腸道菌群，增加如 *Bacteroides acidifaciens* 等短鏈脂肪酸產生菌的豐度；代謝體分析進一步證實乙酸（acetate）水平顯著上升。機制研究揭示，乙酸能抑制纖維母細胞中 HDAC2 的活性，進而提升組蛋白 H3K27 的乙醯化水平，抑制 TGF-β 誘導的纖維母細胞活化。本研究提出了一條「微生物-代謝-表觀遺傳」軸線，指出 RS 可藉由促進乙酸生成來對抗腸道纖維化，為治療纖維化相關疾病提供了新的科學依據與潛在治療靶點。</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1404,28 +1396,28 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42660482/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42657522/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>42647084</t>
+          <t>42656127</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Diet quality, gut microbiome, and inflammatory signatures in Puerto Rican adults with Crohn disease: a multidimensional analysis.</t>
+          <t>Development and Validation of Mock Communities as Quality Control Materials for Clinical Metagenomic Next-Generation Sequencing.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Inflammatory bowel diseases</t>
+          <t>Annals of laboratory medicine</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1434,7 +1426,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>60位患有克隆氏症的成年人 (60 adults with CD)</t>
+          <t>25 次重複分析（針對開發出的四種模擬群落進行評估）</t>
         </is>
       </c>
       <c r="G19" t="b">
@@ -1442,52 +1434,54 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Diet is increasingly recognized as a modifiable factor influencing gut microbiome and outcomes in Crohn disease (CD), yet data in underrepresented populations remain limited. We evaluated diet quality, dietary patterns, gut microbiome composition, inflammatory markers, and patient-reported outcomes in adults with CD from Puerto Rico. We conducted a cross-sectional analysis of 60 adults with CD enrolled prior to dietary intervention in a parent study. Dietary intake was assessed using 24-hour recalls and evaluated using the Healthy Eating Index-2015 (HEI-2015), Alternative Healthy Eating Index-2010 (AHEI-2010), and exploratory dietary pattern analysis. The gut microbiome was assessed by shotgun metagenomic sequencing. Clinical outcomes included fecal calprotectin, C-reactive protein (CRP), a 96-cytokine panel, short Crohn Disease Activity Index (sCDAI), and short Inflammatory Bowel Disease Questionnaire (sIBDQ). Associations were evaluated using unadjusted and adjusted models with false discovery rate (FDR) correction. Overall diet quality was poor and characterized by low intake of fruits, vegetables, whole grains, and fiber, alongside high intake of saturated fat, added sugars, and animal-derived protein. Four dietary patterns were identified: vegetable-rich, dairy-rich, fruit-rich, and coffee/sweetener-rich. Participants adhering to the fruit-rich pattern exhibited the highest diet quality scores. Higher HEI-2015 scores were associated with greater gut microbial diversity and differences in overall microbiome composition. Participants with greater adherence to the vegetable-rich pattern showed modest increases in microbial diversity. Exploratory analyses suggested that higher fruit intake and adherence to a fruit-rich dietary pattern were associated with lower fecal calprotectin and CRP levels, whereas adherence to a vegetable-rich pattern was associated with better health-related quality of life (HRQoL) and adherence to a coffee/sweetener-rich pattern was associated with a worse symptom burden. However, no associations between dietary metrics and inflammatory markers, cytokines, or clinical outcomes remained significant after FDR correction. Most participants were in clinical remission despite substantial impairment in HRQoL. Adults with CD in Puerto Rico exhibited poor diet quality that was associated with gut microbial diversity and exploratory differences in clinical outcomes. While these findings support the influence of diet on the microbiome and clinical outcomes, larger longitudinal studies are needed to determine whether dietary improvements can influence disease outcomes this underrepresented population.</t>
+          <t>Metagenomic next-generation sequencing (NGS) enables comprehensive detection of a broad spectrum of microorganisms. However, its clinical application faces two major challenges: the development of appropriate microbiome-based biomarkers and the need to ensure the reproducibility and quality of the microbiome analytical workflow. Therefore, we developed four types of bead-based mock communities as standard materials for microbiome analysis and evaluated potential experimental biases arising from nucleic acid extraction and sequence analysis. Mock communities were assembled from strains isolated from clinical specimens and selected considering Gram reaction, taxonomic phylogeny, and prevalence, and processed into frozen beads. The communities were analyzed using shotgun whole-metagenome sequencing. The effect of DNA extraction kit choice was evaluated using the Thermo Fisher Scientific MagMAX Microbiome Ultra Nucleic Acid Isolation Kit and Qiagen PowerSoil Kit. Four types of mock communities comprising 26 species commonly found in the gastrointestinal tract, respiratory tract, skin, and genital tract plus cerebrospinal fluid were developed considering Gram reaction, GC content, and phylogenetic distribution. Across 25 repeated analyses, the median repeatability of each taxon was 18.97% (range, 2.87%-107.38%), while within-laboratory imprecision was 26.22% (range, 9.26%-153.83%). Repeatability remained below 10% for most dominant taxa with relative abundances &gt;20%. The choice of DNA extraction kit had a significant effect on taxonomic distributions. Microbial mock communities are essential QC materials for clinical metagenomic NGS. Further studies are needed to minimize variability and establish a standardized protocol for clinical implementation.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>本研究探討波多黎各克隆氏症（CD）成年患者的飲食品質、腸道菌相與發炎指標的關係。研究發現，受試者普遍飲食品質不佳，而較高的飲食品質（特別是富含水果的飲食模式）與較高的腸道菌群多樣性顯著相關。探索性分析顯示，多攝取水果與較低的發炎指標（鈣衛蛋白和C反應蛋白）相關，而蔬菜為主的飲食與較佳的生活品質相關（但經FDR校正後未達顯著）。本研究首次揭示了該少數受關注族群中飲食對菌相與臨床症狀的影響，為未來透過飲食干預管理CD及改善患者預後提供了科學依據。</t>
+          <t>本研究旨在解決臨床宏基因組次世代定序（mNGS）在品質控制與再現性上的挑戰，開發了四種基於珠粒的「模擬微生物群落」（mock communities）作為標準品。這些群落涵蓋了腸道、呼吸道、皮膚、生殖道及腦脊髓液中常見的 26 種菌株。研究透過鳥槍法全宏基因體定序（shotgun metagenomics）評估了不同 DNA 萃取試劑盒（MagMAX 與 PowerSoil）及實驗流程對結果的偏誤影響。結果顯示，微生物的檢測豐度會顯著受到萃取試劑盒選擇的干擾，且在 25 次重複實驗中，群落組成存在一定的實驗室內誤差。此研究確立了模擬群落作為臨床 mNGS 品質控制材料的重要性，對於推動微生物組檢測的標準化流程與臨床應用具有關鍵價值。</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42647084/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42656127/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>42644416</t>
+          <t>42660482</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nationwide cohort study reveals low bifidobacteria and distinct microbiota composition and function in Swedish newborns.</t>
+          <t>Artificial light pollution alters epilithic microbial communities and functional biodeterioration-related functional potentials in subterranean sandstone environments.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11</v>
+          <t>Environmental pollution (Barking, Essex : 1987)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>16S, metagenomics</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>308 名瑞典新生兒的糞便檢體</t>
+          <t>未提及（原文僅提及針對浙江龍游石窟進行採樣，未具體標示樣本總數）</t>
         </is>
       </c>
       <c r="G20" t="b">
@@ -1495,45 +1489,49 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>NCT06285630.</t>
+          <t>Artificial light pollution represents an important anthropogenic disturbance in subterranean heritage environments, yet its associations with epilithic microbial communities and biodeterioration processes remain poorly understood. In tourist-accessible subterranean caves, artificial illumination creates persistent illuminated areas on stone surfaces that may alter microbial community assembly and biogeochemical functions associated with biofilm development. Here, the Longyou Grottoes, a large underground sandstone cave complex in Zhejiang, China, were investigated using 16S rRNA gene sequencing and metagenomics. Bacterial communities dominated all samples (&gt;98% relative abundance). Cyanobacteriota were enriched under artificial light and sunlight (&gt;40%), whereas Pseudomonadota and Actinomycetota prevailed in darkness. Dark sites exhibited higher bacterial alpha diversity and more complex co-occurrence networks. Compared with sunlight and dark environments, the artificial-light environment was associated with greater stochasticity in bacterial community assembly, broader niche breadth, and lower niche overlap. Metabolic potential analysis further revealed light-dependent metabolic shifts: artificial light enhanced assimilatory nitrogen and sulfur metabolism, sunlight promoted nitrogen fixation, and darkness favored nitrification, denitrification, and sulfur oxidation. However, bacterial community patterns were also associated with temperature, humidity, pH, and soluble salts, indicating that the observed differentiation reflected the combined influence of light and environmental heterogeneity. These findings identify artificial lighting as an important and manageable environmental factor associated with epilithic bacterial communities and provide a basis for integrating lighting management with environmental control in the preventive conservation of subterranean sandstone heritage.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>本研究旨在探討瑞典新生兒的腸道菌相組成與功能特徵。透過總體基因體學分析，研究發現瑞典新生兒腸道中的雙歧桿菌（特別是嬰兒雙歧桿菌）豐度顯著偏低，並呈現出獨特的菌相結構與代謝功能。此現象與現代化生活型態及分娩方式密切相關。這項全國性世代研究揭示了現代環境對嬰兒早期腸道微生態建立的深遠影響，為未來的臨床嬰幼兒益生菌介入與健康照護策略提供了關鍵的科學依據。</t>
+          <t>本研究探討人工光污染對地下砂岩環境中岩面微生物群落及其功能潛力的影響。研究發現，在龍游石窟中，細菌群落佔據絕對優勢；人工光照射促進了藍細菌（Cyanobacteriota）的增殖，而黑暗環境則維持了更高的群落多樣性與複雜的共現網絡。透過代謝潛力分析，研究揭示了環境光照對微生物代謝途徑的調控：人工光環境強化了氮與硫的同化作用，日光環境促進了固氮作用，而黑暗環境則有利於硝化、反硝化與硫氧化過程。此外，細菌群落的分化亦受溫度、濕度、pH值及可溶性鹽分等環境因子綜合影響。本研究釐清了人工照明作為地下遺產環境中關鍵人為干擾因素的角色，為制定砂岩文化遺產的預防性保護措施提供了科學依據與光照管理建議。</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42644416/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42660482/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>42648171</t>
+          <t>42660360</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Co-occurrence of muddy off flavor and cyanotoxin genes in the polluted Guandu river waters (Rio de Janeiro, Brazil).</t>
+          <t>Elucidating the aromatic formation of humus via quorum sensing and redox function of thermophilic microbiota in compost.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>The Science of the total environment</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Bioresource technology</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>metagenomics, others (metaproteomics)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1546,45 +1544,49 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>The Guandu river basin is responsible for supplying Rio de Janeiro municipality, Brazil, with drinking water. This study investigated water quality during the geosmin crisis in January and March 2020, by relating the water quality and odor compounds with metagenomic tools. Guandu river water was eutrophic. The cyanobacterial genera identified were Microcystis, Planktothrix, Dolichospermum, Nostoc, Synechococcus, Planktothricoides, and Cyanobium, indicating that bloom-associated communities in the system are taxonomically diverse. Functional annotation of metagenomic sequences revealed the presence of genes associated with the biosynthesis of taste-and-odor compounds, including geosmin (geoA) and 2-methylisoborneol (mic), as well as multiple biosynthetic clusters related to cyanotoxin production. Genes linked to microcystin (mcy), saxitoxin (sxt), anatoxin (ana), cylindrospermopsin (cyr), lyngbyatoxin (ltx), guanitoxin (gnt), and nodularin (nda) were detected across the dataset, indicating a broad genetic potential for the production of secondary metabolites relevant to water quality. The co-occurrence of cyanotoxins, geosmin and 2-MIB genes suggests that off-flavor is an indication of cyanotoxin potential production in the water.</t>
+          <t>Quorum sensing (QS) modulates bacterial metabolism to regulate humus formation. However, the functional interaction modes of signal molecules, QS-related proteins, and microbial humification function during composting remain unclear. This study aimed to clarify the role of QS-related gene expression in regulating humification via applying metagenomics and metaproteomics. Combined addition of MnSO4 and Fe0 (CMF) significantly raised humic acid (HA) content (33.53 mg g-1) and polymerization degree (2.60) compared with other treatments. Multi-dimensional results revealed that CMF-derived HA and its products exhibited greater thermal stability, high aromaticity, and practical applicability. CMF increased the relative abundances of most QS-related and humification-related oxidoreductase genes throughout composting, especially during the thermophilic stage. Metaproteomic profiles verified that both QS expression and humification metabolism were hyperactivated during the thermophilic stage of CMF. Correlation analysis showed that QS gene expression potentially and preferentially influenced lignin-protein and polyphenol pathways during humification. Overall, CMF enriched thermophiles (Bacillota, Chloroflexota, and Myxococcota), further up-regulated the expression of major QS-related genes [K02035 (ABC.PE.S), K13075 (ahlD), K14645, K15580 (oppA), and K02055 (ABC.SP.S)], elevated levels of signal molecules, and promoted QS effects. Network analysis, qPCR, and simulated in vitro validation experiments confirmed that the response of key QS modules [K13075 (ahlD) and 3-OXO-C8-HSL] potentially facilitated interspecies communication and cooperation among bacteria, which concurrently enhanced downstream microbial metabolic behaviors (microbial redox activities and the metabolism of carbohydrates and amino acids) that aid in driving HA aromatization. This work provides new insight into the ecological roles of QS-related microbes and their precise regulation of compost humification.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>本研究旨在探究巴西里約熱內盧瓜杜河於2020年初爆發土臭素危機期間的水質狀況，並利用總體基因體學技術探討水質異味與微生物群落之關聯。研究發現，該富營養化水體中含有多種藍菌，且功能性註釋顯示其富含合成土臭素（*geoA*）與2-甲基異莰醇（*mic*）等異味物質的基因。更重要的是，多種藍菌毒素（如微囊藻毒素、石房蛤毒素等）的合成基因群與這些異味基因呈現共存。此發現證實了水體異味的出現與藍菌毒素的潛在生成具有高度相關性，可作為飲用水安全監測及評估藍菌毒素潛在危害的重要預警指標。</t>
+          <t>本研究旨在探討堆肥過程中，群聚感應（Quorum sensing, QS）如何調節微生物的腐植化代謝功能。研究透過宏基因組學（metagenomics）與宏蛋白質組學（metaproteomics）分析，發現添加 MnSO4 與 Fe0（CMF）能顯著提升腐植酸（HA）含量及其聚合度。結果顯示，CMF 處理促進了高溫期微生物的 QS 相關基因與氧化還原酶基因的表現，特別是特定菌群（如 Bacillota, Chloroflexota 等）的豐度增加。研究證實，透過關鍵 QS 模組（如 ahlD 與 3-OXO-C8-HSL）介導的種間溝通，能有效活化碳水化合物與胺基酸代謝，進而推動腐植酸的芳香化過程，提升最終產物的熱穩定性與芳香性。此發現揭示了 QS 機制在堆肥腐植化過程中的關鍵調節作用，為優化有機廢棄物處理及堆肥品質提供了科學理論依據。</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42648171/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42660360/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>42647759</t>
+          <t>42660365</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Gut Microbiome in Multiple Sclerosis.</t>
+          <t>Enhancing Cr(VI) bioreduction via Na+-stimulated intracellular energy metabolism and electron transfer using methane as electron donor.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Neurology(R) neuroimmunology &amp; neuroinflammation</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Bioresource technology</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>16S, metagenomics</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1597,52 +1599,54 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Multiple sclerosis (MS) is a chronic inflammatory demyelinating disease of the CNS whose risk and course are shaped by both genetic and environmental factors, among which the intestinal microbiota has emerged as a key, potentially modifiable contributor. People with MS frequently display altered gut microbiota, characterized by depletion of fiber-fermenting, short-chain fatty acid (SCFA)-producing commensals, and expansion of taxa associated with mucus degradation and proinflammatory metabolism. These compositional shifts are paralleled by broad changes in blood and CSF metabolites, including reduced SCFAs, tryptophan-derived aryl hydrocarbon receptor ligands, and secondary bile acids. In addition, several reports highlight the accumulation of aromatic amino acid-derived phenolic and indolic compounds and specific lipid mediators linked to neuroinflammation and neurodegeneration. In this up-to-date review, we synthesize evidence from experimental models and human studies showing how microbial metabolites can influence MS pathogenesis through converging mechanisms: modulation of gut and blood-brain barrier integrity; shaping of T-cell and B-cell responses; direct effects on microglia, astrocytes, and oligodendrocyte lineage cells after crossing into the CNS; and modulation of neural circuits, particularly those involving the vagus nerve. Finally, we highlight current gaps, including the need for longitudinal, harmonized multiomic cohorts, and mechanistic studies integrating microbiome, metabolome, and host readouts across gut, blood, and CNS. Overall, available data support a model in which coordinated disruption of the gut microbiota-metabolite axis, rather than any single pathogen, contributes to MS, opening avenues for microbiota-based and metabolite-based biomarkers and therapies aimed at restoring immune and neuroglial homeostasis.</t>
+          <t>Anaerobic oxidation of methane (AOM) coupled with Cr(VI) bioreduction process offers a cost-effective pathway to simultaneously mitigate methane emissions and remediate Cr(VI) contamination. However, its practical application is limited by insufficient intracellular energy generation and low electron transfer efficiency. This study elucidated the regulatory role and mechanism of Na+, a transmembrane electrochemical gradient driver, on the metabolic activity and electron transfer of this coupled system. Batch experiments demonstrated that NaCl addition significantly improved Cr(VI) reduction efficiency, achieving complete removal in the treatment group by the end of the first cycle compared to only 79.8 % in the control. Microbial community analysis showed that Na+ enriched AOM-capable Methanobacterium and extracellular electron transfer (EET)-capable electroactive bacterium unclassified_o_DTU014, which likely formed a syntrophic consortium to mediate Cr(VI) reduction. Electrochemical measurements and 3D-EEM spectroscopy revealed that Na+ enhanced microbial aggregate electron storage capacity, reduced electron transfer resistance, and promoted extracellular polymeric substance (EPS) secretion of tyrosine-like proteins and humic acid-like substances, thereby strengthening extracellular electron transfer. Key metabolic indicators showed 26.2 % higher coenzyme F420 and 37.4 % higher intracellular ATP levels in Na+-treated groups. Metagenomic analysis confirmed that Na+ upregulated genes encoding reverse methanogenesis enzymes (Mcr, Mtr) and membrane-bound electron transfer complexes (Fpo, HdrDE), while downregulating intracellular chromate reductase (ChrR) genes, indicating that EET-mediated extracellular Cr(VI) reduction played a critical role under Na+ stimulation. This study first reveals the mechanism of Na+-promoted AOM-coupled Cr(VI) reduction via enhanced energy metabolism and electron transfer, providing a crucial theoretical basis for methane-driven Cr(VI) remediation.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>本研究探討多發性硬化症（MS）與腸道微生物群之間的關聯。研究指出，MS 患者的腸道菌相呈現失調狀態，包括短鏈脂肪酸（SCFA）產生菌減少，以及促發炎代謝菌的增加。這些微生物群落的變化伴隨著血液與腦脊髓液中代謝物（如色胺酸衍生物、膽汁酸及 SCFA）的顯著改變，這些物質經證實與神經發炎及退化密切相關。文中綜述了微生物代謝產物如何透過調節腸道與血腦屏障完整性、影響免疫細胞（T/B 細胞）反應，以及直接作用於神經膠質細胞來參與 MS 的致病機制。總結而言，MS 的發生與腸道菌群-代謝物軸的整體失調有關，而非單一病原體所致。該研究強調未來需進行多體學（multiomics）整合分析，以開發基於微生物群的生物標記與創新治療策略，旨在恢復患者的免疫與神經恆定。</t>
+          <t>本研究旨在探討鈉離子（Na+）對甲烷厭氧氧化（AOM）耦合六價鉻（Cr(VI)）還原系統的調控機制。實驗結果顯示，添加 NaCl 能顯著提升 Cr(VI) 的還原效率。微生物群落分析指出，Na+ 富集了具備 AOM 能力的甲烷桿菌（*Methanobacterium*）與具備胞外電子傳遞（EET）能力的電活性細菌，兩者形成共生體系。機制上，Na+ 增強了微生物聚體的電子儲存容量，降低電子傳遞阻力，並促進酪胺酸與腐植酸類物質的胞外聚合物（EPS）分泌。宏基因體分析證實，Na+ 上調了逆向產甲烷途徑（Mcr, Mtr）與膜結合電子傳遞複合物（Fpo, HdrDE）基因，同時增加輔酶 F420 與 ATP 水平，證實 Na+ 是透過強化胞內能量代謝與 EET 來提升還原效率。此發現為利用甲烷修復重金屬污染提供了重要的科學依據與理論基礎。</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42647759/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42660365/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>42647164</t>
+          <t>42660466</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sex differences in the gut microbiome and related metabolites: role in cardiometabolic disease.</t>
+          <t>Polystyrene nanoplastics exposure induces reproductive toxicity in male mice associated with the gut-liver/testis axis.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11</v>
+          <t>Toxicology and applied pharmacology</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics, others (Transcriptomics)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>未提及（本文為綜論性回顧文章，非原創實驗研究）</t>
+          <t>未提及（僅提及使用雄性 CD-1 小鼠，未註明具體數量）</t>
         </is>
       </c>
       <c r="G23" t="b">
@@ -1650,50 +1654,52 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sex differences in major cardiometabolic diseases (CMD), such as type 2 diabetes, metabolic dysfunction-associated steatotic liver disease, and cardiovascular disease, have been increasingly recognized across the life course. During the reproductive stage, women generally have a more favorable cardiometabolic risk profile than men, but their risk of experiencing CMD significantly increases after menopause. Emerging evidence suggests that sexually dimorphic gut microbiota and gut microbiota-related metabolites (GMRMs) may contribute to such sex disparities. However, existing findings are heterogeneous and underlying mechanisms remain incompletely understood. In this review, we synthesize the evidence examining sex differences in gut microbial diversity, overall composition, taxa abundances, and levels of GMRMs across key life stages, including pre-puberty, adolescence, and different phases of adulthood (with emphasis on pre- and post-menopausal periods). We summarize potential biological mechanisms underlying sexual dimorphism in the gut microbiome and GMRMs, emphasizing the central role of sex steroids, along with contributions from immune function and other host and environmental factors. We further integrate evidence linking sexually dimorphic microbial taxa (e.g., Akkermansia muciniphila, Eubacterium, Ruminococcus, and other Firmicutes taxa) and GMRMs (e.g., microbiota-derived short-chain fatty acids, secondary bile acids, and trimethylamine N-oxide) to key cardiometabolic pathways involving inflammation, glucose and lipid metabolism, and vascular function. Finally, we identify critical knowledge gaps and emphasize the need for future large longitudinal studies that would integrate repeated measurements of the gut microbiome, untargeted metabolomics, and sex steroid hormones across the life course. Such approaches are essential to clarify biological pathways and inform sex-specific microbiome-based interventions for CMD prevention and management.</t>
+          <t>Environmental nanoplastics are increasingly prevalent in global environments and represent an emerging systemic health risk, yet the mechanistic links between nanoplastic exposure and multi-organ dysfunction in mammals remain incompletely characterized. We integrated phenotypic assessments, gut shotgun metagenomics, and dual-organ transcriptomics to investigate the toxic effects of 28-day oral exposure to polystyrene nanoplastics (PS-NPs) in male CD-1 mice. PS-NPs induced a non-monotonic dose-dependent response, characterized by significant body weight loss at high doses, severe impairment of sperm motility, and progressive epididymal histopathological lesions. Gut metagenomics revealed significant microbiota dysbiosis, including an elevated Firmicutes/Bacteroidota ratio and marked depletion of beneficial commensal bacteria such as Ligilactobacillus murinus. Hepatic transcriptomics identified dysregulation of metabolic, detoxification, and circadian rhythm pathways, while testicular transcriptomics identified sustained transcriptional downregulation of genes annotated to steroid hormone biosynthesis and alterations in FoxO and apoptosis-related signaling. Spearman correlation network analysis identified associations between specific microbial shifts and organ-specific transcriptional alterations, providing a hypothesis-generating framework for the proposed gut-liver/testis axis. Together, these findings indicate that, under the present experimental conditions, oral PS-NPs exposure was associated with gut microbial dysbiosis, hepatic transcriptional perturbations, reduced sperm motility, and epididymal histopathological alterations, while the mechanistic relationships among these changes require further experimental validation.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>本文旨在探討性別差異在腸道微生物群與相關代謝物（GMRMs）中如何影響心臟代謝疾病（CMD）。研究指出，受性類固醇、免疫功能及環境因素影響，腸道菌相與代謝產物存在顯著的性別二態性。女性在生育期較男性具備更佳的心臟代謝特徵，但停經後風險顯著升高，此變化與特定菌屬（如 *Akkermansia muciniphila*）及代謝物（如短鏈脂肪酸、次級膽汁酸、TMAO）的豐度改變密切相關。這些微生物與代謝物透過調節發炎反應、醣脂代謝及血管功能，進而影響 CMD 的發生。本文強調未來需透過大型縱向研究，結合微生物組學、代謝組學與荷爾蒙監測，以深入解析其生物學機制，並開發針對不同性別的精準微生物介入療法，對於預防及管理心臟代謝疾病具有重要的科學價值。</t>
+          <t>本研究探討口服聚苯乙烯奈米塑膠（PS-NPs）對雄性小鼠造成的生殖毒性及其潛在機制。透過為期 28 天的暴露實驗，研究團隊整合總體基因體學與雙器官轉錄體學分析，發現 PS-NPs 會導致體重減輕、精子活力顯著下降及附睪病理損傷。宏基因體分析顯示腸道菌群失調，特別是厚壁菌門與擬桿菌門比例失衡，以及有益菌 *Ligilactobacillus murinus* 的耗損。轉錄體學結果進一步揭示肝臟代謝與生理時鐘途徑的紊亂，以及睪丸中類固醇激素合成基因的下調與細胞凋亡訊號的活化。研究提出「腸道-肝臟/睪丸軸」假說，認為奈米塑膠透過改變腸道微生態，進而引發肝臟代謝與睪丸功能障礙。此發現強調了環境奈米塑膠對多器官系統的潛在危害，為環境毒理學與生殖健康風險評估提供了重要的分子生物學證據。</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42647164/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42660466/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>42644751</t>
+          <t>42647600</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Soil amelioration impacts viral ecology in saline-alkali lands.</t>
+          <t>Urogenital immune signatures are associated with birth outcomes after maternal urinary tract infection.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>The ISME journal</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Science translational medicine</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>14.6</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>未提及（僅說明樣品來自中國4個主要鹽鹼地區，各包含「鹽鹼」與「改良後」兩種狀態之土壤）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G24" t="b">
@@ -1701,12 +1707,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>The continuous expansion of saline-alkali lands under climate change threatens food security and reduces soil carbon stocks. A common mitigation strategy is soil amelioration, which converts degraded soils back into an arable state. Microbes play critical roles in soil health and recovery. However, the viruses that infect these microbial communities, and their potential impacts during saline-alkali soil restoration, remain largely unknown. Here, we combined total soil metagenomics and viromics to investigate host-linked viral ecology across four major saline-alkali regions in China, each encompassing two soil amelioration statuses: saline-alkali and reclaimed. We found that viral community structure was shaped by both geography and soil amelioration status, with salinity and alkalinity emerging as key environmental factors. Viral populations were sensitive to soil restoration, showing strong amelioration-status endemism with functional adaptations. Virus-host dynamics ranged from reduced temperate viruses to abundance mismatches in those infecting key carbon-cycling microorganisms, including carbohydrate degraders. 13C-cellulose DNA-SIP experiments provided further support for this mismatch by tracing assimilated carbon transfer between active host and virus populations. Compared with saline-alkali soils, the relative abundance of hosts in restored soils increased from 39.0% to 61.0%, whereas the linked viruses decreased from 60.6% to 39.4%. Together, these findings reveal an underappreciated role of viruses in shaping saline-alkali soil amelioration trajectories, and could improve management strategies for degraded land recovery and carbon storage.</t>
+          <t>Preterm birth is the leading cause of infant mortality, resulting in more than 1 million neonatal deaths globally each year. Maternal urinary tract infection (UTI) during pregnancy increases risk for preterm birth; however, biological processes mediating UTI-associated preterm birth are not well described. We established a murine maternal UTI model in which challenge with uropathogenic Escherichia coli (UPEC) initiated preterm labor and birth in about half of dams. Although bacterial burdens were similar, dams experiencing preterm birth displayed excessive bladder inflammation, elevated placental and decidual cytokines, higher proportions of male fetuses, and lower maternal serum interleukin-10 (IL-10) compared with nonlaboring dams. Exogenous IL-10 or lymph node sequestration of T cells reduced placental type 17 T helper cells (TH17 cells) and abrogated preterm birth. In a human pregnancy cohort, we correlated urinary cytokines with birth outcomes and urine culture status. These analyses yielded an exploratory, noninvasive culture-agnostic system for evaluating preterm birth risk, implicating T cell-related cytokines including IL-10, IL-15, GM-CSF, and RANTES. These findings demonstrate that our murine model provides a platform to investigate immunological and microbial factors governing UTI-associated preterm birth and, coupled with patient samples, may be used to identify candidate biomarkers and mechanistic targets for future investigation.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>本研究旨在探討鹽鹼地改良過程中，病毒對土壤微生物生態與碳循環的影響。研究結合總體基因體與病毒體學，分析中國四大鹽鹼區。結果顯示，土壤改良狀態、鹽度與鹼度是塑造病毒社群的關鍵。在改良土壤中，宿主微生物相對豐度顯著上升（39.0%至61.0%），而關聯病毒減少（60.6%至39.4%），且溫和病毒比例降低，碳循環關鍵微生物的病毒與宿主出現豐度失衡。13C-纖維素DNA-SIP實驗證實了兩者間的活性碳轉移。此發現揭示了病毒在鹽鹼地恢復中的關鍵作用，有助優化土地改良與碳儲存策略。</t>
+          <t>本研究旨在探討孕婦尿路感染（UTI）導致早產的免疫機制。研究團隊建立尿路致病性大腸桿菌（UPEC）感染的孕鼠模型，發現發生早產的母鼠伴隨更嚴重的膀胱發炎、胎盤細胞激素升高及血清IL-10降低；給予外源性IL-10或抑制T細胞，能減少胎盤TH17細胞並預防早產。此外，人類佇列研究證實，尿液中T細胞相關細胞激素（如IL-10、IL-15等）與早產風險密切相關。本研究結合動物模型與臨床樣本，揭示了UTI引發早產的免疫關鍵，並為未來篩檢及治療提供了潛在的非侵入性生物標誌物與機制標靶。</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1716,37 +1722,35 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42644751/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647600/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>42647600</t>
+          <t>42657129</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Urogenital immune signatures are associated with birth outcomes after maternal urinary tract infection.</t>
+          <t>Pulmonary Infiltrates, Airway Mucosal Lesions and Respiratory Microbiology After Freshwater Drowning: A Case Report.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Science translational medicine</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>14.6</v>
-      </c>
+          <t>Respirology case reports</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>1 例病患（n=1）</t>
         </is>
       </c>
       <c r="G25" t="b">
@@ -1754,12 +1758,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Preterm birth is the leading cause of infant mortality, resulting in more than 1 million neonatal deaths globally each year. Maternal urinary tract infection (UTI) during pregnancy increases risk for preterm birth; however, biological processes mediating UTI-associated preterm birth are not well described. We established a murine maternal UTI model in which challenge with uropathogenic Escherichia coli (UPEC) initiated preterm labor and birth in about half of dams. Although bacterial burdens were similar, dams experiencing preterm birth displayed excessive bladder inflammation, elevated placental and decidual cytokines, higher proportions of male fetuses, and lower maternal serum interleukin-10 (IL-10) compared with nonlaboring dams. Exogenous IL-10 or lymph node sequestration of T cells reduced placental type 17 T helper cells (TH17 cells) and abrogated preterm birth. In a human pregnancy cohort, we correlated urinary cytokines with birth outcomes and urine culture status. These analyses yielded an exploratory, noninvasive culture-agnostic system for evaluating preterm birth risk, implicating T cell-related cytokines including IL-10, IL-15, GM-CSF, and RANTES. These findings demonstrate that our murine model provides a platform to investigate immunological and microbial factors governing UTI-associated preterm birth and, coupled with patient samples, may be used to identify candidate biomarkers and mechanistic targets for future investigation.</t>
+          <t>Early pulmonary abnormalities after freshwater drowning can be overinterpreted as bacterial pneumonia, especially when inflammatory biomarkers and respiratory microbiology are positive. A 20-year-old man was resuscitated after approximately 2 min of freshwater submersion. Day 1 chest CT showed bilateral lower-lobe-predominant opacities compatible with non-cardiogenic pulmonary oedema and aspiration-related lung injury, with near-complete resolution by Day 25. Day 3 bronchoscopy showed diffuse, non-removable, millet-seed-like whitish tracheal mucosal protrusions with hyperaemia and oedema, compatible with acute irritative airway injury. BALF mNGS detected multiple gram-negative bacterial signals, predominantly Klebsiella pneumoniae, while sputum culture yielded ESBL-negative, susceptible K. pneumoniae. Possible drowning-associated pneumonia was considered because of aspiration, fever, markedly elevated inflammatory biomarkers and concordant microbiology; however, rapid radiological improvement and clinical stability suggested a substantial non-infectious component. The patient recovered after an 8-day course of piperacillin-tazobactam without antibiotic escalation, corticosteroids, mechanical ventilation or acute respiratory distress syndrome.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>本研究旨在探討孕婦尿路感染（UTI）導致早產的免疫機制。研究團隊建立尿路致病性大腸桿菌（UPEC）感染的孕鼠模型，發現發生早產的母鼠伴隨更嚴重的膀胱發炎、胎盤細胞激素升高及血清IL-10降低；給予外源性IL-10或抑制T細胞，能減少胎盤TH17細胞並預防早產。此外，人類佇列研究證實，尿液中T細胞相關細胞激素（如IL-10、IL-15等）與早產風險密切相關。本研究結合動物模型與臨床樣本，揭示了UTI引發早產的免疫關鍵，並為未來篩檢及治療提供了潛在的非侵入性生物標誌物與機制標靶。</t>
+          <t>本研究透過單一病例報告，探討淡水溺水後肺部浸潤與呼吸道損傷的臨床鑑別診斷。一名 20 歲男性溺水後出現肺水腫與氣道黏膜病變，臨床表現極易與細菌性肺炎混淆。研究利用 mNGS（宏基因組次世代定序）檢測支氣管肺泡灌洗液，雖確認存在肺炎克雷伯菌（*Klebsiella pneumoniae*）訊號，但影像學與臨床病程顯示其肺部損傷主要源於吸入性損傷及急性化學性氣道刺激，而非嚴重的細菌感染。此案例凸顯了臨床判斷溺水相關肺炎時的挑戰，強調在面對看似感染的臨床數據時，應綜合考量影像改善速度與臨床穩定性，避免過度診斷與不必要的抗生素升級，對急性溺水病患的精準治療具有重要的臨床參考價值。</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1769,37 +1773,37 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42647600/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42657129/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>42648218</t>
+          <t>42649294</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Agricultural sprinkler irrigation systems as environmental reservoirs and airborne dissemination sources of Legionella pneumophila.</t>
+          <t>Synergistic degradation of fucoidans in the ocean.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Journal of environmental management</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>8.4</v>
+        <v>48.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>metagenomics, small genome</t>
+          <t>metabolomics, metagenomics</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>未明確提及具體檢體數量（僅指出於西班牙東北部農村的兩個區域，針對灌溉池塘與溝渠進行採樣）</t>
+          <t>未提及（該研究採用重組海洋微生物群落進行實驗，未提供具體的生物樣本人數或檢體數量）</t>
         </is>
       </c>
       <c r="G26" t="b">
@@ -1807,12 +1811,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sprinkler irrigation systems are critical for modern agriculture but represent largely unrecognized aquatic environments capable of sustaining opportunistic human pathogens. Among them, Legionella pneumophila is of particular concern due to its ability to colonize engineered water systems, persist under fluctuating environmental conditions, and be transmitted through aerosols. In this study, we conducted a comprehensive microbiological and genomic investigation of irrigation ponds and ditches in a rural area of north-east Spain where two zones were sampled. Metagenomic profiling revealed highly diverse microbial communities encompassing more than 20,000 species, including 21 airborne-transmissible bacterial pathogens of clinical relevance. Notably, L. pneumophila was detected in both zones, with a relative abundance of up to 4.6 %. Culture-based isolation confirmed the presence of L. pneumophila serogroup 1, Pontiac group, Benidorm subgroup, sequence type 15. Phylogenetic analysis demonstrated a close relationship between this environmental strain and clinical isolates obtained during a Legionnaires' disease outbreak occurred in 2015, which had remained without a confirmed environmental source. Meteorological data from the exposure period revealed wind conditions favouring long-distance aerosol dispersion from irrigated fields toward residential areas. Our findings provide evidence that irrigation infrastructures can act as environmental reservoirs and dissemination routes of L. pneumophila among other airborne pathogens. These results underscore the need to incorporate agricultural irrigation systems into routine environmental surveillance, outbreak investigations, and public health risk assessments.</t>
+          <t>Fucoidans, a class of complex polysaccharides produced by brown algae and diatoms, contribute to long-term carbon sequestration owing to their resistance to microbial degradation1,2. Although individual microorganisms can break down portions of these polysaccharides3-5, it remains unclear whether complete breakdown is possible in nature and, if so, by what mechanisms. Here we show that fucoidans are degraded through synergistic interactions between specialized bacteria with complementary metabolic functions. Using metabolomic analysis of a reconstructed marine consortium, we uncovered metabolic guilds of bacteria that preferentially degrade either the sulfated fucose backbone or the side branches of rare monomers. This functional division of labour leads to an unexpectedly high number of synergistic interactions between different degraders that enhanced degradation efficiency up to 97.1%. Despite varying fucoidan structures across different types of algae6, the metabolic functions of degraders remained conserved, enabling quantitative prediction of degradation outcomes based on community and substrate composition. The frequent co-occurrence of functionally complementary fucoidan degraders in ocean metagenomes suggests that synergistic degradation is a globally relevant strategy. Our findings suggest that the environmental turnover of complex biopolymers depends not only on individual metabolic capabilities of degraders but also on ecological interactions shaped by substrate architecture. This work provides a mechanistic framework for understanding carbon cycling in the ocean and for engineering synthetic microbial consortia to degrade recalcitrant polysaccharides.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>本研究旨在探討農業噴灌系統是否為嗜肺軍團菌（*Legionella pneumophila*）等致病菌的環境宿主與空氣傳播源。團隊對西班牙農村灌溉水體進行分析，總體基因體學顯示其含有逾2萬種微生物，包括21種臨床相關的空氣傳播病原體，且嗜肺軍團菌相對豐度達4.6%。研究成功分離出嗜肺軍團菌血清型1（ST15），系統發育分析證實該環境株與2015年退伍軍人症爆發的臨床分離株高度相關。氣象數據亦支持風向有利於氣膠從農田長距離擴散至住宅區。此發現證實農業灌溉系統為軍團菌的傳播媒介，強調應將其納入例行環境監測與公衛風險評估。</t>
+          <t>本研究探討海洋中複雜多醣體「褐藻醣膠」（fucoidans）的微生物降解機制。儘管褐藻醣膠因其抗降解性在碳封存中扮演關鍵角色，但過往對於其在自然界中是否能被完全分解並不清楚。研究發現，褐藻醣膠的降解並非單一物種所能完成，而是透過具有互補代謝功能的細菌群落進行「協同作用」。透過代謝體學分析，研究團隊識別出專門降解硫酸岩藻糖骨架與稀有單醣側鏈的代謝群組（metabolic guilds），這種分工合作能將降解效率大幅提升至 97.1%。此外，研究顯示此代謝功能在不同環境下具有高度保守性，且在海洋宏基因組中普遍存在。本研究揭示了生物聚合物的環境周轉率取決於微生物間的生態交互作用，為理解海洋碳循環機制提供了重要框架，並為未來利用人工合成微生物群落降解頑固性多醣體提供了技術基礎。</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1822,37 +1826,35 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42648218/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42649294/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>42648293</t>
+          <t>42644746</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Defined human Clostridia consortia reverse colitis via dual effects of tryptophan metabolites on microbiota and immunity.</t>
+          <t>Metabolic division of labour drives estuarine-coastal N2O emissions.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cell host &amp; microbe</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>18.7</v>
-      </c>
+          <t>The ISME journal</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>metagenomics, metabolomics</t>
+          <t>metagenomics, metatranscriptomics</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>974 個重建的 N2O 相關基因體（原文未提及具體的環境樣本採集數量）</t>
         </is>
       </c>
       <c r="G27" t="b">
@@ -1860,12 +1862,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Microbial dysbiosis and disrupted mucosal immune homeostasis are integrally involved in the pathogenesis of inflammatory bowel diseases (IBDs). Live biotherapeutic products (LBPs) offer a potential therapeutic strategy to restore beneficial microbes and mitigate disease. We investigated the therapeutic efficacy of 2 LBPs, human Clostridia consortia 17-mix and 11-mix, by treating established colitis in murine models. Both LBPs exhibited therapeutic effects in T cell-mediated chronic colitis models induced by human microbiota and in pathobiont-driven gnotobiotic colitis models established with combinations of IBD-relevant human-derived strains. Metagenomic and metabolomic analyses elucidated mechanisms that go beyond established functions driven by short-chain fatty acids (SCFAs) and interleukin (IL)-10-producing regulatory T cells. Notably, LBPs exerted therapeutic effects by directly inhibiting resident pathobionts and through IL-10-independent activation of host anti-inflammatory aryl hydrocarbon receptor (AhR) pathways by bacterial tryptophan metabolites. These results elucidate SCFA- and IL-10-independent protective mechanisms exerted by defined resident bacterial strains that are depleted in IBD dysbiosis.</t>
+          <t>Estuarine and coastal systems are global hotspots of marine nitrous oxide (N2O) emissions, where microbial nitrification and denitrification are the primary processes regulating N2O dynamics. However, how interactions among different N2O-associated microorganisms influence ecosystem-scale N2O emissions remains poorly understood. This study combined in situ N2O concentrations, 15N-based potential rates, metagenomics, metatranscriptomics, and genome-scale metabolic model analysis to explore N2O production and reduction processes in estuarine and coastal systems. Potential N2O production and reduction rates, together with in situ concentrations, the relative abundance, and the transcriptional activity of associated genes, were significantly higher at low salinity and declined toward coastal regions. Based on the gene content of 974 recovered N2O-associated genomes, microorganisms were classified into three functional groups: net N2O producers, net N2O consumers, and self-sustaining N2O players. The abundance, composition, and activity of these functional groups shifted along estuarine-coastal gradients. A larger NO/N2O exchange gap, reflecting the imbalance between model-inferred NO and N2O handoff potentials, was found at low salinity and was associated with elevated bottom-water N2O concentrations. Together, community-level division of labour and the associated exchange gap provide a conceptual framework for linking N2O-related functional groups to N2O accumulation in estuarine-coastal ecosystems.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>本研究探討了兩種由人類梭狀芽孢桿菌組成的活體生物藥物（LBP，分別為 17-mix 和 11-mix）治療小鼠結腸炎的療效與機制。研究發現，這些菌群能有效緩解小鼠的慢性與特定病原體誘導的結腸炎。宏基因組學與代謝組學分析顯示，除了傳統的短鏈脂肪酸（SCFA）和 IL-10 途徑外，LBP 還能直接抑制共生病原菌，並透過細菌色胺酸代謝物，以不依賴 IL-10 的方式激活宿主的芳香烴受體（AhR）抗炎途徑。此發現揭示了腸道有益菌保護腸道的新機制，為發炎性腸道疾病（IBD）的微生態療法提供了重要科學依據。</t>
+          <t>本研究旨在探討河口與沿海系統中，微生物交互作用如何驅動一氧化二氮（N2O）的排放。研究結合現場觀測、15N同位素速率、總體基因體與轉錄體學，重建了974個N2O相關基因體。結果指出，低鹽度區域的N2O產生與還原速率及基因表達顯著較高。研究將微生物劃分為淨產生者、淨消費者與自給自足者，並發現低鹽度區因群落間物質交換失衡，存在較大的NO/N2O交換缺口，進而導致底層水體N2O顯著累積。本研究建立了群落水平的「分工與交換缺口」理論框架，為預測及理解海洋生態系統N2O排放提供了關鍵的科學依據。</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1875,7 +1877,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42648293/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42644746/</t>
         </is>
       </c>
     </row>
@@ -1935,28 +1937,30 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>42644746</t>
+          <t>42648293</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Metabolic division of labour drives estuarine-coastal N2O emissions.</t>
+          <t>Defined human Clostridia consortia reverse colitis via dual effects of tryptophan metabolites on microbiota and immunity.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>The ISME journal</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>Cell host &amp; microbe</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>18.7</v>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>metagenomics, metatranscriptomics</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>974 個重建的 N2O 相關基因體（原文未提及具體的環境樣本採集數量）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G29" t="b">
@@ -1964,12 +1968,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Estuarine and coastal systems are global hotspots of marine nitrous oxide (N2O) emissions, where microbial nitrification and denitrification are the primary processes regulating N2O dynamics. However, how interactions among different N2O-associated microorganisms influence ecosystem-scale N2O emissions remains poorly understood. This study combined in situ N2O concentrations, 15N-based potential rates, metagenomics, metatranscriptomics, and genome-scale metabolic model analysis to explore N2O production and reduction processes in estuarine and coastal systems. Potential N2O production and reduction rates, together with in situ concentrations, the relative abundance, and the transcriptional activity of associated genes, were significantly higher at low salinity and declined toward coastal regions. Based on the gene content of 974 recovered N2O-associated genomes, microorganisms were classified into three functional groups: net N2O producers, net N2O consumers, and self-sustaining N2O players. The abundance, composition, and activity of these functional groups shifted along estuarine-coastal gradients. A larger NO/N2O exchange gap, reflecting the imbalance between model-inferred NO and N2O handoff potentials, was found at low salinity and was associated with elevated bottom-water N2O concentrations. Together, community-level division of labour and the associated exchange gap provide a conceptual framework for linking N2O-related functional groups to N2O accumulation in estuarine-coastal ecosystems.</t>
+          <t>Microbial dysbiosis and disrupted mucosal immune homeostasis are integrally involved in the pathogenesis of inflammatory bowel diseases (IBDs). Live biotherapeutic products (LBPs) offer a potential therapeutic strategy to restore beneficial microbes and mitigate disease. We investigated the therapeutic efficacy of 2 LBPs, human Clostridia consortia 17-mix and 11-mix, by treating established colitis in murine models. Both LBPs exhibited therapeutic effects in T cell-mediated chronic colitis models induced by human microbiota and in pathobiont-driven gnotobiotic colitis models established with combinations of IBD-relevant human-derived strains. Metagenomic and metabolomic analyses elucidated mechanisms that go beyond established functions driven by short-chain fatty acids (SCFAs) and interleukin (IL)-10-producing regulatory T cells. Notably, LBPs exerted therapeutic effects by directly inhibiting resident pathobionts and through IL-10-independent activation of host anti-inflammatory aryl hydrocarbon receptor (AhR) pathways by bacterial tryptophan metabolites. These results elucidate SCFA- and IL-10-independent protective mechanisms exerted by defined resident bacterial strains that are depleted in IBD dysbiosis.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>本研究旨在探討河口與沿海系統中，微生物交互作用如何驅動一氧化二氮（N2O）的排放。研究結合現場觀測、15N同位素速率、總體基因體與轉錄體學，重建了974個N2O相關基因體。結果指出，低鹽度區域的N2O產生與還原速率及基因表達顯著較高。研究將微生物劃分為淨產生者、淨消費者與自給自足者，並發現低鹽度區因群落間物質交換失衡，存在較大的NO/N2O交換缺口，進而導致底層水體N2O顯著累積。本研究建立了群落水平的「分工與交換缺口」理論框架，為預測及理解海洋生態系統N2O排放提供了關鍵的科學依據。</t>
+          <t>本研究探討了兩種由人類梭狀芽孢桿菌組成的活體生物藥物（LBP，分別為 17-mix 和 11-mix）治療小鼠結腸炎的療效與機制。研究發現，這些菌群能有效緩解小鼠的慢性與特定病原體誘導的結腸炎。宏基因組學與代謝組學分析顯示，除了傳統的短鏈脂肪酸（SCFA）和 IL-10 途徑外，LBP 還能直接抑制共生病原菌，並透過細菌色胺酸代謝物，以不依賴 IL-10 的方式激活宿主的芳香烴受體（AhR）抗炎途徑。此發現揭示了腸道有益菌保護腸道的新機制，為發炎性腸道疾病（IBD）的微生態療法提供了重要科學依據。</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1979,39 +1983,37 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42644746/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648293/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>42649294</t>
+          <t>42648218</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Synergistic degradation of fucoidans in the ocean.</t>
+          <t>Agricultural sprinkler irrigation systems as environmental reservoirs and airborne dissemination sources of Legionella pneumophila.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nature</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>48.5</t>
-        </is>
+          <t>Journal of environmental management</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>8.4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>metabolomics, metagenomics</t>
+          <t>metagenomics, small genome</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>未提及（該研究採用重組海洋微生物群落進行實驗，未提供具體的生物樣本人數或檢體數量）</t>
+          <t>未明確提及具體檢體數量（僅指出於西班牙東北部農村的兩個區域，針對灌溉池塘與溝渠進行採樣）</t>
         </is>
       </c>
       <c r="G30" t="b">
@@ -2019,12 +2021,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Fucoidans, a class of complex polysaccharides produced by brown algae and diatoms, contribute to long-term carbon sequestration owing to their resistance to microbial degradation1,2. Although individual microorganisms can break down portions of these polysaccharides3-5, it remains unclear whether complete breakdown is possible in nature and, if so, by what mechanisms. Here we show that fucoidans are degraded through synergistic interactions between specialized bacteria with complementary metabolic functions. Using metabolomic analysis of a reconstructed marine consortium, we uncovered metabolic guilds of bacteria that preferentially degrade either the sulfated fucose backbone or the side branches of rare monomers. This functional division of labour leads to an unexpectedly high number of synergistic interactions between different degraders that enhanced degradation efficiency up to 97.1%. Despite varying fucoidan structures across different types of algae6, the metabolic functions of degraders remained conserved, enabling quantitative prediction of degradation outcomes based on community and substrate composition. The frequent co-occurrence of functionally complementary fucoidan degraders in ocean metagenomes suggests that synergistic degradation is a globally relevant strategy. Our findings suggest that the environmental turnover of complex biopolymers depends not only on individual metabolic capabilities of degraders but also on ecological interactions shaped by substrate architecture. This work provides a mechanistic framework for understanding carbon cycling in the ocean and for engineering synthetic microbial consortia to degrade recalcitrant polysaccharides.</t>
+          <t>Sprinkler irrigation systems are critical for modern agriculture but represent largely unrecognized aquatic environments capable of sustaining opportunistic human pathogens. Among them, Legionella pneumophila is of particular concern due to its ability to colonize engineered water systems, persist under fluctuating environmental conditions, and be transmitted through aerosols. In this study, we conducted a comprehensive microbiological and genomic investigation of irrigation ponds and ditches in a rural area of north-east Spain where two zones were sampled. Metagenomic profiling revealed highly diverse microbial communities encompassing more than 20,000 species, including 21 airborne-transmissible bacterial pathogens of clinical relevance. Notably, L. pneumophila was detected in both zones, with a relative abundance of up to 4.6 %. Culture-based isolation confirmed the presence of L. pneumophila serogroup 1, Pontiac group, Benidorm subgroup, sequence type 15. Phylogenetic analysis demonstrated a close relationship between this environmental strain and clinical isolates obtained during a Legionnaires' disease outbreak occurred in 2015, which had remained without a confirmed environmental source. Meteorological data from the exposure period revealed wind conditions favouring long-distance aerosol dispersion from irrigated fields toward residential areas. Our findings provide evidence that irrigation infrastructures can act as environmental reservoirs and dissemination routes of L. pneumophila among other airborne pathogens. These results underscore the need to incorporate agricultural irrigation systems into routine environmental surveillance, outbreak investigations, and public health risk assessments.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>本研究探討海洋中複雜多醣體「褐藻醣膠」（fucoidans）的微生物降解機制。儘管褐藻醣膠因其抗降解性在碳封存中扮演關鍵角色，但過往對於其在自然界中是否能被完全分解並不清楚。研究發現，褐藻醣膠的降解並非單一物種所能完成，而是透過具有互補代謝功能的細菌群落進行「協同作用」。透過代謝體學分析，研究團隊識別出專門降解硫酸岩藻糖骨架與稀有單醣側鏈的代謝群組（metabolic guilds），這種分工合作能將降解效率大幅提升至 97.1%。此外，研究顯示此代謝功能在不同環境下具有高度保守性，且在海洋宏基因組中普遍存在。本研究揭示了生物聚合物的環境周轉率取決於微生物間的生態交互作用，為理解海洋碳循環機制提供了重要框架，並為未來利用人工合成微生物群落降解頑固性多醣體提供了技術基礎。</t>
+          <t>本研究旨在探討農業噴灌系統是否為嗜肺軍團菌（*Legionella pneumophila*）等致病菌的環境宿主與空氣傳播源。團隊對西班牙農村灌溉水體進行分析，總體基因體學顯示其含有逾2萬種微生物，包括21種臨床相關的空氣傳播病原體，且嗜肺軍團菌相對豐度達4.6%。研究成功分離出嗜肺軍團菌血清型1（ST15），系統發育分析證實該環境株與2015年退伍軍人症爆發的臨床分離株高度相關。氣象數據亦支持風向有利於氣膠從農田長距離擴散至住宅區。此發現證實農業灌溉系統為軍團菌的傳播媒介，強調應將其納入例行環境監測與公衛風險評估。</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2034,31 +2036,27 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42649294/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648218/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>42657129</t>
+          <t>42644751</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pulmonary Infiltrates, Airway Mucosal Lesions and Respiratory Microbiology After Freshwater Drowning: A Case Report.</t>
+          <t>Soil amelioration impacts viral ecology in saline-alkali lands.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Respirology case reports</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>The ISME journal</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>metagenomics</t>
@@ -2066,7 +2064,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1 例病患（n=1）</t>
+          <t>未提及（僅說明樣品來自中國4個主要鹽鹼地區，各包含「鹽鹼」與「改良後」兩種狀態之土壤）</t>
         </is>
       </c>
       <c r="G31" t="b">
@@ -2074,12 +2072,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Early pulmonary abnormalities after freshwater drowning can be overinterpreted as bacterial pneumonia, especially when inflammatory biomarkers and respiratory microbiology are positive. A 20-year-old man was resuscitated after approximately 2 min of freshwater submersion. Day 1 chest CT showed bilateral lower-lobe-predominant opacities compatible with non-cardiogenic pulmonary oedema and aspiration-related lung injury, with near-complete resolution by Day 25. Day 3 bronchoscopy showed diffuse, non-removable, millet-seed-like whitish tracheal mucosal protrusions with hyperaemia and oedema, compatible with acute irritative airway injury. BALF mNGS detected multiple gram-negative bacterial signals, predominantly Klebsiella pneumoniae, while sputum culture yielded ESBL-negative, susceptible K. pneumoniae. Possible drowning-associated pneumonia was considered because of aspiration, fever, markedly elevated inflammatory biomarkers and concordant microbiology; however, rapid radiological improvement and clinical stability suggested a substantial non-infectious component. The patient recovered after an 8-day course of piperacillin-tazobactam without antibiotic escalation, corticosteroids, mechanical ventilation or acute respiratory distress syndrome.</t>
+          <t>The continuous expansion of saline-alkali lands under climate change threatens food security and reduces soil carbon stocks. A common mitigation strategy is soil amelioration, which converts degraded soils back into an arable state. Microbes play critical roles in soil health and recovery. However, the viruses that infect these microbial communities, and their potential impacts during saline-alkali soil restoration, remain largely unknown. Here, we combined total soil metagenomics and viromics to investigate host-linked viral ecology across four major saline-alkali regions in China, each encompassing two soil amelioration statuses: saline-alkali and reclaimed. We found that viral community structure was shaped by both geography and soil amelioration status, with salinity and alkalinity emerging as key environmental factors. Viral populations were sensitive to soil restoration, showing strong amelioration-status endemism with functional adaptations. Virus-host dynamics ranged from reduced temperate viruses to abundance mismatches in those infecting key carbon-cycling microorganisms, including carbohydrate degraders. 13C-cellulose DNA-SIP experiments provided further support for this mismatch by tracing assimilated carbon transfer between active host and virus populations. Compared with saline-alkali soils, the relative abundance of hosts in restored soils increased from 39.0% to 61.0%, whereas the linked viruses decreased from 60.6% to 39.4%. Together, these findings reveal an underappreciated role of viruses in shaping saline-alkali soil amelioration trajectories, and could improve management strategies for degraded land recovery and carbon storage.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>本研究透過單一病例報告，探討淡水溺水後肺部浸潤與呼吸道損傷的臨床鑑別診斷。一名 20 歲男性溺水後出現肺水腫與氣道黏膜病變，臨床表現極易與細菌性肺炎混淆。研究利用 mNGS（宏基因組次世代定序）檢測支氣管肺泡灌洗液，雖確認存在肺炎克雷伯菌（*Klebsiella pneumoniae*）訊號，但影像學與臨床病程顯示其肺部損傷主要源於吸入性損傷及急性化學性氣道刺激，而非嚴重的細菌感染。此案例凸顯了臨床判斷溺水相關肺炎時的挑戰，強調在面對看似感染的臨床數據時，應綜合考量影像改善速度與臨床穩定性，避免過度診斷與不必要的抗生素升級，對急性溺水病患的精準治療具有重要的臨床參考價值。</t>
+          <t>本研究旨在探討鹽鹼地改良過程中，病毒對土壤微生物生態與碳循環的影響。研究結合總體基因體與病毒體學，分析中國四大鹽鹼區。結果顯示，土壤改良狀態、鹽度與鹼度是塑造病毒社群的關鍵。在改良土壤中，宿主微生物相對豐度顯著上升（39.0%至61.0%），而關聯病毒減少（60.6%至39.4%），且溫和病毒比例降低，碳循環關鍵微生物的病毒與宿主出現豐度失衡。13C-纖維素DNA-SIP實驗證實了兩者間的活性碳轉移。此發現揭示了病毒在鹽鹼地恢復中的關鍵作用，有助優化土地改良與碳儲存策略。</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2089,37 +2087,37 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42657129/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42644751/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>42642836</t>
+          <t>42647084</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Microbiome-mediated regulation of pathogen virulence: Molecular mechanisms and clinical implications.</t>
+          <t>Diet quality, gut microbiome, and inflammatory signatures in Puerto Rican adults with Crohn disease: a multidimensional analysis.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Virulence</t>
+          <t>Inflammatory bowel diseases</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>60位患有克隆氏症的成年人 (60 adults with CD)</t>
         </is>
       </c>
       <c r="G32" t="b">
@@ -2127,627 +2125,623 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>The human microbiome profoundly influences pathogen virulence and disease susceptibility through diverse molecular mechanisms. This review, focused on literature from 2016 to 2026, synthesizes knowledge on microbiome-mediated regulation examining major pathogens including Vibrio cholerae, enterohemorrhagic Escherichia coli, Salmonella species, Clostridioides difficile, and Staphylococcus aureus. A triangular interaction model is presented, linking host immunity, resident microbiome, and invading pathogen to frame infection outcomes. Commensal bacteria regulate pathogen behavior through quorum sensing interference, metabolite-mediated regulation via short-chain fatty acids and bile acids, competitive exclusion, immune response modulation, and direct antimicrobial production. Key species-Lactobacillus spp. Bifidobacterium spp. Bacteroides thetaiotaomicron, and Faecalibacterium prausnitzii-employ distinct molecular strategies against these pathogens. Organ-on-chip platforms and multi-omics advances reveal context-dependent interactions. Clinical applications including rationally designed probiotics, fecal microbiota transplantation, and precision microbiome engineering show promise despite challenges of inter-individual microbiome variability, representing a paradigm shift toward ecosystem-based infectious disease management.</t>
+          <t>Diet is increasingly recognized as a modifiable factor influencing gut microbiome and outcomes in Crohn disease (CD), yet data in underrepresented populations remain limited. We evaluated diet quality, dietary patterns, gut microbiome composition, inflammatory markers, and patient-reported outcomes in adults with CD from Puerto Rico. We conducted a cross-sectional analysis of 60 adults with CD enrolled prior to dietary intervention in a parent study. Dietary intake was assessed using 24-hour recalls and evaluated using the Healthy Eating Index-2015 (HEI-2015), Alternative Healthy Eating Index-2010 (AHEI-2010), and exploratory dietary pattern analysis. The gut microbiome was assessed by shotgun metagenomic sequencing. Clinical outcomes included fecal calprotectin, C-reactive protein (CRP), a 96-cytokine panel, short Crohn Disease Activity Index (sCDAI), and short Inflammatory Bowel Disease Questionnaire (sIBDQ). Associations were evaluated using unadjusted and adjusted models with false discovery rate (FDR) correction. Overall diet quality was poor and characterized by low intake of fruits, vegetables, whole grains, and fiber, alongside high intake of saturated fat, added sugars, and animal-derived protein. Four dietary patterns were identified: vegetable-rich, dairy-rich, fruit-rich, and coffee/sweetener-rich. Participants adhering to the fruit-rich pattern exhibited the highest diet quality scores. Higher HEI-2015 scores were associated with greater gut microbial diversity and differences in overall microbiome composition. Participants with greater adherence to the vegetable-rich pattern showed modest increases in microbial diversity. Exploratory analyses suggested that higher fruit intake and adherence to a fruit-rich dietary pattern were associated with lower fecal calprotectin and CRP levels, whereas adherence to a vegetable-rich pattern was associated with better health-related quality of life (HRQoL) and adherence to a coffee/sweetener-rich pattern was associated with a worse symptom burden. However, no associations between dietary metrics and inflammatory markers, cytokines, or clinical outcomes remained significant after FDR correction. Most participants were in clinical remission despite substantial impairment in HRQoL. Adults with CD in Puerto Rico exhibited poor diet quality that was associated with gut microbial diversity and exploratory differences in clinical outcomes. While these findings support the influence of diet on the microbiome and clinical outcomes, larger longitudinal studies are needed to determine whether dietary improvements can influence disease outcomes this underrepresented population.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>本研究綜述了2016年至2026年間關於腸道微生物群調控病原體毒力（如霍亂弧菌、大腸桿菌、沙門氏菌等）的分子機制。作者提出了一個結合宿主免疫、共生菌群與入侵病原體的「三角交互模型」，闡述了共生菌如何透過群體感應干擾、代謝產物（如短鏈脂肪酸、膽汁酸）調節、競爭性排斥及免疫調節來抑制病原體。研究強調了乳酸桿菌、雙歧桿菌及普拉梭菌等關鍵菌種的保護機制，並探討了器官晶片與多體學技術在揭示交互作用上的貢獻。此研究主張從生態系統角度管理傳染病，指出益生菌設計、糞便菌群移植及精準微生物組工程是未來治療的關鍵方向，雖面臨個體差異挑戰，但為臨床感染控制提供了典範轉移。</t>
+          <t>本研究探討波多黎各克隆氏症（CD）成年患者的飲食品質、腸道菌相與發炎指標的關係。研究發現，受試者普遍飲食品質不佳，而較高的飲食品質（特別是富含水果的飲食模式）與較高的腸道菌群多樣性顯著相關。探索性分析顯示，多攝取水果與較低的發炎指標（鈣衛蛋白和C反應蛋白）相關，而蔬菜為主的飲食與較佳的生活品質相關（但經FDR校正後未達顯著）。本研究首次揭示了該少數受關注族群中飲食對菌相與臨床症狀的影響，為未來透過飲食干預管理CD及改善患者預後提供了科學依據。</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42642836/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647084/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>42647164</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Sex differences in the gut microbiome and related metabolites: role in cardiometabolic disease.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Gut microbes</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>未提及（本文為綜論性回顧文章，非原創實驗研究）</t>
+        </is>
+      </c>
+      <c r="G33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sex differences in major cardiometabolic diseases (CMD), such as type 2 diabetes, metabolic dysfunction-associated steatotic liver disease, and cardiovascular disease, have been increasingly recognized across the life course. During the reproductive stage, women generally have a more favorable cardiometabolic risk profile than men, but their risk of experiencing CMD significantly increases after menopause. Emerging evidence suggests that sexually dimorphic gut microbiota and gut microbiota-related metabolites (GMRMs) may contribute to such sex disparities. However, existing findings are heterogeneous and underlying mechanisms remain incompletely understood. In this review, we synthesize the evidence examining sex differences in gut microbial diversity, overall composition, taxa abundances, and levels of GMRMs across key life stages, including pre-puberty, adolescence, and different phases of adulthood (with emphasis on pre- and post-menopausal periods). We summarize potential biological mechanisms underlying sexual dimorphism in the gut microbiome and GMRMs, emphasizing the central role of sex steroids, along with contributions from immune function and other host and environmental factors. We further integrate evidence linking sexually dimorphic microbial taxa (e.g., Akkermansia muciniphila, Eubacterium, Ruminococcus, and other Firmicutes taxa) and GMRMs (e.g., microbiota-derived short-chain fatty acids, secondary bile acids, and trimethylamine N-oxide) to key cardiometabolic pathways involving inflammation, glucose and lipid metabolism, and vascular function. Finally, we identify critical knowledge gaps and emphasize the need for future large longitudinal studies that would integrate repeated measurements of the gut microbiome, untargeted metabolomics, and sex steroid hormones across the life course. Such approaches are essential to clarify biological pathways and inform sex-specific microbiome-based interventions for CMD prevention and management.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>本文旨在探討性別差異在腸道微生物群與相關代謝物（GMRMs）中如何影響心臟代謝疾病（CMD）。研究指出，受性類固醇、免疫功能及環境因素影響，腸道菌相與代謝產物存在顯著的性別二態性。女性在生育期較男性具備更佳的心臟代謝特徵，但停經後風險顯著升高，此變化與特定菌屬（如 *Akkermansia muciniphila*）及代謝物（如短鏈脂肪酸、次級膽汁酸、TMAO）的豐度改變密切相關。這些微生物與代謝物透過調節發炎反應、醣脂代謝及血管功能，進而影響 CMD 的發生。本文強調未來需透過大型縱向研究，結合微生物組學、代謝組學與荷爾蒙監測，以深入解析其生物學機制，並開發針對不同性別的精準微生物介入療法，對於預防及管理心臟代謝疾病具有重要的科學價值。</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647164/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>42647759</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>The Gut Microbiome in Multiple Sclerosis.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Neurology(R) neuroimmunology &amp; neuroinflammation</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Multiple sclerosis (MS) is a chronic inflammatory demyelinating disease of the CNS whose risk and course are shaped by both genetic and environmental factors, among which the intestinal microbiota has emerged as a key, potentially modifiable contributor. People with MS frequently display altered gut microbiota, characterized by depletion of fiber-fermenting, short-chain fatty acid (SCFA)-producing commensals, and expansion of taxa associated with mucus degradation and proinflammatory metabolism. These compositional shifts are paralleled by broad changes in blood and CSF metabolites, including reduced SCFAs, tryptophan-derived aryl hydrocarbon receptor ligands, and secondary bile acids. In addition, several reports highlight the accumulation of aromatic amino acid-derived phenolic and indolic compounds and specific lipid mediators linked to neuroinflammation and neurodegeneration. In this up-to-date review, we synthesize evidence from experimental models and human studies showing how microbial metabolites can influence MS pathogenesis through converging mechanisms: modulation of gut and blood-brain barrier integrity; shaping of T-cell and B-cell responses; direct effects on microglia, astrocytes, and oligodendrocyte lineage cells after crossing into the CNS; and modulation of neural circuits, particularly those involving the vagus nerve. Finally, we highlight current gaps, including the need for longitudinal, harmonized multiomic cohorts, and mechanistic studies integrating microbiome, metabolome, and host readouts across gut, blood, and CNS. Overall, available data support a model in which coordinated disruption of the gut microbiota-metabolite axis, rather than any single pathogen, contributes to MS, opening avenues for microbiota-based and metabolite-based biomarkers and therapies aimed at restoring immune and neuroglial homeostasis.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>本研究探討多發性硬化症（MS）與腸道微生物群之間的關聯。研究指出，MS 患者的腸道菌相呈現失調狀態，包括短鏈脂肪酸（SCFA）產生菌減少，以及促發炎代謝菌的增加。這些微生物群落的變化伴隨著血液與腦脊髓液中代謝物（如色胺酸衍生物、膽汁酸及 SCFA）的顯著改變，這些物質經證實與神經發炎及退化密切相關。文中綜述了微生物代謝產物如何透過調節腸道與血腦屏障完整性、影響免疫細胞（T/B 細胞）反應，以及直接作用於神經膠質細胞來參與 MS 的致病機制。總結而言，MS 的發生與腸道菌群-代謝物軸的整體失調有關，而非單一病原體所致。該研究強調未來需進行多體學（multiomics）整合分析，以開發基於微生物群的生物標記與創新治療策略，旨在恢復患者的免疫與神經恆定。</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647759/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>42648171</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Co-occurrence of muddy off flavor and cyanotoxin genes in the polluted Guandu river waters (Rio de Janeiro, Brazil).</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>The Science of the total environment</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>metagenomics</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G35" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>The Guandu river basin is responsible for supplying Rio de Janeiro municipality, Brazil, with drinking water. This study investigated water quality during the geosmin crisis in January and March 2020, by relating the water quality and odor compounds with metagenomic tools. Guandu river water was eutrophic. The cyanobacterial genera identified were Microcystis, Planktothrix, Dolichospermum, Nostoc, Synechococcus, Planktothricoides, and Cyanobium, indicating that bloom-associated communities in the system are taxonomically diverse. Functional annotation of metagenomic sequences revealed the presence of genes associated with the biosynthesis of taste-and-odor compounds, including geosmin (geoA) and 2-methylisoborneol (mic), as well as multiple biosynthetic clusters related to cyanotoxin production. Genes linked to microcystin (mcy), saxitoxin (sxt), anatoxin (ana), cylindrospermopsin (cyr), lyngbyatoxin (ltx), guanitoxin (gnt), and nodularin (nda) were detected across the dataset, indicating a broad genetic potential for the production of secondary metabolites relevant to water quality. The co-occurrence of cyanotoxins, geosmin and 2-MIB genes suggests that off-flavor is an indication of cyanotoxin potential production in the water.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>本研究旨在探究巴西里約熱內盧瓜杜河於2020年初爆發土臭素危機期間的水質狀況，並利用總體基因體學技術探討水質異味與微生物群落之關聯。研究發現，該富營養化水體中含有多種藍菌，且功能性註釋顯示其富含合成土臭素（*geoA*）與2-甲基異莰醇（*mic*）等異味物質的基因。更重要的是，多種藍菌毒素（如微囊藻毒素、石房蛤毒素等）的合成基因群與這些異味基因呈現共存。此發現證實了水體異味的出現與藍菌毒素的潛在生成具有高度相關性，可作為飲用水安全監測及評估藍菌毒素潛在危害的重要預警指標。</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648171/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>42644416</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Nationwide cohort study reveals low bifidobacteria and distinct microbiota composition and function in Swedish newborns.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Gut microbes</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>metagenomics</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>308 名瑞典新生兒的糞便檢體</t>
+        </is>
+      </c>
+      <c r="G36" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>NCT06285630.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>本研究旨在探討瑞典新生兒的腸道菌相組成與功能特徵。透過總體基因體學分析，研究發現瑞典新生兒腸道中的雙歧桿菌（特別是嬰兒雙歧桿菌）豐度顯著偏低，並呈現出獨特的菌相結構與代謝功能。此現象與現代化生活型態及分娩方式密切相關。這項全國性世代研究揭示了現代環境對嬰兒早期腸道微生態建立的深遠影響，為未來的臨床嬰幼兒益生菌介入與健康照護策略提供了關鍵的科學依據。</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42644416/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>42641146</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Engineered bacterial therapeutics from synthetic biology to clinical translation: A multi-database scientometric analysis, 2000-2026.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Human vaccines &amp; immunotherapeutics</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1,730 篇學術文章與評論</t>
+        </is>
+      </c>
+      <c r="G37" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Engineered bacterial therapeutics integrate programmable strain engineering with biomedical functions such as sensing, delivery, immune modulation, microbiome intervention, and disease management. This study conducted a multi-database bibliometric analysis to map the knowledge structure, collaboration patterns, and translational direction of this field. Bibliographic records were retrieved from Web of Science Core Collection, Scopus, and PubMed for publications from 1 January 2000 to 1 June 2026. After document-type filtering, time restriction, deduplication, language screening, and manual eligibility assessment, 1,730 English-language articles and reviews were included. CiteSpace 6.4.R1, VOSviewer 1.6.20, and the bibliometrix R package were used to analyze publication trends, collaboration networks, journal co-citation, dual-map citation trajectories, citation bursts, keyword co-occurrence, and thematic evolution. Publication output increased steadily, with faster growth after 2020; 2025 was the highest-output complete year, while 2026 represented a partial retrieval year. China and the United States were the leading contributors, although institutional collaboration remained regionally clustered. Co-citation, citation-burst, and keyword analyses showed a shift from bacterial chassis construction and circuit design toward engineered probiotics, gut microbiota-related therapy, cancer immunotherapy, drug delivery, live biotherapeutic products, and clinical translation. Persistent translational priorities include controllability, safety, manufacturing consistency, and regulatory alignment.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>本研究透過文獻計量學方法，系統性分析 2000 年至 2026 年間有關「工程化細菌治療」的 1,730 篇學術文獻。研究旨在釐清該領域的知識結構、國際合作模式及臨床轉化趨勢。分析顯示，該領域自 2020 年後顯著加速發展，中國與美國為主要貢獻國。核心研究主軸已由早期的細菌底盤構建與基因電路設計，轉向工程化益生菌、癌症免疫治療、藥物遞送及活體生物藥物（LBP）的開發。科學意義在於確立了該領域從實驗室轉向臨床應用的優先議題，即解決控制力、生物安全性、生產一致性與法規調適等挑戰，為未來工程化細菌作為精準醫療工具的發展提供關鍵決策參考。</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42641146/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>42642834</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Glycosylation in gut-brain communication: from the intestinal barrier and microbiota to immune and neural signaling.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Gut microbes</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G38" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>The gut-brain axis is a complex bidirectional communication network linking the gastrointestinal tract and the central nervous system. Its dysregulation is closely associated with a wide range of gastrointestinal, metabolic, and neuropsychiatric disorders. Glycosylation, one of the most prevalent and structurally diverse post-translational modifications of proteins and lipids, is increasingly recognized as a regulator of multiple processes within the gut-brain axis. In this review, we summarize evidence that glycosylation influences several steps of gut-brain communication, including intestinal barrier function, microbial glycan metabolism, immune signaling, enteric and vagal pathways, blood-brain barrier integrity, and neural responses. We distinguish direct mechanistic findings from associative observations and discuss the more limited evidence for brain-to-gut regulation of intestinal glycosylation. In addition, we discuss the potential of glycosylation-targeted nutritional and microbiota-based interventions and highlight emerging opportunities to integrate glycomics with other omics approaches to dissect the complex regulatory networks underlying the gut-brain axis. In conclusion, elucidating how glycosylation shapes signaling along the gut-brain axis may open new avenues for understanding disease pathogenesis and for developing targeted therapeutic strategies.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>本文探討「腸-腦軸線」（Gut-Brain Axis）中醣基化（Glycosylation）修飾的關鍵調節角色。醣基化作為蛋白質與脂質重要的轉譯後修飾，深刻影響腸道屏障功能、微生物聚醣代謝、免疫訊息傳遞及血腦屏障完整性。研究重點解析了醣基化如何調控腸道與中樞神經系統間的溝通，並區分了機制性證據與相關性觀察。本文不僅強調了醣基化在維繫軸線穩定中的核心地位，更提出透過營養干預與微生物調節，結合多體學（Omics）分析醣基化網絡，將有望為神經精神疾病與代謝性障礙提供創新的診斷與治療策略。</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42642834/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>42640100</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Revisiting gut microbiota-driven ammonia metabolism: from disease burden to physiological adaptation.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Gut microbes</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G39" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Ammonia homeostasis is governed by interconnected host and microbial pathways, including hepatic ureagenesis, glutamine synthesis, and gut microbiota-mediated urea hydrolysis, proteolysis, and amino acid deamination. Ammonia has historically been viewed primarily as a nitrogenous waste product and neurotoxic molecule, a concept strongly supported by studies of hyperammonemia and hepatic encephalopathy. Impaired hepatic clearance, portosystemic shunting, and enhanced gut-derived ammonia input increase systemic ammonia burden and are linked to neurological dysfunction, muscle wasting, immune dysregulation, and progression of liver disease. In the gut lumen and mucosal environment, however, gut microbes not only generate ammonia but can also reuse ammonia-derived nitrogen for amino acid synthesis, microbial biomass formation, and community nitrogen exchange. Evidence from selected physiological and preclinical models indicates that microbiota-derived ammonia may contribute to nitrogen recycling, microbial community maintenance, enteric neural regulation, or metabolic adaptation under defined conditions. These roles are more context-specific and less broadly established than the pathological effects of systemic hyperammonemia. When epithelial barrier integrity is compromised, hepatic clearance declines, or host buffering reserves are depleted, elevated ammonia can increase epithelial exposure, portal ammonia input, or peripheral blood ammonia. Conversely, evidence that reduced microbiota-derived ammonia contributes to disease remains limited and currently comes mainly from selected animal models. This review re-examines ammonia metabolism from a gut microbiota-centered perspective. We discuss the ecological origins, spatial distribution, exposure characteristics, host-interface effects, and context-specific outcomes of microbiota-derived ammonia in physiology and disease, and discuss how ammonia should be measured, stratified, and targeted in microbial nitrogen metabolism.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>本綜述重新審視了腸道菌群驅動的氨代謝，探討其從疾病負擔到生理適應的雙重角色。傳統上，氨被視為具神經毒性的代謝廢物，與高氨血症、肝性腦病及肝病惡化密切相關。然而，在腸道微環境中，微生物不僅產生氨，亦能利用氨源氮進行氨基酸合成與群落氮循環，展現出維持腸道神經與代謝適應等生理功能。文章強調，氨的病理與生理效應高度取決於上皮屏障、肝臟清除能力及宿主緩衝儲備。本研究為腸道微生物氮代謝提供了新的生態與臨床視角，並討論了未來如何精確測量及標靶氨代謝的策略。</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42640100/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>42642622</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Deployable high-fidelity metagenome binning at scale with QuickBin.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Communications biology</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>metagenomics</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>297 個真實總體基因體數據集 (297 real metagenomes)</t>
+        </is>
+      </c>
+      <c r="G40" t="b">
+        <v>0</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Reconstructing genomes from metagenomic assemblies is foundational to microbiome research, yet binning faces a persistent trade-off between fidelity and throughput. Many high-accuracy methods rely on GPU-intensive workflows, marker-gene postprocessing, or heavy computational resources, limiting reproducible use at scale. Here, we present QuickBin, a CPU-native, marker-free binning algorithm designed to recover near-complete, ultra-low-contamination metagenome-assembled genomes (MAGs) efficiently. QuickBin pairs a GC-coverage spatial index (BinMap) with an early-exit Oracle cascade of similarity tests (scalar composition/coverage filters and SIMD-accelerated k-mer comparisons), reserving a compact neural network exclusively for ambiguous merges. Across synthetic communities, evaluated by marker-based and contig-origin ground truth, QuickBin maximizes high-fidelity sequence recovery. In benchmarking 297 diverse real metagenomes, QuickBin completed all runs, recovering more high-quality MAGs (≥95% completeness, ≤1% contamination) than resource-intensive alternatives that frequently failed. QuickBin provides a practical path to reproducible, genome-resolved metagenomics at scale for downstream comparative analyses. Open-source at: https://github.com/bbushnell/BBTools .</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>本研究開發了 QuickBin，這是一種無需標記基因且僅需 CPU 運行的總體基因體分箱（binning）演算法，旨在高效重建高完整度且極低污染的總體基因體組裝基因體（MAGs）。QuickBin 結合了 GC 含量與覆蓋度的空間索引及快速相似性過濾機制，僅在處理模糊合併時使用輕量級神經網路。在 297 個真實總體基因體數據集的基準測試中，QuickBin 成功完成所有運行，且重建的高品質 MAGs 數量超越了其他耗費資源或容易失敗的現有工具。此技術為大規模、可重複的基因體解析總體基因體學研究提供了實用的解決方案。</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42642622/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>42640624</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Gut microbial diversity at baseline conditions the clinical, microbiome, and metabolic response to paraprobiotic Lactiplantibacillus plantarum LRCC5282 in overweight adults.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Gut microbes</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>16S, metabolomics</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>120 位過重成人</t>
+        </is>
+      </c>
+      <c r="G41" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>The gut microbiota is increasingly recognized as a target for obesity management; however, whether baseline gut microbial diversity conditions responsiveness to microbiota-targeted interventions remains unclear. We aimed to investigate whether baseline gut microbial diversity is associated with responsiveness to a paraprobiotic derived from Lactiplantibacillus plantarum LRCC5282 (LP5282-P) in overweight adults. In a 12-week, randomized, double-blind, placebo-controlled, multicenter trial of 120 overweight adults, LP5282-P produced no significant between-group differences in any clinical outcome across the overall per-protocol population. However, in the low-diversity subgroup, LP5282-P was associated with significant reductions in body weight, body mass index, and circulating leptin levels. These clinical changes were accompanied by compositional shifts in the gut microbiota, including higher relative abundances of Christensenellaceae, Faecalibacterium, and Alistipes. Fecal metabolite profiles showed elevated acetate and butyrate concentrations and altered bile acid composition. Within the low-diversity subgroup, changes in the relative abundances of Akkermansia and Eubacterium were inversely correlated with changes in body weight, body fat mass, and leptin levels. In contrast, the high-diversity subgroup exhibited no consistent response across the outcome domains examined. Overall, baseline gut microbial diversity was associated with differential responsiveness to LP5282-P, supporting its potential use as a stratification variable in future microbiota-targeted intervention trials. Further studies integrating direct measures of microbial activity and host response are warranted to elucidate the biological pathways underlying this diversity-dependent responsiveness. Trial registration: Clinical Research Information Service (CRIS), KCT0008119.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>本研究旨在探討基準線腸道微生物多樣性，是否會影響過重成人對副乾酪乳桿菌（LP5282-P）介入的臨床、菌群及代謝反應。在一項為期12週、納入120位過重成人的臨床試驗中，整體人群並未展現顯著差異；然而，在「低多樣性」亞群中，LP5282-P顯著降低了受試者的體重、BMI與血清瘦素水平，並促使腸道有益菌（如 *Faecalibacterium* 與 *Alistipes*）豐度上升，同時提升糞便中乙酸與丁酸濃度並改變膽汁酸組成。相反地，「高多樣性」亞群則無一致反應。此研究證實基準線菌群多樣性是預測益生菌療效的重要關鍵，可作為未來精準微生態介入與體重管理的分層依據。</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42640624/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>42642466</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Empirical evidence for gut microbial influence on human brain neurochemistry via the gut-brain axis.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Molecular psychiatry</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>metagenomics</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G42" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>The gut microbiome produces metabolites with potential neuroactive properties, many of which act locally within the gut. While preclinical studies suggest these microbial pathways can influence cognitive and emotional processes, human evidence remains limited. This study investigates associations between gut microbiome-derived neuroactive functional potential and in vivo brain neurotransmitter concentrations in healthy young females. Using proton magnetic resonance spectroscopy (¹H-MRS), we quantified GABA and glutamate levels in the dorsolateral prefrontal cortex (dlPFC), anterior cingulate cortex (ACC), and inferior occipital gyrus (IOG). Parallel metagenomic profiling characterised microbial functional potential for pathways related to the synthesis and degradation of GABA, glutamate, short-chain fatty acids (SCFAs), p-cresol, and inositol. Region-specific associations were observed between these microbial pathways and cortical GABA and glutamate levels, including excitatory/inhibitory (E/I) balance, a key marker of neuroplasticity and mental health. Notably, microbial glutamate degradation and inositol synthesis potential were associated with IOG E/I balance, while additional pathways including GABA metabolism, p-cresol production, and SCFA synthesis showed distinct associations across regions. Exploratory analyses also identified links between microbial functional potential and anxiety, depressive symptoms, and sleep quality. Together, these findings provide new human evidence that variation in microbial functional potential corresponds with regional cortical neurochemistry and psychological wellbeing, highlighting the gut-brain axis as a promising avenue for mechanistically informed microbiome-based- interventions.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>本研究旨在探討健康女性的腸道菌群功能潛力與大腦活體神經傳導物質（GABA與麩胺酸）濃度的關聯。研究結合腦部質子磁共振波譜（¹H-MRS）與總體基因體學分析，發現微生物中參與GABA、麩胺酸、短鏈脂肪酸、對甲酚及肌醇代謝的通路，與大腦特定區域（如背外側前額葉、前扣帶迴與下枕葉）的神經傳導物質水平及興奮/抑制平衡（E/I）具有區域特異性關聯。探索性分析亦顯示微生物功能與焦慮、抑鬱及睡眠品質相關。本研究為腸道菌群影響人類大腦神經化學與心理健康提供了直接的人體實證，為未來開發以微生物為基礎的腦腸軸臨床干預奠定基礎。</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42642466/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>42648179</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Simultaneous removal of nitrogen, Cu2+, and bisphenol A in a hydrogel-biochar-AQDS immobilized bioreactor with added bicarbonate: Performance and metagenomic insights.</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Journal of hazardous materials</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D43" t="n">
         <v>11.3</v>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>metagenomics</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>未提及</t>
         </is>
       </c>
-      <c r="G33" t="b">
-        <v>0</v>
-      </c>
-      <c r="H33" t="inlineStr">
+      <c r="G43" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" t="inlineStr">
         <is>
           <t>As the complexity of industrial wastewater pollution continues to increase, the simultaneous removal of nitrogen, metal contaminants, and persistent organic pollutants under low carbon conditions has become a key challenge for biological treatment systems. To address the operational instability and dependence on carbon sources observed in immobilized systems when exposed to copper (Cu2+) and bisphenol A (BPA), the Pseudoalteromonas japonicus strain LY0623 was integrated into a hydrogel-biochar-AQDS composite carrier to construct a multifunctional immobilized biofilm system. Notably, under conditions containing only NaHCO3, the R4 system achieved an NH4+-N removal rate of 89%. Under conditions where Cu2+ and BPA coexist, the R4 system achieved removal of NH4+-N (89%), NO3--N (100%), Cu2+ (85%), and BPA (88%). Sediment characterization confirmed that Cu2+ was immobilized through adsorption, complexation, and microbiologically induced carbonate precipitation (MICP). Metagenomic analysis further indicated that the Pseudomonadota phylum remained the dominant phylum, while functional pathways associated with inorganic carbon assimilation, HNAD nitrogen metabolism, endogenous carbon transformation, biomineralization, electron transfer, and aromatic compound degradation were preserved. By combining ammonia oxidation driven energy production, inorganic carbon utilization, redox mediated processes, and biomineralization, this study provides a highly promising low carbon strategy for treating industrial wastewater containing mixed pollutants.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>本研究旨在解決低碳條件下，工業廢水中氮、重金屬（Cu2+）與雙酚A（BPA）等混合污染物難以同時高效生物降解的挑戰。研究人員將日本假交替單胞菌（*Pseudoalteromonas japonicus*）LY0623菌株整合至水凝膠-生物炭-AQDS複合載體中，構建出新型固定化生物膜系統（R4系統）。
 研究發現，在僅添加碳酸氫鈉（無機碳源）的條件下，該系統成功實現了NH4+-N（89%）、NO3--N（100%）、Cu2+（85%）和BPA（88%）的高效同時去除。總體基因體學分析證實，變形菌門（Pseudomonadota）為優勢菌群，且系統中與無機碳同化、異營硝化-好氧反硝化（HNAD）、生物礦化及芳香族化合物降解相關的功能通路均得到有效維持。本研究結合了氨氧化產能與生物礦化等機制，為混合污染廢水處理提供了一種具前景的低碳生物修復策略。</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/42648179/</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>42642466</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Empirical evidence for gut microbial influence on human brain neurochemistry via the gut-brain axis.</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Molecular psychiatry</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>metagenomics</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>未提及</t>
-        </is>
-      </c>
-      <c r="G34" t="b">
-        <v>0</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>The gut microbiome produces metabolites with potential neuroactive properties, many of which act locally within the gut. While preclinical studies suggest these microbial pathways can influence cognitive and emotional processes, human evidence remains limited. This study investigates associations between gut microbiome-derived neuroactive functional potential and in vivo brain neurotransmitter concentrations in healthy young females. Using proton magnetic resonance spectroscopy (¹H-MRS), we quantified GABA and glutamate levels in the dorsolateral prefrontal cortex (dlPFC), anterior cingulate cortex (ACC), and inferior occipital gyrus (IOG). Parallel metagenomic profiling characterised microbial functional potential for pathways related to the synthesis and degradation of GABA, glutamate, short-chain fatty acids (SCFAs), p-cresol, and inositol. Region-specific associations were observed between these microbial pathways and cortical GABA and glutamate levels, including excitatory/inhibitory (E/I) balance, a key marker of neuroplasticity and mental health. Notably, microbial glutamate degradation and inositol synthesis potential were associated with IOG E/I balance, while additional pathways including GABA metabolism, p-cresol production, and SCFA synthesis showed distinct associations across regions. Exploratory analyses also identified links between microbial functional potential and anxiety, depressive symptoms, and sleep quality. Together, these findings provide new human evidence that variation in microbial functional potential corresponds with regional cortical neurochemistry and psychological wellbeing, highlighting the gut-brain axis as a promising avenue for mechanistically informed microbiome-based- interventions.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>本研究旨在探討健康女性的腸道菌群功能潛力與大腦活體神經傳導物質（GABA與麩胺酸）濃度的關聯。研究結合腦部質子磁共振波譜（¹H-MRS）與總體基因體學分析，發現微生物中參與GABA、麩胺酸、短鏈脂肪酸、對甲酚及肌醇代謝的通路，與大腦特定區域（如背外側前額葉、前扣帶迴與下枕葉）的神經傳導物質水平及興奮/抑制平衡（E/I）具有區域特異性關聯。探索性分析亦顯示微生物功能與焦慮、抑鬱及睡眠品質相關。本研究為腸道菌群影響人類大腦神經化學與心理健康提供了直接的人體實證，為未來開發以微生物為基礎的腦腸軸臨床干預奠定基礎。</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42642466/</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>42640624</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Gut microbial diversity at baseline conditions the clinical, microbiome, and metabolic response to paraprobiotic Lactiplantibacillus plantarum LRCC5282 in overweight adults.</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Gut microbes</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>11</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>16S, metabolomics</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>120 位過重成人</t>
-        </is>
-      </c>
-      <c r="G35" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>The gut microbiota is increasingly recognized as a target for obesity management; however, whether baseline gut microbial diversity conditions responsiveness to microbiota-targeted interventions remains unclear. We aimed to investigate whether baseline gut microbial diversity is associated with responsiveness to a paraprobiotic derived from Lactiplantibacillus plantarum LRCC5282 (LP5282-P) in overweight adults. In a 12-week, randomized, double-blind, placebo-controlled, multicenter trial of 120 overweight adults, LP5282-P produced no significant between-group differences in any clinical outcome across the overall per-protocol population. However, in the low-diversity subgroup, LP5282-P was associated with significant reductions in body weight, body mass index, and circulating leptin levels. These clinical changes were accompanied by compositional shifts in the gut microbiota, including higher relative abundances of Christensenellaceae, Faecalibacterium, and Alistipes. Fecal metabolite profiles showed elevated acetate and butyrate concentrations and altered bile acid composition. Within the low-diversity subgroup, changes in the relative abundances of Akkermansia and Eubacterium were inversely correlated with changes in body weight, body fat mass, and leptin levels. In contrast, the high-diversity subgroup exhibited no consistent response across the outcome domains examined. Overall, baseline gut microbial diversity was associated with differential responsiveness to LP5282-P, supporting its potential use as a stratification variable in future microbiota-targeted intervention trials. Further studies integrating direct measures of microbial activity and host response are warranted to elucidate the biological pathways underlying this diversity-dependent responsiveness. Trial registration: Clinical Research Information Service (CRIS), KCT0008119.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>本研究旨在探討基準線腸道微生物多樣性，是否會影響過重成人對副乾酪乳桿菌（LP5282-P）介入的臨床、菌群及代謝反應。在一項為期12週、納入120位過重成人的臨床試驗中，整體人群並未展現顯著差異；然而，在「低多樣性」亞群中，LP5282-P顯著降低了受試者的體重、BMI與血清瘦素水平，並促使腸道有益菌（如 *Faecalibacterium* 與 *Alistipes*）豐度上升，同時提升糞便中乙酸與丁酸濃度並改變膽汁酸組成。相反地，「高多樣性」亞群則無一致反應。此研究證實基準線菌群多樣性是預測益生菌療效的重要關鍵，可作為未來精準微生態介入與體重管理的分層依據。</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42640624/</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>42642622</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Deployable high-fidelity metagenome binning at scale with QuickBin.</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Communications biology</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>metagenomics</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>297 個真實總體基因體數據集 (297 real metagenomes)</t>
-        </is>
-      </c>
-      <c r="G36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Reconstructing genomes from metagenomic assemblies is foundational to microbiome research, yet binning faces a persistent trade-off between fidelity and throughput. Many high-accuracy methods rely on GPU-intensive workflows, marker-gene postprocessing, or heavy computational resources, limiting reproducible use at scale. Here, we present QuickBin, a CPU-native, marker-free binning algorithm designed to recover near-complete, ultra-low-contamination metagenome-assembled genomes (MAGs) efficiently. QuickBin pairs a GC-coverage spatial index (BinMap) with an early-exit Oracle cascade of similarity tests (scalar composition/coverage filters and SIMD-accelerated k-mer comparisons), reserving a compact neural network exclusively for ambiguous merges. Across synthetic communities, evaluated by marker-based and contig-origin ground truth, QuickBin maximizes high-fidelity sequence recovery. In benchmarking 297 diverse real metagenomes, QuickBin completed all runs, recovering more high-quality MAGs (≥95% completeness, ≤1% contamination) than resource-intensive alternatives that frequently failed. QuickBin provides a practical path to reproducible, genome-resolved metagenomics at scale for downstream comparative analyses. Open-source at: https://github.com/bbushnell/BBTools .</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>本研究開發了 QuickBin，這是一種無需標記基因且僅需 CPU 運行的總體基因體分箱（binning）演算法，旨在高效重建高完整度且極低污染的總體基因體組裝基因體（MAGs）。QuickBin 結合了 GC 含量與覆蓋度的空間索引及快速相似性過濾機制，僅在處理模糊合併時使用輕量級神經網路。在 297 個真實總體基因體數據集的基準測試中，QuickBin 成功完成所有運行，且重建的高品質 MAGs 數量超越了其他耗費資源或容易失敗的現有工具。此技術為大規模、可重複的基因體解析總體基因體學研究提供了實用的解決方案。</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42642622/</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>42640100</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Revisiting gut microbiota-driven ammonia metabolism: from disease burden to physiological adaptation.</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Gut microbes</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>11</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>others</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>未提及</t>
-        </is>
-      </c>
-      <c r="G37" t="b">
-        <v>0</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Ammonia homeostasis is governed by interconnected host and microbial pathways, including hepatic ureagenesis, glutamine synthesis, and gut microbiota-mediated urea hydrolysis, proteolysis, and amino acid deamination. Ammonia has historically been viewed primarily as a nitrogenous waste product and neurotoxic molecule, a concept strongly supported by studies of hyperammonemia and hepatic encephalopathy. Impaired hepatic clearance, portosystemic shunting, and enhanced gut-derived ammonia input increase systemic ammonia burden and are linked to neurological dysfunction, muscle wasting, immune dysregulation, and progression of liver disease. In the gut lumen and mucosal environment, however, gut microbes not only generate ammonia but can also reuse ammonia-derived nitrogen for amino acid synthesis, microbial biomass formation, and community nitrogen exchange. Evidence from selected physiological and preclinical models indicates that microbiota-derived ammonia may contribute to nitrogen recycling, microbial community maintenance, enteric neural regulation, or metabolic adaptation under defined conditions. These roles are more context-specific and less broadly established than the pathological effects of systemic hyperammonemia. When epithelial barrier integrity is compromised, hepatic clearance declines, or host buffering reserves are depleted, elevated ammonia can increase epithelial exposure, portal ammonia input, or peripheral blood ammonia. Conversely, evidence that reduced microbiota-derived ammonia contributes to disease remains limited and currently comes mainly from selected animal models. This review re-examines ammonia metabolism from a gut microbiota-centered perspective. We discuss the ecological origins, spatial distribution, exposure characteristics, host-interface effects, and context-specific outcomes of microbiota-derived ammonia in physiology and disease, and discuss how ammonia should be measured, stratified, and targeted in microbial nitrogen metabolism.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>本綜述重新審視了腸道菌群驅動的氨代謝，探討其從疾病負擔到生理適應的雙重角色。傳統上，氨被視為具神經毒性的代謝廢物，與高氨血症、肝性腦病及肝病惡化密切相關。然而，在腸道微環境中，微生物不僅產生氨，亦能利用氨源氮進行氨基酸合成與群落氮循環，展現出維持腸道神經與代謝適應等生理功能。文章強調，氨的病理與生理效應高度取決於上皮屏障、肝臟清除能力及宿主緩衝儲備。本研究為腸道微生物氮代謝提供了新的生態與臨床視角，並討論了未來如何精確測量及標靶氨代謝的策略。</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42640100/</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>42642834</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Glycosylation in gut-brain communication: from the intestinal barrier and microbiota to immune and neural signaling.</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Gut microbes</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>11</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>others</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>未提及</t>
-        </is>
-      </c>
-      <c r="G38" t="b">
-        <v>0</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>The gut-brain axis is a complex bidirectional communication network linking the gastrointestinal tract and the central nervous system. Its dysregulation is closely associated with a wide range of gastrointestinal, metabolic, and neuropsychiatric disorders. Glycosylation, one of the most prevalent and structurally diverse post-translational modifications of proteins and lipids, is increasingly recognized as a regulator of multiple processes within the gut-brain axis. In this review, we summarize evidence that glycosylation influences several steps of gut-brain communication, including intestinal barrier function, microbial glycan metabolism, immune signaling, enteric and vagal pathways, blood-brain barrier integrity, and neural responses. We distinguish direct mechanistic findings from associative observations and discuss the more limited evidence for brain-to-gut regulation of intestinal glycosylation. In addition, we discuss the potential of glycosylation-targeted nutritional and microbiota-based interventions and highlight emerging opportunities to integrate glycomics with other omics approaches to dissect the complex regulatory networks underlying the gut-brain axis. In conclusion, elucidating how glycosylation shapes signaling along the gut-brain axis may open new avenues for understanding disease pathogenesis and for developing targeted therapeutic strategies.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>本文探討「腸-腦軸線」（Gut-Brain Axis）中醣基化（Glycosylation）修飾的關鍵調節角色。醣基化作為蛋白質與脂質重要的轉譯後修飾，深刻影響腸道屏障功能、微生物聚醣代謝、免疫訊息傳遞及血腦屏障完整性。研究重點解析了醣基化如何調控腸道與中樞神經系統間的溝通，並區分了機制性證據與相關性觀察。本文不僅強調了醣基化在維繫軸線穩定中的核心地位，更提出透過營養干預與微生物調節，結合多體學（Omics）分析醣基化網絡，將有望為神經精神疾病與代謝性障礙提供創新的診斷與治療策略。</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42642834/</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>42641146</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Engineered bacterial therapeutics from synthetic biology to clinical translation: A multi-database scientometric analysis, 2000-2026.</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Human vaccines &amp; immunotherapeutics</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>others</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>1,730 篇學術文章與評論</t>
-        </is>
-      </c>
-      <c r="G39" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Engineered bacterial therapeutics integrate programmable strain engineering with biomedical functions such as sensing, delivery, immune modulation, microbiome intervention, and disease management. This study conducted a multi-database bibliometric analysis to map the knowledge structure, collaboration patterns, and translational direction of this field. Bibliographic records were retrieved from Web of Science Core Collection, Scopus, and PubMed for publications from 1 January 2000 to 1 June 2026. After document-type filtering, time restriction, deduplication, language screening, and manual eligibility assessment, 1,730 English-language articles and reviews were included. CiteSpace 6.4.R1, VOSviewer 1.6.20, and the bibliometrix R package were used to analyze publication trends, collaboration networks, journal co-citation, dual-map citation trajectories, citation bursts, keyword co-occurrence, and thematic evolution. Publication output increased steadily, with faster growth after 2020; 2025 was the highest-output complete year, while 2026 represented a partial retrieval year. China and the United States were the leading contributors, although institutional collaboration remained regionally clustered. Co-citation, citation-burst, and keyword analyses showed a shift from bacterial chassis construction and circuit design toward engineered probiotics, gut microbiota-related therapy, cancer immunotherapy, drug delivery, live biotherapeutic products, and clinical translation. Persistent translational priorities include controllability, safety, manufacturing consistency, and regulatory alignment.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>本研究透過文獻計量學方法，系統性分析 2000 年至 2026 年間有關「工程化細菌治療」的 1,730 篇學術文獻。研究旨在釐清該領域的知識結構、國際合作模式及臨床轉化趨勢。分析顯示，該領域自 2020 年後顯著加速發展，中國與美國為主要貢獻國。核心研究主軸已由早期的細菌底盤構建與基因電路設計，轉向工程化益生菌、癌症免疫治療、藥物遞送及活體生物藥物（LBP）的開發。科學意義在於確立了該領域從實驗室轉向臨床應用的優先議題，即解決控制力、生物安全性、生產一致性與法規調適等挑戰，為未來工程化細菌作為精準醫療工具的發展提供關鍵決策參考。</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42641146/</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>42635406</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Separating extracellular from intracellular fecal metabolites exposes cross-feeding architecture in the gut: exploring metabolite partitioning and ecological associations.</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Gut microbes</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>11</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>metagenomics, metabolomics</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>63 個糞便檢體（來自 63 位健康受試者）</t>
-        </is>
-      </c>
-      <c r="G40" t="b">
-        <v>0</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>The gut microbiota forms a complex ecosystem through metabolic interdependence (cross-feeding). However, conventional fecal metabolomics typically quantifies only total metabolite pools, making it difficult to distinguish extracellular-enriched metabolite pools from predominantly cell-associated ones, and thus limiting reconstruction of in situ metabolic networks. Here, we quantified fecal metabolites in paired fractions from the same specimen: an undisrupted fraction representing the extracellular pool and a strongly bead-beaten fraction representing the total pool; the intracellular pool was defined as the difference between total and extracellular measurements. Stool samples from 63 healthy individuals were analyzed for short-chain fatty acids, polyamines, and water-soluble vitamins, and the results were integrated with shotgun metagenomic profiles of species composition and functional genes. Vitamins exhibited two distinct behaviors. Adenosylcobalamin (a vitamin B12 coenzyme) was detectable only after disruption, and together with thiamine (B1) and niacin (B3) was classified as an intracellular-retained type (Type 1). In contrast, biotin (B7) and pantothenate (B5) showed higher extracellular proportions (Type 2). Integrative analyses further indicated that Type 1 thiamine was negatively associated with Blautia, consistent with intensive microbial utilization, whereas Type 2 biotin was strongly positively associated with Alistipes, suggesting links to ecological niches shaped by luminal pH and fermentation modes (carbohydrate vs protein fermentation). Fraction-resolved quantification provides a practical operational framework to differentiate extracellular from cell-associated metabolite pools, helping reconcile metagenomic potential with metabolomic reality and enabling deeper inference of cross-feeding structure in the gut ecosystem.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>本研究針對腸道微生物的代謝互營機制（cross-feeding）進行探討。傳統糞便代謝組學僅能分析總代謝物，無法區分細胞外與細胞內代謝池，限制了對代謝網絡的解析。研究團隊透過對比未破碎（代表細胞外池）與強力破碎（代表總代謝池）的糞便樣本，成功推算出細胞內代謝物的分佈。針對短鏈脂肪酸、多胺與水溶性維生素的分析顯示，維生素呈現兩類分佈：B12、B1 與 B3 傾向保留於細胞內（Type 1），而 B7 與 B5 則富集於細胞外（Type 2）。結合宏基因組分析發現，Type 1 代謝物與特定細菌（如 *Blautia*）的利用模式顯著相關，Type 2 代謝物則與 *Alistipes* 及腸道生態位特徵（如 pH 值、發酵類型）相關。此方法為區分代謝物空間分佈提供了實用架構，有助於更精確地將宏基因組功能潛力與代謝體現實連結，深入理解腸道微生物的互營生態結構。</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42635406/</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>42635403</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Baseline gut microbiome ecology predicts long-term fat mass loss after bariatric surgery: evidence for a thrifty Bifidobacterium phenotype.</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Gut microbes</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>11</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>16S, metabolomics</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>85 位重度肥胖患者及 21 位健康對照組（共 106 名受試者）</t>
-        </is>
-      </c>
-      <c r="G41" t="b">
-        <v>0</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Bariatric surgery (BS) induces weight loss, but long-term success involves complex host-microbiome interactions. We evaluated the longitudinal impact of BS, microbiome resilience, and Mediterranean Diet (MedDiet) adherence up to 24 months. This prospective observational study included 85 patients with severe obesity undergoing BS and 21 normal-weight healthy controls (HC). MedDiet adherence (PREDIMED) was assessed before surgery. Fecal microbiota (16S-rRNA sequencing) and metabolomics (1H-NMR spectroscopy) were analyzed at baseline and at 1-, 6-, and 12-months post-BS. Clinical outcomes and fat mass, evaluated by bioimpedanciometry, were tracked up to 24 months. At baseline, patients exhibited higher microbial Shannon diversity than controls (p = 0.041), alongside a dysfunctional microbiome and metabolome characterized by a higher Firmicutes/Bacteroidetes ratio and elevated levels of branched-chain amino acids (p &lt; 0.0001). Ordinary Least Squares (OLS) regression analysis revealed that MedDiet adherence and type 2 diabetes status significantly modulated baseline diversity. At 12 months post-BS, the gut ecosystem underwent profound remodeling, characterized by depletion of Bifidobacterium spp. and an increase in butyrate levels (p &lt; 0.0001), establishing a novel adaptive state distinct from HC. Baseline gut ecology significantly conditioned long-term BS outcomes: patients in the highest quartile of baseline Bifidobacterium spp. lost significantly less fat mass at 24 months than those in the lowest (6.6% vs. 13.2%, p = 0.010). High baseline Bifidobacterium abundance paradoxically acts as a "thrifty microbiome," potentially maximizing energy harvest and limiting surgery-induced fat loss. Overall, BS induces adaptive microbiome restoration rather than true normalization, highlighting the potential for precision interventions prior to surgery.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>本研究探討減重手術（BS）後腸道微生物群與長期減脂效果的關聯。研究追蹤 85 名患者於術前及術後長達 24 個月的變化，分析發現手術顯著重塑了腸道菌相與代謝環境，特別是雙歧桿菌（*Bifidobacterium*）的耗竭與丁酸鹽的增加。關鍵發現指出，術前高豐度的雙歧桿菌反而成為一種「節儉型表型」，會增加能量攝取效率，導致術後 24 個月的脂肪減少量顯著較少（6.6% 對比 13.2%）。這顯示減重手術並非使微生物組回歸常態，而是引發一種適應性重組。此研究凸顯了術前腸道生態作為預測手術成效生物標記的潛力，對於未來制定精準的術前介入策略具有重要的臨床指導意義。</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42635403/</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>42659434</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Blechomonas campbelli from Ctenocephalides felis: in vitro development, thermotolerance, and phylogenetic insights.</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Memorias do Instituto Oswaldo Cruz</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>metagenomics, others</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>340 隻跳蚤（每 4 隻混合為一組，共 85 組檢體），最終獲得 1 個分離株（FL-1）</t>
-        </is>
-      </c>
-      <c r="G42" t="b">
-        <v>0</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Blechomonas spp. are flea-specific monoxenous trypanosomatids, whose biology, host range, and geographic distribution remain poorly understood, even for species inhabiting ubiquitous cat and dog fleas. To isolate and characterise blechomonads from fleas of domestic dogs in Brazil, focusing on culture growth, morphology, and phylogenetic relationships. Fleas collected from dogs in Sabará, Brazil, were morphologically identified and screened by cultivation. The isolate FL-1 was analysed for temperature-dependent growth, morphology, and phylogeny using 18S rRNA and gGAPDH sequences, including those mined from public metagenomic datasets. Of 340 fleas (four per pool), only one culture tested positive. Growth was optimal at 25ºC, reduced at 30ºC, and absent at 35ºC. Four cell types were revealed, including a predominant "uromonad" stage specialised for attachment and aggregation. Phylogenetic analyses placed the isolate within Blechomonas campbelli and indicated that this species and Blechomonas lauriereadi occur in Ctenocephalides spp. from multiple continents. Blechomonas campbelli exhibits developmental adaptations to the flea gut and limited tolerance to elevated temperatures, constraining its potential to persist in warm-blooded hosts. These findings highlight the value of combining culture-based and in silico approaches to investigate flea-associated trypanosomatids.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>本研究旨在分離並鑑定巴西犬隻跳蚤中的隱鞭蟲（*Blechomonas*），探討其生長、形態與系統發育。研究從340隻跳蚤中成功分離出FL-1株，經鑑定為 *Blechomonas campbelli*。該菌最適生長溫度為25°C，在35°C下無法存活，並具有四種細胞形態（含利於附著的uromonad階段）。系統發育分析證實該物種廣泛分佈於全球的櫛頭蚤屬中。此發現表明其具有適應跳蚤腸道的發育特徵，但因耐熱性差，難以在溫血宿主體內存活。本研究證實了結合傳統培養與公共總體基因體數據挖掘在研究跳蚤相關寄生蟲上的重要價值。</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42659434/</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>42635401</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Fecal filtrate transplantation as salvage therapy for fulminant Clostridioides difficile infection in adult hematological patients during chemotherapy-induced aplasia: a pilot experience.</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Gut microbes</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>11</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>16S, metagenomics</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>3 位成人血液腫瘤患者</t>
-        </is>
-      </c>
-      <c r="G43" t="b">
-        <v>0</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Fulminant Clostridioides difficile infection (CDI) in patients with hematologic malignancies during chemotherapy-induced aplasia carries high mortality and limited treatment options. Our objective was to evaluate fecal filtrate transplantation (FFT) as a salvage therapy for fulminant CDI during aplasia, and to explore whether donor-recipient phage dynamics may contribute to clinical response. We conducted a single-center, prospective, protocol-defined pilot case series study including consecutive adults with hematologic malignancies, chemotherapy-induced grade-4 aplasia and fulminant CDI, refractory to ≥5 d of high-dose oral vancomycin plus intravenous metronidazole and tigecycline. FFT was prepared from a single unrelated donor using sequential centrifugation and filtration, and administered via nasogastric tube in two doses. The primary outcome was sustained clinical cure, secondary outcomes included survival and adverse events, assessed at +14 and +30 d post-FFT. 16S rRNA gene sequencing was used to assess microbiome compositions, while viral metagenomics and in vitro propagation assays were employed to characterize donor-recipient phageome interactions. Three patients with adverse-risk acute myeloid leukemia and fulminant CDI caused by genetically distinct C. difficile strains received FFT. All patients achieved clinical resolution by day +14, accompanied by improvements in abdominal distension and inflammatory markers. By day +30, one patient died from Pseudomonas aeruginosa septic shock, while two maintained remission with confirmatory follow-up. FFT was well tolerated, with no procedure-related immediate complications or FFT-attributable adverse events. Microbiome and phage profiling revealed heterogeneous responses, including shifts in bacterial community composition, with no clear evidence for a general role of donor-derived phages in CDI resolution. In contrast, we observed induction of prophages harbored by recipient-associated Clostridium species, which may have contributed to decolonization through stress-induced entry into the lytic cycle. FFT was feasible, with rapid sustained CDI resolution in hematologic patients with chemotherapy-induced aplasia. ClinicalTrials.gov identifier NCT07172191. Prospective single-center pilot study of fecal filtrate transplantation (FFT) for fulminant-refractory C. difficile infection in three aplastic adult hematologic patients. FFT was well tolerated, achieved rapid clinical cure, and showed heterogeneous microbiome and phageome modulation, potentially contributing to therapeutic effects.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>本研究旨在評估糞便濾液移植（FFT）作為挽救療法，治療化療致免疫不全之血液腫瘤患者合併難治猛爆性艱難梭菌感染（CDI）的療效，並探討供受體間噬菌體的動力學關係。此臨床先導試驗納入3位患者，結果顯示FFT耐受性良好，所有患者在接受治療後14天內均達到臨床緩解。微生態與噬菌體體學分析顯示，臨床症狀的改善並非源於供體噬菌體的直接轉移，而是FFT可能誘發了受體腸道內艱難梭菌的原噬菌體進入溶菌週期，進而促進病原菌清除。本研究證實FFT在此高風險族群中具安全性與可行性，為難治性CDI提供了創新的機制見解與治療選擇。</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42635401/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>42634246</t>
+          <t>42642836</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Natural microbiota confer life-long protection against obesity via an early-life, immune-mediated effect on brown adipocytes.</t>
+          <t>Microbiome-mediated regulation of pathogen virulence: Molecular mechanisms and clinical implications.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>Virulence</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11</v>
+        <v>5.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2764,50 +2758,52 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Obesity, a major risk factor for metabolic disease, has increased in industrialized nations alongside a reduction in gut microbiota diversity. Reconstituting laboratory mice with complex, natural microbiota and commensals from wild mice resulted in protection against diet-induced obesity. These natural microbiota reduced weight gain in both male and female mice of different genetic backgrounds throughout their life and increased energy expenditure. Single-nuclei RNA sequencing identified a dominant adipocyte population in brown adipose tissue (BAT) with a transcriptional signature of increased thermogenic activity, while white adipose tissue mass and beiging were reduced. Protection against diet-induced obesity was transferable to adult germ-free mice via exposure to natural microbiota, indicating an association with the timing of immune response induction rather than BAT developmental programming. However, protection against diet-induced obesity did not require type 2 immune signaling, as shown in STAT6 knockout mice. Rather, it was associated with increased levels of chemokines and monocytes in BAT in early life, pointing to a role of infiltrating myeloid cells. Indeed, CCR2-deficient mice with natural microbiota lacked the BAT transcriptional signature of increased thermogenic activity, increased energy expenditure, and protection against diet-induced obesity that wild-type mice with natural microbiota exhibited. The latter was restored upon injection with wild-type bone marrow. Taken together, these findings identify a novel microbiota‒immune‒adipose tissue axis that results in increased BAT thermogenesis and improved energy balance throughout life.</t>
+          <t>The human microbiome profoundly influences pathogen virulence and disease susceptibility through diverse molecular mechanisms. This review, focused on literature from 2016 to 2026, synthesizes knowledge on microbiome-mediated regulation examining major pathogens including Vibrio cholerae, enterohemorrhagic Escherichia coli, Salmonella species, Clostridioides difficile, and Staphylococcus aureus. A triangular interaction model is presented, linking host immunity, resident microbiome, and invading pathogen to frame infection outcomes. Commensal bacteria regulate pathogen behavior through quorum sensing interference, metabolite-mediated regulation via short-chain fatty acids and bile acids, competitive exclusion, immune response modulation, and direct antimicrobial production. Key species-Lactobacillus spp. Bifidobacterium spp. Bacteroides thetaiotaomicron, and Faecalibacterium prausnitzii-employ distinct molecular strategies against these pathogens. Organ-on-chip platforms and multi-omics advances reveal context-dependent interactions. Clinical applications including rationally designed probiotics, fecal microbiota transplantation, and precision microbiome engineering show promise despite challenges of inter-individual microbiome variability, representing a paradigm shift toward ecosystem-based infectious disease management.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>本研究旨在探討野生小鼠的天然腸道菌相如何預防飲食引起的肥胖。研究發現，移植天然菌相能終生保護不同遺傳背景的實驗小鼠免於肥胖，並顯著增加能量消耗。單細胞核RNA定序（snRNA-seq）顯示，這與褐色脂肪組織（BAT）中產熱活性增強的脂肪細胞亞群有關。此保護機制並非透過第二型免疫信號，而是依賴於早期生命階段骨髓源性細胞（特別是CCR2+單核細胞）向BAT的浸潤與免疫調節。本研究首次揭示了一條全新的「腸道菌群—免疫—脂肪組織」軸，證實早期菌相暴露能透過免疫介導促進褐色脂肪產熱，為肥胖及代謝性疾病的防治提供了新穎的科學依據與治療靶點。</t>
+          <t>本研究綜述了2016年至2026年間關於腸道微生物群調控病原體毒力（如霍亂弧菌、大腸桿菌、沙門氏菌等）的分子機制。作者提出了一個結合宿主免疫、共生菌群與入侵病原體的「三角交互模型」，闡述了共生菌如何透過群體感應干擾、代謝產物（如短鏈脂肪酸、膽汁酸）調節、競爭性排斥及免疫調節來抑制病原體。研究強調了乳酸桿菌、雙歧桿菌及普拉梭菌等關鍵菌種的保護機制，並探討了器官晶片與多體學技術在揭示交互作用上的貢獻。此研究主張從生態系統角度管理傳染病，指出益生菌設計、糞便菌群移植及精準微生物組工程是未來治療的關鍵方向，雖面臨個體差異挑戰，但為臨床感染控制提供了典範轉移。</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42634246/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42642836/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>42644084</t>
+          <t>42635406</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Viral metagenomics of synanthropic urban bats: A surveillance strategy for uncovering potentially zoonotic viruses.</t>
+          <t>Separating extracellular from intracellular fecal metabolites exposes cross-feeding architecture in the gut: exploring metabolite partitioning and ecological associations.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>One health (Amsterdam, Netherlands)</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>Gut microbes</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11</v>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2,422 隻蝙蝠中篩選出的 150 對肺與腸道檢體</t>
+          <t>63 個糞便檢體（來自 63 位健康受試者）</t>
         </is>
       </c>
       <c r="G45" t="b">
@@ -2815,50 +2811,52 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Bats are natural reservoirs for diverse viruses, including coronaviruses, filoviruses, and paramyxoviruses, several of those known to be involved in zoonotic spillover events and demanding an integrated surveillance. Here, we present a framework that leverages Brazil's rabies passive surveillance programme to detect bat-borne viruses. Using an algorithm to select representative specimens from 2422 bats collected across São Paulo state, we submitted 150 paired lung and intestine samples to nanopore metagenomic sequencing. We detected 98 viral contigs from 12 families of public health relevance, including Arenaviridae, Coronaviridae, and Paramyxoviridae. Notably, the approach identified a previously unknown filovirus in bats in the Americas, validating the framework's capacity for epidemic preparedness. These findings reveal an undetected viral diversity and demonstrate how existing animal surveillance can monitor pathogen threats. Crucially, in a workshop involving multisectoral One Health experts in Brazil, this framework was validated as a scalable model for national expansion, adapted for low- and middle-income countries (LMICs).</t>
+          <t>The gut microbiota forms a complex ecosystem through metabolic interdependence (cross-feeding). However, conventional fecal metabolomics typically quantifies only total metabolite pools, making it difficult to distinguish extracellular-enriched metabolite pools from predominantly cell-associated ones, and thus limiting reconstruction of in situ metabolic networks. Here, we quantified fecal metabolites in paired fractions from the same specimen: an undisrupted fraction representing the extracellular pool and a strongly bead-beaten fraction representing the total pool; the intracellular pool was defined as the difference between total and extracellular measurements. Stool samples from 63 healthy individuals were analyzed for short-chain fatty acids, polyamines, and water-soluble vitamins, and the results were integrated with shotgun metagenomic profiles of species composition and functional genes. Vitamins exhibited two distinct behaviors. Adenosylcobalamin (a vitamin B12 coenzyme) was detectable only after disruption, and together with thiamine (B1) and niacin (B3) was classified as an intracellular-retained type (Type 1). In contrast, biotin (B7) and pantothenate (B5) showed higher extracellular proportions (Type 2). Integrative analyses further indicated that Type 1 thiamine was negatively associated with Blautia, consistent with intensive microbial utilization, whereas Type 2 biotin was strongly positively associated with Alistipes, suggesting links to ecological niches shaped by luminal pH and fermentation modes (carbohydrate vs protein fermentation). Fraction-resolved quantification provides a practical operational framework to differentiate extracellular from cell-associated metabolite pools, helping reconcile metagenomic potential with metabolomic reality and enabling deeper inference of cross-feeding structure in the gut ecosystem.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>本研究旨在建立一個結合巴西現有狂犬病被動監測計畫的病毒總體基因體學監測架構，以偵測都市蝙蝠所攜帶的潛在人畜共通病毒。研究團隊從聖保羅州收集的 2,422 隻蝙蝠中，篩選出 150 對肺部與腸道檢體進行奈米孔定序。結果成功偵測到 12 個與公共衛生密切相關病毒科的 98 個病毒基因片段（包括沙狀、冠狀與副黏液病毒科等），更首次在美洲蝙蝠中發現一種未知絲狀病毒。此研究不僅揭示了未曾被發現的病毒多樣性，證實利用現有動物監測系統預防流行病的可行性，更為中低收入國家提供了一個具備「健康一體」（One Health）共識、可擴展至全國的傳染病監測模型。</t>
+          <t>本研究針對腸道微生物的代謝互營機制（cross-feeding）進行探討。傳統糞便代謝組學僅能分析總代謝物，無法區分細胞外與細胞內代謝池，限制了對代謝網絡的解析。研究團隊透過對比未破碎（代表細胞外池）與強力破碎（代表總代謝池）的糞便樣本，成功推算出細胞內代謝物的分佈。針對短鏈脂肪酸、多胺與水溶性維生素的分析顯示，維生素呈現兩類分佈：B12、B1 與 B3 傾向保留於細胞內（Type 1），而 B7 與 B5 則富集於細胞外（Type 2）。結合宏基因組分析發現，Type 1 代謝物與特定細菌（如 *Blautia*）的利用模式顯著相關，Type 2 代謝物則與 *Alistipes* 及腸道生態位特徵（如 pH 值、發酵類型）相關。此方法為區分代謝物空間分佈提供了實用架構，有助於更精確地將宏基因組功能潛力與代謝體現實連結，深入理解腸道微生物的互營生態結構。</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42644084/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42635406/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>42637484</t>
+          <t>42635403</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Insights into the analysis of microbial communities in fermented foods from the perspective of DNA-based techniques.</t>
+          <t>Baseline gut microbiome ecology predicts long-term fat mass loss after bariatric surgery: evidence for a thrifty Bifidobacterium phenotype.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Food research international (Ottawa, Ont.)</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>Gut microbes</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11</v>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>16S, metagenomics</t>
+          <t>16S, metabolomics</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>85 位重度肥胖患者及 21 位健康對照組（共 106 名受試者）</t>
         </is>
       </c>
       <c r="G46" t="b">
@@ -2866,50 +2864,52 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>The quality, flavor, and stability of fermented foods depend on the microbial community. However, microbial dynamics are difficult to observe directly, leading to limited control over fermentation. High-throughput sequencing is a revolutionary tool for microbial characterization, among which DNA-based amplicon and metagenomic sequencing are core techniques. Nevertheless, the related data processing workflows in the context of fermented foods have not yet been systematically summarized, hindering the translation of research findings into fermentation practices. This review clarifies the applications of amplicon and metagenomic sequencing in fermented foods. For amplicon sequencing, the impacts of target regions, data preprocessing, and reference databases are addressed. For metagenomic sequencing, sequencing strategies, read-based and binning-based analytical methods, functional annotation, and species-specific databases are discussed. In addition, major strategies for downstream analysis of community data are summarized, including microbial diversity, co-occurrence networks, niche and community assembly, key environmental drivers, and machine learning-based prediction. Amplicon sequencing efficiently reveals microbial succession during fermentation but has limitations in functional annotation. Metagenomic sequencing is notable for functional annotation, enabling the linkage between microbial communities and metabolic potential alongside community characterization. Standardized data preprocessing and specific databases are critical for improving characterization. For community data, integrated analysis allows uncovering the driving factors of microbial succession, thereby helping to regulate fermentation. Notably, the compositional nature of the data must be considered and validated to avoid spurious associations. In summary, the exponential growth of sequencing data will propel the era of precision fermentation.</t>
+          <t>Bariatric surgery (BS) induces weight loss, but long-term success involves complex host-microbiome interactions. We evaluated the longitudinal impact of BS, microbiome resilience, and Mediterranean Diet (MedDiet) adherence up to 24 months. This prospective observational study included 85 patients with severe obesity undergoing BS and 21 normal-weight healthy controls (HC). MedDiet adherence (PREDIMED) was assessed before surgery. Fecal microbiota (16S-rRNA sequencing) and metabolomics (1H-NMR spectroscopy) were analyzed at baseline and at 1-, 6-, and 12-months post-BS. Clinical outcomes and fat mass, evaluated by bioimpedanciometry, were tracked up to 24 months. At baseline, patients exhibited higher microbial Shannon diversity than controls (p = 0.041), alongside a dysfunctional microbiome and metabolome characterized by a higher Firmicutes/Bacteroidetes ratio and elevated levels of branched-chain amino acids (p &lt; 0.0001). Ordinary Least Squares (OLS) regression analysis revealed that MedDiet adherence and type 2 diabetes status significantly modulated baseline diversity. At 12 months post-BS, the gut ecosystem underwent profound remodeling, characterized by depletion of Bifidobacterium spp. and an increase in butyrate levels (p &lt; 0.0001), establishing a novel adaptive state distinct from HC. Baseline gut ecology significantly conditioned long-term BS outcomes: patients in the highest quartile of baseline Bifidobacterium spp. lost significantly less fat mass at 24 months than those in the lowest (6.6% vs. 13.2%, p = 0.010). High baseline Bifidobacterium abundance paradoxically acts as a "thrifty microbiome," potentially maximizing energy harvest and limiting surgery-induced fat loss. Overall, BS induces adaptive microbiome restoration rather than true normalization, highlighting the potential for precision interventions prior to surgery.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>本文為一篇綜述性研究，旨在探討以 DNA 為基礎的高通量定序技術（包含擴增子定序與宏基因組學）在發酵食品微生物群落分析中的應用。研究指出，儘管高通量定序技術已成為解析微生物動態的革命性工具，但目前缺乏系統性的數據處理框架，限制了科學發現向產業實踐的轉化。本文詳細梳理了從目標區域選擇、數據預處理、參考數據庫建立到下游生物資訊分析（如共現網絡、生態棲位構建及機器學習預測）的標準化流程。研究強調，擴增子定序雖能有效揭示群落演替，但在功能註解上存在限制；而宏基因組學則具備更強的功能解析潛力，能將微生物組成與代謝功能聯繫起來。透過標準化數據處理流程並考慮數據的組成特性，這些先進技術將精準調控發酵過程，引領精密發酵時代的到來。</t>
+          <t>本研究探討減重手術（BS）後腸道微生物群與長期減脂效果的關聯。研究追蹤 85 名患者於術前及術後長達 24 個月的變化，分析發現手術顯著重塑了腸道菌相與代謝環境，特別是雙歧桿菌（*Bifidobacterium*）的耗竭與丁酸鹽的增加。關鍵發現指出，術前高豐度的雙歧桿菌反而成為一種「節儉型表型」，會增加能量攝取效率，導致術後 24 個月的脂肪減少量顯著較少（6.6% 對比 13.2%）。這顯示減重手術並非使微生物組回歸常態，而是引發一種適應性重組。此研究凸顯了術前腸道生態作為預測手術成效生物標記的潛力，對於未來制定精準的術前介入策略具有重要的臨床指導意義。</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42637484/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42635403/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>42637478</t>
+          <t>42659434</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Effects of sorghum variety on fermentation microecology and flavor characteristics of sesame-flavor Baijiu.</t>
+          <t>Blechomonas campbelli from Ctenocephalides felis: in vitro development, thermotolerance, and phylogenetic insights.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Food research international (Ottawa, Ont.)</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>Memorias do Instituto Oswaldo Cruz</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2.5</v>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>metagenomics, others</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>3 種高粱品種（Hongyingzi, Hei'e, G），於 2 輪發酵週期中，在 3 個時間點（0、15、50 天）採集發酵酒醅檢體（樣本總數依實驗設計推算為 18 組發酵樣品）</t>
+          <t>340 隻跳蚤（每 4 隻混合為一組，共 85 組檢體），最終獲得 1 個分離株（FL-1）</t>
         </is>
       </c>
       <c r="G47" t="b">
@@ -2917,50 +2917,52 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sorghum, the principal raw material for Baijiu fermentation, plays a key role in shaping fermentation microecology and flavor formation. However, the effects of sorghum varietal differences on sesame-flavor Baijiu fermentation remain insufficiently understood. In this study, three sorghum varieties, Hongyingzi (R), Hei'e (B), and a domestic cultivar (G), were compared over two consecutive fermentation rounds. Fermented grain (Jiupei) samples collected at 0, 15, and 50 days were analyzed for physicochemical properties, enzyme activities, microbial communities, volatile compounds in Jiupei and base liquor, and the taste characteristics of the corresponding base liquor. Despite showing similar overall fermentation trends, the three sorghum varieties differed in acid accumulation, starch utilization, microbial succession, and volatile composition. Fungal communities shifted from early Pichia dominance to multi-genus coexistence, whereas bacterial communities progressively converged toward Lactobacillus dominance. A total of 218 and 258 volatile compounds were identified in Jiupei and 176 and 192 in base liquor from the first and second rounds, respectively. Esters were the dominant differential class, and volatile-marker profiles varied among sorghum varieties and fermentation rounds, with no single variety showing consistent enrichment across all sesame-flavor-related compounds. These results indicate that sorghum variety is an important factor associated with microbial assembly and flavor formation during sesame-flavor Baijiu fermentation, and provide a basis for raw material selection and flavor-oriented process optimization.</t>
+          <t>Blechomonas spp. are flea-specific monoxenous trypanosomatids, whose biology, host range, and geographic distribution remain poorly understood, even for species inhabiting ubiquitous cat and dog fleas. To isolate and characterise blechomonads from fleas of domestic dogs in Brazil, focusing on culture growth, morphology, and phylogenetic relationships. Fleas collected from dogs in Sabará, Brazil, were morphologically identified and screened by cultivation. The isolate FL-1 was analysed for temperature-dependent growth, morphology, and phylogeny using 18S rRNA and gGAPDH sequences, including those mined from public metagenomic datasets. Of 340 fleas (four per pool), only one culture tested positive. Growth was optimal at 25ºC, reduced at 30ºC, and absent at 35ºC. Four cell types were revealed, including a predominant "uromonad" stage specialised for attachment and aggregation. Phylogenetic analyses placed the isolate within Blechomonas campbelli and indicated that this species and Blechomonas lauriereadi occur in Ctenocephalides spp. from multiple continents. Blechomonas campbelli exhibits developmental adaptations to the flea gut and limited tolerance to elevated temperatures, constraining its potential to persist in warm-blooded hosts. These findings highlight the value of combining culture-based and in silico approaches to investigate flea-associated trypanosomatids.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>本研究旨在探討不同高粱品種對芝麻香型白酒發酵過程中，微生物群落結構與風味代謝物質形成的影響。研究比較了紅纓子（R）、黑鵝（B）與國內品種（G）三種高粱，分析其在發酵過程中的理化特性、微生物演替及揮發性化合物組成。研究發現，儘管各品種發酵趨勢相似，但在酸度累積、澱粉利用率及微生物群落演替上存在顯著差異；真菌群落由早期的畢赤酵母（*Pichia*）主導轉變為多菌屬共存，細菌群落則趨向於乳桿菌（*Lactobacillus*）主導。分析鑑定出上百種揮發性化合物，其中酯類是導致風味差異的主要代謝物。本研究證實了高粱品種是決定白酒發酵微生物群落組裝與最終風味品質的關鍵因子，為白酒產業的原料選擇與製程最佳化提供了重要的科學依據。</t>
+          <t>本研究旨在分離並鑑定巴西犬隻跳蚤中的隱鞭蟲（*Blechomonas*），探討其生長、形態與系統發育。研究從340隻跳蚤中成功分離出FL-1株，經鑑定為 *Blechomonas campbelli*。該菌最適生長溫度為25°C，在35°C下無法存活，並具有四種細胞形態（含利於附著的uromonad階段）。系統發育分析證實該物種廣泛分佈於全球的櫛頭蚤屬中。此發現表明其具有適應跳蚤腸道的發育特徵，但因耐熱性差，難以在溫血宿主體內存活。本研究證實了結合傳統培養與公共總體基因體數據挖掘在研究跳蚤相關寄生蟲上的重要價值。</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42637478/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42659434/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>42637476</t>
+          <t>42635401</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>A Shenling Baizhu San polysaccharide fraction (SLP-2)-based synbiotic alleviates lactose-induced gut dysfunction via a microbiota-metabolite-barrier axis.</t>
+          <t>Fecal filtrate transplantation as salvage therapy for fulminant Clostridioides difficile infection in adult hematological patients during chemotherapy-induced aplasia: a pilot experience.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Food research international (Ottawa, Ont.)</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>Gut microbes</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11</v>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>16S, metagenomics</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>3 位成人血液腫瘤患者</t>
         </is>
       </c>
       <c r="G48" t="b">
@@ -2968,45 +2970,47 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Lactose intolerance (LI) is a common digestive disorder, and its management still relies largely on dietary restriction. Because gut microbial fermentation and barrier dysfunction contribute to LI-related symptoms, microbiota-targeted prebiotic or synbiotic strategies may provide complementary approaches. However, the active plant-polysaccharide fractions and their microbial partners remain unclear. This study aimed to identify the bioactive polysaccharide fraction from Shenling Baizhu San and evaluate its pairing with responder bacteria for alleviating high-lactose diet (HLD)-induced intestinal dysfunction. Stepwise ethanol precipitation yielded SLP-2, which was subsequently identified as the principal bioactive fraction through human fecal fermentation, monoculture assays, and an HLD rat model. SLP-2 enriched Eubacterium-associated taxa and supported the growth of Akkermansia muciniphila in monoculture and in vivo. Building on this, a synbiotic combining SLP-2 with A. muciniphila and E. rectale alleviated HLD-induced gut dysfunction; the antibiotic-matched comparison with the probiotics-only group supported an SLP-2-associated contribution. The synbiotic intervention was associated with increased tight junction proteins, MUC2 expression, improved intestinal architecture, and thicker mucus layers. Multi-omics analysis linked co-metabolites, including intestinal 6-MGG and HTy-Ac and systemic DHPV-G, with barrier restoration and an immune profile characterized by increased IL-10 and lower TLR4 expression. These findings suggest that SLP-2-based synbiotic intervention alleviates HLD-induced intestinal dysfunction through microbiota-metabolite-barrier modulation, providing preclinical evidence for future functional-food strategies pending human validation.</t>
+          <t>Fulminant Clostridioides difficile infection (CDI) in patients with hematologic malignancies during chemotherapy-induced aplasia carries high mortality and limited treatment options. Our objective was to evaluate fecal filtrate transplantation (FFT) as a salvage therapy for fulminant CDI during aplasia, and to explore whether donor-recipient phage dynamics may contribute to clinical response. We conducted a single-center, prospective, protocol-defined pilot case series study including consecutive adults with hematologic malignancies, chemotherapy-induced grade-4 aplasia and fulminant CDI, refractory to ≥5 d of high-dose oral vancomycin plus intravenous metronidazole and tigecycline. FFT was prepared from a single unrelated donor using sequential centrifugation and filtration, and administered via nasogastric tube in two doses. The primary outcome was sustained clinical cure, secondary outcomes included survival and adverse events, assessed at +14 and +30 d post-FFT. 16S rRNA gene sequencing was used to assess microbiome compositions, while viral metagenomics and in vitro propagation assays were employed to characterize donor-recipient phageome interactions. Three patients with adverse-risk acute myeloid leukemia and fulminant CDI caused by genetically distinct C. difficile strains received FFT. All patients achieved clinical resolution by day +14, accompanied by improvements in abdominal distension and inflammatory markers. By day +30, one patient died from Pseudomonas aeruginosa septic shock, while two maintained remission with confirmatory follow-up. FFT was well tolerated, with no procedure-related immediate complications or FFT-attributable adverse events. Microbiome and phage profiling revealed heterogeneous responses, including shifts in bacterial community composition, with no clear evidence for a general role of donor-derived phages in CDI resolution. In contrast, we observed induction of prophages harbored by recipient-associated Clostridium species, which may have contributed to decolonization through stress-induced entry into the lytic cycle. FFT was feasible, with rapid sustained CDI resolution in hematologic patients with chemotherapy-induced aplasia. ClinicalTrials.gov identifier NCT07172191. Prospective single-center pilot study of fecal filtrate transplantation (FFT) for fulminant-refractory C. difficile infection in three aplastic adult hematologic patients. FFT was well tolerated, achieved rapid clinical cure, and showed heterogeneous microbiome and phageome modulation, potentially contributing to therapeutic effects.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>本研究旨在探討參苓白朮散多醣活性組分（SLP-2）結合特定菌株，對高乳糖飲食（HLD）引發之腸道功能障礙的緩解作用。研究發現，SLP-2能促進*A. muciniphila*與真桿菌屬相關菌群生長。以SLP-2搭配益生菌的合生元配方，能顯著改善HLD大鼠的腸道屏障，包含增加緊密連接蛋白與MUC2表達、增厚黏液層。多體學分析顯示，其保護作用與腸道及全身性代謝物（如6-MGG、DHPV-G）的調節，以及抗發炎反應（提升IL-10、降低TLR4）密切相關。此發現為開發防治乳糖不耐症的功能性食品提供了臨床前依據。</t>
+          <t>本研究旨在評估糞便濾液移植（FFT）作為挽救療法，治療化療致免疫不全之血液腫瘤患者合併難治猛爆性艱難梭菌感染（CDI）的療效，並探討供受體間噬菌體的動力學關係。此臨床先導試驗納入3位患者，結果顯示FFT耐受性良好，所有患者在接受治療後14天內均達到臨床緩解。微生態與噬菌體體學分析顯示，臨床症狀的改善並非源於供體噬菌體的直接轉移，而是FFT可能誘發了受體腸道內艱難梭菌的原噬菌體進入溶菌週期，進而促進病原菌清除。本研究證實FFT在此高風險族群中具安全性與可行性，為難治性CDI提供了創新的機制見解與治療選擇。</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42637476/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42635401/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>42637471</t>
+          <t>42634246</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Fucoidan from giant kelp alleviates postmenopausal osteoporosis by regulating the betaine-OPG/RANKL/RANK signaling axis.</t>
+          <t>Natural microbiota confer life-long protection against obesity via an early-life, immune-mediated effect on brown adipocytes.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Food research international (Ottawa, Ont.)</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>Gut microbes</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11</v>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3019,50 +3023,50 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Postmenopausal osteoporosis (PMOP), characterized by excessive bone resorption and impaired bone remodeling, remains a significant global health challenge. This study investigated the protective effects of fucoidan from giant kelp (GKP) against PMOP and its underlying mechanisms in ovariectomized mice. GKP supplementation attenuated bone loss by preserving trabecular microarchitecture, normalizing systemic mineral homeostasis, and suppressing osteoclastogenesis, as evidenced by the downregulation of osteoclast-related genes. 16S rRNA gene sequencing revealed that GKP reshaped the gut microbiota by decreasing the Bacteroidota/Firmicutes ratio and enriching beneficial taxa, which promoted short-chain fatty acid production. Targeted metabolomics revealed that GKP induced profound systemic metabolic reprogramming, particularly amino acid metabolism, and identified betaine as a key systemic metabolite effector upregulated following GKP treatment. In vitro assays demonstrated that betaine suppressed receptor activator of nuclear factor-κB ligand (RANKL)-induced osteoclast differentiation and mitigated inflammation. In vivo validation demonstrated that betaine intervention recapitulated the osteoprotective phenotype observed in GKP-treated mice, which was associated with regulation of the osteoprotegerin/RANKL/RANK signaling axis. These results indicate that GKP exerts anti-osteoporotic effects in association with changes in gut microbiota and systemic metabolism, while betaine-mediated regulation of the OPG/RANKL/RANK signaling may contribute to its osteoprotective activity.</t>
+          <t>Obesity, a major risk factor for metabolic disease, has increased in industrialized nations alongside a reduction in gut microbiota diversity. Reconstituting laboratory mice with complex, natural microbiota and commensals from wild mice resulted in protection against diet-induced obesity. These natural microbiota reduced weight gain in both male and female mice of different genetic backgrounds throughout their life and increased energy expenditure. Single-nuclei RNA sequencing identified a dominant adipocyte population in brown adipose tissue (BAT) with a transcriptional signature of increased thermogenic activity, while white adipose tissue mass and beiging were reduced. Protection against diet-induced obesity was transferable to adult germ-free mice via exposure to natural microbiota, indicating an association with the timing of immune response induction rather than BAT developmental programming. However, protection against diet-induced obesity did not require type 2 immune signaling, as shown in STAT6 knockout mice. Rather, it was associated with increased levels of chemokines and monocytes in BAT in early life, pointing to a role of infiltrating myeloid cells. Indeed, CCR2-deficient mice with natural microbiota lacked the BAT transcriptional signature of increased thermogenic activity, increased energy expenditure, and protection against diet-induced obesity that wild-type mice with natural microbiota exhibited. The latter was restored upon injection with wild-type bone marrow. Taken together, these findings identify a novel microbiota‒immune‒adipose tissue axis that results in increased BAT thermogenesis and improved energy balance throughout life.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>本研究探討巨藻褐藻醣膠（GKP）對去卵巢小鼠更年期後骨質疏鬆症（PMOP）的保護機制。結果顯示，補充GKP能有效減少骨質流失並抑制破骨細胞生成。16S定序顯示GKP重塑了腸道菌群（降低擬桿菌門/厚壁菌門比例），促進短鏈脂肪酸產生。代謝組學分析發現，GKP顯著提升了系統性代謝物甜菜鹼（betaine）的含量。體內外實驗進一步證實，甜菜鹼透過調控OPG/RANKL/RANK信號軸，能抑制破骨細胞分化並緩解骨質流失。本研究證實GKP具備透過「腸道菌群-代謝物」軸抗骨質疏鬆的潛力，為PMOP防治提供了科學依據。</t>
+          <t>本研究旨在探討野生小鼠的天然腸道菌相如何預防飲食引起的肥胖。研究發現，移植天然菌相能終生保護不同遺傳背景的實驗小鼠免於肥胖，並顯著增加能量消耗。單細胞核RNA定序（snRNA-seq）顯示，這與褐色脂肪組織（BAT）中產熱活性增強的脂肪細胞亞群有關。此保護機制並非透過第二型免疫信號，而是依賴於早期生命階段骨髓源性細胞（特別是CCR2+單核細胞）向BAT的浸潤與免疫調節。本研究首次揭示了一條全新的「腸道菌群—免疫—脂肪組織」軸，證實早期菌相暴露能透過免疫介導促進褐色脂肪產熱，為肥胖及代謝性疾病的防治提供了新穎的科學依據與治療靶點。</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42637471/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42634246/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>42637450</t>
+          <t>42644084</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Highland barley polysaccharides promoted lactose intestinal fermentation in vitro: Unveiling the dynamic response of gut microbiota and polysaccharide structure.</t>
+          <t>Viral metagenomics of synanthropic urban bats: A surveillance strategy for uncovering potentially zoonotic viruses.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Food research international (Ottawa, Ont.)</t>
+          <t>One health (Amsterdam, Netherlands)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>乳糖不耐症患者的糞便檢體（未提及具體數量）</t>
+          <t>2,422 隻蝙蝠中篩選出的 150 對肺與腸道檢體</t>
         </is>
       </c>
       <c r="G50" t="b">
@@ -3070,45 +3074,49 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Lactose intolerance affects over 70% of the global population due to the untimely metabolism of lactose in the colon. To accelerate lactose metabolism, we innovatively employed highland barley polysaccharides (HBP) to modulate the colonic fermentation efficiency of lactose using an in vitro fermentation model and fecal samples from lactose intolerant patients. With the addition of HBP, the consumption efficiency of lactose began to increase after 6 h of fermentation. At 48 h, lactose consumption increased by 29%, surpassing the effect of commercial prebiotics. Meanwhile, HBP with lower molecular weight (HBP-L, 8.69 × 104 g/Mol) exhibited more effective impacts than HBP with high molecular weight (HBP-H, 1.22 × 105 g/Mol), which was particularly evident during the 12-48 h of fermentation. More importantly, HBP, particularly HBP-L, substantially enriched Segatella, Bifidobacterium, and Ligilactobacillus in a time-dependent manner and was positively correlated with decreased lactose levels and elevated bacterial lactase activity, resulting in significant conversion of lactose to lactic acid and short-chain fatty acids. During the first 12 h of fermentation, HBP-L underwent more significant degradation than HBP-H. Meanwhile, the xylose residues and Glcp glycosidic bonds in HBP-L were preferentially utilized, while it was glucose residue in HBP-H. Thus, it indicated that HBPs were degraded and altered the composition of the gut microbiota, thereby enhancing the fermentation efficiency of lactose. Our findings provide a theoretical basis for developing targeted prebiotic foods to manage lactose intolerance.</t>
+          <t>Bats are natural reservoirs for diverse viruses, including coronaviruses, filoviruses, and paramyxoviruses, several of those known to be involved in zoonotic spillover events and demanding an integrated surveillance. Here, we present a framework that leverages Brazil's rabies passive surveillance programme to detect bat-borne viruses. Using an algorithm to select representative specimens from 2422 bats collected across São Paulo state, we submitted 150 paired lung and intestine samples to nanopore metagenomic sequencing. We detected 98 viral contigs from 12 families of public health relevance, including Arenaviridae, Coronaviridae, and Paramyxoviridae. Notably, the approach identified a previously unknown filovirus in bats in the Americas, validating the framework's capacity for epidemic preparedness. These findings reveal an undetected viral diversity and demonstrate how existing animal surveillance can monitor pathogen threats. Crucially, in a workshop involving multisectoral One Health experts in Brazil, this framework was validated as a scalable model for national expansion, adapted for low- and middle-income countries (LMICs).</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>本研究旨在探討青稞多醣（HBP）如何調控乳糖不耐症患者的腸道菌群，以促進體外乳糖發酵與代謝。研究發現，添加 HBP（特別是低分子量的 HBP-L）能在發酵 48 小時後提升乳糖消耗效率達 29%，效果顯著優於商業益生元。機制上，HBP-L 在發酵初期降解更為顯著，並能隨時間特異性富集 *Segatella*、雙歧桿菌屬（*Bifidobacterium*）及 *Ligilactobacillus*，進而提升細菌乳糖酶活性，將乳糖轉化為乳酸與短鏈脂肪酸。本研究證實了青稞多醣能透過重塑腸道菌群結構來加速乳糖代謝，為開發緩解乳糖不耐症的標靶益生元食品提供了重要科學依據。</t>
+          <t>本研究旨在建立一個結合巴西現有狂犬病被動監測計畫的病毒總體基因體學監測架構，以偵測都市蝙蝠所攜帶的潛在人畜共通病毒。研究團隊從聖保羅州收集的 2,422 隻蝙蝠中，篩選出 150 對肺部與腸道檢體進行奈米孔定序。結果成功偵測到 12 個與公共衛生密切相關病毒科的 98 個病毒基因片段（包括沙狀、冠狀與副黏液病毒科等），更首次在美洲蝙蝠中發現一種未知絲狀病毒。此研究不僅揭示了未曾被發現的病毒多樣性，證實利用現有動物監測系統預防流行病的可行性，更為中低收入國家提供了一個具備「健康一體」（One Health）共識、可擴展至全國的傳染病監測模型。</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42637450/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42644084/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>42637441</t>
+          <t>42668212</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Microbial succession drives quality deterioration in refrigerated golden pompano (Trachinotus ovatus): regulatory network of dominant spoilage microbiota on characteristic biomarkers.</t>
+          <t>Correlation between microbial communities, metabolites, and bioactivities in fermented mare's milk revealed by metagenomics and metabolomics.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Food research international (Ottawa, Ont.)</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>Food microbiology</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3121,54 +3129,50 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Elucidating the quality deterioration mechanisms of refrigerated golden pompano (Trachinotus ovatus), this study integrated 16S rRNA gene sequencing and untargeted metabolomics to systematically dissect how microbial ecological succession drives metabolic changes. As critical spoilage indicators, total volatile basic nitrogen (TVB-N) and thiobarbituric acid reactive substances (TBARS) continuously increased during storage, indicating significant deterioration by day 6. Microbial community succession analysis revealed that Psychrobacter, Shewanella, and Pseudomonas gradually became the dominant microbiota in the late storage stage. Metabolite enrichment analysis further demonstrated that this shift redirected the metabolic focus from early-stage nucleotide degradation to late-stage protein hydrolysis and amino acid metabolism. Moreover, multivariate statistical analysis identified 50 potential spoilage biomarkers, among which biogenic amines (histamine, tyramine, and phenylethylamine) were recognized as key indicators reflecting spoilage progression. Correlation network analysis revealed positive correlations between Pseudomonas and Shewanella abundances and the accumulation of these biogenic amines. This suggests that these two genera act as the core functional microbiota, driving spoilage metabolite generation and subsequent quality deterioration. Pathway analysis of potential spoilage biomarker generation indicates that amino acid and nucleotide metabolism constitute the core spoilage pathways, with lipid oxidation serving as a complementary mechanism. Overall, this study elucidates the spoilage mechanisms of refrigerated golden pompano, providing chemical targets for early biomarker detection and targeted antibacterial strategies.</t>
+          <t>Koumiss exhibits various functional properties, including antioxidant, hypoglycemic, and antihypertensive effects; however, natural fermentation is characterized by an uncontrollable microbial community structure, significant fluctuations in product quality, and a lack of specialized fermentation agents. The mechanisms underlying the links between microbial communities, functional metabolites, and bioactivity in natural and inoculated fermentation systems remain unclear. Therefore, this study employed bioactivity assays, metagenomics, and non-targeted metabolomics to systematically analyze differences in microbial communities, metabolite composition, and functional activities of mare's milk under different fermentation regimes. The results indicated that, compared with natural fermentation, inoculated fermentation with a mixed lactic acid bacteria (LAB) culture significantly enhanced the antioxidant, α-glucosidase, α-amylase inhibitory activities, and ACE inhibitory activity of mare's milk; microbial diversity in fermented samples was significantly reduced, with a more pronounced decrease in the inoculated group. Metabolomic analysis revealed that inoculated fermentation significantly enriched functional metabolites, including lipids and organic acids. Correlation analysis indicated that the abundance of Lactiplantibacillus and Limosilactobacillus was significantly positively correlated with beneficial metabolites (e.g., linoleic acid, α-linolenic acid) and functional activities. The lipid and amino acid metabolic pathways are closely associated with the differences in in vitro biological activity of inoculated fermented mare's milk. This study provides a fermentation starter that can improve the in vitro functional activity of mare's milk and reveals the potential metabolic links between LAB fermentation and the altered functional traits of mare's milk, thereby providing a theoretical basis and technical support for the development of high-value-added fermented mare's milk products.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>本研究旨在探討冷藏金鯧魚品質劣化的機制。研究結合 16S rRNA 基因定序與非靶向代謝組學，分析微生物群落演替如何驅動代謝變化。結果顯示，金鯧魚冷藏至第 6 天時顯著腐敗。在貯藏後期，*Psychrobacter*、*Shewanella* 與 *Pseudomonas* 逐漸成為優勢菌群，使代謝焦點自初期的核苷酸降解轉向後期的蛋白質水解與氨基酸代謝。研究鑑定出 50 個潛在腐敗生物標誌物（如組胺、酪胺等生物胺），並發現 *Pseudomonas* 和 *Shewanella* 的豐度與這些生物胺的累積呈正相關，為驅動腐敗的核心菌群。本研究闡明了金鯧魚的腐敗機制，為食品早期變質檢測及靶向抑菌策略提供了科學依據與化學標靶。</t>
+          <t>本研究旨在探討馬乳（Koumiss）在天然發酵與接種乳酸菌發酵下，微生物群落、代謝產物與生理活性之間的關聯。研究結果顯示，接種混合乳酸菌發酵能顯著提升馬乳的抗氧化能力，以及對 α-葡萄糖苷酶、α-澱粉酶及血管張力素轉換酶（ACE）的抑制活性，同時降低了微生物多樣性。代謝體學分析證實，接種發酵促進了脂質與有機酸等功能性代謝物的生成。相關性分析進一步指出，植物乳桿菌（*Lactiplantibacillus*）與檸檬乳桿菌（*Limosilactobacillus*）的豐度與亞麻油酸、α-次亞麻油酸等益生代謝物及生理活性呈正相關。本研究揭示了特定乳酸菌發酵改善馬乳功能特性的代謝機制，為開發具高附加價值的發酵馬乳產品提供了重要的理論依據與技術支撐。</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42637441/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42668212/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>42662912</t>
+          <t>42637484</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Insights into antibiotic resistomes from gut meta-genome-assembled genomes of the free-range chickens.</t>
+          <t>Insights into the analysis of microbial communities in fermented foods from the perspective of DNA-based techniques.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Veterinary and animal science</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
+          <t>Food research international (Ottawa, Ont.)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>16S, metagenomics</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>120 個放養雞糞便檢體（重建出 2,146 個總體基因體組裝基因體/MAGs）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G52" t="b">
@@ -3176,34 +3180,34 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Antibiotic resistance is a growing global threat, and the chicken gut microbiome is a significant reservoir of antibiotic resistance genes (ARGs). To investigate the presence of ARGs in free-range chickens, which are in closer contact with humans and live in closer proximity to human settlements. In this study, we used metagenomic sequencing to characterize the resistome of the chicken gut. We collected 120 fecal samples from free-range chickens across four Chinese provinces and constructed both metagenome-assembled genomes (MAGs) and comprehensive gene catalogs to investigate microbial community structures and ARG distributions. A total of 2,146 MAGs were reconstructed, encompassing 660 species from 26 phyla, forming a comprehensive genomic catalog of the chicken gut microbiota. We identified 254,316 ARGs representing 159 unique resistance genes across 35 antibiotic classes, with multidrug, tetracycline, glycopeptide, and peptide resistance being most prevalent. Notably, ARG distribution showed strong regional variation, influenced by environmental factors and local farming practices. Mobile genetic elements (MGEs), averaging 33.8 per MAG, were positively correlated with ARG abundance (R = 0.77), underscoring their role in facilitating resistance gene dissemination. Specific MAGs-including strains of Escherichia coli and Klebsiella pneumoniae-harbored hundreds of ARGs and virulence factors, highlighting potential high-risk vectors for resistance spread. Our findings reveal a diverse and regionally dynamic antibiotic resistome in the chicken gut, shaped by microbial composition, environment, and host factors. This study provides a valuable genomic resource and emphasizes the need for targeted interventions and surveillance strategies to mitigate antibiotic resistance in poultry production systems.</t>
+          <t>The quality, flavor, and stability of fermented foods depend on the microbial community. However, microbial dynamics are difficult to observe directly, leading to limited control over fermentation. High-throughput sequencing is a revolutionary tool for microbial characterization, among which DNA-based amplicon and metagenomic sequencing are core techniques. Nevertheless, the related data processing workflows in the context of fermented foods have not yet been systematically summarized, hindering the translation of research findings into fermentation practices. This review clarifies the applications of amplicon and metagenomic sequencing in fermented foods. For amplicon sequencing, the impacts of target regions, data preprocessing, and reference databases are addressed. For metagenomic sequencing, sequencing strategies, read-based and binning-based analytical methods, functional annotation, and species-specific databases are discussed. In addition, major strategies for downstream analysis of community data are summarized, including microbial diversity, co-occurrence networks, niche and community assembly, key environmental drivers, and machine learning-based prediction. Amplicon sequencing efficiently reveals microbial succession during fermentation but has limitations in functional annotation. Metagenomic sequencing is notable for functional annotation, enabling the linkage between microbial communities and metabolic potential alongside community characterization. Standardized data preprocessing and specific databases are critical for improving characterization. For community data, integrated analysis allows uncovering the driving factors of microbial succession, thereby helping to regulate fermentation. Notably, the compositional nature of the data must be considered and validated to avoid spurious associations. In summary, the exponential growth of sequencing data will propel the era of precision fermentation.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>本研究利用總體基因體定序技術分析中國四省120個放養雞糞便檢體，成功重建2,146個總體基因體組裝基因體（MAGs）。研究鑑定出254,316個抗藥性基因（ARGs），以多重抗藥性與四環黴素抗性最普遍。ARGs分佈呈現顯著的地區差異，且移動遺傳元件與其豐度呈高度正相關，顯示其在抗藥性傳播中的關鍵作用。此外，大腸桿菌與肺炎克雷伯氏菌等特定菌株攜帶大量ARGs與毒力因子，屬高風險傳播媒介。本研究為禽類腸道菌群提供了寶貴的基因組資源，並強調在養殖系統中實施針對性監控以防範抗藥性傳播的必要性。</t>
+          <t>本文為一篇綜述性研究，旨在探討以 DNA 為基礎的高通量定序技術（包含擴增子定序與宏基因組學）在發酵食品微生物群落分析中的應用。研究指出，儘管高通量定序技術已成為解析微生物動態的革命性工具，但目前缺乏系統性的數據處理框架，限制了科學發現向產業實踐的轉化。本文詳細梳理了從目標區域選擇、數據預處理、參考數據庫建立到下游生物資訊分析（如共現網絡、生態棲位構建及機器學習預測）的標準化流程。研究強調，擴增子定序雖能有效揭示群落演替，但在功能註解上存在限制；而宏基因組學則具備更強的功能解析潛力，能將微生物組成與代謝功能聯繫起來。透過標準化數據處理流程並考慮數據的組成特性，這些先進技術將精準調控發酵過程，引領精密發酵時代的到來。</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42662912/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42637484/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>42637430</t>
+          <t>42637478</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Regional differentiation of microbial communities and metabolites in Yunnan dry-cured beef: insights from high-throughput sequencing and untargeted metabolomics.</t>
+          <t>Effects of sorghum variety on fermentation microecology and flavor characteristics of sesame-flavor Baijiu.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3219,7 +3223,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>3 種高粱品種（Hongyingzi, Hei'e, G），於 2 輪發酵週期中，在 3 個時間點（0、15、50 天）採集發酵酒醅檢體（樣本總數依實驗設計推算為 18 組發酵樣品）</t>
         </is>
       </c>
       <c r="G53" t="b">
@@ -3227,34 +3231,34 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>To reveal the effects of regional processing on quality, microbial communities and metabolites of traditional Yunnan dry-cured beef, samples from Xundian (XD), Yuxi (YX) and Honghe (HH) were analyzed. High-throughput sequencing and UHPLC-Q-Exactive HF/MS untargeted metabolomics were applied. Sensory scores and physicochemical Properties differed significantly (p &lt; 0.05). Bacillota and Staphylococcus dominated bacterial communities. The observed differences in microbial communities and metabolites among regions are shaped by the combined effects of geographical environment and processing conditions. Ascomycota was the main fungal phylum. Debaryomyces dominated XD and HH samples. YX samples had a unique fungal profile dominated by Rhodotorula and Cladosporium. A total of 1320 metabolites were identified. 196 differential metabolites were screened. Key pathways included glycerophospholipid metabolism, pyrimidine metabolism and arachidonic acid metabolism. Correlation analysis indicated that Staphylococcus and Lactococcus were positively associated with amino acid derivatives, while Latilactobacillus and Debaryomyces correlated with organic acids and glycerophospholipids. These findings revealed the potential microbial-metabolic association underlying regional quality differences. They provide support for quality control and traceability of dry-cured beef.</t>
+          <t>Sorghum, the principal raw material for Baijiu fermentation, plays a key role in shaping fermentation microecology and flavor formation. However, the effects of sorghum varietal differences on sesame-flavor Baijiu fermentation remain insufficiently understood. In this study, three sorghum varieties, Hongyingzi (R), Hei'e (B), and a domestic cultivar (G), were compared over two consecutive fermentation rounds. Fermented grain (Jiupei) samples collected at 0, 15, and 50 days were analyzed for physicochemical properties, enzyme activities, microbial communities, volatile compounds in Jiupei and base liquor, and the taste characteristics of the corresponding base liquor. Despite showing similar overall fermentation trends, the three sorghum varieties differed in acid accumulation, starch utilization, microbial succession, and volatile composition. Fungal communities shifted from early Pichia dominance to multi-genus coexistence, whereas bacterial communities progressively converged toward Lactobacillus dominance. A total of 218 and 258 volatile compounds were identified in Jiupei and 176 and 192 in base liquor from the first and second rounds, respectively. Esters were the dominant differential class, and volatile-marker profiles varied among sorghum varieties and fermentation rounds, with no single variety showing consistent enrichment across all sesame-flavor-related compounds. These results indicate that sorghum variety is an important factor associated with microbial assembly and flavor formation during sesame-flavor Baijiu fermentation, and provide a basis for raw material selection and flavor-oriented process optimization.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>本研究旨在探討地理區域與加工工藝對雲南傳統乾醃牛肉（尋甸、玉溪、紅河三地）品質、微生物群落及代謝物的影響。研究結合高通量定序與非靶向代謝組學技術，發現不同地區的乾醃牛肉在感官評分與理化性質上存有顯著差異。細菌群落以厚壁菌門和葡萄球菌屬為主；真菌群落中，尋甸和紅河樣品以德巴利酵母屬為主，玉溪樣品則以紅酵母屬與枝孢菌屬為特有優勢菌。代謝組學共鑑定出1320種代謝物，其中196種為差異代謝物，主要涉及甘油磷脂、嘧啶及花生四烯酸代謝通路。關聯分析顯示，葡萄球菌屬和乳球菌屬與氨基酸衍生物呈正相關，而廣義乳桿菌屬與德巴利酵母屬則與有機酸及甘油磷脂密切相關。本研究揭示了微生物與代謝物的關聯性，為乾醃牛肉的品質控制與產地溯源提供了重要科學依據。</t>
+          <t>本研究旨在探討不同高粱品種對芝麻香型白酒發酵過程中，微生物群落結構與風味代謝物質形成的影響。研究比較了紅纓子（R）、黑鵝（B）與國內品種（G）三種高粱，分析其在發酵過程中的理化特性、微生物演替及揮發性化合物組成。研究發現，儘管各品種發酵趨勢相似，但在酸度累積、澱粉利用率及微生物群落演替上存在顯著差異；真菌群落由早期的畢赤酵母（*Pichia*）主導轉變為多菌屬共存，細菌群落則趨向於乳桿菌（*Lactobacillus*）主導。分析鑑定出上百種揮發性化合物，其中酯類是導致風味差異的主要代謝物。本研究證實了高粱品種是決定白酒發酵微生物群落組裝與最終風味品質的關鍵因子，為白酒產業的原料選擇與製程最佳化提供了重要的科學依據。</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42637430/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42637478/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>42637417</t>
+          <t>42637476</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Allergic responses, gut microbiome and serum metabolism of mice: Effects of epigallocatechin gallate combined with sodium pyrophosphate modified parvalbumin.</t>
+          <t>A Shenling Baizhu San polysaccharide fraction (SLP-2)-based synbiotic alleviates lactose-induced gut dysfunction via a microbiota-metabolite-barrier axis.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3278,20 +3282,330 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
+          <t>Lactose intolerance (LI) is a common digestive disorder, and its management still relies largely on dietary restriction. Because gut microbial fermentation and barrier dysfunction contribute to LI-related symptoms, microbiota-targeted prebiotic or synbiotic strategies may provide complementary approaches. However, the active plant-polysaccharide fractions and their microbial partners remain unclear. This study aimed to identify the bioactive polysaccharide fraction from Shenling Baizhu San and evaluate its pairing with responder bacteria for alleviating high-lactose diet (HLD)-induced intestinal dysfunction. Stepwise ethanol precipitation yielded SLP-2, which was subsequently identified as the principal bioactive fraction through human fecal fermentation, monoculture assays, and an HLD rat model. SLP-2 enriched Eubacterium-associated taxa and supported the growth of Akkermansia muciniphila in monoculture and in vivo. Building on this, a synbiotic combining SLP-2 with A. muciniphila and E. rectale alleviated HLD-induced gut dysfunction; the antibiotic-matched comparison with the probiotics-only group supported an SLP-2-associated contribution. The synbiotic intervention was associated with increased tight junction proteins, MUC2 expression, improved intestinal architecture, and thicker mucus layers. Multi-omics analysis linked co-metabolites, including intestinal 6-MGG and HTy-Ac and systemic DHPV-G, with barrier restoration and an immune profile characterized by increased IL-10 and lower TLR4 expression. These findings suggest that SLP-2-based synbiotic intervention alleviates HLD-induced intestinal dysfunction through microbiota-metabolite-barrier modulation, providing preclinical evidence for future functional-food strategies pending human validation.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>本研究旨在探討參苓白朮散多醣活性組分（SLP-2）結合特定菌株，對高乳糖飲食（HLD）引發之腸道功能障礙的緩解作用。研究發現，SLP-2能促進*A. muciniphila*與真桿菌屬相關菌群生長。以SLP-2搭配益生菌的合生元配方，能顯著改善HLD大鼠的腸道屏障，包含增加緊密連接蛋白與MUC2表達、增厚黏液層。多體學分析顯示，其保護作用與腸道及全身性代謝物（如6-MGG、DHPV-G）的調節，以及抗發炎反應（提升IL-10、降低TLR4）密切相關。此發現為開發防治乳糖不耐症的功能性食品提供了臨床前依據。</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42637476/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>42637471</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Fucoidan from giant kelp alleviates postmenopausal osteoporosis by regulating the betaine-OPG/RANKL/RANK signaling axis.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Food research international (Ottawa, Ont.)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>16S, metabolomics</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Postmenopausal osteoporosis (PMOP), characterized by excessive bone resorption and impaired bone remodeling, remains a significant global health challenge. This study investigated the protective effects of fucoidan from giant kelp (GKP) against PMOP and its underlying mechanisms in ovariectomized mice. GKP supplementation attenuated bone loss by preserving trabecular microarchitecture, normalizing systemic mineral homeostasis, and suppressing osteoclastogenesis, as evidenced by the downregulation of osteoclast-related genes. 16S rRNA gene sequencing revealed that GKP reshaped the gut microbiota by decreasing the Bacteroidota/Firmicutes ratio and enriching beneficial taxa, which promoted short-chain fatty acid production. Targeted metabolomics revealed that GKP induced profound systemic metabolic reprogramming, particularly amino acid metabolism, and identified betaine as a key systemic metabolite effector upregulated following GKP treatment. In vitro assays demonstrated that betaine suppressed receptor activator of nuclear factor-κB ligand (RANKL)-induced osteoclast differentiation and mitigated inflammation. In vivo validation demonstrated that betaine intervention recapitulated the osteoprotective phenotype observed in GKP-treated mice, which was associated with regulation of the osteoprotegerin/RANKL/RANK signaling axis. These results indicate that GKP exerts anti-osteoporotic effects in association with changes in gut microbiota and systemic metabolism, while betaine-mediated regulation of the OPG/RANKL/RANK signaling may contribute to its osteoprotective activity.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>本研究探討巨藻褐藻醣膠（GKP）對去卵巢小鼠更年期後骨質疏鬆症（PMOP）的保護機制。結果顯示，補充GKP能有效減少骨質流失並抑制破骨細胞生成。16S定序顯示GKP重塑了腸道菌群（降低擬桿菌門/厚壁菌門比例），促進短鏈脂肪酸產生。代謝組學分析發現，GKP顯著提升了系統性代謝物甜菜鹼（betaine）的含量。體內外實驗進一步證實，甜菜鹼透過調控OPG/RANKL/RANK信號軸，能抑制破骨細胞分化並緩解骨質流失。本研究證實GKP具備透過「腸道菌群-代謝物」軸抗骨質疏鬆的潛力，為PMOP防治提供了科學依據。</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42637471/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>42637450</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Highland barley polysaccharides promoted lactose intestinal fermentation in vitro: Unveiling the dynamic response of gut microbiota and polysaccharide structure.</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Food research international (Ottawa, Ont.)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>16S, metabolomics</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>乳糖不耐症患者的糞便檢體（未提及具體數量）</t>
+        </is>
+      </c>
+      <c r="G56" t="b">
+        <v>0</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Lactose intolerance affects over 70% of the global population due to the untimely metabolism of lactose in the colon. To accelerate lactose metabolism, we innovatively employed highland barley polysaccharides (HBP) to modulate the colonic fermentation efficiency of lactose using an in vitro fermentation model and fecal samples from lactose intolerant patients. With the addition of HBP, the consumption efficiency of lactose began to increase after 6 h of fermentation. At 48 h, lactose consumption increased by 29%, surpassing the effect of commercial prebiotics. Meanwhile, HBP with lower molecular weight (HBP-L, 8.69 × 104 g/Mol) exhibited more effective impacts than HBP with high molecular weight (HBP-H, 1.22 × 105 g/Mol), which was particularly evident during the 12-48 h of fermentation. More importantly, HBP, particularly HBP-L, substantially enriched Segatella, Bifidobacterium, and Ligilactobacillus in a time-dependent manner and was positively correlated with decreased lactose levels and elevated bacterial lactase activity, resulting in significant conversion of lactose to lactic acid and short-chain fatty acids. During the first 12 h of fermentation, HBP-L underwent more significant degradation than HBP-H. Meanwhile, the xylose residues and Glcp glycosidic bonds in HBP-L were preferentially utilized, while it was glucose residue in HBP-H. Thus, it indicated that HBPs were degraded and altered the composition of the gut microbiota, thereby enhancing the fermentation efficiency of lactose. Our findings provide a theoretical basis for developing targeted prebiotic foods to manage lactose intolerance.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>本研究旨在探討青稞多醣（HBP）如何調控乳糖不耐症患者的腸道菌群，以促進體外乳糖發酵與代謝。研究發現，添加 HBP（特別是低分子量的 HBP-L）能在發酵 48 小時後提升乳糖消耗效率達 29%，效果顯著優於商業益生元。機制上，HBP-L 在發酵初期降解更為顯著，並能隨時間特異性富集 *Segatella*、雙歧桿菌屬（*Bifidobacterium*）及 *Ligilactobacillus*，進而提升細菌乳糖酶活性，將乳糖轉化為乳酸與短鏈脂肪酸。本研究證實了青稞多醣能透過重塑腸道菌群結構來加速乳糖代謝，為開發緩解乳糖不耐症的標靶益生元食品提供了重要科學依據。</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42637450/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>42662912</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Insights into antibiotic resistomes from gut meta-genome-assembled genomes of the free-range chickens.</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Veterinary and animal science</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>metagenomics, small genome</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>120 個糞便檢體</t>
+        </is>
+      </c>
+      <c r="G57" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Antibiotic resistance is a growing global threat, and the chicken gut microbiome is a significant reservoir of antibiotic resistance genes (ARGs). To investigate the presence of ARGs in free-range chickens, which are in closer contact with humans and live in closer proximity to human settlements. In this study, we used metagenomic sequencing to characterize the resistome of the chicken gut. We collected 120 fecal samples from free-range chickens across four Chinese provinces and constructed both metagenome-assembled genomes (MAGs) and comprehensive gene catalogs to investigate microbial community structures and ARG distributions. A total of 2,146 MAGs were reconstructed, encompassing 660 species from 26 phyla, forming a comprehensive genomic catalog of the chicken gut microbiota. We identified 254,316 ARGs representing 159 unique resistance genes across 35 antibiotic classes, with multidrug, tetracycline, glycopeptide, and peptide resistance being most prevalent. Notably, ARG distribution showed strong regional variation, influenced by environmental factors and local farming practices. Mobile genetic elements (MGEs), averaging 33.8 per MAG, were positively correlated with ARG abundance (R = 0.77), underscoring their role in facilitating resistance gene dissemination. Specific MAGs-including strains of Escherichia coli and Klebsiella pneumoniae-harbored hundreds of ARGs and virulence factors, highlighting potential high-risk vectors for resistance spread. Our findings reveal a diverse and regionally dynamic antibiotic resistome in the chicken gut, shaped by microbial composition, environment, and host factors. This study provides a valuable genomic resource and emphasizes the need for targeted interventions and surveillance strategies to mitigate antibiotic resistance in poultry production systems.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>本研究旨在探討放山雞腸道菌群中的抗生素抗藥性基因（ARGs）儲存庫。研究團隊分析了來自中國四個省份的 120 個糞便檢體，透過總體基因體定序重組出 2,146 個基因組（MAGs），涵蓋 660 個物種，建立了完善的雞隻腸道基因組目錄。結果顯示，雞隻腸道內存在多樣化的 ARGs，尤以多重抗藥性、四環黴素及胜肽類抗藥性最為常見。研究發現抗藥性基因的分布具有顯著的區域差異，且與移動遺傳因子（MGEs）呈現高度正相關，顯示 MGEs 在基因傳播中扮演關鍵角色。此外，大腸桿菌與肺炎克雷伯氏菌等特定菌株被識別為攜帶大量抗藥性與毒力因子的高風險載體。本研究揭示了環境與農耕實踐對腸道抗藥體系的塑造作用，為公共衛生監控與家禽業抗藥性管理提供了重要的科學依據與基因資源。</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42662912/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>42637441</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Microbial succession drives quality deterioration in refrigerated golden pompano (Trachinotus ovatus): regulatory network of dominant spoilage microbiota on characteristic biomarkers.</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Food research international (Ottawa, Ont.)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>16S, metabolomics</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G58" t="b">
+        <v>0</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Elucidating the quality deterioration mechanisms of refrigerated golden pompano (Trachinotus ovatus), this study integrated 16S rRNA gene sequencing and untargeted metabolomics to systematically dissect how microbial ecological succession drives metabolic changes. As critical spoilage indicators, total volatile basic nitrogen (TVB-N) and thiobarbituric acid reactive substances (TBARS) continuously increased during storage, indicating significant deterioration by day 6. Microbial community succession analysis revealed that Psychrobacter, Shewanella, and Pseudomonas gradually became the dominant microbiota in the late storage stage. Metabolite enrichment analysis further demonstrated that this shift redirected the metabolic focus from early-stage nucleotide degradation to late-stage protein hydrolysis and amino acid metabolism. Moreover, multivariate statistical analysis identified 50 potential spoilage biomarkers, among which biogenic amines (histamine, tyramine, and phenylethylamine) were recognized as key indicators reflecting spoilage progression. Correlation network analysis revealed positive correlations between Pseudomonas and Shewanella abundances and the accumulation of these biogenic amines. This suggests that these two genera act as the core functional microbiota, driving spoilage metabolite generation and subsequent quality deterioration. Pathway analysis of potential spoilage biomarker generation indicates that amino acid and nucleotide metabolism constitute the core spoilage pathways, with lipid oxidation serving as a complementary mechanism. Overall, this study elucidates the spoilage mechanisms of refrigerated golden pompano, providing chemical targets for early biomarker detection and targeted antibacterial strategies.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>本研究旨在探討冷藏金鯧魚品質劣化的機制。研究結合 16S rRNA 基因定序與非靶向代謝組學，分析微生物群落演替如何驅動代謝變化。結果顯示，金鯧魚冷藏至第 6 天時顯著腐敗。在貯藏後期，*Psychrobacter*、*Shewanella* 與 *Pseudomonas* 逐漸成為優勢菌群，使代謝焦點自初期的核苷酸降解轉向後期的蛋白質水解與氨基酸代謝。研究鑑定出 50 個潛在腐敗生物標誌物（如組胺、酪胺等生物胺），並發現 *Pseudomonas* 和 *Shewanella* 的豐度與這些生物胺的累積呈正相關，為驅動腐敗的核心菌群。本研究闡明了金鯧魚的腐敗機制，為食品早期變質檢測及靶向抑菌策略提供了科學依據與化學標靶。</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42637441/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>42637430</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Regional differentiation of microbial communities and metabolites in Yunnan dry-cured beef: insights from high-throughput sequencing and untargeted metabolomics.</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Food research international (Ottawa, Ont.)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>16S, metabolomics</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G59" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>To reveal the effects of regional processing on quality, microbial communities and metabolites of traditional Yunnan dry-cured beef, samples from Xundian (XD), Yuxi (YX) and Honghe (HH) were analyzed. High-throughput sequencing and UHPLC-Q-Exactive HF/MS untargeted metabolomics were applied. Sensory scores and physicochemical Properties differed significantly (p &lt; 0.05). Bacillota and Staphylococcus dominated bacterial communities. The observed differences in microbial communities and metabolites among regions are shaped by the combined effects of geographical environment and processing conditions. Ascomycota was the main fungal phylum. Debaryomyces dominated XD and HH samples. YX samples had a unique fungal profile dominated by Rhodotorula and Cladosporium. A total of 1320 metabolites were identified. 196 differential metabolites were screened. Key pathways included glycerophospholipid metabolism, pyrimidine metabolism and arachidonic acid metabolism. Correlation analysis indicated that Staphylococcus and Lactococcus were positively associated with amino acid derivatives, while Latilactobacillus and Debaryomyces correlated with organic acids and glycerophospholipids. These findings revealed the potential microbial-metabolic association underlying regional quality differences. They provide support for quality control and traceability of dry-cured beef.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>本研究旨在探討地理區域與加工工藝對雲南傳統乾醃牛肉（尋甸、玉溪、紅河三地）品質、微生物群落及代謝物的影響。研究結合高通量定序與非靶向代謝組學技術，發現不同地區的乾醃牛肉在感官評分與理化性質上存有顯著差異。細菌群落以厚壁菌門和葡萄球菌屬為主；真菌群落中，尋甸和紅河樣品以德巴利酵母屬為主，玉溪樣品則以紅酵母屬與枝孢菌屬為特有優勢菌。代謝組學共鑑定出1320種代謝物，其中196種為差異代謝物，主要涉及甘油磷脂、嘧啶及花生四烯酸代謝通路。關聯分析顯示，葡萄球菌屬和乳球菌屬與氨基酸衍生物呈正相關，而廣義乳桿菌屬與德巴利酵母屬則與有機酸及甘油磷脂密切相關。本研究揭示了微生物與代謝物的關聯性，為乾醃牛肉的品質控制與產地溯源提供了重要科學依據。</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42637430/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>42637417</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Allergic responses, gut microbiome and serum metabolism of mice: Effects of epigallocatechin gallate combined with sodium pyrophosphate modified parvalbumin.</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Food research international (Ottawa, Ont.)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>16S, metabolomics</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G60" t="b">
+        <v>0</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
           <t>Epigallocatechin gallate (EGCG) combined with sodium pyrophosphate (SP) modified parvalbumin (PV) was proposed to sensitize mice, and investigated whether allergic responses changes were associated with gut microbiome and serum metabolism of mice. EGCG combined with SP modified PV has structural changes, and alleviated jejunal damage in mice, while decreased specific serum IgG, IgG1 and IgE levels and may rebalanced Th1/Th2 immune responses. PV-induced allergic responses disrupted gut microbiota and reduced short-chain fatty acids (SCFAs) levels. In contrast, the modified PV could alter the relative abundance of allergic responses-related gut microbiota, such as g__unclassified_f__Lachnospiraceae, g__norank_o__Clostridia_UCG-014 and g__Alistipes, alongside elevated SCFAs levels. Additionally, the modified PV could affect multiple metabolic pathways in serum, and exert a positive impact on phosphatidylethanolamine and phosphatidylcholine levels in glycerophospholipid metabolism. Therefore, the reduction in the allergic responses of PV modified by EGCG and SP were associated with changes in gut microbiota and modulation of glycerophospholipid metabolisms. These correlational observations provided preliminary associative evidence supporting the potential utility of combined EGCG-SP modification as a hypoallergenic processing approach for fish parvalbumin mitigation.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>本研究旨在探討利用表沒食子兒茶素沒食子酸酯（EGCG）結合焦磷酸鈉（SP）修飾魚類主要過敏原小清蛋白（PV），對小鼠過敏反應、腸道菌群及血清代謝的影響。結果顯示，修飾後的PV結構發生改變，能顯著減輕小鼠空腸損傷，降低血清特異性IgG、IgG1及IgE水平，並重建Th1/Th2免疫平衡。此外，修飾後的PV調節了過敏相關腸道菌群（如*Lachnospiraceae*與*Alistipes*）的相對豐度，提升了短鏈脂肪酸（SCFAs）含量，並改善血清甘油磷脂代謝。本研究證實EGCG-SP聯合修飾可作為降低魚類過敏原性的潛在低致敏加工方法。</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/42637417/</t>
         </is>

--- a/papers_database.xlsx
+++ b/papers_database.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>38 個森林與草地生態系統的土壤樣本（於 2009 年與 2019 年進行跨越十年的重複採樣）</t>
+          <t>38 個森林與草原生態系統的土壤（分別於 2009 年與 2019 年進行兩次重複採樣）</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -514,7 +514,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>本研究旨在探討真實世界中長期環境變化（如氮沉降）對土壤微生物群落與健康的影響。研究團隊於2009年與2019年，對中國東部38個森林和草地生態系統進行跨越十年的土壤重複採樣，並利用總體基因體學進行分析。結果顯示，十年間土壤微生物多樣性顯著增加了17%。在多項環境因子中，大氣氮沉降是驅動微生物群落變化的最強預測因子，其與氮循環基因豐度增加及空間周轉率降低密切相關。此外，碳降解與磷循環相關基因增加，而病原體、抗藥性基因及DNA病毒豐度則下降，伴隨土壤綜合健康指數的提升。本研究證實了長期、實際環境變化對微生物的影響，與短期高劑量模擬實驗的結果截然不同，對評估全球變遷下的生態系統健康具有重要科學意義。</t>
+          <t>本研究旨在探討真實自然環境的長期變化對土壤微生物群落與健康的影響。研究團隊於2009與2019年，對中國東部38個森林與草原生態系統進行跨越十年的重複採樣，並利用總體基因體學分析。結果顯示，十年間土壤微生物多樣性增加17%。大氣氮沉降是驅動變化的最強因子，與氮循環基因增加及群落空間周轉率降低密切相關。此外，碳降解與磷循環基因增加，而病原體與抗藥性基因減少，提升了整體土壤健康。本研究證實微生物對長期環境變化的響應與短期高強度模擬實驗有顯著差異，為全球變遷研究提供重要科學依據。</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22 位人類受試者（11 位健康對照組與 11 位長新冠患者）及 ABx 小鼠模型</t>
+          <t>健康對照組 11 位、長新冠（LCOVID）患者 11 位（共 22 個糞便檢體），以及接受糞便移植的抗生素處理（ABx）小鼠（小鼠具體數量未提及）</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -569,7 +569,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>本研究旨在探討長新冠（Long COVID）患者持續兩年的腸道菌相變化及其致病機制。研究透過宏基因組學與液相層析質譜儀（LC-MS）分析人類糞便樣本，發現長新冠患者的腸道微生物多樣性降低，促發炎細菌（如 Streptococcus salivarius）增加，而具抗發炎功能的細菌（如 Faecalibacterium）則減少；同時，碳水化合物降解及短鏈脂肪酸代謝路徑受到抑制。實驗將患者糞便移植至抗生素處理小鼠後，成功誘發了肺部與腸道發炎及焦慮行為，且小鼠對肺炎克雷伯氏菌的抵抗力顯著下降。這些發現證實了長新冠患者的腸道菌群失調具有直接致病潛力，足以在動物模型中重現長新冠相關症狀，為未來開發針對腸道菌群的診斷標記與治療策略提供了關鍵的科學依據。</t>
+          <t>本研究旨在探討罹患長新冠（LCOVID）長達兩年之患者的腸道菌群與代謝物變化，並透過小鼠糞便移植（FMT）驗證其因果關係。研究顯示，LCOVID患者的腸道菌群多樣性顯著降低，促炎菌（如*Streptococcus salivarius*）增加，抗炎菌減少；且其糞便代謝物在短鏈脂肪酸（SCFA）生成與碳水化合物降解等方面出現受損。將患者糞便移植至小鼠後，成功誘發了肺部與腸道發炎、焦慮行為，並削弱了小鼠對肺部感染的抵抗力。本研究證實腸道菌群失衡足以促進長新冠症狀，為未來開發以腸道微生態為核心的長新冠療法奠定了科學依據。</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>未提及（此文為綜述論文，非原始實驗研究）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -624,7 +624,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>本研究針對黃麻脫膠（retting）製程進行系統性回顧，旨在推動傳統經驗式工法轉向精準生物加工。內容探討了黃麻纖維的結構特徵、微生物演替機制、胞外酵素網以及環境因子如何協同影響纖維分離效率與品質。文中評估了多種新興策略，如定義明確的微生物群系應用、酵素輔助處理及水資源高效循環技術。此外，透過整合多體學（基因體、轉錄體、蛋白質體、代謝體）、系統生物學與人工智慧，提出了一套數位決策輔助框架，以解決傳統工藝缺乏標準化、程序變異大及環境污染等問題。總體而言，本研究強調將黃麻脫膠轉型為可預測的精準生物加工，對於提升產業生產力、促進循環生物經濟及環境永續發展具有顯著的科學意義與指導價值。</t>
+          <t>本綜述探討黃麻漚麻（脫膠）技術如何從傳統經驗操作轉型為精準生物製造。文章系統性整合了黃麻韌皮纖維結構、細胞壁降解、微生物群落演替、胞外酶網絡及環境調節因子的最新進展。同時，評估了特定微生物菌群、酶輔助漚麻與多體學（基因體、轉錄體、代謝體）及人工智慧等技術在製程監控中的潛力，並指出當前在微生物交互作用、標準菌群及工業放大上的關鍵瓶頸。本研究為黃麻漚麻邁向標準化、可預測與環保永續的精準生物加工提供了系統級框架。</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（摘要僅指出包含多個大腸直腸癌病患隊列與 Apc min/+ 小鼠模型，但未標註具體樣本數量）</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -679,7 +679,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>本研究探討腸道共生菌 *Agathobacter rectalis* (Ar) 在大腸直腸癌 (CRC) 中的作用。研究發現，CRC 患者體內 Ar 顯著減少，而補充 Ar 能抑制小鼠大腸腫瘤生長。代謝組學分析證實，Ar 產生的代謝物 (-)-表沒食子兒茶素 (EGC) 為關鍵抑癌物質。機制上，EGC 透過直接結合並穩定 pSREBF2，阻斷其與 SCAP 的交互作用，進而抑制 SREBF2 活化，下調膽固醇合成與 MAPK 訊號通路，進而抑制 CRC 細胞生長與遷移。本研究首次揭示了 Ar-EGC「微生物-代謝物」軸對宿主膽固醇代謝的調控機制，為 CRC 的臨床預防與治療提供了全新的靶點與策略。</t>
+          <t>本研究旨在探討腸道共生菌直腸桿菌（*Agathobacter rectalis*, Ar）在大腸直腸癌（CRC）中的作用與分子機制。總體基因體學分析顯示，CRC 患者糞便中的 Ar 豐度顯著降低。動物實驗證實，Ar 能有效減少 Apc min/+ 小鼠的結腸腫瘤數量與體積。代謝組學分析發現，Ar 能產生關鍵代謝物表兒茶素（EGC）。機制上，EGC 可直接結合並穩定 pSREBF2，阻斷 pSREBF2-SCAP 的交互作用，進而抑制 SREBF2 的剪切活化，下調膽固醇合成基因（如 FDPS、PCSK9）的表達並抑制 MAPK 訊號。本研究揭示了 Ar-EGC 微生物-代謝物軸藉由調控膽固醇代謝抑制 CRC 腫瘤生成的新機制，為 CRC 治療提供新策略。</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>未提及（僅提及不同溫度的 TWB 與不同處理方式的模擬系統，未提供具體的生物樣品或實驗重複次數）</t>
+          <t>未提及（僅說明使用盆栽模擬系統「per pot」，未提及具體樣本或盆栽數量）</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -734,7 +734,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>本研究探討茶葉廢棄物生物炭（TWB）在處理農業土壤 PFAS 污染及溫室氣體排放的應用價值。結果顯示，經 500°C 處理的 TWB 因具備最佳的孔隙與表面特性，在全土混合施用下，可顯著降低土壤與滲濾液中的 PFOS 與 PFOA 濃度，並使植物地上部的 PFAS 累積量下降約 36%。此外，TWB 處理能減少一氧化二氮（N2O）排放並增進甲烷（CH4）吸收。宏基因組分析指出，此效益主要源於生物炭的物理化學吸附，而非微生物脫氟作用。本研究確立了生物炭作為同時緩解 PFAS 污染與氣候變遷的潛力，並強調施用策略應視目標而定：全土混合有利於固定 PFAS，而表面施用則在溫室氣體減排上表現更佳。</t>
+          <t>本研究旨在評估茶渣生物炭（TWB）在模擬的PFAS污染土壤-滲濾液-植物系統中，對於抑制全氟和多氟烷基物質（PFAS）遷移及減少溫室氣體（N2O和CH4）排放的雙重效應。研究發現，在500 °C下製備的TWB-500效果最佳。若將其均勻混合於全土中，可使植物地上部的PFAS濃度降低約36%，並顯著降低土壤和滲濾液中的PFAS含量。此外，TWB處理還減少了N2O累積排放並促進CH4淨吸收。總體基因體學分析顯示，與氮循環相關的基因豐度有所下降，解釋了N2O排放減少的機制；而有機氟降解基因並未富集，證實PFAS的控制主要源於物理化學阻控而非微生物去氟作用。此研究證明TWB-500能有效整合PFAS固化與溫室氣體管理，且施用方式（全土混合或表層施作）可依環境整治優先目標進行客製化調整。</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>178 位受試者（免疫功能低下組 n=77，免疫功能健全組 n=101）</t>
+          <t>178位疑似侵襲性肺麴菌病（IPA）患者（包含77位免疫功能低下患者與101位免疫功能正常患者）</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -789,7 +789,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>本研究探討支氣管肺泡灌洗液總體基因體定序（BALF-mNGS）在診斷侵襲性肺麴菌病（IPA）中的應用價值。研究核心在於區分「感染」與「定殖」，並分析不同免疫狀態下的肺部微生物特徵。結果顯示，透過計算麴菌屬的單位定序讀數（RPTM），可有效建立臨床判斷閾值，且該數值與免疫功能低下患者的 90 天死亡率高度相關。此外，mNGS 分析揭示了感染與定殖在微生物群落結構上的差異。此技術不僅能精準區分病原與菌群，還能避免不必要的抗真菌藥物濫用，並為免疫功能低下患者提供重要的預後分層參考，具備高度臨床應用潛力。</t>
+          <t>本研究旨在評估支氣管肺泡灌洗液總體基因體次世代定序（BALF-mNGS）在區分疑似侵襲性肺麴菌病（IPA）患者「感染」與「定植」的臨床價值，並探討其肺部微生態特徵。研究納入178位患者，發現感染者的麴菌相對豐度（RPTM）顯著高於定植者，並針對免疫功能低下與正常組分別訂定出24與33的最佳臨界值。微生態分析顯示兩組具有不同的菌群結構。臨床上，BALF-mNGS能有效引導抗真菌治療，避免定植患者過度治療；而在免疫功能低下組中，高麴菌RPTM值與90天高死亡率顯著相關。此技術不僅能精準診斷，更具備患者預後風險分層的潛力。</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1 個水樣樣本（40 ml）</t>
+          <t>1 個 40 ml 的淡水湖泊水樣</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -844,7 +844,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>本研究旨在透過病毒宏基因組學（viral metagenomics）技術，分析採集自美國亞利桑那州弗拉格斯塔夫（Flagstaff）附近一處淡水湖泊的 40 毫升水樣。研究成功鑑定出 295 個環狀病毒基因體序列，其中包含 126 個 Cressdnaviricota 門與 169 個 Phixviricota 門的病毒成員。此研究擴展了我們對淡水生態系統中病毒多樣性的認知，特別是針對這兩個特定病毒門類的基因體結構提供了基礎數據，有助於進一步解析環境病毒在水生生態系中的演化關係與功能角色。</t>
+          <t>本研究旨在探討美國亞利桑那州 Flagstaff 附近一處小型淡水湖泊中的病毒多樣性。研究團隊對 40 毫升的水樣進行病毒總體基因體學（viral metagenomics）分析，成功鑑定並組裝出 295 個環狀病毒基因體序列。在這些病毒中，有 126 個屬於 Cressdnaviricota 門（環狀單鏈 DNA 病毒），另有 169 個屬於 Phixviricota 門（微小噬菌體相關病毒）。此研究的科學意義在於顯著擴充了淡水生態系統中這兩大病毒門的基因體數據，並證實即使在極少量的環境水樣中，也蘊藏著極高多樣性且未知的病毒資源，有助於深化對淡水微生態系統及病毒演化多樣性的理解。</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>3種不同的接種源（海洋沉積物、河口沉積物、厭氧污泥）</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -899,7 +899,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>本研究旨在探討三種不同微生物接種源（海洋沉積物、河口沉積物及厭氧污泥）對微生物燃料電池（MFC）處理亞甲基藍（MB）染料廢水效能的影響。實驗結果顯示，以海洋沉積物作為接種源的 MFC 在產電性能上表現最佳（35 mW/m²），而厭氧污泥接種組則在染料脫色率（96%）與 COD 去除率（75%）上表現最為突出。透過宏基因組學（metagenomics）分析，研究證實了電活性細菌群落中關鍵酵素與代謝路徑的存在，進一步解釋了不同接種源在電子轉移及染料降解過程中的功能差異。本研究證實 MFC 系統在處理染料廢水方面具有極高的應用潛力，且處理後的廢水毒性顯著降低，為生物電化學修復技術提供了科學數據支撐，對工業染料廢水處理具有重要的環境應用價值。</t>
+          <t>本研究旨在比較雙腔式微生物燃料電池（MFC）中，三種不同接種源（海洋沉積物、河口沉積物、厭氧污泥）在降解亞甲藍染料與產電的效率。結果顯示，海洋沉積物系統具最高的功率密度（35 mW/m²）與庫倫效率（25%）；厭氧污泥系統則有最佳的化學需氧量去除率（75%）與脫色率（96%）。處理後廢水的植物毒性顯著降低。宏基因組學分析揭示了關鍵產電菌的分布及參與降解與發電的酶和代謝途徑。本研究證實了不同接種源在 MFC 污水處理與生物發電的潛力，並闡明了其微生物學機制。</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>metagenomics, small genome</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>本研究透過宏基因組解析技術，深入探討加勒比海笛鯛（*Hypoplectrus* spp.）魚鰓微生物群落。研究分析了來自 15 個物種、共 353 個魚鰓樣本，成功組裝出 70 個宏基因組組裝基因體（MAGs）。研究發現魚鰓微生物群落具有高度特異性，區別於周遭海域環境。特別是 Burkholderiaceae 科下的一個支系，在不同魚種、地點與年份間皆高度盛行，且基因體編碼了完整的碳固定與硫氧化代謝路徑，展現出化能合成潛力，這是學界首次證實魚類魚鰓可能共生此類細菌。此發現揭示了魚鰓生態系統中複雜的微生物交互作用，這些細菌不僅參與氮循環與抗生素生產，其族群結構更與宿主魚類的地理分布演化高度相關，為理解魚類生理穩態與免疫反應提供了全新的科學視角。</t>
+          <t>本研究針對加勒比海地區 15 種「蝴蝶魚」（Hypoplectrus spp.）進行了大規模的宏基因組研究。透過分析 353 個魚鰓檢體並重建 70 個宏基因組組裝基因組（MAGs），研究發現魚鰓微生物群落與周圍海水環境顯著不同，具有獨特的演化軌跡。最重大的發現是鑑定出一種具高度普遍性的 Burkholderiaceae 細菌，該菌株擁有完整的固碳與硫氧化代謝路徑，顯示其具備化能合成潛力，這是科學界首次在魚類鰓部發現此類共生菌。此外，該菌株的基因體結構與宿主魚類的地理分布呈現高度一致性。此研究揭示了魚鰓微生物生態系統的複雜性，並為魚類生理、恆定性及免疫反應與微生物間的交互作用提供了重要的演化科學基礎。</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>278 位腸胃道癌症患者</t>
+          <t>278 位胃腸道癌症患者及同基因腫瘤小鼠模型</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>本研究旨在探討腸道菌群如何影響胃腸道（GI）癌症對免疫治療的反應與背後機制。對278位GI癌症患者的總體基因體分析顯示，唾液乳桿菌（*Lactobacillus salivarius*）在治療有反應者體內顯著富集。動物實驗證實，該菌及其關聯代謝物鵝去氧膽酸（CDCA）能顯著增強抗PD-1療效。機制上，CDCA誘導腫瘤細胞產生活性氧（ROS）並觸發免疫原性細胞死亡，同時促使巨噬細胞向抗腫瘤的M1型極化，進而活化CD8+ T細胞。本研究證實了*L. salivarius*與CDCA在提升胃腸道癌症免疫治療效果上的臨床應用潛力，有望作為新型免疫治療佐劑。</t>
+          <t>本研究旨在探討腸道菌群影響胃腸道（GI）癌症免疫治療反應的具體機制。透過對 278 位 GI 癌症患者的總體基因體分析，發現唾液乳桿菌（*Lactobacillus salivarius*）在治療有反應的患者體內顯著富集。於小鼠模型中，該菌能增加抗腫瘤 M1 型巨噬細胞與 CD8+ T 細胞的浸潤，顯著提升抗 PD-1 療效。研究進一步證實，該菌的代謝物鵝去氧膽酸（CDCA）為關鍵功能分子，能透過誘導活性氧（ROS）引發腫瘤細胞的免疫原性死亡，並促進巨噬細胞向 M1 型極化，從而激活 CD8+ T 細胞的抗腫瘤免疫反應。本研究揭示了唾液乳桿菌及其代謝物 CDCA 作為增強 GI 癌症免疫治療活性佐劑的臨床潛力。</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>metagenomics, small genome</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>未提及（摘要未明確列出具體的檢體總數或個體數量）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>本研究旨在評估放牧牲畜（犛牛、藏綿羊）與瀕危物種普氏原羚共用棲地時，基因危害（含抗藥性基因 ARGs、金屬抗性基因 MRGs 及毒力因子 VFs）的傳播風險。研究利用總體基因體學（metagenomics）與基因體解析技術，發現牲畜體內的基因危害豐度顯著高於普氏原羚。透過來源溯源分析，普氏原羚約 64% 的抗藥性組分可歸因於牲畜，證實了放牧界面下的微生物交互作用。此外，轉座子（如 tnpA）與抗性基因的高度共現性，顯示了基因水平轉移的潛在危機；研究更成功從牲畜與普氏原羚的微生物基因體中，鑑定出攜帶多重抗性與毒力因子的細菌宿主。本研究建立的分析框架，為監測野生動物與家畜介面下的抗藥性傳播提供了重要的科學依據與監測策略。</t>
+          <t>本研究旨在評估放牧家畜與瀕危野生普氏原羚接觸介面上的遺傳危害（如抗藥性基因 ARG、金屬耐受基因 MRG 與毒力因子 VF）暴露風險。研究利用總體基因體學分析氛牛、藏羊、普氏原羚及當地表土，結果顯示家畜體內的 MRG 和高風險 ARG 豐度顯著高於普氏原羚。來源追蹤分析（FEAST）指出，普氏原羚約 64% 的抗藥組組成可歸因於這兩種家畜，僅不到 1% 來自土壤。此外，研究透過基因組解析定位了攜帶危害基因與移動遺傳因子的細菌宿主。本研究不僅闡明了遺傳危害的來源與傳播關聯，也為野生動物與家畜接觸介面的多層級生物安全監測提供了重要科學依據。</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>253 位嬰兒</t>
+          <t>253 位嬰兒（收集 253 份基線糞便檢體，其中 250 位提供至少 2 次檢體，241 位提供全部 3 次檢體）</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PREVENT 1 是一項瑞典全國性、前瞻性的嬰兒隊列研究，旨在探討生命最初兩年內的腸道微生物群發育過程，並分析微生物群動態變化與餵養方式、感染、生長發育及日常生活福祉的關聯。該研究透過縱向追蹤，於三個階段收集 253 位嬰兒的糞便檢體，並運用宏基因組定序（shotgun metagenomics）進行分析，同時整合家長問卷、糞便影像及嬰兒啼哭紀錄等數據。此研究建立了一個高品質的資料庫，未來將深入解析嬰兒腸道微生物群的組成、抗藥性基因組（resistome）及其功能路徑，並探討其如何受抗生素暴露及早期環境因素影響，對於理解生命早期微生物群與健康結果的因果機制具有重要科學意義。</t>
+          <t>本研究建立瑞典全國性嬰兒追蹤世代「PREVENT 1」，旨在透過縱向總體基因體學分析，描繪嬰兒出生後前兩年的腸道菌相發育軌跡，並探討其與餵養、生長及感染等健康指標的關聯。研究成功招募253名足月嬰兒，並在三個時間點重複收集糞便檢體與問卷，受試者維持率極高（241名嬰兒提供全部三次檢體）。此世代研究提供高質量的臨床與多體學數據，未來將深入分析抗生素暴露與飲食如何形塑嬰兒腸道菌群、抗藥性基因組及代謝途徑，對理解早期生命健康極具臨床與科學價值。</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>未提及（文中僅提及 CaOx 大鼠與小鼠模型，未說明具體樣本數量）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G14" t="b">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>本研究探討腸道微生物與草酸鈣（CaOx）腎結石形成的機制。透過多體學分析，研究發現異別石膽酸（isoalloLCA）在結石模型中的糞便、血液及腎臟中均顯著升高，且來源於腸道菌群。機制研究顯示，isoalloLCA 可結合 PARP1 蛋白，進而誘導腎小管上皮細胞發生由 PARP1 介導的細胞凋亡（Parthanatos），導致腎損傷與結石惡化。動物實驗證實，透過藥物抑制或基因敲除 PARP1，可有效減緩結石形成及腎臟損害。此研究不僅闡明了「腸道菌群—isoalloLCA—PARP1—細胞凋亡」這一關鍵致病軸線，更為臨床上以 PARP1 作為腎結石防治的新型治療靶點提供了強有力的科學證據。</t>
+          <t>本研究旨在探討腸道菌群及其代謝物在草酸鈣（CaOx）腎結石形成中的作用機制。研究利用多組學技術（16S定序、宏基因組學與空間代謝組學），證實源自腸道菌群的代謝物「異別石膽酸（isoalloLCA）」在草酸鈣大鼠及患者體內顯著升高。機制上，isoalloLCA能與PARP1蛋白特異性結合，引發DNA損傷與粒線體受損，進而促進腎小管上皮細胞發生PARP1介導的「守護者細胞凋亡（parthanatos）」與結晶沉積。動物實驗證實，清除腸道菌或抑制PARP1活性（如使用AZD5305）可顯著減輕腎損傷。本研究揭示了「腸道菌群-isoalloLCA-PARP1-parthanatos」軸在腎結石病理中的關鍵角色，並指出PARP1為具潛力的臨床治療靶點。</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>metagenomics, small genome</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1 個臨床病例</t>
+          <t>1位急性發熱疾病患者（單一病例）</t>
         </is>
       </c>
       <c r="G15" t="b">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>本研究報告了一名居住於哥倫比亞亞馬遜普圖馬約地區（Putumayo）的患者，在 2023-2024 年拉丁美洲奧羅普切熱（Oropouche fever）大規模流行期間，因急性發燒就診並被檢測出感染 C 群正布尼亞病毒（Group C Orthobunyavirus）。研究團隊利用針對脊椎動物病毒的宏基因組定序技術（VirCapSeq-VERT）進行病原體鑑定，成功辨識出屬於 Caraparu 複合群的病毒，並分離出該病毒株。儘管本研究僅限於單一病例且缺乏血清學或長期臨床數據追蹤，但研究結果強烈支持在亞馬遜等傳染病流行地區，針對不明原因發燒病例應用無偏見的分子檢測技術，對於臨床診斷及病原體監測具有重要的科學價值。</t>
+          <t>本研究旨在調查2023-2024年拉丁美洲奧羅普切熱（Oropouche fever）疫情期間，哥倫比亞亞馬遜地區一名急性發熱患者的病因。研究團隊採用針對脊椎動物病毒的總體基因體學（宏基因組）定序技術（VirCapSeq-VERT），成功鑑定並分離出一種與Caraparu複合體相關的C群正布尼亞病毒（Group C Orthobunyavirus）。由於此類病毒臨床表現與其他蟲媒病毒相似，診斷極具挑戰。本研究雖僅基於單一病例，但其結果強調了在亞馬遜盆地等流行病疫區，使用無偏向性分子檢測技術對於診斷不明原因發熱疾病的重要臨床與科學價值。</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1246,30 +1246,30 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>42658871</t>
+          <t>42656127</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Breastmilk microbiota and its association with infant iron deficiency anaemia: A 16S rRNA metagenomic study in Peruvian mothers cohort.</t>
+          <t>Development and Validation of Mock Communities as Quality Control Materials for Clinical Metagenomic Next-Generation Sequencing.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PloS one</t>
+          <t>Annals of laboratory medicine</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>16S</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>46 對母嬰（46 個母乳檢體）</t>
+          <t>25 次重複分析（針對開發出的四種模擬群落進行評估）</t>
         </is>
       </c>
       <c r="G16" t="b">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Anaemia is one of the most important public health challenges in developing countries. The global burden is estimated at 1.8 billion people, affecting approximately 30% of all children. Despite the implementation of multiple strategies over several decades, up to 42.5% of children under 3 years of age suffer anaemia in rural areas of Peru. We studied the microbiota of breastmilk (hBM) from mothers with children under the age of 1 and analysed its association with their iron deficiency anaemia. 46 mother-child pairs were recruited from Talara, a town on the northern coast of Peru and classified according to the clinical status of the children. Children with anaemia were also tested for ferritin level to classify them as iron deficiency anaemia (IDA) or non-iron deficiency anaemia (non-IDA). hBM samples were taken from the mothers after careful instruction to reduce the risk of sample contamination and the microbiome was analyzed using 16S rRNA sequencing. Streptococcus and Staphylococcus were the predominant genera, with 90% of bacterial abundance being explained by 14 genera. Alpha diversity analysis showed that hBM from mothers of children with non-IDA had higher levels of bacterial richness than hBM from healthy (p &lt; 0.01) and IDA (p &lt; 0.05) participants. Principal coordinates analysis did not yield differential clusters but showed a disparity in the spread of samples for non-IDA group when compared with the other groups. IDA group showed higher burden of Corynebacterium, Acinetobacter, Paludibacter and Nitrospira, while exhibiting a trend towards a lower burden of Streptococcus. No statistically significant differences were identified on demographic characteristics. This study suggests that hBM microbiota may differ in mothers of children with IDA and non-IDA, highlighting the necessity of further in-depth research to elucidate potential factors associated with its pathogenesis.</t>
+          <t>Metagenomic next-generation sequencing (NGS) enables comprehensive detection of a broad spectrum of microorganisms. However, its clinical application faces two major challenges: the development of appropriate microbiome-based biomarkers and the need to ensure the reproducibility and quality of the microbiome analytical workflow. Therefore, we developed four types of bead-based mock communities as standard materials for microbiome analysis and evaluated potential experimental biases arising from nucleic acid extraction and sequence analysis. Mock communities were assembled from strains isolated from clinical specimens and selected considering Gram reaction, taxonomic phylogeny, and prevalence, and processed into frozen beads. The communities were analyzed using shotgun whole-metagenome sequencing. The effect of DNA extraction kit choice was evaluated using the Thermo Fisher Scientific MagMAX Microbiome Ultra Nucleic Acid Isolation Kit and Qiagen PowerSoil Kit. Four types of mock communities comprising 26 species commonly found in the gastrointestinal tract, respiratory tract, skin, and genital tract plus cerebrospinal fluid were developed considering Gram reaction, GC content, and phylogenetic distribution. Across 25 repeated analyses, the median repeatability of each taxon was 18.97% (range, 2.87%-107.38%), while within-laboratory imprecision was 26.22% (range, 9.26%-153.83%). Repeatability remained below 10% for most dominant taxa with relative abundances &gt;20%. The choice of DNA extraction kit had a significant effect on taxonomic distributions. Microbial mock communities are essential QC materials for clinical metagenomic NGS. Further studies are needed to minimize variability and establish a standardized protocol for clinical implementation.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>本研究探討祕魯農村地區嬰兒缺鐵性貧血（IDA）與母親母乳（hBM）菌相之間的關聯。研究對象為 46 對母嬰，透過 16S rRNA 定序分析母乳微生物群落，發現母乳菌相以鏈球菌屬（Streptococcus）與葡萄球菌屬（Staphylococcus）為優勢菌群。研究結果顯示，非貧血組嬰兒的母親，其母乳具備較高的細菌豐富度。此外，IDA 組嬰兒母親的母乳中，棒狀桿菌屬（Corynebacterium）與不動桿菌屬（Acinetobacter）等細菌豐度較高，而鏈球菌屬則呈現下降趨勢。此研究發現母乳微生物群組成可能與嬰兒貧血狀態相關，雖無法直接證實因果關係，但為後續探討嬰兒貧血的致病機制提供了重要的微生物學線索。</t>
+          <t>本研究旨在解決臨床宏基因組次世代定序（mNGS）在品質控制與再現性上的挑戰，開發了四種基於珠粒的「模擬微生物群落」（mock communities）作為標準品。這些群落涵蓋了腸道、呼吸道、皮膚、生殖道及腦脊髓液中常見的 26 種菌株。研究透過鳥槍法全宏基因體定序（shotgun metagenomics）評估了不同 DNA 萃取試劑盒（MagMAX 與 PowerSoil）及實驗流程對結果的偏誤影響。結果顯示，微生物的檢測豐度會顯著受到萃取試劑盒選擇的干擾，且在 25 次重複實驗中，群落組成存在一定的實驗室內誤差。此研究確立了模擬群落作為臨床 mNGS 品質控制材料的重要性，對於推動微生物組檢測的標準化流程與臨床應用具有關鍵價值。</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1292,35 +1292,37 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42658871/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42656127/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>42658844</t>
+          <t>42657522</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Enrichment and Characterization of a Haloalkaline-tolerant Anammox Bacterium.</t>
+          <t>Resistant starch alleviates intestinal fibrosis involving an acetate-mediated HDAC2-H3K27ac axis in fibroblasts.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>The ISME journal</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Food &amp; function</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>5.4</v>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>metagenomics, small genome, others (transcriptional profiling)</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>未提及（研究基於特定實驗室富集培養物之實驗與分析）</t>
+          <t>未提及（研究使用 DSS 誘導的小鼠模型以及人類與小鼠的原代纖維母細胞，但未具體說明樣本數）</t>
         </is>
       </c>
       <c r="G17" t="b">
@@ -1328,12 +1330,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Metagenomic surveys have substantially expanded the known diversity of anaerobic ammonium-oxidizing (anammox) bacteria. However, the physiological traits of newly proposed anammox genera remain largely hypothetical due to the lack of cultured representatives. Although niche differentiation driven by salinity, organic substrates, and oxygen is well documented in anammox bacteria, adaptations to alkaline environments remain uncharacterized. Moreover, no anammox lineage has been identified as an alkaline specialist. Herein, we report the enrichment (&gt;80% relative abundance) of an anammox bacterium, provisionally named Candidatus Loosdrechtia alkalitolerans, which represents the cultured member of the genus Ca. Loosdrechtia. Ca. L. alkalitolerans exhibits marked haloalkaline tolerance, outcompeting other freshwater anammox genera under long-term saline-alkaline stress conditions (0.5% NaCl; pH~9.13). Comparative genomics revealed that among freshwater anammox lineages, only Ca. L. alkalitolerans encodes a complete multiple resistance and pH adaptation (Mrp) cation/proton antiporter operon. Batch assays with transcriptional profiling demonstrated that sodium addition upregulated mrp expression and recovered anammox activity under alkaline stress, suggesting that Mrp-mediated cation/proton exchange may contribute to pH homeostasis in Ca. L. alkalitolerans. Furthermore, database mining revealed that the habitat of Ca. L. alkalitolerans is not restricted to haloalkaline environments, but extends to diverse freshwater and wastewater ecosystems. These findings provide mechanistic insight into saline-alkaline tolerance in anammox bacteria, expanding understanding of their physiological plasticity and ecological roles.</t>
+          <t>Dietary fibre-based interventions are of growing interest for the prevention and treatment of digestive diseases. In this study, we investigated the effect of resistant starch (RS) on intestinal fibrosis, a stricturing condition driven by excessive extracellular matrix (ECM) accumulation. RS was found to alleviate intestinal fibrosis in a dextran sulfate sodium (DSS)-induced chronic colitis mouse model, as evidenced by restored colon length, reduced ECM deposition (fibronectin and collagen I), and decreased levels of α-smooth muscle actin. Given that RS is fermented by the gut microbiota in the colon, metagenomic sequencing revealed that RS reshaped the composition of the gut microbiota and increased the abundance of beneficial gut bacteria, including Bacteroides acidifaciens, Faecalibaculum rodentium, and Bifidobacterium pseudolongum, which are known to enhance the production of short-chain fatty acids. Targeted metabolomic analysis further showed a marked increase in acetate levels, which was associated with reduced intestinal fibrosis. However, direct in vivo evidence that acetate is required for the anti-fibrotic effect of RS remains lacking. Using human (CCD-18Co) and primary mouse intestinal fibroblasts, the major ECM-producing cells that drive fibrosis progression, we demonstrated that acetate inhibited TGF-β-induced fibroblast activation by inhibiting histone deacetylase 2, thereby enhancing the acetylation level of histone H3 at lysine 27. Collectively, these results suggest a potential microbial-metabolic-epigenetic axis linking RS and acetate to fibrosis attenuation, which awaits causal validation in vivo. This axis holds promise as a therapeutic target for fibrotic diseases.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>本研究成功富集並鑑定出一種耐鹽鹼的厭氧氨氧化（Anammox）細菌，命名為 *Candidatus Loosdrechtia alkalitolerans*。該菌株在長期高鹽、高鹼（0.5% NaCl，pH 9.13）環境下表現出強大的競爭優勢。透過基因體比較分析，研究發現該菌株含有特殊的 Mrp 陽離子/質子反向轉運蛋白操縱子，這是其適應鹼性環境的關鍵機制；轉錄組分析進一步證實，在鹼性壓力下，補充鈉離子可上調 Mrp 表現並恢復其代謝活性。此發現不僅揭示了厭氧氨氧化菌應對鹽鹼逆境的生理分子機制，證明了該菌在廣泛的淡水與廢水生態系統中具有潛在的生態地位，更為未來工業廢水處理中的脫氮技術應用提供了理論基礎與科學見解。</t>
+          <t>本研究探討抗性澱粉（RS）對腸道纖維化的改善作用及其潛在機制。透過 DSS 誘導的小鼠結腸炎模型，研究發現 RS 可有效減輕腸道纖維化並減少細胞外基質堆積。宏基因體定序顯示 RS 能重塑腸道菌群，增加如 *Bacteroides acidifaciens* 等短鏈脂肪酸產生菌的豐度；代謝體分析進一步證實乙酸（acetate）水平顯著上升。機制研究揭示，乙酸能抑制纖維母細胞中 HDAC2 的活性，進而提升組蛋白 H3K27 的乙醯化水平，抑制 TGF-β 誘導的纖維母細胞活化。本研究提出了一條「微生物-代謝-表觀遺傳」軸線，指出 RS 可藉由促進乙酸生成來對抗腸道纖維化，為治療纖維化相關疾病提供了新的科學依據與潛在治療靶點。</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1343,37 +1345,35 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42658844/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42657522/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>42657522</t>
+          <t>42658844</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Resistant starch alleviates intestinal fibrosis involving an acetate-mediated HDAC2-H3K27ac axis in fibroblasts.</t>
+          <t>Enrichment and Characterization of a Haloalkaline-tolerant Anammox Bacterium.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Food &amp; function</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>5.4</v>
-      </c>
+          <t>The ISME journal</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>metagenomics, metabolomics</t>
+          <t>metagenomics, small genome, others (transcriptional profiling)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>未提及（研究使用 DSS 誘導的小鼠模型以及人類與小鼠的原代纖維母細胞，但未具體說明樣本數）</t>
+          <t>未提及（研究基於特定實驗室富集培養物之實驗與分析）</t>
         </is>
       </c>
       <c r="G18" t="b">
@@ -1381,12 +1381,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Dietary fibre-based interventions are of growing interest for the prevention and treatment of digestive diseases. In this study, we investigated the effect of resistant starch (RS) on intestinal fibrosis, a stricturing condition driven by excessive extracellular matrix (ECM) accumulation. RS was found to alleviate intestinal fibrosis in a dextran sulfate sodium (DSS)-induced chronic colitis mouse model, as evidenced by restored colon length, reduced ECM deposition (fibronectin and collagen I), and decreased levels of α-smooth muscle actin. Given that RS is fermented by the gut microbiota in the colon, metagenomic sequencing revealed that RS reshaped the composition of the gut microbiota and increased the abundance of beneficial gut bacteria, including Bacteroides acidifaciens, Faecalibaculum rodentium, and Bifidobacterium pseudolongum, which are known to enhance the production of short-chain fatty acids. Targeted metabolomic analysis further showed a marked increase in acetate levels, which was associated with reduced intestinal fibrosis. However, direct in vivo evidence that acetate is required for the anti-fibrotic effect of RS remains lacking. Using human (CCD-18Co) and primary mouse intestinal fibroblasts, the major ECM-producing cells that drive fibrosis progression, we demonstrated that acetate inhibited TGF-β-induced fibroblast activation by inhibiting histone deacetylase 2, thereby enhancing the acetylation level of histone H3 at lysine 27. Collectively, these results suggest a potential microbial-metabolic-epigenetic axis linking RS and acetate to fibrosis attenuation, which awaits causal validation in vivo. This axis holds promise as a therapeutic target for fibrotic diseases.</t>
+          <t>Metagenomic surveys have substantially expanded the known diversity of anaerobic ammonium-oxidizing (anammox) bacteria. However, the physiological traits of newly proposed anammox genera remain largely hypothetical due to the lack of cultured representatives. Although niche differentiation driven by salinity, organic substrates, and oxygen is well documented in anammox bacteria, adaptations to alkaline environments remain uncharacterized. Moreover, no anammox lineage has been identified as an alkaline specialist. Herein, we report the enrichment (&gt;80% relative abundance) of an anammox bacterium, provisionally named Candidatus Loosdrechtia alkalitolerans, which represents the cultured member of the genus Ca. Loosdrechtia. Ca. L. alkalitolerans exhibits marked haloalkaline tolerance, outcompeting other freshwater anammox genera under long-term saline-alkaline stress conditions (0.5% NaCl; pH~9.13). Comparative genomics revealed that among freshwater anammox lineages, only Ca. L. alkalitolerans encodes a complete multiple resistance and pH adaptation (Mrp) cation/proton antiporter operon. Batch assays with transcriptional profiling demonstrated that sodium addition upregulated mrp expression and recovered anammox activity under alkaline stress, suggesting that Mrp-mediated cation/proton exchange may contribute to pH homeostasis in Ca. L. alkalitolerans. Furthermore, database mining revealed that the habitat of Ca. L. alkalitolerans is not restricted to haloalkaline environments, but extends to diverse freshwater and wastewater ecosystems. These findings provide mechanistic insight into saline-alkaline tolerance in anammox bacteria, expanding understanding of their physiological plasticity and ecological roles.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>本研究探討抗性澱粉（RS）對腸道纖維化的改善作用及其潛在機制。透過 DSS 誘導的小鼠結腸炎模型，研究發現 RS 可有效減輕腸道纖維化並減少細胞外基質堆積。宏基因體定序顯示 RS 能重塑腸道菌群，增加如 *Bacteroides acidifaciens* 等短鏈脂肪酸產生菌的豐度；代謝體分析進一步證實乙酸（acetate）水平顯著上升。機制研究揭示，乙酸能抑制纖維母細胞中 HDAC2 的活性，進而提升組蛋白 H3K27 的乙醯化水平，抑制 TGF-β 誘導的纖維母細胞活化。本研究提出了一條「微生物-代謝-表觀遺傳」軸線，指出 RS 可藉由促進乙酸生成來對抗腸道纖維化，為治療纖維化相關疾病提供了新的科學依據與潛在治療靶點。</t>
+          <t>本研究成功富集並鑑定出一種耐鹽鹼的厭氧氨氧化（Anammox）細菌，命名為 *Candidatus Loosdrechtia alkalitolerans*。該菌株在長期高鹽、高鹼（0.5% NaCl，pH 9.13）環境下表現出強大的競爭優勢。透過基因體比較分析，研究發現該菌株含有特殊的 Mrp 陽離子/質子反向轉運蛋白操縱子，這是其適應鹼性環境的關鍵機制；轉錄組分析進一步證實，在鹼性壓力下，補充鈉離子可上調 Mrp 表現並恢復其代謝活性。此發現不僅揭示了厭氧氨氧化菌應對鹽鹼逆境的生理分子機制，證明了該菌在廣泛的淡水與廢水生態系統中具有潛在的生態地位，更為未來工業廢水處理中的脫氮技術應用提供了理論基礎與科學見解。</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1396,37 +1396,37 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42657522/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42658844/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>42656127</t>
+          <t>42658871</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Development and Validation of Mock Communities as Quality Control Materials for Clinical Metagenomic Next-Generation Sequencing.</t>
+          <t>Breastmilk microbiota and its association with infant iron deficiency anaemia: A 16S rRNA metagenomic study in Peruvian mothers cohort.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Annals of laboratory medicine</t>
+          <t>PloS one</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>16S</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25 次重複分析（針對開發出的四種模擬群落進行評估）</t>
+          <t>46 對母嬰（46 個母乳檢體）</t>
         </is>
       </c>
       <c r="G19" t="b">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Metagenomic next-generation sequencing (NGS) enables comprehensive detection of a broad spectrum of microorganisms. However, its clinical application faces two major challenges: the development of appropriate microbiome-based biomarkers and the need to ensure the reproducibility and quality of the microbiome analytical workflow. Therefore, we developed four types of bead-based mock communities as standard materials for microbiome analysis and evaluated potential experimental biases arising from nucleic acid extraction and sequence analysis. Mock communities were assembled from strains isolated from clinical specimens and selected considering Gram reaction, taxonomic phylogeny, and prevalence, and processed into frozen beads. The communities were analyzed using shotgun whole-metagenome sequencing. The effect of DNA extraction kit choice was evaluated using the Thermo Fisher Scientific MagMAX Microbiome Ultra Nucleic Acid Isolation Kit and Qiagen PowerSoil Kit. Four types of mock communities comprising 26 species commonly found in the gastrointestinal tract, respiratory tract, skin, and genital tract plus cerebrospinal fluid were developed considering Gram reaction, GC content, and phylogenetic distribution. Across 25 repeated analyses, the median repeatability of each taxon was 18.97% (range, 2.87%-107.38%), while within-laboratory imprecision was 26.22% (range, 9.26%-153.83%). Repeatability remained below 10% for most dominant taxa with relative abundances &gt;20%. The choice of DNA extraction kit had a significant effect on taxonomic distributions. Microbial mock communities are essential QC materials for clinical metagenomic NGS. Further studies are needed to minimize variability and establish a standardized protocol for clinical implementation.</t>
+          <t>Anaemia is one of the most important public health challenges in developing countries. The global burden is estimated at 1.8 billion people, affecting approximately 30% of all children. Despite the implementation of multiple strategies over several decades, up to 42.5% of children under 3 years of age suffer anaemia in rural areas of Peru. We studied the microbiota of breastmilk (hBM) from mothers with children under the age of 1 and analysed its association with their iron deficiency anaemia. 46 mother-child pairs were recruited from Talara, a town on the northern coast of Peru and classified according to the clinical status of the children. Children with anaemia were also tested for ferritin level to classify them as iron deficiency anaemia (IDA) or non-iron deficiency anaemia (non-IDA). hBM samples were taken from the mothers after careful instruction to reduce the risk of sample contamination and the microbiome was analyzed using 16S rRNA sequencing. Streptococcus and Staphylococcus were the predominant genera, with 90% of bacterial abundance being explained by 14 genera. Alpha diversity analysis showed that hBM from mothers of children with non-IDA had higher levels of bacterial richness than hBM from healthy (p &lt; 0.01) and IDA (p &lt; 0.05) participants. Principal coordinates analysis did not yield differential clusters but showed a disparity in the spread of samples for non-IDA group when compared with the other groups. IDA group showed higher burden of Corynebacterium, Acinetobacter, Paludibacter and Nitrospira, while exhibiting a trend towards a lower burden of Streptococcus. No statistically significant differences were identified on demographic characteristics. This study suggests that hBM microbiota may differ in mothers of children with IDA and non-IDA, highlighting the necessity of further in-depth research to elucidate potential factors associated with its pathogenesis.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>本研究旨在解決臨床宏基因組次世代定序（mNGS）在品質控制與再現性上的挑戰，開發了四種基於珠粒的「模擬微生物群落」（mock communities）作為標準品。這些群落涵蓋了腸道、呼吸道、皮膚、生殖道及腦脊髓液中常見的 26 種菌株。研究透過鳥槍法全宏基因體定序（shotgun metagenomics）評估了不同 DNA 萃取試劑盒（MagMAX 與 PowerSoil）及實驗流程對結果的偏誤影響。結果顯示，微生物的檢測豐度會顯著受到萃取試劑盒選擇的干擾，且在 25 次重複實驗中，群落組成存在一定的實驗室內誤差。此研究確立了模擬群落作為臨床 mNGS 品質控制材料的重要性，對於推動微生物組檢測的標準化流程與臨床應用具有關鍵價值。</t>
+          <t>本研究探討祕魯農村地區嬰兒缺鐵性貧血（IDA）與母親母乳（hBM）菌相之間的關聯。研究對象為 46 對母嬰，透過 16S rRNA 定序分析母乳微生物群落，發現母乳菌相以鏈球菌屬（Streptococcus）與葡萄球菌屬（Staphylococcus）為優勢菌群。研究結果顯示，非貧血組嬰兒的母親，其母乳具備較高的細菌豐富度。此外，IDA 組嬰兒母親的母乳中，棒狀桿菌屬（Corynebacterium）與不動桿菌屬（Acinetobacter）等細菌豐度較高，而鏈球菌屬則呈現下降趨勢。此研究發現母乳微生物群組成可能與嬰兒貧血狀態相關，雖無法直接證實因果關係，但為後續探討嬰兒貧血的致病機制提供了重要的微生物學線索。</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42656127/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42658871/</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>未提及（原文僅提及針對浙江龍游石窟進行採樣，未具體標示樣本總數）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G20" t="b">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>本研究探討人工光污染對地下砂岩環境中岩面微生物群落及其功能潛力的影響。研究發現，在龍游石窟中，細菌群落佔據絕對優勢；人工光照射促進了藍細菌（Cyanobacteriota）的增殖，而黑暗環境則維持了更高的群落多樣性與複雜的共現網絡。透過代謝潛力分析，研究揭示了環境光照對微生物代謝途徑的調控：人工光環境強化了氮與硫的同化作用，日光環境促進了固氮作用，而黑暗環境則有利於硝化、反硝化與硫氧化過程。此外，細菌群落的分化亦受溫度、濕度、pH值及可溶性鹽分等環境因子綜合影響。本研究釐清了人工照明作為地下遺產環境中關鍵人為干擾因素的角色，為制定砂岩文化遺產的預防性保護措施提供了科學依據與光照管理建議。</t>
+          <t>本研究探討人造光污染對地下砂岩古蹟（龍游石窟）岩表微生物群落及生物降解功能的影響。透過16S rRNA定序與總體基因體學分析，發現光照顯著改變群落結構：人工光與日光下藍菌門富集，而黑暗環境則由假單胞菌門和放線菌門主導，且黑暗處具更高的多樣性與網絡複雜度。代謝潛力分析顯示，人工光增強了同化性氮、硫代謝，而黑暗則利於硝化與硫氧化。此外，群落分化也與溫濕度及pH等環境因子相關。本研究證實人造光源是調控地下微生物的重要因子，為砂岩文物的預防性保護與照光管理提供科學依據。</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>metagenomics, others (metaproteomics)</t>
+          <t>metagenomics, others</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>本研究旨在探討堆肥過程中，群聚感應（Quorum sensing, QS）如何調節微生物的腐植化代謝功能。研究透過宏基因組學（metagenomics）與宏蛋白質組學（metaproteomics）分析，發現添加 MnSO4 與 Fe0（CMF）能顯著提升腐植酸（HA）含量及其聚合度。結果顯示，CMF 處理促進了高溫期微生物的 QS 相關基因與氧化還原酶基因的表現，特別是特定菌群（如 Bacillota, Chloroflexota 等）的豐度增加。研究證實，透過關鍵 QS 模組（如 ahlD 與 3-OXO-C8-HSL）介導的種間溝通，能有效活化碳水化合物與胺基酸代謝，進而推動腐植酸的芳香化過程，提升最終產物的熱穩定性與芳香性。此發現揭示了 QS 機制在堆肥腐植化過程中的關鍵調節作用，為優化有機廢棄物處理及堆肥品質提供了科學理論依據。</t>
+          <t>本研究旨在利用總體基因體學與總體蛋白質組學技術，探討群體感應（QS）相關基因表達在堆肥腐植化過程中的調節機制。研究發現，聯合添加硫酸錳與零價鐵（CMF）能顯著提高腐植酸（HA）的含量、熱穩定性與芳香度。CMF顯著富集了高溫微生物（如Bacillota、Chloroflexota和Myxococcota），並在高溫期上調關鍵QS相關基因（如ahlD）的表達與訊號分子水平。網路分析與體外實驗進一步證實，關鍵QS模組促進了菌群間的交流合作，進而增強下游的微生物氧化還原活性及碳水化合物與氨基酸代謝，共同驅動腐植酸的芳香化。本研究為QS微生物在堆肥腐植化中的生態角色與精準調控提供了全新見解。</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>本研究旨在探討鈉離子（Na+）對甲烷厭氧氧化（AOM）耦合六價鉻（Cr(VI)）還原系統的調控機制。實驗結果顯示，添加 NaCl 能顯著提升 Cr(VI) 的還原效率。微生物群落分析指出，Na+ 富集了具備 AOM 能力的甲烷桿菌（*Methanobacterium*）與具備胞外電子傳遞（EET）能力的電活性細菌，兩者形成共生體系。機制上，Na+ 增強了微生物聚體的電子儲存容量，降低電子傳遞阻力，並促進酪胺酸與腐植酸類物質的胞外聚合物（EPS）分泌。宏基因體分析證實，Na+ 上調了逆向產甲烷途徑（Mcr, Mtr）與膜結合電子傳遞複合物（Fpo, HdrDE）基因，同時增加輔酶 F420 與 ATP 水平，證實 Na+ 是透過強化胞內能量代謝與 EET 來提升還原效率。此發現為利用甲烷修復重金屬污染提供了重要的科學依據與理論基礎。</t>
+          <t>本研究旨在探討跨膜電化學梯度驅動者——鈉離子（Na+），如何調控「甲烷厭氧氧化（AOM）耦合六價鉻 [Cr(VI)] 生物還原系統」的代謝活性與電子傳遞機制。研究發現，添加 NaCl 能顯著提升 Cr(VI) 的去除效率。微生物分析顯示，Na+ 富集了具 AOM 能力的 *Methanobacterium* 與具胞外電子傳遞（EET）能力的電活性細菌，形成協同共生關係。此外，Na+ 提高了微生物的胞內 ATP 與輔酶 F420 水平，並促進胞外聚合物（EPS）分泌以降低電子傳遞阻力。總體基因體學分析進一步證實，Na+ 上調了逆向產甲烷及膜結合電子傳遞複合物的關鍵基因。本研究首次審視並揭示了 Na+ 促進 AOM 耦合 Cr(VI) 還原的生物能量學機制，為利用甲烷進行重金屬生物整治提供了重要理論基礎。</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>metagenomics, others (Transcriptomics)</t>
+          <t>metagenomics, others</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>未提及（僅提及使用雄性 CD-1 小鼠，未註明具體數量）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G23" t="b">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>本研究探討口服聚苯乙烯奈米塑膠（PS-NPs）對雄性小鼠造成的生殖毒性及其潛在機制。透過為期 28 天的暴露實驗，研究團隊整合總體基因體學與雙器官轉錄體學分析，發現 PS-NPs 會導致體重減輕、精子活力顯著下降及附睪病理損傷。宏基因體分析顯示腸道菌群失調，特別是厚壁菌門與擬桿菌門比例失衡，以及有益菌 *Ligilactobacillus murinus* 的耗損。轉錄體學結果進一步揭示肝臟代謝與生理時鐘途徑的紊亂，以及睪丸中類固醇激素合成基因的下調與細胞凋亡訊號的活化。研究提出「腸道-肝臟/睪丸軸」假說，認為奈米塑膠透過改變腸道微生態，進而引發肝臟代謝與睪丸功能障礙。此發現強調了環境奈米塑膠對多器官系統的潛在危害，為環境毒理學與生殖健康風險評估提供了重要的分子生物學證據。</t>
+          <t>本研究探討口服聚苯乙烯奈米塑料（PS-NPs）28天對雄性CD-1小鼠的毒性效應及其作用機制。研究發現，PS-NPs暴露會引發非單調劑量依賴性反應，導致小鼠體重顯著減輕、精子活力嚴重受損及附睾病理病變。腸道總體基因體學分析顯示，PS-NPs引起腸道菌群失調（厚壁菌門/擬桿菌門比例升高，有益菌如鼠乳桿菌顯著減少）。雙器官轉錄組學分析進一步證實，肝臟中代謝、解毒與晝夜節律途徑失調，而睾丸中類固醇激素合成基因持續下調且凋亡信號改變。本研究首次揭示了奈米塑料誘導生殖毒性與「腸-肝/睾丸軸」的關聯，為環境微塑料的哺乳動物多器官毒性機制提供了重要科學依據。</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1676,30 +1676,30 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>42647600</t>
+          <t>42648218</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Urogenital immune signatures are associated with birth outcomes after maternal urinary tract infection.</t>
+          <t>Agricultural sprinkler irrigation systems as environmental reservoirs and airborne dissemination sources of Legionella pneumophila.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Science translational medicine</t>
+          <t>Journal of environmental management</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>8.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics, small genome</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未明確提及具體檢體數量（僅指出於西班牙東北部農村的兩個區域，針對灌溉池塘與溝渠進行採樣）</t>
         </is>
       </c>
       <c r="G24" t="b">
@@ -1707,12 +1707,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Preterm birth is the leading cause of infant mortality, resulting in more than 1 million neonatal deaths globally each year. Maternal urinary tract infection (UTI) during pregnancy increases risk for preterm birth; however, biological processes mediating UTI-associated preterm birth are not well described. We established a murine maternal UTI model in which challenge with uropathogenic Escherichia coli (UPEC) initiated preterm labor and birth in about half of dams. Although bacterial burdens were similar, dams experiencing preterm birth displayed excessive bladder inflammation, elevated placental and decidual cytokines, higher proportions of male fetuses, and lower maternal serum interleukin-10 (IL-10) compared with nonlaboring dams. Exogenous IL-10 or lymph node sequestration of T cells reduced placental type 17 T helper cells (TH17 cells) and abrogated preterm birth. In a human pregnancy cohort, we correlated urinary cytokines with birth outcomes and urine culture status. These analyses yielded an exploratory, noninvasive culture-agnostic system for evaluating preterm birth risk, implicating T cell-related cytokines including IL-10, IL-15, GM-CSF, and RANTES. These findings demonstrate that our murine model provides a platform to investigate immunological and microbial factors governing UTI-associated preterm birth and, coupled with patient samples, may be used to identify candidate biomarkers and mechanistic targets for future investigation.</t>
+          <t>Sprinkler irrigation systems are critical for modern agriculture but represent largely unrecognized aquatic environments capable of sustaining opportunistic human pathogens. Among them, Legionella pneumophila is of particular concern due to its ability to colonize engineered water systems, persist under fluctuating environmental conditions, and be transmitted through aerosols. In this study, we conducted a comprehensive microbiological and genomic investigation of irrigation ponds and ditches in a rural area of north-east Spain where two zones were sampled. Metagenomic profiling revealed highly diverse microbial communities encompassing more than 20,000 species, including 21 airborne-transmissible bacterial pathogens of clinical relevance. Notably, L. pneumophila was detected in both zones, with a relative abundance of up to 4.6 %. Culture-based isolation confirmed the presence of L. pneumophila serogroup 1, Pontiac group, Benidorm subgroup, sequence type 15. Phylogenetic analysis demonstrated a close relationship between this environmental strain and clinical isolates obtained during a Legionnaires' disease outbreak occurred in 2015, which had remained without a confirmed environmental source. Meteorological data from the exposure period revealed wind conditions favouring long-distance aerosol dispersion from irrigated fields toward residential areas. Our findings provide evidence that irrigation infrastructures can act as environmental reservoirs and dissemination routes of L. pneumophila among other airborne pathogens. These results underscore the need to incorporate agricultural irrigation systems into routine environmental surveillance, outbreak investigations, and public health risk assessments.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>本研究旨在探討孕婦尿路感染（UTI）導致早產的免疫機制。研究團隊建立尿路致病性大腸桿菌（UPEC）感染的孕鼠模型，發現發生早產的母鼠伴隨更嚴重的膀胱發炎、胎盤細胞激素升高及血清IL-10降低；給予外源性IL-10或抑制T細胞，能減少胎盤TH17細胞並預防早產。此外，人類佇列研究證實，尿液中T細胞相關細胞激素（如IL-10、IL-15等）與早產風險密切相關。本研究結合動物模型與臨床樣本，揭示了UTI引發早產的免疫關鍵，並為未來篩檢及治療提供了潛在的非侵入性生物標誌物與機制標靶。</t>
+          <t>本研究旨在探討農業噴灌系統是否為嗜肺軍團菌（*Legionella pneumophila*）等致病菌的環境宿主與空氣傳播源。團隊對西班牙農村灌溉水體進行分析，總體基因體學顯示其含有逾2萬種微生物，包括21種臨床相關的空氣傳播病原體，且嗜肺軍團菌相對豐度達4.6%。研究成功分離出嗜肺軍團菌血清型1（ST15），系統發育分析證實該環境株與2015年退伍軍人症爆發的臨床分離株高度相關。氣象數據亦支持風向有利於氣膠從農田長距離擴散至住宅區。此發現證實農業灌溉系統為軍團菌的傳播媒介，強調應將其納入例行環境監測與公衛風險評估。</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1722,27 +1722,29 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42647600/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648218/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>42657129</t>
+          <t>42644416</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pulmonary Infiltrates, Airway Mucosal Lesions and Respiratory Microbiology After Freshwater Drowning: A Case Report.</t>
+          <t>Nationwide cohort study reveals low bifidobacteria and distinct microbiota composition and function in Swedish newborns.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Respirology case reports</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>Gut microbes</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11</v>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>metagenomics</t>
@@ -1750,7 +1752,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1 例病患（n=1）</t>
+          <t>308 名瑞典新生兒的糞便檢體</t>
         </is>
       </c>
       <c r="G25" t="b">
@@ -1758,12 +1760,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Early pulmonary abnormalities after freshwater drowning can be overinterpreted as bacterial pneumonia, especially when inflammatory biomarkers and respiratory microbiology are positive. A 20-year-old man was resuscitated after approximately 2 min of freshwater submersion. Day 1 chest CT showed bilateral lower-lobe-predominant opacities compatible with non-cardiogenic pulmonary oedema and aspiration-related lung injury, with near-complete resolution by Day 25. Day 3 bronchoscopy showed diffuse, non-removable, millet-seed-like whitish tracheal mucosal protrusions with hyperaemia and oedema, compatible with acute irritative airway injury. BALF mNGS detected multiple gram-negative bacterial signals, predominantly Klebsiella pneumoniae, while sputum culture yielded ESBL-negative, susceptible K. pneumoniae. Possible drowning-associated pneumonia was considered because of aspiration, fever, markedly elevated inflammatory biomarkers and concordant microbiology; however, rapid radiological improvement and clinical stability suggested a substantial non-infectious component. The patient recovered after an 8-day course of piperacillin-tazobactam without antibiotic escalation, corticosteroids, mechanical ventilation or acute respiratory distress syndrome.</t>
+          <t>NCT06285630.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>本研究透過單一病例報告，探討淡水溺水後肺部浸潤與呼吸道損傷的臨床鑑別診斷。一名 20 歲男性溺水後出現肺水腫與氣道黏膜病變，臨床表現極易與細菌性肺炎混淆。研究利用 mNGS（宏基因組次世代定序）檢測支氣管肺泡灌洗液，雖確認存在肺炎克雷伯菌（*Klebsiella pneumoniae*）訊號，但影像學與臨床病程顯示其肺部損傷主要源於吸入性損傷及急性化學性氣道刺激，而非嚴重的細菌感染。此案例凸顯了臨床判斷溺水相關肺炎時的挑戰，強調在面對看似感染的臨床數據時，應綜合考量影像改善速度與臨床穩定性，避免過度診斷與不必要的抗生素升級，對急性溺水病患的精準治療具有重要的臨床參考價值。</t>
+          <t>本研究旨在探討瑞典新生兒的腸道菌相組成與功能特徵。透過總體基因體學分析，研究發現瑞典新生兒腸道中的雙歧桿菌（特別是嬰兒雙歧桿菌）豐度顯著偏低，並呈現出獨特的菌相結構與代謝功能。此現象與現代化生活型態及分娩方式密切相關。這項全國性世代研究揭示了現代環境對嬰兒早期腸道微生態建立的深遠影響，為未來的臨床嬰幼兒益生菌介入與健康照護策略提供了關鍵的科學依據。</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1773,37 +1775,35 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42657129/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42644416/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>42649294</t>
+          <t>42648171</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Synergistic degradation of fucoidans in the ocean.</t>
+          <t>Co-occurrence of muddy off flavor and cyanotoxin genes in the polluted Guandu river waters (Rio de Janeiro, Brazil).</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nature</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>48.5</v>
-      </c>
+          <t>The Science of the total environment</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>metabolomics, metagenomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>未提及（該研究採用重組海洋微生物群落進行實驗，未提供具體的生物樣本人數或檢體數量）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G26" t="b">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Fucoidans, a class of complex polysaccharides produced by brown algae and diatoms, contribute to long-term carbon sequestration owing to their resistance to microbial degradation1,2. Although individual microorganisms can break down portions of these polysaccharides3-5, it remains unclear whether complete breakdown is possible in nature and, if so, by what mechanisms. Here we show that fucoidans are degraded through synergistic interactions between specialized bacteria with complementary metabolic functions. Using metabolomic analysis of a reconstructed marine consortium, we uncovered metabolic guilds of bacteria that preferentially degrade either the sulfated fucose backbone or the side branches of rare monomers. This functional division of labour leads to an unexpectedly high number of synergistic interactions between different degraders that enhanced degradation efficiency up to 97.1%. Despite varying fucoidan structures across different types of algae6, the metabolic functions of degraders remained conserved, enabling quantitative prediction of degradation outcomes based on community and substrate composition. The frequent co-occurrence of functionally complementary fucoidan degraders in ocean metagenomes suggests that synergistic degradation is a globally relevant strategy. Our findings suggest that the environmental turnover of complex biopolymers depends not only on individual metabolic capabilities of degraders but also on ecological interactions shaped by substrate architecture. This work provides a mechanistic framework for understanding carbon cycling in the ocean and for engineering synthetic microbial consortia to degrade recalcitrant polysaccharides.</t>
+          <t>The Guandu river basin is responsible for supplying Rio de Janeiro municipality, Brazil, with drinking water. This study investigated water quality during the geosmin crisis in January and March 2020, by relating the water quality and odor compounds with metagenomic tools. Guandu river water was eutrophic. The cyanobacterial genera identified were Microcystis, Planktothrix, Dolichospermum, Nostoc, Synechococcus, Planktothricoides, and Cyanobium, indicating that bloom-associated communities in the system are taxonomically diverse. Functional annotation of metagenomic sequences revealed the presence of genes associated with the biosynthesis of taste-and-odor compounds, including geosmin (geoA) and 2-methylisoborneol (mic), as well as multiple biosynthetic clusters related to cyanotoxin production. Genes linked to microcystin (mcy), saxitoxin (sxt), anatoxin (ana), cylindrospermopsin (cyr), lyngbyatoxin (ltx), guanitoxin (gnt), and nodularin (nda) were detected across the dataset, indicating a broad genetic potential for the production of secondary metabolites relevant to water quality. The co-occurrence of cyanotoxins, geosmin and 2-MIB genes suggests that off-flavor is an indication of cyanotoxin potential production in the water.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>本研究探討海洋中複雜多醣體「褐藻醣膠」（fucoidans）的微生物降解機制。儘管褐藻醣膠因其抗降解性在碳封存中扮演關鍵角色，但過往對於其在自然界中是否能被完全分解並不清楚。研究發現，褐藻醣膠的降解並非單一物種所能完成，而是透過具有互補代謝功能的細菌群落進行「協同作用」。透過代謝體學分析，研究團隊識別出專門降解硫酸岩藻糖骨架與稀有單醣側鏈的代謝群組（metabolic guilds），這種分工合作能將降解效率大幅提升至 97.1%。此外，研究顯示此代謝功能在不同環境下具有高度保守性，且在海洋宏基因組中普遍存在。本研究揭示了生物聚合物的環境周轉率取決於微生物間的生態交互作用，為理解海洋碳循環機制提供了重要框架，並為未來利用人工合成微生物群落降解頑固性多醣體提供了技術基礎。</t>
+          <t>本研究旨在探究巴西里約熱內盧瓜杜河於2020年初爆發土臭素危機期間的水質狀況，並利用總體基因體學技術探討水質異味與微生物群落之關聯。研究發現，該富營養化水體中含有多種藍菌，且功能性註釋顯示其富含合成土臭素（*geoA*）與2-甲基異莰醇（*mic*）等異味物質的基因。更重要的是，多種藍菌毒素（如微囊藻毒素、石房蛤毒素等）的合成基因群與這些異味基因呈現共存。此發現證實了水體異味的出現與藍菌毒素的潛在生成具有高度相關性，可作為飲用水安全監測及評估藍菌毒素潛在危害的重要預警指標。</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1826,35 +1826,35 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42649294/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648171/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>42644746</t>
+          <t>42647759</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Metabolic division of labour drives estuarine-coastal N2O emissions.</t>
+          <t>The Gut Microbiome in Multiple Sclerosis.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>The ISME journal</t>
+          <t>Neurology(R) neuroimmunology &amp; neuroinflammation</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>metagenomics, metatranscriptomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>974 個重建的 N2O 相關基因體（原文未提及具體的環境樣本採集數量）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G27" t="b">
@@ -1862,12 +1862,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Estuarine and coastal systems are global hotspots of marine nitrous oxide (N2O) emissions, where microbial nitrification and denitrification are the primary processes regulating N2O dynamics. However, how interactions among different N2O-associated microorganisms influence ecosystem-scale N2O emissions remains poorly understood. This study combined in situ N2O concentrations, 15N-based potential rates, metagenomics, metatranscriptomics, and genome-scale metabolic model analysis to explore N2O production and reduction processes in estuarine and coastal systems. Potential N2O production and reduction rates, together with in situ concentrations, the relative abundance, and the transcriptional activity of associated genes, were significantly higher at low salinity and declined toward coastal regions. Based on the gene content of 974 recovered N2O-associated genomes, microorganisms were classified into three functional groups: net N2O producers, net N2O consumers, and self-sustaining N2O players. The abundance, composition, and activity of these functional groups shifted along estuarine-coastal gradients. A larger NO/N2O exchange gap, reflecting the imbalance between model-inferred NO and N2O handoff potentials, was found at low salinity and was associated with elevated bottom-water N2O concentrations. Together, community-level division of labour and the associated exchange gap provide a conceptual framework for linking N2O-related functional groups to N2O accumulation in estuarine-coastal ecosystems.</t>
+          <t>Multiple sclerosis (MS) is a chronic inflammatory demyelinating disease of the CNS whose risk and course are shaped by both genetic and environmental factors, among which the intestinal microbiota has emerged as a key, potentially modifiable contributor. People with MS frequently display altered gut microbiota, characterized by depletion of fiber-fermenting, short-chain fatty acid (SCFA)-producing commensals, and expansion of taxa associated with mucus degradation and proinflammatory metabolism. These compositional shifts are paralleled by broad changes in blood and CSF metabolites, including reduced SCFAs, tryptophan-derived aryl hydrocarbon receptor ligands, and secondary bile acids. In addition, several reports highlight the accumulation of aromatic amino acid-derived phenolic and indolic compounds and specific lipid mediators linked to neuroinflammation and neurodegeneration. In this up-to-date review, we synthesize evidence from experimental models and human studies showing how microbial metabolites can influence MS pathogenesis through converging mechanisms: modulation of gut and blood-brain barrier integrity; shaping of T-cell and B-cell responses; direct effects on microglia, astrocytes, and oligodendrocyte lineage cells after crossing into the CNS; and modulation of neural circuits, particularly those involving the vagus nerve. Finally, we highlight current gaps, including the need for longitudinal, harmonized multiomic cohorts, and mechanistic studies integrating microbiome, metabolome, and host readouts across gut, blood, and CNS. Overall, available data support a model in which coordinated disruption of the gut microbiota-metabolite axis, rather than any single pathogen, contributes to MS, opening avenues for microbiota-based and metabolite-based biomarkers and therapies aimed at restoring immune and neuroglial homeostasis.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>本研究旨在探討河口與沿海系統中，微生物交互作用如何驅動一氧化二氮（N2O）的排放。研究結合現場觀測、15N同位素速率、總體基因體與轉錄體學，重建了974個N2O相關基因體。結果指出，低鹽度區域的N2O產生與還原速率及基因表達顯著較高。研究將微生物劃分為淨產生者、淨消費者與自給自足者，並發現低鹽度區因群落間物質交換失衡，存在較大的NO/N2O交換缺口，進而導致底層水體N2O顯著累積。本研究建立了群落水平的「分工與交換缺口」理論框架，為預測及理解海洋生態系統N2O排放提供了關鍵的科學依據。</t>
+          <t>本研究探討多發性硬化症（MS）與腸道微生物群之間的關聯。研究指出，MS 患者的腸道菌相呈現失調狀態，包括短鏈脂肪酸（SCFA）產生菌減少，以及促發炎代謝菌的增加。這些微生物群落的變化伴隨著血液與腦脊髓液中代謝物（如色胺酸衍生物、膽汁酸及 SCFA）的顯著改變，這些物質經證實與神經發炎及退化密切相關。文中綜述了微生物代謝產物如何透過調節腸道與血腦屏障完整性、影響免疫細胞（T/B 細胞）反應，以及直接作用於神經膠質細胞來參與 MS 的致病機制。總結而言，MS 的發生與腸道菌群-代謝物軸的整體失調有關，而非單一病原體所致。該研究強調未來需進行多體學（multiomics）整合分析，以開發基於微生物群的生物標記與創新治療策略，旨在恢復患者的免疫與神經恆定。</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1877,37 +1877,37 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42644746/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647759/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>42648688</t>
+          <t>42647164</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Temperature Sensitivity of Pyrrhotite-Driven Metavanadate Bioreduction in Groundwater.</t>
+          <t>Sex differences in the gut microbiome and related metabolites: role in cardiometabolic disease.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Environmental research</t>
+          <t>Gut microbes</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>7.7</v>
+        <v>11</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（本文為綜論性回顧文章，非原創實驗研究）</t>
         </is>
       </c>
       <c r="G28" t="b">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Pyrrhotite-driven metavanadate [V(V)] bioreduction is a promising green strategy for the remediation of vanadium-contaminated aquifers. However, how this microbially driven process responds to different temperatures remains unclear. Herein, the responses of pyrrhotite-driven V(V) bioreduction to different temperatures ranging from 4 to 45 °C were investigated. V(V) removal first increased and then decreased with increasing temperature, peaking at 35 °C, with the reaction rate constant reaching 0.077 d-1. V(V) could be reduced to VO2 precipitates, accompanied by oxidation of S(-II) and Fe(II) to sulfate and Fe(III), respectively. Metagenomic binning revealed that S(-II) oxidation was more sensitive to temperature changes than Fe(II) oxidation for V(V) reducers. Bacteria coupling V(V) reduction with both S(-II) and Fe(II) oxidation (e.g., Ramlibacter sp.) were detected exclusively at 35 °C. The transcription of functional genes (related to V(V) reduction, S(-II) oxidation, and Fe(II) oxidation), electron transport activity and related components all exhibited a temperature-dependent pattern, first increasing and then decreasing, with a peak at 35 °C. This study reveals the temperature sensitivity of pyrrhotite-driven V(V) bioreduction, which is helpful for risk assessment and targeted bioremediation of vanadium contamination under different temperature conditions.</t>
+          <t>Sex differences in major cardiometabolic diseases (CMD), such as type 2 diabetes, metabolic dysfunction-associated steatotic liver disease, and cardiovascular disease, have been increasingly recognized across the life course. During the reproductive stage, women generally have a more favorable cardiometabolic risk profile than men, but their risk of experiencing CMD significantly increases after menopause. Emerging evidence suggests that sexually dimorphic gut microbiota and gut microbiota-related metabolites (GMRMs) may contribute to such sex disparities. However, existing findings are heterogeneous and underlying mechanisms remain incompletely understood. In this review, we synthesize the evidence examining sex differences in gut microbial diversity, overall composition, taxa abundances, and levels of GMRMs across key life stages, including pre-puberty, adolescence, and different phases of adulthood (with emphasis on pre- and post-menopausal periods). We summarize potential biological mechanisms underlying sexual dimorphism in the gut microbiome and GMRMs, emphasizing the central role of sex steroids, along with contributions from immune function and other host and environmental factors. We further integrate evidence linking sexually dimorphic microbial taxa (e.g., Akkermansia muciniphila, Eubacterium, Ruminococcus, and other Firmicutes taxa) and GMRMs (e.g., microbiota-derived short-chain fatty acids, secondary bile acids, and trimethylamine N-oxide) to key cardiometabolic pathways involving inflammation, glucose and lipid metabolism, and vascular function. Finally, we identify critical knowledge gaps and emphasize the need for future large longitudinal studies that would integrate repeated measurements of the gut microbiome, untargeted metabolomics, and sex steroid hormones across the life course. Such approaches are essential to clarify biological pathways and inform sex-specific microbiome-based interventions for CMD prevention and management.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>本研究旨在探討不同溫度（4至45 °C）對地下水中磁黃鐵礦驅動的偏釩酸鹽 [V(V)] 生物還原過程之影響。研究發現，V(V) 去除率隨溫度升高呈先升後降趨勢，並在 35 °C 時達到峰值（反應速率常數 0.077 d⁻¹），此時 V(V) 被還原為 VO₂ 沉澱，並伴隨硫與鐵的氧化。總體基因體 binning 分析顯示，還原菌的硫氧化過程對溫度變化比鐵氧化更為敏感，且僅在 35 °C 下偵測到能同時耦合硫與鐵氧化的關鍵細菌（如 *Ramlibacter* sp.）。此外，相關功能基因轉錄與電子傳遞活性亦在 35 °C 達到頂峰。本研究揭示了該還原作用的溫度敏感性，為釩污染的環境風險評估與精準生物整治提供了科學依據。</t>
+          <t>本文旨在探討性別差異在腸道微生物群與相關代謝物（GMRMs）中如何影響心臟代謝疾病（CMD）。研究指出，受性類固醇、免疫功能及環境因素影響，腸道菌相與代謝產物存在顯著的性別二態性。女性在生育期較男性具備更佳的心臟代謝特徵，但停經後風險顯著升高，此變化與特定菌屬（如 *Akkermansia muciniphila*）及代謝物（如短鏈脂肪酸、次級膽汁酸、TMAO）的豐度改變密切相關。這些微生物與代謝物透過調節發炎反應、醣脂代謝及血管功能，進而影響 CMD 的發生。本文強調未來需透過大型縱向研究，結合微生物組學、代謝組學與荷爾蒙監測，以深入解析其生物學機制，並開發針對不同性別的精準微生物介入療法，對於預防及管理心臟代謝疾病具有重要的科學價值。</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1930,37 +1930,37 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42648688/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647164/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>42648293</t>
+          <t>42647084</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Defined human Clostridia consortia reverse colitis via dual effects of tryptophan metabolites on microbiota and immunity.</t>
+          <t>Diet quality, gut microbiome, and inflammatory signatures in Puerto Rican adults with Crohn disease: a multidimensional analysis.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cell host &amp; microbe</t>
+          <t>Inflammatory bowel diseases</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>18.7</v>
+        <v>4.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>metagenomics, metabolomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>60位患有克隆氏症的成年人 (60 adults with CD)</t>
         </is>
       </c>
       <c r="G29" t="b">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Microbial dysbiosis and disrupted mucosal immune homeostasis are integrally involved in the pathogenesis of inflammatory bowel diseases (IBDs). Live biotherapeutic products (LBPs) offer a potential therapeutic strategy to restore beneficial microbes and mitigate disease. We investigated the therapeutic efficacy of 2 LBPs, human Clostridia consortia 17-mix and 11-mix, by treating established colitis in murine models. Both LBPs exhibited therapeutic effects in T cell-mediated chronic colitis models induced by human microbiota and in pathobiont-driven gnotobiotic colitis models established with combinations of IBD-relevant human-derived strains. Metagenomic and metabolomic analyses elucidated mechanisms that go beyond established functions driven by short-chain fatty acids (SCFAs) and interleukin (IL)-10-producing regulatory T cells. Notably, LBPs exerted therapeutic effects by directly inhibiting resident pathobionts and through IL-10-independent activation of host anti-inflammatory aryl hydrocarbon receptor (AhR) pathways by bacterial tryptophan metabolites. These results elucidate SCFA- and IL-10-independent protective mechanisms exerted by defined resident bacterial strains that are depleted in IBD dysbiosis.</t>
+          <t>Diet is increasingly recognized as a modifiable factor influencing gut microbiome and outcomes in Crohn disease (CD), yet data in underrepresented populations remain limited. We evaluated diet quality, dietary patterns, gut microbiome composition, inflammatory markers, and patient-reported outcomes in adults with CD from Puerto Rico. We conducted a cross-sectional analysis of 60 adults with CD enrolled prior to dietary intervention in a parent study. Dietary intake was assessed using 24-hour recalls and evaluated using the Healthy Eating Index-2015 (HEI-2015), Alternative Healthy Eating Index-2010 (AHEI-2010), and exploratory dietary pattern analysis. The gut microbiome was assessed by shotgun metagenomic sequencing. Clinical outcomes included fecal calprotectin, C-reactive protein (CRP), a 96-cytokine panel, short Crohn Disease Activity Index (sCDAI), and short Inflammatory Bowel Disease Questionnaire (sIBDQ). Associations were evaluated using unadjusted and adjusted models with false discovery rate (FDR) correction. Overall diet quality was poor and characterized by low intake of fruits, vegetables, whole grains, and fiber, alongside high intake of saturated fat, added sugars, and animal-derived protein. Four dietary patterns were identified: vegetable-rich, dairy-rich, fruit-rich, and coffee/sweetener-rich. Participants adhering to the fruit-rich pattern exhibited the highest diet quality scores. Higher HEI-2015 scores were associated with greater gut microbial diversity and differences in overall microbiome composition. Participants with greater adherence to the vegetable-rich pattern showed modest increases in microbial diversity. Exploratory analyses suggested that higher fruit intake and adherence to a fruit-rich dietary pattern were associated with lower fecal calprotectin and CRP levels, whereas adherence to a vegetable-rich pattern was associated with better health-related quality of life (HRQoL) and adherence to a coffee/sweetener-rich pattern was associated with a worse symptom burden. However, no associations between dietary metrics and inflammatory markers, cytokines, or clinical outcomes remained significant after FDR correction. Most participants were in clinical remission despite substantial impairment in HRQoL. Adults with CD in Puerto Rico exhibited poor diet quality that was associated with gut microbial diversity and exploratory differences in clinical outcomes. While these findings support the influence of diet on the microbiome and clinical outcomes, larger longitudinal studies are needed to determine whether dietary improvements can influence disease outcomes this underrepresented population.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>本研究探討了兩種由人類梭狀芽孢桿菌組成的活體生物藥物（LBP，分別為 17-mix 和 11-mix）治療小鼠結腸炎的療效與機制。研究發現，這些菌群能有效緩解小鼠的慢性與特定病原體誘導的結腸炎。宏基因組學與代謝組學分析顯示，除了傳統的短鏈脂肪酸（SCFA）和 IL-10 途徑外，LBP 還能直接抑制共生病原菌，並透過細菌色胺酸代謝物，以不依賴 IL-10 的方式激活宿主的芳香烴受體（AhR）抗炎途徑。此發現揭示了腸道有益菌保護腸道的新機制，為發炎性腸道疾病（IBD）的微生態療法提供了重要科學依據。</t>
+          <t>本研究探討波多黎各克隆氏症（CD）成年患者的飲食品質、腸道菌相與發炎指標的關係。研究發現，受試者普遍飲食品質不佳，而較高的飲食品質（特別是富含水果的飲食模式）與較高的腸道菌群多樣性顯著相關。探索性分析顯示，多攝取水果與較低的發炎指標（鈣衛蛋白和C反應蛋白）相關，而蔬菜為主的飲食與較佳的生活品質相關（但經FDR校正後未達顯著）。本研究首次揭示了該少數受關注族群中飲食對菌相與臨床症狀的影響，為未來透過飲食干預管理CD及改善患者預後提供了科學依據。</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1983,37 +1983,35 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42648293/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647084/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>42648218</t>
+          <t>42644751</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Agricultural sprinkler irrigation systems as environmental reservoirs and airborne dissemination sources of Legionella pneumophila.</t>
+          <t>Soil amelioration impacts viral ecology in saline-alkali lands.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Journal of environmental management</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>8.4</v>
-      </c>
+          <t>The ISME journal</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>metagenomics, small genome</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>未明確提及具體檢體數量（僅指出於西班牙東北部農村的兩個區域，針對灌溉池塘與溝渠進行採樣）</t>
+          <t>未提及（僅說明樣品來自中國4個主要鹽鹼地區，各包含「鹽鹼」與「改良後」兩種狀態之土壤）</t>
         </is>
       </c>
       <c r="G30" t="b">
@@ -2021,12 +2019,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sprinkler irrigation systems are critical for modern agriculture but represent largely unrecognized aquatic environments capable of sustaining opportunistic human pathogens. Among them, Legionella pneumophila is of particular concern due to its ability to colonize engineered water systems, persist under fluctuating environmental conditions, and be transmitted through aerosols. In this study, we conducted a comprehensive microbiological and genomic investigation of irrigation ponds and ditches in a rural area of north-east Spain where two zones were sampled. Metagenomic profiling revealed highly diverse microbial communities encompassing more than 20,000 species, including 21 airborne-transmissible bacterial pathogens of clinical relevance. Notably, L. pneumophila was detected in both zones, with a relative abundance of up to 4.6 %. Culture-based isolation confirmed the presence of L. pneumophila serogroup 1, Pontiac group, Benidorm subgroup, sequence type 15. Phylogenetic analysis demonstrated a close relationship between this environmental strain and clinical isolates obtained during a Legionnaires' disease outbreak occurred in 2015, which had remained without a confirmed environmental source. Meteorological data from the exposure period revealed wind conditions favouring long-distance aerosol dispersion from irrigated fields toward residential areas. Our findings provide evidence that irrigation infrastructures can act as environmental reservoirs and dissemination routes of L. pneumophila among other airborne pathogens. These results underscore the need to incorporate agricultural irrigation systems into routine environmental surveillance, outbreak investigations, and public health risk assessments.</t>
+          <t>The continuous expansion of saline-alkali lands under climate change threatens food security and reduces soil carbon stocks. A common mitigation strategy is soil amelioration, which converts degraded soils back into an arable state. Microbes play critical roles in soil health and recovery. However, the viruses that infect these microbial communities, and their potential impacts during saline-alkali soil restoration, remain largely unknown. Here, we combined total soil metagenomics and viromics to investigate host-linked viral ecology across four major saline-alkali regions in China, each encompassing two soil amelioration statuses: saline-alkali and reclaimed. We found that viral community structure was shaped by both geography and soil amelioration status, with salinity and alkalinity emerging as key environmental factors. Viral populations were sensitive to soil restoration, showing strong amelioration-status endemism with functional adaptations. Virus-host dynamics ranged from reduced temperate viruses to abundance mismatches in those infecting key carbon-cycling microorganisms, including carbohydrate degraders. 13C-cellulose DNA-SIP experiments provided further support for this mismatch by tracing assimilated carbon transfer between active host and virus populations. Compared with saline-alkali soils, the relative abundance of hosts in restored soils increased from 39.0% to 61.0%, whereas the linked viruses decreased from 60.6% to 39.4%. Together, these findings reveal an underappreciated role of viruses in shaping saline-alkali soil amelioration trajectories, and could improve management strategies for degraded land recovery and carbon storage.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>本研究旨在探討農業噴灌系統是否為嗜肺軍團菌（*Legionella pneumophila*）等致病菌的環境宿主與空氣傳播源。團隊對西班牙農村灌溉水體進行分析，總體基因體學顯示其含有逾2萬種微生物，包括21種臨床相關的空氣傳播病原體，且嗜肺軍團菌相對豐度達4.6%。研究成功分離出嗜肺軍團菌血清型1（ST15），系統發育分析證實該環境株與2015年退伍軍人症爆發的臨床分離株高度相關。氣象數據亦支持風向有利於氣膠從農田長距離擴散至住宅區。此發現證實農業灌溉系統為軍團菌的傳播媒介，強調應將其納入例行環境監測與公衛風險評估。</t>
+          <t>本研究旨在探討鹽鹼地改良過程中，病毒對土壤微生物生態與碳循環的影響。研究結合總體基因體與病毒體學，分析中國四大鹽鹼區。結果顯示，土壤改良狀態、鹽度與鹼度是塑造病毒社群的關鍵。在改良土壤中，宿主微生物相對豐度顯著上升（39.0%至61.0%），而關聯病毒減少（60.6%至39.4%），且溫和病毒比例降低，碳循環關鍵微生物的病毒與宿主出現豐度失衡。13C-纖維素DNA-SIP實驗證實了兩者間的活性碳轉移。此發現揭示了病毒在鹽鹼地恢復中的關鍵作用，有助優化土地改良與碳儲存策略。</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2036,35 +2034,37 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42648218/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42644751/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>42644751</t>
+          <t>42648293</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Soil amelioration impacts viral ecology in saline-alkali lands.</t>
+          <t>Defined human Clostridia consortia reverse colitis via dual effects of tryptophan metabolites on microbiota and immunity.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>The ISME journal</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>Cell host &amp; microbe</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>18.7</v>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>未提及（僅說明樣品來自中國4個主要鹽鹼地區，各包含「鹽鹼」與「改良後」兩種狀態之土壤）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G31" t="b">
@@ -2072,12 +2072,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>The continuous expansion of saline-alkali lands under climate change threatens food security and reduces soil carbon stocks. A common mitigation strategy is soil amelioration, which converts degraded soils back into an arable state. Microbes play critical roles in soil health and recovery. However, the viruses that infect these microbial communities, and their potential impacts during saline-alkali soil restoration, remain largely unknown. Here, we combined total soil metagenomics and viromics to investigate host-linked viral ecology across four major saline-alkali regions in China, each encompassing two soil amelioration statuses: saline-alkali and reclaimed. We found that viral community structure was shaped by both geography and soil amelioration status, with salinity and alkalinity emerging as key environmental factors. Viral populations were sensitive to soil restoration, showing strong amelioration-status endemism with functional adaptations. Virus-host dynamics ranged from reduced temperate viruses to abundance mismatches in those infecting key carbon-cycling microorganisms, including carbohydrate degraders. 13C-cellulose DNA-SIP experiments provided further support for this mismatch by tracing assimilated carbon transfer between active host and virus populations. Compared with saline-alkali soils, the relative abundance of hosts in restored soils increased from 39.0% to 61.0%, whereas the linked viruses decreased from 60.6% to 39.4%. Together, these findings reveal an underappreciated role of viruses in shaping saline-alkali soil amelioration trajectories, and could improve management strategies for degraded land recovery and carbon storage.</t>
+          <t>Microbial dysbiosis and disrupted mucosal immune homeostasis are integrally involved in the pathogenesis of inflammatory bowel diseases (IBDs). Live biotherapeutic products (LBPs) offer a potential therapeutic strategy to restore beneficial microbes and mitigate disease. We investigated the therapeutic efficacy of 2 LBPs, human Clostridia consortia 17-mix and 11-mix, by treating established colitis in murine models. Both LBPs exhibited therapeutic effects in T cell-mediated chronic colitis models induced by human microbiota and in pathobiont-driven gnotobiotic colitis models established with combinations of IBD-relevant human-derived strains. Metagenomic and metabolomic analyses elucidated mechanisms that go beyond established functions driven by short-chain fatty acids (SCFAs) and interleukin (IL)-10-producing regulatory T cells. Notably, LBPs exerted therapeutic effects by directly inhibiting resident pathobionts and through IL-10-independent activation of host anti-inflammatory aryl hydrocarbon receptor (AhR) pathways by bacterial tryptophan metabolites. These results elucidate SCFA- and IL-10-independent protective mechanisms exerted by defined resident bacterial strains that are depleted in IBD dysbiosis.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>本研究旨在探討鹽鹼地改良過程中，病毒對土壤微生物生態與碳循環的影響。研究結合總體基因體與病毒體學，分析中國四大鹽鹼區。結果顯示，土壤改良狀態、鹽度與鹼度是塑造病毒社群的關鍵。在改良土壤中，宿主微生物相對豐度顯著上升（39.0%至61.0%），而關聯病毒減少（60.6%至39.4%），且溫和病毒比例降低，碳循環關鍵微生物的病毒與宿主出現豐度失衡。13C-纖維素DNA-SIP實驗證實了兩者間的活性碳轉移。此發現揭示了病毒在鹽鹼地恢復中的關鍵作用，有助優化土地改良與碳儲存策略。</t>
+          <t>本研究探討了兩種由人類梭狀芽孢桿菌組成的活體生物藥物（LBP，分別為 17-mix 和 11-mix）治療小鼠結腸炎的療效與機制。研究發現，這些菌群能有效緩解小鼠的慢性與特定病原體誘導的結腸炎。宏基因組學與代謝組學分析顯示，除了傳統的短鏈脂肪酸（SCFA）和 IL-10 途徑外，LBP 還能直接抑制共生病原菌，並透過細菌色胺酸代謝物，以不依賴 IL-10 的方式激活宿主的芳香烴受體（AhR）抗炎途徑。此發現揭示了腸道有益菌保護腸道的新機制，為發炎性腸道疾病（IBD）的微生態療法提供了重要科學依據。</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2087,37 +2087,37 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42644751/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648293/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>42647084</t>
+          <t>42647600</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Diet quality, gut microbiome, and inflammatory signatures in Puerto Rican adults with Crohn disease: a multidimensional analysis.</t>
+          <t>Urogenital immune signatures are associated with birth outcomes after maternal urinary tract infection.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Inflammatory bowel diseases</t>
+          <t>Science translational medicine</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4.3</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>60位患有克隆氏症的成年人 (60 adults with CD)</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G32" t="b">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Diet is increasingly recognized as a modifiable factor influencing gut microbiome and outcomes in Crohn disease (CD), yet data in underrepresented populations remain limited. We evaluated diet quality, dietary patterns, gut microbiome composition, inflammatory markers, and patient-reported outcomes in adults with CD from Puerto Rico. We conducted a cross-sectional analysis of 60 adults with CD enrolled prior to dietary intervention in a parent study. Dietary intake was assessed using 24-hour recalls and evaluated using the Healthy Eating Index-2015 (HEI-2015), Alternative Healthy Eating Index-2010 (AHEI-2010), and exploratory dietary pattern analysis. The gut microbiome was assessed by shotgun metagenomic sequencing. Clinical outcomes included fecal calprotectin, C-reactive protein (CRP), a 96-cytokine panel, short Crohn Disease Activity Index (sCDAI), and short Inflammatory Bowel Disease Questionnaire (sIBDQ). Associations were evaluated using unadjusted and adjusted models with false discovery rate (FDR) correction. Overall diet quality was poor and characterized by low intake of fruits, vegetables, whole grains, and fiber, alongside high intake of saturated fat, added sugars, and animal-derived protein. Four dietary patterns were identified: vegetable-rich, dairy-rich, fruit-rich, and coffee/sweetener-rich. Participants adhering to the fruit-rich pattern exhibited the highest diet quality scores. Higher HEI-2015 scores were associated with greater gut microbial diversity and differences in overall microbiome composition. Participants with greater adherence to the vegetable-rich pattern showed modest increases in microbial diversity. Exploratory analyses suggested that higher fruit intake and adherence to a fruit-rich dietary pattern were associated with lower fecal calprotectin and CRP levels, whereas adherence to a vegetable-rich pattern was associated with better health-related quality of life (HRQoL) and adherence to a coffee/sweetener-rich pattern was associated with a worse symptom burden. However, no associations between dietary metrics and inflammatory markers, cytokines, or clinical outcomes remained significant after FDR correction. Most participants were in clinical remission despite substantial impairment in HRQoL. Adults with CD in Puerto Rico exhibited poor diet quality that was associated with gut microbial diversity and exploratory differences in clinical outcomes. While these findings support the influence of diet on the microbiome and clinical outcomes, larger longitudinal studies are needed to determine whether dietary improvements can influence disease outcomes this underrepresented population.</t>
+          <t>Preterm birth is the leading cause of infant mortality, resulting in more than 1 million neonatal deaths globally each year. Maternal urinary tract infection (UTI) during pregnancy increases risk for preterm birth; however, biological processes mediating UTI-associated preterm birth are not well described. We established a murine maternal UTI model in which challenge with uropathogenic Escherichia coli (UPEC) initiated preterm labor and birth in about half of dams. Although bacterial burdens were similar, dams experiencing preterm birth displayed excessive bladder inflammation, elevated placental and decidual cytokines, higher proportions of male fetuses, and lower maternal serum interleukin-10 (IL-10) compared with nonlaboring dams. Exogenous IL-10 or lymph node sequestration of T cells reduced placental type 17 T helper cells (TH17 cells) and abrogated preterm birth. In a human pregnancy cohort, we correlated urinary cytokines with birth outcomes and urine culture status. These analyses yielded an exploratory, noninvasive culture-agnostic system for evaluating preterm birth risk, implicating T cell-related cytokines including IL-10, IL-15, GM-CSF, and RANTES. These findings demonstrate that our murine model provides a platform to investigate immunological and microbial factors governing UTI-associated preterm birth and, coupled with patient samples, may be used to identify candidate biomarkers and mechanistic targets for future investigation.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>本研究探討波多黎各克隆氏症（CD）成年患者的飲食品質、腸道菌相與發炎指標的關係。研究發現，受試者普遍飲食品質不佳，而較高的飲食品質（特別是富含水果的飲食模式）與較高的腸道菌群多樣性顯著相關。探索性分析顯示，多攝取水果與較低的發炎指標（鈣衛蛋白和C反應蛋白）相關，而蔬菜為主的飲食與較佳的生活品質相關（但經FDR校正後未達顯著）。本研究首次揭示了該少數受關注族群中飲食對菌相與臨床症狀的影響，為未來透過飲食干預管理CD及改善患者預後提供了科學依據。</t>
+          <t>本研究旨在探討孕婦尿路感染（UTI）導致早產的免疫機制。研究團隊建立尿路致病性大腸桿菌（UPEC）感染的孕鼠模型，發現發生早產的母鼠伴隨更嚴重的膀胱發炎、胎盤細胞激素升高及血清IL-10降低；給予外源性IL-10或抑制T細胞，能減少胎盤TH17細胞並預防早產。此外，人類佇列研究證實，尿液中T細胞相關細胞激素（如IL-10、IL-15等）與早產風險密切相關。本研究結合動物模型與臨床樣本，揭示了UTI引發早產的免疫關鍵，並為未來篩檢及治療提供了潛在的非侵入性生物標誌物與機制標靶。</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2140,37 +2140,37 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42647084/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647600/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>42647164</t>
+          <t>42648688</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sex differences in the gut microbiome and related metabolites: role in cardiometabolic disease.</t>
+          <t>Temperature Sensitivity of Pyrrhotite-Driven Metavanadate Bioreduction in Groundwater.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>Environmental research</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11</v>
+        <v>7.7</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>未提及（本文為綜論性回顧文章，非原創實驗研究）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G33" t="b">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sex differences in major cardiometabolic diseases (CMD), such as type 2 diabetes, metabolic dysfunction-associated steatotic liver disease, and cardiovascular disease, have been increasingly recognized across the life course. During the reproductive stage, women generally have a more favorable cardiometabolic risk profile than men, but their risk of experiencing CMD significantly increases after menopause. Emerging evidence suggests that sexually dimorphic gut microbiota and gut microbiota-related metabolites (GMRMs) may contribute to such sex disparities. However, existing findings are heterogeneous and underlying mechanisms remain incompletely understood. In this review, we synthesize the evidence examining sex differences in gut microbial diversity, overall composition, taxa abundances, and levels of GMRMs across key life stages, including pre-puberty, adolescence, and different phases of adulthood (with emphasis on pre- and post-menopausal periods). We summarize potential biological mechanisms underlying sexual dimorphism in the gut microbiome and GMRMs, emphasizing the central role of sex steroids, along with contributions from immune function and other host and environmental factors. We further integrate evidence linking sexually dimorphic microbial taxa (e.g., Akkermansia muciniphila, Eubacterium, Ruminococcus, and other Firmicutes taxa) and GMRMs (e.g., microbiota-derived short-chain fatty acids, secondary bile acids, and trimethylamine N-oxide) to key cardiometabolic pathways involving inflammation, glucose and lipid metabolism, and vascular function. Finally, we identify critical knowledge gaps and emphasize the need for future large longitudinal studies that would integrate repeated measurements of the gut microbiome, untargeted metabolomics, and sex steroid hormones across the life course. Such approaches are essential to clarify biological pathways and inform sex-specific microbiome-based interventions for CMD prevention and management.</t>
+          <t>Pyrrhotite-driven metavanadate [V(V)] bioreduction is a promising green strategy for the remediation of vanadium-contaminated aquifers. However, how this microbially driven process responds to different temperatures remains unclear. Herein, the responses of pyrrhotite-driven V(V) bioreduction to different temperatures ranging from 4 to 45 °C were investigated. V(V) removal first increased and then decreased with increasing temperature, peaking at 35 °C, with the reaction rate constant reaching 0.077 d-1. V(V) could be reduced to VO2 precipitates, accompanied by oxidation of S(-II) and Fe(II) to sulfate and Fe(III), respectively. Metagenomic binning revealed that S(-II) oxidation was more sensitive to temperature changes than Fe(II) oxidation for V(V) reducers. Bacteria coupling V(V) reduction with both S(-II) and Fe(II) oxidation (e.g., Ramlibacter sp.) were detected exclusively at 35 °C. The transcription of functional genes (related to V(V) reduction, S(-II) oxidation, and Fe(II) oxidation), electron transport activity and related components all exhibited a temperature-dependent pattern, first increasing and then decreasing, with a peak at 35 °C. This study reveals the temperature sensitivity of pyrrhotite-driven V(V) bioreduction, which is helpful for risk assessment and targeted bioremediation of vanadium contamination under different temperature conditions.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>本文旨在探討性別差異在腸道微生物群與相關代謝物（GMRMs）中如何影響心臟代謝疾病（CMD）。研究指出，受性類固醇、免疫功能及環境因素影響，腸道菌相與代謝產物存在顯著的性別二態性。女性在生育期較男性具備更佳的心臟代謝特徵，但停經後風險顯著升高，此變化與特定菌屬（如 *Akkermansia muciniphila*）及代謝物（如短鏈脂肪酸、次級膽汁酸、TMAO）的豐度改變密切相關。這些微生物與代謝物透過調節發炎反應、醣脂代謝及血管功能，進而影響 CMD 的發生。本文強調未來需透過大型縱向研究，結合微生物組學、代謝組學與荷爾蒙監測，以深入解析其生物學機制，並開發針對不同性別的精準微生物介入療法，對於預防及管理心臟代謝疾病具有重要的科學價值。</t>
+          <t>本研究旨在探討不同溫度（4至45 °C）對地下水中磁黃鐵礦驅動的偏釩酸鹽 [V(V)] 生物還原過程之影響。研究發現，V(V) 去除率隨溫度升高呈先升後降趨勢，並在 35 °C 時達到峰值（反應速率常數 0.077 d⁻¹），此時 V(V) 被還原為 VO₂ 沉澱，並伴隨硫與鐵的氧化。總體基因體 binning 分析顯示，還原菌的硫氧化過程對溫度變化比鐵氧化更為敏感，且僅在 35 °C 下偵測到能同時耦合硫與鐵氧化的關鍵細菌（如 *Ramlibacter* sp.）。此外，相關功能基因轉錄與電子傳遞活性亦在 35 °C 達到頂峰。本研究揭示了該還原作用的溫度敏感性，為釩污染的環境風險評估與精準生物整治提供了科學依據。</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2193,35 +2193,35 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42647164/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648688/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>42647759</t>
+          <t>42644746</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Gut Microbiome in Multiple Sclerosis.</t>
+          <t>Metabolic division of labour drives estuarine-coastal N2O emissions.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Neurology(R) neuroimmunology &amp; neuroinflammation</t>
+          <t>The ISME journal</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics, metatranscriptomics</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>974 個重建的 N2O 相關基因體（原文未提及具體的環境樣本採集數量）</t>
         </is>
       </c>
       <c r="G34" t="b">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Multiple sclerosis (MS) is a chronic inflammatory demyelinating disease of the CNS whose risk and course are shaped by both genetic and environmental factors, among which the intestinal microbiota has emerged as a key, potentially modifiable contributor. People with MS frequently display altered gut microbiota, characterized by depletion of fiber-fermenting, short-chain fatty acid (SCFA)-producing commensals, and expansion of taxa associated with mucus degradation and proinflammatory metabolism. These compositional shifts are paralleled by broad changes in blood and CSF metabolites, including reduced SCFAs, tryptophan-derived aryl hydrocarbon receptor ligands, and secondary bile acids. In addition, several reports highlight the accumulation of aromatic amino acid-derived phenolic and indolic compounds and specific lipid mediators linked to neuroinflammation and neurodegeneration. In this up-to-date review, we synthesize evidence from experimental models and human studies showing how microbial metabolites can influence MS pathogenesis through converging mechanisms: modulation of gut and blood-brain barrier integrity; shaping of T-cell and B-cell responses; direct effects on microglia, astrocytes, and oligodendrocyte lineage cells after crossing into the CNS; and modulation of neural circuits, particularly those involving the vagus nerve. Finally, we highlight current gaps, including the need for longitudinal, harmonized multiomic cohorts, and mechanistic studies integrating microbiome, metabolome, and host readouts across gut, blood, and CNS. Overall, available data support a model in which coordinated disruption of the gut microbiota-metabolite axis, rather than any single pathogen, contributes to MS, opening avenues for microbiota-based and metabolite-based biomarkers and therapies aimed at restoring immune and neuroglial homeostasis.</t>
+          <t>Estuarine and coastal systems are global hotspots of marine nitrous oxide (N2O) emissions, where microbial nitrification and denitrification are the primary processes regulating N2O dynamics. However, how interactions among different N2O-associated microorganisms influence ecosystem-scale N2O emissions remains poorly understood. This study combined in situ N2O concentrations, 15N-based potential rates, metagenomics, metatranscriptomics, and genome-scale metabolic model analysis to explore N2O production and reduction processes in estuarine and coastal systems. Potential N2O production and reduction rates, together with in situ concentrations, the relative abundance, and the transcriptional activity of associated genes, were significantly higher at low salinity and declined toward coastal regions. Based on the gene content of 974 recovered N2O-associated genomes, microorganisms were classified into three functional groups: net N2O producers, net N2O consumers, and self-sustaining N2O players. The abundance, composition, and activity of these functional groups shifted along estuarine-coastal gradients. A larger NO/N2O exchange gap, reflecting the imbalance between model-inferred NO and N2O handoff potentials, was found at low salinity and was associated with elevated bottom-water N2O concentrations. Together, community-level division of labour and the associated exchange gap provide a conceptual framework for linking N2O-related functional groups to N2O accumulation in estuarine-coastal ecosystems.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>本研究探討多發性硬化症（MS）與腸道微生物群之間的關聯。研究指出，MS 患者的腸道菌相呈現失調狀態，包括短鏈脂肪酸（SCFA）產生菌減少，以及促發炎代謝菌的增加。這些微生物群落的變化伴隨著血液與腦脊髓液中代謝物（如色胺酸衍生物、膽汁酸及 SCFA）的顯著改變，這些物質經證實與神經發炎及退化密切相關。文中綜述了微生物代謝產物如何透過調節腸道與血腦屏障完整性、影響免疫細胞（T/B 細胞）反應，以及直接作用於神經膠質細胞來參與 MS 的致病機制。總結而言，MS 的發生與腸道菌群-代謝物軸的整體失調有關，而非單一病原體所致。該研究強調未來需進行多體學（multiomics）整合分析，以開發基於微生物群的生物標記與創新治療策略，旨在恢復患者的免疫與神經恆定。</t>
+          <t>本研究旨在探討河口與沿海系統中，微生物交互作用如何驅動一氧化二氮（N2O）的排放。研究結合現場觀測、15N同位素速率、總體基因體與轉錄體學，重建了974個N2O相關基因體。結果指出，低鹽度區域的N2O產生與還原速率及基因表達顯著較高。研究將微生物劃分為淨產生者、淨消費者與自給自足者，並發現低鹽度區因群落間物質交換失衡，存在較大的NO/N2O交換缺口，進而導致底層水體N2O顯著累積。本研究建立了群落水平的「分工與交換缺口」理論框架，為預測及理解海洋生態系統N2O排放提供了關鍵的科學依據。</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2244,35 +2244,37 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42647759/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42644746/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>42648171</t>
+          <t>42649294</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Co-occurrence of muddy off flavor and cyanotoxin genes in the polluted Guandu river waters (Rio de Janeiro, Brazil).</t>
+          <t>Synergistic degradation of fucoidans in the ocean.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>The Science of the total environment</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>48.5</v>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>metabolomics, metagenomics</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（該研究採用重組海洋微生物群落進行實驗，未提供具體的生物樣本人數或檢體數量）</t>
         </is>
       </c>
       <c r="G35" t="b">
@@ -2280,12 +2282,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>The Guandu river basin is responsible for supplying Rio de Janeiro municipality, Brazil, with drinking water. This study investigated water quality during the geosmin crisis in January and March 2020, by relating the water quality and odor compounds with metagenomic tools. Guandu river water was eutrophic. The cyanobacterial genera identified were Microcystis, Planktothrix, Dolichospermum, Nostoc, Synechococcus, Planktothricoides, and Cyanobium, indicating that bloom-associated communities in the system are taxonomically diverse. Functional annotation of metagenomic sequences revealed the presence of genes associated with the biosynthesis of taste-and-odor compounds, including geosmin (geoA) and 2-methylisoborneol (mic), as well as multiple biosynthetic clusters related to cyanotoxin production. Genes linked to microcystin (mcy), saxitoxin (sxt), anatoxin (ana), cylindrospermopsin (cyr), lyngbyatoxin (ltx), guanitoxin (gnt), and nodularin (nda) were detected across the dataset, indicating a broad genetic potential for the production of secondary metabolites relevant to water quality. The co-occurrence of cyanotoxins, geosmin and 2-MIB genes suggests that off-flavor is an indication of cyanotoxin potential production in the water.</t>
+          <t>Fucoidans, a class of complex polysaccharides produced by brown algae and diatoms, contribute to long-term carbon sequestration owing to their resistance to microbial degradation1,2. Although individual microorganisms can break down portions of these polysaccharides3-5, it remains unclear whether complete breakdown is possible in nature and, if so, by what mechanisms. Here we show that fucoidans are degraded through synergistic interactions between specialized bacteria with complementary metabolic functions. Using metabolomic analysis of a reconstructed marine consortium, we uncovered metabolic guilds of bacteria that preferentially degrade either the sulfated fucose backbone or the side branches of rare monomers. This functional division of labour leads to an unexpectedly high number of synergistic interactions between different degraders that enhanced degradation efficiency up to 97.1%. Despite varying fucoidan structures across different types of algae6, the metabolic functions of degraders remained conserved, enabling quantitative prediction of degradation outcomes based on community and substrate composition. The frequent co-occurrence of functionally complementary fucoidan degraders in ocean metagenomes suggests that synergistic degradation is a globally relevant strategy. Our findings suggest that the environmental turnover of complex biopolymers depends not only on individual metabolic capabilities of degraders but also on ecological interactions shaped by substrate architecture. This work provides a mechanistic framework for understanding carbon cycling in the ocean and for engineering synthetic microbial consortia to degrade recalcitrant polysaccharides.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>本研究旨在探究巴西里約熱內盧瓜杜河於2020年初爆發土臭素危機期間的水質狀況，並利用總體基因體學技術探討水質異味與微生物群落之關聯。研究發現，該富營養化水體中含有多種藍菌，且功能性註釋顯示其富含合成土臭素（*geoA*）與2-甲基異莰醇（*mic*）等異味物質的基因。更重要的是，多種藍菌毒素（如微囊藻毒素、石房蛤毒素等）的合成基因群與這些異味基因呈現共存。此發現證實了水體異味的出現與藍菌毒素的潛在生成具有高度相關性，可作為飲用水安全監測及評估藍菌毒素潛在危害的重要預警指標。</t>
+          <t>本研究探討海洋中複雜多醣體「褐藻醣膠」（fucoidans）的微生物降解機制。儘管褐藻醣膠因其抗降解性在碳封存中扮演關鍵角色，但過往對於其在自然界中是否能被完全分解並不清楚。研究發現，褐藻醣膠的降解並非單一物種所能完成，而是透過具有互補代謝功能的細菌群落進行「協同作用」。透過代謝體學分析，研究團隊識別出專門降解硫酸岩藻糖骨架與稀有單醣側鏈的代謝群組（metabolic guilds），這種分工合作能將降解效率大幅提升至 97.1%。此外，研究顯示此代謝功能在不同環境下具有高度保守性，且在海洋宏基因組中普遍存在。本研究揭示了生物聚合物的環境周轉率取決於微生物間的生態交互作用，為理解海洋碳循環機制提供了重要框架，並為未來利用人工合成微生物群落降解頑固性多醣體提供了技術基礎。</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2295,29 +2297,27 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42648171/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42649294/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>42644416</t>
+          <t>42657129</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nationwide cohort study reveals low bifidobacteria and distinct microbiota composition and function in Swedish newborns.</t>
+          <t>Pulmonary Infiltrates, Airway Mucosal Lesions and Respiratory Microbiology After Freshwater Drowning: A Case Report.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>11</v>
-      </c>
+          <t>Respirology case reports</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>metagenomics</t>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>308 名瑞典新生兒的糞便檢體</t>
+          <t>1 例病患（n=1）</t>
         </is>
       </c>
       <c r="G36" t="b">
@@ -2333,12 +2333,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>NCT06285630.</t>
+          <t>Early pulmonary abnormalities after freshwater drowning can be overinterpreted as bacterial pneumonia, especially when inflammatory biomarkers and respiratory microbiology are positive. A 20-year-old man was resuscitated after approximately 2 min of freshwater submersion. Day 1 chest CT showed bilateral lower-lobe-predominant opacities compatible with non-cardiogenic pulmonary oedema and aspiration-related lung injury, with near-complete resolution by Day 25. Day 3 bronchoscopy showed diffuse, non-removable, millet-seed-like whitish tracheal mucosal protrusions with hyperaemia and oedema, compatible with acute irritative airway injury. BALF mNGS detected multiple gram-negative bacterial signals, predominantly Klebsiella pneumoniae, while sputum culture yielded ESBL-negative, susceptible K. pneumoniae. Possible drowning-associated pneumonia was considered because of aspiration, fever, markedly elevated inflammatory biomarkers and concordant microbiology; however, rapid radiological improvement and clinical stability suggested a substantial non-infectious component. The patient recovered after an 8-day course of piperacillin-tazobactam without antibiotic escalation, corticosteroids, mechanical ventilation or acute respiratory distress syndrome.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>本研究旨在探討瑞典新生兒的腸道菌相組成與功能特徵。透過總體基因體學分析，研究發現瑞典新生兒腸道中的雙歧桿菌（特別是嬰兒雙歧桿菌）豐度顯著偏低，並呈現出獨特的菌相結構與代謝功能。此現象與現代化生活型態及分娩方式密切相關。這項全國性世代研究揭示了現代環境對嬰兒早期腸道微生態建立的深遠影響，為未來的臨床嬰幼兒益生菌介入與健康照護策略提供了關鍵的科學依據。</t>
+          <t>本研究透過單一病例報告，探討淡水溺水後肺部浸潤與呼吸道損傷的臨床鑑別診斷。一名 20 歲男性溺水後出現肺水腫與氣道黏膜病變，臨床表現極易與細菌性肺炎混淆。研究利用 mNGS（宏基因組次世代定序）檢測支氣管肺泡灌洗液，雖確認存在肺炎克雷伯菌（*Klebsiella pneumoniae*）訊號，但影像學與臨床病程顯示其肺部損傷主要源於吸入性損傷及急性化學性氣道刺激，而非嚴重的細菌感染。此案例凸顯了臨床判斷溺水相關肺炎時的挑戰，強調在面對看似感染的臨床數據時，應綜合考量影像改善速度與臨床穩定性，避免過度診斷與不必要的抗生素升級，對急性溺水病患的精準治療具有重要的臨床參考價值。</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2348,28 +2348,28 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42644416/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42657129/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>42641146</t>
+          <t>42642836</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Engineered bacterial therapeutics from synthetic biology to clinical translation: A multi-database scientometric analysis, 2000-2026.</t>
+          <t>Microbiome-mediated regulation of pathogen virulence: Molecular mechanisms and clinical implications.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Human vaccines &amp; immunotherapeutics</t>
+          <t>Virulence</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1,730 篇學術文章與評論</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G37" t="b">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Engineered bacterial therapeutics integrate programmable strain engineering with biomedical functions such as sensing, delivery, immune modulation, microbiome intervention, and disease management. This study conducted a multi-database bibliometric analysis to map the knowledge structure, collaboration patterns, and translational direction of this field. Bibliographic records were retrieved from Web of Science Core Collection, Scopus, and PubMed for publications from 1 January 2000 to 1 June 2026. After document-type filtering, time restriction, deduplication, language screening, and manual eligibility assessment, 1,730 English-language articles and reviews were included. CiteSpace 6.4.R1, VOSviewer 1.6.20, and the bibliometrix R package were used to analyze publication trends, collaboration networks, journal co-citation, dual-map citation trajectories, citation bursts, keyword co-occurrence, and thematic evolution. Publication output increased steadily, with faster growth after 2020; 2025 was the highest-output complete year, while 2026 represented a partial retrieval year. China and the United States were the leading contributors, although institutional collaboration remained regionally clustered. Co-citation, citation-burst, and keyword analyses showed a shift from bacterial chassis construction and circuit design toward engineered probiotics, gut microbiota-related therapy, cancer immunotherapy, drug delivery, live biotherapeutic products, and clinical translation. Persistent translational priorities include controllability, safety, manufacturing consistency, and regulatory alignment.</t>
+          <t>The human microbiome profoundly influences pathogen virulence and disease susceptibility through diverse molecular mechanisms. This review, focused on literature from 2016 to 2026, synthesizes knowledge on microbiome-mediated regulation examining major pathogens including Vibrio cholerae, enterohemorrhagic Escherichia coli, Salmonella species, Clostridioides difficile, and Staphylococcus aureus. A triangular interaction model is presented, linking host immunity, resident microbiome, and invading pathogen to frame infection outcomes. Commensal bacteria regulate pathogen behavior through quorum sensing interference, metabolite-mediated regulation via short-chain fatty acids and bile acids, competitive exclusion, immune response modulation, and direct antimicrobial production. Key species-Lactobacillus spp. Bifidobacterium spp. Bacteroides thetaiotaomicron, and Faecalibacterium prausnitzii-employ distinct molecular strategies against these pathogens. Organ-on-chip platforms and multi-omics advances reveal context-dependent interactions. Clinical applications including rationally designed probiotics, fecal microbiota transplantation, and precision microbiome engineering show promise despite challenges of inter-individual microbiome variability, representing a paradigm shift toward ecosystem-based infectious disease management.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>本研究透過文獻計量學方法，系統性分析 2000 年至 2026 年間有關「工程化細菌治療」的 1,730 篇學術文獻。研究旨在釐清該領域的知識結構、國際合作模式及臨床轉化趨勢。分析顯示，該領域自 2020 年後顯著加速發展，中國與美國為主要貢獻國。核心研究主軸已由早期的細菌底盤構建與基因電路設計，轉向工程化益生菌、癌症免疫治療、藥物遞送及活體生物藥物（LBP）的開發。科學意義在於確立了該領域從實驗室轉向臨床應用的優先議題，即解決控制力、生物安全性、生產一致性與法規調適等挑戰，為未來工程化細菌作為精準醫療工具的發展提供關鍵決策參考。</t>
+          <t>本研究綜述了2016年至2026年間關於腸道微生物群調控病原體毒力（如霍亂弧菌、大腸桿菌、沙門氏菌等）的分子機制。作者提出了一個結合宿主免疫、共生菌群與入侵病原體的「三角交互模型」，闡述了共生菌如何透過群體感應干擾、代謝產物（如短鏈脂肪酸、膽汁酸）調節、競爭性排斥及免疫調節來抑制病原體。研究強調了乳酸桿菌、雙歧桿菌及普拉梭菌等關鍵菌種的保護機制，並探討了器官晶片與多體學技術在揭示交互作用上的貢獻。此研究主張從生態系統角度管理傳染病，指出益生菌設計、糞便菌群移植及精準微生物組工程是未來治療的關鍵方向，雖面臨個體差異挑戰，但為臨床感染控制提供了典範轉移。</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2401,32 +2401,32 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42641146/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42642836/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>42642834</t>
+          <t>42648179</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Glycosylation in gut-brain communication: from the intestinal barrier and microbiota to immune and neural signaling.</t>
+          <t>Simultaneous removal of nitrogen, Cu2+, and bisphenol A in a hydrogel-biochar-AQDS immobilized bioreactor with added bicarbonate: Performance and metagenomic insights.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>Journal of hazardous materials</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2439,12 +2439,13 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>The gut-brain axis is a complex bidirectional communication network linking the gastrointestinal tract and the central nervous system. Its dysregulation is closely associated with a wide range of gastrointestinal, metabolic, and neuropsychiatric disorders. Glycosylation, one of the most prevalent and structurally diverse post-translational modifications of proteins and lipids, is increasingly recognized as a regulator of multiple processes within the gut-brain axis. In this review, we summarize evidence that glycosylation influences several steps of gut-brain communication, including intestinal barrier function, microbial glycan metabolism, immune signaling, enteric and vagal pathways, blood-brain barrier integrity, and neural responses. We distinguish direct mechanistic findings from associative observations and discuss the more limited evidence for brain-to-gut regulation of intestinal glycosylation. In addition, we discuss the potential of glycosylation-targeted nutritional and microbiota-based interventions and highlight emerging opportunities to integrate glycomics with other omics approaches to dissect the complex regulatory networks underlying the gut-brain axis. In conclusion, elucidating how glycosylation shapes signaling along the gut-brain axis may open new avenues for understanding disease pathogenesis and for developing targeted therapeutic strategies.</t>
+          <t>As the complexity of industrial wastewater pollution continues to increase, the simultaneous removal of nitrogen, metal contaminants, and persistent organic pollutants under low carbon conditions has become a key challenge for biological treatment systems. To address the operational instability and dependence on carbon sources observed in immobilized systems when exposed to copper (Cu2+) and bisphenol A (BPA), the Pseudoalteromonas japonicus strain LY0623 was integrated into a hydrogel-biochar-AQDS composite carrier to construct a multifunctional immobilized biofilm system. Notably, under conditions containing only NaHCO3, the R4 system achieved an NH4+-N removal rate of 89%. Under conditions where Cu2+ and BPA coexist, the R4 system achieved removal of NH4+-N (89%), NO3--N (100%), Cu2+ (85%), and BPA (88%). Sediment characterization confirmed that Cu2+ was immobilized through adsorption, complexation, and microbiologically induced carbonate precipitation (MICP). Metagenomic analysis further indicated that the Pseudomonadota phylum remained the dominant phylum, while functional pathways associated with inorganic carbon assimilation, HNAD nitrogen metabolism, endogenous carbon transformation, biomineralization, electron transfer, and aromatic compound degradation were preserved. By combining ammonia oxidation driven energy production, inorganic carbon utilization, redox mediated processes, and biomineralization, this study provides a highly promising low carbon strategy for treating industrial wastewater containing mixed pollutants.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>本文探討「腸-腦軸線」（Gut-Brain Axis）中醣基化（Glycosylation）修飾的關鍵調節角色。醣基化作為蛋白質與脂質重要的轉譯後修飾，深刻影響腸道屏障功能、微生物聚醣代謝、免疫訊息傳遞及血腦屏障完整性。研究重點解析了醣基化如何調控腸道與中樞神經系統間的溝通，並區分了機制性證據與相關性觀察。本文不僅強調了醣基化在維繫軸線穩定中的核心地位，更提出透過營養干預與微生物調節，結合多體學（Omics）分析醣基化網絡，將有望為神經精神疾病與代謝性障礙提供創新的診斷與治療策略。</t>
+          <t>本研究旨在解決低碳條件下，工業廢水中氮、重金屬（Cu2+）與雙酚A（BPA）等混合污染物難以同時高效生物降解的挑戰。研究人員將日本假交替單胞菌（*Pseudoalteromonas japonicus*）LY0623菌株整合至水凝膠-生物炭-AQDS複合載體中，構建出新型固定化生物膜系統（R4系統）。
+研究發現，在僅添加碳酸氫鈉（無機碳源）的條件下，該系統成功實現了NH4+-N（89%）、NO3--N（100%）、Cu2+（85%）和BPA（88%）的高效同時去除。總體基因體學分析證實，變形菌門（Pseudomonadota）為優勢菌群，且系統中與無機碳同化、異營硝化-好氧反硝化（HNAD）、生物礦化及芳香族化合物降解相關的功能通路均得到有效維持。本研究結合了氨氧化產能與生物礦化等機制，為混合污染廢水處理提供了一種具前景的低碳生物修復策略。</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2454,32 +2455,32 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42642834/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648179/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>42640100</t>
+          <t>42642466</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Revisiting gut microbiota-driven ammonia metabolism: from disease burden to physiological adaptation.</t>
+          <t>Empirical evidence for gut microbial influence on human brain neurochemistry via the gut-brain axis.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>Molecular psychiatry</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11</v>
+        <v>10.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2492,12 +2493,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Ammonia homeostasis is governed by interconnected host and microbial pathways, including hepatic ureagenesis, glutamine synthesis, and gut microbiota-mediated urea hydrolysis, proteolysis, and amino acid deamination. Ammonia has historically been viewed primarily as a nitrogenous waste product and neurotoxic molecule, a concept strongly supported by studies of hyperammonemia and hepatic encephalopathy. Impaired hepatic clearance, portosystemic shunting, and enhanced gut-derived ammonia input increase systemic ammonia burden and are linked to neurological dysfunction, muscle wasting, immune dysregulation, and progression of liver disease. In the gut lumen and mucosal environment, however, gut microbes not only generate ammonia but can also reuse ammonia-derived nitrogen for amino acid synthesis, microbial biomass formation, and community nitrogen exchange. Evidence from selected physiological and preclinical models indicates that microbiota-derived ammonia may contribute to nitrogen recycling, microbial community maintenance, enteric neural regulation, or metabolic adaptation under defined conditions. These roles are more context-specific and less broadly established than the pathological effects of systemic hyperammonemia. When epithelial barrier integrity is compromised, hepatic clearance declines, or host buffering reserves are depleted, elevated ammonia can increase epithelial exposure, portal ammonia input, or peripheral blood ammonia. Conversely, evidence that reduced microbiota-derived ammonia contributes to disease remains limited and currently comes mainly from selected animal models. This review re-examines ammonia metabolism from a gut microbiota-centered perspective. We discuss the ecological origins, spatial distribution, exposure characteristics, host-interface effects, and context-specific outcomes of microbiota-derived ammonia in physiology and disease, and discuss how ammonia should be measured, stratified, and targeted in microbial nitrogen metabolism.</t>
+          <t>The gut microbiome produces metabolites with potential neuroactive properties, many of which act locally within the gut. While preclinical studies suggest these microbial pathways can influence cognitive and emotional processes, human evidence remains limited. This study investigates associations between gut microbiome-derived neuroactive functional potential and in vivo brain neurotransmitter concentrations in healthy young females. Using proton magnetic resonance spectroscopy (¹H-MRS), we quantified GABA and glutamate levels in the dorsolateral prefrontal cortex (dlPFC), anterior cingulate cortex (ACC), and inferior occipital gyrus (IOG). Parallel metagenomic profiling characterised microbial functional potential for pathways related to the synthesis and degradation of GABA, glutamate, short-chain fatty acids (SCFAs), p-cresol, and inositol. Region-specific associations were observed between these microbial pathways and cortical GABA and glutamate levels, including excitatory/inhibitory (E/I) balance, a key marker of neuroplasticity and mental health. Notably, microbial glutamate degradation and inositol synthesis potential were associated with IOG E/I balance, while additional pathways including GABA metabolism, p-cresol production, and SCFA synthesis showed distinct associations across regions. Exploratory analyses also identified links between microbial functional potential and anxiety, depressive symptoms, and sleep quality. Together, these findings provide new human evidence that variation in microbial functional potential corresponds with regional cortical neurochemistry and psychological wellbeing, highlighting the gut-brain axis as a promising avenue for mechanistically informed microbiome-based- interventions.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>本綜述重新審視了腸道菌群驅動的氨代謝，探討其從疾病負擔到生理適應的雙重角色。傳統上，氨被視為具神經毒性的代謝廢物，與高氨血症、肝性腦病及肝病惡化密切相關。然而，在腸道微環境中，微生物不僅產生氨，亦能利用氨源氮進行氨基酸合成與群落氮循環，展現出維持腸道神經與代謝適應等生理功能。文章強調，氨的病理與生理效應高度取決於上皮屏障、肝臟清除能力及宿主緩衝儲備。本研究為腸道微生物氮代謝提供了新的生態與臨床視角，並討論了未來如何精確測量及標靶氨代謝的策略。</t>
+          <t>本研究旨在探討健康女性的腸道菌群功能潛力與大腦活體神經傳導物質（GABA與麩胺酸）濃度的關聯。研究結合腦部質子磁共振波譜（¹H-MRS）與總體基因體學分析，發現微生物中參與GABA、麩胺酸、短鏈脂肪酸、對甲酚及肌醇代謝的通路，與大腦特定區域（如背外側前額葉、前扣帶迴與下枕葉）的神經傳導物質水平及興奮/抑制平衡（E/I）具有區域特異性關聯。探索性分析亦顯示微生物功能與焦慮、抑鬱及睡眠品質相關。本研究為腸道菌群影響人類大腦神經化學與心理健康提供了直接的人體實證，為未來開發以微生物為基礎的腦腸軸臨床干預奠定基礎。</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2507,37 +2508,37 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42640100/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42642466/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>42642622</t>
+          <t>42640624</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Deployable high-fidelity metagenome binning at scale with QuickBin.</t>
+          <t>Gut microbial diversity at baseline conditions the clinical, microbiome, and metabolic response to paraprobiotic Lactiplantibacillus plantarum LRCC5282 in overweight adults.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Communications biology</t>
+          <t>Gut microbes</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>5.1</v>
+        <v>11</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>16S, metabolomics</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>297 個真實總體基因體數據集 (297 real metagenomes)</t>
+          <t>120 位過重成人</t>
         </is>
       </c>
       <c r="G40" t="b">
@@ -2545,12 +2546,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Reconstructing genomes from metagenomic assemblies is foundational to microbiome research, yet binning faces a persistent trade-off between fidelity and throughput. Many high-accuracy methods rely on GPU-intensive workflows, marker-gene postprocessing, or heavy computational resources, limiting reproducible use at scale. Here, we present QuickBin, a CPU-native, marker-free binning algorithm designed to recover near-complete, ultra-low-contamination metagenome-assembled genomes (MAGs) efficiently. QuickBin pairs a GC-coverage spatial index (BinMap) with an early-exit Oracle cascade of similarity tests (scalar composition/coverage filters and SIMD-accelerated k-mer comparisons), reserving a compact neural network exclusively for ambiguous merges. Across synthetic communities, evaluated by marker-based and contig-origin ground truth, QuickBin maximizes high-fidelity sequence recovery. In benchmarking 297 diverse real metagenomes, QuickBin completed all runs, recovering more high-quality MAGs (≥95% completeness, ≤1% contamination) than resource-intensive alternatives that frequently failed. QuickBin provides a practical path to reproducible, genome-resolved metagenomics at scale for downstream comparative analyses. Open-source at: https://github.com/bbushnell/BBTools .</t>
+          <t>The gut microbiota is increasingly recognized as a target for obesity management; however, whether baseline gut microbial diversity conditions responsiveness to microbiota-targeted interventions remains unclear. We aimed to investigate whether baseline gut microbial diversity is associated with responsiveness to a paraprobiotic derived from Lactiplantibacillus plantarum LRCC5282 (LP5282-P) in overweight adults. In a 12-week, randomized, double-blind, placebo-controlled, multicenter trial of 120 overweight adults, LP5282-P produced no significant between-group differences in any clinical outcome across the overall per-protocol population. However, in the low-diversity subgroup, LP5282-P was associated with significant reductions in body weight, body mass index, and circulating leptin levels. These clinical changes were accompanied by compositional shifts in the gut microbiota, including higher relative abundances of Christensenellaceae, Faecalibacterium, and Alistipes. Fecal metabolite profiles showed elevated acetate and butyrate concentrations and altered bile acid composition. Within the low-diversity subgroup, changes in the relative abundances of Akkermansia and Eubacterium were inversely correlated with changes in body weight, body fat mass, and leptin levels. In contrast, the high-diversity subgroup exhibited no consistent response across the outcome domains examined. Overall, baseline gut microbial diversity was associated with differential responsiveness to LP5282-P, supporting its potential use as a stratification variable in future microbiota-targeted intervention trials. Further studies integrating direct measures of microbial activity and host response are warranted to elucidate the biological pathways underlying this diversity-dependent responsiveness. Trial registration: Clinical Research Information Service (CRIS), KCT0008119.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>本研究開發了 QuickBin，這是一種無需標記基因且僅需 CPU 運行的總體基因體分箱（binning）演算法，旨在高效重建高完整度且極低污染的總體基因體組裝基因體（MAGs）。QuickBin 結合了 GC 含量與覆蓋度的空間索引及快速相似性過濾機制，僅在處理模糊合併時使用輕量級神經網路。在 297 個真實總體基因體數據集的基準測試中，QuickBin 成功完成所有運行，且重建的高品質 MAGs 數量超越了其他耗費資源或容易失敗的現有工具。此技術為大規模、可重複的基因體解析總體基因體學研究提供了實用的解決方案。</t>
+          <t>本研究旨在探討基準線腸道微生物多樣性，是否會影響過重成人對副乾酪乳桿菌（LP5282-P）介入的臨床、菌群及代謝反應。在一項為期12週、納入120位過重成人的臨床試驗中，整體人群並未展現顯著差異；然而，在「低多樣性」亞群中，LP5282-P顯著降低了受試者的體重、BMI與血清瘦素水平，並促使腸道有益菌（如 *Faecalibacterium* 與 *Alistipes*）豐度上升，同時提升糞便中乙酸與丁酸濃度並改變膽汁酸組成。相反地，「高多樣性」亞群則無一致反應。此研究證實基準線菌群多樣性是預測益生菌療效的重要關鍵，可作為未來精準微生態介入與體重管理的分層依據。</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2560,37 +2561,37 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42642622/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42640624/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>42640624</t>
+          <t>42642622</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Gut microbial diversity at baseline conditions the clinical, microbiome, and metabolic response to paraprobiotic Lactiplantibacillus plantarum LRCC5282 in overweight adults.</t>
+          <t>Deployable high-fidelity metagenome binning at scale with QuickBin.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>Communications biology</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11</v>
+        <v>5.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>120 位過重成人</t>
+          <t>297 個真實總體基因體數據集 (297 real metagenomes)</t>
         </is>
       </c>
       <c r="G41" t="b">
@@ -2598,12 +2599,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>The gut microbiota is increasingly recognized as a target for obesity management; however, whether baseline gut microbial diversity conditions responsiveness to microbiota-targeted interventions remains unclear. We aimed to investigate whether baseline gut microbial diversity is associated with responsiveness to a paraprobiotic derived from Lactiplantibacillus plantarum LRCC5282 (LP5282-P) in overweight adults. In a 12-week, randomized, double-blind, placebo-controlled, multicenter trial of 120 overweight adults, LP5282-P produced no significant between-group differences in any clinical outcome across the overall per-protocol population. However, in the low-diversity subgroup, LP5282-P was associated with significant reductions in body weight, body mass index, and circulating leptin levels. These clinical changes were accompanied by compositional shifts in the gut microbiota, including higher relative abundances of Christensenellaceae, Faecalibacterium, and Alistipes. Fecal metabolite profiles showed elevated acetate and butyrate concentrations and altered bile acid composition. Within the low-diversity subgroup, changes in the relative abundances of Akkermansia and Eubacterium were inversely correlated with changes in body weight, body fat mass, and leptin levels. In contrast, the high-diversity subgroup exhibited no consistent response across the outcome domains examined. Overall, baseline gut microbial diversity was associated with differential responsiveness to LP5282-P, supporting its potential use as a stratification variable in future microbiota-targeted intervention trials. Further studies integrating direct measures of microbial activity and host response are warranted to elucidate the biological pathways underlying this diversity-dependent responsiveness. Trial registration: Clinical Research Information Service (CRIS), KCT0008119.</t>
+          <t>Reconstructing genomes from metagenomic assemblies is foundational to microbiome research, yet binning faces a persistent trade-off between fidelity and throughput. Many high-accuracy methods rely on GPU-intensive workflows, marker-gene postprocessing, or heavy computational resources, limiting reproducible use at scale. Here, we present QuickBin, a CPU-native, marker-free binning algorithm designed to recover near-complete, ultra-low-contamination metagenome-assembled genomes (MAGs) efficiently. QuickBin pairs a GC-coverage spatial index (BinMap) with an early-exit Oracle cascade of similarity tests (scalar composition/coverage filters and SIMD-accelerated k-mer comparisons), reserving a compact neural network exclusively for ambiguous merges. Across synthetic communities, evaluated by marker-based and contig-origin ground truth, QuickBin maximizes high-fidelity sequence recovery. In benchmarking 297 diverse real metagenomes, QuickBin completed all runs, recovering more high-quality MAGs (≥95% completeness, ≤1% contamination) than resource-intensive alternatives that frequently failed. QuickBin provides a practical path to reproducible, genome-resolved metagenomics at scale for downstream comparative analyses. Open-source at: https://github.com/bbushnell/BBTools .</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>本研究旨在探討基準線腸道微生物多樣性，是否會影響過重成人對副乾酪乳桿菌（LP5282-P）介入的臨床、菌群及代謝反應。在一項為期12週、納入120位過重成人的臨床試驗中，整體人群並未展現顯著差異；然而，在「低多樣性」亞群中，LP5282-P顯著降低了受試者的體重、BMI與血清瘦素水平，並促使腸道有益菌（如 *Faecalibacterium* 與 *Alistipes*）豐度上升，同時提升糞便中乙酸與丁酸濃度並改變膽汁酸組成。相反地，「高多樣性」亞群則無一致反應。此研究證實基準線菌群多樣性是預測益生菌療效的重要關鍵，可作為未來精準微生態介入與體重管理的分層依據。</t>
+          <t>本研究開發了 QuickBin，這是一種無需標記基因且僅需 CPU 運行的總體基因體分箱（binning）演算法，旨在高效重建高完整度且極低污染的總體基因體組裝基因體（MAGs）。QuickBin 結合了 GC 含量與覆蓋度的空間索引及快速相似性過濾機制，僅在處理模糊合併時使用輕量級神經網路。在 297 個真實總體基因體數據集的基準測試中，QuickBin 成功完成所有運行，且重建的高品質 MAGs 數量超越了其他耗費資源或容易失敗的現有工具。此技術為大規模、可重複的基因體解析總體基因體學研究提供了實用的解決方案。</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2613,32 +2614,32 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42640624/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42642622/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>42642466</t>
+          <t>42640100</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Empirical evidence for gut microbial influence on human brain neurochemistry via the gut-brain axis.</t>
+          <t>Revisiting gut microbiota-driven ammonia metabolism: from disease burden to physiological adaptation.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Molecular psychiatry</t>
+          <t>Gut microbes</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10.1</v>
+        <v>11</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2651,12 +2652,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>The gut microbiome produces metabolites with potential neuroactive properties, many of which act locally within the gut. While preclinical studies suggest these microbial pathways can influence cognitive and emotional processes, human evidence remains limited. This study investigates associations between gut microbiome-derived neuroactive functional potential and in vivo brain neurotransmitter concentrations in healthy young females. Using proton magnetic resonance spectroscopy (¹H-MRS), we quantified GABA and glutamate levels in the dorsolateral prefrontal cortex (dlPFC), anterior cingulate cortex (ACC), and inferior occipital gyrus (IOG). Parallel metagenomic profiling characterised microbial functional potential for pathways related to the synthesis and degradation of GABA, glutamate, short-chain fatty acids (SCFAs), p-cresol, and inositol. Region-specific associations were observed between these microbial pathways and cortical GABA and glutamate levels, including excitatory/inhibitory (E/I) balance, a key marker of neuroplasticity and mental health. Notably, microbial glutamate degradation and inositol synthesis potential were associated with IOG E/I balance, while additional pathways including GABA metabolism, p-cresol production, and SCFA synthesis showed distinct associations across regions. Exploratory analyses also identified links between microbial functional potential and anxiety, depressive symptoms, and sleep quality. Together, these findings provide new human evidence that variation in microbial functional potential corresponds with regional cortical neurochemistry and psychological wellbeing, highlighting the gut-brain axis as a promising avenue for mechanistically informed microbiome-based- interventions.</t>
+          <t>Ammonia homeostasis is governed by interconnected host and microbial pathways, including hepatic ureagenesis, glutamine synthesis, and gut microbiota-mediated urea hydrolysis, proteolysis, and amino acid deamination. Ammonia has historically been viewed primarily as a nitrogenous waste product and neurotoxic molecule, a concept strongly supported by studies of hyperammonemia and hepatic encephalopathy. Impaired hepatic clearance, portosystemic shunting, and enhanced gut-derived ammonia input increase systemic ammonia burden and are linked to neurological dysfunction, muscle wasting, immune dysregulation, and progression of liver disease. In the gut lumen and mucosal environment, however, gut microbes not only generate ammonia but can also reuse ammonia-derived nitrogen for amino acid synthesis, microbial biomass formation, and community nitrogen exchange. Evidence from selected physiological and preclinical models indicates that microbiota-derived ammonia may contribute to nitrogen recycling, microbial community maintenance, enteric neural regulation, or metabolic adaptation under defined conditions. These roles are more context-specific and less broadly established than the pathological effects of systemic hyperammonemia. When epithelial barrier integrity is compromised, hepatic clearance declines, or host buffering reserves are depleted, elevated ammonia can increase epithelial exposure, portal ammonia input, or peripheral blood ammonia. Conversely, evidence that reduced microbiota-derived ammonia contributes to disease remains limited and currently comes mainly from selected animal models. This review re-examines ammonia metabolism from a gut microbiota-centered perspective. We discuss the ecological origins, spatial distribution, exposure characteristics, host-interface effects, and context-specific outcomes of microbiota-derived ammonia in physiology and disease, and discuss how ammonia should be measured, stratified, and targeted in microbial nitrogen metabolism.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>本研究旨在探討健康女性的腸道菌群功能潛力與大腦活體神經傳導物質（GABA與麩胺酸）濃度的關聯。研究結合腦部質子磁共振波譜（¹H-MRS）與總體基因體學分析，發現微生物中參與GABA、麩胺酸、短鏈脂肪酸、對甲酚及肌醇代謝的通路，與大腦特定區域（如背外側前額葉、前扣帶迴與下枕葉）的神經傳導物質水平及興奮/抑制平衡（E/I）具有區域特異性關聯。探索性分析亦顯示微生物功能與焦慮、抑鬱及睡眠品質相關。本研究為腸道菌群影響人類大腦神經化學與心理健康提供了直接的人體實證，為未來開發以微生物為基礎的腦腸軸臨床干預奠定基礎。</t>
+          <t>本綜述重新審視了腸道菌群驅動的氨代謝，探討其從疾病負擔到生理適應的雙重角色。傳統上，氨被視為具神經毒性的代謝廢物，與高氨血症、肝性腦病及肝病惡化密切相關。然而，在腸道微環境中，微生物不僅產生氨，亦能利用氨源氮進行氨基酸合成與群落氮循環，展現出維持腸道神經與代謝適應等生理功能。文章強調，氨的病理與生理效應高度取決於上皮屏障、肝臟清除能力及宿主緩衝儲備。本研究為腸道微生物氮代謝提供了新的生態與臨床視角，並討論了未來如何精確測量及標靶氨代謝的策略。</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2666,32 +2667,32 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42642466/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42640100/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>42648179</t>
+          <t>42642834</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Simultaneous removal of nitrogen, Cu2+, and bisphenol A in a hydrogel-biochar-AQDS immobilized bioreactor with added bicarbonate: Performance and metagenomic insights.</t>
+          <t>Glycosylation in gut-brain communication: from the intestinal barrier and microbiota to immune and neural signaling.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Journal of hazardous materials</t>
+          <t>Gut microbes</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.3</v>
+        <v>11</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2704,13 +2705,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>As the complexity of industrial wastewater pollution continues to increase, the simultaneous removal of nitrogen, metal contaminants, and persistent organic pollutants under low carbon conditions has become a key challenge for biological treatment systems. To address the operational instability and dependence on carbon sources observed in immobilized systems when exposed to copper (Cu2+) and bisphenol A (BPA), the Pseudoalteromonas japonicus strain LY0623 was integrated into a hydrogel-biochar-AQDS composite carrier to construct a multifunctional immobilized biofilm system. Notably, under conditions containing only NaHCO3, the R4 system achieved an NH4+-N removal rate of 89%. Under conditions where Cu2+ and BPA coexist, the R4 system achieved removal of NH4+-N (89%), NO3--N (100%), Cu2+ (85%), and BPA (88%). Sediment characterization confirmed that Cu2+ was immobilized through adsorption, complexation, and microbiologically induced carbonate precipitation (MICP). Metagenomic analysis further indicated that the Pseudomonadota phylum remained the dominant phylum, while functional pathways associated with inorganic carbon assimilation, HNAD nitrogen metabolism, endogenous carbon transformation, biomineralization, electron transfer, and aromatic compound degradation were preserved. By combining ammonia oxidation driven energy production, inorganic carbon utilization, redox mediated processes, and biomineralization, this study provides a highly promising low carbon strategy for treating industrial wastewater containing mixed pollutants.</t>
+          <t>The gut-brain axis is a complex bidirectional communication network linking the gastrointestinal tract and the central nervous system. Its dysregulation is closely associated with a wide range of gastrointestinal, metabolic, and neuropsychiatric disorders. Glycosylation, one of the most prevalent and structurally diverse post-translational modifications of proteins and lipids, is increasingly recognized as a regulator of multiple processes within the gut-brain axis. In this review, we summarize evidence that glycosylation influences several steps of gut-brain communication, including intestinal barrier function, microbial glycan metabolism, immune signaling, enteric and vagal pathways, blood-brain barrier integrity, and neural responses. We distinguish direct mechanistic findings from associative observations and discuss the more limited evidence for brain-to-gut regulation of intestinal glycosylation. In addition, we discuss the potential of glycosylation-targeted nutritional and microbiota-based interventions and highlight emerging opportunities to integrate glycomics with other omics approaches to dissect the complex regulatory networks underlying the gut-brain axis. In conclusion, elucidating how glycosylation shapes signaling along the gut-brain axis may open new avenues for understanding disease pathogenesis and for developing targeted therapeutic strategies.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>本研究旨在解決低碳條件下，工業廢水中氮、重金屬（Cu2+）與雙酚A（BPA）等混合污染物難以同時高效生物降解的挑戰。研究人員將日本假交替單胞菌（*Pseudoalteromonas japonicus*）LY0623菌株整合至水凝膠-生物炭-AQDS複合載體中，構建出新型固定化生物膜系統（R4系統）。
-研究發現，在僅添加碳酸氫鈉（無機碳源）的條件下，該系統成功實現了NH4+-N（89%）、NO3--N（100%）、Cu2+（85%）和BPA（88%）的高效同時去除。總體基因體學分析證實，變形菌門（Pseudomonadota）為優勢菌群，且系統中與無機碳同化、異營硝化-好氧反硝化（HNAD）、生物礦化及芳香族化合物降解相關的功能通路均得到有效維持。本研究結合了氨氧化產能與生物礦化等機制，為混合污染廢水處理提供了一種具前景的低碳生物修復策略。</t>
+          <t>本文探討「腸-腦軸線」（Gut-Brain Axis）中醣基化（Glycosylation）修飾的關鍵調節角色。醣基化作為蛋白質與脂質重要的轉譯後修飾，深刻影響腸道屏障功能、微生物聚醣代謝、免疫訊息傳遞及血腦屏障完整性。研究重點解析了醣基化如何調控腸道與中樞神經系統間的溝通，並區分了機制性證據與相關性觀察。本文不僅強調了醣基化在維繫軸線穩定中的核心地位，更提出透過營養干預與微生物調節，結合多體學（Omics）分析醣基化網絡，將有望為神經精神疾病與代謝性障礙提供創新的診斷與治療策略。</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2720,28 +2720,28 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42648179/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42642834/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>42642836</t>
+          <t>42641146</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Microbiome-mediated regulation of pathogen virulence: Molecular mechanisms and clinical implications.</t>
+          <t>Engineered bacterial therapeutics from synthetic biology to clinical translation: A multi-database scientometric analysis, 2000-2026.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Virulence</t>
+          <t>Human vaccines &amp; immunotherapeutics</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5.4</v>
+        <v>3.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>1,730 篇學術文章與評論</t>
         </is>
       </c>
       <c r="G44" t="b">
@@ -2758,12 +2758,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>The human microbiome profoundly influences pathogen virulence and disease susceptibility through diverse molecular mechanisms. This review, focused on literature from 2016 to 2026, synthesizes knowledge on microbiome-mediated regulation examining major pathogens including Vibrio cholerae, enterohemorrhagic Escherichia coli, Salmonella species, Clostridioides difficile, and Staphylococcus aureus. A triangular interaction model is presented, linking host immunity, resident microbiome, and invading pathogen to frame infection outcomes. Commensal bacteria regulate pathogen behavior through quorum sensing interference, metabolite-mediated regulation via short-chain fatty acids and bile acids, competitive exclusion, immune response modulation, and direct antimicrobial production. Key species-Lactobacillus spp. Bifidobacterium spp. Bacteroides thetaiotaomicron, and Faecalibacterium prausnitzii-employ distinct molecular strategies against these pathogens. Organ-on-chip platforms and multi-omics advances reveal context-dependent interactions. Clinical applications including rationally designed probiotics, fecal microbiota transplantation, and precision microbiome engineering show promise despite challenges of inter-individual microbiome variability, representing a paradigm shift toward ecosystem-based infectious disease management.</t>
+          <t>Engineered bacterial therapeutics integrate programmable strain engineering with biomedical functions such as sensing, delivery, immune modulation, microbiome intervention, and disease management. This study conducted a multi-database bibliometric analysis to map the knowledge structure, collaboration patterns, and translational direction of this field. Bibliographic records were retrieved from Web of Science Core Collection, Scopus, and PubMed for publications from 1 January 2000 to 1 June 2026. After document-type filtering, time restriction, deduplication, language screening, and manual eligibility assessment, 1,730 English-language articles and reviews were included. CiteSpace 6.4.R1, VOSviewer 1.6.20, and the bibliometrix R package were used to analyze publication trends, collaboration networks, journal co-citation, dual-map citation trajectories, citation bursts, keyword co-occurrence, and thematic evolution. Publication output increased steadily, with faster growth after 2020; 2025 was the highest-output complete year, while 2026 represented a partial retrieval year. China and the United States were the leading contributors, although institutional collaboration remained regionally clustered. Co-citation, citation-burst, and keyword analyses showed a shift from bacterial chassis construction and circuit design toward engineered probiotics, gut microbiota-related therapy, cancer immunotherapy, drug delivery, live biotherapeutic products, and clinical translation. Persistent translational priorities include controllability, safety, manufacturing consistency, and regulatory alignment.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>本研究綜述了2016年至2026年間關於腸道微生物群調控病原體毒力（如霍亂弧菌、大腸桿菌、沙門氏菌等）的分子機制。作者提出了一個結合宿主免疫、共生菌群與入侵病原體的「三角交互模型」，闡述了共生菌如何透過群體感應干擾、代謝產物（如短鏈脂肪酸、膽汁酸）調節、競爭性排斥及免疫調節來抑制病原體。研究強調了乳酸桿菌、雙歧桿菌及普拉梭菌等關鍵菌種的保護機制，並探討了器官晶片與多體學技術在揭示交互作用上的貢獻。此研究主張從生態系統角度管理傳染病，指出益生菌設計、糞便菌群移植及精準微生物組工程是未來治療的關鍵方向，雖面臨個體差異挑戰，但為臨床感染控制提供了典範轉移。</t>
+          <t>本研究透過文獻計量學方法，系統性分析 2000 年至 2026 年間有關「工程化細菌治療」的 1,730 篇學術文獻。研究旨在釐清該領域的知識結構、國際合作模式及臨床轉化趨勢。分析顯示，該領域自 2020 年後顯著加速發展，中國與美國為主要貢獻國。核心研究主軸已由早期的細菌底盤構建與基因電路設計，轉向工程化益生菌、癌症免疫治療、藥物遞送及活體生物藥物（LBP）的開發。科學意義在於確立了該領域從實驗室轉向臨床應用的優先議題，即解決控制力、生物安全性、生產一致性與法規調適等挑戰，為未來工程化細菌作為精準醫療工具的發展提供關鍵決策參考。</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42642836/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42641146/</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>本研究旨在探討馬乳（Koumiss）在天然發酵與接種乳酸菌發酵下，微生物群落、代謝產物與生理活性之間的關聯。研究結果顯示，接種混合乳酸菌發酵能顯著提升馬乳的抗氧化能力，以及對 α-葡萄糖苷酶、α-澱粉酶及血管張力素轉換酶（ACE）的抑制活性，同時降低了微生物多樣性。代謝體學分析證實，接種發酵促進了脂質與有機酸等功能性代謝物的生成。相關性分析進一步指出，植物乳桿菌（*Lactiplantibacillus*）與檸檬乳桿菌（*Limosilactobacillus*）的豐度與亞麻油酸、α-次亞麻油酸等益生代謝物及生理活性呈正相關。本研究揭示了特定乳酸菌發酵改善馬乳功能特性的代謝機制，為開發具高附加價值的發酵馬乳產品提供了重要的理論依據與技術支撐。</t>
+          <t>本研究旨在探討自然發酵與接種乳酸菌（LAB）發酵對馬奶（Koumiss）微生物群落、代謝物及生物活性的影響與關聯。研究利用總體基因體學與非靶向代謝組學技術發現，相較於自然發酵，接種混合乳酸菌發酵顯著提升了馬奶的抗氧化、降血糖（抑制α-葡萄糖苷酶與α-澱粉酶）及抗高血壓（抑制ACE）之體外活性。雖然接種發酵降低了微生物多樣性，但顯著富集了脂質和有機酸等功能性代謝物。相關性分析顯示，植物乳桿菌與黏液乳桿菌的豐度與有益代謝物（如亞麻油酸、α-次亞麻油酸）及生物活性呈顯著正相關。本研究揭示了乳酸菌發酵提升馬奶功能特性的代謝機制，為開發高價值發酵馬奶產品提供了理論與技術支持。</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>metagenomics, small genome</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>120 個糞便檢體</t>
+          <t>120 個放養雞糞便檢體（重建出 2,146 個宏基因組組裝基因組/MAGs）</t>
         </is>
       </c>
       <c r="G57" t="b">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>本研究旨在探討放山雞腸道菌群中的抗生素抗藥性基因（ARGs）儲存庫。研究團隊分析了來自中國四個省份的 120 個糞便檢體，透過總體基因體定序重組出 2,146 個基因組（MAGs），涵蓋 660 個物種，建立了完善的雞隻腸道基因組目錄。結果顯示，雞隻腸道內存在多樣化的 ARGs，尤以多重抗藥性、四環黴素及胜肽類抗藥性最為常見。研究發現抗藥性基因的分布具有顯著的區域差異，且與移動遺傳因子（MGEs）呈現高度正相關，顯示 MGEs 在基因傳播中扮演關鍵角色。此外，大腸桿菌與肺炎克雷伯氏菌等特定菌株被識別為攜帶大量抗藥性與毒力因子的高風險載體。本研究揭示了環境與農耕實踐對腸道抗藥體系的塑造作用，為公共衛生監控與家禽業抗藥性管理提供了重要的科學依據與基因資源。</t>
+          <t>本研究旨在探討放養雞腸道菌群中的抗生素抗藥性基因（ARGs）分布。研究團隊分析了中國四省的120個放養雞糞便檢體，重建出2,146個宏基因組組裝基因組（MAGs）。結果共鑑定出254,316個ARGs，以多重抗藥性與四環黴素抗性最為普遍。ARGs分布具顯著地域差異，且與行動遺傳元件（MGEs）呈強正相關（R=0.77），證實其高傳播潛力。此外，大腸桿菌和肺炎克雷伯氏菌等特定菌株被發現攜帶多種ARGs與毒力因子，為潛在的高風險傳播媒介。本研究建立的基因組資源，對制定禽類抗藥性監控與防治策略具有重要科學價值。</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">

--- a/papers_database.xlsx
+++ b/papers_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>42666020</t>
+          <t>42668932</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Decadal Resampling Reveals Widespread Increases in Soil Microbial Diversity Associated With Nitrogen Deposition.</t>
+          <t>Ureaplasma parvum meningitis in neonates: A retrospective case study and literature review.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Global change biology</t>
+          <t>Pakistan journal of medical sciences</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>38 個森林與草原生態系統的土壤（分別於 2009 年與 2019 年進行兩次重複採樣）</t>
+          <t>17 個案例（1 例本研究案例 + 16 例文獻回顧案例）</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -509,54 +509,54 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Simulated manipulation experiments, such as nitrogen addition to mimic atmospheric nitrogen deposition, are widely used in global change research. However, experimental manipulations may differ from real-world environmental change in their intensity, duration, and co-occurrence, leaving long-term changes in soil microbial communities and soil health insufficiently understood. To address this gap, we resampled soils from 38 forest and grassland ecosystems across eastern China in 2009 and 2019 and assessed microbial taxonomic and functional diversity using shotgun metagenomics. Microbial diversity increased by 17% over the decade, accompanied by clear shifts in community composition. Among the environmental variables considered, nitrogen deposition (~19 kg nitrogen ha-1 year-1 across ecosystems) was the strongest predictor of changes in seven of 12 microbial community metrics. Larger nitrogen deposition was also associated with increased relative abundances of nitrogen-cycling genes and reduced spatial turnover in microbial community composition. These effects were consistent with a potential alleviation of nitrogen limitation and weakening of deterministic community assembly, although these mechanisms could not be directly established. In addition, increases in genes associated with carbon degradation and phosphorus cycling, together with declines in the relative abundances of pathogens, antibiotic resistance genes, and DNA viruses, coincided with the raise of the composite soil health index. Our findings demonstrate widespread decadal increases in soil microbial diversity and soil health across eastern China, with nitrogen deposition emerging as their strongest environmental factor. These results highlight that microbial responses to long-term ambient environmental change can differ markedly from responses inferred from short-term or high-intensity manipulation experiments.</t>
+          <t>To investigate the clinical characteristics and advances in diagnosis and treatment of neonatal Ureaplasma parvum (U. parvum) meningitis. Clinical manifestations, diagnosis, treatment, and follow-up data of a neonate with persistent fever, normal blood routine, but persistently abnormal cerebrospinal fluid (CSF) results due to U. parvum meningitis were retrospectively analyzed. A literature review was conducted to identify relevant studies reporting on neonatal U. parvum meningitis published until May 2025. A male infant born at 35+2 weeks of gestation with eight hours of premature rupture of membranes (PROM) was admitted at 17 days of age with persistent fever. The routine blood test was normal, while the CSF suggested purulent meningitis. Empirical treatment was ineffective, and metagenomic next-generation sequencing (mNGS) of CSF confirmed U. parvum meningitis. The infant recovered after three weeks of azithromycin treatment, but a language delay was found at two-year follow-up. The literature review identified 16 previously reported cases of U. parvum meningitis, which were combined with the current case, totaling 17 cases. Main manifestations included fever and convulsions, or initial circulatory and respiratory symptoms. CSF in the included studies showed leukocytosis, decreased glucose, and elevated protein. Diagnosis was mainly based on mNGS, and the predominant treatment consisted of macrolides, sometimes combined with quinolones, for 3-10 weeks. Two patients relapsed after drug withdrawal, and one had elevated liver enzymes. Major neurological complications included lateral ventricular dilatation and hydrocephalus, cerebral hemorrhage, infarction, malacia, and herniation. Most cases had a favorable prognosis, with rare developmental delay. Clinical manifestations of neonatal U. parvum meningitis are nonspecific. Some patients present with normal blood routine but purulent CSF. U. parvum meningitis should be suspected in patients with poor response to empirical antibiotics and confirmed by CSF mNGS. Macrolides are biologically rational and commonly used for neonatal U. parvum meningitis; however, the optimal regimen and duration remain unclear due to limited and heterogeneous case-based evidence.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>本研究旨在探討真實自然環境的長期變化對土壤微生物群落與健康的影響。研究團隊於2009與2019年，對中國東部38個森林與草原生態系統進行跨越十年的重複採樣，並利用總體基因體學分析。結果顯示，十年間土壤微生物多樣性增加17%。大氣氮沉降是驅動變化的最強因子，與氮循環基因增加及群落空間周轉率降低密切相關。此外，碳降解與磷循環基因增加，而病原體與抗藥性基因減少，提升了整體土壤健康。本研究證實微生物對長期環境變化的響應與短期高強度模擬實驗有顯著差異，為全球變遷研究提供重要科學依據。</t>
+          <t>本研究旨在探討新生兒解脲支原體（U. parvum）腦膜炎的臨床特徵、診斷及治療。該病症狀缺乏特異性，常表現為發燒與腦脊液（CSF）異常，但血液常規檢查往往正常，導致經驗性抗生素治療無效。研究顯示，宏基因組二代測序（mNGS）是確診該病的重要工具。透過回顧包含本個案在內的 17 例病例，發現大環內酯類藥物為主要治療手段，療程通常需 3 至 10 週。儘管多數患者預後良好，但部分個案仍可能出現腦室擴張、腦梗塞等嚴重神經系統併發症及長期發育遲緩。本研究強調，對於抗生素治療反應不佳的新生兒腦膜炎，臨床醫師應高度懷疑並及早進行 mNGS 檢測，以利精準治療並降低神經後遺症風險。</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42666020/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42668932/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>42667585</t>
+          <t>42669365</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Gut Microbiota from Patients with Long COVID Persisting for 2 Years Result in Alterations in Mice that Resemble Post-COVID Symptoms.</t>
+          <t>In situ fermentation-coupled symbiosis of polyphosphate-accumulating organisms and microalgae for efficient nutrient removal and sludge reduction in low carbon-to-nitrogen ratios wastewater.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Probiotics and antimicrobial proteins</t>
+          <t>Bioresource technology</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16S, metagenomics, metabolomics</t>
+          <t>metagenomics, others</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>健康對照組 11 位、長新冠（LCOVID）患者 11 位（共 22 個糞便檢體），以及接受糞便移植的抗生素處理（ABx）小鼠（小鼠具體數量未提及）</t>
+          <t>未提及（文中未明確指出具體的檢體或樣本總數量）</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -564,54 +564,54 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Human gut microbiota (GM) has been identified as a potentially important factor influencing the development of long COVID (LCOVID). The aim of this study was to understand the GM of LCOVID, which lasted for two years, in order to improve public awareness. Human gut microbiota and its metabolites were assessed in a healthy control group (n = 11) (HC) unexposed to SARS-CoV-2 and an LCOVID group (n = 11) in Hainan, China, using Shotgun metagenomics and liquid chromatography-mass spectrometry (LC-MS) of feces. The causal role of the microbiota in LCOVID was further validated by transplanting feces from the subjects into ABx mice using Histopathology and 16 S rRNA sequencing. Fecal microbial diversity was lower in patients with LCOVID compared with that in HC. Pro-inflammatory bacteria such as Streptococcus_salivarius and Streptococcus_parasanguinis increased, whereas anti-inflammatory bacteria such as Faecalibacterium_SGB15346 and Alistipes_onderdonkii decreased. Fecal metabolites from LCOVID were impaired in carbohydrate degradation, indole production, SCFA production, and fatty acid degradation. Transplantation of feces from patients with LCOVID into mice results in lung inflammation, intestinal inflammation, and anxiety. In addition, transplanted mice showed worse outcomes during Klebsiella_pneumoniae infections. Transplanted mice and the key bacteria Streptococcus_salivarius had the same worse outcomes in the D-IBS model by limb binding. GM from patients with LCOVID was altered significantly and sufficiently to promote LCOVID symptoms in mice, suggesting that it may be a potential therapeutic target.</t>
+          <t>Microalgae-bacteria consortia (MBC) integrated with polyphosphate-accumulating organisms (PAOs) treat wastewater sustainably, but face excess sludge and light-dark mismatch issues. This study developed in situ fermentation-coupled photo simultaneous nitrification-denitrification phosphorus removal (F/P-SNDPR) systems by incorporating fermentative PAOs into MBC for low carbon-to-nitrogen ratios (C/N) wastewater. The effects of light-dark cycles on nutrient removal, sludge fermentation, and microbial dynamics were investigated. Under an optimal 16 h dark/8h light cycle, the F/P-SNDPR system achieved &gt; 83% nitrogen and &gt; 95% phosphorus removal, with low sludge production (312.21 mgVSS/d) and low net CO2 emissions. Prolonged light and dark phases promoted early microbial apoptosis and subsequent cell lysis, respectively, thereby facilitating fermentation. Combined dark duration and photoinhibition suppress nitrite-oxidizing bacteria, enabling stable partial nitrification. Flow cytometry and metagenomic results identified Candidatus Phosphoribacter as the primary fermentative microorganism. Its fermentation-associated genes, including LivFGHMK and Pta, facilitated volatile fatty acid (VFA) production during the dark phase. The generated VFA supported Candidatus Accumulibacter/Candidatus Competibacter to enhance nutrient removal, driven by key functional genes for polyphosphate metabolism (Ppk and Ppx) and denitrification (NirS, NirK, and NosZ). Overall, The F/P-SNDPR system offers a low-carbon strategy for efficient low C/N wastewater treatment without mechanical aeration or external carbon addition, while reducing sludge production.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>本研究旨在探討罹患長新冠（LCOVID）長達兩年之患者的腸道菌群與代謝物變化，並透過小鼠糞便移植（FMT）驗證其因果關係。研究顯示，LCOVID患者的腸道菌群多樣性顯著降低，促炎菌（如*Streptococcus salivarius*）增加，抗炎菌減少；且其糞便代謝物在短鏈脂肪酸（SCFA）生成與碳水化合物降解等方面出現受損。將患者糞便移植至小鼠後，成功誘發了肺部與腸道發炎、焦慮行為，並削弱了小鼠對肺部感染的抵抗力。本研究證實腸道菌群失衡足以促進長新冠症狀，為未來開發以腸道微生態為核心的長新冠療法奠定了科學依據。</t>
+          <t>本研究開發了一種結合原位發酵與光合同步硝化-反硝化除磷（F/P-SNDPR）的微藻-細菌共生系統，旨在解決低碳氮比（C/N）廢水處理中常見的污泥過量與能耗問題。實驗發現，透過最適化的 16 小時黑暗與 8 小時光照循環，該系統能有效提升氮（&gt;83%）與磷（&gt;95%）的去除率，並顯著減少污泥產量與淨二氧化碳排放。宏基因體分析揭示，「Candidatus Phosphoribacter」為關鍵的發酵菌，其產生的揮發性脂肪酸（VFA）可支持「Candidatus Accumulibacter」等菌群進行高效除磷與反硝化作用。此技術透過微生物間的代謝耦合，無需外加碳源或機械曝氣，為低碳廢水處理提供了一項永續且具經濟效益的解決方案。</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42667585/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42669365/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>42667435</t>
+          <t>42666020</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>From traditional retting to precision bioprocessing: microbial ecology, enzymatic selectivity, and systems biology of jute retting.</t>
+          <t>Decadal Resampling Reveals Widespread Increases in Soil Microbial Diversity Associated With Nitrogen Deposition.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Antonie van Leeuwenhoek</t>
+          <t>Global change biology</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>38 個森林與草原生態系統（2009 年與 2019 年兩次採樣）</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -619,12 +619,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Jute is one of the world's most important lignocellulosic fibre crops, yet its commercial value remains highly dependent on retting, a biologically mediated fibre extraction process still largely governed by empirical practices and variable environmental conditions. Recent advances in microbial ecology, enzymology, molecular biology, and bioprocess engineering have transformed retting from a traditional post-harvest operation into a controllable lignocellulosic bioconversion process. This review synthesizes current understanding of the structural organization of jute bast fibres, selective degradation of plant cell-wall polymers, microbial succession, extracellular enzyme networks, and physicochemical factors regulating fibre liberation. It highlights the coordinated interactions among cell-wall architecture, microbial communities, enzyme specificity, and environmental conditions that collectively determine retting efficiency and fibre quality. Emerging precision retting strategies, including defined microbial consortia, enzyme-assisted retting, ribbon retting, controlled processing systems, and water-efficient technologies, are critically evaluated for their potential to improve process reproducibility, fibre quality, and environmental sustainability. The review also examines metagenomics, metatranscriptomics, metaproteomics, metabolomics, systems biology, and artificial intelligence as enabling technologies for microbiome-guided process monitoring, predictive modelling, and digital decision support. Furthermore, this review discusses the integration of precision retting within circular bioeconomy frameworks through resource recovery, pollution mitigation, climate-resilient processing, and lignocellulosic biorefineries. Key knowledge gaps, including limited understanding of microbial interactions, lack of standardized microbial consortia, insufficient process-monitoring tools, fragmented multi-omics datasets, and challenges in industrial scale-up, are identified. Overall, this review presents a systems-level framework for advancing jute retting toward standardized, predictive, and environmentally sustainable precision bioprocessing.</t>
+          <t>Simulated manipulation experiments, such as nitrogen addition to mimic atmospheric nitrogen deposition, are widely used in global change research. However, experimental manipulations may differ from real-world environmental change in their intensity, duration, and co-occurrence, leaving long-term changes in soil microbial communities and soil health insufficiently understood. To address this gap, we resampled soils from 38 forest and grassland ecosystems across eastern China in 2009 and 2019 and assessed microbial taxonomic and functional diversity using shotgun metagenomics. Microbial diversity increased by 17% over the decade, accompanied by clear shifts in community composition. Among the environmental variables considered, nitrogen deposition (~19 kg nitrogen ha-1 year-1 across ecosystems) was the strongest predictor of changes in seven of 12 microbial community metrics. Larger nitrogen deposition was also associated with increased relative abundances of nitrogen-cycling genes and reduced spatial turnover in microbial community composition. These effects were consistent with a potential alleviation of nitrogen limitation and weakening of deterministic community assembly, although these mechanisms could not be directly established. In addition, increases in genes associated with carbon degradation and phosphorus cycling, together with declines in the relative abundances of pathogens, antibiotic resistance genes, and DNA viruses, coincided with the raise of the composite soil health index. Our findings demonstrate widespread decadal increases in soil microbial diversity and soil health across eastern China, with nitrogen deposition emerging as their strongest environmental factor. These results highlight that microbial responses to long-term ambient environmental change can differ markedly from responses inferred from short-term or high-intensity manipulation experiments.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>本綜述探討黃麻漚麻（脫膠）技術如何從傳統經驗操作轉型為精準生物製造。文章系統性整合了黃麻韌皮纖維結構、細胞壁降解、微生物群落演替、胞外酶網絡及環境調節因子的最新進展。同時，評估了特定微生物菌群、酶輔助漚麻與多體學（基因體、轉錄體、代謝體）及人工智慧等技術在製程監控中的潛力，並指出當前在微生物交互作用、標準菌群及工業放大上的關鍵瓶頸。本研究為黃麻漚麻邁向標準化、可預測與環保永續的精準生物加工提供了系統級框架。</t>
+          <t>本研究針對中國東部 38 個森林與草原生態系統進行十年跨度的重複採樣，旨在探討真實環境下氮沉降對土壤微生物群落的影響。研究利用總體基因體學（shotgun metagenomics）分析發現，過去十年內土壤微生物的分類與功能多樣性顯著增加了 17%。氮沉降被識別為驅動群落結構變遷的最主要環境因子，並與氮循環基因的相對豐度增加、微生物群落空間周轉率降低密切相關。此外，研究觀察到碳降解與磷循環基因的上升，以及病原體、抗藥性基因與 DNA 病毒的減少，進而提升了整體的土壤健康指數。此發現挑戰了過去依賴短期或高強度模擬實驗的認知，強調真實環境下的長期氮沉降可減緩微生物的養分限制，對生態系統健康具有複雜且深遠的正面影響。</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -634,39 +634,39 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42667435/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42666020/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>42665998</t>
+          <t>42667585</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Agathobacter rectalis suppresses colorectal tumorigenesis via an epigallocatechin-SREBF2 axis controlling cholesterol metabolism.</t>
+          <t>Gut Microbiota from Patients with Long COVID Persisting for 2 Years Result in Alterations in Mice that Resemble Post-COVID Symptoms.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>Probiotics and antimicrobial proteins</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>metagenomics, metabolomics</t>
+          <t>metagenomics, metabolomics, 16S</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>未提及（摘要僅指出包含多個大腸直腸癌病患隊列與 Apc min/+ 小鼠模型，但未標註具體樣本數量）</t>
+          <t>22 位人類受試者（11 位健康對照、11 位長新冠患者）及若干小鼠模型</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -674,39 +674,39 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Beneficial effects of the gut commensal Agathobacter rectalis (Ar) are reported in diseases, yet its role in colorectal cancer (CRC) remains unclear. Here, metagenomic analysis revealed consistent fecal Ar depletion across CRC cohorts. In Apc min/+ mice, Ar inhibited colon tumorigenesis, reducing tumor number and volume versus E. coli and PBS controls. LC-MS/MS metabolomics showed decreased fecal cholesterol and altered lipid/cholesterol pathways after Ar treatment. In vitro, Ar-conditioned medium suppressed CRC cell growth, clonogenicity, migration, and cell cycle progression. LC-MS/MS identified (-)-epigallocatechin (EGC) as an Ar-derived metabolite absent in control bacteria. EGC recapitulated Ar-mediated anti-CRC effects in vitro and in vivo, with metabolic changes linked to lipid/cholesterol pathways. Transcriptomics showed that EGC suppressed SREBP signaling, cholesterol metabolism, and MAPK pathways. Mechanistically, EGC reduced nuclear SREBF2 and its transcriptional activity, downregulated cholesterol synthesis/metabolism genes, including FDPS and PCSK9, and suppressed MAPK signaling. Molecular docking suggested that EGC may bind pSREBF2 or SCAP. Cellular thermal shift assay revealed that EGC interacts with and stabilizes pSREBF2, but not SCAP. Co-immunoprecipitation demonstrated that EGC reduces pSREBF2-SCAP interaction, thereby inhibiting SCAP-mediated SREBF2 cleavage activation. Together, these findings define an Ar-EGC microbe-metabolite axis and support Ar/EGC-based interventions targeting cholesterol metabolism in CRC.</t>
+          <t>Human gut microbiota (GM) has been identified as a potentially important factor influencing the development of long COVID (LCOVID). The aim of this study was to understand the GM of LCOVID, which lasted for two years, in order to improve public awareness. Human gut microbiota and its metabolites were assessed in a healthy control group (n = 11) (HC) unexposed to SARS-CoV-2 and an LCOVID group (n = 11) in Hainan, China, using Shotgun metagenomics and liquid chromatography-mass spectrometry (LC-MS) of feces. The causal role of the microbiota in LCOVID was further validated by transplanting feces from the subjects into ABx mice using Histopathology and 16 S rRNA sequencing. Fecal microbial diversity was lower in patients with LCOVID compared with that in HC. Pro-inflammatory bacteria such as Streptococcus_salivarius and Streptococcus_parasanguinis increased, whereas anti-inflammatory bacteria such as Faecalibacterium_SGB15346 and Alistipes_onderdonkii decreased. Fecal metabolites from LCOVID were impaired in carbohydrate degradation, indole production, SCFA production, and fatty acid degradation. Transplantation of feces from patients with LCOVID into mice results in lung inflammation, intestinal inflammation, and anxiety. In addition, transplanted mice showed worse outcomes during Klebsiella_pneumoniae infections. Transplanted mice and the key bacteria Streptococcus_salivarius had the same worse outcomes in the D-IBS model by limb binding. GM from patients with LCOVID was altered significantly and sufficiently to promote LCOVID symptoms in mice, suggesting that it may be a potential therapeutic target.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>本研究旨在探討腸道共生菌直腸桿菌（*Agathobacter rectalis*, Ar）在大腸直腸癌（CRC）中的作用與分子機制。總體基因體學分析顯示，CRC 患者糞便中的 Ar 豐度顯著降低。動物實驗證實，Ar 能有效減少 Apc min/+ 小鼠的結腸腫瘤數量與體積。代謝組學分析發現，Ar 能產生關鍵代謝物表兒茶素（EGC）。機制上，EGC 可直接結合並穩定 pSREBF2，阻斷 pSREBF2-SCAP 的交互作用，進而抑制 SREBF2 的剪切活化，下調膽固醇合成基因（如 FDPS、PCSK9）的表達並抑制 MAPK 訊號。本研究揭示了 Ar-EGC 微生物-代謝物軸藉由調控膽固醇代謝抑制 CRC 腫瘤生成的新機制，為 CRC 治療提供新策略。</t>
+          <t>本研究旨在探討持續兩年之長新冠（Long COVID）患者的腸道菌群特徵及其致病潛力。透過宏基因組學與代謝體學分析，發現患者腸道菌群多樣性顯著下降，促發炎菌種（如 *Streptococcus salivarius*）增加，而具抗發炎功能的菌種（如 *Faecalibacterium*）則減少；同時，碳水化合物降解與短鏈脂肪酸生成等代謝功能受損。將患者糞便菌群移植至小鼠模型後，成功誘發了肺部與腸道發炎及焦慮行為，並加劇小鼠對肺炎克雷伯氏菌的易感性。本研究證實長新冠患者的腸道菌群失調具有因果效應，足以引發類似長新冠的臨床症狀，顯示調節腸道菌群可能是未來治療長新冠的潛在策略。</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42665998/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42667585/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>42664608</t>
+          <t>42667435</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Application-dependent effects of tea waste biochar on PFAS mobility and N2O and CH4 emissions in agricultural soil.</t>
+          <t>From traditional retting to precision bioprocessing: microbial ecology, enzymatic selectivity, and systems biology of jute retting.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Waste management (New York, N.Y.)</t>
+          <t>Antonie van Leeuwenhoek</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -716,12 +716,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>未提及（僅說明使用盆栽模擬系統「per pot」，未提及具體樣本或盆栽數量）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -729,54 +729,52 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Per- and polyfluoroalkyl substances (PFAS) in agricultural soils can migrate into crops and may alter soil greenhouse gas emissions, yet remediation strategies rarely address these risks simultaneously. This study evaluated tea waste biochar (TWB) produced at 400, 500, and 600 °C and applied at 5-20 g per pot by whole-soil mixing or surface-layer placement in a simulated PFAS-contaminated soil-leachate-plant system. Perfluorooctane sulfonate (PFOS) and perfluorooctanoic acid (PFOA) distributions, nitrous oxide (N2O) and methane (CH4) fluxes, and microbial responses were examined. TWB produced at 500 °C showed the most favorable combination of pore accessibility, surface hydrophobicity, and interfacial charge, with material-associated PFOS and PFOA enrichments of 0.12 and 0.57 μg/g, respectively. Whole-soil mixing with TWB-500 lowered soil and leachate PFAS levels and reduced PFAS concentrations in plant shoots by approximately 36% relative to the contaminated control. TWB treatments also reduced cumulative N2O emissions and enhanced net CH4 uptake. Metagenomic analysis showed lower relative abundances of genes associated with nitrogen fixation, ammonia oxidation, and several N2O-producing pathways, whereas CH4-cycling genes responded differently to the two application methods. Organic fluorine transformation genes were not enriched, indicating that PFAS control mainly resulted from physicochemical retention rather than enhanced microbial defluorination. Overall, TWB-500 can integrate PFAS stabilization with greenhouse gas management, but the optimal placement depends on the remediation objective: whole-soil mixing favors PFAS immobilization, whereas surface-layer application provides greater greenhouse gas mitigation.</t>
+          <t>Jute is one of the world's most important lignocellulosic fibre crops, yet its commercial value remains highly dependent on retting, a biologically mediated fibre extraction process still largely governed by empirical practices and variable environmental conditions. Recent advances in microbial ecology, enzymology, molecular biology, and bioprocess engineering have transformed retting from a traditional post-harvest operation into a controllable lignocellulosic bioconversion process. This review synthesizes current understanding of the structural organization of jute bast fibres, selective degradation of plant cell-wall polymers, microbial succession, extracellular enzyme networks, and physicochemical factors regulating fibre liberation. It highlights the coordinated interactions among cell-wall architecture, microbial communities, enzyme specificity, and environmental conditions that collectively determine retting efficiency and fibre quality. Emerging precision retting strategies, including defined microbial consortia, enzyme-assisted retting, ribbon retting, controlled processing systems, and water-efficient technologies, are critically evaluated for their potential to improve process reproducibility, fibre quality, and environmental sustainability. The review also examines metagenomics, metatranscriptomics, metaproteomics, metabolomics, systems biology, and artificial intelligence as enabling technologies for microbiome-guided process monitoring, predictive modelling, and digital decision support. Furthermore, this review discusses the integration of precision retting within circular bioeconomy frameworks through resource recovery, pollution mitigation, climate-resilient processing, and lignocellulosic biorefineries. Key knowledge gaps, including limited understanding of microbial interactions, lack of standardized microbial consortia, insufficient process-monitoring tools, fragmented multi-omics datasets, and challenges in industrial scale-up, are identified. Overall, this review presents a systems-level framework for advancing jute retting toward standardized, predictive, and environmentally sustainable precision bioprocessing.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>本研究旨在評估茶渣生物炭（TWB）在模擬的PFAS污染土壤-滲濾液-植物系統中，對於抑制全氟和多氟烷基物質（PFAS）遷移及減少溫室氣體（N2O和CH4）排放的雙重效應。研究發現，在500 °C下製備的TWB-500效果最佳。若將其均勻混合於全土中，可使植物地上部的PFAS濃度降低約36%，並顯著降低土壤和滲濾液中的PFAS含量。此外，TWB處理還減少了N2O累積排放並促進CH4淨吸收。總體基因體學分析顯示，與氮循環相關的基因豐度有所下降，解釋了N2O排放減少的機制；而有機氟降解基因並未富集，證實PFAS的控制主要源於物理化學阻控而非微生物去氟作用。此研究證明TWB-500能有效整合PFAS固化與溫室氣體管理，且施用方式（全土混合或表層施作）可依環境整治優先目標進行客製化調整。</t>
+          <t>本文針對黃麻「浸漬法」（retting）進行系統性綜述，旨在將傳統經驗式的纖維提取過程，轉型為可控的精準生物加工技術。研究探討了植物細胞壁結構、微生物演替機制及胞外酶系統如何共同影響纖維解離與品質。作者強調，透過整合宏基因組學、宏轉錄組學、宏蛋白質組學與代謝體學等多體學技術，結合人工智慧模型，能有效提升浸漬過程的監測能力與可預測性。該研究對於推動循環生物經濟具有重大意義，透過標準化微生物群落與精準生物加工策略，不僅能優化纖維生產效率與品質，亦能解決環境污染問題，為黃麻產業實現永續與數位化轉型提供了理論框架與技術路徑。</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42664608/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42667435/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>42663459</t>
+          <t>42663468</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Clinical application of BALF-mNGS in immunocompromised and immunocompetent patients with suspected invasive pulmonary aspergillosis: differentiating infection from colonization, microbiome features, and clinical impact.</t>
+          <t>Genomes of cressdnaviricots and phixviricots in a freshwater lake sample from Arizona, USA.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Microbiology spectrum</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
+          <t>Microbiology resource announcements</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>metagenomics, small genome</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>178位疑似侵襲性肺麴菌病（IPA）患者（包含77位免疫功能低下患者與101位免疫功能正常患者）</t>
+          <t>1 個 40 ml 的淡水湖泊水樣</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -784,12 +782,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Invasive pulmonary aspergillosis (IPA) not only causes high morbidity and mortality, especially in immunocompromised patients, but also occurs in immunocompetent individuals. Differentiating infection from colonization is challenging, and bronchoalveolar lavage fluid metagenomic next-generation sequencing (BALF-mNGS) may aid diagnosis, microbiome profiling, and clinical assessment. We retrospectively analyzed patients with suspected IPA who underwent BALF-mNGS between December 2021 and March 2025. Patients were classified by immune status. IPA diagnosis was based on EORTC/MSGERC 2020 criteria in immunocompromised patients, while immunocompetent cases were adjudicated using an integrated clinical, radiological, and microbiological assessment. A total of 178 patients were finally included and classified according to immune status into an immunocompromised group (n = 77) and an immunocompetent group (n = 101). Aspergillus_ reads per ten million (RPTM) values were significantly higher in infection versus colonization cases in both groups, with optimal cut-offs of 24 (gray zone: 22-60) for the immunocompromised group and 33 (gray zone: 17-48) for the immunocompetent group. Microbiome analysis revealed distinct community structures between infection and colonization groups, with Aspergillus remaining significantly enriched after false discovery rate (FDR) correction in immunocompromised patients, while no taxa remained significant after FDR correction in immunocompetent patients. BALF-mNGS guided antifungal therapy, avoiding unnecessary treatment in colonized patients, and higher Aspergillus_RPTM was associated with increased 90-day mortality in immunocompromised patients. BALF-mNGS may accurately distinguish Aspergillus infection from colonization and reveal microbial shifts, particularly in immunocompromised patients. It can guide targeted antifungal therapy, avoid unnecessary treatment, and higher Aspergillus_RPTM was associated with 90-day mortality in immunocompromised patients, suggesting its potential value for risk stratification.IMPORTANCEBALF-mNGS with quantitative thresholds improves differentiation between Aspergillus infection and colonization. It reveals distinct lung microbiome patterns under different immune statuses, extending beyond simple pathogen detection. Higher Aspergillus burden is associated with worse outcomes in immunocompromised patients, suggesting its potential value for risk stratification.</t>
+          <t>A viral metagenomic analysis of a 40 ml water sample from a small freshwater lake near Flagstaff, Arizona, USA, resulted in the identification of 295 circular viral genome sequences. Of these, 126 are members of Cressdnaviricota and 169 of Phixviricota phyla.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>本研究旨在評估支氣管肺泡灌洗液總體基因體次世代定序（BALF-mNGS）在區分疑似侵襲性肺麴菌病（IPA）患者「感染」與「定植」的臨床價值，並探討其肺部微生態特徵。研究納入178位患者，發現感染者的麴菌相對豐度（RPTM）顯著高於定植者，並針對免疫功能低下與正常組分別訂定出24與33的最佳臨界值。微生態分析顯示兩組具有不同的菌群結構。臨床上，BALF-mNGS能有效引導抗真菌治療，避免定植患者過度治療；而在免疫功能低下組中，高麴菌RPTM值與90天高死亡率顯著相關。此技術不僅能精準診斷，更具備患者預後風險分層的潛力。</t>
+          <t>本研究旨在探討美國亞利桑那州 Flagstaff 附近一處小型淡水湖泊中的病毒多樣性。研究團隊對 40 毫升的水樣進行病毒總體基因體學（viral metagenomics）分析，成功鑑定並組裝出 295 個環狀病毒基因體序列。在這些病毒中，有 126 個屬於 Cressdnaviricota 門（環狀單鏈 DNA 病毒），另有 169 個屬於 Phixviricota 門（微小噬菌體相關病毒）。此研究的科學意義在於顯著擴充了淡水生態系統中這兩大病毒門的基因體數據，並證實即使在極少量的環境水樣中，也蘊藏著極高多樣性且未知的病毒資源，有助於深化對淡水微生態系統及病毒演化多樣性的理解。</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -799,39 +797,35 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42663459/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42663468/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>42663468</t>
+          <t>42665077</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Genomes of cressdnaviricots and phixviricots in a freshwater lake sample from Arizona, USA.</t>
+          <t>Metagenomic Characterization of Potential Exposure to Genetic Hazards at the Interface Between Grazing Livestock and Przewalski's Gazelle.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Microbiology resource announcements</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
+          <t>Environmental pollution (Barking, Essex : 1987)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>metagenomics, small genome</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1 個 40 ml 的淡水湖泊水樣</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -839,12 +833,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>A viral metagenomic analysis of a 40 ml water sample from a small freshwater lake near Flagstaff, Arizona, USA, resulted in the identification of 295 circular viral genome sequences. Of these, 126 are members of Cressdnaviricota and 169 of Phixviricota phyla.</t>
+          <t>Livestock and endangered wildlife increasingly share grazing landscapes, yet the sources, mobility-associated contexts, and bacterial hosts of livestock-associated genetic hazards in wildlife microbiomes remain poorly resolved. We analyzed metagenomes from yak, Tibetan sheep, Przewalski's gazelle, and local topsoil within an Acquired Genetic Risk (AGR) conceptual framework integrating genetic hazard burden, compositional source attribution, mobility-associated evidence, and bacterial genomic context. MRGs and Rank I and Rank III ARGs were more abundant in livestock than in Przewalski's gazelle, whereas VF abundance was highest in yak. FEAST attributed approximately 64% of the Przewalski's gazelle resistome composition to the two livestock source profiles, less than 1% to sampled topsoil, and approximately 36% remained unassigned. MGE profiles were associated with ARGs, MRGs, and VFs, while tnpA ranked highest in random forest models and was associated with total ARG abundance (R2 = 0.618). Short-read contigs containing hazard genes and MGE markers provided localized mobility-associated sequence context. Genome-resolved analysis identified distinct bacterial contexts: TS.Bin143, an Escherichia coli MAG from Tibetan sheep, contained ARGs, MRGs, VFs, tnpA, and IS91, whereas PG.Bin275, a Hylemonella sp. MAG from Przewalski's gazelle, contained tnpA. These findings extend wildlife resistome assessment beyond abundance profiling toward source attribution, mobility-associated sequence context, and bacterial host resolution, supporting multilevel surveillance of genetic hazard exposure at livestock-wildlife interfaces.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>本研究旨在探討美國亞利桑那州 Flagstaff 附近一處小型淡水湖泊中的病毒多樣性。研究團隊對 40 毫升的水樣進行病毒總體基因體學（viral metagenomics）分析，成功鑑定並組裝出 295 個環狀病毒基因體序列。在這些病毒中，有 126 個屬於 Cressdnaviricota 門（環狀單鏈 DNA 病毒），另有 169 個屬於 Phixviricota 門（微小噬菌體相關病毒）。此研究的科學意義在於顯著擴充了淡水生態系統中這兩大病毒門的基因體數據，並證實即使在極少量的環境水樣中，也蘊藏著極高多樣性且未知的病毒資源，有助於深化對淡水微生態系統及病毒演化多樣性的理解。</t>
+          <t>本研究旨在評估放牧家畜與瀕危野生普氏原羚接觸介面上的遺傳危害（如抗藥性基因 ARG、金屬耐受基因 MRG 與毒力因子 VF）暴露風險。研究利用總體基因體學分析氛牛、藏羊、普氏原羚及當地表土，結果顯示家畜體內的 MRG 和高風險 ARG 豐度顯著高於普氏原羚。來源追蹤分析（FEAST）指出，普氏原羚約 64% 的抗藥組組成可歸因於這兩種家畜，僅不到 1% 來自土壤。此外，研究透過基因組解析定位了攜帶危害基因與移動遺傳因子的細菌宿主。本研究不僅闡明了遺傳危害的來源與傳播關聯，也為野生動物與家畜接觸介面的多層級生物安全監測提供了重要科學依據。</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -854,39 +848,35 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42663468/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42665077/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>42663694</t>
+          <t>42664954</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Comparative Analysis of Different Anodic Inoculum in Microbial Fuel Cell for Efficient Methylene Blue Dye Degradation.</t>
+          <t>Lactobacillus salivarius potentiates gastrointestinal cancer immunotherapy through its metabolite chenodeoxycholic acid.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Current microbiology</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2.6</t>
-        </is>
-      </c>
+          <t>Cell reports. Medicine</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3種不同的接種源（海洋沉積物、河口沉積物、厭氧污泥）</t>
+          <t>278 位胃腸道癌症患者及同基因腫瘤小鼠模型</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -894,12 +884,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>This study investigates three different inoculum sources in dual-chamber microbial fuel cells (MFCs), such as Marine Sediment (MFC-MS), Estuary Sediment (MFC-ES), and Anaerobic Sludge (MFC-AS), to compare the efficacy for Methylene Blue (MB) dye degradation and electricity generation. All the MFCs were operated under identical conditions in batch mode using synthetic wastewater containing 3000 mg/L COD made using sodium acetate. The electrochemical study reveals that MFC inoculated with marine sediment achieved maximum power density of 35 mW/m² followed by anaerobic sludge (31 mW/m²) and estuary sediment (25 mW/m²). Statistical analysis was employed to evaluate performance differences among the systems and to support result interpretation. Maximum COD removal efficiency of 75% was obtained by MFC-AS, and coulombic efficiency (CE) was higher for MFC-MS with 25%. Maximum decolorization efficiency was noted in MFC with anaerobic sludge, which obtained 96% decolorization over 96 h. Comparative and trend-based statistical evaluation confirmed the superior treatment performance of MFC-assisted systems. The phytotoxicity study revealed that the toxicity effect of dye wastewater was reduced to its maximum after treatment in the MFC system. The dominant performance of MFC-MS is due to the efficiency of the major electrogenic bacteria concentrated in the inoculum. The functional annotation using the data obtained from metagenomics reveals the presence and role of various enzymes and pathways involved.</t>
+          <t>Immune checkpoint inhibitor therapy has improved gastrointestinal (GI) cancer management; however, many patients exhibit resistance. Although gut microbiota influences immunotherapeutic responses, the underlying mechanisms remain unclear. Metagenomic analysis of 278 GI cancer patients reveals that Lactobacillus salivarius (L. salivarius) is enriched in responders and enhances anti-PD-1 efficacy in syngeneic tumor models by increasing the infiltration of antitumor M1-like macrophages and CD8+ T cells and enhancing CD8+ T cell effector function. L. salivarius-associated chenodeoxycholic acid (CDCA) is identified as a functional metabolite. CDCA recapitulates the antitumor effects of L. salivarius and significantly improves anti-PD-1 efficacy in vivo, an effect attenuated by depleting macrophages or CD8+ T cells. Mechanistically, CDCA-induced reactive oxygen species triggers immunogenic cell death in tumor cells and polarizes macrophages toward antitumor M1 phenotype, activating CD8+ T cell antitumor immunity. These findings identify L. salivarius and its associated metabolite CDCA as a promising adjuvant for potentiating immunotherapy in GI cancers.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>本研究旨在比較雙腔式微生物燃料電池（MFC）中，三種不同接種源（海洋沉積物、河口沉積物、厭氧污泥）在降解亞甲藍染料與產電的效率。結果顯示，海洋沉積物系統具最高的功率密度（35 mW/m²）與庫倫效率（25%）；厭氧污泥系統則有最佳的化學需氧量去除率（75%）與脫色率（96%）。處理後廢水的植物毒性顯著降低。宏基因組學分析揭示了關鍵產電菌的分布及參與降解與發電的酶和代謝途徑。本研究證實了不同接種源在 MFC 污水處理與生物發電的潛力，並闡明了其微生物學機制。</t>
+          <t>本研究旨在探討腸道菌群影響胃腸道（GI）癌症免疫治療反應的具體機制。透過對 278 位 GI 癌症患者的總體基因體分析，發現唾液乳桿菌（*Lactobacillus salivarius*）在治療有反應的患者體內顯著富集。於小鼠模型中，該菌能增加抗腫瘤 M1 型巨噬細胞與 CD8+ T 細胞的浸潤，顯著提升抗 PD-1 療效。研究進一步證實，該菌的代謝物鵝去氧膽酸（CDCA）為關鍵功能分子，能透過誘導活性氧（ROS）引發腫瘤細胞的免疫原性死亡，並促進巨噬細胞向 M1 型極化，從而激活 CD8+ T 細胞的抗腫瘤免疫反應。本研究揭示了唾液乳桿菌及其代謝物 CDCA 作為增強 GI 癌症免疫治療活性佐劑的臨床潛力。</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -909,7 +899,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42663694/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42664954/</t>
         </is>
       </c>
     </row>
@@ -929,10 +919,8 @@
           <t>PLoS genetics</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>3.7</t>
-        </is>
+      <c r="D10" t="n">
+        <v>3.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -971,32 +959,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>42664954</t>
+          <t>42663694</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lactobacillus salivarius potentiates gastrointestinal cancer immunotherapy through its metabolite chenodeoxycholic acid.</t>
+          <t>Comparative Analysis of Different Anodic Inoculum in Microbial Fuel Cell for Efficient Methylene Blue Dye Degradation.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cell reports. Medicine</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Current microbiology</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>metagenomics, metabolomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>278 位胃腸道癌症患者及同基因腫瘤小鼠模型</t>
+          <t>3種不同的接種源（海洋沉積物、河口沉積物、厭氧污泥）</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -1004,12 +990,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Immune checkpoint inhibitor therapy has improved gastrointestinal (GI) cancer management; however, many patients exhibit resistance. Although gut microbiota influences immunotherapeutic responses, the underlying mechanisms remain unclear. Metagenomic analysis of 278 GI cancer patients reveals that Lactobacillus salivarius (L. salivarius) is enriched in responders and enhances anti-PD-1 efficacy in syngeneic tumor models by increasing the infiltration of antitumor M1-like macrophages and CD8+ T cells and enhancing CD8+ T cell effector function. L. salivarius-associated chenodeoxycholic acid (CDCA) is identified as a functional metabolite. CDCA recapitulates the antitumor effects of L. salivarius and significantly improves anti-PD-1 efficacy in vivo, an effect attenuated by depleting macrophages or CD8+ T cells. Mechanistically, CDCA-induced reactive oxygen species triggers immunogenic cell death in tumor cells and polarizes macrophages toward antitumor M1 phenotype, activating CD8+ T cell antitumor immunity. These findings identify L. salivarius and its associated metabolite CDCA as a promising adjuvant for potentiating immunotherapy in GI cancers.</t>
+          <t>This study investigates three different inoculum sources in dual-chamber microbial fuel cells (MFCs), such as Marine Sediment (MFC-MS), Estuary Sediment (MFC-ES), and Anaerobic Sludge (MFC-AS), to compare the efficacy for Methylene Blue (MB) dye degradation and electricity generation. All the MFCs were operated under identical conditions in batch mode using synthetic wastewater containing 3000 mg/L COD made using sodium acetate. The electrochemical study reveals that MFC inoculated with marine sediment achieved maximum power density of 35 mW/m² followed by anaerobic sludge (31 mW/m²) and estuary sediment (25 mW/m²). Statistical analysis was employed to evaluate performance differences among the systems and to support result interpretation. Maximum COD removal efficiency of 75% was obtained by MFC-AS, and coulombic efficiency (CE) was higher for MFC-MS with 25%. Maximum decolorization efficiency was noted in MFC with anaerobic sludge, which obtained 96% decolorization over 96 h. Comparative and trend-based statistical evaluation confirmed the superior treatment performance of MFC-assisted systems. The phytotoxicity study revealed that the toxicity effect of dye wastewater was reduced to its maximum after treatment in the MFC system. The dominant performance of MFC-MS is due to the efficiency of the major electrogenic bacteria concentrated in the inoculum. The functional annotation using the data obtained from metagenomics reveals the presence and role of various enzymes and pathways involved.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>本研究旨在探討腸道菌群影響胃腸道（GI）癌症免疫治療反應的具體機制。透過對 278 位 GI 癌症患者的總體基因體分析，發現唾液乳桿菌（*Lactobacillus salivarius*）在治療有反應的患者體內顯著富集。於小鼠模型中，該菌能增加抗腫瘤 M1 型巨噬細胞與 CD8+ T 細胞的浸潤，顯著提升抗 PD-1 療效。研究進一步證實，該菌的代謝物鵝去氧膽酸（CDCA）為關鍵功能分子，能透過誘導活性氧（ROS）引發腫瘤細胞的免疫原性死亡，並促進巨噬細胞向 M1 型極化，從而激活 CD8+ T 細胞的抗腫瘤免疫反應。本研究揭示了唾液乳桿菌及其代謝物 CDCA 作為增強 GI 癌症免疫治療活性佐劑的臨床潛力。</t>
+          <t>本研究旨在比較雙腔式微生物燃料電池（MFC）中，三種不同接種源（海洋沉積物、河口沉積物、厭氧污泥）在降解亞甲藍染料與產電的效率。結果顯示，海洋沉積物系統具最高的功率密度（35 mW/m²）與庫倫效率（25%）；厭氧污泥系統則有最佳的化學需氧量去除率（75%）與脫色率（96%）。處理後廢水的植物毒性顯著降低。宏基因組學分析揭示了關鍵產電菌的分布及參與降解與發電的酶和代謝途徑。本研究證實了不同接種源在 MFC 污水處理與生物發電的潛力，並闡明了其微生物學機制。</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1019,34 +1005,34 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42664954/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42663694/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>42665077</t>
+          <t>42665998</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Metagenomic Characterization of Potential Exposure to Genetic Hazards at the Interface Between Grazing Livestock and Przewalski's Gazelle.</t>
+          <t>Agathobacter rectalis suppresses colorectal tumorigenesis via an epigallocatechin-SREBF2 axis controlling cholesterol metabolism.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Environmental pollution (Barking, Essex : 1987)</t>
+          <t>Gut microbes</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1059,12 +1045,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Livestock and endangered wildlife increasingly share grazing landscapes, yet the sources, mobility-associated contexts, and bacterial hosts of livestock-associated genetic hazards in wildlife microbiomes remain poorly resolved. We analyzed metagenomes from yak, Tibetan sheep, Przewalski's gazelle, and local topsoil within an Acquired Genetic Risk (AGR) conceptual framework integrating genetic hazard burden, compositional source attribution, mobility-associated evidence, and bacterial genomic context. MRGs and Rank I and Rank III ARGs were more abundant in livestock than in Przewalski's gazelle, whereas VF abundance was highest in yak. FEAST attributed approximately 64% of the Przewalski's gazelle resistome composition to the two livestock source profiles, less than 1% to sampled topsoil, and approximately 36% remained unassigned. MGE profiles were associated with ARGs, MRGs, and VFs, while tnpA ranked highest in random forest models and was associated with total ARG abundance (R2 = 0.618). Short-read contigs containing hazard genes and MGE markers provided localized mobility-associated sequence context. Genome-resolved analysis identified distinct bacterial contexts: TS.Bin143, an Escherichia coli MAG from Tibetan sheep, contained ARGs, MRGs, VFs, tnpA, and IS91, whereas PG.Bin275, a Hylemonella sp. MAG from Przewalski's gazelle, contained tnpA. These findings extend wildlife resistome assessment beyond abundance profiling toward source attribution, mobility-associated sequence context, and bacterial host resolution, supporting multilevel surveillance of genetic hazard exposure at livestock-wildlife interfaces.</t>
+          <t>Beneficial effects of the gut commensal Agathobacter rectalis (Ar) are reported in diseases, yet its role in colorectal cancer (CRC) remains unclear. Here, metagenomic analysis revealed consistent fecal Ar depletion across CRC cohorts. In Apc min/+ mice, Ar inhibited colon tumorigenesis, reducing tumor number and volume versus E. coli and PBS controls. LC-MS/MS metabolomics showed decreased fecal cholesterol and altered lipid/cholesterol pathways after Ar treatment. In vitro, Ar-conditioned medium suppressed CRC cell growth, clonogenicity, migration, and cell cycle progression. LC-MS/MS identified (-)-epigallocatechin (EGC) as an Ar-derived metabolite absent in control bacteria. EGC recapitulated Ar-mediated anti-CRC effects in vitro and in vivo, with metabolic changes linked to lipid/cholesterol pathways. Transcriptomics showed that EGC suppressed SREBP signaling, cholesterol metabolism, and MAPK pathways. Mechanistically, EGC reduced nuclear SREBF2 and its transcriptional activity, downregulated cholesterol synthesis/metabolism genes, including FDPS and PCSK9, and suppressed MAPK signaling. Molecular docking suggested that EGC may bind pSREBF2 or SCAP. Cellular thermal shift assay revealed that EGC interacts with and stabilizes pSREBF2, but not SCAP. Co-immunoprecipitation demonstrated that EGC reduces pSREBF2-SCAP interaction, thereby inhibiting SCAP-mediated SREBF2 cleavage activation. Together, these findings define an Ar-EGC microbe-metabolite axis and support Ar/EGC-based interventions targeting cholesterol metabolism in CRC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>本研究旨在評估放牧家畜與瀕危野生普氏原羚接觸介面上的遺傳危害（如抗藥性基因 ARG、金屬耐受基因 MRG 與毒力因子 VF）暴露風險。研究利用總體基因體學分析氛牛、藏羊、普氏原羚及當地表土，結果顯示家畜體內的 MRG 和高風險 ARG 豐度顯著高於普氏原羚。來源追蹤分析（FEAST）指出，普氏原羚約 64% 的抗藥組組成可歸因於這兩種家畜，僅不到 1% 來自土壤。此外，研究透過基因組解析定位了攜帶危害基因與移動遺傳因子的細菌宿主。本研究不僅闡明了遺傳危害的來源與傳播關聯，也為野生動物與家畜接觸介面的多層級生物安全監測提供了重要科學依據。</t>
+          <t>本研究旨在探討腸道共生菌 *Agathobacter rectalis* (Ar) 在大腸直腸癌 (CRC) 中的作用。總體基因體分析顯示 CRC 患者糞便中 Ar 顯著減少；動物實驗證實 Ar 能抑制小鼠大腸腫瘤生長。代謝組學分析進一步純化出 Ar 的關鍵代謝物「表沒食子兒茶素」(EGC)。機制上，EGC 會與 pSREBF2 結合，阻斷其與 SCAP 的交互作用，進而抑制 SREBF2 的活化、降低膽固醇合成與代謝基因表現，並抑制 MAPK 訊號通路。本研究揭示了 Ar-EGC 微生物-代謝物軸抑制腫瘤的機制，為靶向膽固醇代謝的 CRC 防治提供了新策略。</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1074,30 +1060,28 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42665077/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42665998/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>42665338</t>
+          <t>42663459</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PREVENT 1, a nationwide Swedish infant cohort for longitudinal gut microbiome profiling and early-life health outcomes: cohort profile.</t>
+          <t>Clinical application of BALF-mNGS in immunocompromised and immunocompetent patients with suspected invasive pulmonary aspergillosis: differentiating infection from colonization, microbiome features, and clinical impact.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BMJ open</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
+          <t>Microbiology spectrum</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1106,7 +1090,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>253 位嬰兒（收集 253 份基線糞便檢體，其中 250 位提供至少 2 次檢體，241 位提供全部 3 次檢體）</t>
+          <t>178位疑似侵襲性肺麴菌病（IPA）患者（包含77位免疫功能低下患者與101位免疫功能正常患者）</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -1114,12 +1098,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>PREVENT 1 is a nationwide, prospective Swedish infant cohort established to characterise gut microbiome development during the first 2 years of life and to relate microbial trajectories to feeding, infections, growth and everyday well-being. The study integrates repeated infant stool sampling with shotgun metagenomics analysis with aligned parental questionnaires, stool photographs and infant cry recordings collected at three approximately 3-month intervals for each infant. Families were recruited nationwide in Sweden from September 2023 through targeted digital channels. Eligible participants were term-born infants residing in Sweden and aged &lt;1 year at enrolment. Baseline questionnaire data and stool samples were collected from 253 infants. Parents completed questionnaires covering socio-demographic characteristics and health, pregnancy and delivery, postnatal factors, infant environment, feeding and growth, infections and other health outcomes, gastrointestinal symptoms and everyday well-being. Retention was high, with 248 families completing at least one follow-up questionnaire at Phase 2 and 243 at Phase 3. For stool samples, 250 infants provided at least two samples and 241 provided all three. At enrolment, 42.3% of infants were older than 7 months, 73.9% had weight-for-length z-scores in the normal range and exclusive breastfeeding at 4 months was reported for 58.9%. Three-phase sample and questionnaire data collection was completed in December 2024. Future analyses will examine microbiome features, resistome profiles and functional pathways in relation to antibiotic exposure, feeding, growth and infant health outcomes. Subject to ethical approval and participant consent, follow-up may include further stool collection and Swedish register linkage. NCT06285630.</t>
+          <t>Invasive pulmonary aspergillosis (IPA) not only causes high morbidity and mortality, especially in immunocompromised patients, but also occurs in immunocompetent individuals. Differentiating infection from colonization is challenging, and bronchoalveolar lavage fluid metagenomic next-generation sequencing (BALF-mNGS) may aid diagnosis, microbiome profiling, and clinical assessment. We retrospectively analyzed patients with suspected IPA who underwent BALF-mNGS between December 2021 and March 2025. Patients were classified by immune status. IPA diagnosis was based on EORTC/MSGERC 2020 criteria in immunocompromised patients, while immunocompetent cases were adjudicated using an integrated clinical, radiological, and microbiological assessment. A total of 178 patients were finally included and classified according to immune status into an immunocompromised group (n = 77) and an immunocompetent group (n = 101). Aspergillus_ reads per ten million (RPTM) values were significantly higher in infection versus colonization cases in both groups, with optimal cut-offs of 24 (gray zone: 22-60) for the immunocompromised group and 33 (gray zone: 17-48) for the immunocompetent group. Microbiome analysis revealed distinct community structures between infection and colonization groups, with Aspergillus remaining significantly enriched after false discovery rate (FDR) correction in immunocompromised patients, while no taxa remained significant after FDR correction in immunocompetent patients. BALF-mNGS guided antifungal therapy, avoiding unnecessary treatment in colonized patients, and higher Aspergillus_RPTM was associated with increased 90-day mortality in immunocompromised patients. BALF-mNGS may accurately distinguish Aspergillus infection from colonization and reveal microbial shifts, particularly in immunocompromised patients. It can guide targeted antifungal therapy, avoid unnecessary treatment, and higher Aspergillus_RPTM was associated with 90-day mortality in immunocompromised patients, suggesting its potential value for risk stratification.IMPORTANCEBALF-mNGS with quantitative thresholds improves differentiation between Aspergillus infection and colonization. It reveals distinct lung microbiome patterns under different immune statuses, extending beyond simple pathogen detection. Higher Aspergillus burden is associated with worse outcomes in immunocompromised patients, suggesting its potential value for risk stratification.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>本研究建立瑞典全國性嬰兒追蹤世代「PREVENT 1」，旨在透過縱向總體基因體學分析，描繪嬰兒出生後前兩年的腸道菌相發育軌跡，並探討其與餵養、生長及感染等健康指標的關聯。研究成功招募253名足月嬰兒，並在三個時間點重複收集糞便檢體與問卷，受試者維持率極高（241名嬰兒提供全部三次檢體）。此世代研究提供高質量的臨床與多體學數據，未來將深入分析抗生素暴露與飲食如何形塑嬰兒腸道菌群、抗藥性基因組及代謝途徑，對理解早期生命健康極具臨床與科學價值。</t>
+          <t>本研究旨在評估支氣管肺泡灌洗液總體基因體次世代定序（BALF-mNGS）在區分疑似侵襲性肺麴菌病（IPA）患者「感染」與「定植」的臨床價值，並探討其肺部微生態特徵。研究納入178位患者，發現感染者的麴菌相對豐度（RPTM）顯著高於定植者，並針對免疫功能低下與正常組分別訂定出24與33的最佳臨界值。微生態分析顯示兩組具有不同的菌群結構。臨床上，BALF-mNGS能有效引導抗真菌治療，避免定植患者過度治療；而在免疫功能低下組中，高麴菌RPTM值與90天高死亡率顯著相關。此技術不僅能精準診斷，更具備患者預後風險分層的潛力。</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1129,39 +1113,35 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42665338/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42663459/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>42666033</t>
+          <t>42664608</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gut Microbiota-Isoallolithocholic Acid Crosstalk Promotes Calcium Oxalate Kidney Stone Formation via PARP1-Mediated Parthanatos.</t>
+          <t>Application-dependent effects of tea waste biochar on PFAS mobility and N2O and CH4 emissions in agricultural soil.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Advanced science (Weinheim, Baden-Wurttemberg, Germany)</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>Waste management (New York, N.Y.)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>16S, metagenomics, metabolomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（僅說明使用盆栽模擬系統「per pot」，未提及具體樣本或盆栽數量）</t>
         </is>
       </c>
       <c r="G14" t="b">
@@ -1169,12 +1149,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Bile acids have been implicated in calcium oxalate (CaOx) nephrolithiasis. Here, we employ multi-omics approaches to identify isoallolithocholic acid (isoalloLCA) as the key bile acid elevated in the feces, serum, kidney, and urine of CaOx rats, confirmed by spatial metabolomics. 16S sequencing and metagenomic analyses indicate that elevated isoalloLCA levels in CaOx rats or individuals are likely of microbial origin. Mechanistically, isoalloLCA binds to PARP1 via specific molecular interactions validated by surface plasmon resonance and cellular thermal shift assays. Knockdown of PARP1 by adeno-associated virus microinjection or pharmacological inhibition with PARP1 inhibitor AZD5305 significantly attenuates isoalloLCA-mediated crystal deposition, renal tubular injury, and mitochondrial functional impairment in both the CaOx rat and mouse models. Furthermore, the antibiotic-mediated depletion of the gut microbiota in mice markedly reduced isoalloLCA levels, whereas fecal microbiota transplantationut contributes to isoalloLCA-mediated CaOx stone formation, demonstrating a causal link between gut microbiota and isoalloLCA. In vitro, isoalloLCA promoted oxalate-induced renal tubular epithelial cell injury and parthanatos via targeting PARP1, including DNA damage, excessive PARP1 activation, PAR accumulation, mitochondrial damage, nuclear translocation of AIF and MIF. These findings establish the microbiota-isoalloLCA-PARP1-parthanatos axis in CaOx nephrolithiasis and identify PARP1 as a promising therapeutic target for kidney stone management.</t>
+          <t>Per- and polyfluoroalkyl substances (PFAS) in agricultural soils can migrate into crops and may alter soil greenhouse gas emissions, yet remediation strategies rarely address these risks simultaneously. This study evaluated tea waste biochar (TWB) produced at 400, 500, and 600 °C and applied at 5-20 g per pot by whole-soil mixing or surface-layer placement in a simulated PFAS-contaminated soil-leachate-plant system. Perfluorooctane sulfonate (PFOS) and perfluorooctanoic acid (PFOA) distributions, nitrous oxide (N2O) and methane (CH4) fluxes, and microbial responses were examined. TWB produced at 500 °C showed the most favorable combination of pore accessibility, surface hydrophobicity, and interfacial charge, with material-associated PFOS and PFOA enrichments of 0.12 and 0.57 μg/g, respectively. Whole-soil mixing with TWB-500 lowered soil and leachate PFAS levels and reduced PFAS concentrations in plant shoots by approximately 36% relative to the contaminated control. TWB treatments also reduced cumulative N2O emissions and enhanced net CH4 uptake. Metagenomic analysis showed lower relative abundances of genes associated with nitrogen fixation, ammonia oxidation, and several N2O-producing pathways, whereas CH4-cycling genes responded differently to the two application methods. Organic fluorine transformation genes were not enriched, indicating that PFAS control mainly resulted from physicochemical retention rather than enhanced microbial defluorination. Overall, TWB-500 can integrate PFAS stabilization with greenhouse gas management, but the optimal placement depends on the remediation objective: whole-soil mixing favors PFAS immobilization, whereas surface-layer application provides greater greenhouse gas mitigation.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>本研究旨在探討腸道菌群及其代謝物在草酸鈣（CaOx）腎結石形成中的作用機制。研究利用多組學技術（16S定序、宏基因組學與空間代謝組學），證實源自腸道菌群的代謝物「異別石膽酸（isoalloLCA）」在草酸鈣大鼠及患者體內顯著升高。機制上，isoalloLCA能與PARP1蛋白特異性結合，引發DNA損傷與粒線體受損，進而促進腎小管上皮細胞發生PARP1介導的「守護者細胞凋亡（parthanatos）」與結晶沉積。動物實驗證實，清除腸道菌或抑制PARP1活性（如使用AZD5305）可顯著減輕腎損傷。本研究揭示了「腸道菌群-isoalloLCA-PARP1-parthanatos」軸在腎結石病理中的關鍵角色，並指出PARP1為具潛力的臨床治療靶點。</t>
+          <t>本研究旨在評估茶渣生物炭（TWB）在模擬的PFAS污染土壤-滲濾液-植物系統中，對於抑制全氟和多氟烷基物質（PFAS）遷移及減少溫室氣體（N2O和CH4）排放的雙重效應。研究發現，在500 °C下製備的TWB-500效果最佳。若將其均勻混合於全土中，可使植物地上部的PFAS濃度降低約36%，並顯著降低土壤和滲濾液中的PFAS含量。此外，TWB處理還減少了N2O累積排放並促進CH4淨吸收。總體基因體學分析顯示，與氮循環相關的基因豐度有所下降，解釋了N2O排放減少的機制；而有機氟降解基因並未富集，證實PFAS的控制主要源於物理化學阻控而非微生物去氟作用。此研究證明TWB-500能有效整合PFAS固化與溫室氣體管理，且施用方式（全土混合或表層施作）可依環境整治優先目標進行客製化調整。</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1184,30 +1164,28 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42666033/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42664608/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>42660108</t>
+          <t>42665338</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Group C Orthobunyavirus Infection in a Patient from the Amazon Putumayo Region of Colombia During an Oropouche Fever Epidemic.</t>
+          <t>PREVENT 1, a nationwide Swedish infant cohort for longitudinal gut microbiome profiling and early-life health outcomes: cohort profile.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>The American journal of tropical medicine and hygiene</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>BMJ open</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1216,7 +1194,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1位急性發熱疾病患者（單一病例）</t>
+          <t>253 位嬰兒（收集 253 份基線糞便檢體，其中 250 位提供至少 2 次檢體，241 位提供全部 3 次檢體）</t>
         </is>
       </c>
       <c r="G15" t="b">
@@ -1224,52 +1202,54 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Orthobunyaviruses, one of the largest and most diverse genera of viruses, include numerous reassortant viruses and present diagnostic challenges due to similar clinical presentations with other arboviral infections. The detection and isolation of a group C orthobunyavirus from a patient with acute febrile illness from Puerto Ospina, Putumayo Department, Colombia during the 2023-2024 Latin American Oropouche fever regional outbreaks are reported in the present study. Using a vertebrate virus-focused metagenomics sequencing approach with VirCapSeq-VERT, a virus related to the Caraparu complex was identified, and a virus isolate was obtained. Although limited to a single case and without serological or longitudinal clinical confirmation, these findings underscore the value of unbiased molecular approaches for unresolved febrile illness diagnosis in endemic settings such as the Amazon basin.</t>
+          <t>PREVENT 1 is a nationwide, prospective Swedish infant cohort established to characterise gut microbiome development during the first 2 years of life and to relate microbial trajectories to feeding, infections, growth and everyday well-being. The study integrates repeated infant stool sampling with shotgun metagenomics analysis with aligned parental questionnaires, stool photographs and infant cry recordings collected at three approximately 3-month intervals for each infant. Families were recruited nationwide in Sweden from September 2023 through targeted digital channels. Eligible participants were term-born infants residing in Sweden and aged &lt;1 year at enrolment. Baseline questionnaire data and stool samples were collected from 253 infants. Parents completed questionnaires covering socio-demographic characteristics and health, pregnancy and delivery, postnatal factors, infant environment, feeding and growth, infections and other health outcomes, gastrointestinal symptoms and everyday well-being. Retention was high, with 248 families completing at least one follow-up questionnaire at Phase 2 and 243 at Phase 3. For stool samples, 250 infants provided at least two samples and 241 provided all three. At enrolment, 42.3% of infants were older than 7 months, 73.9% had weight-for-length z-scores in the normal range and exclusive breastfeeding at 4 months was reported for 58.9%. Three-phase sample and questionnaire data collection was completed in December 2024. Future analyses will examine microbiome features, resistome profiles and functional pathways in relation to antibiotic exposure, feeding, growth and infant health outcomes. Subject to ethical approval and participant consent, follow-up may include further stool collection and Swedish register linkage. NCT06285630.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>本研究旨在調查2023-2024年拉丁美洲奧羅普切熱（Oropouche fever）疫情期間，哥倫比亞亞馬遜地區一名急性發熱患者的病因。研究團隊採用針對脊椎動物病毒的總體基因體學（宏基因組）定序技術（VirCapSeq-VERT），成功鑑定並分離出一種與Caraparu複合體相關的C群正布尼亞病毒（Group C Orthobunyavirus）。由於此類病毒臨床表現與其他蟲媒病毒相似，診斷極具挑戰。本研究雖僅基於單一病例，但其結果強調了在亞馬遜盆地等流行病疫區，使用無偏向性分子檢測技術對於診斷不明原因發熱疾病的重要臨床與科學價值。</t>
+          <t>本研究建立瑞典全國性嬰兒追蹤世代「PREVENT 1」，旨在透過縱向總體基因體學分析，描繪嬰兒出生後前兩年的腸道菌相發育軌跡，並探討其與餵養、生長及感染等健康指標的關聯。研究成功招募253名足月嬰兒，並在三個時間點重複收集糞便檢體與問卷，受試者維持率極高（241名嬰兒提供全部三次檢體）。此世代研究提供高質量的臨床與多體學數據，未來將深入分析抗生素暴露與飲食如何形塑嬰兒腸道菌群、抗藥性基因組及代謝途徑，對理解早期生命健康極具臨床與科學價值。</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42660108/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42665338/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>42656127</t>
+          <t>42666033</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Development and Validation of Mock Communities as Quality Control Materials for Clinical Metagenomic Next-Generation Sequencing.</t>
+          <t>Gut Microbiota-Isoallolithocholic Acid Crosstalk Promotes Calcium Oxalate Kidney Stone Formation via PARP1-Mediated Parthanatos.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Annals of laboratory medicine</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>3.9</v>
+          <t>Advanced science (Weinheim, Baden-Wurttemberg, Germany)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>16S, metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25 次重複分析（針對開發出的四種模擬群落進行評估）</t>
+          <t>未提及（文中僅提及 CaOx 大鼠與小鼠模型，未說明具體樣本數量）</t>
         </is>
       </c>
       <c r="G16" t="b">
@@ -1277,52 +1257,52 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Metagenomic next-generation sequencing (NGS) enables comprehensive detection of a broad spectrum of microorganisms. However, its clinical application faces two major challenges: the development of appropriate microbiome-based biomarkers and the need to ensure the reproducibility and quality of the microbiome analytical workflow. Therefore, we developed four types of bead-based mock communities as standard materials for microbiome analysis and evaluated potential experimental biases arising from nucleic acid extraction and sequence analysis. Mock communities were assembled from strains isolated from clinical specimens and selected considering Gram reaction, taxonomic phylogeny, and prevalence, and processed into frozen beads. The communities were analyzed using shotgun whole-metagenome sequencing. The effect of DNA extraction kit choice was evaluated using the Thermo Fisher Scientific MagMAX Microbiome Ultra Nucleic Acid Isolation Kit and Qiagen PowerSoil Kit. Four types of mock communities comprising 26 species commonly found in the gastrointestinal tract, respiratory tract, skin, and genital tract plus cerebrospinal fluid were developed considering Gram reaction, GC content, and phylogenetic distribution. Across 25 repeated analyses, the median repeatability of each taxon was 18.97% (range, 2.87%-107.38%), while within-laboratory imprecision was 26.22% (range, 9.26%-153.83%). Repeatability remained below 10% for most dominant taxa with relative abundances &gt;20%. The choice of DNA extraction kit had a significant effect on taxonomic distributions. Microbial mock communities are essential QC materials for clinical metagenomic NGS. Further studies are needed to minimize variability and establish a standardized protocol for clinical implementation.</t>
+          <t>Bile acids have been implicated in calcium oxalate (CaOx) nephrolithiasis. Here, we employ multi-omics approaches to identify isoallolithocholic acid (isoalloLCA) as the key bile acid elevated in the feces, serum, kidney, and urine of CaOx rats, confirmed by spatial metabolomics. 16S sequencing and metagenomic analyses indicate that elevated isoalloLCA levels in CaOx rats or individuals are likely of microbial origin. Mechanistically, isoalloLCA binds to PARP1 via specific molecular interactions validated by surface plasmon resonance and cellular thermal shift assays. Knockdown of PARP1 by adeno-associated virus microinjection or pharmacological inhibition with PARP1 inhibitor AZD5305 significantly attenuates isoalloLCA-mediated crystal deposition, renal tubular injury, and mitochondrial functional impairment in both the CaOx rat and mouse models. Furthermore, the antibiotic-mediated depletion of the gut microbiota in mice markedly reduced isoalloLCA levels, whereas fecal microbiota transplantationut contributes to isoalloLCA-mediated CaOx stone formation, demonstrating a causal link between gut microbiota and isoalloLCA. In vitro, isoalloLCA promoted oxalate-induced renal tubular epithelial cell injury and parthanatos via targeting PARP1, including DNA damage, excessive PARP1 activation, PAR accumulation, mitochondrial damage, nuclear translocation of AIF and MIF. These findings establish the microbiota-isoalloLCA-PARP1-parthanatos axis in CaOx nephrolithiasis and identify PARP1 as a promising therapeutic target for kidney stone management.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>本研究旨在解決臨床宏基因組次世代定序（mNGS）在品質控制與再現性上的挑戰，開發了四種基於珠粒的「模擬微生物群落」（mock communities）作為標準品。這些群落涵蓋了腸道、呼吸道、皮膚、生殖道及腦脊髓液中常見的 26 種菌株。研究透過鳥槍法全宏基因體定序（shotgun metagenomics）評估了不同 DNA 萃取試劑盒（MagMAX 與 PowerSoil）及實驗流程對結果的偏誤影響。結果顯示，微生物的檢測豐度會顯著受到萃取試劑盒選擇的干擾，且在 25 次重複實驗中，群落組成存在一定的實驗室內誤差。此研究確立了模擬群落作為臨床 mNGS 品質控制材料的重要性，對於推動微生物組檢測的標準化流程與臨床應用具有關鍵價值。</t>
+          <t>本研究探討腸道菌群與草酸鈣（CaOx）腎結石形成的病理機制。研究發現，異別石膽酸（isoalloLCA）在結石模型的大鼠與人類檢體中顯著升高，且來源於腸道菌群。透過空間代謝體學、16S 及宏基因組分析，研究確認了腸道菌群與 isoalloLCA 之間的因果關係。機制研究顯示，isoalloLCA 可直接結合並活化 PARP1，進而觸發腎小管上皮細胞的「副凋亡」（Parthanatos），導致細胞損傷與結晶沉積。動物實驗證實，透過藥物抑制或基因剔除 PARP1 可有效減輕腎臟損傷。此研究揭示了「腸道菌群—isoalloLCA—PARP1—副凋亡」這一全新的軸線，證實了該路徑在腎結石形成中的核心作用，並將 PARP1 定位為治療腎結石的潛在藥物標靶。</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42656127/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42666033/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>42657522</t>
+          <t>42656127</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Resistant starch alleviates intestinal fibrosis involving an acetate-mediated HDAC2-H3K27ac axis in fibroblasts.</t>
+          <t>Development and Validation of Mock Communities as Quality Control Materials for Clinical Metagenomic Next-Generation Sequencing.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Food &amp; function</t>
+          <t>Annals of laboratory medicine</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5.4</v>
+        <v>3.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>metagenomics, metabolomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>未提及（研究使用 DSS 誘導的小鼠模型以及人類與小鼠的原代纖維母細胞，但未具體說明樣本數）</t>
+          <t>25 次重複分析（針對開發出的四種模擬群落進行評估）</t>
         </is>
       </c>
       <c r="G17" t="b">
@@ -1330,12 +1310,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Dietary fibre-based interventions are of growing interest for the prevention and treatment of digestive diseases. In this study, we investigated the effect of resistant starch (RS) on intestinal fibrosis, a stricturing condition driven by excessive extracellular matrix (ECM) accumulation. RS was found to alleviate intestinal fibrosis in a dextran sulfate sodium (DSS)-induced chronic colitis mouse model, as evidenced by restored colon length, reduced ECM deposition (fibronectin and collagen I), and decreased levels of α-smooth muscle actin. Given that RS is fermented by the gut microbiota in the colon, metagenomic sequencing revealed that RS reshaped the composition of the gut microbiota and increased the abundance of beneficial gut bacteria, including Bacteroides acidifaciens, Faecalibaculum rodentium, and Bifidobacterium pseudolongum, which are known to enhance the production of short-chain fatty acids. Targeted metabolomic analysis further showed a marked increase in acetate levels, which was associated with reduced intestinal fibrosis. However, direct in vivo evidence that acetate is required for the anti-fibrotic effect of RS remains lacking. Using human (CCD-18Co) and primary mouse intestinal fibroblasts, the major ECM-producing cells that drive fibrosis progression, we demonstrated that acetate inhibited TGF-β-induced fibroblast activation by inhibiting histone deacetylase 2, thereby enhancing the acetylation level of histone H3 at lysine 27. Collectively, these results suggest a potential microbial-metabolic-epigenetic axis linking RS and acetate to fibrosis attenuation, which awaits causal validation in vivo. This axis holds promise as a therapeutic target for fibrotic diseases.</t>
+          <t>Metagenomic next-generation sequencing (NGS) enables comprehensive detection of a broad spectrum of microorganisms. However, its clinical application faces two major challenges: the development of appropriate microbiome-based biomarkers and the need to ensure the reproducibility and quality of the microbiome analytical workflow. Therefore, we developed four types of bead-based mock communities as standard materials for microbiome analysis and evaluated potential experimental biases arising from nucleic acid extraction and sequence analysis. Mock communities were assembled from strains isolated from clinical specimens and selected considering Gram reaction, taxonomic phylogeny, and prevalence, and processed into frozen beads. The communities were analyzed using shotgun whole-metagenome sequencing. The effect of DNA extraction kit choice was evaluated using the Thermo Fisher Scientific MagMAX Microbiome Ultra Nucleic Acid Isolation Kit and Qiagen PowerSoil Kit. Four types of mock communities comprising 26 species commonly found in the gastrointestinal tract, respiratory tract, skin, and genital tract plus cerebrospinal fluid were developed considering Gram reaction, GC content, and phylogenetic distribution. Across 25 repeated analyses, the median repeatability of each taxon was 18.97% (range, 2.87%-107.38%), while within-laboratory imprecision was 26.22% (range, 9.26%-153.83%). Repeatability remained below 10% for most dominant taxa with relative abundances &gt;20%. The choice of DNA extraction kit had a significant effect on taxonomic distributions. Microbial mock communities are essential QC materials for clinical metagenomic NGS. Further studies are needed to minimize variability and establish a standardized protocol for clinical implementation.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>本研究探討抗性澱粉（RS）對腸道纖維化的改善作用及其潛在機制。透過 DSS 誘導的小鼠結腸炎模型，研究發現 RS 可有效減輕腸道纖維化並減少細胞外基質堆積。宏基因體定序顯示 RS 能重塑腸道菌群，增加如 *Bacteroides acidifaciens* 等短鏈脂肪酸產生菌的豐度；代謝體分析進一步證實乙酸（acetate）水平顯著上升。機制研究揭示，乙酸能抑制纖維母細胞中 HDAC2 的活性，進而提升組蛋白 H3K27 的乙醯化水平，抑制 TGF-β 誘導的纖維母細胞活化。本研究提出了一條「微生物-代謝-表觀遺傳」軸線，指出 RS 可藉由促進乙酸生成來對抗腸道纖維化，為治療纖維化相關疾病提供了新的科學依據與潛在治療靶點。</t>
+          <t>本研究旨在解決臨床宏基因組次世代定序（mNGS）在品質控制與再現性上的挑戰，開發了四種基於珠粒的「模擬微生物群落」（mock communities）作為標準品。這些群落涵蓋了腸道、呼吸道、皮膚、生殖道及腦脊髓液中常見的 26 種菌株。研究透過鳥槍法全宏基因體定序（shotgun metagenomics）評估了不同 DNA 萃取試劑盒（MagMAX 與 PowerSoil）及實驗流程對結果的偏誤影響。結果顯示，微生物的檢測豐度會顯著受到萃取試劑盒選擇的干擾，且在 25 次重複實驗中，群落組成存在一定的實驗室內誤差。此研究確立了模擬群落作為臨床 mNGS 品質控制材料的重要性，對於推動微生物組檢測的標準化流程與臨床應用具有關鍵價值。</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1345,35 +1325,37 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42657522/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42656127/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>42658844</t>
+          <t>42657522</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Enrichment and Characterization of a Haloalkaline-tolerant Anammox Bacterium.</t>
+          <t>Resistant starch alleviates intestinal fibrosis involving an acetate-mediated HDAC2-H3K27ac axis in fibroblasts.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>The ISME journal</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Food &amp; function</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>5.4</v>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>metagenomics, small genome, others (transcriptional profiling)</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>未提及（研究基於特定實驗室富集培養物之實驗與分析）</t>
+          <t>未提及（研究使用 DSS 誘導的小鼠模型以及人類與小鼠的原代纖維母細胞，但未具體說明樣本數）</t>
         </is>
       </c>
       <c r="G18" t="b">
@@ -1381,12 +1363,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Metagenomic surveys have substantially expanded the known diversity of anaerobic ammonium-oxidizing (anammox) bacteria. However, the physiological traits of newly proposed anammox genera remain largely hypothetical due to the lack of cultured representatives. Although niche differentiation driven by salinity, organic substrates, and oxygen is well documented in anammox bacteria, adaptations to alkaline environments remain uncharacterized. Moreover, no anammox lineage has been identified as an alkaline specialist. Herein, we report the enrichment (&gt;80% relative abundance) of an anammox bacterium, provisionally named Candidatus Loosdrechtia alkalitolerans, which represents the cultured member of the genus Ca. Loosdrechtia. Ca. L. alkalitolerans exhibits marked haloalkaline tolerance, outcompeting other freshwater anammox genera under long-term saline-alkaline stress conditions (0.5% NaCl; pH~9.13). Comparative genomics revealed that among freshwater anammox lineages, only Ca. L. alkalitolerans encodes a complete multiple resistance and pH adaptation (Mrp) cation/proton antiporter operon. Batch assays with transcriptional profiling demonstrated that sodium addition upregulated mrp expression and recovered anammox activity under alkaline stress, suggesting that Mrp-mediated cation/proton exchange may contribute to pH homeostasis in Ca. L. alkalitolerans. Furthermore, database mining revealed that the habitat of Ca. L. alkalitolerans is not restricted to haloalkaline environments, but extends to diverse freshwater and wastewater ecosystems. These findings provide mechanistic insight into saline-alkaline tolerance in anammox bacteria, expanding understanding of their physiological plasticity and ecological roles.</t>
+          <t>Dietary fibre-based interventions are of growing interest for the prevention and treatment of digestive diseases. In this study, we investigated the effect of resistant starch (RS) on intestinal fibrosis, a stricturing condition driven by excessive extracellular matrix (ECM) accumulation. RS was found to alleviate intestinal fibrosis in a dextran sulfate sodium (DSS)-induced chronic colitis mouse model, as evidenced by restored colon length, reduced ECM deposition (fibronectin and collagen I), and decreased levels of α-smooth muscle actin. Given that RS is fermented by the gut microbiota in the colon, metagenomic sequencing revealed that RS reshaped the composition of the gut microbiota and increased the abundance of beneficial gut bacteria, including Bacteroides acidifaciens, Faecalibaculum rodentium, and Bifidobacterium pseudolongum, which are known to enhance the production of short-chain fatty acids. Targeted metabolomic analysis further showed a marked increase in acetate levels, which was associated with reduced intestinal fibrosis. However, direct in vivo evidence that acetate is required for the anti-fibrotic effect of RS remains lacking. Using human (CCD-18Co) and primary mouse intestinal fibroblasts, the major ECM-producing cells that drive fibrosis progression, we demonstrated that acetate inhibited TGF-β-induced fibroblast activation by inhibiting histone deacetylase 2, thereby enhancing the acetylation level of histone H3 at lysine 27. Collectively, these results suggest a potential microbial-metabolic-epigenetic axis linking RS and acetate to fibrosis attenuation, which awaits causal validation in vivo. This axis holds promise as a therapeutic target for fibrotic diseases.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>本研究成功富集並鑑定出一種耐鹽鹼的厭氧氨氧化（Anammox）細菌，命名為 *Candidatus Loosdrechtia alkalitolerans*。該菌株在長期高鹽、高鹼（0.5% NaCl，pH 9.13）環境下表現出強大的競爭優勢。透過基因體比較分析，研究發現該菌株含有特殊的 Mrp 陽離子/質子反向轉運蛋白操縱子，這是其適應鹼性環境的關鍵機制；轉錄組分析進一步證實，在鹼性壓力下，補充鈉離子可上調 Mrp 表現並恢復其代謝活性。此發現不僅揭示了厭氧氨氧化菌應對鹽鹼逆境的生理分子機制，證明了該菌在廣泛的淡水與廢水生態系統中具有潛在的生態地位，更為未來工業廢水處理中的脫氮技術應用提供了理論基礎與科學見解。</t>
+          <t>本研究探討抗性澱粉（RS）對腸道纖維化的改善作用及其潛在機制。透過 DSS 誘導的小鼠結腸炎模型，研究發現 RS 可有效減輕腸道纖維化並減少細胞外基質堆積。宏基因體定序顯示 RS 能重塑腸道菌群，增加如 *Bacteroides acidifaciens* 等短鏈脂肪酸產生菌的豐度；代謝體分析進一步證實乙酸（acetate）水平顯著上升。機制研究揭示，乙酸能抑制纖維母細胞中 HDAC2 的活性，進而提升組蛋白 H3K27 的乙醯化水平，抑制 TGF-β 誘導的纖維母細胞活化。本研究提出了一條「微生物-代謝-表觀遺傳」軸線，指出 RS 可藉由促進乙酸生成來對抗腸道纖維化，為治療纖維化相關疾病提供了新的科學依據與潛在治療靶點。</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1396,37 +1378,35 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42658844/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42657522/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>42658871</t>
+          <t>42660108</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Breastmilk microbiota and its association with infant iron deficiency anaemia: A 16S rRNA metagenomic study in Peruvian mothers cohort.</t>
+          <t>Group C Orthobunyavirus Infection in a Patient from the Amazon Putumayo Region of Colombia During an Oropouche Fever Epidemic.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PloS one</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>2.6</v>
-      </c>
+          <t>The American journal of tropical medicine and hygiene</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16S</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>46 對母嬰（46 個母乳檢體）</t>
+          <t>1位急性發熱疾病患者（單一病例）</t>
         </is>
       </c>
       <c r="G19" t="b">
@@ -1434,12 +1414,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Anaemia is one of the most important public health challenges in developing countries. The global burden is estimated at 1.8 billion people, affecting approximately 30% of all children. Despite the implementation of multiple strategies over several decades, up to 42.5% of children under 3 years of age suffer anaemia in rural areas of Peru. We studied the microbiota of breastmilk (hBM) from mothers with children under the age of 1 and analysed its association with their iron deficiency anaemia. 46 mother-child pairs were recruited from Talara, a town on the northern coast of Peru and classified according to the clinical status of the children. Children with anaemia were also tested for ferritin level to classify them as iron deficiency anaemia (IDA) or non-iron deficiency anaemia (non-IDA). hBM samples were taken from the mothers after careful instruction to reduce the risk of sample contamination and the microbiome was analyzed using 16S rRNA sequencing. Streptococcus and Staphylococcus were the predominant genera, with 90% of bacterial abundance being explained by 14 genera. Alpha diversity analysis showed that hBM from mothers of children with non-IDA had higher levels of bacterial richness than hBM from healthy (p &lt; 0.01) and IDA (p &lt; 0.05) participants. Principal coordinates analysis did not yield differential clusters but showed a disparity in the spread of samples for non-IDA group when compared with the other groups. IDA group showed higher burden of Corynebacterium, Acinetobacter, Paludibacter and Nitrospira, while exhibiting a trend towards a lower burden of Streptococcus. No statistically significant differences were identified on demographic characteristics. This study suggests that hBM microbiota may differ in mothers of children with IDA and non-IDA, highlighting the necessity of further in-depth research to elucidate potential factors associated with its pathogenesis.</t>
+          <t>Orthobunyaviruses, one of the largest and most diverse genera of viruses, include numerous reassortant viruses and present diagnostic challenges due to similar clinical presentations with other arboviral infections. The detection and isolation of a group C orthobunyavirus from a patient with acute febrile illness from Puerto Ospina, Putumayo Department, Colombia during the 2023-2024 Latin American Oropouche fever regional outbreaks are reported in the present study. Using a vertebrate virus-focused metagenomics sequencing approach with VirCapSeq-VERT, a virus related to the Caraparu complex was identified, and a virus isolate was obtained. Although limited to a single case and without serological or longitudinal clinical confirmation, these findings underscore the value of unbiased molecular approaches for unresolved febrile illness diagnosis in endemic settings such as the Amazon basin.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>本研究探討祕魯農村地區嬰兒缺鐵性貧血（IDA）與母親母乳（hBM）菌相之間的關聯。研究對象為 46 對母嬰，透過 16S rRNA 定序分析母乳微生物群落，發現母乳菌相以鏈球菌屬（Streptococcus）與葡萄球菌屬（Staphylococcus）為優勢菌群。研究結果顯示，非貧血組嬰兒的母親，其母乳具備較高的細菌豐富度。此外，IDA 組嬰兒母親的母乳中，棒狀桿菌屬（Corynebacterium）與不動桿菌屬（Acinetobacter）等細菌豐度較高，而鏈球菌屬則呈現下降趨勢。此研究發現母乳微生物群組成可能與嬰兒貧血狀態相關，雖無法直接證實因果關係，但為後續探討嬰兒貧血的致病機制提供了重要的微生物學線索。</t>
+          <t>本研究旨在調查2023-2024年拉丁美洲奧羅普切熱（Oropouche fever）疫情期間，哥倫比亞亞馬遜地區一名急性發熱患者的病因。研究團隊採用針對脊椎動物病毒的總體基因體學（宏基因組）定序技術（VirCapSeq-VERT），成功鑑定並分離出一種與Caraparu複合體相關的C群正布尼亞病毒（Group C Orthobunyavirus）。由於此類病毒臨床表現與其他蟲媒病毒相似，診斷極具挑戰。本研究雖僅基於單一病例，但其結果強調了在亞馬遜盆地等流行病疫區，使用無偏向性分子檢測技術對於診斷不明原因發熱疾病的重要臨床與科學價值。</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1449,7 +1429,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42658871/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42660108/</t>
         </is>
       </c>
     </row>
@@ -1469,11 +1449,7 @@
           <t>Environmental pollution (Barking, Essex : 1987)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>16S, metagenomics</t>
@@ -1524,10 +1500,8 @@
           <t>Bioresource technology</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
+      <c r="D21" t="n">
+        <v>9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1579,10 +1553,8 @@
           <t>Bioresource technology</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
+      <c r="D22" t="n">
+        <v>9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1634,10 +1606,8 @@
           <t>Toxicology and applied pharmacology</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
+      <c r="D23" t="n">
+        <v>3.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1676,30 +1646,30 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>42648218</t>
+          <t>42658871</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Agricultural sprinkler irrigation systems as environmental reservoirs and airborne dissemination sources of Legionella pneumophila.</t>
+          <t>Breastmilk microbiota and its association with infant iron deficiency anaemia: A 16S rRNA metagenomic study in Peruvian mothers cohort.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Journal of environmental management</t>
+          <t>PloS one</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>8.4</v>
+        <v>2.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>metagenomics, small genome</t>
+          <t>16S</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>未明確提及具體檢體數量（僅指出於西班牙東北部農村的兩個區域，針對灌溉池塘與溝渠進行採樣）</t>
+          <t>46 對母嬰（46 個母乳檢體）</t>
         </is>
       </c>
       <c r="G24" t="b">
@@ -1707,52 +1677,50 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sprinkler irrigation systems are critical for modern agriculture but represent largely unrecognized aquatic environments capable of sustaining opportunistic human pathogens. Among them, Legionella pneumophila is of particular concern due to its ability to colonize engineered water systems, persist under fluctuating environmental conditions, and be transmitted through aerosols. In this study, we conducted a comprehensive microbiological and genomic investigation of irrigation ponds and ditches in a rural area of north-east Spain where two zones were sampled. Metagenomic profiling revealed highly diverse microbial communities encompassing more than 20,000 species, including 21 airborne-transmissible bacterial pathogens of clinical relevance. Notably, L. pneumophila was detected in both zones, with a relative abundance of up to 4.6 %. Culture-based isolation confirmed the presence of L. pneumophila serogroup 1, Pontiac group, Benidorm subgroup, sequence type 15. Phylogenetic analysis demonstrated a close relationship between this environmental strain and clinical isolates obtained during a Legionnaires' disease outbreak occurred in 2015, which had remained without a confirmed environmental source. Meteorological data from the exposure period revealed wind conditions favouring long-distance aerosol dispersion from irrigated fields toward residential areas. Our findings provide evidence that irrigation infrastructures can act as environmental reservoirs and dissemination routes of L. pneumophila among other airborne pathogens. These results underscore the need to incorporate agricultural irrigation systems into routine environmental surveillance, outbreak investigations, and public health risk assessments.</t>
+          <t>Anaemia is one of the most important public health challenges in developing countries. The global burden is estimated at 1.8 billion people, affecting approximately 30% of all children. Despite the implementation of multiple strategies over several decades, up to 42.5% of children under 3 years of age suffer anaemia in rural areas of Peru. We studied the microbiota of breastmilk (hBM) from mothers with children under the age of 1 and analysed its association with their iron deficiency anaemia. 46 mother-child pairs were recruited from Talara, a town on the northern coast of Peru and classified according to the clinical status of the children. Children with anaemia were also tested for ferritin level to classify them as iron deficiency anaemia (IDA) or non-iron deficiency anaemia (non-IDA). hBM samples were taken from the mothers after careful instruction to reduce the risk of sample contamination and the microbiome was analyzed using 16S rRNA sequencing. Streptococcus and Staphylococcus were the predominant genera, with 90% of bacterial abundance being explained by 14 genera. Alpha diversity analysis showed that hBM from mothers of children with non-IDA had higher levels of bacterial richness than hBM from healthy (p &lt; 0.01) and IDA (p &lt; 0.05) participants. Principal coordinates analysis did not yield differential clusters but showed a disparity in the spread of samples for non-IDA group when compared with the other groups. IDA group showed higher burden of Corynebacterium, Acinetobacter, Paludibacter and Nitrospira, while exhibiting a trend towards a lower burden of Streptococcus. No statistically significant differences were identified on demographic characteristics. This study suggests that hBM microbiota may differ in mothers of children with IDA and non-IDA, highlighting the necessity of further in-depth research to elucidate potential factors associated with its pathogenesis.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>本研究旨在探討農業噴灌系統是否為嗜肺軍團菌（*Legionella pneumophila*）等致病菌的環境宿主與空氣傳播源。團隊對西班牙農村灌溉水體進行分析，總體基因體學顯示其含有逾2萬種微生物，包括21種臨床相關的空氣傳播病原體，且嗜肺軍團菌相對豐度達4.6%。研究成功分離出嗜肺軍團菌血清型1（ST15），系統發育分析證實該環境株與2015年退伍軍人症爆發的臨床分離株高度相關。氣象數據亦支持風向有利於氣膠從農田長距離擴散至住宅區。此發現證實農業灌溉系統為軍團菌的傳播媒介，強調應將其納入例行環境監測與公衛風險評估。</t>
+          <t>本研究探討祕魯農村地區嬰兒缺鐵性貧血（IDA）與母親母乳（hBM）菌相之間的關聯。研究對象為 46 對母嬰，透過 16S rRNA 定序分析母乳微生物群落，發現母乳菌相以鏈球菌屬（Streptococcus）與葡萄球菌屬（Staphylococcus）為優勢菌群。研究結果顯示，非貧血組嬰兒的母親，其母乳具備較高的細菌豐富度。此外，IDA 組嬰兒母親的母乳中，棒狀桿菌屬（Corynebacterium）與不動桿菌屬（Acinetobacter）等細菌豐度較高，而鏈球菌屬則呈現下降趨勢。此研究發現母乳微生物群組成可能與嬰兒貧血狀態相關，雖無法直接證實因果關係，但為後續探討嬰兒貧血的致病機制提供了重要的微生物學線索。</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42648218/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42658871/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>42644416</t>
+          <t>42658844</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nationwide cohort study reveals low bifidobacteria and distinct microbiota composition and function in Swedish newborns.</t>
+          <t>Enrichment and Characterization of a Haloalkaline-tolerant Anammox Bacterium.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>11</v>
-      </c>
+          <t>The ISME journal</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>metagenomics, small genome, others (transcriptional profiling)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>308 名瑞典新生兒的糞便檢體</t>
+          <t>未提及（研究基於特定實驗室富集培養物之實驗與分析）</t>
         </is>
       </c>
       <c r="G25" t="b">
@@ -1760,39 +1728,39 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>NCT06285630.</t>
+          <t>Metagenomic surveys have substantially expanded the known diversity of anaerobic ammonium-oxidizing (anammox) bacteria. However, the physiological traits of newly proposed anammox genera remain largely hypothetical due to the lack of cultured representatives. Although niche differentiation driven by salinity, organic substrates, and oxygen is well documented in anammox bacteria, adaptations to alkaline environments remain uncharacterized. Moreover, no anammox lineage has been identified as an alkaline specialist. Herein, we report the enrichment (&gt;80% relative abundance) of an anammox bacterium, provisionally named Candidatus Loosdrechtia alkalitolerans, which represents the cultured member of the genus Ca. Loosdrechtia. Ca. L. alkalitolerans exhibits marked haloalkaline tolerance, outcompeting other freshwater anammox genera under long-term saline-alkaline stress conditions (0.5% NaCl; pH~9.13). Comparative genomics revealed that among freshwater anammox lineages, only Ca. L. alkalitolerans encodes a complete multiple resistance and pH adaptation (Mrp) cation/proton antiporter operon. Batch assays with transcriptional profiling demonstrated that sodium addition upregulated mrp expression and recovered anammox activity under alkaline stress, suggesting that Mrp-mediated cation/proton exchange may contribute to pH homeostasis in Ca. L. alkalitolerans. Furthermore, database mining revealed that the habitat of Ca. L. alkalitolerans is not restricted to haloalkaline environments, but extends to diverse freshwater and wastewater ecosystems. These findings provide mechanistic insight into saline-alkaline tolerance in anammox bacteria, expanding understanding of their physiological plasticity and ecological roles.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>本研究旨在探討瑞典新生兒的腸道菌相組成與功能特徵。透過總體基因體學分析，研究發現瑞典新生兒腸道中的雙歧桿菌（特別是嬰兒雙歧桿菌）豐度顯著偏低，並呈現出獨特的菌相結構與代謝功能。此現象與現代化生活型態及分娩方式密切相關。這項全國性世代研究揭示了現代環境對嬰兒早期腸道微生態建立的深遠影響，為未來的臨床嬰幼兒益生菌介入與健康照護策略提供了關鍵的科學依據。</t>
+          <t>本研究成功富集並鑑定出一種耐鹽鹼的厭氧氨氧化（Anammox）細菌，命名為 *Candidatus Loosdrechtia alkalitolerans*。該菌株在長期高鹽、高鹼（0.5% NaCl，pH 9.13）環境下表現出強大的競爭優勢。透過基因體比較分析，研究發現該菌株含有特殊的 Mrp 陽離子/質子反向轉運蛋白操縱子，這是其適應鹼性環境的關鍵機制；轉錄組分析進一步證實，在鹼性壓力下，補充鈉離子可上調 Mrp 表現並恢復其代謝活性。此發現不僅揭示了厭氧氨氧化菌應對鹽鹼逆境的生理分子機制，證明了該菌在廣泛的淡水與廢水生態系統中具有潛在的生態地位，更為未來工業廢水處理中的脫氮技術應用提供了理論基礎與科學見解。</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42644416/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42658844/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>42648171</t>
+          <t>42644751</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Co-occurrence of muddy off flavor and cyanotoxin genes in the polluted Guandu river waters (Rio de Janeiro, Brazil).</t>
+          <t>Soil amelioration impacts viral ecology in saline-alkali lands.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>The Science of the total environment</t>
+          <t>The ISME journal</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1803,7 +1771,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（僅說明樣品來自中國4個主要鹽鹼地區，各包含「鹽鹼」與「改良後」兩種狀態之土壤）</t>
         </is>
       </c>
       <c r="G26" t="b">
@@ -1811,12 +1779,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>The Guandu river basin is responsible for supplying Rio de Janeiro municipality, Brazil, with drinking water. This study investigated water quality during the geosmin crisis in January and March 2020, by relating the water quality and odor compounds with metagenomic tools. Guandu river water was eutrophic. The cyanobacterial genera identified were Microcystis, Planktothrix, Dolichospermum, Nostoc, Synechococcus, Planktothricoides, and Cyanobium, indicating that bloom-associated communities in the system are taxonomically diverse. Functional annotation of metagenomic sequences revealed the presence of genes associated with the biosynthesis of taste-and-odor compounds, including geosmin (geoA) and 2-methylisoborneol (mic), as well as multiple biosynthetic clusters related to cyanotoxin production. Genes linked to microcystin (mcy), saxitoxin (sxt), anatoxin (ana), cylindrospermopsin (cyr), lyngbyatoxin (ltx), guanitoxin (gnt), and nodularin (nda) were detected across the dataset, indicating a broad genetic potential for the production of secondary metabolites relevant to water quality. The co-occurrence of cyanotoxins, geosmin and 2-MIB genes suggests that off-flavor is an indication of cyanotoxin potential production in the water.</t>
+          <t>The continuous expansion of saline-alkali lands under climate change threatens food security and reduces soil carbon stocks. A common mitigation strategy is soil amelioration, which converts degraded soils back into an arable state. Microbes play critical roles in soil health and recovery. However, the viruses that infect these microbial communities, and their potential impacts during saline-alkali soil restoration, remain largely unknown. Here, we combined total soil metagenomics and viromics to investigate host-linked viral ecology across four major saline-alkali regions in China, each encompassing two soil amelioration statuses: saline-alkali and reclaimed. We found that viral community structure was shaped by both geography and soil amelioration status, with salinity and alkalinity emerging as key environmental factors. Viral populations were sensitive to soil restoration, showing strong amelioration-status endemism with functional adaptations. Virus-host dynamics ranged from reduced temperate viruses to abundance mismatches in those infecting key carbon-cycling microorganisms, including carbohydrate degraders. 13C-cellulose DNA-SIP experiments provided further support for this mismatch by tracing assimilated carbon transfer between active host and virus populations. Compared with saline-alkali soils, the relative abundance of hosts in restored soils increased from 39.0% to 61.0%, whereas the linked viruses decreased from 60.6% to 39.4%. Together, these findings reveal an underappreciated role of viruses in shaping saline-alkali soil amelioration trajectories, and could improve management strategies for degraded land recovery and carbon storage.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>本研究旨在探究巴西里約熱內盧瓜杜河於2020年初爆發土臭素危機期間的水質狀況，並利用總體基因體學技術探討水質異味與微生物群落之關聯。研究發現，該富營養化水體中含有多種藍菌，且功能性註釋顯示其富含合成土臭素（*geoA*）與2-甲基異莰醇（*mic*）等異味物質的基因。更重要的是，多種藍菌毒素（如微囊藻毒素、石房蛤毒素等）的合成基因群與這些異味基因呈現共存。此發現證實了水體異味的出現與藍菌毒素的潛在生成具有高度相關性，可作為飲用水安全監測及評估藍菌毒素潛在危害的重要預警指標。</t>
+          <t>本研究旨在探討鹽鹼地改良過程中，病毒對土壤微生物生態與碳循環的影響。研究結合總體基因體與病毒體學，分析中國四大鹽鹼區。結果顯示，土壤改良狀態、鹽度與鹼度是塑造病毒社群的關鍵。在改良土壤中，宿主微生物相對豐度顯著上升（39.0%至61.0%），而關聯病毒減少（60.6%至39.4%），且溫和病毒比例降低，碳循環關鍵微生物的病毒與宿主出現豐度失衡。13C-纖維素DNA-SIP實驗證實了兩者間的活性碳轉移。此發現揭示了病毒在鹽鹼地恢復中的關鍵作用，有助優化土地改良與碳儲存策略。</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1826,30 +1794,32 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42648171/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42644751/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>42647759</t>
+          <t>42648293</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Gut Microbiome in Multiple Sclerosis.</t>
+          <t>Defined human Clostridia consortia reverse colitis via dual effects of tryptophan metabolites on microbiota and immunity.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Neurology(R) neuroimmunology &amp; neuroinflammation</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>Cell host &amp; microbe</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>18.7</v>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1862,12 +1832,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Multiple sclerosis (MS) is a chronic inflammatory demyelinating disease of the CNS whose risk and course are shaped by both genetic and environmental factors, among which the intestinal microbiota has emerged as a key, potentially modifiable contributor. People with MS frequently display altered gut microbiota, characterized by depletion of fiber-fermenting, short-chain fatty acid (SCFA)-producing commensals, and expansion of taxa associated with mucus degradation and proinflammatory metabolism. These compositional shifts are paralleled by broad changes in blood and CSF metabolites, including reduced SCFAs, tryptophan-derived aryl hydrocarbon receptor ligands, and secondary bile acids. In addition, several reports highlight the accumulation of aromatic amino acid-derived phenolic and indolic compounds and specific lipid mediators linked to neuroinflammation and neurodegeneration. In this up-to-date review, we synthesize evidence from experimental models and human studies showing how microbial metabolites can influence MS pathogenesis through converging mechanisms: modulation of gut and blood-brain barrier integrity; shaping of T-cell and B-cell responses; direct effects on microglia, astrocytes, and oligodendrocyte lineage cells after crossing into the CNS; and modulation of neural circuits, particularly those involving the vagus nerve. Finally, we highlight current gaps, including the need for longitudinal, harmonized multiomic cohorts, and mechanistic studies integrating microbiome, metabolome, and host readouts across gut, blood, and CNS. Overall, available data support a model in which coordinated disruption of the gut microbiota-metabolite axis, rather than any single pathogen, contributes to MS, opening avenues for microbiota-based and metabolite-based biomarkers and therapies aimed at restoring immune and neuroglial homeostasis.</t>
+          <t>Microbial dysbiosis and disrupted mucosal immune homeostasis are integrally involved in the pathogenesis of inflammatory bowel diseases (IBDs). Live biotherapeutic products (LBPs) offer a potential therapeutic strategy to restore beneficial microbes and mitigate disease. We investigated the therapeutic efficacy of 2 LBPs, human Clostridia consortia 17-mix and 11-mix, by treating established colitis in murine models. Both LBPs exhibited therapeutic effects in T cell-mediated chronic colitis models induced by human microbiota and in pathobiont-driven gnotobiotic colitis models established with combinations of IBD-relevant human-derived strains. Metagenomic and metabolomic analyses elucidated mechanisms that go beyond established functions driven by short-chain fatty acids (SCFAs) and interleukin (IL)-10-producing regulatory T cells. Notably, LBPs exerted therapeutic effects by directly inhibiting resident pathobionts and through IL-10-independent activation of host anti-inflammatory aryl hydrocarbon receptor (AhR) pathways by bacterial tryptophan metabolites. These results elucidate SCFA- and IL-10-independent protective mechanisms exerted by defined resident bacterial strains that are depleted in IBD dysbiosis.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>本研究探討多發性硬化症（MS）與腸道微生物群之間的關聯。研究指出，MS 患者的腸道菌相呈現失調狀態，包括短鏈脂肪酸（SCFA）產生菌減少，以及促發炎代謝菌的增加。這些微生物群落的變化伴隨著血液與腦脊髓液中代謝物（如色胺酸衍生物、膽汁酸及 SCFA）的顯著改變，這些物質經證實與神經發炎及退化密切相關。文中綜述了微生物代謝產物如何透過調節腸道與血腦屏障完整性、影響免疫細胞（T/B 細胞）反應，以及直接作用於神經膠質細胞來參與 MS 的致病機制。總結而言，MS 的發生與腸道菌群-代謝物軸的整體失調有關，而非單一病原體所致。該研究強調未來需進行多體學（multiomics）整合分析，以開發基於微生物群的生物標記與創新治療策略，旨在恢復患者的免疫與神經恆定。</t>
+          <t>本研究探討了兩種由人類梭狀芽孢桿菌組成的活體生物藥物（LBP，分別為 17-mix 和 11-mix）治療小鼠結腸炎的療效與機制。研究發現，這些菌群能有效緩解小鼠的慢性與特定病原體誘導的結腸炎。宏基因組學與代謝組學分析顯示，除了傳統的短鏈脂肪酸（SCFA）和 IL-10 途徑外，LBP 還能直接抑制共生病原菌，並透過細菌色胺酸代謝物，以不依賴 IL-10 的方式激活宿主的芳香烴受體（AhR）抗炎途徑。此發現揭示了腸道有益菌保護腸道的新機制，為發炎性腸道疾病（IBD）的微生態療法提供了重要科學依據。</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1877,37 +1847,37 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42647759/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648293/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>42647164</t>
+          <t>42647084</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sex differences in the gut microbiome and related metabolites: role in cardiometabolic disease.</t>
+          <t>Diet quality, gut microbiome, and inflammatory signatures in Puerto Rican adults with Crohn disease: a multidimensional analysis.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>Inflammatory bowel diseases</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11</v>
+        <v>4.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>未提及（本文為綜論性回顧文章，非原創實驗研究）</t>
+          <t>60位患有克隆氏症的成年人 (60 adults with CD)</t>
         </is>
       </c>
       <c r="G28" t="b">
@@ -1915,12 +1885,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sex differences in major cardiometabolic diseases (CMD), such as type 2 diabetes, metabolic dysfunction-associated steatotic liver disease, and cardiovascular disease, have been increasingly recognized across the life course. During the reproductive stage, women generally have a more favorable cardiometabolic risk profile than men, but their risk of experiencing CMD significantly increases after menopause. Emerging evidence suggests that sexually dimorphic gut microbiota and gut microbiota-related metabolites (GMRMs) may contribute to such sex disparities. However, existing findings are heterogeneous and underlying mechanisms remain incompletely understood. In this review, we synthesize the evidence examining sex differences in gut microbial diversity, overall composition, taxa abundances, and levels of GMRMs across key life stages, including pre-puberty, adolescence, and different phases of adulthood (with emphasis on pre- and post-menopausal periods). We summarize potential biological mechanisms underlying sexual dimorphism in the gut microbiome and GMRMs, emphasizing the central role of sex steroids, along with contributions from immune function and other host and environmental factors. We further integrate evidence linking sexually dimorphic microbial taxa (e.g., Akkermansia muciniphila, Eubacterium, Ruminococcus, and other Firmicutes taxa) and GMRMs (e.g., microbiota-derived short-chain fatty acids, secondary bile acids, and trimethylamine N-oxide) to key cardiometabolic pathways involving inflammation, glucose and lipid metabolism, and vascular function. Finally, we identify critical knowledge gaps and emphasize the need for future large longitudinal studies that would integrate repeated measurements of the gut microbiome, untargeted metabolomics, and sex steroid hormones across the life course. Such approaches are essential to clarify biological pathways and inform sex-specific microbiome-based interventions for CMD prevention and management.</t>
+          <t>Diet is increasingly recognized as a modifiable factor influencing gut microbiome and outcomes in Crohn disease (CD), yet data in underrepresented populations remain limited. We evaluated diet quality, dietary patterns, gut microbiome composition, inflammatory markers, and patient-reported outcomes in adults with CD from Puerto Rico. We conducted a cross-sectional analysis of 60 adults with CD enrolled prior to dietary intervention in a parent study. Dietary intake was assessed using 24-hour recalls and evaluated using the Healthy Eating Index-2015 (HEI-2015), Alternative Healthy Eating Index-2010 (AHEI-2010), and exploratory dietary pattern analysis. The gut microbiome was assessed by shotgun metagenomic sequencing. Clinical outcomes included fecal calprotectin, C-reactive protein (CRP), a 96-cytokine panel, short Crohn Disease Activity Index (sCDAI), and short Inflammatory Bowel Disease Questionnaire (sIBDQ). Associations were evaluated using unadjusted and adjusted models with false discovery rate (FDR) correction. Overall diet quality was poor and characterized by low intake of fruits, vegetables, whole grains, and fiber, alongside high intake of saturated fat, added sugars, and animal-derived protein. Four dietary patterns were identified: vegetable-rich, dairy-rich, fruit-rich, and coffee/sweetener-rich. Participants adhering to the fruit-rich pattern exhibited the highest diet quality scores. Higher HEI-2015 scores were associated with greater gut microbial diversity and differences in overall microbiome composition. Participants with greater adherence to the vegetable-rich pattern showed modest increases in microbial diversity. Exploratory analyses suggested that higher fruit intake and adherence to a fruit-rich dietary pattern were associated with lower fecal calprotectin and CRP levels, whereas adherence to a vegetable-rich pattern was associated with better health-related quality of life (HRQoL) and adherence to a coffee/sweetener-rich pattern was associated with a worse symptom burden. However, no associations between dietary metrics and inflammatory markers, cytokines, or clinical outcomes remained significant after FDR correction. Most participants were in clinical remission despite substantial impairment in HRQoL. Adults with CD in Puerto Rico exhibited poor diet quality that was associated with gut microbial diversity and exploratory differences in clinical outcomes. While these findings support the influence of diet on the microbiome and clinical outcomes, larger longitudinal studies are needed to determine whether dietary improvements can influence disease outcomes this underrepresented population.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>本文旨在探討性別差異在腸道微生物群與相關代謝物（GMRMs）中如何影響心臟代謝疾病（CMD）。研究指出，受性類固醇、免疫功能及環境因素影響，腸道菌相與代謝產物存在顯著的性別二態性。女性在生育期較男性具備更佳的心臟代謝特徵，但停經後風險顯著升高，此變化與特定菌屬（如 *Akkermansia muciniphila*）及代謝物（如短鏈脂肪酸、次級膽汁酸、TMAO）的豐度改變密切相關。這些微生物與代謝物透過調節發炎反應、醣脂代謝及血管功能，進而影響 CMD 的發生。本文強調未來需透過大型縱向研究，結合微生物組學、代謝組學與荷爾蒙監測，以深入解析其生物學機制，並開發針對不同性別的精準微生物介入療法，對於預防及管理心臟代謝疾病具有重要的科學價值。</t>
+          <t>本研究探討波多黎各克隆氏症（CD）成年患者的飲食品質、腸道菌相與發炎指標的關係。研究發現，受試者普遍飲食品質不佳，而較高的飲食品質（特別是富含水果的飲食模式）與較高的腸道菌群多樣性顯著相關。探索性分析顯示，多攝取水果與較低的發炎指標（鈣衛蛋白和C反應蛋白）相關，而蔬菜為主的飲食與較佳的生活品質相關（但經FDR校正後未達顯著）。本研究首次揭示了該少數受關注族群中飲食對菌相與臨床症狀的影響，為未來透過飲食干預管理CD及改善患者預後提供了科學依據。</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1930,37 +1900,37 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42647164/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647084/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>42647084</t>
+          <t>42647600</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Diet quality, gut microbiome, and inflammatory signatures in Puerto Rican adults with Crohn disease: a multidimensional analysis.</t>
+          <t>Urogenital immune signatures are associated with birth outcomes after maternal urinary tract infection.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Inflammatory bowel diseases</t>
+          <t>Science translational medicine</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4.3</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>60位患有克隆氏症的成年人 (60 adults with CD)</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G29" t="b">
@@ -1968,12 +1938,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Diet is increasingly recognized as a modifiable factor influencing gut microbiome and outcomes in Crohn disease (CD), yet data in underrepresented populations remain limited. We evaluated diet quality, dietary patterns, gut microbiome composition, inflammatory markers, and patient-reported outcomes in adults with CD from Puerto Rico. We conducted a cross-sectional analysis of 60 adults with CD enrolled prior to dietary intervention in a parent study. Dietary intake was assessed using 24-hour recalls and evaluated using the Healthy Eating Index-2015 (HEI-2015), Alternative Healthy Eating Index-2010 (AHEI-2010), and exploratory dietary pattern analysis. The gut microbiome was assessed by shotgun metagenomic sequencing. Clinical outcomes included fecal calprotectin, C-reactive protein (CRP), a 96-cytokine panel, short Crohn Disease Activity Index (sCDAI), and short Inflammatory Bowel Disease Questionnaire (sIBDQ). Associations were evaluated using unadjusted and adjusted models with false discovery rate (FDR) correction. Overall diet quality was poor and characterized by low intake of fruits, vegetables, whole grains, and fiber, alongside high intake of saturated fat, added sugars, and animal-derived protein. Four dietary patterns were identified: vegetable-rich, dairy-rich, fruit-rich, and coffee/sweetener-rich. Participants adhering to the fruit-rich pattern exhibited the highest diet quality scores. Higher HEI-2015 scores were associated with greater gut microbial diversity and differences in overall microbiome composition. Participants with greater adherence to the vegetable-rich pattern showed modest increases in microbial diversity. Exploratory analyses suggested that higher fruit intake and adherence to a fruit-rich dietary pattern were associated with lower fecal calprotectin and CRP levels, whereas adherence to a vegetable-rich pattern was associated with better health-related quality of life (HRQoL) and adherence to a coffee/sweetener-rich pattern was associated with a worse symptom burden. However, no associations between dietary metrics and inflammatory markers, cytokines, or clinical outcomes remained significant after FDR correction. Most participants were in clinical remission despite substantial impairment in HRQoL. Adults with CD in Puerto Rico exhibited poor diet quality that was associated with gut microbial diversity and exploratory differences in clinical outcomes. While these findings support the influence of diet on the microbiome and clinical outcomes, larger longitudinal studies are needed to determine whether dietary improvements can influence disease outcomes this underrepresented population.</t>
+          <t>Preterm birth is the leading cause of infant mortality, resulting in more than 1 million neonatal deaths globally each year. Maternal urinary tract infection (UTI) during pregnancy increases risk for preterm birth; however, biological processes mediating UTI-associated preterm birth are not well described. We established a murine maternal UTI model in which challenge with uropathogenic Escherichia coli (UPEC) initiated preterm labor and birth in about half of dams. Although bacterial burdens were similar, dams experiencing preterm birth displayed excessive bladder inflammation, elevated placental and decidual cytokines, higher proportions of male fetuses, and lower maternal serum interleukin-10 (IL-10) compared with nonlaboring dams. Exogenous IL-10 or lymph node sequestration of T cells reduced placental type 17 T helper cells (TH17 cells) and abrogated preterm birth. In a human pregnancy cohort, we correlated urinary cytokines with birth outcomes and urine culture status. These analyses yielded an exploratory, noninvasive culture-agnostic system for evaluating preterm birth risk, implicating T cell-related cytokines including IL-10, IL-15, GM-CSF, and RANTES. These findings demonstrate that our murine model provides a platform to investigate immunological and microbial factors governing UTI-associated preterm birth and, coupled with patient samples, may be used to identify candidate biomarkers and mechanistic targets for future investigation.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>本研究探討波多黎各克隆氏症（CD）成年患者的飲食品質、腸道菌相與發炎指標的關係。研究發現，受試者普遍飲食品質不佳，而較高的飲食品質（特別是富含水果的飲食模式）與較高的腸道菌群多樣性顯著相關。探索性分析顯示，多攝取水果與較低的發炎指標（鈣衛蛋白和C反應蛋白）相關，而蔬菜為主的飲食與較佳的生活品質相關（但經FDR校正後未達顯著）。本研究首次揭示了該少數受關注族群中飲食對菌相與臨床症狀的影響，為未來透過飲食干預管理CD及改善患者預後提供了科學依據。</t>
+          <t>本研究旨在探討孕婦尿路感染（UTI）導致早產的免疫機制。研究團隊建立尿路致病性大腸桿菌（UPEC）感染的孕鼠模型，發現發生早產的母鼠伴隨更嚴重的膀胱發炎、胎盤細胞激素升高及血清IL-10降低；給予外源性IL-10或抑制T細胞，能減少胎盤TH17細胞並預防早產。此外，人類佇列研究證實，尿液中T細胞相關細胞激素（如IL-10、IL-15等）與早產風險密切相關。本研究結合動物模型與臨床樣本，揭示了UTI引發早產的免疫關鍵，並為未來篩檢及治療提供了潛在的非侵入性生物標誌物與機制標靶。</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1983,27 +1953,29 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42647084/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647600/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>42644751</t>
+          <t>42648688</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Soil amelioration impacts viral ecology in saline-alkali lands.</t>
+          <t>Temperature Sensitivity of Pyrrhotite-Driven Metavanadate Bioreduction in Groundwater.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>The ISME journal</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>Environmental research</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>7.7</v>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>metagenomics</t>
@@ -2011,7 +1983,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>未提及（僅說明樣品來自中國4個主要鹽鹼地區，各包含「鹽鹼」與「改良後」兩種狀態之土壤）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G30" t="b">
@@ -2019,12 +1991,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>The continuous expansion of saline-alkali lands under climate change threatens food security and reduces soil carbon stocks. A common mitigation strategy is soil amelioration, which converts degraded soils back into an arable state. Microbes play critical roles in soil health and recovery. However, the viruses that infect these microbial communities, and their potential impacts during saline-alkali soil restoration, remain largely unknown. Here, we combined total soil metagenomics and viromics to investigate host-linked viral ecology across four major saline-alkali regions in China, each encompassing two soil amelioration statuses: saline-alkali and reclaimed. We found that viral community structure was shaped by both geography and soil amelioration status, with salinity and alkalinity emerging as key environmental factors. Viral populations were sensitive to soil restoration, showing strong amelioration-status endemism with functional adaptations. Virus-host dynamics ranged from reduced temperate viruses to abundance mismatches in those infecting key carbon-cycling microorganisms, including carbohydrate degraders. 13C-cellulose DNA-SIP experiments provided further support for this mismatch by tracing assimilated carbon transfer between active host and virus populations. Compared with saline-alkali soils, the relative abundance of hosts in restored soils increased from 39.0% to 61.0%, whereas the linked viruses decreased from 60.6% to 39.4%. Together, these findings reveal an underappreciated role of viruses in shaping saline-alkali soil amelioration trajectories, and could improve management strategies for degraded land recovery and carbon storage.</t>
+          <t>Pyrrhotite-driven metavanadate [V(V)] bioreduction is a promising green strategy for the remediation of vanadium-contaminated aquifers. However, how this microbially driven process responds to different temperatures remains unclear. Herein, the responses of pyrrhotite-driven V(V) bioreduction to different temperatures ranging from 4 to 45 °C were investigated. V(V) removal first increased and then decreased with increasing temperature, peaking at 35 °C, with the reaction rate constant reaching 0.077 d-1. V(V) could be reduced to VO2 precipitates, accompanied by oxidation of S(-II) and Fe(II) to sulfate and Fe(III), respectively. Metagenomic binning revealed that S(-II) oxidation was more sensitive to temperature changes than Fe(II) oxidation for V(V) reducers. Bacteria coupling V(V) reduction with both S(-II) and Fe(II) oxidation (e.g., Ramlibacter sp.) were detected exclusively at 35 °C. The transcription of functional genes (related to V(V) reduction, S(-II) oxidation, and Fe(II) oxidation), electron transport activity and related components all exhibited a temperature-dependent pattern, first increasing and then decreasing, with a peak at 35 °C. This study reveals the temperature sensitivity of pyrrhotite-driven V(V) bioreduction, which is helpful for risk assessment and targeted bioremediation of vanadium contamination under different temperature conditions.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>本研究旨在探討鹽鹼地改良過程中，病毒對土壤微生物生態與碳循環的影響。研究結合總體基因體與病毒體學，分析中國四大鹽鹼區。結果顯示，土壤改良狀態、鹽度與鹼度是塑造病毒社群的關鍵。在改良土壤中，宿主微生物相對豐度顯著上升（39.0%至61.0%），而關聯病毒減少（60.6%至39.4%），且溫和病毒比例降低，碳循環關鍵微生物的病毒與宿主出現豐度失衡。13C-纖維素DNA-SIP實驗證實了兩者間的活性碳轉移。此發現揭示了病毒在鹽鹼地恢復中的關鍵作用，有助優化土地改良與碳儲存策略。</t>
+          <t>本研究旨在探討不同溫度（4至45 °C）對地下水中磁黃鐵礦驅動的偏釩酸鹽 [V(V)] 生物還原過程之影響。研究發現，V(V) 去除率隨溫度升高呈先升後降趨勢，並在 35 °C 時達到峰值（反應速率常數 0.077 d⁻¹），此時 V(V) 被還原為 VO₂ 沉澱，並伴隨硫與鐵的氧化。總體基因體 binning 分析顯示，還原菌的硫氧化過程對溫度變化比鐵氧化更為敏感，且僅在 35 °C 下偵測到能同時耦合硫與鐵氧化的關鍵細菌（如 *Ramlibacter* sp.）。此外，相關功能基因轉錄與電子傳遞活性亦在 35 °C 達到頂峰。本研究揭示了該還原作用的溫度敏感性，為釩污染的環境風險評估與精準生物整治提供了科學依據。</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2034,37 +2006,35 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42644751/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648688/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>42648293</t>
+          <t>42644746</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Defined human Clostridia consortia reverse colitis via dual effects of tryptophan metabolites on microbiota and immunity.</t>
+          <t>Metabolic division of labour drives estuarine-coastal N2O emissions.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cell host &amp; microbe</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>18.7</v>
-      </c>
+          <t>The ISME journal</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>metagenomics, metabolomics</t>
+          <t>metagenomics, metatranscriptomics</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>974 個重建的 N2O 相關基因體（原文未提及具體的環境樣本採集數量）</t>
         </is>
       </c>
       <c r="G31" t="b">
@@ -2072,12 +2042,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Microbial dysbiosis and disrupted mucosal immune homeostasis are integrally involved in the pathogenesis of inflammatory bowel diseases (IBDs). Live biotherapeutic products (LBPs) offer a potential therapeutic strategy to restore beneficial microbes and mitigate disease. We investigated the therapeutic efficacy of 2 LBPs, human Clostridia consortia 17-mix and 11-mix, by treating established colitis in murine models. Both LBPs exhibited therapeutic effects in T cell-mediated chronic colitis models induced by human microbiota and in pathobiont-driven gnotobiotic colitis models established with combinations of IBD-relevant human-derived strains. Metagenomic and metabolomic analyses elucidated mechanisms that go beyond established functions driven by short-chain fatty acids (SCFAs) and interleukin (IL)-10-producing regulatory T cells. Notably, LBPs exerted therapeutic effects by directly inhibiting resident pathobionts and through IL-10-independent activation of host anti-inflammatory aryl hydrocarbon receptor (AhR) pathways by bacterial tryptophan metabolites. These results elucidate SCFA- and IL-10-independent protective mechanisms exerted by defined resident bacterial strains that are depleted in IBD dysbiosis.</t>
+          <t>Estuarine and coastal systems are global hotspots of marine nitrous oxide (N2O) emissions, where microbial nitrification and denitrification are the primary processes regulating N2O dynamics. However, how interactions among different N2O-associated microorganisms influence ecosystem-scale N2O emissions remains poorly understood. This study combined in situ N2O concentrations, 15N-based potential rates, metagenomics, metatranscriptomics, and genome-scale metabolic model analysis to explore N2O production and reduction processes in estuarine and coastal systems. Potential N2O production and reduction rates, together with in situ concentrations, the relative abundance, and the transcriptional activity of associated genes, were significantly higher at low salinity and declined toward coastal regions. Based on the gene content of 974 recovered N2O-associated genomes, microorganisms were classified into three functional groups: net N2O producers, net N2O consumers, and self-sustaining N2O players. The abundance, composition, and activity of these functional groups shifted along estuarine-coastal gradients. A larger NO/N2O exchange gap, reflecting the imbalance between model-inferred NO and N2O handoff potentials, was found at low salinity and was associated with elevated bottom-water N2O concentrations. Together, community-level division of labour and the associated exchange gap provide a conceptual framework for linking N2O-related functional groups to N2O accumulation in estuarine-coastal ecosystems.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>本研究探討了兩種由人類梭狀芽孢桿菌組成的活體生物藥物（LBP，分別為 17-mix 和 11-mix）治療小鼠結腸炎的療效與機制。研究發現，這些菌群能有效緩解小鼠的慢性與特定病原體誘導的結腸炎。宏基因組學與代謝組學分析顯示，除了傳統的短鏈脂肪酸（SCFA）和 IL-10 途徑外，LBP 還能直接抑制共生病原菌，並透過細菌色胺酸代謝物，以不依賴 IL-10 的方式激活宿主的芳香烴受體（AhR）抗炎途徑。此發現揭示了腸道有益菌保護腸道的新機制，為發炎性腸道疾病（IBD）的微生態療法提供了重要科學依據。</t>
+          <t>本研究旨在探討河口與沿海系統中，微生物交互作用如何驅動一氧化二氮（N2O）的排放。研究結合現場觀測、15N同位素速率、總體基因體與轉錄體學，重建了974個N2O相關基因體。結果指出，低鹽度區域的N2O產生與還原速率及基因表達顯著較高。研究將微生物劃分為淨產生者、淨消費者與自給自足者，並發現低鹽度區因群落間物質交換失衡，存在較大的NO/N2O交換缺口，進而導致底層水體N2O顯著累積。本研究建立了群落水平的「分工與交換缺口」理論框架，為預測及理解海洋生態系統N2O排放提供了關鍵的科學依據。</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2087,37 +2057,37 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42648293/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42644746/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>42647600</t>
+          <t>42649294</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Urogenital immune signatures are associated with birth outcomes after maternal urinary tract infection.</t>
+          <t>Synergistic degradation of fucoidans in the ocean.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Science translational medicine</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>48.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metabolomics, metagenomics</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（該研究採用重組海洋微生物群落進行實驗，未提供具體的生物樣本人數或檢體數量）</t>
         </is>
       </c>
       <c r="G32" t="b">
@@ -2125,12 +2095,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Preterm birth is the leading cause of infant mortality, resulting in more than 1 million neonatal deaths globally each year. Maternal urinary tract infection (UTI) during pregnancy increases risk for preterm birth; however, biological processes mediating UTI-associated preterm birth are not well described. We established a murine maternal UTI model in which challenge with uropathogenic Escherichia coli (UPEC) initiated preterm labor and birth in about half of dams. Although bacterial burdens were similar, dams experiencing preterm birth displayed excessive bladder inflammation, elevated placental and decidual cytokines, higher proportions of male fetuses, and lower maternal serum interleukin-10 (IL-10) compared with nonlaboring dams. Exogenous IL-10 or lymph node sequestration of T cells reduced placental type 17 T helper cells (TH17 cells) and abrogated preterm birth. In a human pregnancy cohort, we correlated urinary cytokines with birth outcomes and urine culture status. These analyses yielded an exploratory, noninvasive culture-agnostic system for evaluating preterm birth risk, implicating T cell-related cytokines including IL-10, IL-15, GM-CSF, and RANTES. These findings demonstrate that our murine model provides a platform to investigate immunological and microbial factors governing UTI-associated preterm birth and, coupled with patient samples, may be used to identify candidate biomarkers and mechanistic targets for future investigation.</t>
+          <t>Fucoidans, a class of complex polysaccharides produced by brown algae and diatoms, contribute to long-term carbon sequestration owing to their resistance to microbial degradation1,2. Although individual microorganisms can break down portions of these polysaccharides3-5, it remains unclear whether complete breakdown is possible in nature and, if so, by what mechanisms. Here we show that fucoidans are degraded through synergistic interactions between specialized bacteria with complementary metabolic functions. Using metabolomic analysis of a reconstructed marine consortium, we uncovered metabolic guilds of bacteria that preferentially degrade either the sulfated fucose backbone or the side branches of rare monomers. This functional division of labour leads to an unexpectedly high number of synergistic interactions between different degraders that enhanced degradation efficiency up to 97.1%. Despite varying fucoidan structures across different types of algae6, the metabolic functions of degraders remained conserved, enabling quantitative prediction of degradation outcomes based on community and substrate composition. The frequent co-occurrence of functionally complementary fucoidan degraders in ocean metagenomes suggests that synergistic degradation is a globally relevant strategy. Our findings suggest that the environmental turnover of complex biopolymers depends not only on individual metabolic capabilities of degraders but also on ecological interactions shaped by substrate architecture. This work provides a mechanistic framework for understanding carbon cycling in the ocean and for engineering synthetic microbial consortia to degrade recalcitrant polysaccharides.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>本研究旨在探討孕婦尿路感染（UTI）導致早產的免疫機制。研究團隊建立尿路致病性大腸桿菌（UPEC）感染的孕鼠模型，發現發生早產的母鼠伴隨更嚴重的膀胱發炎、胎盤細胞激素升高及血清IL-10降低；給予外源性IL-10或抑制T細胞，能減少胎盤TH17細胞並預防早產。此外，人類佇列研究證實，尿液中T細胞相關細胞激素（如IL-10、IL-15等）與早產風險密切相關。本研究結合動物模型與臨床樣本，揭示了UTI引發早產的免疫關鍵，並為未來篩檢及治療提供了潛在的非侵入性生物標誌物與機制標靶。</t>
+          <t>本研究探討海洋中複雜多醣體「褐藻醣膠」（fucoidans）的微生物降解機制。儘管褐藻醣膠因其抗降解性在碳封存中扮演關鍵角色，但過往對於其在自然界中是否能被完全分解並不清楚。研究發現，褐藻醣膠的降解並非單一物種所能完成，而是透過具有互補代謝功能的細菌群落進行「協同作用」。透過代謝體學分析，研究團隊識別出專門降解硫酸岩藻糖骨架與稀有單醣側鏈的代謝群組（metabolic guilds），這種分工合作能將降解效率大幅提升至 97.1%。此外，研究顯示此代謝功能在不同環境下具有高度保守性，且在海洋宏基因組中普遍存在。本研究揭示了生物聚合物的環境周轉率取決於微生物間的生態交互作用，為理解海洋碳循環機制提供了重要框架，並為未來利用人工合成微生物群落降解頑固性多醣體提供了技術基礎。</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2140,29 +2110,27 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42647600/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42649294/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>42648688</t>
+          <t>42657129</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Temperature Sensitivity of Pyrrhotite-Driven Metavanadate Bioreduction in Groundwater.</t>
+          <t>Pulmonary Infiltrates, Airway Mucosal Lesions and Respiratory Microbiology After Freshwater Drowning: A Case Report.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Environmental research</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>7.7</v>
-      </c>
+          <t>Respirology case reports</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>metagenomics</t>
@@ -2170,7 +2138,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>1 例病患（n=1）</t>
         </is>
       </c>
       <c r="G33" t="b">
@@ -2178,12 +2146,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Pyrrhotite-driven metavanadate [V(V)] bioreduction is a promising green strategy for the remediation of vanadium-contaminated aquifers. However, how this microbially driven process responds to different temperatures remains unclear. Herein, the responses of pyrrhotite-driven V(V) bioreduction to different temperatures ranging from 4 to 45 °C were investigated. V(V) removal first increased and then decreased with increasing temperature, peaking at 35 °C, with the reaction rate constant reaching 0.077 d-1. V(V) could be reduced to VO2 precipitates, accompanied by oxidation of S(-II) and Fe(II) to sulfate and Fe(III), respectively. Metagenomic binning revealed that S(-II) oxidation was more sensitive to temperature changes than Fe(II) oxidation for V(V) reducers. Bacteria coupling V(V) reduction with both S(-II) and Fe(II) oxidation (e.g., Ramlibacter sp.) were detected exclusively at 35 °C. The transcription of functional genes (related to V(V) reduction, S(-II) oxidation, and Fe(II) oxidation), electron transport activity and related components all exhibited a temperature-dependent pattern, first increasing and then decreasing, with a peak at 35 °C. This study reveals the temperature sensitivity of pyrrhotite-driven V(V) bioreduction, which is helpful for risk assessment and targeted bioremediation of vanadium contamination under different temperature conditions.</t>
+          <t>Early pulmonary abnormalities after freshwater drowning can be overinterpreted as bacterial pneumonia, especially when inflammatory biomarkers and respiratory microbiology are positive. A 20-year-old man was resuscitated after approximately 2 min of freshwater submersion. Day 1 chest CT showed bilateral lower-lobe-predominant opacities compatible with non-cardiogenic pulmonary oedema and aspiration-related lung injury, with near-complete resolution by Day 25. Day 3 bronchoscopy showed diffuse, non-removable, millet-seed-like whitish tracheal mucosal protrusions with hyperaemia and oedema, compatible with acute irritative airway injury. BALF mNGS detected multiple gram-negative bacterial signals, predominantly Klebsiella pneumoniae, while sputum culture yielded ESBL-negative, susceptible K. pneumoniae. Possible drowning-associated pneumonia was considered because of aspiration, fever, markedly elevated inflammatory biomarkers and concordant microbiology; however, rapid radiological improvement and clinical stability suggested a substantial non-infectious component. The patient recovered after an 8-day course of piperacillin-tazobactam without antibiotic escalation, corticosteroids, mechanical ventilation or acute respiratory distress syndrome.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>本研究旨在探討不同溫度（4至45 °C）對地下水中磁黃鐵礦驅動的偏釩酸鹽 [V(V)] 生物還原過程之影響。研究發現，V(V) 去除率隨溫度升高呈先升後降趨勢，並在 35 °C 時達到峰值（反應速率常數 0.077 d⁻¹），此時 V(V) 被還原為 VO₂ 沉澱，並伴隨硫與鐵的氧化。總體基因體 binning 分析顯示，還原菌的硫氧化過程對溫度變化比鐵氧化更為敏感，且僅在 35 °C 下偵測到能同時耦合硫與鐵氧化的關鍵細菌（如 *Ramlibacter* sp.）。此外，相關功能基因轉錄與電子傳遞活性亦在 35 °C 達到頂峰。本研究揭示了該還原作用的溫度敏感性，為釩污染的環境風險評估與精準生物整治提供了科學依據。</t>
+          <t>本研究透過單一病例報告，探討淡水溺水後肺部浸潤與呼吸道損傷的臨床鑑別診斷。一名 20 歲男性溺水後出現肺水腫與氣道黏膜病變，臨床表現極易與細菌性肺炎混淆。研究利用 mNGS（宏基因組次世代定序）檢測支氣管肺泡灌洗液，雖確認存在肺炎克雷伯菌（*Klebsiella pneumoniae*）訊號，但影像學與臨床病程顯示其肺部損傷主要源於吸入性損傷及急性化學性氣道刺激，而非嚴重的細菌感染。此案例凸顯了臨床判斷溺水相關肺炎時的挑戰，強調在面對看似感染的臨床數據時，應綜合考量影像改善速度與臨床穩定性，避免過度診斷與不必要的抗生素升級，對急性溺水病患的精準治療具有重要的臨床參考價值。</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2193,35 +2161,37 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42648688/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42657129/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>42644746</t>
+          <t>42647164</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Metabolic division of labour drives estuarine-coastal N2O emissions.</t>
+          <t>Sex differences in the gut microbiome and related metabolites: role in cardiometabolic disease.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>The ISME journal</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>Gut microbes</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11</v>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>metagenomics, metatranscriptomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>974 個重建的 N2O 相關基因體（原文未提及具體的環境樣本採集數量）</t>
+          <t>未提及（本文為綜論性回顧文章，非原創實驗研究）</t>
         </is>
       </c>
       <c r="G34" t="b">
@@ -2229,12 +2199,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Estuarine and coastal systems are global hotspots of marine nitrous oxide (N2O) emissions, where microbial nitrification and denitrification are the primary processes regulating N2O dynamics. However, how interactions among different N2O-associated microorganisms influence ecosystem-scale N2O emissions remains poorly understood. This study combined in situ N2O concentrations, 15N-based potential rates, metagenomics, metatranscriptomics, and genome-scale metabolic model analysis to explore N2O production and reduction processes in estuarine and coastal systems. Potential N2O production and reduction rates, together with in situ concentrations, the relative abundance, and the transcriptional activity of associated genes, were significantly higher at low salinity and declined toward coastal regions. Based on the gene content of 974 recovered N2O-associated genomes, microorganisms were classified into three functional groups: net N2O producers, net N2O consumers, and self-sustaining N2O players. The abundance, composition, and activity of these functional groups shifted along estuarine-coastal gradients. A larger NO/N2O exchange gap, reflecting the imbalance between model-inferred NO and N2O handoff potentials, was found at low salinity and was associated with elevated bottom-water N2O concentrations. Together, community-level division of labour and the associated exchange gap provide a conceptual framework for linking N2O-related functional groups to N2O accumulation in estuarine-coastal ecosystems.</t>
+          <t>Sex differences in major cardiometabolic diseases (CMD), such as type 2 diabetes, metabolic dysfunction-associated steatotic liver disease, and cardiovascular disease, have been increasingly recognized across the life course. During the reproductive stage, women generally have a more favorable cardiometabolic risk profile than men, but their risk of experiencing CMD significantly increases after menopause. Emerging evidence suggests that sexually dimorphic gut microbiota and gut microbiota-related metabolites (GMRMs) may contribute to such sex disparities. However, existing findings are heterogeneous and underlying mechanisms remain incompletely understood. In this review, we synthesize the evidence examining sex differences in gut microbial diversity, overall composition, taxa abundances, and levels of GMRMs across key life stages, including pre-puberty, adolescence, and different phases of adulthood (with emphasis on pre- and post-menopausal periods). We summarize potential biological mechanisms underlying sexual dimorphism in the gut microbiome and GMRMs, emphasizing the central role of sex steroids, along with contributions from immune function and other host and environmental factors. We further integrate evidence linking sexually dimorphic microbial taxa (e.g., Akkermansia muciniphila, Eubacterium, Ruminococcus, and other Firmicutes taxa) and GMRMs (e.g., microbiota-derived short-chain fatty acids, secondary bile acids, and trimethylamine N-oxide) to key cardiometabolic pathways involving inflammation, glucose and lipid metabolism, and vascular function. Finally, we identify critical knowledge gaps and emphasize the need for future large longitudinal studies that would integrate repeated measurements of the gut microbiome, untargeted metabolomics, and sex steroid hormones across the life course. Such approaches are essential to clarify biological pathways and inform sex-specific microbiome-based interventions for CMD prevention and management.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>本研究旨在探討河口與沿海系統中，微生物交互作用如何驅動一氧化二氮（N2O）的排放。研究結合現場觀測、15N同位素速率、總體基因體與轉錄體學，重建了974個N2O相關基因體。結果指出，低鹽度區域的N2O產生與還原速率及基因表達顯著較高。研究將微生物劃分為淨產生者、淨消費者與自給自足者，並發現低鹽度區因群落間物質交換失衡，存在較大的NO/N2O交換缺口，進而導致底層水體N2O顯著累積。本研究建立了群落水平的「分工與交換缺口」理論框架，為預測及理解海洋生態系統N2O排放提供了關鍵的科學依據。</t>
+          <t>本文旨在探討性別差異在腸道微生物群與相關代謝物（GMRMs）中如何影響心臟代謝疾病（CMD）。研究指出，受性類固醇、免疫功能及環境因素影響，腸道菌相與代謝產物存在顯著的性別二態性。女性在生育期較男性具備更佳的心臟代謝特徵，但停經後風險顯著升高，此變化與特定菌屬（如 *Akkermansia muciniphila*）及代謝物（如短鏈脂肪酸、次級膽汁酸、TMAO）的豐度改變密切相關。這些微生物與代謝物透過調節發炎反應、醣脂代謝及血管功能，進而影響 CMD 的發生。本文強調未來需透過大型縱向研究，結合微生物組學、代謝組學與荷爾蒙監測，以深入解析其生物學機制，並開發針對不同性別的精準微生物介入療法，對於預防及管理心臟代謝疾病具有重要的科學價值。</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2244,37 +2214,35 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42644746/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647164/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>42649294</t>
+          <t>42647759</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Synergistic degradation of fucoidans in the ocean.</t>
+          <t>The Gut Microbiome in Multiple Sclerosis.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Nature</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>48.5</v>
-      </c>
+          <t>Neurology(R) neuroimmunology &amp; neuroinflammation</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>metabolomics, metagenomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>未提及（該研究採用重組海洋微生物群落進行實驗，未提供具體的生物樣本人數或檢體數量）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G35" t="b">
@@ -2282,12 +2250,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Fucoidans, a class of complex polysaccharides produced by brown algae and diatoms, contribute to long-term carbon sequestration owing to their resistance to microbial degradation1,2. Although individual microorganisms can break down portions of these polysaccharides3-5, it remains unclear whether complete breakdown is possible in nature and, if so, by what mechanisms. Here we show that fucoidans are degraded through synergistic interactions between specialized bacteria with complementary metabolic functions. Using metabolomic analysis of a reconstructed marine consortium, we uncovered metabolic guilds of bacteria that preferentially degrade either the sulfated fucose backbone or the side branches of rare monomers. This functional division of labour leads to an unexpectedly high number of synergistic interactions between different degraders that enhanced degradation efficiency up to 97.1%. Despite varying fucoidan structures across different types of algae6, the metabolic functions of degraders remained conserved, enabling quantitative prediction of degradation outcomes based on community and substrate composition. The frequent co-occurrence of functionally complementary fucoidan degraders in ocean metagenomes suggests that synergistic degradation is a globally relevant strategy. Our findings suggest that the environmental turnover of complex biopolymers depends not only on individual metabolic capabilities of degraders but also on ecological interactions shaped by substrate architecture. This work provides a mechanistic framework for understanding carbon cycling in the ocean and for engineering synthetic microbial consortia to degrade recalcitrant polysaccharides.</t>
+          <t>Multiple sclerosis (MS) is a chronic inflammatory demyelinating disease of the CNS whose risk and course are shaped by both genetic and environmental factors, among which the intestinal microbiota has emerged as a key, potentially modifiable contributor. People with MS frequently display altered gut microbiota, characterized by depletion of fiber-fermenting, short-chain fatty acid (SCFA)-producing commensals, and expansion of taxa associated with mucus degradation and proinflammatory metabolism. These compositional shifts are paralleled by broad changes in blood and CSF metabolites, including reduced SCFAs, tryptophan-derived aryl hydrocarbon receptor ligands, and secondary bile acids. In addition, several reports highlight the accumulation of aromatic amino acid-derived phenolic and indolic compounds and specific lipid mediators linked to neuroinflammation and neurodegeneration. In this up-to-date review, we synthesize evidence from experimental models and human studies showing how microbial metabolites can influence MS pathogenesis through converging mechanisms: modulation of gut and blood-brain barrier integrity; shaping of T-cell and B-cell responses; direct effects on microglia, astrocytes, and oligodendrocyte lineage cells after crossing into the CNS; and modulation of neural circuits, particularly those involving the vagus nerve. Finally, we highlight current gaps, including the need for longitudinal, harmonized multiomic cohorts, and mechanistic studies integrating microbiome, metabolome, and host readouts across gut, blood, and CNS. Overall, available data support a model in which coordinated disruption of the gut microbiota-metabolite axis, rather than any single pathogen, contributes to MS, opening avenues for microbiota-based and metabolite-based biomarkers and therapies aimed at restoring immune and neuroglial homeostasis.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>本研究探討海洋中複雜多醣體「褐藻醣膠」（fucoidans）的微生物降解機制。儘管褐藻醣膠因其抗降解性在碳封存中扮演關鍵角色，但過往對於其在自然界中是否能被完全分解並不清楚。研究發現，褐藻醣膠的降解並非單一物種所能完成，而是透過具有互補代謝功能的細菌群落進行「協同作用」。透過代謝體學分析，研究團隊識別出專門降解硫酸岩藻糖骨架與稀有單醣側鏈的代謝群組（metabolic guilds），這種分工合作能將降解效率大幅提升至 97.1%。此外，研究顯示此代謝功能在不同環境下具有高度保守性，且在海洋宏基因組中普遍存在。本研究揭示了生物聚合物的環境周轉率取決於微生物間的生態交互作用，為理解海洋碳循環機制提供了重要框架，並為未來利用人工合成微生物群落降解頑固性多醣體提供了技術基礎。</t>
+          <t>本研究探討多發性硬化症（MS）與腸道微生物群之間的關聯。研究指出，MS 患者的腸道菌相呈現失調狀態，包括短鏈脂肪酸（SCFA）產生菌減少，以及促發炎代謝菌的增加。這些微生物群落的變化伴隨著血液與腦脊髓液中代謝物（如色胺酸衍生物、膽汁酸及 SCFA）的顯著改變，這些物質經證實與神經發炎及退化密切相關。文中綜述了微生物代謝產物如何透過調節腸道與血腦屏障完整性、影響免疫細胞（T/B 細胞）反應，以及直接作用於神經膠質細胞來參與 MS 的致病機制。總結而言，MS 的發生與腸道菌群-代謝物軸的整體失調有關，而非單一病原體所致。該研究強調未來需進行多體學（multiomics）整合分析，以開發基於微生物群的生物標記與創新治療策略，旨在恢復患者的免疫與神經恆定。</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2297,24 +2265,24 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42649294/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647759/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>42657129</t>
+          <t>42648171</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pulmonary Infiltrates, Airway Mucosal Lesions and Respiratory Microbiology After Freshwater Drowning: A Case Report.</t>
+          <t>Co-occurrence of muddy off flavor and cyanotoxin genes in the polluted Guandu river waters (Rio de Janeiro, Brazil).</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Respirology case reports</t>
+          <t>The Science of the total environment</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -2325,7 +2293,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1 例病患（n=1）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G36" t="b">
@@ -2333,12 +2301,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Early pulmonary abnormalities after freshwater drowning can be overinterpreted as bacterial pneumonia, especially when inflammatory biomarkers and respiratory microbiology are positive. A 20-year-old man was resuscitated after approximately 2 min of freshwater submersion. Day 1 chest CT showed bilateral lower-lobe-predominant opacities compatible with non-cardiogenic pulmonary oedema and aspiration-related lung injury, with near-complete resolution by Day 25. Day 3 bronchoscopy showed diffuse, non-removable, millet-seed-like whitish tracheal mucosal protrusions with hyperaemia and oedema, compatible with acute irritative airway injury. BALF mNGS detected multiple gram-negative bacterial signals, predominantly Klebsiella pneumoniae, while sputum culture yielded ESBL-negative, susceptible K. pneumoniae. Possible drowning-associated pneumonia was considered because of aspiration, fever, markedly elevated inflammatory biomarkers and concordant microbiology; however, rapid radiological improvement and clinical stability suggested a substantial non-infectious component. The patient recovered after an 8-day course of piperacillin-tazobactam without antibiotic escalation, corticosteroids, mechanical ventilation or acute respiratory distress syndrome.</t>
+          <t>The Guandu river basin is responsible for supplying Rio de Janeiro municipality, Brazil, with drinking water. This study investigated water quality during the geosmin crisis in January and March 2020, by relating the water quality and odor compounds with metagenomic tools. Guandu river water was eutrophic. The cyanobacterial genera identified were Microcystis, Planktothrix, Dolichospermum, Nostoc, Synechococcus, Planktothricoides, and Cyanobium, indicating that bloom-associated communities in the system are taxonomically diverse. Functional annotation of metagenomic sequences revealed the presence of genes associated with the biosynthesis of taste-and-odor compounds, including geosmin (geoA) and 2-methylisoborneol (mic), as well as multiple biosynthetic clusters related to cyanotoxin production. Genes linked to microcystin (mcy), saxitoxin (sxt), anatoxin (ana), cylindrospermopsin (cyr), lyngbyatoxin (ltx), guanitoxin (gnt), and nodularin (nda) were detected across the dataset, indicating a broad genetic potential for the production of secondary metabolites relevant to water quality. The co-occurrence of cyanotoxins, geosmin and 2-MIB genes suggests that off-flavor is an indication of cyanotoxin potential production in the water.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>本研究透過單一病例報告，探討淡水溺水後肺部浸潤與呼吸道損傷的臨床鑑別診斷。一名 20 歲男性溺水後出現肺水腫與氣道黏膜病變，臨床表現極易與細菌性肺炎混淆。研究利用 mNGS（宏基因組次世代定序）檢測支氣管肺泡灌洗液，雖確認存在肺炎克雷伯菌（*Klebsiella pneumoniae*）訊號，但影像學與臨床病程顯示其肺部損傷主要源於吸入性損傷及急性化學性氣道刺激，而非嚴重的細菌感染。此案例凸顯了臨床判斷溺水相關肺炎時的挑戰，強調在面對看似感染的臨床數據時，應綜合考量影像改善速度與臨床穩定性，避免過度診斷與不必要的抗生素升級，對急性溺水病患的精準治療具有重要的臨床參考價值。</t>
+          <t>本研究旨在探究巴西里約熱內盧瓜杜河於2020年初爆發土臭素危機期間的水質狀況，並利用總體基因體學技術探討水質異味與微生物群落之關聯。研究發現，該富營養化水體中含有多種藍菌，且功能性註釋顯示其富含合成土臭素（*geoA*）與2-甲基異莰醇（*mic*）等異味物質的基因。更重要的是，多種藍菌毒素（如微囊藻毒素、石房蛤毒素等）的合成基因群與這些異味基因呈現共存。此發現證實了水體異味的出現與藍菌毒素的潛在生成具有高度相關性，可作為飲用水安全監測及評估藍菌毒素潛在危害的重要預警指標。</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2348,37 +2316,37 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42657129/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648171/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>42642836</t>
+          <t>42644416</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Microbiome-mediated regulation of pathogen virulence: Molecular mechanisms and clinical implications.</t>
+          <t>Nationwide cohort study reveals low bifidobacteria and distinct microbiota composition and function in Swedish newborns.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Virulence</t>
+          <t>Gut microbes</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>5.4</v>
+        <v>11</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>308 名瑞典新生兒的糞便檢體</t>
         </is>
       </c>
       <c r="G37" t="b">
@@ -2386,530 +2354,532 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>The human microbiome profoundly influences pathogen virulence and disease susceptibility through diverse molecular mechanisms. This review, focused on literature from 2016 to 2026, synthesizes knowledge on microbiome-mediated regulation examining major pathogens including Vibrio cholerae, enterohemorrhagic Escherichia coli, Salmonella species, Clostridioides difficile, and Staphylococcus aureus. A triangular interaction model is presented, linking host immunity, resident microbiome, and invading pathogen to frame infection outcomes. Commensal bacteria regulate pathogen behavior through quorum sensing interference, metabolite-mediated regulation via short-chain fatty acids and bile acids, competitive exclusion, immune response modulation, and direct antimicrobial production. Key species-Lactobacillus spp. Bifidobacterium spp. Bacteroides thetaiotaomicron, and Faecalibacterium prausnitzii-employ distinct molecular strategies against these pathogens. Organ-on-chip platforms and multi-omics advances reveal context-dependent interactions. Clinical applications including rationally designed probiotics, fecal microbiota transplantation, and precision microbiome engineering show promise despite challenges of inter-individual microbiome variability, representing a paradigm shift toward ecosystem-based infectious disease management.</t>
+          <t>NCT06285630.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>本研究綜述了2016年至2026年間關於腸道微生物群調控病原體毒力（如霍亂弧菌、大腸桿菌、沙門氏菌等）的分子機制。作者提出了一個結合宿主免疫、共生菌群與入侵病原體的「三角交互模型」，闡述了共生菌如何透過群體感應干擾、代謝產物（如短鏈脂肪酸、膽汁酸）調節、競爭性排斥及免疫調節來抑制病原體。研究強調了乳酸桿菌、雙歧桿菌及普拉梭菌等關鍵菌種的保護機制，並探討了器官晶片與多體學技術在揭示交互作用上的貢獻。此研究主張從生態系統角度管理傳染病，指出益生菌設計、糞便菌群移植及精準微生物組工程是未來治療的關鍵方向，雖面臨個體差異挑戰，但為臨床感染控制提供了典範轉移。</t>
+          <t>本研究旨在探討瑞典新生兒的腸道菌相組成與功能特徵。透過總體基因體學分析，研究發現瑞典新生兒腸道中的雙歧桿菌（特別是嬰兒雙歧桿菌）豐度顯著偏低，並呈現出獨特的菌相結構與代謝功能。此現象與現代化生活型態及分娩方式密切相關。這項全國性世代研究揭示了現代環境對嬰兒早期腸道微生態建立的深遠影響，為未來的臨床嬰幼兒益生菌介入與健康照護策略提供了關鍵的科學依據。</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42642836/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42644416/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>42669226</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Preparation and chemical characterization of polyphenol-rich extract from Tsaoko Fructus: alleviation of ulcerative colitis in mice by modulating gut microbiota and suppressing the JNK1-cJun signaling.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Phytomedicine : international journal of phytotherapy and phytopharmacology</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>metagenomics, others</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G38" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Tsaoko Fructus, a traditional Chinese medicinal herb, has long been used to alleviate gastritis and enteritis. Nevertheless, the active constituents and underlying anti-inflammatory mechanisms remain insufficiently characterized. This study aims to optimize a polyphenol-rich fraction (3CB) from Tsaoko Fructus, evaluate its effects against ulcerative colitis (UC), and reveal the underlying mechanisms of action. The preparation of 3CB was optimized using response surface methodology (RSM), and its major constituents were identified by LC-PDA-MS analysis. A murine UC model was established by administering dextran sulfate sodium (DSS). To evaluate the effects of 3CB on UC mice, metagenomic sequencing of the intestinal microbiome and RNA sequencing of colon tissues were conducted. The anti-inflammatory activity of 3CB and its principal constituents was further verified by quantitative real-time PCR (qPCR), Enzyme linked immunosorbent assay (ELISA), Western blotting, immunohistochemical staining, and histopathological analysis. Network pharmacology, molecular docking, and surface plasmon resonance (SPR) assays were employed to elucidate the molecular mechanisms underlying the anti-inflammatory effects of 3CB. 3CB significantly alleviated UC symptoms in DSS-induced mice, reshaped the gut microbiota with reducing pathogenic Pseudomonadota and Deferribacterota while enriching beneficial Bacteroidota, and restored microbial amino sugar and nucleotide sugar metabolism pathways of intestinal flora. Additionally, 3CB preserved colonic oxidative phosphorylation, protected the mucus barrier, and suppressed inflammatory cell infiltration and the expression of cytokines. Seven major polyphenols were identified in 3CB, with epicatechin (3) and epiafzelechin (6) being the most abundant. Mechanistic investigation revealed that the anti-inflammatory effect of 3CB was partially dependent on the JNK1-modulated MAPK signaling pathway. JNK1 was identified as a direct target of 3CB, with epiafzelechin (6) exhibiting a high binding affinity (Kd = 10.4 μM). 3CB ameliorates UC potentially through modulation of gut microbiota, protection of the mucus barrier, and JNK1-targeted anti-inflammatory effects, highlighting its potential as a protective intervention for inflammatory bowel disease (IBD).</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>本研究旨在探討草果（Tsaoko Fructus）富含多酚之萃取物（3CB）對潰瘍性結腸炎（UC）的緩解作用及其機制。研究透過 LC-PDA-MS 定性出 3CB 中的七種主要多酚成分，並利用 DSS 誘導的小鼠 UC 模型進行實驗。結果顯示，3CB 能顯著緩解結腸炎臨床症狀，其機制涉及調節腸道微生物群（如減少致病菌 Pseudomonadota，增加有益菌 Bacteroidota）並恢復代謝路徑。分子層面上，3CB 能保護黏液屏障、抑制發炎因子表現，且被證實能直接靶向並調控 JNK1-cJun 訊號傳導路徑，其中成分表兒茶素（epiafzelechin）展現出高結合親和力。本研究證實草果多酚具有作為發炎性腸道疾病治療潛力藥物的科學價值，為中藥臨床應用提供了分子機制依據。</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42669226/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>42648218</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Agricultural sprinkler irrigation systems as environmental reservoirs and airborne dissemination sources of Legionella pneumophila.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Journal of environmental management</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>metagenomics, small genome</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>未明確提及具體檢體數量（僅指出於西班牙東北部農村的兩個區域，針對灌溉池塘與溝渠進行採樣）</t>
+        </is>
+      </c>
+      <c r="G39" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sprinkler irrigation systems are critical for modern agriculture but represent largely unrecognized aquatic environments capable of sustaining opportunistic human pathogens. Among them, Legionella pneumophila is of particular concern due to its ability to colonize engineered water systems, persist under fluctuating environmental conditions, and be transmitted through aerosols. In this study, we conducted a comprehensive microbiological and genomic investigation of irrigation ponds and ditches in a rural area of north-east Spain where two zones were sampled. Metagenomic profiling revealed highly diverse microbial communities encompassing more than 20,000 species, including 21 airborne-transmissible bacterial pathogens of clinical relevance. Notably, L. pneumophila was detected in both zones, with a relative abundance of up to 4.6 %. Culture-based isolation confirmed the presence of L. pneumophila serogroup 1, Pontiac group, Benidorm subgroup, sequence type 15. Phylogenetic analysis demonstrated a close relationship between this environmental strain and clinical isolates obtained during a Legionnaires' disease outbreak occurred in 2015, which had remained without a confirmed environmental source. Meteorological data from the exposure period revealed wind conditions favouring long-distance aerosol dispersion from irrigated fields toward residential areas. Our findings provide evidence that irrigation infrastructures can act as environmental reservoirs and dissemination routes of L. pneumophila among other airborne pathogens. These results underscore the need to incorporate agricultural irrigation systems into routine environmental surveillance, outbreak investigations, and public health risk assessments.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>本研究旨在探討農業噴灌系統是否為嗜肺軍團菌（*Legionella pneumophila*）等致病菌的環境宿主與空氣傳播源。團隊對西班牙農村灌溉水體進行分析，總體基因體學顯示其含有逾2萬種微生物，包括21種臨床相關的空氣傳播病原體，且嗜肺軍團菌相對豐度達4.6%。研究成功分離出嗜肺軍團菌血清型1（ST15），系統發育分析證實該環境株與2015年退伍軍人症爆發的臨床分離株高度相關。氣象數據亦支持風向有利於氣膠從農田長距離擴散至住宅區。此發現證實農業灌溉系統為軍團菌的傳播媒介，強調應將其納入例行環境監測與公衛風險評估。</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648218/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>42642836</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Microbiome-mediated regulation of pathogen virulence: Molecular mechanisms and clinical implications.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Virulence</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G40" t="b">
+        <v>0</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>The human microbiome profoundly influences pathogen virulence and disease susceptibility through diverse molecular mechanisms. This review, focused on literature from 2016 to 2026, synthesizes knowledge on microbiome-mediated regulation examining major pathogens including Vibrio cholerae, enterohemorrhagic Escherichia coli, Salmonella species, Clostridioides difficile, and Staphylococcus aureus. A triangular interaction model is presented, linking host immunity, resident microbiome, and invading pathogen to frame infection outcomes. Commensal bacteria regulate pathogen behavior through quorum sensing interference, metabolite-mediated regulation via short-chain fatty acids and bile acids, competitive exclusion, immune response modulation, and direct antimicrobial production. Key species-Lactobacillus spp. Bifidobacterium spp. Bacteroides thetaiotaomicron, and Faecalibacterium prausnitzii-employ distinct molecular strategies against these pathogens. Organ-on-chip platforms and multi-omics advances reveal context-dependent interactions. Clinical applications including rationally designed probiotics, fecal microbiota transplantation, and precision microbiome engineering show promise despite challenges of inter-individual microbiome variability, representing a paradigm shift toward ecosystem-based infectious disease management.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>本研究綜述了2016年至2026年間關於腸道微生物群調控病原體毒力（如霍亂弧菌、大腸桿菌、沙門氏菌等）的分子機制。作者提出了一個結合宿主免疫、共生菌群與入侵病原體的「三角交互模型」，闡述了共生菌如何透過群體感應干擾、代謝產物（如短鏈脂肪酸、膽汁酸）調節、競爭性排斥及免疫調節來抑制病原體。研究強調了乳酸桿菌、雙歧桿菌及普拉梭菌等關鍵菌種的保護機制，並探討了器官晶片與多體學技術在揭示交互作用上的貢獻。此研究主張從生態系統角度管理傳染病，指出益生菌設計、糞便菌群移植及精準微生物組工程是未來治療的關鍵方向，雖面臨個體差異挑戰，但為臨床感染控制提供了典範轉移。</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42642836/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>42642834</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Glycosylation in gut-brain communication: from the intestinal barrier and microbiota to immune and neural signaling.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Gut microbes</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G41" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>The gut-brain axis is a complex bidirectional communication network linking the gastrointestinal tract and the central nervous system. Its dysregulation is closely associated with a wide range of gastrointestinal, metabolic, and neuropsychiatric disorders. Glycosylation, one of the most prevalent and structurally diverse post-translational modifications of proteins and lipids, is increasingly recognized as a regulator of multiple processes within the gut-brain axis. In this review, we summarize evidence that glycosylation influences several steps of gut-brain communication, including intestinal barrier function, microbial glycan metabolism, immune signaling, enteric and vagal pathways, blood-brain barrier integrity, and neural responses. We distinguish direct mechanistic findings from associative observations and discuss the more limited evidence for brain-to-gut regulation of intestinal glycosylation. In addition, we discuss the potential of glycosylation-targeted nutritional and microbiota-based interventions and highlight emerging opportunities to integrate glycomics with other omics approaches to dissect the complex regulatory networks underlying the gut-brain axis. In conclusion, elucidating how glycosylation shapes signaling along the gut-brain axis may open new avenues for understanding disease pathogenesis and for developing targeted therapeutic strategies.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>本文探討「腸-腦軸線」（Gut-Brain Axis）中醣基化（Glycosylation）修飾的關鍵調節角色。醣基化作為蛋白質與脂質重要的轉譯後修飾，深刻影響腸道屏障功能、微生物聚醣代謝、免疫訊息傳遞及血腦屏障完整性。研究重點解析了醣基化如何調控腸道與中樞神經系統間的溝通，並區分了機制性證據與相關性觀察。本文不僅強調了醣基化在維繫軸線穩定中的核心地位，更提出透過營養干預與微生物調節，結合多體學（Omics）分析醣基化網絡，將有望為神經精神疾病與代謝性障礙提供創新的診斷與治療策略。</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42642834/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>42640100</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Revisiting gut microbiota-driven ammonia metabolism: from disease burden to physiological adaptation.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Gut microbes</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G42" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Ammonia homeostasis is governed by interconnected host and microbial pathways, including hepatic ureagenesis, glutamine synthesis, and gut microbiota-mediated urea hydrolysis, proteolysis, and amino acid deamination. Ammonia has historically been viewed primarily as a nitrogenous waste product and neurotoxic molecule, a concept strongly supported by studies of hyperammonemia and hepatic encephalopathy. Impaired hepatic clearance, portosystemic shunting, and enhanced gut-derived ammonia input increase systemic ammonia burden and are linked to neurological dysfunction, muscle wasting, immune dysregulation, and progression of liver disease. In the gut lumen and mucosal environment, however, gut microbes not only generate ammonia but can also reuse ammonia-derived nitrogen for amino acid synthesis, microbial biomass formation, and community nitrogen exchange. Evidence from selected physiological and preclinical models indicates that microbiota-derived ammonia may contribute to nitrogen recycling, microbial community maintenance, enteric neural regulation, or metabolic adaptation under defined conditions. These roles are more context-specific and less broadly established than the pathological effects of systemic hyperammonemia. When epithelial barrier integrity is compromised, hepatic clearance declines, or host buffering reserves are depleted, elevated ammonia can increase epithelial exposure, portal ammonia input, or peripheral blood ammonia. Conversely, evidence that reduced microbiota-derived ammonia contributes to disease remains limited and currently comes mainly from selected animal models. This review re-examines ammonia metabolism from a gut microbiota-centered perspective. We discuss the ecological origins, spatial distribution, exposure characteristics, host-interface effects, and context-specific outcomes of microbiota-derived ammonia in physiology and disease, and discuss how ammonia should be measured, stratified, and targeted in microbial nitrogen metabolism.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>本綜述重新審視了腸道菌群驅動的氨代謝，探討其從疾病負擔到生理適應的雙重角色。傳統上，氨被視為具神經毒性的代謝廢物，與高氨血症、肝性腦病及肝病惡化密切相關。然而，在腸道微環境中，微生物不僅產生氨，亦能利用氨源氮進行氨基酸合成與群落氮循環，展現出維持腸道神經與代謝適應等生理功能。文章強調，氨的病理與生理效應高度取決於上皮屏障、肝臟清除能力及宿主緩衝儲備。本研究為腸道微生物氮代謝提供了新的生態與臨床視角，並討論了未來如何精確測量及標靶氨代謝的策略。</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42640100/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>42642622</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Deployable high-fidelity metagenome binning at scale with QuickBin.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Communications biology</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>metagenomics</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>297 個真實總體基因體數據集 (297 real metagenomes)</t>
+        </is>
+      </c>
+      <c r="G43" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Reconstructing genomes from metagenomic assemblies is foundational to microbiome research, yet binning faces a persistent trade-off between fidelity and throughput. Many high-accuracy methods rely on GPU-intensive workflows, marker-gene postprocessing, or heavy computational resources, limiting reproducible use at scale. Here, we present QuickBin, a CPU-native, marker-free binning algorithm designed to recover near-complete, ultra-low-contamination metagenome-assembled genomes (MAGs) efficiently. QuickBin pairs a GC-coverage spatial index (BinMap) with an early-exit Oracle cascade of similarity tests (scalar composition/coverage filters and SIMD-accelerated k-mer comparisons), reserving a compact neural network exclusively for ambiguous merges. Across synthetic communities, evaluated by marker-based and contig-origin ground truth, QuickBin maximizes high-fidelity sequence recovery. In benchmarking 297 diverse real metagenomes, QuickBin completed all runs, recovering more high-quality MAGs (≥95% completeness, ≤1% contamination) than resource-intensive alternatives that frequently failed. QuickBin provides a practical path to reproducible, genome-resolved metagenomics at scale for downstream comparative analyses. Open-source at: https://github.com/bbushnell/BBTools .</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>本研究開發了 QuickBin，這是一種無需標記基因且僅需 CPU 運行的總體基因體分箱（binning）演算法，旨在高效重建高完整度且極低污染的總體基因體組裝基因體（MAGs）。QuickBin 結合了 GC 含量與覆蓋度的空間索引及快速相似性過濾機制，僅在處理模糊合併時使用輕量級神經網路。在 297 個真實總體基因體數據集的基準測試中，QuickBin 成功完成所有運行，且重建的高品質 MAGs 數量超越了其他耗費資源或容易失敗的現有工具。此技術為大規模、可重複的基因體解析總體基因體學研究提供了實用的解決方案。</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42642622/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>42640624</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Gut microbial diversity at baseline conditions the clinical, microbiome, and metabolic response to paraprobiotic Lactiplantibacillus plantarum LRCC5282 in overweight adults.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Gut microbes</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>16S, metabolomics</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>120 位過重成人</t>
+        </is>
+      </c>
+      <c r="G44" t="b">
+        <v>0</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>The gut microbiota is increasingly recognized as a target for obesity management; however, whether baseline gut microbial diversity conditions responsiveness to microbiota-targeted interventions remains unclear. We aimed to investigate whether baseline gut microbial diversity is associated with responsiveness to a paraprobiotic derived from Lactiplantibacillus plantarum LRCC5282 (LP5282-P) in overweight adults. In a 12-week, randomized, double-blind, placebo-controlled, multicenter trial of 120 overweight adults, LP5282-P produced no significant between-group differences in any clinical outcome across the overall per-protocol population. However, in the low-diversity subgroup, LP5282-P was associated with significant reductions in body weight, body mass index, and circulating leptin levels. These clinical changes were accompanied by compositional shifts in the gut microbiota, including higher relative abundances of Christensenellaceae, Faecalibacterium, and Alistipes. Fecal metabolite profiles showed elevated acetate and butyrate concentrations and altered bile acid composition. Within the low-diversity subgroup, changes in the relative abundances of Akkermansia and Eubacterium were inversely correlated with changes in body weight, body fat mass, and leptin levels. In contrast, the high-diversity subgroup exhibited no consistent response across the outcome domains examined. Overall, baseline gut microbial diversity was associated with differential responsiveness to LP5282-P, supporting its potential use as a stratification variable in future microbiota-targeted intervention trials. Further studies integrating direct measures of microbial activity and host response are warranted to elucidate the biological pathways underlying this diversity-dependent responsiveness. Trial registration: Clinical Research Information Service (CRIS), KCT0008119.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>本研究旨在探討基準線腸道微生物多樣性，是否會影響過重成人對副乾酪乳桿菌（LP5282-P）介入的臨床、菌群及代謝反應。在一項為期12週、納入120位過重成人的臨床試驗中，整體人群並未展現顯著差異；然而，在「低多樣性」亞群中，LP5282-P顯著降低了受試者的體重、BMI與血清瘦素水平，並促使腸道有益菌（如 *Faecalibacterium* 與 *Alistipes*）豐度上升，同時提升糞便中乙酸與丁酸濃度並改變膽汁酸組成。相反地，「高多樣性」亞群則無一致反應。此研究證實基準線菌群多樣性是預測益生菌療效的重要關鍵，可作為未來精準微生態介入與體重管理的分層依據。</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42640624/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>42642466</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Empirical evidence for gut microbial influence on human brain neurochemistry via the gut-brain axis.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Molecular psychiatry</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>metagenomics</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G45" t="b">
+        <v>0</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>The gut microbiome produces metabolites with potential neuroactive properties, many of which act locally within the gut. While preclinical studies suggest these microbial pathways can influence cognitive and emotional processes, human evidence remains limited. This study investigates associations between gut microbiome-derived neuroactive functional potential and in vivo brain neurotransmitter concentrations in healthy young females. Using proton magnetic resonance spectroscopy (¹H-MRS), we quantified GABA and glutamate levels in the dorsolateral prefrontal cortex (dlPFC), anterior cingulate cortex (ACC), and inferior occipital gyrus (IOG). Parallel metagenomic profiling characterised microbial functional potential for pathways related to the synthesis and degradation of GABA, glutamate, short-chain fatty acids (SCFAs), p-cresol, and inositol. Region-specific associations were observed between these microbial pathways and cortical GABA and glutamate levels, including excitatory/inhibitory (E/I) balance, a key marker of neuroplasticity and mental health. Notably, microbial glutamate degradation and inositol synthesis potential were associated with IOG E/I balance, while additional pathways including GABA metabolism, p-cresol production, and SCFA synthesis showed distinct associations across regions. Exploratory analyses also identified links between microbial functional potential and anxiety, depressive symptoms, and sleep quality. Together, these findings provide new human evidence that variation in microbial functional potential corresponds with regional cortical neurochemistry and psychological wellbeing, highlighting the gut-brain axis as a promising avenue for mechanistically informed microbiome-based- interventions.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>本研究旨在探討健康女性的腸道菌群功能潛力與大腦活體神經傳導物質（GABA與麩胺酸）濃度的關聯。研究結合腦部質子磁共振波譜（¹H-MRS）與總體基因體學分析，發現微生物中參與GABA、麩胺酸、短鏈脂肪酸、對甲酚及肌醇代謝的通路，與大腦特定區域（如背外側前額葉、前扣帶迴與下枕葉）的神經傳導物質水平及興奮/抑制平衡（E/I）具有區域特異性關聯。探索性分析亦顯示微生物功能與焦慮、抑鬱及睡眠品質相關。本研究為腸道菌群影響人類大腦神經化學與心理健康提供了直接的人體實證，為未來開發以微生物為基礎的腦腸軸臨床干預奠定基礎。</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42642466/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>42648179</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Simultaneous removal of nitrogen, Cu2+, and bisphenol A in a hydrogel-biochar-AQDS immobilized bioreactor with added bicarbonate: Performance and metagenomic insights.</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Journal of hazardous materials</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D46" t="n">
         <v>11.3</v>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>metagenomics</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>未提及</t>
         </is>
       </c>
-      <c r="G38" t="b">
-        <v>0</v>
-      </c>
-      <c r="H38" t="inlineStr">
+      <c r="G46" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" t="inlineStr">
         <is>
           <t>As the complexity of industrial wastewater pollution continues to increase, the simultaneous removal of nitrogen, metal contaminants, and persistent organic pollutants under low carbon conditions has become a key challenge for biological treatment systems. To address the operational instability and dependence on carbon sources observed in immobilized systems when exposed to copper (Cu2+) and bisphenol A (BPA), the Pseudoalteromonas japonicus strain LY0623 was integrated into a hydrogel-biochar-AQDS composite carrier to construct a multifunctional immobilized biofilm system. Notably, under conditions containing only NaHCO3, the R4 system achieved an NH4+-N removal rate of 89%. Under conditions where Cu2+ and BPA coexist, the R4 system achieved removal of NH4+-N (89%), NO3--N (100%), Cu2+ (85%), and BPA (88%). Sediment characterization confirmed that Cu2+ was immobilized through adsorption, complexation, and microbiologically induced carbonate precipitation (MICP). Metagenomic analysis further indicated that the Pseudomonadota phylum remained the dominant phylum, while functional pathways associated with inorganic carbon assimilation, HNAD nitrogen metabolism, endogenous carbon transformation, biomineralization, electron transfer, and aromatic compound degradation were preserved. By combining ammonia oxidation driven energy production, inorganic carbon utilization, redox mediated processes, and biomineralization, this study provides a highly promising low carbon strategy for treating industrial wastewater containing mixed pollutants.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>本研究旨在解決低碳條件下，工業廢水中氮、重金屬（Cu2+）與雙酚A（BPA）等混合污染物難以同時高效生物降解的挑戰。研究人員將日本假交替單胞菌（*Pseudoalteromonas japonicus*）LY0623菌株整合至水凝膠-生物炭-AQDS複合載體中，構建出新型固定化生物膜系統（R4系統）。
 研究發現，在僅添加碳酸氫鈉（無機碳源）的條件下，該系統成功實現了NH4+-N（89%）、NO3--N（100%）、Cu2+（85%）和BPA（88%）的高效同時去除。總體基因體學分析證實，變形菌門（Pseudomonadota）為優勢菌群，且系統中與無機碳同化、異營硝化-好氧反硝化（HNAD）、生物礦化及芳香族化合物降解相關的功能通路均得到有效維持。本研究結合了氨氧化產能與生物礦化等機制，為混合污染廢水處理提供了一種具前景的低碳生物修復策略。</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/42648179/</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>42642466</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Empirical evidence for gut microbial influence on human brain neurochemistry via the gut-brain axis.</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Molecular psychiatry</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>metagenomics</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>未提及</t>
-        </is>
-      </c>
-      <c r="G39" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>The gut microbiome produces metabolites with potential neuroactive properties, many of which act locally within the gut. While preclinical studies suggest these microbial pathways can influence cognitive and emotional processes, human evidence remains limited. This study investigates associations between gut microbiome-derived neuroactive functional potential and in vivo brain neurotransmitter concentrations in healthy young females. Using proton magnetic resonance spectroscopy (¹H-MRS), we quantified GABA and glutamate levels in the dorsolateral prefrontal cortex (dlPFC), anterior cingulate cortex (ACC), and inferior occipital gyrus (IOG). Parallel metagenomic profiling characterised microbial functional potential for pathways related to the synthesis and degradation of GABA, glutamate, short-chain fatty acids (SCFAs), p-cresol, and inositol. Region-specific associations were observed between these microbial pathways and cortical GABA and glutamate levels, including excitatory/inhibitory (E/I) balance, a key marker of neuroplasticity and mental health. Notably, microbial glutamate degradation and inositol synthesis potential were associated with IOG E/I balance, while additional pathways including GABA metabolism, p-cresol production, and SCFA synthesis showed distinct associations across regions. Exploratory analyses also identified links between microbial functional potential and anxiety, depressive symptoms, and sleep quality. Together, these findings provide new human evidence that variation in microbial functional potential corresponds with regional cortical neurochemistry and psychological wellbeing, highlighting the gut-brain axis as a promising avenue for mechanistically informed microbiome-based- interventions.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>本研究旨在探討健康女性的腸道菌群功能潛力與大腦活體神經傳導物質（GABA與麩胺酸）濃度的關聯。研究結合腦部質子磁共振波譜（¹H-MRS）與總體基因體學分析，發現微生物中參與GABA、麩胺酸、短鏈脂肪酸、對甲酚及肌醇代謝的通路，與大腦特定區域（如背外側前額葉、前扣帶迴與下枕葉）的神經傳導物質水平及興奮/抑制平衡（E/I）具有區域特異性關聯。探索性分析亦顯示微生物功能與焦慮、抑鬱及睡眠品質相關。本研究為腸道菌群影響人類大腦神經化學與心理健康提供了直接的人體實證，為未來開發以微生物為基礎的腦腸軸臨床干預奠定基礎。</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42642466/</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>42640624</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Gut microbial diversity at baseline conditions the clinical, microbiome, and metabolic response to paraprobiotic Lactiplantibacillus plantarum LRCC5282 in overweight adults.</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Gut microbes</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>11</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>16S, metabolomics</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>120 位過重成人</t>
-        </is>
-      </c>
-      <c r="G40" t="b">
-        <v>0</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>The gut microbiota is increasingly recognized as a target for obesity management; however, whether baseline gut microbial diversity conditions responsiveness to microbiota-targeted interventions remains unclear. We aimed to investigate whether baseline gut microbial diversity is associated with responsiveness to a paraprobiotic derived from Lactiplantibacillus plantarum LRCC5282 (LP5282-P) in overweight adults. In a 12-week, randomized, double-blind, placebo-controlled, multicenter trial of 120 overweight adults, LP5282-P produced no significant between-group differences in any clinical outcome across the overall per-protocol population. However, in the low-diversity subgroup, LP5282-P was associated with significant reductions in body weight, body mass index, and circulating leptin levels. These clinical changes were accompanied by compositional shifts in the gut microbiota, including higher relative abundances of Christensenellaceae, Faecalibacterium, and Alistipes. Fecal metabolite profiles showed elevated acetate and butyrate concentrations and altered bile acid composition. Within the low-diversity subgroup, changes in the relative abundances of Akkermansia and Eubacterium were inversely correlated with changes in body weight, body fat mass, and leptin levels. In contrast, the high-diversity subgroup exhibited no consistent response across the outcome domains examined. Overall, baseline gut microbial diversity was associated with differential responsiveness to LP5282-P, supporting its potential use as a stratification variable in future microbiota-targeted intervention trials. Further studies integrating direct measures of microbial activity and host response are warranted to elucidate the biological pathways underlying this diversity-dependent responsiveness. Trial registration: Clinical Research Information Service (CRIS), KCT0008119.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>本研究旨在探討基準線腸道微生物多樣性，是否會影響過重成人對副乾酪乳桿菌（LP5282-P）介入的臨床、菌群及代謝反應。在一項為期12週、納入120位過重成人的臨床試驗中，整體人群並未展現顯著差異；然而，在「低多樣性」亞群中，LP5282-P顯著降低了受試者的體重、BMI與血清瘦素水平，並促使腸道有益菌（如 *Faecalibacterium* 與 *Alistipes*）豐度上升，同時提升糞便中乙酸與丁酸濃度並改變膽汁酸組成。相反地，「高多樣性」亞群則無一致反應。此研究證實基準線菌群多樣性是預測益生菌療效的重要關鍵，可作為未來精準微生態介入與體重管理的分層依據。</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42640624/</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>42642622</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Deployable high-fidelity metagenome binning at scale with QuickBin.</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Communications biology</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>metagenomics</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>297 個真實總體基因體數據集 (297 real metagenomes)</t>
-        </is>
-      </c>
-      <c r="G41" t="b">
-        <v>0</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Reconstructing genomes from metagenomic assemblies is foundational to microbiome research, yet binning faces a persistent trade-off between fidelity and throughput. Many high-accuracy methods rely on GPU-intensive workflows, marker-gene postprocessing, or heavy computational resources, limiting reproducible use at scale. Here, we present QuickBin, a CPU-native, marker-free binning algorithm designed to recover near-complete, ultra-low-contamination metagenome-assembled genomes (MAGs) efficiently. QuickBin pairs a GC-coverage spatial index (BinMap) with an early-exit Oracle cascade of similarity tests (scalar composition/coverage filters and SIMD-accelerated k-mer comparisons), reserving a compact neural network exclusively for ambiguous merges. Across synthetic communities, evaluated by marker-based and contig-origin ground truth, QuickBin maximizes high-fidelity sequence recovery. In benchmarking 297 diverse real metagenomes, QuickBin completed all runs, recovering more high-quality MAGs (≥95% completeness, ≤1% contamination) than resource-intensive alternatives that frequently failed. QuickBin provides a practical path to reproducible, genome-resolved metagenomics at scale for downstream comparative analyses. Open-source at: https://github.com/bbushnell/BBTools .</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>本研究開發了 QuickBin，這是一種無需標記基因且僅需 CPU 運行的總體基因體分箱（binning）演算法，旨在高效重建高完整度且極低污染的總體基因體組裝基因體（MAGs）。QuickBin 結合了 GC 含量與覆蓋度的空間索引及快速相似性過濾機制，僅在處理模糊合併時使用輕量級神經網路。在 297 個真實總體基因體數據集的基準測試中，QuickBin 成功完成所有運行，且重建的高品質 MAGs 數量超越了其他耗費資源或容易失敗的現有工具。此技術為大規模、可重複的基因體解析總體基因體學研究提供了實用的解決方案。</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42642622/</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>42640100</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Revisiting gut microbiota-driven ammonia metabolism: from disease burden to physiological adaptation.</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Gut microbes</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>11</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>others</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>未提及</t>
-        </is>
-      </c>
-      <c r="G42" t="b">
-        <v>0</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Ammonia homeostasis is governed by interconnected host and microbial pathways, including hepatic ureagenesis, glutamine synthesis, and gut microbiota-mediated urea hydrolysis, proteolysis, and amino acid deamination. Ammonia has historically been viewed primarily as a nitrogenous waste product and neurotoxic molecule, a concept strongly supported by studies of hyperammonemia and hepatic encephalopathy. Impaired hepatic clearance, portosystemic shunting, and enhanced gut-derived ammonia input increase systemic ammonia burden and are linked to neurological dysfunction, muscle wasting, immune dysregulation, and progression of liver disease. In the gut lumen and mucosal environment, however, gut microbes not only generate ammonia but can also reuse ammonia-derived nitrogen for amino acid synthesis, microbial biomass formation, and community nitrogen exchange. Evidence from selected physiological and preclinical models indicates that microbiota-derived ammonia may contribute to nitrogen recycling, microbial community maintenance, enteric neural regulation, or metabolic adaptation under defined conditions. These roles are more context-specific and less broadly established than the pathological effects of systemic hyperammonemia. When epithelial barrier integrity is compromised, hepatic clearance declines, or host buffering reserves are depleted, elevated ammonia can increase epithelial exposure, portal ammonia input, or peripheral blood ammonia. Conversely, evidence that reduced microbiota-derived ammonia contributes to disease remains limited and currently comes mainly from selected animal models. This review re-examines ammonia metabolism from a gut microbiota-centered perspective. We discuss the ecological origins, spatial distribution, exposure characteristics, host-interface effects, and context-specific outcomes of microbiota-derived ammonia in physiology and disease, and discuss how ammonia should be measured, stratified, and targeted in microbial nitrogen metabolism.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>本綜述重新審視了腸道菌群驅動的氨代謝，探討其從疾病負擔到生理適應的雙重角色。傳統上，氨被視為具神經毒性的代謝廢物，與高氨血症、肝性腦病及肝病惡化密切相關。然而，在腸道微環境中，微生物不僅產生氨，亦能利用氨源氮進行氨基酸合成與群落氮循環，展現出維持腸道神經與代謝適應等生理功能。文章強調，氨的病理與生理效應高度取決於上皮屏障、肝臟清除能力及宿主緩衝儲備。本研究為腸道微生物氮代謝提供了新的生態與臨床視角，並討論了未來如何精確測量及標靶氨代謝的策略。</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42640100/</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>42642834</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Glycosylation in gut-brain communication: from the intestinal barrier and microbiota to immune and neural signaling.</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Gut microbes</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>11</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>others</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>未提及</t>
-        </is>
-      </c>
-      <c r="G43" t="b">
-        <v>0</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>The gut-brain axis is a complex bidirectional communication network linking the gastrointestinal tract and the central nervous system. Its dysregulation is closely associated with a wide range of gastrointestinal, metabolic, and neuropsychiatric disorders. Glycosylation, one of the most prevalent and structurally diverse post-translational modifications of proteins and lipids, is increasingly recognized as a regulator of multiple processes within the gut-brain axis. In this review, we summarize evidence that glycosylation influences several steps of gut-brain communication, including intestinal barrier function, microbial glycan metabolism, immune signaling, enteric and vagal pathways, blood-brain barrier integrity, and neural responses. We distinguish direct mechanistic findings from associative observations and discuss the more limited evidence for brain-to-gut regulation of intestinal glycosylation. In addition, we discuss the potential of glycosylation-targeted nutritional and microbiota-based interventions and highlight emerging opportunities to integrate glycomics with other omics approaches to dissect the complex regulatory networks underlying the gut-brain axis. In conclusion, elucidating how glycosylation shapes signaling along the gut-brain axis may open new avenues for understanding disease pathogenesis and for developing targeted therapeutic strategies.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>本文探討「腸-腦軸線」（Gut-Brain Axis）中醣基化（Glycosylation）修飾的關鍵調節角色。醣基化作為蛋白質與脂質重要的轉譯後修飾，深刻影響腸道屏障功能、微生物聚醣代謝、免疫訊息傳遞及血腦屏障完整性。研究重點解析了醣基化如何調控腸道與中樞神經系統間的溝通，並區分了機制性證據與相關性觀察。本文不僅強調了醣基化在維繫軸線穩定中的核心地位，更提出透過營養干預與微生物調節，結合多體學（Omics）分析醣基化網絡，將有望為神經精神疾病與代謝性障礙提供創新的診斷與治療策略。</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42642834/</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>42641146</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Engineered bacterial therapeutics from synthetic biology to clinical translation: A multi-database scientometric analysis, 2000-2026.</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Human vaccines &amp; immunotherapeutics</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>others</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>1,730 篇學術文章與評論</t>
-        </is>
-      </c>
-      <c r="G44" t="b">
-        <v>0</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Engineered bacterial therapeutics integrate programmable strain engineering with biomedical functions such as sensing, delivery, immune modulation, microbiome intervention, and disease management. This study conducted a multi-database bibliometric analysis to map the knowledge structure, collaboration patterns, and translational direction of this field. Bibliographic records were retrieved from Web of Science Core Collection, Scopus, and PubMed for publications from 1 January 2000 to 1 June 2026. After document-type filtering, time restriction, deduplication, language screening, and manual eligibility assessment, 1,730 English-language articles and reviews were included. CiteSpace 6.4.R1, VOSviewer 1.6.20, and the bibliometrix R package were used to analyze publication trends, collaboration networks, journal co-citation, dual-map citation trajectories, citation bursts, keyword co-occurrence, and thematic evolution. Publication output increased steadily, with faster growth after 2020; 2025 was the highest-output complete year, while 2026 represented a partial retrieval year. China and the United States were the leading contributors, although institutional collaboration remained regionally clustered. Co-citation, citation-burst, and keyword analyses showed a shift from bacterial chassis construction and circuit design toward engineered probiotics, gut microbiota-related therapy, cancer immunotherapy, drug delivery, live biotherapeutic products, and clinical translation. Persistent translational priorities include controllability, safety, manufacturing consistency, and regulatory alignment.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>本研究透過文獻計量學方法，系統性分析 2000 年至 2026 年間有關「工程化細菌治療」的 1,730 篇學術文獻。研究旨在釐清該領域的知識結構、國際合作模式及臨床轉化趨勢。分析顯示，該領域自 2020 年後顯著加速發展，中國與美國為主要貢獻國。核心研究主軸已由早期的細菌底盤構建與基因電路設計，轉向工程化益生菌、癌症免疫治療、藥物遞送及活體生物藥物（LBP）的開發。科學意義在於確立了該領域從實驗室轉向臨床應用的優先議題，即解決控制力、生物安全性、生產一致性與法規調適等挑戰，為未來工程化細菌作為精準醫療工具的發展提供關鍵決策參考。</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42641146/</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>42635406</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Separating extracellular from intracellular fecal metabolites exposes cross-feeding architecture in the gut: exploring metabolite partitioning and ecological associations.</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Gut microbes</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>11</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>metagenomics, metabolomics</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>63 個糞便檢體（來自 63 位健康受試者）</t>
-        </is>
-      </c>
-      <c r="G45" t="b">
-        <v>0</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>The gut microbiota forms a complex ecosystem through metabolic interdependence (cross-feeding). However, conventional fecal metabolomics typically quantifies only total metabolite pools, making it difficult to distinguish extracellular-enriched metabolite pools from predominantly cell-associated ones, and thus limiting reconstruction of in situ metabolic networks. Here, we quantified fecal metabolites in paired fractions from the same specimen: an undisrupted fraction representing the extracellular pool and a strongly bead-beaten fraction representing the total pool; the intracellular pool was defined as the difference between total and extracellular measurements. Stool samples from 63 healthy individuals were analyzed for short-chain fatty acids, polyamines, and water-soluble vitamins, and the results were integrated with shotgun metagenomic profiles of species composition and functional genes. Vitamins exhibited two distinct behaviors. Adenosylcobalamin (a vitamin B12 coenzyme) was detectable only after disruption, and together with thiamine (B1) and niacin (B3) was classified as an intracellular-retained type (Type 1). In contrast, biotin (B7) and pantothenate (B5) showed higher extracellular proportions (Type 2). Integrative analyses further indicated that Type 1 thiamine was negatively associated with Blautia, consistent with intensive microbial utilization, whereas Type 2 biotin was strongly positively associated with Alistipes, suggesting links to ecological niches shaped by luminal pH and fermentation modes (carbohydrate vs protein fermentation). Fraction-resolved quantification provides a practical operational framework to differentiate extracellular from cell-associated metabolite pools, helping reconcile metagenomic potential with metabolomic reality and enabling deeper inference of cross-feeding structure in the gut ecosystem.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>本研究針對腸道微生物的代謝互營機制（cross-feeding）進行探討。傳統糞便代謝組學僅能分析總代謝物，無法區分細胞外與細胞內代謝池，限制了對代謝網絡的解析。研究團隊透過對比未破碎（代表細胞外池）與強力破碎（代表總代謝池）的糞便樣本，成功推算出細胞內代謝物的分佈。針對短鏈脂肪酸、多胺與水溶性維生素的分析顯示，維生素呈現兩類分佈：B12、B1 與 B3 傾向保留於細胞內（Type 1），而 B7 與 B5 則富集於細胞外（Type 2）。結合宏基因組分析發現，Type 1 代謝物與特定細菌（如 *Blautia*）的利用模式顯著相關，Type 2 代謝物則與 *Alistipes* 及腸道生態位特徵（如 pH 值、發酵類型）相關。此方法為區分代謝物空間分佈提供了實用架構，有助於更精確地將宏基因組功能潛力與代謝體現實連結，深入理解腸道微生物的互營生態結構。</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42635406/</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>42635403</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Baseline gut microbiome ecology predicts long-term fat mass loss after bariatric surgery: evidence for a thrifty Bifidobacterium phenotype.</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Gut microbes</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>11</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>16S, metabolomics</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>85 位重度肥胖患者及 21 位健康對照組（共 106 名受試者）</t>
-        </is>
-      </c>
-      <c r="G46" t="b">
-        <v>0</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Bariatric surgery (BS) induces weight loss, but long-term success involves complex host-microbiome interactions. We evaluated the longitudinal impact of BS, microbiome resilience, and Mediterranean Diet (MedDiet) adherence up to 24 months. This prospective observational study included 85 patients with severe obesity undergoing BS and 21 normal-weight healthy controls (HC). MedDiet adherence (PREDIMED) was assessed before surgery. Fecal microbiota (16S-rRNA sequencing) and metabolomics (1H-NMR spectroscopy) were analyzed at baseline and at 1-, 6-, and 12-months post-BS. Clinical outcomes and fat mass, evaluated by bioimpedanciometry, were tracked up to 24 months. At baseline, patients exhibited higher microbial Shannon diversity than controls (p = 0.041), alongside a dysfunctional microbiome and metabolome characterized by a higher Firmicutes/Bacteroidetes ratio and elevated levels of branched-chain amino acids (p &lt; 0.0001). Ordinary Least Squares (OLS) regression analysis revealed that MedDiet adherence and type 2 diabetes status significantly modulated baseline diversity. At 12 months post-BS, the gut ecosystem underwent profound remodeling, characterized by depletion of Bifidobacterium spp. and an increase in butyrate levels (p &lt; 0.0001), establishing a novel adaptive state distinct from HC. Baseline gut ecology significantly conditioned long-term BS outcomes: patients in the highest quartile of baseline Bifidobacterium spp. lost significantly less fat mass at 24 months than those in the lowest (6.6% vs. 13.2%, p = 0.010). High baseline Bifidobacterium abundance paradoxically acts as a "thrifty microbiome," potentially maximizing energy harvest and limiting surgery-induced fat loss. Overall, BS induces adaptive microbiome restoration rather than true normalization, highlighting the potential for precision interventions prior to surgery.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>本研究探討減重手術（BS）後腸道微生物群與長期減脂效果的關聯。研究追蹤 85 名患者於術前及術後長達 24 個月的變化，分析發現手術顯著重塑了腸道菌相與代謝環境，特別是雙歧桿菌（*Bifidobacterium*）的耗竭與丁酸鹽的增加。關鍵發現指出，術前高豐度的雙歧桿菌反而成為一種「節儉型表型」，會增加能量攝取效率，導致術後 24 個月的脂肪減少量顯著較少（6.6% 對比 13.2%）。這顯示減重手術並非使微生物組回歸常態，而是引發一種適應性重組。此研究凸顯了術前腸道生態作為預測手術成效生物標記的潛力，對於未來制定精準的術前介入策略具有重要的臨床指導意義。</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42635403/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>42659434</t>
+          <t>42641146</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Blechomonas campbelli from Ctenocephalides felis: in vitro development, thermotolerance, and phylogenetic insights.</t>
+          <t>Engineered bacterial therapeutics from synthetic biology to clinical translation: A multi-database scientometric analysis, 2000-2026.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Memorias do Instituto Oswaldo Cruz</t>
+          <t>Human vaccines &amp; immunotherapeutics</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>metagenomics, others</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>340 隻跳蚤（每 4 隻混合為一組，共 85 組檢體），最終獲得 1 個分離株（FL-1）</t>
+          <t>1,730 篇學術文章與評論</t>
         </is>
       </c>
       <c r="G47" t="b">
@@ -2917,22 +2887,22 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Blechomonas spp. are flea-specific monoxenous trypanosomatids, whose biology, host range, and geographic distribution remain poorly understood, even for species inhabiting ubiquitous cat and dog fleas. To isolate and characterise blechomonads from fleas of domestic dogs in Brazil, focusing on culture growth, morphology, and phylogenetic relationships. Fleas collected from dogs in Sabará, Brazil, were morphologically identified and screened by cultivation. The isolate FL-1 was analysed for temperature-dependent growth, morphology, and phylogeny using 18S rRNA and gGAPDH sequences, including those mined from public metagenomic datasets. Of 340 fleas (four per pool), only one culture tested positive. Growth was optimal at 25ºC, reduced at 30ºC, and absent at 35ºC. Four cell types were revealed, including a predominant "uromonad" stage specialised for attachment and aggregation. Phylogenetic analyses placed the isolate within Blechomonas campbelli and indicated that this species and Blechomonas lauriereadi occur in Ctenocephalides spp. from multiple continents. Blechomonas campbelli exhibits developmental adaptations to the flea gut and limited tolerance to elevated temperatures, constraining its potential to persist in warm-blooded hosts. These findings highlight the value of combining culture-based and in silico approaches to investigate flea-associated trypanosomatids.</t>
+          <t>Engineered bacterial therapeutics integrate programmable strain engineering with biomedical functions such as sensing, delivery, immune modulation, microbiome intervention, and disease management. This study conducted a multi-database bibliometric analysis to map the knowledge structure, collaboration patterns, and translational direction of this field. Bibliographic records were retrieved from Web of Science Core Collection, Scopus, and PubMed for publications from 1 January 2000 to 1 June 2026. After document-type filtering, time restriction, deduplication, language screening, and manual eligibility assessment, 1,730 English-language articles and reviews were included. CiteSpace 6.4.R1, VOSviewer 1.6.20, and the bibliometrix R package were used to analyze publication trends, collaboration networks, journal co-citation, dual-map citation trajectories, citation bursts, keyword co-occurrence, and thematic evolution. Publication output increased steadily, with faster growth after 2020; 2025 was the highest-output complete year, while 2026 represented a partial retrieval year. China and the United States were the leading contributors, although institutional collaboration remained regionally clustered. Co-citation, citation-burst, and keyword analyses showed a shift from bacterial chassis construction and circuit design toward engineered probiotics, gut microbiota-related therapy, cancer immunotherapy, drug delivery, live biotherapeutic products, and clinical translation. Persistent translational priorities include controllability, safety, manufacturing consistency, and regulatory alignment.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>本研究旨在分離並鑑定巴西犬隻跳蚤中的隱鞭蟲（*Blechomonas*），探討其生長、形態與系統發育。研究從340隻跳蚤中成功分離出FL-1株，經鑑定為 *Blechomonas campbelli*。該菌最適生長溫度為25°C，在35°C下無法存活，並具有四種細胞形態（含利於附著的uromonad階段）。系統發育分析證實該物種廣泛分佈於全球的櫛頭蚤屬中。此發現表明其具有適應跳蚤腸道的發育特徵，但因耐熱性差，難以在溫血宿主體內存活。本研究證實了結合傳統培養與公共總體基因體數據挖掘在研究跳蚤相關寄生蟲上的重要價值。</t>
+          <t>本研究透過文獻計量學方法，系統性分析 2000 年至 2026 年間有關「工程化細菌治療」的 1,730 篇學術文獻。研究旨在釐清該領域的知識結構、國際合作模式及臨床轉化趨勢。分析顯示，該領域自 2020 年後顯著加速發展，中國與美國為主要貢獻國。核心研究主軸已由早期的細菌底盤構建與基因電路設計，轉向工程化益生菌、癌症免疫治療、藥物遞送及活體生物藥物（LBP）的開發。科學意義在於確立了該領域從實驗室轉向臨床應用的優先議題，即解決控制力、生物安全性、生產一致性與法規調適等挑戰，為未來工程化細菌作為精準醫療工具的發展提供關鍵決策參考。</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42659434/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42641146/</t>
         </is>
       </c>
     </row>
@@ -2992,30 +2962,30 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>42634246</t>
+          <t>42659434</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Natural microbiota confer life-long protection against obesity via an early-life, immune-mediated effect on brown adipocytes.</t>
+          <t>Blechomonas campbelli from Ctenocephalides felis: in vitro development, thermotolerance, and phylogenetic insights.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>Memorias do Instituto Oswaldo Cruz</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11</v>
+        <v>2.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics, others</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>340 隻跳蚤（每 4 隻混合為一組，共 85 組檢體），最終獲得 1 個分離株（FL-1）</t>
         </is>
       </c>
       <c r="G49" t="b">
@@ -3023,50 +2993,52 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Obesity, a major risk factor for metabolic disease, has increased in industrialized nations alongside a reduction in gut microbiota diversity. Reconstituting laboratory mice with complex, natural microbiota and commensals from wild mice resulted in protection against diet-induced obesity. These natural microbiota reduced weight gain in both male and female mice of different genetic backgrounds throughout their life and increased energy expenditure. Single-nuclei RNA sequencing identified a dominant adipocyte population in brown adipose tissue (BAT) with a transcriptional signature of increased thermogenic activity, while white adipose tissue mass and beiging were reduced. Protection against diet-induced obesity was transferable to adult germ-free mice via exposure to natural microbiota, indicating an association with the timing of immune response induction rather than BAT developmental programming. However, protection against diet-induced obesity did not require type 2 immune signaling, as shown in STAT6 knockout mice. Rather, it was associated with increased levels of chemokines and monocytes in BAT in early life, pointing to a role of infiltrating myeloid cells. Indeed, CCR2-deficient mice with natural microbiota lacked the BAT transcriptional signature of increased thermogenic activity, increased energy expenditure, and protection against diet-induced obesity that wild-type mice with natural microbiota exhibited. The latter was restored upon injection with wild-type bone marrow. Taken together, these findings identify a novel microbiota‒immune‒adipose tissue axis that results in increased BAT thermogenesis and improved energy balance throughout life.</t>
+          <t>Blechomonas spp. are flea-specific monoxenous trypanosomatids, whose biology, host range, and geographic distribution remain poorly understood, even for species inhabiting ubiquitous cat and dog fleas. To isolate and characterise blechomonads from fleas of domestic dogs in Brazil, focusing on culture growth, morphology, and phylogenetic relationships. Fleas collected from dogs in Sabará, Brazil, were morphologically identified and screened by cultivation. The isolate FL-1 was analysed for temperature-dependent growth, morphology, and phylogeny using 18S rRNA and gGAPDH sequences, including those mined from public metagenomic datasets. Of 340 fleas (four per pool), only one culture tested positive. Growth was optimal at 25ºC, reduced at 30ºC, and absent at 35ºC. Four cell types were revealed, including a predominant "uromonad" stage specialised for attachment and aggregation. Phylogenetic analyses placed the isolate within Blechomonas campbelli and indicated that this species and Blechomonas lauriereadi occur in Ctenocephalides spp. from multiple continents. Blechomonas campbelli exhibits developmental adaptations to the flea gut and limited tolerance to elevated temperatures, constraining its potential to persist in warm-blooded hosts. These findings highlight the value of combining culture-based and in silico approaches to investigate flea-associated trypanosomatids.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>本研究旨在探討野生小鼠的天然腸道菌相如何預防飲食引起的肥胖。研究發現，移植天然菌相能終生保護不同遺傳背景的實驗小鼠免於肥胖，並顯著增加能量消耗。單細胞核RNA定序（snRNA-seq）顯示，這與褐色脂肪組織（BAT）中產熱活性增強的脂肪細胞亞群有關。此保護機制並非透過第二型免疫信號，而是依賴於早期生命階段骨髓源性細胞（特別是CCR2+單核細胞）向BAT的浸潤與免疫調節。本研究首次揭示了一條全新的「腸道菌群—免疫—脂肪組織」軸，證實早期菌相暴露能透過免疫介導促進褐色脂肪產熱，為肥胖及代謝性疾病的防治提供了新穎的科學依據與治療靶點。</t>
+          <t>本研究旨在分離並鑑定巴西犬隻跳蚤中的隱鞭蟲（*Blechomonas*），探討其生長、形態與系統發育。研究從340隻跳蚤中成功分離出FL-1株，經鑑定為 *Blechomonas campbelli*。該菌最適生長溫度為25°C，在35°C下無法存活，並具有四種細胞形態（含利於附著的uromonad階段）。系統發育分析證實該物種廣泛分佈於全球的櫛頭蚤屬中。此發現表明其具有適應跳蚤腸道的發育特徵，但因耐熱性差，難以在溫血宿主體內存活。本研究證實了結合傳統培養與公共總體基因體數據挖掘在研究跳蚤相關寄生蟲上的重要價值。</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42634246/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42659434/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>42644084</t>
+          <t>42635403</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Viral metagenomics of synanthropic urban bats: A surveillance strategy for uncovering potentially zoonotic viruses.</t>
+          <t>Baseline gut microbiome ecology predicts long-term fat mass loss after bariatric surgery: evidence for a thrifty Bifidobacterium phenotype.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>One health (Amsterdam, Netherlands)</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>Gut microbes</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11</v>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>16S, metabolomics</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2,422 隻蝙蝠中篩選出的 150 對肺與腸道檢體</t>
+          <t>85 位重度肥胖患者及 21 位健康對照組（共 106 名受試者）</t>
         </is>
       </c>
       <c r="G50" t="b">
@@ -3074,45 +3046,43 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Bats are natural reservoirs for diverse viruses, including coronaviruses, filoviruses, and paramyxoviruses, several of those known to be involved in zoonotic spillover events and demanding an integrated surveillance. Here, we present a framework that leverages Brazil's rabies passive surveillance programme to detect bat-borne viruses. Using an algorithm to select representative specimens from 2422 bats collected across São Paulo state, we submitted 150 paired lung and intestine samples to nanopore metagenomic sequencing. We detected 98 viral contigs from 12 families of public health relevance, including Arenaviridae, Coronaviridae, and Paramyxoviridae. Notably, the approach identified a previously unknown filovirus in bats in the Americas, validating the framework's capacity for epidemic preparedness. These findings reveal an undetected viral diversity and demonstrate how existing animal surveillance can monitor pathogen threats. Crucially, in a workshop involving multisectoral One Health experts in Brazil, this framework was validated as a scalable model for national expansion, adapted for low- and middle-income countries (LMICs).</t>
+          <t>Bariatric surgery (BS) induces weight loss, but long-term success involves complex host-microbiome interactions. We evaluated the longitudinal impact of BS, microbiome resilience, and Mediterranean Diet (MedDiet) adherence up to 24 months. This prospective observational study included 85 patients with severe obesity undergoing BS and 21 normal-weight healthy controls (HC). MedDiet adherence (PREDIMED) was assessed before surgery. Fecal microbiota (16S-rRNA sequencing) and metabolomics (1H-NMR spectroscopy) were analyzed at baseline and at 1-, 6-, and 12-months post-BS. Clinical outcomes and fat mass, evaluated by bioimpedanciometry, were tracked up to 24 months. At baseline, patients exhibited higher microbial Shannon diversity than controls (p = 0.041), alongside a dysfunctional microbiome and metabolome characterized by a higher Firmicutes/Bacteroidetes ratio and elevated levels of branched-chain amino acids (p &lt; 0.0001). Ordinary Least Squares (OLS) regression analysis revealed that MedDiet adherence and type 2 diabetes status significantly modulated baseline diversity. At 12 months post-BS, the gut ecosystem underwent profound remodeling, characterized by depletion of Bifidobacterium spp. and an increase in butyrate levels (p &lt; 0.0001), establishing a novel adaptive state distinct from HC. Baseline gut ecology significantly conditioned long-term BS outcomes: patients in the highest quartile of baseline Bifidobacterium spp. lost significantly less fat mass at 24 months than those in the lowest (6.6% vs. 13.2%, p = 0.010). High baseline Bifidobacterium abundance paradoxically acts as a "thrifty microbiome," potentially maximizing energy harvest and limiting surgery-induced fat loss. Overall, BS induces adaptive microbiome restoration rather than true normalization, highlighting the potential for precision interventions prior to surgery.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>本研究旨在建立一個結合巴西現有狂犬病被動監測計畫的病毒總體基因體學監測架構，以偵測都市蝙蝠所攜帶的潛在人畜共通病毒。研究團隊從聖保羅州收集的 2,422 隻蝙蝠中，篩選出 150 對肺部與腸道檢體進行奈米孔定序。結果成功偵測到 12 個與公共衛生密切相關病毒科的 98 個病毒基因片段（包括沙狀、冠狀與副黏液病毒科等），更首次在美洲蝙蝠中發現一種未知絲狀病毒。此研究不僅揭示了未曾被發現的病毒多樣性，證實利用現有動物監測系統預防流行病的可行性，更為中低收入國家提供了一個具備「健康一體」（One Health）共識、可擴展至全國的傳染病監測模型。</t>
+          <t>本研究探討減重手術（BS）後腸道微生物群與長期減脂效果的關聯。研究追蹤 85 名患者於術前及術後長達 24 個月的變化，分析發現手術顯著重塑了腸道菌相與代謝環境，特別是雙歧桿菌（*Bifidobacterium*）的耗竭與丁酸鹽的增加。關鍵發現指出，術前高豐度的雙歧桿菌反而成為一種「節儉型表型」，會增加能量攝取效率，導致術後 24 個月的脂肪減少量顯著較少（6.6% 對比 13.2%）。這顯示減重手術並非使微生物組回歸常態，而是引發一種適應性重組。此研究凸顯了術前腸道生態作為預測手術成效生物標記的潛力，對於未來制定精準的術前介入策略具有重要的臨床指導意義。</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42644084/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42635403/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>42668212</t>
+          <t>42635406</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Correlation between microbial communities, metabolites, and bioactivities in fermented mare's milk revealed by metagenomics and metabolomics.</t>
+          <t>Separating extracellular from intracellular fecal metabolites exposes cross-feeding architecture in the gut: exploring metabolite partitioning and ecological associations.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Food microbiology</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>4.6</t>
-        </is>
+          <t>Gut microbes</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -3121,7 +3091,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>63 個糞便檢體（來自 63 位健康受試者）</t>
         </is>
       </c>
       <c r="G51" t="b">
@@ -3129,45 +3099,49 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Koumiss exhibits various functional properties, including antioxidant, hypoglycemic, and antihypertensive effects; however, natural fermentation is characterized by an uncontrollable microbial community structure, significant fluctuations in product quality, and a lack of specialized fermentation agents. The mechanisms underlying the links between microbial communities, functional metabolites, and bioactivity in natural and inoculated fermentation systems remain unclear. Therefore, this study employed bioactivity assays, metagenomics, and non-targeted metabolomics to systematically analyze differences in microbial communities, metabolite composition, and functional activities of mare's milk under different fermentation regimes. The results indicated that, compared with natural fermentation, inoculated fermentation with a mixed lactic acid bacteria (LAB) culture significantly enhanced the antioxidant, α-glucosidase, α-amylase inhibitory activities, and ACE inhibitory activity of mare's milk; microbial diversity in fermented samples was significantly reduced, with a more pronounced decrease in the inoculated group. Metabolomic analysis revealed that inoculated fermentation significantly enriched functional metabolites, including lipids and organic acids. Correlation analysis indicated that the abundance of Lactiplantibacillus and Limosilactobacillus was significantly positively correlated with beneficial metabolites (e.g., linoleic acid, α-linolenic acid) and functional activities. The lipid and amino acid metabolic pathways are closely associated with the differences in in vitro biological activity of inoculated fermented mare's milk. This study provides a fermentation starter that can improve the in vitro functional activity of mare's milk and reveals the potential metabolic links between LAB fermentation and the altered functional traits of mare's milk, thereby providing a theoretical basis and technical support for the development of high-value-added fermented mare's milk products.</t>
+          <t>The gut microbiota forms a complex ecosystem through metabolic interdependence (cross-feeding). However, conventional fecal metabolomics typically quantifies only total metabolite pools, making it difficult to distinguish extracellular-enriched metabolite pools from predominantly cell-associated ones, and thus limiting reconstruction of in situ metabolic networks. Here, we quantified fecal metabolites in paired fractions from the same specimen: an undisrupted fraction representing the extracellular pool and a strongly bead-beaten fraction representing the total pool; the intracellular pool was defined as the difference between total and extracellular measurements. Stool samples from 63 healthy individuals were analyzed for short-chain fatty acids, polyamines, and water-soluble vitamins, and the results were integrated with shotgun metagenomic profiles of species composition and functional genes. Vitamins exhibited two distinct behaviors. Adenosylcobalamin (a vitamin B12 coenzyme) was detectable only after disruption, and together with thiamine (B1) and niacin (B3) was classified as an intracellular-retained type (Type 1). In contrast, biotin (B7) and pantothenate (B5) showed higher extracellular proportions (Type 2). Integrative analyses further indicated that Type 1 thiamine was negatively associated with Blautia, consistent with intensive microbial utilization, whereas Type 2 biotin was strongly positively associated with Alistipes, suggesting links to ecological niches shaped by luminal pH and fermentation modes (carbohydrate vs protein fermentation). Fraction-resolved quantification provides a practical operational framework to differentiate extracellular from cell-associated metabolite pools, helping reconcile metagenomic potential with metabolomic reality and enabling deeper inference of cross-feeding structure in the gut ecosystem.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>本研究旨在探討自然發酵與接種乳酸菌（LAB）發酵對馬奶（Koumiss）微生物群落、代謝物及生物活性的影響與關聯。研究利用總體基因體學與非靶向代謝組學技術發現，相較於自然發酵，接種混合乳酸菌發酵顯著提升了馬奶的抗氧化、降血糖（抑制α-葡萄糖苷酶與α-澱粉酶）及抗高血壓（抑制ACE）之體外活性。雖然接種發酵降低了微生物多樣性，但顯著富集了脂質和有機酸等功能性代謝物。相關性分析顯示，植物乳桿菌與黏液乳桿菌的豐度與有益代謝物（如亞麻油酸、α-次亞麻油酸）及生物活性呈顯著正相關。本研究揭示了乳酸菌發酵提升馬奶功能特性的代謝機制，為開發高價值發酵馬奶產品提供了理論與技術支持。</t>
+          <t>本研究針對腸道微生物的代謝互營機制（cross-feeding）進行探討。傳統糞便代謝組學僅能分析總代謝物，無法區分細胞外與細胞內代謝池，限制了對代謝網絡的解析。研究團隊透過對比未破碎（代表細胞外池）與強力破碎（代表總代謝池）的糞便樣本，成功推算出細胞內代謝物的分佈。針對短鏈脂肪酸、多胺與水溶性維生素的分析顯示，維生素呈現兩類分佈：B12、B1 與 B3 傾向保留於細胞內（Type 1），而 B7 與 B5 則富集於細胞外（Type 2）。結合宏基因組分析發現，Type 1 代謝物與特定細菌（如 *Blautia*）的利用模式顯著相關，Type 2 代謝物則與 *Alistipes* 及腸道生態位特徵（如 pH 值、發酵類型）相關。此方法為區分代謝物空間分佈提供了實用架構，有助於更精確地將宏基因組功能潛力與代謝體現實連結，深入理解腸道微生物的互營生態結構。</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42668212/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42635406/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>42637484</t>
+          <t>42668680</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Insights into the analysis of microbial communities in fermented foods from the perspective of DNA-based techniques.</t>
+          <t>Proximity-ligation metagenomics reveals differential plasmid and chromosomal antimicrobial resistance gene carriage in disrupted gut ecosystems.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Food research international (Ottawa, Ont.)</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>iScience</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>16S, metagenomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3180,50 +3154,52 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>The quality, flavor, and stability of fermented foods depend on the microbial community. However, microbial dynamics are difficult to observe directly, leading to limited control over fermentation. High-throughput sequencing is a revolutionary tool for microbial characterization, among which DNA-based amplicon and metagenomic sequencing are core techniques. Nevertheless, the related data processing workflows in the context of fermented foods have not yet been systematically summarized, hindering the translation of research findings into fermentation practices. This review clarifies the applications of amplicon and metagenomic sequencing in fermented foods. For amplicon sequencing, the impacts of target regions, data preprocessing, and reference databases are addressed. For metagenomic sequencing, sequencing strategies, read-based and binning-based analytical methods, functional annotation, and species-specific databases are discussed. In addition, major strategies for downstream analysis of community data are summarized, including microbial diversity, co-occurrence networks, niche and community assembly, key environmental drivers, and machine learning-based prediction. Amplicon sequencing efficiently reveals microbial succession during fermentation but has limitations in functional annotation. Metagenomic sequencing is notable for functional annotation, enabling the linkage between microbial communities and metabolic potential alongside community characterization. Standardized data preprocessing and specific databases are critical for improving characterization. For community data, integrated analysis allows uncovering the driving factors of microbial succession, thereby helping to regulate fermentation. Notably, the compositional nature of the data must be considered and validated to avoid spurious associations. In summary, the exponential growth of sequencing data will propel the era of precision fermentation.</t>
+          <t>Distinct ecological pressures shape accumulation of antimicrobial resistance genes (ARGs) and virulence genes in the gut microbiome. In this study, we used proximity ligation shotgun metagenomics to characterize bacterial host-mobilome relationships associated with antimicrobial resistance and virulence genes in two disease cohorts with microbiome dysbiosis: recurrent Clostridioides difficile infection (rCDI) and cirrhosis. Microbiome dysbiosis in patients with rCDI is primarily driven by prolonged antibiotic exposure, whereas dysbiosis in patients with cirrhosis results from altered gut physiology. We found an increased relative abundance of chromosomally linked antibiotic resistance determinants in both disease cohorts compared with healthy controls. The rCDI cohorts additionally exhibited increased relative abundance of plasmid-mediated ARGs.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>本文為一篇綜述性研究，旨在探討以 DNA 為基礎的高通量定序技術（包含擴增子定序與宏基因組學）在發酵食品微生物群落分析中的應用。研究指出，儘管高通量定序技術已成為解析微生物動態的革命性工具，但目前缺乏系統性的數據處理框架，限制了科學發現向產業實踐的轉化。本文詳細梳理了從目標區域選擇、數據預處理、參考數據庫建立到下游生物資訊分析（如共現網絡、生態棲位構建及機器學習預測）的標準化流程。研究強調，擴增子定序雖能有效揭示群落演替，但在功能註解上存在限制；而宏基因組學則具備更強的功能解析潛力，能將微生物組成與代謝功能聯繫起來。透過標準化數據處理流程並考慮數據的組成特性，這些先進技術將精準調控發酵過程，引領精密發酵時代的到來。</t>
+          <t>本研究利用鄰近連接總體基因體學技術，分析復發性困難梭菌感染（rCDI）與肝硬化兩種腸道菌群失調患者的抗藥性基因（ARGs）與毒力基因。研究發現，與健康對照組相比，兩組患者染色體上的抗藥基因相對豐度皆顯著增加。然而，因長期抗生素暴露驅動的 rCDI 患者，其質體介導的抗藥基因（plasmid-mediated ARGs）豐度亦額外顯著提升。此發現揭示了不同生態壓力（抗生素暴露 vs. 生理病變）如何差異性地塑造腸道抗藥基因組，對於理解抗藥性傳播機制具有重要的科學意義。</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42637484/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42668680/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>42637478</t>
+          <t>42634246</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Effects of sorghum variety on fermentation microecology and flavor characteristics of sesame-flavor Baijiu.</t>
+          <t>Natural microbiota confer life-long protection against obesity via an early-life, immune-mediated effect on brown adipocytes.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Food research international (Ottawa, Ont.)</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>Gut microbes</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11</v>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>3 種高粱品種（Hongyingzi, Hei'e, G），於 2 輪發酵週期中，在 3 個時間點（0、15、50 天）採集發酵酒醅檢體（樣本總數依實驗設計推算為 18 組發酵樣品）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G53" t="b">
@@ -3231,50 +3207,50 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Sorghum, the principal raw material for Baijiu fermentation, plays a key role in shaping fermentation microecology and flavor formation. However, the effects of sorghum varietal differences on sesame-flavor Baijiu fermentation remain insufficiently understood. In this study, three sorghum varieties, Hongyingzi (R), Hei'e (B), and a domestic cultivar (G), were compared over two consecutive fermentation rounds. Fermented grain (Jiupei) samples collected at 0, 15, and 50 days were analyzed for physicochemical properties, enzyme activities, microbial communities, volatile compounds in Jiupei and base liquor, and the taste characteristics of the corresponding base liquor. Despite showing similar overall fermentation trends, the three sorghum varieties differed in acid accumulation, starch utilization, microbial succession, and volatile composition. Fungal communities shifted from early Pichia dominance to multi-genus coexistence, whereas bacterial communities progressively converged toward Lactobacillus dominance. A total of 218 and 258 volatile compounds were identified in Jiupei and 176 and 192 in base liquor from the first and second rounds, respectively. Esters were the dominant differential class, and volatile-marker profiles varied among sorghum varieties and fermentation rounds, with no single variety showing consistent enrichment across all sesame-flavor-related compounds. These results indicate that sorghum variety is an important factor associated with microbial assembly and flavor formation during sesame-flavor Baijiu fermentation, and provide a basis for raw material selection and flavor-oriented process optimization.</t>
+          <t>Obesity, a major risk factor for metabolic disease, has increased in industrialized nations alongside a reduction in gut microbiota diversity. Reconstituting laboratory mice with complex, natural microbiota and commensals from wild mice resulted in protection against diet-induced obesity. These natural microbiota reduced weight gain in both male and female mice of different genetic backgrounds throughout their life and increased energy expenditure. Single-nuclei RNA sequencing identified a dominant adipocyte population in brown adipose tissue (BAT) with a transcriptional signature of increased thermogenic activity, while white adipose tissue mass and beiging were reduced. Protection against diet-induced obesity was transferable to adult germ-free mice via exposure to natural microbiota, indicating an association with the timing of immune response induction rather than BAT developmental programming. However, protection against diet-induced obesity did not require type 2 immune signaling, as shown in STAT6 knockout mice. Rather, it was associated with increased levels of chemokines and monocytes in BAT in early life, pointing to a role of infiltrating myeloid cells. Indeed, CCR2-deficient mice with natural microbiota lacked the BAT transcriptional signature of increased thermogenic activity, increased energy expenditure, and protection against diet-induced obesity that wild-type mice with natural microbiota exhibited. The latter was restored upon injection with wild-type bone marrow. Taken together, these findings identify a novel microbiota‒immune‒adipose tissue axis that results in increased BAT thermogenesis and improved energy balance throughout life.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>本研究旨在探討不同高粱品種對芝麻香型白酒發酵過程中，微生物群落結構與風味代謝物質形成的影響。研究比較了紅纓子（R）、黑鵝（B）與國內品種（G）三種高粱，分析其在發酵過程中的理化特性、微生物演替及揮發性化合物組成。研究發現，儘管各品種發酵趨勢相似，但在酸度累積、澱粉利用率及微生物群落演替上存在顯著差異；真菌群落由早期的畢赤酵母（*Pichia*）主導轉變為多菌屬共存，細菌群落則趨向於乳桿菌（*Lactobacillus*）主導。分析鑑定出上百種揮發性化合物，其中酯類是導致風味差異的主要代謝物。本研究證實了高粱品種是決定白酒發酵微生物群落組裝與最終風味品質的關鍵因子，為白酒產業的原料選擇與製程最佳化提供了重要的科學依據。</t>
+          <t>本研究旨在探討野生小鼠的天然腸道菌相如何預防飲食引起的肥胖。研究發現，移植天然菌相能終生保護不同遺傳背景的實驗小鼠免於肥胖，並顯著增加能量消耗。單細胞核RNA定序（snRNA-seq）顯示，這與褐色脂肪組織（BAT）中產熱活性增強的脂肪細胞亞群有關。此保護機制並非透過第二型免疫信號，而是依賴於早期生命階段骨髓源性細胞（特別是CCR2+單核細胞）向BAT的浸潤與免疫調節。本研究首次揭示了一條全新的「腸道菌群—免疫—脂肪組織」軸，證實早期菌相暴露能透過免疫介導促進褐色脂肪產熱，為肥胖及代謝性疾病的防治提供了新穎的科學依據與治療靶點。</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42637478/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42634246/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>42637476</t>
+          <t>42644084</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>A Shenling Baizhu San polysaccharide fraction (SLP-2)-based synbiotic alleviates lactose-induced gut dysfunction via a microbiota-metabolite-barrier axis.</t>
+          <t>Viral metagenomics of synanthropic urban bats: A surveillance strategy for uncovering potentially zoonotic viruses.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Food research international (Ottawa, Ont.)</t>
+          <t>One health (Amsterdam, Netherlands)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>2,422 隻蝙蝠中篩選出的 150 對肺與腸道檢體</t>
         </is>
       </c>
       <c r="G54" t="b">
@@ -3282,45 +3258,49 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Lactose intolerance (LI) is a common digestive disorder, and its management still relies largely on dietary restriction. Because gut microbial fermentation and barrier dysfunction contribute to LI-related symptoms, microbiota-targeted prebiotic or synbiotic strategies may provide complementary approaches. However, the active plant-polysaccharide fractions and their microbial partners remain unclear. This study aimed to identify the bioactive polysaccharide fraction from Shenling Baizhu San and evaluate its pairing with responder bacteria for alleviating high-lactose diet (HLD)-induced intestinal dysfunction. Stepwise ethanol precipitation yielded SLP-2, which was subsequently identified as the principal bioactive fraction through human fecal fermentation, monoculture assays, and an HLD rat model. SLP-2 enriched Eubacterium-associated taxa and supported the growth of Akkermansia muciniphila in monoculture and in vivo. Building on this, a synbiotic combining SLP-2 with A. muciniphila and E. rectale alleviated HLD-induced gut dysfunction; the antibiotic-matched comparison with the probiotics-only group supported an SLP-2-associated contribution. The synbiotic intervention was associated with increased tight junction proteins, MUC2 expression, improved intestinal architecture, and thicker mucus layers. Multi-omics analysis linked co-metabolites, including intestinal 6-MGG and HTy-Ac and systemic DHPV-G, with barrier restoration and an immune profile characterized by increased IL-10 and lower TLR4 expression. These findings suggest that SLP-2-based synbiotic intervention alleviates HLD-induced intestinal dysfunction through microbiota-metabolite-barrier modulation, providing preclinical evidence for future functional-food strategies pending human validation.</t>
+          <t>Bats are natural reservoirs for diverse viruses, including coronaviruses, filoviruses, and paramyxoviruses, several of those known to be involved in zoonotic spillover events and demanding an integrated surveillance. Here, we present a framework that leverages Brazil's rabies passive surveillance programme to detect bat-borne viruses. Using an algorithm to select representative specimens from 2422 bats collected across São Paulo state, we submitted 150 paired lung and intestine samples to nanopore metagenomic sequencing. We detected 98 viral contigs from 12 families of public health relevance, including Arenaviridae, Coronaviridae, and Paramyxoviridae. Notably, the approach identified a previously unknown filovirus in bats in the Americas, validating the framework's capacity for epidemic preparedness. These findings reveal an undetected viral diversity and demonstrate how existing animal surveillance can monitor pathogen threats. Crucially, in a workshop involving multisectoral One Health experts in Brazil, this framework was validated as a scalable model for national expansion, adapted for low- and middle-income countries (LMICs).</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>本研究旨在探討參苓白朮散多醣活性組分（SLP-2）結合特定菌株，對高乳糖飲食（HLD）引發之腸道功能障礙的緩解作用。研究發現，SLP-2能促進*A. muciniphila*與真桿菌屬相關菌群生長。以SLP-2搭配益生菌的合生元配方，能顯著改善HLD大鼠的腸道屏障，包含增加緊密連接蛋白與MUC2表達、增厚黏液層。多體學分析顯示，其保護作用與腸道及全身性代謝物（如6-MGG、DHPV-G）的調節，以及抗發炎反應（提升IL-10、降低TLR4）密切相關。此發現為開發防治乳糖不耐症的功能性食品提供了臨床前依據。</t>
+          <t>本研究旨在建立一個結合巴西現有狂犬病被動監測計畫的病毒總體基因體學監測架構，以偵測都市蝙蝠所攜帶的潛在人畜共通病毒。研究團隊從聖保羅州收集的 2,422 隻蝙蝠中，篩選出 150 對肺部與腸道檢體進行奈米孔定序。結果成功偵測到 12 個與公共衛生密切相關病毒科的 98 個病毒基因片段（包括沙狀、冠狀與副黏液病毒科等），更首次在美洲蝙蝠中發現一種未知絲狀病毒。此研究不僅揭示了未曾被發現的病毒多樣性，證實利用現有動物監測系統預防流行病的可行性，更為中低收入國家提供了一個具備「健康一體」（One Health）共識、可擴展至全國的傳染病監測模型。</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42637476/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42644084/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>42637471</t>
+          <t>42668212</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fucoidan from giant kelp alleviates postmenopausal osteoporosis by regulating the betaine-OPG/RANKL/RANK signaling axis.</t>
+          <t>Correlation between microbial communities, metabolites, and bioactivities in fermented mare's milk revealed by metagenomics and metabolomics.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Food research international (Ottawa, Ont.)</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>Food microbiology</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3333,50 +3313,54 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Postmenopausal osteoporosis (PMOP), characterized by excessive bone resorption and impaired bone remodeling, remains a significant global health challenge. This study investigated the protective effects of fucoidan from giant kelp (GKP) against PMOP and its underlying mechanisms in ovariectomized mice. GKP supplementation attenuated bone loss by preserving trabecular microarchitecture, normalizing systemic mineral homeostasis, and suppressing osteoclastogenesis, as evidenced by the downregulation of osteoclast-related genes. 16S rRNA gene sequencing revealed that GKP reshaped the gut microbiota by decreasing the Bacteroidota/Firmicutes ratio and enriching beneficial taxa, which promoted short-chain fatty acid production. Targeted metabolomics revealed that GKP induced profound systemic metabolic reprogramming, particularly amino acid metabolism, and identified betaine as a key systemic metabolite effector upregulated following GKP treatment. In vitro assays demonstrated that betaine suppressed receptor activator of nuclear factor-κB ligand (RANKL)-induced osteoclast differentiation and mitigated inflammation. In vivo validation demonstrated that betaine intervention recapitulated the osteoprotective phenotype observed in GKP-treated mice, which was associated with regulation of the osteoprotegerin/RANKL/RANK signaling axis. These results indicate that GKP exerts anti-osteoporotic effects in association with changes in gut microbiota and systemic metabolism, while betaine-mediated regulation of the OPG/RANKL/RANK signaling may contribute to its osteoprotective activity.</t>
+          <t>Koumiss exhibits various functional properties, including antioxidant, hypoglycemic, and antihypertensive effects; however, natural fermentation is characterized by an uncontrollable microbial community structure, significant fluctuations in product quality, and a lack of specialized fermentation agents. The mechanisms underlying the links between microbial communities, functional metabolites, and bioactivity in natural and inoculated fermentation systems remain unclear. Therefore, this study employed bioactivity assays, metagenomics, and non-targeted metabolomics to systematically analyze differences in microbial communities, metabolite composition, and functional activities of mare's milk under different fermentation regimes. The results indicated that, compared with natural fermentation, inoculated fermentation with a mixed lactic acid bacteria (LAB) culture significantly enhanced the antioxidant, α-glucosidase, α-amylase inhibitory activities, and ACE inhibitory activity of mare's milk; microbial diversity in fermented samples was significantly reduced, with a more pronounced decrease in the inoculated group. Metabolomic analysis revealed that inoculated fermentation significantly enriched functional metabolites, including lipids and organic acids. Correlation analysis indicated that the abundance of Lactiplantibacillus and Limosilactobacillus was significantly positively correlated with beneficial metabolites (e.g., linoleic acid, α-linolenic acid) and functional activities. The lipid and amino acid metabolic pathways are closely associated with the differences in in vitro biological activity of inoculated fermented mare's milk. This study provides a fermentation starter that can improve the in vitro functional activity of mare's milk and reveals the potential metabolic links between LAB fermentation and the altered functional traits of mare's milk, thereby providing a theoretical basis and technical support for the development of high-value-added fermented mare's milk products.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>本研究探討巨藻褐藻醣膠（GKP）對去卵巢小鼠更年期後骨質疏鬆症（PMOP）的保護機制。結果顯示，補充GKP能有效減少骨質流失並抑制破骨細胞生成。16S定序顯示GKP重塑了腸道菌群（降低擬桿菌門/厚壁菌門比例），促進短鏈脂肪酸產生。代謝組學分析發現，GKP顯著提升了系統性代謝物甜菜鹼（betaine）的含量。體內外實驗進一步證實，甜菜鹼透過調控OPG/RANKL/RANK信號軸，能抑制破骨細胞分化並緩解骨質流失。本研究證實GKP具備透過「腸道菌群-代謝物」軸抗骨質疏鬆的潛力，為PMOP防治提供了科學依據。</t>
+          <t>本研究旨在探究馬奶在天然與人工接種發酵模式下，微生物群落、功能性代謝物與生物活性之間的關聯與機制。結果顯示，相較於天然發酵，接種混合乳酸菌（LAB）發酵能顯著提升馬奶的抗氧化、降血糖（抑制α-葡萄糖苷酶及α-澱粉酶）和降血壓（抑制ACE）之體外活性。雖然接種發酵降低了微生物多樣性，但能顯著富集脂質和有機酸等功能性代謝物。關聯分析證實，植物乳桿菌和粘液乳桿菌的豐度與亞油酸、α-次麻油酸等有益代謝物及功能活性呈顯著正相關。此研究揭示了乳酸菌發酵對馬奶功能特性的代謝調控機制，為開發高附加價值的馬奶發酵產品奠定了科學基礎。</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42637471/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42668212/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>42637450</t>
+          <t>42666298</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Highland barley polysaccharides promoted lactose intestinal fermentation in vitro: Unveiling the dynamic response of gut microbiota and polysaccharide structure.</t>
+          <t>Multi-layer gut microbiome variation in type 2 diabetes despite preserved higher-order community structure.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Food research international (Ottawa, Ont.)</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>Frontiers in microbiology</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>乳糖不耐症患者的糞便檢體（未提及具體數量）</t>
+          <t>82 個糞便檢體（包含 41 位第二型糖尿病患者與 41 位健康對照組）</t>
         </is>
       </c>
       <c r="G56" t="b">
@@ -3384,44 +3368,44 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Lactose intolerance affects over 70% of the global population due to the untimely metabolism of lactose in the colon. To accelerate lactose metabolism, we innovatively employed highland barley polysaccharides (HBP) to modulate the colonic fermentation efficiency of lactose using an in vitro fermentation model and fecal samples from lactose intolerant patients. With the addition of HBP, the consumption efficiency of lactose began to increase after 6 h of fermentation. At 48 h, lactose consumption increased by 29%, surpassing the effect of commercial prebiotics. Meanwhile, HBP with lower molecular weight (HBP-L, 8.69 × 104 g/Mol) exhibited more effective impacts than HBP with high molecular weight (HBP-H, 1.22 × 105 g/Mol), which was particularly evident during the 12-48 h of fermentation. More importantly, HBP, particularly HBP-L, substantially enriched Segatella, Bifidobacterium, and Ligilactobacillus in a time-dependent manner and was positively correlated with decreased lactose levels and elevated bacterial lactase activity, resulting in significant conversion of lactose to lactic acid and short-chain fatty acids. During the first 12 h of fermentation, HBP-L underwent more significant degradation than HBP-H. Meanwhile, the xylose residues and Glcp glycosidic bonds in HBP-L were preferentially utilized, while it was glucose residue in HBP-H. Thus, it indicated that HBPs were degraded and altered the composition of the gut microbiota, thereby enhancing the fermentation efficiency of lactose. Our findings provide a theoretical basis for developing targeted prebiotic foods to manage lactose intolerance.</t>
+          <t>Type 2 diabetes (T2D) has been consistently associated with alterations in the gut microbiome, although disease, treatment, diet, and other host factors may contribute to the observed patterns. How these associations are organized across different biological levels of the microbial ecosystem remains incompletely understood. We performed shotgun metagenomic sequencing of fecal samples from 82 individuals, including 41 patients with T2D and 41 age-, sex-, and body mass index-matched healthy controls. Taxonomic profiling, functional pathway analysis, enterotype characterization, ecological network inference, and interpretable machine-learning approaches were integrated to characterize microbiome variation across multiple organizational levels. Despite clear clinical differences between groups, particularly fasting blood glucose, the overall ecological architecture of the gut microbiome remained broadly preserved. Dominant phylum-level composition and enterotype structure were maintained, whereas variation became apparent at finer biological scales. Species-level analyses identified 42 differentially abundant taxa. Community diversity analysis showed reduced Chao1 richness (P = 0.024), increased Simpson diversity (P = 0.024), unchanged Shannon diversity (P = 0.126), and a modest shift in community composition (PERMANOVA, R 2 = 0.040, P = 0.006). Functional profiling showed no pathway-level significance after multiple-testing correction but directional trends across several metabolic modules. Exploratory Spearman-based networks differed in topology between groups; because relative-abundance data are compositional, these differences cannot be interpreted as direct ecological interactions or definitive network rewiring. Machine-learning models achieved a within-cohort cross-validated AUC of up to 0.91, but lacked independent external validation. These findings provide a multi-layer description of T2D-associated gut microbiome variation within this cohort. The data are consistent with preserved higher-order community organization accompanied by finer-scale differences in species composition, functional potential, community-state occupancy, statistical co-occurrence, and within-cohort discriminative features. Medication confounding, compositional effects, technical artifacts, and the absence of external validation limit causal, ecological, and diagnostic interpretation. Larger longitudinal, multi-site, medication-resolved, and independently validated studies are required.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>本研究旨在探討青稞多醣（HBP）如何調控乳糖不耐症患者的腸道菌群，以促進體外乳糖發酵與代謝。研究發現，添加 HBP（特別是低分子量的 HBP-L）能在發酵 48 小時後提升乳糖消耗效率達 29%，效果顯著優於商業益生元。機制上，HBP-L 在發酵初期降解更為顯著，並能隨時間特異性富集 *Segatella*、雙歧桿菌屬（*Bifidobacterium*）及 *Ligilactobacillus*，進而提升細菌乳糖酶活性，將乳糖轉化為乳酸與短鏈脂肪酸。本研究證實了青稞多醣能透過重塑腸道菌群結構來加速乳糖代謝，為開發緩解乳糖不耐症的標靶益生元食品提供了重要科學依據。</t>
+          <t>本研究透過總體基因體定序（Shotgun metagenomics），探討第二型糖尿病（T2D）患者與健康個體在腸道微生物群落結構上的多層次差異。研究發現，儘管兩組間存在顯著的臨床指標（如空腹血糖）差異，但腸道微生物的宏觀生態架構，包括主要菌門組成與腸型分佈，仍保持高度穩定。差異主要發生在細微的生物學尺度，表現為 42 個物種的豐度改變、Chao1 豐富度下降及群落組成的輕微偏移。雖然功能性路徑分析未達顯著差異，但機器學習模型顯示微生物特徵對區分 T2D 患者具有極高潛力（AUC 達 0.91）。本研究強調 T2D 患者的微生物變異表現為「宏觀結構保存」與「物種細微層面失衡」並存。儘管該模型具有高度鑑別力，但因缺乏外部驗證及藥物干擾等侷限，未來仍需更大規模的長期研究來確認其臨床意義。</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42637450/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42666298/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>42662912</t>
+          <t>42666306</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Insights into antibiotic resistomes from gut meta-genome-assembled genomes of the free-range chickens.</t>
+          <t>Ecological assembly of mucosal and fecal microbiomes in ulcerative colitis across genes, functions, and species.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Veterinary and animal science</t>
+          <t>Frontiers in microbiology</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3431,7 +3415,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>120 個放養雞糞便檢體（重建出 2,146 個宏基因組組裝基因組/MAGs）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G57" t="b">
@@ -3439,50 +3423,54 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Antibiotic resistance is a growing global threat, and the chicken gut microbiome is a significant reservoir of antibiotic resistance genes (ARGs). To investigate the presence of ARGs in free-range chickens, which are in closer contact with humans and live in closer proximity to human settlements. In this study, we used metagenomic sequencing to characterize the resistome of the chicken gut. We collected 120 fecal samples from free-range chickens across four Chinese provinces and constructed both metagenome-assembled genomes (MAGs) and comprehensive gene catalogs to investigate microbial community structures and ARG distributions. A total of 2,146 MAGs were reconstructed, encompassing 660 species from 26 phyla, forming a comprehensive genomic catalog of the chicken gut microbiota. We identified 254,316 ARGs representing 159 unique resistance genes across 35 antibiotic classes, with multidrug, tetracycline, glycopeptide, and peptide resistance being most prevalent. Notably, ARG distribution showed strong regional variation, influenced by environmental factors and local farming practices. Mobile genetic elements (MGEs), averaging 33.8 per MAG, were positively correlated with ARG abundance (R = 0.77), underscoring their role in facilitating resistance gene dissemination. Specific MAGs-including strains of Escherichia coli and Klebsiella pneumoniae-harbored hundreds of ARGs and virulence factors, highlighting potential high-risk vectors for resistance spread. Our findings reveal a diverse and regionally dynamic antibiotic resistome in the chicken gut, shaped by microbial composition, environment, and host factors. This study provides a valuable genomic resource and emphasizes the need for targeted interventions and surveillance strategies to mitigate antibiotic resistance in poultry production systems.</t>
+          <t>Inflammatory bowel disease (IBD) is associated with gut microbial dysbiosis, yet the ecological processes underlying community assembly remain unclear. Here, we applied Sloan's neutral community model to examine the relative contributions of stochastic and deterministic processes across multiple ecological layers, including metagenomic genes (MGs), molecular functions (MFs), and microbial species (archaea, bacteria, fungi, and viruses), in fecal and mucosal microbiota from healthy controls and ulcerative colitis (UC) patients. Across all layers, most MGs, MFs, and species conformed to neutral expectations, indicating a dominant role of stochastic processes in community assembly. However, UC was consistently associated with an increased proportion of neutral MFs and species, accompanied by a reduction in non-neutral components, suggesting weakened selective constraints under disease conditions. Ecological niche further modulated these patterns. Fecal communities harbored significantly higher proportions of non-neutral MFs and species compared to mucosal communities, indicating stronger deterministic processes in feces. Analysis of selection-state transitions revealed extensive changes in selection status in UC, particularly in mucosal environments, where both functional and taxonomic profiles showed marked transition. These changes were primarily driven by the gain and loss of selection rather than directional switching, indicating that UC alters the strength and presence of selection rather than reversing its direction. Together, these findings provide a multi-layered ecological framework for understanding UC-associated dysbiosis, highlighting increased neutrality and selection rewiring as key features of microbial community assembly under disease conditions.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>本研究旨在探討放養雞腸道菌群中的抗生素抗藥性基因（ARGs）分布。研究團隊分析了中國四省的120個放養雞糞便檢體，重建出2,146個宏基因組組裝基因組（MAGs）。結果共鑑定出254,316個ARGs，以多重抗藥性與四環黴素抗性最為普遍。ARGs分布具顯著地域差異，且與行動遺傳元件（MGEs）呈強正相關（R=0.77），證實其高傳播潛力。此外，大腸桿菌和肺炎克雷伯氏菌等特定菌株被發現攜帶多種ARGs與毒力因子，為潛在的高風險傳播媒介。本研究建立的基因組資源，對制定禽類抗藥性監控與防治策略具有重要科學價值。</t>
+          <t>本研究旨在探討潰瘍性結腸炎（UC）患者腸道微生物群落組裝的生態機制。研究人員應用 Sloan 中性群落模型，分析了健康對照組與 UC 患者的糞便及黏膜樣本，涵蓋微生物基因（MGs）、分子功能（MFs）及多界物種（古菌、細菌、真菌與病毒）。研究發現，儘管腸道微生物組裝主要受隨機過程驅動，但 UC 患者的群落呈現出更高的「中性」特徵，暗示疾病狀態下選擇壓力減弱。此外，糞便樣本較黏膜樣本展現出更強的決定性選擇。分析顯示，UC 導致黏膜環境中微生物群落的選擇狀態發生顯著重組，且主要源於選擇壓力的消失或獲得，而非方向性轉變。這些發現構建了一個多層次的生態框架，揭示了 UC 相關菌群失調的核心特徵在於群落組裝的中性化趨勢及選擇壓力的重塑，為理解發炎性腸道疾病的微生態機制提供了科學依據。</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42662912/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42666306/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>42637441</t>
+          <t>42666371</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Microbial succession drives quality deterioration in refrigerated golden pompano (Trachinotus ovatus): regulatory network of dominant spoilage microbiota on characteristic biomarkers.</t>
+          <t>HPV vaccination associates with Lactobacillus crispatus-dominant vaginal microbiota in women with cervical lesions: a metagenomic study.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Food research international (Ottawa, Ont.)</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>Frontiers in microbiology</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>59 個陰道檢體（HPV 未接種組 n=26，接種組 n=33）</t>
         </is>
       </c>
       <c r="G58" t="b">
@@ -3490,50 +3478,54 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Elucidating the quality deterioration mechanisms of refrigerated golden pompano (Trachinotus ovatus), this study integrated 16S rRNA gene sequencing and untargeted metabolomics to systematically dissect how microbial ecological succession drives metabolic changes. As critical spoilage indicators, total volatile basic nitrogen (TVB-N) and thiobarbituric acid reactive substances (TBARS) continuously increased during storage, indicating significant deterioration by day 6. Microbial community succession analysis revealed that Psychrobacter, Shewanella, and Pseudomonas gradually became the dominant microbiota in the late storage stage. Metabolite enrichment analysis further demonstrated that this shift redirected the metabolic focus from early-stage nucleotide degradation to late-stage protein hydrolysis and amino acid metabolism. Moreover, multivariate statistical analysis identified 50 potential spoilage biomarkers, among which biogenic amines (histamine, tyramine, and phenylethylamine) were recognized as key indicators reflecting spoilage progression. Correlation network analysis revealed positive correlations between Pseudomonas and Shewanella abundances and the accumulation of these biogenic amines. This suggests that these two genera act as the core functional microbiota, driving spoilage metabolite generation and subsequent quality deterioration. Pathway analysis of potential spoilage biomarker generation indicates that amino acid and nucleotide metabolism constitute the core spoilage pathways, with lipid oxidation serving as a complementary mechanism. Overall, this study elucidates the spoilage mechanisms of refrigerated golden pompano, providing chemical targets for early biomarker detection and targeted antibacterial strategies.</t>
+          <t>Human papillomavirus (HPV) vaccination provides high-level protection against cervical cancer through type-specific antibodies, although breakthrough and persistent high-risk HPV (hrHPV) infections may still occur in some vaccinated women. In addition to neutralizing antibodies, vaccination elicits other immune mechanisms that may influence viral persistence and disease progression. Because mucosal immunity is closely linked to the vaginal microbiota, microbial composition may also play an important role in HPV susceptibility, with Lactobacillus crispatus dominance associated with protection, and dysbiosis with impaired mucosal immunity. Whether HPV vaccination is associated with favorable microbiota signatures in women with confirmed cervical cancer-related conditions remains unknown. We analyzed vaginal samples via shotgun metagenomic sequencing from a cross-sectional study of 59 pre-menopausal women (&lt;50 years) with confirmed cervical lesions (HPV-unvaccinated n = 26, vaccinated n = 33). Alpha diversity (Shannon and Inverse Simpson indices) did not differ significantly by vaccination status, suggesting within-sample microbial diversity between the groups, but Bray-Curtis-based PERMANOVA indicated a statistically significant difference in overall community composition between groups (p = 0.042). Among women with CST I, 90.9% were vaccinated, whereas among women with CST IV, 60.0% were unvaccinated. At the species level, L. crispatus relative abundance was higher in vaccinated women in the unadjusted analysis; however, this association was attenuated and was not statistically significant after multivariable adjustment. HPV vaccination status was associated with a higher prevalence of L. crispatus-dominant, health-associated vaginal microbiota among women with cervical lesions. These findings support the hypothesis that HPV vaccination status is associated with L. crispatus dominance in this population, but mechanistic pathways remain to be elucidated.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>本研究旨在探討冷藏金鯧魚品質劣化的機制。研究結合 16S rRNA 基因定序與非靶向代謝組學，分析微生物群落演替如何驅動代謝變化。結果顯示，金鯧魚冷藏至第 6 天時顯著腐敗。在貯藏後期，*Psychrobacter*、*Shewanella* 與 *Pseudomonas* 逐漸成為優勢菌群，使代謝焦點自初期的核苷酸降解轉向後期的蛋白質水解與氨基酸代謝。研究鑑定出 50 個潛在腐敗生物標誌物（如組胺、酪胺等生物胺），並發現 *Pseudomonas* 和 *Shewanella* 的豐度與這些生物胺的累積呈正相關，為驅動腐敗的核心菌群。本研究闡明了金鯧魚的腐敗機制，為食品早期變質檢測及靶向抑菌策略提供了科學依據與化學標靶。</t>
+          <t>本研究旨在探討 HPV 疫苗接種與患有子宮頸病變女性之陰道微生物群落結構間的關聯。研究透過鳥槍法總體基因體定序（shotgun metagenomics）分析 59 名停經前女性的陰道檢體，結果發現儘管兩組間的微生物多樣性（Alpha diversity）無顯著差異，但整體的群落結構（Beta diversity）在接種與未接種者間存在統計學上的顯著差異。數據顯示，HPV 疫苗接種與促進「捲曲乳桿菌（*L. crispatus*）優勢型」的陰道菌相具有正相關性。此發現暗示 HPV 疫苗除產生抗體外，可能透過調節陰道微生物環境來增強黏膜免疫保護力。此研究對於理解疫苗如何透過影響宿主微生物組，進而降低 HPV 持續感染與子宮頸病變風險提供了科學依據，未來仍需進一步研究其潛在的免疫調控機制。</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42637441/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42666371/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>42637430</t>
+          <t>42666411</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Regional differentiation of microbial communities and metabolites in Yunnan dry-cured beef: insights from high-throughput sequencing and untargeted metabolomics.</t>
+          <t>Aztreonam-avibactam therapy following surgical source control for bla NDM -positive carbapenem-resistant Klebsiella pneumoniae intra-abdominal infection in an infant: a case report.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Food research international (Ottawa, Ont.)</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>Frontiers in pharmacology</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>1 個嬰兒案例</t>
         </is>
       </c>
       <c r="G59" t="b">
@@ -3541,71 +3533,536 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>To reveal the effects of regional processing on quality, microbial communities and metabolites of traditional Yunnan dry-cured beef, samples from Xundian (XD), Yuxi (YX) and Honghe (HH) were analyzed. High-throughput sequencing and UHPLC-Q-Exactive HF/MS untargeted metabolomics were applied. Sensory scores and physicochemical Properties differed significantly (p &lt; 0.05). Bacillota and Staphylococcus dominated bacterial communities. The observed differences in microbial communities and metabolites among regions are shaped by the combined effects of geographical environment and processing conditions. Ascomycota was the main fungal phylum. Debaryomyces dominated XD and HH samples. YX samples had a unique fungal profile dominated by Rhodotorula and Cladosporium. A total of 1320 metabolites were identified. 196 differential metabolites were screened. Key pathways included glycerophospholipid metabolism, pyrimidine metabolism and arachidonic acid metabolism. Correlation analysis indicated that Staphylococcus and Lactococcus were positively associated with amino acid derivatives, while Latilactobacillus and Debaryomyces correlated with organic acids and glycerophospholipids. These findings revealed the potential microbial-metabolic association underlying regional quality differences. They provide support for quality control and traceability of dry-cured beef.</t>
+          <t>Treating carbapenem-resistant Klebsiella pneumoniae (CRKP) is challenging, particularly when resistance is mediated by New Delhi metallo-β-lactamase (NDM). Clinical experience with fixed-combination aztreonam-avibactam (ATM-AVI) in young infants remains extremely limited. Here, we report a case of a 2-month-old boy who underwent emergency laparotomy for intestinal obstruction owing to small bowel volvulus with segmental necrosis, followed by bowel resection and reanastomosis. His postoperative course was complicated by respiratory failure, coagulopathy, septic shock, recurrent abdominal distension, and massive ascites. Blood cultures were negative, whereas metagenomic next-generation sequencing of blood detected K. pneumoniae and Enterococcus faecium. Owing to the worsening of his condition, diagnostic paracentesis and repeat laparotomy were performed, revealing an anastomotic leak. Intraoperative pus culture yielded bla NDM -positive CRKP. The isolate was resistant to carbapenems and ceftazidime-AVI but was susceptible to ATM-AVI, with a minimum inhibitory concentration of ≤4 mg/L. ATM-AVI was administered at 30 mg/kg every 8 h, based on the aztreonam component, for 14 days; linezolid and fluconazole were co-administered as part of the broader anti-infective regimen. The combination of definitive surgical source control, targeted antimicrobial therapy, and comprehensive intensive care successfully controlled the infection and stabilized his hemodynamics. The patient defervesced within 24 h of the first ATM-AVI dose. Inflammatory markers declined rapidly, allowing safe extubation. Follow-up abdominal cultures remained negative. No hepatic or renal toxicity was observed during treatment. This case suggests that, when combined with adequate surgical source control, ATM-AVI may represent a valuable mechanism- and susceptibility-guided pharmacological component in a multidisciplinary treatment paradigm for severe bla NDM -positive CRKP infections in selected infants.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>本研究旨在探討地理區域與加工工藝對雲南傳統乾醃牛肉（尋甸、玉溪、紅河三地）品質、微生物群落及代謝物的影響。研究結合高通量定序與非靶向代謝組學技術，發現不同地區的乾醃牛肉在感官評分與理化性質上存有顯著差異。細菌群落以厚壁菌門和葡萄球菌屬為主；真菌群落中，尋甸和紅河樣品以德巴利酵母屬為主，玉溪樣品則以紅酵母屬與枝孢菌屬為特有優勢菌。代謝組學共鑑定出1320種代謝物，其中196種為差異代謝物，主要涉及甘油磷脂、嘧啶及花生四烯酸代謝通路。關聯分析顯示，葡萄球菌屬和乳球菌屬與氨基酸衍生物呈正相關，而廣義乳桿菌屬與德巴利酵母屬則與有機酸及甘油磷脂密切相關。本研究揭示了微生物與代謝物的關聯性，為乾醃牛肉的品質控制與產地溯源提供了重要科學依據。</t>
+          <t>本研究報告了一名 2 個月大嬰兒因腸扭轉及腸壞死術後併發嚴重腹腔內感染的個案。該患兒感染了帶有 *bla*NDM 基因的碳青黴烯類抗藥性肺炎克雷伯菌（CRKP），傳統治療方案受限。臨床醫師透過宏基因體次世代定序（mNGS）精準檢測出致病菌，並在實施外科手術控制感染源的基礎上，給予 Aztreonam-avibactam (ATM-AVI) 藥物治療。結果顯示，患者於給藥後 24 小時內退燒，發炎指標迅速下降，且治療期間未見肝腎毒性。此案例證實，對於臨床治療極為棘手的耐藥性 CRKP 感染，結合外科手術與 ATM-AVI 的標靶藥物治療，在嬰兒患者中具備可行性與安全性，為臨床處理此類多重抗藥性病原體提供了重要的參考依據。</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42637430/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42666411/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>42665791</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Presumably recurrent Ureaplasma parvum infection in a female peritoneal dialysis patient: a case report and literature review.</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>BMC nephrology</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>metagenomics</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>n=1（單一個案報告）</t>
+        </is>
+      </c>
+      <c r="G60" t="b">
+        <v>0</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Peritoneal dialysis-associated peritonitis (PDAP) caused by Ureaplasma parvum (U. parvum) is exceedingly rare, and its diagnosis is particularly challenging due to the organism's biological characteristics and the limitations of conventional detection methods. To date, only sporadic case reports are available, but the diagnostic processes and clinical characteristics of PDAP caused by U. parvum infection have not been comprehensively reported yet. We report a 35-year-old female patient undergoing continuous ambulatory peritoneal dialysis (CAPD) who experienced three episodes of peritonitis within a six-month period. Despite empirical antibiotic therapy leading to clinical improvement, routine microbiological cultures of the dialysate remained negative during each episode. During the third episode, metagenomic next-generation sequencing (mNGS) of the peritoneal dialysis (PD) effluent finally detected U. parvum as the causative pathogen. Following removing a potential risk factor, an intrauterine device (IUD), and adjusting the antimicrobial therapy to intraperitoneal (IP) levofloxacin and oral azithromycin, the patient achieved complete recovery and successfully resumed PD. Based on this experience, we documented the characteristic clinical profile of such infections and proposed an exploratory clinical diagnosis and treatment flowchart. Patients with recurrent culture-negative PDAP, especially female with an IUD, should be evaluated for U. parvum infection as a potential pathogen. mNGS facilitates the rapid detection of pathogens that traditional methods may fail to identify. Effective management of such infections necessitates not only targeted antimicrobial therapy guided by precise pathogen identification, but also the removal of potential risk factors such as the IUD.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>本研究探討了一例腹膜透析相關性腹膜炎（PDAP）患者，因反覆出現文化檢測陰性的腹膜炎症狀，最終透過宏基因組次世代定序（mNGS）確診為微小脲原體（*Ureaplasma parvum*）感染。該研究強調了傳統微生物培養技術在偵測特定生長緩慢或特殊細菌時的局限性。透過移除潛在風險因子（子宮內避孕器）並調整抗生素治療方案，患者成功康復。此個案證實，對於臨床上反覆發生、培養陰性的腹膜炎，特別是女性患者，應將 *U. parvum* 列為潛在病原體，且 mNGS 技術在精準診斷罕見及難以培養的病原體上具備極高臨床價值。</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42665791/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>42637484</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Insights into the analysis of microbial communities in fermented foods from the perspective of DNA-based techniques.</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Food research international (Ottawa, Ont.)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>16S, metagenomics</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G61" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>The quality, flavor, and stability of fermented foods depend on the microbial community. However, microbial dynamics are difficult to observe directly, leading to limited control over fermentation. High-throughput sequencing is a revolutionary tool for microbial characterization, among which DNA-based amplicon and metagenomic sequencing are core techniques. Nevertheless, the related data processing workflows in the context of fermented foods have not yet been systematically summarized, hindering the translation of research findings into fermentation practices. This review clarifies the applications of amplicon and metagenomic sequencing in fermented foods. For amplicon sequencing, the impacts of target regions, data preprocessing, and reference databases are addressed. For metagenomic sequencing, sequencing strategies, read-based and binning-based analytical methods, functional annotation, and species-specific databases are discussed. In addition, major strategies for downstream analysis of community data are summarized, including microbial diversity, co-occurrence networks, niche and community assembly, key environmental drivers, and machine learning-based prediction. Amplicon sequencing efficiently reveals microbial succession during fermentation but has limitations in functional annotation. Metagenomic sequencing is notable for functional annotation, enabling the linkage between microbial communities and metabolic potential alongside community characterization. Standardized data preprocessing and specific databases are critical for improving characterization. For community data, integrated analysis allows uncovering the driving factors of microbial succession, thereby helping to regulate fermentation. Notably, the compositional nature of the data must be considered and validated to avoid spurious associations. In summary, the exponential growth of sequencing data will propel the era of precision fermentation.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>本文為一篇綜述性研究，旨在探討以 DNA 為基礎的高通量定序技術（包含擴增子定序與宏基因組學）在發酵食品微生物群落分析中的應用。研究指出，儘管高通量定序技術已成為解析微生物動態的革命性工具，但目前缺乏系統性的數據處理框架，限制了科學發現向產業實踐的轉化。本文詳細梳理了從目標區域選擇、數據預處理、參考數據庫建立到下游生物資訊分析（如共現網絡、生態棲位構建及機器學習預測）的標準化流程。研究強調，擴增子定序雖能有效揭示群落演替，但在功能註解上存在限制；而宏基因組學則具備更強的功能解析潛力，能將微生物組成與代謝功能聯繫起來。透過標準化數據處理流程並考慮數據的組成特性，這些先進技術將精準調控發酵過程，引領精密發酵時代的到來。</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42637484/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>42637478</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Effects of sorghum variety on fermentation microecology and flavor characteristics of sesame-flavor Baijiu.</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Food research international (Ottawa, Ont.)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>16S, metabolomics</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>3 種高粱品種（Hongyingzi, Hei'e, G），於 2 輪發酵週期中，在 3 個時間點（0、15、50 天）採集發酵酒醅檢體（樣本總數依實驗設計推算為 18 組發酵樣品）</t>
+        </is>
+      </c>
+      <c r="G62" t="b">
+        <v>0</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sorghum, the principal raw material for Baijiu fermentation, plays a key role in shaping fermentation microecology and flavor formation. However, the effects of sorghum varietal differences on sesame-flavor Baijiu fermentation remain insufficiently understood. In this study, three sorghum varieties, Hongyingzi (R), Hei'e (B), and a domestic cultivar (G), were compared over two consecutive fermentation rounds. Fermented grain (Jiupei) samples collected at 0, 15, and 50 days were analyzed for physicochemical properties, enzyme activities, microbial communities, volatile compounds in Jiupei and base liquor, and the taste characteristics of the corresponding base liquor. Despite showing similar overall fermentation trends, the three sorghum varieties differed in acid accumulation, starch utilization, microbial succession, and volatile composition. Fungal communities shifted from early Pichia dominance to multi-genus coexistence, whereas bacterial communities progressively converged toward Lactobacillus dominance. A total of 218 and 258 volatile compounds were identified in Jiupei and 176 and 192 in base liquor from the first and second rounds, respectively. Esters were the dominant differential class, and volatile-marker profiles varied among sorghum varieties and fermentation rounds, with no single variety showing consistent enrichment across all sesame-flavor-related compounds. These results indicate that sorghum variety is an important factor associated with microbial assembly and flavor formation during sesame-flavor Baijiu fermentation, and provide a basis for raw material selection and flavor-oriented process optimization.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>本研究旨在探討不同高粱品種對芝麻香型白酒發酵過程中，微生物群落結構與風味代謝物質形成的影響。研究比較了紅纓子（R）、黑鵝（B）與國內品種（G）三種高粱，分析其在發酵過程中的理化特性、微生物演替及揮發性化合物組成。研究發現，儘管各品種發酵趨勢相似，但在酸度累積、澱粉利用率及微生物群落演替上存在顯著差異；真菌群落由早期的畢赤酵母（*Pichia*）主導轉變為多菌屬共存，細菌群落則趨向於乳桿菌（*Lactobacillus*）主導。分析鑑定出上百種揮發性化合物，其中酯類是導致風味差異的主要代謝物。本研究證實了高粱品種是決定白酒發酵微生物群落組裝與最終風味品質的關鍵因子，為白酒產業的原料選擇與製程最佳化提供了重要的科學依據。</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42637478/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>42637476</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>A Shenling Baizhu San polysaccharide fraction (SLP-2)-based synbiotic alleviates lactose-induced gut dysfunction via a microbiota-metabolite-barrier axis.</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Food research international (Ottawa, Ont.)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>16S, metabolomics</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G63" t="b">
+        <v>0</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Lactose intolerance (LI) is a common digestive disorder, and its management still relies largely on dietary restriction. Because gut microbial fermentation and barrier dysfunction contribute to LI-related symptoms, microbiota-targeted prebiotic or synbiotic strategies may provide complementary approaches. However, the active plant-polysaccharide fractions and their microbial partners remain unclear. This study aimed to identify the bioactive polysaccharide fraction from Shenling Baizhu San and evaluate its pairing with responder bacteria for alleviating high-lactose diet (HLD)-induced intestinal dysfunction. Stepwise ethanol precipitation yielded SLP-2, which was subsequently identified as the principal bioactive fraction through human fecal fermentation, monoculture assays, and an HLD rat model. SLP-2 enriched Eubacterium-associated taxa and supported the growth of Akkermansia muciniphila in monoculture and in vivo. Building on this, a synbiotic combining SLP-2 with A. muciniphila and E. rectale alleviated HLD-induced gut dysfunction; the antibiotic-matched comparison with the probiotics-only group supported an SLP-2-associated contribution. The synbiotic intervention was associated with increased tight junction proteins, MUC2 expression, improved intestinal architecture, and thicker mucus layers. Multi-omics analysis linked co-metabolites, including intestinal 6-MGG and HTy-Ac and systemic DHPV-G, with barrier restoration and an immune profile characterized by increased IL-10 and lower TLR4 expression. These findings suggest that SLP-2-based synbiotic intervention alleviates HLD-induced intestinal dysfunction through microbiota-metabolite-barrier modulation, providing preclinical evidence for future functional-food strategies pending human validation.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>本研究旨在探討參苓白朮散多醣活性組分（SLP-2）結合特定菌株，對高乳糖飲食（HLD）引發之腸道功能障礙的緩解作用。研究發現，SLP-2能促進*A. muciniphila*與真桿菌屬相關菌群生長。以SLP-2搭配益生菌的合生元配方，能顯著改善HLD大鼠的腸道屏障，包含增加緊密連接蛋白與MUC2表達、增厚黏液層。多體學分析顯示，其保護作用與腸道及全身性代謝物（如6-MGG、DHPV-G）的調節，以及抗發炎反應（提升IL-10、降低TLR4）密切相關。此發現為開發防治乳糖不耐症的功能性食品提供了臨床前依據。</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42637476/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>42637471</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Fucoidan from giant kelp alleviates postmenopausal osteoporosis by regulating the betaine-OPG/RANKL/RANK signaling axis.</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Food research international (Ottawa, Ont.)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>16S, metabolomics</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G64" t="b">
+        <v>0</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Postmenopausal osteoporosis (PMOP), characterized by excessive bone resorption and impaired bone remodeling, remains a significant global health challenge. This study investigated the protective effects of fucoidan from giant kelp (GKP) against PMOP and its underlying mechanisms in ovariectomized mice. GKP supplementation attenuated bone loss by preserving trabecular microarchitecture, normalizing systemic mineral homeostasis, and suppressing osteoclastogenesis, as evidenced by the downregulation of osteoclast-related genes. 16S rRNA gene sequencing revealed that GKP reshaped the gut microbiota by decreasing the Bacteroidota/Firmicutes ratio and enriching beneficial taxa, which promoted short-chain fatty acid production. Targeted metabolomics revealed that GKP induced profound systemic metabolic reprogramming, particularly amino acid metabolism, and identified betaine as a key systemic metabolite effector upregulated following GKP treatment. In vitro assays demonstrated that betaine suppressed receptor activator of nuclear factor-κB ligand (RANKL)-induced osteoclast differentiation and mitigated inflammation. In vivo validation demonstrated that betaine intervention recapitulated the osteoprotective phenotype observed in GKP-treated mice, which was associated with regulation of the osteoprotegerin/RANKL/RANK signaling axis. These results indicate that GKP exerts anti-osteoporotic effects in association with changes in gut microbiota and systemic metabolism, while betaine-mediated regulation of the OPG/RANKL/RANK signaling may contribute to its osteoprotective activity.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>本研究探討巨藻褐藻醣膠（GKP）對去卵巢小鼠更年期後骨質疏鬆症（PMOP）的保護機制。結果顯示，補充GKP能有效減少骨質流失並抑制破骨細胞生成。16S定序顯示GKP重塑了腸道菌群（降低擬桿菌門/厚壁菌門比例），促進短鏈脂肪酸產生。代謝組學分析發現，GKP顯著提升了系統性代謝物甜菜鹼（betaine）的含量。體內外實驗進一步證實，甜菜鹼透過調控OPG/RANKL/RANK信號軸，能抑制破骨細胞分化並緩解骨質流失。本研究證實GKP具備透過「腸道菌群-代謝物」軸抗骨質疏鬆的潛力，為PMOP防治提供了科學依據。</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42637471/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>42637450</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Highland barley polysaccharides promoted lactose intestinal fermentation in vitro: Unveiling the dynamic response of gut microbiota and polysaccharide structure.</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Food research international (Ottawa, Ont.)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>16S, metabolomics</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>乳糖不耐症患者的糞便檢體（未提及具體數量）</t>
+        </is>
+      </c>
+      <c r="G65" t="b">
+        <v>0</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Lactose intolerance affects over 70% of the global population due to the untimely metabolism of lactose in the colon. To accelerate lactose metabolism, we innovatively employed highland barley polysaccharides (HBP) to modulate the colonic fermentation efficiency of lactose using an in vitro fermentation model and fecal samples from lactose intolerant patients. With the addition of HBP, the consumption efficiency of lactose began to increase after 6 h of fermentation. At 48 h, lactose consumption increased by 29%, surpassing the effect of commercial prebiotics. Meanwhile, HBP with lower molecular weight (HBP-L, 8.69 × 104 g/Mol) exhibited more effective impacts than HBP with high molecular weight (HBP-H, 1.22 × 105 g/Mol), which was particularly evident during the 12-48 h of fermentation. More importantly, HBP, particularly HBP-L, substantially enriched Segatella, Bifidobacterium, and Ligilactobacillus in a time-dependent manner and was positively correlated with decreased lactose levels and elevated bacterial lactase activity, resulting in significant conversion of lactose to lactic acid and short-chain fatty acids. During the first 12 h of fermentation, HBP-L underwent more significant degradation than HBP-H. Meanwhile, the xylose residues and Glcp glycosidic bonds in HBP-L were preferentially utilized, while it was glucose residue in HBP-H. Thus, it indicated that HBPs were degraded and altered the composition of the gut microbiota, thereby enhancing the fermentation efficiency of lactose. Our findings provide a theoretical basis for developing targeted prebiotic foods to manage lactose intolerance.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>本研究旨在探討青稞多醣（HBP）如何調控乳糖不耐症患者的腸道菌群，以促進體外乳糖發酵與代謝。研究發現，添加 HBP（特別是低分子量的 HBP-L）能在發酵 48 小時後提升乳糖消耗效率達 29%，效果顯著優於商業益生元。機制上，HBP-L 在發酵初期降解更為顯著，並能隨時間特異性富集 *Segatella*、雙歧桿菌屬（*Bifidobacterium*）及 *Ligilactobacillus*，進而提升細菌乳糖酶活性，將乳糖轉化為乳酸與短鏈脂肪酸。本研究證實了青稞多醣能透過重塑腸道菌群結構來加速乳糖代謝，為開發緩解乳糖不耐症的標靶益生元食品提供了重要科學依據。</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42637450/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>42662912</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Insights into antibiotic resistomes from gut meta-genome-assembled genomes of the free-range chickens.</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Veterinary and animal science</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>metagenomics</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>120 個放養雞糞便檢體（重建出 2,146 個宏基因組組裝基因組/MAGs）</t>
+        </is>
+      </c>
+      <c r="G66" t="b">
+        <v>0</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Antibiotic resistance is a growing global threat, and the chicken gut microbiome is a significant reservoir of antibiotic resistance genes (ARGs). To investigate the presence of ARGs in free-range chickens, which are in closer contact with humans and live in closer proximity to human settlements. In this study, we used metagenomic sequencing to characterize the resistome of the chicken gut. We collected 120 fecal samples from free-range chickens across four Chinese provinces and constructed both metagenome-assembled genomes (MAGs) and comprehensive gene catalogs to investigate microbial community structures and ARG distributions. A total of 2,146 MAGs were reconstructed, encompassing 660 species from 26 phyla, forming a comprehensive genomic catalog of the chicken gut microbiota. We identified 254,316 ARGs representing 159 unique resistance genes across 35 antibiotic classes, with multidrug, tetracycline, glycopeptide, and peptide resistance being most prevalent. Notably, ARG distribution showed strong regional variation, influenced by environmental factors and local farming practices. Mobile genetic elements (MGEs), averaging 33.8 per MAG, were positively correlated with ARG abundance (R = 0.77), underscoring their role in facilitating resistance gene dissemination. Specific MAGs-including strains of Escherichia coli and Klebsiella pneumoniae-harbored hundreds of ARGs and virulence factors, highlighting potential high-risk vectors for resistance spread. Our findings reveal a diverse and regionally dynamic antibiotic resistome in the chicken gut, shaped by microbial composition, environment, and host factors. This study provides a valuable genomic resource and emphasizes the need for targeted interventions and surveillance strategies to mitigate antibiotic resistance in poultry production systems.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>本研究旨在探討放養雞腸道菌群中的抗生素抗藥性基因（ARGs）分布。研究團隊分析了中國四省的120個放養雞糞便檢體，重建出2,146個宏基因組組裝基因組（MAGs）。結果共鑑定出254,316個ARGs，以多重抗藥性與四環黴素抗性最為普遍。ARGs分布具顯著地域差異，且與行動遺傳元件（MGEs）呈強正相關（R=0.77），證實其高傳播潛力。此外，大腸桿菌和肺炎克雷伯氏菌等特定菌株被發現攜帶多種ARGs與毒力因子，為潛在的高風險傳播媒介。本研究建立的基因組資源，對制定禽類抗藥性監控與防治策略具有重要科學價值。</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42662912/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>42637441</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Microbial succession drives quality deterioration in refrigerated golden pompano (Trachinotus ovatus): regulatory network of dominant spoilage microbiota on characteristic biomarkers.</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Food research international (Ottawa, Ont.)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>16S, metabolomics</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G67" t="b">
+        <v>0</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Elucidating the quality deterioration mechanisms of refrigerated golden pompano (Trachinotus ovatus), this study integrated 16S rRNA gene sequencing and untargeted metabolomics to systematically dissect how microbial ecological succession drives metabolic changes. As critical spoilage indicators, total volatile basic nitrogen (TVB-N) and thiobarbituric acid reactive substances (TBARS) continuously increased during storage, indicating significant deterioration by day 6. Microbial community succession analysis revealed that Psychrobacter, Shewanella, and Pseudomonas gradually became the dominant microbiota in the late storage stage. Metabolite enrichment analysis further demonstrated that this shift redirected the metabolic focus from early-stage nucleotide degradation to late-stage protein hydrolysis and amino acid metabolism. Moreover, multivariate statistical analysis identified 50 potential spoilage biomarkers, among which biogenic amines (histamine, tyramine, and phenylethylamine) were recognized as key indicators reflecting spoilage progression. Correlation network analysis revealed positive correlations between Pseudomonas and Shewanella abundances and the accumulation of these biogenic amines. This suggests that these two genera act as the core functional microbiota, driving spoilage metabolite generation and subsequent quality deterioration. Pathway analysis of potential spoilage biomarker generation indicates that amino acid and nucleotide metabolism constitute the core spoilage pathways, with lipid oxidation serving as a complementary mechanism. Overall, this study elucidates the spoilage mechanisms of refrigerated golden pompano, providing chemical targets for early biomarker detection and targeted antibacterial strategies.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>本研究旨在探討冷藏金鯧魚品質劣化的機制。研究結合 16S rRNA 基因定序與非靶向代謝組學，分析微生物群落演替如何驅動代謝變化。結果顯示，金鯧魚冷藏至第 6 天時顯著腐敗。在貯藏後期，*Psychrobacter*、*Shewanella* 與 *Pseudomonas* 逐漸成為優勢菌群，使代謝焦點自初期的核苷酸降解轉向後期的蛋白質水解與氨基酸代謝。研究鑑定出 50 個潛在腐敗生物標誌物（如組胺、酪胺等生物胺），並發現 *Pseudomonas* 和 *Shewanella* 的豐度與這些生物胺的累積呈正相關，為驅動腐敗的核心菌群。本研究闡明了金鯧魚的腐敗機制，為食品早期變質檢測及靶向抑菌策略提供了科學依據與化學標靶。</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42637441/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>42637430</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Regional differentiation of microbial communities and metabolites in Yunnan dry-cured beef: insights from high-throughput sequencing and untargeted metabolomics.</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Food research international (Ottawa, Ont.)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>16S, metabolomics</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G68" t="b">
+        <v>0</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>To reveal the effects of regional processing on quality, microbial communities and metabolites of traditional Yunnan dry-cured beef, samples from Xundian (XD), Yuxi (YX) and Honghe (HH) were analyzed. High-throughput sequencing and UHPLC-Q-Exactive HF/MS untargeted metabolomics were applied. Sensory scores and physicochemical Properties differed significantly (p &lt; 0.05). Bacillota and Staphylococcus dominated bacterial communities. The observed differences in microbial communities and metabolites among regions are shaped by the combined effects of geographical environment and processing conditions. Ascomycota was the main fungal phylum. Debaryomyces dominated XD and HH samples. YX samples had a unique fungal profile dominated by Rhodotorula and Cladosporium. A total of 1320 metabolites were identified. 196 differential metabolites were screened. Key pathways included glycerophospholipid metabolism, pyrimidine metabolism and arachidonic acid metabolism. Correlation analysis indicated that Staphylococcus and Lactococcus were positively associated with amino acid derivatives, while Latilactobacillus and Debaryomyces correlated with organic acids and glycerophospholipids. These findings revealed the potential microbial-metabolic association underlying regional quality differences. They provide support for quality control and traceability of dry-cured beef.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>本研究旨在探討地理區域與加工工藝對雲南傳統乾醃牛肉（尋甸、玉溪、紅河三地）品質、微生物群落及代謝物的影響。研究結合高通量定序與非靶向代謝組學技術，發現不同地區的乾醃牛肉在感官評分與理化性質上存有顯著差異。細菌群落以厚壁菌門和葡萄球菌屬為主；真菌群落中，尋甸和紅河樣品以德巴利酵母屬為主，玉溪樣品則以紅酵母屬與枝孢菌屬為特有優勢菌。代謝組學共鑑定出1320種代謝物，其中196種為差異代謝物，主要涉及甘油磷脂、嘧啶及花生四烯酸代謝通路。關聯分析顯示，葡萄球菌屬和乳球菌屬與氨基酸衍生物呈正相關，而廣義乳桿菌屬與德巴利酵母屬則與有機酸及甘油磷脂密切相關。本研究揭示了微生物與代謝物的關聯性，為乾醃牛肉的品質控制與產地溯源提供了重要科學依據。</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42637430/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>42637417</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>Allergic responses, gut microbiome and serum metabolism of mice: Effects of epigallocatechin gallate combined with sodium pyrophosphate modified parvalbumin.</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Food research international (Ottawa, Ont.)</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
         <is>
           <t>16S, metabolomics</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>未提及</t>
         </is>
       </c>
-      <c r="G60" t="b">
-        <v>0</v>
-      </c>
-      <c r="H60" t="inlineStr">
+      <c r="G69" t="b">
+        <v>0</v>
+      </c>
+      <c r="H69" t="inlineStr">
         <is>
           <t>Epigallocatechin gallate (EGCG) combined with sodium pyrophosphate (SP) modified parvalbumin (PV) was proposed to sensitize mice, and investigated whether allergic responses changes were associated with gut microbiome and serum metabolism of mice. EGCG combined with SP modified PV has structural changes, and alleviated jejunal damage in mice, while decreased specific serum IgG, IgG1 and IgE levels and may rebalanced Th1/Th2 immune responses. PV-induced allergic responses disrupted gut microbiota and reduced short-chain fatty acids (SCFAs) levels. In contrast, the modified PV could alter the relative abundance of allergic responses-related gut microbiota, such as g__unclassified_f__Lachnospiraceae, g__norank_o__Clostridia_UCG-014 and g__Alistipes, alongside elevated SCFAs levels. Additionally, the modified PV could affect multiple metabolic pathways in serum, and exert a positive impact on phosphatidylethanolamine and phosphatidylcholine levels in glycerophospholipid metabolism. Therefore, the reduction in the allergic responses of PV modified by EGCG and SP were associated with changes in gut microbiota and modulation of glycerophospholipid metabolisms. These correlational observations provided preliminary associative evidence supporting the potential utility of combined EGCG-SP modification as a hypoallergenic processing approach for fish parvalbumin mitigation.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>本研究旨在探討利用表沒食子兒茶素沒食子酸酯（EGCG）結合焦磷酸鈉（SP）修飾魚類主要過敏原小清蛋白（PV），對小鼠過敏反應、腸道菌群及血清代謝的影響。結果顯示，修飾後的PV結構發生改變，能顯著減輕小鼠空腸損傷，降低血清特異性IgG、IgG1及IgE水平，並重建Th1/Th2免疫平衡。此外，修飾後的PV調節了過敏相關腸道菌群（如*Lachnospiraceae*與*Alistipes*）的相對豐度，提升了短鏈脂肪酸（SCFAs）含量，並改善血清甘油磷脂代謝。本研究證實EGCG-SP聯合修飾可作為降低魚類過敏原性的潛在低致敏加工方法。</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/42637417/</t>
         </is>

--- a/papers_database.xlsx
+++ b/papers_database.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17 個案例（1 例本研究案例 + 16 例文獻回顧案例）</t>
+          <t>1 例新生兒病例與文獻回顧之 16 例（共計 17 例）</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -514,7 +514,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>本研究旨在探討新生兒解脲支原體（U. parvum）腦膜炎的臨床特徵、診斷及治療。該病症狀缺乏特異性，常表現為發燒與腦脊液（CSF）異常，但血液常規檢查往往正常，導致經驗性抗生素治療無效。研究顯示，宏基因組二代測序（mNGS）是確診該病的重要工具。透過回顧包含本個案在內的 17 例病例，發現大環內酯類藥物為主要治療手段，療程通常需 3 至 10 週。儘管多數患者預後良好，但部分個案仍可能出現腦室擴張、腦梗塞等嚴重神經系統併發症及長期發育遲緩。本研究強調，對於抗生素治療反應不佳的新生兒腦膜炎，臨床醫師應高度懷疑並及早進行 mNGS 檢測，以利精準治療並降低神經後遺症風險。</t>
+          <t>本研究旨在探討新生兒微小脲原體（*Ureaplasma parvum*）腦膜炎的臨床特徵、診斷與治療。研究分析了一例經腦脊髓液宏基因組定序（mNGS）確診的男嬰病例，並結合文獻回顧，共納入17例。結果顯示，該病臨床表現缺乏特異性，主要為發燒與抽搐，部分患兒血常規正常但腦脊髓液呈化膿性改變，常規治療效果不佳，診斷高度依賴mNGS。治療以大環內酯類藥物為主，多數預後良好。本研究的臨床意義在於，強調對於經驗性抗生素治療無效的新生兒腦膜炎，應及早進行腦脊髓液mNGS檢測以明確病因，並指導抗生素的精準使用。</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -551,12 +551,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>metagenomics, others</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>未提及（文中未明確指出具體的檢體或樣本總數量）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -569,7 +569,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>本研究開發了一種結合原位發酵與光合同步硝化-反硝化除磷（F/P-SNDPR）的微藻-細菌共生系統，旨在解決低碳氮比（C/N）廢水處理中常見的污泥過量與能耗問題。實驗發現，透過最適化的 16 小時黑暗與 8 小時光照循環，該系統能有效提升氮（&gt;83%）與磷（&gt;95%）的去除率，並顯著減少污泥產量與淨二氧化碳排放。宏基因體分析揭示，「Candidatus Phosphoribacter」為關鍵的發酵菌，其產生的揮發性脂肪酸（VFA）可支持「Candidatus Accumulibacter」等菌群進行高效除磷與反硝化作用。此技術透過微生物間的代謝耦合，無需外加碳源或機械曝氣，為低碳廢水處理提供了一項永續且具經濟效益的解決方案。</t>
+          <t>本研究開發了一種結合原位發酵與光照同步硝化反硝化除磷（F/P-SNDPR）的系統，旨在解決低碳氮比（C/N）廢水處理中剩餘污泥過多與光暗不匹配的問題。在最佳的16小時黑暗/8小時光照循環下，該系統實現了超過83%的氮和95%的磷去除率，並顯著降低污泥產量與二氧化碳排放。總體基因體學分析顯示，*Candidatus* Phosphoribacter 為主要發酵微生物，其發酵相關基因在暗期產生揮發性脂肪酸（VFA），進而支持 *Candidatus* Accumulibacter 等菌群進行高效脫氮除磷。此系統為低碳氮比廢水處理提供了一種無需機械曝氣或外加碳源、且能減少污泥的低碳高效新策略。</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>38 個森林與草原生態系統（2009 年與 2019 年兩次採樣）</t>
+          <t>38 個森林與草原生態系的土壤檢體（分別於 2009 年與 2019 年進行兩次重現採樣）</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -624,7 +624,8 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>本研究針對中國東部 38 個森林與草原生態系統進行十年跨度的重複採樣，旨在探討真實環境下氮沉降對土壤微生物群落的影響。研究利用總體基因體學（shotgun metagenomics）分析發現，過去十年內土壤微生物的分類與功能多樣性顯著增加了 17%。氮沉降被識別為驅動群落結構變遷的最主要環境因子，並與氮循環基因的相對豐度增加、微生物群落空間周轉率降低密切相關。此外，研究觀察到碳降解與磷循環基因的上升，以及病原體、抗藥性基因與 DNA 病毒的減少，進而提升了整體的土壤健康指數。此發現挑戰了過去依賴短期或高強度模擬實驗的認知，強調真實環境下的長期氮沉降可減緩微生物的養分限制，對生態系統健康具有複雜且深遠的正面影響。</t>
+          <t>本研究旨在探討真實世界中長期環境變化（如大氣氮沉降）對土壤微生物群落及土壤健康的影響。研究團隊於 2009 年與 2019 年，對中國東部 38 個森林和草原生態系的土壤進行重新採樣，並透過總體基因體學（shotgun metagenomics）分析其分類與功能多樣性。
+結果顯示，十年間土壤微生物多樣性顯著提升了 17%。在眾多環境因子中，氮沉降是預測群落變化的最強因子，其不僅促進了氮、碳、磷循環相關基因的豐度，更伴隨病原體、抗藥性基因及 DNA 病毒的減少，從而提升了綜合土壤健康指數。此研究證實了真實世界長期、低強度的環境變遷對生態系統的正面影響，並強調其微生物反應與短期高強度的人工模擬實驗結果存在顯著差異，對全球變遷研究具有重要科學價值。</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -661,12 +662,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>metagenomics, metabolomics, 16S</t>
+          <t>16S, metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22 位人類受試者（11 位健康對照、11 位長新冠患者）及若干小鼠模型</t>
+          <t>11位健康對照組受試者與11位長期新冠（LCOVID）患者（共22個糞便檢體），以及接受糞菌移植的抗生素處理（ABx）小鼠（具體小鼠數量未提及）。</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -679,7 +680,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>本研究旨在探討持續兩年之長新冠（Long COVID）患者的腸道菌群特徵及其致病潛力。透過宏基因組學與代謝體學分析，發現患者腸道菌群多樣性顯著下降，促發炎菌種（如 *Streptococcus salivarius*）增加，而具抗發炎功能的菌種（如 *Faecalibacterium*）則減少；同時，碳水化合物降解與短鏈脂肪酸生成等代謝功能受損。將患者糞便菌群移植至小鼠模型後，成功誘發了肺部與腸道發炎及焦慮行為，並加劇小鼠對肺炎克雷伯氏菌的易感性。本研究證實長新冠患者的腸道菌群失調具有因果效應，足以引發類似長新冠的臨床症狀，顯示調節腸道菌群可能是未來治療長新冠的潛在策略。</t>
+          <t>本研究旨在探討持續兩年之新冠後遺症（LCOVID）患者的腸道菌群特徵及其致病機制。研究結合宏基因組與代謝組學分析，發現LCOVID患者的腸道菌相多樣性降低，促炎菌（如唾液鏈球菌）增加，而抗炎菌減少，且碳水化合物與短鏈脂肪酸等代謝路徑受損。將患者糞便移植至小鼠後，成功誘發肺部與腸道發炎、焦慮行為，並加劇肺炎克雷伯菌感染與腸躁症症狀。此結果證實腸道菌群失衡是驅動LCOVID症狀的關鍵因子，具備作為潛在治療靶點的臨床科學價值。</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -734,7 +735,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>本文針對黃麻「浸漬法」（retting）進行系統性綜述，旨在將傳統經驗式的纖維提取過程，轉型為可控的精準生物加工技術。研究探討了植物細胞壁結構、微生物演替機制及胞外酶系統如何共同影響纖維解離與品質。作者強調，透過整合宏基因組學、宏轉錄組學、宏蛋白質組學與代謝體學等多體學技術，結合人工智慧模型，能有效提升浸漬過程的監測能力與可預測性。該研究對於推動循環生物經濟具有重大意義，透過標準化微生物群落與精準生物加工策略，不僅能優化纖維生產效率與品質，亦能解決環境污染問題，為黃麻產業實現永續與數位化轉型提供了理論框架與技術路徑。</t>
+          <t>本綜述探討黃麻漚麻（retting）技術從傳統經驗法轉向精準生物加工的最新進展。文章系統性整合了黃麻韌皮纖維結構、微生物群落演替、胞外酶網絡及物理化學調控因子的研究，並評估了特定微生物菌群、酶輔助漚麻及控溫系統等精準策略。同時，探討了多體學技術（如總體基因體學、代謝組學等）與人工智慧在過程監測與預測模型中的應用潛力。最後，文章指出了微生物相互作用不明、缺乏標準化菌群及產業化放大等關鍵知識空白，為實現標準化、可預測且環保的精準黃麻生物加工提供了系統性框架，對促進循環生物經濟具有重要科學意義。</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -751,30 +752,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>42663468</t>
+          <t>42664954</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Genomes of cressdnaviricots and phixviricots in a freshwater lake sample from Arizona, USA.</t>
+          <t>Lactobacillus salivarius potentiates gastrointestinal cancer immunotherapy through its metabolite chenodeoxycholic acid.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Microbiology resource announcements</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.6</v>
-      </c>
+          <t>Cell reports. Medicine</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>metagenomics, small genome</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1 個 40 ml 的淡水湖泊水樣</t>
+          <t>278 位胃腸道癌症患者及同基因腫瘤小鼠模型</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -782,12 +781,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>A viral metagenomic analysis of a 40 ml water sample from a small freshwater lake near Flagstaff, Arizona, USA, resulted in the identification of 295 circular viral genome sequences. Of these, 126 are members of Cressdnaviricota and 169 of Phixviricota phyla.</t>
+          <t>Immune checkpoint inhibitor therapy has improved gastrointestinal (GI) cancer management; however, many patients exhibit resistance. Although gut microbiota influences immunotherapeutic responses, the underlying mechanisms remain unclear. Metagenomic analysis of 278 GI cancer patients reveals that Lactobacillus salivarius (L. salivarius) is enriched in responders and enhances anti-PD-1 efficacy in syngeneic tumor models by increasing the infiltration of antitumor M1-like macrophages and CD8+ T cells and enhancing CD8+ T cell effector function. L. salivarius-associated chenodeoxycholic acid (CDCA) is identified as a functional metabolite. CDCA recapitulates the antitumor effects of L. salivarius and significantly improves anti-PD-1 efficacy in vivo, an effect attenuated by depleting macrophages or CD8+ T cells. Mechanistically, CDCA-induced reactive oxygen species triggers immunogenic cell death in tumor cells and polarizes macrophages toward antitumor M1 phenotype, activating CD8+ T cell antitumor immunity. These findings identify L. salivarius and its associated metabolite CDCA as a promising adjuvant for potentiating immunotherapy in GI cancers.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>本研究旨在探討美國亞利桑那州 Flagstaff 附近一處小型淡水湖泊中的病毒多樣性。研究團隊對 40 毫升的水樣進行病毒總體基因體學（viral metagenomics）分析，成功鑑定並組裝出 295 個環狀病毒基因體序列。在這些病毒中，有 126 個屬於 Cressdnaviricota 門（環狀單鏈 DNA 病毒），另有 169 個屬於 Phixviricota 門（微小噬菌體相關病毒）。此研究的科學意義在於顯著擴充了淡水生態系統中這兩大病毒門的基因體數據，並證實即使在極少量的環境水樣中，也蘊藏著極高多樣性且未知的病毒資源，有助於深化對淡水微生態系統及病毒演化多樣性的理解。</t>
+          <t>本研究旨在探討腸道菌群影響胃腸道（GI）癌症免疫治療反應的具體機制。透過對 278 位 GI 癌症患者的總體基因體分析，發現唾液乳桿菌（*Lactobacillus salivarius*）在治療有反應的患者體內顯著富集。於小鼠模型中，該菌能增加抗腫瘤 M1 型巨噬細胞與 CD8+ T 細胞的浸潤，顯著提升抗 PD-1 療效。研究進一步證實，該菌的代謝物鵝去氧膽酸（CDCA）為關鍵功能分子，能透過誘導活性氧（ROS）引發腫瘤細胞的免疫原性死亡，並促進巨噬細胞向 M1 型極化，從而激活 CD8+ T 細胞的抗腫瘤免疫反應。本研究揭示了唾液乳桿菌及其代謝物 CDCA 作為增強 GI 癌症免疫治療活性佐劑的臨床潛力。</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -797,24 +796,24 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42663468/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42664954/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>42665077</t>
+          <t>42664608</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Metagenomic Characterization of Potential Exposure to Genetic Hazards at the Interface Between Grazing Livestock and Przewalski's Gazelle.</t>
+          <t>Application-dependent effects of tea waste biochar on PFAS mobility and N2O and CH4 emissions in agricultural soil.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Environmental pollution (Barking, Essex : 1987)</t>
+          <t>Waste management (New York, N.Y.)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -825,7 +824,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（僅說明使用盆栽模擬系統「per pot」，未提及具體樣本或盆栽數量）</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -833,12 +832,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Livestock and endangered wildlife increasingly share grazing landscapes, yet the sources, mobility-associated contexts, and bacterial hosts of livestock-associated genetic hazards in wildlife microbiomes remain poorly resolved. We analyzed metagenomes from yak, Tibetan sheep, Przewalski's gazelle, and local topsoil within an Acquired Genetic Risk (AGR) conceptual framework integrating genetic hazard burden, compositional source attribution, mobility-associated evidence, and bacterial genomic context. MRGs and Rank I and Rank III ARGs were more abundant in livestock than in Przewalski's gazelle, whereas VF abundance was highest in yak. FEAST attributed approximately 64% of the Przewalski's gazelle resistome composition to the two livestock source profiles, less than 1% to sampled topsoil, and approximately 36% remained unassigned. MGE profiles were associated with ARGs, MRGs, and VFs, while tnpA ranked highest in random forest models and was associated with total ARG abundance (R2 = 0.618). Short-read contigs containing hazard genes and MGE markers provided localized mobility-associated sequence context. Genome-resolved analysis identified distinct bacterial contexts: TS.Bin143, an Escherichia coli MAG from Tibetan sheep, contained ARGs, MRGs, VFs, tnpA, and IS91, whereas PG.Bin275, a Hylemonella sp. MAG from Przewalski's gazelle, contained tnpA. These findings extend wildlife resistome assessment beyond abundance profiling toward source attribution, mobility-associated sequence context, and bacterial host resolution, supporting multilevel surveillance of genetic hazard exposure at livestock-wildlife interfaces.</t>
+          <t>Per- and polyfluoroalkyl substances (PFAS) in agricultural soils can migrate into crops and may alter soil greenhouse gas emissions, yet remediation strategies rarely address these risks simultaneously. This study evaluated tea waste biochar (TWB) produced at 400, 500, and 600 °C and applied at 5-20 g per pot by whole-soil mixing or surface-layer placement in a simulated PFAS-contaminated soil-leachate-plant system. Perfluorooctane sulfonate (PFOS) and perfluorooctanoic acid (PFOA) distributions, nitrous oxide (N2O) and methane (CH4) fluxes, and microbial responses were examined. TWB produced at 500 °C showed the most favorable combination of pore accessibility, surface hydrophobicity, and interfacial charge, with material-associated PFOS and PFOA enrichments of 0.12 and 0.57 μg/g, respectively. Whole-soil mixing with TWB-500 lowered soil and leachate PFAS levels and reduced PFAS concentrations in plant shoots by approximately 36% relative to the contaminated control. TWB treatments also reduced cumulative N2O emissions and enhanced net CH4 uptake. Metagenomic analysis showed lower relative abundances of genes associated with nitrogen fixation, ammonia oxidation, and several N2O-producing pathways, whereas CH4-cycling genes responded differently to the two application methods. Organic fluorine transformation genes were not enriched, indicating that PFAS control mainly resulted from physicochemical retention rather than enhanced microbial defluorination. Overall, TWB-500 can integrate PFAS stabilization with greenhouse gas management, but the optimal placement depends on the remediation objective: whole-soil mixing favors PFAS immobilization, whereas surface-layer application provides greater greenhouse gas mitigation.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>本研究旨在評估放牧家畜與瀕危野生普氏原羚接觸介面上的遺傳危害（如抗藥性基因 ARG、金屬耐受基因 MRG 與毒力因子 VF）暴露風險。研究利用總體基因體學分析氛牛、藏羊、普氏原羚及當地表土，結果顯示家畜體內的 MRG 和高風險 ARG 豐度顯著高於普氏原羚。來源追蹤分析（FEAST）指出，普氏原羚約 64% 的抗藥組組成可歸因於這兩種家畜，僅不到 1% 來自土壤。此外，研究透過基因組解析定位了攜帶危害基因與移動遺傳因子的細菌宿主。本研究不僅闡明了遺傳危害的來源與傳播關聯，也為野生動物與家畜接觸介面的多層級生物安全監測提供了重要科學依據。</t>
+          <t>本研究旨在評估茶渣生物炭（TWB）在模擬的PFAS污染土壤-滲濾液-植物系統中，對於抑制全氟和多氟烷基物質（PFAS）遷移及減少溫室氣體（N2O和CH4）排放的雙重效應。研究發現，在500 °C下製備的TWB-500效果最佳。若將其均勻混合於全土中，可使植物地上部的PFAS濃度降低約36%，並顯著降低土壤和滲濾液中的PFAS含量。此外，TWB處理還減少了N2O累積排放並促進CH4淨吸收。總體基因體學分析顯示，與氮循環相關的基因豐度有所下降，解釋了N2O排放減少的機制；而有機氟降解基因並未富集，證實PFAS的控制主要源於物理化學阻控而非微生物去氟作用。此研究證明TWB-500能有效整合PFAS固化與溫室氣體管理，且施用方式（全土混合或表層施作）可依環境整治優先目標進行客製化調整。</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -848,35 +847,37 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42665077/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42664608/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>42664954</t>
+          <t>42663459</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lactobacillus salivarius potentiates gastrointestinal cancer immunotherapy through its metabolite chenodeoxycholic acid.</t>
+          <t>Clinical application of BALF-mNGS in immunocompromised and immunocompetent patients with suspected invasive pulmonary aspergillosis: differentiating infection from colonization, microbiome features, and clinical impact.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cell reports. Medicine</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Microbiology spectrum</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3.8</v>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>metagenomics, metabolomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>278 位胃腸道癌症患者及同基因腫瘤小鼠模型</t>
+          <t>178位疑似侵襲性肺麴菌病（IPA）患者（包含77位免疫功能低下患者與101位免疫功能正常患者）</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -884,12 +885,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Immune checkpoint inhibitor therapy has improved gastrointestinal (GI) cancer management; however, many patients exhibit resistance. Although gut microbiota influences immunotherapeutic responses, the underlying mechanisms remain unclear. Metagenomic analysis of 278 GI cancer patients reveals that Lactobacillus salivarius (L. salivarius) is enriched in responders and enhances anti-PD-1 efficacy in syngeneic tumor models by increasing the infiltration of antitumor M1-like macrophages and CD8+ T cells and enhancing CD8+ T cell effector function. L. salivarius-associated chenodeoxycholic acid (CDCA) is identified as a functional metabolite. CDCA recapitulates the antitumor effects of L. salivarius and significantly improves anti-PD-1 efficacy in vivo, an effect attenuated by depleting macrophages or CD8+ T cells. Mechanistically, CDCA-induced reactive oxygen species triggers immunogenic cell death in tumor cells and polarizes macrophages toward antitumor M1 phenotype, activating CD8+ T cell antitumor immunity. These findings identify L. salivarius and its associated metabolite CDCA as a promising adjuvant for potentiating immunotherapy in GI cancers.</t>
+          <t>Invasive pulmonary aspergillosis (IPA) not only causes high morbidity and mortality, especially in immunocompromised patients, but also occurs in immunocompetent individuals. Differentiating infection from colonization is challenging, and bronchoalveolar lavage fluid metagenomic next-generation sequencing (BALF-mNGS) may aid diagnosis, microbiome profiling, and clinical assessment. We retrospectively analyzed patients with suspected IPA who underwent BALF-mNGS between December 2021 and March 2025. Patients were classified by immune status. IPA diagnosis was based on EORTC/MSGERC 2020 criteria in immunocompromised patients, while immunocompetent cases were adjudicated using an integrated clinical, radiological, and microbiological assessment. A total of 178 patients were finally included and classified according to immune status into an immunocompromised group (n = 77) and an immunocompetent group (n = 101). Aspergillus_ reads per ten million (RPTM) values were significantly higher in infection versus colonization cases in both groups, with optimal cut-offs of 24 (gray zone: 22-60) for the immunocompromised group and 33 (gray zone: 17-48) for the immunocompetent group. Microbiome analysis revealed distinct community structures between infection and colonization groups, with Aspergillus remaining significantly enriched after false discovery rate (FDR) correction in immunocompromised patients, while no taxa remained significant after FDR correction in immunocompetent patients. BALF-mNGS guided antifungal therapy, avoiding unnecessary treatment in colonized patients, and higher Aspergillus_RPTM was associated with increased 90-day mortality in immunocompromised patients. BALF-mNGS may accurately distinguish Aspergillus infection from colonization and reveal microbial shifts, particularly in immunocompromised patients. It can guide targeted antifungal therapy, avoid unnecessary treatment, and higher Aspergillus_RPTM was associated with 90-day mortality in immunocompromised patients, suggesting its potential value for risk stratification.IMPORTANCEBALF-mNGS with quantitative thresholds improves differentiation between Aspergillus infection and colonization. It reveals distinct lung microbiome patterns under different immune statuses, extending beyond simple pathogen detection. Higher Aspergillus burden is associated with worse outcomes in immunocompromised patients, suggesting its potential value for risk stratification.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>本研究旨在探討腸道菌群影響胃腸道（GI）癌症免疫治療反應的具體機制。透過對 278 位 GI 癌症患者的總體基因體分析，發現唾液乳桿菌（*Lactobacillus salivarius*）在治療有反應的患者體內顯著富集。於小鼠模型中，該菌能增加抗腫瘤 M1 型巨噬細胞與 CD8+ T 細胞的浸潤，顯著提升抗 PD-1 療效。研究進一步證實，該菌的代謝物鵝去氧膽酸（CDCA）為關鍵功能分子，能透過誘導活性氧（ROS）引發腫瘤細胞的免疫原性死亡，並促進巨噬細胞向 M1 型極化，從而激活 CD8+ T 細胞的抗腫瘤免疫反應。本研究揭示了唾液乳桿菌及其代謝物 CDCA 作為增強 GI 癌症免疫治療活性佐劑的臨床潛力。</t>
+          <t>本研究旨在評估支氣管肺泡灌洗液總體基因體次世代定序（BALF-mNGS）在區分疑似侵襲性肺麴菌病（IPA）患者「感染」與「定植」的臨床價值，並探討其肺部微生態特徵。研究納入178位患者，發現感染者的麴菌相對豐度（RPTM）顯著高於定植者，並針對免疫功能低下與正常組分別訂定出24與33的最佳臨界值。微生態分析顯示兩組具有不同的菌群結構。臨床上，BALF-mNGS能有效引導抗真菌治療，避免定植患者過度治療；而在免疫功能低下組中，高麴菌RPTM值與90天高死亡率顯著相關。此技術不僅能精準診斷，更具備患者預後風險分層的潛力。</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -899,28 +900,28 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42664954/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42663459/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>42664252</t>
+          <t>42663694</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Proteobacteria with chemosynthetic potential are highly prevalent in the gills of Hypoplectrus reef fishes.</t>
+          <t>Comparative Analysis of Different Anodic Inoculum in Microbial Fuel Cell for Efficient Methylene Blue Dye Degradation.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PLoS genetics</t>
+          <t>Current microbiology</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -929,7 +930,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>353 個魚鰓檢體</t>
+          <t>3種不同的接種源（海洋沉積物、河口沉積物、厭氧污泥）</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -937,12 +938,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Fishes host a diverse microbiome in their gills, but a broad characterization of this microbiome at the metagenomic level is lacking. Here, we apply genome-resolved metagenomics to the gills of the hamlets (Hypoplectrus spp), a group of reef fishes from the Greater Caribbean. The analysis of 353 gill samples from 15 hamlet species collected at eight locations over 13 years revealed a stark contrast between the gill microbiota and reef water microbial communities, indicating a distinct and specific gill microbiome. A total of 70 gill-associated metagenome-assembled genomes (MAGs) were recovered. These MAGs belong to 17 lineages, most of which are novel. They relate to known fish gill pathogens, fish gut microbes, free-living and biofilm-associated taxa, indicating that the gill microbiome was assembled from a collection of distinct eco-evolutionary trajectories. The MAGs harbor diverse metabolic modules, involved notably in nitrogen cycling, antibiotic production and biofilm formation, revealing a highly dynamic microbial ecosystem. One lineage in the Burkholderiaceae family was outstandingly prevalent across fish host species, sampling locations and years. Its genome encoded complete metabolic modules for carbon fixation and sulfur oxidation, indicating chemosynthetic potential. To the best of our knowledge, this is the first line of evidence that fishes may host sulfur-oxidizing chemosynthetic bacteria in their gills. The functional significance of this chemosynthetic potential for the fish host or other members of the gill microbiome remains to be established. The high prevalence of this lineage allowed to build a pangenome. It revealed large-scale geographic structure (western Caribbean, eastern Caribbean and Gulf of Mexico), which parallels the phylogenomic pattern observed in the hamlets. Overall, our findings point to complex fish host-microbe and microbe-microbe eco-evolutionary interactions in the gills that may influence fish physiology, homeostasis and immune response.</t>
+          <t>This study investigates three different inoculum sources in dual-chamber microbial fuel cells (MFCs), such as Marine Sediment (MFC-MS), Estuary Sediment (MFC-ES), and Anaerobic Sludge (MFC-AS), to compare the efficacy for Methylene Blue (MB) dye degradation and electricity generation. All the MFCs were operated under identical conditions in batch mode using synthetic wastewater containing 3000 mg/L COD made using sodium acetate. The electrochemical study reveals that MFC inoculated with marine sediment achieved maximum power density of 35 mW/m² followed by anaerobic sludge (31 mW/m²) and estuary sediment (25 mW/m²). Statistical analysis was employed to evaluate performance differences among the systems and to support result interpretation. Maximum COD removal efficiency of 75% was obtained by MFC-AS, and coulombic efficiency (CE) was higher for MFC-MS with 25%. Maximum decolorization efficiency was noted in MFC with anaerobic sludge, which obtained 96% decolorization over 96 h. Comparative and trend-based statistical evaluation confirmed the superior treatment performance of MFC-assisted systems. The phytotoxicity study revealed that the toxicity effect of dye wastewater was reduced to its maximum after treatment in the MFC system. The dominant performance of MFC-MS is due to the efficiency of the major electrogenic bacteria concentrated in the inoculum. The functional annotation using the data obtained from metagenomics reveals the presence and role of various enzymes and pathways involved.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>本研究針對加勒比海地區 15 種「蝴蝶魚」（Hypoplectrus spp.）進行了大規模的宏基因組研究。透過分析 353 個魚鰓檢體並重建 70 個宏基因組組裝基因組（MAGs），研究發現魚鰓微生物群落與周圍海水環境顯著不同，具有獨特的演化軌跡。最重大的發現是鑑定出一種具高度普遍性的 Burkholderiaceae 細菌，該菌株擁有完整的固碳與硫氧化代謝路徑，顯示其具備化能合成潛力，這是科學界首次在魚類鰓部發現此類共生菌。此外，該菌株的基因體結構與宿主魚類的地理分布呈現高度一致性。此研究揭示了魚鰓微生物生態系統的複雜性，並為魚類生理、恆定性及免疫反應與微生物間的交互作用提供了重要的演化科學基礎。</t>
+          <t>本研究旨在比較雙腔式微生物燃料電池（MFC）中，三種不同接種源（海洋沉積物、河口沉積物、厭氧污泥）在降解亞甲藍染料與產電的效率。結果顯示，海洋沉積物系統具最高的功率密度（35 mW/m²）與庫倫效率（25%）；厭氧污泥系統則有最佳的化學需氧量去除率（75%）與脫色率（96%）。處理後廢水的植物毒性顯著降低。宏基因組學分析揭示了關鍵產電菌的分布及參與降解與發電的酶和代謝途徑。本研究證實了不同接種源在 MFC 污水處理與生物發電的潛力，並闡明了其微生物學機制。</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -952,28 +953,28 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42664252/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42663694/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>42663694</t>
+          <t>42664252</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Comparative Analysis of Different Anodic Inoculum in Microbial Fuel Cell for Efficient Methylene Blue Dye Degradation.</t>
+          <t>Proteobacteria with chemosynthetic potential are highly prevalent in the gills of Hypoplectrus reef fishes.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Current microbiology</t>
+          <t>PLoS genetics</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -982,7 +983,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3種不同的接種源（海洋沉積物、河口沉積物、厭氧污泥）</t>
+          <t>353 個魚鰓檢體</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -990,12 +991,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>This study investigates three different inoculum sources in dual-chamber microbial fuel cells (MFCs), such as Marine Sediment (MFC-MS), Estuary Sediment (MFC-ES), and Anaerobic Sludge (MFC-AS), to compare the efficacy for Methylene Blue (MB) dye degradation and electricity generation. All the MFCs were operated under identical conditions in batch mode using synthetic wastewater containing 3000 mg/L COD made using sodium acetate. The electrochemical study reveals that MFC inoculated with marine sediment achieved maximum power density of 35 mW/m² followed by anaerobic sludge (31 mW/m²) and estuary sediment (25 mW/m²). Statistical analysis was employed to evaluate performance differences among the systems and to support result interpretation. Maximum COD removal efficiency of 75% was obtained by MFC-AS, and coulombic efficiency (CE) was higher for MFC-MS with 25%. Maximum decolorization efficiency was noted in MFC with anaerobic sludge, which obtained 96% decolorization over 96 h. Comparative and trend-based statistical evaluation confirmed the superior treatment performance of MFC-assisted systems. The phytotoxicity study revealed that the toxicity effect of dye wastewater was reduced to its maximum after treatment in the MFC system. The dominant performance of MFC-MS is due to the efficiency of the major electrogenic bacteria concentrated in the inoculum. The functional annotation using the data obtained from metagenomics reveals the presence and role of various enzymes and pathways involved.</t>
+          <t>Fishes host a diverse microbiome in their gills, but a broad characterization of this microbiome at the metagenomic level is lacking. Here, we apply genome-resolved metagenomics to the gills of the hamlets (Hypoplectrus spp), a group of reef fishes from the Greater Caribbean. The analysis of 353 gill samples from 15 hamlet species collected at eight locations over 13 years revealed a stark contrast between the gill microbiota and reef water microbial communities, indicating a distinct and specific gill microbiome. A total of 70 gill-associated metagenome-assembled genomes (MAGs) were recovered. These MAGs belong to 17 lineages, most of which are novel. They relate to known fish gill pathogens, fish gut microbes, free-living and biofilm-associated taxa, indicating that the gill microbiome was assembled from a collection of distinct eco-evolutionary trajectories. The MAGs harbor diverse metabolic modules, involved notably in nitrogen cycling, antibiotic production and biofilm formation, revealing a highly dynamic microbial ecosystem. One lineage in the Burkholderiaceae family was outstandingly prevalent across fish host species, sampling locations and years. Its genome encoded complete metabolic modules for carbon fixation and sulfur oxidation, indicating chemosynthetic potential. To the best of our knowledge, this is the first line of evidence that fishes may host sulfur-oxidizing chemosynthetic bacteria in their gills. The functional significance of this chemosynthetic potential for the fish host or other members of the gill microbiome remains to be established. The high prevalence of this lineage allowed to build a pangenome. It revealed large-scale geographic structure (western Caribbean, eastern Caribbean and Gulf of Mexico), which parallels the phylogenomic pattern observed in the hamlets. Overall, our findings point to complex fish host-microbe and microbe-microbe eco-evolutionary interactions in the gills that may influence fish physiology, homeostasis and immune response.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>本研究旨在比較雙腔式微生物燃料電池（MFC）中，三種不同接種源（海洋沉積物、河口沉積物、厭氧污泥）在降解亞甲藍染料與產電的效率。結果顯示，海洋沉積物系統具最高的功率密度（35 mW/m²）與庫倫效率（25%）；厭氧污泥系統則有最佳的化學需氧量去除率（75%）與脫色率（96%）。處理後廢水的植物毒性顯著降低。宏基因組學分析揭示了關鍵產電菌的分布及參與降解與發電的酶和代謝途徑。本研究證實了不同接種源在 MFC 污水處理與生物發電的潛力，並闡明了其微生物學機制。</t>
+          <t>本研究針對加勒比海地區 15 種「蝴蝶魚」（Hypoplectrus spp.）進行了大規模的宏基因組研究。透過分析 353 個魚鰓檢體並重建 70 個宏基因組組裝基因組（MAGs），研究發現魚鰓微生物群落與周圍海水環境顯著不同，具有獨特的演化軌跡。最重大的發現是鑑定出一種具高度普遍性的 Burkholderiaceae 細菌，該菌株擁有完整的固碳與硫氧化代謝路徑，顯示其具備化能合成潛力，這是科學界首次在魚類鰓部發現此類共生菌。此外，該菌株的基因體結構與宿主魚類的地理分布呈現高度一致性。此研究揭示了魚鰓微生物生態系統的複雜性，並為魚類生理、恆定性及免疫反應與微生物間的交互作用提供了重要的演化科學基礎。</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1005,7 +1006,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42663694/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42664252/</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1051,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>本研究旨在探討腸道共生菌 *Agathobacter rectalis* (Ar) 在大腸直腸癌 (CRC) 中的作用。總體基因體分析顯示 CRC 患者糞便中 Ar 顯著減少；動物實驗證實 Ar 能抑制小鼠大腸腫瘤生長。代謝組學分析進一步純化出 Ar 的關鍵代謝物「表沒食子兒茶素」(EGC)。機制上，EGC 會與 pSREBF2 結合，阻斷其與 SCAP 的交互作用，進而抑制 SREBF2 的活化、降低膽固醇合成與代謝基因表現，並抑制 MAPK 訊號通路。本研究揭示了 Ar-EGC 微生物-代謝物軸抑制腫瘤的機制，為靶向膽固醇代謝的 CRC 防治提供了新策略。</t>
+          <t>本研究探討腸道共生菌 *Agathobacter rectalis* (Ar) 在大腸直腸癌 (CRC) 中的作用機制。宏基因組分析顯示 CRC 患者體內 Ar 顯著減少；小鼠實驗證實 Ar 能抑制腫瘤生長。代謝組學分析發現 Ar 能產生特定代謝物表沒食子兒茶素 (EGC)。體內外實驗顯示，EGC 可抑制 CRC 細胞生長與膽固醇代謝。機制上，EGC 透過與 pSREBF2 結合並穩定之，阻斷其與 SCAP 的交互作用，進而抑制 SREBF2 活化及下游膽固醇合成基因（如 FDPS、PCSK9）的表達，並抑制 MAPK 訊號。此研究確立了 Ar-EGC 微生物-代謝物軸，為靶向膽固醇代謝的 CRC 防治提供了新策略。</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1067,22 +1068,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>42663459</t>
+          <t>42665077</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Clinical application of BALF-mNGS in immunocompromised and immunocompetent patients with suspected invasive pulmonary aspergillosis: differentiating infection from colonization, microbiome features, and clinical impact.</t>
+          <t>Metagenomic Characterization of Potential Exposure to Genetic Hazards at the Interface Between Grazing Livestock and Przewalski's Gazelle.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Microbiology spectrum</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>3.8</v>
-      </c>
+          <t>Environmental pollution (Barking, Essex : 1987)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>metagenomics</t>
@@ -1090,7 +1089,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>178位疑似侵襲性肺麴菌病（IPA）患者（包含77位免疫功能低下患者與101位免疫功能正常患者）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -1098,12 +1097,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Invasive pulmonary aspergillosis (IPA) not only causes high morbidity and mortality, especially in immunocompromised patients, but also occurs in immunocompetent individuals. Differentiating infection from colonization is challenging, and bronchoalveolar lavage fluid metagenomic next-generation sequencing (BALF-mNGS) may aid diagnosis, microbiome profiling, and clinical assessment. We retrospectively analyzed patients with suspected IPA who underwent BALF-mNGS between December 2021 and March 2025. Patients were classified by immune status. IPA diagnosis was based on EORTC/MSGERC 2020 criteria in immunocompromised patients, while immunocompetent cases were adjudicated using an integrated clinical, radiological, and microbiological assessment. A total of 178 patients were finally included and classified according to immune status into an immunocompromised group (n = 77) and an immunocompetent group (n = 101). Aspergillus_ reads per ten million (RPTM) values were significantly higher in infection versus colonization cases in both groups, with optimal cut-offs of 24 (gray zone: 22-60) for the immunocompromised group and 33 (gray zone: 17-48) for the immunocompetent group. Microbiome analysis revealed distinct community structures between infection and colonization groups, with Aspergillus remaining significantly enriched after false discovery rate (FDR) correction in immunocompromised patients, while no taxa remained significant after FDR correction in immunocompetent patients. BALF-mNGS guided antifungal therapy, avoiding unnecessary treatment in colonized patients, and higher Aspergillus_RPTM was associated with increased 90-day mortality in immunocompromised patients. BALF-mNGS may accurately distinguish Aspergillus infection from colonization and reveal microbial shifts, particularly in immunocompromised patients. It can guide targeted antifungal therapy, avoid unnecessary treatment, and higher Aspergillus_RPTM was associated with 90-day mortality in immunocompromised patients, suggesting its potential value for risk stratification.IMPORTANCEBALF-mNGS with quantitative thresholds improves differentiation between Aspergillus infection and colonization. It reveals distinct lung microbiome patterns under different immune statuses, extending beyond simple pathogen detection. Higher Aspergillus burden is associated with worse outcomes in immunocompromised patients, suggesting its potential value for risk stratification.</t>
+          <t>Livestock and endangered wildlife increasingly share grazing landscapes, yet the sources, mobility-associated contexts, and bacterial hosts of livestock-associated genetic hazards in wildlife microbiomes remain poorly resolved. We analyzed metagenomes from yak, Tibetan sheep, Przewalski's gazelle, and local topsoil within an Acquired Genetic Risk (AGR) conceptual framework integrating genetic hazard burden, compositional source attribution, mobility-associated evidence, and bacterial genomic context. MRGs and Rank I and Rank III ARGs were more abundant in livestock than in Przewalski's gazelle, whereas VF abundance was highest in yak. FEAST attributed approximately 64% of the Przewalski's gazelle resistome composition to the two livestock source profiles, less than 1% to sampled topsoil, and approximately 36% remained unassigned. MGE profiles were associated with ARGs, MRGs, and VFs, while tnpA ranked highest in random forest models and was associated with total ARG abundance (R2 = 0.618). Short-read contigs containing hazard genes and MGE markers provided localized mobility-associated sequence context. Genome-resolved analysis identified distinct bacterial contexts: TS.Bin143, an Escherichia coli MAG from Tibetan sheep, contained ARGs, MRGs, VFs, tnpA, and IS91, whereas PG.Bin275, a Hylemonella sp. MAG from Przewalski's gazelle, contained tnpA. These findings extend wildlife resistome assessment beyond abundance profiling toward source attribution, mobility-associated sequence context, and bacterial host resolution, supporting multilevel surveillance of genetic hazard exposure at livestock-wildlife interfaces.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>本研究旨在評估支氣管肺泡灌洗液總體基因體次世代定序（BALF-mNGS）在區分疑似侵襲性肺麴菌病（IPA）患者「感染」與「定植」的臨床價值，並探討其肺部微生態特徵。研究納入178位患者，發現感染者的麴菌相對豐度（RPTM）顯著高於定植者，並針對免疫功能低下與正常組分別訂定出24與33的最佳臨界值。微生態分析顯示兩組具有不同的菌群結構。臨床上，BALF-mNGS能有效引導抗真菌治療，避免定植患者過度治療；而在免疫功能低下組中，高麴菌RPTM值與90天高死亡率顯著相關。此技術不僅能精準診斷，更具備患者預後風險分層的潛力。</t>
+          <t>本研究旨在評估放牧家畜與瀕危野生普氏原羚接觸介面上的遺傳危害（如抗藥性基因 ARG、金屬耐受基因 MRG 與毒力因子 VF）暴露風險。研究利用總體基因體學分析氛牛、藏羊、普氏原羚及當地表土，結果顯示家畜體內的 MRG 和高風險 ARG 豐度顯著高於普氏原羚。來源追蹤分析（FEAST）指出，普氏原羚約 64% 的抗藥組組成可歸因於這兩種家畜，僅不到 1% 來自土壤。此外，研究透過基因組解析定位了攜帶危害基因與移動遺傳因子的細菌宿主。本研究不僅闡明了遺傳危害的來源與傳播關聯，也為野生動物與家畜接觸介面的多層級生物安全監測提供了重要科學依據。</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1113,35 +1112,37 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42663459/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42665077/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>42664608</t>
+          <t>42663468</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Application-dependent effects of tea waste biochar on PFAS mobility and N2O and CH4 emissions in agricultural soil.</t>
+          <t>Genomes of cressdnaviricots and phixviricots in a freshwater lake sample from Arizona, USA.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Waste management (New York, N.Y.)</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Microbiology resource announcements</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.6</v>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>metagenomics, small genome</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>未提及（僅說明使用盆栽模擬系統「per pot」，未提及具體樣本或盆栽數量）</t>
+          <t>1 個 40 ml 的淡水湖泊水樣</t>
         </is>
       </c>
       <c r="G14" t="b">
@@ -1149,12 +1150,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Per- and polyfluoroalkyl substances (PFAS) in agricultural soils can migrate into crops and may alter soil greenhouse gas emissions, yet remediation strategies rarely address these risks simultaneously. This study evaluated tea waste biochar (TWB) produced at 400, 500, and 600 °C and applied at 5-20 g per pot by whole-soil mixing or surface-layer placement in a simulated PFAS-contaminated soil-leachate-plant system. Perfluorooctane sulfonate (PFOS) and perfluorooctanoic acid (PFOA) distributions, nitrous oxide (N2O) and methane (CH4) fluxes, and microbial responses were examined. TWB produced at 500 °C showed the most favorable combination of pore accessibility, surface hydrophobicity, and interfacial charge, with material-associated PFOS and PFOA enrichments of 0.12 and 0.57 μg/g, respectively. Whole-soil mixing with TWB-500 lowered soil and leachate PFAS levels and reduced PFAS concentrations in plant shoots by approximately 36% relative to the contaminated control. TWB treatments also reduced cumulative N2O emissions and enhanced net CH4 uptake. Metagenomic analysis showed lower relative abundances of genes associated with nitrogen fixation, ammonia oxidation, and several N2O-producing pathways, whereas CH4-cycling genes responded differently to the two application methods. Organic fluorine transformation genes were not enriched, indicating that PFAS control mainly resulted from physicochemical retention rather than enhanced microbial defluorination. Overall, TWB-500 can integrate PFAS stabilization with greenhouse gas management, but the optimal placement depends on the remediation objective: whole-soil mixing favors PFAS immobilization, whereas surface-layer application provides greater greenhouse gas mitigation.</t>
+          <t>A viral metagenomic analysis of a 40 ml water sample from a small freshwater lake near Flagstaff, Arizona, USA, resulted in the identification of 295 circular viral genome sequences. Of these, 126 are members of Cressdnaviricota and 169 of Phixviricota phyla.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>本研究旨在評估茶渣生物炭（TWB）在模擬的PFAS污染土壤-滲濾液-植物系統中，對於抑制全氟和多氟烷基物質（PFAS）遷移及減少溫室氣體（N2O和CH4）排放的雙重效應。研究發現，在500 °C下製備的TWB-500效果最佳。若將其均勻混合於全土中，可使植物地上部的PFAS濃度降低約36%，並顯著降低土壤和滲濾液中的PFAS含量。此外，TWB處理還減少了N2O累積排放並促進CH4淨吸收。總體基因體學分析顯示，與氮循環相關的基因豐度有所下降，解釋了N2O排放減少的機制；而有機氟降解基因並未富集，證實PFAS的控制主要源於物理化學阻控而非微生物去氟作用。此研究證明TWB-500能有效整合PFAS固化與溫室氣體管理，且施用方式（全土混合或表層施作）可依環境整治優先目標進行客製化調整。</t>
+          <t>本研究旨在探討美國亞利桑那州 Flagstaff 附近一處小型淡水湖泊中的病毒多樣性。研究團隊對 40 毫升的水樣進行病毒總體基因體學（viral metagenomics）分析，成功鑑定並組裝出 295 個環狀病毒基因體序列。在這些病毒中，有 126 個屬於 Cressdnaviricota 門（環狀單鏈 DNA 病毒），另有 169 個屬於 Phixviricota 門（微小噬菌體相關病毒）。此研究的科學意義在於顯著擴充了淡水生態系統中這兩大病毒門的基因體數據，並證實即使在極少量的環境水樣中，也蘊藏著極高多樣性且未知的病毒資源，有助於深化對淡水微生態系統及病毒演化多樣性的理解。</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1164,7 +1165,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42664608/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42663468/</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1250,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>未提及（文中僅提及 CaOx 大鼠與小鼠模型，未說明具體樣本數量）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G16" t="b">
@@ -1262,7 +1263,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>本研究探討腸道菌群與草酸鈣（CaOx）腎結石形成的病理機制。研究發現，異別石膽酸（isoalloLCA）在結石模型的大鼠與人類檢體中顯著升高，且來源於腸道菌群。透過空間代謝體學、16S 及宏基因組分析，研究確認了腸道菌群與 isoalloLCA 之間的因果關係。機制研究顯示，isoalloLCA 可直接結合並活化 PARP1，進而觸發腎小管上皮細胞的「副凋亡」（Parthanatos），導致細胞損傷與結晶沉積。動物實驗證實，透過藥物抑制或基因剔除 PARP1 可有效減輕腎臟損傷。此研究揭示了「腸道菌群—isoalloLCA—PARP1—副凋亡」這一全新的軸線，證實了該路徑在腎結石形成中的核心作用，並將 PARP1 定位為治療腎結石的潛在藥物標靶。</t>
+          <t>本研究旨在探討腸道菌群及其代謝物異別石膽酸（isoalloLCA）在草酸鈣（CaOx）腎結石形成中的作用與分子機制。透過整合16S定序、宏基因組學與空間代謝組學，研究發現 CaOx 大鼠及患者體內的腸道菌源 isoalloLCA 顯著升高。機制上，isoalloLCA 能直接結合並激活 PARP1 蛋白，誘導腎小管上皮細胞發生 PARP1 介導的細胞凋亡樣壞死（parthanatos），導致 DNA 與線粒體受損。於動物模型中，敲低或抑制 PARP1，或利用抗生素清除腸道菌群，皆能顯著減輕結晶沉積與腎損傷。本研究揭示了「腸道菌群-isoalloLCA-PARP1-parthanatos」軸在腎結石病理中的關鍵角色，並指出 PARP1 為臨床治療腎結石的具潛力靶點。</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1279,30 +1280,30 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>42656127</t>
+          <t>42657522</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Development and Validation of Mock Communities as Quality Control Materials for Clinical Metagenomic Next-Generation Sequencing.</t>
+          <t>Resistant starch alleviates intestinal fibrosis involving an acetate-mediated HDAC2-H3K27ac axis in fibroblasts.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Annals of laboratory medicine</t>
+          <t>Food &amp; function</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25 次重複分析（針對開發出的四種模擬群落進行評估）</t>
+          <t>未提及（研究使用 DSS 誘導的小鼠模型以及人類與小鼠的原代纖維母細胞，但未具體說明樣本數）</t>
         </is>
       </c>
       <c r="G17" t="b">
@@ -1310,12 +1311,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Metagenomic next-generation sequencing (NGS) enables comprehensive detection of a broad spectrum of microorganisms. However, its clinical application faces two major challenges: the development of appropriate microbiome-based biomarkers and the need to ensure the reproducibility and quality of the microbiome analytical workflow. Therefore, we developed four types of bead-based mock communities as standard materials for microbiome analysis and evaluated potential experimental biases arising from nucleic acid extraction and sequence analysis. Mock communities were assembled from strains isolated from clinical specimens and selected considering Gram reaction, taxonomic phylogeny, and prevalence, and processed into frozen beads. The communities were analyzed using shotgun whole-metagenome sequencing. The effect of DNA extraction kit choice was evaluated using the Thermo Fisher Scientific MagMAX Microbiome Ultra Nucleic Acid Isolation Kit and Qiagen PowerSoil Kit. Four types of mock communities comprising 26 species commonly found in the gastrointestinal tract, respiratory tract, skin, and genital tract plus cerebrospinal fluid were developed considering Gram reaction, GC content, and phylogenetic distribution. Across 25 repeated analyses, the median repeatability of each taxon was 18.97% (range, 2.87%-107.38%), while within-laboratory imprecision was 26.22% (range, 9.26%-153.83%). Repeatability remained below 10% for most dominant taxa with relative abundances &gt;20%. The choice of DNA extraction kit had a significant effect on taxonomic distributions. Microbial mock communities are essential QC materials for clinical metagenomic NGS. Further studies are needed to minimize variability and establish a standardized protocol for clinical implementation.</t>
+          <t>Dietary fibre-based interventions are of growing interest for the prevention and treatment of digestive diseases. In this study, we investigated the effect of resistant starch (RS) on intestinal fibrosis, a stricturing condition driven by excessive extracellular matrix (ECM) accumulation. RS was found to alleviate intestinal fibrosis in a dextran sulfate sodium (DSS)-induced chronic colitis mouse model, as evidenced by restored colon length, reduced ECM deposition (fibronectin and collagen I), and decreased levels of α-smooth muscle actin. Given that RS is fermented by the gut microbiota in the colon, metagenomic sequencing revealed that RS reshaped the composition of the gut microbiota and increased the abundance of beneficial gut bacteria, including Bacteroides acidifaciens, Faecalibaculum rodentium, and Bifidobacterium pseudolongum, which are known to enhance the production of short-chain fatty acids. Targeted metabolomic analysis further showed a marked increase in acetate levels, which was associated with reduced intestinal fibrosis. However, direct in vivo evidence that acetate is required for the anti-fibrotic effect of RS remains lacking. Using human (CCD-18Co) and primary mouse intestinal fibroblasts, the major ECM-producing cells that drive fibrosis progression, we demonstrated that acetate inhibited TGF-β-induced fibroblast activation by inhibiting histone deacetylase 2, thereby enhancing the acetylation level of histone H3 at lysine 27. Collectively, these results suggest a potential microbial-metabolic-epigenetic axis linking RS and acetate to fibrosis attenuation, which awaits causal validation in vivo. This axis holds promise as a therapeutic target for fibrotic diseases.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>本研究旨在解決臨床宏基因組次世代定序（mNGS）在品質控制與再現性上的挑戰，開發了四種基於珠粒的「模擬微生物群落」（mock communities）作為標準品。這些群落涵蓋了腸道、呼吸道、皮膚、生殖道及腦脊髓液中常見的 26 種菌株。研究透過鳥槍法全宏基因體定序（shotgun metagenomics）評估了不同 DNA 萃取試劑盒（MagMAX 與 PowerSoil）及實驗流程對結果的偏誤影響。結果顯示，微生物的檢測豐度會顯著受到萃取試劑盒選擇的干擾，且在 25 次重複實驗中，群落組成存在一定的實驗室內誤差。此研究確立了模擬群落作為臨床 mNGS 品質控制材料的重要性，對於推動微生物組檢測的標準化流程與臨床應用具有關鍵價值。</t>
+          <t>本研究探討抗性澱粉（RS）對腸道纖維化的改善作用及其潛在機制。透過 DSS 誘導的小鼠結腸炎模型，研究發現 RS 可有效減輕腸道纖維化並減少細胞外基質堆積。宏基因體定序顯示 RS 能重塑腸道菌群，增加如 *Bacteroides acidifaciens* 等短鏈脂肪酸產生菌的豐度；代謝體分析進一步證實乙酸（acetate）水平顯著上升。機制研究揭示，乙酸能抑制纖維母細胞中 HDAC2 的活性，進而提升組蛋白 H3K27 的乙醯化水平，抑制 TGF-β 誘導的纖維母細胞活化。本研究提出了一條「微生物-代謝-表觀遺傳」軸線，指出 RS 可藉由促進乙酸生成來對抗腸道纖維化，為治療纖維化相關疾病提供了新的科學依據與潛在治療靶點。</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1325,37 +1326,35 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42656127/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42657522/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>42657522</t>
+          <t>42660108</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Resistant starch alleviates intestinal fibrosis involving an acetate-mediated HDAC2-H3K27ac axis in fibroblasts.</t>
+          <t>Group C Orthobunyavirus Infection in a Patient from the Amazon Putumayo Region of Colombia During an Oropouche Fever Epidemic.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Food &amp; function</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>5.4</v>
-      </c>
+          <t>The American journal of tropical medicine and hygiene</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>metagenomics, metabolomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>未提及（研究使用 DSS 誘導的小鼠模型以及人類與小鼠的原代纖維母細胞，但未具體說明樣本數）</t>
+          <t>1位急性發熱疾病患者（單一病例）</t>
         </is>
       </c>
       <c r="G18" t="b">
@@ -1363,12 +1362,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Dietary fibre-based interventions are of growing interest for the prevention and treatment of digestive diseases. In this study, we investigated the effect of resistant starch (RS) on intestinal fibrosis, a stricturing condition driven by excessive extracellular matrix (ECM) accumulation. RS was found to alleviate intestinal fibrosis in a dextran sulfate sodium (DSS)-induced chronic colitis mouse model, as evidenced by restored colon length, reduced ECM deposition (fibronectin and collagen I), and decreased levels of α-smooth muscle actin. Given that RS is fermented by the gut microbiota in the colon, metagenomic sequencing revealed that RS reshaped the composition of the gut microbiota and increased the abundance of beneficial gut bacteria, including Bacteroides acidifaciens, Faecalibaculum rodentium, and Bifidobacterium pseudolongum, which are known to enhance the production of short-chain fatty acids. Targeted metabolomic analysis further showed a marked increase in acetate levels, which was associated with reduced intestinal fibrosis. However, direct in vivo evidence that acetate is required for the anti-fibrotic effect of RS remains lacking. Using human (CCD-18Co) and primary mouse intestinal fibroblasts, the major ECM-producing cells that drive fibrosis progression, we demonstrated that acetate inhibited TGF-β-induced fibroblast activation by inhibiting histone deacetylase 2, thereby enhancing the acetylation level of histone H3 at lysine 27. Collectively, these results suggest a potential microbial-metabolic-epigenetic axis linking RS and acetate to fibrosis attenuation, which awaits causal validation in vivo. This axis holds promise as a therapeutic target for fibrotic diseases.</t>
+          <t>Orthobunyaviruses, one of the largest and most diverse genera of viruses, include numerous reassortant viruses and present diagnostic challenges due to similar clinical presentations with other arboviral infections. The detection and isolation of a group C orthobunyavirus from a patient with acute febrile illness from Puerto Ospina, Putumayo Department, Colombia during the 2023-2024 Latin American Oropouche fever regional outbreaks are reported in the present study. Using a vertebrate virus-focused metagenomics sequencing approach with VirCapSeq-VERT, a virus related to the Caraparu complex was identified, and a virus isolate was obtained. Although limited to a single case and without serological or longitudinal clinical confirmation, these findings underscore the value of unbiased molecular approaches for unresolved febrile illness diagnosis in endemic settings such as the Amazon basin.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>本研究探討抗性澱粉（RS）對腸道纖維化的改善作用及其潛在機制。透過 DSS 誘導的小鼠結腸炎模型，研究發現 RS 可有效減輕腸道纖維化並減少細胞外基質堆積。宏基因體定序顯示 RS 能重塑腸道菌群，增加如 *Bacteroides acidifaciens* 等短鏈脂肪酸產生菌的豐度；代謝體分析進一步證實乙酸（acetate）水平顯著上升。機制研究揭示，乙酸能抑制纖維母細胞中 HDAC2 的活性，進而提升組蛋白 H3K27 的乙醯化水平，抑制 TGF-β 誘導的纖維母細胞活化。本研究提出了一條「微生物-代謝-表觀遺傳」軸線，指出 RS 可藉由促進乙酸生成來對抗腸道纖維化，為治療纖維化相關疾病提供了新的科學依據與潛在治療靶點。</t>
+          <t>本研究旨在調查2023-2024年拉丁美洲奧羅普切熱（Oropouche fever）疫情期間，哥倫比亞亞馬遜地區一名急性發熱患者的病因。研究團隊採用針對脊椎動物病毒的總體基因體學（宏基因組）定序技術（VirCapSeq-VERT），成功鑑定並分離出一種與Caraparu複合體相關的C群正布尼亞病毒（Group C Orthobunyavirus）。由於此類病毒臨床表現與其他蟲媒病毒相似，診斷極具挑戰。本研究雖僅基於單一病例，但其結果強調了在亞馬遜盆地等流行病疫區，使用無偏向性分子檢測技術對於診斷不明原因發熱疾病的重要臨床與科學價值。</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1378,27 +1377,29 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42657522/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42660108/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>42660108</t>
+          <t>42656127</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Group C Orthobunyavirus Infection in a Patient from the Amazon Putumayo Region of Colombia During an Oropouche Fever Epidemic.</t>
+          <t>Development and Validation of Mock Communities as Quality Control Materials for Clinical Metagenomic Next-Generation Sequencing.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>The American journal of tropical medicine and hygiene</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Annals of laboratory medicine</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>3.9</v>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>metagenomics</t>
@@ -1406,7 +1407,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1位急性發熱疾病患者（單一病例）</t>
+          <t>25 次重複分析（針對開發出的四種模擬群落進行評估）</t>
         </is>
       </c>
       <c r="G19" t="b">
@@ -1414,12 +1415,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Orthobunyaviruses, one of the largest and most diverse genera of viruses, include numerous reassortant viruses and present diagnostic challenges due to similar clinical presentations with other arboviral infections. The detection and isolation of a group C orthobunyavirus from a patient with acute febrile illness from Puerto Ospina, Putumayo Department, Colombia during the 2023-2024 Latin American Oropouche fever regional outbreaks are reported in the present study. Using a vertebrate virus-focused metagenomics sequencing approach with VirCapSeq-VERT, a virus related to the Caraparu complex was identified, and a virus isolate was obtained. Although limited to a single case and without serological or longitudinal clinical confirmation, these findings underscore the value of unbiased molecular approaches for unresolved febrile illness diagnosis in endemic settings such as the Amazon basin.</t>
+          <t>Metagenomic next-generation sequencing (NGS) enables comprehensive detection of a broad spectrum of microorganisms. However, its clinical application faces two major challenges: the development of appropriate microbiome-based biomarkers and the need to ensure the reproducibility and quality of the microbiome analytical workflow. Therefore, we developed four types of bead-based mock communities as standard materials for microbiome analysis and evaluated potential experimental biases arising from nucleic acid extraction and sequence analysis. Mock communities were assembled from strains isolated from clinical specimens and selected considering Gram reaction, taxonomic phylogeny, and prevalence, and processed into frozen beads. The communities were analyzed using shotgun whole-metagenome sequencing. The effect of DNA extraction kit choice was evaluated using the Thermo Fisher Scientific MagMAX Microbiome Ultra Nucleic Acid Isolation Kit and Qiagen PowerSoil Kit. Four types of mock communities comprising 26 species commonly found in the gastrointestinal tract, respiratory tract, skin, and genital tract plus cerebrospinal fluid were developed considering Gram reaction, GC content, and phylogenetic distribution. Across 25 repeated analyses, the median repeatability of each taxon was 18.97% (range, 2.87%-107.38%), while within-laboratory imprecision was 26.22% (range, 9.26%-153.83%). Repeatability remained below 10% for most dominant taxa with relative abundances &gt;20%. The choice of DNA extraction kit had a significant effect on taxonomic distributions. Microbial mock communities are essential QC materials for clinical metagenomic NGS. Further studies are needed to minimize variability and establish a standardized protocol for clinical implementation.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>本研究旨在調查2023-2024年拉丁美洲奧羅普切熱（Oropouche fever）疫情期間，哥倫比亞亞馬遜地區一名急性發熱患者的病因。研究團隊採用針對脊椎動物病毒的總體基因體學（宏基因組）定序技術（VirCapSeq-VERT），成功鑑定並分離出一種與Caraparu複合體相關的C群正布尼亞病毒（Group C Orthobunyavirus）。由於此類病毒臨床表現與其他蟲媒病毒相似，診斷極具挑戰。本研究雖僅基於單一病例，但其結果強調了在亞馬遜盆地等流行病疫區，使用無偏向性分子檢測技術對於診斷不明原因發熱疾病的重要臨床與科學價值。</t>
+          <t>本研究旨在解決臨床宏基因組次世代定序（mNGS）在品質控制與再現性上的挑戰，開發了四種基於珠粒的「模擬微生物群落」（mock communities）作為標準品。這些群落涵蓋了腸道、呼吸道、皮膚、生殖道及腦脊髓液中常見的 26 種菌株。研究透過鳥槍法全宏基因體定序（shotgun metagenomics）評估了不同 DNA 萃取試劑盒（MagMAX 與 PowerSoil）及實驗流程對結果的偏誤影響。結果顯示，微生物的檢測豐度會顯著受到萃取試劑盒選擇的干擾，且在 25 次重複實驗中，群落組成存在一定的實驗室內誤差。此研究確立了模擬群落作為臨床 mNGS 品質控制材料的重要性，對於推動微生物組檢測的標準化流程與臨床應用具有關鍵價值。</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1429,27 +1430,29 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42660108/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42656127/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>42660482</t>
+          <t>42660365</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Artificial light pollution alters epilithic microbial communities and functional biodeterioration-related functional potentials in subterranean sandstone environments.</t>
+          <t>Enhancing Cr(VI) bioreduction via Na+-stimulated intracellular energy metabolism and electron transfer using methane as electron donor.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Environmental pollution (Barking, Essex : 1987)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Bioresource technology</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>9</v>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>16S, metagenomics</t>
@@ -1465,12 +1468,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Artificial light pollution represents an important anthropogenic disturbance in subterranean heritage environments, yet its associations with epilithic microbial communities and biodeterioration processes remain poorly understood. In tourist-accessible subterranean caves, artificial illumination creates persistent illuminated areas on stone surfaces that may alter microbial community assembly and biogeochemical functions associated with biofilm development. Here, the Longyou Grottoes, a large underground sandstone cave complex in Zhejiang, China, were investigated using 16S rRNA gene sequencing and metagenomics. Bacterial communities dominated all samples (&gt;98% relative abundance). Cyanobacteriota were enriched under artificial light and sunlight (&gt;40%), whereas Pseudomonadota and Actinomycetota prevailed in darkness. Dark sites exhibited higher bacterial alpha diversity and more complex co-occurrence networks. Compared with sunlight and dark environments, the artificial-light environment was associated with greater stochasticity in bacterial community assembly, broader niche breadth, and lower niche overlap. Metabolic potential analysis further revealed light-dependent metabolic shifts: artificial light enhanced assimilatory nitrogen and sulfur metabolism, sunlight promoted nitrogen fixation, and darkness favored nitrification, denitrification, and sulfur oxidation. However, bacterial community patterns were also associated with temperature, humidity, pH, and soluble salts, indicating that the observed differentiation reflected the combined influence of light and environmental heterogeneity. These findings identify artificial lighting as an important and manageable environmental factor associated with epilithic bacterial communities and provide a basis for integrating lighting management with environmental control in the preventive conservation of subterranean sandstone heritage.</t>
+          <t>Anaerobic oxidation of methane (AOM) coupled with Cr(VI) bioreduction process offers a cost-effective pathway to simultaneously mitigate methane emissions and remediate Cr(VI) contamination. However, its practical application is limited by insufficient intracellular energy generation and low electron transfer efficiency. This study elucidated the regulatory role and mechanism of Na+, a transmembrane electrochemical gradient driver, on the metabolic activity and electron transfer of this coupled system. Batch experiments demonstrated that NaCl addition significantly improved Cr(VI) reduction efficiency, achieving complete removal in the treatment group by the end of the first cycle compared to only 79.8 % in the control. Microbial community analysis showed that Na+ enriched AOM-capable Methanobacterium and extracellular electron transfer (EET)-capable electroactive bacterium unclassified_o_DTU014, which likely formed a syntrophic consortium to mediate Cr(VI) reduction. Electrochemical measurements and 3D-EEM spectroscopy revealed that Na+ enhanced microbial aggregate electron storage capacity, reduced electron transfer resistance, and promoted extracellular polymeric substance (EPS) secretion of tyrosine-like proteins and humic acid-like substances, thereby strengthening extracellular electron transfer. Key metabolic indicators showed 26.2 % higher coenzyme F420 and 37.4 % higher intracellular ATP levels in Na+-treated groups. Metagenomic analysis confirmed that Na+ upregulated genes encoding reverse methanogenesis enzymes (Mcr, Mtr) and membrane-bound electron transfer complexes (Fpo, HdrDE), while downregulating intracellular chromate reductase (ChrR) genes, indicating that EET-mediated extracellular Cr(VI) reduction played a critical role under Na+ stimulation. This study first reveals the mechanism of Na+-promoted AOM-coupled Cr(VI) reduction via enhanced energy metabolism and electron transfer, providing a crucial theoretical basis for methane-driven Cr(VI) remediation.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>本研究探討人造光污染對地下砂岩古蹟（龍游石窟）岩表微生物群落及生物降解功能的影響。透過16S rRNA定序與總體基因體學分析，發現光照顯著改變群落結構：人工光與日光下藍菌門富集，而黑暗環境則由假單胞菌門和放線菌門主導，且黑暗處具更高的多樣性與網絡複雜度。代謝潛力分析顯示，人工光增強了同化性氮、硫代謝，而黑暗則利於硝化與硫氧化。此外，群落分化也與溫濕度及pH等環境因子相關。本研究證實人造光源是調控地下微生物的重要因子，為砂岩文物的預防性保護與照光管理提供科學依據。</t>
+          <t>本研究旨在探討跨膜電化學梯度驅動者——鈉離子（Na+），如何調控「甲烷厭氧氧化（AOM）耦合六價鉻 [Cr(VI)] 生物還原系統」的代謝活性與電子傳遞機制。研究發現，添加 NaCl 能顯著提升 Cr(VI) 的去除效率。微生物分析顯示，Na+ 富集了具 AOM 能力的 *Methanobacterium* 與具胞外電子傳遞（EET）能力的電活性細菌，形成協同共生關係。此外，Na+ 提高了微生物的胞內 ATP 與輔酶 F420 水平，並促進胞外聚合物（EPS）分泌以降低電子傳遞阻力。總體基因體學分析進一步證實，Na+ 上調了逆向產甲烷及膜結合電子傳遞複合物的關鍵基因。本研究首次審視並揭示了 Na+ 促進 AOM 耦合 Cr(VI) 還原的生物能量學機制，為利用甲烷進行重金屬生物整治提供了重要理論基礎。</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1480,28 +1483,28 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42660482/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42660365/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>42660360</t>
+          <t>42660466</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Elucidating the aromatic formation of humus via quorum sensing and redox function of thermophilic microbiota in compost.</t>
+          <t>Polystyrene nanoplastics exposure induces reproductive toxicity in male mice associated with the gut-liver/testis axis.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bioresource technology</t>
+          <t>Toxicology and applied pharmacology</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>3.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1518,12 +1521,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Quorum sensing (QS) modulates bacterial metabolism to regulate humus formation. However, the functional interaction modes of signal molecules, QS-related proteins, and microbial humification function during composting remain unclear. This study aimed to clarify the role of QS-related gene expression in regulating humification via applying metagenomics and metaproteomics. Combined addition of MnSO4 and Fe0 (CMF) significantly raised humic acid (HA) content (33.53 mg g-1) and polymerization degree (2.60) compared with other treatments. Multi-dimensional results revealed that CMF-derived HA and its products exhibited greater thermal stability, high aromaticity, and practical applicability. CMF increased the relative abundances of most QS-related and humification-related oxidoreductase genes throughout composting, especially during the thermophilic stage. Metaproteomic profiles verified that both QS expression and humification metabolism were hyperactivated during the thermophilic stage of CMF. Correlation analysis showed that QS gene expression potentially and preferentially influenced lignin-protein and polyphenol pathways during humification. Overall, CMF enriched thermophiles (Bacillota, Chloroflexota, and Myxococcota), further up-regulated the expression of major QS-related genes [K02035 (ABC.PE.S), K13075 (ahlD), K14645, K15580 (oppA), and K02055 (ABC.SP.S)], elevated levels of signal molecules, and promoted QS effects. Network analysis, qPCR, and simulated in vitro validation experiments confirmed that the response of key QS modules [K13075 (ahlD) and 3-OXO-C8-HSL] potentially facilitated interspecies communication and cooperation among bacteria, which concurrently enhanced downstream microbial metabolic behaviors (microbial redox activities and the metabolism of carbohydrates and amino acids) that aid in driving HA aromatization. This work provides new insight into the ecological roles of QS-related microbes and their precise regulation of compost humification.</t>
+          <t>Environmental nanoplastics are increasingly prevalent in global environments and represent an emerging systemic health risk, yet the mechanistic links between nanoplastic exposure and multi-organ dysfunction in mammals remain incompletely characterized. We integrated phenotypic assessments, gut shotgun metagenomics, and dual-organ transcriptomics to investigate the toxic effects of 28-day oral exposure to polystyrene nanoplastics (PS-NPs) in male CD-1 mice. PS-NPs induced a non-monotonic dose-dependent response, characterized by significant body weight loss at high doses, severe impairment of sperm motility, and progressive epididymal histopathological lesions. Gut metagenomics revealed significant microbiota dysbiosis, including an elevated Firmicutes/Bacteroidota ratio and marked depletion of beneficial commensal bacteria such as Ligilactobacillus murinus. Hepatic transcriptomics identified dysregulation of metabolic, detoxification, and circadian rhythm pathways, while testicular transcriptomics identified sustained transcriptional downregulation of genes annotated to steroid hormone biosynthesis and alterations in FoxO and apoptosis-related signaling. Spearman correlation network analysis identified associations between specific microbial shifts and organ-specific transcriptional alterations, providing a hypothesis-generating framework for the proposed gut-liver/testis axis. Together, these findings indicate that, under the present experimental conditions, oral PS-NPs exposure was associated with gut microbial dysbiosis, hepatic transcriptional perturbations, reduced sperm motility, and epididymal histopathological alterations, while the mechanistic relationships among these changes require further experimental validation.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>本研究旨在利用總體基因體學與總體蛋白質組學技術，探討群體感應（QS）相關基因表達在堆肥腐植化過程中的調節機制。研究發現，聯合添加硫酸錳與零價鐵（CMF）能顯著提高腐植酸（HA）的含量、熱穩定性與芳香度。CMF顯著富集了高溫微生物（如Bacillota、Chloroflexota和Myxococcota），並在高溫期上調關鍵QS相關基因（如ahlD）的表達與訊號分子水平。網路分析與體外實驗進一步證實，關鍵QS模組促進了菌群間的交流合作，進而增強下游的微生物氧化還原活性及碳水化合物與氨基酸代謝，共同驅動腐植酸的芳香化。本研究為QS微生物在堆肥腐植化中的生態角色與精準調控提供了全新見解。</t>
+          <t>本研究探討口服聚苯乙烯奈米塑料（PS-NPs）28天對雄性CD-1小鼠的毒性效應及其作用機制。研究發現，PS-NPs暴露會引發非單調劑量依賴性反應，導致小鼠體重顯著減輕、精子活力嚴重受損及附睾病理病變。腸道總體基因體學分析顯示，PS-NPs引起腸道菌群失調（厚壁菌門/擬桿菌門比例升高，有益菌如鼠乳桿菌顯著減少）。雙器官轉錄組學分析進一步證實，肝臟中代謝、解毒與晝夜節律途徑失調，而睾丸中類固醇激素合成基因持續下調且凋亡信號改變。本研究首次揭示了奈米塑料誘導生殖毒性與「腸-肝/睾丸軸」的關聯，為環境微塑料的哺乳動物多器官毒性機制提供了重要科學依據。</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1533,37 +1536,37 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42660360/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42660466/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>42660365</t>
+          <t>42658871</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Enhancing Cr(VI) bioreduction via Na+-stimulated intracellular energy metabolism and electron transfer using methane as electron donor.</t>
+          <t>Breastmilk microbiota and its association with infant iron deficiency anaemia: A 16S rRNA metagenomic study in Peruvian mothers cohort.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bioresource technology</t>
+          <t>PloS one</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>2.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>16S, metagenomics</t>
+          <t>16S</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>46 對母嬰（46 個母乳檢體）</t>
         </is>
       </c>
       <c r="G22" t="b">
@@ -1571,12 +1574,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Anaerobic oxidation of methane (AOM) coupled with Cr(VI) bioreduction process offers a cost-effective pathway to simultaneously mitigate methane emissions and remediate Cr(VI) contamination. However, its practical application is limited by insufficient intracellular energy generation and low electron transfer efficiency. This study elucidated the regulatory role and mechanism of Na+, a transmembrane electrochemical gradient driver, on the metabolic activity and electron transfer of this coupled system. Batch experiments demonstrated that NaCl addition significantly improved Cr(VI) reduction efficiency, achieving complete removal in the treatment group by the end of the first cycle compared to only 79.8 % in the control. Microbial community analysis showed that Na+ enriched AOM-capable Methanobacterium and extracellular electron transfer (EET)-capable electroactive bacterium unclassified_o_DTU014, which likely formed a syntrophic consortium to mediate Cr(VI) reduction. Electrochemical measurements and 3D-EEM spectroscopy revealed that Na+ enhanced microbial aggregate electron storage capacity, reduced electron transfer resistance, and promoted extracellular polymeric substance (EPS) secretion of tyrosine-like proteins and humic acid-like substances, thereby strengthening extracellular electron transfer. Key metabolic indicators showed 26.2 % higher coenzyme F420 and 37.4 % higher intracellular ATP levels in Na+-treated groups. Metagenomic analysis confirmed that Na+ upregulated genes encoding reverse methanogenesis enzymes (Mcr, Mtr) and membrane-bound electron transfer complexes (Fpo, HdrDE), while downregulating intracellular chromate reductase (ChrR) genes, indicating that EET-mediated extracellular Cr(VI) reduction played a critical role under Na+ stimulation. This study first reveals the mechanism of Na+-promoted AOM-coupled Cr(VI) reduction via enhanced energy metabolism and electron transfer, providing a crucial theoretical basis for methane-driven Cr(VI) remediation.</t>
+          <t>Anaemia is one of the most important public health challenges in developing countries. The global burden is estimated at 1.8 billion people, affecting approximately 30% of all children. Despite the implementation of multiple strategies over several decades, up to 42.5% of children under 3 years of age suffer anaemia in rural areas of Peru. We studied the microbiota of breastmilk (hBM) from mothers with children under the age of 1 and analysed its association with their iron deficiency anaemia. 46 mother-child pairs were recruited from Talara, a town on the northern coast of Peru and classified according to the clinical status of the children. Children with anaemia were also tested for ferritin level to classify them as iron deficiency anaemia (IDA) or non-iron deficiency anaemia (non-IDA). hBM samples were taken from the mothers after careful instruction to reduce the risk of sample contamination and the microbiome was analyzed using 16S rRNA sequencing. Streptococcus and Staphylococcus were the predominant genera, with 90% of bacterial abundance being explained by 14 genera. Alpha diversity analysis showed that hBM from mothers of children with non-IDA had higher levels of bacterial richness than hBM from healthy (p &lt; 0.01) and IDA (p &lt; 0.05) participants. Principal coordinates analysis did not yield differential clusters but showed a disparity in the spread of samples for non-IDA group when compared with the other groups. IDA group showed higher burden of Corynebacterium, Acinetobacter, Paludibacter and Nitrospira, while exhibiting a trend towards a lower burden of Streptococcus. No statistically significant differences were identified on demographic characteristics. This study suggests that hBM microbiota may differ in mothers of children with IDA and non-IDA, highlighting the necessity of further in-depth research to elucidate potential factors associated with its pathogenesis.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>本研究旨在探討跨膜電化學梯度驅動者——鈉離子（Na+），如何調控「甲烷厭氧氧化（AOM）耦合六價鉻 [Cr(VI)] 生物還原系統」的代謝活性與電子傳遞機制。研究發現，添加 NaCl 能顯著提升 Cr(VI) 的去除效率。微生物分析顯示，Na+ 富集了具 AOM 能力的 *Methanobacterium* 與具胞外電子傳遞（EET）能力的電活性細菌，形成協同共生關係。此外，Na+ 提高了微生物的胞內 ATP 與輔酶 F420 水平，並促進胞外聚合物（EPS）分泌以降低電子傳遞阻力。總體基因體學分析進一步證實，Na+ 上調了逆向產甲烷及膜結合電子傳遞複合物的關鍵基因。本研究首次審視並揭示了 Na+ 促進 AOM 耦合 Cr(VI) 還原的生物能量學機制，為利用甲烷進行重金屬生物整治提供了重要理論基礎。</t>
+          <t>本研究探討祕魯農村地區嬰兒缺鐵性貧血（IDA）與母親母乳（hBM）菌相之間的關聯。研究對象為 46 對母嬰，透過 16S rRNA 定序分析母乳微生物群落，發現母乳菌相以鏈球菌屬（Streptococcus）與葡萄球菌屬（Staphylococcus）為優勢菌群。研究結果顯示，非貧血組嬰兒的母親，其母乳具備較高的細菌豐富度。此外，IDA 組嬰兒母親的母乳中，棒狀桿菌屬（Corynebacterium）與不動桿菌屬（Acinetobacter）等細菌豐度較高，而鏈球菌屬則呈現下降趨勢。此研究發現母乳微生物群組成可能與嬰兒貧血狀態相關，雖無法直接證實因果關係，但為後續探討嬰兒貧血的致病機制提供了重要的微生物學線索。</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1586,37 +1589,35 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42660365/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42658871/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>42660466</t>
+          <t>42658844</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Polystyrene nanoplastics exposure induces reproductive toxicity in male mice associated with the gut-liver/testis axis.</t>
+          <t>Enrichment and Characterization of a Haloalkaline-tolerant Anammox Bacterium.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Toxicology and applied pharmacology</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>3.4</v>
-      </c>
+          <t>The ISME journal</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>metagenomics, others</t>
+          <t>metagenomics, small genome, others (transcriptional profiling)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（研究基於特定實驗室富集培養物之實驗與分析）</t>
         </is>
       </c>
       <c r="G23" t="b">
@@ -1624,12 +1625,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Environmental nanoplastics are increasingly prevalent in global environments and represent an emerging systemic health risk, yet the mechanistic links between nanoplastic exposure and multi-organ dysfunction in mammals remain incompletely characterized. We integrated phenotypic assessments, gut shotgun metagenomics, and dual-organ transcriptomics to investigate the toxic effects of 28-day oral exposure to polystyrene nanoplastics (PS-NPs) in male CD-1 mice. PS-NPs induced a non-monotonic dose-dependent response, characterized by significant body weight loss at high doses, severe impairment of sperm motility, and progressive epididymal histopathological lesions. Gut metagenomics revealed significant microbiota dysbiosis, including an elevated Firmicutes/Bacteroidota ratio and marked depletion of beneficial commensal bacteria such as Ligilactobacillus murinus. Hepatic transcriptomics identified dysregulation of metabolic, detoxification, and circadian rhythm pathways, while testicular transcriptomics identified sustained transcriptional downregulation of genes annotated to steroid hormone biosynthesis and alterations in FoxO and apoptosis-related signaling. Spearman correlation network analysis identified associations between specific microbial shifts and organ-specific transcriptional alterations, providing a hypothesis-generating framework for the proposed gut-liver/testis axis. Together, these findings indicate that, under the present experimental conditions, oral PS-NPs exposure was associated with gut microbial dysbiosis, hepatic transcriptional perturbations, reduced sperm motility, and epididymal histopathological alterations, while the mechanistic relationships among these changes require further experimental validation.</t>
+          <t>Metagenomic surveys have substantially expanded the known diversity of anaerobic ammonium-oxidizing (anammox) bacteria. However, the physiological traits of newly proposed anammox genera remain largely hypothetical due to the lack of cultured representatives. Although niche differentiation driven by salinity, organic substrates, and oxygen is well documented in anammox bacteria, adaptations to alkaline environments remain uncharacterized. Moreover, no anammox lineage has been identified as an alkaline specialist. Herein, we report the enrichment (&gt;80% relative abundance) of an anammox bacterium, provisionally named Candidatus Loosdrechtia alkalitolerans, which represents the cultured member of the genus Ca. Loosdrechtia. Ca. L. alkalitolerans exhibits marked haloalkaline tolerance, outcompeting other freshwater anammox genera under long-term saline-alkaline stress conditions (0.5% NaCl; pH~9.13). Comparative genomics revealed that among freshwater anammox lineages, only Ca. L. alkalitolerans encodes a complete multiple resistance and pH adaptation (Mrp) cation/proton antiporter operon. Batch assays with transcriptional profiling demonstrated that sodium addition upregulated mrp expression and recovered anammox activity under alkaline stress, suggesting that Mrp-mediated cation/proton exchange may contribute to pH homeostasis in Ca. L. alkalitolerans. Furthermore, database mining revealed that the habitat of Ca. L. alkalitolerans is not restricted to haloalkaline environments, but extends to diverse freshwater and wastewater ecosystems. These findings provide mechanistic insight into saline-alkaline tolerance in anammox bacteria, expanding understanding of their physiological plasticity and ecological roles.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>本研究探討口服聚苯乙烯奈米塑料（PS-NPs）28天對雄性CD-1小鼠的毒性效應及其作用機制。研究發現，PS-NPs暴露會引發非單調劑量依賴性反應，導致小鼠體重顯著減輕、精子活力嚴重受損及附睾病理病變。腸道總體基因體學分析顯示，PS-NPs引起腸道菌群失調（厚壁菌門/擬桿菌門比例升高，有益菌如鼠乳桿菌顯著減少）。雙器官轉錄組學分析進一步證實，肝臟中代謝、解毒與晝夜節律途徑失調，而睾丸中類固醇激素合成基因持續下調且凋亡信號改變。本研究首次揭示了奈米塑料誘導生殖毒性與「腸-肝/睾丸軸」的關聯，為環境微塑料的哺乳動物多器官毒性機制提供了重要科學依據。</t>
+          <t>本研究成功富集並鑑定出一種耐鹽鹼的厭氧氨氧化（Anammox）細菌，命名為 *Candidatus Loosdrechtia alkalitolerans*。該菌株在長期高鹽、高鹼（0.5% NaCl，pH 9.13）環境下表現出強大的競爭優勢。透過基因體比較分析，研究發現該菌株含有特殊的 Mrp 陽離子/質子反向轉運蛋白操縱子，這是其適應鹼性環境的關鍵機制；轉錄組分析進一步證實，在鹼性壓力下，補充鈉離子可上調 Mrp 表現並恢復其代謝活性。此發現不僅揭示了厭氧氨氧化菌應對鹽鹼逆境的生理分子機制，證明了該菌在廣泛的淡水與廢水生態系統中具有潛在的生態地位，更為未來工業廢水處理中的脫氮技術應用提供了理論基礎與科學見解。</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1639,37 +1640,37 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42660466/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42658844/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>42658871</t>
+          <t>42660360</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Breastmilk microbiota and its association with infant iron deficiency anaemia: A 16S rRNA metagenomic study in Peruvian mothers cohort.</t>
+          <t>Elucidating the aromatic formation of humus via quorum sensing and redox function of thermophilic microbiota in compost.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PloS one</t>
+          <t>Bioresource technology</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2.6</v>
+        <v>9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>16S</t>
+          <t>metagenomics, others</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>46 對母嬰（46 個母乳檢體）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G24" t="b">
@@ -1677,12 +1678,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Anaemia is one of the most important public health challenges in developing countries. The global burden is estimated at 1.8 billion people, affecting approximately 30% of all children. Despite the implementation of multiple strategies over several decades, up to 42.5% of children under 3 years of age suffer anaemia in rural areas of Peru. We studied the microbiota of breastmilk (hBM) from mothers with children under the age of 1 and analysed its association with their iron deficiency anaemia. 46 mother-child pairs were recruited from Talara, a town on the northern coast of Peru and classified according to the clinical status of the children. Children with anaemia were also tested for ferritin level to classify them as iron deficiency anaemia (IDA) or non-iron deficiency anaemia (non-IDA). hBM samples were taken from the mothers after careful instruction to reduce the risk of sample contamination and the microbiome was analyzed using 16S rRNA sequencing. Streptococcus and Staphylococcus were the predominant genera, with 90% of bacterial abundance being explained by 14 genera. Alpha diversity analysis showed that hBM from mothers of children with non-IDA had higher levels of bacterial richness than hBM from healthy (p &lt; 0.01) and IDA (p &lt; 0.05) participants. Principal coordinates analysis did not yield differential clusters but showed a disparity in the spread of samples for non-IDA group when compared with the other groups. IDA group showed higher burden of Corynebacterium, Acinetobacter, Paludibacter and Nitrospira, while exhibiting a trend towards a lower burden of Streptococcus. No statistically significant differences were identified on demographic characteristics. This study suggests that hBM microbiota may differ in mothers of children with IDA and non-IDA, highlighting the necessity of further in-depth research to elucidate potential factors associated with its pathogenesis.</t>
+          <t>Quorum sensing (QS) modulates bacterial metabolism to regulate humus formation. However, the functional interaction modes of signal molecules, QS-related proteins, and microbial humification function during composting remain unclear. This study aimed to clarify the role of QS-related gene expression in regulating humification via applying metagenomics and metaproteomics. Combined addition of MnSO4 and Fe0 (CMF) significantly raised humic acid (HA) content (33.53 mg g-1) and polymerization degree (2.60) compared with other treatments. Multi-dimensional results revealed that CMF-derived HA and its products exhibited greater thermal stability, high aromaticity, and practical applicability. CMF increased the relative abundances of most QS-related and humification-related oxidoreductase genes throughout composting, especially during the thermophilic stage. Metaproteomic profiles verified that both QS expression and humification metabolism were hyperactivated during the thermophilic stage of CMF. Correlation analysis showed that QS gene expression potentially and preferentially influenced lignin-protein and polyphenol pathways during humification. Overall, CMF enriched thermophiles (Bacillota, Chloroflexota, and Myxococcota), further up-regulated the expression of major QS-related genes [K02035 (ABC.PE.S), K13075 (ahlD), K14645, K15580 (oppA), and K02055 (ABC.SP.S)], elevated levels of signal molecules, and promoted QS effects. Network analysis, qPCR, and simulated in vitro validation experiments confirmed that the response of key QS modules [K13075 (ahlD) and 3-OXO-C8-HSL] potentially facilitated interspecies communication and cooperation among bacteria, which concurrently enhanced downstream microbial metabolic behaviors (microbial redox activities and the metabolism of carbohydrates and amino acids) that aid in driving HA aromatization. This work provides new insight into the ecological roles of QS-related microbes and their precise regulation of compost humification.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>本研究探討祕魯農村地區嬰兒缺鐵性貧血（IDA）與母親母乳（hBM）菌相之間的關聯。研究對象為 46 對母嬰，透過 16S rRNA 定序分析母乳微生物群落，發現母乳菌相以鏈球菌屬（Streptococcus）與葡萄球菌屬（Staphylococcus）為優勢菌群。研究結果顯示，非貧血組嬰兒的母親，其母乳具備較高的細菌豐富度。此外，IDA 組嬰兒母親的母乳中，棒狀桿菌屬（Corynebacterium）與不動桿菌屬（Acinetobacter）等細菌豐度較高，而鏈球菌屬則呈現下降趨勢。此研究發現母乳微生物群組成可能與嬰兒貧血狀態相關，雖無法直接證實因果關係，但為後續探討嬰兒貧血的致病機制提供了重要的微生物學線索。</t>
+          <t>本研究旨在利用總體基因體學與總體蛋白質組學技術，探討群體感應（QS）相關基因表達在堆肥腐植化過程中的調節機制。研究發現，聯合添加硫酸錳與零價鐵（CMF）能顯著提高腐植酸（HA）的含量、熱穩定性與芳香度。CMF顯著富集了高溫微生物（如Bacillota、Chloroflexota和Myxococcota），並在高溫期上調關鍵QS相關基因（如ahlD）的表達與訊號分子水平。網路分析與體外實驗進一步證實，關鍵QS模組促進了菌群間的交流合作，進而增強下游的微生物氧化還原活性及碳水化合物與氨基酸代謝，共同驅動腐植酸的芳香化。本研究為QS微生物在堆肥腐植化中的生態角色與精準調控提供了全新見解。</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1692,35 +1693,35 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42658871/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42660360/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>42658844</t>
+          <t>42660482</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Enrichment and Characterization of a Haloalkaline-tolerant Anammox Bacterium.</t>
+          <t>Artificial light pollution alters epilithic microbial communities and functional biodeterioration-related functional potentials in subterranean sandstone environments.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>The ISME journal</t>
+          <t>Environmental pollution (Barking, Essex : 1987)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>metagenomics, small genome, others (transcriptional profiling)</t>
+          <t>16S, metagenomics</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>未提及（研究基於特定實驗室富集培養物之實驗與分析）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G25" t="b">
@@ -1728,12 +1729,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Metagenomic surveys have substantially expanded the known diversity of anaerobic ammonium-oxidizing (anammox) bacteria. However, the physiological traits of newly proposed anammox genera remain largely hypothetical due to the lack of cultured representatives. Although niche differentiation driven by salinity, organic substrates, and oxygen is well documented in anammox bacteria, adaptations to alkaline environments remain uncharacterized. Moreover, no anammox lineage has been identified as an alkaline specialist. Herein, we report the enrichment (&gt;80% relative abundance) of an anammox bacterium, provisionally named Candidatus Loosdrechtia alkalitolerans, which represents the cultured member of the genus Ca. Loosdrechtia. Ca. L. alkalitolerans exhibits marked haloalkaline tolerance, outcompeting other freshwater anammox genera under long-term saline-alkaline stress conditions (0.5% NaCl; pH~9.13). Comparative genomics revealed that among freshwater anammox lineages, only Ca. L. alkalitolerans encodes a complete multiple resistance and pH adaptation (Mrp) cation/proton antiporter operon. Batch assays with transcriptional profiling demonstrated that sodium addition upregulated mrp expression and recovered anammox activity under alkaline stress, suggesting that Mrp-mediated cation/proton exchange may contribute to pH homeostasis in Ca. L. alkalitolerans. Furthermore, database mining revealed that the habitat of Ca. L. alkalitolerans is not restricted to haloalkaline environments, but extends to diverse freshwater and wastewater ecosystems. These findings provide mechanistic insight into saline-alkaline tolerance in anammox bacteria, expanding understanding of their physiological plasticity and ecological roles.</t>
+          <t>Artificial light pollution represents an important anthropogenic disturbance in subterranean heritage environments, yet its associations with epilithic microbial communities and biodeterioration processes remain poorly understood. In tourist-accessible subterranean caves, artificial illumination creates persistent illuminated areas on stone surfaces that may alter microbial community assembly and biogeochemical functions associated with biofilm development. Here, the Longyou Grottoes, a large underground sandstone cave complex in Zhejiang, China, were investigated using 16S rRNA gene sequencing and metagenomics. Bacterial communities dominated all samples (&gt;98% relative abundance). Cyanobacteriota were enriched under artificial light and sunlight (&gt;40%), whereas Pseudomonadota and Actinomycetota prevailed in darkness. Dark sites exhibited higher bacterial alpha diversity and more complex co-occurrence networks. Compared with sunlight and dark environments, the artificial-light environment was associated with greater stochasticity in bacterial community assembly, broader niche breadth, and lower niche overlap. Metabolic potential analysis further revealed light-dependent metabolic shifts: artificial light enhanced assimilatory nitrogen and sulfur metabolism, sunlight promoted nitrogen fixation, and darkness favored nitrification, denitrification, and sulfur oxidation. However, bacterial community patterns were also associated with temperature, humidity, pH, and soluble salts, indicating that the observed differentiation reflected the combined influence of light and environmental heterogeneity. These findings identify artificial lighting as an important and manageable environmental factor associated with epilithic bacterial communities and provide a basis for integrating lighting management with environmental control in the preventive conservation of subterranean sandstone heritage.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>本研究成功富集並鑑定出一種耐鹽鹼的厭氧氨氧化（Anammox）細菌，命名為 *Candidatus Loosdrechtia alkalitolerans*。該菌株在長期高鹽、高鹼（0.5% NaCl，pH 9.13）環境下表現出強大的競爭優勢。透過基因體比較分析，研究發現該菌株含有特殊的 Mrp 陽離子/質子反向轉運蛋白操縱子，這是其適應鹼性環境的關鍵機制；轉錄組分析進一步證實，在鹼性壓力下，補充鈉離子可上調 Mrp 表現並恢復其代謝活性。此發現不僅揭示了厭氧氨氧化菌應對鹽鹼逆境的生理分子機制，證明了該菌在廣泛的淡水與廢水生態系統中具有潛在的生態地位，更為未來工業廢水處理中的脫氮技術應用提供了理論基礎與科學見解。</t>
+          <t>本研究探討人造光污染對地下砂岩古蹟（龍游石窟）岩表微生物群落及生物降解功能的影響。透過16S rRNA定序與總體基因體學分析，發現光照顯著改變群落結構：人工光與日光下藍菌門富集，而黑暗環境則由假單胞菌門和放線菌門主導，且黑暗處具更高的多樣性與網絡複雜度。代謝潛力分析顯示，人工光增強了同化性氮、硫代謝，而黑暗則利於硝化與硫氧化。此外，群落分化也與溫濕度及pH等環境因子相關。本研究證實人造光源是調控地下微生物的重要因子，為砂岩文物的預防性保護與照光管理提供科學依據。</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1743,35 +1744,37 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42658844/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42660482/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>42644751</t>
+          <t>42649294</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Soil amelioration impacts viral ecology in saline-alkali lands.</t>
+          <t>Synergistic degradation of fucoidans in the ocean.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>The ISME journal</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>48.5</v>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>metabolomics, metagenomics</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>未提及（僅說明樣品來自中國4個主要鹽鹼地區，各包含「鹽鹼」與「改良後」兩種狀態之土壤）</t>
+          <t>未提及（該研究採用重組海洋微生物群落進行實驗，未提供具體的生物樣本人數或檢體數量）</t>
         </is>
       </c>
       <c r="G26" t="b">
@@ -1779,12 +1782,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>The continuous expansion of saline-alkali lands under climate change threatens food security and reduces soil carbon stocks. A common mitigation strategy is soil amelioration, which converts degraded soils back into an arable state. Microbes play critical roles in soil health and recovery. However, the viruses that infect these microbial communities, and their potential impacts during saline-alkali soil restoration, remain largely unknown. Here, we combined total soil metagenomics and viromics to investigate host-linked viral ecology across four major saline-alkali regions in China, each encompassing two soil amelioration statuses: saline-alkali and reclaimed. We found that viral community structure was shaped by both geography and soil amelioration status, with salinity and alkalinity emerging as key environmental factors. Viral populations were sensitive to soil restoration, showing strong amelioration-status endemism with functional adaptations. Virus-host dynamics ranged from reduced temperate viruses to abundance mismatches in those infecting key carbon-cycling microorganisms, including carbohydrate degraders. 13C-cellulose DNA-SIP experiments provided further support for this mismatch by tracing assimilated carbon transfer between active host and virus populations. Compared with saline-alkali soils, the relative abundance of hosts in restored soils increased from 39.0% to 61.0%, whereas the linked viruses decreased from 60.6% to 39.4%. Together, these findings reveal an underappreciated role of viruses in shaping saline-alkali soil amelioration trajectories, and could improve management strategies for degraded land recovery and carbon storage.</t>
+          <t>Fucoidans, a class of complex polysaccharides produced by brown algae and diatoms, contribute to long-term carbon sequestration owing to their resistance to microbial degradation1,2. Although individual microorganisms can break down portions of these polysaccharides3-5, it remains unclear whether complete breakdown is possible in nature and, if so, by what mechanisms. Here we show that fucoidans are degraded through synergistic interactions between specialized bacteria with complementary metabolic functions. Using metabolomic analysis of a reconstructed marine consortium, we uncovered metabolic guilds of bacteria that preferentially degrade either the sulfated fucose backbone or the side branches of rare monomers. This functional division of labour leads to an unexpectedly high number of synergistic interactions between different degraders that enhanced degradation efficiency up to 97.1%. Despite varying fucoidan structures across different types of algae6, the metabolic functions of degraders remained conserved, enabling quantitative prediction of degradation outcomes based on community and substrate composition. The frequent co-occurrence of functionally complementary fucoidan degraders in ocean metagenomes suggests that synergistic degradation is a globally relevant strategy. Our findings suggest that the environmental turnover of complex biopolymers depends not only on individual metabolic capabilities of degraders but also on ecological interactions shaped by substrate architecture. This work provides a mechanistic framework for understanding carbon cycling in the ocean and for engineering synthetic microbial consortia to degrade recalcitrant polysaccharides.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>本研究旨在探討鹽鹼地改良過程中，病毒對土壤微生物生態與碳循環的影響。研究結合總體基因體與病毒體學，分析中國四大鹽鹼區。結果顯示，土壤改良狀態、鹽度與鹼度是塑造病毒社群的關鍵。在改良土壤中，宿主微生物相對豐度顯著上升（39.0%至61.0%），而關聯病毒減少（60.6%至39.4%），且溫和病毒比例降低，碳循環關鍵微生物的病毒與宿主出現豐度失衡。13C-纖維素DNA-SIP實驗證實了兩者間的活性碳轉移。此發現揭示了病毒在鹽鹼地恢復中的關鍵作用，有助優化土地改良與碳儲存策略。</t>
+          <t>本研究探討海洋中複雜多醣體「褐藻醣膠」（fucoidans）的微生物降解機制。儘管褐藻醣膠因其抗降解性在碳封存中扮演關鍵角色，但過往對於其在自然界中是否能被完全分解並不清楚。研究發現，褐藻醣膠的降解並非單一物種所能完成，而是透過具有互補代謝功能的細菌群落進行「協同作用」。透過代謝體學分析，研究團隊識別出專門降解硫酸岩藻糖骨架與稀有單醣側鏈的代謝群組（metabolic guilds），這種分工合作能將降解效率大幅提升至 97.1%。此外，研究顯示此代謝功能在不同環境下具有高度保守性，且在海洋宏基因組中普遍存在。本研究揭示了生物聚合物的環境周轉率取決於微生物間的生態交互作用，為理解海洋碳循環機制提供了重要框架，並為未來利用人工合成微生物群落降解頑固性多醣體提供了技術基礎。</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1794,37 +1797,35 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42644751/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42649294/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>42648293</t>
+          <t>42657129</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Defined human Clostridia consortia reverse colitis via dual effects of tryptophan metabolites on microbiota and immunity.</t>
+          <t>Pulmonary Infiltrates, Airway Mucosal Lesions and Respiratory Microbiology After Freshwater Drowning: A Case Report.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cell host &amp; microbe</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>18.7</v>
-      </c>
+          <t>Respirology case reports</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>metagenomics, metabolomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>1 例病患（n=1）</t>
         </is>
       </c>
       <c r="G27" t="b">
@@ -1832,12 +1833,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Microbial dysbiosis and disrupted mucosal immune homeostasis are integrally involved in the pathogenesis of inflammatory bowel diseases (IBDs). Live biotherapeutic products (LBPs) offer a potential therapeutic strategy to restore beneficial microbes and mitigate disease. We investigated the therapeutic efficacy of 2 LBPs, human Clostridia consortia 17-mix and 11-mix, by treating established colitis in murine models. Both LBPs exhibited therapeutic effects in T cell-mediated chronic colitis models induced by human microbiota and in pathobiont-driven gnotobiotic colitis models established with combinations of IBD-relevant human-derived strains. Metagenomic and metabolomic analyses elucidated mechanisms that go beyond established functions driven by short-chain fatty acids (SCFAs) and interleukin (IL)-10-producing regulatory T cells. Notably, LBPs exerted therapeutic effects by directly inhibiting resident pathobionts and through IL-10-independent activation of host anti-inflammatory aryl hydrocarbon receptor (AhR) pathways by bacterial tryptophan metabolites. These results elucidate SCFA- and IL-10-independent protective mechanisms exerted by defined resident bacterial strains that are depleted in IBD dysbiosis.</t>
+          <t>Early pulmonary abnormalities after freshwater drowning can be overinterpreted as bacterial pneumonia, especially when inflammatory biomarkers and respiratory microbiology are positive. A 20-year-old man was resuscitated after approximately 2 min of freshwater submersion. Day 1 chest CT showed bilateral lower-lobe-predominant opacities compatible with non-cardiogenic pulmonary oedema and aspiration-related lung injury, with near-complete resolution by Day 25. Day 3 bronchoscopy showed diffuse, non-removable, millet-seed-like whitish tracheal mucosal protrusions with hyperaemia and oedema, compatible with acute irritative airway injury. BALF mNGS detected multiple gram-negative bacterial signals, predominantly Klebsiella pneumoniae, while sputum culture yielded ESBL-negative, susceptible K. pneumoniae. Possible drowning-associated pneumonia was considered because of aspiration, fever, markedly elevated inflammatory biomarkers and concordant microbiology; however, rapid radiological improvement and clinical stability suggested a substantial non-infectious component. The patient recovered after an 8-day course of piperacillin-tazobactam without antibiotic escalation, corticosteroids, mechanical ventilation or acute respiratory distress syndrome.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>本研究探討了兩種由人類梭狀芽孢桿菌組成的活體生物藥物（LBP，分別為 17-mix 和 11-mix）治療小鼠結腸炎的療效與機制。研究發現，這些菌群能有效緩解小鼠的慢性與特定病原體誘導的結腸炎。宏基因組學與代謝組學分析顯示，除了傳統的短鏈脂肪酸（SCFA）和 IL-10 途徑外，LBP 還能直接抑制共生病原菌，並透過細菌色胺酸代謝物，以不依賴 IL-10 的方式激活宿主的芳香烴受體（AhR）抗炎途徑。此發現揭示了腸道有益菌保護腸道的新機制，為發炎性腸道疾病（IBD）的微生態療法提供了重要科學依據。</t>
+          <t>本研究透過單一病例報告，探討淡水溺水後肺部浸潤與呼吸道損傷的臨床鑑別診斷。一名 20 歲男性溺水後出現肺水腫與氣道黏膜病變，臨床表現極易與細菌性肺炎混淆。研究利用 mNGS（宏基因組次世代定序）檢測支氣管肺泡灌洗液，雖確認存在肺炎克雷伯菌（*Klebsiella pneumoniae*）訊號，但影像學與臨床病程顯示其肺部損傷主要源於吸入性損傷及急性化學性氣道刺激，而非嚴重的細菌感染。此案例凸顯了臨床判斷溺水相關肺炎時的挑戰，強調在面對看似感染的臨床數據時，應綜合考量影像改善速度與臨床穩定性，避免過度診斷與不必要的抗生素升級，對急性溺水病患的精準治療具有重要的臨床參考價值。</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1847,37 +1848,35 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42648293/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42657129/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>42647084</t>
+          <t>42644746</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Diet quality, gut microbiome, and inflammatory signatures in Puerto Rican adults with Crohn disease: a multidimensional analysis.</t>
+          <t>Metabolic division of labour drives estuarine-coastal N2O emissions.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Inflammatory bowel diseases</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>4.3</v>
-      </c>
+          <t>The ISME journal</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>metagenomics, metatranscriptomics</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60位患有克隆氏症的成年人 (60 adults with CD)</t>
+          <t>974 個重建的 N2O 相關基因體（原文未提及具體的環境樣本採集數量）</t>
         </is>
       </c>
       <c r="G28" t="b">
@@ -1885,12 +1884,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Diet is increasingly recognized as a modifiable factor influencing gut microbiome and outcomes in Crohn disease (CD), yet data in underrepresented populations remain limited. We evaluated diet quality, dietary patterns, gut microbiome composition, inflammatory markers, and patient-reported outcomes in adults with CD from Puerto Rico. We conducted a cross-sectional analysis of 60 adults with CD enrolled prior to dietary intervention in a parent study. Dietary intake was assessed using 24-hour recalls and evaluated using the Healthy Eating Index-2015 (HEI-2015), Alternative Healthy Eating Index-2010 (AHEI-2010), and exploratory dietary pattern analysis. The gut microbiome was assessed by shotgun metagenomic sequencing. Clinical outcomes included fecal calprotectin, C-reactive protein (CRP), a 96-cytokine panel, short Crohn Disease Activity Index (sCDAI), and short Inflammatory Bowel Disease Questionnaire (sIBDQ). Associations were evaluated using unadjusted and adjusted models with false discovery rate (FDR) correction. Overall diet quality was poor and characterized by low intake of fruits, vegetables, whole grains, and fiber, alongside high intake of saturated fat, added sugars, and animal-derived protein. Four dietary patterns were identified: vegetable-rich, dairy-rich, fruit-rich, and coffee/sweetener-rich. Participants adhering to the fruit-rich pattern exhibited the highest diet quality scores. Higher HEI-2015 scores were associated with greater gut microbial diversity and differences in overall microbiome composition. Participants with greater adherence to the vegetable-rich pattern showed modest increases in microbial diversity. Exploratory analyses suggested that higher fruit intake and adherence to a fruit-rich dietary pattern were associated with lower fecal calprotectin and CRP levels, whereas adherence to a vegetable-rich pattern was associated with better health-related quality of life (HRQoL) and adherence to a coffee/sweetener-rich pattern was associated with a worse symptom burden. However, no associations between dietary metrics and inflammatory markers, cytokines, or clinical outcomes remained significant after FDR correction. Most participants were in clinical remission despite substantial impairment in HRQoL. Adults with CD in Puerto Rico exhibited poor diet quality that was associated with gut microbial diversity and exploratory differences in clinical outcomes. While these findings support the influence of diet on the microbiome and clinical outcomes, larger longitudinal studies are needed to determine whether dietary improvements can influence disease outcomes this underrepresented population.</t>
+          <t>Estuarine and coastal systems are global hotspots of marine nitrous oxide (N2O) emissions, where microbial nitrification and denitrification are the primary processes regulating N2O dynamics. However, how interactions among different N2O-associated microorganisms influence ecosystem-scale N2O emissions remains poorly understood. This study combined in situ N2O concentrations, 15N-based potential rates, metagenomics, metatranscriptomics, and genome-scale metabolic model analysis to explore N2O production and reduction processes in estuarine and coastal systems. Potential N2O production and reduction rates, together with in situ concentrations, the relative abundance, and the transcriptional activity of associated genes, were significantly higher at low salinity and declined toward coastal regions. Based on the gene content of 974 recovered N2O-associated genomes, microorganisms were classified into three functional groups: net N2O producers, net N2O consumers, and self-sustaining N2O players. The abundance, composition, and activity of these functional groups shifted along estuarine-coastal gradients. A larger NO/N2O exchange gap, reflecting the imbalance between model-inferred NO and N2O handoff potentials, was found at low salinity and was associated with elevated bottom-water N2O concentrations. Together, community-level division of labour and the associated exchange gap provide a conceptual framework for linking N2O-related functional groups to N2O accumulation in estuarine-coastal ecosystems.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>本研究探討波多黎各克隆氏症（CD）成年患者的飲食品質、腸道菌相與發炎指標的關係。研究發現，受試者普遍飲食品質不佳，而較高的飲食品質（特別是富含水果的飲食模式）與較高的腸道菌群多樣性顯著相關。探索性分析顯示，多攝取水果與較低的發炎指標（鈣衛蛋白和C反應蛋白）相關，而蔬菜為主的飲食與較佳的生活品質相關（但經FDR校正後未達顯著）。本研究首次揭示了該少數受關注族群中飲食對菌相與臨床症狀的影響，為未來透過飲食干預管理CD及改善患者預後提供了科學依據。</t>
+          <t>本研究旨在探討河口與沿海系統中，微生物交互作用如何驅動一氧化二氮（N2O）的排放。研究結合現場觀測、15N同位素速率、總體基因體與轉錄體學，重建了974個N2O相關基因體。結果指出，低鹽度區域的N2O產生與還原速率及基因表達顯著較高。研究將微生物劃分為淨產生者、淨消費者與自給自足者，並發現低鹽度區因群落間物質交換失衡，存在較大的NO/N2O交換缺口，進而導致底層水體N2O顯著累積。本研究建立了群落水平的「分工與交換缺口」理論框架，為預測及理解海洋生態系統N2O排放提供了關鍵的科學依據。</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1900,28 +1899,28 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42647084/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42644746/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>42647600</t>
+          <t>42647164</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Urogenital immune signatures are associated with birth outcomes after maternal urinary tract infection.</t>
+          <t>Sex differences in the gut microbiome and related metabolites: role in cardiometabolic disease.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Science translational medicine</t>
+          <t>Gut microbes</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>11</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1930,7 +1929,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（本文為綜論性回顧文章，非原創實驗研究）</t>
         </is>
       </c>
       <c r="G29" t="b">
@@ -1938,12 +1937,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Preterm birth is the leading cause of infant mortality, resulting in more than 1 million neonatal deaths globally each year. Maternal urinary tract infection (UTI) during pregnancy increases risk for preterm birth; however, biological processes mediating UTI-associated preterm birth are not well described. We established a murine maternal UTI model in which challenge with uropathogenic Escherichia coli (UPEC) initiated preterm labor and birth in about half of dams. Although bacterial burdens were similar, dams experiencing preterm birth displayed excessive bladder inflammation, elevated placental and decidual cytokines, higher proportions of male fetuses, and lower maternal serum interleukin-10 (IL-10) compared with nonlaboring dams. Exogenous IL-10 or lymph node sequestration of T cells reduced placental type 17 T helper cells (TH17 cells) and abrogated preterm birth. In a human pregnancy cohort, we correlated urinary cytokines with birth outcomes and urine culture status. These analyses yielded an exploratory, noninvasive culture-agnostic system for evaluating preterm birth risk, implicating T cell-related cytokines including IL-10, IL-15, GM-CSF, and RANTES. These findings demonstrate that our murine model provides a platform to investigate immunological and microbial factors governing UTI-associated preterm birth and, coupled with patient samples, may be used to identify candidate biomarkers and mechanistic targets for future investigation.</t>
+          <t>Sex differences in major cardiometabolic diseases (CMD), such as type 2 diabetes, metabolic dysfunction-associated steatotic liver disease, and cardiovascular disease, have been increasingly recognized across the life course. During the reproductive stage, women generally have a more favorable cardiometabolic risk profile than men, but their risk of experiencing CMD significantly increases after menopause. Emerging evidence suggests that sexually dimorphic gut microbiota and gut microbiota-related metabolites (GMRMs) may contribute to such sex disparities. However, existing findings are heterogeneous and underlying mechanisms remain incompletely understood. In this review, we synthesize the evidence examining sex differences in gut microbial diversity, overall composition, taxa abundances, and levels of GMRMs across key life stages, including pre-puberty, adolescence, and different phases of adulthood (with emphasis on pre- and post-menopausal periods). We summarize potential biological mechanisms underlying sexual dimorphism in the gut microbiome and GMRMs, emphasizing the central role of sex steroids, along with contributions from immune function and other host and environmental factors. We further integrate evidence linking sexually dimorphic microbial taxa (e.g., Akkermansia muciniphila, Eubacterium, Ruminococcus, and other Firmicutes taxa) and GMRMs (e.g., microbiota-derived short-chain fatty acids, secondary bile acids, and trimethylamine N-oxide) to key cardiometabolic pathways involving inflammation, glucose and lipid metabolism, and vascular function. Finally, we identify critical knowledge gaps and emphasize the need for future large longitudinal studies that would integrate repeated measurements of the gut microbiome, untargeted metabolomics, and sex steroid hormones across the life course. Such approaches are essential to clarify biological pathways and inform sex-specific microbiome-based interventions for CMD prevention and management.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>本研究旨在探討孕婦尿路感染（UTI）導致早產的免疫機制。研究團隊建立尿路致病性大腸桿菌（UPEC）感染的孕鼠模型，發現發生早產的母鼠伴隨更嚴重的膀胱發炎、胎盤細胞激素升高及血清IL-10降低；給予外源性IL-10或抑制T細胞，能減少胎盤TH17細胞並預防早產。此外，人類佇列研究證實，尿液中T細胞相關細胞激素（如IL-10、IL-15等）與早產風險密切相關。本研究結合動物模型與臨床樣本，揭示了UTI引發早產的免疫關鍵，並為未來篩檢及治療提供了潛在的非侵入性生物標誌物與機制標靶。</t>
+          <t>本文旨在探討性別差異在腸道微生物群與相關代謝物（GMRMs）中如何影響心臟代謝疾病（CMD）。研究指出，受性類固醇、免疫功能及環境因素影響，腸道菌相與代謝產物存在顯著的性別二態性。女性在生育期較男性具備更佳的心臟代謝特徵，但停經後風險顯著升高，此變化與特定菌屬（如 *Akkermansia muciniphila*）及代謝物（如短鏈脂肪酸、次級膽汁酸、TMAO）的豐度改變密切相關。這些微生物與代謝物透過調節發炎反應、醣脂代謝及血管功能，進而影響 CMD 的發生。本文強調未來需透過大型縱向研究，結合微生物組學、代謝組學與荷爾蒙監測，以深入解析其生物學機制，並開發針對不同性別的精準微生物介入療法，對於預防及管理心臟代謝疾病具有重要的科學價值。</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1953,32 +1952,30 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42647600/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647164/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>42648688</t>
+          <t>42647759</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Temperature Sensitivity of Pyrrhotite-Driven Metavanadate Bioreduction in Groundwater.</t>
+          <t>The Gut Microbiome in Multiple Sclerosis.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Environmental research</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>7.7</v>
-      </c>
+          <t>Neurology(R) neuroimmunology &amp; neuroinflammation</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1991,12 +1988,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Pyrrhotite-driven metavanadate [V(V)] bioreduction is a promising green strategy for the remediation of vanadium-contaminated aquifers. However, how this microbially driven process responds to different temperatures remains unclear. Herein, the responses of pyrrhotite-driven V(V) bioreduction to different temperatures ranging from 4 to 45 °C were investigated. V(V) removal first increased and then decreased with increasing temperature, peaking at 35 °C, with the reaction rate constant reaching 0.077 d-1. V(V) could be reduced to VO2 precipitates, accompanied by oxidation of S(-II) and Fe(II) to sulfate and Fe(III), respectively. Metagenomic binning revealed that S(-II) oxidation was more sensitive to temperature changes than Fe(II) oxidation for V(V) reducers. Bacteria coupling V(V) reduction with both S(-II) and Fe(II) oxidation (e.g., Ramlibacter sp.) were detected exclusively at 35 °C. The transcription of functional genes (related to V(V) reduction, S(-II) oxidation, and Fe(II) oxidation), electron transport activity and related components all exhibited a temperature-dependent pattern, first increasing and then decreasing, with a peak at 35 °C. This study reveals the temperature sensitivity of pyrrhotite-driven V(V) bioreduction, which is helpful for risk assessment and targeted bioremediation of vanadium contamination under different temperature conditions.</t>
+          <t>Multiple sclerosis (MS) is a chronic inflammatory demyelinating disease of the CNS whose risk and course are shaped by both genetic and environmental factors, among which the intestinal microbiota has emerged as a key, potentially modifiable contributor. People with MS frequently display altered gut microbiota, characterized by depletion of fiber-fermenting, short-chain fatty acid (SCFA)-producing commensals, and expansion of taxa associated with mucus degradation and proinflammatory metabolism. These compositional shifts are paralleled by broad changes in blood and CSF metabolites, including reduced SCFAs, tryptophan-derived aryl hydrocarbon receptor ligands, and secondary bile acids. In addition, several reports highlight the accumulation of aromatic amino acid-derived phenolic and indolic compounds and specific lipid mediators linked to neuroinflammation and neurodegeneration. In this up-to-date review, we synthesize evidence from experimental models and human studies showing how microbial metabolites can influence MS pathogenesis through converging mechanisms: modulation of gut and blood-brain barrier integrity; shaping of T-cell and B-cell responses; direct effects on microglia, astrocytes, and oligodendrocyte lineage cells after crossing into the CNS; and modulation of neural circuits, particularly those involving the vagus nerve. Finally, we highlight current gaps, including the need for longitudinal, harmonized multiomic cohorts, and mechanistic studies integrating microbiome, metabolome, and host readouts across gut, blood, and CNS. Overall, available data support a model in which coordinated disruption of the gut microbiota-metabolite axis, rather than any single pathogen, contributes to MS, opening avenues for microbiota-based and metabolite-based biomarkers and therapies aimed at restoring immune and neuroglial homeostasis.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>本研究旨在探討不同溫度（4至45 °C）對地下水中磁黃鐵礦驅動的偏釩酸鹽 [V(V)] 生物還原過程之影響。研究發現，V(V) 去除率隨溫度升高呈先升後降趨勢，並在 35 °C 時達到峰值（反應速率常數 0.077 d⁻¹），此時 V(V) 被還原為 VO₂ 沉澱，並伴隨硫與鐵的氧化。總體基因體 binning 分析顯示，還原菌的硫氧化過程對溫度變化比鐵氧化更為敏感，且僅在 35 °C 下偵測到能同時耦合硫與鐵氧化的關鍵細菌（如 *Ramlibacter* sp.）。此外，相關功能基因轉錄與電子傳遞活性亦在 35 °C 達到頂峰。本研究揭示了該還原作用的溫度敏感性，為釩污染的環境風險評估與精準生物整治提供了科學依據。</t>
+          <t>本研究探討多發性硬化症（MS）與腸道微生物群之間的關聯。研究指出，MS 患者的腸道菌相呈現失調狀態，包括短鏈脂肪酸（SCFA）產生菌減少，以及促發炎代謝菌的增加。這些微生物群落的變化伴隨著血液與腦脊髓液中代謝物（如色胺酸衍生物、膽汁酸及 SCFA）的顯著改變，這些物質經證實與神經發炎及退化密切相關。文中綜述了微生物代謝產物如何透過調節腸道與血腦屏障完整性、影響免疫細胞（T/B 細胞）反應，以及直接作用於神經膠質細胞來參與 MS 的致病機制。總結而言，MS 的發生與腸道菌群-代謝物軸的整體失調有關，而非單一病原體所致。該研究強調未來需進行多體學（multiomics）整合分析，以開發基於微生物群的生物標記與創新治療策略，旨在恢復患者的免疫與神經恆定。</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2006,35 +2003,35 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42648688/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647759/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>42644746</t>
+          <t>42648171</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Metabolic division of labour drives estuarine-coastal N2O emissions.</t>
+          <t>Co-occurrence of muddy off flavor and cyanotoxin genes in the polluted Guandu river waters (Rio de Janeiro, Brazil).</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>The ISME journal</t>
+          <t>The Science of the total environment</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>metagenomics, metatranscriptomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>974 個重建的 N2O 相關基因體（原文未提及具體的環境樣本採集數量）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G31" t="b">
@@ -2042,12 +2039,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Estuarine and coastal systems are global hotspots of marine nitrous oxide (N2O) emissions, where microbial nitrification and denitrification are the primary processes regulating N2O dynamics. However, how interactions among different N2O-associated microorganisms influence ecosystem-scale N2O emissions remains poorly understood. This study combined in situ N2O concentrations, 15N-based potential rates, metagenomics, metatranscriptomics, and genome-scale metabolic model analysis to explore N2O production and reduction processes in estuarine and coastal systems. Potential N2O production and reduction rates, together with in situ concentrations, the relative abundance, and the transcriptional activity of associated genes, were significantly higher at low salinity and declined toward coastal regions. Based on the gene content of 974 recovered N2O-associated genomes, microorganisms were classified into three functional groups: net N2O producers, net N2O consumers, and self-sustaining N2O players. The abundance, composition, and activity of these functional groups shifted along estuarine-coastal gradients. A larger NO/N2O exchange gap, reflecting the imbalance between model-inferred NO and N2O handoff potentials, was found at low salinity and was associated with elevated bottom-water N2O concentrations. Together, community-level division of labour and the associated exchange gap provide a conceptual framework for linking N2O-related functional groups to N2O accumulation in estuarine-coastal ecosystems.</t>
+          <t>The Guandu river basin is responsible for supplying Rio de Janeiro municipality, Brazil, with drinking water. This study investigated water quality during the geosmin crisis in January and March 2020, by relating the water quality and odor compounds with metagenomic tools. Guandu river water was eutrophic. The cyanobacterial genera identified were Microcystis, Planktothrix, Dolichospermum, Nostoc, Synechococcus, Planktothricoides, and Cyanobium, indicating that bloom-associated communities in the system are taxonomically diverse. Functional annotation of metagenomic sequences revealed the presence of genes associated with the biosynthesis of taste-and-odor compounds, including geosmin (geoA) and 2-methylisoborneol (mic), as well as multiple biosynthetic clusters related to cyanotoxin production. Genes linked to microcystin (mcy), saxitoxin (sxt), anatoxin (ana), cylindrospermopsin (cyr), lyngbyatoxin (ltx), guanitoxin (gnt), and nodularin (nda) were detected across the dataset, indicating a broad genetic potential for the production of secondary metabolites relevant to water quality. The co-occurrence of cyanotoxins, geosmin and 2-MIB genes suggests that off-flavor is an indication of cyanotoxin potential production in the water.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>本研究旨在探討河口與沿海系統中，微生物交互作用如何驅動一氧化二氮（N2O）的排放。研究結合現場觀測、15N同位素速率、總體基因體與轉錄體學，重建了974個N2O相關基因體。結果指出，低鹽度區域的N2O產生與還原速率及基因表達顯著較高。研究將微生物劃分為淨產生者、淨消費者與自給自足者，並發現低鹽度區因群落間物質交換失衡，存在較大的NO/N2O交換缺口，進而導致底層水體N2O顯著累積。本研究建立了群落水平的「分工與交換缺口」理論框架，為預測及理解海洋生態系統N2O排放提供了關鍵的科學依據。</t>
+          <t>本研究旨在探究巴西里約熱內盧瓜杜河於2020年初爆發土臭素危機期間的水質狀況，並利用總體基因體學技術探討水質異味與微生物群落之關聯。研究發現，該富營養化水體中含有多種藍菌，且功能性註釋顯示其富含合成土臭素（*geoA*）與2-甲基異莰醇（*mic*）等異味物質的基因。更重要的是，多種藍菌毒素（如微囊藻毒素、石房蛤毒素等）的合成基因群與這些異味基因呈現共存。此發現證實了水體異味的出現與藍菌毒素的潛在生成具有高度相關性，可作為飲用水安全監測及評估藍菌毒素潛在危害的重要預警指標。</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2057,37 +2054,37 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42644746/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648171/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>42649294</t>
+          <t>42644416</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Synergistic degradation of fucoidans in the ocean.</t>
+          <t>Nationwide cohort study reveals low bifidobacteria and distinct microbiota composition and function in Swedish newborns.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>Gut microbes</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>48.5</v>
+        <v>11</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>metabolomics, metagenomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>未提及（該研究採用重組海洋微生物群落進行實驗，未提供具體的生物樣本人數或檢體數量）</t>
+          <t>308 名瑞典新生兒的糞便檢體</t>
         </is>
       </c>
       <c r="G32" t="b">
@@ -2095,12 +2092,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Fucoidans, a class of complex polysaccharides produced by brown algae and diatoms, contribute to long-term carbon sequestration owing to their resistance to microbial degradation1,2. Although individual microorganisms can break down portions of these polysaccharides3-5, it remains unclear whether complete breakdown is possible in nature and, if so, by what mechanisms. Here we show that fucoidans are degraded through synergistic interactions between specialized bacteria with complementary metabolic functions. Using metabolomic analysis of a reconstructed marine consortium, we uncovered metabolic guilds of bacteria that preferentially degrade either the sulfated fucose backbone or the side branches of rare monomers. This functional division of labour leads to an unexpectedly high number of synergistic interactions between different degraders that enhanced degradation efficiency up to 97.1%. Despite varying fucoidan structures across different types of algae6, the metabolic functions of degraders remained conserved, enabling quantitative prediction of degradation outcomes based on community and substrate composition. The frequent co-occurrence of functionally complementary fucoidan degraders in ocean metagenomes suggests that synergistic degradation is a globally relevant strategy. Our findings suggest that the environmental turnover of complex biopolymers depends not only on individual metabolic capabilities of degraders but also on ecological interactions shaped by substrate architecture. This work provides a mechanistic framework for understanding carbon cycling in the ocean and for engineering synthetic microbial consortia to degrade recalcitrant polysaccharides.</t>
+          <t>NCT06285630.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>本研究探討海洋中複雜多醣體「褐藻醣膠」（fucoidans）的微生物降解機制。儘管褐藻醣膠因其抗降解性在碳封存中扮演關鍵角色，但過往對於其在自然界中是否能被完全分解並不清楚。研究發現，褐藻醣膠的降解並非單一物種所能完成，而是透過具有互補代謝功能的細菌群落進行「協同作用」。透過代謝體學分析，研究團隊識別出專門降解硫酸岩藻糖骨架與稀有單醣側鏈的代謝群組（metabolic guilds），這種分工合作能將降解效率大幅提升至 97.1%。此外，研究顯示此代謝功能在不同環境下具有高度保守性，且在海洋宏基因組中普遍存在。本研究揭示了生物聚合物的環境周轉率取決於微生物間的生態交互作用，為理解海洋碳循環機制提供了重要框架，並為未來利用人工合成微生物群落降解頑固性多醣體提供了技術基礎。</t>
+          <t>本研究旨在探討瑞典新生兒的腸道菌相組成與功能特徵。透過總體基因體學分析，研究發現瑞典新生兒腸道中的雙歧桿菌（特別是嬰兒雙歧桿菌）豐度顯著偏低，並呈現出獨特的菌相結構與代謝功能。此現象與現代化生活型態及分娩方式密切相關。這項全國性世代研究揭示了現代環境對嬰兒早期腸道微生態建立的深遠影響，為未來的臨床嬰幼兒益生菌介入與健康照護策略提供了關鍵的科學依據。</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2110,35 +2107,37 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42649294/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42644416/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>42657129</t>
+          <t>42648218</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pulmonary Infiltrates, Airway Mucosal Lesions and Respiratory Microbiology After Freshwater Drowning: A Case Report.</t>
+          <t>Agricultural sprinkler irrigation systems as environmental reservoirs and airborne dissemination sources of Legionella pneumophila.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Respirology case reports</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>Journal of environmental management</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>8.4</v>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>metagenomics, small genome</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1 例病患（n=1）</t>
+          <t>未明確提及具體檢體數量（僅指出於西班牙東北部農村的兩個區域，針對灌溉池塘與溝渠進行採樣）</t>
         </is>
       </c>
       <c r="G33" t="b">
@@ -2146,12 +2145,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Early pulmonary abnormalities after freshwater drowning can be overinterpreted as bacterial pneumonia, especially when inflammatory biomarkers and respiratory microbiology are positive. A 20-year-old man was resuscitated after approximately 2 min of freshwater submersion. Day 1 chest CT showed bilateral lower-lobe-predominant opacities compatible with non-cardiogenic pulmonary oedema and aspiration-related lung injury, with near-complete resolution by Day 25. Day 3 bronchoscopy showed diffuse, non-removable, millet-seed-like whitish tracheal mucosal protrusions with hyperaemia and oedema, compatible with acute irritative airway injury. BALF mNGS detected multiple gram-negative bacterial signals, predominantly Klebsiella pneumoniae, while sputum culture yielded ESBL-negative, susceptible K. pneumoniae. Possible drowning-associated pneumonia was considered because of aspiration, fever, markedly elevated inflammatory biomarkers and concordant microbiology; however, rapid radiological improvement and clinical stability suggested a substantial non-infectious component. The patient recovered after an 8-day course of piperacillin-tazobactam without antibiotic escalation, corticosteroids, mechanical ventilation or acute respiratory distress syndrome.</t>
+          <t>Sprinkler irrigation systems are critical for modern agriculture but represent largely unrecognized aquatic environments capable of sustaining opportunistic human pathogens. Among them, Legionella pneumophila is of particular concern due to its ability to colonize engineered water systems, persist under fluctuating environmental conditions, and be transmitted through aerosols. In this study, we conducted a comprehensive microbiological and genomic investigation of irrigation ponds and ditches in a rural area of north-east Spain where two zones were sampled. Metagenomic profiling revealed highly diverse microbial communities encompassing more than 20,000 species, including 21 airborne-transmissible bacterial pathogens of clinical relevance. Notably, L. pneumophila was detected in both zones, with a relative abundance of up to 4.6 %. Culture-based isolation confirmed the presence of L. pneumophila serogroup 1, Pontiac group, Benidorm subgroup, sequence type 15. Phylogenetic analysis demonstrated a close relationship between this environmental strain and clinical isolates obtained during a Legionnaires' disease outbreak occurred in 2015, which had remained without a confirmed environmental source. Meteorological data from the exposure period revealed wind conditions favouring long-distance aerosol dispersion from irrigated fields toward residential areas. Our findings provide evidence that irrigation infrastructures can act as environmental reservoirs and dissemination routes of L. pneumophila among other airborne pathogens. These results underscore the need to incorporate agricultural irrigation systems into routine environmental surveillance, outbreak investigations, and public health risk assessments.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>本研究透過單一病例報告，探討淡水溺水後肺部浸潤與呼吸道損傷的臨床鑑別診斷。一名 20 歲男性溺水後出現肺水腫與氣道黏膜病變，臨床表現極易與細菌性肺炎混淆。研究利用 mNGS（宏基因組次世代定序）檢測支氣管肺泡灌洗液，雖確認存在肺炎克雷伯菌（*Klebsiella pneumoniae*）訊號，但影像學與臨床病程顯示其肺部損傷主要源於吸入性損傷及急性化學性氣道刺激，而非嚴重的細菌感染。此案例凸顯了臨床判斷溺水相關肺炎時的挑戰，強調在面對看似感染的臨床數據時，應綜合考量影像改善速度與臨床穩定性，避免過度診斷與不必要的抗生素升級，對急性溺水病患的精準治療具有重要的臨床參考價值。</t>
+          <t>本研究旨在探討農業噴灌系統是否為嗜肺軍團菌（*Legionella pneumophila*）等致病菌的環境宿主與空氣傳播源。團隊對西班牙農村灌溉水體進行分析，總體基因體學顯示其含有逾2萬種微生物，包括21種臨床相關的空氣傳播病原體，且嗜肺軍團菌相對豐度達4.6%。研究成功分離出嗜肺軍團菌血清型1（ST15），系統發育分析證實該環境株與2015年退伍軍人症爆發的臨床分離株高度相關。氣象數據亦支持風向有利於氣膠從農田長距離擴散至住宅區。此發現證實農業灌溉系統為軍團菌的傳播媒介，強調應將其納入例行環境監測與公衛風險評估。</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2161,37 +2160,37 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42657129/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648218/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>42647164</t>
+          <t>42648688</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sex differences in the gut microbiome and related metabolites: role in cardiometabolic disease.</t>
+          <t>Temperature Sensitivity of Pyrrhotite-Driven Metavanadate Bioreduction in Groundwater.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>Environmental research</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11</v>
+        <v>7.7</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>未提及（本文為綜論性回顧文章，非原創實驗研究）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G34" t="b">
@@ -2199,12 +2198,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sex differences in major cardiometabolic diseases (CMD), such as type 2 diabetes, metabolic dysfunction-associated steatotic liver disease, and cardiovascular disease, have been increasingly recognized across the life course. During the reproductive stage, women generally have a more favorable cardiometabolic risk profile than men, but their risk of experiencing CMD significantly increases after menopause. Emerging evidence suggests that sexually dimorphic gut microbiota and gut microbiota-related metabolites (GMRMs) may contribute to such sex disparities. However, existing findings are heterogeneous and underlying mechanisms remain incompletely understood. In this review, we synthesize the evidence examining sex differences in gut microbial diversity, overall composition, taxa abundances, and levels of GMRMs across key life stages, including pre-puberty, adolescence, and different phases of adulthood (with emphasis on pre- and post-menopausal periods). We summarize potential biological mechanisms underlying sexual dimorphism in the gut microbiome and GMRMs, emphasizing the central role of sex steroids, along with contributions from immune function and other host and environmental factors. We further integrate evidence linking sexually dimorphic microbial taxa (e.g., Akkermansia muciniphila, Eubacterium, Ruminococcus, and other Firmicutes taxa) and GMRMs (e.g., microbiota-derived short-chain fatty acids, secondary bile acids, and trimethylamine N-oxide) to key cardiometabolic pathways involving inflammation, glucose and lipid metabolism, and vascular function. Finally, we identify critical knowledge gaps and emphasize the need for future large longitudinal studies that would integrate repeated measurements of the gut microbiome, untargeted metabolomics, and sex steroid hormones across the life course. Such approaches are essential to clarify biological pathways and inform sex-specific microbiome-based interventions for CMD prevention and management.</t>
+          <t>Pyrrhotite-driven metavanadate [V(V)] bioreduction is a promising green strategy for the remediation of vanadium-contaminated aquifers. However, how this microbially driven process responds to different temperatures remains unclear. Herein, the responses of pyrrhotite-driven V(V) bioreduction to different temperatures ranging from 4 to 45 °C were investigated. V(V) removal first increased and then decreased with increasing temperature, peaking at 35 °C, with the reaction rate constant reaching 0.077 d-1. V(V) could be reduced to VO2 precipitates, accompanied by oxidation of S(-II) and Fe(II) to sulfate and Fe(III), respectively. Metagenomic binning revealed that S(-II) oxidation was more sensitive to temperature changes than Fe(II) oxidation for V(V) reducers. Bacteria coupling V(V) reduction with both S(-II) and Fe(II) oxidation (e.g., Ramlibacter sp.) were detected exclusively at 35 °C. The transcription of functional genes (related to V(V) reduction, S(-II) oxidation, and Fe(II) oxidation), electron transport activity and related components all exhibited a temperature-dependent pattern, first increasing and then decreasing, with a peak at 35 °C. This study reveals the temperature sensitivity of pyrrhotite-driven V(V) bioreduction, which is helpful for risk assessment and targeted bioremediation of vanadium contamination under different temperature conditions.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>本文旨在探討性別差異在腸道微生物群與相關代謝物（GMRMs）中如何影響心臟代謝疾病（CMD）。研究指出，受性類固醇、免疫功能及環境因素影響，腸道菌相與代謝產物存在顯著的性別二態性。女性在生育期較男性具備更佳的心臟代謝特徵，但停經後風險顯著升高，此變化與特定菌屬（如 *Akkermansia muciniphila*）及代謝物（如短鏈脂肪酸、次級膽汁酸、TMAO）的豐度改變密切相關。這些微生物與代謝物透過調節發炎反應、醣脂代謝及血管功能，進而影響 CMD 的發生。本文強調未來需透過大型縱向研究，結合微生物組學、代謝組學與荷爾蒙監測，以深入解析其生物學機制，並開發針對不同性別的精準微生物介入療法，對於預防及管理心臟代謝疾病具有重要的科學價值。</t>
+          <t>本研究旨在探討不同溫度（4至45 °C）對地下水中磁黃鐵礦驅動的偏釩酸鹽 [V(V)] 生物還原過程之影響。研究發現，V(V) 去除率隨溫度升高呈先升後降趨勢，並在 35 °C 時達到峰值（反應速率常數 0.077 d⁻¹），此時 V(V) 被還原為 VO₂ 沉澱，並伴隨硫與鐵的氧化。總體基因體 binning 分析顯示，還原菌的硫氧化過程對溫度變化比鐵氧化更為敏感，且僅在 35 °C 下偵測到能同時耦合硫與鐵氧化的關鍵細菌（如 *Ramlibacter* sp.）。此外，相關功能基因轉錄與電子傳遞活性亦在 35 °C 達到頂峰。本研究揭示了該還原作用的溫度敏感性，為釩污染的環境風險評估與精準生物整治提供了科學依據。</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2214,27 +2213,29 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42647164/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648688/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>42647759</t>
+          <t>42647600</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Gut Microbiome in Multiple Sclerosis.</t>
+          <t>Urogenital immune signatures are associated with birth outcomes after maternal urinary tract infection.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Neurology(R) neuroimmunology &amp; neuroinflammation</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Science translational medicine</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>14.6</v>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>others</t>
@@ -2250,12 +2251,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Multiple sclerosis (MS) is a chronic inflammatory demyelinating disease of the CNS whose risk and course are shaped by both genetic and environmental factors, among which the intestinal microbiota has emerged as a key, potentially modifiable contributor. People with MS frequently display altered gut microbiota, characterized by depletion of fiber-fermenting, short-chain fatty acid (SCFA)-producing commensals, and expansion of taxa associated with mucus degradation and proinflammatory metabolism. These compositional shifts are paralleled by broad changes in blood and CSF metabolites, including reduced SCFAs, tryptophan-derived aryl hydrocarbon receptor ligands, and secondary bile acids. In addition, several reports highlight the accumulation of aromatic amino acid-derived phenolic and indolic compounds and specific lipid mediators linked to neuroinflammation and neurodegeneration. In this up-to-date review, we synthesize evidence from experimental models and human studies showing how microbial metabolites can influence MS pathogenesis through converging mechanisms: modulation of gut and blood-brain barrier integrity; shaping of T-cell and B-cell responses; direct effects on microglia, astrocytes, and oligodendrocyte lineage cells after crossing into the CNS; and modulation of neural circuits, particularly those involving the vagus nerve. Finally, we highlight current gaps, including the need for longitudinal, harmonized multiomic cohorts, and mechanistic studies integrating microbiome, metabolome, and host readouts across gut, blood, and CNS. Overall, available data support a model in which coordinated disruption of the gut microbiota-metabolite axis, rather than any single pathogen, contributes to MS, opening avenues for microbiota-based and metabolite-based biomarkers and therapies aimed at restoring immune and neuroglial homeostasis.</t>
+          <t>Preterm birth is the leading cause of infant mortality, resulting in more than 1 million neonatal deaths globally each year. Maternal urinary tract infection (UTI) during pregnancy increases risk for preterm birth; however, biological processes mediating UTI-associated preterm birth are not well described. We established a murine maternal UTI model in which challenge with uropathogenic Escherichia coli (UPEC) initiated preterm labor and birth in about half of dams. Although bacterial burdens were similar, dams experiencing preterm birth displayed excessive bladder inflammation, elevated placental and decidual cytokines, higher proportions of male fetuses, and lower maternal serum interleukin-10 (IL-10) compared with nonlaboring dams. Exogenous IL-10 or lymph node sequestration of T cells reduced placental type 17 T helper cells (TH17 cells) and abrogated preterm birth. In a human pregnancy cohort, we correlated urinary cytokines with birth outcomes and urine culture status. These analyses yielded an exploratory, noninvasive culture-agnostic system for evaluating preterm birth risk, implicating T cell-related cytokines including IL-10, IL-15, GM-CSF, and RANTES. These findings demonstrate that our murine model provides a platform to investigate immunological and microbial factors governing UTI-associated preterm birth and, coupled with patient samples, may be used to identify candidate biomarkers and mechanistic targets for future investigation.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>本研究探討多發性硬化症（MS）與腸道微生物群之間的關聯。研究指出，MS 患者的腸道菌相呈現失調狀態，包括短鏈脂肪酸（SCFA）產生菌減少，以及促發炎代謝菌的增加。這些微生物群落的變化伴隨著血液與腦脊髓液中代謝物（如色胺酸衍生物、膽汁酸及 SCFA）的顯著改變，這些物質經證實與神經發炎及退化密切相關。文中綜述了微生物代謝產物如何透過調節腸道與血腦屏障完整性、影響免疫細胞（T/B 細胞）反應，以及直接作用於神經膠質細胞來參與 MS 的致病機制。總結而言，MS 的發生與腸道菌群-代謝物軸的整體失調有關，而非單一病原體所致。該研究強調未來需進行多體學（multiomics）整合分析，以開發基於微生物群的生物標記與創新治療策略，旨在恢復患者的免疫與神經恆定。</t>
+          <t>本研究旨在探討孕婦尿路感染（UTI）導致早產的免疫機制。研究團隊建立尿路致病性大腸桿菌（UPEC）感染的孕鼠模型，發現發生早產的母鼠伴隨更嚴重的膀胱發炎、胎盤細胞激素升高及血清IL-10降低；給予外源性IL-10或抑制T細胞，能減少胎盤TH17細胞並預防早產。此外，人類佇列研究證實，尿液中T細胞相關細胞激素（如IL-10、IL-15等）與早產風險密切相關。本研究結合動物模型與臨床樣本，揭示了UTI引發早產的免疫關鍵，並為未來篩檢及治療提供了潛在的非侵入性生物標誌物與機制標靶。</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2265,27 +2266,29 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42647759/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647600/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>42648171</t>
+          <t>42647084</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Co-occurrence of muddy off flavor and cyanotoxin genes in the polluted Guandu river waters (Rio de Janeiro, Brazil).</t>
+          <t>Diet quality, gut microbiome, and inflammatory signatures in Puerto Rican adults with Crohn disease: a multidimensional analysis.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>The Science of the total environment</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>Inflammatory bowel diseases</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>4.3</v>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>metagenomics</t>
@@ -2293,7 +2296,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>60位患有克隆氏症的成年人 (60 adults with CD)</t>
         </is>
       </c>
       <c r="G36" t="b">
@@ -2301,12 +2304,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>The Guandu river basin is responsible for supplying Rio de Janeiro municipality, Brazil, with drinking water. This study investigated water quality during the geosmin crisis in January and March 2020, by relating the water quality and odor compounds with metagenomic tools. Guandu river water was eutrophic. The cyanobacterial genera identified were Microcystis, Planktothrix, Dolichospermum, Nostoc, Synechococcus, Planktothricoides, and Cyanobium, indicating that bloom-associated communities in the system are taxonomically diverse. Functional annotation of metagenomic sequences revealed the presence of genes associated with the biosynthesis of taste-and-odor compounds, including geosmin (geoA) and 2-methylisoborneol (mic), as well as multiple biosynthetic clusters related to cyanotoxin production. Genes linked to microcystin (mcy), saxitoxin (sxt), anatoxin (ana), cylindrospermopsin (cyr), lyngbyatoxin (ltx), guanitoxin (gnt), and nodularin (nda) were detected across the dataset, indicating a broad genetic potential for the production of secondary metabolites relevant to water quality. The co-occurrence of cyanotoxins, geosmin and 2-MIB genes suggests that off-flavor is an indication of cyanotoxin potential production in the water.</t>
+          <t>Diet is increasingly recognized as a modifiable factor influencing gut microbiome and outcomes in Crohn disease (CD), yet data in underrepresented populations remain limited. We evaluated diet quality, dietary patterns, gut microbiome composition, inflammatory markers, and patient-reported outcomes in adults with CD from Puerto Rico. We conducted a cross-sectional analysis of 60 adults with CD enrolled prior to dietary intervention in a parent study. Dietary intake was assessed using 24-hour recalls and evaluated using the Healthy Eating Index-2015 (HEI-2015), Alternative Healthy Eating Index-2010 (AHEI-2010), and exploratory dietary pattern analysis. The gut microbiome was assessed by shotgun metagenomic sequencing. Clinical outcomes included fecal calprotectin, C-reactive protein (CRP), a 96-cytokine panel, short Crohn Disease Activity Index (sCDAI), and short Inflammatory Bowel Disease Questionnaire (sIBDQ). Associations were evaluated using unadjusted and adjusted models with false discovery rate (FDR) correction. Overall diet quality was poor and characterized by low intake of fruits, vegetables, whole grains, and fiber, alongside high intake of saturated fat, added sugars, and animal-derived protein. Four dietary patterns were identified: vegetable-rich, dairy-rich, fruit-rich, and coffee/sweetener-rich. Participants adhering to the fruit-rich pattern exhibited the highest diet quality scores. Higher HEI-2015 scores were associated with greater gut microbial diversity and differences in overall microbiome composition. Participants with greater adherence to the vegetable-rich pattern showed modest increases in microbial diversity. Exploratory analyses suggested that higher fruit intake and adherence to a fruit-rich dietary pattern were associated with lower fecal calprotectin and CRP levels, whereas adherence to a vegetable-rich pattern was associated with better health-related quality of life (HRQoL) and adherence to a coffee/sweetener-rich pattern was associated with a worse symptom burden. However, no associations between dietary metrics and inflammatory markers, cytokines, or clinical outcomes remained significant after FDR correction. Most participants were in clinical remission despite substantial impairment in HRQoL. Adults with CD in Puerto Rico exhibited poor diet quality that was associated with gut microbial diversity and exploratory differences in clinical outcomes. While these findings support the influence of diet on the microbiome and clinical outcomes, larger longitudinal studies are needed to determine whether dietary improvements can influence disease outcomes this underrepresented population.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>本研究旨在探究巴西里約熱內盧瓜杜河於2020年初爆發土臭素危機期間的水質狀況，並利用總體基因體學技術探討水質異味與微生物群落之關聯。研究發現，該富營養化水體中含有多種藍菌，且功能性註釋顯示其富含合成土臭素（*geoA*）與2-甲基異莰醇（*mic*）等異味物質的基因。更重要的是，多種藍菌毒素（如微囊藻毒素、石房蛤毒素等）的合成基因群與這些異味基因呈現共存。此發現證實了水體異味的出現與藍菌毒素的潛在生成具有高度相關性，可作為飲用水安全監測及評估藍菌毒素潛在危害的重要預警指標。</t>
+          <t>本研究探討波多黎各克隆氏症（CD）成年患者的飲食品質、腸道菌相與發炎指標的關係。研究發現，受試者普遍飲食品質不佳，而較高的飲食品質（特別是富含水果的飲食模式）與較高的腸道菌群多樣性顯著相關。探索性分析顯示，多攝取水果與較低的發炎指標（鈣衛蛋白和C反應蛋白）相關，而蔬菜為主的飲食與較佳的生活品質相關（但經FDR校正後未達顯著）。本研究首次揭示了該少數受關注族群中飲食對菌相與臨床症狀的影響，為未來透過飲食干預管理CD及改善患者預後提供了科學依據。</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2316,37 +2319,37 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42648171/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647084/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>42644416</t>
+          <t>42648293</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nationwide cohort study reveals low bifidobacteria and distinct microbiota composition and function in Swedish newborns.</t>
+          <t>Defined human Clostridia consortia reverse colitis via dual effects of tryptophan metabolites on microbiota and immunity.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>Cell host &amp; microbe</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11</v>
+        <v>18.7</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>308 名瑞典新生兒的糞便檢體</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G37" t="b">
@@ -2354,12 +2357,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>NCT06285630.</t>
+          <t>Microbial dysbiosis and disrupted mucosal immune homeostasis are integrally involved in the pathogenesis of inflammatory bowel diseases (IBDs). Live biotherapeutic products (LBPs) offer a potential therapeutic strategy to restore beneficial microbes and mitigate disease. We investigated the therapeutic efficacy of 2 LBPs, human Clostridia consortia 17-mix and 11-mix, by treating established colitis in murine models. Both LBPs exhibited therapeutic effects in T cell-mediated chronic colitis models induced by human microbiota and in pathobiont-driven gnotobiotic colitis models established with combinations of IBD-relevant human-derived strains. Metagenomic and metabolomic analyses elucidated mechanisms that go beyond established functions driven by short-chain fatty acids (SCFAs) and interleukin (IL)-10-producing regulatory T cells. Notably, LBPs exerted therapeutic effects by directly inhibiting resident pathobionts and through IL-10-independent activation of host anti-inflammatory aryl hydrocarbon receptor (AhR) pathways by bacterial tryptophan metabolites. These results elucidate SCFA- and IL-10-independent protective mechanisms exerted by defined resident bacterial strains that are depleted in IBD dysbiosis.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>本研究旨在探討瑞典新生兒的腸道菌相組成與功能特徵。透過總體基因體學分析，研究發現瑞典新生兒腸道中的雙歧桿菌（特別是嬰兒雙歧桿菌）豐度顯著偏低，並呈現出獨特的菌相結構與代謝功能。此現象與現代化生活型態及分娩方式密切相關。這項全國性世代研究揭示了現代環境對嬰兒早期腸道微生態建立的深遠影響，為未來的臨床嬰幼兒益生菌介入與健康照護策略提供了關鍵的科學依據。</t>
+          <t>本研究探討了兩種由人類梭狀芽孢桿菌組成的活體生物藥物（LBP，分別為 17-mix 和 11-mix）治療小鼠結腸炎的療效與機制。研究發現，這些菌群能有效緩解小鼠的慢性與特定病原體誘導的結腸炎。宏基因組學與代謝組學分析顯示，除了傳統的短鏈脂肪酸（SCFA）和 IL-10 途徑外，LBP 還能直接抑制共生病原菌，並透過細菌色胺酸代謝物，以不依賴 IL-10 的方式激活宿主的芳香烴受體（AhR）抗炎途徑。此發現揭示了腸道有益菌保護腸道的新機制，為發炎性腸道疾病（IBD）的微生態療法提供了重要科學依據。</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2369,7 +2372,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42644416/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648293/</t>
         </is>
       </c>
     </row>
@@ -2396,12 +2399,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>metagenomics, others</t>
+          <t>metagenomics, metabolomics, others</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（僅說明使用 DSS 誘導之潰瘍性結腸炎小鼠模型）</t>
         </is>
       </c>
       <c r="G38" t="b">
@@ -2414,7 +2417,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>本研究旨在探討草果（Tsaoko Fructus）富含多酚之萃取物（3CB）對潰瘍性結腸炎（UC）的緩解作用及其機制。研究透過 LC-PDA-MS 定性出 3CB 中的七種主要多酚成分，並利用 DSS 誘導的小鼠 UC 模型進行實驗。結果顯示，3CB 能顯著緩解結腸炎臨床症狀，其機制涉及調節腸道微生物群（如減少致病菌 Pseudomonadota，增加有益菌 Bacteroidota）並恢復代謝路徑。分子層面上，3CB 能保護黏液屏障、抑制發炎因子表現，且被證實能直接靶向並調控 JNK1-cJun 訊號傳導路徑，其中成分表兒茶素（epiafzelechin）展現出高結合親和力。本研究證實草果多酚具有作為發炎性腸道疾病治療潛力藥物的科學價值，為中藥臨床應用提供了分子機制依據。</t>
+          <t>本研究旨在優化草果富含多酚成分（3CB）並探討其對DSS誘導之小鼠潰瘍性結腸炎（UC）的緩解機制。結果顯示，3CB能顯著減輕小鼠UC症狀、保護腸黏膜屏障並抑制發炎。此外，3CB顯著重塑腸道菌群，減少有害的變形菌門與脫鐵桿菌門，增加有益的擬桿菌門，並恢復其代謝途徑。化學分析鑑定出7種主要多酚，其中表阿福兒茶素（epiafzelechin）對JNK1展現高親和力。機制研究證實，3CB主要透過靶向JNK1並抑制MAPK信號通路發揮抗炎作用。本研究表明草果多酚具有作為發炎性腸道疾病保護性干預藥物的潛力。</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2431,30 +2434,28 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>42648218</t>
+          <t>42644751</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Agricultural sprinkler irrigation systems as environmental reservoirs and airborne dissemination sources of Legionella pneumophila.</t>
+          <t>Soil amelioration impacts viral ecology in saline-alkali lands.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Journal of environmental management</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>8.4</v>
-      </c>
+          <t>The ISME journal</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>metagenomics, small genome</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>未明確提及具體檢體數量（僅指出於西班牙東北部農村的兩個區域，針對灌溉池塘與溝渠進行採樣）</t>
+          <t>未提及（僅說明樣品來自中國4個主要鹽鹼地區，各包含「鹽鹼」與「改良後」兩種狀態之土壤）</t>
         </is>
       </c>
       <c r="G39" t="b">
@@ -2462,12 +2463,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sprinkler irrigation systems are critical for modern agriculture but represent largely unrecognized aquatic environments capable of sustaining opportunistic human pathogens. Among them, Legionella pneumophila is of particular concern due to its ability to colonize engineered water systems, persist under fluctuating environmental conditions, and be transmitted through aerosols. In this study, we conducted a comprehensive microbiological and genomic investigation of irrigation ponds and ditches in a rural area of north-east Spain where two zones were sampled. Metagenomic profiling revealed highly diverse microbial communities encompassing more than 20,000 species, including 21 airborne-transmissible bacterial pathogens of clinical relevance. Notably, L. pneumophila was detected in both zones, with a relative abundance of up to 4.6 %. Culture-based isolation confirmed the presence of L. pneumophila serogroup 1, Pontiac group, Benidorm subgroup, sequence type 15. Phylogenetic analysis demonstrated a close relationship between this environmental strain and clinical isolates obtained during a Legionnaires' disease outbreak occurred in 2015, which had remained without a confirmed environmental source. Meteorological data from the exposure period revealed wind conditions favouring long-distance aerosol dispersion from irrigated fields toward residential areas. Our findings provide evidence that irrigation infrastructures can act as environmental reservoirs and dissemination routes of L. pneumophila among other airborne pathogens. These results underscore the need to incorporate agricultural irrigation systems into routine environmental surveillance, outbreak investigations, and public health risk assessments.</t>
+          <t>The continuous expansion of saline-alkali lands under climate change threatens food security and reduces soil carbon stocks. A common mitigation strategy is soil amelioration, which converts degraded soils back into an arable state. Microbes play critical roles in soil health and recovery. However, the viruses that infect these microbial communities, and their potential impacts during saline-alkali soil restoration, remain largely unknown. Here, we combined total soil metagenomics and viromics to investigate host-linked viral ecology across four major saline-alkali regions in China, each encompassing two soil amelioration statuses: saline-alkali and reclaimed. We found that viral community structure was shaped by both geography and soil amelioration status, with salinity and alkalinity emerging as key environmental factors. Viral populations were sensitive to soil restoration, showing strong amelioration-status endemism with functional adaptations. Virus-host dynamics ranged from reduced temperate viruses to abundance mismatches in those infecting key carbon-cycling microorganisms, including carbohydrate degraders. 13C-cellulose DNA-SIP experiments provided further support for this mismatch by tracing assimilated carbon transfer between active host and virus populations. Compared with saline-alkali soils, the relative abundance of hosts in restored soils increased from 39.0% to 61.0%, whereas the linked viruses decreased from 60.6% to 39.4%. Together, these findings reveal an underappreciated role of viruses in shaping saline-alkali soil amelioration trajectories, and could improve management strategies for degraded land recovery and carbon storage.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>本研究旨在探討農業噴灌系統是否為嗜肺軍團菌（*Legionella pneumophila*）等致病菌的環境宿主與空氣傳播源。團隊對西班牙農村灌溉水體進行分析，總體基因體學顯示其含有逾2萬種微生物，包括21種臨床相關的空氣傳播病原體，且嗜肺軍團菌相對豐度達4.6%。研究成功分離出嗜肺軍團菌血清型1（ST15），系統發育分析證實該環境株與2015年退伍軍人症爆發的臨床分離株高度相關。氣象數據亦支持風向有利於氣膠從農田長距離擴散至住宅區。此發現證實農業灌溉系統為軍團菌的傳播媒介，強調應將其納入例行環境監測與公衛風險評估。</t>
+          <t>本研究旨在探討鹽鹼地改良過程中，病毒對土壤微生物生態與碳循環的影響。研究結合總體基因體與病毒體學，分析中國四大鹽鹼區。結果顯示，土壤改良狀態、鹽度與鹼度是塑造病毒社群的關鍵。在改良土壤中，宿主微生物相對豐度顯著上升（39.0%至61.0%），而關聯病毒減少（60.6%至39.4%），且溫和病毒比例降低，碳循環關鍵微生物的病毒與宿主出現豐度失衡。13C-纖維素DNA-SIP實驗證實了兩者間的活性碳轉移。此發現揭示了病毒在鹽鹼地恢復中的關鍵作用，有助優化土地改良與碳儲存策略。</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2477,7 +2478,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42648218/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42644751/</t>
         </is>
       </c>
     </row>
@@ -2537,25 +2538,25 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>42642834</t>
+          <t>42648179</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Glycosylation in gut-brain communication: from the intestinal barrier and microbiota to immune and neural signaling.</t>
+          <t>Simultaneous removal of nitrogen, Cu2+, and bisphenol A in a hydrogel-biochar-AQDS immobilized bioreactor with added bicarbonate: Performance and metagenomic insights.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>Journal of hazardous materials</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2568,12 +2569,13 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>The gut-brain axis is a complex bidirectional communication network linking the gastrointestinal tract and the central nervous system. Its dysregulation is closely associated with a wide range of gastrointestinal, metabolic, and neuropsychiatric disorders. Glycosylation, one of the most prevalent and structurally diverse post-translational modifications of proteins and lipids, is increasingly recognized as a regulator of multiple processes within the gut-brain axis. In this review, we summarize evidence that glycosylation influences several steps of gut-brain communication, including intestinal barrier function, microbial glycan metabolism, immune signaling, enteric and vagal pathways, blood-brain barrier integrity, and neural responses. We distinguish direct mechanistic findings from associative observations and discuss the more limited evidence for brain-to-gut regulation of intestinal glycosylation. In addition, we discuss the potential of glycosylation-targeted nutritional and microbiota-based interventions and highlight emerging opportunities to integrate glycomics with other omics approaches to dissect the complex regulatory networks underlying the gut-brain axis. In conclusion, elucidating how glycosylation shapes signaling along the gut-brain axis may open new avenues for understanding disease pathogenesis and for developing targeted therapeutic strategies.</t>
+          <t>As the complexity of industrial wastewater pollution continues to increase, the simultaneous removal of nitrogen, metal contaminants, and persistent organic pollutants under low carbon conditions has become a key challenge for biological treatment systems. To address the operational instability and dependence on carbon sources observed in immobilized systems when exposed to copper (Cu2+) and bisphenol A (BPA), the Pseudoalteromonas japonicus strain LY0623 was integrated into a hydrogel-biochar-AQDS composite carrier to construct a multifunctional immobilized biofilm system. Notably, under conditions containing only NaHCO3, the R4 system achieved an NH4+-N removal rate of 89%. Under conditions where Cu2+ and BPA coexist, the R4 system achieved removal of NH4+-N (89%), NO3--N (100%), Cu2+ (85%), and BPA (88%). Sediment characterization confirmed that Cu2+ was immobilized through adsorption, complexation, and microbiologically induced carbonate precipitation (MICP). Metagenomic analysis further indicated that the Pseudomonadota phylum remained the dominant phylum, while functional pathways associated with inorganic carbon assimilation, HNAD nitrogen metabolism, endogenous carbon transformation, biomineralization, electron transfer, and aromatic compound degradation were preserved. By combining ammonia oxidation driven energy production, inorganic carbon utilization, redox mediated processes, and biomineralization, this study provides a highly promising low carbon strategy for treating industrial wastewater containing mixed pollutants.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>本文探討「腸-腦軸線」（Gut-Brain Axis）中醣基化（Glycosylation）修飾的關鍵調節角色。醣基化作為蛋白質與脂質重要的轉譯後修飾，深刻影響腸道屏障功能、微生物聚醣代謝、免疫訊息傳遞及血腦屏障完整性。研究重點解析了醣基化如何調控腸道與中樞神經系統間的溝通，並區分了機制性證據與相關性觀察。本文不僅強調了醣基化在維繫軸線穩定中的核心地位，更提出透過營養干預與微生物調節，結合多體學（Omics）分析醣基化網絡，將有望為神經精神疾病與代謝性障礙提供創新的診斷與治療策略。</t>
+          <t>本研究旨在解決低碳條件下，工業廢水中氮、重金屬（Cu2+）與雙酚A（BPA）等混合污染物難以同時高效生物降解的挑戰。研究人員將日本假交替單胞菌（*Pseudoalteromonas japonicus*）LY0623菌株整合至水凝膠-生物炭-AQDS複合載體中，構建出新型固定化生物膜系統（R4系統）。
+研究發現，在僅添加碳酸氫鈉（無機碳源）的條件下，該系統成功實現了NH4+-N（89%）、NO3--N（100%）、Cu2+（85%）和BPA（88%）的高效同時去除。總體基因體學分析證實，變形菌門（Pseudomonadota）為優勢菌群，且系統中與無機碳同化、異營硝化-好氧反硝化（HNAD）、生物礦化及芳香族化合物降解相關的功能通路均得到有效維持。本研究結合了氨氧化產能與生物礦化等機制，為混合污染廢水處理提供了一種具前景的低碳生物修復策略。</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2583,32 +2585,32 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42642834/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648179/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>42640100</t>
+          <t>42642466</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Revisiting gut microbiota-driven ammonia metabolism: from disease burden to physiological adaptation.</t>
+          <t>Empirical evidence for gut microbial influence on human brain neurochemistry via the gut-brain axis.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>Molecular psychiatry</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11</v>
+        <v>10.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2621,12 +2623,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Ammonia homeostasis is governed by interconnected host and microbial pathways, including hepatic ureagenesis, glutamine synthesis, and gut microbiota-mediated urea hydrolysis, proteolysis, and amino acid deamination. Ammonia has historically been viewed primarily as a nitrogenous waste product and neurotoxic molecule, a concept strongly supported by studies of hyperammonemia and hepatic encephalopathy. Impaired hepatic clearance, portosystemic shunting, and enhanced gut-derived ammonia input increase systemic ammonia burden and are linked to neurological dysfunction, muscle wasting, immune dysregulation, and progression of liver disease. In the gut lumen and mucosal environment, however, gut microbes not only generate ammonia but can also reuse ammonia-derived nitrogen for amino acid synthesis, microbial biomass formation, and community nitrogen exchange. Evidence from selected physiological and preclinical models indicates that microbiota-derived ammonia may contribute to nitrogen recycling, microbial community maintenance, enteric neural regulation, or metabolic adaptation under defined conditions. These roles are more context-specific and less broadly established than the pathological effects of systemic hyperammonemia. When epithelial barrier integrity is compromised, hepatic clearance declines, or host buffering reserves are depleted, elevated ammonia can increase epithelial exposure, portal ammonia input, or peripheral blood ammonia. Conversely, evidence that reduced microbiota-derived ammonia contributes to disease remains limited and currently comes mainly from selected animal models. This review re-examines ammonia metabolism from a gut microbiota-centered perspective. We discuss the ecological origins, spatial distribution, exposure characteristics, host-interface effects, and context-specific outcomes of microbiota-derived ammonia in physiology and disease, and discuss how ammonia should be measured, stratified, and targeted in microbial nitrogen metabolism.</t>
+          <t>The gut microbiome produces metabolites with potential neuroactive properties, many of which act locally within the gut. While preclinical studies suggest these microbial pathways can influence cognitive and emotional processes, human evidence remains limited. This study investigates associations between gut microbiome-derived neuroactive functional potential and in vivo brain neurotransmitter concentrations in healthy young females. Using proton magnetic resonance spectroscopy (¹H-MRS), we quantified GABA and glutamate levels in the dorsolateral prefrontal cortex (dlPFC), anterior cingulate cortex (ACC), and inferior occipital gyrus (IOG). Parallel metagenomic profiling characterised microbial functional potential for pathways related to the synthesis and degradation of GABA, glutamate, short-chain fatty acids (SCFAs), p-cresol, and inositol. Region-specific associations were observed between these microbial pathways and cortical GABA and glutamate levels, including excitatory/inhibitory (E/I) balance, a key marker of neuroplasticity and mental health. Notably, microbial glutamate degradation and inositol synthesis potential were associated with IOG E/I balance, while additional pathways including GABA metabolism, p-cresol production, and SCFA synthesis showed distinct associations across regions. Exploratory analyses also identified links between microbial functional potential and anxiety, depressive symptoms, and sleep quality. Together, these findings provide new human evidence that variation in microbial functional potential corresponds with regional cortical neurochemistry and psychological wellbeing, highlighting the gut-brain axis as a promising avenue for mechanistically informed microbiome-based- interventions.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>本綜述重新審視了腸道菌群驅動的氨代謝，探討其從疾病負擔到生理適應的雙重角色。傳統上，氨被視為具神經毒性的代謝廢物，與高氨血症、肝性腦病及肝病惡化密切相關。然而，在腸道微環境中，微生物不僅產生氨，亦能利用氨源氮進行氨基酸合成與群落氮循環，展現出維持腸道神經與代謝適應等生理功能。文章強調，氨的病理與生理效應高度取決於上皮屏障、肝臟清除能力及宿主緩衝儲備。本研究為腸道微生物氮代謝提供了新的生態與臨床視角，並討論了未來如何精確測量及標靶氨代謝的策略。</t>
+          <t>本研究旨在探討健康女性的腸道菌群功能潛力與大腦活體神經傳導物質（GABA與麩胺酸）濃度的關聯。研究結合腦部質子磁共振波譜（¹H-MRS）與總體基因體學分析，發現微生物中參與GABA、麩胺酸、短鏈脂肪酸、對甲酚及肌醇代謝的通路，與大腦特定區域（如背外側前額葉、前扣帶迴與下枕葉）的神經傳導物質水平及興奮/抑制平衡（E/I）具有區域特異性關聯。探索性分析亦顯示微生物功能與焦慮、抑鬱及睡眠品質相關。本研究為腸道菌群影響人類大腦神經化學與心理健康提供了直接的人體實證，為未來開發以微生物為基礎的腦腸軸臨床干預奠定基礎。</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2636,37 +2638,37 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42640100/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42642466/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>42642622</t>
+          <t>42640624</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Deployable high-fidelity metagenome binning at scale with QuickBin.</t>
+          <t>Gut microbial diversity at baseline conditions the clinical, microbiome, and metabolic response to paraprobiotic Lactiplantibacillus plantarum LRCC5282 in overweight adults.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Communications biology</t>
+          <t>Gut microbes</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>5.1</v>
+        <v>11</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>16S, metabolomics</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>297 個真實總體基因體數據集 (297 real metagenomes)</t>
+          <t>120 位過重成人</t>
         </is>
       </c>
       <c r="G43" t="b">
@@ -2674,12 +2676,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Reconstructing genomes from metagenomic assemblies is foundational to microbiome research, yet binning faces a persistent trade-off between fidelity and throughput. Many high-accuracy methods rely on GPU-intensive workflows, marker-gene postprocessing, or heavy computational resources, limiting reproducible use at scale. Here, we present QuickBin, a CPU-native, marker-free binning algorithm designed to recover near-complete, ultra-low-contamination metagenome-assembled genomes (MAGs) efficiently. QuickBin pairs a GC-coverage spatial index (BinMap) with an early-exit Oracle cascade of similarity tests (scalar composition/coverage filters and SIMD-accelerated k-mer comparisons), reserving a compact neural network exclusively for ambiguous merges. Across synthetic communities, evaluated by marker-based and contig-origin ground truth, QuickBin maximizes high-fidelity sequence recovery. In benchmarking 297 diverse real metagenomes, QuickBin completed all runs, recovering more high-quality MAGs (≥95% completeness, ≤1% contamination) than resource-intensive alternatives that frequently failed. QuickBin provides a practical path to reproducible, genome-resolved metagenomics at scale for downstream comparative analyses. Open-source at: https://github.com/bbushnell/BBTools .</t>
+          <t>The gut microbiota is increasingly recognized as a target for obesity management; however, whether baseline gut microbial diversity conditions responsiveness to microbiota-targeted interventions remains unclear. We aimed to investigate whether baseline gut microbial diversity is associated with responsiveness to a paraprobiotic derived from Lactiplantibacillus plantarum LRCC5282 (LP5282-P) in overweight adults. In a 12-week, randomized, double-blind, placebo-controlled, multicenter trial of 120 overweight adults, LP5282-P produced no significant between-group differences in any clinical outcome across the overall per-protocol population. However, in the low-diversity subgroup, LP5282-P was associated with significant reductions in body weight, body mass index, and circulating leptin levels. These clinical changes were accompanied by compositional shifts in the gut microbiota, including higher relative abundances of Christensenellaceae, Faecalibacterium, and Alistipes. Fecal metabolite profiles showed elevated acetate and butyrate concentrations and altered bile acid composition. Within the low-diversity subgroup, changes in the relative abundances of Akkermansia and Eubacterium were inversely correlated with changes in body weight, body fat mass, and leptin levels. In contrast, the high-diversity subgroup exhibited no consistent response across the outcome domains examined. Overall, baseline gut microbial diversity was associated with differential responsiveness to LP5282-P, supporting its potential use as a stratification variable in future microbiota-targeted intervention trials. Further studies integrating direct measures of microbial activity and host response are warranted to elucidate the biological pathways underlying this diversity-dependent responsiveness. Trial registration: Clinical Research Information Service (CRIS), KCT0008119.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>本研究開發了 QuickBin，這是一種無需標記基因且僅需 CPU 運行的總體基因體分箱（binning）演算法，旨在高效重建高完整度且極低污染的總體基因體組裝基因體（MAGs）。QuickBin 結合了 GC 含量與覆蓋度的空間索引及快速相似性過濾機制，僅在處理模糊合併時使用輕量級神經網路。在 297 個真實總體基因體數據集的基準測試中，QuickBin 成功完成所有運行，且重建的高品質 MAGs 數量超越了其他耗費資源或容易失敗的現有工具。此技術為大規模、可重複的基因體解析總體基因體學研究提供了實用的解決方案。</t>
+          <t>本研究旨在探討基準線腸道微生物多樣性，是否會影響過重成人對副乾酪乳桿菌（LP5282-P）介入的臨床、菌群及代謝反應。在一項為期12週、納入120位過重成人的臨床試驗中，整體人群並未展現顯著差異；然而，在「低多樣性」亞群中，LP5282-P顯著降低了受試者的體重、BMI與血清瘦素水平，並促使腸道有益菌（如 *Faecalibacterium* 與 *Alistipes*）豐度上升，同時提升糞便中乙酸與丁酸濃度並改變膽汁酸組成。相反地，「高多樣性」亞群則無一致反應。此研究證實基準線菌群多樣性是預測益生菌療效的重要關鍵，可作為未來精準微生態介入與體重管理的分層依據。</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2689,37 +2691,37 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42642622/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42640624/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>42640624</t>
+          <t>42642622</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Gut microbial diversity at baseline conditions the clinical, microbiome, and metabolic response to paraprobiotic Lactiplantibacillus plantarum LRCC5282 in overweight adults.</t>
+          <t>Deployable high-fidelity metagenome binning at scale with QuickBin.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>Communications biology</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11</v>
+        <v>5.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>120 位過重成人</t>
+          <t>297 個真實總體基因體數據集 (297 real metagenomes)</t>
         </is>
       </c>
       <c r="G44" t="b">
@@ -2727,12 +2729,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>The gut microbiota is increasingly recognized as a target for obesity management; however, whether baseline gut microbial diversity conditions responsiveness to microbiota-targeted interventions remains unclear. We aimed to investigate whether baseline gut microbial diversity is associated with responsiveness to a paraprobiotic derived from Lactiplantibacillus plantarum LRCC5282 (LP5282-P) in overweight adults. In a 12-week, randomized, double-blind, placebo-controlled, multicenter trial of 120 overweight adults, LP5282-P produced no significant between-group differences in any clinical outcome across the overall per-protocol population. However, in the low-diversity subgroup, LP5282-P was associated with significant reductions in body weight, body mass index, and circulating leptin levels. These clinical changes were accompanied by compositional shifts in the gut microbiota, including higher relative abundances of Christensenellaceae, Faecalibacterium, and Alistipes. Fecal metabolite profiles showed elevated acetate and butyrate concentrations and altered bile acid composition. Within the low-diversity subgroup, changes in the relative abundances of Akkermansia and Eubacterium were inversely correlated with changes in body weight, body fat mass, and leptin levels. In contrast, the high-diversity subgroup exhibited no consistent response across the outcome domains examined. Overall, baseline gut microbial diversity was associated with differential responsiveness to LP5282-P, supporting its potential use as a stratification variable in future microbiota-targeted intervention trials. Further studies integrating direct measures of microbial activity and host response are warranted to elucidate the biological pathways underlying this diversity-dependent responsiveness. Trial registration: Clinical Research Information Service (CRIS), KCT0008119.</t>
+          <t>Reconstructing genomes from metagenomic assemblies is foundational to microbiome research, yet binning faces a persistent trade-off between fidelity and throughput. Many high-accuracy methods rely on GPU-intensive workflows, marker-gene postprocessing, or heavy computational resources, limiting reproducible use at scale. Here, we present QuickBin, a CPU-native, marker-free binning algorithm designed to recover near-complete, ultra-low-contamination metagenome-assembled genomes (MAGs) efficiently. QuickBin pairs a GC-coverage spatial index (BinMap) with an early-exit Oracle cascade of similarity tests (scalar composition/coverage filters and SIMD-accelerated k-mer comparisons), reserving a compact neural network exclusively for ambiguous merges. Across synthetic communities, evaluated by marker-based and contig-origin ground truth, QuickBin maximizes high-fidelity sequence recovery. In benchmarking 297 diverse real metagenomes, QuickBin completed all runs, recovering more high-quality MAGs (≥95% completeness, ≤1% contamination) than resource-intensive alternatives that frequently failed. QuickBin provides a practical path to reproducible, genome-resolved metagenomics at scale for downstream comparative analyses. Open-source at: https://github.com/bbushnell/BBTools .</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>本研究旨在探討基準線腸道微生物多樣性，是否會影響過重成人對副乾酪乳桿菌（LP5282-P）介入的臨床、菌群及代謝反應。在一項為期12週、納入120位過重成人的臨床試驗中，整體人群並未展現顯著差異；然而，在「低多樣性」亞群中，LP5282-P顯著降低了受試者的體重、BMI與血清瘦素水平，並促使腸道有益菌（如 *Faecalibacterium* 與 *Alistipes*）豐度上升，同時提升糞便中乙酸與丁酸濃度並改變膽汁酸組成。相反地，「高多樣性」亞群則無一致反應。此研究證實基準線菌群多樣性是預測益生菌療效的重要關鍵，可作為未來精準微生態介入與體重管理的分層依據。</t>
+          <t>本研究開發了 QuickBin，這是一種無需標記基因且僅需 CPU 運行的總體基因體分箱（binning）演算法，旨在高效重建高完整度且極低污染的總體基因體組裝基因體（MAGs）。QuickBin 結合了 GC 含量與覆蓋度的空間索引及快速相似性過濾機制，僅在處理模糊合併時使用輕量級神經網路。在 297 個真實總體基因體數據集的基準測試中，QuickBin 成功完成所有運行，且重建的高品質 MAGs 數量超越了其他耗費資源或容易失敗的現有工具。此技術為大規模、可重複的基因體解析總體基因體學研究提供了實用的解決方案。</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2742,32 +2744,32 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42640624/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42642622/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>42642466</t>
+          <t>42640100</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Empirical evidence for gut microbial influence on human brain neurochemistry via the gut-brain axis.</t>
+          <t>Revisiting gut microbiota-driven ammonia metabolism: from disease burden to physiological adaptation.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Molecular psychiatry</t>
+          <t>Gut microbes</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10.1</v>
+        <v>11</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2780,12 +2782,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>The gut microbiome produces metabolites with potential neuroactive properties, many of which act locally within the gut. While preclinical studies suggest these microbial pathways can influence cognitive and emotional processes, human evidence remains limited. This study investigates associations between gut microbiome-derived neuroactive functional potential and in vivo brain neurotransmitter concentrations in healthy young females. Using proton magnetic resonance spectroscopy (¹H-MRS), we quantified GABA and glutamate levels in the dorsolateral prefrontal cortex (dlPFC), anterior cingulate cortex (ACC), and inferior occipital gyrus (IOG). Parallel metagenomic profiling characterised microbial functional potential for pathways related to the synthesis and degradation of GABA, glutamate, short-chain fatty acids (SCFAs), p-cresol, and inositol. Region-specific associations were observed between these microbial pathways and cortical GABA and glutamate levels, including excitatory/inhibitory (E/I) balance, a key marker of neuroplasticity and mental health. Notably, microbial glutamate degradation and inositol synthesis potential were associated with IOG E/I balance, while additional pathways including GABA metabolism, p-cresol production, and SCFA synthesis showed distinct associations across regions. Exploratory analyses also identified links between microbial functional potential and anxiety, depressive symptoms, and sleep quality. Together, these findings provide new human evidence that variation in microbial functional potential corresponds with regional cortical neurochemistry and psychological wellbeing, highlighting the gut-brain axis as a promising avenue for mechanistically informed microbiome-based- interventions.</t>
+          <t>Ammonia homeostasis is governed by interconnected host and microbial pathways, including hepatic ureagenesis, glutamine synthesis, and gut microbiota-mediated urea hydrolysis, proteolysis, and amino acid deamination. Ammonia has historically been viewed primarily as a nitrogenous waste product and neurotoxic molecule, a concept strongly supported by studies of hyperammonemia and hepatic encephalopathy. Impaired hepatic clearance, portosystemic shunting, and enhanced gut-derived ammonia input increase systemic ammonia burden and are linked to neurological dysfunction, muscle wasting, immune dysregulation, and progression of liver disease. In the gut lumen and mucosal environment, however, gut microbes not only generate ammonia but can also reuse ammonia-derived nitrogen for amino acid synthesis, microbial biomass formation, and community nitrogen exchange. Evidence from selected physiological and preclinical models indicates that microbiota-derived ammonia may contribute to nitrogen recycling, microbial community maintenance, enteric neural regulation, or metabolic adaptation under defined conditions. These roles are more context-specific and less broadly established than the pathological effects of systemic hyperammonemia. When epithelial barrier integrity is compromised, hepatic clearance declines, or host buffering reserves are depleted, elevated ammonia can increase epithelial exposure, portal ammonia input, or peripheral blood ammonia. Conversely, evidence that reduced microbiota-derived ammonia contributes to disease remains limited and currently comes mainly from selected animal models. This review re-examines ammonia metabolism from a gut microbiota-centered perspective. We discuss the ecological origins, spatial distribution, exposure characteristics, host-interface effects, and context-specific outcomes of microbiota-derived ammonia in physiology and disease, and discuss how ammonia should be measured, stratified, and targeted in microbial nitrogen metabolism.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>本研究旨在探討健康女性的腸道菌群功能潛力與大腦活體神經傳導物質（GABA與麩胺酸）濃度的關聯。研究結合腦部質子磁共振波譜（¹H-MRS）與總體基因體學分析，發現微生物中參與GABA、麩胺酸、短鏈脂肪酸、對甲酚及肌醇代謝的通路，與大腦特定區域（如背外側前額葉、前扣帶迴與下枕葉）的神經傳導物質水平及興奮/抑制平衡（E/I）具有區域特異性關聯。探索性分析亦顯示微生物功能與焦慮、抑鬱及睡眠品質相關。本研究為腸道菌群影響人類大腦神經化學與心理健康提供了直接的人體實證，為未來開發以微生物為基礎的腦腸軸臨床干預奠定基礎。</t>
+          <t>本綜述重新審視了腸道菌群驅動的氨代謝，探討其從疾病負擔到生理適應的雙重角色。傳統上，氨被視為具神經毒性的代謝廢物，與高氨血症、肝性腦病及肝病惡化密切相關。然而，在腸道微環境中，微生物不僅產生氨，亦能利用氨源氮進行氨基酸合成與群落氮循環，展現出維持腸道神經與代謝適應等生理功能。文章強調，氨的病理與生理效應高度取決於上皮屏障、肝臟清除能力及宿主緩衝儲備。本研究為腸道微生物氮代謝提供了新的生態與臨床視角，並討論了未來如何精確測量及標靶氨代謝的策略。</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2795,32 +2797,32 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42642466/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42640100/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>42648179</t>
+          <t>42642834</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Simultaneous removal of nitrogen, Cu2+, and bisphenol A in a hydrogel-biochar-AQDS immobilized bioreactor with added bicarbonate: Performance and metagenomic insights.</t>
+          <t>Glycosylation in gut-brain communication: from the intestinal barrier and microbiota to immune and neural signaling.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Journal of hazardous materials</t>
+          <t>Gut microbes</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.3</v>
+        <v>11</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2833,13 +2835,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>As the complexity of industrial wastewater pollution continues to increase, the simultaneous removal of nitrogen, metal contaminants, and persistent organic pollutants under low carbon conditions has become a key challenge for biological treatment systems. To address the operational instability and dependence on carbon sources observed in immobilized systems when exposed to copper (Cu2+) and bisphenol A (BPA), the Pseudoalteromonas japonicus strain LY0623 was integrated into a hydrogel-biochar-AQDS composite carrier to construct a multifunctional immobilized biofilm system. Notably, under conditions containing only NaHCO3, the R4 system achieved an NH4+-N removal rate of 89%. Under conditions where Cu2+ and BPA coexist, the R4 system achieved removal of NH4+-N (89%), NO3--N (100%), Cu2+ (85%), and BPA (88%). Sediment characterization confirmed that Cu2+ was immobilized through adsorption, complexation, and microbiologically induced carbonate precipitation (MICP). Metagenomic analysis further indicated that the Pseudomonadota phylum remained the dominant phylum, while functional pathways associated with inorganic carbon assimilation, HNAD nitrogen metabolism, endogenous carbon transformation, biomineralization, electron transfer, and aromatic compound degradation were preserved. By combining ammonia oxidation driven energy production, inorganic carbon utilization, redox mediated processes, and biomineralization, this study provides a highly promising low carbon strategy for treating industrial wastewater containing mixed pollutants.</t>
+          <t>The gut-brain axis is a complex bidirectional communication network linking the gastrointestinal tract and the central nervous system. Its dysregulation is closely associated with a wide range of gastrointestinal, metabolic, and neuropsychiatric disorders. Glycosylation, one of the most prevalent and structurally diverse post-translational modifications of proteins and lipids, is increasingly recognized as a regulator of multiple processes within the gut-brain axis. In this review, we summarize evidence that glycosylation influences several steps of gut-brain communication, including intestinal barrier function, microbial glycan metabolism, immune signaling, enteric and vagal pathways, blood-brain barrier integrity, and neural responses. We distinguish direct mechanistic findings from associative observations and discuss the more limited evidence for brain-to-gut regulation of intestinal glycosylation. In addition, we discuss the potential of glycosylation-targeted nutritional and microbiota-based interventions and highlight emerging opportunities to integrate glycomics with other omics approaches to dissect the complex regulatory networks underlying the gut-brain axis. In conclusion, elucidating how glycosylation shapes signaling along the gut-brain axis may open new avenues for understanding disease pathogenesis and for developing targeted therapeutic strategies.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>本研究旨在解決低碳條件下，工業廢水中氮、重金屬（Cu2+）與雙酚A（BPA）等混合污染物難以同時高效生物降解的挑戰。研究人員將日本假交替單胞菌（*Pseudoalteromonas japonicus*）LY0623菌株整合至水凝膠-生物炭-AQDS複合載體中，構建出新型固定化生物膜系統（R4系統）。
-研究發現，在僅添加碳酸氫鈉（無機碳源）的條件下，該系統成功實現了NH4+-N（89%）、NO3--N（100%）、Cu2+（85%）和BPA（88%）的高效同時去除。總體基因體學分析證實，變形菌門（Pseudomonadota）為優勢菌群，且系統中與無機碳同化、異營硝化-好氧反硝化（HNAD）、生物礦化及芳香族化合物降解相關的功能通路均得到有效維持。本研究結合了氨氧化產能與生物礦化等機制，為混合污染廢水處理提供了一種具前景的低碳生物修復策略。</t>
+          <t>本文探討「腸-腦軸線」（Gut-Brain Axis）中醣基化（Glycosylation）修飾的關鍵調節角色。醣基化作為蛋白質與脂質重要的轉譯後修飾，深刻影響腸道屏障功能、微生物聚醣代謝、免疫訊息傳遞及血腦屏障完整性。研究重點解析了醣基化如何調控腸道與中樞神經系統間的溝通，並區分了機制性證據與相關性觀察。本文不僅強調了醣基化在維繫軸線穩定中的核心地位，更提出透過營養干預與微生物調節，結合多體學（Omics）分析醣基化網絡，將有望為神經精神疾病與代謝性障礙提供創新的診斷與治療策略。</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2849,7 +2850,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42648179/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42642834/</t>
         </is>
       </c>
     </row>
@@ -2909,12 +2910,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>42635401</t>
+          <t>42635406</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fecal filtrate transplantation as salvage therapy for fulminant Clostridioides difficile infection in adult hematological patients during chemotherapy-induced aplasia: a pilot experience.</t>
+          <t>Separating extracellular from intracellular fecal metabolites exposes cross-feeding architecture in the gut: exploring metabolite partitioning and ecological associations.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2927,12 +2928,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>16S, metagenomics</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>3 位成人血液腫瘤患者</t>
+          <t>63 個糞便檢體（來自 63 位健康受試者）</t>
         </is>
       </c>
       <c r="G48" t="b">
@@ -2940,12 +2941,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Fulminant Clostridioides difficile infection (CDI) in patients with hematologic malignancies during chemotherapy-induced aplasia carries high mortality and limited treatment options. Our objective was to evaluate fecal filtrate transplantation (FFT) as a salvage therapy for fulminant CDI during aplasia, and to explore whether donor-recipient phage dynamics may contribute to clinical response. We conducted a single-center, prospective, protocol-defined pilot case series study including consecutive adults with hematologic malignancies, chemotherapy-induced grade-4 aplasia and fulminant CDI, refractory to ≥5 d of high-dose oral vancomycin plus intravenous metronidazole and tigecycline. FFT was prepared from a single unrelated donor using sequential centrifugation and filtration, and administered via nasogastric tube in two doses. The primary outcome was sustained clinical cure, secondary outcomes included survival and adverse events, assessed at +14 and +30 d post-FFT. 16S rRNA gene sequencing was used to assess microbiome compositions, while viral metagenomics and in vitro propagation assays were employed to characterize donor-recipient phageome interactions. Three patients with adverse-risk acute myeloid leukemia and fulminant CDI caused by genetically distinct C. difficile strains received FFT. All patients achieved clinical resolution by day +14, accompanied by improvements in abdominal distension and inflammatory markers. By day +30, one patient died from Pseudomonas aeruginosa septic shock, while two maintained remission with confirmatory follow-up. FFT was well tolerated, with no procedure-related immediate complications or FFT-attributable adverse events. Microbiome and phage profiling revealed heterogeneous responses, including shifts in bacterial community composition, with no clear evidence for a general role of donor-derived phages in CDI resolution. In contrast, we observed induction of prophages harbored by recipient-associated Clostridium species, which may have contributed to decolonization through stress-induced entry into the lytic cycle. FFT was feasible, with rapid sustained CDI resolution in hematologic patients with chemotherapy-induced aplasia. ClinicalTrials.gov identifier NCT07172191. Prospective single-center pilot study of fecal filtrate transplantation (FFT) for fulminant-refractory C. difficile infection in three aplastic adult hematologic patients. FFT was well tolerated, achieved rapid clinical cure, and showed heterogeneous microbiome and phageome modulation, potentially contributing to therapeutic effects.</t>
+          <t>The gut microbiota forms a complex ecosystem through metabolic interdependence (cross-feeding). However, conventional fecal metabolomics typically quantifies only total metabolite pools, making it difficult to distinguish extracellular-enriched metabolite pools from predominantly cell-associated ones, and thus limiting reconstruction of in situ metabolic networks. Here, we quantified fecal metabolites in paired fractions from the same specimen: an undisrupted fraction representing the extracellular pool and a strongly bead-beaten fraction representing the total pool; the intracellular pool was defined as the difference between total and extracellular measurements. Stool samples from 63 healthy individuals were analyzed for short-chain fatty acids, polyamines, and water-soluble vitamins, and the results were integrated with shotgun metagenomic profiles of species composition and functional genes. Vitamins exhibited two distinct behaviors. Adenosylcobalamin (a vitamin B12 coenzyme) was detectable only after disruption, and together with thiamine (B1) and niacin (B3) was classified as an intracellular-retained type (Type 1). In contrast, biotin (B7) and pantothenate (B5) showed higher extracellular proportions (Type 2). Integrative analyses further indicated that Type 1 thiamine was negatively associated with Blautia, consistent with intensive microbial utilization, whereas Type 2 biotin was strongly positively associated with Alistipes, suggesting links to ecological niches shaped by luminal pH and fermentation modes (carbohydrate vs protein fermentation). Fraction-resolved quantification provides a practical operational framework to differentiate extracellular from cell-associated metabolite pools, helping reconcile metagenomic potential with metabolomic reality and enabling deeper inference of cross-feeding structure in the gut ecosystem.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>本研究旨在評估糞便濾液移植（FFT）作為挽救療法，治療化療致免疫不全之血液腫瘤患者合併難治猛爆性艱難梭菌感染（CDI）的療效，並探討供受體間噬菌體的動力學關係。此臨床先導試驗納入3位患者，結果顯示FFT耐受性良好，所有患者在接受治療後14天內均達到臨床緩解。微生態與噬菌體體學分析顯示，臨床症狀的改善並非源於供體噬菌體的直接轉移，而是FFT可能誘發了受體腸道內艱難梭菌的原噬菌體進入溶菌週期，進而促進病原菌清除。本研究證實FFT在此高風險族群中具安全性與可行性，為難治性CDI提供了創新的機制見解與治療選擇。</t>
+          <t>本研究針對腸道微生物的代謝互營機制（cross-feeding）進行探討。傳統糞便代謝組學僅能分析總代謝物，無法區分細胞外與細胞內代謝池，限制了對代謝網絡的解析。研究團隊透過對比未破碎（代表細胞外池）與強力破碎（代表總代謝池）的糞便樣本，成功推算出細胞內代謝物的分佈。針對短鏈脂肪酸、多胺與水溶性維生素的分析顯示，維生素呈現兩類分佈：B12、B1 與 B3 傾向保留於細胞內（Type 1），而 B7 與 B5 則富集於細胞外（Type 2）。結合宏基因組分析發現，Type 1 代謝物與特定細菌（如 *Blautia*）的利用模式顯著相關，Type 2 代謝物則與 *Alistipes* 及腸道生態位特徵（如 pH 值、發酵類型）相關。此方法為區分代謝物空間分佈提供了實用架構，有助於更精確地將宏基因組功能潛力與代謝體現實連結，深入理解腸道微生物的互營生態結構。</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2955,37 +2956,37 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42635401/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42635406/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>42659434</t>
+          <t>42635403</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Blechomonas campbelli from Ctenocephalides felis: in vitro development, thermotolerance, and phylogenetic insights.</t>
+          <t>Baseline gut microbiome ecology predicts long-term fat mass loss after bariatric surgery: evidence for a thrifty Bifidobacterium phenotype.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Memorias do Instituto Oswaldo Cruz</t>
+          <t>Gut microbes</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>metagenomics, others</t>
+          <t>16S, metabolomics</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>340 隻跳蚤（每 4 隻混合為一組，共 85 組檢體），最終獲得 1 個分離株（FL-1）</t>
+          <t>85 位重度肥胖患者及 21 位健康對照組（共 106 名受試者）</t>
         </is>
       </c>
       <c r="G49" t="b">
@@ -2993,12 +2994,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Blechomonas spp. are flea-specific monoxenous trypanosomatids, whose biology, host range, and geographic distribution remain poorly understood, even for species inhabiting ubiquitous cat and dog fleas. To isolate and characterise blechomonads from fleas of domestic dogs in Brazil, focusing on culture growth, morphology, and phylogenetic relationships. Fleas collected from dogs in Sabará, Brazil, were morphologically identified and screened by cultivation. The isolate FL-1 was analysed for temperature-dependent growth, morphology, and phylogeny using 18S rRNA and gGAPDH sequences, including those mined from public metagenomic datasets. Of 340 fleas (four per pool), only one culture tested positive. Growth was optimal at 25ºC, reduced at 30ºC, and absent at 35ºC. Four cell types were revealed, including a predominant "uromonad" stage specialised for attachment and aggregation. Phylogenetic analyses placed the isolate within Blechomonas campbelli and indicated that this species and Blechomonas lauriereadi occur in Ctenocephalides spp. from multiple continents. Blechomonas campbelli exhibits developmental adaptations to the flea gut and limited tolerance to elevated temperatures, constraining its potential to persist in warm-blooded hosts. These findings highlight the value of combining culture-based and in silico approaches to investigate flea-associated trypanosomatids.</t>
+          <t>Bariatric surgery (BS) induces weight loss, but long-term success involves complex host-microbiome interactions. We evaluated the longitudinal impact of BS, microbiome resilience, and Mediterranean Diet (MedDiet) adherence up to 24 months. This prospective observational study included 85 patients with severe obesity undergoing BS and 21 normal-weight healthy controls (HC). MedDiet adherence (PREDIMED) was assessed before surgery. Fecal microbiota (16S-rRNA sequencing) and metabolomics (1H-NMR spectroscopy) were analyzed at baseline and at 1-, 6-, and 12-months post-BS. Clinical outcomes and fat mass, evaluated by bioimpedanciometry, were tracked up to 24 months. At baseline, patients exhibited higher microbial Shannon diversity than controls (p = 0.041), alongside a dysfunctional microbiome and metabolome characterized by a higher Firmicutes/Bacteroidetes ratio and elevated levels of branched-chain amino acids (p &lt; 0.0001). Ordinary Least Squares (OLS) regression analysis revealed that MedDiet adherence and type 2 diabetes status significantly modulated baseline diversity. At 12 months post-BS, the gut ecosystem underwent profound remodeling, characterized by depletion of Bifidobacterium spp. and an increase in butyrate levels (p &lt; 0.0001), establishing a novel adaptive state distinct from HC. Baseline gut ecology significantly conditioned long-term BS outcomes: patients in the highest quartile of baseline Bifidobacterium spp. lost significantly less fat mass at 24 months than those in the lowest (6.6% vs. 13.2%, p = 0.010). High baseline Bifidobacterium abundance paradoxically acts as a "thrifty microbiome," potentially maximizing energy harvest and limiting surgery-induced fat loss. Overall, BS induces adaptive microbiome restoration rather than true normalization, highlighting the potential for precision interventions prior to surgery.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>本研究旨在分離並鑑定巴西犬隻跳蚤中的隱鞭蟲（*Blechomonas*），探討其生長、形態與系統發育。研究從340隻跳蚤中成功分離出FL-1株，經鑑定為 *Blechomonas campbelli*。該菌最適生長溫度為25°C，在35°C下無法存活，並具有四種細胞形態（含利於附著的uromonad階段）。系統發育分析證實該物種廣泛分佈於全球的櫛頭蚤屬中。此發現表明其具有適應跳蚤腸道的發育特徵，但因耐熱性差，難以在溫血宿主體內存活。本研究證實了結合傳統培養與公共總體基因體數據挖掘在研究跳蚤相關寄生蟲上的重要價值。</t>
+          <t>本研究探討減重手術（BS）後腸道微生物群與長期減脂效果的關聯。研究追蹤 85 名患者於術前及術後長達 24 個月的變化，分析發現手術顯著重塑了腸道菌相與代謝環境，特別是雙歧桿菌（*Bifidobacterium*）的耗竭與丁酸鹽的增加。關鍵發現指出，術前高豐度的雙歧桿菌反而成為一種「節儉型表型」，會增加能量攝取效率，導致術後 24 個月的脂肪減少量顯著較少（6.6% 對比 13.2%）。這顯示減重手術並非使微生物組回歸常態，而是引發一種適應性重組。此研究凸顯了術前腸道生態作為預測手術成效生物標記的潛力，對於未來制定精準的術前介入策略具有重要的臨床指導意義。</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3008,37 +3009,37 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42659434/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42635403/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>42635403</t>
+          <t>42659434</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Baseline gut microbiome ecology predicts long-term fat mass loss after bariatric surgery: evidence for a thrifty Bifidobacterium phenotype.</t>
+          <t>Blechomonas campbelli from Ctenocephalides felis: in vitro development, thermotolerance, and phylogenetic insights.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>Memorias do Instituto Oswaldo Cruz</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11</v>
+        <v>2.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>metagenomics, others</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>85 位重度肥胖患者及 21 位健康對照組（共 106 名受試者）</t>
+          <t>340 隻跳蚤（每 4 隻混合為一組，共 85 組檢體），最終獲得 1 個分離株（FL-1）</t>
         </is>
       </c>
       <c r="G50" t="b">
@@ -3046,12 +3047,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Bariatric surgery (BS) induces weight loss, but long-term success involves complex host-microbiome interactions. We evaluated the longitudinal impact of BS, microbiome resilience, and Mediterranean Diet (MedDiet) adherence up to 24 months. This prospective observational study included 85 patients with severe obesity undergoing BS and 21 normal-weight healthy controls (HC). MedDiet adherence (PREDIMED) was assessed before surgery. Fecal microbiota (16S-rRNA sequencing) and metabolomics (1H-NMR spectroscopy) were analyzed at baseline and at 1-, 6-, and 12-months post-BS. Clinical outcomes and fat mass, evaluated by bioimpedanciometry, were tracked up to 24 months. At baseline, patients exhibited higher microbial Shannon diversity than controls (p = 0.041), alongside a dysfunctional microbiome and metabolome characterized by a higher Firmicutes/Bacteroidetes ratio and elevated levels of branched-chain amino acids (p &lt; 0.0001). Ordinary Least Squares (OLS) regression analysis revealed that MedDiet adherence and type 2 diabetes status significantly modulated baseline diversity. At 12 months post-BS, the gut ecosystem underwent profound remodeling, characterized by depletion of Bifidobacterium spp. and an increase in butyrate levels (p &lt; 0.0001), establishing a novel adaptive state distinct from HC. Baseline gut ecology significantly conditioned long-term BS outcomes: patients in the highest quartile of baseline Bifidobacterium spp. lost significantly less fat mass at 24 months than those in the lowest (6.6% vs. 13.2%, p = 0.010). High baseline Bifidobacterium abundance paradoxically acts as a "thrifty microbiome," potentially maximizing energy harvest and limiting surgery-induced fat loss. Overall, BS induces adaptive microbiome restoration rather than true normalization, highlighting the potential for precision interventions prior to surgery.</t>
+          <t>Blechomonas spp. are flea-specific monoxenous trypanosomatids, whose biology, host range, and geographic distribution remain poorly understood, even for species inhabiting ubiquitous cat and dog fleas. To isolate and characterise blechomonads from fleas of domestic dogs in Brazil, focusing on culture growth, morphology, and phylogenetic relationships. Fleas collected from dogs in Sabará, Brazil, were morphologically identified and screened by cultivation. The isolate FL-1 was analysed for temperature-dependent growth, morphology, and phylogeny using 18S rRNA and gGAPDH sequences, including those mined from public metagenomic datasets. Of 340 fleas (four per pool), only one culture tested positive. Growth was optimal at 25ºC, reduced at 30ºC, and absent at 35ºC. Four cell types were revealed, including a predominant "uromonad" stage specialised for attachment and aggregation. Phylogenetic analyses placed the isolate within Blechomonas campbelli and indicated that this species and Blechomonas lauriereadi occur in Ctenocephalides spp. from multiple continents. Blechomonas campbelli exhibits developmental adaptations to the flea gut and limited tolerance to elevated temperatures, constraining its potential to persist in warm-blooded hosts. These findings highlight the value of combining culture-based and in silico approaches to investigate flea-associated trypanosomatids.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>本研究探討減重手術（BS）後腸道微生物群與長期減脂效果的關聯。研究追蹤 85 名患者於術前及術後長達 24 個月的變化，分析發現手術顯著重塑了腸道菌相與代謝環境，特別是雙歧桿菌（*Bifidobacterium*）的耗竭與丁酸鹽的增加。關鍵發現指出，術前高豐度的雙歧桿菌反而成為一種「節儉型表型」，會增加能量攝取效率，導致術後 24 個月的脂肪減少量顯著較少（6.6% 對比 13.2%）。這顯示減重手術並非使微生物組回歸常態，而是引發一種適應性重組。此研究凸顯了術前腸道生態作為預測手術成效生物標記的潛力，對於未來制定精準的術前介入策略具有重要的臨床指導意義。</t>
+          <t>本研究旨在分離並鑑定巴西犬隻跳蚤中的隱鞭蟲（*Blechomonas*），探討其生長、形態與系統發育。研究從340隻跳蚤中成功分離出FL-1株，經鑑定為 *Blechomonas campbelli*。該菌最適生長溫度為25°C，在35°C下無法存活，並具有四種細胞形態（含利於附著的uromonad階段）。系統發育分析證實該物種廣泛分佈於全球的櫛頭蚤屬中。此發現表明其具有適應跳蚤腸道的發育特徵，但因耐熱性差，難以在溫血宿主體內存活。本研究證實了結合傳統培養與公共總體基因體數據挖掘在研究跳蚤相關寄生蟲上的重要價值。</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3061,19 +3062,19 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42635403/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42659434/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>42635406</t>
+          <t>42635401</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Separating extracellular from intracellular fecal metabolites exposes cross-feeding architecture in the gut: exploring metabolite partitioning and ecological associations.</t>
+          <t>Fecal filtrate transplantation as salvage therapy for fulminant Clostridioides difficile infection in adult hematological patients during chemotherapy-induced aplasia: a pilot experience.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3086,12 +3087,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>metagenomics, metabolomics</t>
+          <t>16S, metagenomics</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>63 個糞便檢體（來自 63 位健康受試者）</t>
+          <t>3 位成人血液腫瘤患者</t>
         </is>
       </c>
       <c r="G51" t="b">
@@ -3099,12 +3100,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>The gut microbiota forms a complex ecosystem through metabolic interdependence (cross-feeding). However, conventional fecal metabolomics typically quantifies only total metabolite pools, making it difficult to distinguish extracellular-enriched metabolite pools from predominantly cell-associated ones, and thus limiting reconstruction of in situ metabolic networks. Here, we quantified fecal metabolites in paired fractions from the same specimen: an undisrupted fraction representing the extracellular pool and a strongly bead-beaten fraction representing the total pool; the intracellular pool was defined as the difference between total and extracellular measurements. Stool samples from 63 healthy individuals were analyzed for short-chain fatty acids, polyamines, and water-soluble vitamins, and the results were integrated with shotgun metagenomic profiles of species composition and functional genes. Vitamins exhibited two distinct behaviors. Adenosylcobalamin (a vitamin B12 coenzyme) was detectable only after disruption, and together with thiamine (B1) and niacin (B3) was classified as an intracellular-retained type (Type 1). In contrast, biotin (B7) and pantothenate (B5) showed higher extracellular proportions (Type 2). Integrative analyses further indicated that Type 1 thiamine was negatively associated with Blautia, consistent with intensive microbial utilization, whereas Type 2 biotin was strongly positively associated with Alistipes, suggesting links to ecological niches shaped by luminal pH and fermentation modes (carbohydrate vs protein fermentation). Fraction-resolved quantification provides a practical operational framework to differentiate extracellular from cell-associated metabolite pools, helping reconcile metagenomic potential with metabolomic reality and enabling deeper inference of cross-feeding structure in the gut ecosystem.</t>
+          <t>Fulminant Clostridioides difficile infection (CDI) in patients with hematologic malignancies during chemotherapy-induced aplasia carries high mortality and limited treatment options. Our objective was to evaluate fecal filtrate transplantation (FFT) as a salvage therapy for fulminant CDI during aplasia, and to explore whether donor-recipient phage dynamics may contribute to clinical response. We conducted a single-center, prospective, protocol-defined pilot case series study including consecutive adults with hematologic malignancies, chemotherapy-induced grade-4 aplasia and fulminant CDI, refractory to ≥5 d of high-dose oral vancomycin plus intravenous metronidazole and tigecycline. FFT was prepared from a single unrelated donor using sequential centrifugation and filtration, and administered via nasogastric tube in two doses. The primary outcome was sustained clinical cure, secondary outcomes included survival and adverse events, assessed at +14 and +30 d post-FFT. 16S rRNA gene sequencing was used to assess microbiome compositions, while viral metagenomics and in vitro propagation assays were employed to characterize donor-recipient phageome interactions. Three patients with adverse-risk acute myeloid leukemia and fulminant CDI caused by genetically distinct C. difficile strains received FFT. All patients achieved clinical resolution by day +14, accompanied by improvements in abdominal distension and inflammatory markers. By day +30, one patient died from Pseudomonas aeruginosa septic shock, while two maintained remission with confirmatory follow-up. FFT was well tolerated, with no procedure-related immediate complications or FFT-attributable adverse events. Microbiome and phage profiling revealed heterogeneous responses, including shifts in bacterial community composition, with no clear evidence for a general role of donor-derived phages in CDI resolution. In contrast, we observed induction of prophages harbored by recipient-associated Clostridium species, which may have contributed to decolonization through stress-induced entry into the lytic cycle. FFT was feasible, with rapid sustained CDI resolution in hematologic patients with chemotherapy-induced aplasia. ClinicalTrials.gov identifier NCT07172191. Prospective single-center pilot study of fecal filtrate transplantation (FFT) for fulminant-refractory C. difficile infection in three aplastic adult hematologic patients. FFT was well tolerated, achieved rapid clinical cure, and showed heterogeneous microbiome and phageome modulation, potentially contributing to therapeutic effects.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>本研究針對腸道微生物的代謝互營機制（cross-feeding）進行探討。傳統糞便代謝組學僅能分析總代謝物，無法區分細胞外與細胞內代謝池，限制了對代謝網絡的解析。研究團隊透過對比未破碎（代表細胞外池）與強力破碎（代表總代謝池）的糞便樣本，成功推算出細胞內代謝物的分佈。針對短鏈脂肪酸、多胺與水溶性維生素的分析顯示，維生素呈現兩類分佈：B12、B1 與 B3 傾向保留於細胞內（Type 1），而 B7 與 B5 則富集於細胞外（Type 2）。結合宏基因組分析發現，Type 1 代謝物與特定細菌（如 *Blautia*）的利用模式顯著相關，Type 2 代謝物則與 *Alistipes* 及腸道生態位特徵（如 pH 值、發酵類型）相關。此方法為區分代謝物空間分佈提供了實用架構，有助於更精確地將宏基因組功能潛力與代謝體現實連結，深入理解腸道微生物的互營生態結構。</t>
+          <t>本研究旨在評估糞便濾液移植（FFT）作為挽救療法，治療化療致免疫不全之血液腫瘤患者合併難治猛爆性艱難梭菌感染（CDI）的療效，並探討供受體間噬菌體的動力學關係。此臨床先導試驗納入3位患者，結果顯示FFT耐受性良好，所有患者在接受治療後14天內均達到臨床緩解。微生態與噬菌體體學分析顯示，臨床症狀的改善並非源於供體噬菌體的直接轉移，而是FFT可能誘發了受體腸道內艱難梭菌的原噬菌體進入溶菌週期，進而促進病原菌清除。本研究證實FFT在此高風險族群中具安全性與可行性，為難治性CDI提供了創新的機制見解與治療選擇。</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3114,7 +3115,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42635406/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42635401/</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3160,8 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>本研究利用鄰近連接總體基因體學技術，分析復發性困難梭菌感染（rCDI）與肝硬化兩種腸道菌群失調患者的抗藥性基因（ARGs）與毒力基因。研究發現，與健康對照組相比，兩組患者染色體上的抗藥基因相對豐度皆顯著增加。然而，因長期抗生素暴露驅動的 rCDI 患者，其質體介導的抗藥基因（plasmid-mediated ARGs）豐度亦額外顯著提升。此發現揭示了不同生態壓力（抗生素暴露 vs. 生理病變）如何差異性地塑造腸道抗藥基因組，對於理解抗藥性傳播機制具有重要的科學意義。</t>
+          <t>本研究旨在利用鄰近連接總體基因體學（proximity-ligation metagenomics）技術，解析腸道菌相失衡下，抗藥性基因（ARGs）與毒力基因在宿主染色體及質體（可移動遺傳因子）上的分佈特徵。研究對比了兩種因不同機制引發腸道失衡的臨床族群：長期抗生素暴露的復發性困難梭菌感染（rCDI）患者，以及生理結構改變的肝硬化患者。
+結果顯示，與健康對照組相比，兩組患者體內染色體連結的抗藥性基因豐度均顯著增加；然而，唯有rCDI組另外展現出質體媒介抗藥性基因的增加。此發現揭示了不同的生態壓力會塑造獨特的耐藥基因分佈，對於評估腸道耐藥性傳播具有重要臨床與科學價值。</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3318,7 +3320,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>本研究旨在探究馬奶在天然與人工接種發酵模式下，微生物群落、功能性代謝物與生物活性之間的關聯與機制。結果顯示，相較於天然發酵，接種混合乳酸菌（LAB）發酵能顯著提升馬奶的抗氧化、降血糖（抑制α-葡萄糖苷酶及α-澱粉酶）和降血壓（抑制ACE）之體外活性。雖然接種發酵降低了微生物多樣性，但能顯著富集脂質和有機酸等功能性代謝物。關聯分析證實，植物乳桿菌和粘液乳桿菌的豐度與亞油酸、α-次麻油酸等有益代謝物及功能活性呈顯著正相關。此研究揭示了乳酸菌發酵對馬奶功能特性的代謝調控機制，為開發高附加價值的馬奶發酵產品奠定了科學基礎。</t>
+          <t>本研究旨在探討馬奶在天然與接種發酵過程中，微生物群落、功能性代謝物與生物活性之間的關聯。研究發現，相較於天然發酵，接種混合乳酸菌（LAB）發酵雖顯著降低了微生物多樣性，但能顯著提升馬奶的抗氧化、降血糖及降血壓等體外生物活性，並富集脂質和有機酸等功能代謝物。分析顯示，植物乳桿菌屬與限制乳桿菌屬的豐度與亞麻酸等有益代謝物及活性呈顯著正相關。此研究揭示了乳酸菌發酵提升馬奶功能特性的潛在代謝機制，為開發高附加價值的發酵馬奶產品提供了發酵劑選擇與理論支持。</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3360,7 +3362,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>82 個糞便檢體（包含 41 位第二型糖尿病患者與 41 位健康對照組）</t>
+          <t>82 位受試者的糞便檢體（包含 41 位第二型糖尿病患者與 41 位年齡、性別及 BMI 匹配的健康對照者）</t>
         </is>
       </c>
       <c r="G56" t="b">
@@ -3373,7 +3375,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>本研究透過總體基因體定序（Shotgun metagenomics），探討第二型糖尿病（T2D）患者與健康個體在腸道微生物群落結構上的多層次差異。研究發現，儘管兩組間存在顯著的臨床指標（如空腹血糖）差異，但腸道微生物的宏觀生態架構，包括主要菌門組成與腸型分佈，仍保持高度穩定。差異主要發生在細微的生物學尺度，表現為 42 個物種的豐度改變、Chao1 豐富度下降及群落組成的輕微偏移。雖然功能性路徑分析未達顯著差異，但機器學習模型顯示微生物特徵對區分 T2D 患者具有極高潛力（AUC 達 0.91）。本研究強調 T2D 患者的微生物變異表現為「宏觀結構保存」與「物種細微層面失衡」並存。儘管該模型具有高度鑑別力，但因缺乏外部驗證及藥物干擾等侷限，未來仍需更大規模的長期研究來確認其臨床意義。</t>
+          <t>本研究旨在探討第二型糖尿病（T2D）患者腸道菌相在不同生物層級的變異。透過對82名受試者進行糞便總體基因體定序，發現儘管兩組臨床指標差異顯著，腸道菌群的宏觀生態結構（如門級組成與腸型）仍大致維持。然而，在細微層級則展現顯著變異，包括鑑定出42種豐度差異物種，且T2D組的Chao1豐富度顯著降低。機器學習模型在組內預測T2D的AUC達0.91。此研究揭示了T2D中腸道菌相「宏觀穩定、微觀失衡」的多層次特徵，但亦指出藥物混雜與缺乏外部驗證等限制，未來仍需更大規模的縱向研究。</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3428,7 +3430,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>本研究旨在探討潰瘍性結腸炎（UC）患者腸道微生物群落組裝的生態機制。研究人員應用 Sloan 中性群落模型，分析了健康對照組與 UC 患者的糞便及黏膜樣本，涵蓋微生物基因（MGs）、分子功能（MFs）及多界物種（古菌、細菌、真菌與病毒）。研究發現，儘管腸道微生物組裝主要受隨機過程驅動，但 UC 患者的群落呈現出更高的「中性」特徵，暗示疾病狀態下選擇壓力減弱。此外，糞便樣本較黏膜樣本展現出更強的決定性選擇。分析顯示，UC 導致黏膜環境中微生物群落的選擇狀態發生顯著重組，且主要源於選擇壓力的消失或獲得，而非方向性轉變。這些發現構建了一個多層次的生態框架，揭示了 UC 相關菌群失調的核心特徵在於群落組裝的中性化趨勢及選擇壓力的重塑，為理解發炎性腸道疾病的微生態機制提供了科學依據。</t>
+          <t>本研究旨在探討潰瘍性結腸炎（UC）患者與健康對照組在糞便及黏膜微生物群中，基因、功能和物種層面的生態組裝機制。研究發現，隨機性過程在群落組裝中占主導地位，但UC患者表現出更高比例的中性特徵，顯示疾病狀態下選擇壓力減弱。此外，糞便群落比黏膜群落受到更強的確定性選擇。UC主要藉由改變選擇壓力的強度與存在（而非改變其方向）來重塑微生物群，且此現象在黏膜中尤為顯著。本研究為理解UC相關的菌群失調提供了多維生態框架，指出中性增加與選擇重組為其核心特徵。</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3470,7 +3472,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>59 個陰道檢體（HPV 未接種組 n=26，接種組 n=33）</t>
+          <t>59位患有子宮頸病變的停經前女性陰道檢體（其中26位未接種HPV疫苗，33位已接種疫苗）</t>
         </is>
       </c>
       <c r="G58" t="b">
@@ -3483,7 +3485,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>本研究旨在探討 HPV 疫苗接種與患有子宮頸病變女性之陰道微生物群落結構間的關聯。研究透過鳥槍法總體基因體定序（shotgun metagenomics）分析 59 名停經前女性的陰道檢體，結果發現儘管兩組間的微生物多樣性（Alpha diversity）無顯著差異，但整體的群落結構（Beta diversity）在接種與未接種者間存在統計學上的顯著差異。數據顯示，HPV 疫苗接種與促進「捲曲乳桿菌（*L. crispatus*）優勢型」的陰道菌相具有正相關性。此發現暗示 HPV 疫苗除產生抗體外，可能透過調節陰道微生物環境來增強黏膜免疫保護力。此研究對於理解疫苗如何透過影響宿主微生物組，進而降低 HPV 持續感染與子宮頸病變風險提供了科學依據，未來仍需進一步研究其潛在的免疫調控機制。</t>
+          <t>本研究旨在探討HPV疫苗接種是否與子宮頸病變女性的健康陰道菌相（特別是卷曲乳桿菌 *L. crispatus* 優勢）相關。研究利用總體基因體定序分析59位子宮頸病變女性的陰道檢體。結果顯示，已接種與未接種疫苗者的整體菌落結構有顯著差異：在健康型陰道狀態（CST I）中，90.9%為已接種者；而在菌相失衡型（CST IV）中，則有60%為未接種者，且接種疫苗者體內卷曲乳桿菌相對豐度較高。此發現顯示HPV疫苗接種可能與維持健康、乳桿菌為主的陰道微生態相關，為評估疫苗對黏膜免疫與病變預後的影響提供了新視角。</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3525,7 +3527,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1 個嬰兒案例</t>
+          <t>1名2個月大的男嬰 (n=1)</t>
         </is>
       </c>
       <c r="G59" t="b">
@@ -3538,7 +3540,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>本研究報告了一名 2 個月大嬰兒因腸扭轉及腸壞死術後併發嚴重腹腔內感染的個案。該患兒感染了帶有 *bla*NDM 基因的碳青黴烯類抗藥性肺炎克雷伯菌（CRKP），傳統治療方案受限。臨床醫師透過宏基因體次世代定序（mNGS）精準檢測出致病菌，並在實施外科手術控制感染源的基礎上，給予 Aztreonam-avibactam (ATM-AVI) 藥物治療。結果顯示，患者於給藥後 24 小時內退燒，發炎指標迅速下降，且治療期間未見肝腎毒性。此案例證實，對於臨床治療極為棘手的耐藥性 CRKP 感染，結合外科手術與 ATM-AVI 的標靶藥物治療，在嬰兒患者中具備可行性與安全性，為臨床處理此類多重抗藥性病原體提供了重要的參考依據。</t>
+          <t>本病例報告描述了一名2個月大男嬰在腸道手術後，因攜帶 $bla_{NDM}$ 基因的耐碳青黴烯肺炎克雷伯菌（CRKP）引發嚴重腹腔感染與敗血性休克。透過血液總體基因體次世代定序（mNGS）與手術膿液培養確立診斷。在進行外科手術源頭控制的基礎上，給予目標性氨曲南-阿維巴坦（ATM-AVI）治療14天。患者在用藥24小時內退燒，發炎指標迅速下降並順利拔管，且未出現肝腎毒性。此案例顯示，結合外科清除與藥敏導向的ATM-AVI聯合療法，對嬰幼兒嚴重 $bla_{NDM}$ 陽性CRKP感染具有臨床安全性與療效，為極低齡患者提供了重要的診療參考。</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3580,7 +3582,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>n=1（單一個案報告）</t>
+          <t>1 位 35 歲女性腹膜透析患者（個案報告）</t>
         </is>
       </c>
       <c r="G60" t="b">
@@ -3593,7 +3595,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>本研究探討了一例腹膜透析相關性腹膜炎（PDAP）患者，因反覆出現文化檢測陰性的腹膜炎症狀，最終透過宏基因組次世代定序（mNGS）確診為微小脲原體（*Ureaplasma parvum*）感染。該研究強調了傳統微生物培養技術在偵測特定生長緩慢或特殊細菌時的局限性。透過移除潛在風險因子（子宮內避孕器）並調整抗生素治療方案，患者成功康復。此個案證實，對於臨床上反覆發生、培養陰性的腹膜炎，特別是女性患者，應將 *U. parvum* 列為潛在病原體，且 mNGS 技術在精準診斷罕見及難以培養的病原體上具備極高臨床價值。</t>
+          <t>本研究旨在探討由微小脲原體（*Ureaplasma parvum*）引起的罕見反覆性腹膜透析相關腹膜炎（PDAP）診治。研究報導了一名35歲女性患者在六個月內經歷三次腹膜炎，傳統培養均呈陰性，最終透過腹膜透析液的宏基因組二代定序（mNGS）成功偵測出微小脲原體。在移除潛在風險因子（子宮內避孕器）並給予針對性抗生素治療後，患者完全康復。此案例證實了mNGS在診斷傳統方法難以檢出的病原體時的關鍵作用，並指出對於培養陰性的反覆性腹膜炎患者（特別是裝有避孕器的女性），應警惕微小脲原體感染，並據此提出臨床診斷與治療流程。</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">

--- a/papers_database.xlsx
+++ b/papers_database.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16S, others</t>
+          <t>16S</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -514,7 +514,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>本研究旨在探討牙周病中揮發性硫化物（VSCs）代謝、微生物群落與局部免疫反應之間的複雜交互作用。研究團隊分析了五種口腔生態位，結合硫化物濃度直接測量、功能性半胱胺酸/甲硫胺酸降解分析、16S rRNA 擴增子定序及細胞激素定量。結果顯示，牙周炎患者的齦下硫化氫（H2S）濃度顯著升高，且與微生物組成改變及特定發炎因子（如 IL-1β、IL-8）呈現高度相關。研究指出，硫代謝呈現明顯的空間組織性，並隨疾病嚴重程度動態調整，其中齦下菌斑被鑑定為硫化物代謝的核心區域。本研究不僅證實齦下 H2S 可作為監測微生物失調與發炎狀況的功能性標記，亦為未來開發用於牙周病即時監測（Point-of-care）的感測技術或診斷工具提供了科學依據。</t>
+          <t>本研究旨在探討牙周病不同階段中，五個口腔微生態棲地（唾液、舌苔、齦下、齦上及牙縫菌斑）的硫代謝、微生物群與局部免疫反應之關聯。研究發現，齦下硫化氫（H2S）濃度在牙周病患者中顯著升高，且與菌群結構移形及細胞激素變化密切相關，其中齦下與舌苔生物膜具有最強的H2S產生效率。網路分析更揭示了揮發性硫化物（VSCs）、細胞激素與特定菌屬（如 *Fusobacterium* 與 *Prevotella*）之間存在棲地特異性的耦合關係。本研究證實齦下H2S可作為整合微生態失調與發炎反應的功能性指標，為未來開發非侵入性牙周病即時監測工具（如氣體感測器）奠定了重要科學基礎。</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>本研究旨在探討海洋暖化導致海帶林流失並被草皮藻取代，是否會影響礁區微生物結構、功能及營養循環。研究整合總體基因體學與非靶向代謝組學，發現海帶林的崩潰顯著改變了礁區微生物群落組成及生化機制，使海帶與草皮藻主導的礁區呈現出截然不同的代謝組特徵，以及由微生物驅動的元素利用與轉化模式。研究證實微生物在維持海帶林生態系功能中扮演關鍵角色，並揭示人類活動引起的海洋暖化會對微生物介導的化學作用產生級聯效應，這對評估沿海碳儲存與營養再生具有重要科學價值。</t>
+          <t>本研究旨在探討氣候暖化導致海帶林被低矮草皮狀藻類取代後，是否會改變礁區微生物的結構、功能（如碳與養分循環）。研究團隊結合總體基因體學與非標靶代謝組學技術，證實海帶林的流失會顯著改變礁區微生物群落組成及其生化機制，進而在海帶與草皮狀藻類主導的礁區中，產生截然不同的代謝組及微生物驅動之元素利用與轉化模式。此結果表明微生物在形塑海帶林生態系功能中扮演關鍵角色，並證實人類活動引起的海洋變暖會對微生物介導的化學作用產生級聯效應，進而對沿岸碳儲存與養分再生帶來深遠影響。</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（文章僅提到使用全球性數據集與分離菌株進行分析，未具體標示樣本總數）</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -624,7 +624,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>本研究旨在探討南極極端且隔離的土壤環境中，微生物是否具有特有性與在地適應性。研究團隊以廣泛分佈的節桿菌屬（*Arthrobacter*）為對象，分析全球總體基因體數據並進行菌株基因組比較。結果發現，高達90%的南極菌株僅存在於該大陸（具特有性），且其基因組特徵與環境耐受性皆展現出對南極極端環境的獨特適應力。此發現證實了極地微生物的在地適應與地理隔離分布，對理解極端環境下的微生物演化與生態學具有重要科學意義。</t>
+          <t>本研究旨在探討南極土壤微生物是否因地理隔離與極端氣候而演化出獨特的在地適應性。研究聚焦於全球分佈廣泛的「節桿菌屬」（*Arthrobacter*），透過分析全球土壤宏基因組數據，發現南極土壤中 90% 的節桿菌菌株皆為南極特有種，證實了該地區微生物的高度地方性（endemism）。進一步透過菌株培養表型分析與基因體比較，研究發現南極菌株具備特定的基因組特徵與環境耐受力，使其能適應南極寒冷且乾燥的極端環境。此發現不僅揭示了微生物在地理隔離下的演化模式，更證實了南極微生物群落具有獨特的在地適應機制，對於理解微生物的全球擴散限制與極地生態系統的演化歷程具有重要科學意義。</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>本文為針對發表於《Science of The Total Environment》期刊之論文《木質纖維素廢棄物的環境影響及其作為智慧載體的有效開發——推動更綠色、更環保的生物催化系統》的撤回聲明（Retraction notice）。由於原文摘要欄位顯示為「無提供摘要」，且該文獻本質上為一則學術撤回通告，非具體的研究性論文，因此無法獲取其實際的研究技術、樣本數量與具體實驗結果。該公告的主要科學意義在於維護學術研究的嚴謹性與文獻資料庫的正確性。</t>
+          <t>本文為學術期刊《Science of the Total Environment》針對 2020 年刊登之文章「Environmental impact of lignocellulosic wastes and their effective exploitation as smart carriers - A drive towards greener and eco-friendlier biocatalytic systems」所發布的正式撤稿聲明。由於原始研究內容已被撤回，該聲明並未包含任何實驗數據、樣本分析或科學發現。撤稿通常源於作者發現數據錯誤、倫理問題或研究結論存在不可重現的重大瑕疵，因此該文不具備生物醫學參考價值。</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>metagenomics, others</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>本文件為一篇撤銷聲明（Retraction notice），針對先前發表於《Science of The Total Environment》之系統性文獻回顧論文進行撤回。該原論文主題旨在探討海水養殖廢水中的抗生素與抗藥性基因（ARGs），並分析利用微藻-細菌共生系統（MBSS）去除抗生素的效果，以及透過總體基因體學（metagenomics）技術對 ARGs 進行特徵分析。由於本篇僅為撤回公告且無提供摘要，故無法獲知具體的研究數據、樣本數或撤回之具體原因。此公告的發表有助於維護學術界的文獻品質與科學誠信。</t>
+          <t>本文為一篇撤稿聲明，所撤回的原論文為一項系統性文獻回顧。該原研究之核心目的在於探討海水養殖廢水中抗生素的殘留情形，並評估「微藻-細菌共生系統（MBSS）」去除抗生素的效果，同時利用總體基因體學（metagenomics）技術來表徵抗生素耐藥基因（ARGs）的分布特徵。由於本公告僅為撤稿通知且未提供原文摘要，因此無法取得具體的研究樣本數量與實驗發現。此撤稿之發佈主要在於維護學術文獻的嚴謹性、準確性與科學誠信。</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>4種微塑料材料（AP、PE、PP、PS）（具體重複樣本數量未提及）</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -789,8 +789,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>本研究旨在探討纖維素/聚酯混合微塑料（如無塵紙 AP）與傳統純合成塑料（PE、PP、PS）在厭氧消化系統中，對塑料圈（plastisphere）微生物群落及抗生素耐藥基因（ARGs）傳播風險的影響。
-研究發現，AP 因具備纖維結構與可生物降解的纖維素，擁有最高的生物膜生物量。多體學分析顯示，傳統塑料主要富集多重耐藥基因並引發較高的細胞氧化壓力；而AP則選擇性富集多黏菌素耐藥基因（Mcr-5.1 與 Mcr-5.2），且其耐藥基因與可移動遺傳因子（MGE）的共定位率高達12.7%，具備最高的耐藥性傳播風險。本研究證實聚合物成分是決定耐藥組裝的關鍵，強調未來污泥耐藥風險評估應納入此類混合材料。</t>
+          <t>本研究旨在評估纖維素/聚酯混合微塑料（如無塵紙 AP）在厭氧消化系統中，相較於傳統合成微塑料（PE、PP、PS）對「塑料圈」病原菌與抗藥性基因（ARGs）的傳播風險。研究顯示，AP 因具纖維結構及可利用的纖維素，其生物膜量和胞外聚合物最高。不同於合成微塑料主要富集多重抗藥基因，AP 選擇性富集多黏菌素抗藥基因（Mcr-5.1/5.2），且其抗藥基因與行動遺傳元件的共定位率達 12.7%，具最高的抗藥性風險。本研究證實聚合物成分是形塑塑料圈抗藥性的關鍵，強調污泥抗藥性評估應特別納入混合型微塑料。</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,7 +844,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>本研究探討白洋淀濕地岸邊帶水位波動對溫室氣體（GHG）排放及微生物碳氮循環的影響。研究發現，高水位條件可顯著降低 CO2 與 N2O 的通量。透過宏基因組組裝基因體（MAG）分析，研究確認 Methylococcaceae、Methanosarcinaceae 與 Anaeromyxobacteraceae 為調控甲烷與氧化亞氮排放的關鍵微生物群落。特別是發現一類具備完整硝酸鹽還原與甲烷氧化耦合路徑的 Methylomirabilales 類群，其豐度隨水位升高而下降，顯示此類微生物在緩解溫室氣體排放中扮演重要角色。本研究揭示了水文管理對濕地微生物碳氮代謝的調控機制，為利用水文調節策略減緩濕地溫室氣體排放提供了關鍵科學依據與潛在的微生物標的。</t>
+          <t>本研究探討白洋淀湖泊消落帶在水位波動下，溫室氣體（GHG）排放與碳氮耦合過程的時空動態及微生物驅動機制。研究發現，高水位條件能顯著降低二氧化碳（CO2）和一氧化二氮（N2O）的排放通量。水位變化是形塑微生物群落結構的關鍵，其中Methylococcaceae、Methanosarcinaceae與Anaeromyxobacteraceae分別調控甲烷（CH4）和N2O的動態。此外，研究重構出一個高質量的Methylomirabilales總體基因體組裝基因體（MAG），該菌具備硝酸鹽還原與甲烷氧化耦合的完整途徑，其豐度與水位呈負相關，證實此類碳氮耦合細菌有助於減少溫室氣體排放。本研究為透過水文管理減緩濕地溫室氣體排放提供了關鍵的理論依據與微生物靶點。</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -882,12 +881,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5, 2</t>
+          <t>metagenomics, others</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>未提及（研究使用現有的參考基因體與總體基因體資料庫進行生物資訊學分析，未明確列出特定樣本總數）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -900,8 +899,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>本研究旨在解決傳統細菌抗噬菌體防禦系統識別方法的效率限制。研究團隊開發了一套生物資訊分析流程，利用「小型絲胺酸重組酶（small serine recombinases）」作為基因標記，以搜尋並識別細菌基因體及總體基因體中已知與未知的抗噬菌體防禦系統。
-透過基因連鎖分析、轉錄共表現預測及蛋白質結構域統計，研究證實小型絲胺酸重組酶與多種防禦系統在基因組結構上高度相關，能作為廣泛篩選多種細菌門類的有效「誘餌」。實驗驗證成功發現 KAP P-loop NTPases 與抗噬菌體結構域的融合，並確立了原核生物 Schlafen 蛋白作為新型抗噬菌體防禦系統的地位。此研究提供了一種強大且高效的挖掘工具，對於深入理解細菌如何抵抗噬菌體感染具有重要科學意義，並有助於推動噬菌體療法的進一步發展。</t>
+          <t>本研究開發了一套生物資訊分析流程，利用「小型絲氨酸重組酶（small serine recombinases）」作為基因標記，以搜尋已知及未知的細菌抗噬菌體防禦系統。團隊透過檢索參考基因體與總體基因體，證實該重組酶與防禦系統具備強烈的遺傳連鎖，並藉此成功鑑定出 KAP P-loop NTPases 相關結構域和原核 Schlafen 蛋白質為新型抗噬菌體防禦系統。此發現證實小型絲氨酸重組酶是跨菌門尋找防禦系統的可靠標記，對理解細菌免疫機制及推動噬菌體療法具有重要科學價值。</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -956,7 +954,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>本研究旨在探討新熱帶區《Sabethes》屬蚊子體內的病毒多樣性，特別聚焦於《Spiciviridae》病毒科。研究人員透過總體基因體學（metagenomics）分析了 19 個蚊子樣本池，成功鑑定出兩種隸屬於《Spiciviridae》的新型病毒，暫定名為 Sabethes virus 1 (SV1) 與 Sabethes virus 2 (SV2)。系統發生學分析顯示，這些新病毒與現有物種在 RNA 依賴性 RNA 聚合酶（RdRp）序列上具有顯著的遺傳差異（&gt;20%）。此發現不僅擴展了科學界對《Spiciviridae》基因體多樣性的理解，更指出該科病毒的演化複雜度遠超目前的分類範疇，暗示存在尚未被國際病毒分類委員會（ICTV）所定義的新分類群，對病毒分類學與蟲媒病毒的演化研究具有重要科學意義。</t>
+          <t>本研究旨在探討新熱帶區《Sabethes》屬蚊子體內的病毒多樣性，特別針對 Ghabrivirales 目下的 Spiciviridae 病毒科進行分析。透過宏基因組定序技術，研究團隊從 19 個蚊子樣本池中發現了兩種新型病毒，暫命名為 Sabethes virus 1 (SV1) 與 Sabethes virus 2 (SV2)。系統發生學分析顯示，這兩種病毒在 RNA 依賴性 RNA 聚合酶 (RdRp) 蛋白序列上，與已知病毒具有超過 20% 的遺傳差異。此發現不僅擴展了 Spiciviridae 的基因組多樣性，更顯示現行病毒分類可能低估了該病毒科的演化複雜度，為國際病毒分類委員會 (ICTV) 未來的分類架構提供了重要的科學依據。</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -998,7 +996,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（文中僅提及針對兩種蜜蜂物種進行分析，未具體標示樣本總數）</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -1011,7 +1009,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>本研究透過宏基因組定序（shotgun metagenomics），深入探討東方蜜蜂（*Apis cerana*）與西方蜜蜂（*Apis mellifera*）腸道內細菌與真菌群落的結構差異。研究發現，蜜蜂腸道微生物組具備高度的宿主特異性，其中細菌多樣性在西方蜜蜂中顯著較高，而真菌多樣性則兩者相當。分析指出，儘管真菌組成以子囊菌門為主，但細菌與真菌的共現模式呈現宿主專一性。功能預測顯示，西方蜜蜂的細菌群落展現出更強的碳水化合物代謝與營養循環能力。此研究揭示了宿主種類如何驅動跨界（細菌與真菌）微生物組的結構與功能分化，對於理解蜜蜂腸道微生物的生態功能及其與宿主的演化關係具有重要科學意義。</t>
+          <t>本研究透過宏基因體定序（Shotgun metagenomics），深入探討東方蜜蜂（*Apis cerana*）與西方蜜蜂（*Apis mellifera*）腸道內細菌與真菌群落的組成與功能差異。研究發現，儘管細菌多樣性在不同蜂種間存在顯著差異，但兩者的真菌群落多樣性相當。分析顯示，兩種蜜蜂的細菌與真菌群落結構呈現強烈的宿主特異性，顯示宿主物種為微生物組成的主要驅動力。此外，透過 LEfSe 分析發現兩者在關鍵分類群（如西方蜜蜂的酵母菌與東方蜜蜂的擔子菌門）與代謝功能（如碳水化合物代謝）上具有顯著差異。本研究不僅填補了蜜蜂腸道真菌群落研究的空白，更揭示了跨界（細菌-真菌）的交互作用機制，對理解蜜蜂共生微生物的生態適應與演化具有重要的科學意義。</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1053,7 +1051,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>131 位女性的術前糞便檢體（包含 23 例良性、47 例高風險/非侵襲性、61 例惡性乳腺疾病患者）</t>
+          <t>131 個糞便檢體（包含良性疾病 23 例、高風險/非侵入性疾病 47 例、惡性腫瘤 61 例）</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -1066,7 +1064,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>本研究旨在探討罹患良性、高風險/非侵襲性及惡性乳腺疾病女性中，身體質量指數（BMI）、乳房密度與腸道菌群多樣性、組成及功能代謝途徑的關聯。研究發現，患者腸道菌群的α多樣性與BMI呈負相關，且β多樣性因疾病類型和BMI而異。高BMI患者體內富集了*Dorea*、*Blautia*和*Streptococcus*等菌屬；功能分析顯示，與NAD生物合成、葉酸及芳香族胺基酸代謝相關的基因途徑豐度顯著增加，其中*Blautia*可能透過色胺酸代謝與NAD合成產生關聯。本研究揭示了肥胖相關腸道菌群與乳腺疾病的潛在聯繫，為未來研究肥胖如何透過微生物群驅動乳腺癌發展奠定了科學基礎。</t>
+          <t>本研究探討體重指數（BMI）與乳房疾病患者腸道微生物組成及功能路徑的關聯。透過對 131 名術前女性患者進行淺層總體基因體定序，研究發現腸道菌相多樣性與 BMI 呈負相關。BMI 較高的受試者在細菌分類上顯現 *Dorea*、*Blautia* 及 *Streptococcus* 屬的富集；在功能路徑上，與 NAD 生物合成、葉酸及芳香族胺基酸代謝相關的基因表現顯著增加。特別是 *Blautia* 菌屬可能透過色胺酸代謝連結至 NAD 生物合成路徑。此研究結果證實 BMI 與腸道微生物特徵的顯著差異，並提出肥胖相關腸道菌群可能參與乳癌發展的機制假設，為未來針對該領域的病理研究提供了科學依據。</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1103,12 +1101,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>metagenomics, metabolomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>10 對母嬰（共 40 個唾液與牙菌斑檢體）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -1121,7 +1119,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>本研究透過前瞻性世代研究，探討嬰幼兒口腔生態系在 1 至 2 歲期間的縱向發展。研究利用宏基因組學與非標記代謝組學技術，分析 10 對母嬰的唾液及牙菌斑樣本。結果顯示，嬰兒的口腔微生物組、病毒組及代謝組隨年齡增長出現顯著演替，且代謝變化以牙菌斑最為劇烈，涵蓋能量、胺基酸、核苷酸及脂質代謝途徑。相比之下，母親的代謝特徵相對穩定。研究並發現口腔內的細菌與病毒存在跨界交互作用，且隨年齡增長而減弱。此研究揭示了嬰幼兒口腔微生態的動態建構過程，不僅提供口腔微生物群落演替的基礎數據，更對於理解早期口腔發育及其對代謝健康的長期影響具有重要的臨床科學參考價值。</t>
+          <t>AI 分析失敗，請參考英文原文。</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1158,12 +1156,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>metagenomics, metabolomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>未提及（文中僅提及隨機分組及檢體類型，未提供具體樣本總數）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G14" t="b">
@@ -1176,7 +1174,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>本研究探討太子參皂苷（RPS）作為雞隻雞毒黴漿菌（MG）減毒疫苗（MGAV）佐劑的增效機制。研究發現，RPS 不僅能顯著提高 MG 特異性抗體水平與免疫調節細胞因子表現，還能改善氣管黏膜的完整性。透過宏基因組學與代謝組學分析，證實 RPS 能富集呼吸道中的 *Lactobacillus sp. UMNPBX13*，進而促進磷脂醯膽鹼（PC）的代謝產出。PC 與 MGAV 的協同作用能增強黏膜免疫力。此研究闡明了 RPS 通過重塑呼吸道微生物群及其代謝物來優化疫苗效力的機制，為家禽疫苗研發與黏膜免疫增強策略提供了重要的科學依據。</t>
+          <t>AI 分析失敗，請參考英文原文。</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1213,12 +1211,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>metagenomics, others (基因功能驗證與酵素活性分析)</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1,578 個全球人類腸道總體基因體樣本</t>
+          <t>1,578 個人類腸道總體基因體 (human gut metagenomes)</t>
         </is>
       </c>
       <c r="G15" t="b">
@@ -1231,8 +1229,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>本研究探討人類腸道微生物群中「漆酶」（laccase）對氟化化合物的生物轉化潛力。研究團隊分析了來自全球、橫跨狩獵採集部落至現代化城市人口共 1,578 個腸道總體基因體數據，發現漆酶編碼基因在人類腸道中廣泛分佈，且其豐度與多樣性與居住地的都市化程度顯著相關。
-實驗部分，研究人員成功異源表達了 8 種腸道來源的漆酶，其中 6 種具備酵素活性。特別是來自韋榮氏球菌屬（*Veillonella*）的漆酶，被證實能有效分解農藥（如賽氟蟎、扶吉胺）及工業化學品（雙酚 AF）。此發現揭示了人類腸道微生物組中隱藏的酵素功能，對於理解腸道菌群如何代謝外源性化學物質、減輕環境毒物對人體的潛在危害，具有重要的臨床與環境毒理學意義。</t>
+          <t>本研究旨在探討人類腸道菌群中漆酶（laccases）對環境氟化化合物的生物轉化潛力。研究分析了全球不同城市化程度的1,578個腸道總體基因體，發現漆酶同源基因廣泛存在，且其豐度與系統發育多樣性與城市化程度呈顯著正相關。實驗進一步異源表達了8種源自腸道總體基因體的漆酶，其中6種具備活性；源自*Veillonella*菌的漆酶能有效降解特定農藥（cyflumetofen、fluazinam）及工業化學品（雙酚AF）。此研究結合全球總體基因體數據與活性篩選，證實了腸道菌群酶降解農業與工業化學污染物的潛力，具備重要的環境健康與科學意義。</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1287,8 +1284,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>本研究針對低碳氮比（C/N）廢水處理的挑戰，開發了一種整合發酵聚磷菌（PAOs）與微藻細菌共生體（MBC）的原位發酵同步硝化反硝化除磷（F/P-SNDPR）系統。實驗證實，透過優化 16 小時黑暗與 8 小時光照的週期，系統在無需外部碳源或機械曝氣下，氮與磷的去除率分別達 83% 與 95% 以上，並顯著降低了污泥產量與淨二氧化碳排放。
-透過總體基因體學分析，研究識別出 *Candidatus Phosphoribacter* 為關鍵發酵菌株，其功能基因（如 *LivFGHMK* 與 *Pta*）在黑暗期產生的揮發性脂肪酸（VFA），有效支持了除磷與反硝化菌群的活性。此研究揭示了微生物群落透過特定功能基因（如 *Ppk*, *Ppx*, *NirS*, *NirK* 等）進行代謝協作的機制，為工業廢水處理提供了一種具高度節能與環境友善性的低碳解決方案。</t>
+          <t>本研究開發了一種結合原位發酵與光合同步硝化-反硝化除磷的系統（F/P-SNDPR），旨在解決低碳氮比（C/N）廢水處理中常見的過量污泥與能耗問題。研究發現，在優化的16小時黑暗與8小時光照循環下，該系統展現了卓越的除氮（&gt;83%）與除磷（&gt;95%）效率，且顯著降低了污泥產量。宏基因體分析顯示，*Candidatus Phosphoribacter* 是關鍵的發酵菌株，透過黑暗期的發酵作用產生揮發性脂肪酸（VFA），進而支持除磷菌（*Candidatus Accumulibacter/Competibacter*）的代謝與除磷脫氮功能。此技術無需額外添加碳源或機械曝氣，為低碳廢水處理提供了一種具備經濟效益與環境永續性的綠色策略。</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1378,12 +1374,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>16S, metabolomics (基於文中提到 chromatographic complexity 進行代謝物分析)</t>
+          <t>16S</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>未提及 (文中僅提及採樣與分析結果，未明確說明樣本的具體數量或重複次數)</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G18" t="b">
@@ -1396,7 +1392,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>本研究旨在評估添加大型與微量營養素之本土森林微生物群與酸性乳清生物肥料的理化及生物特性。研究發現，經過厭氧發酵與營養強化後的生物肥料，其化學環境發生顯著變化，包括pH值的穩定與氧化還原電位的改變。透過16S rRNA擴增子定序分析顯示，經強化後的生物肥料（MNS）相較於未強化組，展現了更高的菌群豐富度與分類多樣性，且兩者皆以乳酸菌相關屬與梭菌屬為優勢菌種。此外，層析分析亦證實強化處理提升了營養轉化的複雜度。整體而言，利用本土微生物群進行礦物發酵能優化生物肥料的微生物組成，並有望提高養分的生物可利用性，為開發永續農業肥料提供了科學依據。</t>
+          <t>本研究旨在評估由天然森林微生物與酸乳清製成、並富含大與微量營養素之生物肥料在發酵過程中的化學、生物及微生物群落特徵。研究發現，發酵顯著改變了系統的 pH 值與氧化還原電位（ORP）。16S rRNA 擴增子定序分析顯示，相較於未富集營養的原始肥料，模型營養液（MNS）展現出更高的微生物物種豐富度與多樣性，但兩者皆由乳酸菌相關屬與梭菌屬（Clostridium）等發酵菌群主導。本研究證實，透過天然微生物發酵礦物能改善化學環境、提升微生物多樣性並促進營養轉化，具備提高植物營養生物有效性的潛力，對推動永續農業發展具有重要科學意義。</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1571,17 +1567,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>42665077</t>
+          <t>42664608</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Metagenomic Characterization of Potential Exposure to Genetic Hazards at the Interface Between Grazing Livestock and Przewalski's Gazelle.</t>
+          <t>Application-dependent effects of tea waste biochar on PFAS mobility and N2O and CH4 emissions in agricultural soil.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Environmental pollution (Barking, Essex : 1987)</t>
+          <t>Waste management (New York, N.Y.)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1592,7 +1588,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（僅說明使用盆栽模擬系統「per pot」，未提及具體樣本或盆栽數量）</t>
         </is>
       </c>
       <c r="G22" t="b">
@@ -1600,12 +1596,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Livestock and endangered wildlife increasingly share grazing landscapes, yet the sources, mobility-associated contexts, and bacterial hosts of livestock-associated genetic hazards in wildlife microbiomes remain poorly resolved. We analyzed metagenomes from yak, Tibetan sheep, Przewalski's gazelle, and local topsoil within an Acquired Genetic Risk (AGR) conceptual framework integrating genetic hazard burden, compositional source attribution, mobility-associated evidence, and bacterial genomic context. MRGs and Rank I and Rank III ARGs were more abundant in livestock than in Przewalski's gazelle, whereas VF abundance was highest in yak. FEAST attributed approximately 64% of the Przewalski's gazelle resistome composition to the two livestock source profiles, less than 1% to sampled topsoil, and approximately 36% remained unassigned. MGE profiles were associated with ARGs, MRGs, and VFs, while tnpA ranked highest in random forest models and was associated with total ARG abundance (R2 = 0.618). Short-read contigs containing hazard genes and MGE markers provided localized mobility-associated sequence context. Genome-resolved analysis identified distinct bacterial contexts: TS.Bin143, an Escherichia coli MAG from Tibetan sheep, contained ARGs, MRGs, VFs, tnpA, and IS91, whereas PG.Bin275, a Hylemonella sp. MAG from Przewalski's gazelle, contained tnpA. These findings extend wildlife resistome assessment beyond abundance profiling toward source attribution, mobility-associated sequence context, and bacterial host resolution, supporting multilevel surveillance of genetic hazard exposure at livestock-wildlife interfaces.</t>
+          <t>Per- and polyfluoroalkyl substances (PFAS) in agricultural soils can migrate into crops and may alter soil greenhouse gas emissions, yet remediation strategies rarely address these risks simultaneously. This study evaluated tea waste biochar (TWB) produced at 400, 500, and 600 °C and applied at 5-20 g per pot by whole-soil mixing or surface-layer placement in a simulated PFAS-contaminated soil-leachate-plant system. Perfluorooctane sulfonate (PFOS) and perfluorooctanoic acid (PFOA) distributions, nitrous oxide (N2O) and methane (CH4) fluxes, and microbial responses were examined. TWB produced at 500 °C showed the most favorable combination of pore accessibility, surface hydrophobicity, and interfacial charge, with material-associated PFOS and PFOA enrichments of 0.12 and 0.57 μg/g, respectively. Whole-soil mixing with TWB-500 lowered soil and leachate PFAS levels and reduced PFAS concentrations in plant shoots by approximately 36% relative to the contaminated control. TWB treatments also reduced cumulative N2O emissions and enhanced net CH4 uptake. Metagenomic analysis showed lower relative abundances of genes associated with nitrogen fixation, ammonia oxidation, and several N2O-producing pathways, whereas CH4-cycling genes responded differently to the two application methods. Organic fluorine transformation genes were not enriched, indicating that PFAS control mainly resulted from physicochemical retention rather than enhanced microbial defluorination. Overall, TWB-500 can integrate PFAS stabilization with greenhouse gas management, but the optimal placement depends on the remediation objective: whole-soil mixing favors PFAS immobilization, whereas surface-layer application provides greater greenhouse gas mitigation.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>本研究旨在評估放牧家畜與瀕危野生普氏原羚接觸介面上的遺傳危害（如抗藥性基因 ARG、金屬耐受基因 MRG 與毒力因子 VF）暴露風險。研究利用總體基因體學分析氛牛、藏羊、普氏原羚及當地表土，結果顯示家畜體內的 MRG 和高風險 ARG 豐度顯著高於普氏原羚。來源追蹤分析（FEAST）指出，普氏原羚約 64% 的抗藥組組成可歸因於這兩種家畜，僅不到 1% 來自土壤。此外，研究透過基因組解析定位了攜帶危害基因與移動遺傳因子的細菌宿主。本研究不僅闡明了遺傳危害的來源與傳播關聯，也為野生動物與家畜接觸介面的多層級生物安全監測提供了重要科學依據。</t>
+          <t>本研究旨在評估茶渣生物炭（TWB）在模擬的PFAS污染土壤-滲濾液-植物系統中，對於抑制全氟和多氟烷基物質（PFAS）遷移及減少溫室氣體（N2O和CH4）排放的雙重效應。研究發現，在500 °C下製備的TWB-500效果最佳。若將其均勻混合於全土中，可使植物地上部的PFAS濃度降低約36%，並顯著降低土壤和滲濾液中的PFAS含量。此外，TWB處理還減少了N2O累積排放並促進CH4淨吸收。總體基因體學分析顯示，與氮循環相關的基因豐度有所下降，解釋了N2O排放減少的機制；而有機氟降解基因並未富集，證實PFAS的控制主要源於物理化學阻控而非微生物去氟作用。此研究證明TWB-500能有效整合PFAS固化與溫室氣體管理，且施用方式（全土混合或表層施作）可依環境整治優先目標進行客製化調整。</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1615,37 +1611,37 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42665077/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42664608/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>42665998</t>
+          <t>42665338</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Agathobacter rectalis suppresses colorectal tumorigenesis via an epigallocatechin-SREBF2 axis controlling cholesterol metabolism.</t>
+          <t>PREVENT 1, a nationwide Swedish infant cohort for longitudinal gut microbiome profiling and early-life health outcomes: cohort profile.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>BMJ open</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11</v>
+        <v>2.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>metagenomics, metabolomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>253 位嬰兒（收集 253 份基線糞便檢體，其中 250 位提供至少 2 次檢體，241 位提供全部 3 次檢體）</t>
         </is>
       </c>
       <c r="G23" t="b">
@@ -1653,12 +1649,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Beneficial effects of the gut commensal Agathobacter rectalis (Ar) are reported in diseases, yet its role in colorectal cancer (CRC) remains unclear. Here, metagenomic analysis revealed consistent fecal Ar depletion across CRC cohorts. In Apc min/+ mice, Ar inhibited colon tumorigenesis, reducing tumor number and volume versus E. coli and PBS controls. LC-MS/MS metabolomics showed decreased fecal cholesterol and altered lipid/cholesterol pathways after Ar treatment. In vitro, Ar-conditioned medium suppressed CRC cell growth, clonogenicity, migration, and cell cycle progression. LC-MS/MS identified (-)-epigallocatechin (EGC) as an Ar-derived metabolite absent in control bacteria. EGC recapitulated Ar-mediated anti-CRC effects in vitro and in vivo, with metabolic changes linked to lipid/cholesterol pathways. Transcriptomics showed that EGC suppressed SREBP signaling, cholesterol metabolism, and MAPK pathways. Mechanistically, EGC reduced nuclear SREBF2 and its transcriptional activity, downregulated cholesterol synthesis/metabolism genes, including FDPS and PCSK9, and suppressed MAPK signaling. Molecular docking suggested that EGC may bind pSREBF2 or SCAP. Cellular thermal shift assay revealed that EGC interacts with and stabilizes pSREBF2, but not SCAP. Co-immunoprecipitation demonstrated that EGC reduces pSREBF2-SCAP interaction, thereby inhibiting SCAP-mediated SREBF2 cleavage activation. Together, these findings define an Ar-EGC microbe-metabolite axis and support Ar/EGC-based interventions targeting cholesterol metabolism in CRC.</t>
+          <t>PREVENT 1 is a nationwide, prospective Swedish infant cohort established to characterise gut microbiome development during the first 2 years of life and to relate microbial trajectories to feeding, infections, growth and everyday well-being. The study integrates repeated infant stool sampling with shotgun metagenomics analysis with aligned parental questionnaires, stool photographs and infant cry recordings collected at three approximately 3-month intervals for each infant. Families were recruited nationwide in Sweden from September 2023 through targeted digital channels. Eligible participants were term-born infants residing in Sweden and aged &lt;1 year at enrolment. Baseline questionnaire data and stool samples were collected from 253 infants. Parents completed questionnaires covering socio-demographic characteristics and health, pregnancy and delivery, postnatal factors, infant environment, feeding and growth, infections and other health outcomes, gastrointestinal symptoms and everyday well-being. Retention was high, with 248 families completing at least one follow-up questionnaire at Phase 2 and 243 at Phase 3. For stool samples, 250 infants provided at least two samples and 241 provided all three. At enrolment, 42.3% of infants were older than 7 months, 73.9% had weight-for-length z-scores in the normal range and exclusive breastfeeding at 4 months was reported for 58.9%. Three-phase sample and questionnaire data collection was completed in December 2024. Future analyses will examine microbiome features, resistome profiles and functional pathways in relation to antibiotic exposure, feeding, growth and infant health outcomes. Subject to ethical approval and participant consent, follow-up may include further stool collection and Swedish register linkage. NCT06285630.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>本研究探討腸道共生菌 *Agathobacter rectalis* (Ar) 在大腸直腸癌 (CRC) 中的作用機制。宏基因組分析顯示 CRC 患者體內 Ar 顯著減少；小鼠實驗證實 Ar 能抑制腫瘤生長。代謝組學分析發現 Ar 能產生特定代謝物表沒食子兒茶素 (EGC)。體內外實驗顯示，EGC 可抑制 CRC 細胞生長與膽固醇代謝。機制上，EGC 透過與 pSREBF2 結合並穩定之，阻斷其與 SCAP 的交互作用，進而抑制 SREBF2 活化及下游膽固醇合成基因（如 FDPS、PCSK9）的表達，並抑制 MAPK 訊號。此研究確立了 Ar-EGC 微生物-代謝物軸，為靶向膽固醇代謝的 CRC 防治提供了新策略。</t>
+          <t>本研究建立瑞典全國性嬰兒追蹤世代「PREVENT 1」，旨在透過縱向總體基因體學分析，描繪嬰兒出生後前兩年的腸道菌相發育軌跡，並探討其與餵養、生長及感染等健康指標的關聯。研究成功招募253名足月嬰兒，並在三個時間點重複收集糞便檢體與問卷，受試者維持率極高（241名嬰兒提供全部三次檢體）。此世代研究提供高質量的臨床與多體學數據，未來將深入分析抗生素暴露與飲食如何形塑嬰兒腸道菌群、抗藥性基因組及代謝途徑，對理解早期生命健康極具臨床與科學價值。</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1668,28 +1664,28 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42665998/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42665338/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>42664252</t>
+          <t>42663694</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Proteobacteria with chemosynthetic potential are highly prevalent in the gills of Hypoplectrus reef fishes.</t>
+          <t>Comparative Analysis of Different Anodic Inoculum in Microbial Fuel Cell for Efficient Methylene Blue Dye Degradation.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PLoS genetics</t>
+          <t>Current microbiology</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1698,7 +1694,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>353 個魚鰓檢體</t>
+          <t>3種不同的接種源（海洋沉積物、河口沉積物、厭氧污泥）</t>
         </is>
       </c>
       <c r="G24" t="b">
@@ -1706,12 +1702,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Fishes host a diverse microbiome in their gills, but a broad characterization of this microbiome at the metagenomic level is lacking. Here, we apply genome-resolved metagenomics to the gills of the hamlets (Hypoplectrus spp), a group of reef fishes from the Greater Caribbean. The analysis of 353 gill samples from 15 hamlet species collected at eight locations over 13 years revealed a stark contrast between the gill microbiota and reef water microbial communities, indicating a distinct and specific gill microbiome. A total of 70 gill-associated metagenome-assembled genomes (MAGs) were recovered. These MAGs belong to 17 lineages, most of which are novel. They relate to known fish gill pathogens, fish gut microbes, free-living and biofilm-associated taxa, indicating that the gill microbiome was assembled from a collection of distinct eco-evolutionary trajectories. The MAGs harbor diverse metabolic modules, involved notably in nitrogen cycling, antibiotic production and biofilm formation, revealing a highly dynamic microbial ecosystem. One lineage in the Burkholderiaceae family was outstandingly prevalent across fish host species, sampling locations and years. Its genome encoded complete metabolic modules for carbon fixation and sulfur oxidation, indicating chemosynthetic potential. To the best of our knowledge, this is the first line of evidence that fishes may host sulfur-oxidizing chemosynthetic bacteria in their gills. The functional significance of this chemosynthetic potential for the fish host or other members of the gill microbiome remains to be established. The high prevalence of this lineage allowed to build a pangenome. It revealed large-scale geographic structure (western Caribbean, eastern Caribbean and Gulf of Mexico), which parallels the phylogenomic pattern observed in the hamlets. Overall, our findings point to complex fish host-microbe and microbe-microbe eco-evolutionary interactions in the gills that may influence fish physiology, homeostasis and immune response.</t>
+          <t>This study investigates three different inoculum sources in dual-chamber microbial fuel cells (MFCs), such as Marine Sediment (MFC-MS), Estuary Sediment (MFC-ES), and Anaerobic Sludge (MFC-AS), to compare the efficacy for Methylene Blue (MB) dye degradation and electricity generation. All the MFCs were operated under identical conditions in batch mode using synthetic wastewater containing 3000 mg/L COD made using sodium acetate. The electrochemical study reveals that MFC inoculated with marine sediment achieved maximum power density of 35 mW/m² followed by anaerobic sludge (31 mW/m²) and estuary sediment (25 mW/m²). Statistical analysis was employed to evaluate performance differences among the systems and to support result interpretation. Maximum COD removal efficiency of 75% was obtained by MFC-AS, and coulombic efficiency (CE) was higher for MFC-MS with 25%. Maximum decolorization efficiency was noted in MFC with anaerobic sludge, which obtained 96% decolorization over 96 h. Comparative and trend-based statistical evaluation confirmed the superior treatment performance of MFC-assisted systems. The phytotoxicity study revealed that the toxicity effect of dye wastewater was reduced to its maximum after treatment in the MFC system. The dominant performance of MFC-MS is due to the efficiency of the major electrogenic bacteria concentrated in the inoculum. The functional annotation using the data obtained from metagenomics reveals the presence and role of various enzymes and pathways involved.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>本研究針對加勒比海地區 15 種「蝴蝶魚」（Hypoplectrus spp.）進行了大規模的宏基因組研究。透過分析 353 個魚鰓檢體並重建 70 個宏基因組組裝基因組（MAGs），研究發現魚鰓微生物群落與周圍海水環境顯著不同，具有獨特的演化軌跡。最重大的發現是鑑定出一種具高度普遍性的 Burkholderiaceae 細菌，該菌株擁有完整的固碳與硫氧化代謝路徑，顯示其具備化能合成潛力，這是科學界首次在魚類鰓部發現此類共生菌。此外，該菌株的基因體結構與宿主魚類的地理分布呈現高度一致性。此研究揭示了魚鰓微生物生態系統的複雜性，並為魚類生理、恆定性及免疫反應與微生物間的交互作用提供了重要的演化科學基礎。</t>
+          <t>本研究旨在比較雙腔式微生物燃料電池（MFC）中，三種不同接種源（海洋沉積物、河口沉積物、厭氧污泥）在降解亞甲藍染料與產電的效率。結果顯示，海洋沉積物系統具最高的功率密度（35 mW/m²）與庫倫效率（25%）；厭氧污泥系統則有最佳的化學需氧量去除率（75%）與脫色率（96%）。處理後廢水的植物毒性顯著降低。宏基因組學分析揭示了關鍵產電菌的分布及參與降解與發電的酶和代謝途徑。本研究證實了不同接種源在 MFC 污水處理與生物發電的潛力，並闡明了其微生物學機制。</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1721,28 +1717,28 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42664252/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42663694/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>42663459</t>
+          <t>42664252</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Clinical application of BALF-mNGS in immunocompromised and immunocompetent patients with suspected invasive pulmonary aspergillosis: differentiating infection from colonization, microbiome features, and clinical impact.</t>
+          <t>Proteobacteria with chemosynthetic potential are highly prevalent in the gills of Hypoplectrus reef fishes.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Microbiology spectrum</t>
+          <t>PLoS genetics</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1751,7 +1747,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>178位疑似侵襲性肺麴菌病（IPA）患者（包含77位免疫功能低下患者與101位免疫功能正常患者）</t>
+          <t>353 個魚鰓檢體</t>
         </is>
       </c>
       <c r="G25" t="b">
@@ -1759,12 +1755,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Invasive pulmonary aspergillosis (IPA) not only causes high morbidity and mortality, especially in immunocompromised patients, but also occurs in immunocompetent individuals. Differentiating infection from colonization is challenging, and bronchoalveolar lavage fluid metagenomic next-generation sequencing (BALF-mNGS) may aid diagnosis, microbiome profiling, and clinical assessment. We retrospectively analyzed patients with suspected IPA who underwent BALF-mNGS between December 2021 and March 2025. Patients were classified by immune status. IPA diagnosis was based on EORTC/MSGERC 2020 criteria in immunocompromised patients, while immunocompetent cases were adjudicated using an integrated clinical, radiological, and microbiological assessment. A total of 178 patients were finally included and classified according to immune status into an immunocompromised group (n = 77) and an immunocompetent group (n = 101). Aspergillus_ reads per ten million (RPTM) values were significantly higher in infection versus colonization cases in both groups, with optimal cut-offs of 24 (gray zone: 22-60) for the immunocompromised group and 33 (gray zone: 17-48) for the immunocompetent group. Microbiome analysis revealed distinct community structures between infection and colonization groups, with Aspergillus remaining significantly enriched after false discovery rate (FDR) correction in immunocompromised patients, while no taxa remained significant after FDR correction in immunocompetent patients. BALF-mNGS guided antifungal therapy, avoiding unnecessary treatment in colonized patients, and higher Aspergillus_RPTM was associated with increased 90-day mortality in immunocompromised patients. BALF-mNGS may accurately distinguish Aspergillus infection from colonization and reveal microbial shifts, particularly in immunocompromised patients. It can guide targeted antifungal therapy, avoid unnecessary treatment, and higher Aspergillus_RPTM was associated with 90-day mortality in immunocompromised patients, suggesting its potential value for risk stratification.IMPORTANCEBALF-mNGS with quantitative thresholds improves differentiation between Aspergillus infection and colonization. It reveals distinct lung microbiome patterns under different immune statuses, extending beyond simple pathogen detection. Higher Aspergillus burden is associated with worse outcomes in immunocompromised patients, suggesting its potential value for risk stratification.</t>
+          <t>Fishes host a diverse microbiome in their gills, but a broad characterization of this microbiome at the metagenomic level is lacking. Here, we apply genome-resolved metagenomics to the gills of the hamlets (Hypoplectrus spp), a group of reef fishes from the Greater Caribbean. The analysis of 353 gill samples from 15 hamlet species collected at eight locations over 13 years revealed a stark contrast between the gill microbiota and reef water microbial communities, indicating a distinct and specific gill microbiome. A total of 70 gill-associated metagenome-assembled genomes (MAGs) were recovered. These MAGs belong to 17 lineages, most of which are novel. They relate to known fish gill pathogens, fish gut microbes, free-living and biofilm-associated taxa, indicating that the gill microbiome was assembled from a collection of distinct eco-evolutionary trajectories. The MAGs harbor diverse metabolic modules, involved notably in nitrogen cycling, antibiotic production and biofilm formation, revealing a highly dynamic microbial ecosystem. One lineage in the Burkholderiaceae family was outstandingly prevalent across fish host species, sampling locations and years. Its genome encoded complete metabolic modules for carbon fixation and sulfur oxidation, indicating chemosynthetic potential. To the best of our knowledge, this is the first line of evidence that fishes may host sulfur-oxidizing chemosynthetic bacteria in their gills. The functional significance of this chemosynthetic potential for the fish host or other members of the gill microbiome remains to be established. The high prevalence of this lineage allowed to build a pangenome. It revealed large-scale geographic structure (western Caribbean, eastern Caribbean and Gulf of Mexico), which parallels the phylogenomic pattern observed in the hamlets. Overall, our findings point to complex fish host-microbe and microbe-microbe eco-evolutionary interactions in the gills that may influence fish physiology, homeostasis and immune response.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>本研究旨在評估支氣管肺泡灌洗液總體基因體次世代定序（BALF-mNGS）在區分疑似侵襲性肺麴菌病（IPA）患者「感染」與「定植」的臨床價值，並探討其肺部微生態特徵。研究納入178位患者，發現感染者的麴菌相對豐度（RPTM）顯著高於定植者，並針對免疫功能低下與正常組分別訂定出24與33的最佳臨界值。微生態分析顯示兩組具有不同的菌群結構。臨床上，BALF-mNGS能有效引導抗真菌治療，避免定植患者過度治療；而在免疫功能低下組中，高麴菌RPTM值與90天高死亡率顯著相關。此技術不僅能精準診斷，更具備患者預後風險分層的潛力。</t>
+          <t>本研究針對加勒比海地區 15 種「蝴蝶魚」（Hypoplectrus spp.）進行了大規模的宏基因組研究。透過分析 353 個魚鰓檢體並重建 70 個宏基因組組裝基因組（MAGs），研究發現魚鰓微生物群落與周圍海水環境顯著不同，具有獨特的演化軌跡。最重大的發現是鑑定出一種具高度普遍性的 Burkholderiaceae 細菌，該菌株擁有完整的固碳與硫氧化代謝路徑，顯示其具備化能合成潛力，這是科學界首次在魚類鰓部發現此類共生菌。此外，該菌株的基因體結構與宿主魚類的地理分布呈現高度一致性。此研究揭示了魚鰓微生物生態系統的複雜性，並為魚類生理、恆定性及免疫反應與微生物間的交互作用提供了重要的演化科學基礎。</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1774,28 +1770,28 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42663459/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42664252/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>42663694</t>
+          <t>42663459</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Comparative Analysis of Different Anodic Inoculum in Microbial Fuel Cell for Efficient Methylene Blue Dye Degradation.</t>
+          <t>Clinical application of BALF-mNGS in immunocompromised and immunocompetent patients with suspected invasive pulmonary aspergillosis: differentiating infection from colonization, microbiome features, and clinical impact.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Current microbiology</t>
+          <t>Microbiology spectrum</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1804,7 +1800,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>3種不同的接種源（海洋沉積物、河口沉積物、厭氧污泥）</t>
+          <t>178位疑似侵襲性肺麴菌病（IPA）患者（包含77位免疫功能低下患者與101位免疫功能正常患者）</t>
         </is>
       </c>
       <c r="G26" t="b">
@@ -1812,12 +1808,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>This study investigates three different inoculum sources in dual-chamber microbial fuel cells (MFCs), such as Marine Sediment (MFC-MS), Estuary Sediment (MFC-ES), and Anaerobic Sludge (MFC-AS), to compare the efficacy for Methylene Blue (MB) dye degradation and electricity generation. All the MFCs were operated under identical conditions in batch mode using synthetic wastewater containing 3000 mg/L COD made using sodium acetate. The electrochemical study reveals that MFC inoculated with marine sediment achieved maximum power density of 35 mW/m² followed by anaerobic sludge (31 mW/m²) and estuary sediment (25 mW/m²). Statistical analysis was employed to evaluate performance differences among the systems and to support result interpretation. Maximum COD removal efficiency of 75% was obtained by MFC-AS, and coulombic efficiency (CE) was higher for MFC-MS with 25%. Maximum decolorization efficiency was noted in MFC with anaerobic sludge, which obtained 96% decolorization over 96 h. Comparative and trend-based statistical evaluation confirmed the superior treatment performance of MFC-assisted systems. The phytotoxicity study revealed that the toxicity effect of dye wastewater was reduced to its maximum after treatment in the MFC system. The dominant performance of MFC-MS is due to the efficiency of the major electrogenic bacteria concentrated in the inoculum. The functional annotation using the data obtained from metagenomics reveals the presence and role of various enzymes and pathways involved.</t>
+          <t>Invasive pulmonary aspergillosis (IPA) not only causes high morbidity and mortality, especially in immunocompromised patients, but also occurs in immunocompetent individuals. Differentiating infection from colonization is challenging, and bronchoalveolar lavage fluid metagenomic next-generation sequencing (BALF-mNGS) may aid diagnosis, microbiome profiling, and clinical assessment. We retrospectively analyzed patients with suspected IPA who underwent BALF-mNGS between December 2021 and March 2025. Patients were classified by immune status. IPA diagnosis was based on EORTC/MSGERC 2020 criteria in immunocompromised patients, while immunocompetent cases were adjudicated using an integrated clinical, radiological, and microbiological assessment. A total of 178 patients were finally included and classified according to immune status into an immunocompromised group (n = 77) and an immunocompetent group (n = 101). Aspergillus_ reads per ten million (RPTM) values were significantly higher in infection versus colonization cases in both groups, with optimal cut-offs of 24 (gray zone: 22-60) for the immunocompromised group and 33 (gray zone: 17-48) for the immunocompetent group. Microbiome analysis revealed distinct community structures between infection and colonization groups, with Aspergillus remaining significantly enriched after false discovery rate (FDR) correction in immunocompromised patients, while no taxa remained significant after FDR correction in immunocompetent patients. BALF-mNGS guided antifungal therapy, avoiding unnecessary treatment in colonized patients, and higher Aspergillus_RPTM was associated with increased 90-day mortality in immunocompromised patients. BALF-mNGS may accurately distinguish Aspergillus infection from colonization and reveal microbial shifts, particularly in immunocompromised patients. It can guide targeted antifungal therapy, avoid unnecessary treatment, and higher Aspergillus_RPTM was associated with 90-day mortality in immunocompromised patients, suggesting its potential value for risk stratification.IMPORTANCEBALF-mNGS with quantitative thresholds improves differentiation between Aspergillus infection and colonization. It reveals distinct lung microbiome patterns under different immune statuses, extending beyond simple pathogen detection. Higher Aspergillus burden is associated with worse outcomes in immunocompromised patients, suggesting its potential value for risk stratification.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>本研究旨在比較雙腔式微生物燃料電池（MFC）中，三種不同接種源（海洋沉積物、河口沉積物、厭氧污泥）在降解亞甲藍染料與產電的效率。結果顯示，海洋沉積物系統具最高的功率密度（35 mW/m²）與庫倫效率（25%）；厭氧污泥系統則有最佳的化學需氧量去除率（75%）與脫色率（96%）。處理後廢水的植物毒性顯著降低。宏基因組學分析揭示了關鍵產電菌的分布及參與降解與發電的酶和代謝途徑。本研究證實了不同接種源在 MFC 污水處理與生物發電的潛力，並闡明了其微生物學機制。</t>
+          <t>本研究旨在評估支氣管肺泡灌洗液總體基因體次世代定序（BALF-mNGS）在區分疑似侵襲性肺麴菌病（IPA）患者「感染」與「定植」的臨床價值，並探討其肺部微生態特徵。研究納入178位患者，發現感染者的麴菌相對豐度（RPTM）顯著高於定植者，並針對免疫功能低下與正常組分別訂定出24與33的最佳臨界值。微生態分析顯示兩組具有不同的菌群結構。臨床上，BALF-mNGS能有效引導抗真菌治療，避免定植患者過度治療；而在免疫功能低下組中，高麴菌RPTM值與90天高死亡率顯著相關。此技術不僅能精準診斷，更具備患者預後風險分層的潛力。</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1827,37 +1823,35 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42663694/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42663459/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>42665338</t>
+          <t>42666033</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PREVENT 1, a nationwide Swedish infant cohort for longitudinal gut microbiome profiling and early-life health outcomes: cohort profile.</t>
+          <t>Gut Microbiota-Isoallolithocholic Acid Crosstalk Promotes Calcium Oxalate Kidney Stone Formation via PARP1-Mediated Parthanatos.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BMJ open</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>2.3</v>
-      </c>
+          <t>Advanced science (Weinheim, Baden-Wurttemberg, Germany)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>16S, metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>253 位嬰兒（收集 253 份基線糞便檢體，其中 250 位提供至少 2 次檢體，241 位提供全部 3 次檢體）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G27" t="b">
@@ -1865,12 +1859,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>PREVENT 1 is a nationwide, prospective Swedish infant cohort established to characterise gut microbiome development during the first 2 years of life and to relate microbial trajectories to feeding, infections, growth and everyday well-being. The study integrates repeated infant stool sampling with shotgun metagenomics analysis with aligned parental questionnaires, stool photographs and infant cry recordings collected at three approximately 3-month intervals for each infant. Families were recruited nationwide in Sweden from September 2023 through targeted digital channels. Eligible participants were term-born infants residing in Sweden and aged &lt;1 year at enrolment. Baseline questionnaire data and stool samples were collected from 253 infants. Parents completed questionnaires covering socio-demographic characteristics and health, pregnancy and delivery, postnatal factors, infant environment, feeding and growth, infections and other health outcomes, gastrointestinal symptoms and everyday well-being. Retention was high, with 248 families completing at least one follow-up questionnaire at Phase 2 and 243 at Phase 3. For stool samples, 250 infants provided at least two samples and 241 provided all three. At enrolment, 42.3% of infants were older than 7 months, 73.9% had weight-for-length z-scores in the normal range and exclusive breastfeeding at 4 months was reported for 58.9%. Three-phase sample and questionnaire data collection was completed in December 2024. Future analyses will examine microbiome features, resistome profiles and functional pathways in relation to antibiotic exposure, feeding, growth and infant health outcomes. Subject to ethical approval and participant consent, follow-up may include further stool collection and Swedish register linkage. NCT06285630.</t>
+          <t>Bile acids have been implicated in calcium oxalate (CaOx) nephrolithiasis. Here, we employ multi-omics approaches to identify isoallolithocholic acid (isoalloLCA) as the key bile acid elevated in the feces, serum, kidney, and urine of CaOx rats, confirmed by spatial metabolomics. 16S sequencing and metagenomic analyses indicate that elevated isoalloLCA levels in CaOx rats or individuals are likely of microbial origin. Mechanistically, isoalloLCA binds to PARP1 via specific molecular interactions validated by surface plasmon resonance and cellular thermal shift assays. Knockdown of PARP1 by adeno-associated virus microinjection or pharmacological inhibition with PARP1 inhibitor AZD5305 significantly attenuates isoalloLCA-mediated crystal deposition, renal tubular injury, and mitochondrial functional impairment in both the CaOx rat and mouse models. Furthermore, the antibiotic-mediated depletion of the gut microbiota in mice markedly reduced isoalloLCA levels, whereas fecal microbiota transplantationut contributes to isoalloLCA-mediated CaOx stone formation, demonstrating a causal link between gut microbiota and isoalloLCA. In vitro, isoalloLCA promoted oxalate-induced renal tubular epithelial cell injury and parthanatos via targeting PARP1, including DNA damage, excessive PARP1 activation, PAR accumulation, mitochondrial damage, nuclear translocation of AIF and MIF. These findings establish the microbiota-isoalloLCA-PARP1-parthanatos axis in CaOx nephrolithiasis and identify PARP1 as a promising therapeutic target for kidney stone management.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>本研究建立瑞典全國性嬰兒追蹤世代「PREVENT 1」，旨在透過縱向總體基因體學分析，描繪嬰兒出生後前兩年的腸道菌相發育軌跡，並探討其與餵養、生長及感染等健康指標的關聯。研究成功招募253名足月嬰兒，並在三個時間點重複收集糞便檢體與問卷，受試者維持率極高（241名嬰兒提供全部三次檢體）。此世代研究提供高質量的臨床與多體學數據，未來將深入分析抗生素暴露與飲食如何形塑嬰兒腸道菌群、抗藥性基因組及代謝途徑，對理解早期生命健康極具臨床與科學價值。</t>
+          <t>本研究旨在探討腸道菌群及其代謝物異別石膽酸（isoalloLCA）在草酸鈣（CaOx）腎結石形成中的作用與分子機制。透過整合16S定序、宏基因組學與空間代謝組學，研究發現 CaOx 大鼠及患者體內的腸道菌源 isoalloLCA 顯著升高。機制上，isoalloLCA 能直接結合並激活 PARP1 蛋白，誘導腎小管上皮細胞發生 PARP1 介導的細胞凋亡樣壞死（parthanatos），導致 DNA 與線粒體受損。於動物模型中，敲低或抑制 PARP1，或利用抗生素清除腸道菌群，皆能顯著減輕結晶沉積與腎損傷。本研究揭示了「腸道菌群-isoalloLCA-PARP1-parthanatos」軸在腎結石病理中的關鍵角色，並指出 PARP1 為臨床治療腎結石的具潛力靶點。</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1880,35 +1874,37 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42665338/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42666033/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>42664608</t>
+          <t>42665998</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Application-dependent effects of tea waste biochar on PFAS mobility and N2O and CH4 emissions in agricultural soil.</t>
+          <t>Agathobacter rectalis suppresses colorectal tumorigenesis via an epigallocatechin-SREBF2 axis controlling cholesterol metabolism.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Waste management (New York, N.Y.)</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>Gut microbes</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11</v>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>未提及（僅說明使用盆栽模擬系統「per pot」，未提及具體樣本或盆栽數量）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G28" t="b">
@@ -1916,12 +1912,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Per- and polyfluoroalkyl substances (PFAS) in agricultural soils can migrate into crops and may alter soil greenhouse gas emissions, yet remediation strategies rarely address these risks simultaneously. This study evaluated tea waste biochar (TWB) produced at 400, 500, and 600 °C and applied at 5-20 g per pot by whole-soil mixing or surface-layer placement in a simulated PFAS-contaminated soil-leachate-plant system. Perfluorooctane sulfonate (PFOS) and perfluorooctanoic acid (PFOA) distributions, nitrous oxide (N2O) and methane (CH4) fluxes, and microbial responses were examined. TWB produced at 500 °C showed the most favorable combination of pore accessibility, surface hydrophobicity, and interfacial charge, with material-associated PFOS and PFOA enrichments of 0.12 and 0.57 μg/g, respectively. Whole-soil mixing with TWB-500 lowered soil and leachate PFAS levels and reduced PFAS concentrations in plant shoots by approximately 36% relative to the contaminated control. TWB treatments also reduced cumulative N2O emissions and enhanced net CH4 uptake. Metagenomic analysis showed lower relative abundances of genes associated with nitrogen fixation, ammonia oxidation, and several N2O-producing pathways, whereas CH4-cycling genes responded differently to the two application methods. Organic fluorine transformation genes were not enriched, indicating that PFAS control mainly resulted from physicochemical retention rather than enhanced microbial defluorination. Overall, TWB-500 can integrate PFAS stabilization with greenhouse gas management, but the optimal placement depends on the remediation objective: whole-soil mixing favors PFAS immobilization, whereas surface-layer application provides greater greenhouse gas mitigation.</t>
+          <t>Beneficial effects of the gut commensal Agathobacter rectalis (Ar) are reported in diseases, yet its role in colorectal cancer (CRC) remains unclear. Here, metagenomic analysis revealed consistent fecal Ar depletion across CRC cohorts. In Apc min/+ mice, Ar inhibited colon tumorigenesis, reducing tumor number and volume versus E. coli and PBS controls. LC-MS/MS metabolomics showed decreased fecal cholesterol and altered lipid/cholesterol pathways after Ar treatment. In vitro, Ar-conditioned medium suppressed CRC cell growth, clonogenicity, migration, and cell cycle progression. LC-MS/MS identified (-)-epigallocatechin (EGC) as an Ar-derived metabolite absent in control bacteria. EGC recapitulated Ar-mediated anti-CRC effects in vitro and in vivo, with metabolic changes linked to lipid/cholesterol pathways. Transcriptomics showed that EGC suppressed SREBP signaling, cholesterol metabolism, and MAPK pathways. Mechanistically, EGC reduced nuclear SREBF2 and its transcriptional activity, downregulated cholesterol synthesis/metabolism genes, including FDPS and PCSK9, and suppressed MAPK signaling. Molecular docking suggested that EGC may bind pSREBF2 or SCAP. Cellular thermal shift assay revealed that EGC interacts with and stabilizes pSREBF2, but not SCAP. Co-immunoprecipitation demonstrated that EGC reduces pSREBF2-SCAP interaction, thereby inhibiting SCAP-mediated SREBF2 cleavage activation. Together, these findings define an Ar-EGC microbe-metabolite axis and support Ar/EGC-based interventions targeting cholesterol metabolism in CRC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>本研究旨在評估茶渣生物炭（TWB）在模擬的PFAS污染土壤-滲濾液-植物系統中，對於抑制全氟和多氟烷基物質（PFAS）遷移及減少溫室氣體（N2O和CH4）排放的雙重效應。研究發現，在500 °C下製備的TWB-500效果最佳。若將其均勻混合於全土中，可使植物地上部的PFAS濃度降低約36%，並顯著降低土壤和滲濾液中的PFAS含量。此外，TWB處理還減少了N2O累積排放並促進CH4淨吸收。總體基因體學分析顯示，與氮循環相關的基因豐度有所下降，解釋了N2O排放減少的機制；而有機氟降解基因並未富集，證實PFAS的控制主要源於物理化學阻控而非微生物去氟作用。此研究證明TWB-500能有效整合PFAS固化與溫室氣體管理，且施用方式（全土混合或表層施作）可依環境整治優先目標進行客製化調整。</t>
+          <t>本研究探討腸道共生菌 *Agathobacter rectalis* (Ar) 在大腸直腸癌 (CRC) 中的作用機制。宏基因組分析顯示 CRC 患者體內 Ar 顯著減少；小鼠實驗證實 Ar 能抑制腫瘤生長。代謝組學分析發現 Ar 能產生特定代謝物表沒食子兒茶素 (EGC)。體內外實驗顯示，EGC 可抑制 CRC 細胞生長與膽固醇代謝。機制上，EGC 透過與 pSREBF2 結合並穩定之，阻斷其與 SCAP 的交互作用，進而抑制 SREBF2 活化及下游膽固醇合成基因（如 FDPS、PCSK9）的表達，並抑制 MAPK 訊號。此研究確立了 Ar-EGC 微生物-代謝物軸，為靶向膽固醇代謝的 CRC 防治提供了新策略。</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1931,35 +1927,35 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42664608/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42665998/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>42664954</t>
+          <t>42665077</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lactobacillus salivarius potentiates gastrointestinal cancer immunotherapy through its metabolite chenodeoxycholic acid.</t>
+          <t>Metagenomic Characterization of Potential Exposure to Genetic Hazards at the Interface Between Grazing Livestock and Przewalski's Gazelle.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cell reports. Medicine</t>
+          <t>Environmental pollution (Barking, Essex : 1987)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>metagenomics, metabolomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>278 位胃腸道癌症患者及同基因腫瘤小鼠模型</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G29" t="b">
@@ -1967,12 +1963,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Immune checkpoint inhibitor therapy has improved gastrointestinal (GI) cancer management; however, many patients exhibit resistance. Although gut microbiota influences immunotherapeutic responses, the underlying mechanisms remain unclear. Metagenomic analysis of 278 GI cancer patients reveals that Lactobacillus salivarius (L. salivarius) is enriched in responders and enhances anti-PD-1 efficacy in syngeneic tumor models by increasing the infiltration of antitumor M1-like macrophages and CD8+ T cells and enhancing CD8+ T cell effector function. L. salivarius-associated chenodeoxycholic acid (CDCA) is identified as a functional metabolite. CDCA recapitulates the antitumor effects of L. salivarius and significantly improves anti-PD-1 efficacy in vivo, an effect attenuated by depleting macrophages or CD8+ T cells. Mechanistically, CDCA-induced reactive oxygen species triggers immunogenic cell death in tumor cells and polarizes macrophages toward antitumor M1 phenotype, activating CD8+ T cell antitumor immunity. These findings identify L. salivarius and its associated metabolite CDCA as a promising adjuvant for potentiating immunotherapy in GI cancers.</t>
+          <t>Livestock and endangered wildlife increasingly share grazing landscapes, yet the sources, mobility-associated contexts, and bacterial hosts of livestock-associated genetic hazards in wildlife microbiomes remain poorly resolved. We analyzed metagenomes from yak, Tibetan sheep, Przewalski's gazelle, and local topsoil within an Acquired Genetic Risk (AGR) conceptual framework integrating genetic hazard burden, compositional source attribution, mobility-associated evidence, and bacterial genomic context. MRGs and Rank I and Rank III ARGs were more abundant in livestock than in Przewalski's gazelle, whereas VF abundance was highest in yak. FEAST attributed approximately 64% of the Przewalski's gazelle resistome composition to the two livestock source profiles, less than 1% to sampled topsoil, and approximately 36% remained unassigned. MGE profiles were associated with ARGs, MRGs, and VFs, while tnpA ranked highest in random forest models and was associated with total ARG abundance (R2 = 0.618). Short-read contigs containing hazard genes and MGE markers provided localized mobility-associated sequence context. Genome-resolved analysis identified distinct bacterial contexts: TS.Bin143, an Escherichia coli MAG from Tibetan sheep, contained ARGs, MRGs, VFs, tnpA, and IS91, whereas PG.Bin275, a Hylemonella sp. MAG from Przewalski's gazelle, contained tnpA. These findings extend wildlife resistome assessment beyond abundance profiling toward source attribution, mobility-associated sequence context, and bacterial host resolution, supporting multilevel surveillance of genetic hazard exposure at livestock-wildlife interfaces.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>本研究旨在探討腸道菌群影響胃腸道（GI）癌症免疫治療反應的具體機制。透過對 278 位 GI 癌症患者的總體基因體分析，發現唾液乳桿菌（*Lactobacillus salivarius*）在治療有反應的患者體內顯著富集。於小鼠模型中，該菌能增加抗腫瘤 M1 型巨噬細胞與 CD8+ T 細胞的浸潤，顯著提升抗 PD-1 療效。研究進一步證實，該菌的代謝物鵝去氧膽酸（CDCA）為關鍵功能分子，能透過誘導活性氧（ROS）引發腫瘤細胞的免疫原性死亡，並促進巨噬細胞向 M1 型極化，從而激活 CD8+ T 細胞的抗腫瘤免疫反應。本研究揭示了唾液乳桿菌及其代謝物 CDCA 作為增強 GI 癌症免疫治療活性佐劑的臨床潛力。</t>
+          <t>本研究旨在評估放牧家畜與瀕危野生普氏原羚接觸介面上的遺傳危害（如抗藥性基因 ARG、金屬耐受基因 MRG 與毒力因子 VF）暴露風險。研究利用總體基因體學分析氛牛、藏羊、普氏原羚及當地表土，結果顯示家畜體內的 MRG 和高風險 ARG 豐度顯著高於普氏原羚。來源追蹤分析（FEAST）指出，普氏原羚約 64% 的抗藥組組成可歸因於這兩種家畜，僅不到 1% 來自土壤。此外，研究透過基因組解析定位了攜帶危害基因與移動遺傳因子的細菌宿主。本研究不僅闡明了遺傳危害的來源與傳播關聯，也為野生動物與家畜接觸介面的多層級生物安全監測提供了重要科學依據。</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1982,35 +1978,37 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42664954/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42665077/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>42666033</t>
+          <t>42663468</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Gut Microbiota-Isoallolithocholic Acid Crosstalk Promotes Calcium Oxalate Kidney Stone Formation via PARP1-Mediated Parthanatos.</t>
+          <t>Genomes of cressdnaviricots and phixviricots in a freshwater lake sample from Arizona, USA.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Advanced science (Weinheim, Baden-Wurttemberg, Germany)</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>Microbiology resource announcements</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.6</v>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>16S, metagenomics, metabolomics</t>
+          <t>metagenomics, small genome</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>1 個 40 ml 的淡水湖泊水樣</t>
         </is>
       </c>
       <c r="G30" t="b">
@@ -2018,12 +2016,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Bile acids have been implicated in calcium oxalate (CaOx) nephrolithiasis. Here, we employ multi-omics approaches to identify isoallolithocholic acid (isoalloLCA) as the key bile acid elevated in the feces, serum, kidney, and urine of CaOx rats, confirmed by spatial metabolomics. 16S sequencing and metagenomic analyses indicate that elevated isoalloLCA levels in CaOx rats or individuals are likely of microbial origin. Mechanistically, isoalloLCA binds to PARP1 via specific molecular interactions validated by surface plasmon resonance and cellular thermal shift assays. Knockdown of PARP1 by adeno-associated virus microinjection or pharmacological inhibition with PARP1 inhibitor AZD5305 significantly attenuates isoalloLCA-mediated crystal deposition, renal tubular injury, and mitochondrial functional impairment in both the CaOx rat and mouse models. Furthermore, the antibiotic-mediated depletion of the gut microbiota in mice markedly reduced isoalloLCA levels, whereas fecal microbiota transplantationut contributes to isoalloLCA-mediated CaOx stone formation, demonstrating a causal link between gut microbiota and isoalloLCA. In vitro, isoalloLCA promoted oxalate-induced renal tubular epithelial cell injury and parthanatos via targeting PARP1, including DNA damage, excessive PARP1 activation, PAR accumulation, mitochondrial damage, nuclear translocation of AIF and MIF. These findings establish the microbiota-isoalloLCA-PARP1-parthanatos axis in CaOx nephrolithiasis and identify PARP1 as a promising therapeutic target for kidney stone management.</t>
+          <t>A viral metagenomic analysis of a 40 ml water sample from a small freshwater lake near Flagstaff, Arizona, USA, resulted in the identification of 295 circular viral genome sequences. Of these, 126 are members of Cressdnaviricota and 169 of Phixviricota phyla.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>本研究旨在探討腸道菌群及其代謝物異別石膽酸（isoalloLCA）在草酸鈣（CaOx）腎結石形成中的作用與分子機制。透過整合16S定序、宏基因組學與空間代謝組學，研究發現 CaOx 大鼠及患者體內的腸道菌源 isoalloLCA 顯著升高。機制上，isoalloLCA 能直接結合並激活 PARP1 蛋白，誘導腎小管上皮細胞發生 PARP1 介導的細胞凋亡樣壞死（parthanatos），導致 DNA 與線粒體受損。於動物模型中，敲低或抑制 PARP1，或利用抗生素清除腸道菌群，皆能顯著減輕結晶沉積與腎損傷。本研究揭示了「腸道菌群-isoalloLCA-PARP1-parthanatos」軸在腎結石病理中的關鍵角色，並指出 PARP1 為臨床治療腎結石的具潛力靶點。</t>
+          <t>本研究旨在探討美國亞利桑那州 Flagstaff 附近一處小型淡水湖泊中的病毒多樣性。研究團隊對 40 毫升的水樣進行病毒總體基因體學（viral metagenomics）分析，成功鑑定並組裝出 295 個環狀病毒基因體序列。在這些病毒中，有 126 個屬於 Cressdnaviricota 門（環狀單鏈 DNA 病毒），另有 169 個屬於 Phixviricota 門（微小噬菌體相關病毒）。此研究的科學意義在於顯著擴充了淡水生態系統中這兩大病毒門的基因體數據，並證實即使在極少量的環境水樣中，也蘊藏著極高多樣性且未知的病毒資源，有助於深化對淡水微生態系統及病毒演化多樣性的理解。</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2033,37 +2031,35 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42666033/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42663468/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>42663468</t>
+          <t>42664954</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Genomes of cressdnaviricots and phixviricots in a freshwater lake sample from Arizona, USA.</t>
+          <t>Lactobacillus salivarius potentiates gastrointestinal cancer immunotherapy through its metabolite chenodeoxycholic acid.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Microbiology resource announcements</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>0.6</v>
-      </c>
+          <t>Cell reports. Medicine</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>metagenomics, small genome</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1 個 40 ml 的淡水湖泊水樣</t>
+          <t>278 位胃腸道癌症患者及同基因腫瘤小鼠模型</t>
         </is>
       </c>
       <c r="G31" t="b">
@@ -2071,12 +2067,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>A viral metagenomic analysis of a 40 ml water sample from a small freshwater lake near Flagstaff, Arizona, USA, resulted in the identification of 295 circular viral genome sequences. Of these, 126 are members of Cressdnaviricota and 169 of Phixviricota phyla.</t>
+          <t>Immune checkpoint inhibitor therapy has improved gastrointestinal (GI) cancer management; however, many patients exhibit resistance. Although gut microbiota influences immunotherapeutic responses, the underlying mechanisms remain unclear. Metagenomic analysis of 278 GI cancer patients reveals that Lactobacillus salivarius (L. salivarius) is enriched in responders and enhances anti-PD-1 efficacy in syngeneic tumor models by increasing the infiltration of antitumor M1-like macrophages and CD8+ T cells and enhancing CD8+ T cell effector function. L. salivarius-associated chenodeoxycholic acid (CDCA) is identified as a functional metabolite. CDCA recapitulates the antitumor effects of L. salivarius and significantly improves anti-PD-1 efficacy in vivo, an effect attenuated by depleting macrophages or CD8+ T cells. Mechanistically, CDCA-induced reactive oxygen species triggers immunogenic cell death in tumor cells and polarizes macrophages toward antitumor M1 phenotype, activating CD8+ T cell antitumor immunity. These findings identify L. salivarius and its associated metabolite CDCA as a promising adjuvant for potentiating immunotherapy in GI cancers.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>本研究旨在探討美國亞利桑那州 Flagstaff 附近一處小型淡水湖泊中的病毒多樣性。研究團隊對 40 毫升的水樣進行病毒總體基因體學（viral metagenomics）分析，成功鑑定並組裝出 295 個環狀病毒基因體序列。在這些病毒中，有 126 個屬於 Cressdnaviricota 門（環狀單鏈 DNA 病毒），另有 169 個屬於 Phixviricota 門（微小噬菌體相關病毒）。此研究的科學意義在於顯著擴充了淡水生態系統中這兩大病毒門的基因體數據，並證實即使在極少量的環境水樣中，也蘊藏著極高多樣性且未知的病毒資源，有助於深化對淡水微生態系統及病毒演化多樣性的理解。</t>
+          <t>本研究旨在探討腸道菌群影響胃腸道（GI）癌症免疫治療反應的具體機制。透過對 278 位 GI 癌症患者的總體基因體分析，發現唾液乳桿菌（*Lactobacillus salivarius*）在治療有反應的患者體內顯著富集。於小鼠模型中，該菌能增加抗腫瘤 M1 型巨噬細胞與 CD8+ T 細胞的浸潤，顯著提升抗 PD-1 療效。研究進一步證實，該菌的代謝物鵝去氧膽酸（CDCA）為關鍵功能分子，能透過誘導活性氧（ROS）引發腫瘤細胞的免疫原性死亡，並促進巨噬細胞向 M1 型極化，從而激活 CD8+ T 細胞的抗腫瘤免疫反應。本研究揭示了唾液乳桿菌及其代謝物 CDCA 作為增強 GI 癌症免疫治療活性佐劑的臨床潛力。</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2086,37 +2082,37 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42663468/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42664954/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>42660466</t>
+          <t>42656127</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Polystyrene nanoplastics exposure induces reproductive toxicity in male mice associated with the gut-liver/testis axis.</t>
+          <t>Development and Validation of Mock Communities as Quality Control Materials for Clinical Metagenomic Next-Generation Sequencing.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Toxicology and applied pharmacology</t>
+          <t>Annals of laboratory medicine</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>metagenomics, others</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>25 次重複分析（針對開發出的四種模擬群落進行評估）</t>
         </is>
       </c>
       <c r="G32" t="b">
@@ -2124,12 +2120,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Environmental nanoplastics are increasingly prevalent in global environments and represent an emerging systemic health risk, yet the mechanistic links between nanoplastic exposure and multi-organ dysfunction in mammals remain incompletely characterized. We integrated phenotypic assessments, gut shotgun metagenomics, and dual-organ transcriptomics to investigate the toxic effects of 28-day oral exposure to polystyrene nanoplastics (PS-NPs) in male CD-1 mice. PS-NPs induced a non-monotonic dose-dependent response, characterized by significant body weight loss at high doses, severe impairment of sperm motility, and progressive epididymal histopathological lesions. Gut metagenomics revealed significant microbiota dysbiosis, including an elevated Firmicutes/Bacteroidota ratio and marked depletion of beneficial commensal bacteria such as Ligilactobacillus murinus. Hepatic transcriptomics identified dysregulation of metabolic, detoxification, and circadian rhythm pathways, while testicular transcriptomics identified sustained transcriptional downregulation of genes annotated to steroid hormone biosynthesis and alterations in FoxO and apoptosis-related signaling. Spearman correlation network analysis identified associations between specific microbial shifts and organ-specific transcriptional alterations, providing a hypothesis-generating framework for the proposed gut-liver/testis axis. Together, these findings indicate that, under the present experimental conditions, oral PS-NPs exposure was associated with gut microbial dysbiosis, hepatic transcriptional perturbations, reduced sperm motility, and epididymal histopathological alterations, while the mechanistic relationships among these changes require further experimental validation.</t>
+          <t>Metagenomic next-generation sequencing (NGS) enables comprehensive detection of a broad spectrum of microorganisms. However, its clinical application faces two major challenges: the development of appropriate microbiome-based biomarkers and the need to ensure the reproducibility and quality of the microbiome analytical workflow. Therefore, we developed four types of bead-based mock communities as standard materials for microbiome analysis and evaluated potential experimental biases arising from nucleic acid extraction and sequence analysis. Mock communities were assembled from strains isolated from clinical specimens and selected considering Gram reaction, taxonomic phylogeny, and prevalence, and processed into frozen beads. The communities were analyzed using shotgun whole-metagenome sequencing. The effect of DNA extraction kit choice was evaluated using the Thermo Fisher Scientific MagMAX Microbiome Ultra Nucleic Acid Isolation Kit and Qiagen PowerSoil Kit. Four types of mock communities comprising 26 species commonly found in the gastrointestinal tract, respiratory tract, skin, and genital tract plus cerebrospinal fluid were developed considering Gram reaction, GC content, and phylogenetic distribution. Across 25 repeated analyses, the median repeatability of each taxon was 18.97% (range, 2.87%-107.38%), while within-laboratory imprecision was 26.22% (range, 9.26%-153.83%). Repeatability remained below 10% for most dominant taxa with relative abundances &gt;20%. The choice of DNA extraction kit had a significant effect on taxonomic distributions. Microbial mock communities are essential QC materials for clinical metagenomic NGS. Further studies are needed to minimize variability and establish a standardized protocol for clinical implementation.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>本研究探討口服聚苯乙烯奈米塑料（PS-NPs）28天對雄性CD-1小鼠的毒性效應及其作用機制。研究發現，PS-NPs暴露會引發非單調劑量依賴性反應，導致小鼠體重顯著減輕、精子活力嚴重受損及附睾病理病變。腸道總體基因體學分析顯示，PS-NPs引起腸道菌群失調（厚壁菌門/擬桿菌門比例升高，有益菌如鼠乳桿菌顯著減少）。雙器官轉錄組學分析進一步證實，肝臟中代謝、解毒與晝夜節律途徑失調，而睾丸中類固醇激素合成基因持續下調且凋亡信號改變。本研究首次揭示了奈米塑料誘導生殖毒性與「腸-肝/睾丸軸」的關聯，為環境微塑料的哺乳動物多器官毒性機制提供了重要科學依據。</t>
+          <t>本研究旨在解決臨床宏基因組次世代定序（mNGS）在品質控制與再現性上的挑戰，開發了四種基於珠粒的「模擬微生物群落」（mock communities）作為標準品。這些群落涵蓋了腸道、呼吸道、皮膚、生殖道及腦脊髓液中常見的 26 種菌株。研究透過鳥槍法全宏基因體定序（shotgun metagenomics）評估了不同 DNA 萃取試劑盒（MagMAX 與 PowerSoil）及實驗流程對結果的偏誤影響。結果顯示，微生物的檢測豐度會顯著受到萃取試劑盒選擇的干擾，且在 25 次重複實驗中，群落組成存在一定的實驗室內誤差。此研究確立了模擬群落作為臨床 mNGS 品質控制材料的重要性，對於推動微生物組檢測的標準化流程與臨床應用具有關鍵價值。</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2139,37 +2135,37 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42660466/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42656127/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>42658871</t>
+          <t>42660365</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Breastmilk microbiota and its association with infant iron deficiency anaemia: A 16S rRNA metagenomic study in Peruvian mothers cohort.</t>
+          <t>Enhancing Cr(VI) bioreduction via Na+-stimulated intracellular energy metabolism and electron transfer using methane as electron donor.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PloS one</t>
+          <t>Bioresource technology</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2.6</v>
+        <v>9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>16S</t>
+          <t>16S, metagenomics</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>46 對母嬰（46 個母乳檢體）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G33" t="b">
@@ -2177,12 +2173,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Anaemia is one of the most important public health challenges in developing countries. The global burden is estimated at 1.8 billion people, affecting approximately 30% of all children. Despite the implementation of multiple strategies over several decades, up to 42.5% of children under 3 years of age suffer anaemia in rural areas of Peru. We studied the microbiota of breastmilk (hBM) from mothers with children under the age of 1 and analysed its association with their iron deficiency anaemia. 46 mother-child pairs were recruited from Talara, a town on the northern coast of Peru and classified according to the clinical status of the children. Children with anaemia were also tested for ferritin level to classify them as iron deficiency anaemia (IDA) or non-iron deficiency anaemia (non-IDA). hBM samples were taken from the mothers after careful instruction to reduce the risk of sample contamination and the microbiome was analyzed using 16S rRNA sequencing. Streptococcus and Staphylococcus were the predominant genera, with 90% of bacterial abundance being explained by 14 genera. Alpha diversity analysis showed that hBM from mothers of children with non-IDA had higher levels of bacterial richness than hBM from healthy (p &lt; 0.01) and IDA (p &lt; 0.05) participants. Principal coordinates analysis did not yield differential clusters but showed a disparity in the spread of samples for non-IDA group when compared with the other groups. IDA group showed higher burden of Corynebacterium, Acinetobacter, Paludibacter and Nitrospira, while exhibiting a trend towards a lower burden of Streptococcus. No statistically significant differences were identified on demographic characteristics. This study suggests that hBM microbiota may differ in mothers of children with IDA and non-IDA, highlighting the necessity of further in-depth research to elucidate potential factors associated with its pathogenesis.</t>
+          <t>Anaerobic oxidation of methane (AOM) coupled with Cr(VI) bioreduction process offers a cost-effective pathway to simultaneously mitigate methane emissions and remediate Cr(VI) contamination. However, its practical application is limited by insufficient intracellular energy generation and low electron transfer efficiency. This study elucidated the regulatory role and mechanism of Na+, a transmembrane electrochemical gradient driver, on the metabolic activity and electron transfer of this coupled system. Batch experiments demonstrated that NaCl addition significantly improved Cr(VI) reduction efficiency, achieving complete removal in the treatment group by the end of the first cycle compared to only 79.8 % in the control. Microbial community analysis showed that Na+ enriched AOM-capable Methanobacterium and extracellular electron transfer (EET)-capable electroactive bacterium unclassified_o_DTU014, which likely formed a syntrophic consortium to mediate Cr(VI) reduction. Electrochemical measurements and 3D-EEM spectroscopy revealed that Na+ enhanced microbial aggregate electron storage capacity, reduced electron transfer resistance, and promoted extracellular polymeric substance (EPS) secretion of tyrosine-like proteins and humic acid-like substances, thereby strengthening extracellular electron transfer. Key metabolic indicators showed 26.2 % higher coenzyme F420 and 37.4 % higher intracellular ATP levels in Na+-treated groups. Metagenomic analysis confirmed that Na+ upregulated genes encoding reverse methanogenesis enzymes (Mcr, Mtr) and membrane-bound electron transfer complexes (Fpo, HdrDE), while downregulating intracellular chromate reductase (ChrR) genes, indicating that EET-mediated extracellular Cr(VI) reduction played a critical role under Na+ stimulation. This study first reveals the mechanism of Na+-promoted AOM-coupled Cr(VI) reduction via enhanced energy metabolism and electron transfer, providing a crucial theoretical basis for methane-driven Cr(VI) remediation.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>本研究探討祕魯農村地區嬰兒缺鐵性貧血（IDA）與母親母乳（hBM）菌相之間的關聯。研究對象為 46 對母嬰，透過 16S rRNA 定序分析母乳微生物群落，發現母乳菌相以鏈球菌屬（Streptococcus）與葡萄球菌屬（Staphylococcus）為優勢菌群。研究結果顯示，非貧血組嬰兒的母親，其母乳具備較高的細菌豐富度。此外，IDA 組嬰兒母親的母乳中，棒狀桿菌屬（Corynebacterium）與不動桿菌屬（Acinetobacter）等細菌豐度較高，而鏈球菌屬則呈現下降趨勢。此研究發現母乳微生物群組成可能與嬰兒貧血狀態相關，雖無法直接證實因果關係，但為後續探討嬰兒貧血的致病機制提供了重要的微生物學線索。</t>
+          <t>本研究旨在探討跨膜電化學梯度驅動者——鈉離子（Na+），如何調控「甲烷厭氧氧化（AOM）耦合六價鉻 [Cr(VI)] 生物還原系統」的代謝活性與電子傳遞機制。研究發現，添加 NaCl 能顯著提升 Cr(VI) 的去除效率。微生物分析顯示，Na+ 富集了具 AOM 能力的 *Methanobacterium* 與具胞外電子傳遞（EET）能力的電活性細菌，形成協同共生關係。此外，Na+ 提高了微生物的胞內 ATP 與輔酶 F420 水平，並促進胞外聚合物（EPS）分泌以降低電子傳遞阻力。總體基因體學分析進一步證實，Na+ 上調了逆向產甲烷及膜結合電子傳遞複合物的關鍵基因。本研究首次審視並揭示了 Na+ 促進 AOM 耦合 Cr(VI) 還原的生物能量學機制，為利用甲烷進行重金屬生物整治提供了重要理論基礎。</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2192,37 +2188,35 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42658871/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42660365/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>42660360</t>
+          <t>42660108</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Elucidating the aromatic formation of humus via quorum sensing and redox function of thermophilic microbiota in compost.</t>
+          <t>Group C Orthobunyavirus Infection in a Patient from the Amazon Putumayo Region of Colombia During an Oropouche Fever Epidemic.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bioresource technology</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>9</v>
-      </c>
+          <t>The American journal of tropical medicine and hygiene</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>metagenomics, others</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>1位急性發熱疾病患者（單一病例）</t>
         </is>
       </c>
       <c r="G34" t="b">
@@ -2230,12 +2224,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Quorum sensing (QS) modulates bacterial metabolism to regulate humus formation. However, the functional interaction modes of signal molecules, QS-related proteins, and microbial humification function during composting remain unclear. This study aimed to clarify the role of QS-related gene expression in regulating humification via applying metagenomics and metaproteomics. Combined addition of MnSO4 and Fe0 (CMF) significantly raised humic acid (HA) content (33.53 mg g-1) and polymerization degree (2.60) compared with other treatments. Multi-dimensional results revealed that CMF-derived HA and its products exhibited greater thermal stability, high aromaticity, and practical applicability. CMF increased the relative abundances of most QS-related and humification-related oxidoreductase genes throughout composting, especially during the thermophilic stage. Metaproteomic profiles verified that both QS expression and humification metabolism were hyperactivated during the thermophilic stage of CMF. Correlation analysis showed that QS gene expression potentially and preferentially influenced lignin-protein and polyphenol pathways during humification. Overall, CMF enriched thermophiles (Bacillota, Chloroflexota, and Myxococcota), further up-regulated the expression of major QS-related genes [K02035 (ABC.PE.S), K13075 (ahlD), K14645, K15580 (oppA), and K02055 (ABC.SP.S)], elevated levels of signal molecules, and promoted QS effects. Network analysis, qPCR, and simulated in vitro validation experiments confirmed that the response of key QS modules [K13075 (ahlD) and 3-OXO-C8-HSL] potentially facilitated interspecies communication and cooperation among bacteria, which concurrently enhanced downstream microbial metabolic behaviors (microbial redox activities and the metabolism of carbohydrates and amino acids) that aid in driving HA aromatization. This work provides new insight into the ecological roles of QS-related microbes and their precise regulation of compost humification.</t>
+          <t>Orthobunyaviruses, one of the largest and most diverse genera of viruses, include numerous reassortant viruses and present diagnostic challenges due to similar clinical presentations with other arboviral infections. The detection and isolation of a group C orthobunyavirus from a patient with acute febrile illness from Puerto Ospina, Putumayo Department, Colombia during the 2023-2024 Latin American Oropouche fever regional outbreaks are reported in the present study. Using a vertebrate virus-focused metagenomics sequencing approach with VirCapSeq-VERT, a virus related to the Caraparu complex was identified, and a virus isolate was obtained. Although limited to a single case and without serological or longitudinal clinical confirmation, these findings underscore the value of unbiased molecular approaches for unresolved febrile illness diagnosis in endemic settings such as the Amazon basin.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>本研究旨在利用總體基因體學與總體蛋白質組學技術，探討群體感應（QS）相關基因表達在堆肥腐植化過程中的調節機制。研究發現，聯合添加硫酸錳與零價鐵（CMF）能顯著提高腐植酸（HA）的含量、熱穩定性與芳香度。CMF顯著富集了高溫微生物（如Bacillota、Chloroflexota和Myxococcota），並在高溫期上調關鍵QS相關基因（如ahlD）的表達與訊號分子水平。網路分析與體外實驗進一步證實，關鍵QS模組促進了菌群間的交流合作，進而增強下游的微生物氧化還原活性及碳水化合物與氨基酸代謝，共同驅動腐植酸的芳香化。本研究為QS微生物在堆肥腐植化中的生態角色與精準調控提供了全新見解。</t>
+          <t>本研究旨在調查2023-2024年拉丁美洲奧羅普切熱（Oropouche fever）疫情期間，哥倫比亞亞馬遜地區一名急性發熱患者的病因。研究團隊採用針對脊椎動物病毒的總體基因體學（宏基因組）定序技術（VirCapSeq-VERT），成功鑑定並分離出一種與Caraparu複合體相關的C群正布尼亞病毒（Group C Orthobunyavirus）。由於此類病毒臨床表現與其他蟲媒病毒相似，診斷極具挑戰。本研究雖僅基於單一病例，但其結果強調了在亞馬遜盆地等流行病疫區，使用無偏向性分子檢測技術對於診斷不明原因發熱疾病的重要臨床與科學價值。</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2245,35 +2239,35 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42660360/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42660108/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>42658844</t>
+          <t>42660482</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Enrichment and Characterization of a Haloalkaline-tolerant Anammox Bacterium.</t>
+          <t>Artificial light pollution alters epilithic microbial communities and functional biodeterioration-related functional potentials in subterranean sandstone environments.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>The ISME journal</t>
+          <t>Environmental pollution (Barking, Essex : 1987)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>metagenomics, small genome, others (transcriptional profiling)</t>
+          <t>16S, metagenomics</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>未提及（研究基於特定實驗室富集培養物之實驗與分析）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G35" t="b">
@@ -2281,12 +2275,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Metagenomic surveys have substantially expanded the known diversity of anaerobic ammonium-oxidizing (anammox) bacteria. However, the physiological traits of newly proposed anammox genera remain largely hypothetical due to the lack of cultured representatives. Although niche differentiation driven by salinity, organic substrates, and oxygen is well documented in anammox bacteria, adaptations to alkaline environments remain uncharacterized. Moreover, no anammox lineage has been identified as an alkaline specialist. Herein, we report the enrichment (&gt;80% relative abundance) of an anammox bacterium, provisionally named Candidatus Loosdrechtia alkalitolerans, which represents the cultured member of the genus Ca. Loosdrechtia. Ca. L. alkalitolerans exhibits marked haloalkaline tolerance, outcompeting other freshwater anammox genera under long-term saline-alkaline stress conditions (0.5% NaCl; pH~9.13). Comparative genomics revealed that among freshwater anammox lineages, only Ca. L. alkalitolerans encodes a complete multiple resistance and pH adaptation (Mrp) cation/proton antiporter operon. Batch assays with transcriptional profiling demonstrated that sodium addition upregulated mrp expression and recovered anammox activity under alkaline stress, suggesting that Mrp-mediated cation/proton exchange may contribute to pH homeostasis in Ca. L. alkalitolerans. Furthermore, database mining revealed that the habitat of Ca. L. alkalitolerans is not restricted to haloalkaline environments, but extends to diverse freshwater and wastewater ecosystems. These findings provide mechanistic insight into saline-alkaline tolerance in anammox bacteria, expanding understanding of their physiological plasticity and ecological roles.</t>
+          <t>Artificial light pollution represents an important anthropogenic disturbance in subterranean heritage environments, yet its associations with epilithic microbial communities and biodeterioration processes remain poorly understood. In tourist-accessible subterranean caves, artificial illumination creates persistent illuminated areas on stone surfaces that may alter microbial community assembly and biogeochemical functions associated with biofilm development. Here, the Longyou Grottoes, a large underground sandstone cave complex in Zhejiang, China, were investigated using 16S rRNA gene sequencing and metagenomics. Bacterial communities dominated all samples (&gt;98% relative abundance). Cyanobacteriota were enriched under artificial light and sunlight (&gt;40%), whereas Pseudomonadota and Actinomycetota prevailed in darkness. Dark sites exhibited higher bacterial alpha diversity and more complex co-occurrence networks. Compared with sunlight and dark environments, the artificial-light environment was associated with greater stochasticity in bacterial community assembly, broader niche breadth, and lower niche overlap. Metabolic potential analysis further revealed light-dependent metabolic shifts: artificial light enhanced assimilatory nitrogen and sulfur metabolism, sunlight promoted nitrogen fixation, and darkness favored nitrification, denitrification, and sulfur oxidation. However, bacterial community patterns were also associated with temperature, humidity, pH, and soluble salts, indicating that the observed differentiation reflected the combined influence of light and environmental heterogeneity. These findings identify artificial lighting as an important and manageable environmental factor associated with epilithic bacterial communities and provide a basis for integrating lighting management with environmental control in the preventive conservation of subterranean sandstone heritage.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>本研究成功富集並鑑定出一種耐鹽鹼的厭氧氨氧化（Anammox）細菌，命名為 *Candidatus Loosdrechtia alkalitolerans*。該菌株在長期高鹽、高鹼（0.5% NaCl，pH 9.13）環境下表現出強大的競爭優勢。透過基因體比較分析，研究發現該菌株含有特殊的 Mrp 陽離子/質子反向轉運蛋白操縱子，這是其適應鹼性環境的關鍵機制；轉錄組分析進一步證實，在鹼性壓力下，補充鈉離子可上調 Mrp 表現並恢復其代謝活性。此發現不僅揭示了厭氧氨氧化菌應對鹽鹼逆境的生理分子機制，證明了該菌在廣泛的淡水與廢水生態系統中具有潛在的生態地位，更為未來工業廢水處理中的脫氮技術應用提供了理論基礎與科學見解。</t>
+          <t>本研究探討人造光污染對地下砂岩古蹟（龍游石窟）岩表微生物群落及生物降解功能的影響。透過16S rRNA定序與總體基因體學分析，發現光照顯著改變群落結構：人工光與日光下藍菌門富集，而黑暗環境則由假單胞菌門和放線菌門主導，且黑暗處具更高的多樣性與網絡複雜度。代謝潛力分析顯示，人工光增強了同化性氮、硫代謝，而黑暗則利於硝化與硫氧化。此外，群落分化也與溫濕度及pH等環境因子相關。本研究證實人造光源是調控地下微生物的重要因子，為砂岩文物的預防性保護與照光管理提供科學依據。</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2296,37 +2290,37 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42658844/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42660482/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>42656127</t>
+          <t>42660360</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Development and Validation of Mock Communities as Quality Control Materials for Clinical Metagenomic Next-Generation Sequencing.</t>
+          <t>Elucidating the aromatic formation of humus via quorum sensing and redox function of thermophilic microbiota in compost.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Annals of laboratory medicine</t>
+          <t>Bioresource technology</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3.9</v>
+        <v>9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>metagenomics, others</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>25 次重複分析（針對開發出的四種模擬群落進行評估）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G36" t="b">
@@ -2334,12 +2328,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Metagenomic next-generation sequencing (NGS) enables comprehensive detection of a broad spectrum of microorganisms. However, its clinical application faces two major challenges: the development of appropriate microbiome-based biomarkers and the need to ensure the reproducibility and quality of the microbiome analytical workflow. Therefore, we developed four types of bead-based mock communities as standard materials for microbiome analysis and evaluated potential experimental biases arising from nucleic acid extraction and sequence analysis. Mock communities were assembled from strains isolated from clinical specimens and selected considering Gram reaction, taxonomic phylogeny, and prevalence, and processed into frozen beads. The communities were analyzed using shotgun whole-metagenome sequencing. The effect of DNA extraction kit choice was evaluated using the Thermo Fisher Scientific MagMAX Microbiome Ultra Nucleic Acid Isolation Kit and Qiagen PowerSoil Kit. Four types of mock communities comprising 26 species commonly found in the gastrointestinal tract, respiratory tract, skin, and genital tract plus cerebrospinal fluid were developed considering Gram reaction, GC content, and phylogenetic distribution. Across 25 repeated analyses, the median repeatability of each taxon was 18.97% (range, 2.87%-107.38%), while within-laboratory imprecision was 26.22% (range, 9.26%-153.83%). Repeatability remained below 10% for most dominant taxa with relative abundances &gt;20%. The choice of DNA extraction kit had a significant effect on taxonomic distributions. Microbial mock communities are essential QC materials for clinical metagenomic NGS. Further studies are needed to minimize variability and establish a standardized protocol for clinical implementation.</t>
+          <t>Quorum sensing (QS) modulates bacterial metabolism to regulate humus formation. However, the functional interaction modes of signal molecules, QS-related proteins, and microbial humification function during composting remain unclear. This study aimed to clarify the role of QS-related gene expression in regulating humification via applying metagenomics and metaproteomics. Combined addition of MnSO4 and Fe0 (CMF) significantly raised humic acid (HA) content (33.53 mg g-1) and polymerization degree (2.60) compared with other treatments. Multi-dimensional results revealed that CMF-derived HA and its products exhibited greater thermal stability, high aromaticity, and practical applicability. CMF increased the relative abundances of most QS-related and humification-related oxidoreductase genes throughout composting, especially during the thermophilic stage. Metaproteomic profiles verified that both QS expression and humification metabolism were hyperactivated during the thermophilic stage of CMF. Correlation analysis showed that QS gene expression potentially and preferentially influenced lignin-protein and polyphenol pathways during humification. Overall, CMF enriched thermophiles (Bacillota, Chloroflexota, and Myxococcota), further up-regulated the expression of major QS-related genes [K02035 (ABC.PE.S), K13075 (ahlD), K14645, K15580 (oppA), and K02055 (ABC.SP.S)], elevated levels of signal molecules, and promoted QS effects. Network analysis, qPCR, and simulated in vitro validation experiments confirmed that the response of key QS modules [K13075 (ahlD) and 3-OXO-C8-HSL] potentially facilitated interspecies communication and cooperation among bacteria, which concurrently enhanced downstream microbial metabolic behaviors (microbial redox activities and the metabolism of carbohydrates and amino acids) that aid in driving HA aromatization. This work provides new insight into the ecological roles of QS-related microbes and their precise regulation of compost humification.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>本研究旨在解決臨床宏基因組次世代定序（mNGS）在品質控制與再現性上的挑戰，開發了四種基於珠粒的「模擬微生物群落」（mock communities）作為標準品。這些群落涵蓋了腸道、呼吸道、皮膚、生殖道及腦脊髓液中常見的 26 種菌株。研究透過鳥槍法全宏基因體定序（shotgun metagenomics）評估了不同 DNA 萃取試劑盒（MagMAX 與 PowerSoil）及實驗流程對結果的偏誤影響。結果顯示，微生物的檢測豐度會顯著受到萃取試劑盒選擇的干擾，且在 25 次重複實驗中，群落組成存在一定的實驗室內誤差。此研究確立了模擬群落作為臨床 mNGS 品質控制材料的重要性，對於推動微生物組檢測的標準化流程與臨床應用具有關鍵價值。</t>
+          <t>本研究旨在利用總體基因體學與總體蛋白質組學技術，探討群體感應（QS）相關基因表達在堆肥腐植化過程中的調節機制。研究發現，聯合添加硫酸錳與零價鐵（CMF）能顯著提高腐植酸（HA）的含量、熱穩定性與芳香度。CMF顯著富集了高溫微生物（如Bacillota、Chloroflexota和Myxococcota），並在高溫期上調關鍵QS相關基因（如ahlD）的表達與訊號分子水平。網路分析與體外實驗進一步證實，關鍵QS模組促進了菌群間的交流合作，進而增強下游的微生物氧化還原活性及碳水化合物與氨基酸代謝，共同驅動腐植酸的芳香化。本研究為QS微生物在堆肥腐植化中的生態角色與精準調控提供了全新見解。</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2349,37 +2343,35 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42656127/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42660360/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>42660365</t>
+          <t>42658844</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Enhancing Cr(VI) bioreduction via Na+-stimulated intracellular energy metabolism and electron transfer using methane as electron donor.</t>
+          <t>Enrichment and Characterization of a Haloalkaline-tolerant Anammox Bacterium.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bioresource technology</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>9</v>
-      </c>
+          <t>The ISME journal</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>16S, metagenomics</t>
+          <t>metagenomics, small genome, others (transcriptional profiling)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（研究基於特定實驗室富集培養物之實驗與分析）</t>
         </is>
       </c>
       <c r="G37" t="b">
@@ -2387,12 +2379,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Anaerobic oxidation of methane (AOM) coupled with Cr(VI) bioreduction process offers a cost-effective pathway to simultaneously mitigate methane emissions and remediate Cr(VI) contamination. However, its practical application is limited by insufficient intracellular energy generation and low electron transfer efficiency. This study elucidated the regulatory role and mechanism of Na+, a transmembrane electrochemical gradient driver, on the metabolic activity and electron transfer of this coupled system. Batch experiments demonstrated that NaCl addition significantly improved Cr(VI) reduction efficiency, achieving complete removal in the treatment group by the end of the first cycle compared to only 79.8 % in the control. Microbial community analysis showed that Na+ enriched AOM-capable Methanobacterium and extracellular electron transfer (EET)-capable electroactive bacterium unclassified_o_DTU014, which likely formed a syntrophic consortium to mediate Cr(VI) reduction. Electrochemical measurements and 3D-EEM spectroscopy revealed that Na+ enhanced microbial aggregate electron storage capacity, reduced electron transfer resistance, and promoted extracellular polymeric substance (EPS) secretion of tyrosine-like proteins and humic acid-like substances, thereby strengthening extracellular electron transfer. Key metabolic indicators showed 26.2 % higher coenzyme F420 and 37.4 % higher intracellular ATP levels in Na+-treated groups. Metagenomic analysis confirmed that Na+ upregulated genes encoding reverse methanogenesis enzymes (Mcr, Mtr) and membrane-bound electron transfer complexes (Fpo, HdrDE), while downregulating intracellular chromate reductase (ChrR) genes, indicating that EET-mediated extracellular Cr(VI) reduction played a critical role under Na+ stimulation. This study first reveals the mechanism of Na+-promoted AOM-coupled Cr(VI) reduction via enhanced energy metabolism and electron transfer, providing a crucial theoretical basis for methane-driven Cr(VI) remediation.</t>
+          <t>Metagenomic surveys have substantially expanded the known diversity of anaerobic ammonium-oxidizing (anammox) bacteria. However, the physiological traits of newly proposed anammox genera remain largely hypothetical due to the lack of cultured representatives. Although niche differentiation driven by salinity, organic substrates, and oxygen is well documented in anammox bacteria, adaptations to alkaline environments remain uncharacterized. Moreover, no anammox lineage has been identified as an alkaline specialist. Herein, we report the enrichment (&gt;80% relative abundance) of an anammox bacterium, provisionally named Candidatus Loosdrechtia alkalitolerans, which represents the cultured member of the genus Ca. Loosdrechtia. Ca. L. alkalitolerans exhibits marked haloalkaline tolerance, outcompeting other freshwater anammox genera under long-term saline-alkaline stress conditions (0.5% NaCl; pH~9.13). Comparative genomics revealed that among freshwater anammox lineages, only Ca. L. alkalitolerans encodes a complete multiple resistance and pH adaptation (Mrp) cation/proton antiporter operon. Batch assays with transcriptional profiling demonstrated that sodium addition upregulated mrp expression and recovered anammox activity under alkaline stress, suggesting that Mrp-mediated cation/proton exchange may contribute to pH homeostasis in Ca. L. alkalitolerans. Furthermore, database mining revealed that the habitat of Ca. L. alkalitolerans is not restricted to haloalkaline environments, but extends to diverse freshwater and wastewater ecosystems. These findings provide mechanistic insight into saline-alkaline tolerance in anammox bacteria, expanding understanding of their physiological plasticity and ecological roles.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>本研究旨在探討跨膜電化學梯度驅動者——鈉離子（Na+），如何調控「甲烷厭氧氧化（AOM）耦合六價鉻 [Cr(VI)] 生物還原系統」的代謝活性與電子傳遞機制。研究發現，添加 NaCl 能顯著提升 Cr(VI) 的去除效率。微生物分析顯示，Na+ 富集了具 AOM 能力的 *Methanobacterium* 與具胞外電子傳遞（EET）能力的電活性細菌，形成協同共生關係。此外，Na+ 提高了微生物的胞內 ATP 與輔酶 F420 水平，並促進胞外聚合物（EPS）分泌以降低電子傳遞阻力。總體基因體學分析進一步證實，Na+ 上調了逆向產甲烷及膜結合電子傳遞複合物的關鍵基因。本研究首次審視並揭示了 Na+ 促進 AOM 耦合 Cr(VI) 還原的生物能量學機制，為利用甲烷進行重金屬生物整治提供了重要理論基礎。</t>
+          <t>本研究成功富集並鑑定出一種耐鹽鹼的厭氧氨氧化（Anammox）細菌，命名為 *Candidatus Loosdrechtia alkalitolerans*。該菌株在長期高鹽、高鹼（0.5% NaCl，pH 9.13）環境下表現出強大的競爭優勢。透過基因體比較分析，研究發現該菌株含有特殊的 Mrp 陽離子/質子反向轉運蛋白操縱子，這是其適應鹼性環境的關鍵機制；轉錄組分析進一步證實，在鹼性壓力下，補充鈉離子可上調 Mrp 表現並恢復其代謝活性。此發現不僅揭示了厭氧氨氧化菌應對鹽鹼逆境的生理分子機制，證明了該菌在廣泛的淡水與廢水生態系統中具有潛在的生態地位，更為未來工業廢水處理中的脫氮技術應用提供了理論基礎與科學見解。</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2402,35 +2394,37 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42660365/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42658844/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>42660482</t>
+          <t>42657522</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Artificial light pollution alters epilithic microbial communities and functional biodeterioration-related functional potentials in subterranean sandstone environments.</t>
+          <t>Resistant starch alleviates intestinal fibrosis involving an acetate-mediated HDAC2-H3K27ac axis in fibroblasts.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Environmental pollution (Barking, Essex : 1987)</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>Food &amp; function</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>5.4</v>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>16S, metagenomics</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（研究使用 DSS 誘導的小鼠模型以及人類與小鼠的原代纖維母細胞，但未具體說明樣本數）</t>
         </is>
       </c>
       <c r="G38" t="b">
@@ -2438,12 +2432,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Artificial light pollution represents an important anthropogenic disturbance in subterranean heritage environments, yet its associations with epilithic microbial communities and biodeterioration processes remain poorly understood. In tourist-accessible subterranean caves, artificial illumination creates persistent illuminated areas on stone surfaces that may alter microbial community assembly and biogeochemical functions associated with biofilm development. Here, the Longyou Grottoes, a large underground sandstone cave complex in Zhejiang, China, were investigated using 16S rRNA gene sequencing and metagenomics. Bacterial communities dominated all samples (&gt;98% relative abundance). Cyanobacteriota were enriched under artificial light and sunlight (&gt;40%), whereas Pseudomonadota and Actinomycetota prevailed in darkness. Dark sites exhibited higher bacterial alpha diversity and more complex co-occurrence networks. Compared with sunlight and dark environments, the artificial-light environment was associated with greater stochasticity in bacterial community assembly, broader niche breadth, and lower niche overlap. Metabolic potential analysis further revealed light-dependent metabolic shifts: artificial light enhanced assimilatory nitrogen and sulfur metabolism, sunlight promoted nitrogen fixation, and darkness favored nitrification, denitrification, and sulfur oxidation. However, bacterial community patterns were also associated with temperature, humidity, pH, and soluble salts, indicating that the observed differentiation reflected the combined influence of light and environmental heterogeneity. These findings identify artificial lighting as an important and manageable environmental factor associated with epilithic bacterial communities and provide a basis for integrating lighting management with environmental control in the preventive conservation of subterranean sandstone heritage.</t>
+          <t>Dietary fibre-based interventions are of growing interest for the prevention and treatment of digestive diseases. In this study, we investigated the effect of resistant starch (RS) on intestinal fibrosis, a stricturing condition driven by excessive extracellular matrix (ECM) accumulation. RS was found to alleviate intestinal fibrosis in a dextran sulfate sodium (DSS)-induced chronic colitis mouse model, as evidenced by restored colon length, reduced ECM deposition (fibronectin and collagen I), and decreased levels of α-smooth muscle actin. Given that RS is fermented by the gut microbiota in the colon, metagenomic sequencing revealed that RS reshaped the composition of the gut microbiota and increased the abundance of beneficial gut bacteria, including Bacteroides acidifaciens, Faecalibaculum rodentium, and Bifidobacterium pseudolongum, which are known to enhance the production of short-chain fatty acids. Targeted metabolomic analysis further showed a marked increase in acetate levels, which was associated with reduced intestinal fibrosis. However, direct in vivo evidence that acetate is required for the anti-fibrotic effect of RS remains lacking. Using human (CCD-18Co) and primary mouse intestinal fibroblasts, the major ECM-producing cells that drive fibrosis progression, we demonstrated that acetate inhibited TGF-β-induced fibroblast activation by inhibiting histone deacetylase 2, thereby enhancing the acetylation level of histone H3 at lysine 27. Collectively, these results suggest a potential microbial-metabolic-epigenetic axis linking RS and acetate to fibrosis attenuation, which awaits causal validation in vivo. This axis holds promise as a therapeutic target for fibrotic diseases.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>本研究探討人造光污染對地下砂岩古蹟（龍游石窟）岩表微生物群落及生物降解功能的影響。透過16S rRNA定序與總體基因體學分析，發現光照顯著改變群落結構：人工光與日光下藍菌門富集，而黑暗環境則由假單胞菌門和放線菌門主導，且黑暗處具更高的多樣性與網絡複雜度。代謝潛力分析顯示，人工光增強了同化性氮、硫代謝，而黑暗則利於硝化與硫氧化。此外，群落分化也與溫濕度及pH等環境因子相關。本研究證實人造光源是調控地下微生物的重要因子，為砂岩文物的預防性保護與照光管理提供科學依據。</t>
+          <t>本研究探討抗性澱粉（RS）對腸道纖維化的改善作用及其潛在機制。透過 DSS 誘導的小鼠結腸炎模型，研究發現 RS 可有效減輕腸道纖維化並減少細胞外基質堆積。宏基因體定序顯示 RS 能重塑腸道菌群，增加如 *Bacteroides acidifaciens* 等短鏈脂肪酸產生菌的豐度；代謝體分析進一步證實乙酸（acetate）水平顯著上升。機制研究揭示，乙酸能抑制纖維母細胞中 HDAC2 的活性，進而提升組蛋白 H3K27 的乙醯化水平，抑制 TGF-β 誘導的纖維母細胞活化。本研究提出了一條「微生物-代謝-表觀遺傳」軸線，指出 RS 可藉由促進乙酸生成來對抗腸道纖維化，為治療纖維化相關疾病提供了新的科學依據與潛在治療靶點。</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2453,35 +2447,37 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42660482/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42657522/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>42660108</t>
+          <t>42658871</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Group C Orthobunyavirus Infection in a Patient from the Amazon Putumayo Region of Colombia During an Oropouche Fever Epidemic.</t>
+          <t>Breastmilk microbiota and its association with infant iron deficiency anaemia: A 16S rRNA metagenomic study in Peruvian mothers cohort.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>The American journal of tropical medicine and hygiene</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>PloS one</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2.6</v>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>16S</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1位急性發熱疾病患者（單一病例）</t>
+          <t>46 對母嬰（46 個母乳檢體）</t>
         </is>
       </c>
       <c r="G39" t="b">
@@ -2489,12 +2485,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Orthobunyaviruses, one of the largest and most diverse genera of viruses, include numerous reassortant viruses and present diagnostic challenges due to similar clinical presentations with other arboviral infections. The detection and isolation of a group C orthobunyavirus from a patient with acute febrile illness from Puerto Ospina, Putumayo Department, Colombia during the 2023-2024 Latin American Oropouche fever regional outbreaks are reported in the present study. Using a vertebrate virus-focused metagenomics sequencing approach with VirCapSeq-VERT, a virus related to the Caraparu complex was identified, and a virus isolate was obtained. Although limited to a single case and without serological or longitudinal clinical confirmation, these findings underscore the value of unbiased molecular approaches for unresolved febrile illness diagnosis in endemic settings such as the Amazon basin.</t>
+          <t>Anaemia is one of the most important public health challenges in developing countries. The global burden is estimated at 1.8 billion people, affecting approximately 30% of all children. Despite the implementation of multiple strategies over several decades, up to 42.5% of children under 3 years of age suffer anaemia in rural areas of Peru. We studied the microbiota of breastmilk (hBM) from mothers with children under the age of 1 and analysed its association with their iron deficiency anaemia. 46 mother-child pairs were recruited from Talara, a town on the northern coast of Peru and classified according to the clinical status of the children. Children with anaemia were also tested for ferritin level to classify them as iron deficiency anaemia (IDA) or non-iron deficiency anaemia (non-IDA). hBM samples were taken from the mothers after careful instruction to reduce the risk of sample contamination and the microbiome was analyzed using 16S rRNA sequencing. Streptococcus and Staphylococcus were the predominant genera, with 90% of bacterial abundance being explained by 14 genera. Alpha diversity analysis showed that hBM from mothers of children with non-IDA had higher levels of bacterial richness than hBM from healthy (p &lt; 0.01) and IDA (p &lt; 0.05) participants. Principal coordinates analysis did not yield differential clusters but showed a disparity in the spread of samples for non-IDA group when compared with the other groups. IDA group showed higher burden of Corynebacterium, Acinetobacter, Paludibacter and Nitrospira, while exhibiting a trend towards a lower burden of Streptococcus. No statistically significant differences were identified on demographic characteristics. This study suggests that hBM microbiota may differ in mothers of children with IDA and non-IDA, highlighting the necessity of further in-depth research to elucidate potential factors associated with its pathogenesis.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>本研究旨在調查2023-2024年拉丁美洲奧羅普切熱（Oropouche fever）疫情期間，哥倫比亞亞馬遜地區一名急性發熱患者的病因。研究團隊採用針對脊椎動物病毒的總體基因體學（宏基因組）定序技術（VirCapSeq-VERT），成功鑑定並分離出一種與Caraparu複合體相關的C群正布尼亞病毒（Group C Orthobunyavirus）。由於此類病毒臨床表現與其他蟲媒病毒相似，診斷極具挑戰。本研究雖僅基於單一病例，但其結果強調了在亞馬遜盆地等流行病疫區，使用無偏向性分子檢測技術對於診斷不明原因發熱疾病的重要臨床與科學價值。</t>
+          <t>本研究探討祕魯農村地區嬰兒缺鐵性貧血（IDA）與母親母乳（hBM）菌相之間的關聯。研究對象為 46 對母嬰，透過 16S rRNA 定序分析母乳微生物群落，發現母乳菌相以鏈球菌屬（Streptococcus）與葡萄球菌屬（Staphylococcus）為優勢菌群。研究結果顯示，非貧血組嬰兒的母親，其母乳具備較高的細菌豐富度。此外，IDA 組嬰兒母親的母乳中，棒狀桿菌屬（Corynebacterium）與不動桿菌屬（Acinetobacter）等細菌豐度較高，而鏈球菌屬則呈現下降趨勢。此研究發現母乳微生物群組成可能與嬰兒貧血狀態相關，雖無法直接證實因果關係，但為後續探討嬰兒貧血的致病機制提供了重要的微生物學線索。</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2504,37 +2500,37 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42660108/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42658871/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>42657522</t>
+          <t>42660466</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Resistant starch alleviates intestinal fibrosis involving an acetate-mediated HDAC2-H3K27ac axis in fibroblasts.</t>
+          <t>Polystyrene nanoplastics exposure induces reproductive toxicity in male mice associated with the gut-liver/testis axis.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Food &amp; function</t>
+          <t>Toxicology and applied pharmacology</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>metagenomics, metabolomics</t>
+          <t>metagenomics, others</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>未提及（研究使用 DSS 誘導的小鼠模型以及人類與小鼠的原代纖維母細胞，但未具體說明樣本數）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G40" t="b">
@@ -2542,12 +2538,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Dietary fibre-based interventions are of growing interest for the prevention and treatment of digestive diseases. In this study, we investigated the effect of resistant starch (RS) on intestinal fibrosis, a stricturing condition driven by excessive extracellular matrix (ECM) accumulation. RS was found to alleviate intestinal fibrosis in a dextran sulfate sodium (DSS)-induced chronic colitis mouse model, as evidenced by restored colon length, reduced ECM deposition (fibronectin and collagen I), and decreased levels of α-smooth muscle actin. Given that RS is fermented by the gut microbiota in the colon, metagenomic sequencing revealed that RS reshaped the composition of the gut microbiota and increased the abundance of beneficial gut bacteria, including Bacteroides acidifaciens, Faecalibaculum rodentium, and Bifidobacterium pseudolongum, which are known to enhance the production of short-chain fatty acids. Targeted metabolomic analysis further showed a marked increase in acetate levels, which was associated with reduced intestinal fibrosis. However, direct in vivo evidence that acetate is required for the anti-fibrotic effect of RS remains lacking. Using human (CCD-18Co) and primary mouse intestinal fibroblasts, the major ECM-producing cells that drive fibrosis progression, we demonstrated that acetate inhibited TGF-β-induced fibroblast activation by inhibiting histone deacetylase 2, thereby enhancing the acetylation level of histone H3 at lysine 27. Collectively, these results suggest a potential microbial-metabolic-epigenetic axis linking RS and acetate to fibrosis attenuation, which awaits causal validation in vivo. This axis holds promise as a therapeutic target for fibrotic diseases.</t>
+          <t>Environmental nanoplastics are increasingly prevalent in global environments and represent an emerging systemic health risk, yet the mechanistic links between nanoplastic exposure and multi-organ dysfunction in mammals remain incompletely characterized. We integrated phenotypic assessments, gut shotgun metagenomics, and dual-organ transcriptomics to investigate the toxic effects of 28-day oral exposure to polystyrene nanoplastics (PS-NPs) in male CD-1 mice. PS-NPs induced a non-monotonic dose-dependent response, characterized by significant body weight loss at high doses, severe impairment of sperm motility, and progressive epididymal histopathological lesions. Gut metagenomics revealed significant microbiota dysbiosis, including an elevated Firmicutes/Bacteroidota ratio and marked depletion of beneficial commensal bacteria such as Ligilactobacillus murinus. Hepatic transcriptomics identified dysregulation of metabolic, detoxification, and circadian rhythm pathways, while testicular transcriptomics identified sustained transcriptional downregulation of genes annotated to steroid hormone biosynthesis and alterations in FoxO and apoptosis-related signaling. Spearman correlation network analysis identified associations between specific microbial shifts and organ-specific transcriptional alterations, providing a hypothesis-generating framework for the proposed gut-liver/testis axis. Together, these findings indicate that, under the present experimental conditions, oral PS-NPs exposure was associated with gut microbial dysbiosis, hepatic transcriptional perturbations, reduced sperm motility, and epididymal histopathological alterations, while the mechanistic relationships among these changes require further experimental validation.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>本研究探討抗性澱粉（RS）對腸道纖維化的改善作用及其潛在機制。透過 DSS 誘導的小鼠結腸炎模型，研究發現 RS 可有效減輕腸道纖維化並減少細胞外基質堆積。宏基因體定序顯示 RS 能重塑腸道菌群，增加如 *Bacteroides acidifaciens* 等短鏈脂肪酸產生菌的豐度；代謝體分析進一步證實乙酸（acetate）水平顯著上升。機制研究揭示，乙酸能抑制纖維母細胞中 HDAC2 的活性，進而提升組蛋白 H3K27 的乙醯化水平，抑制 TGF-β 誘導的纖維母細胞活化。本研究提出了一條「微生物-代謝-表觀遺傳」軸線，指出 RS 可藉由促進乙酸生成來對抗腸道纖維化，為治療纖維化相關疾病提供了新的科學依據與潛在治療靶點。</t>
+          <t>本研究探討口服聚苯乙烯奈米塑料（PS-NPs）28天對雄性CD-1小鼠的毒性效應及其作用機制。研究發現，PS-NPs暴露會引發非單調劑量依賴性反應，導致小鼠體重顯著減輕、精子活力嚴重受損及附睾病理病變。腸道總體基因體學分析顯示，PS-NPs引起腸道菌群失調（厚壁菌門/擬桿菌門比例升高，有益菌如鼠乳桿菌顯著減少）。雙器官轉錄組學分析進一步證實，肝臟中代謝、解毒與晝夜節律途徑失調，而睾丸中類固醇激素合成基因持續下調且凋亡信號改變。本研究首次揭示了奈米塑料誘導生殖毒性與「腸-肝/睾丸軸」的關聯，為環境微塑料的哺乳動物多器官毒性機制提供了重要科學依據。</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2557,27 +2553,29 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42657522/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42660466/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>42647759</t>
+          <t>42647600</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The Gut Microbiome in Multiple Sclerosis.</t>
+          <t>Urogenital immune signatures are associated with birth outcomes after maternal urinary tract infection.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Neurology(R) neuroimmunology &amp; neuroinflammation</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>Science translational medicine</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>14.6</v>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>others</t>
@@ -2593,12 +2591,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Multiple sclerosis (MS) is a chronic inflammatory demyelinating disease of the CNS whose risk and course are shaped by both genetic and environmental factors, among which the intestinal microbiota has emerged as a key, potentially modifiable contributor. People with MS frequently display altered gut microbiota, characterized by depletion of fiber-fermenting, short-chain fatty acid (SCFA)-producing commensals, and expansion of taxa associated with mucus degradation and proinflammatory metabolism. These compositional shifts are paralleled by broad changes in blood and CSF metabolites, including reduced SCFAs, tryptophan-derived aryl hydrocarbon receptor ligands, and secondary bile acids. In addition, several reports highlight the accumulation of aromatic amino acid-derived phenolic and indolic compounds and specific lipid mediators linked to neuroinflammation and neurodegeneration. In this up-to-date review, we synthesize evidence from experimental models and human studies showing how microbial metabolites can influence MS pathogenesis through converging mechanisms: modulation of gut and blood-brain barrier integrity; shaping of T-cell and B-cell responses; direct effects on microglia, astrocytes, and oligodendrocyte lineage cells after crossing into the CNS; and modulation of neural circuits, particularly those involving the vagus nerve. Finally, we highlight current gaps, including the need for longitudinal, harmonized multiomic cohorts, and mechanistic studies integrating microbiome, metabolome, and host readouts across gut, blood, and CNS. Overall, available data support a model in which coordinated disruption of the gut microbiota-metabolite axis, rather than any single pathogen, contributes to MS, opening avenues for microbiota-based and metabolite-based biomarkers and therapies aimed at restoring immune and neuroglial homeostasis.</t>
+          <t>Preterm birth is the leading cause of infant mortality, resulting in more than 1 million neonatal deaths globally each year. Maternal urinary tract infection (UTI) during pregnancy increases risk for preterm birth; however, biological processes mediating UTI-associated preterm birth are not well described. We established a murine maternal UTI model in which challenge with uropathogenic Escherichia coli (UPEC) initiated preterm labor and birth in about half of dams. Although bacterial burdens were similar, dams experiencing preterm birth displayed excessive bladder inflammation, elevated placental and decidual cytokines, higher proportions of male fetuses, and lower maternal serum interleukin-10 (IL-10) compared with nonlaboring dams. Exogenous IL-10 or lymph node sequestration of T cells reduced placental type 17 T helper cells (TH17 cells) and abrogated preterm birth. In a human pregnancy cohort, we correlated urinary cytokines with birth outcomes and urine culture status. These analyses yielded an exploratory, noninvasive culture-agnostic system for evaluating preterm birth risk, implicating T cell-related cytokines including IL-10, IL-15, GM-CSF, and RANTES. These findings demonstrate that our murine model provides a platform to investigate immunological and microbial factors governing UTI-associated preterm birth and, coupled with patient samples, may be used to identify candidate biomarkers and mechanistic targets for future investigation.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>本研究探討多發性硬化症（MS）與腸道微生物群之間的關聯。研究指出，MS 患者的腸道菌相呈現失調狀態，包括短鏈脂肪酸（SCFA）產生菌減少，以及促發炎代謝菌的增加。這些微生物群落的變化伴隨著血液與腦脊髓液中代謝物（如色胺酸衍生物、膽汁酸及 SCFA）的顯著改變，這些物質經證實與神經發炎及退化密切相關。文中綜述了微生物代謝產物如何透過調節腸道與血腦屏障完整性、影響免疫細胞（T/B 細胞）反應，以及直接作用於神經膠質細胞來參與 MS 的致病機制。總結而言，MS 的發生與腸道菌群-代謝物軸的整體失調有關，而非單一病原體所致。該研究強調未來需進行多體學（multiomics）整合分析，以開發基於微生物群的生物標記與創新治療策略，旨在恢復患者的免疫與神經恆定。</t>
+          <t>本研究旨在探討孕婦尿路感染（UTI）導致早產的免疫機制。研究團隊建立尿路致病性大腸桿菌（UPEC）感染的孕鼠模型，發現發生早產的母鼠伴隨更嚴重的膀胱發炎、胎盤細胞激素升高及血清IL-10降低；給予外源性IL-10或抑制T細胞，能減少胎盤TH17細胞並預防早產。此外，人類佇列研究證實，尿液中T細胞相關細胞激素（如IL-10、IL-15等）與早產風險密切相關。本研究結合動物模型與臨床樣本，揭示了UTI引發早產的免疫關鍵，並為未來篩檢及治療提供了潛在的非侵入性生物標誌物與機制標靶。</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2608,19 +2606,19 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42647759/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647600/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>42644751</t>
+          <t>42644746</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Soil amelioration impacts viral ecology in saline-alkali lands.</t>
+          <t>Metabolic division of labour drives estuarine-coastal N2O emissions.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2631,12 +2629,12 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>metagenomics, metatranscriptomics</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>未提及（僅說明樣品來自中國4個主要鹽鹼地區，各包含「鹽鹼」與「改良後」兩種狀態之土壤）</t>
+          <t>974 個重建的 N2O 相關基因體（原文未提及具體的環境樣本採集數量）</t>
         </is>
       </c>
       <c r="G42" t="b">
@@ -2644,12 +2642,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>The continuous expansion of saline-alkali lands under climate change threatens food security and reduces soil carbon stocks. A common mitigation strategy is soil amelioration, which converts degraded soils back into an arable state. Microbes play critical roles in soil health and recovery. However, the viruses that infect these microbial communities, and their potential impacts during saline-alkali soil restoration, remain largely unknown. Here, we combined total soil metagenomics and viromics to investigate host-linked viral ecology across four major saline-alkali regions in China, each encompassing two soil amelioration statuses: saline-alkali and reclaimed. We found that viral community structure was shaped by both geography and soil amelioration status, with salinity and alkalinity emerging as key environmental factors. Viral populations were sensitive to soil restoration, showing strong amelioration-status endemism with functional adaptations. Virus-host dynamics ranged from reduced temperate viruses to abundance mismatches in those infecting key carbon-cycling microorganisms, including carbohydrate degraders. 13C-cellulose DNA-SIP experiments provided further support for this mismatch by tracing assimilated carbon transfer between active host and virus populations. Compared with saline-alkali soils, the relative abundance of hosts in restored soils increased from 39.0% to 61.0%, whereas the linked viruses decreased from 60.6% to 39.4%. Together, these findings reveal an underappreciated role of viruses in shaping saline-alkali soil amelioration trajectories, and could improve management strategies for degraded land recovery and carbon storage.</t>
+          <t>Estuarine and coastal systems are global hotspots of marine nitrous oxide (N2O) emissions, where microbial nitrification and denitrification are the primary processes regulating N2O dynamics. However, how interactions among different N2O-associated microorganisms influence ecosystem-scale N2O emissions remains poorly understood. This study combined in situ N2O concentrations, 15N-based potential rates, metagenomics, metatranscriptomics, and genome-scale metabolic model analysis to explore N2O production and reduction processes in estuarine and coastal systems. Potential N2O production and reduction rates, together with in situ concentrations, the relative abundance, and the transcriptional activity of associated genes, were significantly higher at low salinity and declined toward coastal regions. Based on the gene content of 974 recovered N2O-associated genomes, microorganisms were classified into three functional groups: net N2O producers, net N2O consumers, and self-sustaining N2O players. The abundance, composition, and activity of these functional groups shifted along estuarine-coastal gradients. A larger NO/N2O exchange gap, reflecting the imbalance between model-inferred NO and N2O handoff potentials, was found at low salinity and was associated with elevated bottom-water N2O concentrations. Together, community-level division of labour and the associated exchange gap provide a conceptual framework for linking N2O-related functional groups to N2O accumulation in estuarine-coastal ecosystems.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>本研究旨在探討鹽鹼地改良過程中，病毒對土壤微生物生態與碳循環的影響。研究結合總體基因體與病毒體學，分析中國四大鹽鹼區。結果顯示，土壤改良狀態、鹽度與鹼度是塑造病毒社群的關鍵。在改良土壤中，宿主微生物相對豐度顯著上升（39.0%至61.0%），而關聯病毒減少（60.6%至39.4%），且溫和病毒比例降低，碳循環關鍵微生物的病毒與宿主出現豐度失衡。13C-纖維素DNA-SIP實驗證實了兩者間的活性碳轉移。此發現揭示了病毒在鹽鹼地恢復中的關鍵作用，有助優化土地改良與碳儲存策略。</t>
+          <t>本研究旨在探討河口與沿海系統中，微生物交互作用如何驅動一氧化二氮（N2O）的排放。研究結合現場觀測、15N同位素速率、總體基因體與轉錄體學，重建了974個N2O相關基因體。結果指出，低鹽度區域的N2O產生與還原速率及基因表達顯著較高。研究將微生物劃分為淨產生者、淨消費者與自給自足者，並發現低鹽度區因群落間物質交換失衡，存在較大的NO/N2O交換缺口，進而導致底層水體N2O顯著累積。本研究建立了群落水平的「分工與交換缺口」理論框架，為預測及理解海洋生態系統N2O排放提供了關鍵的科學依據。</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2659,37 +2657,37 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42644751/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42644746/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>42648293</t>
+          <t>42649294</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Defined human Clostridia consortia reverse colitis via dual effects of tryptophan metabolites on microbiota and immunity.</t>
+          <t>Synergistic degradation of fucoidans in the ocean.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cell host &amp; microbe</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>18.7</v>
+        <v>48.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>metagenomics, metabolomics</t>
+          <t>metabolomics, metagenomics</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（該研究採用重組海洋微生物群落進行實驗，未提供具體的生物樣本人數或檢體數量）</t>
         </is>
       </c>
       <c r="G43" t="b">
@@ -2697,12 +2695,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Microbial dysbiosis and disrupted mucosal immune homeostasis are integrally involved in the pathogenesis of inflammatory bowel diseases (IBDs). Live biotherapeutic products (LBPs) offer a potential therapeutic strategy to restore beneficial microbes and mitigate disease. We investigated the therapeutic efficacy of 2 LBPs, human Clostridia consortia 17-mix and 11-mix, by treating established colitis in murine models. Both LBPs exhibited therapeutic effects in T cell-mediated chronic colitis models induced by human microbiota and in pathobiont-driven gnotobiotic colitis models established with combinations of IBD-relevant human-derived strains. Metagenomic and metabolomic analyses elucidated mechanisms that go beyond established functions driven by short-chain fatty acids (SCFAs) and interleukin (IL)-10-producing regulatory T cells. Notably, LBPs exerted therapeutic effects by directly inhibiting resident pathobionts and through IL-10-independent activation of host anti-inflammatory aryl hydrocarbon receptor (AhR) pathways by bacterial tryptophan metabolites. These results elucidate SCFA- and IL-10-independent protective mechanisms exerted by defined resident bacterial strains that are depleted in IBD dysbiosis.</t>
+          <t>Fucoidans, a class of complex polysaccharides produced by brown algae and diatoms, contribute to long-term carbon sequestration owing to their resistance to microbial degradation1,2. Although individual microorganisms can break down portions of these polysaccharides3-5, it remains unclear whether complete breakdown is possible in nature and, if so, by what mechanisms. Here we show that fucoidans are degraded through synergistic interactions between specialized bacteria with complementary metabolic functions. Using metabolomic analysis of a reconstructed marine consortium, we uncovered metabolic guilds of bacteria that preferentially degrade either the sulfated fucose backbone or the side branches of rare monomers. This functional division of labour leads to an unexpectedly high number of synergistic interactions between different degraders that enhanced degradation efficiency up to 97.1%. Despite varying fucoidan structures across different types of algae6, the metabolic functions of degraders remained conserved, enabling quantitative prediction of degradation outcomes based on community and substrate composition. The frequent co-occurrence of functionally complementary fucoidan degraders in ocean metagenomes suggests that synergistic degradation is a globally relevant strategy. Our findings suggest that the environmental turnover of complex biopolymers depends not only on individual metabolic capabilities of degraders but also on ecological interactions shaped by substrate architecture. This work provides a mechanistic framework for understanding carbon cycling in the ocean and for engineering synthetic microbial consortia to degrade recalcitrant polysaccharides.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>本研究探討了兩種由人類梭狀芽孢桿菌組成的活體生物藥物（LBP，分別為 17-mix 和 11-mix）治療小鼠結腸炎的療效與機制。研究發現，這些菌群能有效緩解小鼠的慢性與特定病原體誘導的結腸炎。宏基因組學與代謝組學分析顯示，除了傳統的短鏈脂肪酸（SCFA）和 IL-10 途徑外，LBP 還能直接抑制共生病原菌，並透過細菌色胺酸代謝物，以不依賴 IL-10 的方式激活宿主的芳香烴受體（AhR）抗炎途徑。此發現揭示了腸道有益菌保護腸道的新機制，為發炎性腸道疾病（IBD）的微生態療法提供了重要科學依據。</t>
+          <t>本研究探討海洋中複雜多醣體「褐藻醣膠」（fucoidans）的微生物降解機制。儘管褐藻醣膠因其抗降解性在碳封存中扮演關鍵角色，但過往對於其在自然界中是否能被完全分解並不清楚。研究發現，褐藻醣膠的降解並非單一物種所能完成，而是透過具有互補代謝功能的細菌群落進行「協同作用」。透過代謝體學分析，研究團隊識別出專門降解硫酸岩藻糖骨架與稀有單醣側鏈的代謝群組（metabolic guilds），這種分工合作能將降解效率大幅提升至 97.1%。此外，研究顯示此代謝功能在不同環境下具有高度保守性，且在海洋宏基因組中普遍存在。本研究揭示了生物聚合物的環境周轉率取決於微生物間的生態交互作用，為理解海洋碳循環機制提供了重要框架，並為未來利用人工合成微生物群落降解頑固性多醣體提供了技術基礎。</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2712,29 +2710,27 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42648293/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42649294/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>42647084</t>
+          <t>42657129</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Diet quality, gut microbiome, and inflammatory signatures in Puerto Rican adults with Crohn disease: a multidimensional analysis.</t>
+          <t>Pulmonary Infiltrates, Airway Mucosal Lesions and Respiratory Microbiology After Freshwater Drowning: A Case Report.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Inflammatory bowel diseases</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>4.3</v>
-      </c>
+          <t>Respirology case reports</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>metagenomics</t>
@@ -2742,7 +2738,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>60位患有克隆氏症的成年人 (60 adults with CD)</t>
+          <t>1 例病患（n=1）</t>
         </is>
       </c>
       <c r="G44" t="b">
@@ -2750,12 +2746,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Diet is increasingly recognized as a modifiable factor influencing gut microbiome and outcomes in Crohn disease (CD), yet data in underrepresented populations remain limited. We evaluated diet quality, dietary patterns, gut microbiome composition, inflammatory markers, and patient-reported outcomes in adults with CD from Puerto Rico. We conducted a cross-sectional analysis of 60 adults with CD enrolled prior to dietary intervention in a parent study. Dietary intake was assessed using 24-hour recalls and evaluated using the Healthy Eating Index-2015 (HEI-2015), Alternative Healthy Eating Index-2010 (AHEI-2010), and exploratory dietary pattern analysis. The gut microbiome was assessed by shotgun metagenomic sequencing. Clinical outcomes included fecal calprotectin, C-reactive protein (CRP), a 96-cytokine panel, short Crohn Disease Activity Index (sCDAI), and short Inflammatory Bowel Disease Questionnaire (sIBDQ). Associations were evaluated using unadjusted and adjusted models with false discovery rate (FDR) correction. Overall diet quality was poor and characterized by low intake of fruits, vegetables, whole grains, and fiber, alongside high intake of saturated fat, added sugars, and animal-derived protein. Four dietary patterns were identified: vegetable-rich, dairy-rich, fruit-rich, and coffee/sweetener-rich. Participants adhering to the fruit-rich pattern exhibited the highest diet quality scores. Higher HEI-2015 scores were associated with greater gut microbial diversity and differences in overall microbiome composition. Participants with greater adherence to the vegetable-rich pattern showed modest increases in microbial diversity. Exploratory analyses suggested that higher fruit intake and adherence to a fruit-rich dietary pattern were associated with lower fecal calprotectin and CRP levels, whereas adherence to a vegetable-rich pattern was associated with better health-related quality of life (HRQoL) and adherence to a coffee/sweetener-rich pattern was associated with a worse symptom burden. However, no associations between dietary metrics and inflammatory markers, cytokines, or clinical outcomes remained significant after FDR correction. Most participants were in clinical remission despite substantial impairment in HRQoL. Adults with CD in Puerto Rico exhibited poor diet quality that was associated with gut microbial diversity and exploratory differences in clinical outcomes. While these findings support the influence of diet on the microbiome and clinical outcomes, larger longitudinal studies are needed to determine whether dietary improvements can influence disease outcomes this underrepresented population.</t>
+          <t>Early pulmonary abnormalities after freshwater drowning can be overinterpreted as bacterial pneumonia, especially when inflammatory biomarkers and respiratory microbiology are positive. A 20-year-old man was resuscitated after approximately 2 min of freshwater submersion. Day 1 chest CT showed bilateral lower-lobe-predominant opacities compatible with non-cardiogenic pulmonary oedema and aspiration-related lung injury, with near-complete resolution by Day 25. Day 3 bronchoscopy showed diffuse, non-removable, millet-seed-like whitish tracheal mucosal protrusions with hyperaemia and oedema, compatible with acute irritative airway injury. BALF mNGS detected multiple gram-negative bacterial signals, predominantly Klebsiella pneumoniae, while sputum culture yielded ESBL-negative, susceptible K. pneumoniae. Possible drowning-associated pneumonia was considered because of aspiration, fever, markedly elevated inflammatory biomarkers and concordant microbiology; however, rapid radiological improvement and clinical stability suggested a substantial non-infectious component. The patient recovered after an 8-day course of piperacillin-tazobactam without antibiotic escalation, corticosteroids, mechanical ventilation or acute respiratory distress syndrome.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>本研究探討波多黎各克隆氏症（CD）成年患者的飲食品質、腸道菌相與發炎指標的關係。研究發現，受試者普遍飲食品質不佳，而較高的飲食品質（特別是富含水果的飲食模式）與較高的腸道菌群多樣性顯著相關。探索性分析顯示，多攝取水果與較低的發炎指標（鈣衛蛋白和C反應蛋白）相關，而蔬菜為主的飲食與較佳的生活品質相關（但經FDR校正後未達顯著）。本研究首次揭示了該少數受關注族群中飲食對菌相與臨床症狀的影響，為未來透過飲食干預管理CD及改善患者預後提供了科學依據。</t>
+          <t>本研究透過單一病例報告，探討淡水溺水後肺部浸潤與呼吸道損傷的臨床鑑別診斷。一名 20 歲男性溺水後出現肺水腫與氣道黏膜病變，臨床表現極易與細菌性肺炎混淆。研究利用 mNGS（宏基因組次世代定序）檢測支氣管肺泡灌洗液，雖確認存在肺炎克雷伯菌（*Klebsiella pneumoniae*）訊號，但影像學與臨床病程顯示其肺部損傷主要源於吸入性損傷及急性化學性氣道刺激，而非嚴重的細菌感染。此案例凸顯了臨床判斷溺水相關肺炎時的挑戰，強調在面對看似感染的臨床數據時，應綜合考量影像改善速度與臨床穩定性，避免過度診斷與不必要的抗生素升級，對急性溺水病患的精準治療具有重要的臨床參考價值。</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2765,28 +2761,28 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42647084/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42657129/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>42647600</t>
+          <t>42647164</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Urogenital immune signatures are associated with birth outcomes after maternal urinary tract infection.</t>
+          <t>Sex differences in the gut microbiome and related metabolites: role in cardiometabolic disease.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Science translational medicine</t>
+          <t>Gut microbes</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>14.6</v>
+        <v>11</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2795,7 +2791,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（本文為綜論性回顧文章，非原創實驗研究）</t>
         </is>
       </c>
       <c r="G45" t="b">
@@ -2803,12 +2799,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Preterm birth is the leading cause of infant mortality, resulting in more than 1 million neonatal deaths globally each year. Maternal urinary tract infection (UTI) during pregnancy increases risk for preterm birth; however, biological processes mediating UTI-associated preterm birth are not well described. We established a murine maternal UTI model in which challenge with uropathogenic Escherichia coli (UPEC) initiated preterm labor and birth in about half of dams. Although bacterial burdens were similar, dams experiencing preterm birth displayed excessive bladder inflammation, elevated placental and decidual cytokines, higher proportions of male fetuses, and lower maternal serum interleukin-10 (IL-10) compared with nonlaboring dams. Exogenous IL-10 or lymph node sequestration of T cells reduced placental type 17 T helper cells (TH17 cells) and abrogated preterm birth. In a human pregnancy cohort, we correlated urinary cytokines with birth outcomes and urine culture status. These analyses yielded an exploratory, noninvasive culture-agnostic system for evaluating preterm birth risk, implicating T cell-related cytokines including IL-10, IL-15, GM-CSF, and RANTES. These findings demonstrate that our murine model provides a platform to investigate immunological and microbial factors governing UTI-associated preterm birth and, coupled with patient samples, may be used to identify candidate biomarkers and mechanistic targets for future investigation.</t>
+          <t>Sex differences in major cardiometabolic diseases (CMD), such as type 2 diabetes, metabolic dysfunction-associated steatotic liver disease, and cardiovascular disease, have been increasingly recognized across the life course. During the reproductive stage, women generally have a more favorable cardiometabolic risk profile than men, but their risk of experiencing CMD significantly increases after menopause. Emerging evidence suggests that sexually dimorphic gut microbiota and gut microbiota-related metabolites (GMRMs) may contribute to such sex disparities. However, existing findings are heterogeneous and underlying mechanisms remain incompletely understood. In this review, we synthesize the evidence examining sex differences in gut microbial diversity, overall composition, taxa abundances, and levels of GMRMs across key life stages, including pre-puberty, adolescence, and different phases of adulthood (with emphasis on pre- and post-menopausal periods). We summarize potential biological mechanisms underlying sexual dimorphism in the gut microbiome and GMRMs, emphasizing the central role of sex steroids, along with contributions from immune function and other host and environmental factors. We further integrate evidence linking sexually dimorphic microbial taxa (e.g., Akkermansia muciniphila, Eubacterium, Ruminococcus, and other Firmicutes taxa) and GMRMs (e.g., microbiota-derived short-chain fatty acids, secondary bile acids, and trimethylamine N-oxide) to key cardiometabolic pathways involving inflammation, glucose and lipid metabolism, and vascular function. Finally, we identify critical knowledge gaps and emphasize the need for future large longitudinal studies that would integrate repeated measurements of the gut microbiome, untargeted metabolomics, and sex steroid hormones across the life course. Such approaches are essential to clarify biological pathways and inform sex-specific microbiome-based interventions for CMD prevention and management.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>本研究旨在探討孕婦尿路感染（UTI）導致早產的免疫機制。研究團隊建立尿路致病性大腸桿菌（UPEC）感染的孕鼠模型，發現發生早產的母鼠伴隨更嚴重的膀胱發炎、胎盤細胞激素升高及血清IL-10降低；給予外源性IL-10或抑制T細胞，能減少胎盤TH17細胞並預防早產。此外，人類佇列研究證實，尿液中T細胞相關細胞激素（如IL-10、IL-15等）與早產風險密切相關。本研究結合動物模型與臨床樣本，揭示了UTI引發早產的免疫關鍵，並為未來篩檢及治療提供了潛在的非侵入性生物標誌物與機制標靶。</t>
+          <t>本文旨在探討性別差異在腸道微生物群與相關代謝物（GMRMs）中如何影響心臟代謝疾病（CMD）。研究指出，受性類固醇、免疫功能及環境因素影響，腸道菌相與代謝產物存在顯著的性別二態性。女性在生育期較男性具備更佳的心臟代謝特徵，但停經後風險顯著升高，此變化與特定菌屬（如 *Akkermansia muciniphila*）及代謝物（如短鏈脂肪酸、次級膽汁酸、TMAO）的豐度改變密切相關。這些微生物與代謝物透過調節發炎反應、醣脂代謝及血管功能，進而影響 CMD 的發生。本文強調未來需透過大型縱向研究，結合微生物組學、代謝組學與荷爾蒙監測，以深入解析其生物學機制，並開發針對不同性別的精準微生物介入療法，對於預防及管理心臟代謝疾病具有重要的科學價值。</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2818,37 +2814,35 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42647600/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647164/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>42648218</t>
+          <t>42648171</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Agricultural sprinkler irrigation systems as environmental reservoirs and airborne dissemination sources of Legionella pneumophila.</t>
+          <t>Co-occurrence of muddy off flavor and cyanotoxin genes in the polluted Guandu river waters (Rio de Janeiro, Brazil).</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Journal of environmental management</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>8.4</v>
-      </c>
+          <t>The Science of the total environment</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>metagenomics, small genome</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>未明確提及具體檢體數量（僅指出於西班牙東北部農村的兩個區域，針對灌溉池塘與溝渠進行採樣）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G46" t="b">
@@ -2856,12 +2850,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sprinkler irrigation systems are critical for modern agriculture but represent largely unrecognized aquatic environments capable of sustaining opportunistic human pathogens. Among them, Legionella pneumophila is of particular concern due to its ability to colonize engineered water systems, persist under fluctuating environmental conditions, and be transmitted through aerosols. In this study, we conducted a comprehensive microbiological and genomic investigation of irrigation ponds and ditches in a rural area of north-east Spain where two zones were sampled. Metagenomic profiling revealed highly diverse microbial communities encompassing more than 20,000 species, including 21 airborne-transmissible bacterial pathogens of clinical relevance. Notably, L. pneumophila was detected in both zones, with a relative abundance of up to 4.6 %. Culture-based isolation confirmed the presence of L. pneumophila serogroup 1, Pontiac group, Benidorm subgroup, sequence type 15. Phylogenetic analysis demonstrated a close relationship between this environmental strain and clinical isolates obtained during a Legionnaires' disease outbreak occurred in 2015, which had remained without a confirmed environmental source. Meteorological data from the exposure period revealed wind conditions favouring long-distance aerosol dispersion from irrigated fields toward residential areas. Our findings provide evidence that irrigation infrastructures can act as environmental reservoirs and dissemination routes of L. pneumophila among other airborne pathogens. These results underscore the need to incorporate agricultural irrigation systems into routine environmental surveillance, outbreak investigations, and public health risk assessments.</t>
+          <t>The Guandu river basin is responsible for supplying Rio de Janeiro municipality, Brazil, with drinking water. This study investigated water quality during the geosmin crisis in January and March 2020, by relating the water quality and odor compounds with metagenomic tools. Guandu river water was eutrophic. The cyanobacterial genera identified were Microcystis, Planktothrix, Dolichospermum, Nostoc, Synechococcus, Planktothricoides, and Cyanobium, indicating that bloom-associated communities in the system are taxonomically diverse. Functional annotation of metagenomic sequences revealed the presence of genes associated with the biosynthesis of taste-and-odor compounds, including geosmin (geoA) and 2-methylisoborneol (mic), as well as multiple biosynthetic clusters related to cyanotoxin production. Genes linked to microcystin (mcy), saxitoxin (sxt), anatoxin (ana), cylindrospermopsin (cyr), lyngbyatoxin (ltx), guanitoxin (gnt), and nodularin (nda) were detected across the dataset, indicating a broad genetic potential for the production of secondary metabolites relevant to water quality. The co-occurrence of cyanotoxins, geosmin and 2-MIB genes suggests that off-flavor is an indication of cyanotoxin potential production in the water.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>本研究旨在探討農業噴灌系統是否為嗜肺軍團菌（*Legionella pneumophila*）等致病菌的環境宿主與空氣傳播源。團隊對西班牙農村灌溉水體進行分析，總體基因體學顯示其含有逾2萬種微生物，包括21種臨床相關的空氣傳播病原體，且嗜肺軍團菌相對豐度達4.6%。研究成功分離出嗜肺軍團菌血清型1（ST15），系統發育分析證實該環境株與2015年退伍軍人症爆發的臨床分離株高度相關。氣象數據亦支持風向有利於氣膠從農田長距離擴散至住宅區。此發現證實農業灌溉系統為軍團菌的傳播媒介，強調應將其納入例行環境監測與公衛風險評估。</t>
+          <t>本研究旨在探究巴西里約熱內盧瓜杜河於2020年初爆發土臭素危機期間的水質狀況，並利用總體基因體學技術探討水質異味與微生物群落之關聯。研究發現，該富營養化水體中含有多種藍菌，且功能性註釋顯示其富含合成土臭素（*geoA*）與2-甲基異莰醇（*mic*）等異味物質的基因。更重要的是，多種藍菌毒素（如微囊藻毒素、石房蛤毒素等）的合成基因群與這些異味基因呈現共存。此發現證實了水體異味的出現與藍菌毒素的潛在生成具有高度相關性，可作為飲用水安全監測及評估藍菌毒素潛在危害的重要預警指標。</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2871,7 +2865,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42648218/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648171/</t>
         </is>
       </c>
     </row>
@@ -2931,28 +2925,30 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>42648171</t>
+          <t>42648218</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Co-occurrence of muddy off flavor and cyanotoxin genes in the polluted Guandu river waters (Rio de Janeiro, Brazil).</t>
+          <t>Agricultural sprinkler irrigation systems as environmental reservoirs and airborne dissemination sources of Legionella pneumophila.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>The Science of the total environment</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>Journal of environmental management</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>8.4</v>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>metagenomics, small genome</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未明確提及具體檢體數量（僅指出於西班牙東北部農村的兩個區域，針對灌溉池塘與溝渠進行採樣）</t>
         </is>
       </c>
       <c r="G48" t="b">
@@ -2960,12 +2956,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>The Guandu river basin is responsible for supplying Rio de Janeiro municipality, Brazil, with drinking water. This study investigated water quality during the geosmin crisis in January and March 2020, by relating the water quality and odor compounds with metagenomic tools. Guandu river water was eutrophic. The cyanobacterial genera identified were Microcystis, Planktothrix, Dolichospermum, Nostoc, Synechococcus, Planktothricoides, and Cyanobium, indicating that bloom-associated communities in the system are taxonomically diverse. Functional annotation of metagenomic sequences revealed the presence of genes associated with the biosynthesis of taste-and-odor compounds, including geosmin (geoA) and 2-methylisoborneol (mic), as well as multiple biosynthetic clusters related to cyanotoxin production. Genes linked to microcystin (mcy), saxitoxin (sxt), anatoxin (ana), cylindrospermopsin (cyr), lyngbyatoxin (ltx), guanitoxin (gnt), and nodularin (nda) were detected across the dataset, indicating a broad genetic potential for the production of secondary metabolites relevant to water quality. The co-occurrence of cyanotoxins, geosmin and 2-MIB genes suggests that off-flavor is an indication of cyanotoxin potential production in the water.</t>
+          <t>Sprinkler irrigation systems are critical for modern agriculture but represent largely unrecognized aquatic environments capable of sustaining opportunistic human pathogens. Among them, Legionella pneumophila is of particular concern due to its ability to colonize engineered water systems, persist under fluctuating environmental conditions, and be transmitted through aerosols. In this study, we conducted a comprehensive microbiological and genomic investigation of irrigation ponds and ditches in a rural area of north-east Spain where two zones were sampled. Metagenomic profiling revealed highly diverse microbial communities encompassing more than 20,000 species, including 21 airborne-transmissible bacterial pathogens of clinical relevance. Notably, L. pneumophila was detected in both zones, with a relative abundance of up to 4.6 %. Culture-based isolation confirmed the presence of L. pneumophila serogroup 1, Pontiac group, Benidorm subgroup, sequence type 15. Phylogenetic analysis demonstrated a close relationship between this environmental strain and clinical isolates obtained during a Legionnaires' disease outbreak occurred in 2015, which had remained without a confirmed environmental source. Meteorological data from the exposure period revealed wind conditions favouring long-distance aerosol dispersion from irrigated fields toward residential areas. Our findings provide evidence that irrigation infrastructures can act as environmental reservoirs and dissemination routes of L. pneumophila among other airborne pathogens. These results underscore the need to incorporate agricultural irrigation systems into routine environmental surveillance, outbreak investigations, and public health risk assessments.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>本研究旨在探究巴西里約熱內盧瓜杜河於2020年初爆發土臭素危機期間的水質狀況，並利用總體基因體學技術探討水質異味與微生物群落之關聯。研究發現，該富營養化水體中含有多種藍菌，且功能性註釋顯示其富含合成土臭素（*geoA*）與2-甲基異莰醇（*mic*）等異味物質的基因。更重要的是，多種藍菌毒素（如微囊藻毒素、石房蛤毒素等）的合成基因群與這些異味基因呈現共存。此發現證實了水體異味的出現與藍菌毒素的潛在生成具有高度相關性，可作為飲用水安全監測及評估藍菌毒素潛在危害的重要預警指標。</t>
+          <t>本研究旨在探討農業噴灌系統是否為嗜肺軍團菌（*Legionella pneumophila*）等致病菌的環境宿主與空氣傳播源。團隊對西班牙農村灌溉水體進行分析，總體基因體學顯示其含有逾2萬種微生物，包括21種臨床相關的空氣傳播病原體，且嗜肺軍團菌相對豐度達4.6%。研究成功分離出嗜肺軍團菌血清型1（ST15），系統發育分析證實該環境株與2015年退伍軍人症爆發的臨床分離株高度相關。氣象數據亦支持風向有利於氣膠從農田長距離擴散至住宅區。此發現證實農業灌溉系統為軍團菌的傳播媒介，強調應將其納入例行環境監測與公衛風險評估。</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2975,7 +2971,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42648171/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648218/</t>
         </is>
       </c>
     </row>
@@ -3035,30 +3031,30 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>42647164</t>
+          <t>42647084</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sex differences in the gut microbiome and related metabolites: role in cardiometabolic disease.</t>
+          <t>Diet quality, gut microbiome, and inflammatory signatures in Puerto Rican adults with Crohn disease: a multidimensional analysis.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>Inflammatory bowel diseases</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11</v>
+        <v>4.3</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>未提及（本文為綜論性回顧文章，非原創實驗研究）</t>
+          <t>60位患有克隆氏症的成年人 (60 adults with CD)</t>
         </is>
       </c>
       <c r="G50" t="b">
@@ -3066,12 +3062,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sex differences in major cardiometabolic diseases (CMD), such as type 2 diabetes, metabolic dysfunction-associated steatotic liver disease, and cardiovascular disease, have been increasingly recognized across the life course. During the reproductive stage, women generally have a more favorable cardiometabolic risk profile than men, but their risk of experiencing CMD significantly increases after menopause. Emerging evidence suggests that sexually dimorphic gut microbiota and gut microbiota-related metabolites (GMRMs) may contribute to such sex disparities. However, existing findings are heterogeneous and underlying mechanisms remain incompletely understood. In this review, we synthesize the evidence examining sex differences in gut microbial diversity, overall composition, taxa abundances, and levels of GMRMs across key life stages, including pre-puberty, adolescence, and different phases of adulthood (with emphasis on pre- and post-menopausal periods). We summarize potential biological mechanisms underlying sexual dimorphism in the gut microbiome and GMRMs, emphasizing the central role of sex steroids, along with contributions from immune function and other host and environmental factors. We further integrate evidence linking sexually dimorphic microbial taxa (e.g., Akkermansia muciniphila, Eubacterium, Ruminococcus, and other Firmicutes taxa) and GMRMs (e.g., microbiota-derived short-chain fatty acids, secondary bile acids, and trimethylamine N-oxide) to key cardiometabolic pathways involving inflammation, glucose and lipid metabolism, and vascular function. Finally, we identify critical knowledge gaps and emphasize the need for future large longitudinal studies that would integrate repeated measurements of the gut microbiome, untargeted metabolomics, and sex steroid hormones across the life course. Such approaches are essential to clarify biological pathways and inform sex-specific microbiome-based interventions for CMD prevention and management.</t>
+          <t>Diet is increasingly recognized as a modifiable factor influencing gut microbiome and outcomes in Crohn disease (CD), yet data in underrepresented populations remain limited. We evaluated diet quality, dietary patterns, gut microbiome composition, inflammatory markers, and patient-reported outcomes in adults with CD from Puerto Rico. We conducted a cross-sectional analysis of 60 adults with CD enrolled prior to dietary intervention in a parent study. Dietary intake was assessed using 24-hour recalls and evaluated using the Healthy Eating Index-2015 (HEI-2015), Alternative Healthy Eating Index-2010 (AHEI-2010), and exploratory dietary pattern analysis. The gut microbiome was assessed by shotgun metagenomic sequencing. Clinical outcomes included fecal calprotectin, C-reactive protein (CRP), a 96-cytokine panel, short Crohn Disease Activity Index (sCDAI), and short Inflammatory Bowel Disease Questionnaire (sIBDQ). Associations were evaluated using unadjusted and adjusted models with false discovery rate (FDR) correction. Overall diet quality was poor and characterized by low intake of fruits, vegetables, whole grains, and fiber, alongside high intake of saturated fat, added sugars, and animal-derived protein. Four dietary patterns were identified: vegetable-rich, dairy-rich, fruit-rich, and coffee/sweetener-rich. Participants adhering to the fruit-rich pattern exhibited the highest diet quality scores. Higher HEI-2015 scores were associated with greater gut microbial diversity and differences in overall microbiome composition. Participants with greater adherence to the vegetable-rich pattern showed modest increases in microbial diversity. Exploratory analyses suggested that higher fruit intake and adherence to a fruit-rich dietary pattern were associated with lower fecal calprotectin and CRP levels, whereas adherence to a vegetable-rich pattern was associated with better health-related quality of life (HRQoL) and adherence to a coffee/sweetener-rich pattern was associated with a worse symptom burden. However, no associations between dietary metrics and inflammatory markers, cytokines, or clinical outcomes remained significant after FDR correction. Most participants were in clinical remission despite substantial impairment in HRQoL. Adults with CD in Puerto Rico exhibited poor diet quality that was associated with gut microbial diversity and exploratory differences in clinical outcomes. While these findings support the influence of diet on the microbiome and clinical outcomes, larger longitudinal studies are needed to determine whether dietary improvements can influence disease outcomes this underrepresented population.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>本文旨在探討性別差異在腸道微生物群與相關代謝物（GMRMs）中如何影響心臟代謝疾病（CMD）。研究指出，受性類固醇、免疫功能及環境因素影響，腸道菌相與代謝產物存在顯著的性別二態性。女性在生育期較男性具備更佳的心臟代謝特徵，但停經後風險顯著升高，此變化與特定菌屬（如 *Akkermansia muciniphila*）及代謝物（如短鏈脂肪酸、次級膽汁酸、TMAO）的豐度改變密切相關。這些微生物與代謝物透過調節發炎反應、醣脂代謝及血管功能，進而影響 CMD 的發生。本文強調未來需透過大型縱向研究，結合微生物組學、代謝組學與荷爾蒙監測，以深入解析其生物學機制，並開發針對不同性別的精準微生物介入療法，對於預防及管理心臟代謝疾病具有重要的科學價值。</t>
+          <t>本研究探討波多黎各克隆氏症（CD）成年患者的飲食品質、腸道菌相與發炎指標的關係。研究發現，受試者普遍飲食品質不佳，而較高的飲食品質（特別是富含水果的飲食模式）與較高的腸道菌群多樣性顯著相關。探索性分析顯示，多攝取水果與較低的發炎指標（鈣衛蛋白和C反應蛋白）相關，而蔬菜為主的飲食與較佳的生活品質相關（但經FDR校正後未達顯著）。本研究首次揭示了該少數受關注族群中飲食對菌相與臨床症狀的影響，為未來透過飲食干預管理CD及改善患者預後提供了科學依據。</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3081,24 +3077,24 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42647164/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647084/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>42657129</t>
+          <t>42644751</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Pulmonary Infiltrates, Airway Mucosal Lesions and Respiratory Microbiology After Freshwater Drowning: A Case Report.</t>
+          <t>Soil amelioration impacts viral ecology in saline-alkali lands.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Respirology case reports</t>
+          <t>The ISME journal</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -3109,7 +3105,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1 例病患（n=1）</t>
+          <t>未提及（僅說明樣品來自中國4個主要鹽鹼地區，各包含「鹽鹼」與「改良後」兩種狀態之土壤）</t>
         </is>
       </c>
       <c r="G51" t="b">
@@ -3117,12 +3113,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Early pulmonary abnormalities after freshwater drowning can be overinterpreted as bacterial pneumonia, especially when inflammatory biomarkers and respiratory microbiology are positive. A 20-year-old man was resuscitated after approximately 2 min of freshwater submersion. Day 1 chest CT showed bilateral lower-lobe-predominant opacities compatible with non-cardiogenic pulmonary oedema and aspiration-related lung injury, with near-complete resolution by Day 25. Day 3 bronchoscopy showed diffuse, non-removable, millet-seed-like whitish tracheal mucosal protrusions with hyperaemia and oedema, compatible with acute irritative airway injury. BALF mNGS detected multiple gram-negative bacterial signals, predominantly Klebsiella pneumoniae, while sputum culture yielded ESBL-negative, susceptible K. pneumoniae. Possible drowning-associated pneumonia was considered because of aspiration, fever, markedly elevated inflammatory biomarkers and concordant microbiology; however, rapid radiological improvement and clinical stability suggested a substantial non-infectious component. The patient recovered after an 8-day course of piperacillin-tazobactam without antibiotic escalation, corticosteroids, mechanical ventilation or acute respiratory distress syndrome.</t>
+          <t>The continuous expansion of saline-alkali lands under climate change threatens food security and reduces soil carbon stocks. A common mitigation strategy is soil amelioration, which converts degraded soils back into an arable state. Microbes play critical roles in soil health and recovery. However, the viruses that infect these microbial communities, and their potential impacts during saline-alkali soil restoration, remain largely unknown. Here, we combined total soil metagenomics and viromics to investigate host-linked viral ecology across four major saline-alkali regions in China, each encompassing two soil amelioration statuses: saline-alkali and reclaimed. We found that viral community structure was shaped by both geography and soil amelioration status, with salinity and alkalinity emerging as key environmental factors. Viral populations were sensitive to soil restoration, showing strong amelioration-status endemism with functional adaptations. Virus-host dynamics ranged from reduced temperate viruses to abundance mismatches in those infecting key carbon-cycling microorganisms, including carbohydrate degraders. 13C-cellulose DNA-SIP experiments provided further support for this mismatch by tracing assimilated carbon transfer between active host and virus populations. Compared with saline-alkali soils, the relative abundance of hosts in restored soils increased from 39.0% to 61.0%, whereas the linked viruses decreased from 60.6% to 39.4%. Together, these findings reveal an underappreciated role of viruses in shaping saline-alkali soil amelioration trajectories, and could improve management strategies for degraded land recovery and carbon storage.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>本研究透過單一病例報告，探討淡水溺水後肺部浸潤與呼吸道損傷的臨床鑑別診斷。一名 20 歲男性溺水後出現肺水腫與氣道黏膜病變，臨床表現極易與細菌性肺炎混淆。研究利用 mNGS（宏基因組次世代定序）檢測支氣管肺泡灌洗液，雖確認存在肺炎克雷伯菌（*Klebsiella pneumoniae*）訊號，但影像學與臨床病程顯示其肺部損傷主要源於吸入性損傷及急性化學性氣道刺激，而非嚴重的細菌感染。此案例凸顯了臨床判斷溺水相關肺炎時的挑戰，強調在面對看似感染的臨床數據時，應綜合考量影像改善速度與臨床穩定性，避免過度診斷與不必要的抗生素升級，對急性溺水病患的精準治療具有重要的臨床參考價值。</t>
+          <t>本研究旨在探討鹽鹼地改良過程中，病毒對土壤微生物生態與碳循環的影響。研究結合總體基因體與病毒體學，分析中國四大鹽鹼區。結果顯示，土壤改良狀態、鹽度與鹼度是塑造病毒社群的關鍵。在改良土壤中，宿主微生物相對豐度顯著上升（39.0%至61.0%），而關聯病毒減少（60.6%至39.4%），且溫和病毒比例降低，碳循環關鍵微生物的病毒與宿主出現豐度失衡。13C-纖維素DNA-SIP實驗證實了兩者間的活性碳轉移。此發現揭示了病毒在鹽鹼地恢復中的關鍵作用，有助優化土地改良與碳儲存策略。</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3132,37 +3128,35 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42657129/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42644751/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>42649294</t>
+          <t>42647759</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Synergistic degradation of fucoidans in the ocean.</t>
+          <t>The Gut Microbiome in Multiple Sclerosis.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Nature</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>48.5</v>
-      </c>
+          <t>Neurology(R) neuroimmunology &amp; neuroinflammation</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>metabolomics, metagenomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>未提及（該研究採用重組海洋微生物群落進行實驗，未提供具體的生物樣本人數或檢體數量）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G52" t="b">
@@ -3170,12 +3164,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Fucoidans, a class of complex polysaccharides produced by brown algae and diatoms, contribute to long-term carbon sequestration owing to their resistance to microbial degradation1,2. Although individual microorganisms can break down portions of these polysaccharides3-5, it remains unclear whether complete breakdown is possible in nature and, if so, by what mechanisms. Here we show that fucoidans are degraded through synergistic interactions between specialized bacteria with complementary metabolic functions. Using metabolomic analysis of a reconstructed marine consortium, we uncovered metabolic guilds of bacteria that preferentially degrade either the sulfated fucose backbone or the side branches of rare monomers. This functional division of labour leads to an unexpectedly high number of synergistic interactions between different degraders that enhanced degradation efficiency up to 97.1%. Despite varying fucoidan structures across different types of algae6, the metabolic functions of degraders remained conserved, enabling quantitative prediction of degradation outcomes based on community and substrate composition. The frequent co-occurrence of functionally complementary fucoidan degraders in ocean metagenomes suggests that synergistic degradation is a globally relevant strategy. Our findings suggest that the environmental turnover of complex biopolymers depends not only on individual metabolic capabilities of degraders but also on ecological interactions shaped by substrate architecture. This work provides a mechanistic framework for understanding carbon cycling in the ocean and for engineering synthetic microbial consortia to degrade recalcitrant polysaccharides.</t>
+          <t>Multiple sclerosis (MS) is a chronic inflammatory demyelinating disease of the CNS whose risk and course are shaped by both genetic and environmental factors, among which the intestinal microbiota has emerged as a key, potentially modifiable contributor. People with MS frequently display altered gut microbiota, characterized by depletion of fiber-fermenting, short-chain fatty acid (SCFA)-producing commensals, and expansion of taxa associated with mucus degradation and proinflammatory metabolism. These compositional shifts are paralleled by broad changes in blood and CSF metabolites, including reduced SCFAs, tryptophan-derived aryl hydrocarbon receptor ligands, and secondary bile acids. In addition, several reports highlight the accumulation of aromatic amino acid-derived phenolic and indolic compounds and specific lipid mediators linked to neuroinflammation and neurodegeneration. In this up-to-date review, we synthesize evidence from experimental models and human studies showing how microbial metabolites can influence MS pathogenesis through converging mechanisms: modulation of gut and blood-brain barrier integrity; shaping of T-cell and B-cell responses; direct effects on microglia, astrocytes, and oligodendrocyte lineage cells after crossing into the CNS; and modulation of neural circuits, particularly those involving the vagus nerve. Finally, we highlight current gaps, including the need for longitudinal, harmonized multiomic cohorts, and mechanistic studies integrating microbiome, metabolome, and host readouts across gut, blood, and CNS. Overall, available data support a model in which coordinated disruption of the gut microbiota-metabolite axis, rather than any single pathogen, contributes to MS, opening avenues for microbiota-based and metabolite-based biomarkers and therapies aimed at restoring immune and neuroglial homeostasis.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>本研究探討海洋中複雜多醣體「褐藻醣膠」（fucoidans）的微生物降解機制。儘管褐藻醣膠因其抗降解性在碳封存中扮演關鍵角色，但過往對於其在自然界中是否能被完全分解並不清楚。研究發現，褐藻醣膠的降解並非單一物種所能完成，而是透過具有互補代謝功能的細菌群落進行「協同作用」。透過代謝體學分析，研究團隊識別出專門降解硫酸岩藻糖骨架與稀有單醣側鏈的代謝群組（metabolic guilds），這種分工合作能將降解效率大幅提升至 97.1%。此外，研究顯示此代謝功能在不同環境下具有高度保守性，且在海洋宏基因組中普遍存在。本研究揭示了生物聚合物的環境周轉率取決於微生物間的生態交互作用，為理解海洋碳循環機制提供了重要框架，並為未來利用人工合成微生物群落降解頑固性多醣體提供了技術基礎。</t>
+          <t>本研究探討多發性硬化症（MS）與腸道微生物群之間的關聯。研究指出，MS 患者的腸道菌相呈現失調狀態，包括短鏈脂肪酸（SCFA）產生菌減少，以及促發炎代謝菌的增加。這些微生物群落的變化伴隨著血液與腦脊髓液中代謝物（如色胺酸衍生物、膽汁酸及 SCFA）的顯著改變，這些物質經證實與神經發炎及退化密切相關。文中綜述了微生物代謝產物如何透過調節腸道與血腦屏障完整性、影響免疫細胞（T/B 細胞）反應，以及直接作用於神經膠質細胞來參與 MS 的致病機制。總結而言，MS 的發生與腸道菌群-代謝物軸的整體失調有關，而非單一病原體所致。該研究強調未來需進行多體學（multiomics）整合分析，以開發基於微生物群的生物標記與創新治療策略，旨在恢復患者的免疫與神經恆定。</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3185,7 +3179,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42649294/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42647759/</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3224,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>本研究探討常見解熱鎮痛藥物（乙醯胺酚 APAP 與布洛芬 IBU）對下水道生物薄膜中硫化氫（H2S）累積的影響。實驗發現，這兩類藥物會改變生物薄膜外胞體聚合物（EPS）的組成，導致蛋白質減少、多醣與腐植酸增加，造成 EPS 介面硬化。宏基因體分析顯示，藥物暴露會抑制菌體鞭毛組裝並增強附著力，同時改變硫代謝路徑，顯著提升還原硫酸鹽的基因表現（dsrA/B）並降低硫化物的氧化能力。此研究揭示了藥物殘留如何透過重塑生物薄膜結構與微生物功能，加劇下水道中危險氣體 H2S 的累積，為都市污水處理與公共衛生安全提供了重要的科學依據。</t>
+          <t>本研究旨在探討下水道中常見的退燒藥——乙醯胺酚（APAP）與布洛芬（IBU），對有害氣體硫化氫（H2S）累積、生物膜胞外聚合物（EPS）特性及微生物功能潛力的影響。研究發現，兩種藥物會改變H2S的釋放模式，導致後期累積量顯著超越對照組，其中IBU的促進效果比APAP更強。藥物暴露會導致EPS結構重塑，使其界面剛性化。總體基因體學分析進一步證實，藥物促使生物膜附著能力增強、終端亞硫酸鹽還原潛力（dsrA/B基因相關）提升，並降低了硫化物氧化潛力。本研究揭示退燒藥是過去被低估的環境壓力源，會藉由重塑生物膜結構來加劇下水道H2S累積，對都市基礎設施安全具有重要科學意義。</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3267,7 +3261,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>metagenomics, others (Transcriptomics, LC-PDA-MS, Western blotting, qPCR, ELISA, molecular docking)</t>
+          <t>metagenomics, others</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3285,7 +3279,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>本研究旨在探討草果多酚提取物（3CB）對潰瘍性結腸炎（UC）的緩解作用及其機制。研究利用響應面法優化3CB製備，並透過LC-PDA-MS鑑定出七種多酚成分，其中表兒茶素與表 afzelechin 含量最豐。在DSS誘導的UC小鼠模型中，3CB表現出顯著的治療效果：透過宏基因組定序發現，3CB能重塑腸道菌群，增加有益菌門（Bacteroidota）並抑制致病菌（Pseudomonadota等），同時恢復微生物的氨基糖與核苷酸糖代謝。此外，3CB能保護結腸黏膜屏障、抑制發炎因子表達，其機制涉及直接結合並抑制JNK1蛋白，進而調節JNK1-cJun訊息傳遞路徑。本研究證實了草果多酚透過菌群調節與抗發炎雙重途徑緩解結腸炎的潛力，為發炎性腸道疾病的臨床介入提供了科學依據。</t>
+          <t>本研究旨在探討草果富含多酚成分（3CB）對小鼠潰瘍性結腸炎（UC）的緩解作用及其機制。研究發現，3CB能顯著減輕UC症狀、保護腸黏膜屏障並抑制發炎。總體基因體分析顯示，3CB能重塑腸道菌相（減少有害菌Pseudomonadota、增加益菌Bacteroidota）並恢復其功能代謝通路。機制上，3CB中的活性成分「表阿福豆素」能高親和力結合並抑制JNK1，進而阻斷MAPK發炎訊號傳導。本研究證實草果多酚具有調節腸道菌群與靶向抗發炎的雙重作用，為發炎性腸道疾病（IBD）治療提供了潛在的天然藥物選擇。</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3302,28 +3296,30 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>42644746</t>
+          <t>42648293</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Metabolic division of labour drives estuarine-coastal N2O emissions.</t>
+          <t>Defined human Clostridia consortia reverse colitis via dual effects of tryptophan metabolites on microbiota and immunity.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>The ISME journal</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>Cell host &amp; microbe</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>18.7</v>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>metagenomics, metatranscriptomics</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>974 個重建的 N2O 相關基因體（原文未提及具體的環境樣本採集數量）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G55" t="b">
@@ -3331,12 +3327,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Estuarine and coastal systems are global hotspots of marine nitrous oxide (N2O) emissions, where microbial nitrification and denitrification are the primary processes regulating N2O dynamics. However, how interactions among different N2O-associated microorganisms influence ecosystem-scale N2O emissions remains poorly understood. This study combined in situ N2O concentrations, 15N-based potential rates, metagenomics, metatranscriptomics, and genome-scale metabolic model analysis to explore N2O production and reduction processes in estuarine and coastal systems. Potential N2O production and reduction rates, together with in situ concentrations, the relative abundance, and the transcriptional activity of associated genes, were significantly higher at low salinity and declined toward coastal regions. Based on the gene content of 974 recovered N2O-associated genomes, microorganisms were classified into three functional groups: net N2O producers, net N2O consumers, and self-sustaining N2O players. The abundance, composition, and activity of these functional groups shifted along estuarine-coastal gradients. A larger NO/N2O exchange gap, reflecting the imbalance between model-inferred NO and N2O handoff potentials, was found at low salinity and was associated with elevated bottom-water N2O concentrations. Together, community-level division of labour and the associated exchange gap provide a conceptual framework for linking N2O-related functional groups to N2O accumulation in estuarine-coastal ecosystems.</t>
+          <t>Microbial dysbiosis and disrupted mucosal immune homeostasis are integrally involved in the pathogenesis of inflammatory bowel diseases (IBDs). Live biotherapeutic products (LBPs) offer a potential therapeutic strategy to restore beneficial microbes and mitigate disease. We investigated the therapeutic efficacy of 2 LBPs, human Clostridia consortia 17-mix and 11-mix, by treating established colitis in murine models. Both LBPs exhibited therapeutic effects in T cell-mediated chronic colitis models induced by human microbiota and in pathobiont-driven gnotobiotic colitis models established with combinations of IBD-relevant human-derived strains. Metagenomic and metabolomic analyses elucidated mechanisms that go beyond established functions driven by short-chain fatty acids (SCFAs) and interleukin (IL)-10-producing regulatory T cells. Notably, LBPs exerted therapeutic effects by directly inhibiting resident pathobionts and through IL-10-independent activation of host anti-inflammatory aryl hydrocarbon receptor (AhR) pathways by bacterial tryptophan metabolites. These results elucidate SCFA- and IL-10-independent protective mechanisms exerted by defined resident bacterial strains that are depleted in IBD dysbiosis.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>本研究旨在探討河口與沿海系統中，微生物交互作用如何驅動一氧化二氮（N2O）的排放。研究結合現場觀測、15N同位素速率、總體基因體與轉錄體學，重建了974個N2O相關基因體。結果指出，低鹽度區域的N2O產生與還原速率及基因表達顯著較高。研究將微生物劃分為淨產生者、淨消費者與自給自足者，並發現低鹽度區因群落間物質交換失衡，存在較大的NO/N2O交換缺口，進而導致底層水體N2O顯著累積。本研究建立了群落水平的「分工與交換缺口」理論框架，為預測及理解海洋生態系統N2O排放提供了關鍵的科學依據。</t>
+          <t>本研究探討了兩種由人類梭狀芽孢桿菌組成的活體生物藥物（LBP，分別為 17-mix 和 11-mix）治療小鼠結腸炎的療效與機制。研究發現，這些菌群能有效緩解小鼠的慢性與特定病原體誘導的結腸炎。宏基因組學與代謝組學分析顯示，除了傳統的短鏈脂肪酸（SCFA）和 IL-10 途徑外，LBP 還能直接抑制共生病原菌，並透過細菌色胺酸代謝物，以不依賴 IL-10 的方式激活宿主的芳香烴受體（AhR）抗炎途徑。此發現揭示了腸道有益菌保護腸道的新機制，為發炎性腸道疾病（IBD）的微生態療法提供了重要科學依據。</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3346,19 +3342,19 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42644746/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648293/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>42640624</t>
+          <t>42640100</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Gut microbial diversity at baseline conditions the clinical, microbiome, and metabolic response to paraprobiotic Lactiplantibacillus plantarum LRCC5282 in overweight adults.</t>
+          <t>Revisiting gut microbiota-driven ammonia metabolism: from disease burden to physiological adaptation.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3371,12 +3367,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>120 位過重成人</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G56" t="b">
@@ -3384,12 +3380,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>The gut microbiota is increasingly recognized as a target for obesity management; however, whether baseline gut microbial diversity conditions responsiveness to microbiota-targeted interventions remains unclear. We aimed to investigate whether baseline gut microbial diversity is associated with responsiveness to a paraprobiotic derived from Lactiplantibacillus plantarum LRCC5282 (LP5282-P) in overweight adults. In a 12-week, randomized, double-blind, placebo-controlled, multicenter trial of 120 overweight adults, LP5282-P produced no significant between-group differences in any clinical outcome across the overall per-protocol population. However, in the low-diversity subgroup, LP5282-P was associated with significant reductions in body weight, body mass index, and circulating leptin levels. These clinical changes were accompanied by compositional shifts in the gut microbiota, including higher relative abundances of Christensenellaceae, Faecalibacterium, and Alistipes. Fecal metabolite profiles showed elevated acetate and butyrate concentrations and altered bile acid composition. Within the low-diversity subgroup, changes in the relative abundances of Akkermansia and Eubacterium were inversely correlated with changes in body weight, body fat mass, and leptin levels. In contrast, the high-diversity subgroup exhibited no consistent response across the outcome domains examined. Overall, baseline gut microbial diversity was associated with differential responsiveness to LP5282-P, supporting its potential use as a stratification variable in future microbiota-targeted intervention trials. Further studies integrating direct measures of microbial activity and host response are warranted to elucidate the biological pathways underlying this diversity-dependent responsiveness. Trial registration: Clinical Research Information Service (CRIS), KCT0008119.</t>
+          <t>Ammonia homeostasis is governed by interconnected host and microbial pathways, including hepatic ureagenesis, glutamine synthesis, and gut microbiota-mediated urea hydrolysis, proteolysis, and amino acid deamination. Ammonia has historically been viewed primarily as a nitrogenous waste product and neurotoxic molecule, a concept strongly supported by studies of hyperammonemia and hepatic encephalopathy. Impaired hepatic clearance, portosystemic shunting, and enhanced gut-derived ammonia input increase systemic ammonia burden and are linked to neurological dysfunction, muscle wasting, immune dysregulation, and progression of liver disease. In the gut lumen and mucosal environment, however, gut microbes not only generate ammonia but can also reuse ammonia-derived nitrogen for amino acid synthesis, microbial biomass formation, and community nitrogen exchange. Evidence from selected physiological and preclinical models indicates that microbiota-derived ammonia may contribute to nitrogen recycling, microbial community maintenance, enteric neural regulation, or metabolic adaptation under defined conditions. These roles are more context-specific and less broadly established than the pathological effects of systemic hyperammonemia. When epithelial barrier integrity is compromised, hepatic clearance declines, or host buffering reserves are depleted, elevated ammonia can increase epithelial exposure, portal ammonia input, or peripheral blood ammonia. Conversely, evidence that reduced microbiota-derived ammonia contributes to disease remains limited and currently comes mainly from selected animal models. This review re-examines ammonia metabolism from a gut microbiota-centered perspective. We discuss the ecological origins, spatial distribution, exposure characteristics, host-interface effects, and context-specific outcomes of microbiota-derived ammonia in physiology and disease, and discuss how ammonia should be measured, stratified, and targeted in microbial nitrogen metabolism.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>本研究旨在探討基準線腸道微生物多樣性，是否會影響過重成人對副乾酪乳桿菌（LP5282-P）介入的臨床、菌群及代謝反應。在一項為期12週、納入120位過重成人的臨床試驗中，整體人群並未展現顯著差異；然而，在「低多樣性」亞群中，LP5282-P顯著降低了受試者的體重、BMI與血清瘦素水平，並促使腸道有益菌（如 *Faecalibacterium* 與 *Alistipes*）豐度上升，同時提升糞便中乙酸與丁酸濃度並改變膽汁酸組成。相反地，「高多樣性」亞群則無一致反應。此研究證實基準線菌群多樣性是預測益生菌療效的重要關鍵，可作為未來精準微生態介入與體重管理的分層依據。</t>
+          <t>本綜述重新審視了腸道菌群驅動的氨代謝，探討其從疾病負擔到生理適應的雙重角色。傳統上，氨被視為具神經毒性的代謝廢物，與高氨血症、肝性腦病及肝病惡化密切相關。然而，在腸道微環境中，微生物不僅產生氨，亦能利用氨源氮進行氨基酸合成與群落氮循環，展現出維持腸道神經與代謝適應等生理功能。文章強調，氨的病理與生理效應高度取決於上皮屏障、肝臟清除能力及宿主緩衝儲備。本研究為腸道微生物氮代謝提供了新的生態與臨床視角，並討論了未來如何精確測量及標靶氨代謝的策略。</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3399,37 +3395,37 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42640624/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42640100/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>42641146</t>
+          <t>42648179</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Engineered bacterial therapeutics from synthetic biology to clinical translation: A multi-database scientometric analysis, 2000-2026.</t>
+          <t>Simultaneous removal of nitrogen, Cu2+, and bisphenol A in a hydrogel-biochar-AQDS immobilized bioreactor with added bicarbonate: Performance and metagenomic insights.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Human vaccines &amp; immunotherapeutics</t>
+          <t>Journal of hazardous materials</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.5</v>
+        <v>11.3</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1,730 篇學術文章與評論</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G57" t="b">
@@ -3437,12 +3433,13 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Engineered bacterial therapeutics integrate programmable strain engineering with biomedical functions such as sensing, delivery, immune modulation, microbiome intervention, and disease management. This study conducted a multi-database bibliometric analysis to map the knowledge structure, collaboration patterns, and translational direction of this field. Bibliographic records were retrieved from Web of Science Core Collection, Scopus, and PubMed for publications from 1 January 2000 to 1 June 2026. After document-type filtering, time restriction, deduplication, language screening, and manual eligibility assessment, 1,730 English-language articles and reviews were included. CiteSpace 6.4.R1, VOSviewer 1.6.20, and the bibliometrix R package were used to analyze publication trends, collaboration networks, journal co-citation, dual-map citation trajectories, citation bursts, keyword co-occurrence, and thematic evolution. Publication output increased steadily, with faster growth after 2020; 2025 was the highest-output complete year, while 2026 represented a partial retrieval year. China and the United States were the leading contributors, although institutional collaboration remained regionally clustered. Co-citation, citation-burst, and keyword analyses showed a shift from bacterial chassis construction and circuit design toward engineered probiotics, gut microbiota-related therapy, cancer immunotherapy, drug delivery, live biotherapeutic products, and clinical translation. Persistent translational priorities include controllability, safety, manufacturing consistency, and regulatory alignment.</t>
+          <t>As the complexity of industrial wastewater pollution continues to increase, the simultaneous removal of nitrogen, metal contaminants, and persistent organic pollutants under low carbon conditions has become a key challenge for biological treatment systems. To address the operational instability and dependence on carbon sources observed in immobilized systems when exposed to copper (Cu2+) and bisphenol A (BPA), the Pseudoalteromonas japonicus strain LY0623 was integrated into a hydrogel-biochar-AQDS composite carrier to construct a multifunctional immobilized biofilm system. Notably, under conditions containing only NaHCO3, the R4 system achieved an NH4+-N removal rate of 89%. Under conditions where Cu2+ and BPA coexist, the R4 system achieved removal of NH4+-N (89%), NO3--N (100%), Cu2+ (85%), and BPA (88%). Sediment characterization confirmed that Cu2+ was immobilized through adsorption, complexation, and microbiologically induced carbonate precipitation (MICP). Metagenomic analysis further indicated that the Pseudomonadota phylum remained the dominant phylum, while functional pathways associated with inorganic carbon assimilation, HNAD nitrogen metabolism, endogenous carbon transformation, biomineralization, electron transfer, and aromatic compound degradation were preserved. By combining ammonia oxidation driven energy production, inorganic carbon utilization, redox mediated processes, and biomineralization, this study provides a highly promising low carbon strategy for treating industrial wastewater containing mixed pollutants.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>本研究透過文獻計量學方法，系統性分析 2000 年至 2026 年間有關「工程化細菌治療」的 1,730 篇學術文獻。研究旨在釐清該領域的知識結構、國際合作模式及臨床轉化趨勢。分析顯示，該領域自 2020 年後顯著加速發展，中國與美國為主要貢獻國。核心研究主軸已由早期的細菌底盤構建與基因電路設計，轉向工程化益生菌、癌症免疫治療、藥物遞送及活體生物藥物（LBP）的開發。科學意義在於確立了該領域從實驗室轉向臨床應用的優先議題，即解決控制力、生物安全性、生產一致性與法規調適等挑戰，為未來工程化細菌作為精準醫療工具的發展提供關鍵決策參考。</t>
+          <t>本研究旨在解決低碳條件下，工業廢水中氮、重金屬（Cu2+）與雙酚A（BPA）等混合污染物難以同時高效生物降解的挑戰。研究人員將日本假交替單胞菌（*Pseudoalteromonas japonicus*）LY0623菌株整合至水凝膠-生物炭-AQDS複合載體中，構建出新型固定化生物膜系統（R4系統）。
+研究發現，在僅添加碳酸氫鈉（無機碳源）的條件下，該系統成功實現了NH4+-N（89%）、NO3--N（100%）、Cu2+（85%）和BPA（88%）的高效同時去除。總體基因體學分析證實，變形菌門（Pseudomonadota）為優勢菌群，且系統中與無機碳同化、異營硝化-好氧反硝化（HNAD）、生物礦化及芳香族化合物降解相關的功能通路均得到有效維持。本研究結合了氨氧化產能與生物礦化等機制，為混合污染廢水處理提供了一種具前景的低碳生物修復策略。</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3452,32 +3449,32 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42641146/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42648179/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>42642834</t>
+          <t>42642466</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Glycosylation in gut-brain communication: from the intestinal barrier and microbiota to immune and neural signaling.</t>
+          <t>Empirical evidence for gut microbial influence on human brain neurochemistry via the gut-brain axis.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>Molecular psychiatry</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11</v>
+        <v>10.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3490,12 +3487,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>The gut-brain axis is a complex bidirectional communication network linking the gastrointestinal tract and the central nervous system. Its dysregulation is closely associated with a wide range of gastrointestinal, metabolic, and neuropsychiatric disorders. Glycosylation, one of the most prevalent and structurally diverse post-translational modifications of proteins and lipids, is increasingly recognized as a regulator of multiple processes within the gut-brain axis. In this review, we summarize evidence that glycosylation influences several steps of gut-brain communication, including intestinal barrier function, microbial glycan metabolism, immune signaling, enteric and vagal pathways, blood-brain barrier integrity, and neural responses. We distinguish direct mechanistic findings from associative observations and discuss the more limited evidence for brain-to-gut regulation of intestinal glycosylation. In addition, we discuss the potential of glycosylation-targeted nutritional and microbiota-based interventions and highlight emerging opportunities to integrate glycomics with other omics approaches to dissect the complex regulatory networks underlying the gut-brain axis. In conclusion, elucidating how glycosylation shapes signaling along the gut-brain axis may open new avenues for understanding disease pathogenesis and for developing targeted therapeutic strategies.</t>
+          <t>The gut microbiome produces metabolites with potential neuroactive properties, many of which act locally within the gut. While preclinical studies suggest these microbial pathways can influence cognitive and emotional processes, human evidence remains limited. This study investigates associations between gut microbiome-derived neuroactive functional potential and in vivo brain neurotransmitter concentrations in healthy young females. Using proton magnetic resonance spectroscopy (¹H-MRS), we quantified GABA and glutamate levels in the dorsolateral prefrontal cortex (dlPFC), anterior cingulate cortex (ACC), and inferior occipital gyrus (IOG). Parallel metagenomic profiling characterised microbial functional potential for pathways related to the synthesis and degradation of GABA, glutamate, short-chain fatty acids (SCFAs), p-cresol, and inositol. Region-specific associations were observed between these microbial pathways and cortical GABA and glutamate levels, including excitatory/inhibitory (E/I) balance, a key marker of neuroplasticity and mental health. Notably, microbial glutamate degradation and inositol synthesis potential were associated with IOG E/I balance, while additional pathways including GABA metabolism, p-cresol production, and SCFA synthesis showed distinct associations across regions. Exploratory analyses also identified links between microbial functional potential and anxiety, depressive symptoms, and sleep quality. Together, these findings provide new human evidence that variation in microbial functional potential corresponds with regional cortical neurochemistry and psychological wellbeing, highlighting the gut-brain axis as a promising avenue for mechanistically informed microbiome-based- interventions.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>本文探討「腸-腦軸線」（Gut-Brain Axis）中醣基化（Glycosylation）修飾的關鍵調節角色。醣基化作為蛋白質與脂質重要的轉譯後修飾，深刻影響腸道屏障功能、微生物聚醣代謝、免疫訊息傳遞及血腦屏障完整性。研究重點解析了醣基化如何調控腸道與中樞神經系統間的溝通，並區分了機制性證據與相關性觀察。本文不僅強調了醣基化在維繫軸線穩定中的核心地位，更提出透過營養干預與微生物調節，結合多體學（Omics）分析醣基化網絡，將有望為神經精神疾病與代謝性障礙提供創新的診斷與治療策略。</t>
+          <t>本研究旨在探討健康女性的腸道菌群功能潛力與大腦活體神經傳導物質（GABA與麩胺酸）濃度的關聯。研究結合腦部質子磁共振波譜（¹H-MRS）與總體基因體學分析，發現微生物中參與GABA、麩胺酸、短鏈脂肪酸、對甲酚及肌醇代謝的通路，與大腦特定區域（如背外側前額葉、前扣帶迴與下枕葉）的神經傳導物質水平及興奮/抑制平衡（E/I）具有區域特異性關聯。探索性分析亦顯示微生物功能與焦慮、抑鬱及睡眠品質相關。本研究為腸道菌群影響人類大腦神經化學與心理健康提供了直接的人體實證，為未來開發以微生物為基礎的腦腸軸臨床干預奠定基礎。</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3505,28 +3502,28 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42642834/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42642466/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>42640100</t>
+          <t>42642836</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Revisiting gut microbiota-driven ammonia metabolism: from disease burden to physiological adaptation.</t>
+          <t>Microbiome-mediated regulation of pathogen virulence: Molecular mechanisms and clinical implications.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Gut microbes</t>
+          <t>Virulence</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11</v>
+        <v>5.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -3543,12 +3540,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Ammonia homeostasis is governed by interconnected host and microbial pathways, including hepatic ureagenesis, glutamine synthesis, and gut microbiota-mediated urea hydrolysis, proteolysis, and amino acid deamination. Ammonia has historically been viewed primarily as a nitrogenous waste product and neurotoxic molecule, a concept strongly supported by studies of hyperammonemia and hepatic encephalopathy. Impaired hepatic clearance, portosystemic shunting, and enhanced gut-derived ammonia input increase systemic ammonia burden and are linked to neurological dysfunction, muscle wasting, immune dysregulation, and progression of liver disease. In the gut lumen and mucosal environment, however, gut microbes not only generate ammonia but can also reuse ammonia-derived nitrogen for amino acid synthesis, microbial biomass formation, and community nitrogen exchange. Evidence from selected physiological and preclinical models indicates that microbiota-derived ammonia may contribute to nitrogen recycling, microbial community maintenance, enteric neural regulation, or metabolic adaptation under defined conditions. These roles are more context-specific and less broadly established than the pathological effects of systemic hyperammonemia. When epithelial barrier integrity is compromised, hepatic clearance declines, or host buffering reserves are depleted, elevated ammonia can increase epithelial exposure, portal ammonia input, or peripheral blood ammonia. Conversely, evidence that reduced microbiota-derived ammonia contributes to disease remains limited and currently comes mainly from selected animal models. This review re-examines ammonia metabolism from a gut microbiota-centered perspective. We discuss the ecological origins, spatial distribution, exposure characteristics, host-interface effects, and context-specific outcomes of microbiota-derived ammonia in physiology and disease, and discuss how ammonia should be measured, stratified, and targeted in microbial nitrogen metabolism.</t>
+          <t>The human microbiome profoundly influences pathogen virulence and disease susceptibility through diverse molecular mechanisms. This review, focused on literature from 2016 to 2026, synthesizes knowledge on microbiome-mediated regulation examining major pathogens including Vibrio cholerae, enterohemorrhagic Escherichia coli, Salmonella species, Clostridioides difficile, and Staphylococcus aureus. A triangular interaction model is presented, linking host immunity, resident microbiome, and invading pathogen to frame infection outcomes. Commensal bacteria regulate pathogen behavior through quorum sensing interference, metabolite-mediated regulation via short-chain fatty acids and bile acids, competitive exclusion, immune response modulation, and direct antimicrobial production. Key species-Lactobacillus spp. Bifidobacterium spp. Bacteroides thetaiotaomicron, and Faecalibacterium prausnitzii-employ distinct molecular strategies against these pathogens. Organ-on-chip platforms and multi-omics advances reveal context-dependent interactions. Clinical applications including rationally designed probiotics, fecal microbiota transplantation, and precision microbiome engineering show promise despite challenges of inter-individual microbiome variability, representing a paradigm shift toward ecosystem-based infectious disease management.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>本綜述重新審視了腸道菌群驅動的氨代謝，探討其從疾病負擔到生理適應的雙重角色。傳統上，氨被視為具神經毒性的代謝廢物，與高氨血症、肝性腦病及肝病惡化密切相關。然而，在腸道微環境中，微生物不僅產生氨，亦能利用氨源氮進行氨基酸合成與群落氮循環，展現出維持腸道神經與代謝適應等生理功能。文章強調，氨的病理與生理效應高度取決於上皮屏障、肝臟清除能力及宿主緩衝儲備。本研究為腸道微生物氮代謝提供了新的生態與臨床視角，並討論了未來如何精確測量及標靶氨代謝的策略。</t>
+          <t>本研究綜述了2016年至2026年間關於腸道微生物群調控病原體毒力（如霍亂弧菌、大腸桿菌、沙門氏菌等）的分子機制。作者提出了一個結合宿主免疫、共生菌群與入侵病原體的「三角交互模型」，闡述了共生菌如何透過群體感應干擾、代謝產物（如短鏈脂肪酸、膽汁酸）調節、競爭性排斥及免疫調節來抑制病原體。研究強調了乳酸桿菌、雙歧桿菌及普拉梭菌等關鍵菌種的保護機制，並探討了器官晶片與多體學技術在揭示交互作用上的貢獻。此研究主張從生態系統角度管理傳染病，指出益生菌設計、糞便菌群移植及精準微生物組工程是未來治療的關鍵方向，雖面臨個體差異挑戰，但為臨床感染控制提供了典範轉移。</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3558,7 +3555,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42640100/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42642836/</t>
         </is>
       </c>
     </row>
@@ -3618,30 +3615,30 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>42642836</t>
+          <t>42640624</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Microbiome-mediated regulation of pathogen virulence: Molecular mechanisms and clinical implications.</t>
+          <t>Gut microbial diversity at baseline conditions the clinical, microbiome, and metabolic response to paraprobiotic Lactiplantibacillus plantarum LRCC5282 in overweight adults.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Virulence</t>
+          <t>Gut microbes</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>5.4</v>
+        <v>11</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>16S, metabolomics</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>120 位過重成人</t>
         </is>
       </c>
       <c r="G61" t="b">
@@ -3649,12 +3646,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>The human microbiome profoundly influences pathogen virulence and disease susceptibility through diverse molecular mechanisms. This review, focused on literature from 2016 to 2026, synthesizes knowledge on microbiome-mediated regulation examining major pathogens including Vibrio cholerae, enterohemorrhagic Escherichia coli, Salmonella species, Clostridioides difficile, and Staphylococcus aureus. A triangular interaction model is presented, linking host immunity, resident microbiome, and invading pathogen to frame infection outcomes. Commensal bacteria regulate pathogen behavior through quorum sensing interference, metabolite-mediated regulation via short-chain fatty acids and bile acids, competitive exclusion, immune response modulation, and direct antimicrobial production. Key species-Lactobacillus spp. Bifidobacterium spp. Bacteroides thetaiotaomicron, and Faecalibacterium prausnitzii-employ distinct molecular strategies against these pathogens. Organ-on-chip platforms and multi-omics advances reveal context-dependent interactions. Clinical applications including rationally designed probiotics, fecal microbiota transplantation, and precision microbiome engineering show promise despite challenges of inter-individual microbiome variability, representing a paradigm shift toward ecosystem-based infectious disease management.</t>
+          <t>The gut microbiota is increasingly recognized as a target for obesity management; however, whether baseline gut microbial diversity conditions responsiveness to microbiota-targeted interventions remains unclear. We aimed to investigate whether baseline gut microbial diversity is associated with responsiveness to a paraprobiotic derived from Lactiplantibacillus plantarum LRCC5282 (LP5282-P) in overweight adults. In a 12-week, randomized, double-blind, placebo-controlled, multicenter trial of 120 overweight adults, LP5282-P produced no significant between-group differences in any clinical outcome across the overall per-protocol population. However, in the low-diversity subgroup, LP5282-P was associated with significant reductions in body weight, body mass index, and circulating leptin levels. These clinical changes were accompanied by compositional shifts in the gut microbiota, including higher relative abundances of Christensenellaceae, Faecalibacterium, and Alistipes. Fecal metabolite profiles showed elevated acetate and butyrate concentrations and altered bile acid composition. Within the low-diversity subgroup, changes in the relative abundances of Akkermansia and Eubacterium were inversely correlated with changes in body weight, body fat mass, and leptin levels. In contrast, the high-diversity subgroup exhibited no consistent response across the outcome domains examined. Overall, baseline gut microbial diversity was associated with differential responsiveness to LP5282-P, supporting its potential use as a stratification variable in future microbiota-targeted intervention trials. Further studies integrating direct measures of microbial activity and host response are warranted to elucidate the biological pathways underlying this diversity-dependent responsiveness. Trial registration: Clinical Research Information Service (CRIS), KCT0008119.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>本研究綜述了2016年至2026年間關於腸道微生物群調控病原體毒力（如霍亂弧菌、大腸桿菌、沙門氏菌等）的分子機制。作者提出了一個結合宿主免疫、共生菌群與入侵病原體的「三角交互模型」，闡述了共生菌如何透過群體感應干擾、代謝產物（如短鏈脂肪酸、膽汁酸）調節、競爭性排斥及免疫調節來抑制病原體。研究強調了乳酸桿菌、雙歧桿菌及普拉梭菌等關鍵菌種的保護機制，並探討了器官晶片與多體學技術在揭示交互作用上的貢獻。此研究主張從生態系統角度管理傳染病，指出益生菌設計、糞便菌群移植及精準微生物組工程是未來治療的關鍵方向，雖面臨個體差異挑戰，但為臨床感染控制提供了典範轉移。</t>
+          <t>本研究旨在探討基準線腸道微生物多樣性，是否會影響過重成人對副乾酪乳桿菌（LP5282-P）介入的臨床、菌群及代謝反應。在一項為期12週、納入120位過重成人的臨床試驗中，整體人群並未展現顯著差異；然而，在「低多樣性」亞群中，LP5282-P顯著降低了受試者的體重、BMI與血清瘦素水平，並促使腸道有益菌（如 *Faecalibacterium* 與 *Alistipes*）豐度上升，同時提升糞便中乙酸與丁酸濃度並改變膽汁酸組成。相反地，「高多樣性」亞群則無一致反應。此研究證實基準線菌群多樣性是預測益生菌療效的重要關鍵，可作為未來精準微生態介入與體重管理的分層依據。</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3664,32 +3661,32 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42642836/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42640624/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>42642466</t>
+          <t>42642834</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Empirical evidence for gut microbial influence on human brain neurochemistry via the gut-brain axis.</t>
+          <t>Glycosylation in gut-brain communication: from the intestinal barrier and microbiota to immune and neural signaling.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Molecular psychiatry</t>
+          <t>Gut microbes</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.1</v>
+        <v>11</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3702,12 +3699,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>The gut microbiome produces metabolites with potential neuroactive properties, many of which act locally within the gut. While preclinical studies suggest these microbial pathways can influence cognitive and emotional processes, human evidence remains limited. This study investigates associations between gut microbiome-derived neuroactive functional potential and in vivo brain neurotransmitter concentrations in healthy young females. Using proton magnetic resonance spectroscopy (¹H-MRS), we quantified GABA and glutamate levels in the dorsolateral prefrontal cortex (dlPFC), anterior cingulate cortex (ACC), and inferior occipital gyrus (IOG). Parallel metagenomic profiling characterised microbial functional potential for pathways related to the synthesis and degradation of GABA, glutamate, short-chain fatty acids (SCFAs), p-cresol, and inositol. Region-specific associations were observed between these microbial pathways and cortical GABA and glutamate levels, including excitatory/inhibitory (E/I) balance, a key marker of neuroplasticity and mental health. Notably, microbial glutamate degradation and inositol synthesis potential were associated with IOG E/I balance, while additional pathways including GABA metabolism, p-cresol production, and SCFA synthesis showed distinct associations across regions. Exploratory analyses also identified links between microbial functional potential and anxiety, depressive symptoms, and sleep quality. Together, these findings provide new human evidence that variation in microbial functional potential corresponds with regional cortical neurochemistry and psychological wellbeing, highlighting the gut-brain axis as a promising avenue for mechanistically informed microbiome-based- interventions.</t>
+          <t>The gut-brain axis is a complex bidirectional communication network linking the gastrointestinal tract and the central nervous system. Its dysregulation is closely associated with a wide range of gastrointestinal, metabolic, and neuropsychiatric disorders. Glycosylation, one of the most prevalent and structurally diverse post-translational modifications of proteins and lipids, is increasingly recognized as a regulator of multiple processes within the gut-brain axis. In this review, we summarize evidence that glycosylation influences several steps of gut-brain communication, including intestinal barrier function, microbial glycan metabolism, immune signaling, enteric and vagal pathways, blood-brain barrier integrity, and neural responses. We distinguish direct mechanistic findings from associative observations and discuss the more limited evidence for brain-to-gut regulation of intestinal glycosylation. In addition, we discuss the potential of glycosylation-targeted nutritional and microbiota-based interventions and highlight emerging opportunities to integrate glycomics with other omics approaches to dissect the complex regulatory networks underlying the gut-brain axis. In conclusion, elucidating how glycosylation shapes signaling along the gut-brain axis may open new avenues for understanding disease pathogenesis and for developing targeted therapeutic strategies.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>本研究旨在探討健康女性的腸道菌群功能潛力與大腦活體神經傳導物質（GABA與麩胺酸）濃度的關聯。研究結合腦部質子磁共振波譜（¹H-MRS）與總體基因體學分析，發現微生物中參與GABA、麩胺酸、短鏈脂肪酸、對甲酚及肌醇代謝的通路，與大腦特定區域（如背外側前額葉、前扣帶迴與下枕葉）的神經傳導物質水平及興奮/抑制平衡（E/I）具有區域特異性關聯。探索性分析亦顯示微生物功能與焦慮、抑鬱及睡眠品質相關。本研究為腸道菌群影響人類大腦神經化學與心理健康提供了直接的人體實證，為未來開發以微生物為基礎的腦腸軸臨床干預奠定基礎。</t>
+          <t>本文探討「腸-腦軸線」（Gut-Brain Axis）中醣基化（Glycosylation）修飾的關鍵調節角色。醣基化作為蛋白質與脂質重要的轉譯後修飾，深刻影響腸道屏障功能、微生物聚醣代謝、免疫訊息傳遞及血腦屏障完整性。研究重點解析了醣基化如何調控腸道與中樞神經系統間的溝通，並區分了機制性證據與相關性觀察。本文不僅強調了醣基化在維繫軸線穩定中的核心地位，更提出透過營養干預與微生物調節，結合多體學（Omics）分析醣基化網絡，將有望為神經精神疾病與代謝性障礙提供創新的診斷與治療策略。</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3717,37 +3714,37 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42642466/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42642834/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>42648179</t>
+          <t>42641146</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Simultaneous removal of nitrogen, Cu2+, and bisphenol A in a hydrogel-biochar-AQDS immobilized bioreactor with added bicarbonate: Performance and metagenomic insights.</t>
+          <t>Engineered bacterial therapeutics from synthetic biology to clinical translation: A multi-database scientometric analysis, 2000-2026.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Journal of hazardous materials</t>
+          <t>Human vaccines &amp; immunotherapeutics</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.3</v>
+        <v>3.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>others</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>1,730 篇學術文章與評論</t>
         </is>
       </c>
       <c r="G63" t="b">
@@ -3755,13 +3752,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>As the complexity of industrial wastewater pollution continues to increase, the simultaneous removal of nitrogen, metal contaminants, and persistent organic pollutants under low carbon conditions has become a key challenge for biological treatment systems. To address the operational instability and dependence on carbon sources observed in immobilized systems when exposed to copper (Cu2+) and bisphenol A (BPA), the Pseudoalteromonas japonicus strain LY0623 was integrated into a hydrogel-biochar-AQDS composite carrier to construct a multifunctional immobilized biofilm system. Notably, under conditions containing only NaHCO3, the R4 system achieved an NH4+-N removal rate of 89%. Under conditions where Cu2+ and BPA coexist, the R4 system achieved removal of NH4+-N (89%), NO3--N (100%), Cu2+ (85%), and BPA (88%). Sediment characterization confirmed that Cu2+ was immobilized through adsorption, complexation, and microbiologically induced carbonate precipitation (MICP). Metagenomic analysis further indicated that the Pseudomonadota phylum remained the dominant phylum, while functional pathways associated with inorganic carbon assimilation, HNAD nitrogen metabolism, endogenous carbon transformation, biomineralization, electron transfer, and aromatic compound degradation were preserved. By combining ammonia oxidation driven energy production, inorganic carbon utilization, redox mediated processes, and biomineralization, this study provides a highly promising low carbon strategy for treating industrial wastewater containing mixed pollutants.</t>
+          <t>Engineered bacterial therapeutics integrate programmable strain engineering with biomedical functions such as sensing, delivery, immune modulation, microbiome intervention, and disease management. This study conducted a multi-database bibliometric analysis to map the knowledge structure, collaboration patterns, and translational direction of this field. Bibliographic records were retrieved from Web of Science Core Collection, Scopus, and PubMed for publications from 1 January 2000 to 1 June 2026. After document-type filtering, time restriction, deduplication, language screening, and manual eligibility assessment, 1,730 English-language articles and reviews were included. CiteSpace 6.4.R1, VOSviewer 1.6.20, and the bibliometrix R package were used to analyze publication trends, collaboration networks, journal co-citation, dual-map citation trajectories, citation bursts, keyword co-occurrence, and thematic evolution. Publication output increased steadily, with faster growth after 2020; 2025 was the highest-output complete year, while 2026 represented a partial retrieval year. China and the United States were the leading contributors, although institutional collaboration remained regionally clustered. Co-citation, citation-burst, and keyword analyses showed a shift from bacterial chassis construction and circuit design toward engineered probiotics, gut microbiota-related therapy, cancer immunotherapy, drug delivery, live biotherapeutic products, and clinical translation. Persistent translational priorities include controllability, safety, manufacturing consistency, and regulatory alignment.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>本研究旨在解決低碳條件下，工業廢水中氮、重金屬（Cu2+）與雙酚A（BPA）等混合污染物難以同時高效生物降解的挑戰。研究人員將日本假交替單胞菌（*Pseudoalteromonas japonicus*）LY0623菌株整合至水凝膠-生物炭-AQDS複合載體中，構建出新型固定化生物膜系統（R4系統）。
-研究發現，在僅添加碳酸氫鈉（無機碳源）的條件下，該系統成功實現了NH4+-N（89%）、NO3--N（100%）、Cu2+（85%）和BPA（88%）的高效同時去除。總體基因體學分析證實，變形菌門（Pseudomonadota）為優勢菌群，且系統中與無機碳同化、異營硝化-好氧反硝化（HNAD）、生物礦化及芳香族化合物降解相關的功能通路均得到有效維持。本研究結合了氨氧化產能與生物礦化等機制，為混合污染廢水處理提供了一種具前景的低碳生物修復策略。</t>
+          <t>本研究透過文獻計量學方法，系統性分析 2000 年至 2026 年間有關「工程化細菌治療」的 1,730 篇學術文獻。研究旨在釐清該領域的知識結構、國際合作模式及臨床轉化趨勢。分析顯示，該領域自 2020 年後顯著加速發展，中國與美國為主要貢獻國。核心研究主軸已由早期的細菌底盤構建與基因電路設計，轉向工程化益生菌、癌症免疫治療、藥物遞送及活體生物藥物（LBP）的開發。科學意義在於確立了該領域從實驗室轉向臨床應用的優先議題，即解決控制力、生物安全性、生產一致性與法規調適等挑戰，為未來工程化細菌作為精準醫療工具的發展提供關鍵決策參考。</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3771,19 +3767,19 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42648179/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42641146/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>42635403</t>
+          <t>42635401</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Baseline gut microbiome ecology predicts long-term fat mass loss after bariatric surgery: evidence for a thrifty Bifidobacterium phenotype.</t>
+          <t>Fecal filtrate transplantation as salvage therapy for fulminant Clostridioides difficile infection in adult hematological patients during chemotherapy-induced aplasia: a pilot experience.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3796,12 +3792,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>16S, metabolomics</t>
+          <t>16S, metagenomics</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>85 位重度肥胖患者及 21 位健康對照組（共 106 名受試者）</t>
+          <t>3 位成人血液腫瘤患者</t>
         </is>
       </c>
       <c r="G64" t="b">
@@ -3809,12 +3805,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Bariatric surgery (BS) induces weight loss, but long-term success involves complex host-microbiome interactions. We evaluated the longitudinal impact of BS, microbiome resilience, and Mediterranean Diet (MedDiet) adherence up to 24 months. This prospective observational study included 85 patients with severe obesity undergoing BS and 21 normal-weight healthy controls (HC). MedDiet adherence (PREDIMED) was assessed before surgery. Fecal microbiota (16S-rRNA sequencing) and metabolomics (1H-NMR spectroscopy) were analyzed at baseline and at 1-, 6-, and 12-months post-BS. Clinical outcomes and fat mass, evaluated by bioimpedanciometry, were tracked up to 24 months. At baseline, patients exhibited higher microbial Shannon diversity than controls (p = 0.041), alongside a dysfunctional microbiome and metabolome characterized by a higher Firmicutes/Bacteroidetes ratio and elevated levels of branched-chain amino acids (p &lt; 0.0001). Ordinary Least Squares (OLS) regression analysis revealed that MedDiet adherence and type 2 diabetes status significantly modulated baseline diversity. At 12 months post-BS, the gut ecosystem underwent profound remodeling, characterized by depletion of Bifidobacterium spp. and an increase in butyrate levels (p &lt; 0.0001), establishing a novel adaptive state distinct from HC. Baseline gut ecology significantly conditioned long-term BS outcomes: patients in the highest quartile of baseline Bifidobacterium spp. lost significantly less fat mass at 24 months than those in the lowest (6.6% vs. 13.2%, p = 0.010). High baseline Bifidobacterium abundance paradoxically acts as a "thrifty microbiome," potentially maximizing energy harvest and limiting surgery-induced fat loss. Overall, BS induces adaptive microbiome restoration rather than true normalization, highlighting the potential for precision interventions prior to surgery.</t>
+          <t>Fulminant Clostridioides difficile infection (CDI) in patients with hematologic malignancies during chemotherapy-induced aplasia carries high mortality and limited treatment options. Our objective was to evaluate fecal filtrate transplantation (FFT) as a salvage therapy for fulminant CDI during aplasia, and to explore whether donor-recipient phage dynamics may contribute to clinical response. We conducted a single-center, prospective, protocol-defined pilot case series study including consecutive adults with hematologic malignancies, chemotherapy-induced grade-4 aplasia and fulminant CDI, refractory to ≥5 d of high-dose oral vancomycin plus intravenous metronidazole and tigecycline. FFT was prepared from a single unrelated donor using sequential centrifugation and filtration, and administered via nasogastric tube in two doses. The primary outcome was sustained clinical cure, secondary outcomes included survival and adverse events, assessed at +14 and +30 d post-FFT. 16S rRNA gene sequencing was used to assess microbiome compositions, while viral metagenomics and in vitro propagation assays were employed to characterize donor-recipient phageome interactions. Three patients with adverse-risk acute myeloid leukemia and fulminant CDI caused by genetically distinct C. difficile strains received FFT. All patients achieved clinical resolution by day +14, accompanied by improvements in abdominal distension and inflammatory markers. By day +30, one patient died from Pseudomonas aeruginosa septic shock, while two maintained remission with confirmatory follow-up. FFT was well tolerated, with no procedure-related immediate complications or FFT-attributable adverse events. Microbiome and phage profiling revealed heterogeneous responses, including shifts in bacterial community composition, with no clear evidence for a general role of donor-derived phages in CDI resolution. In contrast, we observed induction of prophages harbored by recipient-associated Clostridium species, which may have contributed to decolonization through stress-induced entry into the lytic cycle. FFT was feasible, with rapid sustained CDI resolution in hematologic patients with chemotherapy-induced aplasia. ClinicalTrials.gov identifier NCT07172191. Prospective single-center pilot study of fecal filtrate transplantation (FFT) for fulminant-refractory C. difficile infection in three aplastic adult hematologic patients. FFT was well tolerated, achieved rapid clinical cure, and showed heterogeneous microbiome and phageome modulation, potentially contributing to therapeutic effects.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>本研究探討減重手術（BS）後腸道微生物群與長期減脂效果的關聯。研究追蹤 85 名患者於術前及術後長達 24 個月的變化，分析發現手術顯著重塑了腸道菌相與代謝環境，特別是雙歧桿菌（*Bifidobacterium*）的耗竭與丁酸鹽的增加。關鍵發現指出，術前高豐度的雙歧桿菌反而成為一種「節儉型表型」，會增加能量攝取效率，導致術後 24 個月的脂肪減少量顯著較少（6.6% 對比 13.2%）。這顯示減重手術並非使微生物組回歸常態，而是引發一種適應性重組。此研究凸顯了術前腸道生態作為預測手術成效生物標記的潛力，對於未來制定精準的術前介入策略具有重要的臨床指導意義。</t>
+          <t>本研究旨在評估糞便濾液移植（FFT）作為挽救療法，治療化療致免疫不全之血液腫瘤患者合併難治猛爆性艱難梭菌感染（CDI）的療效，並探討供受體間噬菌體的動力學關係。此臨床先導試驗納入3位患者，結果顯示FFT耐受性良好，所有患者在接受治療後14天內均達到臨床緩解。微生態與噬菌體體學分析顯示，臨床症狀的改善並非源於供體噬菌體的直接轉移，而是FFT可能誘發了受體腸道內艱難梭菌的原噬菌體進入溶菌週期，進而促進病原菌清除。本研究證實FFT在此高風險族群中具安全性與可行性，為難治性CDI提供了創新的機制見解與治療選擇。</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3824,19 +3820,19 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42635403/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42635401/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>42635401</t>
+          <t>42635406</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Fecal filtrate transplantation as salvage therapy for fulminant Clostridioides difficile infection in adult hematological patients during chemotherapy-induced aplasia: a pilot experience.</t>
+          <t>Separating extracellular from intracellular fecal metabolites exposes cross-feeding architecture in the gut: exploring metabolite partitioning and ecological associations.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3849,12 +3845,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>16S, metagenomics</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>3 位成人血液腫瘤患者</t>
+          <t>63 個糞便檢體（來自 63 位健康受試者）</t>
         </is>
       </c>
       <c r="G65" t="b">
@@ -3862,12 +3858,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Fulminant Clostridioides difficile infection (CDI) in patients with hematologic malignancies during chemotherapy-induced aplasia carries high mortality and limited treatment options. Our objective was to evaluate fecal filtrate transplantation (FFT) as a salvage therapy for fulminant CDI during aplasia, and to explore whether donor-recipient phage dynamics may contribute to clinical response. We conducted a single-center, prospective, protocol-defined pilot case series study including consecutive adults with hematologic malignancies, chemotherapy-induced grade-4 aplasia and fulminant CDI, refractory to ≥5 d of high-dose oral vancomycin plus intravenous metronidazole and tigecycline. FFT was prepared from a single unrelated donor using sequential centrifugation and filtration, and administered via nasogastric tube in two doses. The primary outcome was sustained clinical cure, secondary outcomes included survival and adverse events, assessed at +14 and +30 d post-FFT. 16S rRNA gene sequencing was used to assess microbiome compositions, while viral metagenomics and in vitro propagation assays were employed to characterize donor-recipient phageome interactions. Three patients with adverse-risk acute myeloid leukemia and fulminant CDI caused by genetically distinct C. difficile strains received FFT. All patients achieved clinical resolution by day +14, accompanied by improvements in abdominal distension and inflammatory markers. By day +30, one patient died from Pseudomonas aeruginosa septic shock, while two maintained remission with confirmatory follow-up. FFT was well tolerated, with no procedure-related immediate complications or FFT-attributable adverse events. Microbiome and phage profiling revealed heterogeneous responses, including shifts in bacterial community composition, with no clear evidence for a general role of donor-derived phages in CDI resolution. In contrast, we observed induction of prophages harbored by recipient-associated Clostridium species, which may have contributed to decolonization through stress-induced entry into the lytic cycle. FFT was feasible, with rapid sustained CDI resolution in hematologic patients with chemotherapy-induced aplasia. ClinicalTrials.gov identifier NCT07172191. Prospective single-center pilot study of fecal filtrate transplantation (FFT) for fulminant-refractory C. difficile infection in three aplastic adult hematologic patients. FFT was well tolerated, achieved rapid clinical cure, and showed heterogeneous microbiome and phageome modulation, potentially contributing to therapeutic effects.</t>
+          <t>The gut microbiota forms a complex ecosystem through metabolic interdependence (cross-feeding). However, conventional fecal metabolomics typically quantifies only total metabolite pools, making it difficult to distinguish extracellular-enriched metabolite pools from predominantly cell-associated ones, and thus limiting reconstruction of in situ metabolic networks. Here, we quantified fecal metabolites in paired fractions from the same specimen: an undisrupted fraction representing the extracellular pool and a strongly bead-beaten fraction representing the total pool; the intracellular pool was defined as the difference between total and extracellular measurements. Stool samples from 63 healthy individuals were analyzed for short-chain fatty acids, polyamines, and water-soluble vitamins, and the results were integrated with shotgun metagenomic profiles of species composition and functional genes. Vitamins exhibited two distinct behaviors. Adenosylcobalamin (a vitamin B12 coenzyme) was detectable only after disruption, and together with thiamine (B1) and niacin (B3) was classified as an intracellular-retained type (Type 1). In contrast, biotin (B7) and pantothenate (B5) showed higher extracellular proportions (Type 2). Integrative analyses further indicated that Type 1 thiamine was negatively associated with Blautia, consistent with intensive microbial utilization, whereas Type 2 biotin was strongly positively associated with Alistipes, suggesting links to ecological niches shaped by luminal pH and fermentation modes (carbohydrate vs protein fermentation). Fraction-resolved quantification provides a practical operational framework to differentiate extracellular from cell-associated metabolite pools, helping reconcile metagenomic potential with metabolomic reality and enabling deeper inference of cross-feeding structure in the gut ecosystem.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>本研究旨在評估糞便濾液移植（FFT）作為挽救療法，治療化療致免疫不全之血液腫瘤患者合併難治猛爆性艱難梭菌感染（CDI）的療效，並探討供受體間噬菌體的動力學關係。此臨床先導試驗納入3位患者，結果顯示FFT耐受性良好，所有患者在接受治療後14天內均達到臨床緩解。微生態與噬菌體體學分析顯示，臨床症狀的改善並非源於供體噬菌體的直接轉移，而是FFT可能誘發了受體腸道內艱難梭菌的原噬菌體進入溶菌週期，進而促進病原菌清除。本研究證實FFT在此高風險族群中具安全性與可行性，為難治性CDI提供了創新的機制見解與治療選擇。</t>
+          <t>本研究針對腸道微生物的代謝互營機制（cross-feeding）進行探討。傳統糞便代謝組學僅能分析總代謝物，無法區分細胞外與細胞內代謝池，限制了對代謝網絡的解析。研究團隊透過對比未破碎（代表細胞外池）與強力破碎（代表總代謝池）的糞便樣本，成功推算出細胞內代謝物的分佈。針對短鏈脂肪酸、多胺與水溶性維生素的分析顯示，維生素呈現兩類分佈：B12、B1 與 B3 傾向保留於細胞內（Type 1），而 B7 與 B5 則富集於細胞外（Type 2）。結合宏基因組分析發現，Type 1 代謝物與特定細菌（如 *Blautia*）的利用模式顯著相關，Type 2 代謝物則與 *Alistipes* 及腸道生態位特徵（如 pH 值、發酵類型）相關。此方法為區分代謝物空間分佈提供了實用架構，有助於更精確地將宏基因組功能潛力與代謝體現實連結，深入理解腸道微生物的互營生態結構。</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3877,7 +3873,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42635401/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42635406/</t>
         </is>
       </c>
     </row>
@@ -3975,8 +3971,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>本研究旨在探討不同生態壓力如何影響腸道菌相失衡患者體內抗藥性基因（ARGs）與毒力基因的累積。研究團隊利用「鄰近連接總體基因體學」（proximity-ligation metagenomics）技術，分析了復發性困難梭菌感染（rCDI，由抗生素暴露驅動）與肝硬化（由腸道生理改變驅動）兩類患者的細菌宿主與行動基因組（mobilome）關係。
-研究發現，相較於健康對照組，兩組臨床患者的染色體關聯抗藥性基因豐度均顯著增加；然而，僅有rCDI患者額外呈現質體介導的抗藥性基因豐度上升。本研究揭示了不同的生態壓力會選擇性地塑造抗藥性基因在基因體中的定位（染色體或質體），對理解臨床腸道菌相失衡與抗藥性傳播機制具有重要科學意義。</t>
+          <t>本研究旨在利用鄰近連接總體基因體學（proximity-ligation metagenomics）技術，探討不同生態壓力對腸道菌相失衡患者體內抗藥性基因（ARGs）與毒力基因累積的影響。研究分析了因長期抗生素暴露導致菌相失衡的復發性困難梭菌感染（rCDI）患者，以及因生理改變導致失衡的肝硬化患者。結果發現，相較於健康對照組，兩類患者體內由染色體攜帶的抗藥性基因相對豐度皆顯著增加；然而，rCDI患者更額外表現出質體介導之抗藥性基因豐度的上升。此發現揭示了不同病理壓力如何形塑抗藥性基因在細菌基因體中的定位，對理解腸道抗藥性的傳播具有重要科學價值。</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3993,12 +3988,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>42635406</t>
+          <t>42635403</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Separating extracellular from intracellular fecal metabolites exposes cross-feeding architecture in the gut: exploring metabolite partitioning and ecological associations.</t>
+          <t>Baseline gut microbiome ecology predicts long-term fat mass loss after bariatric surgery: evidence for a thrifty Bifidobacterium phenotype.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4011,12 +4006,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>metagenomics, metabolomics</t>
+          <t>16S, metabolomics</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>63 個糞便檢體（來自 63 位健康受試者）</t>
+          <t>85 位重度肥胖患者及 21 位健康對照組（共 106 名受試者）</t>
         </is>
       </c>
       <c r="G68" t="b">
@@ -4024,12 +4019,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>The gut microbiota forms a complex ecosystem through metabolic interdependence (cross-feeding). However, conventional fecal metabolomics typically quantifies only total metabolite pools, making it difficult to distinguish extracellular-enriched metabolite pools from predominantly cell-associated ones, and thus limiting reconstruction of in situ metabolic networks. Here, we quantified fecal metabolites in paired fractions from the same specimen: an undisrupted fraction representing the extracellular pool and a strongly bead-beaten fraction representing the total pool; the intracellular pool was defined as the difference between total and extracellular measurements. Stool samples from 63 healthy individuals were analyzed for short-chain fatty acids, polyamines, and water-soluble vitamins, and the results were integrated with shotgun metagenomic profiles of species composition and functional genes. Vitamins exhibited two distinct behaviors. Adenosylcobalamin (a vitamin B12 coenzyme) was detectable only after disruption, and together with thiamine (B1) and niacin (B3) was classified as an intracellular-retained type (Type 1). In contrast, biotin (B7) and pantothenate (B5) showed higher extracellular proportions (Type 2). Integrative analyses further indicated that Type 1 thiamine was negatively associated with Blautia, consistent with intensive microbial utilization, whereas Type 2 biotin was strongly positively associated with Alistipes, suggesting links to ecological niches shaped by luminal pH and fermentation modes (carbohydrate vs protein fermentation). Fraction-resolved quantification provides a practical operational framework to differentiate extracellular from cell-associated metabolite pools, helping reconcile metagenomic potential with metabolomic reality and enabling deeper inference of cross-feeding structure in the gut ecosystem.</t>
+          <t>Bariatric surgery (BS) induces weight loss, but long-term success involves complex host-microbiome interactions. We evaluated the longitudinal impact of BS, microbiome resilience, and Mediterranean Diet (MedDiet) adherence up to 24 months. This prospective observational study included 85 patients with severe obesity undergoing BS and 21 normal-weight healthy controls (HC). MedDiet adherence (PREDIMED) was assessed before surgery. Fecal microbiota (16S-rRNA sequencing) and metabolomics (1H-NMR spectroscopy) were analyzed at baseline and at 1-, 6-, and 12-months post-BS. Clinical outcomes and fat mass, evaluated by bioimpedanciometry, were tracked up to 24 months. At baseline, patients exhibited higher microbial Shannon diversity than controls (p = 0.041), alongside a dysfunctional microbiome and metabolome characterized by a higher Firmicutes/Bacteroidetes ratio and elevated levels of branched-chain amino acids (p &lt; 0.0001). Ordinary Least Squares (OLS) regression analysis revealed that MedDiet adherence and type 2 diabetes status significantly modulated baseline diversity. At 12 months post-BS, the gut ecosystem underwent profound remodeling, characterized by depletion of Bifidobacterium spp. and an increase in butyrate levels (p &lt; 0.0001), establishing a novel adaptive state distinct from HC. Baseline gut ecology significantly conditioned long-term BS outcomes: patients in the highest quartile of baseline Bifidobacterium spp. lost significantly less fat mass at 24 months than those in the lowest (6.6% vs. 13.2%, p = 0.010). High baseline Bifidobacterium abundance paradoxically acts as a "thrifty microbiome," potentially maximizing energy harvest and limiting surgery-induced fat loss. Overall, BS induces adaptive microbiome restoration rather than true normalization, highlighting the potential for precision interventions prior to surgery.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>本研究針對腸道微生物的代謝互營機制（cross-feeding）進行探討。傳統糞便代謝組學僅能分析總代謝物，無法區分細胞外與細胞內代謝池，限制了對代謝網絡的解析。研究團隊透過對比未破碎（代表細胞外池）與強力破碎（代表總代謝池）的糞便樣本，成功推算出細胞內代謝物的分佈。針對短鏈脂肪酸、多胺與水溶性維生素的分析顯示，維生素呈現兩類分佈：B12、B1 與 B3 傾向保留於細胞內（Type 1），而 B7 與 B5 則富集於細胞外（Type 2）。結合宏基因組分析發現，Type 1 代謝物與特定細菌（如 *Blautia*）的利用模式顯著相關，Type 2 代謝物則與 *Alistipes* 及腸道生態位特徵（如 pH 值、發酵類型）相關。此方法為區分代謝物空間分佈提供了實用架構，有助於更精確地將宏基因組功能潛力與代謝體現實連結，深入理解腸道微生物的互營生態結構。</t>
+          <t>本研究探討減重手術（BS）後腸道微生物群與長期減脂效果的關聯。研究追蹤 85 名患者於術前及術後長達 24 個月的變化，分析發現手術顯著重塑了腸道菌相與代謝環境，特別是雙歧桿菌（*Bifidobacterium*）的耗竭與丁酸鹽的增加。關鍵發現指出，術前高豐度的雙歧桿菌反而成為一種「節儉型表型」，會增加能量攝取效率，導致術後 24 個月的脂肪減少量顯著較少（6.6% 對比 13.2%）。這顯示減重手術並非使微生物組回歸常態，而是引發一種適應性重組。此研究凸顯了術前腸道生態作為預測手術成效生物標記的潛力，對於未來制定精準的術前介入策略具有重要的臨床指導意義。</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4039,7 +4034,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42635406/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42635403/</t>
         </is>
       </c>
     </row>
@@ -4203,21 +4198,21 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>42666411</t>
+          <t>42666371</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Aztreonam-avibactam therapy following surgical source control for bla NDM -positive carbapenem-resistant Klebsiella pneumoniae intra-abdominal infection in an infant: a case report.</t>
+          <t>HPV vaccination associates with Lactobacillus crispatus-dominant vaginal microbiota in women with cervical lesions: a metagenomic study.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Frontiers in pharmacology</t>
+          <t>Frontiers in microbiology</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -4226,7 +4221,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1名2個月大的男嬰 (n=1)</t>
+          <t>59位患有子宮頸病變的停經前女性陰道檢體（其中26位未接種HPV疫苗，33位已接種疫苗）</t>
         </is>
       </c>
       <c r="G72" t="b">
@@ -4234,12 +4229,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Treating carbapenem-resistant Klebsiella pneumoniae (CRKP) is challenging, particularly when resistance is mediated by New Delhi metallo-β-lactamase (NDM). Clinical experience with fixed-combination aztreonam-avibactam (ATM-AVI) in young infants remains extremely limited. Here, we report a case of a 2-month-old boy who underwent emergency laparotomy for intestinal obstruction owing to small bowel volvulus with segmental necrosis, followed by bowel resection and reanastomosis. His postoperative course was complicated by respiratory failure, coagulopathy, septic shock, recurrent abdominal distension, and massive ascites. Blood cultures were negative, whereas metagenomic next-generation sequencing of blood detected K. pneumoniae and Enterococcus faecium. Owing to the worsening of his condition, diagnostic paracentesis and repeat laparotomy were performed, revealing an anastomotic leak. Intraoperative pus culture yielded bla NDM -positive CRKP. The isolate was resistant to carbapenems and ceftazidime-AVI but was susceptible to ATM-AVI, with a minimum inhibitory concentration of ≤4 mg/L. ATM-AVI was administered at 30 mg/kg every 8 h, based on the aztreonam component, for 14 days; linezolid and fluconazole were co-administered as part of the broader anti-infective regimen. The combination of definitive surgical source control, targeted antimicrobial therapy, and comprehensive intensive care successfully controlled the infection and stabilized his hemodynamics. The patient defervesced within 24 h of the first ATM-AVI dose. Inflammatory markers declined rapidly, allowing safe extubation. Follow-up abdominal cultures remained negative. No hepatic or renal toxicity was observed during treatment. This case suggests that, when combined with adequate surgical source control, ATM-AVI may represent a valuable mechanism- and susceptibility-guided pharmacological component in a multidisciplinary treatment paradigm for severe bla NDM -positive CRKP infections in selected infants.</t>
+          <t>Human papillomavirus (HPV) vaccination provides high-level protection against cervical cancer through type-specific antibodies, although breakthrough and persistent high-risk HPV (hrHPV) infections may still occur in some vaccinated women. In addition to neutralizing antibodies, vaccination elicits other immune mechanisms that may influence viral persistence and disease progression. Because mucosal immunity is closely linked to the vaginal microbiota, microbial composition may also play an important role in HPV susceptibility, with Lactobacillus crispatus dominance associated with protection, and dysbiosis with impaired mucosal immunity. Whether HPV vaccination is associated with favorable microbiota signatures in women with confirmed cervical cancer-related conditions remains unknown. We analyzed vaginal samples via shotgun metagenomic sequencing from a cross-sectional study of 59 pre-menopausal women (&lt;50 years) with confirmed cervical lesions (HPV-unvaccinated n = 26, vaccinated n = 33). Alpha diversity (Shannon and Inverse Simpson indices) did not differ significantly by vaccination status, suggesting within-sample microbial diversity between the groups, but Bray-Curtis-based PERMANOVA indicated a statistically significant difference in overall community composition between groups (p = 0.042). Among women with CST I, 90.9% were vaccinated, whereas among women with CST IV, 60.0% were unvaccinated. At the species level, L. crispatus relative abundance was higher in vaccinated women in the unadjusted analysis; however, this association was attenuated and was not statistically significant after multivariable adjustment. HPV vaccination status was associated with a higher prevalence of L. crispatus-dominant, health-associated vaginal microbiota among women with cervical lesions. These findings support the hypothesis that HPV vaccination status is associated with L. crispatus dominance in this population, but mechanistic pathways remain to be elucidated.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>本病例報告描述了一名2個月大男嬰在腸道手術後，因攜帶 $bla_{NDM}$ 基因的耐碳青黴烯肺炎克雷伯菌（CRKP）引發嚴重腹腔感染與敗血性休克。透過血液總體基因體次世代定序（mNGS）與手術膿液培養確立診斷。在進行外科手術源頭控制的基礎上，給予目標性氨曲南-阿維巴坦（ATM-AVI）治療14天。患者在用藥24小時內退燒，發炎指標迅速下降並順利拔管，且未出現肝腎毒性。此案例顯示，結合外科清除與藥敏導向的ATM-AVI聯合療法，對嬰幼兒嚴重 $bla_{NDM}$ 陽性CRKP感染具有臨床安全性與療效，為極低齡患者提供了重要的診療參考。</t>
+          <t>本研究旨在探討HPV疫苗接種是否與子宮頸病變女性的健康陰道菌相（特別是卷曲乳桿菌 *L. crispatus* 優勢）相關。研究利用總體基因體定序分析59位子宮頸病變女性的陰道檢體。結果顯示，已接種與未接種疫苗者的整體菌落結構有顯著差異：在健康型陰道狀態（CST I）中，90.9%為已接種者；而在菌相失衡型（CST IV）中，則有60%為未接種者，且接種疫苗者體內卷曲乳桿菌相對豐度較高。此發現顯示HPV疫苗接種可能與維持健康、乳桿菌為主的陰道微生態相關，為評估疫苗對黏膜免疫與病變預後的影響提供了新視角。</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4249,28 +4244,28 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42666411/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42666371/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>42666298</t>
+          <t>42666411</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Multi-layer gut microbiome variation in type 2 diabetes despite preserved higher-order community structure.</t>
+          <t>Aztreonam-avibactam therapy following surgical source control for bla NDM -positive carbapenem-resistant Klebsiella pneumoniae intra-abdominal infection in an infant: a case report.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Frontiers in microbiology</t>
+          <t>Frontiers in pharmacology</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -4279,7 +4274,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>82 位受試者的糞便檢體（包含 41 位第二型糖尿病患者與 41 位年齡、性別及 BMI 匹配的健康對照者）</t>
+          <t>1名2個月大的男嬰 (n=1)</t>
         </is>
       </c>
       <c r="G73" t="b">
@@ -4287,12 +4282,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Type 2 diabetes (T2D) has been consistently associated with alterations in the gut microbiome, although disease, treatment, diet, and other host factors may contribute to the observed patterns. How these associations are organized across different biological levels of the microbial ecosystem remains incompletely understood. We performed shotgun metagenomic sequencing of fecal samples from 82 individuals, including 41 patients with T2D and 41 age-, sex-, and body mass index-matched healthy controls. Taxonomic profiling, functional pathway analysis, enterotype characterization, ecological network inference, and interpretable machine-learning approaches were integrated to characterize microbiome variation across multiple organizational levels. Despite clear clinical differences between groups, particularly fasting blood glucose, the overall ecological architecture of the gut microbiome remained broadly preserved. Dominant phylum-level composition and enterotype structure were maintained, whereas variation became apparent at finer biological scales. Species-level analyses identified 42 differentially abundant taxa. Community diversity analysis showed reduced Chao1 richness (P = 0.024), increased Simpson diversity (P = 0.024), unchanged Shannon diversity (P = 0.126), and a modest shift in community composition (PERMANOVA, R 2 = 0.040, P = 0.006). Functional profiling showed no pathway-level significance after multiple-testing correction but directional trends across several metabolic modules. Exploratory Spearman-based networks differed in topology between groups; because relative-abundance data are compositional, these differences cannot be interpreted as direct ecological interactions or definitive network rewiring. Machine-learning models achieved a within-cohort cross-validated AUC of up to 0.91, but lacked independent external validation. These findings provide a multi-layer description of T2D-associated gut microbiome variation within this cohort. The data are consistent with preserved higher-order community organization accompanied by finer-scale differences in species composition, functional potential, community-state occupancy, statistical co-occurrence, and within-cohort discriminative features. Medication confounding, compositional effects, technical artifacts, and the absence of external validation limit causal, ecological, and diagnostic interpretation. Larger longitudinal, multi-site, medication-resolved, and independently validated studies are required.</t>
+          <t>Treating carbapenem-resistant Klebsiella pneumoniae (CRKP) is challenging, particularly when resistance is mediated by New Delhi metallo-β-lactamase (NDM). Clinical experience with fixed-combination aztreonam-avibactam (ATM-AVI) in young infants remains extremely limited. Here, we report a case of a 2-month-old boy who underwent emergency laparotomy for intestinal obstruction owing to small bowel volvulus with segmental necrosis, followed by bowel resection and reanastomosis. His postoperative course was complicated by respiratory failure, coagulopathy, septic shock, recurrent abdominal distension, and massive ascites. Blood cultures were negative, whereas metagenomic next-generation sequencing of blood detected K. pneumoniae and Enterococcus faecium. Owing to the worsening of his condition, diagnostic paracentesis and repeat laparotomy were performed, revealing an anastomotic leak. Intraoperative pus culture yielded bla NDM -positive CRKP. The isolate was resistant to carbapenems and ceftazidime-AVI but was susceptible to ATM-AVI, with a minimum inhibitory concentration of ≤4 mg/L. ATM-AVI was administered at 30 mg/kg every 8 h, based on the aztreonam component, for 14 days; linezolid and fluconazole were co-administered as part of the broader anti-infective regimen. The combination of definitive surgical source control, targeted antimicrobial therapy, and comprehensive intensive care successfully controlled the infection and stabilized his hemodynamics. The patient defervesced within 24 h of the first ATM-AVI dose. Inflammatory markers declined rapidly, allowing safe extubation. Follow-up abdominal cultures remained negative. No hepatic or renal toxicity was observed during treatment. This case suggests that, when combined with adequate surgical source control, ATM-AVI may represent a valuable mechanism- and susceptibility-guided pharmacological component in a multidisciplinary treatment paradigm for severe bla NDM -positive CRKP infections in selected infants.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>本研究旨在探討第二型糖尿病（T2D）患者腸道菌相在不同生物層級的變異。透過對82名受試者進行糞便總體基因體定序，發現儘管兩組臨床指標差異顯著，腸道菌群的宏觀生態結構（如門級組成與腸型）仍大致維持。然而，在細微層級則展現顯著變異，包括鑑定出42種豐度差異物種，且T2D組的Chao1豐富度顯著降低。機器學習模型在組內預測T2D的AUC達0.91。此研究揭示了T2D中腸道菌相「宏觀穩定、微觀失衡」的多層次特徵，但亦指出藥物混雜與缺乏外部驗證等限制，未來仍需更大規模的縱向研究。</t>
+          <t>本病例報告描述了一名2個月大男嬰在腸道手術後，因攜帶 $bla_{NDM}$ 基因的耐碳青黴烯肺炎克雷伯菌（CRKP）引發嚴重腹腔感染與敗血性休克。透過血液總體基因體次世代定序（mNGS）與手術膿液培養確立診斷。在進行外科手術源頭控制的基礎上，給予目標性氨曲南-阿維巴坦（ATM-AVI）治療14天。患者在用藥24小時內退燒，發炎指標迅速下降並順利拔管，且未出現肝腎毒性。此案例顯示，結合外科清除與藥敏導向的ATM-AVI聯合療法，對嬰幼兒嚴重 $bla_{NDM}$ 陽性CRKP感染具有臨床安全性與療效，為極低齡患者提供了重要的診療參考。</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4302,19 +4297,19 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42666298/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42666411/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>42666306</t>
+          <t>42666298</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ecological assembly of mucosal and fecal microbiomes in ulcerative colitis across genes, functions, and species.</t>
+          <t>Multi-layer gut microbiome variation in type 2 diabetes despite preserved higher-order community structure.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4332,7 +4327,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>82 位受試者的糞便檢體（包含 41 位第二型糖尿病患者與 41 位年齡、性別及 BMI 匹配的健康對照者）</t>
         </is>
       </c>
       <c r="G74" t="b">
@@ -4340,12 +4335,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Inflammatory bowel disease (IBD) is associated with gut microbial dysbiosis, yet the ecological processes underlying community assembly remain unclear. Here, we applied Sloan's neutral community model to examine the relative contributions of stochastic and deterministic processes across multiple ecological layers, including metagenomic genes (MGs), molecular functions (MFs), and microbial species (archaea, bacteria, fungi, and viruses), in fecal and mucosal microbiota from healthy controls and ulcerative colitis (UC) patients. Across all layers, most MGs, MFs, and species conformed to neutral expectations, indicating a dominant role of stochastic processes in community assembly. However, UC was consistently associated with an increased proportion of neutral MFs and species, accompanied by a reduction in non-neutral components, suggesting weakened selective constraints under disease conditions. Ecological niche further modulated these patterns. Fecal communities harbored significantly higher proportions of non-neutral MFs and species compared to mucosal communities, indicating stronger deterministic processes in feces. Analysis of selection-state transitions revealed extensive changes in selection status in UC, particularly in mucosal environments, where both functional and taxonomic profiles showed marked transition. These changes were primarily driven by the gain and loss of selection rather than directional switching, indicating that UC alters the strength and presence of selection rather than reversing its direction. Together, these findings provide a multi-layered ecological framework for understanding UC-associated dysbiosis, highlighting increased neutrality and selection rewiring as key features of microbial community assembly under disease conditions.</t>
+          <t>Type 2 diabetes (T2D) has been consistently associated with alterations in the gut microbiome, although disease, treatment, diet, and other host factors may contribute to the observed patterns. How these associations are organized across different biological levels of the microbial ecosystem remains incompletely understood. We performed shotgun metagenomic sequencing of fecal samples from 82 individuals, including 41 patients with T2D and 41 age-, sex-, and body mass index-matched healthy controls. Taxonomic profiling, functional pathway analysis, enterotype characterization, ecological network inference, and interpretable machine-learning approaches were integrated to characterize microbiome variation across multiple organizational levels. Despite clear clinical differences between groups, particularly fasting blood glucose, the overall ecological architecture of the gut microbiome remained broadly preserved. Dominant phylum-level composition and enterotype structure were maintained, whereas variation became apparent at finer biological scales. Species-level analyses identified 42 differentially abundant taxa. Community diversity analysis showed reduced Chao1 richness (P = 0.024), increased Simpson diversity (P = 0.024), unchanged Shannon diversity (P = 0.126), and a modest shift in community composition (PERMANOVA, R 2 = 0.040, P = 0.006). Functional profiling showed no pathway-level significance after multiple-testing correction but directional trends across several metabolic modules. Exploratory Spearman-based networks differed in topology between groups; because relative-abundance data are compositional, these differences cannot be interpreted as direct ecological interactions or definitive network rewiring. Machine-learning models achieved a within-cohort cross-validated AUC of up to 0.91, but lacked independent external validation. These findings provide a multi-layer description of T2D-associated gut microbiome variation within this cohort. The data are consistent with preserved higher-order community organization accompanied by finer-scale differences in species composition, functional potential, community-state occupancy, statistical co-occurrence, and within-cohort discriminative features. Medication confounding, compositional effects, technical artifacts, and the absence of external validation limit causal, ecological, and diagnostic interpretation. Larger longitudinal, multi-site, medication-resolved, and independently validated studies are required.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>本研究旨在探討潰瘍性結腸炎（UC）患者與健康對照組在糞便及黏膜微生物群中，基因、功能和物種層面的生態組裝機制。研究發現，隨機性過程在群落組裝中占主導地位，但UC患者表現出更高比例的中性特徵，顯示疾病狀態下選擇壓力減弱。此外，糞便群落比黏膜群落受到更強的確定性選擇。UC主要藉由改變選擇壓力的強度與存在（而非改變其方向）來重塑微生物群，且此現象在黏膜中尤為顯著。本研究為理解UC相關的菌群失調提供了多維生態框架，指出中性增加與選擇重組為其核心特徵。</t>
+          <t>本研究旨在探討第二型糖尿病（T2D）患者腸道菌相在不同生物層級的變異。透過對82名受試者進行糞便總體基因體定序，發現儘管兩組臨床指標差異顯著，腸道菌群的宏觀生態結構（如門級組成與腸型）仍大致維持。然而，在細微層級則展現顯著變異，包括鑑定出42種豐度差異物種，且T2D組的Chao1豐富度顯著降低。機器學習模型在組內預測T2D的AUC達0.91。此研究揭示了T2D中腸道菌相「宏觀穩定、微觀失衡」的多層次特徵，但亦指出藥物混雜與缺乏外部驗證等限制，未來仍需更大規模的縱向研究。</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4355,19 +4350,19 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42666306/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42666298/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>42666371</t>
+          <t>42666306</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>HPV vaccination associates with Lactobacillus crispatus-dominant vaginal microbiota in women with cervical lesions: a metagenomic study.</t>
+          <t>Ecological assembly of mucosal and fecal microbiomes in ulcerative colitis across genes, functions, and species.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4385,7 +4380,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>59位患有子宮頸病變的停經前女性陰道檢體（其中26位未接種HPV疫苗，33位已接種疫苗）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G75" t="b">
@@ -4393,12 +4388,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Human papillomavirus (HPV) vaccination provides high-level protection against cervical cancer through type-specific antibodies, although breakthrough and persistent high-risk HPV (hrHPV) infections may still occur in some vaccinated women. In addition to neutralizing antibodies, vaccination elicits other immune mechanisms that may influence viral persistence and disease progression. Because mucosal immunity is closely linked to the vaginal microbiota, microbial composition may also play an important role in HPV susceptibility, with Lactobacillus crispatus dominance associated with protection, and dysbiosis with impaired mucosal immunity. Whether HPV vaccination is associated with favorable microbiota signatures in women with confirmed cervical cancer-related conditions remains unknown. We analyzed vaginal samples via shotgun metagenomic sequencing from a cross-sectional study of 59 pre-menopausal women (&lt;50 years) with confirmed cervical lesions (HPV-unvaccinated n = 26, vaccinated n = 33). Alpha diversity (Shannon and Inverse Simpson indices) did not differ significantly by vaccination status, suggesting within-sample microbial diversity between the groups, but Bray-Curtis-based PERMANOVA indicated a statistically significant difference in overall community composition between groups (p = 0.042). Among women with CST I, 90.9% were vaccinated, whereas among women with CST IV, 60.0% were unvaccinated. At the species level, L. crispatus relative abundance was higher in vaccinated women in the unadjusted analysis; however, this association was attenuated and was not statistically significant after multivariable adjustment. HPV vaccination status was associated with a higher prevalence of L. crispatus-dominant, health-associated vaginal microbiota among women with cervical lesions. These findings support the hypothesis that HPV vaccination status is associated with L. crispatus dominance in this population, but mechanistic pathways remain to be elucidated.</t>
+          <t>Inflammatory bowel disease (IBD) is associated with gut microbial dysbiosis, yet the ecological processes underlying community assembly remain unclear. Here, we applied Sloan's neutral community model to examine the relative contributions of stochastic and deterministic processes across multiple ecological layers, including metagenomic genes (MGs), molecular functions (MFs), and microbial species (archaea, bacteria, fungi, and viruses), in fecal and mucosal microbiota from healthy controls and ulcerative colitis (UC) patients. Across all layers, most MGs, MFs, and species conformed to neutral expectations, indicating a dominant role of stochastic processes in community assembly. However, UC was consistently associated with an increased proportion of neutral MFs and species, accompanied by a reduction in non-neutral components, suggesting weakened selective constraints under disease conditions. Ecological niche further modulated these patterns. Fecal communities harbored significantly higher proportions of non-neutral MFs and species compared to mucosal communities, indicating stronger deterministic processes in feces. Analysis of selection-state transitions revealed extensive changes in selection status in UC, particularly in mucosal environments, where both functional and taxonomic profiles showed marked transition. These changes were primarily driven by the gain and loss of selection rather than directional switching, indicating that UC alters the strength and presence of selection rather than reversing its direction. Together, these findings provide a multi-layered ecological framework for understanding UC-associated dysbiosis, highlighting increased neutrality and selection rewiring as key features of microbial community assembly under disease conditions.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>本研究旨在探討HPV疫苗接種是否與子宮頸病變女性的健康陰道菌相（特別是卷曲乳桿菌 *L. crispatus* 優勢）相關。研究利用總體基因體定序分析59位子宮頸病變女性的陰道檢體。結果顯示，已接種與未接種疫苗者的整體菌落結構有顯著差異：在健康型陰道狀態（CST I）中，90.9%為已接種者；而在菌相失衡型（CST IV）中，則有60%為未接種者，且接種疫苗者體內卷曲乳桿菌相對豐度較高。此發現顯示HPV疫苗接種可能與維持健康、乳桿菌為主的陰道微生態相關，為評估疫苗對黏膜免疫與病變預後的影響提供了新視角。</t>
+          <t>本研究旨在探討潰瘍性結腸炎（UC）患者與健康對照組在糞便及黏膜微生物群中，基因、功能和物種層面的生態組裝機制。研究發現，隨機性過程在群落組裝中占主導地位，但UC患者表現出更高比例的中性特徵，顯示疾病狀態下選擇壓力減弱。此外，糞便群落比黏膜群落受到更強的確定性選擇。UC主要藉由改變選擇壓力的強度與存在（而非改變其方向）來重塑微生物群，且此現象在黏膜中尤為顯著。本研究為理解UC相關的菌群失調提供了多維生態框架，指出中性增加與選擇重組為其核心特徵。</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4408,7 +4403,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42666371/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42666306/</t>
         </is>
       </c>
     </row>
@@ -4967,7 +4962,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>本綜述全面探討了由瘧原蟲屬（*Plasmodium*）引起並經蚊子傳播的禽瘧疾。文章系統性地整合了該疾病的生物學、流行病學、致病機制、臨床特徵（如貧血與高致死率）及經濟影響。在診斷方面，涵蓋了傳統塗片到分子工具（如PCR、NGS與總體基因體學）；在防治上，討論了有限的藥物治療與多維度的控制策略（如棲地改良、引進沃爾巴克氏體內共生菌及抗病育種）。此回顧旨在為脆弱鳥類族群的保育與管理策略提供重要科學依據，以減緩禽瘧疾對生態與經濟造成的衝擊。</t>
+          <t>本研究是一篇針對禽類瘧疾（avian malaria）的全面性文獻綜述。核心目的在於系統性整合該疾病在生物學、流行病學、致病機制、臨床特徵、經濟影響、診斷、治療及控制策略方面的現有知識。文章指出，禽類瘧疾由瘧原蟲（Plasmodium）引起並經由蚊子傳播，對全球多種鳥類構成嚴重威脅，特別是幼鳥與免疫力低下個體。診斷上結合了傳統血塗片與現代分子技術（如PCR、次世代定序、總體基因體學與轉錄體學等）；治療則依賴特定抗瘧藥與支持性照護。本綜述的科學意義在於為易感鳥類族群的保育、疾病預防與管理策略提供了關鍵的學術依據與指引。</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">

--- a/papers_database.xlsx
+++ b/papers_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K86"/>
+  <dimension ref="A1:K104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>42671210</t>
+          <t>42677827</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sulfur metabolism and immune-microbial networks across oral niches in periodontal disease.</t>
+          <t>Bacteroides cellulosilyticus-derived 2-hydroxyphenylacetic acid rectifies hepatic lipid homeostasis in MASLD by targeting the PPARγ-CD36 axis.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Microbiology spectrum</t>
+          <t>Gut microbes</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16S</t>
+          <t>metagenomics, metabolomics, others</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -509,54 +509,54 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Volatile sulfur compounds (VSCs) integrate microbial metabolism with local inflammation in periodontal disease. We profiled five oral niches (saliva, tongue, subgingival, supragingival, and interdental plaque) across clinical health, gingivitis, and periodontitis by combining direct VSC measurements (subgingival and oral headspace H2S/CH3SH), functional cysteine/methionine degradation assays, 16S rRNA profiling, gingival crevicular fluid cytokines, and targeted qPCR. Subgingival H2S concentrations were significantly elevated in periodontitis after adjusting for age, sex, plaque index, and subgingival bacterial load (β = 1.24, P = 0.03), and tracked shifts in community composition and the cytokine milieu. Oral headspace CH3SH increased with disease, whereas headspace H2S showed a bimodal pattern (health and periodontitis). In cysteine assays, subgingival and tongue biofilms were the most efficient H2S producers per mg protein; this ranking was preserved after normalization to total bacteria by qPCR. Metagenome predictions indicated enhanced sulfur metabolism in disease, particularly in subgingival plaque, with relative enrichment of SAM-cycle/methionine biosynthesis pathways in health. Methionine degradation to CH3SH increased with disease severity, shifting from subgingival sites in health to interdental/supragingival plaque in disease, and occurring most frequently in saliva. Correlation networks revealed niche- and diagnosis-specific coupling among VSCs, cytokines, and taxa, including associations of Capnocytophaga, Fusobacterium, Prevotella, and Corynebacterium, with IL-1β, IL-4, IL-8, and MCP-1. Together, these data identify the subgingival crevice as a disproportionate source of sulfide and show that sulfur metabolism is spatially organized and disease-responsive. We show that subgingival H2S as a functional marker that integrates microbial dysbiosis and inflammation.IMPORTANCEWe asked how metabolism, microbes, and immunity fit together during gum disease. Using a systems approach across five oral sites, we combined sulfur metabolite measurements, functional assays, microbiome profiling, and cytokine data, and analyzed them as one network. The result is a comprehensive map showing that sulfur metabolism is spatially organized, disease-responsive, and tightly coupled to local immune signals, with the subgingival niche playing an outsized role. Further, this integrated readout turns sulfur metabolism into a useful window on dysbiosis and inflammation and offers a path toward simple monitoring of periodontal disease, such as point-of-care sensors detecting subgingival hydrogen sulfide or methanethiol, or functional assays in which a methionine rinse is followed by measurement of oral headspace gases to assess microbial sulfur metabolism.</t>
+          <t>The gut microbiota plays an important role in the occurrence and development of metabolic dysfunction-associated steatotic liver disease (MASLD), but the specific molecular mechanisms involved have not been fully elucidated. In this study, human cohort studies were performed to identify that the relative abundance of Bacteroides cellulosilyticus (B. cellulosilyticus) was significantly decreased in patients with MASLD. Through the integration of metagenomic and metabolomic analyses, it was confirmed that B. cellulosilyticus and its metabolite 2-hydroxyphenylacetic acid (2HPAA) are key factors regulating the occurrence and development of MASLD. Single-cell sequencing and lipidomic analyses revealed that 2HPAA can enter the liver through the enterohepatic circulation to exert regulatory effects. Specifically, 2HPAA inhibits the peroxisome proliferator-activated receptor γ (PPARγ) signaling pathway, thereby suppressing the expression of the fatty acid transporter CD36. Meanwhile, 2HPAA regulates lipid metabolism in hepatocytes by significantly enhancing palmitate conversion efficiency and inhibiting CD36 palmitoylation. This dual regulatory effect on CD36 expression and palmitoylation can reduce lipid accumulation in hepatocytes and ultimately alleviate MASLD progression. These findings reveal the mechanism by which B. cellulosilyticus and 2HPAA alleviate MASLD by targeting the PPARγ-CD36 pathway. This work provides a new perspective for the study of gut microbiota-host interactions in regulating liver diseases.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>本研究旨在探討牙周病不同階段中，五個口腔微生態棲地（唾液、舌苔、齦下、齦上及牙縫菌斑）的硫代謝、微生物群與局部免疫反應之關聯。研究發現，齦下硫化氫（H2S）濃度在牙周病患者中顯著升高，且與菌群結構移形及細胞激素變化密切相關，其中齦下與舌苔生物膜具有最強的H2S產生效率。網路分析更揭示了揮發性硫化物（VSCs）、細胞激素與特定菌屬（如 *Fusobacterium* 與 *Prevotella*）之間存在棲地特異性的耦合關係。本研究證實齦下H2S可作為整合微生態失調與發炎反應的功能性指標，為未來開發非侵入性牙周病即時監測工具（如氣體感測器）奠定了重要科學基礎。</t>
+          <t>本研究旨在探討腸道菌群調控代謝功能障礙相關脂肪性肝病（MASLD）的具體分子機制。研究發現，MASLD患者體內的纖維素分解擬桿菌（*Bacteroides cellulosilyticus*）豐度顯著降低。透過整合總體基因體學與代謝組學分析，證實該菌及其代謝產物 2-羥基苯乙酸（2HPAA）是緩解 MASLD 的關鍵因子。機制上，2HPAA 經腸肝循環進入肝臟，藉由抑制 PPARγ 信號通路來下調脂肪酸轉運蛋白 CD36 的表達，並提升棕櫚酸轉換效率與抑制 CD36 棕櫚醯化，從而減少肝細胞脂質累積。本研究揭示了腸道菌-宿主交互作用的新機制，為 MASLD 的治療提供了新視角與潛在靶點。</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42671210/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42677827/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>42673455</t>
+          <t>42679877</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kelp forest collapse alters the reef microbiome and associated metabolome.</t>
+          <t>Bioaugmentation enabled simultaneous biodegradation of sulfadiazine and nitrification.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Proceedings of the National Academy of Sciences of the United States of America</t>
+          <t>Environmental research</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>metagenomics, metabolomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（原文僅提及實驗室規模之模擬試驗，未明確說明採樣個體或樣本數目）</t>
         </is>
       </c>
       <c r="G3" t="b">
@@ -564,54 +564,54 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>In many temperate regions experiencing rapid ocean warming, kelp forests are being replaced by low-lying turf algae. Yet, whether this change in biogenic habitat alters reef-level microbial structure and function, including carbon and nutrient cycling, remains largely unknown. Here, we integrated shotgun metagenomics and nontargeted metabolomics to reveal that kelp forest loss alters the composition of the reef microbial community and its associated biochemical machinery, resulting in distinct metabolomes and microbially driven elemental use/transformations on kelp- vs. turf-dominated reefs. Our results therefore suggest that microbes play a key role in shaping kelp forest ecosystem functioning. Further, they demonstrate that human-induced ocean warming has cascading effects on microbially mediated chemistry, with implications for coastal carbon storage and nutrient regeneration.</t>
+          <t>Antibiotics are detected in surface waters in part because classical wastewater-treatment processes are ineffective for biodegrading them. Furthermore, the presence of antibiotics can inhibit the performance of biological treatment, particularly for nitrification, but an effective strategy for simultaneous antibiotics and nitrogen removals was not reported so far. This work targeted biodegradation of the common sulfanilamide antibiotic sulfadiazine (SDZ) and its inhibition of nitrification. The experimental results showed that nitrification rate decreased to 3.4 mg/(L·h) and 1.9 mg/(L·h) (from 19 mg/(L·h)) when normal nitrifying biomass (NNB) was exposed to SDZ at 10 mg/L and 20 mg/L due to inhibition by SDZ. Bioaugmentation of NNB with a SDZ-acclimated biomass (SDAB) enabled biodegradation of SDZ, which relieved its inhibition of nitrification. In the presence of 20 mg/L of SDZ, the NH4+-N removal rate reached at 7.8 mg/(L·h), which was more than 4-fold faster with SDAB bioaugmentation. Metagenomic analysis supported that NNB was responsible for nitrification, while bioaugmented SDAB was responsible for SDZ biodegradation that allowed simultaneous removal of NH4+-N and SDZ. For example, metagenomic analysis further showed that SDAB contained 4 genes for monooxygenations critical to initiating SDZ biodegradation, but NNB was enriched in genes for oxidations of NH4+ and NO2-.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>本研究旨在探討氣候暖化導致海帶林被低矮草皮狀藻類取代後，是否會改變礁區微生物的結構、功能（如碳與養分循環）。研究團隊結合總體基因體學與非標靶代謝組學技術，證實海帶林的流失會顯著改變礁區微生物群落組成及其生化機制，進而在海帶與草皮狀藻類主導的礁區中，產生截然不同的代謝組及微生物驅動之元素利用與轉化模式。此結果表明微生物在形塑海帶林生態系功能中扮演關鍵角色，並證實人類活動引起的海洋變暖會對微生物介導的化學作用產生級聯效應，進而對沿岸碳儲存與養分再生帶來深遠影響。</t>
+          <t>本研究旨在解決廢水處理過程中磺胺類抗生素（如磺胺嘧啶，SDZ）對硝化作用的抑制問題。研究顯示，SDZ 會顯著降低硝化菌的活性，導致氮去除效率大幅下降。研究團隊透過引入經馴化的 SDZ 降解菌群（SDAB）進行生物強化（Bioaugmentation），成功在處理系統中實現了 SDZ 的生物降解，進而緩解其對硝化作用的抑制。宏基因體分析證實，加入的 SDAB 含有啟動 SDZ 降解的關鍵單加氧酶基因，而原始硝化菌群（NNB）則保留了主要的氨氧化功能，兩者協作實現了廢水中氨氮與抗生素的同步去除。此成果為改善廢水處理技術、減緩環境抗生素汙染提供了具實務潛力的生物策略。</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42673455/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42679877/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>42673474</t>
+          <t>42675508</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Evidence for endemism and local adaptation in Antarctic soil bacteria.</t>
+          <t>Rumen DNA virome plasticity and viral metabolic potential are associated with seasonal adaptation in grazing yak and cattle on the Qinghai-Tibet Plateau.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Proceedings of the National Academy of Sciences of the United States of America</t>
+          <t>Journal of animal science and biotechnology</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>metagenomics, small genome</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>未提及（文章僅提到使用全球性數據集與分離菌株進行分析，未具體標示樣本總數）</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -619,49 +619,49 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Antarctic soils represent one of the most extreme environments for microbial life on Earth, yet they harbor heterogeneous and diverse microbial communities. Biologists have long hypothesized that Antarctic microorganisms are unique from those found on other continents due to the extreme geographic isolation and the cold, dry, and challenging conditions typical of Antarctica. To test this hypothesis, we focused on a cosmopolitan bacterial genus, Arthrobacter, that is widely distributed across global soils. We first profiled a global metagenomic dataset from both Antarctic and non-Antarctic surface soils to quantify the distributions of Arthrobacter strains. Despite high strain-level diversity, 90% of the strains found in the Antarctic soils were only found on the continent. We then used cultivation-based phenotypic analyses and strain-level genomic comparisons to assess how Antarctic strains and non-Antarctic strains differ in their traits and environmental preferences. Not only did we find evidence of endemism, but Antarctic Arthrobacter also have genomic characteristics and environmental tolerances that suggest they are uniquely adapted to Antarctic conditions.</t>
+          <t>As a diverse and abundant component of the rumen ecosystem, viruses interact with other microorganisms and are thought to influence microbial metabolism and host productivity. However, how the rumen virome responds to seasonal fluctuations in extreme environments remains poorly understood. Here, metagenomic analyses were used to investigate temporal dynamics of viral diversity, functional potential, and virus-host associations in the rumen virome of yak and cattle on the Qinghai-Tibet Plateau across warm and cold seasons. Rumen viral communities exhibited pronounced seasonal variation in both yaks and cattle, with higher alpha diversity observed during the cold season than in the warm season. Across seasons, the yak rumen virome showed greater alpha diversity and community stability than that of cattle. In total, 27,353 temperate and 31,976 virulent viral operational taxonomic units (vOTUs) were identified, predominantly belonging to the class Caudoviricetes. These viruses were linked to microbial hosts spanning 24 bacterial and 8 archaeal phyla, with Bacteroidota and Bacillota representing the dominant lineages. Virus-host associations were more numerous in the cold season and showed distinct host-specific patterns between yaks and cattle. Cold-season virome exhibited reduced diversity of anti-defense genes and enrichment of auxiliary metabolic genes (AMGs) associated with fatty acid metabolism and hemicellulose degradation. Notably, greater divergence between yaks and cattle was observed during the cold season: the yak rumen virome was enriched in pathways related to amino acid, lipid, and energy metabolism, as well as cellulose-degrading CAZyme families, whereas the cattle rumen virome showed enrichment in general carbohydrate metabolism and replication and repair processes. Seasonal plasticity of rumen DNA virome and pronounced interspecific divergence between yaks and cattle provide insight into their distinct microbial processes in the harsh environment of the Qinghai-Tibet Plateau. These findings suggest that the rumen DNA virome exhibits complex ecological and functional responses to seasonal variation and may be associated with host-microbiome interactions and nutrient utilization under environmental stress. This study highlights the ecological relevance of rumen viral genomes in understanding virus-microbiome interactions, microbial adaptation, and nutrient utilization in high-altitude ruminants.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>本研究旨在探討南極土壤微生物是否因地理隔離與極端氣候而演化出獨特的在地適應性。研究聚焦於全球分佈廣泛的「節桿菌屬」（*Arthrobacter*），透過分析全球土壤宏基因組數據，發現南極土壤中 90% 的節桿菌菌株皆為南極特有種，證實了該地區微生物的高度地方性（endemism）。進一步透過菌株培養表型分析與基因體比較，研究發現南極菌株具備特定的基因組特徵與環境耐受力，使其能適應南極寒冷且乾燥的極端環境。此發現不僅揭示了微生物在地理隔離下的演化模式，更證實了南極微生物群落具有獨特的在地適應機制，對於理解微生物的全球擴散限制與極地生態系統的演化歷程具有重要科學意義。</t>
+          <t>本研究旨在探討青藏高原犛牛與黃牛瘤胃病毒體（DNA virome）在不同季節下的動態變化。研究利用總體基因體學分析發現，瘤胃病毒群落具有顯著的季節性差異，且冷季時的病毒多樣性高於暖季；其中犛牛的病毒體表現出比黃牛更高的穩定性與多樣性。病毒主要隸屬於尾噬菌體綱（Caudoviricetes），並與多種細菌及古菌宿主存在交互作用。在冷季環境下，病毒體透過富集與脂肪酸代謝及半纖維素降解相關的輔助代謝基因（AMGs）來適應壓力。此外，犛牛與黃牛在冷季的病毒功能呈現高度分歧：犛牛病毒體更傾向於能量代謝與纖維素降解，而黃牛則偏向基礎碳水化合物代謝。本研究揭示了瘤胃病毒體在調控宿主微生物群適應極端環境中的關鍵作用，並突顯了犛牛與黃牛在營養利用機制上的生物學差異，為高海拔反芻動物的環境適應策略提供了重要科學依據。</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42673474/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42675508/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>42674953</t>
+          <t>42677482</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Retraction notice to "Environmental impact of lignocellulosic wastes and their effective exploitation as smart carriers - A drive towards greener and eco-friendlier biocatalytic systems" [Sci. Total Environ. 722 (2020) 137903].</t>
+          <t>Nano-boron nitride enhances soybean growth and symbiotic nitrogen fixation by modulating the rhizosphere microbiome and biogeochemical cycling.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The Science of the total environment</t>
+          <t>Nanoscale</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -674,54 +674,54 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>無提供摘要。</t>
+          <t>Nanotechnology offers promising strategies for sustainable agriculture, yet the systemic mechanisms by which nanomaterials enhance legume nitrogen fixation remain insufficiently understood. The multi-scale impacts of nano-boron nitride (nano-BN) on soybean growth, biological nitrogen fixation, and rhizosphere microbial communities were investigated. Soil addition of 50 mg kg-1 nano-BN significantly promoted plant biomass, nodule biomass, and leghemoglobin content by 10.0%, 27.4%, and 39.4%, respectively, compared to the untreated control. Nano-BN also enhanced the NH4+-N and NO3--N content by 24.3% and 19.9% in root tissues, while reducing these levels in rhizosphere soil. Additionally, nano-BN enriched rhizosphere-dissolved organic matter, particularly humic-like components. Metagenomic analysis revealed that nano-BN reshaped carbon and nitrogen cycling functional genes, enhancing CO2 fixation and aerobic respiration; the nitrogen fixation functional gene nifH was upregulated by 27.7%. Microbial community analysis demonstrated increased bacterial diversity and abundance of beneficial taxa, particularly Bradyrhizobium, which increased by 24.9%. Co-occurrence network analysis revealed enhanced positive interactions and greater topological complexity upon the addition of nano-BN compared to the untreated control, indicating improved community stability. Collectively, these findings demonstrate that nano-BN promotes soybean growth through integrated regulation of nutrient cycling, symbiotic nitrogen fixation, and rhizosphere microbiome assembly. Nano-BN represents an innovative nano-fertilization strategy for enhancing biological nitrogen fixation, improving nutrient use efficiency, and advancing sustainable agricultural systems.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>本文為學術期刊《Science of the Total Environment》針對 2020 年刊登之文章「Environmental impact of lignocellulosic wastes and their effective exploitation as smart carriers - A drive towards greener and eco-friendlier biocatalytic systems」所發布的正式撤稿聲明。由於原始研究內容已被撤回，該聲明並未包含任何實驗數據、樣本分析或科學發現。撤稿通常源於作者發現數據錯誤、倫理問題或研究結論存在不可重現的重大瑕疵，因此該文不具備生物醫學參考價值。</t>
+          <t>本研究探討奈米氮化硼（nano-BN）對大豆生長及共生固氮作用的影響。實驗顯示，在土壤中添加 50 mg kg⁻¹ 的 nano-BN 能顯著增加大豆植株與根瘤生物量，並提升根部血紅素含量。宏基因體分析發現，nano-BN 重塑了根際微生物群落，不僅提升了細菌多樣性，更顯著增加了關鍵固氮菌「慢生根瘤菌」（*Bradyrhizobium*）的豐度，並上調了固氮關鍵基因 *nifH* 的表現。此外，nano-BN 優化了根際養分循環與溶解性有機物質結構，增強了微生物間的正向交互作用與群落穩定性。這項研究揭示了奈米肥料透過調控微生物組與生物地球化學循環來促進作物生長的機制，為推動農業永續發展提供了創新的奈米技術策略。</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42674953/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42677482/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>42674950</t>
+          <t>42677877</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Retraction notice to "A systematic review of antibiotics and antibiotic resistance genes (ARGs) in mariculture wastewater: Antibiotics removal by microalgal-bacterial symbiotic system (MBSS), ARGs characterization on the metagenomic" [Sci. Total Environ. 930 (2024) 172601].</t>
+          <t>Comprehensive Viral Detection and Profiling of Plasma Cell-Free RNA in Patients With Suspected Hemophagocytic Lymphohistiocytosis.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>The Science of the total environment</t>
+          <t>Journal of medical virology</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>metagenomics, others</t>
+          <t>metagenomics, metatranscriptomics</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>19 位小兒科受試者（17 位疑似 HLH 患者及 2 位確診對照組）</t>
         </is>
       </c>
       <c r="G6" t="b">
@@ -729,54 +729,54 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>無提供摘要。</t>
+          <t>Hemophagocytic lymphohistiocytosis (HLH) is a severe, rapidly progressive disease. While viral infection is considered a common etiology of pediatric HLH, specific causative viruses other than the Epstein-Barr virus (EBV) have been rarely identified. This study utilized metagenomic next-generation sequencing (NGS) to identify potential causative pathogens in plasma samples from 17 pediatric patients with suspected HLH. Additionally, one case each of confirmed EBV- and cytomegalovirus (CMV)-associated HLH was analyzed for methodological validation. Plasma cell-free RNA (cfRNA) profiling was performed using NGS data to assess the host transcriptome response. Significant viral reads of human herpesvirus-6B, human herpesvirus-7, and Hubei reo-like virus (HRLV) 14 were detected using metagenomic NGS in one patient each. Plasma cfRNA profiles from five patients with viral infection (including EBV and CMV) were compared to those of 14 patients without viral infection. By comparing the two patient groups, 1053 differentially expressed genes were identified. The gene ontology (GO) term of "adaptive immune response" (GO: 0002250) was significantly enriched among upregulated genes in the virus-positive group. Furthermore, an isolated cluster consisting specifically of mitochondrial RNAs, was identified in the upregulated genes of the virus-positive group. Using metagenomic NGS, several candidate viral pathogens were identified in patients with suspected infection-related HLH. The viral genome of HRLV 14, previously undetected in human clinical samples, was identified in one patient. The results from plasma cfRNA profiling suggest that mitochondrial RNAs may reflect the underlying pathogenesis of virus-associated HLH and have potential utility as disease biomarkers.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>本文為一篇撤稿聲明，所撤回的原論文為一項系統性文獻回顧。該原研究之核心目的在於探討海水養殖廢水中抗生素的殘留情形，並評估「微藻-細菌共生系統（MBSS）」去除抗生素的效果，同時利用總體基因體學（metagenomics）技術來表徵抗生素耐藥基因（ARGs）的分布特徵。由於本公告僅為撤稿通知且未提供原文摘要，因此無法取得具體的研究樣本數量與實驗發現。此撤稿之發佈主要在於維護學術文獻的嚴謹性、準確性與科學誠信。</t>
+          <t>噬血細胞淋巴組織細胞增生症（HLH）是一種進展迅速且嚴重的疾病，本研究旨在透過次世代定序（NGS）技術，對 17 位疑似 HLH 的兒科患者進行血漿游離 RNA（cfRNA）分析，以探討潛在的病原體與宿主轉錄體反應。研究發現，透過宏基因組學分析，成功於患者體內檢測出包含人類皰疹病毒 6B、7 型及罕見的湖北里奧樣病毒（HRLV）14。此外，比較病毒陽性與陰性組的宿主 cfRNA 差異，共篩選出 1,053 個差異表現基因，主要與「適應性免疫反應」相關。特別的是，研究發現粒線體 RNA 在病毒感染組中呈現顯著上調，顯示其在病毒相關性 HLH 的致病機制中扮演重要角色，並具有開發為疾病生物標誌物的臨床應用潛力。此研究不僅擴展了 HLH 病毒病原體的檢測範疇，也為理解該病的分子免疫機轉提供了新視角。</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42674950/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42677877/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>42674139</t>
+          <t>42678156</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cellulose/polyester-blended microplastics amplify plastisphere pathogen and antibiotic resistome risks.</t>
+          <t>Multi-kingdom gut microbiota analyses identify biomarkers of different types of pediatric short bowel syndrome.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bioresource technology</t>
+          <t>mSystems</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16S, metagenomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>4種微塑料材料（AP、PE、PP、PS）（具體重複樣本數量未提及）</t>
+          <t>60 個糞便檢體（26 位健康對照組，34 位兒童短腸症候群患者，包含 8 例 SBS I、15 例 SBS II、11 例 SBS III）</t>
         </is>
       </c>
       <c r="G7" t="b">
@@ -784,44 +784,44 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Microplastics (MPs) are important vectors for antibiotic resistance genes (ARGs) in anaerobic digestion systems, yet the risks posed by cellulose/polyester-blended materials remain poorly understood. In this study, commercial airlaid paper (AP; 45 % cellulose and 55 % polyester), polyethylene (PE), polypropylene (PP), and polystyrene (PS) were incubated in anaerobic reactors for 60  days. Biofilm characterization, extracellular polymeric substances (EPS) analysis, 16 S rRNA sequencing, and metagenomics were used to compare plastisphere formation, microbial assembly, ARG/mobile genetic element (MGE) profiles, and potential pathogen composition. Owing to its fibrous structure and bioavailable cellulose fraction, AP exhibited the highest biofilm biomass and EPS content. In contrast, PE, PP, and PS induced stronger interfacial stress, especially PS, as indicated by increased reactive oxygen species, lactate dehydrogenase release, and enrichment of oxidative stress, SOS response, and multidrug efflux pump related genes. Metagenomic analysis showed that fully synthetic MPs mainly enriched multidrug resistance genes, whereas AP selectively enriched polymyxin resistance genes, particularly Mcr-5.1 and Mcr-5.2. AP also exhibited the highest ARG-MGE co-localization rate (12.7 %) and antibiotic resistance risk. Overall, these findings identify polymer composition as a key factor shaping plastisphere resistome assembly and indicate that cellulose/polyester-blended materials require specific consideration in sludge-associated antimicrobial resistance risk assessments.</t>
+          <t>Despite recent advances in bacterial profiling across the three anatomical types of pediatric short bowel syndrome (SBS), the gut multi-kingdom remains unexplored. We characterized the four-kingdom gut microbiota using modified DNA extraction and deep shotgun metagenomic sequencing of fecal samples from 26 healthy controls and 34 pediatric SBS patients comprising three types (8 SBS I, 15 SBS II, and 11 SBS III). Overall, children with SBS exhibited a significant reduction in α-diversity compared with controls, with no difference observed among SBS types. Compared with controls, the proportion of archaea was significantly decreased in all SBS types, while bacteria, fungi, and viruses remained similar across types. Different types of SBS exhibited distinct microbial signatures: SBS I was enriched with pathogens (such as species from the Streptococcus and Klebsiella genera); SBS II was marked by a depletion of beneficial short-chain fatty acid-producing species (such as Faecalibacterium prausnitzii); and SBS III displayed loss of bile acid-metabolizing species, alongside a significant expansion of Lactobacillus species. Ecological networks were rewired in SBS, with disruption pronounced in SBS I. Functional analysis revealed that core metabolic pathways were markedly suppressed in SBS I compared with controls. Integrated correlation analyses revealed ileocecal valve loss as the primary determinant of SBS I microbial profiles, linking it to impaired secretory functions and hepatic injury. Our findings deciphered type-specific alterations in the multi-kingdom microbiota and their functional profiles, providing the basis for designing precision microbial therapies aimed at improving long-term outcomes for children with SBS.IMPORTANCEPediatric short bowel syndrome (SBS) is a primary cause of intestinal failure, yet prior research characterizing the gut microbiota has focused almost exclusively on bacteria. In this study, we characterized the multi-kingdom microbiome (including bacteria, fungi, archaea, and viruses) across the three anatomical types of pediatric SBS. We found that different SBS subtypes showed distinct microbial patterns: SBS I was enriched in pathogens, SBS II exhibited a depletion of beneficial short-chain fatty acid-producing species, and SBS III was characterized by a loss of bile acid-metabolizing microbes with an expansion of Lactobacillus. Functional analysis showed that SBS I had markedly suppressed core metabolic pathways, and integrated analyses identified the ileocecal valve as a key determinant of microbial gene profiles, with its loss linked to impaired secretion and liver injury. These findings provide a comprehensive multi-kingdom view of the pediatric SBS microbiome and highlight anatomical determinants shaping host-microbiome dysfunction.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>本研究旨在評估纖維素/聚酯混合微塑料（如無塵紙 AP）在厭氧消化系統中，相較於傳統合成微塑料（PE、PP、PS）對「塑料圈」病原菌與抗藥性基因（ARGs）的傳播風險。研究顯示，AP 因具纖維結構及可利用的纖維素，其生物膜量和胞外聚合物最高。不同於合成微塑料主要富集多重抗藥基因，AP 選擇性富集多黏菌素抗藥基因（Mcr-5.1/5.2），且其抗藥基因與行動遺傳元件的共定位率達 12.7%，具最高的抗藥性風險。本研究證實聚合物成分是形塑塑料圈抗藥性的關鍵，強調污泥抗藥性評估應特別納入混合型微塑料。</t>
+          <t>本研究旨在探討兒童短腸症候群（SBS）患者的多界腸道微生物群落（包含細菌、真菌、古菌與病毒）。研究透過深度總體基因體定序（shotgun metagenomics）發現，SBS 患者腸道微生物的多樣性顯著低於健康對照組。研究證實不同解剖類型的 SBS 具有獨特的微生物特徵：SBS I 型富含病原菌且代謝路徑受抑制；SBS II 型缺乏產短鏈脂肪酸的益菌；SBS III 型則出現膽酸代謝菌減少及乳酸桿菌增生。此外，研究揭示了迴盲瓣（ileocecal valve）缺失是影響 SBS I 型微生物譜與肝損傷的關鍵因素。此研究填補了過去僅針對細菌研究的缺口，提供 SBS 患者臨床診斷的精準微生物生物標記，並為發展針對不同病理類型的微生態治療策略奠定了科學基礎。</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42674139/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42678156/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>42673827</t>
+          <t>42678158</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Elevated water levels drive greenhouse gas mitigation in the riparian zone profile.</t>
+          <t>xoxF-linked methanol oxidation signals recur across wetland metagenomes.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Journal of environmental management</t>
+          <t>Microbiology spectrum</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>IMG/M 資料庫中之濕地相關紀錄（具體數量未提及），以及一個濕地表層沈積物共同組裝資料集（Wetland Surface Sediment combined assembly）。</t>
         </is>
       </c>
       <c r="G8" t="b">
@@ -839,54 +839,54 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Wetlands are critical for climate regulation, with their hyporheic zone serving as sensitive interfaces for groundwater-soil-atmosphere exchange. These zones are active hotspots for carbon-nitrogen cycling and greenhouse gas (GHG) emissions (CO2, CH4, N2O), yet the impact of water level fluctuations on these emissions and their microbial drivers in freshwater wetlands remains poorly understood. This study investigated the spatiotemporal dynamics of GHG emissions and carbon-nitrogen coupling processes along riparian soil profiles of Baiyangdian Lake during water level fluctuations. Employing static chamber measurements, microcosms, quantitative PCR, Metagenome-Assembled genome (MAG) analyses, and Structural Equation Modeling (SEM), we observed that GHG emissions were significantly affected by water level fluctuations. Specifically, CO2 and N2O fluxes, as well as CO2 production potential were significantly lower at high-water-level conditions. Water level also emerged as a key driver of microbial community structure, with Methylococcaceae and Methanosarcinaceae as key regulators of CH4 emission, and Anaeromyxobacteraceae as central to N2O dynamics. A high-quality Methylomirabilales-like MAG, possessing the complete pathway for coupled nitrate reduction and methane oxidation, was identified. Its abundance negatively correlated with water level, suggesting that these C-N coupling bacteria contribute to reducing GHG emissions. This study provides crucial theoretical insights and identifies microbial targets for mitigating wetland GHG emission through hydrological management.</t>
+          <t>Wetlands are globally important methane-cycling ecosystems, but methanol oxidation remains less frequently emphasized than methane oxidation in community-level metagenomic analyses. Recent studies have highlighted the ecological importance of the lanthanide-dependent methanol dehydrogenase XoxF, yet wetland-focused xoxF literature remains comparatively limited relative to marine, freshwater, and other environmental systems. Here, we screened wetland-associated records in IMG/M using methane-metabolism and enzyme-centered queries focused on EC 1.1.2.10/xoxF and related methanol-oxidation annotations. Wetland-associated data sets repeatedly returned xoxF-linked annotations. We then examined a representative data set, a Wetland Surface Sediment combined assembly, to assess the relative representation of methanol-oxidation-associated annotations. In this co-assembly, xoxF/EC 1.1.2.10 was the most frequently recovered methanol-oxidation-associated annotation in the queried annotation space, with 1,996 genes, compared with 428 genes assigned to mxa-like EC 1.1.2.7 functions and 235 genes assigned to mdo/EC 1.1.99.37. KEGG-linked organism context included canonical methanotrophic and methylotrophic genera, including Methylococcus, Methylomonas, Methylotuvimicrobium, Methylovulum, and Methylophaga, while also extending into broader environmental Proteobacteria. Together, these data indicate that xoxF-linked methanol oxidation annotations recur across wetland metagenomes and are strongly represented in a representative wetland surface sediment co-assembly. Because this study relies on database annotations rather than organism-resolved pathway reconstruction or activity measurements, the results are best interpreted as community-level functional potential rather than evidence of xoxF-mediated activity, flux, or ecological dominance. These findings support wetlands as an underexamined but relevant setting for future clade-resolved, genome-resolved, and activity-resolved studies of xoxF-associated methanol oxidation. Wetlands play a major role in Earth's methane cycle, but studies of wetland microbes often focus more on methane itself than on the downstream step of methanol oxidation. Our study shows that wetland metagenomes repeatedly contain strong signals for xoxF, a gene linked to lanthanide-dependent methanol oxidation. In a representative wetland surface sediment co-assembly, xoxF-associated annotations were much more abundant than classical methanol dehydrogenase annotations, suggesting that this pathway may be especially important in wetland microbial communities. Because most previous xoxF studies have focused on marine, freshwater, or other non-wetland systems, these findings highlight wetlands as an underexplored setting for methanol-processing metabolism. This work provides a foundation for future studies connecting these signals to specific microbes, environmental conditions, and methane-cycling processes in wetlands.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>本研究探討白洋淀湖泊消落帶在水位波動下，溫室氣體（GHG）排放與碳氮耦合過程的時空動態及微生物驅動機制。研究發現，高水位條件能顯著降低二氧化碳（CO2）和一氧化二氮（N2O）的排放通量。水位變化是形塑微生物群落結構的關鍵，其中Methylococcaceae、Methanosarcinaceae與Anaeromyxobacteraceae分別調控甲烷（CH4）和N2O的動態。此外，研究重構出一個高質量的Methylomirabilales總體基因體組裝基因體（MAG），該菌具備硝酸鹽還原與甲烷氧化耦合的完整途徑，其豐度與水位呈負相關，證實此類碳氮耦合細菌有助於減少溫室氣體排放。本研究為透過水文管理減緩濕地溫室氣體排放提供了關鍵的理論依據與微生物靶點。</t>
+          <t>本研究旨在探討濕地生態系中微生物代謝甲醇的功能潛力，特別是針對稀土元素依賴型甲醇脫氫酶（XoxF）的基因分布。透過分析 IMG/M 資料庫中的濕地總體基因體數據，研究發現 xoxF 基因在濕地環境中廣泛存在。在濕地表層沈積物的共同組裝資料集中，xoxF（EC 1.1.2.10）的基因數量高達 1,996 個，遠超傳統的 mxa 型與 mdo 型甲醇脫氫酶基因。這些基因與多種已知產甲烷菌及甲基營養菌屬（如 Methylococcus, Methylomonas 等）高度相關。此研究揭示了濕地微生物群落中潛在的甲醇氧化路徑，強調了濕地作為代謝研究未充分開發領域的重要性，並為後續探討濕地甲烷循環中微生物的功能角色與生態機制奠定了科學基礎。</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42673827/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42678158/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>42672116</t>
+          <t>42678565</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Small serine recombinases are markers for antiphage defense system discovery.</t>
+          <t>Microbial signal profiles and organism-level concordance between plasma metagenomic sequencing and blood culture in suspected bloodstream infection.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PLoS biology</t>
+          <t>World journal of microbiology &amp; biotechnology</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>metagenomics, others</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>329 個血漿 mNGS 報告（其中 315 個同時進行了血液培養）</t>
         </is>
       </c>
       <c r="G9" t="b">
@@ -894,44 +894,44 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Renewed interest in phage therapy has highlighted a need to understand how bacteria subvert phage infection through antiphage defense systems. Traditionally, strategies to identify antiphage defense systems lack throughput or have limitations for bacterial species where antiphage defense systems are understudied. Herein, we developed a bioinformatic pipeline that uses a small serine recombinase to identify known and unknown antiphage defense systems. Using this approach to query reference genomes and metagenomes, we show that small serine recombinase genes are genetically linked to antiphage defense systems and serve as bait for finding these systems across diverse bacterial phyla. Using co-transcription predictions and statistical analysis of protein domain abundances, we experimentally validated our bioinformatic approach by discovering that KAP P-loop NTPases are fused to putative antiphage domains and reinforce prokaryotic Schlafen proteins as a new class of antiphage defense. Our work shows that small serine recombinases are a reliable genetic marker for the discovery of antiphage defenses across diverse bacterial phyla.</t>
+          <t>Plasma metagenomic next-generation sequencing (mNGS) and blood culture detect different components of the microbial signal and frequently produce discordant organism reports. We characterized microbial signal class, report-derived burden, organism-level concordance, and independent clinical attribution in a retrospective, single-center, episode-level cohort. Among 329 episodes with evaluable plasma mNGS reports, 315 had blood culture performed; 232 were mNGS positive/culture negative and 53 were positive by both methods. In the 232 discordant episodes, the recorded routine-care diagnosis classified 124 as bloodstream infection (BSI) and 108 as non-BSI. Nonviral signals were present in 78.2% and 42.6%, respectively (P &lt; 0.001), and median maximum report-derived sequence counts were 98.5 and 11.5 (P &lt; 0.001). Two laboratory physicians then independently reviewed source records using structured criteria while masked to the recorded BSI label and mNGS organism and sequence-count information. Initial agreement for the five-category BSI assessment was 97.6% (Cohen's kappa, 0.960). Within the mNGS-positive/culture-negative subgroup, adjudicated BSI likelihood showed a modest ordinal association with report burden (Spearman rho = 0.190; P = 0.004), while mNGS organisms were considered supported in 1 episode, plausible in 158, unlikely or contaminant in 72, and unresolved in 1. Among 53 dual-positive episodes, 33 (62.3%) shared at least one species, but only 5 (9.4%) had complete species-set concordance. Plasma mNGS and blood culture therefore frequently generated non-equivalent organism sets. Signal class and report burden contributed graded contextual evidence, but organism-level attribution required clinical review and orthogonal microbiology rather than binary positivity alone.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>本研究開發了一套生物資訊分析流程，利用「小型絲氨酸重組酶（small serine recombinases）」作為基因標記，以搜尋已知及未知的細菌抗噬菌體防禦系統。團隊透過檢索參考基因體與總體基因體，證實該重組酶與防禦系統具備強烈的遺傳連鎖，並藉此成功鑑定出 KAP P-loop NTPases 相關結構域和原核 Schlafen 蛋白質為新型抗噬菌體防禦系統。此發現證實小型絲氨酸重組酶是跨菌門尋找防禦系統的可靠標記，對理解細菌免疫機制及推動噬菌體療法具有重要科學價值。</t>
+          <t>本研究旨在評估血漿宏基因組定序（mNGS）與傳統血液培養在診斷菌血症（BSI）時的診斷一致性。研究分析了 329 例疑似感染個案，發現 mNGS 與培養結果經常出現不一致：在 mNGS 陽性且培養陰性的案例中，約半數被臨床判定為非 BSI。數據顯示，mNGS 的檢出序列數與臨床感染的可能性呈正相關，但即便兩者皆陽性，菌種的一致性亦偏低。結論指出，mNGS 與血液培養檢測的是不同維度的微生物訊號，臨床診斷不應僅依賴 mNGS 的二元結果，而必須結合序列數據負載量、微生物訊號類別，並由臨床醫師進行審慎評估與正交檢驗，以確保診斷的準確性。</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42672116/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42678565/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>42671761</t>
+          <t>42679008</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Virome of neotropical Sabethes mosquitoes reveals two novel viruses in the Spiciviridae family.</t>
+          <t>Syndromic cholera diagnosis masks diverse causes of diarrhoeal disease in Burundi revealed by portable metagenomics.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Virus genes</t>
+          <t>PLoS neglected tropical diseases</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>19 個蚊子樣本池 (nineteen mosquito pools)</t>
+          <t>未提及（文中僅提及部署於健康中心、地區醫院及難民中轉站，未具體列出糞便檢體總數）</t>
         </is>
       </c>
       <c r="G10" t="b">
@@ -949,54 +949,54 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>The family Spiciviridae, belonging to the order Ghabrivirales, is currently composed of only one officially recognized genus, Spicivirus. However, metagenomic studies have revealed an increasing diversity of related viruses, suggesting that the current classification may underestimate their evolutionary complexity. In this context, the aim of the present study was to detect and characterize new viruses related to the Spiciviridae in the family Culicidae mosquitoes. A total of nineteen mosquito pools were sequenced and analyzed using metagenomic approaches and bioinformatics tools. Among these, two novel viruses were identified in four pools (S4, S11, S18, and S19), provisionally named Sabethes virus 1 (SV1) and Sabethes virus 2 (SV2). Phylogenetic inference revealed clades with strong statistical support and genetic divergences greater than 20% in the RNA-dependent RNA polymerase (RdRp) protein. These findings contribute to a detailed analysis of the genomic diversity associated with Spiciviridae. Although Spicivirus is currently the only genus officially recognized, our results suggest the presence of viruses that may represent new taxonomic groupings not yet described by the ICTV.</t>
+          <t>Cholera outbreaks remain a major public-health challenge in sub-Saharan Africa, where diagnostic capacity is limited and clinical case definitions are non-specific and re ly heavily on syndromic diagnosis. Rapid identification of Vibrio cholerae is critical, yet cholera-suspected diarrhoea can have multiple infectious causes not captured by targeted diagnostics. We evaluated a mobile, culture-independent metagenomic sequencing workflow for on-site detection of gastrointestinal pathogens directly from faecal samples in Burundi. The offline workflow combined long-read Oxford Nanopore Technologies (ONT) sequencing with rapid, laptop-based taxonomic and antimicrobial resistance (AMR) screening and was deployed across a health centre, a district hospital, and a refugee transit camp. The frontline and real-time results were verified using both conventional culturing and in-depth bioinformatic analyses. V. cholerae signals were only detected in a subset of suspected cholera cases, while many samples were dominated by alternative bacterial taxa, most frequently Escherichia coli. V. cholerae abundance correlated strongly with detection of the C holera T oxin P hage CTXφ, supporting differentiation between toxigenic signal and background exposure. AMR genes were detected across samples, providing early situational insight into resistance determinants among gastrointestinal bacteria. Mobile, offline metagenomic sequencing enables rapid frontline characterization of gastrointestinal disease, especially cholera-suspected, in resource-limited settings and complements existing diagnostics by improving etiological resolution and outbreak response.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>本研究旨在探討新熱帶區《Sabethes》屬蚊子體內的病毒多樣性，特別針對 Ghabrivirales 目下的 Spiciviridae 病毒科進行分析。透過宏基因組定序技術，研究團隊從 19 個蚊子樣本池中發現了兩種新型病毒，暫命名為 Sabethes virus 1 (SV1) 與 Sabethes virus 2 (SV2)。系統發生學分析顯示，這兩種病毒在 RNA 依賴性 RNA 聚合酶 (RdRp) 蛋白序列上，與已知病毒具有超過 20% 的遺傳差異。此發現不僅擴展了 Spiciviridae 的基因組多樣性，更顯示現行病毒分類可能低估了該病毒科的演化複雜度，為國際病毒分類委員會 (ICTV) 未來的分類架構提供了重要的科學依據。</t>
+          <t>本研究旨在解決布隆迪地區霍亂爆發時，僅依賴臨床症候群診斷導致病原體識別受限的問題。研究團隊開發一套可攜式、不依賴培養的宏基因組定序工作流程，透過 Oxford Nanopore 長讀取技術進行現場檢測。結果顯示，僅有部分疑似病例確實檢出霍亂弧菌（*V. cholerae*），其餘多為大腸桿菌等其他致病菌。該流程成功區分了產毒株與背景環境菌株，並有效偵測抗藥性基因（AMR）。此方法克服了資源匱乏環境下的診斷瓶頸，證實宏基因組學在釐清腹瀉疾病病因、監測抗藥性及提升公共衛生突發事件應對能力方面具有極高的科學價值與臨床潛力。</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42671761/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42679008/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>42671657</t>
+          <t>42679417</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Species-specific structuring of gut bacterial and fungal communities in honey bees Apis cerana and Apis mellifera.</t>
+          <t>Comparative analysis of microbial communities, assembly processes, and life-history strategies in a mariculture-impacted eutrophic bay and adjacent coastal sediments.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Antonie van Leeuwenhoek</t>
+          <t>Ecotoxicology and environmental safety</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>16S, metagenomics</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>未提及（文中僅提及針對兩種蜜蜂物種進行分析，未具體標示樣本總數）</t>
+          <t>未提及（原文僅列出兩地檢體之測定數據範圍，未明確標示具體樣本總數）</t>
         </is>
       </c>
       <c r="G11" t="b">
@@ -1004,54 +1004,54 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Honey bee gut microbiome studies have primarily emphasized bacteria, leaving fungal communities comparatively overlooked despite their ecological and functional importance. Whole-genome shotgun metagenomics of Apis cerana and Apis mellifera revealed fungal assemblages dominated by Ascomycota, with Basidiomycota and Microsporidia in minor proportions, alongside gut bacterial communities composed mainly of Pseudomonadota, Bacillota, and Actinomycetota. The bacterial diversity was markedly higher in A. mellifera (Shannon = 5.90; Simpson = 0.98) than in A. cerana (Shannon = 4.01; Simpson = 0.94; p &gt; 0.05), while fungal diversity remained comparable between species (p &gt; 0.05). Beta-diversity analyses revealed strong host-specific clustering for both bacterial (PERMANOVA R2 = 0.7989, p &gt; 0.05) and fungal communities (R2 = 0.7218, p &gt; 0.05), indicating distinct microbial organization driven by host species. Bacterial-fungal co-occurrence patterns exhibited host-specific structuring, suggesting differential inter-kingdom community organization between A. cerana and A. mellifera. Linear Discriminant Analysis Effect Size (LEfSe) identified 93 discriminatory fungal taxa (45 enriched in A. cerana, 48 in A. mellifera), highlighting yeast-dominated signatures in A. mellifera and Basidiomycota-affiliated enrichments in A. cerana. KEGG and CAZy profiling revealed host- and kingdom-specific functional differences, with bacterial communities of A. mellifera showing distinct representation of carbohydrate metabolism and nutrient-cycling functions, while fungal communities exhibited a comparatively narrower functional repertoire. Together, these findings provide a high-resolution view of honey bee bacterial and fungal microbiomes, highlighting strong host-driven divergence in taxonomy, function, and cross-kingdom interactions.</t>
+          <t>Coastal embayments are increasingly subjected to intensive mariculture, which delivers sustained nutrient, organic matter, and antibiotics to sediments, yet microbiome responses remain poorly understood. Here we compared sediment microbiomes of the eutrophic Xiangshan Bay (XSB) and oligotrophic East China Sea (ECS), integrating cell counts, 16S rRNA amplicon, metagenomics, and cultivation-based resistance assays. Cell counts and amplicon data showed that XSB harbored higher microbial abundance (1.28 ×108-1.34 ×109 vs. 2.07 ×107-4.43 ×108 cells g⁻¹), Chao1 richness (10,374-16,674 vs. 8311-12,281), and Shannon diversity (6.31-7.43 vs. 5.95-6.68). Amplicon-based null and neutral models indicated that community assembly in XSB was less stochastic and more deterministically selected than in the ECS. Life-history traits inferred directly from metagenomic data were consistently elevated in XSB relative to ECS, including 16S rRNA gene copy number (3.35 vs. 2.37), codon usage bias (0.0219 vs. 0.0188), maximum growth potential (0.1208 vs. 0.0844 h-1), genome size (5.63 vs. 5.38 Mb), GC content (56.26% vs. 54.48%), and transposase abundance (3.91% vs. 2.55%), collectively indicating a transition from K- to r-selected life-history strategies. Moreover, metagenomic annotation revealed a similarly expanded resistome in XSB, with 4.5-fold higher antibiotic resistance gene abundance (17.40-45.37 vs. 7.96-25.96 RPM) dominated by efflux-pump mechanisms, while plate assays showed roughly two-fold higher phenotypic resistance to macrolides, tetracyclines, and sulfonamides. These findings demonstrate that microbial community, life-history strategies, and antibiotic resistance respond as a coupled system to mariculture-driven eutrophication, providing a trait-based framework for predicting microbiome trajectories under anthropogenic nutrient enrichment.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>本研究透過宏基因體定序（Shotgun metagenomics），深入探討東方蜜蜂（*Apis cerana*）與西方蜜蜂（*Apis mellifera*）腸道內細菌與真菌群落的組成與功能差異。研究發現，儘管細菌多樣性在不同蜂種間存在顯著差異，但兩者的真菌群落多樣性相當。分析顯示，兩種蜜蜂的細菌與真菌群落結構呈現強烈的宿主特異性，顯示宿主物種為微生物組成的主要驅動力。此外，透過 LEfSe 分析發現兩者在關鍵分類群（如西方蜜蜂的酵母菌與東方蜜蜂的擔子菌門）與代謝功能（如碳水化合物代謝）上具有顯著差異。本研究不僅填補了蜜蜂腸道真菌群落研究的空白，更揭示了跨界（細菌-真菌）的交互作用機制，對理解蜜蜂共生微生物的生態適應與演化具有重要的科學意義。</t>
+          <t>本研究旨在探討海水養殖活動導致的富營養化對沉積物微生物群落的影響。研究比較了富營養化的象山港（XSB）與貧營養的東海（ECS）沉積物，發現養殖活動顯著提升了微生物豐度、豐富度與多樣性。群落組裝分析顯示，XSB 的組裝過程由環境選擇（確定性過程）主導。宏基因體分析揭示，XSB 的微生物展現出由 K-策略向 r-策略轉變的生活史特徵，具備更快的生長潛力、更大的基因體與更高的轉座酶豐度。此外，XSB 沉積物中抗生素抗性基因（ARG）豐度顯著增加，主要透過外排泵機制運作，且表型抗性亦顯著提升。此研究建立了微生物性狀與環境壓力的連結，強調養殖驅動的富營養化會導致微生物群落結構、生活史策略及抗藥性系統性的同步改變，為預測人為干擾下的微生物演變提供了關鍵架構。</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42671657/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42679417/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>42671637</t>
+          <t>42679805</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Body mass index-associated gut microbial taxa and functional pathways in women with benign and malignant breast disease.</t>
+          <t>Maternal secretor status and human milk oligosaccharides influence the infant gut resistome.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Breast cancer research and treatment</t>
+          <t>Cell reports. Medicine</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>131 個糞便檢體（包含良性疾病 23 例、高風險/非侵入性疾病 47 例、惡性腫瘤 61 例）</t>
+          <t>57 個嬰兒糞便檢體、50 個母乳檢體，並包含 MAMI 與 Lifelines NEXT (LLNEXT) 兩個隊列的長期追蹤數據</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -1059,54 +1059,54 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Obesity is an established risk factor for breast cancer and is associated with alterations in gut microbial composition. We evaluated associations among body mass index (BMI), breast density, gut microbial diversity and composition and microbial functional pathways in women undergoing surgery for benign, high-risk/non-invasive, and invasive breast disease. Preoperative stool samples were collected from 131 women (median age 59) with benign (n = 23), high-risk/non-invasive (n = 47), or malignant (n = 61) disease. Shallow shotgun metagenomic sequencing was performed. Taxonomic profiling used Sourmash 4.2.4 (GTDBv207 reference database); functional profiling employed HUMAnN 3.6 with gene families mapped to MetaCyc pathways. α-diversity differed across diagnosis groups and inversely correlated with increasing BMI (Inverse Simpson p = 0.025). β-diversity differed by diagnosis group and BMI. No significant differences in diversity were observed based on age, menopausal status or mammographic breast density. BMI was also associated with enrichment of Dorea, Blautia, and Streptococcus species. Functional pathway profiling showed greater relative abundance of genes involved in NAD biosynthesis, folate metabolism, and aromatic amino acid metabolism pathways with higher BMI. Cross-referencing the most significant taxonomic and functional pathway findings suggested enrichment of Blautia species, via tryptophan metabolism, might link to NAD biosynthesis. In this study of women with benign, high-risk/non-invasive, and invasive breast disease, BMI was associated with distinct differences in gut microbial taxonomy and functional pathway profiles. These hypothesis-generating findings provide a rationale for future study to determine how the obesity-associated microbiome contributes to breast cancer development. Not applicable.</t>
+          <t>The infant gut resistome is established early in life and is shaped by perinatal exposures, yet the mechanisms underlying its modulation remain unclear. We combined shotgun metagenomics of fecal samples from 57 one-month-old infants and paired milk samples from 50 mothers in the MAMI cohort to investigate the influence of maternal secretor status on early-life resistome development. Longitudinal follow-up at 6 and 12 months, and also further validation in the independent Lifelines NEXT (LLNEXT) cohort, support our findings. Cesarean section (C-section) was associated with increased antibiotic resistance gene (ARG) diversity, whereas exclusive breastfeeding reduced ARG abundance and diversity. Maternal secretor status further modified resistome composition among exclusively breastfed infants. Human milk oligosaccharide profiling identified specific glycans underlying these associations, with 2'-fucosyllactose and 6'-sialyllactose showing negative correlations with distinct ARG classes. These findings identify human milk composition as a key determinant of early-life resistome assembly and a potential target for modulating antimicrobial resistance.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>本研究探討體重指數（BMI）與乳房疾病患者腸道微生物組成及功能路徑的關聯。透過對 131 名術前女性患者進行淺層總體基因體定序，研究發現腸道菌相多樣性與 BMI 呈負相關。BMI 較高的受試者在細菌分類上顯現 *Dorea*、*Blautia* 及 *Streptococcus* 屬的富集；在功能路徑上，與 NAD 生物合成、葉酸及芳香族胺基酸代謝相關的基因表現顯著增加。特別是 *Blautia* 菌屬可能透過色胺酸代謝連結至 NAD 生物合成路徑。此研究結果證實 BMI 與腸道微生物特徵的顯著差異，並提出肥胖相關腸道菌群可能參與乳癌發展的機制假設，為未來針對該領域的病理研究提供了科學依據。</t>
+          <t>本研究探討母親分泌型狀態（Secretor status）及母乳寡糖（HMOs）對嬰兒腸道抗藥性基因體（resistome）組成的影響。透過宏基因體學分析，研究發現生產方式與哺育模式為關鍵驅動因子：剖腹產與抗藥性基因多樣性增加有關，而純母乳哺育則可降低抗藥性基因的豐度與多樣性。進一步分析證實，母親分泌型狀態會透過母乳成分調節嬰兒腸道抗藥性基因的分布，特別是母乳中的 2'-岩藻糖基乳糖（2'-FL）與 6'-唾液酸乳糖（6'-SL）與特定抗藥性基因呈現負相關。此發現揭示母乳組成在嬰兒早期抗藥性菌群建立中的關鍵作用，並為透過營養干預手段、減少早期生命階段抗生素抗藥性提供科學依據與潛在臨床策略。</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42671637/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42679805/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>42671180</t>
+          <t>42680085</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Longitudinal development of infant oral ecosystem: salivary metabolomic, bacteriome, and virome dynamics in early infancy.</t>
+          <t>Enhanced volatile fatty acid production from co-fermentation of spent mushroom waste and food waste with rumen microbes: Performance and mechanism.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>mSystems</t>
+          <t>Anaerobe</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>6 組不同比例的共發酵實驗組 (AW/FW ratios: 1:0, 1:1, 2:1, 3:1, 4:1, 0:1)</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -1114,54 +1114,54 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>This prospective cohort study investigated the longitudinal development of the salivary bacteriome, virome, and metabolome during early infancy. We assessed the associations between oral bacteria, viruses, and metabolites from 10 mother-infant dyads, with oral samples collected at 1 and 2 years of age. Forty saliva and plaque samples underwent untargeted metabolomic analysis, and infant saliva samples underwent metagenomic sequencing. Maternal salivary and plaque metabolomic profiles remained largely stable, whereas infant profiles were clearly separated from maternal profiles and changed with age. Notably, infant dental plaque metabolism underwent more substantial changes from year 1 to year 2 than saliva, with age-dependent metabolite shifts mainly involving energy, amino acid, nucleotide, and lipid metabolic pathways. Our findings also revealed significant developmental shifts in salivary bacteriome, virome, and functional pathway profiles during early childhood. The most abundant oral bacteria in early life, comprising over 75% of total abundance, included Veillonella, Streptococcus, Rothia, Prevotella, Neisseria, and Actinomyces species. While human viruses like Roseolovirus were detected, bacteriophages constituted the majority of the virome. Comparing infants at year 1 and year 2, we identified differentially abundant bacteria, viruses, metabolic functional pathways, and specific metabolites. We observed associations between bacteria and viruses, noting that these cross-kingdom relationships attenuated as infants grew. The study results underscore the complex and dynamic development of the oral microbiome, virome, and metabolome during early childhood.IMPORTANCEThe human oral cavity undergoes substantial microbial and metabolic development during early childhood, yet the temporal changes in the infant oral ecosystem remain incompletely understood. In this study, we longitudinally profiled the salivary metabolome, bacteriome, and virome of infants at 1 and 2 years of age. We demonstrated that the infant oral metabolome undergoes substantial developmental shifts, particularly in pathways related to energy, amino acid, and lipid metabolism; whereas maternal metabolic profiles remained stable over the same period. Furthermore, our results revealed the dynamic assembly of infant salivary virome and bacteriome and their associations with the functional pathways and metabolites. These findings provide new insights into the complex and dynamic development of the oral microbiome, virome, and metabolome in early infancy.</t>
+          <t>Co-fermentation of lignocellulosic biomass and food waste (FW) can enhance the production of volatile fatty acids (VFAs) during anaerobic fermentation. However, the effect and mechanism of co-fermentation of Auricularia auricula waste (AW) with FW remains unclear. This study aimed to investigate the effect and mechanism of co-fermentation of Auricularia auricula waste (AW) with food waste (FW) on volatile fatty acid (VFA) production. Anaerobic fermentation experiments were conducted at different AW/FW ratios (1:0, 1:1, 2:1, 3:1, 4:1, 0:1) based on volatile solids (VS). VS removal and VFA concentration were measured, and metagenomic sequencing was performed to elucidate the underlying enhancement mechanism. Co-fermentation significantly improved VS removal and VFA production, with both parameters increasing as the proportion of FW increased. The highest VS removal (48.9%) and VFA concentration (7929 mg/L) were achieved at an AW/FW ratio of 1:1, which were approximately double those of AW alone (22.4% and 3659 mg/L, respectively). Metagenomic analysis revealed that co-fermentation enriched bacterial genera such as Rummeliibacillus (25.4%) and Leuconostoc (9.2%), while Fungal genera Piromyces and Neocallimastix became dominant. Moreover, co-fermentation increased the relative abundance of carbohydrate-active enzymes and activated key functional genes in the VFA production pathway (e.g., ackA, PTA, MDH, HBD). Co-fermentation of AW and FW significantly enhanced the hydrolysis and VFA production. The enhancement mechanism of VFA production during co-fermentation primarily involved the synergistic interaction between substrate nutrient complementation and efficient microbial community. This study provides a feasible strategy for efficient VFA production from spent mushroom waste.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AI 分析失敗，請參考英文原文。</t>
+          <t>本研究旨在探討木耳廢棄物（AW）與廚餘（FW）共發酵對揮發性脂肪酸（VFA）產量之影響及其機制。實驗透過不同比例的共發酵發現，當 AW 與 FW 比例為 1:1 時，VFA 產量與揮發性固體（VS）去除率均達最高值（分別為 7929 mg/L 與 48.9%），較單一 AW 發酵顯著提升。總體基因體分析顯示，共發酵環境下 *Rummeliibacillus* 與 *Leuconostoc* 等細菌，以及 *Piromyces* 和 *Neocallimastix* 等真菌的豐度顯著增加。此外，共發酵顯著提升了碳水化合物活性酶的豐度，並活化了如 *ackA*、*PTA* 等關鍵 VFA 代謝路徑基因。研究證實，透過基質養分互補與優化微生物群落結構，能有效促進廢棄物水解並提升生質化學品產量，為農業與食品廢棄物的循環經濟提供了一項高效的工業策略。</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42671180/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42680085/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>42671179</t>
+          <t>42675564</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Novel insights into Radix Pseudostellariae saponins assist Mycoplasma gallisepticum attenuated vaccine to enhance the immunoprotection of chicken.</t>
+          <t>Does the Gut Microbiota Play a Role in Attention-Deficit/Hyperactivity Disorder in Childhood? A Pilot Study From Turkey.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mSystems</t>
+          <t>Developmental neurobiology</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>16S</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>20 位兒童（10 位 ADHD 患者與 10 位健康對照組）</t>
         </is>
       </c>
       <c r="G14" t="b">
@@ -1169,54 +1169,50 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Mycoplasma gallisepticum (MG) is a major pathogen causing chronic respiratory disease in chickens, and the MG-attenuated vaccine (MGAV) often fails to induce effective mucosal immunity. Radix Pseudostellariae saponins (RPS), important bioactive components of the traditional Chinese herb, have been utilized for immunomodulation, although the underlying mechanisms remain to be elucidated. In this study, chickens were randomly assigned to groups receiving intranasal MGAV alone, MGAV plus RPS at different doses, or appropriate controls. Serum, tracheal mucosa, and respiratory lavage samples were collected for antibody measurement, cytokine profiling, histological assessment, and metagenomic/metabolomic analyses. RPS significantly increased MG-specific antibody levels and enhanced expression of the immunomodulatory cytokines, while suppressing that of pro-inflammatory factors. It also promoted tracheal mucosal integrity by elevating goblet cell numbers and mucosal epithelial height. Through metagenomic and metabolomic analysis, RPS was found to enrich the respiratory bacterium Lactobacillus sp. UMNPBX13, which was positively correlated with the metabolite phosphatidylcholine (PC). Intranasal administration of Lactobacillus increased mucin 2 (MUC2) and PC levels in tracheal mucosa. Similarly, PC combined with MGAV enhanced mucosal immunity by modulating cytokines and increasing MG-specific antibodies. These findings demonstrate that RPS enhances MGAV-induced respiratory mucosal immunity and provides a novel adjuvant strategy for improving poultry respiratory disease vaccines by modulating the respiratory microbiota, specifically through enrichment of Lactobacillus sp. UMNPBX13, which promotes PC production.IMPORTANCEMycoplasma gallisepticum (MG) constitutes a notable challenge to poultry health. Although the MG-attenuated vaccine (MGAV) is widely used for disease control, it often fails to induce robust mucosal immunity. Here, we demonstrate that intranasal co-administration of Radix Pseudostellariae saponins (RPS) with MGAV augments mucosal immunoprotection. Integrated metagenomic and metabolomic analyses revealed that RPS enriches respiratory Lactobacillus, which in turn promotes the production of its key metabolite phosphatidylcholine (PC), thereby supporting mucosal immune enhancement. These findings offer a promising strategy for improving poultry vaccine efficacy and may provide a basis for future exploration of mucosal vaccination approaches in other animal species.</t>
+          <t>The pathophysiology of attention-deficit/hyperactivity disorder (ADHD) is not fully understood, but increasing evidence suggests that gut microbiota may play a role. This study compared the gut microbiota of children with ADHD with that of a control group of healthy children, and examined their dietary and sleep habits. Ten medication-naïve children aged 612 years who had recently been diagnosed with ADHD and ten healthy controls were included. ADHD diagnoses were confirmed using the Schedule for Affective Disorders and Schizophrenia for School-Age ChildrenPresent and Lifetime Version (K-SADS-PL). Sleep and eating habits were assessed using the 2nd Level Sleep Disorder Short Form, the Children's Eating Behaviour Inventory, and a form to collect sociodemographic and clinical information. The gut microbiota were analysed using 16S NGS metagenome analysis. A significant decrease in the Shannon and Simpson diversity index values was observed in the ADHD group compared to the control group. Despite the presence of a percentage difference, no statistically significant differences were observed between the groups with respect to species, genus, family, order, class or phylum. Following evaluation of the sleep and eating habit scale scores, no statistically significant difference between the groups was determined.These findings suggests that children with ADHD may alter gut microbiota diversity.However, the absence of significant taxonomic differences and the small sample size mean that these results should be interpreted with caution. Further, larger, adequately powered studies are needed to validate these findings and clarify the potential role of gut microbiota in the pathophysiology of ADHD.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AI 分析失敗，請參考英文原文。</t>
+          <t>本研究旨在探討兒童注意力不足過動症（ADHD）與腸道微生物群之間的關聯。研究對象為 20 位 6 至 12 歲兒童（各 10 位 ADHD 患者與健康對照組），透過 16S rRNA 次世代定序技術分析其腸道菌相，並評估其睡眠與飲食習慣。研究發現，ADHD 組的腸道微生物多樣性指數（Shannon 與 Simpson index）顯著低於對照組；然而，在物種豐度（從門到種）及生活習慣上，兩組間並未呈現統計學上的顯著差異。儘管結果顯示 ADHD 可能與腸道菌群多樣性改變有關，但受限於樣本數較少，該結論仍需審慎解讀。此研究為 ADHD 的微生物學病理機制提供了初步證據，未來需更大規模的臨床研究以進一步釐清兩者間的關聯。</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42671179/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42675564/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>42671175</t>
+          <t>42674950</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Laccase-mediated biotransformation potential for fluorinated compounds by geographically diverse human gut microbiota.</t>
+          <t>Retraction notice to "A systematic review of antibiotics and antibiotic resistance genes (ARGs) in mariculture wastewater: Antibiotics removal by microalgal-bacterial symbiotic system (MBSS), ARGs characterization on the metagenomic" [Sci. Total Environ. 930 (2024) 172601].</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mBio</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>4.7</t>
-        </is>
-      </c>
+          <t>The Science of the total environment</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>metagenomics, others</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1,578 個人類腸道總體基因體 (human gut metagenomes)</t>
+          <t>未提及</t>
         </is>
       </c>
       <c r="G15" t="b">
@@ -1224,12 +1220,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>The growing prevalence of synthetic organofluorine substances in agrochemicals, food packaging, and consumer products has led to increasing gastrointestinal exposure, with potential consequences for human health. Despite the extreme stability of fluorinated compounds, several microbial pathways for their transformation are known, including those involving laccases, a type of multicopper oxidase. However, the functionality of laccases in the gut microbiome, a natural contact point between food-associated chemicals and microbial biotransformation pathways, is poorly defined. Through a multi-study analysis of 1,578 human gut metagenomes spanning a global gradient from hunter-gatherer societies to industrialized urban populations, we found that laccase-coding gene homologs are widely distributed in the human gut microbiome. We identified a significant association between both the abundance and phylogenetic diversity of laccase homologs and the degree of urbanization. As human gut microbial laccase activity has not been experimentally demonstrated, eight gut metagenome-derived laccases were heterologously expressed and screened for activity with a redox mediator system. Six of the eight laccases demonstrated activity. One of these gut microbial laccases, derived from Veillonella, and three previously characterized laccases were then tested for their capacity to deplete 11 different food-associated chemicals. The Veillonella laccase depleted the agrochemicals cyflumetofen and fluazinam, as well as the industrial chemical bisphenol AF, to a lesser extent. By linking global gut metagenomes with activity assays, this work demonstrates the untapped potential of mining human gut metagenomes for laccases and other microbial enzymes that can actively modify various agricultural and industrial chemicals.IMPORTANCEAs adverse effects of fluorinated compounds on human health are emerging, the responsible enzymes from the human gut microbiome of geographically diverse human cohorts mediating interactions with fluorinated compounds in the gastrointestinal tract remain poorly characterized. In a multi-study analysis of publicly available microbiome sequencing data, we linked the abundance, diversity, and phylogeny of laccases within the gut microbiome to the degree of urbanization of human cohorts and experimentally demonstrated the ability of these laccases to deplete a range of food-associated fluorochemicals. Another significant contribution of our study is in the integration of rural catchment areas as a quantitative metric of urbanization in gut microbiome metagenomics and enzyme activity surveys.</t>
+          <t>無提供摘要。</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>本研究旨在探討人類腸道菌群中漆酶（laccases）對環境氟化化合物的生物轉化潛力。研究分析了全球不同城市化程度的1,578個腸道總體基因體，發現漆酶同源基因廣泛存在，且其豐度與系統發育多樣性與城市化程度呈顯著正相關。實驗進一步異源表達了8種源自腸道總體基因體的漆酶，其中6種具備活性；源自*Veillonella*菌的漆酶能有效降解特定農藥（cyflumetofen、fluazinam）及工業化學品（雙酚AF）。此研究結合全球總體基因體數據與活性篩選，證實了腸道菌群酶降解農業與工業化學污染物的潛力，具備重要的環境健康與科學意義。</t>
+          <t>本文為一篇撤稿聲明，所撤回的原論文為一項系統性文獻回顧。該原研究之核心目的在於探討海水養殖廢水中抗生素的殘留情形，並評估「微藻-細菌共生系統（MBSS）」去除抗生素的效果，同時利用總體基因體學（metagenomics）技術來表徵抗生素耐藥基因（ARGs）的分布特徵。由於本公告僅為撤稿通知且未提供原文摘要，因此無法取得具體的研究樣本數量與實驗發現。此撤稿之發佈主要在於維護學術文獻的嚴謹性、準確性與科學誠信。</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1239,30 +1235,28 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42671175/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42674950/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>42669365</t>
+          <t>42671761</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>In situ fermentation-coupled symbiosis of polyphosphate-accumulating organisms and microalgae for efficient nutrient removal and sludge reduction in low carbon-to-nitrogen ratios wastewater.</t>
+          <t>Virome of neotropical Sabethes mosquitoes reveals two novel viruses in the Spiciviridae family.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bioresource technology</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
+          <t>Virus genes</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1271,7 +1265,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>19 個蚊子樣本池 (nineteen mosquito pools)</t>
         </is>
       </c>
       <c r="G16" t="b">
@@ -1279,44 +1273,42 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Microalgae-bacteria consortia (MBC) integrated with polyphosphate-accumulating organisms (PAOs) treat wastewater sustainably, but face excess sludge and light-dark mismatch issues. This study developed in situ fermentation-coupled photo simultaneous nitrification-denitrification phosphorus removal (F/P-SNDPR) systems by incorporating fermentative PAOs into MBC for low carbon-to-nitrogen ratios (C/N) wastewater. The effects of light-dark cycles on nutrient removal, sludge fermentation, and microbial dynamics were investigated. Under an optimal 16 h dark/8h light cycle, the F/P-SNDPR system achieved &gt; 83% nitrogen and &gt; 95% phosphorus removal, with low sludge production (312.21 mgVSS/d) and low net CO2 emissions. Prolonged light and dark phases promoted early microbial apoptosis and subsequent cell lysis, respectively, thereby facilitating fermentation. Combined dark duration and photoinhibition suppress nitrite-oxidizing bacteria, enabling stable partial nitrification. Flow cytometry and metagenomic results identified Candidatus Phosphoribacter as the primary fermentative microorganism. Its fermentation-associated genes, including LivFGHMK and Pta, facilitated volatile fatty acid (VFA) production during the dark phase. The generated VFA supported Candidatus Accumulibacter/Candidatus Competibacter to enhance nutrient removal, driven by key functional genes for polyphosphate metabolism (Ppk and Ppx) and denitrification (NirS, NirK, and NosZ). Overall, The F/P-SNDPR system offers a low-carbon strategy for efficient low C/N wastewater treatment without mechanical aeration or external carbon addition, while reducing sludge production.</t>
+          <t>The family Spiciviridae, belonging to the order Ghabrivirales, is currently composed of only one officially recognized genus, Spicivirus. However, metagenomic studies have revealed an increasing diversity of related viruses, suggesting that the current classification may underestimate their evolutionary complexity. In this context, the aim of the present study was to detect and characterize new viruses related to the Spiciviridae in the family Culicidae mosquitoes. A total of nineteen mosquito pools were sequenced and analyzed using metagenomic approaches and bioinformatics tools. Among these, two novel viruses were identified in four pools (S4, S11, S18, and S19), provisionally named Sabethes virus 1 (SV1) and Sabethes virus 2 (SV2). Phylogenetic inference revealed clades with strong statistical support and genetic divergences greater than 20% in the RNA-dependent RNA polymerase (RdRp) protein. These findings contribute to a detailed analysis of the genomic diversity associated with Spiciviridae. Although Spicivirus is currently the only genus officially recognized, our results suggest the presence of viruses that may represent new taxonomic groupings not yet described by the ICTV.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>本研究開發了一種結合原位發酵與光合同步硝化-反硝化除磷的系統（F/P-SNDPR），旨在解決低碳氮比（C/N）廢水處理中常見的過量污泥與能耗問題。研究發現，在優化的16小時黑暗與8小時光照循環下，該系統展現了卓越的除氮（&gt;83%）與除磷（&gt;95%）效率，且顯著降低了污泥產量。宏基因體分析顯示，*Candidatus Phosphoribacter* 是關鍵的發酵菌株，透過黑暗期的發酵作用產生揮發性脂肪酸（VFA），進而支持除磷菌（*Candidatus Accumulibacter/Competibacter*）的代謝與除磷脫氮功能。此技術無需額外添加碳源或機械曝氣，為低碳廢水處理提供了一種具備經濟效益與環境永續性的綠色策略。</t>
+          <t>本研究旨在探討新熱帶區《Sabethes》屬蚊子體內的病毒多樣性，特別針對 Ghabrivirales 目下的 Spiciviridae 病毒科進行分析。透過宏基因組定序技術，研究團隊從 19 個蚊子樣本池中發現了兩種新型病毒，暫命名為 Sabethes virus 1 (SV1) 與 Sabethes virus 2 (SV2)。系統發生學分析顯示，這兩種病毒在 RNA 依賴性 RNA 聚合酶 (RdRp) 蛋白序列上，與已知病毒具有超過 20% 的遺傳差異。此發現不僅擴展了 Spiciviridae 的基因組多樣性，更顯示現行病毒分類可能低估了該病毒科的演化複雜度，為國際病毒分類委員會 (ICTV) 未來的分類架構提供了重要的科學依據。</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42669365/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42671761/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>42668932</t>
+          <t>42671657</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ureaplasma parvum meningitis in neonates: A retrospective case study and literature review.</t>
+          <t>Species-specific structuring of gut bacterial and fungal communities in honey bees Apis cerana and Apis mellifera.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pakistan journal of medical sciences</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>1.7</v>
-      </c>
+          <t>Antonie van Leeuwenhoek</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>metagenomics</t>
@@ -1324,7 +1316,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1 例新生兒病例與文獻回顧之 16 例（共計 17 例）</t>
+          <t>未提及（文中僅提及針對兩種蜜蜂物種進行分析，未具體標示樣本總數）</t>
         </is>
       </c>
       <c r="G17" t="b">
@@ -1332,54 +1324,52 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>To investigate the clinical characteristics and advances in diagnosis and treatment of neonatal Ureaplasma parvum (U. parvum) meningitis. Clinical manifestations, diagnosis, treatment, and follow-up data of a neonate with persistent fever, normal blood routine, but persistently abnormal cerebrospinal fluid (CSF) results due to U. parvum meningitis were retrospectively analyzed. A literature review was conducted to identify relevant studies reporting on neonatal U. parvum meningitis published until May 2025. A male infant born at 35+2 weeks of gestation with eight hours of premature rupture of membranes (PROM) was admitted at 17 days of age with persistent fever. The routine blood test was normal, while the CSF suggested purulent meningitis. Empirical treatment was ineffective, and metagenomic next-generation sequencing (mNGS) of CSF confirmed U. parvum meningitis. The infant recovered after three weeks of azithromycin treatment, but a language delay was found at two-year follow-up. The literature review identified 16 previously reported cases of U. parvum meningitis, which were combined with the current case, totaling 17 cases. Main manifestations included fever and convulsions, or initial circulatory and respiratory symptoms. CSF in the included studies showed leukocytosis, decreased glucose, and elevated protein. Diagnosis was mainly based on mNGS, and the predominant treatment consisted of macrolides, sometimes combined with quinolones, for 3-10 weeks. Two patients relapsed after drug withdrawal, and one had elevated liver enzymes. Major neurological complications included lateral ventricular dilatation and hydrocephalus, cerebral hemorrhage, infarction, malacia, and herniation. Most cases had a favorable prognosis, with rare developmental delay. Clinical manifestations of neonatal U. parvum meningitis are nonspecific. Some patients present with normal blood routine but purulent CSF. U. parvum meningitis should be suspected in patients with poor response to empirical antibiotics and confirmed by CSF mNGS. Macrolides are biologically rational and commonly used for neonatal U. parvum meningitis; however, the optimal regimen and duration remain unclear due to limited and heterogeneous case-based evidence.</t>
+          <t>Honey bee gut microbiome studies have primarily emphasized bacteria, leaving fungal communities comparatively overlooked despite their ecological and functional importance. Whole-genome shotgun metagenomics of Apis cerana and Apis mellifera revealed fungal assemblages dominated by Ascomycota, with Basidiomycota and Microsporidia in minor proportions, alongside gut bacterial communities composed mainly of Pseudomonadota, Bacillota, and Actinomycetota. The bacterial diversity was markedly higher in A. mellifera (Shannon = 5.90; Simpson = 0.98) than in A. cerana (Shannon = 4.01; Simpson = 0.94; p &gt; 0.05), while fungal diversity remained comparable between species (p &gt; 0.05). Beta-diversity analyses revealed strong host-specific clustering for both bacterial (PERMANOVA R2 = 0.7989, p &gt; 0.05) and fungal communities (R2 = 0.7218, p &gt; 0.05), indicating distinct microbial organization driven by host species. Bacterial-fungal co-occurrence patterns exhibited host-specific structuring, suggesting differential inter-kingdom community organization between A. cerana and A. mellifera. Linear Discriminant Analysis Effect Size (LEfSe) identified 93 discriminatory fungal taxa (45 enriched in A. cerana, 48 in A. mellifera), highlighting yeast-dominated signatures in A. mellifera and Basidiomycota-affiliated enrichments in A. cerana. KEGG and CAZy profiling revealed host- and kingdom-specific functional differences, with bacterial communities of A. mellifera showing distinct representation of carbohydrate metabolism and nutrient-cycling functions, while fungal communities exhibited a comparatively narrower functional repertoire. Together, these findings provide a high-resolution view of honey bee bacterial and fungal microbiomes, highlighting strong host-driven divergence in taxonomy, function, and cross-kingdom interactions.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>本研究旨在探討新生兒微小脲原體（*Ureaplasma parvum*）腦膜炎的臨床特徵、診斷與治療。研究分析了一例經腦脊髓液宏基因組定序（mNGS）確診的男嬰病例，並結合文獻回顧，共納入17例。結果顯示，該病臨床表現缺乏特異性，主要為發燒與抽搐，部分患兒血常規正常但腦脊髓液呈化膿性改變，常規治療效果不佳，診斷高度依賴mNGS。治療以大環內酯類藥物為主，多數預後良好。本研究的臨床意義在於，強調對於經驗性抗生素治療無效的新生兒腦膜炎，應及早進行腦脊髓液mNGS檢測以明確病因，並指導抗生素的精準使用。</t>
+          <t>本研究透過宏基因體定序（Shotgun metagenomics），深入探討東方蜜蜂（*Apis cerana*）與西方蜜蜂（*Apis mellifera*）腸道內細菌與真菌群落的組成與功能差異。研究發現，儘管細菌多樣性在不同蜂種間存在顯著差異，但兩者的真菌群落多樣性相當。分析顯示，兩種蜜蜂的細菌與真菌群落結構呈現強烈的宿主特異性，顯示宿主物種為微生物組成的主要驅動力。此外，透過 LEfSe 分析發現兩者在關鍵分類群（如西方蜜蜂的酵母菌與東方蜜蜂的擔子菌門）與代謝功能（如碳水化合物代謝）上具有顯著差異。本研究不僅填補了蜜蜂腸道真菌群落研究的空白，更揭示了跨界（細菌-真菌）的交互作用機制，對理解蜜蜂共生微生物的生態適應與演化具有重要的科學意義。</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42668932/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42671657/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>42669940</t>
+          <t>42671637</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Chemical, biological, and metagenomic profile of biofertilizers containing native forest and whey microbiota and enriched with macronutrients and micronutrients.</t>
+          <t>Body mass index-associated gut microbial taxa and functional pathways in women with benign and malignant breast disease.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Journal of the science of food and agriculture</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
+          <t>Breast cancer research and treatment</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>16S</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>131 個糞便檢體（包含良性疾病 23 例、高風險/非侵入性疾病 47 例、惡性腫瘤 61 例）</t>
         </is>
       </c>
       <c r="G18" t="b">
@@ -1387,836 +1377,848 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Biofertilizers are gaining interest as sustainable nutrient sources that enhance nutrient and soil biological quality. The chemical, biological, and metagenomic profiles of biofertilizers produced from native forest microbiota and acidic whey, and enriched with macronutrients and micronutrients through anaerobic fermentation, were evaluated. Fermentation of the biofertilizer base over 4 days increased pH (3.0-3.8) and decreased oxidation-reduction potential (ORP, 178 to -173 mV), while electrical conductivity (EC) remained stable (3.7-4.1 mS cm-1). After enrichment with macronutrients and micronutrients, 35 days of fermentation, and formulation of the model nutrient solution (MNS), pH stabilized around 4.8, and EC decreased to 1.72 mS cm-1. Most biofertilizers, when enriched individually, maintained negative ORP values; however, the increase in ORP observed in the MNS (140 mV) suggests that incorporating the copper-enriched biofertilizer may have contributed to more oxidizing conditions. Biological analysis suggested enhanced nutrient transformation, as revealed by chromatographic complexity in most enriched treatments. The 16S rRNA gene amplicon-based metagenomic profiling showed higher amplicon sequence variant (ASV)-level richness and taxonomic diversity in MNS (592 ASV records and 57 resolved genera) than in the unenriched biofertilizer (342 ASV records and 41 resolved genera). At the genus level, both profiles shared a dominant taxonomic backbone but showed measurable differences in relative abundance patterns (Bray-Curtis = 0.266). Fermentative taxa, including lactic-acid-bacteria-associated genera and Clostridium, dominated both biofertilizers. Mineral-source fermentation by native forest microbiota modified the chemical environment, increased microbial diversity and complexity, and enhanced biological indicators of nutrient transformation; these changes suggest potential for increased nutrient bioavailability. © 2026 Society of Chemical Industry.</t>
+          <t>Obesity is an established risk factor for breast cancer and is associated with alterations in gut microbial composition. We evaluated associations among body mass index (BMI), breast density, gut microbial diversity and composition and microbial functional pathways in women undergoing surgery for benign, high-risk/non-invasive, and invasive breast disease. Preoperative stool samples were collected from 131 women (median age 59) with benign (n = 23), high-risk/non-invasive (n = 47), or malignant (n = 61) disease. Shallow shotgun metagenomic sequencing was performed. Taxonomic profiling used Sourmash 4.2.4 (GTDBv207 reference database); functional profiling employed HUMAnN 3.6 with gene families mapped to MetaCyc pathways. α-diversity differed across diagnosis groups and inversely correlated with increasing BMI (Inverse Simpson p = 0.025). β-diversity differed by diagnosis group and BMI. No significant differences in diversity were observed based on age, menopausal status or mammographic breast density. BMI was also associated with enrichment of Dorea, Blautia, and Streptococcus species. Functional pathway profiling showed greater relative abundance of genes involved in NAD biosynthesis, folate metabolism, and aromatic amino acid metabolism pathways with higher BMI. Cross-referencing the most significant taxonomic and functional pathway findings suggested enrichment of Blautia species, via tryptophan metabolism, might link to NAD biosynthesis. In this study of women with benign, high-risk/non-invasive, and invasive breast disease, BMI was associated with distinct differences in gut microbial taxonomy and functional pathway profiles. These hypothesis-generating findings provide a rationale for future study to determine how the obesity-associated microbiome contributes to breast cancer development. Not applicable.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>本研究旨在評估由天然森林微生物與酸乳清製成、並富含大與微量營養素之生物肥料在發酵過程中的化學、生物及微生物群落特徵。研究發現，發酵顯著改變了系統的 pH 值與氧化還原電位（ORP）。16S rRNA 擴增子定序分析顯示，相較於未富集營養的原始肥料，模型營養液（MNS）展現出更高的微生物物種豐富度與多樣性，但兩者皆由乳酸菌相關屬與梭菌屬（Clostridium）等發酵菌群主導。本研究證實，透過天然微生物發酵礦物能改善化學環境、提升微生物多樣性並促進營養轉化，具備提高植物營養生物有效性的潛力，對推動永續農業發展具有重要科學意義。</t>
+          <t>本研究探討體重指數（BMI）與乳房疾病患者腸道微生物組成及功能路徑的關聯。透過對 131 名術前女性患者進行淺層總體基因體定序，研究發現腸道菌相多樣性與 BMI 呈負相關。BMI 較高的受試者在細菌分類上顯現 *Dorea*、*Blautia* 及 *Streptococcus* 屬的富集；在功能路徑上，與 NAD 生物合成、葉酸及芳香族胺基酸代謝相關的基因表現顯著增加。特別是 *Blautia* 菌屬可能透過色胺酸代謝連結至 NAD 生物合成路徑。此研究結果證實 BMI 與腸道微生物特徵的顯著差異，並提出肥胖相關腸道菌群可能參與乳癌發展的機制假設，為未來針對該領域的病理研究提供了科學依據。</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42669940/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42671637/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>42671180</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Longitudinal development of infant oral ecosystem: salivary metabolomic, bacteriome, and virome dynamics in early infancy.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>mSystems</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>This prospective cohort study investigated the longitudinal development of the salivary bacteriome, virome, and metabolome during early infancy. We assessed the associations between oral bacteria, viruses, and metabolites from 10 mother-infant dyads, with oral samples collected at 1 and 2 years of age. Forty saliva and plaque samples underwent untargeted metabolomic analysis, and infant saliva samples underwent metagenomic sequencing. Maternal salivary and plaque metabolomic profiles remained largely stable, whereas infant profiles were clearly separated from maternal profiles and changed with age. Notably, infant dental plaque metabolism underwent more substantial changes from year 1 to year 2 than saliva, with age-dependent metabolite shifts mainly involving energy, amino acid, nucleotide, and lipid metabolic pathways. Our findings also revealed significant developmental shifts in salivary bacteriome, virome, and functional pathway profiles during early childhood. The most abundant oral bacteria in early life, comprising over 75% of total abundance, included Veillonella, Streptococcus, Rothia, Prevotella, Neisseria, and Actinomyces species. While human viruses like Roseolovirus were detected, bacteriophages constituted the majority of the virome. Comparing infants at year 1 and year 2, we identified differentially abundant bacteria, viruses, metabolic functional pathways, and specific metabolites. We observed associations between bacteria and viruses, noting that these cross-kingdom relationships attenuated as infants grew. The study results underscore the complex and dynamic development of the oral microbiome, virome, and metabolome during early childhood.IMPORTANCEThe human oral cavity undergoes substantial microbial and metabolic development during early childhood, yet the temporal changes in the infant oral ecosystem remain incompletely understood. In this study, we longitudinally profiled the salivary metabolome, bacteriome, and virome of infants at 1 and 2 years of age. We demonstrated that the infant oral metabolome undergoes substantial developmental shifts, particularly in pathways related to energy, amino acid, and lipid metabolism; whereas maternal metabolic profiles remained stable over the same period. Furthermore, our results revealed the dynamic assembly of infant salivary virome and bacteriome and their associations with the functional pathways and metabolites. These findings provide new insights into the complex and dynamic development of the oral microbiome, virome, and metabolome in early infancy.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>AI 分析失敗，請參考英文原文。</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42671180/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>42671179</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Novel insights into Radix Pseudostellariae saponins assist Mycoplasma gallisepticum attenuated vaccine to enhance the immunoprotection of chicken.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>mSystems</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Mycoplasma gallisepticum (MG) is a major pathogen causing chronic respiratory disease in chickens, and the MG-attenuated vaccine (MGAV) often fails to induce effective mucosal immunity. Radix Pseudostellariae saponins (RPS), important bioactive components of the traditional Chinese herb, have been utilized for immunomodulation, although the underlying mechanisms remain to be elucidated. In this study, chickens were randomly assigned to groups receiving intranasal MGAV alone, MGAV plus RPS at different doses, or appropriate controls. Serum, tracheal mucosa, and respiratory lavage samples were collected for antibody measurement, cytokine profiling, histological assessment, and metagenomic/metabolomic analyses. RPS significantly increased MG-specific antibody levels and enhanced expression of the immunomodulatory cytokines, while suppressing that of pro-inflammatory factors. It also promoted tracheal mucosal integrity by elevating goblet cell numbers and mucosal epithelial height. Through metagenomic and metabolomic analysis, RPS was found to enrich the respiratory bacterium Lactobacillus sp. UMNPBX13, which was positively correlated with the metabolite phosphatidylcholine (PC). Intranasal administration of Lactobacillus increased mucin 2 (MUC2) and PC levels in tracheal mucosa. Similarly, PC combined with MGAV enhanced mucosal immunity by modulating cytokines and increasing MG-specific antibodies. These findings demonstrate that RPS enhances MGAV-induced respiratory mucosal immunity and provides a novel adjuvant strategy for improving poultry respiratory disease vaccines by modulating the respiratory microbiota, specifically through enrichment of Lactobacillus sp. UMNPBX13, which promotes PC production.IMPORTANCEMycoplasma gallisepticum (MG) constitutes a notable challenge to poultry health. Although the MG-attenuated vaccine (MGAV) is widely used for disease control, it often fails to induce robust mucosal immunity. Here, we demonstrate that intranasal co-administration of Radix Pseudostellariae saponins (RPS) with MGAV augments mucosal immunoprotection. Integrated metagenomic and metabolomic analyses revealed that RPS enriches respiratory Lactobacillus, which in turn promotes the production of its key metabolite phosphatidylcholine (PC), thereby supporting mucosal immune enhancement. These findings offer a promising strategy for improving poultry vaccine efficacy and may provide a basis for future exploration of mucosal vaccination approaches in other animal species.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>AI 分析失敗，請參考英文原文。</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42671179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>42671175</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Laccase-mediated biotransformation potential for fluorinated compounds by geographically diverse human gut microbiota.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>mBio</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>metagenomics</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1,578 個人類腸道總體基因體 (human gut metagenomes)</t>
+        </is>
+      </c>
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>The growing prevalence of synthetic organofluorine substances in agrochemicals, food packaging, and consumer products has led to increasing gastrointestinal exposure, with potential consequences for human health. Despite the extreme stability of fluorinated compounds, several microbial pathways for their transformation are known, including those involving laccases, a type of multicopper oxidase. However, the functionality of laccases in the gut microbiome, a natural contact point between food-associated chemicals and microbial biotransformation pathways, is poorly defined. Through a multi-study analysis of 1,578 human gut metagenomes spanning a global gradient from hunter-gatherer societies to industrialized urban populations, we found that laccase-coding gene homologs are widely distributed in the human gut microbiome. We identified a significant association between both the abundance and phylogenetic diversity of laccase homologs and the degree of urbanization. As human gut microbial laccase activity has not been experimentally demonstrated, eight gut metagenome-derived laccases were heterologously expressed and screened for activity with a redox mediator system. Six of the eight laccases demonstrated activity. One of these gut microbial laccases, derived from Veillonella, and three previously characterized laccases were then tested for their capacity to deplete 11 different food-associated chemicals. The Veillonella laccase depleted the agrochemicals cyflumetofen and fluazinam, as well as the industrial chemical bisphenol AF, to a lesser extent. By linking global gut metagenomes with activity assays, this work demonstrates the untapped potential of mining human gut metagenomes for laccases and other microbial enzymes that can actively modify various agricultural and industrial chemicals.IMPORTANCEAs adverse effects of fluorinated compounds on human health are emerging, the responsible enzymes from the human gut microbiome of geographically diverse human cohorts mediating interactions with fluorinated compounds in the gastrointestinal tract remain poorly characterized. In a multi-study analysis of publicly available microbiome sequencing data, we linked the abundance, diversity, and phylogeny of laccases within the gut microbiome to the degree of urbanization of human cohorts and experimentally demonstrated the ability of these laccases to deplete a range of food-associated fluorochemicals. Another significant contribution of our study is in the integration of rural catchment areas as a quantitative metric of urbanization in gut microbiome metagenomics and enzyme activity surveys.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>本研究旨在探討人類腸道菌群中漆酶（laccases）對環境氟化化合物的生物轉化潛力。研究分析了全球不同城市化程度的1,578個腸道總體基因體，發現漆酶同源基因廣泛存在，且其豐度與系統發育多樣性與城市化程度呈顯著正相關。實驗進一步異源表達了8種源自腸道總體基因體的漆酶，其中6種具備活性；源自*Veillonella*菌的漆酶能有效降解特定農藥（cyflumetofen、fluazinam）及工業化學品（雙酚AF）。此研究結合全球總體基因體數據與活性篩選，證實了腸道菌群酶降解農業與工業化學污染物的潛力，具備重要的環境健康與科學意義。</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42671175/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>42672116</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Small serine recombinases are markers for antiphage defense system discovery.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PLoS biology</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>metagenomics, others</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G22" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Renewed interest in phage therapy has highlighted a need to understand how bacteria subvert phage infection through antiphage defense systems. Traditionally, strategies to identify antiphage defense systems lack throughput or have limitations for bacterial species where antiphage defense systems are understudied. Herein, we developed a bioinformatic pipeline that uses a small serine recombinase to identify known and unknown antiphage defense systems. Using this approach to query reference genomes and metagenomes, we show that small serine recombinase genes are genetically linked to antiphage defense systems and serve as bait for finding these systems across diverse bacterial phyla. Using co-transcription predictions and statistical analysis of protein domain abundances, we experimentally validated our bioinformatic approach by discovering that KAP P-loop NTPases are fused to putative antiphage domains and reinforce prokaryotic Schlafen proteins as a new class of antiphage defense. Our work shows that small serine recombinases are a reliable genetic marker for the discovery of antiphage defenses across diverse bacterial phyla.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>本研究開發了一套生物資訊分析流程，利用「小型絲氨酸重組酶（small serine recombinases）」作為基因標記，以搜尋已知及未知的細菌抗噬菌體防禦系統。團隊透過檢索參考基因體與總體基因體，證實該重組酶與防禦系統具備強烈的遺傳連鎖，並藉此成功鑑定出 KAP P-loop NTPases 相關結構域和原核 Schlafen 蛋白質為新型抗噬菌體防禦系統。此發現證實小型絲氨酸重組酶是跨菌門尋找防禦系統的可靠標記，對理解細菌免疫機制及推動噬菌體療法具有重要科學價值。</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42672116/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>42674139</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Cellulose/polyester-blended microplastics amplify plastisphere pathogen and antibiotic resistome risks.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Bioresource technology</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>9</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>16S, metagenomics</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>4種微塑料材料（AP、PE、PP、PS）（具體重複樣本數量未提及）</t>
+        </is>
+      </c>
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Microplastics (MPs) are important vectors for antibiotic resistance genes (ARGs) in anaerobic digestion systems, yet the risks posed by cellulose/polyester-blended materials remain poorly understood. In this study, commercial airlaid paper (AP; 45 % cellulose and 55 % polyester), polyethylene (PE), polypropylene (PP), and polystyrene (PS) were incubated in anaerobic reactors for 60  days. Biofilm characterization, extracellular polymeric substances (EPS) analysis, 16 S rRNA sequencing, and metagenomics were used to compare plastisphere formation, microbial assembly, ARG/mobile genetic element (MGE) profiles, and potential pathogen composition. Owing to its fibrous structure and bioavailable cellulose fraction, AP exhibited the highest biofilm biomass and EPS content. In contrast, PE, PP, and PS induced stronger interfacial stress, especially PS, as indicated by increased reactive oxygen species, lactate dehydrogenase release, and enrichment of oxidative stress, SOS response, and multidrug efflux pump related genes. Metagenomic analysis showed that fully synthetic MPs mainly enriched multidrug resistance genes, whereas AP selectively enriched polymyxin resistance genes, particularly Mcr-5.1 and Mcr-5.2. AP also exhibited the highest ARG-MGE co-localization rate (12.7 %) and antibiotic resistance risk. Overall, these findings identify polymer composition as a key factor shaping plastisphere resistome assembly and indicate that cellulose/polyester-blended materials require specific consideration in sludge-associated antimicrobial resistance risk assessments.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>本研究旨在評估纖維素/聚酯混合微塑料（如無塵紙 AP）在厭氧消化系統中，相較於傳統合成微塑料（PE、PP、PS）對「塑料圈」病原菌與抗藥性基因（ARGs）的傳播風險。研究顯示，AP 因具纖維結構及可利用的纖維素，其生物膜量和胞外聚合物最高。不同於合成微塑料主要富集多重抗藥基因，AP 選擇性富集多黏菌素抗藥基因（Mcr-5.1/5.2），且其抗藥基因與行動遺傳元件的共定位率達 12.7%，具最高的抗藥性風險。本研究證實聚合物成分是形塑塑料圈抗藥性的關鍵，強調污泥抗藥性評估應特別納入混合型微塑料。</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42674139/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>42673827</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Elevated water levels drive greenhouse gas mitigation in the riparian zone profile.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Journal of environmental management</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>metagenomics</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Wetlands are critical for climate regulation, with their hyporheic zone serving as sensitive interfaces for groundwater-soil-atmosphere exchange. These zones are active hotspots for carbon-nitrogen cycling and greenhouse gas (GHG) emissions (CO2, CH4, N2O), yet the impact of water level fluctuations on these emissions and their microbial drivers in freshwater wetlands remains poorly understood. This study investigated the spatiotemporal dynamics of GHG emissions and carbon-nitrogen coupling processes along riparian soil profiles of Baiyangdian Lake during water level fluctuations. Employing static chamber measurements, microcosms, quantitative PCR, Metagenome-Assembled genome (MAG) analyses, and Structural Equation Modeling (SEM), we observed that GHG emissions were significantly affected by water level fluctuations. Specifically, CO2 and N2O fluxes, as well as CO2 production potential were significantly lower at high-water-level conditions. Water level also emerged as a key driver of microbial community structure, with Methylococcaceae and Methanosarcinaceae as key regulators of CH4 emission, and Anaeromyxobacteraceae as central to N2O dynamics. A high-quality Methylomirabilales-like MAG, possessing the complete pathway for coupled nitrate reduction and methane oxidation, was identified. Its abundance negatively correlated with water level, suggesting that these C-N coupling bacteria contribute to reducing GHG emissions. This study provides crucial theoretical insights and identifies microbial targets for mitigating wetland GHG emission through hydrological management.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>本研究探討白洋淀湖泊消落帶在水位波動下，溫室氣體（GHG）排放與碳氮耦合過程的時空動態及微生物驅動機制。研究發現，高水位條件能顯著降低二氧化碳（CO2）和一氧化二氮（N2O）的排放通量。水位變化是形塑微生物群落結構的關鍵，其中Methylococcaceae、Methanosarcinaceae與Anaeromyxobacteraceae分別調控甲烷（CH4）和N2O的動態。此外，研究重構出一個高質量的Methylomirabilales總體基因體組裝基因體（MAG），該菌具備硝酸鹽還原與甲烷氧化耦合的完整途徑，其豐度與水位呈負相關，證實此類碳氮耦合細菌有助於減少溫室氣體排放。本研究為透過水文管理減緩濕地溫室氣體排放提供了關鍵的理論依據與微生物靶點。</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42673827/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>42674953</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Retraction notice to "Environmental impact of lignocellulosic wastes and their effective exploitation as smart carriers - A drive towards greener and eco-friendlier biocatalytic systems" [Sci. Total Environ. 722 (2020) 137903].</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>The Science of the total environment</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G25" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>無提供摘要。</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>本文為學術期刊《Science of the Total Environment》針對 2020 年刊登之文章「Environmental impact of lignocellulosic wastes and their effective exploitation as smart carriers - A drive towards greener and eco-friendlier biocatalytic systems」所發布的正式撤稿聲明。由於原始研究內容已被撤回，該聲明並未包含任何實驗數據、樣本分析或科學發現。撤稿通常源於作者發現數據錯誤、倫理問題或研究結論存在不可重現的重大瑕疵，因此該文不具備生物醫學參考價值。</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42674953/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>42671210</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Sulfur metabolism and immune-microbial networks across oral niches in periodontal disease.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Microbiology spectrum</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>16S</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Volatile sulfur compounds (VSCs) integrate microbial metabolism with local inflammation in periodontal disease. We profiled five oral niches (saliva, tongue, subgingival, supragingival, and interdental plaque) across clinical health, gingivitis, and periodontitis by combining direct VSC measurements (subgingival and oral headspace H2S/CH3SH), functional cysteine/methionine degradation assays, 16S rRNA profiling, gingival crevicular fluid cytokines, and targeted qPCR. Subgingival H2S concentrations were significantly elevated in periodontitis after adjusting for age, sex, plaque index, and subgingival bacterial load (β = 1.24, P = 0.03), and tracked shifts in community composition and the cytokine milieu. Oral headspace CH3SH increased with disease, whereas headspace H2S showed a bimodal pattern (health and periodontitis). In cysteine assays, subgingival and tongue biofilms were the most efficient H2S producers per mg protein; this ranking was preserved after normalization to total bacteria by qPCR. Metagenome predictions indicated enhanced sulfur metabolism in disease, particularly in subgingival plaque, with relative enrichment of SAM-cycle/methionine biosynthesis pathways in health. Methionine degradation to CH3SH increased with disease severity, shifting from subgingival sites in health to interdental/supragingival plaque in disease, and occurring most frequently in saliva. Correlation networks revealed niche- and diagnosis-specific coupling among VSCs, cytokines, and taxa, including associations of Capnocytophaga, Fusobacterium, Prevotella, and Corynebacterium, with IL-1β, IL-4, IL-8, and MCP-1. Together, these data identify the subgingival crevice as a disproportionate source of sulfide and show that sulfur metabolism is spatially organized and disease-responsive. We show that subgingival H2S as a functional marker that integrates microbial dysbiosis and inflammation.IMPORTANCEWe asked how metabolism, microbes, and immunity fit together during gum disease. Using a systems approach across five oral sites, we combined sulfur metabolite measurements, functional assays, microbiome profiling, and cytokine data, and analyzed them as one network. The result is a comprehensive map showing that sulfur metabolism is spatially organized, disease-responsive, and tightly coupled to local immune signals, with the subgingival niche playing an outsized role. Further, this integrated readout turns sulfur metabolism into a useful window on dysbiosis and inflammation and offers a path toward simple monitoring of periodontal disease, such as point-of-care sensors detecting subgingival hydrogen sulfide or methanethiol, or functional assays in which a methionine rinse is followed by measurement of oral headspace gases to assess microbial sulfur metabolism.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>本研究旨在探討牙周病不同階段中，五個口腔微生態棲地（唾液、舌苔、齦下、齦上及牙縫菌斑）的硫代謝、微生物群與局部免疫反應之關聯。研究發現，齦下硫化氫（H2S）濃度在牙周病患者中顯著升高，且與菌群結構移形及細胞激素變化密切相關，其中齦下與舌苔生物膜具有最強的H2S產生效率。網路分析更揭示了揮發性硫化物（VSCs）、細胞激素與特定菌屬（如 *Fusobacterium* 與 *Prevotella*）之間存在棲地特異性的耦合關係。本研究證實齦下H2S可作為整合微生態失調與發炎反應的功能性指標，為未來開發非侵入性牙周病即時監測工具（如氣體感測器）奠定了重要科學基礎。</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42671210/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>42673455</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kelp forest collapse alters the reef microbiome and associated metabolome.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Proceedings of the National Academy of Sciences of the United States of America</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>metagenomics, metabolomics</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>In many temperate regions experiencing rapid ocean warming, kelp forests are being replaced by low-lying turf algae. Yet, whether this change in biogenic habitat alters reef-level microbial structure and function, including carbon and nutrient cycling, remains largely unknown. Here, we integrated shotgun metagenomics and nontargeted metabolomics to reveal that kelp forest loss alters the composition of the reef microbial community and its associated biochemical machinery, resulting in distinct metabolomes and microbially driven elemental use/transformations on kelp- vs. turf-dominated reefs. Our results therefore suggest that microbes play a key role in shaping kelp forest ecosystem functioning. Further, they demonstrate that human-induced ocean warming has cascading effects on microbially mediated chemistry, with implications for coastal carbon storage and nutrient regeneration.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>本研究探討暖化導致的海藻林（Kelp forest）退化為草皮藻（Turf algae）對珊瑚礁生態系中微生物群落結構及代謝功能的影響。研究透過整合宏基因組學（shotgun metagenomics）與非標靶代謝組學分析，發現海藻林與草皮藻主導的礁體在微生物組成、生物化學機制及元素循環方面存在顯著差異。研究結果顯示，微生物在調節海藻林生態功能中扮演關鍵角色，且氣候暖化會引發微生物介導的化學連鎖反應。此發現對於理解沿海碳儲存機制及營養鹽再生具有重要的科學意義，強調了微生物群落功能變異在生態系統轉型過程中的關鍵地位。</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42673455/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>42673474</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Evidence for endemism and local adaptation in Antarctic soil bacteria.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Proceedings of the National Academy of Sciences of the United States of America</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>metagenomics, small genome</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>未提及（原文僅提及使用全球性 metagenomic 資料集與菌株基因體比較，未明確標示具體樣本總數）</t>
+        </is>
+      </c>
+      <c r="G28" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Antarctic soils represent one of the most extreme environments for microbial life on Earth, yet they harbor heterogeneous and diverse microbial communities. Biologists have long hypothesized that Antarctic microorganisms are unique from those found on other continents due to the extreme geographic isolation and the cold, dry, and challenging conditions typical of Antarctica. To test this hypothesis, we focused on a cosmopolitan bacterial genus, Arthrobacter, that is widely distributed across global soils. We first profiled a global metagenomic dataset from both Antarctic and non-Antarctic surface soils to quantify the distributions of Arthrobacter strains. Despite high strain-level diversity, 90% of the strains found in the Antarctic soils were only found on the continent. We then used cultivation-based phenotypic analyses and strain-level genomic comparisons to assess how Antarctic strains and non-Antarctic strains differ in their traits and environmental preferences. Not only did we find evidence of endemism, but Antarctic Arthrobacter also have genomic characteristics and environmental tolerances that suggest they are uniquely adapted to Antarctic conditions.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>本研究旨在探討南極土壤微生物是否因地理隔離及極端環境，而演化出獨特的特有種與在地適應性。研究聚焦於全球分布廣泛的節桿菌屬（*Arthrobacter*），透過分析全球土壤宏基因組數據，發現南極土壤中高達 90% 的菌株具有地理特有性。進一步結合菌株全基因體組裝與表型分析，證實南極節桿菌在基因組特徵與環境耐受性上，展現出顯著的區域適應性。此發現證實了南極微生物群落的高度獨特性，對於理解全球微生物的生物地理分布規律，以及極端環境下生物的演化策略具有重要的科學意義。</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42673474/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>42669365</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>In situ fermentation-coupled symbiosis of polyphosphate-accumulating organisms and microalgae for efficient nutrient removal and sludge reduction in low carbon-to-nitrogen ratios wastewater.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Bioresource technology</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>9</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>metagenomics</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G29" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Microalgae-bacteria consortia (MBC) integrated with polyphosphate-accumulating organisms (PAOs) treat wastewater sustainably, but face excess sludge and light-dark mismatch issues. This study developed in situ fermentation-coupled photo simultaneous nitrification-denitrification phosphorus removal (F/P-SNDPR) systems by incorporating fermentative PAOs into MBC for low carbon-to-nitrogen ratios (C/N) wastewater. The effects of light-dark cycles on nutrient removal, sludge fermentation, and microbial dynamics were investigated. Under an optimal 16 h dark/8h light cycle, the F/P-SNDPR system achieved &gt; 83% nitrogen and &gt; 95% phosphorus removal, with low sludge production (312.21 mgVSS/d) and low net CO2 emissions. Prolonged light and dark phases promoted early microbial apoptosis and subsequent cell lysis, respectively, thereby facilitating fermentation. Combined dark duration and photoinhibition suppress nitrite-oxidizing bacteria, enabling stable partial nitrification. Flow cytometry and metagenomic results identified Candidatus Phosphoribacter as the primary fermentative microorganism. Its fermentation-associated genes, including LivFGHMK and Pta, facilitated volatile fatty acid (VFA) production during the dark phase. The generated VFA supported Candidatus Accumulibacter/Candidatus Competibacter to enhance nutrient removal, driven by key functional genes for polyphosphate metabolism (Ppk and Ppx) and denitrification (NirS, NirK, and NosZ). Overall, The F/P-SNDPR system offers a low-carbon strategy for efficient low C/N wastewater treatment without mechanical aeration or external carbon addition, while reducing sludge production.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>本研究開發了一種結合原位發酵與光合同步硝化-反硝化除磷的系統（F/P-SNDPR），旨在解決低碳氮比（C/N）廢水處理中常見的過量污泥與能耗問題。研究發現，在優化的16小時黑暗與8小時光照循環下，該系統展現了卓越的除氮（&gt;83%）與除磷（&gt;95%）效率，且顯著降低了污泥產量。宏基因體分析顯示，*Candidatus Phosphoribacter* 是關鍵的發酵菌株，透過黑暗期的發酵作用產生揮發性脂肪酸（VFA），進而支持除磷菌（*Candidatus Accumulibacter/Competibacter*）的代謝與除磷脫氮功能。此技術無需額外添加碳源或機械曝氣，為低碳廢水處理提供了一種具備經濟效益與環境永續性的綠色策略。</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42669365/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>42669940</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Chemical, biological, and metagenomic profile of biofertilizers containing native forest and whey microbiota and enriched with macronutrients and micronutrients.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Journal of the science of food and agriculture</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>16S</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G30" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Biofertilizers are gaining interest as sustainable nutrient sources that enhance nutrient and soil biological quality. The chemical, biological, and metagenomic profiles of biofertilizers produced from native forest microbiota and acidic whey, and enriched with macronutrients and micronutrients through anaerobic fermentation, were evaluated. Fermentation of the biofertilizer base over 4 days increased pH (3.0-3.8) and decreased oxidation-reduction potential (ORP, 178 to -173 mV), while electrical conductivity (EC) remained stable (3.7-4.1 mS cm-1). After enrichment with macronutrients and micronutrients, 35 days of fermentation, and formulation of the model nutrient solution (MNS), pH stabilized around 4.8, and EC decreased to 1.72 mS cm-1. Most biofertilizers, when enriched individually, maintained negative ORP values; however, the increase in ORP observed in the MNS (140 mV) suggests that incorporating the copper-enriched biofertilizer may have contributed to more oxidizing conditions. Biological analysis suggested enhanced nutrient transformation, as revealed by chromatographic complexity in most enriched treatments. The 16S rRNA gene amplicon-based metagenomic profiling showed higher amplicon sequence variant (ASV)-level richness and taxonomic diversity in MNS (592 ASV records and 57 resolved genera) than in the unenriched biofertilizer (342 ASV records and 41 resolved genera). At the genus level, both profiles shared a dominant taxonomic backbone but showed measurable differences in relative abundance patterns (Bray-Curtis = 0.266). Fermentative taxa, including lactic-acid-bacteria-associated genera and Clostridium, dominated both biofertilizers. Mineral-source fermentation by native forest microbiota modified the chemical environment, increased microbial diversity and complexity, and enhanced biological indicators of nutrient transformation; these changes suggest potential for increased nutrient bioavailability. © 2026 Society of Chemical Industry.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>本研究旨在評估由天然森林微生物與酸乳清製成、並富含大與微量營養素之生物肥料在發酵過程中的化學、生物及微生物群落特徵。研究發現，發酵顯著改變了系統的 pH 值與氧化還原電位（ORP）。16S rRNA 擴增子定序分析顯示，相較於未富集營養的原始肥料，模型營養液（MNS）展現出更高的微生物物種豐富度與多樣性，但兩者皆由乳酸菌相關屬與梭菌屬（Clostridium）等發酵菌群主導。本研究證實，透過天然微生物發酵礦物能改善化學環境、提升微生物多樣性並促進營養轉化，具備提高植物營養生物有效性的潛力，對推動永續農業發展具有重要科學意義。</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42669940/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>42668932</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Ureaplasma parvum meningitis in neonates: A retrospective case study and literature review.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Pakistan journal of medical sciences</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>metagenomics</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1 例新生兒病例與文獻回顧之 16 例（共計 17 例）</t>
+        </is>
+      </c>
+      <c r="G31" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>To investigate the clinical characteristics and advances in diagnosis and treatment of neonatal Ureaplasma parvum (U. parvum) meningitis. Clinical manifestations, diagnosis, treatment, and follow-up data of a neonate with persistent fever, normal blood routine, but persistently abnormal cerebrospinal fluid (CSF) results due to U. parvum meningitis were retrospectively analyzed. A literature review was conducted to identify relevant studies reporting on neonatal U. parvum meningitis published until May 2025. A male infant born at 35+2 weeks of gestation with eight hours of premature rupture of membranes (PROM) was admitted at 17 days of age with persistent fever. The routine blood test was normal, while the CSF suggested purulent meningitis. Empirical treatment was ineffective, and metagenomic next-generation sequencing (mNGS) of CSF confirmed U. parvum meningitis. The infant recovered after three weeks of azithromycin treatment, but a language delay was found at two-year follow-up. The literature review identified 16 previously reported cases of U. parvum meningitis, which were combined with the current case, totaling 17 cases. Main manifestations included fever and convulsions, or initial circulatory and respiratory symptoms. CSF in the included studies showed leukocytosis, decreased glucose, and elevated protein. Diagnosis was mainly based on mNGS, and the predominant treatment consisted of macrolides, sometimes combined with quinolones, for 3-10 weeks. Two patients relapsed after drug withdrawal, and one had elevated liver enzymes. Major neurological complications included lateral ventricular dilatation and hydrocephalus, cerebral hemorrhage, infarction, malacia, and herniation. Most cases had a favorable prognosis, with rare developmental delay. Clinical manifestations of neonatal U. parvum meningitis are nonspecific. Some patients present with normal blood routine but purulent CSF. U. parvum meningitis should be suspected in patients with poor response to empirical antibiotics and confirmed by CSF mNGS. Macrolides are biologically rational and commonly used for neonatal U. parvum meningitis; however, the optimal regimen and duration remain unclear due to limited and heterogeneous case-based evidence.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>本研究旨在探討新生兒微小脲原體（*Ureaplasma parvum*）腦膜炎的臨床特徵、診斷與治療。研究分析了一例經腦脊髓液宏基因組定序（mNGS）確診的男嬰病例，並結合文獻回顧，共納入17例。結果顯示，該病臨床表現缺乏特異性，主要為發燒與抽搐，部分患兒血常規正常但腦脊髓液呈化膿性改變，常規治療效果不佳，診斷高度依賴mNGS。治療以大環內酯類藥物為主，多數預後良好。本研究的臨床意義在於，強調對於經驗性抗生素治療無效的新生兒腦膜炎，應及早進行腦脊髓液mNGS檢測以明確病因，並指導抗生素的精準使用。</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42668932/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>42667435</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>From traditional retting to precision bioprocessing: microbial ecology, enzymatic selectivity, and systems biology of jute retting.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Antonie van Leeuwenhoek</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>未提及</t>
+        </is>
+      </c>
+      <c r="G32" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Jute is one of the world's most important lignocellulosic fibre crops, yet its commercial value remains highly dependent on retting, a biologically mediated fibre extraction process still largely governed by empirical practices and variable environmental conditions. Recent advances in microbial ecology, enzymology, molecular biology, and bioprocess engineering have transformed retting from a traditional post-harvest operation into a controllable lignocellulosic bioconversion process. This review synthesizes current understanding of the structural organization of jute bast fibres, selective degradation of plant cell-wall polymers, microbial succession, extracellular enzyme networks, and physicochemical factors regulating fibre liberation. It highlights the coordinated interactions among cell-wall architecture, microbial communities, enzyme specificity, and environmental conditions that collectively determine retting efficiency and fibre quality. Emerging precision retting strategies, including defined microbial consortia, enzyme-assisted retting, ribbon retting, controlled processing systems, and water-efficient technologies, are critically evaluated for their potential to improve process reproducibility, fibre quality, and environmental sustainability. The review also examines metagenomics, metatranscriptomics, metaproteomics, metabolomics, systems biology, and artificial intelligence as enabling technologies for microbiome-guided process monitoring, predictive modelling, and digital decision support. Furthermore, this review discusses the integration of precision retting within circular bioeconomy frameworks through resource recovery, pollution mitigation, climate-resilient processing, and lignocellulosic biorefineries. Key knowledge gaps, including limited understanding of microbial interactions, lack of standardized microbial consortia, insufficient process-monitoring tools, fragmented multi-omics datasets, and challenges in industrial scale-up, are identified. Overall, this review presents a systems-level framework for advancing jute retting toward standardized, predictive, and environmentally sustainable precision bioprocessing.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>本綜述探討黃麻漚麻（retting）技術從傳統經驗法轉向精準生物加工的最新進展。文章系統性整合了黃麻韌皮纖維結構、微生物群落演替、胞外酶網絡及物理化學調控因子的研究，並評估了特定微生物菌群、酶輔助漚麻及控溫系統等精準策略。同時，探討了多體學技術（如總體基因體學、代謝組學等）與人工智慧在過程監測與預測模型中的應用潛力。最後，文章指出了微生物相互作用不明、缺乏標準化菌群及產業化放大等關鍵知識空白，為實現標準化、可預測且環保的精準黃麻生物加工提供了系統性框架，對促進循環生物經濟具有重要科學意義。</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42667435/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>42666020</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Decadal Resampling Reveals Widespread Increases in Soil Microbial Diversity Associated With Nitrogen Deposition.</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Global change biology</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D33" t="n">
         <v>12</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>metagenomics</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>38 個森林與草原生態系的土壤檢體（分別於 2009 年與 2019 年進行兩次重現採樣）</t>
         </is>
       </c>
-      <c r="G19" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" t="inlineStr">
+      <c r="G33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr">
         <is>
           <t>Simulated manipulation experiments, such as nitrogen addition to mimic atmospheric nitrogen deposition, are widely used in global change research. However, experimental manipulations may differ from real-world environmental change in their intensity, duration, and co-occurrence, leaving long-term changes in soil microbial communities and soil health insufficiently understood. To address this gap, we resampled soils from 38 forest and grassland ecosystems across eastern China in 2009 and 2019 and assessed microbial taxonomic and functional diversity using shotgun metagenomics. Microbial diversity increased by 17% over the decade, accompanied by clear shifts in community composition. Among the environmental variables considered, nitrogen deposition (~19 kg nitrogen ha-1 year-1 across ecosystems) was the strongest predictor of changes in seven of 12 microbial community metrics. Larger nitrogen deposition was also associated with increased relative abundances of nitrogen-cycling genes and reduced spatial turnover in microbial community composition. These effects were consistent with a potential alleviation of nitrogen limitation and weakening of deterministic community assembly, although these mechanisms could not be directly established. In addition, increases in genes associated with carbon degradation and phosphorus cycling, together with declines in the relative abundances of pathogens, antibiotic resistance genes, and DNA viruses, coincided with the raise of the composite soil health index. Our findings demonstrate widespread decadal increases in soil microbial diversity and soil health across eastern China, with nitrogen deposition emerging as their strongest environmental factor. These results highlight that microbial responses to long-term ambient environmental change can differ markedly from responses inferred from short-term or high-intensity manipulation experiments.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>本研究旨在探討真實世界中長期環境變化（如大氣氮沉降）對土壤微生物群落及土壤健康的影響。研究團隊於 2009 年與 2019 年，對中國東部 38 個森林和草原生態系的土壤進行重新採樣，並透過總體基因體學（shotgun metagenomics）分析其分類與功能多樣性。
 結果顯示，十年間土壤微生物多樣性顯著提升了 17%。在眾多環境因子中，氮沉降是預測群落變化的最強因子，其不僅促進了氮、碳、磷循環相關基因的豐度，更伴隨病原體、抗藥性基因及 DNA 病毒的減少，從而提升了綜合土壤健康指數。此研究證實了真實世界長期、低強度的環境變遷對生態系統的正面影響，並強調其微生物反應與短期高強度的人工模擬實驗結果存在顯著差異，對全球變遷研究具有重要科學價值。</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/42666020/</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>42667585</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Gut Microbiota from Patients with Long COVID Persisting for 2 Years Result in Alterations in Mice that Resemble Post-COVID Symptoms.</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Probiotics and antimicrobial proteins</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>16S, metagenomics, metabolomics</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>11位健康對照組受試者與11位長期新冠（LCOVID）患者（共22個糞便檢體），以及接受糞菌移植的抗生素處理（ABx）小鼠（具體小鼠數量未提及）。</t>
-        </is>
-      </c>
-      <c r="G20" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Human gut microbiota (GM) has been identified as a potentially important factor influencing the development of long COVID (LCOVID). The aim of this study was to understand the GM of LCOVID, which lasted for two years, in order to improve public awareness. Human gut microbiota and its metabolites were assessed in a healthy control group (n = 11) (HC) unexposed to SARS-CoV-2 and an LCOVID group (n = 11) in Hainan, China, using Shotgun metagenomics and liquid chromatography-mass spectrometry (LC-MS) of feces. The causal role of the microbiota in LCOVID was further validated by transplanting feces from the subjects into ABx mice using Histopathology and 16 S rRNA sequencing. Fecal microbial diversity was lower in patients with LCOVID compared with that in HC. Pro-inflammatory bacteria such as Streptococcus_salivarius and Streptococcus_parasanguinis increased, whereas anti-inflammatory bacteria such as Faecalibacterium_SGB15346 and Alistipes_onderdonkii decreased. Fecal metabolites from LCOVID were impaired in carbohydrate degradation, indole production, SCFA production, and fatty acid degradation. Transplantation of feces from patients with LCOVID into mice results in lung inflammation, intestinal inflammation, and anxiety. In addition, transplanted mice showed worse outcomes during Klebsiella_pneumoniae infections. Transplanted mice and the key bacteria Streptococcus_salivarius had the same worse outcomes in the D-IBS model by limb binding. GM from patients with LCOVID was altered significantly and sufficiently to promote LCOVID symptoms in mice, suggesting that it may be a potential therapeutic target.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>本研究旨在探討持續兩年之新冠後遺症（LCOVID）患者的腸道菌群特徵及其致病機制。研究結合宏基因組與代謝組學分析，發現LCOVID患者的腸道菌相多樣性降低，促炎菌（如唾液鏈球菌）增加，而抗炎菌減少，且碳水化合物與短鏈脂肪酸等代謝路徑受損。將患者糞便移植至小鼠後，成功誘發肺部與腸道發炎、焦慮行為，並加劇肺炎克雷伯菌感染與腸躁症症狀。此結果證實腸道菌群失衡是驅動LCOVID症狀的關鍵因子，具備作為潛在治療靶點的臨床科學價值。</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42667585/</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>42667435</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>From traditional retting to precision bioprocessing: microbial ecology, enzymatic selectivity, and systems biology of jute retting.</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Antonie van Leeuwenhoek</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>others</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>未提及</t>
-        </is>
-      </c>
-      <c r="G21" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Jute is one of the world's most important lignocellulosic fibre crops, yet its commercial value remains highly dependent on retting, a biologically mediated fibre extraction process still largely governed by empirical practices and variable environmental conditions. Recent advances in microbial ecology, enzymology, molecular biology, and bioprocess engineering have transformed retting from a traditional post-harvest operation into a controllable lignocellulosic bioconversion process. This review synthesizes current understanding of the structural organization of jute bast fibres, selective degradation of plant cell-wall polymers, microbial succession, extracellular enzyme networks, and physicochemical factors regulating fibre liberation. It highlights the coordinated interactions among cell-wall architecture, microbial communities, enzyme specificity, and environmental conditions that collectively determine retting efficiency and fibre quality. Emerging precision retting strategies, including defined microbial consortia, enzyme-assisted retting, ribbon retting, controlled processing systems, and water-efficient technologies, are critically evaluated for their potential to improve process reproducibility, fibre quality, and environmental sustainability. The review also examines metagenomics, metatranscriptomics, metaproteomics, metabolomics, systems biology, and artificial intelligence as enabling technologies for microbiome-guided process monitoring, predictive modelling, and digital decision support. Furthermore, this review discusses the integration of precision retting within circular bioeconomy frameworks through resource recovery, pollution mitigation, climate-resilient processing, and lignocellulosic biorefineries. Key knowledge gaps, including limited understanding of microbial interactions, lack of standardized microbial consortia, insufficient process-monitoring tools, fragmented multi-omics datasets, and challenges in industrial scale-up, are identified. Overall, this review presents a systems-level framework for advancing jute retting toward standardized, predictive, and environmentally sustainable precision bioprocessing.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>本綜述探討黃麻漚麻（retting）技術從傳統經驗法轉向精準生物加工的最新進展。文章系統性整合了黃麻韌皮纖維結構、微生物群落演替、胞外酶網絡及物理化學調控因子的研究，並評估了特定微生物菌群、酶輔助漚麻及控溫系統等精準策略。同時，探討了多體學技術（如總體基因體學、代謝組學等）與人工智慧在過程監測與預測模型中的應用潛力。最後，文章指出了微生物相互作用不明、缺乏標準化菌群及產業化放大等關鍵知識空白，為實現標準化、可預測且環保的精準黃麻生物加工提供了系統性框架，對促進循環生物經濟具有重要科學意義。</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42667435/</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>42664608</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Application-dependent effects of tea waste biochar on PFAS mobility and N2O and CH4 emissions in agricultural soil.</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Waste management (New York, N.Y.)</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>metagenomics</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>未提及（僅說明使用盆栽模擬系統「per pot」，未提及具體樣本或盆栽數量）</t>
-        </is>
-      </c>
-      <c r="G22" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Per- and polyfluoroalkyl substances (PFAS) in agricultural soils can migrate into crops and may alter soil greenhouse gas emissions, yet remediation strategies rarely address these risks simultaneously. This study evaluated tea waste biochar (TWB) produced at 400, 500, and 600 °C and applied at 5-20 g per pot by whole-soil mixing or surface-layer placement in a simulated PFAS-contaminated soil-leachate-plant system. Perfluorooctane sulfonate (PFOS) and perfluorooctanoic acid (PFOA) distributions, nitrous oxide (N2O) and methane (CH4) fluxes, and microbial responses were examined. TWB produced at 500 °C showed the most favorable combination of pore accessibility, surface hydrophobicity, and interfacial charge, with material-associated PFOS and PFOA enrichments of 0.12 and 0.57 μg/g, respectively. Whole-soil mixing with TWB-500 lowered soil and leachate PFAS levels and reduced PFAS concentrations in plant shoots by approximately 36% relative to the contaminated control. TWB treatments also reduced cumulative N2O emissions and enhanced net CH4 uptake. Metagenomic analysis showed lower relative abundances of genes associated with nitrogen fixation, ammonia oxidation, and several N2O-producing pathways, whereas CH4-cycling genes responded differently to the two application methods. Organic fluorine transformation genes were not enriched, indicating that PFAS control mainly resulted from physicochemical retention rather than enhanced microbial defluorination. Overall, TWB-500 can integrate PFAS stabilization with greenhouse gas management, but the optimal placement depends on the remediation objective: whole-soil mixing favors PFAS immobilization, whereas surface-layer application provides greater greenhouse gas mitigation.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>本研究旨在評估茶渣生物炭（TWB）在模擬的PFAS污染土壤-滲濾液-植物系統中，對於抑制全氟和多氟烷基物質（PFAS）遷移及減少溫室氣體（N2O和CH4）排放的雙重效應。研究發現，在500 °C下製備的TWB-500效果最佳。若將其均勻混合於全土中，可使植物地上部的PFAS濃度降低約36%，並顯著降低土壤和滲濾液中的PFAS含量。此外，TWB處理還減少了N2O累積排放並促進CH4淨吸收。總體基因體學分析顯示，與氮循環相關的基因豐度有所下降，解釋了N2O排放減少的機制；而有機氟降解基因並未富集，證實PFAS的控制主要源於物理化學阻控而非微生物去氟作用。此研究證明TWB-500能有效整合PFAS固化與溫室氣體管理，且施用方式（全土混合或表層施作）可依環境整治優先目標進行客製化調整。</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42664608/</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>42665338</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>PREVENT 1, a nationwide Swedish infant cohort for longitudinal gut microbiome profiling and early-life health outcomes: cohort profile.</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>BMJ open</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>metagenomics</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>253 位嬰兒（收集 253 份基線糞便檢體，其中 250 位提供至少 2 次檢體，241 位提供全部 3 次檢體）</t>
-        </is>
-      </c>
-      <c r="G23" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>PREVENT 1 is a nationwide, prospective Swedish infant cohort established to characterise gut microbiome development during the first 2 years of life and to relate microbial trajectories to feeding, infections, growth and everyday well-being. The study integrates repeated infant stool sampling with shotgun metagenomics analysis with aligned parental questionnaires, stool photographs and infant cry recordings collected at three approximately 3-month intervals for each infant. Families were recruited nationwide in Sweden from September 2023 through targeted digital channels. Eligible participants were term-born infants residing in Sweden and aged &lt;1 year at enrolment. Baseline questionnaire data and stool samples were collected from 253 infants. Parents completed questionnaires covering socio-demographic characteristics and health, pregnancy and delivery, postnatal factors, infant environment, feeding and growth, infections and other health outcomes, gastrointestinal symptoms and everyday well-being. Retention was high, with 248 families completing at least one follow-up questionnaire at Phase 2 and 243 at Phase 3. For stool samples, 250 infants provided at least two samples and 241 provided all three. At enrolment, 42.3% of infants were older than 7 months, 73.9% had weight-for-length z-scores in the normal range and exclusive breastfeeding at 4 months was reported for 58.9%. Three-phase sample and questionnaire data collection was completed in December 2024. Future analyses will examine microbiome features, resistome profiles and functional pathways in relation to antibiotic exposure, feeding, growth and infant health outcomes. Subject to ethical approval and participant consent, follow-up may include further stool collection and Swedish register linkage. NCT06285630.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>本研究建立瑞典全國性嬰兒追蹤世代「PREVENT 1」，旨在透過縱向總體基因體學分析，描繪嬰兒出生後前兩年的腸道菌相發育軌跡，並探討其與餵養、生長及感染等健康指標的關聯。研究成功招募253名足月嬰兒，並在三個時間點重複收集糞便檢體與問卷，受試者維持率極高（241名嬰兒提供全部三次檢體）。此世代研究提供高質量的臨床與多體學數據，未來將深入分析抗生素暴露與飲食如何形塑嬰兒腸道菌群、抗藥性基因組及代謝途徑，對理解早期生命健康極具臨床與科學價值。</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42665338/</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>42663694</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Comparative Analysis of Different Anodic Inoculum in Microbial Fuel Cell for Efficient Methylene Blue Dye Degradation.</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Current microbiology</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>metagenomics</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>3種不同的接種源（海洋沉積物、河口沉積物、厭氧污泥）</t>
-        </is>
-      </c>
-      <c r="G24" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>This study investigates three different inoculum sources in dual-chamber microbial fuel cells (MFCs), such as Marine Sediment (MFC-MS), Estuary Sediment (MFC-ES), and Anaerobic Sludge (MFC-AS), to compare the efficacy for Methylene Blue (MB) dye degradation and electricity generation. All the MFCs were operated under identical conditions in batch mode using synthetic wastewater containing 3000 mg/L COD made using sodium acetate. The electrochemical study reveals that MFC inoculated with marine sediment achieved maximum power density of 35 mW/m² followed by anaerobic sludge (31 mW/m²) and estuary sediment (25 mW/m²). Statistical analysis was employed to evaluate performance differences among the systems and to support result interpretation. Maximum COD removal efficiency of 75% was obtained by MFC-AS, and coulombic efficiency (CE) was higher for MFC-MS with 25%. Maximum decolorization efficiency was noted in MFC with anaerobic sludge, which obtained 96% decolorization over 96 h. Comparative and trend-based statistical evaluation confirmed the superior treatment performance of MFC-assisted systems. The phytotoxicity study revealed that the toxicity effect of dye wastewater was reduced to its maximum after treatment in the MFC system. The dominant performance of MFC-MS is due to the efficiency of the major electrogenic bacteria concentrated in the inoculum. The functional annotation using the data obtained from metagenomics reveals the presence and role of various enzymes and pathways involved.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>本研究旨在比較雙腔式微生物燃料電池（MFC）中，三種不同接種源（海洋沉積物、河口沉積物、厭氧污泥）在降解亞甲藍染料與產電的效率。結果顯示，海洋沉積物系統具最高的功率密度（35 mW/m²）與庫倫效率（25%）；厭氧污泥系統則有最佳的化學需氧量去除率（75%）與脫色率（96%）。處理後廢水的植物毒性顯著降低。宏基因組學分析揭示了關鍵產電菌的分布及參與降解與發電的酶和代謝途徑。本研究證實了不同接種源在 MFC 污水處理與生物發電的潛力，並闡明了其微生物學機制。</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42663694/</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>42664252</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Proteobacteria with chemosynthetic potential are highly prevalent in the gills of Hypoplectrus reef fishes.</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>PLoS genetics</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>metagenomics</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>353 個魚鰓檢體</t>
-        </is>
-      </c>
-      <c r="G25" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Fishes host a diverse microbiome in their gills, but a broad characterization of this microbiome at the metagenomic level is lacking. Here, we apply genome-resolved metagenomics to the gills of the hamlets (Hypoplectrus spp), a group of reef fishes from the Greater Caribbean. The analysis of 353 gill samples from 15 hamlet species collected at eight locations over 13 years revealed a stark contrast between the gill microbiota and reef water microbial communities, indicating a distinct and specific gill microbiome. A total of 70 gill-associated metagenome-assembled genomes (MAGs) were recovered. These MAGs belong to 17 lineages, most of which are novel. They relate to known fish gill pathogens, fish gut microbes, free-living and biofilm-associated taxa, indicating that the gill microbiome was assembled from a collection of distinct eco-evolutionary trajectories. The MAGs harbor diverse metabolic modules, involved notably in nitrogen cycling, antibiotic production and biofilm formation, revealing a highly dynamic microbial ecosystem. One lineage in the Burkholderiaceae family was outstandingly prevalent across fish host species, sampling locations and years. Its genome encoded complete metabolic modules for carbon fixation and sulfur oxidation, indicating chemosynthetic potential. To the best of our knowledge, this is the first line of evidence that fishes may host sulfur-oxidizing chemosynthetic bacteria in their gills. The functional significance of this chemosynthetic potential for the fish host or other members of the gill microbiome remains to be established. The high prevalence of this lineage allowed to build a pangenome. It revealed large-scale geographic structure (western Caribbean, eastern Caribbean and Gulf of Mexico), which parallels the phylogenomic pattern observed in the hamlets. Overall, our findings point to complex fish host-microbe and microbe-microbe eco-evolutionary interactions in the gills that may influence fish physiology, homeostasis and immune response.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>本研究針對加勒比海地區 15 種「蝴蝶魚」（Hypoplectrus spp.）進行了大規模的宏基因組研究。透過分析 353 個魚鰓檢體並重建 70 個宏基因組組裝基因組（MAGs），研究發現魚鰓微生物群落與周圍海水環境顯著不同，具有獨特的演化軌跡。最重大的發現是鑑定出一種具高度普遍性的 Burkholderiaceae 細菌，該菌株擁有完整的固碳與硫氧化代謝路徑，顯示其具備化能合成潛力，這是科學界首次在魚類鰓部發現此類共生菌。此外，該菌株的基因體結構與宿主魚類的地理分布呈現高度一致性。此研究揭示了魚鰓微生物生態系統的複雜性，並為魚類生理、恆定性及免疫反應與微生物間的交互作用提供了重要的演化科學基礎。</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42664252/</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>42663459</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Clinical application of BALF-mNGS in immunocompromised and immunocompetent patients with suspected invasive pulmonary aspergillosis: differentiating infection from colonization, microbiome features, and clinical impact.</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Microbiology spectrum</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>metagenomics</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>178位疑似侵襲性肺麴菌病（IPA）患者（包含77位免疫功能低下患者與101位免疫功能正常患者）</t>
-        </is>
-      </c>
-      <c r="G26" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Invasive pulmonary aspergillosis (IPA) not only causes high morbidity and mortality, especially in immunocompromised patients, but also occurs in immunocompetent individuals. Differentiating infection from colonization is challenging, and bronchoalveolar lavage fluid metagenomic next-generation sequencing (BALF-mNGS) may aid diagnosis, microbiome profiling, and clinical assessment. We retrospectively analyzed patients with suspected IPA who underwent BALF-mNGS between December 2021 and March 2025. Patients were classified by immune status. IPA diagnosis was based on EORTC/MSGERC 2020 criteria in immunocompromised patients, while immunocompetent cases were adjudicated using an integrated clinical, radiological, and microbiological assessment. A total of 178 patients were finally included and classified according to immune status into an immunocompromised group (n = 77) and an immunocompetent group (n = 101). Aspergillus_ reads per ten million (RPTM) values were significantly higher in infection versus colonization cases in both groups, with optimal cut-offs of 24 (gray zone: 22-60) for the immunocompromised group and 33 (gray zone: 17-48) for the immunocompetent group. Microbiome analysis revealed distinct community structures between infection and colonization groups, with Aspergillus remaining significantly enriched after false discovery rate (FDR) correction in immunocompromised patients, while no taxa remained significant after FDR correction in immunocompetent patients. BALF-mNGS guided antifungal therapy, avoiding unnecessary treatment in colonized patients, and higher Aspergillus_RPTM was associated with increased 90-day mortality in immunocompromised patients. BALF-mNGS may accurately distinguish Aspergillus infection from colonization and reveal microbial shifts, particularly in immunocompromised patients. It can guide targeted antifungal therapy, avoid unnecessary treatment, and higher Aspergillus_RPTM was associated with 90-day mortality in immunocompromised patients, suggesting its potential value for risk stratification.IMPORTANCEBALF-mNGS with quantitative thresholds improves differentiation between Aspergillus infection and colonization. It reveals distinct lung microbiome patterns under different immune statuses, extending beyond simple pathogen detection. Higher Aspergillus burden is associated with worse outcomes in immunocompromised patients, suggesting its potential value for risk stratification.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>本研究旨在評估支氣管肺泡灌洗液總體基因體次世代定序（BALF-mNGS）在區分疑似侵襲性肺麴菌病（IPA）患者「感染」與「定植」的臨床價值，並探討其肺部微生態特徵。研究納入178位患者，發現感染者的麴菌相對豐度（RPTM）顯著高於定植者，並針對免疫功能低下與正常組分別訂定出24與33的最佳臨界值。微生態分析顯示兩組具有不同的菌群結構。臨床上，BALF-mNGS能有效引導抗真菌治療，避免定植患者過度治療；而在免疫功能低下組中，高麴菌RPTM值與90天高死亡率顯著相關。此技術不僅能精準診斷，更具備患者預後風險分層的潛力。</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42663459/</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>42666033</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Gut Microbiota-Isoallolithocholic Acid Crosstalk Promotes Calcium Oxalate Kidney Stone Formation via PARP1-Mediated Parthanatos.</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Advanced science (Weinheim, Baden-Wurttemberg, Germany)</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>16S, metagenomics, metabolomics</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>未提及</t>
-        </is>
-      </c>
-      <c r="G27" t="b">
-        <v>0</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Bile acids have been implicated in calcium oxalate (CaOx) nephrolithiasis. Here, we employ multi-omics approaches to identify isoallolithocholic acid (isoalloLCA) as the key bile acid elevated in the feces, serum, kidney, and urine of CaOx rats, confirmed by spatial metabolomics. 16S sequencing and metagenomic analyses indicate that elevated isoalloLCA levels in CaOx rats or individuals are likely of microbial origin. Mechanistically, isoalloLCA binds to PARP1 via specific molecular interactions validated by surface plasmon resonance and cellular thermal shift assays. Knockdown of PARP1 by adeno-associated virus microinjection or pharmacological inhibition with PARP1 inhibitor AZD5305 significantly attenuates isoalloLCA-mediated crystal deposition, renal tubular injury, and mitochondrial functional impairment in both the CaOx rat and mouse models. Furthermore, the antibiotic-mediated depletion of the gut microbiota in mice markedly reduced isoalloLCA levels, whereas fecal microbiota transplantationut contributes to isoalloLCA-mediated CaOx stone formation, demonstrating a causal link between gut microbiota and isoalloLCA. In vitro, isoalloLCA promoted oxalate-induced renal tubular epithelial cell injury and parthanatos via targeting PARP1, including DNA damage, excessive PARP1 activation, PAR accumulation, mitochondrial damage, nuclear translocation of AIF and MIF. These findings establish the microbiota-isoalloLCA-PARP1-parthanatos axis in CaOx nephrolithiasis and identify PARP1 as a promising therapeutic target for kidney stone management.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>本研究旨在探討腸道菌群及其代謝物異別石膽酸（isoalloLCA）在草酸鈣（CaOx）腎結石形成中的作用與分子機制。透過整合16S定序、宏基因組學與空間代謝組學，研究發現 CaOx 大鼠及患者體內的腸道菌源 isoalloLCA 顯著升高。機制上，isoalloLCA 能直接結合並激活 PARP1 蛋白，誘導腎小管上皮細胞發生 PARP1 介導的細胞凋亡樣壞死（parthanatos），導致 DNA 與線粒體受損。於動物模型中，敲低或抑制 PARP1，或利用抗生素清除腸道菌群，皆能顯著減輕結晶沉積與腎損傷。本研究揭示了「腸道菌群-isoalloLCA-PARP1-parthanatos」軸在腎結石病理中的關鍵角色，並指出 PARP1 為臨床治療腎結石的具潛力靶點。</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42666033/</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>42665998</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Agathobacter rectalis suppresses colorectal tumorigenesis via an epigallocatechin-SREBF2 axis controlling cholesterol metabolism.</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Gut microbes</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>metagenomics, metabolomics</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>未提及</t>
-        </is>
-      </c>
-      <c r="G28" t="b">
-        <v>0</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Beneficial effects of the gut commensal Agathobacter rectalis (Ar) are reported in diseases, yet its role in colorectal cancer (CRC) remains unclear. Here, metagenomic analysis revealed consistent fecal Ar depletion across CRC cohorts. In Apc min/+ mice, Ar inhibited colon tumorigenesis, reducing tumor number and volume versus E. coli and PBS controls. LC-MS/MS metabolomics showed decreased fecal cholesterol and altered lipid/cholesterol pathways after Ar treatment. In vitro, Ar-conditioned medium suppressed CRC cell growth, clonogenicity, migration, and cell cycle progression. LC-MS/MS identified (-)-epigallocatechin (EGC) as an Ar-derived metabolite absent in control bacteria. EGC recapitulated Ar-mediated anti-CRC effects in vitro and in vivo, with metabolic changes linked to lipid/cholesterol pathways. Transcriptomics showed that EGC suppressed SREBP signaling, cholesterol metabolism, and MAPK pathways. Mechanistically, EGC reduced nuclear SREBF2 and its transcriptional activity, downregulated cholesterol synthesis/metabolism genes, including FDPS and PCSK9, and suppressed MAPK signaling. Molecular docking suggested that EGC may bind pSREBF2 or SCAP. Cellular thermal shift assay revealed that EGC interacts with and stabilizes pSREBF2, but not SCAP. Co-immunoprecipitation demonstrated that EGC reduces pSREBF2-SCAP interaction, thereby inhibiting SCAP-mediated SREBF2 cleavage activation. Together, these findings define an Ar-EGC microbe-metabolite axis and support Ar/EGC-based interventions targeting cholesterol metabolism in CRC.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>本研究探討腸道共生菌 *Agathobacter rectalis* (Ar) 在大腸直腸癌 (CRC) 中的作用機制。宏基因組分析顯示 CRC 患者體內 Ar 顯著減少；小鼠實驗證實 Ar 能抑制腫瘤生長。代謝組學分析發現 Ar 能產生特定代謝物表沒食子兒茶素 (EGC)。體內外實驗顯示，EGC 可抑制 CRC 細胞生長與膽固醇代謝。機制上，EGC 透過與 pSREBF2 結合並穩定之，阻斷其與 SCAP 的交互作用，進而抑制 SREBF2 活化及下游膽固醇合成基因（如 FDPS、PCSK9）的表達，並抑制 MAPK 訊號。此研究確立了 Ar-EGC 微生物-代謝物軸，為靶向膽固醇代謝的 CRC 防治提供了新策略。</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42665998/</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>42665077</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Metagenomic Characterization of Potential Exposure to Genetic Hazards at the Interface Between Grazing Livestock and Przewalski's Gazelle.</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Environmental pollution (Barking, Essex : 1987)</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>metagenomics</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>未提及</t>
-        </is>
-      </c>
-      <c r="G29" t="b">
-        <v>0</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Livestock and endangered wildlife increasingly share grazing landscapes, yet the sources, mobility-associated contexts, and bacterial hosts of livestock-associated genetic hazards in wildlife microbiomes remain poorly resolved. We analyzed metagenomes from yak, Tibetan sheep, Przewalski's gazelle, and local topsoil within an Acquired Genetic Risk (AGR) conceptual framework integrating genetic hazard burden, compositional source attribution, mobility-associated evidence, and bacterial genomic context. MRGs and Rank I and Rank III ARGs were more abundant in livestock than in Przewalski's gazelle, whereas VF abundance was highest in yak. FEAST attributed approximately 64% of the Przewalski's gazelle resistome composition to the two livestock source profiles, less than 1% to sampled topsoil, and approximately 36% remained unassigned. MGE profiles were associated with ARGs, MRGs, and VFs, while tnpA ranked highest in random forest models and was associated with total ARG abundance (R2 = 0.618). Short-read contigs containing hazard genes and MGE markers provided localized mobility-associated sequence context. Genome-resolved analysis identified distinct bacterial contexts: TS.Bin143, an Escherichia coli MAG from Tibetan sheep, contained ARGs, MRGs, VFs, tnpA, and IS91, whereas PG.Bin275, a Hylemonella sp. MAG from Przewalski's gazelle, contained tnpA. These findings extend wildlife resistome assessment beyond abundance profiling toward source attribution, mobility-associated sequence context, and bacterial host resolution, supporting multilevel surveillance of genetic hazard exposure at livestock-wildlife interfaces.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>本研究旨在評估放牧家畜與瀕危野生普氏原羚接觸介面上的遺傳危害（如抗藥性基因 ARG、金屬耐受基因 MRG 與毒力因子 VF）暴露風險。研究利用總體基因體學分析氛牛、藏羊、普氏原羚及當地表土，結果顯示家畜體內的 MRG 和高風險 ARG 豐度顯著高於普氏原羚。來源追蹤分析（FEAST）指出，普氏原羚約 64% 的抗藥組組成可歸因於這兩種家畜，僅不到 1% 來自土壤。此外，研究透過基因組解析定位了攜帶危害基因與移動遺傳因子的細菌宿主。本研究不僅闡明了遺傳危害的來源與傳播關聯，也為野生動物與家畜接觸介面的多層級生物安全監測提供了重要科學依據。</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42665077/</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>42663468</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Genomes of cressdnaviricots and phixviricots in a freshwater lake sample from Arizona, USA.</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Microbiology resource announcements</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>metagenomics, small genome</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>1 個 40 ml 的淡水湖泊水樣</t>
-        </is>
-      </c>
-      <c r="G30" t="b">
-        <v>0</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>A viral metagenomic analysis of a 40 ml water sample from a small freshwater lake near Flagstaff, Arizona, USA, resulted in the identification of 295 circular viral genome sequences. Of these, 126 are members of Cressdnaviricota and 169 of Phixviricota phyla.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>本研究旨在探討美國亞利桑那州 Flagstaff 附近一處小型淡水湖泊中的病毒多樣性。研究團隊對 40 毫升的水樣進行病毒總體基因體學（viral metagenomics）分析，成功鑑定並組裝出 295 個環狀病毒基因體序列。在這些病毒中，有 126 個屬於 Cressdnaviricota 門（環狀單鏈 DNA 病毒），另有 169 個屬於 Phixviricota 門（微小噬菌體相關病毒）。此研究的科學意義在於顯著擴充了淡水生態系統中這兩大病毒門的基因體數據，並證實即使在極少量的環境水樣中，也蘊藏著極高多樣性且未知的病毒資源，有助於深化對淡水微生態系統及病毒演化多樣性的理解。</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42663468/</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>42664954</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Lactobacillus salivarius potentiates gastrointestinal cancer immunotherapy through its metabolite chenodeoxycholic acid.</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Cell reports. Medicine</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>metagenomics, metabolomics</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>278 位胃腸道癌症患者及同基因腫瘤小鼠模型</t>
-        </is>
-      </c>
-      <c r="G31" t="b">
-        <v>0</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Immune checkpoint inhibitor therapy has improved gastrointestinal (GI) cancer management; however, many patients exhibit resistance. Although gut microbiota influences immunotherapeutic responses, the underlying mechanisms remain unclear. Metagenomic analysis of 278 GI cancer patients reveals that Lactobacillus salivarius (L. salivarius) is enriched in responders and enhances anti-PD-1 efficacy in syngeneic tumor models by increasing the infiltration of antitumor M1-like macrophages and CD8+ T cells and enhancing CD8+ T cell effector function. L. salivarius-associated chenodeoxycholic acid (CDCA) is identified as a functional metabolite. CDCA recapitulates the antitumor effects of L. salivarius and significantly improves anti-PD-1 efficacy in vivo, an effect attenuated by depleting macrophages or CD8+ T cells. Mechanistically, CDCA-induced reactive oxygen species triggers immunogenic cell death in tumor cells and polarizes macrophages toward antitumor M1 phenotype, activating CD8+ T cell antitumor immunity. These findings identify L. salivarius and its associated metabolite CDCA as a promising adjuvant for potentiating immunotherapy in GI cancers.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>本研究旨在探討腸道菌群影響胃腸道（GI）癌症免疫治療反應的具體機制。透過對 278 位 GI 癌症患者的總體基因體分析，發現唾液乳桿菌（*Lactobacillus salivarius*）在治療有反應的患者體內顯著富集。於小鼠模型中，該菌能增加抗腫瘤 M1 型巨噬細胞與 CD8+ T 細胞的浸潤，顯著提升抗 PD-1 療效。研究進一步證實，該菌的代謝物鵝去氧膽酸（CDCA）為關鍵功能分子，能透過誘導活性氧（ROS）引發腫瘤細胞的免疫原性死亡，並促進巨噬細胞向 M1 型極化，從而激活 CD8+ T 細胞的抗腫瘤免疫反應。本研究揭示了唾液乳桿菌及其代謝物 CDCA 作為增強 GI 癌症免疫治療活性佐劑的臨床潛力。</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42664954/</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>42656127</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Development and Validation of Mock Communities as Quality Control Materials for Clinical Metagenomic Next-Generation Sequencing.</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Annals of laboratory medicine</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>metagenomics</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>25 次重複分析（針對開發出的四種模擬群落進行評估）</t>
-        </is>
-      </c>
-      <c r="G32" t="b">
-        <v>0</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Metagenomic next-generation sequencing (NGS) enables comprehensive detection of a broad spectrum of microorganisms. However, its clinical application faces two major challenges: the development of appropriate microbiome-based biomarkers and the need to ensure the reproducibility and quality of the microbiome analytical workflow. Therefore, we developed four types of bead-based mock communities as standard materials for microbiome analysis and evaluated potential experimental biases arising from nucleic acid extraction and sequence analysis. Mock communities were assembled from strains isolated from clinical specimens and selected considering Gram reaction, taxonomic phylogeny, and prevalence, and processed into frozen beads. The communities were analyzed using shotgun whole-metagenome sequencing. The effect of DNA extraction kit choice was evaluated using the Thermo Fisher Scientific MagMAX Microbiome Ultra Nucleic Acid Isolation Kit and Qiagen PowerSoil Kit. Four types of mock communities comprising 26 species commonly found in the gastrointestinal tract, respiratory tract, skin, and genital tract plus cerebrospinal fluid were developed considering Gram reaction, GC content, and phylogenetic distribution. Across 25 repeated analyses, the median repeatability of each taxon was 18.97% (range, 2.87%-107.38%), while within-laboratory imprecision was 26.22% (range, 9.26%-153.83%). Repeatability remained below 10% for most dominant taxa with relative abundances &gt;20%. The choice of DNA extraction kit had a significant effect on taxonomic distributions. Microbial mock communities are essential QC materials for clinical metagenomic NGS. Further studies are needed to minimize variability and establish a standardized protocol for clinical implementation.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>本研究旨在解決臨床宏基因組次世代定序（mNGS）在品質控制與再現性上的挑戰，開發了四種基於珠粒的「模擬微生物群落」（mock communities）作為標準品。這些群落涵蓋了腸道、呼吸道、皮膚、生殖道及腦脊髓液中常見的 26 種菌株。研究透過鳥槍法全宏基因體定序（shotgun metagenomics）評估了不同 DNA 萃取試劑盒（MagMAX 與 PowerSoil）及實驗流程對結果的偏誤影響。結果顯示，微生物的檢測豐度會顯著受到萃取試劑盒選擇的干擾，且在 25 次重複實驗中，群落組成存在一定的實驗室內誤差。此研究確立了模擬群落作為臨床 mNGS 品質控制材料的重要性，對於推動微生物組檢測的標準化流程與臨床應用具有關鍵價值。</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42656127/</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>42660365</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Enhancing Cr(VI) bioreduction via Na+-stimulated intracellular energy metabolism and electron transfer using methane as electron donor.</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Bioresource technology</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>9</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>16S, metagenomics</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>未提及</t>
-        </is>
-      </c>
-      <c r="G33" t="b">
-        <v>0</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Anaerobic oxidation of methane (AOM) coupled with Cr(VI) bioreduction process offers a cost-effective pathway to simultaneously mitigate methane emissions and remediate Cr(VI) contamination. However, its practical application is limited by insufficient intracellular energy generation and low electron transfer efficiency. This study elucidated the regulatory role and mechanism of Na+, a transmembrane electrochemical gradient driver, on the metabolic activity and electron transfer of this coupled system. Batch experiments demonstrated that NaCl addition significantly improved Cr(VI) reduction efficiency, achieving complete removal in the treatment group by the end of the first cycle compared to only 79.8 % in the control. Microbial community analysis showed that Na+ enriched AOM-capable Methanobacterium and extracellular electron transfer (EET)-capable electroactive bacterium unclassified_o_DTU014, which likely formed a syntrophic consortium to mediate Cr(VI) reduction. Electrochemical measurements and 3D-EEM spectroscopy revealed that Na+ enhanced microbial aggregate electron storage capacity, reduced electron transfer resistance, and promoted extracellular polymeric substance (EPS) secretion of tyrosine-like proteins and humic acid-like substances, thereby strengthening extracellular electron transfer. Key metabolic indicators showed 26.2 % higher coenzyme F420 and 37.4 % higher intracellular ATP levels in Na+-treated groups. Metagenomic analysis confirmed that Na+ upregulated genes encoding reverse methanogenesis enzymes (Mcr, Mtr) and membrane-bound electron transfer complexes (Fpo, HdrDE), while downregulating intracellular chromate reductase (ChrR) genes, indicating that EET-mediated extracellular Cr(VI) reduction played a critical role under Na+ stimulation. This study first reveals the mechanism of Na+-promoted AOM-coupled Cr(VI) reduction via enhanced energy metabolism and electron transfer, providing a crucial theoretical basis for methane-driven Cr(VI) remediation.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>本研究旨在探討跨膜電化學梯度驅動者——鈉離子（Na+），如何調控「甲烷厭氧氧化（AOM）耦合六價鉻 [Cr(VI)] 生物還原系統」的代謝活性與電子傳遞機制。研究發現，添加 NaCl 能顯著提升 Cr(VI) 的去除效率。微生物分析顯示，Na+ 富集了具 AOM 能力的 *Methanobacterium* 與具胞外電子傳遞（EET）能力的電活性細菌，形成協同共生關係。此外，Na+ 提高了微生物的胞內 ATP 與輔酶 F420 水平，並促進胞外聚合物（EPS）分泌以降低電子傳遞阻力。總體基因體學分析進一步證實，Na+ 上調了逆向產甲烷及膜結合電子傳遞複合物的關鍵基因。本研究首次審視並揭示了 Na+ 促進 AOM 耦合 Cr(VI) 還原的生物能量學機制，為利用甲烷進行重金屬生物整治提供了重要理論基礎。</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42660365/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>42660108</t>
+          <t>42667585</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Group C Orthobunyavirus Infection in a Patient from the Amazon Putumayo Region of Colombia During an Oropouche Fever Epidemic.</t>
+          <t>Gut Microbiota from Patients with Long COVID Persisting for 2 Years Result in Alterations in Mice that Resemble Post-COVID Symptoms.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>The American journal of tropical medicine and hygiene</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>Probiotics and antimicrobial proteins</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>4.4</v>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>metagenomics</t>
+          <t>16S, metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1位急性發熱疾病患者（單一病例）</t>
+          <t>11位健康對照組受試者與11位長期新冠（LCOVID）患者（共22個糞便檢體），以及接受糞菌移植的抗生素處理（ABx）小鼠（具體小鼠數量未提及）。</t>
         </is>
       </c>
       <c r="G34" t="b">
@@ -2224,50 +2226,50 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Orthobunyaviruses, one of the largest and most diverse genera of viruses, include numerous reassortant viruses and present diagnostic challenges due to similar clinical presentations with other arboviral infections. The detection and isolation of a group C orthobunyavirus from a patient with acute febrile illness from Puerto Ospina, Putumayo Department, Colombia during the 2023-2024 Latin American Oropouche fever regional outbreaks are reported in the present study. Using a vertebrate virus-focused metagenomics sequencing approach with VirCapSeq-VERT, a virus related to the Caraparu complex was identified, and a virus isolate was obtained. Although limited to a single case and without serological or longitudinal clinical confirmation, these findings underscore the value of unbiased molecular approaches for unresolved febrile illness diagnosis in endemic settings such as the Amazon basin.</t>
+          <t>Human gut microbiota (GM) has been identified as a potentially important factor influencing the development of long COVID (LCOVID). The aim of this study was to understand the GM of LCOVID, which lasted for two years, in order to improve public awareness. Human gut microbiota and its metabolites were assessed in a healthy control group (n = 11) (HC) unexposed to SARS-CoV-2 and an LCOVID group (n = 11) in Hainan, China, using Shotgun metagenomics and liquid chromatography-mass spectrometry (LC-MS) of feces. The causal role of the microbiota in LCOVID was further validated by transplanting feces from the subjects into ABx mice using Histopathology and 16 S rRNA sequencing. Fecal microbial diversity was lower in patients with LCOVID compared with that in HC. Pro-inflammatory bacteria such as Streptococcus_salivarius and Streptococcus_parasanguinis increased, whereas anti-inflammatory bacteria such as Faecalibacterium_SGB15346 and Alistipes_onderdonkii decreased. Fecal metabolites from LCOVID were impaired in carbohydrate degradation, indole production, SCFA production, and fatty acid degradation. Transplantation of feces from patients with LCOVID into mice results in lung inflammation, intestinal inflammation, and anxiety. In addition, transplanted mice showed worse outcomes during Klebsiella_pneumoniae infections. Transplanted mice and the key bacteria Streptococcus_salivarius had the same worse outcomes in the D-IBS model by limb binding. GM from patients with LCOVID was altered significantly and sufficiently to promote LCOVID symptoms in mice, suggesting that it may be a potential therapeutic target.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>本研究旨在調查2023-2024年拉丁美洲奧羅普切熱（Oropouche fever）疫情期間，哥倫比亞亞馬遜地區一名急性發熱患者的病因。研究團隊採用針對脊椎動物病毒的總體基因體學（宏基因組）定序技術（VirCapSeq-VERT），成功鑑定並分離出一種與Caraparu複合體相關的C群正布尼亞病毒（Group C Orthobunyavirus）。由於此類病毒臨床表現與其他蟲媒病毒相似，診斷極具挑戰。本研究雖僅基於單一病例，但其結果強調了在亞馬遜盆地等流行病疫區，使用無偏向性分子檢測技術對於診斷不明原因發熱疾病的重要臨床與科學價值。</t>
+          <t>本研究旨在探討持續兩年之新冠後遺症（LCOVID）患者的腸道菌群特徵及其致病機制。研究結合宏基因組與代謝組學分析，發現LCOVID患者的腸道菌相多樣性降低，促炎菌（如唾液鏈球菌）增加，而抗炎菌減少，且碳水化合物與短鏈脂肪酸等代謝路徑受損。將患者糞便移植至小鼠後，成功誘發肺部與腸道發炎、焦慮行為，並加劇肺炎克雷伯菌感染與腸躁症症狀。此結果證實腸道菌群失衡是驅動LCOVID症狀的關鍵因子，具備作為潛在治療靶點的臨床科學價值。</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42660108/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42667585/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>42660482</t>
+          <t>42664608</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Artificial light pollution alters epilithic microbial communities and functional biodeterioration-related functional potentials in subterranean sandstone environments.</t>
+          <t>Application-dependent effects of tea waste biochar on PFAS mobility and N2O and CH4 emissions in agricultural soil.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Environmental pollution (Barking, Essex : 1987)</t>
+          <t>Waste management (New York, N.Y.)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>16S, metagenomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>未提及（僅說明使用盆栽模擬系統「per pot」，未提及具體樣本或盆栽數量）</t>
         </is>
       </c>
       <c r="G35" t="b">
@@ -2275,52 +2277,52 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Artificial light pollution represents an important anthropogenic disturbance in subterranean heritage environments, yet its associations with epilithic microbial communities and biodeterioration processes remain poorly understood. In tourist-accessible subterranean caves, artificial illumination creates persistent illuminated areas on stone surfaces that may alter microbial community assembly and biogeochemical functions associated with biofilm development. Here, the Longyou Grottoes, a large underground sandstone cave complex in Zhejiang, China, were investigated using 16S rRNA gene sequencing and metagenomics. Bacterial communities dominated all samples (&gt;98% relative abundance). Cyanobacteriota were enriched under artificial light and sunlight (&gt;40%), whereas Pseudomonadota and Actinomycetota prevailed in darkness. Dark sites exhibited higher bacterial alpha diversity and more complex co-occurrence networks. Compared with sunlight and dark environments, the artificial-light environment was associated with greater stochasticity in bacterial community assembly, broader niche breadth, and lower niche overlap. Metabolic potential analysis further revealed light-dependent metabolic shifts: artificial light enhanced assimilatory nitrogen and sulfur metabolism, sunlight promoted nitrogen fixation, and darkness favored nitrification, denitrification, and sulfur oxidation. However, bacterial community patterns were also associated with temperature, humidity, pH, and soluble salts, indicating that the observed differentiation reflected the combined influence of light and environmental heterogeneity. These findings identify artificial lighting as an important and manageable environmental factor associated with epilithic bacterial communities and provide a basis for integrating lighting management with environmental control in the preventive conservation of subterranean sandstone heritage.</t>
+          <t>Per- and polyfluoroalkyl substances (PFAS) in agricultural soils can migrate into crops and may alter soil greenhouse gas emissions, yet remediation strategies rarely address these risks simultaneously. This study evaluated tea waste biochar (TWB) produced at 400, 500, and 600 °C and applied at 5-20 g per pot by whole-soil mixing or surface-layer placement in a simulated PFAS-contaminated soil-leachate-plant system. Perfluorooctane sulfonate (PFOS) and perfluorooctanoic acid (PFOA) distributions, nitrous oxide (N2O) and methane (CH4) fluxes, and microbial responses were examined. TWB produced at 500 °C showed the most favorable combination of pore accessibility, surface hydrophobicity, and interfacial charge, with material-associated PFOS and PFOA enrichments of 0.12 and 0.57 μg/g, respectively. Whole-soil mixing with TWB-500 lowered soil and leachate PFAS levels and reduced PFAS concentrations in plant shoots by approximately 36% relative to the contaminated control. TWB treatments also reduced cumulative N2O emissions and enhanced net CH4 uptake. Metagenomic analysis showed lower relative abundances of genes associated with nitrogen fixation, ammonia oxidation, and several N2O-producing pathways, whereas CH4-cycling genes responded differently to the two application methods. Organic fluorine transformation genes were not enriched, indicating that PFAS control mainly resulted from physicochemical retention rather than enhanced microbial defluorination. Overall, TWB-500 can integrate PFAS stabilization with greenhouse gas management, but the optimal placement depends on the remediation objective: whole-soil mixing favors PFAS immobilization, whereas surface-layer application provides greater greenhouse gas mitigation.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>本研究探討人造光污染對地下砂岩古蹟（龍游石窟）岩表微生物群落及生物降解功能的影響。透過16S rRNA定序與總體基因體學分析，發現光照顯著改變群落結構：人工光與日光下藍菌門富集，而黑暗環境則由假單胞菌門和放線菌門主導，且黑暗處具更高的多樣性與網絡複雜度。代謝潛力分析顯示，人工光增強了同化性氮、硫代謝，而黑暗則利於硝化與硫氧化。此外，群落分化也與溫濕度及pH等環境因子相關。本研究證實人造光源是調控地下微生物的重要因子，為砂岩文物的預防性保護與照光管理提供科學依據。</t>
+          <t>本研究旨在評估茶渣生物炭（TWB）在模擬的PFAS污染土壤-滲濾液-植物系統中，對於抑制全氟和多氟烷基物質（PFAS）遷移及減少溫室氣體（N2O和CH4）排放的雙重效應。研究發現，在500 °C下製備的TWB-500效果最佳。若將其均勻混合於全土中，可使植物地上部的PFAS濃度降低約36%，並顯著降低土壤和滲濾液中的PFAS含量。此外，TWB處理還減少了N2O累積排放並促進CH4淨吸收。總體基因體學分析顯示，與氮循環相關的基因豐度有所下降，解釋了N2O排放減少的機制；而有機氟降解基因並未富集，證實PFAS的控制主要源於物理化學阻控而非微生物去氟作用。此研究證明TWB-500能有效整合PFAS固化與溫室氣體管理，且施用方式（全土混合或表層施作）可依環境整治優先目標進行客製化調整。</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42660482/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42664608/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>42660360</t>
+          <t>42665338</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Elucidating the aromatic formation of humus via quorum sensing and redox function of thermophilic microbiota in compost.</t>
+          <t>PREVENT 1, a nationwide Swedish infant cohort for longitudinal gut microbiome profiling and early-life health outcomes: cohort profile.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bioresource technology</t>
+          <t>BMJ open</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9</v>
+        <v>2.3</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>metagenomics, others</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>未提及</t>
+          <t>253 位嬰兒（收集 253 份基線糞便檢體，其中 250 位提供至少 2 次檢體，241 位提供全部 3 次檢體）</t>
         </is>
       </c>
       <c r="G36" t="b">
@@ -2328,50 +2330,52 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Quorum sensing (QS) modulates bacterial metabolism to regulate humus formation. However, the functional interaction modes of signal molecules, QS-related proteins, and microbial humification function during composting remain unclear. This study aimed to clarify the role of QS-related gene expression in regulating humification via applying metagenomics and metaproteomics. Combined addition of MnSO4 and Fe0 (CMF) significantly raised humic acid (HA) content (33.53 mg g-1) and polymerization degree (2.60) compared with other treatments. Multi-dimensional results revealed that CMF-derived HA and its products exhibited greater thermal stability, high aromaticity, and practical applicability. CMF increased the relative abundances of most QS-related and humification-related oxidoreductase genes throughout composting, especially during the thermophilic stage. Metaproteomic profiles verified that both QS expression and humification metabolism were hyperactivated during the thermophilic stage of CMF. Correlation analysis showed that QS gene expression potentially and preferentially influenced lignin-protein and polyphenol pathways during humification. Overall, CMF enriched thermophiles (Bacillota, Chloroflexota, and Myxococcota), further up-regulated the expression of major QS-related genes [K02035 (ABC.PE.S), K13075 (ahlD), K14645, K15580 (oppA), and K02055 (ABC.SP.S)], elevated levels of signal molecules, and promoted QS effects. Network analysis, qPCR, and simulated in vitro validation experiments confirmed that the response of key QS modules [K13075 (ahlD) and 3-OXO-C8-HSL] potentially facilitated interspecies communication and cooperation among bacteria, which concurrently enhanced downstream microbial metabolic behaviors (microbial redox activities and the metabolism of carbohydrates and amino acids) that aid in driving HA aromatization. This work provides new insight into the ecological roles of QS-related microbes and their precise regulation of compost humification.</t>
+          <t>PREVENT 1 is a nationwide, prospective Swedish infant cohort established to characterise gut microbiome development during the first 2 years of life and to relate microbial trajectories to feeding, infections, growth and everyday well-being. The study integrates repeated infant stool sampling with shotgun metagenomics analysis with aligned parental questionnaires, stool photographs and infant cry recordings collected at three approximately 3-month intervals for each infant. Families were recruited nationwide in Sweden from September 2023 through targeted digital channels. Eligible participants were term-born infants residing in Sweden and aged &lt;1 year at enrolment. Baseline questionnaire data and stool samples were collected from 253 infants. Parents completed questionnaires covering socio-demographic characteristics and health, pregnancy and delivery, postnatal factors, infant environment, feeding and growth, infections and other health outcomes, gastrointestinal symptoms and everyday well-being. Retention was high, with 248 families completing at least one follow-up questionnaire at Phase 2 and 243 at Phase 3. For stool samples, 250 infants provided at least two samples and 241 provided all three. At enrolment, 42.3% of infants were older than 7 months, 73.9% had weight-for-length z-scores in the normal range and exclusive breastfeeding at 4 months was reported for 58.9%. Three-phase sample and questionnaire data collection was completed in December 2024. Future analyses will examine microbiome features, resistome profiles and functional pathways in relation to antibiotic exposure, feeding, growth and infant health outcomes. Subject to ethical approval and participant consent, follow-up may include further stool collection and Swedish register linkage. NCT06285630.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>本研究旨在利用總體基因體學與總體蛋白質組學技術，探討群體感應（QS）相關基因表達在堆肥腐植化過程中的調節機制。研究發現，聯合添加硫酸錳與零價鐵（CMF）能顯著提高腐植酸（HA）的含量、熱穩定性與芳香度。CMF顯著富集了高溫微生物（如Bacillota、Chloroflexota和Myxococcota），並在高溫期上調關鍵QS相關基因（如ahlD）的表達與訊號分子水平。網路分析與體外實驗進一步證實，關鍵QS模組促進了菌群間的交流合作，進而增強下游的微生物氧化還原活性及碳水化合物與氨基酸代謝，共同驅動腐植酸的芳香化。本研究為QS微生物在堆肥腐植化中的生態角色與精準調控提供了全新見解。</t>
+          <t>本研究建立瑞典全國性嬰兒追蹤世代「PREVENT 1」，旨在透過縱向總體基因體學分析，描繪嬰兒出生後前兩年的腸道菌相發育軌跡，並探討其與餵養、生長及感染等健康指標的關聯。研究成功招募253名足月嬰兒，並在三個時間點重複收集糞便檢體與問卷，受試者維持率極高（241名嬰兒提供全部三次檢體）。此世代研究提供高質量的臨床與多體學數據，未來將深入分析抗生素暴露與飲食如何形塑嬰兒腸道菌群、抗藥性基因組及代謝途徑，對理解早期生命健康極具臨床與科學價值。</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42660360/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42665338/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>42658844</t>
+          <t>42663694</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Enrichment and Characterization of a Haloalkaline-tolerant Anammox Bacterium.</t>
+          <t>Comparative Analysis of Different Anodic Inoculum in Microbial Fuel Cell for Efficient Methylene Blue Dye Degradation.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>The ISME journal</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>Current microbiology</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2.6</v>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>metagenomics, small genome, others (transcriptional profiling)</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>未提及（研究基於特定實驗室富集培養物之實驗與分析）</t>
+          <t>3種不同的接種源（海洋沉積物、河口沉積物、厭氧污泥）</t>
         </is>
       </c>
       <c r="G37" t="b">
@@ -2379,52 +2383,52 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Metagenomic surveys have substantially expanded the known diversity of anaerobic ammonium-oxidizing (anammox) bacteria. However, the physiological traits of newly proposed anammox genera remain largely hypothetical due to the lack of cultured representatives. Although niche differentiation driven by salinity, organic substrates, and oxygen is well documented in anammox bacteria, adaptations to alkaline environments remain uncharacterized. Moreover, no anammox lineage has been identified as an alkaline specialist. Herein, we report the enrichment (&gt;80% relative abundance) of an anammox bacterium, provisionally named Candidatus Loosdrechtia alkalitolerans, which represents the cultured member of the genus Ca. Loosdrechtia. Ca. L. alkalitolerans exhibits marked haloalkaline tolerance, outcompeting other freshwater anammox genera under long-term saline-alkaline stress conditions (0.5% NaCl; pH~9.13). Comparative genomics revealed that among freshwater anammox lineages, only Ca. L. alkalitolerans encodes a complete multiple resistance and pH adaptation (Mrp) cation/proton antiporter operon. Batch assays with transcriptional profiling demonstrated that sodium addition upregulated mrp expression and recovered anammox activity under alkaline stress, suggesting that Mrp-mediated cation/proton exchange may contribute to pH homeostasis in Ca. L. alkalitolerans. Furthermore, database mining revealed that the habitat of Ca. L. alkalitolerans is not restricted to haloalkaline environments, but extends to diverse freshwater and wastewater ecosystems. These findings provide mechanistic insight into saline-alkaline tolerance in anammox bacteria, expanding understanding of their physiological plasticity and ecological roles.</t>
+          <t>This study investigates three different inoculum sources in dual-chamber microbial fuel cells (MFCs), such as Marine Sediment (MFC-MS), Estuary Sediment (MFC-ES), and Anaerobic Sludge (MFC-AS), to compare the efficacy for Methylene Blue (MB) dye degradation and electricity generation. All the MFCs were operated under identical conditions in batch mode using synthetic wastewater containing 3000 mg/L COD made using sodium acetate. The electrochemical study reveals that MFC inoculated with marine sediment achieved maximum power density of 35 mW/m² followed by anaerobic sludge (31 mW/m²) and estuary sediment (25 mW/m²). Statistical analysis was employed to evaluate performance differences among the systems and to support result interpretation. Maximum COD removal efficiency of 75% was obtained by MFC-AS, and coulombic efficiency (CE) was higher for MFC-MS with 25%. Maximum decolorization efficiency was noted in MFC with anaerobic sludge, which obtained 96% decolorization over 96 h. Comparative and trend-based statistical evaluation confirmed the superior treatment performance of MFC-assisted systems. The phytotoxicity study revealed that the toxicity effect of dye wastewater was reduced to its maximum after treatment in the MFC system. The dominant performance of MFC-MS is due to the efficiency of the major electrogenic bacteria concentrated in the inoculum. The functional annotation using the data obtained from metagenomics reveals the presence and role of various enzymes and pathways involved.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>本研究成功富集並鑑定出一種耐鹽鹼的厭氧氨氧化（Anammox）細菌，命名為 *Candidatus Loosdrechtia alkalitolerans*。該菌株在長期高鹽、高鹼（0.5% NaCl，pH 9.13）環境下表現出強大的競爭優勢。透過基因體比較分析，研究發現該菌株含有特殊的 Mrp 陽離子/質子反向轉運蛋白操縱子，這是其適應鹼性環境的關鍵機制；轉錄組分析進一步證實，在鹼性壓力下，補充鈉離子可上調 Mrp 表現並恢復其代謝活性。此發現不僅揭示了厭氧氨氧化菌應對鹽鹼逆境的生理分子機制，證明了該菌在廣泛的淡水與廢水生態系統中具有潛在的生態地位，更為未來工業廢水處理中的脫氮技術應用提供了理論基礎與科學見解。</t>
+          <t>本研究旨在比較雙腔式微生物燃料電池（MFC）中，三種不同接種源（海洋沉積物、河口沉積物、厭氧污泥）在降解亞甲藍染料與產電的效率。結果顯示，海洋沉積物系統具最高的功率密度（35 mW/m²）與庫倫效率（25%）；厭氧污泥系統則有最佳的化學需氧量去除率（75%）與脫色率（96%）。處理後廢水的植物毒性顯著降低。宏基因組學分析揭示了關鍵產電菌的分布及參與降解與發電的酶和代謝途徑。本研究證實了不同接種源在 MFC 污水處理與生物發電的潛力，並闡明了其微生物學機制。</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42658844/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42663694/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>42657522</t>
+          <t>42664252</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Resistant starch alleviates intestinal fibrosis involving an acetate-mediated HDAC2-H3K27ac axis in fibroblasts.</t>
+          <t>Proteobacteria with chemosynthetic potential are highly prevalent in the gills of Hypoplectrus reef fishes.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Food &amp; function</t>
+          <t>PLoS genetics</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5.4</v>
+        <v>3.7</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>metagenomics, metabolomics</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>未提及（研究使用 DSS 誘導的小鼠模型以及人類與小鼠的原代纖維母細胞，但未具體說明樣本數）</t>
+          <t>353 個魚鰓檢體</t>
         </is>
       </c>
       <c r="G38" t="b">
@@ -2432,52 +2436,52 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Dietary fibre-based interventions are of growing interest for the prevention and treatment of digestive diseases. In this study, we investigated the effect of resistant starch (RS) on intestinal fibrosis, a stricturing condition driven by excessive extracellular matrix (ECM) accumulation. RS was found to alleviate intestinal fibrosis in a dextran sulfate sodium (DSS)-induced chronic colitis mouse model, as evidenced by restored colon length, reduced ECM deposition (fibronectin and collagen I), and decreased levels of α-smooth muscle actin. Given that RS is fermented by the gut microbiota in the colon, metagenomic sequencing revealed that RS reshaped the composition of the gut microbiota and increased the abundance of beneficial gut bacteria, including Bacteroides acidifaciens, Faecalibaculum rodentium, and Bifidobacterium pseudolongum, which are known to enhance the production of short-chain fatty acids. Targeted metabolomic analysis further showed a marked increase in acetate levels, which was associated with reduced intestinal fibrosis. However, direct in vivo evidence that acetate is required for the anti-fibrotic effect of RS remains lacking. Using human (CCD-18Co) and primary mouse intestinal fibroblasts, the major ECM-producing cells that drive fibrosis progression, we demonstrated that acetate inhibited TGF-β-induced fibroblast activation by inhibiting histone deacetylase 2, thereby enhancing the acetylation level of histone H3 at lysine 27. Collectively, these results suggest a potential microbial-metabolic-epigenetic axis linking RS and acetate to fibrosis attenuation, which awaits causal validation in vivo. This axis holds promise as a therapeutic target for fibrotic diseases.</t>
+          <t>Fishes host a diverse microbiome in their gills, but a broad characterization of this microbiome at the metagenomic level is lacking. Here, we apply genome-resolved metagenomics to the gills of the hamlets (Hypoplectrus spp), a group of reef fishes from the Greater Caribbean. The analysis of 353 gill samples from 15 hamlet species collected at eight locations over 13 years revealed a stark contrast between the gill microbiota and reef water microbial communities, indicating a distinct and specific gill microbiome. A total of 70 gill-associated metagenome-assembled genomes (MAGs) were recovered. These MAGs belong to 17 lineages, most of which are novel. They relate to known fish gill pathogens, fish gut microbes, free-living and biofilm-associated taxa, indicating that the gill microbiome was assembled from a collection of distinct eco-evolutionary trajectories. The MAGs harbor diverse metabolic modules, involved notably in nitrogen cycling, antibiotic production and biofilm formation, revealing a highly dynamic microbial ecosystem. One lineage in the Burkholderiaceae family was outstandingly prevalent across fish host species, sampling locations and years. Its genome encoded complete metabolic modules for carbon fixation and sulfur oxidation, indicating chemosynthetic potential. To the best of our knowledge, this is the first line of evidence that fishes may host sulfur-oxidizing chemosynthetic bacteria in their gills. The functional significance of this chemosynthetic potential for the fish host or other members of the gill microbiome remains to be established. The high prevalence of this lineage allowed to build a pangenome. It revealed large-scale geographic structure (western Caribbean, eastern Caribbean and Gulf of Mexico), which parallels the phylogenomic pattern observed in the hamlets. Overall, our findings point to complex fish host-microbe and microbe-microbe eco-evolutionary interactions in the gills that may influence fish physiology, homeostasis and immune response.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>本研究探討抗性澱粉（RS）對腸道纖維化的改善作用及其潛在機制。透過 DSS 誘導的小鼠結腸炎模型，研究發現 RS 可有效減輕腸道纖維化並減少細胞外基質堆積。宏基因體定序顯示 RS 能重塑腸道菌群，增加如 *Bacteroides acidifaciens* 等短鏈脂肪酸產生菌的豐度；代謝體分析進一步證實乙酸（acetate）水平顯著上升。機制研究揭示，乙酸能抑制纖維母細胞中 HDAC2 的活性，進而提升組蛋白 H3K27 的乙醯化水平，抑制 TGF-β 誘導的纖維母細胞活化。本研究提出了一條「微生物-代謝-表觀遺傳」軸線，指出 RS 可藉由促進乙酸生成來對抗腸道纖維化，為治療纖維化相關疾病提供了新的科學依據與潛在治療靶點。</t>
+          <t>本研究針對加勒比海地區 15 種「蝴蝶魚」（Hypoplectrus spp.）進行了大規模的宏基因組研究。透過分析 353 個魚鰓檢體並重建 70 個宏基因組組裝基因組（MAGs），研究發現魚鰓微生物群落與周圍海水環境顯著不同，具有獨特的演化軌跡。最重大的發現是鑑定出一種具高度普遍性的 Burkholderiaceae 細菌，該菌株擁有完整的固碳與硫氧化代謝路徑，顯示其具備化能合成潛力，這是科學界首次在魚類鰓部發現此類共生菌。此外，該菌株的基因體結構與宿主魚類的地理分布呈現高度一致性。此研究揭示了魚鰓微生物生態系統的複雜性，並為魚類生理、恆定性及免疫反應與微生物間的交互作用提供了重要的演化科學基礎。</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42657522/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42664252/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>42658871</t>
+          <t>42663459</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Breastmilk microbiota and its association with infant iron deficiency anaemia: A 16S rRNA metagenomic study in Peruvian mothers cohort.</t>
+          <t>Clinical application of BALF-mNGS in immunocompromised and immunocompetent patients with suspected invasive pulmonary aspergillosis: differentiating infection from colonization, microbiome features, and clinical impact.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PloS one</t>
+          <t>Microbiology spectrum</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>16S</t>
+          <t>metagenomics</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>46 對母嬰（46 個母乳檢體）</t>
+          <t>178位疑似侵襲性肺麴菌病（IPA）患者（包含77位免疫功能低下患者與101位免疫功能正常患者）</t>
         </is>
       </c>
       <c r="G39" t="b">
@@ -2485,47 +2489,45 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Anaemia is one of the most important public health challenges in developing countries. The global burden is estimated at 1.8 billion people, affecting approximately 30% of all children. Despite the implementation of multiple strategies over several decades, up to 42.5% of children under 3 years of age suffer anaemia in rural areas of Peru. We studied the microbiota of breastmilk (hBM) from mothers with children under the age of 1 and analysed its association with their iron deficiency anaemia. 46 mother-child pairs were recruited from Talara, a town on the northern coast of Peru and classified according to the clinical status of the children. Children with anaemia were also tested for ferritin level to classify them as iron deficiency anaemia (IDA) or non-iron deficiency anaemia (non-IDA). hBM samples were taken from the mothers after careful instruction to reduce the risk of sample contamination and the microbiome was analyzed using 16S rRNA sequencing. Streptococcus and Staphylococcus were the predominant genera, with 90% of bacterial abundance being explained by 14 genera. Alpha diversity analysis showed that hBM from mothers of children with non-IDA had higher levels of bacterial richness than hBM from healthy (p &lt; 0.01) and IDA (p &lt; 0.05) participants. Principal coordinates analysis did not yield differential clusters but showed a disparity in the spread of samples for non-IDA group when compared with the other groups. IDA group showed higher burden of Corynebacterium, Acinetobacter, Paludibacter and Nitrospira, while exhibiting a trend towards a lower burden of Streptococcus. No statistically significant differences were identified on demographic characteristics. This study suggests that hBM microbiota may differ in mothers of children with IDA and non-IDA, highlighting the necessity of further in-depth research to elucidate potential factors associated with its pathogenesis.</t>
+          <t>Invasive pulmonary aspergillosis (IPA) not only causes high morbidity and mortality, especially in immunocompromised patients, but also occurs in immunocompetent individuals. Differentiating infection from colonization is challenging, and bronchoalveolar lavage fluid metagenomic next-generation sequencing (BALF-mNGS) may aid diagnosis, microbiome profiling, and clinical assessment. We retrospectively analyzed patients with suspected IPA who underwent BALF-mNGS between December 2021 and March 2025. Patients were classified by immune status. IPA diagnosis was based on EORTC/MSGERC 2020 criteria in immunocompromised patients, while immunocompetent cases were adjudicated using an integrated clinical, radiological, and microbiological assessment. A total of 178 patients were finally included and classified according to immune status into an immunocompromised group (n = 77) and an immunocompetent group (n = 101). Aspergillus_ reads per ten million (RPTM) values were significantly higher in infection versus colonization cases in both groups, with optimal cut-offs of 24 (gray zone: 22-60) for the immunocompromised group and 33 (gray zone: 17-48) for the immunocompetent group. Microbiome analysis revealed distinct community structures between infection and colonization groups, with Aspergillus remaining significantly enriched after false discovery rate (FDR) correction in immunocompromised patients, while no taxa remained significant after FDR correction in immunocompetent patients. BALF-mNGS guided antifungal therapy, avoiding unnecessary treatment in colonized patients, and higher Aspergillus_RPTM was associated with increased 90-day mortality in immunocompromised patients. BALF-mNGS may accurately distinguish Aspergillus infection from colonization and reveal microbial shifts, particularly in immunocompromised patients. It can guide targeted antifungal therapy, avoid unnecessary treatment, and higher Aspergillus_RPTM was associated with 90-day mortality in immunocompromised patients, suggesting its potential value for risk stratification.IMPORTANCEBALF-mNGS with quantitative thresholds improves differentiation between Aspergillus infection and colonization. It reveals distinct lung microbiome patterns under different immune statuses, extending beyond simple pathogen detection. Higher Aspergillus burden is associated with worse outcomes in immunocompromised patients, suggesting its potential value for risk stratification.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>本研究探討祕魯農村地區嬰兒缺鐵性貧血（IDA）與母親母乳（hBM）菌相之間的關聯。研究對象為 46 對母嬰，透過 16S rRNA 定序分析母乳微生物群落，發現母乳菌相以鏈球菌屬（Streptococcus）與葡萄球菌屬（Staphylococcus）為優勢菌群。研究結果顯示，非貧血組嬰兒的母親，其母乳具備較高的細菌豐富度。此外，IDA 組嬰兒母親的母乳中，棒狀桿菌屬（Corynebacterium）與不動桿菌屬（Acinetobacter）等細菌豐度較高，而鏈球菌屬則呈現下降趨勢。此研究發現母乳微生物群組成可能與嬰兒貧血狀態相關，雖無法直接證實因果關係，但為後續探討嬰兒貧血的致病機制提供了重要的微生物學線索。</t>
+          <t>本研究旨在評估支氣管肺泡灌洗液總體基因體次世代定序（BALF-mNGS）在區分疑似侵襲性肺麴菌病（IPA）患者「感染」與「定植」的臨床價值，並探討其肺部微生態特徵。研究納入178位患者，發現感染者的麴菌相對豐度（RPTM）顯著高於定植者，並針對免疫功能低下與正常組分別訂定出24與33的最佳臨界值。微生態分析顯示兩組具有不同的菌群結構。臨床上，BALF-mNGS能有效引導抗真菌治療，避免定植患者過度治療；而在免疫功能低下組中，高麴菌RPTM值與90天高死亡率顯著相關。此技術不僅能精準診斷，更具備患者預後風險分層的潛力。</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42658871/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42663459/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>42660466</t>
+          <t>42666033</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Polystyrene nanoplastics exposure induces reproductive toxicity in male mice associated with the gut-liver/testis axis.</t>
+          <t>Gut Microbiota-Isoallolithocholic Acid Crosstalk Promotes Calcium Oxalate Kidney Stone Formation via PARP1-Mediated Parthanatos.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Toxicology and applied pharmacology</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>3.4</v>
-      </c>
+          <t>Advanced science (Weinheim, Baden-Wurttemberg, Germany)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>metagenomics, others</t>
+          <t>16S, metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2538,47 +2540,47 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Environmental nanoplastics are increasingly prevalent in global environments and represent an emerging systemic health risk, yet the mechanistic links between nanoplastic exposure and multi-organ dysfunction in mammals remain incompletely characterized. We integrated phenotypic assessments, gut shotgun metagenomics, and dual-organ transcriptomics to investigate the toxic effects of 28-day oral exposure to polystyrene nanoplastics (PS-NPs) in male CD-1 mice. PS-NPs induced a non-monotonic dose-dependent response, characterized by significant body weight loss at high doses, severe impairment of sperm motility, and progressive epididymal histopathological lesions. Gut metagenomics revealed significant microbiota dysbiosis, including an elevated Firmicutes/Bacteroidota ratio and marked depletion of beneficial commensal bacteria such as Ligilactobacillus murinus. Hepatic transcriptomics identified dysregulation of metabolic, detoxification, and circadian rhythm pathways, while testicular transcriptomics identified sustained transcriptional downregulation of genes annotated to steroid hormone biosynthesis and alterations in FoxO and apoptosis-related signaling. Spearman correlation network analysis identified associations between specific microbial shifts and organ-specific transcriptional alterations, providing a hypothesis-generating framework for the proposed gut-liver/testis axis. Together, these findings indicate that, under the present experimental conditions, oral PS-NPs exposure was associated with gut microbial dysbiosis, hepatic transcriptional perturbations, reduced sperm motility, and epididymal histopathological alterations, while the mechanistic relationships among these changes require further experimental validation.</t>
+          <t>Bile acids have been implicated in calcium oxalate (CaOx) nephrolithiasis. Here, we employ multi-omics approaches to identify isoallolithocholic acid (isoalloLCA) as the key bile acid elevated in the feces, serum, kidney, and urine of CaOx rats, confirmed by spatial metabolomics. 16S sequencing and metagenomic analyses indicate that elevated isoalloLCA levels in CaOx rats or individuals are likely of microbial origin. Mechanistically, isoalloLCA binds to PARP1 via specific molecular interactions validated by surface plasmon resonance and cellular thermal shift assays. Knockdown of PARP1 by adeno-associated virus microinjection or pharmacological inhibition with PARP1 inhibitor AZD5305 significantly attenuates isoalloLCA-mediated crystal deposition, renal tubular injury, and mitochondrial functional impairment in both the CaOx rat and mouse models. Furthermore, the antibiotic-mediated depletion of the gut microbiota in mice markedly reduced isoalloLCA levels, whereas fecal microbiota transplantationut contributes to isoalloLCA-mediated CaOx stone formation, demonstrating a causal link between gut microbiota and isoalloLCA. In vitro, isoalloLCA promoted oxalate-induced renal tubular epithelial cell injury and parthanatos via targeting PARP1, including DNA damage, excessive PARP1 activation, PAR accumulation, mitochondrial damage, nuclear translocation of AIF and MIF. These findings establish the microbiota-isoalloLCA-PARP1-parthanatos axis in CaOx nephrolithiasis and identify PARP1 as a promising therapeutic target for kidney stone management.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>本研究探討口服聚苯乙烯奈米塑料（PS-NPs）28天對雄性CD-1小鼠的毒性效應及其作用機制。研究發現，PS-NPs暴露會引發非單調劑量依賴性反應，導致小鼠體重顯著減輕、精子活力嚴重受損及附睾病理病變。腸道總體基因體學分析顯示，PS-NPs引起腸道菌群失調（厚壁菌門/擬桿菌門比例升高，有益菌如鼠乳桿菌顯著減少）。雙器官轉錄組學分析進一步證實，肝臟中代謝、解毒與晝夜節律途徑失調，而睾丸中類固醇激素合成基因持續下調且凋亡信號改變。本研究首次揭示了奈米塑料誘導生殖毒性與「腸-肝/睾丸軸」的關聯，為環境微塑料的哺乳動物多器官毒性機制提供了重要科學依據。</t>
+          <t>本研究旨在探討腸道菌群及其代謝物異別石膽酸（isoalloLCA）在草酸鈣（CaOx）腎結石形成中的作用與分子機制。透過整合16S定序、宏基因組學與空間代謝組學，研究發現 CaOx 大鼠及患者體內的腸道菌源 isoalloLCA 顯著升高。機制上，isoalloLCA 能直接結合並激活 PARP1 蛋白，誘導腎小管上皮細胞發生 PARP1 介導的細胞凋亡樣壞死（parthanatos），導致 DNA 與線粒體受損。於動物模型中，敲低或抑制 PARP1，或利用抗生素清除腸道菌群，皆能顯著減輕結晶沉積與腎損傷。本研究揭示了「腸道菌群-isoalloLCA-PARP1-parthanatos」軸在腎結石病理中的關鍵角色，並指出 PARP1 為臨床治療腎結石的具潛力靶點。</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/42660466/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42666033/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>42647600</t>
+          <t>42665998</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Urogenital immune signatures are associated with birth outcomes after maternal urinary tract infection.</t>
+          <t>Agathobacter rectalis suppresses colorectal tumorigenesis via an epigallocatechin-SREBF2 axis controlling cholesterol metabolism.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Science translational medicine</t>
+          <t>Gut microbes</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14.6</v>
+        <v>11</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>metagenomics, metabolomics</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2591,50 +2593,50 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Preterm birth is the leading cause of infant mortality, resulting in more than 1 million neonatal deaths globally each year. Maternal urinary tract infection (UTI) during pregnancy increases risk for preterm birth; however, biological processes mediating UTI-associated preterm birth are not well described. We established a murine maternal UTI model in which challenge with uropathogenic Escherichia coli (UPEC) initiated preterm labor and birth in about half of dams. Although bacterial burdens were similar, dams experiencing preterm birth displayed excessive bladder i